--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -40555,10 +40555,10 @@
         <v>46289.04166666666</v>
       </c>
       <c r="L731" s="1" t="n">
-        <v>46289.125</v>
+        <v>46291.33333333334</v>
       </c>
       <c r="M731" s="1" t="n">
-        <v>46292.125</v>
+        <v>46292.79166666666</v>
       </c>
     </row>
     <row r="732">
@@ -40662,13 +40662,13 @@
         </is>
       </c>
       <c r="K733" s="1" t="n">
-        <v>46293.95833333334</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="L733" s="1" t="n">
-        <v>46294</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="M733" s="1" t="n">
-        <v>46296</v>
+        <v>46297.33333333334</v>
       </c>
     </row>
     <row r="734">
@@ -40717,13 +40717,13 @@
         </is>
       </c>
       <c r="K734" s="1" t="n">
-        <v>46298</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="L734" s="1" t="n">
-        <v>46298.04166666666</v>
+        <v>46299.375</v>
       </c>
       <c r="M734" s="1" t="n">
-        <v>46299.04166666666</v>
+        <v>46300.375</v>
       </c>
     </row>
     <row r="735">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -48510,10 +48510,10 @@
         <v>46287.79166666666</v>
       </c>
       <c r="L876" s="1" t="n">
-        <v>46290.95833333334</v>
+        <v>46291.95833333334</v>
       </c>
       <c r="M876" s="1" t="n">
-        <v>46291.875</v>
+        <v>46292.875</v>
       </c>
     </row>
     <row r="877">
@@ -48562,13 +48562,13 @@
         </is>
       </c>
       <c r="K877" s="1" t="n">
-        <v>46298.875</v>
+        <v>46299.875</v>
       </c>
       <c r="L877" s="1" t="n">
-        <v>46298.95833333334</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="M877" s="1" t="n">
-        <v>46299.79166666666</v>
+        <v>46300.79166666666</v>
       </c>
     </row>
     <row r="878">
@@ -48617,13 +48617,13 @@
         </is>
       </c>
       <c r="K878" s="1" t="n">
-        <v>46300.52083333334</v>
+        <v>46301.52083333334</v>
       </c>
       <c r="L878" s="1" t="n">
-        <v>46300.60416666666</v>
+        <v>46301.60416666666</v>
       </c>
       <c r="M878" s="1" t="n">
-        <v>46301.5</v>
+        <v>46302.5</v>
       </c>
     </row>
     <row r="879">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="K879" s="1" t="n">
-        <v>46305.22916666666</v>
+        <v>46306.22916666666</v>
       </c>
       <c r="L879" s="1" t="n">
-        <v>46305.27083333334</v>
+        <v>46306.27083333334</v>
       </c>
       <c r="M879" s="1" t="n">
-        <v>46305.9375</v>
+        <v>46306.9375</v>
       </c>
     </row>
     <row r="880">
@@ -48727,13 +48727,13 @@
         </is>
       </c>
       <c r="K880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L880" s="1" t="n">
-        <v>46312.20833333334</v>
+        <v>46313.20833333334</v>
       </c>
       <c r="M880" s="1" t="n">
-        <v>46312.875</v>
+        <v>46313.875</v>
       </c>
     </row>
     <row r="881">
@@ -48782,13 +48782,13 @@
         </is>
       </c>
       <c r="K881" s="1" t="n">
-        <v>46314.27083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="L881" s="1" t="n">
-        <v>46314.3125</v>
+        <v>46315.3125</v>
       </c>
       <c r="M881" s="1" t="n">
-        <v>46315.3125</v>
+        <v>46316.3125</v>
       </c>
     </row>
     <row r="882">
@@ -48837,13 +48837,13 @@
         </is>
       </c>
       <c r="K882" s="1" t="n">
-        <v>46315.60416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="L882" s="1" t="n">
-        <v>46315.64583333334</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="M882" s="1" t="n">
-        <v>46316.27083333334</v>
+        <v>46317.27083333334</v>
       </c>
     </row>
     <row r="883">
@@ -48892,13 +48892,13 @@
         </is>
       </c>
       <c r="K883" s="1" t="n">
-        <v>46317.77083333334</v>
+        <v>46318.77083333334</v>
       </c>
       <c r="L883" s="1" t="n">
-        <v>46317.97916666666</v>
+        <v>46318.97916666666</v>
       </c>
       <c r="M883" s="1" t="n">
-        <v>46318.64583333334</v>
+        <v>46319.64583333334</v>
       </c>
     </row>
     <row r="884">
@@ -48947,13 +48947,13 @@
         </is>
       </c>
       <c r="K884" s="1" t="n">
-        <v>46325.64583333334</v>
+        <v>46326.64583333334</v>
       </c>
       <c r="L884" s="1" t="n">
-        <v>46325.72916666666</v>
+        <v>46326.72916666666</v>
       </c>
       <c r="M884" s="1" t="n">
-        <v>46326.5625</v>
+        <v>46327.5625</v>
       </c>
     </row>
     <row r="885">
@@ -49002,13 +49002,13 @@
         </is>
       </c>
       <c r="K885" s="1" t="n">
-        <v>46327.64583333334</v>
+        <v>46328.64583333334</v>
       </c>
       <c r="L885" s="1" t="n">
-        <v>46327.72916666666</v>
+        <v>46328.72916666666</v>
       </c>
       <c r="M885" s="1" t="n">
-        <v>46328.22916666666</v>
+        <v>46329.22916666666</v>
       </c>
     </row>
     <row r="886">
@@ -49057,13 +49057,13 @@
         </is>
       </c>
       <c r="K886" s="1" t="n">
-        <v>46332.22916666666</v>
+        <v>46333.22916666666</v>
       </c>
       <c r="L886" s="1" t="n">
-        <v>46332.27083333334</v>
+        <v>46333.27083333334</v>
       </c>
       <c r="M886" s="1" t="n">
-        <v>46332.9375</v>
+        <v>46333.9375</v>
       </c>
     </row>
     <row r="887">
@@ -49112,13 +49112,13 @@
         </is>
       </c>
       <c r="K887" s="1" t="n">
-        <v>46339.35416666666</v>
+        <v>46340.35416666666</v>
       </c>
       <c r="L887" s="1" t="n">
-        <v>46339.5625</v>
+        <v>46340.5625</v>
       </c>
       <c r="M887" s="1" t="n">
-        <v>46340.22916666666</v>
+        <v>46341.22916666666</v>
       </c>
     </row>
     <row r="888">
@@ -49167,13 +49167,13 @@
         </is>
       </c>
       <c r="K888" s="1" t="n">
-        <v>46341.6875</v>
+        <v>46342.6875</v>
       </c>
       <c r="L888" s="1" t="n">
-        <v>46341.72916666666</v>
+        <v>46342.72916666666</v>
       </c>
       <c r="M888" s="1" t="n">
-        <v>46342.72916666666</v>
+        <v>46343.72916666666</v>
       </c>
     </row>
     <row r="889">
@@ -49222,13 +49222,13 @@
         </is>
       </c>
       <c r="K889" s="1" t="n">
-        <v>46343.35416666666</v>
+        <v>46344.35416666666</v>
       </c>
       <c r="L889" s="1" t="n">
-        <v>46343.39583333334</v>
+        <v>46344.39583333334</v>
       </c>
       <c r="M889" s="1" t="n">
-        <v>46344.02083333334</v>
+        <v>46345.02083333334</v>
       </c>
     </row>
     <row r="890">
@@ -49277,13 +49277,13 @@
         </is>
       </c>
       <c r="K890" s="1" t="n">
-        <v>46345.52083333334</v>
+        <v>46346.52083333334</v>
       </c>
       <c r="L890" s="1" t="n">
-        <v>46345.72916666666</v>
+        <v>46346.72916666666</v>
       </c>
       <c r="M890" s="1" t="n">
-        <v>46346.39583333334</v>
+        <v>46347.39583333334</v>
       </c>
     </row>
     <row r="891">
@@ -49332,13 +49332,13 @@
         </is>
       </c>
       <c r="K891" s="1" t="n">
-        <v>46353.39583333334</v>
+        <v>46354.39583333334</v>
       </c>
       <c r="L891" s="1" t="n">
-        <v>46353.47916666666</v>
+        <v>46354.47916666666</v>
       </c>
       <c r="M891" s="1" t="n">
-        <v>46354.3125</v>
+        <v>46355.3125</v>
       </c>
     </row>
     <row r="892">
@@ -49387,13 +49387,13 @@
         </is>
       </c>
       <c r="K892" s="1" t="n">
-        <v>46355.39583333334</v>
+        <v>46356.39583333334</v>
       </c>
       <c r="L892" s="1" t="n">
-        <v>46355.47916666666</v>
+        <v>46356.47916666666</v>
       </c>
       <c r="M892" s="1" t="n">
-        <v>46355.97916666666</v>
+        <v>46356.97916666666</v>
       </c>
     </row>
     <row r="893">
@@ -49442,13 +49442,13 @@
         </is>
       </c>
       <c r="K893" s="1" t="n">
-        <v>46359.97916666666</v>
+        <v>46360.97916666666</v>
       </c>
       <c r="L893" s="1" t="n">
-        <v>46360.02083333334</v>
+        <v>46361.02083333334</v>
       </c>
       <c r="M893" s="1" t="n">
-        <v>46360.6875</v>
+        <v>46361.6875</v>
       </c>
     </row>
     <row r="894">
@@ -49493,13 +49493,13 @@
       </c>
       <c r="J894" t="inlineStr"/>
       <c r="K894" s="1" t="n">
-        <v>46367.10416666666</v>
+        <v>46368.10416666666</v>
       </c>
       <c r="L894" s="1" t="n">
-        <v>46367.3125</v>
+        <v>46368.3125</v>
       </c>
       <c r="M894" s="1" t="n">
-        <v>46367.97916666666</v>
+        <v>46368.97916666666</v>
       </c>
     </row>
     <row r="895">
@@ -60143,13 +60143,13 @@
         </is>
       </c>
       <c r="K1088" s="1" t="n">
-        <v>46303.25</v>
+        <v>46301.10416666666</v>
       </c>
       <c r="L1088" s="1" t="n">
-        <v>46303.33333333334</v>
+        <v>46301.1875</v>
       </c>
       <c r="M1088" s="1" t="n">
-        <v>46304.16666666666</v>
+        <v>46302.02083333334</v>
       </c>
     </row>
     <row r="1089">
@@ -60198,13 +60198,13 @@
         </is>
       </c>
       <c r="K1089" s="1" t="n">
-        <v>46305.16666666666</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="L1089" s="1" t="n">
-        <v>46305.20833333334</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="M1089" s="1" t="n">
-        <v>46305.70833333334</v>
+        <v>46303.60416666666</v>
       </c>
     </row>
     <row r="1090">
@@ -60253,13 +60253,13 @@
         </is>
       </c>
       <c r="K1090" s="1" t="n">
-        <v>46306.79166666666</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="L1090" s="1" t="n">
-        <v>46306.95833333334</v>
+        <v>46304.9375</v>
       </c>
       <c r="M1090" s="1" t="n">
-        <v>46307.75</v>
+        <v>46305.6875</v>
       </c>
     </row>
     <row r="1091">
@@ -60308,13 +60308,13 @@
         </is>
       </c>
       <c r="K1091" s="1" t="n">
-        <v>46313.5</v>
+        <v>46312.02083333334</v>
       </c>
       <c r="L1091" s="1" t="n">
-        <v>46313.54166666666</v>
+        <v>46312.0625</v>
       </c>
       <c r="M1091" s="1" t="n">
-        <v>46313.83333333334</v>
+        <v>46312.35416666666</v>
       </c>
     </row>
     <row r="1092">
@@ -60363,13 +60363,13 @@
         </is>
       </c>
       <c r="K1092" s="1" t="n">
-        <v>46314.125</v>
+        <v>46312.64583333334</v>
       </c>
       <c r="L1092" s="1" t="n">
-        <v>46314.125</v>
+        <v>46312.64583333334</v>
       </c>
       <c r="M1092" s="1" t="n">
-        <v>46315.5</v>
+        <v>46314.02083333334</v>
       </c>
     </row>
     <row r="1093">
@@ -60418,13 +60418,13 @@
         </is>
       </c>
       <c r="K1093" s="1" t="n">
-        <v>46315.75</v>
+        <v>46314.27083333334</v>
       </c>
       <c r="L1093" s="1" t="n">
-        <v>46315.79166666666</v>
+        <v>46314.3125</v>
       </c>
       <c r="M1093" s="1" t="n">
-        <v>46316.25</v>
+        <v>46314.77083333334</v>
       </c>
     </row>
     <row r="1094">
@@ -60473,13 +60473,13 @@
         </is>
       </c>
       <c r="K1094" s="1" t="n">
-        <v>46320.08333333334</v>
+        <v>46318.60416666666</v>
       </c>
       <c r="L1094" s="1" t="n">
-        <v>46320.08333333334</v>
+        <v>46318.60416666666</v>
       </c>
       <c r="M1094" s="1" t="n">
-        <v>46320.54166666666</v>
+        <v>46319.0625</v>
       </c>
     </row>
     <row r="1095">
@@ -60528,13 +60528,13 @@
         </is>
       </c>
       <c r="K1095" s="1" t="n">
-        <v>46321.54166666666</v>
+        <v>46320.0625</v>
       </c>
       <c r="L1095" s="1" t="n">
-        <v>46321.54166666666</v>
+        <v>46320.0625</v>
       </c>
       <c r="M1095" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46320.5625</v>
       </c>
     </row>
     <row r="1096">
@@ -60583,13 +60583,13 @@
         </is>
       </c>
       <c r="K1096" s="1" t="n">
-        <v>46325.66666666666</v>
+        <v>46323.52083333334</v>
       </c>
       <c r="L1096" s="1" t="n">
-        <v>46325.70833333334</v>
+        <v>46323.5625</v>
       </c>
       <c r="M1096" s="1" t="n">
-        <v>46326.33333333334</v>
+        <v>46324.1875</v>
       </c>
     </row>
     <row r="1097">
@@ -60638,13 +60638,13 @@
         </is>
       </c>
       <c r="K1097" s="1" t="n">
-        <v>46327.33333333334</v>
+        <v>46325.1875</v>
       </c>
       <c r="L1097" s="1" t="n">
-        <v>46327.375</v>
+        <v>46325.22916666666</v>
       </c>
       <c r="M1097" s="1" t="n">
-        <v>46327.875</v>
+        <v>46325.72916666666</v>
       </c>
     </row>
     <row r="1098">
@@ -60693,13 +60693,13 @@
         </is>
       </c>
       <c r="K1098" s="1" t="n">
-        <v>46328.95833333334</v>
+        <v>46326.8125</v>
       </c>
       <c r="L1098" s="1" t="n">
-        <v>46329.125</v>
+        <v>46326.97916666666</v>
       </c>
       <c r="M1098" s="1" t="n">
-        <v>46329.91666666666</v>
+        <v>46327.77083333334</v>
       </c>
     </row>
     <row r="1099">
@@ -60748,13 +60748,13 @@
         </is>
       </c>
       <c r="K1099" s="1" t="n">
-        <v>46335.66666666666</v>
+        <v>46333.52083333334</v>
       </c>
       <c r="L1099" s="1" t="n">
-        <v>46335.70833333334</v>
+        <v>46333.5625</v>
       </c>
       <c r="M1099" s="1" t="n">
-        <v>46336</v>
+        <v>46333.85416666666</v>
       </c>
     </row>
     <row r="1100">
@@ -60803,13 +60803,13 @@
         </is>
       </c>
       <c r="K1100" s="1" t="n">
-        <v>46336.29166666666</v>
+        <v>46334.14583333334</v>
       </c>
       <c r="L1100" s="1" t="n">
-        <v>46336.29166666666</v>
+        <v>46334.14583333334</v>
       </c>
       <c r="M1100" s="1" t="n">
-        <v>46337.66666666666</v>
+        <v>46335.52083333334</v>
       </c>
     </row>
     <row r="1101">
@@ -60858,13 +60858,13 @@
         </is>
       </c>
       <c r="K1101" s="1" t="n">
-        <v>46337.91666666666</v>
+        <v>46335.77083333334</v>
       </c>
       <c r="L1101" s="1" t="n">
-        <v>46337.95833333334</v>
+        <v>46335.8125</v>
       </c>
       <c r="M1101" s="1" t="n">
-        <v>46338.41666666666</v>
+        <v>46336.27083333334</v>
       </c>
     </row>
     <row r="1102">
@@ -60913,13 +60913,13 @@
         </is>
       </c>
       <c r="K1102" s="1" t="n">
-        <v>46342.25</v>
+        <v>46340.10416666666</v>
       </c>
       <c r="L1102" s="1" t="n">
-        <v>46342.25</v>
+        <v>46340.10416666666</v>
       </c>
       <c r="M1102" s="1" t="n">
-        <v>46342.70833333334</v>
+        <v>46340.5625</v>
       </c>
     </row>
     <row r="1103">
@@ -60968,13 +60968,13 @@
         </is>
       </c>
       <c r="K1103" s="1" t="n">
-        <v>46343.70833333334</v>
+        <v>46341.5625</v>
       </c>
       <c r="L1103" s="1" t="n">
-        <v>46343.70833333334</v>
+        <v>46341.5625</v>
       </c>
       <c r="M1103" s="1" t="n">
-        <v>46344.20833333334</v>
+        <v>46342.0625</v>
       </c>
     </row>
     <row r="1104">
@@ -61023,13 +61023,13 @@
         </is>
       </c>
       <c r="K1104" s="1" t="n">
-        <v>46346.66666666666</v>
+        <v>46344.52083333334</v>
       </c>
       <c r="L1104" s="1" t="n">
-        <v>46346.70833333334</v>
+        <v>46344.5625</v>
       </c>
       <c r="M1104" s="1" t="n">
-        <v>46347.33333333334</v>
+        <v>46345.1875</v>
       </c>
     </row>
     <row r="1105">
@@ -61078,13 +61078,13 @@
         </is>
       </c>
       <c r="K1105" s="1" t="n">
-        <v>46348.33333333334</v>
+        <v>46346.1875</v>
       </c>
       <c r="L1105" s="1" t="n">
-        <v>46348.375</v>
+        <v>46346.22916666666</v>
       </c>
       <c r="M1105" s="1" t="n">
-        <v>46348.875</v>
+        <v>46346.72916666666</v>
       </c>
     </row>
     <row r="1106">
@@ -61133,13 +61133,13 @@
         </is>
       </c>
       <c r="K1106" s="1" t="n">
-        <v>46349.95833333334</v>
+        <v>46347.8125</v>
       </c>
       <c r="L1106" s="1" t="n">
-        <v>46350.125</v>
+        <v>46347.97916666666</v>
       </c>
       <c r="M1106" s="1" t="n">
-        <v>46350.91666666666</v>
+        <v>46348.77083333334</v>
       </c>
     </row>
     <row r="1107">
@@ -61188,13 +61188,13 @@
         </is>
       </c>
       <c r="K1107" s="1" t="n">
-        <v>46356.66666666666</v>
+        <v>46354.52083333334</v>
       </c>
       <c r="L1107" s="1" t="n">
-        <v>46356.70833333334</v>
+        <v>46354.5625</v>
       </c>
       <c r="M1107" s="1" t="n">
-        <v>46357</v>
+        <v>46354.85416666666</v>
       </c>
     </row>
     <row r="1108">
@@ -61243,13 +61243,13 @@
         </is>
       </c>
       <c r="K1108" s="1" t="n">
-        <v>46357.29166666666</v>
+        <v>46355.14583333334</v>
       </c>
       <c r="L1108" s="1" t="n">
-        <v>46357.29166666666</v>
+        <v>46355.14583333334</v>
       </c>
       <c r="M1108" s="1" t="n">
-        <v>46358.66666666666</v>
+        <v>46356.52083333334</v>
       </c>
     </row>
     <row r="1109">
@@ -61298,13 +61298,13 @@
         </is>
       </c>
       <c r="K1109" s="1" t="n">
-        <v>46358.91666666666</v>
+        <v>46356.77083333334</v>
       </c>
       <c r="L1109" s="1" t="n">
-        <v>46358.95833333334</v>
+        <v>46356.8125</v>
       </c>
       <c r="M1109" s="1" t="n">
-        <v>46359.41666666666</v>
+        <v>46357.27083333334</v>
       </c>
     </row>
     <row r="1110">
@@ -61353,13 +61353,13 @@
         </is>
       </c>
       <c r="K1110" s="1" t="n">
-        <v>46363.25</v>
+        <v>46361.10416666666</v>
       </c>
       <c r="L1110" s="1" t="n">
-        <v>46363.25</v>
+        <v>46361.10416666666</v>
       </c>
       <c r="M1110" s="1" t="n">
-        <v>46363.70833333334</v>
+        <v>46361.5625</v>
       </c>
     </row>
     <row r="1111">
@@ -61404,13 +61404,13 @@
       </c>
       <c r="J1111" t="inlineStr"/>
       <c r="K1111" s="1" t="n">
-        <v>46364.70833333334</v>
+        <v>46362.5625</v>
       </c>
       <c r="L1111" s="1" t="n">
-        <v>46364.70833333334</v>
+        <v>46362.5625</v>
       </c>
       <c r="M1111" s="1" t="n">
-        <v>46365.20833333334</v>
+        <v>46363.0625</v>
       </c>
     </row>
     <row r="1112">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -27324,10 +27324,10 @@
         <v>46290.45833333334</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>46292.25</v>
+        <v>46293.5</v>
       </c>
       <c r="M490" s="1" t="n">
-        <v>46293.83333333334</v>
+        <v>46295.29166666666</v>
       </c>
     </row>
     <row r="491">
@@ -27431,13 +27431,13 @@
         </is>
       </c>
       <c r="K492" s="1" t="n">
-        <v>46294.125</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="L492" s="1" t="n">
-        <v>46294.1875</v>
+        <v>46295.64583333334</v>
       </c>
       <c r="M492" s="1" t="n">
-        <v>46294.66666666666</v>
+        <v>46296.125</v>
       </c>
     </row>
     <row r="493">
@@ -27486,13 +27486,13 @@
         </is>
       </c>
       <c r="K493" s="1" t="n">
-        <v>46296.14583333334</v>
+        <v>46297.60416666666</v>
       </c>
       <c r="L493" s="1" t="n">
-        <v>46297.22916666666</v>
+        <v>46298.6875</v>
       </c>
       <c r="M493" s="1" t="n">
-        <v>46297.72916666666</v>
+        <v>46299.1875</v>
       </c>
     </row>
     <row r="494">
@@ -27541,13 +27541,13 @@
         </is>
       </c>
       <c r="K494" s="1" t="n">
-        <v>46300.6875</v>
+        <v>46302.14583333334</v>
       </c>
       <c r="L494" s="1" t="n">
-        <v>46300.8125</v>
+        <v>46302.27083333334</v>
       </c>
       <c r="M494" s="1" t="n">
-        <v>46301.22916666666</v>
+        <v>46302.6875</v>
       </c>
     </row>
     <row r="495">
@@ -27596,13 +27596,13 @@
         </is>
       </c>
       <c r="K495" s="1" t="n">
-        <v>46313.47916666666</v>
+        <v>46314.9375</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>46314.5625</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="M495" s="1" t="n">
-        <v>46315.22916666666</v>
+        <v>46316.6875</v>
       </c>
     </row>
     <row r="496">
@@ -27651,13 +27651,13 @@
         </is>
       </c>
       <c r="K496" s="1" t="n">
-        <v>46316.47916666666</v>
+        <v>46317.9375</v>
       </c>
       <c r="L496" s="1" t="n">
-        <v>46316.5625</v>
+        <v>46318.02083333334</v>
       </c>
       <c r="M496" s="1" t="n">
-        <v>46317.0625</v>
+        <v>46318.52083333334</v>
       </c>
     </row>
     <row r="497">
@@ -27706,13 +27706,13 @@
         </is>
       </c>
       <c r="K497" s="1" t="n">
-        <v>46317.97916666666</v>
+        <v>46319.4375</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>46318.0625</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="M497" s="1" t="n">
-        <v>46318.64583333334</v>
+        <v>46320.10416666666</v>
       </c>
     </row>
     <row r="498">
@@ -27761,13 +27761,13 @@
         </is>
       </c>
       <c r="K498" s="1" t="n">
-        <v>46327.52083333334</v>
+        <v>46328.97916666666</v>
       </c>
       <c r="L498" s="1" t="n">
-        <v>46328.5625</v>
+        <v>46330.02083333334</v>
       </c>
       <c r="M498" s="1" t="n">
-        <v>46329.14583333334</v>
+        <v>46330.60416666666</v>
       </c>
     </row>
     <row r="499">
@@ -27812,13 +27812,13 @@
       </c>
       <c r="J499" t="inlineStr"/>
       <c r="K499" s="1" t="n">
-        <v>46337.9375</v>
+        <v>46339.39583333334</v>
       </c>
       <c r="L499" s="1" t="n">
-        <v>46337.97916666666</v>
+        <v>46339.4375</v>
       </c>
       <c r="M499" s="1" t="n">
-        <v>46338.72916666666</v>
+        <v>46340.1875</v>
       </c>
     </row>
     <row r="500">
@@ -46476,13 +46476,13 @@
         </is>
       </c>
       <c r="K839" s="1" t="n">
-        <v>46289.79166666666</v>
+        <v>46289.91666666666</v>
       </c>
       <c r="L839" s="1" t="n">
-        <v>46289.83333333334</v>
+        <v>46289.95416666667</v>
       </c>
       <c r="M839" s="1" t="n">
-        <v>46290.25</v>
+        <v>46290.375</v>
       </c>
     </row>
     <row r="840">
@@ -46531,13 +46531,13 @@
         </is>
       </c>
       <c r="K840" s="1" t="n">
-        <v>46291.75</v>
+        <v>46291.875</v>
       </c>
       <c r="L840" s="1" t="n">
-        <v>46291.91666666666</v>
+        <v>46292.04166666666</v>
       </c>
       <c r="M840" s="1" t="n">
-        <v>46292.41666666666</v>
+        <v>46292.54166666666</v>
       </c>
     </row>
     <row r="841">
@@ -46586,13 +46586,13 @@
         </is>
       </c>
       <c r="K841" s="1" t="n">
-        <v>46297.4375</v>
+        <v>46297.5625</v>
       </c>
       <c r="L841" s="1" t="n">
-        <v>46297.5</v>
+        <v>46297.625</v>
       </c>
       <c r="M841" s="1" t="n">
-        <v>46297.75</v>
+        <v>46297.875</v>
       </c>
     </row>
     <row r="842">
@@ -46641,13 +46641,13 @@
         </is>
       </c>
       <c r="K842" s="1" t="n">
-        <v>46298.6875</v>
+        <v>46298.8125</v>
       </c>
       <c r="L842" s="1" t="n">
-        <v>46298.75</v>
+        <v>46298.875</v>
       </c>
       <c r="M842" s="1" t="n">
-        <v>46299.16666666666</v>
+        <v>46299.29166666666</v>
       </c>
     </row>
     <row r="843">
@@ -46696,13 +46696,13 @@
         </is>
       </c>
       <c r="K843" s="1" t="n">
-        <v>46299.5</v>
+        <v>46299.625</v>
       </c>
       <c r="L843" s="1" t="n">
-        <v>46299.54166666666</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="M843" s="1" t="n">
-        <v>46300.16666666666</v>
+        <v>46300.29166666666</v>
       </c>
     </row>
     <row r="844">
@@ -46751,13 +46751,13 @@
         </is>
       </c>
       <c r="K844" s="1" t="n">
-        <v>46301.25</v>
+        <v>46301.375</v>
       </c>
       <c r="L844" s="1" t="n">
-        <v>46303.41666666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="M844" s="1" t="n">
-        <v>46304.41666666666</v>
+        <v>46304.54166666666</v>
       </c>
     </row>
     <row r="845">
@@ -46806,13 +46806,13 @@
         </is>
       </c>
       <c r="K845" s="1" t="n">
-        <v>46308.625</v>
+        <v>46308.75</v>
       </c>
       <c r="L845" s="1" t="n">
-        <v>46309.75</v>
+        <v>46309.875</v>
       </c>
       <c r="M845" s="1" t="n">
-        <v>46310.25</v>
+        <v>46310.375</v>
       </c>
     </row>
     <row r="846">
@@ -46861,13 +46861,13 @@
         </is>
       </c>
       <c r="K846" s="1" t="n">
-        <v>46311.83333333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="L846" s="1" t="n">
-        <v>46311.875</v>
+        <v>46312</v>
       </c>
       <c r="M846" s="1" t="n">
-        <v>46312.29166666666</v>
+        <v>46312.41666666666</v>
       </c>
     </row>
     <row r="847">
@@ -46916,13 +46916,13 @@
         </is>
       </c>
       <c r="K847" s="1" t="n">
-        <v>46312.45833333334</v>
+        <v>46312.58333333334</v>
       </c>
       <c r="L847" s="1" t="n">
-        <v>46312.58333333334</v>
+        <v>46312.70833333334</v>
       </c>
       <c r="M847" s="1" t="n">
-        <v>46313.58333333334</v>
+        <v>46313.70833333334</v>
       </c>
     </row>
     <row r="848">
@@ -46971,13 +46971,13 @@
         </is>
       </c>
       <c r="K848" s="1" t="n">
-        <v>46313.83333333334</v>
+        <v>46313.95833333334</v>
       </c>
       <c r="L848" s="1" t="n">
-        <v>46313.875</v>
+        <v>46314</v>
       </c>
       <c r="M848" s="1" t="n">
-        <v>46314.29166666666</v>
+        <v>46314.41666666666</v>
       </c>
     </row>
     <row r="849">
@@ -47026,13 +47026,13 @@
         </is>
       </c>
       <c r="K849" s="1" t="n">
-        <v>46315.79166666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="L849" s="1" t="n">
-        <v>46316.91666666666</v>
+        <v>46317.04166666666</v>
       </c>
       <c r="M849" s="1" t="n">
-        <v>46317.41666666666</v>
+        <v>46317.54166666666</v>
       </c>
     </row>
     <row r="850">
@@ -47081,13 +47081,13 @@
         </is>
       </c>
       <c r="K850" s="1" t="n">
-        <v>46323.39583333334</v>
+        <v>46323.52083333334</v>
       </c>
       <c r="L850" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46323.58333333334</v>
       </c>
       <c r="M850" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46323.83333333334</v>
       </c>
     </row>
     <row r="851">
@@ -47136,13 +47136,13 @@
         </is>
       </c>
       <c r="K851" s="1" t="n">
-        <v>46324.64583333334</v>
+        <v>46324.77083333334</v>
       </c>
       <c r="L851" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46324.83333333334</v>
       </c>
       <c r="M851" s="1" t="n">
-        <v>46325.125</v>
+        <v>46325.25</v>
       </c>
     </row>
     <row r="852">
@@ -47191,13 +47191,13 @@
         </is>
       </c>
       <c r="K852" s="1" t="n">
-        <v>46325.45833333334</v>
+        <v>46325.58333333334</v>
       </c>
       <c r="L852" s="1" t="n">
-        <v>46325.5</v>
+        <v>46325.625</v>
       </c>
       <c r="M852" s="1" t="n">
-        <v>46326.125</v>
+        <v>46326.25</v>
       </c>
     </row>
     <row r="853">
@@ -47246,13 +47246,13 @@
         </is>
       </c>
       <c r="K853" s="1" t="n">
-        <v>46327.20833333334</v>
+        <v>46327.33333333334</v>
       </c>
       <c r="L853" s="1" t="n">
-        <v>46327.375</v>
+        <v>46327.5</v>
       </c>
       <c r="M853" s="1" t="n">
-        <v>46328.375</v>
+        <v>46328.5</v>
       </c>
     </row>
     <row r="854">
@@ -47301,13 +47301,13 @@
         </is>
       </c>
       <c r="K854" s="1" t="n">
-        <v>46332.58333333334</v>
+        <v>46332.70833333334</v>
       </c>
       <c r="L854" s="1" t="n">
-        <v>46332.70833333334</v>
+        <v>46332.83333333334</v>
       </c>
       <c r="M854" s="1" t="n">
-        <v>46333.20833333334</v>
+        <v>46333.33333333334</v>
       </c>
     </row>
     <row r="855">
@@ -47356,13 +47356,13 @@
         </is>
       </c>
       <c r="K855" s="1" t="n">
-        <v>46334.79166666666</v>
+        <v>46334.91666666666</v>
       </c>
       <c r="L855" s="1" t="n">
-        <v>46334.83333333334</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="M855" s="1" t="n">
-        <v>46335.25</v>
+        <v>46335.375</v>
       </c>
     </row>
     <row r="856">
@@ -47411,13 +47411,13 @@
         </is>
       </c>
       <c r="K856" s="1" t="n">
-        <v>46335.41666666666</v>
+        <v>46335.54166666666</v>
       </c>
       <c r="L856" s="1" t="n">
-        <v>46335.54166666666</v>
+        <v>46335.66666666666</v>
       </c>
       <c r="M856" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46336.66666666666</v>
       </c>
     </row>
     <row r="857">
@@ -47466,13 +47466,13 @@
         </is>
       </c>
       <c r="K857" s="1" t="n">
-        <v>46336.79166666666</v>
+        <v>46336.91666666666</v>
       </c>
       <c r="L857" s="1" t="n">
-        <v>46336.83333333334</v>
+        <v>46336.95833333334</v>
       </c>
       <c r="M857" s="1" t="n">
-        <v>46337.25</v>
+        <v>46337.375</v>
       </c>
     </row>
     <row r="858">
@@ -47521,13 +47521,13 @@
         </is>
       </c>
       <c r="K858" s="1" t="n">
-        <v>46338.75</v>
+        <v>46338.875</v>
       </c>
       <c r="L858" s="1" t="n">
-        <v>46338.875</v>
+        <v>46339</v>
       </c>
       <c r="M858" s="1" t="n">
-        <v>46339.375</v>
+        <v>46339.5</v>
       </c>
     </row>
     <row r="859">
@@ -47576,13 +47576,13 @@
         </is>
       </c>
       <c r="K859" s="1" t="n">
-        <v>46344.39583333334</v>
+        <v>46344.52083333334</v>
       </c>
       <c r="L859" s="1" t="n">
-        <v>46344.45833333334</v>
+        <v>46344.58333333334</v>
       </c>
       <c r="M859" s="1" t="n">
-        <v>46344.70833333334</v>
+        <v>46344.83333333334</v>
       </c>
     </row>
     <row r="860">
@@ -47631,13 +47631,13 @@
         </is>
       </c>
       <c r="K860" s="1" t="n">
-        <v>46345.64583333334</v>
+        <v>46345.77083333334</v>
       </c>
       <c r="L860" s="1" t="n">
-        <v>46345.70833333334</v>
+        <v>46345.83333333334</v>
       </c>
       <c r="M860" s="1" t="n">
-        <v>46346.125</v>
+        <v>46346.25</v>
       </c>
     </row>
     <row r="861">
@@ -47686,13 +47686,13 @@
         </is>
       </c>
       <c r="K861" s="1" t="n">
-        <v>46346.45833333334</v>
+        <v>46346.58333333334</v>
       </c>
       <c r="L861" s="1" t="n">
-        <v>46346.5</v>
+        <v>46346.625</v>
       </c>
       <c r="M861" s="1" t="n">
-        <v>46347.125</v>
+        <v>46347.25</v>
       </c>
     </row>
     <row r="862">
@@ -47741,13 +47741,13 @@
         </is>
       </c>
       <c r="K862" s="1" t="n">
-        <v>46348.20833333334</v>
+        <v>46348.33333333334</v>
       </c>
       <c r="L862" s="1" t="n">
-        <v>46348.375</v>
+        <v>46348.5</v>
       </c>
       <c r="M862" s="1" t="n">
-        <v>46349.375</v>
+        <v>46349.5</v>
       </c>
     </row>
     <row r="863">
@@ -47796,13 +47796,13 @@
         </is>
       </c>
       <c r="K863" s="1" t="n">
-        <v>46353.58333333334</v>
+        <v>46353.70833333334</v>
       </c>
       <c r="L863" s="1" t="n">
-        <v>46353.70833333334</v>
+        <v>46353.83333333334</v>
       </c>
       <c r="M863" s="1" t="n">
-        <v>46354.20833333334</v>
+        <v>46354.33333333334</v>
       </c>
     </row>
     <row r="864">
@@ -47851,13 +47851,13 @@
         </is>
       </c>
       <c r="K864" s="1" t="n">
-        <v>46355.79166666666</v>
+        <v>46355.91666666666</v>
       </c>
       <c r="L864" s="1" t="n">
-        <v>46355.83333333334</v>
+        <v>46355.95833333334</v>
       </c>
       <c r="M864" s="1" t="n">
-        <v>46356.25</v>
+        <v>46356.375</v>
       </c>
     </row>
     <row r="865">
@@ -47906,13 +47906,13 @@
         </is>
       </c>
       <c r="K865" s="1" t="n">
-        <v>46356.41666666666</v>
+        <v>46356.54166666666</v>
       </c>
       <c r="L865" s="1" t="n">
-        <v>46356.54166666666</v>
+        <v>46356.66666666666</v>
       </c>
       <c r="M865" s="1" t="n">
-        <v>46357.54166666666</v>
+        <v>46357.66666666666</v>
       </c>
     </row>
     <row r="866">
@@ -47961,13 +47961,13 @@
         </is>
       </c>
       <c r="K866" s="1" t="n">
-        <v>46357.79166666666</v>
+        <v>46357.91666666666</v>
       </c>
       <c r="L866" s="1" t="n">
-        <v>46357.83333333334</v>
+        <v>46357.95833333334</v>
       </c>
       <c r="M866" s="1" t="n">
-        <v>46358.25</v>
+        <v>46358.375</v>
       </c>
     </row>
     <row r="867">
@@ -48012,13 +48012,13 @@
       </c>
       <c r="J867" t="inlineStr"/>
       <c r="K867" s="1" t="n">
-        <v>46359.75</v>
+        <v>46359.875</v>
       </c>
       <c r="L867" s="1" t="n">
-        <v>46359.875</v>
+        <v>46360</v>
       </c>
       <c r="M867" s="1" t="n">
-        <v>46360.375</v>
+        <v>46360.5</v>
       </c>
     </row>
     <row r="868">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -41046,10 +41046,10 @@
         <v>46288.5</v>
       </c>
       <c r="L740" s="1" t="n">
-        <v>46289.66666666666</v>
+        <v>46293.22916666666</v>
       </c>
       <c r="M740" s="1" t="n">
-        <v>46290.45833333334</v>
+        <v>46293.5</v>
       </c>
     </row>
     <row r="741">
@@ -41098,13 +41098,13 @@
         </is>
       </c>
       <c r="K741" s="1" t="n">
-        <v>46296.20833333334</v>
+        <v>46299.25</v>
       </c>
       <c r="L741" s="1" t="n">
-        <v>46296.25</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="M741" s="1" t="n">
-        <v>46296.54166666666</v>
+        <v>46299.58333333334</v>
       </c>
     </row>
     <row r="742">
@@ -41153,13 +41153,13 @@
         </is>
       </c>
       <c r="K742" s="1" t="n">
-        <v>46296.83333333334</v>
+        <v>46299.875</v>
       </c>
       <c r="L742" s="1" t="n">
-        <v>46296.83333333334</v>
+        <v>46299.875</v>
       </c>
       <c r="M742" s="1" t="n">
-        <v>46298.20833333334</v>
+        <v>46301.25</v>
       </c>
     </row>
     <row r="743">
@@ -41208,13 +41208,13 @@
         </is>
       </c>
       <c r="K743" s="1" t="n">
-        <v>46298.45833333334</v>
+        <v>46301.5</v>
       </c>
       <c r="L743" s="1" t="n">
-        <v>46298.5</v>
+        <v>46301.54166666666</v>
       </c>
       <c r="M743" s="1" t="n">
-        <v>46298.95833333334</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="744">
@@ -41263,13 +41263,13 @@
         </is>
       </c>
       <c r="K744" s="1" t="n">
-        <v>46302.79166666666</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="L744" s="1" t="n">
-        <v>46302.79166666666</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="M744" s="1" t="n">
-        <v>46303.25</v>
+        <v>46306.29166666666</v>
       </c>
     </row>
     <row r="745">
@@ -41318,13 +41318,13 @@
         </is>
       </c>
       <c r="K745" s="1" t="n">
-        <v>46304.25</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="L745" s="1" t="n">
-        <v>46304.25</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="M745" s="1" t="n">
-        <v>46304.70833333334</v>
+        <v>46307.75</v>
       </c>
     </row>
     <row r="746">
@@ -41373,13 +41373,13 @@
         </is>
       </c>
       <c r="K746" s="1" t="n">
-        <v>46307.1875</v>
+        <v>46310.22916666666</v>
       </c>
       <c r="L746" s="1" t="n">
-        <v>46307.22916666666</v>
+        <v>46310.27083333334</v>
       </c>
       <c r="M746" s="1" t="n">
-        <v>46307.85416666666</v>
+        <v>46310.89583333334</v>
       </c>
     </row>
     <row r="747">
@@ -41428,13 +41428,13 @@
         </is>
       </c>
       <c r="K747" s="1" t="n">
-        <v>46308.85416666666</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="L747" s="1" t="n">
-        <v>46308.89583333334</v>
+        <v>46311.9375</v>
       </c>
       <c r="M747" s="1" t="n">
-        <v>46309.39583333334</v>
+        <v>46312.4375</v>
       </c>
     </row>
     <row r="748">
@@ -41483,13 +41483,13 @@
         </is>
       </c>
       <c r="K748" s="1" t="n">
-        <v>46310.47916666666</v>
+        <v>46313.52083333334</v>
       </c>
       <c r="L748" s="1" t="n">
-        <v>46310.64583333334</v>
+        <v>46313.6875</v>
       </c>
       <c r="M748" s="1" t="n">
-        <v>46311.4375</v>
+        <v>46314.47916666666</v>
       </c>
     </row>
     <row r="749">
@@ -41538,13 +41538,13 @@
         </is>
       </c>
       <c r="K749" s="1" t="n">
-        <v>46317.1875</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="L749" s="1" t="n">
-        <v>46317.22916666666</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="M749" s="1" t="n">
-        <v>46317.52083333334</v>
+        <v>46320.5625</v>
       </c>
     </row>
     <row r="750">
@@ -41593,13 +41593,13 @@
         </is>
       </c>
       <c r="K750" s="1" t="n">
-        <v>46317.8125</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="L750" s="1" t="n">
-        <v>46317.8125</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="M750" s="1" t="n">
-        <v>46319.1875</v>
+        <v>46322.22916666666</v>
       </c>
     </row>
     <row r="751">
@@ -41648,13 +41648,13 @@
         </is>
       </c>
       <c r="K751" s="1" t="n">
-        <v>46319.4375</v>
+        <v>46322.47916666666</v>
       </c>
       <c r="L751" s="1" t="n">
-        <v>46319.47916666666</v>
+        <v>46322.52083333334</v>
       </c>
       <c r="M751" s="1" t="n">
-        <v>46319.9375</v>
+        <v>46322.97916666666</v>
       </c>
     </row>
     <row r="752">
@@ -41703,13 +41703,13 @@
         </is>
       </c>
       <c r="K752" s="1" t="n">
-        <v>46323.77083333334</v>
+        <v>46326.8125</v>
       </c>
       <c r="L752" s="1" t="n">
-        <v>46323.77083333334</v>
+        <v>46326.8125</v>
       </c>
       <c r="M752" s="1" t="n">
-        <v>46324.22916666666</v>
+        <v>46327.27083333334</v>
       </c>
     </row>
     <row r="753">
@@ -41758,13 +41758,13 @@
         </is>
       </c>
       <c r="K753" s="1" t="n">
-        <v>46325.22916666666</v>
+        <v>46328.27083333334</v>
       </c>
       <c r="L753" s="1" t="n">
-        <v>46325.22916666666</v>
+        <v>46328.27083333334</v>
       </c>
       <c r="M753" s="1" t="n">
-        <v>46325.72916666666</v>
+        <v>46328.77083333334</v>
       </c>
     </row>
     <row r="754">
@@ -41813,13 +41813,13 @@
         </is>
       </c>
       <c r="K754" s="1" t="n">
-        <v>46328.1875</v>
+        <v>46331.22916666666</v>
       </c>
       <c r="L754" s="1" t="n">
-        <v>46328.22916666666</v>
+        <v>46331.27083333334</v>
       </c>
       <c r="M754" s="1" t="n">
-        <v>46328.85416666666</v>
+        <v>46331.89583333334</v>
       </c>
     </row>
     <row r="755">
@@ -41868,13 +41868,13 @@
         </is>
       </c>
       <c r="K755" s="1" t="n">
-        <v>46329.85416666666</v>
+        <v>46332.89583333334</v>
       </c>
       <c r="L755" s="1" t="n">
-        <v>46329.89583333334</v>
+        <v>46332.9375</v>
       </c>
       <c r="M755" s="1" t="n">
-        <v>46330.39583333334</v>
+        <v>46333.4375</v>
       </c>
     </row>
     <row r="756">
@@ -41923,13 +41923,13 @@
         </is>
       </c>
       <c r="K756" s="1" t="n">
-        <v>46331.47916666666</v>
+        <v>46334.52083333334</v>
       </c>
       <c r="L756" s="1" t="n">
-        <v>46331.64583333334</v>
+        <v>46334.6875</v>
       </c>
       <c r="M756" s="1" t="n">
-        <v>46332.4375</v>
+        <v>46335.47916666666</v>
       </c>
     </row>
     <row r="757">
@@ -41978,13 +41978,13 @@
         </is>
       </c>
       <c r="K757" s="1" t="n">
-        <v>46338.1875</v>
+        <v>46341.22916666666</v>
       </c>
       <c r="L757" s="1" t="n">
-        <v>46338.22916666666</v>
+        <v>46341.27083333334</v>
       </c>
       <c r="M757" s="1" t="n">
-        <v>46338.52083333334</v>
+        <v>46341.5625</v>
       </c>
     </row>
     <row r="758">
@@ -42033,13 +42033,13 @@
         </is>
       </c>
       <c r="K758" s="1" t="n">
-        <v>46338.8125</v>
+        <v>46341.85416666666</v>
       </c>
       <c r="L758" s="1" t="n">
-        <v>46338.8125</v>
+        <v>46341.85416666666</v>
       </c>
       <c r="M758" s="1" t="n">
-        <v>46340.1875</v>
+        <v>46343.22916666666</v>
       </c>
     </row>
     <row r="759">
@@ -42088,13 +42088,13 @@
         </is>
       </c>
       <c r="K759" s="1" t="n">
-        <v>46340.4375</v>
+        <v>46343.47916666666</v>
       </c>
       <c r="L759" s="1" t="n">
-        <v>46340.47916666666</v>
+        <v>46343.52083333334</v>
       </c>
       <c r="M759" s="1" t="n">
-        <v>46340.9375</v>
+        <v>46343.97916666666</v>
       </c>
     </row>
     <row r="760">
@@ -42143,13 +42143,13 @@
         </is>
       </c>
       <c r="K760" s="1" t="n">
-        <v>46344.77083333334</v>
+        <v>46347.8125</v>
       </c>
       <c r="L760" s="1" t="n">
-        <v>46344.77083333334</v>
+        <v>46347.8125</v>
       </c>
       <c r="M760" s="1" t="n">
-        <v>46345.22916666666</v>
+        <v>46348.27083333334</v>
       </c>
     </row>
     <row r="761">
@@ -42198,13 +42198,13 @@
         </is>
       </c>
       <c r="K761" s="1" t="n">
-        <v>46346.22916666666</v>
+        <v>46349.27083333334</v>
       </c>
       <c r="L761" s="1" t="n">
-        <v>46346.22916666666</v>
+        <v>46349.27083333334</v>
       </c>
       <c r="M761" s="1" t="n">
-        <v>46346.72916666666</v>
+        <v>46349.77083333334</v>
       </c>
     </row>
     <row r="762">
@@ -42253,13 +42253,13 @@
         </is>
       </c>
       <c r="K762" s="1" t="n">
-        <v>46349.1875</v>
+        <v>46352.22916666666</v>
       </c>
       <c r="L762" s="1" t="n">
-        <v>46349.22916666666</v>
+        <v>46352.27083333334</v>
       </c>
       <c r="M762" s="1" t="n">
-        <v>46349.85416666666</v>
+        <v>46352.89583333334</v>
       </c>
     </row>
     <row r="763">
@@ -42308,13 +42308,13 @@
         </is>
       </c>
       <c r="K763" s="1" t="n">
-        <v>46350.85416666666</v>
+        <v>46353.89583333334</v>
       </c>
       <c r="L763" s="1" t="n">
-        <v>46350.89583333334</v>
+        <v>46353.9375</v>
       </c>
       <c r="M763" s="1" t="n">
-        <v>46351.39583333334</v>
+        <v>46354.4375</v>
       </c>
     </row>
     <row r="764">
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="K764" s="1" t="n">
-        <v>46352.47916666666</v>
+        <v>46355.52083333334</v>
       </c>
       <c r="L764" s="1" t="n">
-        <v>46352.64583333334</v>
+        <v>46355.6875</v>
       </c>
       <c r="M764" s="1" t="n">
-        <v>46353.4375</v>
+        <v>46356.47916666666</v>
       </c>
     </row>
     <row r="765">
@@ -42418,13 +42418,13 @@
         </is>
       </c>
       <c r="K765" s="1" t="n">
-        <v>46359.1875</v>
+        <v>46362.22916666666</v>
       </c>
       <c r="L765" s="1" t="n">
-        <v>46359.22916666666</v>
+        <v>46362.27083333334</v>
       </c>
       <c r="M765" s="1" t="n">
-        <v>46359.52083333334</v>
+        <v>46362.5625</v>
       </c>
     </row>
     <row r="766">
@@ -42473,13 +42473,13 @@
         </is>
       </c>
       <c r="K766" s="1" t="n">
-        <v>46359.8125</v>
+        <v>46362.85416666666</v>
       </c>
       <c r="L766" s="1" t="n">
-        <v>46359.8125</v>
+        <v>46362.85416666666</v>
       </c>
       <c r="M766" s="1" t="n">
-        <v>46361.1875</v>
+        <v>46364.22916666666</v>
       </c>
     </row>
     <row r="767">
@@ -42528,13 +42528,13 @@
         </is>
       </c>
       <c r="K767" s="1" t="n">
-        <v>46361.4375</v>
+        <v>46364.47916666666</v>
       </c>
       <c r="L767" s="1" t="n">
-        <v>46361.47916666666</v>
+        <v>46364.52083333334</v>
       </c>
       <c r="M767" s="1" t="n">
-        <v>46361.9375</v>
+        <v>46364.97916666666</v>
       </c>
     </row>
     <row r="768">
@@ -42583,13 +42583,13 @@
         </is>
       </c>
       <c r="K768" s="1" t="n">
-        <v>46365.77083333334</v>
+        <v>46368.8125</v>
       </c>
       <c r="L768" s="1" t="n">
-        <v>46365.77083333334</v>
+        <v>46368.8125</v>
       </c>
       <c r="M768" s="1" t="n">
-        <v>46366.22916666666</v>
+        <v>46369.27083333334</v>
       </c>
     </row>
     <row r="769">
@@ -42634,13 +42634,13 @@
       </c>
       <c r="J769" t="inlineStr"/>
       <c r="K769" s="1" t="n">
-        <v>46367.22916666666</v>
+        <v>46370.27083333334</v>
       </c>
       <c r="L769" s="1" t="n">
-        <v>46367.22916666666</v>
+        <v>46370.27083333334</v>
       </c>
       <c r="M769" s="1" t="n">
-        <v>46367.72916666666</v>
+        <v>46370.77083333334</v>
       </c>
     </row>
     <row r="770">
@@ -45276,7 +45276,7 @@
         <v>46289.95416666667</v>
       </c>
       <c r="M817" s="1" t="n">
-        <v>46290.375</v>
+        <v>46290.45416666667</v>
       </c>
     </row>
     <row r="818">
@@ -45325,13 +45325,13 @@
         </is>
       </c>
       <c r="K818" s="1" t="n">
-        <v>46291.875</v>
+        <v>46291.95833333334</v>
       </c>
       <c r="L818" s="1" t="n">
-        <v>46292.04166666666</v>
+        <v>46293</v>
       </c>
       <c r="M818" s="1" t="n">
-        <v>46292.54166666666</v>
+        <v>46293.5</v>
       </c>
     </row>
     <row r="819">
@@ -45380,13 +45380,13 @@
         </is>
       </c>
       <c r="K819" s="1" t="n">
-        <v>46297.5625</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="L819" s="1" t="n">
-        <v>46297.625</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="M819" s="1" t="n">
-        <v>46297.875</v>
+        <v>46298.83333333334</v>
       </c>
     </row>
     <row r="820">
@@ -45435,13 +45435,13 @@
         </is>
       </c>
       <c r="K820" s="1" t="n">
-        <v>46298.8125</v>
+        <v>46299.77083333334</v>
       </c>
       <c r="L820" s="1" t="n">
-        <v>46298.875</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="M820" s="1" t="n">
-        <v>46299.29166666666</v>
+        <v>46300.25</v>
       </c>
     </row>
     <row r="821">
@@ -45490,13 +45490,13 @@
         </is>
       </c>
       <c r="K821" s="1" t="n">
-        <v>46299.625</v>
+        <v>46300.58333333334</v>
       </c>
       <c r="L821" s="1" t="n">
-        <v>46299.66666666666</v>
+        <v>46300.625</v>
       </c>
       <c r="M821" s="1" t="n">
-        <v>46300.29166666666</v>
+        <v>46301.25</v>
       </c>
     </row>
     <row r="822">
@@ -45545,13 +45545,13 @@
         </is>
       </c>
       <c r="K822" s="1" t="n">
-        <v>46301.375</v>
+        <v>46302.33333333334</v>
       </c>
       <c r="L822" s="1" t="n">
-        <v>46303.54166666666</v>
+        <v>46304.5</v>
       </c>
       <c r="M822" s="1" t="n">
-        <v>46304.54166666666</v>
+        <v>46305.5</v>
       </c>
     </row>
     <row r="823">
@@ -45600,13 +45600,13 @@
         </is>
       </c>
       <c r="K823" s="1" t="n">
-        <v>46308.75</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="L823" s="1" t="n">
-        <v>46309.875</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="M823" s="1" t="n">
-        <v>46310.375</v>
+        <v>46311.33333333334</v>
       </c>
     </row>
     <row r="824">
@@ -45655,13 +45655,13 @@
         </is>
       </c>
       <c r="K824" s="1" t="n">
-        <v>46311.95833333334</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="L824" s="1" t="n">
-        <v>46312</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="M824" s="1" t="n">
-        <v>46312.41666666666</v>
+        <v>46313.375</v>
       </c>
     </row>
     <row r="825">
@@ -45710,13 +45710,13 @@
         </is>
       </c>
       <c r="K825" s="1" t="n">
-        <v>46312.58333333334</v>
+        <v>46313.54166666666</v>
       </c>
       <c r="L825" s="1" t="n">
-        <v>46312.70833333334</v>
+        <v>46313.66666666666</v>
       </c>
       <c r="M825" s="1" t="n">
-        <v>46313.70833333334</v>
+        <v>46314.66666666666</v>
       </c>
     </row>
     <row r="826">
@@ -45765,13 +45765,13 @@
         </is>
       </c>
       <c r="K826" s="1" t="n">
-        <v>46313.95833333334</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="L826" s="1" t="n">
-        <v>46314</v>
+        <v>46314.95833333334</v>
       </c>
       <c r="M826" s="1" t="n">
-        <v>46314.41666666666</v>
+        <v>46315.375</v>
       </c>
     </row>
     <row r="827">
@@ -45820,13 +45820,13 @@
         </is>
       </c>
       <c r="K827" s="1" t="n">
-        <v>46315.91666666666</v>
+        <v>46316.875</v>
       </c>
       <c r="L827" s="1" t="n">
-        <v>46317.04166666666</v>
+        <v>46318</v>
       </c>
       <c r="M827" s="1" t="n">
-        <v>46317.54166666666</v>
+        <v>46318.5</v>
       </c>
     </row>
     <row r="828">
@@ -45875,13 +45875,13 @@
         </is>
       </c>
       <c r="K828" s="1" t="n">
-        <v>46323.52083333334</v>
+        <v>46324.47916666666</v>
       </c>
       <c r="L828" s="1" t="n">
-        <v>46323.58333333334</v>
+        <v>46324.54166666666</v>
       </c>
       <c r="M828" s="1" t="n">
-        <v>46323.83333333334</v>
+        <v>46324.79166666666</v>
       </c>
     </row>
     <row r="829">
@@ -45930,13 +45930,13 @@
         </is>
       </c>
       <c r="K829" s="1" t="n">
-        <v>46324.77083333334</v>
+        <v>46325.72916666666</v>
       </c>
       <c r="L829" s="1" t="n">
-        <v>46324.83333333334</v>
+        <v>46325.79166666666</v>
       </c>
       <c r="M829" s="1" t="n">
-        <v>46325.25</v>
+        <v>46326.20833333334</v>
       </c>
     </row>
     <row r="830">
@@ -45985,13 +45985,13 @@
         </is>
       </c>
       <c r="K830" s="1" t="n">
-        <v>46325.58333333334</v>
+        <v>46326.54166666666</v>
       </c>
       <c r="L830" s="1" t="n">
-        <v>46325.625</v>
+        <v>46326.58333333334</v>
       </c>
       <c r="M830" s="1" t="n">
-        <v>46326.25</v>
+        <v>46327.20833333334</v>
       </c>
     </row>
     <row r="831">
@@ -46040,13 +46040,13 @@
         </is>
       </c>
       <c r="K831" s="1" t="n">
-        <v>46327.33333333334</v>
+        <v>46328.29166666666</v>
       </c>
       <c r="L831" s="1" t="n">
-        <v>46327.5</v>
+        <v>46328.45833333334</v>
       </c>
       <c r="M831" s="1" t="n">
-        <v>46328.5</v>
+        <v>46329.45833333334</v>
       </c>
     </row>
     <row r="832">
@@ -46095,13 +46095,13 @@
         </is>
       </c>
       <c r="K832" s="1" t="n">
-        <v>46332.70833333334</v>
+        <v>46333.66666666666</v>
       </c>
       <c r="L832" s="1" t="n">
-        <v>46332.83333333334</v>
+        <v>46333.79166666666</v>
       </c>
       <c r="M832" s="1" t="n">
-        <v>46333.33333333334</v>
+        <v>46334.29166666666</v>
       </c>
     </row>
     <row r="833">
@@ -46150,13 +46150,13 @@
         </is>
       </c>
       <c r="K833" s="1" t="n">
-        <v>46334.91666666666</v>
+        <v>46335.875</v>
       </c>
       <c r="L833" s="1" t="n">
-        <v>46334.95833333334</v>
+        <v>46335.91666666666</v>
       </c>
       <c r="M833" s="1" t="n">
-        <v>46335.375</v>
+        <v>46336.33333333334</v>
       </c>
     </row>
     <row r="834">
@@ -46205,13 +46205,13 @@
         </is>
       </c>
       <c r="K834" s="1" t="n">
-        <v>46335.54166666666</v>
+        <v>46336.5</v>
       </c>
       <c r="L834" s="1" t="n">
-        <v>46335.66666666666</v>
+        <v>46336.625</v>
       </c>
       <c r="M834" s="1" t="n">
-        <v>46336.66666666666</v>
+        <v>46337.625</v>
       </c>
     </row>
     <row r="835">
@@ -46260,13 +46260,13 @@
         </is>
       </c>
       <c r="K835" s="1" t="n">
-        <v>46336.91666666666</v>
+        <v>46337.875</v>
       </c>
       <c r="L835" s="1" t="n">
-        <v>46336.95833333334</v>
+        <v>46337.91666666666</v>
       </c>
       <c r="M835" s="1" t="n">
-        <v>46337.375</v>
+        <v>46338.33333333334</v>
       </c>
     </row>
     <row r="836">
@@ -46315,13 +46315,13 @@
         </is>
       </c>
       <c r="K836" s="1" t="n">
-        <v>46338.875</v>
+        <v>46339.83333333334</v>
       </c>
       <c r="L836" s="1" t="n">
-        <v>46339</v>
+        <v>46339.95833333334</v>
       </c>
       <c r="M836" s="1" t="n">
-        <v>46339.5</v>
+        <v>46340.45833333334</v>
       </c>
     </row>
     <row r="837">
@@ -46370,13 +46370,13 @@
         </is>
       </c>
       <c r="K837" s="1" t="n">
-        <v>46344.52083333334</v>
+        <v>46345.47916666666</v>
       </c>
       <c r="L837" s="1" t="n">
-        <v>46344.58333333334</v>
+        <v>46345.54166666666</v>
       </c>
       <c r="M837" s="1" t="n">
-        <v>46344.83333333334</v>
+        <v>46345.79166666666</v>
       </c>
     </row>
     <row r="838">
@@ -46425,13 +46425,13 @@
         </is>
       </c>
       <c r="K838" s="1" t="n">
-        <v>46345.77083333334</v>
+        <v>46346.72916666666</v>
       </c>
       <c r="L838" s="1" t="n">
-        <v>46345.83333333334</v>
+        <v>46346.79166666666</v>
       </c>
       <c r="M838" s="1" t="n">
-        <v>46346.25</v>
+        <v>46347.20833333334</v>
       </c>
     </row>
     <row r="839">
@@ -46480,13 +46480,13 @@
         </is>
       </c>
       <c r="K839" s="1" t="n">
-        <v>46346.58333333334</v>
+        <v>46347.54166666666</v>
       </c>
       <c r="L839" s="1" t="n">
-        <v>46346.625</v>
+        <v>46347.58333333334</v>
       </c>
       <c r="M839" s="1" t="n">
-        <v>46347.25</v>
+        <v>46348.20833333334</v>
       </c>
     </row>
     <row r="840">
@@ -46535,13 +46535,13 @@
         </is>
       </c>
       <c r="K840" s="1" t="n">
-        <v>46348.33333333334</v>
+        <v>46349.29166666666</v>
       </c>
       <c r="L840" s="1" t="n">
-        <v>46348.5</v>
+        <v>46349.45833333334</v>
       </c>
       <c r="M840" s="1" t="n">
-        <v>46349.5</v>
+        <v>46350.45833333334</v>
       </c>
     </row>
     <row r="841">
@@ -46590,13 +46590,13 @@
         </is>
       </c>
       <c r="K841" s="1" t="n">
-        <v>46353.70833333334</v>
+        <v>46354.66666666666</v>
       </c>
       <c r="L841" s="1" t="n">
-        <v>46353.83333333334</v>
+        <v>46354.79166666666</v>
       </c>
       <c r="M841" s="1" t="n">
-        <v>46354.33333333334</v>
+        <v>46355.29166666666</v>
       </c>
     </row>
     <row r="842">
@@ -46645,13 +46645,13 @@
         </is>
       </c>
       <c r="K842" s="1" t="n">
-        <v>46355.91666666666</v>
+        <v>46356.875</v>
       </c>
       <c r="L842" s="1" t="n">
-        <v>46355.95833333334</v>
+        <v>46356.91666666666</v>
       </c>
       <c r="M842" s="1" t="n">
-        <v>46356.375</v>
+        <v>46357.33333333334</v>
       </c>
     </row>
     <row r="843">
@@ -46700,13 +46700,13 @@
         </is>
       </c>
       <c r="K843" s="1" t="n">
-        <v>46356.54166666666</v>
+        <v>46357.5</v>
       </c>
       <c r="L843" s="1" t="n">
-        <v>46356.66666666666</v>
+        <v>46357.625</v>
       </c>
       <c r="M843" s="1" t="n">
-        <v>46357.66666666666</v>
+        <v>46358.625</v>
       </c>
     </row>
     <row r="844">
@@ -46755,13 +46755,13 @@
         </is>
       </c>
       <c r="K844" s="1" t="n">
-        <v>46357.91666666666</v>
+        <v>46358.875</v>
       </c>
       <c r="L844" s="1" t="n">
-        <v>46357.95833333334</v>
+        <v>46358.91666666666</v>
       </c>
       <c r="M844" s="1" t="n">
-        <v>46358.375</v>
+        <v>46359.33333333334</v>
       </c>
     </row>
     <row r="845">
@@ -46806,13 +46806,13 @@
       </c>
       <c r="J845" t="inlineStr"/>
       <c r="K845" s="1" t="n">
-        <v>46359.875</v>
+        <v>46360.83333333334</v>
       </c>
       <c r="L845" s="1" t="n">
-        <v>46360</v>
+        <v>46360.95833333334</v>
       </c>
       <c r="M845" s="1" t="n">
-        <v>46360.5</v>
+        <v>46361.45833333334</v>
       </c>
     </row>
     <row r="846">
@@ -47304,10 +47304,10 @@
         <v>46287.79166666666</v>
       </c>
       <c r="L854" s="1" t="n">
-        <v>46291.95833333334</v>
+        <v>46291.50416666667</v>
       </c>
       <c r="M854" s="1" t="n">
-        <v>46292.875</v>
+        <v>46292.33333333334</v>
       </c>
     </row>
     <row r="855">
@@ -47356,13 +47356,13 @@
         </is>
       </c>
       <c r="K855" s="1" t="n">
-        <v>46299.875</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="L855" s="1" t="n">
-        <v>46299.95833333334</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="M855" s="1" t="n">
-        <v>46300.79166666666</v>
+        <v>46300.25</v>
       </c>
     </row>
     <row r="856">
@@ -47411,13 +47411,13 @@
         </is>
       </c>
       <c r="K856" s="1" t="n">
-        <v>46301.52083333334</v>
+        <v>46300.97916666666</v>
       </c>
       <c r="L856" s="1" t="n">
-        <v>46301.60416666666</v>
+        <v>46301.0625</v>
       </c>
       <c r="M856" s="1" t="n">
-        <v>46302.5</v>
+        <v>46301.95833333334</v>
       </c>
     </row>
     <row r="857">
@@ -47466,13 +47466,13 @@
         </is>
       </c>
       <c r="K857" s="1" t="n">
-        <v>46306.22916666666</v>
+        <v>46305.6875</v>
       </c>
       <c r="L857" s="1" t="n">
-        <v>46306.27083333334</v>
+        <v>46305.72916666666</v>
       </c>
       <c r="M857" s="1" t="n">
-        <v>46306.9375</v>
+        <v>46306.39583333334</v>
       </c>
     </row>
     <row r="858">
@@ -47521,13 +47521,13 @@
         </is>
       </c>
       <c r="K858" s="1" t="n">
-        <v>46313</v>
+        <v>46312.45833333334</v>
       </c>
       <c r="L858" s="1" t="n">
-        <v>46313.20833333334</v>
+        <v>46312.66666666666</v>
       </c>
       <c r="M858" s="1" t="n">
-        <v>46313.875</v>
+        <v>46313.33333333334</v>
       </c>
     </row>
     <row r="859">
@@ -47576,13 +47576,13 @@
         </is>
       </c>
       <c r="K859" s="1" t="n">
-        <v>46315.27083333334</v>
+        <v>46314.72916666666</v>
       </c>
       <c r="L859" s="1" t="n">
-        <v>46315.3125</v>
+        <v>46314.77083333334</v>
       </c>
       <c r="M859" s="1" t="n">
-        <v>46316.3125</v>
+        <v>46315.77083333334</v>
       </c>
     </row>
     <row r="860">
@@ -47631,13 +47631,13 @@
         </is>
       </c>
       <c r="K860" s="1" t="n">
-        <v>46316.60416666666</v>
+        <v>46316.0625</v>
       </c>
       <c r="L860" s="1" t="n">
-        <v>46316.64583333334</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="M860" s="1" t="n">
-        <v>46317.27083333334</v>
+        <v>46316.72916666666</v>
       </c>
     </row>
     <row r="861">
@@ -47686,13 +47686,13 @@
         </is>
       </c>
       <c r="K861" s="1" t="n">
-        <v>46318.77083333334</v>
+        <v>46318.22916666666</v>
       </c>
       <c r="L861" s="1" t="n">
-        <v>46318.97916666666</v>
+        <v>46318.4375</v>
       </c>
       <c r="M861" s="1" t="n">
-        <v>46319.64583333334</v>
+        <v>46319.10416666666</v>
       </c>
     </row>
     <row r="862">
@@ -47741,13 +47741,13 @@
         </is>
       </c>
       <c r="K862" s="1" t="n">
-        <v>46326.64583333334</v>
+        <v>46326.10416666666</v>
       </c>
       <c r="L862" s="1" t="n">
-        <v>46326.72916666666</v>
+        <v>46326.1875</v>
       </c>
       <c r="M862" s="1" t="n">
-        <v>46327.5625</v>
+        <v>46327.02083333334</v>
       </c>
     </row>
     <row r="863">
@@ -47796,13 +47796,13 @@
         </is>
       </c>
       <c r="K863" s="1" t="n">
-        <v>46328.64583333334</v>
+        <v>46328.10416666666</v>
       </c>
       <c r="L863" s="1" t="n">
-        <v>46328.72916666666</v>
+        <v>46328.1875</v>
       </c>
       <c r="M863" s="1" t="n">
-        <v>46329.22916666666</v>
+        <v>46328.6875</v>
       </c>
     </row>
     <row r="864">
@@ -47851,13 +47851,13 @@
         </is>
       </c>
       <c r="K864" s="1" t="n">
-        <v>46333.22916666666</v>
+        <v>46332.6875</v>
       </c>
       <c r="L864" s="1" t="n">
-        <v>46333.27083333334</v>
+        <v>46332.72916666666</v>
       </c>
       <c r="M864" s="1" t="n">
-        <v>46333.9375</v>
+        <v>46333.39583333334</v>
       </c>
     </row>
     <row r="865">
@@ -47906,13 +47906,13 @@
         </is>
       </c>
       <c r="K865" s="1" t="n">
-        <v>46340.35416666666</v>
+        <v>46339.8125</v>
       </c>
       <c r="L865" s="1" t="n">
-        <v>46340.5625</v>
+        <v>46340.02083333334</v>
       </c>
       <c r="M865" s="1" t="n">
-        <v>46341.22916666666</v>
+        <v>46340.6875</v>
       </c>
     </row>
     <row r="866">
@@ -47961,13 +47961,13 @@
         </is>
       </c>
       <c r="K866" s="1" t="n">
-        <v>46342.6875</v>
+        <v>46342.14583333334</v>
       </c>
       <c r="L866" s="1" t="n">
-        <v>46342.72916666666</v>
+        <v>46342.1875</v>
       </c>
       <c r="M866" s="1" t="n">
-        <v>46343.72916666666</v>
+        <v>46343.1875</v>
       </c>
     </row>
     <row r="867">
@@ -48016,13 +48016,13 @@
         </is>
       </c>
       <c r="K867" s="1" t="n">
-        <v>46344.35416666666</v>
+        <v>46343.8125</v>
       </c>
       <c r="L867" s="1" t="n">
-        <v>46344.39583333334</v>
+        <v>46343.85416666666</v>
       </c>
       <c r="M867" s="1" t="n">
-        <v>46345.02083333334</v>
+        <v>46344.47916666666</v>
       </c>
     </row>
     <row r="868">
@@ -48071,13 +48071,13 @@
         </is>
       </c>
       <c r="K868" s="1" t="n">
-        <v>46346.52083333334</v>
+        <v>46345.97916666666</v>
       </c>
       <c r="L868" s="1" t="n">
-        <v>46346.72916666666</v>
+        <v>46346.1875</v>
       </c>
       <c r="M868" s="1" t="n">
-        <v>46347.39583333334</v>
+        <v>46346.85416666666</v>
       </c>
     </row>
     <row r="869">
@@ -48126,13 +48126,13 @@
         </is>
       </c>
       <c r="K869" s="1" t="n">
-        <v>46354.39583333334</v>
+        <v>46353.85416666666</v>
       </c>
       <c r="L869" s="1" t="n">
-        <v>46354.47916666666</v>
+        <v>46353.9375</v>
       </c>
       <c r="M869" s="1" t="n">
-        <v>46355.3125</v>
+        <v>46354.77083333334</v>
       </c>
     </row>
     <row r="870">
@@ -48181,13 +48181,13 @@
         </is>
       </c>
       <c r="K870" s="1" t="n">
-        <v>46356.39583333334</v>
+        <v>46355.85416666666</v>
       </c>
       <c r="L870" s="1" t="n">
-        <v>46356.47916666666</v>
+        <v>46355.9375</v>
       </c>
       <c r="M870" s="1" t="n">
-        <v>46356.97916666666</v>
+        <v>46356.4375</v>
       </c>
     </row>
     <row r="871">
@@ -48236,13 +48236,13 @@
         </is>
       </c>
       <c r="K871" s="1" t="n">
-        <v>46360.97916666666</v>
+        <v>46360.4375</v>
       </c>
       <c r="L871" s="1" t="n">
-        <v>46361.02083333334</v>
+        <v>46360.47916666666</v>
       </c>
       <c r="M871" s="1" t="n">
-        <v>46361.6875</v>
+        <v>46361.14583333334</v>
       </c>
     </row>
     <row r="872">
@@ -48287,13 +48287,13 @@
       </c>
       <c r="J872" t="inlineStr"/>
       <c r="K872" s="1" t="n">
-        <v>46368.10416666666</v>
+        <v>46367.5625</v>
       </c>
       <c r="L872" s="1" t="n">
-        <v>46368.3125</v>
+        <v>46367.77083333334</v>
       </c>
       <c r="M872" s="1" t="n">
-        <v>46368.97916666666</v>
+        <v>46368.4375</v>
       </c>
     </row>
     <row r="873">
@@ -49005,10 +49005,10 @@
         <v>46287.125</v>
       </c>
       <c r="L885" s="1" t="n">
-        <v>46291.29166666666</v>
+        <v>46292.41666666666</v>
       </c>
       <c r="M885" s="1" t="n">
-        <v>46292.29166666666</v>
+        <v>46293.41666666666</v>
       </c>
     </row>
     <row r="886">
@@ -49057,13 +49057,13 @@
         </is>
       </c>
       <c r="K886" s="1" t="n">
-        <v>46296.5</v>
+        <v>46297.625</v>
       </c>
       <c r="L886" s="1" t="n">
-        <v>46296.625</v>
+        <v>46297.75</v>
       </c>
       <c r="M886" s="1" t="n">
-        <v>46297.125</v>
+        <v>46298.25</v>
       </c>
     </row>
     <row r="887">
@@ -49112,13 +49112,13 @@
         </is>
       </c>
       <c r="K887" s="1" t="n">
-        <v>46298.70833333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="L887" s="1" t="n">
-        <v>46298.75</v>
+        <v>46299.875</v>
       </c>
       <c r="M887" s="1" t="n">
-        <v>46299.16666666666</v>
+        <v>46300.29166666666</v>
       </c>
     </row>
     <row r="888">
@@ -49167,13 +49167,13 @@
         </is>
       </c>
       <c r="K888" s="1" t="n">
-        <v>46299.33333333334</v>
+        <v>46300.45833333334</v>
       </c>
       <c r="L888" s="1" t="n">
-        <v>46299.45833333334</v>
+        <v>46300.58333333334</v>
       </c>
       <c r="M888" s="1" t="n">
-        <v>46300.45833333334</v>
+        <v>46301.58333333334</v>
       </c>
     </row>
     <row r="889">
@@ -49222,13 +49222,13 @@
         </is>
       </c>
       <c r="K889" s="1" t="n">
-        <v>46300.70833333334</v>
+        <v>46301.83333333334</v>
       </c>
       <c r="L889" s="1" t="n">
-        <v>46300.75</v>
+        <v>46301.875</v>
       </c>
       <c r="M889" s="1" t="n">
-        <v>46301.16666666666</v>
+        <v>46302.29166666666</v>
       </c>
     </row>
     <row r="890">
@@ -49277,13 +49277,13 @@
         </is>
       </c>
       <c r="K890" s="1" t="n">
-        <v>46302.66666666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="L890" s="1" t="n">
-        <v>46302.83333333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="M890" s="1" t="n">
-        <v>46303.33333333334</v>
+        <v>46304.45833333334</v>
       </c>
     </row>
     <row r="891">
@@ -49332,13 +49332,13 @@
         </is>
       </c>
       <c r="K891" s="1" t="n">
-        <v>46308.35416666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="L891" s="1" t="n">
-        <v>46308.41666666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="M891" s="1" t="n">
-        <v>46308.66666666666</v>
+        <v>46309.79166666666</v>
       </c>
     </row>
     <row r="892">
@@ -49387,13 +49387,13 @@
         </is>
       </c>
       <c r="K892" s="1" t="n">
-        <v>46309.60416666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="L892" s="1" t="n">
-        <v>46309.66666666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="M892" s="1" t="n">
-        <v>46310.08333333334</v>
+        <v>46311.20833333334</v>
       </c>
     </row>
     <row r="893">
@@ -49442,13 +49442,13 @@
         </is>
       </c>
       <c r="K893" s="1" t="n">
-        <v>46310.41666666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="L893" s="1" t="n">
-        <v>46310.45833333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="M893" s="1" t="n">
-        <v>46311.08333333334</v>
+        <v>46312.20833333334</v>
       </c>
     </row>
     <row r="894">
@@ -49497,13 +49497,13 @@
         </is>
       </c>
       <c r="K894" s="1" t="n">
-        <v>46312.16666666666</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="L894" s="1" t="n">
-        <v>46312.33333333334</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="M894" s="1" t="n">
-        <v>46313.33333333334</v>
+        <v>46314.45833333334</v>
       </c>
     </row>
     <row r="895">
@@ -49552,13 +49552,13 @@
         </is>
       </c>
       <c r="K895" s="1" t="n">
-        <v>46317.54166666666</v>
+        <v>46318.66666666666</v>
       </c>
       <c r="L895" s="1" t="n">
-        <v>46317.66666666666</v>
+        <v>46318.79166666666</v>
       </c>
       <c r="M895" s="1" t="n">
-        <v>46318.16666666666</v>
+        <v>46319.29166666666</v>
       </c>
     </row>
     <row r="896">
@@ -49607,13 +49607,13 @@
         </is>
       </c>
       <c r="K896" s="1" t="n">
-        <v>46319.75</v>
+        <v>46320.875</v>
       </c>
       <c r="L896" s="1" t="n">
-        <v>46319.79166666666</v>
+        <v>46320.91666666666</v>
       </c>
       <c r="M896" s="1" t="n">
-        <v>46320.20833333334</v>
+        <v>46321.33333333334</v>
       </c>
     </row>
     <row r="897">
@@ -49662,13 +49662,13 @@
         </is>
       </c>
       <c r="K897" s="1" t="n">
-        <v>46320.375</v>
+        <v>46321.5</v>
       </c>
       <c r="L897" s="1" t="n">
-        <v>46320.5</v>
+        <v>46321.625</v>
       </c>
       <c r="M897" s="1" t="n">
-        <v>46321.5</v>
+        <v>46322.625</v>
       </c>
     </row>
     <row r="898">
@@ -49717,13 +49717,13 @@
         </is>
       </c>
       <c r="K898" s="1" t="n">
-        <v>46321.75</v>
+        <v>46322.875</v>
       </c>
       <c r="L898" s="1" t="n">
-        <v>46321.79166666666</v>
+        <v>46322.91666666666</v>
       </c>
       <c r="M898" s="1" t="n">
-        <v>46322.20833333334</v>
+        <v>46323.33333333334</v>
       </c>
     </row>
     <row r="899">
@@ -49772,13 +49772,13 @@
         </is>
       </c>
       <c r="K899" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46324.83333333334</v>
       </c>
       <c r="L899" s="1" t="n">
-        <v>46323.83333333334</v>
+        <v>46324.95833333334</v>
       </c>
       <c r="M899" s="1" t="n">
-        <v>46324.33333333334</v>
+        <v>46325.45833333334</v>
       </c>
     </row>
     <row r="900">
@@ -49827,13 +49827,13 @@
         </is>
       </c>
       <c r="K900" s="1" t="n">
-        <v>46330.89583333334</v>
+        <v>46332.02083333334</v>
       </c>
       <c r="L900" s="1" t="n">
-        <v>46330.95833333334</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="M900" s="1" t="n">
-        <v>46331.20833333334</v>
+        <v>46332.33333333334</v>
       </c>
     </row>
     <row r="901">
@@ -49882,13 +49882,13 @@
         </is>
       </c>
       <c r="K901" s="1" t="n">
-        <v>46332.14583333334</v>
+        <v>46333.27083333334</v>
       </c>
       <c r="L901" s="1" t="n">
-        <v>46332.20833333334</v>
+        <v>46333.33333333334</v>
       </c>
       <c r="M901" s="1" t="n">
-        <v>46332.625</v>
+        <v>46333.75</v>
       </c>
     </row>
     <row r="902">
@@ -49937,13 +49937,13 @@
         </is>
       </c>
       <c r="K902" s="1" t="n">
-        <v>46332.95833333334</v>
+        <v>46334.08333333334</v>
       </c>
       <c r="L902" s="1" t="n">
-        <v>46333</v>
+        <v>46334.125</v>
       </c>
       <c r="M902" s="1" t="n">
-        <v>46333.625</v>
+        <v>46334.75</v>
       </c>
     </row>
     <row r="903">
@@ -49992,13 +49992,13 @@
         </is>
       </c>
       <c r="K903" s="1" t="n">
-        <v>46334.70555555556</v>
+        <v>46335.83055555556</v>
       </c>
       <c r="L903" s="1" t="n">
-        <v>46334.87222222222</v>
+        <v>46335.99722222222</v>
       </c>
       <c r="M903" s="1" t="n">
-        <v>46335.87222222222</v>
+        <v>46336.99722222222</v>
       </c>
     </row>
     <row r="904">
@@ -50047,13 +50047,13 @@
         </is>
       </c>
       <c r="K904" s="1" t="n">
-        <v>46340.08055555556</v>
+        <v>46341.20555555556</v>
       </c>
       <c r="L904" s="1" t="n">
-        <v>46340.20555555556</v>
+        <v>46341.33055555556</v>
       </c>
       <c r="M904" s="1" t="n">
-        <v>46340.70555555556</v>
+        <v>46341.83055555556</v>
       </c>
     </row>
     <row r="905">
@@ -50102,13 +50102,13 @@
         </is>
       </c>
       <c r="K905" s="1" t="n">
-        <v>46342.28888888889</v>
+        <v>46343.41388888889</v>
       </c>
       <c r="L905" s="1" t="n">
-        <v>46342.33055555556</v>
+        <v>46343.45555555556</v>
       </c>
       <c r="M905" s="1" t="n">
-        <v>46342.74722222222</v>
+        <v>46343.87222222222</v>
       </c>
     </row>
     <row r="906">
@@ -50157,13 +50157,13 @@
         </is>
       </c>
       <c r="K906" s="1" t="n">
-        <v>46342.91388888889</v>
+        <v>46344.03888888889</v>
       </c>
       <c r="L906" s="1" t="n">
-        <v>46343.03888888889</v>
+        <v>46344.16388888889</v>
       </c>
       <c r="M906" s="1" t="n">
-        <v>46344.03888888889</v>
+        <v>46345.16388888889</v>
       </c>
     </row>
     <row r="907">
@@ -50212,13 +50212,13 @@
         </is>
       </c>
       <c r="K907" s="1" t="n">
-        <v>46344.28888888889</v>
+        <v>46345.41388888889</v>
       </c>
       <c r="L907" s="1" t="n">
-        <v>46344.33055555556</v>
+        <v>46345.45555555556</v>
       </c>
       <c r="M907" s="1" t="n">
-        <v>46344.74722222222</v>
+        <v>46345.87222222222</v>
       </c>
     </row>
     <row r="908">
@@ -50267,13 +50267,13 @@
         </is>
       </c>
       <c r="K908" s="1" t="n">
-        <v>46346.24722222222</v>
+        <v>46347.37222222222</v>
       </c>
       <c r="L908" s="1" t="n">
-        <v>46346.37222222222</v>
+        <v>46347.49722222222</v>
       </c>
       <c r="M908" s="1" t="n">
-        <v>46346.87222222222</v>
+        <v>46347.99722222222</v>
       </c>
     </row>
     <row r="909">
@@ -50322,13 +50322,13 @@
         </is>
       </c>
       <c r="K909" s="1" t="n">
-        <v>46351.89305555556</v>
+        <v>46353.01805555556</v>
       </c>
       <c r="L909" s="1" t="n">
-        <v>46351.95555555556</v>
+        <v>46353.08055555556</v>
       </c>
       <c r="M909" s="1" t="n">
-        <v>46352.20555555556</v>
+        <v>46353.33055555556</v>
       </c>
     </row>
     <row r="910">
@@ -50377,13 +50377,13 @@
         </is>
       </c>
       <c r="K910" s="1" t="n">
-        <v>46353.14305555556</v>
+        <v>46354.26805555556</v>
       </c>
       <c r="L910" s="1" t="n">
-        <v>46353.20555555556</v>
+        <v>46354.33055555556</v>
       </c>
       <c r="M910" s="1" t="n">
-        <v>46353.62222222222</v>
+        <v>46354.74722222222</v>
       </c>
     </row>
     <row r="911">
@@ -50432,13 +50432,13 @@
         </is>
       </c>
       <c r="K911" s="1" t="n">
-        <v>46353.95555555556</v>
+        <v>46355.08055555556</v>
       </c>
       <c r="L911" s="1" t="n">
-        <v>46353.99722222222</v>
+        <v>46355.12222222222</v>
       </c>
       <c r="M911" s="1" t="n">
-        <v>46354.62222222222</v>
+        <v>46355.74722222222</v>
       </c>
     </row>
     <row r="912">
@@ -50487,13 +50487,13 @@
         </is>
       </c>
       <c r="K912" s="1" t="n">
-        <v>46355.70277777778</v>
+        <v>46356.82777777778</v>
       </c>
       <c r="L912" s="1" t="n">
-        <v>46355.86944444444</v>
+        <v>46356.99444444444</v>
       </c>
       <c r="M912" s="1" t="n">
-        <v>46356.86944444444</v>
+        <v>46357.99444444444</v>
       </c>
     </row>
     <row r="913">
@@ -50542,13 +50542,13 @@
         </is>
       </c>
       <c r="K913" s="1" t="n">
-        <v>46361.07777777778</v>
+        <v>46362.20277777778</v>
       </c>
       <c r="L913" s="1" t="n">
-        <v>46361.20277777778</v>
+        <v>46362.32777777778</v>
       </c>
       <c r="M913" s="1" t="n">
-        <v>46361.70277777778</v>
+        <v>46362.82777777778</v>
       </c>
     </row>
     <row r="914">
@@ -50597,13 +50597,13 @@
         </is>
       </c>
       <c r="K914" s="1" t="n">
-        <v>46363.28611111111</v>
+        <v>46364.41111111111</v>
       </c>
       <c r="L914" s="1" t="n">
-        <v>46363.32777777778</v>
+        <v>46364.45277777778</v>
       </c>
       <c r="M914" s="1" t="n">
-        <v>46363.74444444444</v>
+        <v>46364.86944444444</v>
       </c>
     </row>
     <row r="915">
@@ -50652,13 +50652,13 @@
         </is>
       </c>
       <c r="K915" s="1" t="n">
-        <v>46363.91111111111</v>
+        <v>46365.03611111111</v>
       </c>
       <c r="L915" s="1" t="n">
-        <v>46364.03611111111</v>
+        <v>46365.16111111111</v>
       </c>
       <c r="M915" s="1" t="n">
-        <v>46365.03611111111</v>
+        <v>46366.16111111111</v>
       </c>
     </row>
     <row r="916">
@@ -50707,13 +50707,13 @@
         </is>
       </c>
       <c r="K916" s="1" t="n">
-        <v>46365.28611111111</v>
+        <v>46366.41111111111</v>
       </c>
       <c r="L916" s="1" t="n">
-        <v>46365.32777777778</v>
+        <v>46366.45277777778</v>
       </c>
       <c r="M916" s="1" t="n">
-        <v>46365.74444444444</v>
+        <v>46366.86944444444</v>
       </c>
     </row>
     <row r="917">
@@ -50758,13 +50758,13 @@
       </c>
       <c r="J917" t="inlineStr"/>
       <c r="K917" s="1" t="n">
-        <v>46367.24444444444</v>
+        <v>46368.36944444444</v>
       </c>
       <c r="L917" s="1" t="n">
-        <v>46367.36944444444</v>
+        <v>46368.49444444444</v>
       </c>
       <c r="M917" s="1" t="n">
-        <v>46367.86944444444</v>
+        <v>46368.99444444444</v>
       </c>
     </row>
     <row r="918">
@@ -60589,7 +60589,7 @@
         <v>46289.95833333334</v>
       </c>
       <c r="M1096" s="1" t="n">
-        <v>46290.85416666666</v>
+        <v>46290.8375</v>
       </c>
     </row>
     <row r="1097">
@@ -60638,13 +60638,13 @@
         </is>
       </c>
       <c r="K1097" s="1" t="n">
-        <v>46292.04166666666</v>
+        <v>46292</v>
       </c>
       <c r="L1097" s="1" t="n">
-        <v>46292.10416666666</v>
+        <v>46292.0625</v>
       </c>
       <c r="M1097" s="1" t="n">
-        <v>46292.5</v>
+        <v>46292.375</v>
       </c>
     </row>
     <row r="1098">
@@ -60693,13 +60693,13 @@
         </is>
       </c>
       <c r="K1098" s="1" t="n">
-        <v>46292.79166666666</v>
+        <v>46292.66666666666</v>
       </c>
       <c r="L1098" s="1" t="n">
-        <v>46292.83333333334</v>
+        <v>46292.875</v>
       </c>
       <c r="M1098" s="1" t="n">
-        <v>46293.70833333334</v>
+        <v>46294.16666666666</v>
       </c>
     </row>
     <row r="1099">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -27324,10 +27324,10 @@
         <v>46290.45833333334</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>46293.58333333334</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="M490" s="1" t="n">
-        <v>46295.375</v>
+        <v>46296.08333333334</v>
       </c>
     </row>
     <row r="491">
@@ -27431,13 +27431,13 @@
         </is>
       </c>
       <c r="K492" s="1" t="n">
-        <v>46295.66666666666</v>
+        <v>46296.375</v>
       </c>
       <c r="L492" s="1" t="n">
-        <v>46295.72916666666</v>
+        <v>46296.4375</v>
       </c>
       <c r="M492" s="1" t="n">
-        <v>46296.20833333334</v>
+        <v>46296.91666666666</v>
       </c>
     </row>
     <row r="493">
@@ -27486,13 +27486,13 @@
         </is>
       </c>
       <c r="K493" s="1" t="n">
-        <v>46297.6875</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="L493" s="1" t="n">
-        <v>46298.77083333334</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="M493" s="1" t="n">
-        <v>46299.27083333334</v>
+        <v>46299.97916666666</v>
       </c>
     </row>
     <row r="494">
@@ -27541,13 +27541,13 @@
         </is>
       </c>
       <c r="K494" s="1" t="n">
-        <v>46302.22916666666</v>
+        <v>46302.9375</v>
       </c>
       <c r="L494" s="1" t="n">
-        <v>46302.35416666666</v>
+        <v>46303.0625</v>
       </c>
       <c r="M494" s="1" t="n">
-        <v>46302.77083333334</v>
+        <v>46303.47916666666</v>
       </c>
     </row>
     <row r="495">
@@ -27596,13 +27596,13 @@
         </is>
       </c>
       <c r="K495" s="1" t="n">
-        <v>46315.02083333334</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>46316.10416666666</v>
+        <v>46316.8125</v>
       </c>
       <c r="M495" s="1" t="n">
-        <v>46316.77083333334</v>
+        <v>46317.47916666666</v>
       </c>
     </row>
     <row r="496">
@@ -27651,13 +27651,13 @@
         </is>
       </c>
       <c r="K496" s="1" t="n">
-        <v>46318.02083333334</v>
+        <v>46318.72916666666</v>
       </c>
       <c r="L496" s="1" t="n">
-        <v>46318.10416666666</v>
+        <v>46318.8125</v>
       </c>
       <c r="M496" s="1" t="n">
-        <v>46318.60416666666</v>
+        <v>46319.3125</v>
       </c>
     </row>
     <row r="497">
@@ -27706,13 +27706,13 @@
         </is>
       </c>
       <c r="K497" s="1" t="n">
-        <v>46319.52083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>46319.60416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="M497" s="1" t="n">
-        <v>46320.1875</v>
+        <v>46320.89583333334</v>
       </c>
     </row>
     <row r="498">
@@ -27761,13 +27761,13 @@
         </is>
       </c>
       <c r="K498" s="1" t="n">
-        <v>46329.0625</v>
+        <v>46329.77083333334</v>
       </c>
       <c r="L498" s="1" t="n">
-        <v>46330.10416666666</v>
+        <v>46330.8125</v>
       </c>
       <c r="M498" s="1" t="n">
-        <v>46330.6875</v>
+        <v>46331.39583333334</v>
       </c>
     </row>
     <row r="499">
@@ -27812,13 +27812,13 @@
       </c>
       <c r="J499" t="inlineStr"/>
       <c r="K499" s="1" t="n">
-        <v>46339.47916666666</v>
+        <v>46340.1875</v>
       </c>
       <c r="L499" s="1" t="n">
-        <v>46339.52083333334</v>
+        <v>46340.22916666666</v>
       </c>
       <c r="M499" s="1" t="n">
-        <v>46340.27083333334</v>
+        <v>46340.97916666666</v>
       </c>
     </row>
     <row r="500">
@@ -35887,7 +35887,7 @@
         <v>46292.14583333334</v>
       </c>
       <c r="M646" s="1" t="n">
-        <v>46292.625</v>
+        <v>46292.5</v>
       </c>
     </row>
     <row r="647">
@@ -35936,13 +35936,13 @@
         </is>
       </c>
       <c r="K647" s="1" t="n">
-        <v>46295.60416666666</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="L647" s="1" t="n">
-        <v>46295.64583333334</v>
+        <v>46295.52083333334</v>
       </c>
       <c r="M647" s="1" t="n">
-        <v>46296.02083333334</v>
+        <v>46295.89583333334</v>
       </c>
     </row>
     <row r="648">
@@ -35991,13 +35991,13 @@
         </is>
       </c>
       <c r="K648" s="1" t="n">
-        <v>46297.97916666666</v>
+        <v>46297.85416666666</v>
       </c>
       <c r="L648" s="1" t="n">
-        <v>46298.14583333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="M648" s="1" t="n">
-        <v>46298.6875</v>
+        <v>46298.5625</v>
       </c>
     </row>
     <row r="649">
@@ -36046,13 +36046,13 @@
         </is>
       </c>
       <c r="K649" s="1" t="n">
-        <v>46300.47916666666</v>
+        <v>46300.35416666666</v>
       </c>
       <c r="L649" s="1" t="n">
-        <v>46300.52083333334</v>
+        <v>46300.39583333334</v>
       </c>
       <c r="M649" s="1" t="n">
-        <v>46300.77083333334</v>
+        <v>46300.64583333334</v>
       </c>
     </row>
     <row r="650">
@@ -36101,13 +36101,13 @@
         </is>
       </c>
       <c r="K650" s="1" t="n">
+        <v>46301.0625</v>
+      </c>
+      <c r="L650" s="1" t="n">
         <v>46301.1875</v>
       </c>
-      <c r="L650" s="1" t="n">
-        <v>46301.3125</v>
-      </c>
       <c r="M650" s="1" t="n">
-        <v>46302.4375</v>
+        <v>46302.3125</v>
       </c>
     </row>
     <row r="651">
@@ -36156,13 +36156,13 @@
         </is>
       </c>
       <c r="K651" s="1" t="n">
-        <v>46302.77083333334</v>
+        <v>46302.64583333334</v>
       </c>
       <c r="L651" s="1" t="n">
-        <v>46302.8125</v>
+        <v>46302.6875</v>
       </c>
       <c r="M651" s="1" t="n">
-        <v>46303.14583333334</v>
+        <v>46303.02083333334</v>
       </c>
     </row>
     <row r="652">
@@ -36211,13 +36211,13 @@
         </is>
       </c>
       <c r="K652" s="1" t="n">
-        <v>46307.02083333334</v>
+        <v>46306.89583333334</v>
       </c>
       <c r="L652" s="1" t="n">
-        <v>46307.0625</v>
+        <v>46306.9375</v>
       </c>
       <c r="M652" s="1" t="n">
-        <v>46307.47916666666</v>
+        <v>46307.35416666666</v>
       </c>
     </row>
     <row r="653">
@@ -36266,13 +36266,13 @@
         </is>
       </c>
       <c r="K653" s="1" t="n">
-        <v>46307.72916666666</v>
+        <v>46307.60416666666</v>
       </c>
       <c r="L653" s="1" t="n">
-        <v>46307.72916666666</v>
+        <v>46307.60416666666</v>
       </c>
       <c r="M653" s="1" t="n">
-        <v>46308.10416666666</v>
+        <v>46307.97916666666</v>
       </c>
     </row>
     <row r="654">
@@ -36376,13 +36376,13 @@
         </is>
       </c>
       <c r="K655" s="1" t="n">
-        <v>46309.63958333333</v>
+        <v>46309.51458333333</v>
       </c>
       <c r="L655" s="1" t="n">
-        <v>46309.63958333333</v>
+        <v>46309.51458333333</v>
       </c>
       <c r="M655" s="1" t="n">
-        <v>46309.88958333333</v>
+        <v>46309.76458333333</v>
       </c>
     </row>
     <row r="656">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -8440,16 +8440,16 @@
         <v>46288.375</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>46291.75</v>
+        <v>46293.20833333334</v>
       </c>
       <c r="M146" s="1" t="n">
-        <v>46292.45833333334</v>
+        <v>46293.875</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ADHS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8464,16 +8464,16 @@
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2608E</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -8495,16 +8495,16 @@
         <v>46293.875</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>46293.91666666666</v>
+        <v>46294.75</v>
       </c>
       <c r="M147" s="1" t="n">
-        <v>46294.625</v>
+        <v>46295.45833333334</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ADHS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -8519,16 +8519,16 @@
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2608E</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -8547,13 +8547,13 @@
         </is>
       </c>
       <c r="K148" s="1" t="n">
-        <v>46293.875</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>46294.75</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46296.04166666666</v>
       </c>
     </row>
     <row r="149">
@@ -10034,7 +10034,7 @@
         <v>46289.875</v>
       </c>
       <c r="M175" s="1" t="n">
-        <v>46292.52083333334</v>
+        <v>46292.27916666667</v>
       </c>
     </row>
     <row r="176">
@@ -10083,13 +10083,13 @@
         </is>
       </c>
       <c r="K176" s="1" t="n">
-        <v>46295</v>
+        <v>46294.75</v>
       </c>
       <c r="L176" s="1" t="n">
-        <v>46295.16666666666</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="M176" s="1" t="n">
-        <v>46296</v>
+        <v>46295.75</v>
       </c>
     </row>
     <row r="177">
@@ -10138,13 +10138,13 @@
         </is>
       </c>
       <c r="K177" s="1" t="n">
-        <v>46298.54166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="L177" s="1" t="n">
-        <v>46298.60416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="M177" s="1" t="n">
-        <v>46299.10416666666</v>
+        <v>46298.85416666666</v>
       </c>
     </row>
     <row r="178">
@@ -10193,13 +10193,13 @@
         </is>
       </c>
       <c r="K178" s="1" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="L178" s="1" t="n">
-        <v>46299.375</v>
+        <v>46299.125</v>
       </c>
       <c r="M178" s="1" t="n">
-        <v>46299.875</v>
+        <v>46299.625</v>
       </c>
     </row>
     <row r="179">
@@ -10248,13 +10248,13 @@
         </is>
       </c>
       <c r="K179" s="1" t="n">
-        <v>46303.16666666666</v>
+        <v>46302.91666666666</v>
       </c>
       <c r="L179" s="1" t="n">
-        <v>46303.20833333334</v>
+        <v>46302.95833333334</v>
       </c>
       <c r="M179" s="1" t="n">
-        <v>46303.875</v>
+        <v>46303.625</v>
       </c>
     </row>
     <row r="180">
@@ -10303,13 +10303,13 @@
         </is>
       </c>
       <c r="K180" s="1" t="n">
-        <v>46304.95833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="L180" s="1" t="n">
-        <v>46305</v>
+        <v>46304.75</v>
       </c>
       <c r="M180" s="1" t="n">
-        <v>46305.58333333334</v>
+        <v>46305.33333333334</v>
       </c>
     </row>
     <row r="181">
@@ -33911,7 +33911,7 @@
         <v>46292.25</v>
       </c>
       <c r="M610" s="1" t="n">
-        <v>46292.66666666666</v>
+        <v>46292.58333333334</v>
       </c>
     </row>
     <row r="611">
@@ -33960,13 +33960,13 @@
         </is>
       </c>
       <c r="K611" s="1" t="n">
-        <v>46292.79166666666</v>
+        <v>46292.66666666666</v>
       </c>
       <c r="L611" s="1" t="n">
-        <v>46292.91666666666</v>
+        <v>46292.75</v>
       </c>
       <c r="M611" s="1" t="n">
-        <v>46294</v>
+        <v>46293.625</v>
       </c>
     </row>
     <row r="612">
@@ -34015,13 +34015,13 @@
         </is>
       </c>
       <c r="K612" s="1" t="n">
-        <v>46294.16666666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="L612" s="1" t="n">
-        <v>46294.20833333334</v>
+        <v>46293.83333333334</v>
       </c>
       <c r="M612" s="1" t="n">
-        <v>46294.875</v>
+        <v>46294.5</v>
       </c>
     </row>
     <row r="613">
@@ -34070,13 +34070,13 @@
         </is>
       </c>
       <c r="K613" s="1" t="n">
-        <v>46296.33333333334</v>
+        <v>46295.95833333334</v>
       </c>
       <c r="L613" s="1" t="n">
-        <v>46296.5</v>
+        <v>46296.125</v>
       </c>
       <c r="M613" s="1" t="n">
-        <v>46297.375</v>
+        <v>46297.33333333334</v>
       </c>
     </row>
     <row r="614">
@@ -34125,13 +34125,13 @@
         </is>
       </c>
       <c r="K614" s="1" t="n">
-        <v>46302.66666666666</v>
+        <v>46302.83333333334</v>
       </c>
       <c r="L614" s="1" t="n">
-        <v>46302.70833333334</v>
+        <v>46302.875</v>
       </c>
       <c r="M614" s="1" t="n">
-        <v>46303.29166666666</v>
+        <v>46303.875</v>
       </c>
     </row>
     <row r="615">
@@ -34180,13 +34180,13 @@
         </is>
       </c>
       <c r="K615" s="1" t="n">
+        <v>46304.875</v>
+      </c>
+      <c r="L615" s="1" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="L615" s="1" t="n">
-        <v>46304.95833333334</v>
-      </c>
       <c r="M615" s="1" t="n">
-        <v>46305.5</v>
+        <v>46305.91666666666</v>
       </c>
     </row>
     <row r="616">
@@ -35832,7 +35832,7 @@
         <v>46289.29166666666</v>
       </c>
       <c r="M645" s="1" t="n">
-        <v>46292</v>
+        <v>46292.08333333334</v>
       </c>
     </row>
     <row r="646">
@@ -35881,13 +35881,13 @@
         </is>
       </c>
       <c r="K646" s="1" t="n">
-        <v>46292.10416666666</v>
+        <v>46292.16666666666</v>
       </c>
       <c r="L646" s="1" t="n">
-        <v>46292.14583333334</v>
+        <v>46292.22916666666</v>
       </c>
       <c r="M646" s="1" t="n">
-        <v>46292.5</v>
+        <v>46292.62916666667</v>
       </c>
     </row>
     <row r="647">
@@ -35936,13 +35936,13 @@
         </is>
       </c>
       <c r="K647" s="1" t="n">
-        <v>46295.47916666666</v>
+        <v>46295.875</v>
       </c>
       <c r="L647" s="1" t="n">
-        <v>46295.52083333334</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="M647" s="1" t="n">
-        <v>46295.89583333334</v>
+        <v>46296.29166666666</v>
       </c>
     </row>
     <row r="648">
@@ -35991,13 +35991,13 @@
         </is>
       </c>
       <c r="K648" s="1" t="n">
-        <v>46297.85416666666</v>
+        <v>46298.25</v>
       </c>
       <c r="L648" s="1" t="n">
-        <v>46298.02083333334</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="M648" s="1" t="n">
-        <v>46298.5625</v>
+        <v>46298.95833333334</v>
       </c>
     </row>
     <row r="649">
@@ -36046,13 +36046,13 @@
         </is>
       </c>
       <c r="K649" s="1" t="n">
-        <v>46300.35416666666</v>
+        <v>46300.75</v>
       </c>
       <c r="L649" s="1" t="n">
-        <v>46300.39583333334</v>
+        <v>46300.79166666666</v>
       </c>
       <c r="M649" s="1" t="n">
-        <v>46300.64583333334</v>
+        <v>46301.04166666666</v>
       </c>
     </row>
     <row r="650">
@@ -36101,13 +36101,13 @@
         </is>
       </c>
       <c r="K650" s="1" t="n">
-        <v>46301.0625</v>
+        <v>46301.45833333334</v>
       </c>
       <c r="L650" s="1" t="n">
-        <v>46301.1875</v>
+        <v>46301.58333333334</v>
       </c>
       <c r="M650" s="1" t="n">
-        <v>46302.3125</v>
+        <v>46302.70833333334</v>
       </c>
     </row>
     <row r="651">
@@ -36156,13 +36156,13 @@
         </is>
       </c>
       <c r="K651" s="1" t="n">
-        <v>46302.64583333334</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="L651" s="1" t="n">
-        <v>46302.6875</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="M651" s="1" t="n">
-        <v>46303.02083333334</v>
+        <v>46303.41666666666</v>
       </c>
     </row>
     <row r="652">
@@ -36211,13 +36211,13 @@
         </is>
       </c>
       <c r="K652" s="1" t="n">
-        <v>46306.89583333334</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="L652" s="1" t="n">
-        <v>46306.9375</v>
+        <v>46307.33333333334</v>
       </c>
       <c r="M652" s="1" t="n">
-        <v>46307.35416666666</v>
+        <v>46307.75</v>
       </c>
     </row>
     <row r="653">
@@ -36262,17 +36262,17 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="K653" s="1" t="n">
-        <v>46307.60416666666</v>
+        <v>46308</v>
       </c>
       <c r="L653" s="1" t="n">
-        <v>46307.60416666666</v>
+        <v>46308</v>
       </c>
       <c r="M653" s="1" t="n">
-        <v>46307.97916666666</v>
+        <v>46308.375</v>
       </c>
     </row>
     <row r="654">
@@ -36293,41 +36293,41 @@
       </c>
       <c r="D654" t="inlineStr"/>
       <c r="E654" t="n">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>KEL02</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
         <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="J654" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
       <c r="K654" s="1" t="n">
-        <v>46309.28541666667</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="L654" s="1" t="n">
-        <v>46309.32708333333</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="M654" s="1" t="n">
-        <v>46310.03541666667</v>
+        <v>46309.95833333334</v>
       </c>
     </row>
     <row r="655">
@@ -36348,26 +36348,26 @@
       </c>
       <c r="D655" t="inlineStr"/>
       <c r="E655" t="n">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>KEL02</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
@@ -36376,13 +36376,13 @@
         </is>
       </c>
       <c r="K655" s="1" t="n">
-        <v>46309.51458333333</v>
+        <v>46312</v>
       </c>
       <c r="L655" s="1" t="n">
-        <v>46309.51458333333</v>
+        <v>46312.04166666666</v>
       </c>
       <c r="M655" s="1" t="n">
-        <v>46309.76458333333</v>
+        <v>46312.75</v>
       </c>
     </row>
     <row r="656">
@@ -36431,13 +36431,13 @@
         </is>
       </c>
       <c r="K656" s="1" t="n">
-        <v>46310.24305555555</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="L656" s="1" t="n">
-        <v>46310.28472222222</v>
+        <v>46313</v>
       </c>
       <c r="M656" s="1" t="n">
-        <v>46310.61805555555</v>
+        <v>46313.33333333334</v>
       </c>
     </row>
     <row r="657">
@@ -36486,13 +36486,13 @@
         </is>
       </c>
       <c r="K657" s="1" t="n">
-        <v>46314.05833333333</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="L657" s="1" t="n">
-        <v>46314.1</v>
+        <v>46316.625</v>
       </c>
       <c r="M657" s="1" t="n">
-        <v>46314.475</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="658">
@@ -36541,13 +36541,13 @@
         </is>
       </c>
       <c r="K658" s="1" t="n">
-        <v>46316.93333333333</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="L658" s="1" t="n">
-        <v>46317.1</v>
+        <v>46319.625</v>
       </c>
       <c r="M658" s="1" t="n">
-        <v>46317.64166666667</v>
+        <v>46320.16666666666</v>
       </c>
     </row>
     <row r="659">
@@ -36596,13 +36596,13 @@
         </is>
       </c>
       <c r="K659" s="1" t="n">
-        <v>46319.43333333333</v>
+        <v>46321.95833333334</v>
       </c>
       <c r="L659" s="1" t="n">
-        <v>46319.475</v>
+        <v>46322</v>
       </c>
       <c r="M659" s="1" t="n">
-        <v>46319.725</v>
+        <v>46322.25</v>
       </c>
     </row>
     <row r="660">
@@ -36651,13 +36651,13 @@
         </is>
       </c>
       <c r="K660" s="1" t="n">
-        <v>46320.14166666667</v>
+        <v>46322.66666666666</v>
       </c>
       <c r="L660" s="1" t="n">
-        <v>46320.26666666667</v>
+        <v>46322.79166666666</v>
       </c>
       <c r="M660" s="1" t="n">
-        <v>46321.39166666667</v>
+        <v>46323.91666666666</v>
       </c>
     </row>
     <row r="661">
@@ -36706,13 +36706,13 @@
         </is>
       </c>
       <c r="K661" s="1" t="n">
-        <v>46321.725</v>
+        <v>46324.25</v>
       </c>
       <c r="L661" s="1" t="n">
-        <v>46321.76666666667</v>
+        <v>46324.29166666666</v>
       </c>
       <c r="M661" s="1" t="n">
-        <v>46322.1</v>
+        <v>46324.625</v>
       </c>
     </row>
     <row r="662">
@@ -36761,13 +36761,13 @@
         </is>
       </c>
       <c r="K662" s="1" t="n">
-        <v>46325.975</v>
+        <v>46328.5</v>
       </c>
       <c r="L662" s="1" t="n">
-        <v>46326.01666666667</v>
+        <v>46328.54166666666</v>
       </c>
       <c r="M662" s="1" t="n">
-        <v>46326.43333333333</v>
+        <v>46328.95833333334</v>
       </c>
     </row>
     <row r="663">
@@ -36816,13 +36816,13 @@
         </is>
       </c>
       <c r="K663" s="1" t="n">
-        <v>46326.68333333333</v>
+        <v>46329.20833333334</v>
       </c>
       <c r="L663" s="1" t="n">
-        <v>46326.68333333333</v>
+        <v>46329.20833333334</v>
       </c>
       <c r="M663" s="1" t="n">
-        <v>46327.05833333333</v>
+        <v>46329.58333333334</v>
       </c>
     </row>
     <row r="664">
@@ -36871,13 +36871,13 @@
         </is>
       </c>
       <c r="K664" s="1" t="n">
-        <v>46328.30833333333</v>
+        <v>46330.83333333334</v>
       </c>
       <c r="L664" s="1" t="n">
-        <v>46328.30833333333</v>
+        <v>46330.83333333334</v>
       </c>
       <c r="M664" s="1" t="n">
-        <v>46328.55833333333</v>
+        <v>46331.08333333334</v>
       </c>
     </row>
     <row r="665">
@@ -36926,13 +36926,13 @@
         </is>
       </c>
       <c r="K665" s="1" t="n">
-        <v>46330.89166666667</v>
+        <v>46333.62430555555</v>
       </c>
       <c r="L665" s="1" t="n">
-        <v>46330.93333333333</v>
+        <v>46333.66597222222</v>
       </c>
       <c r="M665" s="1" t="n">
-        <v>46331.64166666667</v>
+        <v>46334.37430555555</v>
       </c>
     </row>
     <row r="666">
@@ -36981,13 +36981,13 @@
         </is>
       </c>
       <c r="K666" s="1" t="n">
-        <v>46331.85</v>
+        <v>46334.58263888889</v>
       </c>
       <c r="L666" s="1" t="n">
-        <v>46331.89166666667</v>
+        <v>46334.62430555555</v>
       </c>
       <c r="M666" s="1" t="n">
-        <v>46332.225</v>
+        <v>46334.95763888889</v>
       </c>
     </row>
     <row r="667">
@@ -37036,13 +37036,13 @@
         </is>
       </c>
       <c r="K667" s="1" t="n">
-        <v>46335.05833333333</v>
+        <v>46337.79097222222</v>
       </c>
       <c r="L667" s="1" t="n">
-        <v>46335.1</v>
+        <v>46337.83263888889</v>
       </c>
       <c r="M667" s="1" t="n">
-        <v>46335.475</v>
+        <v>46338.20763888889</v>
       </c>
     </row>
     <row r="668">
@@ -37091,13 +37091,13 @@
         </is>
       </c>
       <c r="K668" s="1" t="n">
-        <v>46337.93333333333</v>
+        <v>46340.66597222222</v>
       </c>
       <c r="L668" s="1" t="n">
-        <v>46338.1</v>
+        <v>46340.83263888889</v>
       </c>
       <c r="M668" s="1" t="n">
-        <v>46338.64166666667</v>
+        <v>46341.37430555555</v>
       </c>
     </row>
     <row r="669">
@@ -37146,13 +37146,13 @@
         </is>
       </c>
       <c r="K669" s="1" t="n">
-        <v>46340.43333333333</v>
+        <v>46343.16597222222</v>
       </c>
       <c r="L669" s="1" t="n">
-        <v>46340.475</v>
+        <v>46343.20763888889</v>
       </c>
       <c r="M669" s="1" t="n">
-        <v>46340.725</v>
+        <v>46343.45763888889</v>
       </c>
     </row>
     <row r="670">
@@ -37201,13 +37201,13 @@
         </is>
       </c>
       <c r="K670" s="1" t="n">
-        <v>46341.14166666667</v>
+        <v>46343.87430555555</v>
       </c>
       <c r="L670" s="1" t="n">
-        <v>46341.26666666667</v>
+        <v>46343.99930555555</v>
       </c>
       <c r="M670" s="1" t="n">
-        <v>46342.39166666667</v>
+        <v>46345.12430555555</v>
       </c>
     </row>
     <row r="671">
@@ -37256,13 +37256,13 @@
         </is>
       </c>
       <c r="K671" s="1" t="n">
-        <v>46342.725</v>
+        <v>46345.45763888889</v>
       </c>
       <c r="L671" s="1" t="n">
-        <v>46342.76666666667</v>
+        <v>46345.49930555555</v>
       </c>
       <c r="M671" s="1" t="n">
-        <v>46343.1</v>
+        <v>46345.83263888889</v>
       </c>
     </row>
     <row r="672">
@@ -37311,13 +37311,13 @@
         </is>
       </c>
       <c r="K672" s="1" t="n">
-        <v>46346.975</v>
+        <v>46349.70763888889</v>
       </c>
       <c r="L672" s="1" t="n">
-        <v>46347.01666666667</v>
+        <v>46349.74930555555</v>
       </c>
       <c r="M672" s="1" t="n">
-        <v>46347.43333333333</v>
+        <v>46350.16597222222</v>
       </c>
     </row>
     <row r="673">
@@ -37366,13 +37366,13 @@
         </is>
       </c>
       <c r="K673" s="1" t="n">
-        <v>46347.68333333333</v>
+        <v>46350.41597222222</v>
       </c>
       <c r="L673" s="1" t="n">
-        <v>46347.68333333333</v>
+        <v>46350.41597222222</v>
       </c>
       <c r="M673" s="1" t="n">
-        <v>46348.05833333333</v>
+        <v>46350.79097222222</v>
       </c>
     </row>
     <row r="674">
@@ -37421,13 +37421,13 @@
         </is>
       </c>
       <c r="K674" s="1" t="n">
-        <v>46349.30833333333</v>
+        <v>46352.04097222222</v>
       </c>
       <c r="L674" s="1" t="n">
-        <v>46349.30833333333</v>
+        <v>46352.04097222222</v>
       </c>
       <c r="M674" s="1" t="n">
-        <v>46349.55833333333</v>
+        <v>46352.29097222222</v>
       </c>
     </row>
     <row r="675">
@@ -37476,13 +37476,13 @@
         </is>
       </c>
       <c r="K675" s="1" t="n">
-        <v>46351.89166666667</v>
+        <v>46354.62430555555</v>
       </c>
       <c r="L675" s="1" t="n">
-        <v>46351.93333333333</v>
+        <v>46354.66597222222</v>
       </c>
       <c r="M675" s="1" t="n">
-        <v>46352.64166666667</v>
+        <v>46355.37430555555</v>
       </c>
     </row>
     <row r="676">
@@ -37531,13 +37531,13 @@
         </is>
       </c>
       <c r="K676" s="1" t="n">
-        <v>46352.85</v>
+        <v>46355.58263888889</v>
       </c>
       <c r="L676" s="1" t="n">
-        <v>46352.89166666667</v>
+        <v>46355.62430555555</v>
       </c>
       <c r="M676" s="1" t="n">
-        <v>46353.225</v>
+        <v>46355.95763888889</v>
       </c>
     </row>
     <row r="677">
@@ -37586,13 +37586,13 @@
         </is>
       </c>
       <c r="K677" s="1" t="n">
-        <v>46356.05833333333</v>
+        <v>46358.79097222222</v>
       </c>
       <c r="L677" s="1" t="n">
-        <v>46356.1</v>
+        <v>46358.83263888889</v>
       </c>
       <c r="M677" s="1" t="n">
-        <v>46356.475</v>
+        <v>46359.20763888889</v>
       </c>
     </row>
     <row r="678">
@@ -37641,13 +37641,13 @@
         </is>
       </c>
       <c r="K678" s="1" t="n">
-        <v>46358.93333333333</v>
+        <v>46361.66597222222</v>
       </c>
       <c r="L678" s="1" t="n">
-        <v>46359.1</v>
+        <v>46361.83263888889</v>
       </c>
       <c r="M678" s="1" t="n">
-        <v>46359.64166666667</v>
+        <v>46362.37430555555</v>
       </c>
     </row>
     <row r="679">
@@ -37696,13 +37696,13 @@
         </is>
       </c>
       <c r="K679" s="1" t="n">
-        <v>46361.43333333333</v>
+        <v>46364.16597222222</v>
       </c>
       <c r="L679" s="1" t="n">
-        <v>46361.475</v>
+        <v>46364.20763888889</v>
       </c>
       <c r="M679" s="1" t="n">
-        <v>46361.725</v>
+        <v>46364.45763888889</v>
       </c>
     </row>
     <row r="680">
@@ -37751,13 +37751,13 @@
         </is>
       </c>
       <c r="K680" s="1" t="n">
-        <v>46362.14166666667</v>
+        <v>46364.87430555555</v>
       </c>
       <c r="L680" s="1" t="n">
-        <v>46362.26666666667</v>
+        <v>46364.99930555555</v>
       </c>
       <c r="M680" s="1" t="n">
-        <v>46363.39166666667</v>
+        <v>46366.12430555555</v>
       </c>
     </row>
     <row r="681">
@@ -37806,13 +37806,13 @@
         </is>
       </c>
       <c r="K681" s="1" t="n">
-        <v>46363.725</v>
+        <v>46366.45763888889</v>
       </c>
       <c r="L681" s="1" t="n">
-        <v>46363.76666666667</v>
+        <v>46366.49930555555</v>
       </c>
       <c r="M681" s="1" t="n">
-        <v>46364.1</v>
+        <v>46366.83263888889</v>
       </c>
     </row>
     <row r="682">
@@ -37861,13 +37861,13 @@
         </is>
       </c>
       <c r="K682" s="1" t="n">
-        <v>46367.975</v>
+        <v>46370.70763888889</v>
       </c>
       <c r="L682" s="1" t="n">
-        <v>46368.01666666667</v>
+        <v>46370.74930555555</v>
       </c>
       <c r="M682" s="1" t="n">
-        <v>46368.43333333333</v>
+        <v>46371.16597222222</v>
       </c>
     </row>
     <row r="683">
@@ -37916,13 +37916,13 @@
         </is>
       </c>
       <c r="K683" s="1" t="n">
-        <v>46368.68333333333</v>
+        <v>46371.41597222222</v>
       </c>
       <c r="L683" s="1" t="n">
-        <v>46368.68333333333</v>
+        <v>46371.41597222222</v>
       </c>
       <c r="M683" s="1" t="n">
-        <v>46369.05833333333</v>
+        <v>46371.79097222222</v>
       </c>
     </row>
     <row r="684">
@@ -37967,13 +37967,13 @@
       </c>
       <c r="J684" t="inlineStr"/>
       <c r="K684" s="1" t="n">
-        <v>46370.30833333333</v>
+        <v>46373.04097222222</v>
       </c>
       <c r="L684" s="1" t="n">
-        <v>46370.30833333333</v>
+        <v>46373.04097222222</v>
       </c>
       <c r="M684" s="1" t="n">
-        <v>46370.55833333333</v>
+        <v>46373.29097222222</v>
       </c>
     </row>
     <row r="685">
@@ -41098,13 +41098,13 @@
         </is>
       </c>
       <c r="K741" s="1" t="n">
-        <v>46299.25</v>
+        <v>46299.375</v>
       </c>
       <c r="L741" s="1" t="n">
-        <v>46299.29166666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="M741" s="1" t="n">
-        <v>46299.58333333334</v>
+        <v>46299.70833333334</v>
       </c>
     </row>
     <row r="742">
@@ -41153,13 +41153,13 @@
         </is>
       </c>
       <c r="K742" s="1" t="n">
-        <v>46299.875</v>
+        <v>46300</v>
       </c>
       <c r="L742" s="1" t="n">
-        <v>46299.875</v>
+        <v>46300</v>
       </c>
       <c r="M742" s="1" t="n">
-        <v>46301.25</v>
+        <v>46301.375</v>
       </c>
     </row>
     <row r="743">
@@ -41208,13 +41208,13 @@
         </is>
       </c>
       <c r="K743" s="1" t="n">
-        <v>46301.5</v>
+        <v>46301.625</v>
       </c>
       <c r="L743" s="1" t="n">
-        <v>46301.54166666666</v>
+        <v>46301.66666666666</v>
       </c>
       <c r="M743" s="1" t="n">
-        <v>46302</v>
+        <v>46302.125</v>
       </c>
     </row>
     <row r="744">
@@ -41263,13 +41263,13 @@
         </is>
       </c>
       <c r="K744" s="1" t="n">
-        <v>46305.83333333334</v>
+        <v>46305.95833333334</v>
       </c>
       <c r="L744" s="1" t="n">
-        <v>46305.83333333334</v>
+        <v>46305.95833333334</v>
       </c>
       <c r="M744" s="1" t="n">
-        <v>46306.29166666666</v>
+        <v>46306.41666666666</v>
       </c>
     </row>
     <row r="745">
@@ -41318,13 +41318,13 @@
         </is>
       </c>
       <c r="K745" s="1" t="n">
-        <v>46307.29166666666</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="L745" s="1" t="n">
-        <v>46307.29166666666</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="M745" s="1" t="n">
-        <v>46307.75</v>
+        <v>46307.875</v>
       </c>
     </row>
     <row r="746">
@@ -41373,13 +41373,13 @@
         </is>
       </c>
       <c r="K746" s="1" t="n">
-        <v>46310.22916666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="L746" s="1" t="n">
-        <v>46310.27083333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="M746" s="1" t="n">
-        <v>46310.89583333334</v>
+        <v>46311.02083333334</v>
       </c>
     </row>
     <row r="747">
@@ -41428,13 +41428,13 @@
         </is>
       </c>
       <c r="K747" s="1" t="n">
-        <v>46311.89583333334</v>
+        <v>46312.02083333334</v>
       </c>
       <c r="L747" s="1" t="n">
-        <v>46311.9375</v>
+        <v>46312.0625</v>
       </c>
       <c r="M747" s="1" t="n">
-        <v>46312.4375</v>
+        <v>46312.5625</v>
       </c>
     </row>
     <row r="748">
@@ -41483,13 +41483,13 @@
         </is>
       </c>
       <c r="K748" s="1" t="n">
-        <v>46313.52083333334</v>
+        <v>46313.64583333334</v>
       </c>
       <c r="L748" s="1" t="n">
-        <v>46313.6875</v>
+        <v>46313.8125</v>
       </c>
       <c r="M748" s="1" t="n">
-        <v>46314.47916666666</v>
+        <v>46314.60416666666</v>
       </c>
     </row>
     <row r="749">
@@ -41538,13 +41538,13 @@
         </is>
       </c>
       <c r="K749" s="1" t="n">
-        <v>46320.22916666666</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="L749" s="1" t="n">
-        <v>46320.27083333334</v>
+        <v>46320.39583333334</v>
       </c>
       <c r="M749" s="1" t="n">
-        <v>46320.5625</v>
+        <v>46320.6875</v>
       </c>
     </row>
     <row r="750">
@@ -41593,13 +41593,13 @@
         </is>
       </c>
       <c r="K750" s="1" t="n">
-        <v>46320.85416666666</v>
+        <v>46320.97916666666</v>
       </c>
       <c r="L750" s="1" t="n">
-        <v>46320.85416666666</v>
+        <v>46320.97916666666</v>
       </c>
       <c r="M750" s="1" t="n">
-        <v>46322.22916666666</v>
+        <v>46322.35416666666</v>
       </c>
     </row>
     <row r="751">
@@ -41648,13 +41648,13 @@
         </is>
       </c>
       <c r="K751" s="1" t="n">
-        <v>46322.47916666666</v>
+        <v>46322.60416666666</v>
       </c>
       <c r="L751" s="1" t="n">
-        <v>46322.52083333334</v>
+        <v>46322.64583333334</v>
       </c>
       <c r="M751" s="1" t="n">
-        <v>46322.97916666666</v>
+        <v>46323.10416666666</v>
       </c>
     </row>
     <row r="752">
@@ -41703,13 +41703,13 @@
         </is>
       </c>
       <c r="K752" s="1" t="n">
-        <v>46326.8125</v>
+        <v>46326.9375</v>
       </c>
       <c r="L752" s="1" t="n">
-        <v>46326.8125</v>
+        <v>46326.9375</v>
       </c>
       <c r="M752" s="1" t="n">
-        <v>46327.27083333334</v>
+        <v>46327.39583333334</v>
       </c>
     </row>
     <row r="753">
@@ -41758,13 +41758,13 @@
         </is>
       </c>
       <c r="K753" s="1" t="n">
-        <v>46328.27083333334</v>
+        <v>46328.39583333334</v>
       </c>
       <c r="L753" s="1" t="n">
-        <v>46328.27083333334</v>
+        <v>46328.39583333334</v>
       </c>
       <c r="M753" s="1" t="n">
-        <v>46328.77083333334</v>
+        <v>46328.89583333334</v>
       </c>
     </row>
     <row r="754">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -8495,10 +8495,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>46294.95833333334</v>
+        <v>46296.125</v>
       </c>
       <c r="M147" s="1" t="n">
-        <v>46295.66666666666</v>
+        <v>46297.79166666666</v>
       </c>
     </row>
     <row r="148">
@@ -18922,13 +18922,13 @@
         </is>
       </c>
       <c r="K337" s="1" t="n">
-        <v>46291.58333333334</v>
+        <v>46292.16666666666</v>
       </c>
       <c r="L337" s="1" t="n">
-        <v>46291.625</v>
+        <v>46292.41666666666</v>
       </c>
       <c r="M337" s="1" t="n">
-        <v>46292.45833333334</v>
+        <v>46293.45833333334</v>
       </c>
     </row>
     <row r="338">
@@ -18977,13 +18977,13 @@
         </is>
       </c>
       <c r="K338" s="1" t="n">
-        <v>46295.39583333334</v>
+        <v>46296.39583333334</v>
       </c>
       <c r="L338" s="1" t="n">
-        <v>46297.45833333334</v>
+        <v>46296.45833333334</v>
       </c>
       <c r="M338" s="1" t="n">
-        <v>46299.16666666666</v>
+        <v>46298.04166666666</v>
       </c>
     </row>
     <row r="339">
@@ -19032,13 +19032,13 @@
         </is>
       </c>
       <c r="K339" s="1" t="n">
-        <v>46301.5625</v>
+        <v>46300.4375</v>
       </c>
       <c r="L339" s="1" t="n">
-        <v>46302.72916666666</v>
+        <v>46301.10416666666</v>
       </c>
       <c r="M339" s="1" t="n">
-        <v>46303.5625</v>
+        <v>46301.9375</v>
       </c>
     </row>
     <row r="340">
@@ -19087,13 +19087,13 @@
         </is>
       </c>
       <c r="K340" s="1" t="n">
-        <v>46305.875</v>
+        <v>46304.25</v>
       </c>
       <c r="L340" s="1" t="n">
-        <v>46306.4375</v>
+        <v>46304.3125</v>
       </c>
       <c r="M340" s="1" t="n">
-        <v>46306.9375</v>
+        <v>46304.8125</v>
       </c>
     </row>
     <row r="341">
@@ -19142,13 +19142,13 @@
         </is>
       </c>
       <c r="K341" s="1" t="n">
-        <v>46307.04166666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="L341" s="1" t="n">
-        <v>46307.16666666666</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="M341" s="1" t="n">
-        <v>46307.625</v>
+        <v>46305.5</v>
       </c>
     </row>
     <row r="342">
@@ -19197,13 +19197,13 @@
         </is>
       </c>
       <c r="K342" s="1" t="n">
-        <v>46310.58333333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="L342" s="1" t="n">
-        <v>46310.625</v>
+        <v>46308.5</v>
       </c>
       <c r="M342" s="1" t="n">
-        <v>46311.29166666666</v>
+        <v>46309.16666666666</v>
       </c>
     </row>
     <row r="343">
@@ -19252,13 +19252,13 @@
         </is>
       </c>
       <c r="K343" s="1" t="n">
-        <v>46312.27083333334</v>
+        <v>46310.14583333334</v>
       </c>
       <c r="L343" s="1" t="n">
-        <v>46312.3125</v>
+        <v>46310.1875</v>
       </c>
       <c r="M343" s="1" t="n">
-        <v>46312.89583333334</v>
+        <v>46310.77083333334</v>
       </c>
     </row>
     <row r="344">
@@ -19307,13 +19307,13 @@
         </is>
       </c>
       <c r="K344" s="1" t="n">
-        <v>46313</v>
+        <v>46310.875</v>
       </c>
       <c r="L344" s="1" t="n">
-        <v>46313.0625</v>
+        <v>46310.9375</v>
       </c>
       <c r="M344" s="1" t="n">
-        <v>46313.39583333334</v>
+        <v>46311.27083333334</v>
       </c>
     </row>
     <row r="345">
@@ -19362,13 +19362,13 @@
         </is>
       </c>
       <c r="K345" s="1" t="n">
-        <v>46314.47916666666</v>
+        <v>46312.35416666666</v>
       </c>
       <c r="L345" s="1" t="n">
-        <v>46314.64583333334</v>
+        <v>46312.52083333334</v>
       </c>
       <c r="M345" s="1" t="n">
-        <v>46315.14583333334</v>
+        <v>46313.02083333334</v>
       </c>
     </row>
     <row r="346">
@@ -19417,13 +19417,13 @@
         </is>
       </c>
       <c r="K346" s="1" t="n">
-        <v>46319.3125</v>
+        <v>46317.1875</v>
       </c>
       <c r="L346" s="1" t="n">
-        <v>46319.47916666666</v>
+        <v>46317.35416666666</v>
       </c>
       <c r="M346" s="1" t="n">
-        <v>46320.3125</v>
+        <v>46318.1875</v>
       </c>
     </row>
     <row r="347">
@@ -19472,13 +19472,13 @@
         </is>
       </c>
       <c r="K347" s="1" t="n">
-        <v>46321.97916666666</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="L347" s="1" t="n">
-        <v>46322.02083333334</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="M347" s="1" t="n">
-        <v>46322.85416666666</v>
+        <v>46320.72916666666</v>
       </c>
     </row>
     <row r="348">
@@ -19527,13 +19527,13 @@
         </is>
       </c>
       <c r="K348" s="1" t="n">
-        <v>46326.02083333334</v>
+        <v>46323.89583333334</v>
       </c>
       <c r="L348" s="1" t="n">
-        <v>46326.10416666666</v>
+        <v>46323.97916666666</v>
       </c>
       <c r="M348" s="1" t="n">
-        <v>46327.77083333334</v>
+        <v>46325.64583333334</v>
       </c>
     </row>
     <row r="349">
@@ -19582,13 +19582,13 @@
         </is>
       </c>
       <c r="K349" s="1" t="n">
-        <v>46330.22916666666</v>
+        <v>46328.10416666666</v>
       </c>
       <c r="L349" s="1" t="n">
-        <v>46330.39583333334</v>
+        <v>46328.27083333334</v>
       </c>
       <c r="M349" s="1" t="n">
-        <v>46331.22916666666</v>
+        <v>46329.10416666666</v>
       </c>
     </row>
     <row r="350">
@@ -19637,13 +19637,13 @@
         </is>
       </c>
       <c r="K350" s="1" t="n">
-        <v>46333.77083333334</v>
+        <v>46331.64583333334</v>
       </c>
       <c r="L350" s="1" t="n">
-        <v>46333.83333333334</v>
+        <v>46331.70833333334</v>
       </c>
       <c r="M350" s="1" t="n">
-        <v>46334.33333333334</v>
+        <v>46332.20833333334</v>
       </c>
     </row>
     <row r="351">
@@ -19692,13 +19692,13 @@
         </is>
       </c>
       <c r="K351" s="1" t="n">
-        <v>46334.5625</v>
+        <v>46332.4375</v>
       </c>
       <c r="L351" s="1" t="n">
-        <v>46334.60416666666</v>
+        <v>46332.47916666666</v>
       </c>
       <c r="M351" s="1" t="n">
-        <v>46335.10416666666</v>
+        <v>46332.97916666666</v>
       </c>
     </row>
     <row r="352">
@@ -19747,13 +19747,13 @@
         </is>
       </c>
       <c r="K352" s="1" t="n">
-        <v>46338.1875</v>
+        <v>46336.27083333334</v>
       </c>
       <c r="L352" s="1" t="n">
-        <v>46338.22916666666</v>
+        <v>46336.3125</v>
       </c>
       <c r="M352" s="1" t="n">
-        <v>46338.89583333334</v>
+        <v>46336.97916666666</v>
       </c>
     </row>
     <row r="353">
@@ -19802,13 +19802,13 @@
         </is>
       </c>
       <c r="K353" s="1" t="n">
-        <v>46339.97916666666</v>
+        <v>46338.0625</v>
       </c>
       <c r="L353" s="1" t="n">
-        <v>46340.02083333334</v>
+        <v>46338.10416666666</v>
       </c>
       <c r="M353" s="1" t="n">
-        <v>46340.60416666666</v>
+        <v>46338.6875</v>
       </c>
     </row>
     <row r="354">
@@ -19857,13 +19857,13 @@
         </is>
       </c>
       <c r="K354" s="1" t="n">
-        <v>46340.79166666666</v>
+        <v>46338.875</v>
       </c>
       <c r="L354" s="1" t="n">
-        <v>46340.85416666666</v>
+        <v>46338.9375</v>
       </c>
       <c r="M354" s="1" t="n">
-        <v>46341.1875</v>
+        <v>46339.27083333334</v>
       </c>
     </row>
     <row r="355">
@@ -19912,13 +19912,13 @@
         </is>
       </c>
       <c r="K355" s="1" t="n">
-        <v>46342.47916666666</v>
+        <v>46340.5625</v>
       </c>
       <c r="L355" s="1" t="n">
-        <v>46342.64583333334</v>
+        <v>46340.72916666666</v>
       </c>
       <c r="M355" s="1" t="n">
-        <v>46343.14583333334</v>
+        <v>46341.22916666666</v>
       </c>
     </row>
     <row r="356">
@@ -19967,13 +19967,13 @@
         </is>
       </c>
       <c r="K356" s="1" t="n">
-        <v>46347.3125</v>
+        <v>46345.39583333334</v>
       </c>
       <c r="L356" s="1" t="n">
-        <v>46347.47916666666</v>
+        <v>46345.5625</v>
       </c>
       <c r="M356" s="1" t="n">
-        <v>46348.3125</v>
+        <v>46346.39583333334</v>
       </c>
     </row>
     <row r="357">
@@ -20022,13 +20022,13 @@
         </is>
       </c>
       <c r="K357" s="1" t="n">
-        <v>46349.97916666666</v>
+        <v>46348.0625</v>
       </c>
       <c r="L357" s="1" t="n">
-        <v>46350.02083333334</v>
+        <v>46348.10416666666</v>
       </c>
       <c r="M357" s="1" t="n">
-        <v>46350.85416666666</v>
+        <v>46348.9375</v>
       </c>
     </row>
     <row r="358">
@@ -20077,13 +20077,13 @@
         </is>
       </c>
       <c r="K358" s="1" t="n">
-        <v>46354.02083333334</v>
+        <v>46352.10416666666</v>
       </c>
       <c r="L358" s="1" t="n">
-        <v>46354.10416666666</v>
+        <v>46352.1875</v>
       </c>
       <c r="M358" s="1" t="n">
-        <v>46355.77083333334</v>
+        <v>46353.85416666666</v>
       </c>
     </row>
     <row r="359">
@@ -20132,13 +20132,13 @@
         </is>
       </c>
       <c r="K359" s="1" t="n">
-        <v>46358.22916666666</v>
+        <v>46356.3125</v>
       </c>
       <c r="L359" s="1" t="n">
-        <v>46358.39583333334</v>
+        <v>46356.47916666666</v>
       </c>
       <c r="M359" s="1" t="n">
-        <v>46359.22916666666</v>
+        <v>46357.3125</v>
       </c>
     </row>
     <row r="360">
@@ -20187,13 +20187,13 @@
         </is>
       </c>
       <c r="K360" s="1" t="n">
-        <v>46361.77083333334</v>
+        <v>46359.85416666666</v>
       </c>
       <c r="L360" s="1" t="n">
-        <v>46361.83333333334</v>
+        <v>46359.91666666666</v>
       </c>
       <c r="M360" s="1" t="n">
-        <v>46362.33333333334</v>
+        <v>46360.41666666666</v>
       </c>
     </row>
     <row r="361">
@@ -20238,13 +20238,13 @@
       </c>
       <c r="J361" t="inlineStr"/>
       <c r="K361" s="1" t="n">
-        <v>46362.5625</v>
+        <v>46360.64583333334</v>
       </c>
       <c r="L361" s="1" t="n">
-        <v>46362.60416666666</v>
+        <v>46360.6875</v>
       </c>
       <c r="M361" s="1" t="n">
-        <v>46363.10416666666</v>
+        <v>46361.1875</v>
       </c>
     </row>
     <row r="362">
@@ -23314,13 +23314,13 @@
         </is>
       </c>
       <c r="K417" s="1" t="n">
-        <v>46287.20833333334</v>
+        <v>46287.04166666666</v>
       </c>
       <c r="L417" s="1" t="n">
-        <v>46287.25</v>
+        <v>46287.08333333334</v>
       </c>
       <c r="M417" s="1" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.33333333334</v>
       </c>
     </row>
     <row r="418">
@@ -23369,13 +23369,13 @@
         </is>
       </c>
       <c r="K418" s="1" t="n">
-        <v>46287.625</v>
+        <v>46287.41666666666</v>
       </c>
       <c r="L418" s="1" t="n">
-        <v>46288.70833333334</v>
+        <v>46287.58333333334</v>
       </c>
       <c r="M418" s="1" t="n">
-        <v>46289.99305555555</v>
+        <v>46288.54166666666</v>
       </c>
     </row>
     <row r="419">
@@ -23424,13 +23424,13 @@
         </is>
       </c>
       <c r="K419" s="1" t="n">
-        <v>46290.20833333334</v>
+        <v>46288.70833333334</v>
       </c>
       <c r="L419" s="1" t="n">
-        <v>46290.66666666666</v>
+        <v>46288.75</v>
       </c>
       <c r="M419" s="1" t="n">
-        <v>46291.04166666666</v>
+        <v>46289.04166666666</v>
       </c>
     </row>
     <row r="420">
@@ -23479,13 +23479,13 @@
         </is>
       </c>
       <c r="K420" s="1" t="n">
-        <v>46292.58333333334</v>
+        <v>46291.83333333334</v>
       </c>
       <c r="L420" s="1" t="n">
-        <v>46292.79166666666</v>
+        <v>46292.04166666666</v>
       </c>
       <c r="M420" s="1" t="n">
-        <v>46293.25</v>
+        <v>46292.5</v>
       </c>
     </row>
     <row r="421">
@@ -25290,13 +25290,13 @@
         </is>
       </c>
       <c r="K453" s="1" t="n">
-        <v>46292.47916666666</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="L453" s="1" t="n">
-        <v>46292.52083333334</v>
+        <v>46294.04166666666</v>
       </c>
       <c r="M453" s="1" t="n">
-        <v>46293.10416666666</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="454">
@@ -25345,13 +25345,13 @@
         </is>
       </c>
       <c r="K454" s="1" t="n">
-        <v>46293.20833333334</v>
+        <v>46295.125</v>
       </c>
       <c r="L454" s="1" t="n">
-        <v>46293.25</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="M454" s="1" t="n">
-        <v>46293.58333333334</v>
+        <v>46295.625</v>
       </c>
     </row>
     <row r="455">
@@ -25400,13 +25400,13 @@
         </is>
       </c>
       <c r="K455" s="1" t="n">
-        <v>46294.64583333334</v>
+        <v>46296.70833333334</v>
       </c>
       <c r="L455" s="1" t="n">
-        <v>46296.8125</v>
+        <v>46296.875</v>
       </c>
       <c r="M455" s="1" t="n">
-        <v>46297.3125</v>
+        <v>46297.375</v>
       </c>
     </row>
     <row r="456">
@@ -25455,13 +25455,13 @@
         </is>
       </c>
       <c r="K456" s="1" t="n">
-        <v>46301.22916666666</v>
+        <v>46301.29166666666</v>
       </c>
       <c r="L456" s="1" t="n">
-        <v>46302.39583333334</v>
+        <v>46301.95833333334</v>
       </c>
       <c r="M456" s="1" t="n">
-        <v>46303.22916666666</v>
+        <v>46302.79166666666</v>
       </c>
     </row>
     <row r="457">
@@ -25510,13 +25510,13 @@
         </is>
       </c>
       <c r="K457" s="1" t="n">
-        <v>46304.75</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="L457" s="1" t="n">
-        <v>46304.79166666666</v>
+        <v>46304.375</v>
       </c>
       <c r="M457" s="1" t="n">
-        <v>46305.625</v>
+        <v>46305.20833333334</v>
       </c>
     </row>
     <row r="458">
@@ -25565,13 +25565,13 @@
         </is>
       </c>
       <c r="K458" s="1" t="n">
-        <v>46308.5625</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="L458" s="1" t="n">
-        <v>46309.625</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="M458" s="1" t="n">
-        <v>46311.33333333334</v>
+        <v>46310.91666666666</v>
       </c>
     </row>
     <row r="459">
@@ -25620,13 +25620,13 @@
         </is>
       </c>
       <c r="K459" s="1" t="n">
-        <v>46313.79166666666</v>
+        <v>46313.375</v>
       </c>
       <c r="L459" s="1" t="n">
-        <v>46313.95833333334</v>
+        <v>46313.54166666666</v>
       </c>
       <c r="M459" s="1" t="n">
-        <v>46314.79166666666</v>
+        <v>46314.375</v>
       </c>
     </row>
     <row r="460">
@@ -25675,13 +25675,13 @@
         </is>
       </c>
       <c r="K460" s="1" t="n">
-        <v>46317.10416666666</v>
+        <v>46316.6875</v>
       </c>
       <c r="L460" s="1" t="n">
-        <v>46317.16666666666</v>
+        <v>46316.75</v>
       </c>
       <c r="M460" s="1" t="n">
-        <v>46317.66666666666</v>
+        <v>46317.25</v>
       </c>
     </row>
     <row r="461">
@@ -25730,13 +25730,13 @@
         </is>
       </c>
       <c r="K461" s="1" t="n">
-        <v>46317.89583333334</v>
+        <v>46317.47916666666</v>
       </c>
       <c r="L461" s="1" t="n">
-        <v>46317.9375</v>
+        <v>46317.52083333334</v>
       </c>
       <c r="M461" s="1" t="n">
-        <v>46318.4375</v>
+        <v>46318.02083333334</v>
       </c>
     </row>
     <row r="462">
@@ -25785,13 +25785,13 @@
         </is>
       </c>
       <c r="K462" s="1" t="n">
-        <v>46321.52083333334</v>
+        <v>46321.10416666666</v>
       </c>
       <c r="L462" s="1" t="n">
-        <v>46321.5625</v>
+        <v>46321.14583333334</v>
       </c>
       <c r="M462" s="1" t="n">
-        <v>46322.22916666666</v>
+        <v>46321.8125</v>
       </c>
     </row>
     <row r="463">
@@ -25840,13 +25840,13 @@
         </is>
       </c>
       <c r="K463" s="1" t="n">
-        <v>46323.3125</v>
+        <v>46322.89583333334</v>
       </c>
       <c r="L463" s="1" t="n">
-        <v>46323.35416666666</v>
+        <v>46322.9375</v>
       </c>
       <c r="M463" s="1" t="n">
-        <v>46323.9375</v>
+        <v>46323.52083333334</v>
       </c>
     </row>
     <row r="464">
@@ -25895,13 +25895,13 @@
         </is>
       </c>
       <c r="K464" s="1" t="n">
-        <v>46324.125</v>
+        <v>46323.70833333334</v>
       </c>
       <c r="L464" s="1" t="n">
-        <v>46324.1875</v>
+        <v>46323.77083333334</v>
       </c>
       <c r="M464" s="1" t="n">
-        <v>46324.52083333334</v>
+        <v>46324.10416666666</v>
       </c>
     </row>
     <row r="465">
@@ -25950,13 +25950,13 @@
         </is>
       </c>
       <c r="K465" s="1" t="n">
-        <v>46325.8125</v>
+        <v>46325.39583333334</v>
       </c>
       <c r="L465" s="1" t="n">
-        <v>46325.97916666666</v>
+        <v>46325.5625</v>
       </c>
       <c r="M465" s="1" t="n">
-        <v>46326.47916666666</v>
+        <v>46326.0625</v>
       </c>
     </row>
     <row r="466">
@@ -26005,13 +26005,13 @@
         </is>
       </c>
       <c r="K466" s="1" t="n">
-        <v>46330.64583333334</v>
+        <v>46330.22916666666</v>
       </c>
       <c r="L466" s="1" t="n">
-        <v>46330.8125</v>
+        <v>46330.39583333334</v>
       </c>
       <c r="M466" s="1" t="n">
-        <v>46331.64583333334</v>
+        <v>46331.22916666666</v>
       </c>
     </row>
     <row r="467">
@@ -26060,13 +26060,13 @@
         </is>
       </c>
       <c r="K467" s="1" t="n">
-        <v>46333.3125</v>
+        <v>46332.89583333334</v>
       </c>
       <c r="L467" s="1" t="n">
-        <v>46333.35416666666</v>
+        <v>46332.9375</v>
       </c>
       <c r="M467" s="1" t="n">
-        <v>46334.1875</v>
+        <v>46333.77083333334</v>
       </c>
     </row>
     <row r="468">
@@ -26115,13 +26115,13 @@
         </is>
       </c>
       <c r="K468" s="1" t="n">
-        <v>46337.35416666666</v>
+        <v>46336.9375</v>
       </c>
       <c r="L468" s="1" t="n">
-        <v>46337.4375</v>
+        <v>46337.02083333334</v>
       </c>
       <c r="M468" s="1" t="n">
-        <v>46339.10416666666</v>
+        <v>46338.6875</v>
       </c>
     </row>
     <row r="469">
@@ -26170,13 +26170,13 @@
         </is>
       </c>
       <c r="K469" s="1" t="n">
-        <v>46341.5625</v>
+        <v>46341.14583333334</v>
       </c>
       <c r="L469" s="1" t="n">
-        <v>46341.72916666666</v>
+        <v>46341.3125</v>
       </c>
       <c r="M469" s="1" t="n">
-        <v>46342.5625</v>
+        <v>46342.14583333334</v>
       </c>
     </row>
     <row r="470">
@@ -26225,13 +26225,13 @@
         </is>
       </c>
       <c r="K470" s="1" t="n">
-        <v>46345.10416666666</v>
+        <v>46344.6875</v>
       </c>
       <c r="L470" s="1" t="n">
-        <v>46345.16666666666</v>
+        <v>46344.75</v>
       </c>
       <c r="M470" s="1" t="n">
-        <v>46345.66666666666</v>
+        <v>46345.25</v>
       </c>
     </row>
     <row r="471">
@@ -26280,13 +26280,13 @@
         </is>
       </c>
       <c r="K471" s="1" t="n">
-        <v>46345.89583333334</v>
+        <v>46345.47916666666</v>
       </c>
       <c r="L471" s="1" t="n">
-        <v>46345.9375</v>
+        <v>46345.52083333334</v>
       </c>
       <c r="M471" s="1" t="n">
-        <v>46346.4375</v>
+        <v>46346.02083333334</v>
       </c>
     </row>
     <row r="472">
@@ -26335,13 +26335,13 @@
         </is>
       </c>
       <c r="K472" s="1" t="n">
-        <v>46349.52083333334</v>
+        <v>46349.10416666666</v>
       </c>
       <c r="L472" s="1" t="n">
-        <v>46349.5625</v>
+        <v>46349.14583333334</v>
       </c>
       <c r="M472" s="1" t="n">
-        <v>46350.22916666666</v>
+        <v>46349.8125</v>
       </c>
     </row>
     <row r="473">
@@ -26390,13 +26390,13 @@
         </is>
       </c>
       <c r="K473" s="1" t="n">
-        <v>46351.3125</v>
+        <v>46350.89583333334</v>
       </c>
       <c r="L473" s="1" t="n">
-        <v>46351.35416666666</v>
+        <v>46350.9375</v>
       </c>
       <c r="M473" s="1" t="n">
-        <v>46351.9375</v>
+        <v>46351.52083333334</v>
       </c>
     </row>
     <row r="474">
@@ -26445,13 +26445,13 @@
         </is>
       </c>
       <c r="K474" s="1" t="n">
-        <v>46352.125</v>
+        <v>46351.70833333334</v>
       </c>
       <c r="L474" s="1" t="n">
-        <v>46352.1875</v>
+        <v>46351.77083333334</v>
       </c>
       <c r="M474" s="1" t="n">
-        <v>46352.52083333334</v>
+        <v>46352.10416666666</v>
       </c>
     </row>
     <row r="475">
@@ -26500,13 +26500,13 @@
         </is>
       </c>
       <c r="K475" s="1" t="n">
-        <v>46353.8125</v>
+        <v>46353.39583333334</v>
       </c>
       <c r="L475" s="1" t="n">
-        <v>46353.97916666666</v>
+        <v>46353.5625</v>
       </c>
       <c r="M475" s="1" t="n">
-        <v>46354.47916666666</v>
+        <v>46354.0625</v>
       </c>
     </row>
     <row r="476">
@@ -26555,13 +26555,13 @@
         </is>
       </c>
       <c r="K476" s="1" t="n">
-        <v>46358.64583333334</v>
+        <v>46358.22916666666</v>
       </c>
       <c r="L476" s="1" t="n">
-        <v>46358.8125</v>
+        <v>46358.39583333334</v>
       </c>
       <c r="M476" s="1" t="n">
-        <v>46359.64583333334</v>
+        <v>46359.22916666666</v>
       </c>
     </row>
     <row r="477">
@@ -26610,13 +26610,13 @@
         </is>
       </c>
       <c r="K477" s="1" t="n">
-        <v>46361.3125</v>
+        <v>46360.89583333334</v>
       </c>
       <c r="L477" s="1" t="n">
-        <v>46361.35416666666</v>
+        <v>46360.9375</v>
       </c>
       <c r="M477" s="1" t="n">
-        <v>46362.1875</v>
+        <v>46361.77083333334</v>
       </c>
     </row>
     <row r="478">
@@ -26665,13 +26665,13 @@
         </is>
       </c>
       <c r="K478" s="1" t="n">
-        <v>46365.35416666666</v>
+        <v>46364.9375</v>
       </c>
       <c r="L478" s="1" t="n">
-        <v>46365.4375</v>
+        <v>46365.02083333334</v>
       </c>
       <c r="M478" s="1" t="n">
-        <v>46367.10416666666</v>
+        <v>46366.6875</v>
       </c>
     </row>
     <row r="479">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="K479" s="1" t="n">
-        <v>46369.5625</v>
+        <v>46369.14583333334</v>
       </c>
       <c r="L479" s="1" t="n">
-        <v>46369.72916666666</v>
+        <v>46369.3125</v>
       </c>
       <c r="M479" s="1" t="n">
-        <v>46370.5625</v>
+        <v>46370.14583333334</v>
       </c>
     </row>
     <row r="480">
@@ -26775,13 +26775,13 @@
         </is>
       </c>
       <c r="K480" s="1" t="n">
-        <v>46373.10416666666</v>
+        <v>46372.6875</v>
       </c>
       <c r="L480" s="1" t="n">
-        <v>46373.16666666666</v>
+        <v>46372.75</v>
       </c>
       <c r="M480" s="1" t="n">
-        <v>46373.66666666666</v>
+        <v>46373.25</v>
       </c>
     </row>
     <row r="481">
@@ -26826,13 +26826,13 @@
       </c>
       <c r="J481" t="inlineStr"/>
       <c r="K481" s="1" t="n">
-        <v>46373.89583333334</v>
+        <v>46373.47916666666</v>
       </c>
       <c r="L481" s="1" t="n">
-        <v>46373.9375</v>
+        <v>46373.52083333334</v>
       </c>
       <c r="M481" s="1" t="n">
-        <v>46374.4375</v>
+        <v>46374.02083333334</v>
       </c>
     </row>
     <row r="482">
@@ -38685,10 +38685,10 @@
         <v>46295.66666666666</v>
       </c>
       <c r="L697" s="1" t="n">
-        <v>46295.72916666666</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="M697" s="1" t="n">
-        <v>46295.97916666666</v>
+        <v>46296.29166666666</v>
       </c>
     </row>
     <row r="698">
@@ -38737,13 +38737,13 @@
         </is>
       </c>
       <c r="K698" s="1" t="n">
-        <v>46297</v>
+        <v>46297.3125</v>
       </c>
       <c r="L698" s="1" t="n">
-        <v>46297.0625</v>
+        <v>46297.375</v>
       </c>
       <c r="M698" s="1" t="n">
-        <v>46297.47916666666</v>
+        <v>46297.79166666666</v>
       </c>
     </row>
     <row r="699">
@@ -38792,13 +38792,13 @@
         </is>
       </c>
       <c r="K699" s="1" t="n">
-        <v>46297.79166666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="L699" s="1" t="n">
-        <v>46297.8125</v>
+        <v>46298.125</v>
       </c>
       <c r="M699" s="1" t="n">
-        <v>46298.41666666666</v>
+        <v>46298.72916666666</v>
       </c>
     </row>
     <row r="700">
@@ -38847,13 +38847,13 @@
         </is>
       </c>
       <c r="K700" s="1" t="n">
-        <v>46303.83333333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="L700" s="1" t="n">
-        <v>46304</v>
+        <v>46304.3125</v>
       </c>
       <c r="M700" s="1" t="n">
-        <v>46304.58333333334</v>
+        <v>46304.89583333334</v>
       </c>
     </row>
     <row r="701">
@@ -38902,13 +38902,13 @@
         </is>
       </c>
       <c r="K701" s="1" t="n">
-        <v>46306.22916666666</v>
+        <v>46306.64583333334</v>
       </c>
       <c r="L701" s="1" t="n">
-        <v>46306.27083333334</v>
+        <v>46306.6875</v>
       </c>
       <c r="M701" s="1" t="n">
-        <v>46306.625</v>
+        <v>46307.04166666666</v>
       </c>
     </row>
     <row r="702">
@@ -38957,13 +38957,13 @@
         </is>
       </c>
       <c r="K702" s="1" t="n">
-        <v>46306.75</v>
+        <v>46307.16666666666</v>
       </c>
       <c r="L702" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46307.25</v>
       </c>
       <c r="M702" s="1" t="n">
-        <v>46307.83333333334</v>
+        <v>46308.25</v>
       </c>
     </row>
     <row r="703">
@@ -39012,13 +39012,13 @@
         </is>
       </c>
       <c r="K703" s="1" t="n">
-        <v>46308.04166666666</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="L703" s="1" t="n">
-        <v>46308.08333333334</v>
+        <v>46308.5</v>
       </c>
       <c r="M703" s="1" t="n">
-        <v>46308.58333333334</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="704">
@@ -39067,13 +39067,13 @@
         </is>
       </c>
       <c r="K704" s="1" t="n">
-        <v>46310.39583333334</v>
+        <v>46310.8125</v>
       </c>
       <c r="L704" s="1" t="n">
-        <v>46310.5625</v>
+        <v>46310.97916666666</v>
       </c>
       <c r="M704" s="1" t="n">
-        <v>46311.25</v>
+        <v>46311.66666666666</v>
       </c>
     </row>
     <row r="705">
@@ -39122,13 +39122,13 @@
         </is>
       </c>
       <c r="K705" s="1" t="n">
-        <v>46319.5</v>
+        <v>46317.66666666666</v>
       </c>
       <c r="L705" s="1" t="n">
-        <v>46319.54166666666</v>
+        <v>46317.70833333334</v>
       </c>
       <c r="M705" s="1" t="n">
-        <v>46320.20833333334</v>
+        <v>46318.375</v>
       </c>
     </row>
     <row r="706">
@@ -39177,13 +39177,13 @@
         </is>
       </c>
       <c r="K706" s="1" t="n">
-        <v>46320.375</v>
+        <v>46318.54166666666</v>
       </c>
       <c r="L706" s="1" t="n">
-        <v>46320.4375</v>
+        <v>46318.60416666666</v>
       </c>
       <c r="M706" s="1" t="n">
-        <v>46320.6875</v>
+        <v>46318.85416666666</v>
       </c>
     </row>
     <row r="707">
@@ -39232,13 +39232,13 @@
         </is>
       </c>
       <c r="K707" s="1" t="n">
-        <v>46321.58333333334</v>
+        <v>46319.75</v>
       </c>
       <c r="L707" s="1" t="n">
-        <v>46321.64583333334</v>
+        <v>46319.8125</v>
       </c>
       <c r="M707" s="1" t="n">
-        <v>46322.0625</v>
+        <v>46320.22916666666</v>
       </c>
     </row>
     <row r="708">
@@ -39287,13 +39287,13 @@
         </is>
       </c>
       <c r="K708" s="1" t="n">
-        <v>46322.33333333334</v>
+        <v>46320.5</v>
       </c>
       <c r="L708" s="1" t="n">
-        <v>46322.35416666666</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="M708" s="1" t="n">
-        <v>46322.95833333334</v>
+        <v>46321.125</v>
       </c>
     </row>
     <row r="709">
@@ -39342,13 +39342,13 @@
         </is>
       </c>
       <c r="K709" s="1" t="n">
-        <v>46327.875</v>
+        <v>46325.95833333334</v>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46328.04166666666</v>
+        <v>46326.125</v>
       </c>
       <c r="M709" s="1" t="n">
-        <v>46328.625</v>
+        <v>46326.70833333334</v>
       </c>
     </row>
     <row r="710">
@@ -39397,13 +39397,13 @@
         </is>
       </c>
       <c r="K710" s="1" t="n">
-        <v>46330.27083333334</v>
+        <v>46328.3125</v>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46330.3125</v>
+        <v>46328.35416666666</v>
       </c>
       <c r="M710" s="1" t="n">
-        <v>46330.66666666666</v>
+        <v>46328.70833333334</v>
       </c>
     </row>
     <row r="711">
@@ -39452,13 +39452,13 @@
         </is>
       </c>
       <c r="K711" s="1" t="n">
-        <v>46330.79166666666</v>
+        <v>46328.83333333334</v>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46330.875</v>
+        <v>46328.91666666666</v>
       </c>
       <c r="M711" s="1" t="n">
-        <v>46331.875</v>
+        <v>46329.91666666666</v>
       </c>
     </row>
     <row r="712">
@@ -39507,13 +39507,13 @@
         </is>
       </c>
       <c r="K712" s="1" t="n">
-        <v>46332.08333333334</v>
+        <v>46330.125</v>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46332.125</v>
+        <v>46330.16666666666</v>
       </c>
       <c r="M712" s="1" t="n">
-        <v>46332.625</v>
+        <v>46330.66666666666</v>
       </c>
     </row>
     <row r="713">
@@ -39562,13 +39562,13 @@
         </is>
       </c>
       <c r="K713" s="1" t="n">
-        <v>46334.4375</v>
+        <v>46332.47916666666</v>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46334.60416666666</v>
+        <v>46332.64583333334</v>
       </c>
       <c r="M713" s="1" t="n">
-        <v>46335.29166666666</v>
+        <v>46333.33333333334</v>
       </c>
     </row>
     <row r="714">
@@ -39617,13 +39617,13 @@
         </is>
       </c>
       <c r="K714" s="1" t="n">
-        <v>46341.79166666666</v>
+        <v>46338.25</v>
       </c>
       <c r="L714" s="1" t="n">
-        <v>46341.83333333334</v>
+        <v>46338.29166666666</v>
       </c>
       <c r="M714" s="1" t="n">
-        <v>46342.5</v>
+        <v>46338.95833333334</v>
       </c>
     </row>
     <row r="715">
@@ -39672,13 +39672,13 @@
         </is>
       </c>
       <c r="K715" s="1" t="n">
-        <v>46342.66666666666</v>
+        <v>46339.125</v>
       </c>
       <c r="L715" s="1" t="n">
-        <v>46342.72916666666</v>
+        <v>46339.1875</v>
       </c>
       <c r="M715" s="1" t="n">
-        <v>46342.97916666666</v>
+        <v>46339.4375</v>
       </c>
     </row>
     <row r="716">
@@ -39727,13 +39727,13 @@
         </is>
       </c>
       <c r="K716" s="1" t="n">
-        <v>46343.875</v>
+        <v>46340.33333333334</v>
       </c>
       <c r="L716" s="1" t="n">
-        <v>46343.9375</v>
+        <v>46340.39583333334</v>
       </c>
       <c r="M716" s="1" t="n">
-        <v>46344.35416666666</v>
+        <v>46340.8125</v>
       </c>
     </row>
     <row r="717">
@@ -39782,13 +39782,13 @@
         </is>
       </c>
       <c r="K717" s="1" t="n">
-        <v>46344.625</v>
+        <v>46341.08333333334</v>
       </c>
       <c r="L717" s="1" t="n">
-        <v>46344.64583333334</v>
+        <v>46341.10416666666</v>
       </c>
       <c r="M717" s="1" t="n">
-        <v>46345.25</v>
+        <v>46341.70833333334</v>
       </c>
     </row>
     <row r="718">
@@ -39837,13 +39837,13 @@
         </is>
       </c>
       <c r="K718" s="1" t="n">
-        <v>46350.16666666666</v>
+        <v>46346.54166666666</v>
       </c>
       <c r="L718" s="1" t="n">
-        <v>46350.33333333334</v>
+        <v>46346.70833333334</v>
       </c>
       <c r="M718" s="1" t="n">
-        <v>46350.91666666666</v>
+        <v>46347.29166666666</v>
       </c>
     </row>
     <row r="719">
@@ -39892,13 +39892,13 @@
         </is>
       </c>
       <c r="K719" s="1" t="n">
-        <v>46352.5625</v>
+        <v>46348.93958333333</v>
       </c>
       <c r="L719" s="1" t="n">
-        <v>46352.60416666666</v>
+        <v>46348.98125</v>
       </c>
       <c r="M719" s="1" t="n">
-        <v>46352.95833333334</v>
+        <v>46349.33541666667</v>
       </c>
     </row>
     <row r="720">
@@ -39947,13 +39947,13 @@
         </is>
       </c>
       <c r="K720" s="1" t="n">
-        <v>46353.08333333334</v>
+        <v>46349.46041666667</v>
       </c>
       <c r="L720" s="1" t="n">
-        <v>46353.16666666666</v>
+        <v>46349.54375</v>
       </c>
       <c r="M720" s="1" t="n">
-        <v>46354.16666666666</v>
+        <v>46350.54375</v>
       </c>
     </row>
     <row r="721">
@@ -40002,13 +40002,13 @@
         </is>
       </c>
       <c r="K721" s="1" t="n">
-        <v>46354.375</v>
+        <v>46350.75208333333</v>
       </c>
       <c r="L721" s="1" t="n">
-        <v>46354.41666666666</v>
+        <v>46350.79375</v>
       </c>
       <c r="M721" s="1" t="n">
-        <v>46354.91666666666</v>
+        <v>46351.29375</v>
       </c>
     </row>
     <row r="722">
@@ -40053,13 +40053,13 @@
       </c>
       <c r="J722" t="inlineStr"/>
       <c r="K722" s="1" t="n">
-        <v>46356.72916666666</v>
+        <v>46353.10625</v>
       </c>
       <c r="L722" s="1" t="n">
-        <v>46356.89583333334</v>
+        <v>46353.27291666667</v>
       </c>
       <c r="M722" s="1" t="n">
-        <v>46357.58333333334</v>
+        <v>46353.96041666667</v>
       </c>
     </row>
     <row r="723">
@@ -44995,13 +44995,13 @@
         </is>
       </c>
       <c r="K812" s="1" t="n">
-        <v>46298.72916666666</v>
+        <v>46299.375</v>
       </c>
       <c r="L812" s="1" t="n">
-        <v>46298.79166666666</v>
+        <v>46299.4375</v>
       </c>
       <c r="M812" s="1" t="n">
-        <v>46299.04166666666</v>
+        <v>46299.6875</v>
       </c>
     </row>
     <row r="813">
@@ -45050,13 +45050,13 @@
         </is>
       </c>
       <c r="K813" s="1" t="n">
-        <v>46299.97916666666</v>
+        <v>46300.70833333334</v>
       </c>
       <c r="L813" s="1" t="n">
-        <v>46300.04166666666</v>
+        <v>46300.77083333334</v>
       </c>
       <c r="M813" s="1" t="n">
-        <v>46300.45833333334</v>
+        <v>46301.1875</v>
       </c>
     </row>
     <row r="814">
@@ -45105,13 +45105,13 @@
         </is>
       </c>
       <c r="K814" s="1" t="n">
-        <v>46300.79166666666</v>
+        <v>46301.54166666666</v>
       </c>
       <c r="L814" s="1" t="n">
-        <v>46300.83333333334</v>
+        <v>46301.58333333334</v>
       </c>
       <c r="M814" s="1" t="n">
-        <v>46301.45833333334</v>
+        <v>46302.20833333334</v>
       </c>
     </row>
     <row r="815">
@@ -45160,13 +45160,13 @@
         </is>
       </c>
       <c r="K815" s="1" t="n">
-        <v>46302.54166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="L815" s="1" t="n">
-        <v>46304.70833333334</v>
+        <v>46306</v>
       </c>
       <c r="M815" s="1" t="n">
-        <v>46305.70833333334</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="816">
@@ -45215,13 +45215,13 @@
         </is>
       </c>
       <c r="K816" s="1" t="n">
-        <v>46309.91666666666</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="L816" s="1" t="n">
-        <v>46311.04166666666</v>
+        <v>46312.33333333334</v>
       </c>
       <c r="M816" s="1" t="n">
-        <v>46311.54166666666</v>
+        <v>46312.83333333334</v>
       </c>
     </row>
     <row r="817">
@@ -45270,13 +45270,13 @@
         </is>
       </c>
       <c r="K817" s="1" t="n">
-        <v>46313.125</v>
+        <v>46314.41666666666</v>
       </c>
       <c r="L817" s="1" t="n">
-        <v>46313.16666666666</v>
+        <v>46314.45833333334</v>
       </c>
       <c r="M817" s="1" t="n">
-        <v>46313.58333333334</v>
+        <v>46314.875</v>
       </c>
     </row>
     <row r="818">
@@ -45325,13 +45325,13 @@
         </is>
       </c>
       <c r="K818" s="1" t="n">
-        <v>46313.75</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="L818" s="1" t="n">
-        <v>46313.875</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="M818" s="1" t="n">
-        <v>46314.875</v>
+        <v>46316.16666666666</v>
       </c>
     </row>
     <row r="819">
@@ -45380,13 +45380,13 @@
         </is>
       </c>
       <c r="K819" s="1" t="n">
-        <v>46315.125</v>
+        <v>46316.41666666666</v>
       </c>
       <c r="L819" s="1" t="n">
-        <v>46315.16666666666</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="M819" s="1" t="n">
-        <v>46315.58333333334</v>
+        <v>46316.875</v>
       </c>
     </row>
     <row r="820">
@@ -45435,13 +45435,13 @@
         </is>
       </c>
       <c r="K820" s="1" t="n">
-        <v>46317.08333333334</v>
+        <v>46318.375</v>
       </c>
       <c r="L820" s="1" t="n">
-        <v>46318.20833333334</v>
+        <v>46319.5</v>
       </c>
       <c r="M820" s="1" t="n">
-        <v>46318.70833333334</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="821">
@@ -45490,13 +45490,13 @@
         </is>
       </c>
       <c r="K821" s="1" t="n">
-        <v>46324.6875</v>
+        <v>46326.02083333334</v>
       </c>
       <c r="L821" s="1" t="n">
-        <v>46324.75</v>
+        <v>46326.08333333334</v>
       </c>
       <c r="M821" s="1" t="n">
-        <v>46325</v>
+        <v>46326.33333333334</v>
       </c>
     </row>
     <row r="822">
@@ -45545,13 +45545,13 @@
         </is>
       </c>
       <c r="K822" s="1" t="n">
-        <v>46325.9375</v>
+        <v>46327.29166666666</v>
       </c>
       <c r="L822" s="1" t="n">
-        <v>46326</v>
+        <v>46327.35416666666</v>
       </c>
       <c r="M822" s="1" t="n">
-        <v>46326.41666666666</v>
+        <v>46327.77083333334</v>
       </c>
     </row>
     <row r="823">
@@ -45600,13 +45600,13 @@
         </is>
       </c>
       <c r="K823" s="1" t="n">
-        <v>46326.75</v>
+        <v>46328.125</v>
       </c>
       <c r="L823" s="1" t="n">
-        <v>46326.79166666666</v>
+        <v>46328.16666666666</v>
       </c>
       <c r="M823" s="1" t="n">
-        <v>46327.41666666666</v>
+        <v>46328.79166666666</v>
       </c>
     </row>
     <row r="824">
@@ -45655,13 +45655,13 @@
         </is>
       </c>
       <c r="K824" s="1" t="n">
-        <v>46328.5</v>
+        <v>46329.875</v>
       </c>
       <c r="L824" s="1" t="n">
-        <v>46328.66666666666</v>
+        <v>46330.04166666666</v>
       </c>
       <c r="M824" s="1" t="n">
-        <v>46329.66666666666</v>
+        <v>46331.04166666666</v>
       </c>
     </row>
     <row r="825">
@@ -45710,13 +45710,13 @@
         </is>
       </c>
       <c r="K825" s="1" t="n">
-        <v>46333.875</v>
+        <v>46335.25</v>
       </c>
       <c r="L825" s="1" t="n">
-        <v>46334</v>
+        <v>46335.375</v>
       </c>
       <c r="M825" s="1" t="n">
-        <v>46334.5</v>
+        <v>46335.875</v>
       </c>
     </row>
     <row r="826">
@@ -45765,13 +45765,13 @@
         </is>
       </c>
       <c r="K826" s="1" t="n">
-        <v>46336.08333333334</v>
+        <v>46337.45833333334</v>
       </c>
       <c r="L826" s="1" t="n">
-        <v>46336.125</v>
+        <v>46337.5</v>
       </c>
       <c r="M826" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46337.91666666666</v>
       </c>
     </row>
     <row r="827">
@@ -45820,13 +45820,13 @@
         </is>
       </c>
       <c r="K827" s="1" t="n">
-        <v>46336.70833333334</v>
+        <v>46338.08333333334</v>
       </c>
       <c r="L827" s="1" t="n">
-        <v>46336.83333333334</v>
+        <v>46338.20833333334</v>
       </c>
       <c r="M827" s="1" t="n">
-        <v>46337.83333333334</v>
+        <v>46339.20833333334</v>
       </c>
     </row>
     <row r="828">
@@ -45875,13 +45875,13 @@
         </is>
       </c>
       <c r="K828" s="1" t="n">
-        <v>46338.08333333334</v>
+        <v>46339.45833333334</v>
       </c>
       <c r="L828" s="1" t="n">
-        <v>46338.125</v>
+        <v>46339.5</v>
       </c>
       <c r="M828" s="1" t="n">
-        <v>46338.54166666666</v>
+        <v>46339.91666666666</v>
       </c>
     </row>
     <row r="829">
@@ -45930,13 +45930,13 @@
         </is>
       </c>
       <c r="K829" s="1" t="n">
-        <v>46340.04166666666</v>
+        <v>46341.41666666666</v>
       </c>
       <c r="L829" s="1" t="n">
-        <v>46340.16666666666</v>
+        <v>46341.54166666666</v>
       </c>
       <c r="M829" s="1" t="n">
-        <v>46340.66666666666</v>
+        <v>46342.04166666666</v>
       </c>
     </row>
     <row r="830">
@@ -45985,13 +45985,13 @@
         </is>
       </c>
       <c r="K830" s="1" t="n">
-        <v>46345.6875</v>
+        <v>46347.0625</v>
       </c>
       <c r="L830" s="1" t="n">
-        <v>46345.75</v>
+        <v>46347.125</v>
       </c>
       <c r="M830" s="1" t="n">
-        <v>46346</v>
+        <v>46347.375</v>
       </c>
     </row>
     <row r="831">
@@ -46040,13 +46040,13 @@
         </is>
       </c>
       <c r="K831" s="1" t="n">
-        <v>46346.9375</v>
+        <v>46348.32083333333</v>
       </c>
       <c r="L831" s="1" t="n">
-        <v>46347</v>
+        <v>46348.38333333333</v>
       </c>
       <c r="M831" s="1" t="n">
-        <v>46347.41666666666</v>
+        <v>46348.8</v>
       </c>
     </row>
     <row r="832">
@@ -46095,13 +46095,13 @@
         </is>
       </c>
       <c r="K832" s="1" t="n">
-        <v>46347.75</v>
+        <v>46349.14166666667</v>
       </c>
       <c r="L832" s="1" t="n">
-        <v>46347.79166666666</v>
+        <v>46349.18333333333</v>
       </c>
       <c r="M832" s="1" t="n">
-        <v>46348.41666666666</v>
+        <v>46349.80833333333</v>
       </c>
     </row>
     <row r="833">
@@ -46150,13 +46150,13 @@
         </is>
       </c>
       <c r="K833" s="1" t="n">
-        <v>46349.5</v>
+        <v>46350.89166666667</v>
       </c>
       <c r="L833" s="1" t="n">
-        <v>46349.66666666666</v>
+        <v>46351.05833333333</v>
       </c>
       <c r="M833" s="1" t="n">
-        <v>46350.66666666666</v>
+        <v>46352.05833333333</v>
       </c>
     </row>
     <row r="834">
@@ -46205,13 +46205,13 @@
         </is>
       </c>
       <c r="K834" s="1" t="n">
-        <v>46354.875</v>
+        <v>46356.26666666667</v>
       </c>
       <c r="L834" s="1" t="n">
-        <v>46355</v>
+        <v>46356.39166666667</v>
       </c>
       <c r="M834" s="1" t="n">
-        <v>46355.5</v>
+        <v>46356.89166666667</v>
       </c>
     </row>
     <row r="835">
@@ -46260,13 +46260,13 @@
         </is>
       </c>
       <c r="K835" s="1" t="n">
-        <v>46357.08333333334</v>
+        <v>46358.475</v>
       </c>
       <c r="L835" s="1" t="n">
-        <v>46357.125</v>
+        <v>46358.51666666667</v>
       </c>
       <c r="M835" s="1" t="n">
-        <v>46357.54166666666</v>
+        <v>46358.93333333333</v>
       </c>
     </row>
     <row r="836">
@@ -46315,13 +46315,13 @@
         </is>
       </c>
       <c r="K836" s="1" t="n">
-        <v>46357.70833333334</v>
+        <v>46359.1</v>
       </c>
       <c r="L836" s="1" t="n">
-        <v>46357.83333333334</v>
+        <v>46359.225</v>
       </c>
       <c r="M836" s="1" t="n">
-        <v>46358.83333333334</v>
+        <v>46360.225</v>
       </c>
     </row>
     <row r="837">
@@ -46370,13 +46370,13 @@
         </is>
       </c>
       <c r="K837" s="1" t="n">
-        <v>46359.08333333334</v>
+        <v>46360.475</v>
       </c>
       <c r="L837" s="1" t="n">
-        <v>46359.125</v>
+        <v>46360.51666666667</v>
       </c>
       <c r="M837" s="1" t="n">
-        <v>46359.54166666666</v>
+        <v>46360.93333333333</v>
       </c>
     </row>
     <row r="838">
@@ -46421,13 +46421,13 @@
       </c>
       <c r="J838" t="inlineStr"/>
       <c r="K838" s="1" t="n">
-        <v>46361.04166666666</v>
+        <v>46362.43333333333</v>
       </c>
       <c r="L838" s="1" t="n">
-        <v>46361.16666666666</v>
+        <v>46362.55833333333</v>
       </c>
       <c r="M838" s="1" t="n">
-        <v>46361.66666666666</v>
+        <v>46363.05833333333</v>
       </c>
     </row>
     <row r="839">
@@ -46974,10 +46974,10 @@
         <v>46299.33333333334</v>
       </c>
       <c r="L848" s="1" t="n">
-        <v>46299.375</v>
+        <v>46301.5</v>
       </c>
       <c r="M848" s="1" t="n">
-        <v>46300.20833333334</v>
+        <v>46302.33333333334</v>
       </c>
     </row>
     <row r="849">
@@ -47026,13 +47026,13 @@
         </is>
       </c>
       <c r="K849" s="1" t="n">
-        <v>46300.9375</v>
+        <v>46303.0625</v>
       </c>
       <c r="L849" s="1" t="n">
-        <v>46301.02083333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="M849" s="1" t="n">
-        <v>46301.91666666666</v>
+        <v>46304.04166666666</v>
       </c>
     </row>
     <row r="850">
@@ -47081,13 +47081,13 @@
         </is>
       </c>
       <c r="K850" s="1" t="n">
-        <v>46305.64583333334</v>
+        <v>46307.77083333334</v>
       </c>
       <c r="L850" s="1" t="n">
-        <v>46305.6875</v>
+        <v>46307.8125</v>
       </c>
       <c r="M850" s="1" t="n">
-        <v>46306.35416666666</v>
+        <v>46308.47916666666</v>
       </c>
     </row>
     <row r="851">
@@ -47136,13 +47136,13 @@
         </is>
       </c>
       <c r="K851" s="1" t="n">
-        <v>46312.41666666666</v>
+        <v>46314.54166666666</v>
       </c>
       <c r="L851" s="1" t="n">
-        <v>46312.625</v>
+        <v>46314.75</v>
       </c>
       <c r="M851" s="1" t="n">
-        <v>46313.29166666666</v>
+        <v>46315.41666666666</v>
       </c>
     </row>
     <row r="852">
@@ -47191,13 +47191,13 @@
         </is>
       </c>
       <c r="K852" s="1" t="n">
-        <v>46314.6875</v>
+        <v>46316.8125</v>
       </c>
       <c r="L852" s="1" t="n">
-        <v>46314.72916666666</v>
+        <v>46316.85416666666</v>
       </c>
       <c r="M852" s="1" t="n">
-        <v>46315.72916666666</v>
+        <v>46317.85416666666</v>
       </c>
     </row>
     <row r="853">
@@ -47246,13 +47246,13 @@
         </is>
       </c>
       <c r="K853" s="1" t="n">
-        <v>46316.02083333334</v>
+        <v>46318.14583333334</v>
       </c>
       <c r="L853" s="1" t="n">
-        <v>46316.0625</v>
+        <v>46318.1875</v>
       </c>
       <c r="M853" s="1" t="n">
-        <v>46316.6875</v>
+        <v>46318.8125</v>
       </c>
     </row>
     <row r="854">
@@ -47301,13 +47301,13 @@
         </is>
       </c>
       <c r="K854" s="1" t="n">
-        <v>46318.1875</v>
+        <v>46320.3125</v>
       </c>
       <c r="L854" s="1" t="n">
-        <v>46318.39583333334</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="M854" s="1" t="n">
-        <v>46319.0625</v>
+        <v>46321.1875</v>
       </c>
     </row>
     <row r="855">
@@ -47356,13 +47356,13 @@
         </is>
       </c>
       <c r="K855" s="1" t="n">
-        <v>46326.0625</v>
+        <v>46328.1875</v>
       </c>
       <c r="L855" s="1" t="n">
-        <v>46326.14583333334</v>
+        <v>46328.27083333334</v>
       </c>
       <c r="M855" s="1" t="n">
-        <v>46326.97916666666</v>
+        <v>46329.10416666666</v>
       </c>
     </row>
     <row r="856">
@@ -47411,13 +47411,13 @@
         </is>
       </c>
       <c r="K856" s="1" t="n">
-        <v>46328.0625</v>
+        <v>46330.1875</v>
       </c>
       <c r="L856" s="1" t="n">
-        <v>46328.14583333334</v>
+        <v>46330.27083333334</v>
       </c>
       <c r="M856" s="1" t="n">
-        <v>46328.64583333334</v>
+        <v>46330.77083333334</v>
       </c>
     </row>
     <row r="857">
@@ -47466,13 +47466,13 @@
         </is>
       </c>
       <c r="K857" s="1" t="n">
-        <v>46332.64583333334</v>
+        <v>46334.77083333334</v>
       </c>
       <c r="L857" s="1" t="n">
-        <v>46332.6875</v>
+        <v>46334.8125</v>
       </c>
       <c r="M857" s="1" t="n">
-        <v>46333.35416666666</v>
+        <v>46335.47916666666</v>
       </c>
     </row>
     <row r="858">
@@ -47521,13 +47521,13 @@
         </is>
       </c>
       <c r="K858" s="1" t="n">
-        <v>46339.77083333334</v>
+        <v>46341.89583333334</v>
       </c>
       <c r="L858" s="1" t="n">
-        <v>46339.97916666666</v>
+        <v>46342.10416666666</v>
       </c>
       <c r="M858" s="1" t="n">
-        <v>46340.64583333334</v>
+        <v>46342.77083333334</v>
       </c>
     </row>
     <row r="859">
@@ -47576,13 +47576,13 @@
         </is>
       </c>
       <c r="K859" s="1" t="n">
-        <v>46342.10416666666</v>
+        <v>46344.22916666666</v>
       </c>
       <c r="L859" s="1" t="n">
-        <v>46342.14583333334</v>
+        <v>46344.27083333334</v>
       </c>
       <c r="M859" s="1" t="n">
-        <v>46343.14583333334</v>
+        <v>46345.27083333334</v>
       </c>
     </row>
     <row r="860">
@@ -47631,13 +47631,13 @@
         </is>
       </c>
       <c r="K860" s="1" t="n">
-        <v>46343.77083333334</v>
+        <v>46345.89583333334</v>
       </c>
       <c r="L860" s="1" t="n">
-        <v>46343.8125</v>
+        <v>46345.9375</v>
       </c>
       <c r="M860" s="1" t="n">
-        <v>46344.4375</v>
+        <v>46346.5625</v>
       </c>
     </row>
     <row r="861">
@@ -47686,13 +47686,13 @@
         </is>
       </c>
       <c r="K861" s="1" t="n">
-        <v>46345.9375</v>
+        <v>46348.0625</v>
       </c>
       <c r="L861" s="1" t="n">
-        <v>46346.14583333334</v>
+        <v>46348.27083333334</v>
       </c>
       <c r="M861" s="1" t="n">
-        <v>46346.8125</v>
+        <v>46348.9375</v>
       </c>
     </row>
     <row r="862">
@@ -47741,13 +47741,13 @@
         </is>
       </c>
       <c r="K862" s="1" t="n">
-        <v>46353.8125</v>
+        <v>46355.9375</v>
       </c>
       <c r="L862" s="1" t="n">
-        <v>46353.89583333334</v>
+        <v>46356.02083333334</v>
       </c>
       <c r="M862" s="1" t="n">
-        <v>46354.72916666666</v>
+        <v>46356.85416666666</v>
       </c>
     </row>
     <row r="863">
@@ -47796,13 +47796,13 @@
         </is>
       </c>
       <c r="K863" s="1" t="n">
-        <v>46355.8125</v>
+        <v>46357.9375</v>
       </c>
       <c r="L863" s="1" t="n">
-        <v>46355.89583333334</v>
+        <v>46358.02083333334</v>
       </c>
       <c r="M863" s="1" t="n">
-        <v>46356.39583333334</v>
+        <v>46358.52083333334</v>
       </c>
     </row>
     <row r="864">
@@ -47851,13 +47851,13 @@
         </is>
       </c>
       <c r="K864" s="1" t="n">
-        <v>46360.39583333334</v>
+        <v>46362.52083333334</v>
       </c>
       <c r="L864" s="1" t="n">
-        <v>46360.4375</v>
+        <v>46362.5625</v>
       </c>
       <c r="M864" s="1" t="n">
-        <v>46361.10416666666</v>
+        <v>46363.22916666666</v>
       </c>
     </row>
     <row r="865">
@@ -47902,13 +47902,13 @@
       </c>
       <c r="J865" t="inlineStr"/>
       <c r="K865" s="1" t="n">
-        <v>46367.52083333334</v>
+        <v>46369.64583333334</v>
       </c>
       <c r="L865" s="1" t="n">
-        <v>46367.72916666666</v>
+        <v>46369.85416666666</v>
       </c>
       <c r="M865" s="1" t="n">
-        <v>46368.39583333334</v>
+        <v>46370.52083333334</v>
       </c>
     </row>
     <row r="866">
@@ -53452,10 +53452,10 @@
         <v>46294.97916666666</v>
       </c>
       <c r="L966" s="1" t="n">
-        <v>46295.58333333334</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="M966" s="1" t="n">
-        <v>46297.08333333334</v>
+        <v>46296.41666666666</v>
       </c>
     </row>
     <row r="967">
@@ -53504,13 +53504,13 @@
         </is>
       </c>
       <c r="K967" s="1" t="n">
-        <v>46297.79166666666</v>
+        <v>46297.125</v>
       </c>
       <c r="L967" s="1" t="n">
-        <v>46297.875</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="M967" s="1" t="n">
-        <v>46298.375</v>
+        <v>46297.70833333334</v>
       </c>
     </row>
     <row r="968">
@@ -53559,13 +53559,13 @@
         </is>
       </c>
       <c r="K968" s="1" t="n">
-        <v>46302.10416666666</v>
+        <v>46301.4375</v>
       </c>
       <c r="L968" s="1" t="n">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="M968" s="1" t="n">
         <v>46302.14583333334</v>
-      </c>
-      <c r="M968" s="1" t="n">
-        <v>46302.8125</v>
       </c>
     </row>
     <row r="969">
@@ -53614,13 +53614,13 @@
         </is>
       </c>
       <c r="K969" s="1" t="n">
-        <v>46308.875</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="L969" s="1" t="n">
+        <v>46308.41666666666</v>
+      </c>
+      <c r="M969" s="1" t="n">
         <v>46309.08333333334</v>
-      </c>
-      <c r="M969" s="1" t="n">
-        <v>46309.75</v>
       </c>
     </row>
     <row r="970">
@@ -53669,13 +53669,13 @@
         </is>
       </c>
       <c r="K970" s="1" t="n">
-        <v>46311.14583333334</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="L970" s="1" t="n">
-        <v>46311.1875</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="M970" s="1" t="n">
-        <v>46312.1875</v>
+        <v>46311.52083333334</v>
       </c>
     </row>
     <row r="971">
@@ -53724,13 +53724,13 @@
         </is>
       </c>
       <c r="K971" s="1" t="n">
+        <v>46311.8125</v>
+      </c>
+      <c r="L971" s="1" t="n">
+        <v>46311.85416666666</v>
+      </c>
+      <c r="M971" s="1" t="n">
         <v>46312.47916666666</v>
-      </c>
-      <c r="L971" s="1" t="n">
-        <v>46312.52083333334</v>
-      </c>
-      <c r="M971" s="1" t="n">
-        <v>46313.14583333334</v>
       </c>
     </row>
     <row r="972">
@@ -53779,13 +53779,13 @@
         </is>
       </c>
       <c r="K972" s="1" t="n">
-        <v>46314.60416666666</v>
+        <v>46313.9375</v>
       </c>
       <c r="L972" s="1" t="n">
+        <v>46314.14583333334</v>
+      </c>
+      <c r="M972" s="1" t="n">
         <v>46314.8125</v>
-      </c>
-      <c r="M972" s="1" t="n">
-        <v>46315.47916666666</v>
       </c>
     </row>
     <row r="973">
@@ -53834,13 +53834,13 @@
         </is>
       </c>
       <c r="K973" s="1" t="n">
-        <v>46322.47916666666</v>
+        <v>46321.8125</v>
       </c>
       <c r="L973" s="1" t="n">
-        <v>46322.5625</v>
+        <v>46321.89583333334</v>
       </c>
       <c r="M973" s="1" t="n">
-        <v>46323.39583333334</v>
+        <v>46322.72916666666</v>
       </c>
     </row>
     <row r="974">
@@ -53889,13 +53889,13 @@
         </is>
       </c>
       <c r="K974" s="1" t="n">
-        <v>46324.47916666666</v>
+        <v>46323.8125</v>
       </c>
       <c r="L974" s="1" t="n">
-        <v>46324.5625</v>
+        <v>46323.89583333334</v>
       </c>
       <c r="M974" s="1" t="n">
-        <v>46325.0625</v>
+        <v>46324.39583333334</v>
       </c>
     </row>
     <row r="975">
@@ -53944,13 +53944,13 @@
         </is>
       </c>
       <c r="K975" s="1" t="n">
-        <v>46329.0625</v>
+        <v>46328.39583333334</v>
       </c>
       <c r="L975" s="1" t="n">
+        <v>46328.4375</v>
+      </c>
+      <c r="M975" s="1" t="n">
         <v>46329.10416666666</v>
-      </c>
-      <c r="M975" s="1" t="n">
-        <v>46329.77083333334</v>
       </c>
     </row>
     <row r="976">
@@ -53999,13 +53999,13 @@
         </is>
       </c>
       <c r="K976" s="1" t="n">
-        <v>46336.1875</v>
+        <v>46335.52083333334</v>
       </c>
       <c r="L976" s="1" t="n">
+        <v>46335.72916666666</v>
+      </c>
+      <c r="M976" s="1" t="n">
         <v>46336.39583333334</v>
-      </c>
-      <c r="M976" s="1" t="n">
-        <v>46337.0625</v>
       </c>
     </row>
     <row r="977">
@@ -54054,13 +54054,13 @@
         </is>
       </c>
       <c r="K977" s="1" t="n">
-        <v>46338.77083333334</v>
+        <v>46338.10416666666</v>
       </c>
       <c r="L977" s="1" t="n">
-        <v>46338.8125</v>
+        <v>46338.14583333334</v>
       </c>
       <c r="M977" s="1" t="n">
-        <v>46339.8125</v>
+        <v>46339.14583333334</v>
       </c>
     </row>
     <row r="978">
@@ -54109,13 +54109,13 @@
         </is>
       </c>
       <c r="K978" s="1" t="n">
+        <v>46339.77083333334</v>
+      </c>
+      <c r="L978" s="1" t="n">
+        <v>46339.8125</v>
+      </c>
+      <c r="M978" s="1" t="n">
         <v>46340.4375</v>
-      </c>
-      <c r="L978" s="1" t="n">
-        <v>46340.47916666666</v>
-      </c>
-      <c r="M978" s="1" t="n">
-        <v>46341.10416666666</v>
       </c>
     </row>
     <row r="979">
@@ -54164,13 +54164,13 @@
         </is>
       </c>
       <c r="K979" s="1" t="n">
-        <v>46342.60416666666</v>
+        <v>46341.9375</v>
       </c>
       <c r="L979" s="1" t="n">
+        <v>46342.14583333334</v>
+      </c>
+      <c r="M979" s="1" t="n">
         <v>46342.8125</v>
-      </c>
-      <c r="M979" s="1" t="n">
-        <v>46343.47916666666</v>
       </c>
     </row>
     <row r="980">
@@ -54219,13 +54219,13 @@
         </is>
       </c>
       <c r="K980" s="1" t="n">
-        <v>46350.47916666666</v>
+        <v>46349.8125</v>
       </c>
       <c r="L980" s="1" t="n">
-        <v>46350.5625</v>
+        <v>46349.89583333334</v>
       </c>
       <c r="M980" s="1" t="n">
-        <v>46351.39583333334</v>
+        <v>46350.72916666666</v>
       </c>
     </row>
     <row r="981">
@@ -54274,13 +54274,13 @@
         </is>
       </c>
       <c r="K981" s="1" t="n">
-        <v>46352.47916666666</v>
+        <v>46351.8125</v>
       </c>
       <c r="L981" s="1" t="n">
-        <v>46352.5625</v>
+        <v>46351.89583333334</v>
       </c>
       <c r="M981" s="1" t="n">
-        <v>46353.0625</v>
+        <v>46352.39583333334</v>
       </c>
     </row>
     <row r="982">
@@ -54329,13 +54329,13 @@
         </is>
       </c>
       <c r="K982" s="1" t="n">
-        <v>46357.0625</v>
+        <v>46356.39583333334</v>
       </c>
       <c r="L982" s="1" t="n">
+        <v>46356.4375</v>
+      </c>
+      <c r="M982" s="1" t="n">
         <v>46357.10416666666</v>
-      </c>
-      <c r="M982" s="1" t="n">
-        <v>46357.77083333334</v>
       </c>
     </row>
     <row r="983">
@@ -54380,13 +54380,13 @@
       </c>
       <c r="J983" t="inlineStr"/>
       <c r="K983" s="1" t="n">
-        <v>46364.1875</v>
+        <v>46363.52083333334</v>
       </c>
       <c r="L983" s="1" t="n">
+        <v>46363.72916666666</v>
+      </c>
+      <c r="M983" s="1" t="n">
         <v>46364.39583333334</v>
-      </c>
-      <c r="M983" s="1" t="n">
-        <v>46365.0625</v>
       </c>
     </row>
     <row r="984">
@@ -57236,13 +57236,13 @@
         </is>
       </c>
       <c r="K1035" s="1" t="n">
-        <v>46290.75</v>
+        <v>46291.41666666666</v>
       </c>
       <c r="L1035" s="1" t="n">
         <v>46291.45833333334</v>
       </c>
       <c r="M1035" s="1" t="n">
-        <v>46293.45833333334</v>
+        <v>46293.04166666666</v>
       </c>
     </row>
     <row r="1036">
@@ -57291,13 +57291,13 @@
         </is>
       </c>
       <c r="K1036" s="1" t="n">
-        <v>46295.85416666666</v>
+        <v>46295.5</v>
       </c>
       <c r="L1036" s="1" t="n">
-        <v>46296.02083333334</v>
+        <v>46295.66666666666</v>
       </c>
       <c r="M1036" s="1" t="n">
-        <v>46296.6875</v>
+        <v>46296.33333333334</v>
       </c>
     </row>
     <row r="1037">
@@ -57346,13 +57346,13 @@
         </is>
       </c>
       <c r="K1037" s="1" t="n">
-        <v>46299.02083333334</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="L1037" s="1" t="n">
-        <v>46299.08333333334</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="M1037" s="1" t="n">
-        <v>46299.58333333334</v>
+        <v>46299.22916666666</v>
       </c>
     </row>
     <row r="1038">
@@ -57401,13 +57401,13 @@
         </is>
       </c>
       <c r="K1038" s="1" t="n">
-        <v>46299.70833333334</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="L1038" s="1" t="n">
-        <v>46299.83333333334</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="M1038" s="1" t="n">
-        <v>46300.29166666666</v>
+        <v>46299.9375</v>
       </c>
     </row>
     <row r="1039">
@@ -57456,13 +57456,13 @@
         </is>
       </c>
       <c r="K1039" s="1" t="n">
-        <v>46303.375</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="L1039" s="1" t="n">
-        <v>46303.41666666666</v>
+        <v>46303.0625</v>
       </c>
       <c r="M1039" s="1" t="n">
-        <v>46304.08333333334</v>
+        <v>46303.72916666666</v>
       </c>
     </row>
     <row r="1040">
@@ -57511,13 +57511,13 @@
         </is>
       </c>
       <c r="K1040" s="1" t="n">
-        <v>46305.16666666666</v>
+        <v>46304.8125</v>
       </c>
       <c r="L1040" s="1" t="n">
-        <v>46305.20833333334</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="M1040" s="1" t="n">
-        <v>46305.79166666666</v>
+        <v>46305.4375</v>
       </c>
     </row>
     <row r="1041">
@@ -57566,13 +57566,13 @@
         </is>
       </c>
       <c r="K1041" s="1" t="n">
-        <v>46305.97916666666</v>
+        <v>46305.625</v>
       </c>
       <c r="L1041" s="1" t="n">
-        <v>46306.04166666666</v>
+        <v>46305.6875</v>
       </c>
       <c r="M1041" s="1" t="n">
-        <v>46306.375</v>
+        <v>46306.02083333334</v>
       </c>
     </row>
     <row r="1042">
@@ -57621,13 +57621,13 @@
         </is>
       </c>
       <c r="K1042" s="1" t="n">
-        <v>46307.66666666666</v>
+        <v>46307.3125</v>
       </c>
       <c r="L1042" s="1" t="n">
-        <v>46307.83333333334</v>
+        <v>46307.47916666666</v>
       </c>
       <c r="M1042" s="1" t="n">
-        <v>46308.33333333334</v>
+        <v>46307.97916666666</v>
       </c>
     </row>
     <row r="1043">
@@ -57676,13 +57676,13 @@
         </is>
       </c>
       <c r="K1043" s="1" t="n">
-        <v>46312.5</v>
+        <v>46312.14583333334</v>
       </c>
       <c r="L1043" s="1" t="n">
-        <v>46312.66666666666</v>
+        <v>46312.3125</v>
       </c>
       <c r="M1043" s="1" t="n">
-        <v>46313.5</v>
+        <v>46313.14583333334</v>
       </c>
     </row>
     <row r="1044">
@@ -57731,13 +57731,13 @@
         </is>
       </c>
       <c r="K1044" s="1" t="n">
-        <v>46315.16666666666</v>
+        <v>46314.8125</v>
       </c>
       <c r="L1044" s="1" t="n">
-        <v>46315.20833333334</v>
+        <v>46314.85416666666</v>
       </c>
       <c r="M1044" s="1" t="n">
-        <v>46316.04166666666</v>
+        <v>46315.6875</v>
       </c>
     </row>
     <row r="1045">
@@ -57786,13 +57786,13 @@
         </is>
       </c>
       <c r="K1045" s="1" t="n">
-        <v>46319.20833333334</v>
+        <v>46318.85416666666</v>
       </c>
       <c r="L1045" s="1" t="n">
-        <v>46319.29166666666</v>
+        <v>46318.9375</v>
       </c>
       <c r="M1045" s="1" t="n">
-        <v>46320.95833333334</v>
+        <v>46320.60416666666</v>
       </c>
     </row>
     <row r="1046">
@@ -57841,13 +57841,13 @@
         </is>
       </c>
       <c r="K1046" s="1" t="n">
-        <v>46323.41666666666</v>
+        <v>46323.0625</v>
       </c>
       <c r="L1046" s="1" t="n">
-        <v>46323.58333333334</v>
+        <v>46323.22916666666</v>
       </c>
       <c r="M1046" s="1" t="n">
-        <v>46324.41666666666</v>
+        <v>46324.0625</v>
       </c>
     </row>
     <row r="1047">
@@ -57896,13 +57896,13 @@
         </is>
       </c>
       <c r="K1047" s="1" t="n">
-        <v>46326.95833333334</v>
+        <v>46326.60416666666</v>
       </c>
       <c r="L1047" s="1" t="n">
-        <v>46327.02083333334</v>
+        <v>46326.66666666666</v>
       </c>
       <c r="M1047" s="1" t="n">
-        <v>46327.52083333334</v>
+        <v>46327.16666666666</v>
       </c>
     </row>
     <row r="1048">
@@ -57951,13 +57951,13 @@
         </is>
       </c>
       <c r="K1048" s="1" t="n">
-        <v>46327.75</v>
+        <v>46327.39583333334</v>
       </c>
       <c r="L1048" s="1" t="n">
-        <v>46327.79166666666</v>
+        <v>46327.4375</v>
       </c>
       <c r="M1048" s="1" t="n">
-        <v>46328.29166666666</v>
+        <v>46327.9375</v>
       </c>
     </row>
     <row r="1049">
@@ -58006,13 +58006,13 @@
         </is>
       </c>
       <c r="K1049" s="1" t="n">
-        <v>46331.375</v>
+        <v>46331.02083333334</v>
       </c>
       <c r="L1049" s="1" t="n">
-        <v>46331.41666666666</v>
+        <v>46331.0625</v>
       </c>
       <c r="M1049" s="1" t="n">
-        <v>46332.08333333334</v>
+        <v>46331.72916666666</v>
       </c>
     </row>
     <row r="1050">
@@ -58061,13 +58061,13 @@
         </is>
       </c>
       <c r="K1050" s="1" t="n">
-        <v>46333.16666666666</v>
+        <v>46332.8125</v>
       </c>
       <c r="L1050" s="1" t="n">
-        <v>46333.20833333334</v>
+        <v>46332.85416666666</v>
       </c>
       <c r="M1050" s="1" t="n">
-        <v>46333.79166666666</v>
+        <v>46333.4375</v>
       </c>
     </row>
     <row r="1051">
@@ -58116,13 +58116,13 @@
         </is>
       </c>
       <c r="K1051" s="1" t="n">
-        <v>46333.97916666666</v>
+        <v>46333.625</v>
       </c>
       <c r="L1051" s="1" t="n">
-        <v>46334.04166666666</v>
+        <v>46333.6875</v>
       </c>
       <c r="M1051" s="1" t="n">
-        <v>46334.375</v>
+        <v>46334.02083333334</v>
       </c>
     </row>
     <row r="1052">
@@ -58171,13 +58171,13 @@
         </is>
       </c>
       <c r="K1052" s="1" t="n">
-        <v>46335.66666666666</v>
+        <v>46335.3125</v>
       </c>
       <c r="L1052" s="1" t="n">
-        <v>46335.83333333334</v>
+        <v>46335.47916666666</v>
       </c>
       <c r="M1052" s="1" t="n">
-        <v>46336.33333333334</v>
+        <v>46335.97916666666</v>
       </c>
     </row>
     <row r="1053">
@@ -58226,13 +58226,13 @@
         </is>
       </c>
       <c r="K1053" s="1" t="n">
-        <v>46340.5</v>
+        <v>46340.14583333334</v>
       </c>
       <c r="L1053" s="1" t="n">
-        <v>46340.66666666666</v>
+        <v>46340.3125</v>
       </c>
       <c r="M1053" s="1" t="n">
-        <v>46341.5</v>
+        <v>46341.14583333334</v>
       </c>
     </row>
     <row r="1054">
@@ -58281,13 +58281,13 @@
         </is>
       </c>
       <c r="K1054" s="1" t="n">
-        <v>46343.16666666666</v>
+        <v>46342.8125</v>
       </c>
       <c r="L1054" s="1" t="n">
-        <v>46343.20833333334</v>
+        <v>46342.85416666666</v>
       </c>
       <c r="M1054" s="1" t="n">
-        <v>46344.04166666666</v>
+        <v>46343.6875</v>
       </c>
     </row>
     <row r="1055">
@@ -58336,13 +58336,13 @@
         </is>
       </c>
       <c r="K1055" s="1" t="n">
-        <v>46347.20833333334</v>
+        <v>46346.85416666666</v>
       </c>
       <c r="L1055" s="1" t="n">
-        <v>46347.29166666666</v>
+        <v>46346.9375</v>
       </c>
       <c r="M1055" s="1" t="n">
-        <v>46348.95833333334</v>
+        <v>46348.60416666666</v>
       </c>
     </row>
     <row r="1056">
@@ -58391,13 +58391,13 @@
         </is>
       </c>
       <c r="K1056" s="1" t="n">
-        <v>46351.41666666666</v>
+        <v>46351.0625</v>
       </c>
       <c r="L1056" s="1" t="n">
-        <v>46351.58333333334</v>
+        <v>46351.22916666666</v>
       </c>
       <c r="M1056" s="1" t="n">
-        <v>46352.41666666666</v>
+        <v>46352.0625</v>
       </c>
     </row>
     <row r="1057">
@@ -58446,13 +58446,13 @@
         </is>
       </c>
       <c r="K1057" s="1" t="n">
-        <v>46354.95833333334</v>
+        <v>46354.60416666666</v>
       </c>
       <c r="L1057" s="1" t="n">
-        <v>46355.02083333334</v>
+        <v>46354.66666666666</v>
       </c>
       <c r="M1057" s="1" t="n">
-        <v>46355.52083333334</v>
+        <v>46355.16666666666</v>
       </c>
     </row>
     <row r="1058">
@@ -58497,13 +58497,13 @@
       </c>
       <c r="J1058" t="inlineStr"/>
       <c r="K1058" s="1" t="n">
-        <v>46355.75</v>
+        <v>46355.39583333334</v>
       </c>
       <c r="L1058" s="1" t="n">
-        <v>46355.79166666666</v>
+        <v>46355.4375</v>
       </c>
       <c r="M1058" s="1" t="n">
-        <v>46356.29166666666</v>
+        <v>46355.9375</v>
       </c>
     </row>
     <row r="1059">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -27214,7 +27214,7 @@
         <v>46290.45833333334</v>
       </c>
       <c r="L488" s="1" t="n">
-        <v>46293.79166666666</v>
+        <v>46293.775</v>
       </c>
       <c r="M488" s="1" t="n">
         <v>46296.08333333334</v>
@@ -27269,7 +27269,7 @@
         <v>46290.45833333334</v>
       </c>
       <c r="L489" s="1" t="n">
-        <v>46293.79166666666</v>
+        <v>46293.775</v>
       </c>
       <c r="M489" s="1" t="n">
         <v>46296.08333333334</v>
@@ -55263,10 +55263,10 @@
         <v>46293.29166666666</v>
       </c>
       <c r="L999" s="1" t="n">
-        <v>46293.33333333334</v>
+        <v>46293.4375</v>
       </c>
       <c r="M999" s="1" t="n">
-        <v>46293.66666666666</v>
+        <v>46293.8125</v>
       </c>
     </row>
     <row r="1000">
@@ -55315,13 +55315,13 @@
         </is>
       </c>
       <c r="K1000" s="1" t="n">
+        <v>46297.625</v>
+      </c>
+      <c r="L1000" s="1" t="n">
         <v>46297.6875</v>
       </c>
-      <c r="L1000" s="1" t="n">
-        <v>46297.75</v>
-      </c>
       <c r="M1000" s="1" t="n">
-        <v>46298.25</v>
+        <v>46298.1875</v>
       </c>
     </row>
     <row r="1001">
@@ -55370,13 +55370,13 @@
         </is>
       </c>
       <c r="K1001" s="1" t="n">
+        <v>46299.20833333334</v>
+      </c>
+      <c r="L1001" s="1" t="n">
         <v>46299.27083333334</v>
       </c>
-      <c r="L1001" s="1" t="n">
-        <v>46299.33333333334</v>
-      </c>
       <c r="M1001" s="1" t="n">
-        <v>46299.95833333334</v>
+        <v>46299.89583333334</v>
       </c>
     </row>
     <row r="1002">
@@ -55425,13 +55425,13 @@
         </is>
       </c>
       <c r="K1002" s="1" t="n">
-        <v>46302.3125</v>
+        <v>46302.25</v>
       </c>
       <c r="L1002" s="1" t="n">
-        <v>46302.35416666666</v>
+        <v>46302.29166666666</v>
       </c>
       <c r="M1002" s="1" t="n">
-        <v>46303.0625</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1003">
@@ -55480,13 +55480,13 @@
         </is>
       </c>
       <c r="K1003" s="1" t="n">
+        <v>46303.29166666666</v>
+      </c>
+      <c r="L1003" s="1" t="n">
         <v>46303.35416666666</v>
       </c>
-      <c r="L1003" s="1" t="n">
-        <v>46303.41666666666</v>
-      </c>
       <c r="M1003" s="1" t="n">
-        <v>46303.75</v>
+        <v>46303.6875</v>
       </c>
     </row>
     <row r="1004">
@@ -55535,13 +55535,13 @@
         </is>
       </c>
       <c r="K1004" s="1" t="n">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="L1004" s="1" t="n">
         <v>46306.64583333334</v>
       </c>
-      <c r="L1004" s="1" t="n">
-        <v>46306.70833333334</v>
-      </c>
       <c r="M1004" s="1" t="n">
-        <v>46307.20833333334</v>
+        <v>46307.14583333334</v>
       </c>
     </row>
     <row r="1005">
@@ -55590,13 +55590,13 @@
         </is>
       </c>
       <c r="K1005" s="1" t="n">
-        <v>46309.4375</v>
+        <v>46309.375</v>
       </c>
       <c r="L1005" s="1" t="n">
-        <v>46309.60416666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="M1005" s="1" t="n">
-        <v>46310.22916666666</v>
+        <v>46310.16666666666</v>
       </c>
     </row>
     <row r="1006">
@@ -55645,13 +55645,13 @@
         </is>
       </c>
       <c r="K1006" s="1" t="n">
-        <v>46311.8125</v>
+        <v>46311.75</v>
       </c>
       <c r="L1006" s="1" t="n">
-        <v>46311.85416666666</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="M1006" s="1" t="n">
-        <v>46312.0625</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="1007">
@@ -55700,13 +55700,13 @@
         </is>
       </c>
       <c r="K1007" s="1" t="n">
-        <v>46312.1875</v>
+        <v>46312.125</v>
       </c>
       <c r="L1007" s="1" t="n">
-        <v>46312.3125</v>
+        <v>46312.25</v>
       </c>
       <c r="M1007" s="1" t="n">
-        <v>46313.77083333334</v>
+        <v>46313.70833333334</v>
       </c>
     </row>
     <row r="1008">
@@ -55755,13 +55755,13 @@
         </is>
       </c>
       <c r="K1008" s="1" t="n">
-        <v>46313.97916666666</v>
+        <v>46313.91666666666</v>
       </c>
       <c r="L1008" s="1" t="n">
-        <v>46314.02083333334</v>
+        <v>46313.95833333334</v>
       </c>
       <c r="M1008" s="1" t="n">
-        <v>46314.35416666666</v>
+        <v>46314.29166666666</v>
       </c>
     </row>
     <row r="1009">
@@ -55810,13 +55810,13 @@
         </is>
       </c>
       <c r="K1009" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="L1009" s="1" t="n">
         <v>46318.0625</v>
       </c>
-      <c r="L1009" s="1" t="n">
-        <v>46318.125</v>
-      </c>
       <c r="M1009" s="1" t="n">
-        <v>46318.625</v>
+        <v>46318.5625</v>
       </c>
     </row>
     <row r="1010">
@@ -55865,13 +55865,13 @@
         </is>
       </c>
       <c r="K1010" s="1" t="n">
+        <v>46319.375</v>
+      </c>
+      <c r="L1010" s="1" t="n">
         <v>46319.4375</v>
       </c>
-      <c r="L1010" s="1" t="n">
-        <v>46319.5</v>
-      </c>
       <c r="M1010" s="1" t="n">
-        <v>46320.125</v>
+        <v>46320.0625</v>
       </c>
     </row>
     <row r="1011">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -27327,7 +27327,7 @@
         <v>46293.79166666666</v>
       </c>
       <c r="M490" s="1" t="n">
-        <v>46296.08333333334</v>
+        <v>46296.25</v>
       </c>
     </row>
     <row r="491">
@@ -27431,13 +27431,13 @@
         </is>
       </c>
       <c r="K492" s="1" t="n">
-        <v>46296.375</v>
+        <v>46296.54166666666</v>
       </c>
       <c r="L492" s="1" t="n">
-        <v>46296.4375</v>
+        <v>46296.60416666666</v>
       </c>
       <c r="M492" s="1" t="n">
-        <v>46296.95833333334</v>
+        <v>46297.125</v>
       </c>
     </row>
     <row r="493">
@@ -27486,13 +27486,13 @@
         </is>
       </c>
       <c r="K493" s="1" t="n">
-        <v>46298.41666666666</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="L493" s="1" t="n">
-        <v>46299.5</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="M493" s="1" t="n">
-        <v>46300</v>
+        <v>46300.16666666666</v>
       </c>
     </row>
     <row r="494">
@@ -27541,13 +27541,13 @@
         </is>
       </c>
       <c r="K494" s="1" t="n">
-        <v>46302.95833333334</v>
+        <v>46303.125</v>
       </c>
       <c r="L494" s="1" t="n">
-        <v>46303.08333333334</v>
+        <v>46303.25</v>
       </c>
       <c r="M494" s="1" t="n">
-        <v>46303.5</v>
+        <v>46303.66666666666</v>
       </c>
     </row>
     <row r="495">
@@ -27596,13 +27596,13 @@
         </is>
       </c>
       <c r="K495" s="1" t="n">
-        <v>46315.75</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>46316.83333333334</v>
+        <v>46317</v>
       </c>
       <c r="M495" s="1" t="n">
-        <v>46317.5</v>
+        <v>46317.66666666666</v>
       </c>
     </row>
     <row r="496">
@@ -27651,13 +27651,13 @@
         </is>
       </c>
       <c r="K496" s="1" t="n">
-        <v>46318.75</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="L496" s="1" t="n">
-        <v>46318.83333333334</v>
+        <v>46319</v>
       </c>
       <c r="M496" s="1" t="n">
-        <v>46319.33333333334</v>
+        <v>46319.5</v>
       </c>
     </row>
     <row r="497">
@@ -27706,13 +27706,13 @@
         </is>
       </c>
       <c r="K497" s="1" t="n">
-        <v>46320.25</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>46320.33333333334</v>
+        <v>46320.5</v>
       </c>
       <c r="M497" s="1" t="n">
-        <v>46320.91666666666</v>
+        <v>46321.08333333334</v>
       </c>
     </row>
     <row r="498">
@@ -27761,13 +27761,13 @@
         </is>
       </c>
       <c r="K498" s="1" t="n">
-        <v>46329.79166666666</v>
+        <v>46329.95833333334</v>
       </c>
       <c r="L498" s="1" t="n">
-        <v>46330.83333333334</v>
+        <v>46331</v>
       </c>
       <c r="M498" s="1" t="n">
-        <v>46331.41666666666</v>
+        <v>46331.58333333334</v>
       </c>
     </row>
     <row r="499">
@@ -27812,13 +27812,13 @@
       </c>
       <c r="J499" t="inlineStr"/>
       <c r="K499" s="1" t="n">
-        <v>46340.20833333334</v>
+        <v>46340.375</v>
       </c>
       <c r="L499" s="1" t="n">
-        <v>46340.25</v>
+        <v>46340.41666666666</v>
       </c>
       <c r="M499" s="1" t="n">
-        <v>46341</v>
+        <v>46341.16666666666</v>
       </c>
     </row>
     <row r="500">
@@ -28362,19 +28362,19 @@
         </is>
       </c>
       <c r="K509" s="1" t="n">
-        <v>46295.89583333334</v>
+        <v>46296.5</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>46295.95833333334</v>
+        <v>46296.5625</v>
       </c>
       <c r="M509" s="1" t="n">
-        <v>46296.70833333334</v>
+        <v>46297.3125</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>SIS2</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -28389,21 +28389,21 @@
       </c>
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="n">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>2606N</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -28429,7 +28429,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>SIS2</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -28444,16 +28444,16 @@
       </c>
       <c r="D511" t="inlineStr"/>
       <c r="E511" t="n">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2606N</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -28472,13 +28472,13 @@
         </is>
       </c>
       <c r="K511" s="1" t="n">
-        <v>46302.97916666666</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>46304.14583333334</v>
+        <v>46304.75</v>
       </c>
       <c r="M511" s="1" t="n">
-        <v>46304.97916666666</v>
+        <v>46305.58333333334</v>
       </c>
     </row>
     <row r="512">
@@ -28539,7 +28539,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>SIS2</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -28554,16 +28554,16 @@
       </c>
       <c r="D513" t="inlineStr"/>
       <c r="E513" t="n">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>2606N</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -28588,13 +28588,13 @@
         <v>46306.27083333334</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>SIS2</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -28609,16 +28609,16 @@
       </c>
       <c r="D514" t="inlineStr"/>
       <c r="E514" t="n">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2606N</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -28637,13 +28637,13 @@
         </is>
       </c>
       <c r="K514" s="1" t="n">
-        <v>46306.22916666666</v>
+        <v>46306.83333333334</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>46306.27083333334</v>
+        <v>46306.875</v>
       </c>
       <c r="M514" s="1" t="n">
-        <v>46308.27083333334</v>
+        <v>46307.875</v>
       </c>
     </row>
     <row r="515">
@@ -28692,13 +28692,13 @@
         </is>
       </c>
       <c r="K515" s="1" t="n">
-        <v>46309.79166666666</v>
+        <v>46309.95833333334</v>
       </c>
       <c r="L515" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="M515" s="1" t="n">
-        <v>46311.79166666666</v>
+        <v>46311.95833333334</v>
       </c>
     </row>
     <row r="516">
@@ -28747,13 +28747,13 @@
         </is>
       </c>
       <c r="K516" s="1" t="n">
-        <v>46312.79166666666</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="L516" s="1" t="n">
-        <v>46315.79166666666</v>
+        <v>46314.95833333334</v>
       </c>
       <c r="M516" s="1" t="n">
-        <v>46316.375</v>
+        <v>46315.54166666666</v>
       </c>
     </row>
     <row r="517">
@@ -28802,13 +28802,13 @@
         </is>
       </c>
       <c r="K517" s="1" t="n">
-        <v>46317.125</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="L517" s="1" t="n">
-        <v>46318.20833333334</v>
+        <v>46317.375</v>
       </c>
       <c r="M517" s="1" t="n">
-        <v>46318.875</v>
+        <v>46318.04166666666</v>
       </c>
     </row>
     <row r="518">
@@ -28857,13 +28857,13 @@
         </is>
       </c>
       <c r="K518" s="1" t="n">
-        <v>46321.875</v>
+        <v>46321.04166666666</v>
       </c>
       <c r="L518" s="1" t="n">
-        <v>46322</v>
+        <v>46321.16666666666</v>
       </c>
       <c r="M518" s="1" t="n">
-        <v>46322.75</v>
+        <v>46321.91666666666</v>
       </c>
     </row>
     <row r="519">
@@ -28912,13 +28912,13 @@
         </is>
       </c>
       <c r="K519" s="1" t="n">
-        <v>46338</v>
+        <v>46337.16666666666</v>
       </c>
       <c r="L519" s="1" t="n">
-        <v>46343.04166666666</v>
+        <v>46342.20833333334</v>
       </c>
       <c r="M519" s="1" t="n">
-        <v>46346.04166666666</v>
+        <v>46345.20833333334</v>
       </c>
     </row>
     <row r="520">
@@ -28963,13 +28963,13 @@
       </c>
       <c r="J520" t="inlineStr"/>
       <c r="K520" s="1" t="n">
-        <v>46364.29166666666</v>
+        <v>46363.45833333334</v>
       </c>
       <c r="L520" s="1" t="n">
-        <v>46364.33333333334</v>
+        <v>46363.5</v>
       </c>
       <c r="M520" s="1" t="n">
-        <v>46365</v>
+        <v>46364.16666666666</v>
       </c>
     </row>
     <row r="521">
@@ -35551,13 +35551,13 @@
         </is>
       </c>
       <c r="K640" s="1" t="n">
-        <v>46295.875</v>
+        <v>46296.08333333334</v>
       </c>
       <c r="L640" s="1" t="n">
-        <v>46295.91666666666</v>
+        <v>46296.125</v>
       </c>
       <c r="M640" s="1" t="n">
-        <v>46296.29166666666</v>
+        <v>46296.75</v>
       </c>
     </row>
     <row r="641">
@@ -35606,13 +35606,13 @@
         </is>
       </c>
       <c r="K641" s="1" t="n">
-        <v>46298.25</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="L641" s="1" t="n">
-        <v>46298.41666666666</v>
+        <v>46298.875</v>
       </c>
       <c r="M641" s="1" t="n">
-        <v>46298.95833333334</v>
+        <v>46299.41666666666</v>
       </c>
     </row>
     <row r="642">
@@ -35661,13 +35661,13 @@
         </is>
       </c>
       <c r="K642" s="1" t="n">
-        <v>46300.75</v>
+        <v>46301.20833333334</v>
       </c>
       <c r="L642" s="1" t="n">
-        <v>46300.79166666666</v>
+        <v>46301.25</v>
       </c>
       <c r="M642" s="1" t="n">
-        <v>46301.04166666666</v>
+        <v>46301.5</v>
       </c>
     </row>
     <row r="643">
@@ -35716,13 +35716,13 @@
         </is>
       </c>
       <c r="K643" s="1" t="n">
-        <v>46301.45833333334</v>
+        <v>46301.91666666666</v>
       </c>
       <c r="L643" s="1" t="n">
-        <v>46301.58333333334</v>
+        <v>46302.04166666666</v>
       </c>
       <c r="M643" s="1" t="n">
-        <v>46302.70833333334</v>
+        <v>46303.16666666666</v>
       </c>
     </row>
     <row r="644">
@@ -35771,13 +35771,13 @@
         </is>
       </c>
       <c r="K644" s="1" t="n">
-        <v>46303.04166666666</v>
+        <v>46303.5</v>
       </c>
       <c r="L644" s="1" t="n">
-        <v>46303.08333333334</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="M644" s="1" t="n">
-        <v>46303.41666666666</v>
+        <v>46303.875</v>
       </c>
     </row>
     <row r="645">
@@ -35826,13 +35826,13 @@
         </is>
       </c>
       <c r="K645" s="1" t="n">
-        <v>46307.29166666666</v>
+        <v>46307.75</v>
       </c>
       <c r="L645" s="1" t="n">
-        <v>46307.33333333334</v>
+        <v>46307.79166666666</v>
       </c>
       <c r="M645" s="1" t="n">
-        <v>46307.75</v>
+        <v>46308.20833333334</v>
       </c>
     </row>
     <row r="646">
@@ -35881,13 +35881,13 @@
         </is>
       </c>
       <c r="K646" s="1" t="n">
-        <v>46308</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="L646" s="1" t="n">
-        <v>46308</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="M646" s="1" t="n">
-        <v>46308.375</v>
+        <v>46308.83333333334</v>
       </c>
     </row>
     <row r="647">
@@ -35936,13 +35936,13 @@
         </is>
       </c>
       <c r="K647" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="L647" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="M647" s="1" t="n">
-        <v>46309.95833333334</v>
+        <v>46310.41666666666</v>
       </c>
     </row>
     <row r="648">
@@ -35991,13 +35991,13 @@
         </is>
       </c>
       <c r="K648" s="1" t="n">
-        <v>46312</v>
+        <v>46312.41666666666</v>
       </c>
       <c r="L648" s="1" t="n">
-        <v>46312.04166666666</v>
+        <v>46312.45833333334</v>
       </c>
       <c r="M648" s="1" t="n">
-        <v>46312.75</v>
+        <v>46313.16666666666</v>
       </c>
     </row>
     <row r="649">
@@ -36046,13 +36046,13 @@
         </is>
       </c>
       <c r="K649" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.375</v>
       </c>
       <c r="L649" s="1" t="n">
-        <v>46313</v>
+        <v>46313.41666666666</v>
       </c>
       <c r="M649" s="1" t="n">
-        <v>46313.33333333334</v>
+        <v>46313.75</v>
       </c>
     </row>
     <row r="650">
@@ -36101,13 +36101,13 @@
         </is>
       </c>
       <c r="K650" s="1" t="n">
-        <v>46316.58333333334</v>
+        <v>46317</v>
       </c>
       <c r="L650" s="1" t="n">
-        <v>46316.625</v>
+        <v>46317.04166666666</v>
       </c>
       <c r="M650" s="1" t="n">
-        <v>46317</v>
+        <v>46317.41666666666</v>
       </c>
     </row>
     <row r="651">
@@ -36156,13 +36156,13 @@
         </is>
       </c>
       <c r="K651" s="1" t="n">
-        <v>46319.45833333334</v>
+        <v>46319.875</v>
       </c>
       <c r="L651" s="1" t="n">
-        <v>46319.625</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="M651" s="1" t="n">
-        <v>46320.16666666666</v>
+        <v>46320.58333333334</v>
       </c>
     </row>
     <row r="652">
@@ -36211,13 +36211,13 @@
         </is>
       </c>
       <c r="K652" s="1" t="n">
-        <v>46321.95833333334</v>
+        <v>46322.375</v>
       </c>
       <c r="L652" s="1" t="n">
-        <v>46322</v>
+        <v>46322.41666666666</v>
       </c>
       <c r="M652" s="1" t="n">
-        <v>46322.25</v>
+        <v>46322.66666666666</v>
       </c>
     </row>
     <row r="653">
@@ -36266,13 +36266,13 @@
         </is>
       </c>
       <c r="K653" s="1" t="n">
-        <v>46322.66666666666</v>
+        <v>46323.08333333334</v>
       </c>
       <c r="L653" s="1" t="n">
-        <v>46322.79166666666</v>
+        <v>46323.20833333334</v>
       </c>
       <c r="M653" s="1" t="n">
-        <v>46323.91666666666</v>
+        <v>46324.33333333334</v>
       </c>
     </row>
     <row r="654">
@@ -36321,13 +36321,13 @@
         </is>
       </c>
       <c r="K654" s="1" t="n">
-        <v>46324.25</v>
+        <v>46324.66666666666</v>
       </c>
       <c r="L654" s="1" t="n">
-        <v>46324.29166666666</v>
+        <v>46324.70833333334</v>
       </c>
       <c r="M654" s="1" t="n">
-        <v>46324.625</v>
+        <v>46325.04166666666</v>
       </c>
     </row>
     <row r="655">
@@ -36376,13 +36376,13 @@
         </is>
       </c>
       <c r="K655" s="1" t="n">
-        <v>46328.5</v>
+        <v>46328.91666666666</v>
       </c>
       <c r="L655" s="1" t="n">
-        <v>46328.54166666666</v>
+        <v>46328.95833333334</v>
       </c>
       <c r="M655" s="1" t="n">
-        <v>46328.95833333334</v>
+        <v>46329.375</v>
       </c>
     </row>
     <row r="656">
@@ -36431,13 +36431,13 @@
         </is>
       </c>
       <c r="K656" s="1" t="n">
-        <v>46329.20833333334</v>
+        <v>46329.625</v>
       </c>
       <c r="L656" s="1" t="n">
-        <v>46329.20833333334</v>
+        <v>46329.625</v>
       </c>
       <c r="M656" s="1" t="n">
-        <v>46329.58333333334</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="657">
@@ -36486,13 +36486,13 @@
         </is>
       </c>
       <c r="K657" s="1" t="n">
-        <v>46330.83333333334</v>
+        <v>46331.25</v>
       </c>
       <c r="L657" s="1" t="n">
-        <v>46330.83333333334</v>
+        <v>46331.25</v>
       </c>
       <c r="M657" s="1" t="n">
-        <v>46331.08333333334</v>
+        <v>46331.5</v>
       </c>
     </row>
     <row r="658">
@@ -36541,13 +36541,13 @@
         </is>
       </c>
       <c r="K658" s="1" t="n">
-        <v>46333.62430555555</v>
+        <v>46334.04097222222</v>
       </c>
       <c r="L658" s="1" t="n">
-        <v>46333.66597222222</v>
+        <v>46334.08263888889</v>
       </c>
       <c r="M658" s="1" t="n">
-        <v>46334.37430555555</v>
+        <v>46334.79097222222</v>
       </c>
     </row>
     <row r="659">
@@ -36596,13 +36596,13 @@
         </is>
       </c>
       <c r="K659" s="1" t="n">
-        <v>46334.58263888889</v>
+        <v>46334.99930555555</v>
       </c>
       <c r="L659" s="1" t="n">
-        <v>46334.62430555555</v>
+        <v>46335.04097222222</v>
       </c>
       <c r="M659" s="1" t="n">
-        <v>46334.95763888889</v>
+        <v>46335.37430555555</v>
       </c>
     </row>
     <row r="660">
@@ -36651,13 +36651,13 @@
         </is>
       </c>
       <c r="K660" s="1" t="n">
-        <v>46337.79097222222</v>
+        <v>46338.20763888889</v>
       </c>
       <c r="L660" s="1" t="n">
-        <v>46337.83263888889</v>
+        <v>46338.24930555555</v>
       </c>
       <c r="M660" s="1" t="n">
-        <v>46338.20763888889</v>
+        <v>46338.62430555555</v>
       </c>
     </row>
     <row r="661">
@@ -36706,13 +36706,13 @@
         </is>
       </c>
       <c r="K661" s="1" t="n">
-        <v>46340.66597222222</v>
+        <v>46341.08263888889</v>
       </c>
       <c r="L661" s="1" t="n">
-        <v>46340.83263888889</v>
+        <v>46341.24930555555</v>
       </c>
       <c r="M661" s="1" t="n">
-        <v>46341.37430555555</v>
+        <v>46341.79097222222</v>
       </c>
     </row>
     <row r="662">
@@ -36761,13 +36761,13 @@
         </is>
       </c>
       <c r="K662" s="1" t="n">
-        <v>46343.16597222222</v>
+        <v>46343.58263888889</v>
       </c>
       <c r="L662" s="1" t="n">
-        <v>46343.20763888889</v>
+        <v>46343.62430555555</v>
       </c>
       <c r="M662" s="1" t="n">
-        <v>46343.45763888889</v>
+        <v>46343.87430555555</v>
       </c>
     </row>
     <row r="663">
@@ -36816,13 +36816,13 @@
         </is>
       </c>
       <c r="K663" s="1" t="n">
-        <v>46343.87430555555</v>
+        <v>46344.29097222222</v>
       </c>
       <c r="L663" s="1" t="n">
-        <v>46343.99930555555</v>
+        <v>46344.41597222222</v>
       </c>
       <c r="M663" s="1" t="n">
-        <v>46345.12430555555</v>
+        <v>46345.54097222222</v>
       </c>
     </row>
     <row r="664">
@@ -36871,13 +36871,13 @@
         </is>
       </c>
       <c r="K664" s="1" t="n">
-        <v>46345.45763888889</v>
+        <v>46345.87430555555</v>
       </c>
       <c r="L664" s="1" t="n">
-        <v>46345.49930555555</v>
+        <v>46345.91597222222</v>
       </c>
       <c r="M664" s="1" t="n">
-        <v>46345.83263888889</v>
+        <v>46346.24930555555</v>
       </c>
     </row>
     <row r="665">
@@ -36926,13 +36926,13 @@
         </is>
       </c>
       <c r="K665" s="1" t="n">
-        <v>46349.70763888889</v>
+        <v>46350.12430555555</v>
       </c>
       <c r="L665" s="1" t="n">
-        <v>46349.74930555555</v>
+        <v>46350.16597222222</v>
       </c>
       <c r="M665" s="1" t="n">
-        <v>46350.16597222222</v>
+        <v>46350.58263888889</v>
       </c>
     </row>
     <row r="666">
@@ -36981,13 +36981,13 @@
         </is>
       </c>
       <c r="K666" s="1" t="n">
-        <v>46350.41597222222</v>
+        <v>46350.83263888889</v>
       </c>
       <c r="L666" s="1" t="n">
-        <v>46350.41597222222</v>
+        <v>46350.83263888889</v>
       </c>
       <c r="M666" s="1" t="n">
-        <v>46350.79097222222</v>
+        <v>46351.20763888889</v>
       </c>
     </row>
     <row r="667">
@@ -37036,13 +37036,13 @@
         </is>
       </c>
       <c r="K667" s="1" t="n">
-        <v>46352.04097222222</v>
+        <v>46352.45763888889</v>
       </c>
       <c r="L667" s="1" t="n">
-        <v>46352.04097222222</v>
+        <v>46352.45763888889</v>
       </c>
       <c r="M667" s="1" t="n">
-        <v>46352.29097222222</v>
+        <v>46352.70763888889</v>
       </c>
     </row>
     <row r="668">
@@ -37091,13 +37091,13 @@
         </is>
       </c>
       <c r="K668" s="1" t="n">
-        <v>46354.62430555555</v>
+        <v>46355.04097222222</v>
       </c>
       <c r="L668" s="1" t="n">
-        <v>46354.66597222222</v>
+        <v>46355.08263888889</v>
       </c>
       <c r="M668" s="1" t="n">
-        <v>46355.37430555555</v>
+        <v>46355.79097222222</v>
       </c>
     </row>
     <row r="669">
@@ -37146,13 +37146,13 @@
         </is>
       </c>
       <c r="K669" s="1" t="n">
-        <v>46355.58263888889</v>
+        <v>46355.99930555555</v>
       </c>
       <c r="L669" s="1" t="n">
-        <v>46355.62430555555</v>
+        <v>46356.04097222222</v>
       </c>
       <c r="M669" s="1" t="n">
-        <v>46355.95763888889</v>
+        <v>46356.37430555555</v>
       </c>
     </row>
     <row r="670">
@@ -37201,13 +37201,13 @@
         </is>
       </c>
       <c r="K670" s="1" t="n">
-        <v>46358.79097222222</v>
+        <v>46359.20763888889</v>
       </c>
       <c r="L670" s="1" t="n">
-        <v>46358.83263888889</v>
+        <v>46359.24930555555</v>
       </c>
       <c r="M670" s="1" t="n">
-        <v>46359.20763888889</v>
+        <v>46359.62430555555</v>
       </c>
     </row>
     <row r="671">
@@ -37256,13 +37256,13 @@
         </is>
       </c>
       <c r="K671" s="1" t="n">
-        <v>46361.66597222222</v>
+        <v>46362.08263888889</v>
       </c>
       <c r="L671" s="1" t="n">
-        <v>46361.83263888889</v>
+        <v>46362.24930555555</v>
       </c>
       <c r="M671" s="1" t="n">
-        <v>46362.37430555555</v>
+        <v>46362.79097222222</v>
       </c>
     </row>
     <row r="672">
@@ -37311,13 +37311,13 @@
         </is>
       </c>
       <c r="K672" s="1" t="n">
-        <v>46364.16597222222</v>
+        <v>46364.58263888889</v>
       </c>
       <c r="L672" s="1" t="n">
-        <v>46364.20763888889</v>
+        <v>46364.62430555555</v>
       </c>
       <c r="M672" s="1" t="n">
-        <v>46364.45763888889</v>
+        <v>46364.87430555555</v>
       </c>
     </row>
     <row r="673">
@@ -37366,13 +37366,13 @@
         </is>
       </c>
       <c r="K673" s="1" t="n">
-        <v>46364.87430555555</v>
+        <v>46365.29097222222</v>
       </c>
       <c r="L673" s="1" t="n">
-        <v>46364.99930555555</v>
+        <v>46365.41597222222</v>
       </c>
       <c r="M673" s="1" t="n">
-        <v>46366.12430555555</v>
+        <v>46366.54097222222</v>
       </c>
     </row>
     <row r="674">
@@ -37421,13 +37421,13 @@
         </is>
       </c>
       <c r="K674" s="1" t="n">
-        <v>46366.45763888889</v>
+        <v>46366.87430555555</v>
       </c>
       <c r="L674" s="1" t="n">
-        <v>46366.49930555555</v>
+        <v>46366.91597222222</v>
       </c>
       <c r="M674" s="1" t="n">
-        <v>46366.83263888889</v>
+        <v>46367.24930555555</v>
       </c>
     </row>
     <row r="675">
@@ -37476,13 +37476,13 @@
         </is>
       </c>
       <c r="K675" s="1" t="n">
-        <v>46370.70763888889</v>
+        <v>46371.12430555555</v>
       </c>
       <c r="L675" s="1" t="n">
-        <v>46370.74930555555</v>
+        <v>46371.16597222222</v>
       </c>
       <c r="M675" s="1" t="n">
-        <v>46371.16597222222</v>
+        <v>46371.58263888889</v>
       </c>
     </row>
     <row r="676">
@@ -37531,13 +37531,13 @@
         </is>
       </c>
       <c r="K676" s="1" t="n">
-        <v>46371.41597222222</v>
+        <v>46371.83263888889</v>
       </c>
       <c r="L676" s="1" t="n">
-        <v>46371.41597222222</v>
+        <v>46371.83263888889</v>
       </c>
       <c r="M676" s="1" t="n">
-        <v>46371.79097222222</v>
+        <v>46372.20763888889</v>
       </c>
     </row>
     <row r="677">
@@ -37582,13 +37582,13 @@
       </c>
       <c r="J677" t="inlineStr"/>
       <c r="K677" s="1" t="n">
-        <v>46373.04097222222</v>
+        <v>46373.45763888889</v>
       </c>
       <c r="L677" s="1" t="n">
-        <v>46373.04097222222</v>
+        <v>46373.45763888889</v>
       </c>
       <c r="M677" s="1" t="n">
-        <v>46373.29097222222</v>
+        <v>46373.70763888889</v>
       </c>
     </row>
     <row r="678">
@@ -43187,10 +43187,10 @@
         <v>46296.41666666666</v>
       </c>
       <c r="L779" s="1" t="n">
-        <v>46296.45833333334</v>
+        <v>46297.29166666666</v>
       </c>
       <c r="M779" s="1" t="n">
-        <v>46297.54166666666</v>
+        <v>46298.41666666666</v>
       </c>
     </row>
     <row r="780">
@@ -43239,13 +43239,13 @@
         </is>
       </c>
       <c r="K780" s="1" t="n">
-        <v>46297.66666666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="L780" s="1" t="n">
-        <v>46297.70833333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="M780" s="1" t="n">
-        <v>46297.95833333334</v>
+        <v>46298.83333333334</v>
       </c>
     </row>
     <row r="781">
@@ -43294,13 +43294,13 @@
         </is>
       </c>
       <c r="K781" s="1" t="n">
-        <v>46298.45833333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="L781" s="1" t="n">
-        <v>46298.54166666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="M781" s="1" t="n">
-        <v>46298.875</v>
+        <v>46299.75</v>
       </c>
     </row>
     <row r="782">
@@ -43349,13 +43349,13 @@
         </is>
       </c>
       <c r="K782" s="1" t="n">
-        <v>46303.83333333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="L782" s="1" t="n">
-        <v>46304</v>
+        <v>46304.875</v>
       </c>
       <c r="M782" s="1" t="n">
-        <v>46304.625</v>
+        <v>46305.5</v>
       </c>
     </row>
     <row r="783">
@@ -43404,13 +43404,13 @@
         </is>
       </c>
       <c r="K783" s="1" t="n">
-        <v>46306.29166666666</v>
+        <v>46307.16666666666</v>
       </c>
       <c r="L783" s="1" t="n">
-        <v>46306.33333333334</v>
+        <v>46307.20833333334</v>
       </c>
       <c r="M783" s="1" t="n">
-        <v>46306.58333333334</v>
+        <v>46307.45833333334</v>
       </c>
     </row>
     <row r="784">
@@ -43459,13 +43459,13 @@
         </is>
       </c>
       <c r="K784" s="1" t="n">
-        <v>46306.66666666666</v>
+        <v>46307.54166666666</v>
       </c>
       <c r="L784" s="1" t="n">
-        <v>46306.79166666666</v>
+        <v>46307.66666666666</v>
       </c>
       <c r="M784" s="1" t="n">
-        <v>46308.29166666666</v>
+        <v>46309.16666666666</v>
       </c>
     </row>
     <row r="785">
@@ -43514,13 +43514,13 @@
         </is>
       </c>
       <c r="K785" s="1" t="n">
-        <v>46308.5</v>
+        <v>46309.375</v>
       </c>
       <c r="L785" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="M785" s="1" t="n">
-        <v>46308.95833333334</v>
+        <v>46309.83333333334</v>
       </c>
     </row>
     <row r="786">
@@ -43569,13 +43569,13 @@
         </is>
       </c>
       <c r="K786" s="1" t="n">
-        <v>46310.58333333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="L786" s="1" t="n">
-        <v>46310.75</v>
+        <v>46311.625</v>
       </c>
       <c r="M786" s="1" t="n">
-        <v>46311.29166666666</v>
+        <v>46312.16666666666</v>
       </c>
     </row>
     <row r="787">
@@ -43624,13 +43624,13 @@
         </is>
       </c>
       <c r="K787" s="1" t="n">
-        <v>46316.58333333334</v>
+        <v>46317.45833333334</v>
       </c>
       <c r="L787" s="1" t="n">
-        <v>46316.625</v>
+        <v>46317.5</v>
       </c>
       <c r="M787" s="1" t="n">
-        <v>46317.70833333334</v>
+        <v>46318.58333333334</v>
       </c>
     </row>
     <row r="788">
@@ -43679,13 +43679,13 @@
         </is>
       </c>
       <c r="K788" s="1" t="n">
-        <v>46317.83333333334</v>
+        <v>46318.70833333334</v>
       </c>
       <c r="L788" s="1" t="n">
-        <v>46317.875</v>
+        <v>46318.75</v>
       </c>
       <c r="M788" s="1" t="n">
-        <v>46318.125</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="789">
@@ -43734,13 +43734,13 @@
         </is>
       </c>
       <c r="K789" s="1" t="n">
-        <v>46318.625</v>
+        <v>46319.5</v>
       </c>
       <c r="L789" s="1" t="n">
-        <v>46318.70833333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="M789" s="1" t="n">
-        <v>46319.04166666666</v>
+        <v>46319.91666666666</v>
       </c>
     </row>
     <row r="790">
@@ -43789,13 +43789,13 @@
         </is>
       </c>
       <c r="K790" s="1" t="n">
-        <v>46323.91666666666</v>
+        <v>46324.79166666666</v>
       </c>
       <c r="L790" s="1" t="n">
-        <v>46324.08333333334</v>
+        <v>46324.95833333334</v>
       </c>
       <c r="M790" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46325.58333333334</v>
       </c>
     </row>
     <row r="791">
@@ -43844,13 +43844,13 @@
         </is>
       </c>
       <c r="K791" s="1" t="n">
-        <v>46326.375</v>
+        <v>46327.25</v>
       </c>
       <c r="L791" s="1" t="n">
-        <v>46326.41666666666</v>
+        <v>46327.29166666666</v>
       </c>
       <c r="M791" s="1" t="n">
-        <v>46326.66666666666</v>
+        <v>46327.54166666666</v>
       </c>
     </row>
     <row r="792">
@@ -43899,13 +43899,13 @@
         </is>
       </c>
       <c r="K792" s="1" t="n">
-        <v>46326.79166666666</v>
+        <v>46327.66666666666</v>
       </c>
       <c r="L792" s="1" t="n">
-        <v>46326.91666666666</v>
+        <v>46327.79166666666</v>
       </c>
       <c r="M792" s="1" t="n">
-        <v>46328.41666666666</v>
+        <v>46329.29166666666</v>
       </c>
     </row>
     <row r="793">
@@ -43954,13 +43954,13 @@
         </is>
       </c>
       <c r="K793" s="1" t="n">
-        <v>46328.625</v>
+        <v>46329.5</v>
       </c>
       <c r="L793" s="1" t="n">
-        <v>46328.66666666666</v>
+        <v>46329.54166666666</v>
       </c>
       <c r="M793" s="1" t="n">
-        <v>46329.08333333334</v>
+        <v>46329.95833333334</v>
       </c>
     </row>
     <row r="794">
@@ -44009,13 +44009,13 @@
         </is>
       </c>
       <c r="K794" s="1" t="n">
-        <v>46330.625</v>
+        <v>46331.5</v>
       </c>
       <c r="L794" s="1" t="n">
-        <v>46330.79166666666</v>
+        <v>46331.66666666666</v>
       </c>
       <c r="M794" s="1" t="n">
-        <v>46331.33333333334</v>
+        <v>46332.20833333334</v>
       </c>
     </row>
     <row r="795">
@@ -44064,13 +44064,13 @@
         </is>
       </c>
       <c r="K795" s="1" t="n">
-        <v>46336.70833333334</v>
+        <v>46337.58333333334</v>
       </c>
       <c r="L795" s="1" t="n">
-        <v>46336.75</v>
+        <v>46337.625</v>
       </c>
       <c r="M795" s="1" t="n">
-        <v>46337.83333333334</v>
+        <v>46338.70833333334</v>
       </c>
     </row>
     <row r="796">
@@ -44119,13 +44119,13 @@
         </is>
       </c>
       <c r="K796" s="1" t="n">
-        <v>46338</v>
+        <v>46338.875</v>
       </c>
       <c r="L796" s="1" t="n">
-        <v>46338.04166666666</v>
+        <v>46338.91666666666</v>
       </c>
       <c r="M796" s="1" t="n">
-        <v>46338.29166666666</v>
+        <v>46339.16666666666</v>
       </c>
     </row>
     <row r="797">
@@ -44174,13 +44174,13 @@
         </is>
       </c>
       <c r="K797" s="1" t="n">
-        <v>46338.75</v>
+        <v>46339.625</v>
       </c>
       <c r="L797" s="1" t="n">
-        <v>46338.83333333334</v>
+        <v>46339.70833333334</v>
       </c>
       <c r="M797" s="1" t="n">
-        <v>46339.16666666666</v>
+        <v>46340.04166666666</v>
       </c>
     </row>
     <row r="798">
@@ -44229,13 +44229,13 @@
         </is>
       </c>
       <c r="K798" s="1" t="n">
-        <v>46344.16666666666</v>
+        <v>46345.04166666666</v>
       </c>
       <c r="L798" s="1" t="n">
-        <v>46344.33333333334</v>
+        <v>46345.20833333334</v>
       </c>
       <c r="M798" s="1" t="n">
-        <v>46344.95833333334</v>
+        <v>46345.83333333334</v>
       </c>
     </row>
     <row r="799">
@@ -44284,13 +44284,13 @@
         </is>
       </c>
       <c r="K799" s="1" t="n">
-        <v>46346.75</v>
+        <v>46347.625</v>
       </c>
       <c r="L799" s="1" t="n">
-        <v>46346.79166666666</v>
+        <v>46347.66666666666</v>
       </c>
       <c r="M799" s="1" t="n">
-        <v>46347.04166666666</v>
+        <v>46347.91666666666</v>
       </c>
     </row>
     <row r="800">
@@ -44339,13 +44339,13 @@
         </is>
       </c>
       <c r="K800" s="1" t="n">
-        <v>46347.33333333334</v>
+        <v>46348.20833333334</v>
       </c>
       <c r="L800" s="1" t="n">
-        <v>46347.45833333334</v>
+        <v>46348.33333333334</v>
       </c>
       <c r="M800" s="1" t="n">
-        <v>46348.95833333334</v>
+        <v>46349.83333333334</v>
       </c>
     </row>
     <row r="801">
@@ -44394,13 +44394,13 @@
         </is>
       </c>
       <c r="K801" s="1" t="n">
-        <v>46349.16666666666</v>
+        <v>46350.04166666666</v>
       </c>
       <c r="L801" s="1" t="n">
-        <v>46349.20833333334</v>
+        <v>46350.08333333334</v>
       </c>
       <c r="M801" s="1" t="n">
-        <v>46349.625</v>
+        <v>46350.5</v>
       </c>
     </row>
     <row r="802">
@@ -44445,13 +44445,13 @@
       </c>
       <c r="J802" t="inlineStr"/>
       <c r="K802" s="1" t="n">
-        <v>46351.20833333334</v>
+        <v>46352.08333333334</v>
       </c>
       <c r="L802" s="1" t="n">
-        <v>46351.375</v>
+        <v>46352.25</v>
       </c>
       <c r="M802" s="1" t="n">
-        <v>46351.91666666666</v>
+        <v>46352.79166666666</v>
       </c>
     </row>
     <row r="803">
@@ -44946,7 +44946,7 @@
         <v>46293.25416666667</v>
       </c>
       <c r="M811" s="1" t="n">
-        <v>46293.70833333334</v>
+        <v>46293.94166666667</v>
       </c>
     </row>
     <row r="812">
@@ -45160,13 +45160,13 @@
         </is>
       </c>
       <c r="K815" s="1" t="n">
-        <v>46303.29166666666</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="L815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M815" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="816">
@@ -45215,13 +45215,13 @@
         </is>
       </c>
       <c r="K816" s="1" t="n">
-        <v>46311.20833333334</v>
+        <v>46312.20833333334</v>
       </c>
       <c r="L816" s="1" t="n">
-        <v>46312.33333333334</v>
+        <v>46313.33333333334</v>
       </c>
       <c r="M816" s="1" t="n">
-        <v>46312.83333333334</v>
+        <v>46313.83333333334</v>
       </c>
     </row>
     <row r="817">
@@ -45270,13 +45270,13 @@
         </is>
       </c>
       <c r="K817" s="1" t="n">
-        <v>46314.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="L817" s="1" t="n">
-        <v>46314.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="M817" s="1" t="n">
-        <v>46314.875</v>
+        <v>46315.875</v>
       </c>
     </row>
     <row r="818">
@@ -45325,13 +45325,13 @@
         </is>
       </c>
       <c r="K818" s="1" t="n">
-        <v>46315.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="L818" s="1" t="n">
-        <v>46315.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="M818" s="1" t="n">
-        <v>46316.16666666666</v>
+        <v>46317.16666666666</v>
       </c>
     </row>
     <row r="819">
@@ -45380,13 +45380,13 @@
         </is>
       </c>
       <c r="K819" s="1" t="n">
-        <v>46316.41666666666</v>
+        <v>46317.41666666666</v>
       </c>
       <c r="L819" s="1" t="n">
-        <v>46316.45833333334</v>
+        <v>46317.45833333334</v>
       </c>
       <c r="M819" s="1" t="n">
-        <v>46316.875</v>
+        <v>46317.875</v>
       </c>
     </row>
     <row r="820">
@@ -45435,13 +45435,13 @@
         </is>
       </c>
       <c r="K820" s="1" t="n">
-        <v>46318.375</v>
+        <v>46319.375</v>
       </c>
       <c r="L820" s="1" t="n">
-        <v>46319.5</v>
+        <v>46320.5</v>
       </c>
       <c r="M820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="821">
@@ -45490,13 +45490,13 @@
         </is>
       </c>
       <c r="K821" s="1" t="n">
-        <v>46326.02083333334</v>
+        <v>46327.10416666666</v>
       </c>
       <c r="L821" s="1" t="n">
-        <v>46326.08333333334</v>
+        <v>46327.16666666666</v>
       </c>
       <c r="M821" s="1" t="n">
-        <v>46326.33333333334</v>
+        <v>46327.41666666666</v>
       </c>
     </row>
     <row r="822">
@@ -45545,13 +45545,13 @@
         </is>
       </c>
       <c r="K822" s="1" t="n">
-        <v>46327.29166666666</v>
+        <v>46328.375</v>
       </c>
       <c r="L822" s="1" t="n">
-        <v>46327.35416666666</v>
+        <v>46328.4375</v>
       </c>
       <c r="M822" s="1" t="n">
-        <v>46327.77083333334</v>
+        <v>46328.85416666666</v>
       </c>
     </row>
     <row r="823">
@@ -45600,13 +45600,13 @@
         </is>
       </c>
       <c r="K823" s="1" t="n">
-        <v>46328.125</v>
+        <v>46329.20833333334</v>
       </c>
       <c r="L823" s="1" t="n">
-        <v>46328.16666666666</v>
+        <v>46329.25</v>
       </c>
       <c r="M823" s="1" t="n">
-        <v>46328.79166666666</v>
+        <v>46329.875</v>
       </c>
     </row>
     <row r="824">
@@ -45655,13 +45655,13 @@
         </is>
       </c>
       <c r="K824" s="1" t="n">
-        <v>46329.875</v>
+        <v>46330.95833333334</v>
       </c>
       <c r="L824" s="1" t="n">
-        <v>46330.04166666666</v>
+        <v>46331.125</v>
       </c>
       <c r="M824" s="1" t="n">
-        <v>46331.04166666666</v>
+        <v>46332.125</v>
       </c>
     </row>
     <row r="825">
@@ -45710,13 +45710,13 @@
         </is>
       </c>
       <c r="K825" s="1" t="n">
-        <v>46335.25</v>
+        <v>46336.33333333334</v>
       </c>
       <c r="L825" s="1" t="n">
-        <v>46335.375</v>
+        <v>46336.45833333334</v>
       </c>
       <c r="M825" s="1" t="n">
-        <v>46335.875</v>
+        <v>46336.95833333334</v>
       </c>
     </row>
     <row r="826">
@@ -45765,13 +45765,13 @@
         </is>
       </c>
       <c r="K826" s="1" t="n">
-        <v>46337.45833333334</v>
+        <v>46338.54166666666</v>
       </c>
       <c r="L826" s="1" t="n">
-        <v>46337.5</v>
+        <v>46338.58333333334</v>
       </c>
       <c r="M826" s="1" t="n">
-        <v>46337.91666666666</v>
+        <v>46339</v>
       </c>
     </row>
     <row r="827">
@@ -45820,13 +45820,13 @@
         </is>
       </c>
       <c r="K827" s="1" t="n">
-        <v>46338.08333333334</v>
+        <v>46339.16666666666</v>
       </c>
       <c r="L827" s="1" t="n">
-        <v>46338.20833333334</v>
+        <v>46339.29166666666</v>
       </c>
       <c r="M827" s="1" t="n">
-        <v>46339.20833333334</v>
+        <v>46340.29166666666</v>
       </c>
     </row>
     <row r="828">
@@ -45875,13 +45875,13 @@
         </is>
       </c>
       <c r="K828" s="1" t="n">
-        <v>46339.45833333334</v>
+        <v>46340.54166666666</v>
       </c>
       <c r="L828" s="1" t="n">
-        <v>46339.5</v>
+        <v>46340.58333333334</v>
       </c>
       <c r="M828" s="1" t="n">
-        <v>46339.91666666666</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="829">
@@ -45930,13 +45930,13 @@
         </is>
       </c>
       <c r="K829" s="1" t="n">
-        <v>46341.41666666666</v>
+        <v>46342.5</v>
       </c>
       <c r="L829" s="1" t="n">
-        <v>46341.54166666666</v>
+        <v>46342.625</v>
       </c>
       <c r="M829" s="1" t="n">
-        <v>46342.04166666666</v>
+        <v>46343.125</v>
       </c>
     </row>
     <row r="830">
@@ -45985,13 +45985,13 @@
         </is>
       </c>
       <c r="K830" s="1" t="n">
-        <v>46347.0625</v>
+        <v>46348.14583333334</v>
       </c>
       <c r="L830" s="1" t="n">
-        <v>46347.125</v>
+        <v>46348.20833333334</v>
       </c>
       <c r="M830" s="1" t="n">
-        <v>46347.375</v>
+        <v>46348.45833333334</v>
       </c>
     </row>
     <row r="831">
@@ -46040,13 +46040,13 @@
         </is>
       </c>
       <c r="K831" s="1" t="n">
-        <v>46348.32083333333</v>
+        <v>46349.40416666667</v>
       </c>
       <c r="L831" s="1" t="n">
-        <v>46348.38333333333</v>
+        <v>46349.46666666667</v>
       </c>
       <c r="M831" s="1" t="n">
-        <v>46348.8</v>
+        <v>46349.88333333333</v>
       </c>
     </row>
     <row r="832">
@@ -46095,13 +46095,13 @@
         </is>
       </c>
       <c r="K832" s="1" t="n">
-        <v>46349.14166666667</v>
+        <v>46350.225</v>
       </c>
       <c r="L832" s="1" t="n">
-        <v>46349.18333333333</v>
+        <v>46350.26666666667</v>
       </c>
       <c r="M832" s="1" t="n">
-        <v>46349.80833333333</v>
+        <v>46350.89166666667</v>
       </c>
     </row>
     <row r="833">
@@ -46150,13 +46150,13 @@
         </is>
       </c>
       <c r="K833" s="1" t="n">
-        <v>46350.89166666667</v>
+        <v>46351.975</v>
       </c>
       <c r="L833" s="1" t="n">
-        <v>46351.05833333333</v>
+        <v>46352.14166666667</v>
       </c>
       <c r="M833" s="1" t="n">
-        <v>46352.05833333333</v>
+        <v>46353.14166666667</v>
       </c>
     </row>
     <row r="834">
@@ -46205,13 +46205,13 @@
         </is>
       </c>
       <c r="K834" s="1" t="n">
-        <v>46356.26666666667</v>
+        <v>46357.35</v>
       </c>
       <c r="L834" s="1" t="n">
-        <v>46356.39166666667</v>
+        <v>46357.475</v>
       </c>
       <c r="M834" s="1" t="n">
-        <v>46356.89166666667</v>
+        <v>46357.975</v>
       </c>
     </row>
     <row r="835">
@@ -46260,13 +46260,13 @@
         </is>
       </c>
       <c r="K835" s="1" t="n">
-        <v>46358.475</v>
+        <v>46359.55833333333</v>
       </c>
       <c r="L835" s="1" t="n">
-        <v>46358.51666666667</v>
+        <v>46359.6</v>
       </c>
       <c r="M835" s="1" t="n">
-        <v>46358.93333333333</v>
+        <v>46360.01666666667</v>
       </c>
     </row>
     <row r="836">
@@ -46315,13 +46315,13 @@
         </is>
       </c>
       <c r="K836" s="1" t="n">
-        <v>46359.1</v>
+        <v>46360.18333333333</v>
       </c>
       <c r="L836" s="1" t="n">
-        <v>46359.225</v>
+        <v>46360.30833333333</v>
       </c>
       <c r="M836" s="1" t="n">
-        <v>46360.225</v>
+        <v>46361.30833333333</v>
       </c>
     </row>
     <row r="837">
@@ -46370,13 +46370,13 @@
         </is>
       </c>
       <c r="K837" s="1" t="n">
-        <v>46360.475</v>
+        <v>46361.55833333333</v>
       </c>
       <c r="L837" s="1" t="n">
-        <v>46360.51666666667</v>
+        <v>46361.6</v>
       </c>
       <c r="M837" s="1" t="n">
-        <v>46360.93333333333</v>
+        <v>46362.01666666667</v>
       </c>
     </row>
     <row r="838">
@@ -46421,13 +46421,13 @@
       </c>
       <c r="J838" t="inlineStr"/>
       <c r="K838" s="1" t="n">
-        <v>46362.43333333333</v>
+        <v>46363.51666666667</v>
       </c>
       <c r="L838" s="1" t="n">
-        <v>46362.55833333333</v>
+        <v>46363.64166666667</v>
       </c>
       <c r="M838" s="1" t="n">
-        <v>46363.05833333333</v>
+        <v>46364.14166666667</v>
       </c>
     </row>
     <row r="839">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46293.625</v>
+        <v>46293.75</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>46293.66666666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>46294.29166666666</v>
@@ -3780,7 +3780,7 @@
         <v>46294.52083333334</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>46295.25</v>
+        <v>46295.08333333334</v>
       </c>
     </row>
     <row r="62">
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46296.14583333334</v>
+        <v>46296.02083333334</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>46296.20833333334</v>
+        <v>46296.08333333334</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>46296.60416666666</v>
+        <v>46296.5</v>
       </c>
     </row>
     <row r="63">
@@ -3884,13 +3884,13 @@
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46296.875</v>
+        <v>46296.77083333334</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>46296.89583333334</v>
+        <v>46297</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>46297.5</v>
+        <v>46297.95833333334</v>
       </c>
     </row>
     <row r="64">
@@ -3939,13 +3939,13 @@
         </is>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46302.41666666666</v>
+        <v>46302.875</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>46302.58333333334</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>46303.16666666666</v>
+        <v>46303.625</v>
       </c>
     </row>
     <row r="65">
@@ -3994,13 +3994,13 @@
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46304.8125</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>46304.85416666666</v>
+        <v>46305.3125</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>46305.20833333334</v>
+        <v>46305.66666666666</v>
       </c>
     </row>
     <row r="66">
@@ -4049,13 +4049,13 @@
         </is>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46305.33333333334</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>46305.41666666666</v>
+        <v>46305.875</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>46306.41666666666</v>
+        <v>46306.875</v>
       </c>
     </row>
     <row r="67">
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46306.625</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>46306.66666666666</v>
+        <v>46307.125</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>46307.16666666666</v>
+        <v>46307.625</v>
       </c>
     </row>
     <row r="68">
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46308.97916666666</v>
+        <v>46309.4375</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>46309.14583333334</v>
+        <v>46309.60416666666</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>46309.83333333334</v>
+        <v>46310.29166666666</v>
       </c>
     </row>
     <row r="69">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46315.04166666666</v>
+        <v>46315.5</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>46315.08333333334</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>46315.75</v>
+        <v>46316.20833333334</v>
       </c>
     </row>
     <row r="70">
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46315.91666666666</v>
+        <v>46316.375</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>46315.97916666666</v>
+        <v>46316.4375</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>46316.22916666666</v>
+        <v>46316.6875</v>
       </c>
     </row>
     <row r="71">
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46317.125</v>
+        <v>46317.58333333334</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>46317.1875</v>
+        <v>46317.64583333334</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>46317.60416666666</v>
+        <v>46318.0625</v>
       </c>
     </row>
     <row r="72">
@@ -4379,13 +4379,13 @@
         </is>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46317.875</v>
+        <v>46318.33333333334</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>46317.89583333334</v>
+        <v>46318.35416666666</v>
       </c>
       <c r="M72" s="1" t="n">
-        <v>46318.5</v>
+        <v>46318.95833333334</v>
       </c>
     </row>
     <row r="73">
@@ -4434,13 +4434,13 @@
         </is>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46323.41666666666</v>
+        <v>46323.875</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>46323.58333333334</v>
+        <v>46324.04166666666</v>
       </c>
       <c r="M73" s="1" t="n">
-        <v>46324.16666666666</v>
+        <v>46324.625</v>
       </c>
     </row>
     <row r="74">
@@ -4489,13 +4489,13 @@
         </is>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46325.8125</v>
+        <v>46326.27083333334</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>46325.85416666666</v>
+        <v>46326.3125</v>
       </c>
       <c r="M74" s="1" t="n">
-        <v>46326.20833333334</v>
+        <v>46326.66666666666</v>
       </c>
     </row>
     <row r="75">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46326.33333333334</v>
+        <v>46326.79166666666</v>
       </c>
       <c r="L75" s="1" t="n">
-        <v>46326.41666666666</v>
+        <v>46326.875</v>
       </c>
       <c r="M75" s="1" t="n">
-        <v>46327.41666666666</v>
+        <v>46327.875</v>
       </c>
     </row>
     <row r="76">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46327.625</v>
+        <v>46328.08333333334</v>
       </c>
       <c r="L76" s="1" t="n">
-        <v>46327.66666666666</v>
+        <v>46328.125</v>
       </c>
       <c r="M76" s="1" t="n">
-        <v>46328.16666666666</v>
+        <v>46328.625</v>
       </c>
     </row>
     <row r="77">
@@ -4654,13 +4654,13 @@
         </is>
       </c>
       <c r="K77" s="1" t="n">
-        <v>46329.97916666666</v>
+        <v>46330.4375</v>
       </c>
       <c r="L77" s="1" t="n">
-        <v>46330.14583333334</v>
+        <v>46330.60416666666</v>
       </c>
       <c r="M77" s="1" t="n">
-        <v>46330.83333333334</v>
+        <v>46331.29166666666</v>
       </c>
     </row>
     <row r="78">
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="K78" s="1" t="n">
-        <v>46336.04166666666</v>
+        <v>46336.5</v>
       </c>
       <c r="L78" s="1" t="n">
-        <v>46336.08333333334</v>
+        <v>46336.54166666666</v>
       </c>
       <c r="M78" s="1" t="n">
-        <v>46336.75</v>
+        <v>46337.20833333334</v>
       </c>
     </row>
     <row r="79">
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="K79" s="1" t="n">
-        <v>46336.91666666666</v>
+        <v>46337.375</v>
       </c>
       <c r="L79" s="1" t="n">
-        <v>46336.97916666666</v>
+        <v>46337.4375</v>
       </c>
       <c r="M79" s="1" t="n">
-        <v>46337.22916666666</v>
+        <v>46337.6875</v>
       </c>
     </row>
     <row r="80">
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="K80" s="1" t="n">
-        <v>46338.125</v>
+        <v>46338.58333333334</v>
       </c>
       <c r="L80" s="1" t="n">
-        <v>46338.1875</v>
+        <v>46338.64583333334</v>
       </c>
       <c r="M80" s="1" t="n">
-        <v>46338.60416666666</v>
+        <v>46339.0625</v>
       </c>
     </row>
     <row r="81">
@@ -4874,13 +4874,13 @@
         </is>
       </c>
       <c r="K81" s="1" t="n">
-        <v>46338.875</v>
+        <v>46339.33333333334</v>
       </c>
       <c r="L81" s="1" t="n">
-        <v>46338.89583333334</v>
+        <v>46339.35416666666</v>
       </c>
       <c r="M81" s="1" t="n">
-        <v>46339.5</v>
+        <v>46339.95833333334</v>
       </c>
     </row>
     <row r="82">
@@ -4929,13 +4929,13 @@
         </is>
       </c>
       <c r="K82" s="1" t="n">
-        <v>46344.41666666666</v>
+        <v>46344.875</v>
       </c>
       <c r="L82" s="1" t="n">
-        <v>46344.58333333334</v>
+        <v>46345.04166666666</v>
       </c>
       <c r="M82" s="1" t="n">
-        <v>46345.16666666666</v>
+        <v>46345.625</v>
       </c>
     </row>
     <row r="83">
@@ -4984,13 +4984,13 @@
         </is>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46346.8125</v>
+        <v>46347.27083333334</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>46346.85416666666</v>
+        <v>46347.3125</v>
       </c>
       <c r="M83" s="1" t="n">
-        <v>46347.20833333334</v>
+        <v>46347.66666666666</v>
       </c>
     </row>
     <row r="84">
@@ -5039,13 +5039,13 @@
         </is>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46347.33333333334</v>
+        <v>46347.79166666666</v>
       </c>
       <c r="L84" s="1" t="n">
-        <v>46347.41666666666</v>
+        <v>46347.875</v>
       </c>
       <c r="M84" s="1" t="n">
-        <v>46348.41666666666</v>
+        <v>46348.875</v>
       </c>
     </row>
     <row r="85">
@@ -5094,13 +5094,13 @@
         </is>
       </c>
       <c r="K85" s="1" t="n">
-        <v>46348.625</v>
+        <v>46349.08333333334</v>
       </c>
       <c r="L85" s="1" t="n">
-        <v>46348.66666666666</v>
+        <v>46349.125</v>
       </c>
       <c r="M85" s="1" t="n">
-        <v>46349.16666666666</v>
+        <v>46349.625</v>
       </c>
     </row>
     <row r="86">
@@ -5145,13 +5145,13 @@
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" s="1" t="n">
-        <v>46350.97916666666</v>
+        <v>46351.4375</v>
       </c>
       <c r="L86" s="1" t="n">
-        <v>46351.14583333334</v>
+        <v>46351.60416666666</v>
       </c>
       <c r="M86" s="1" t="n">
-        <v>46351.83333333334</v>
+        <v>46352.29166666666</v>
       </c>
     </row>
     <row r="87">
@@ -11784,13 +11784,13 @@
         </is>
       </c>
       <c r="K207" s="1" t="n">
-        <v>46294.02083333334</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="L207" s="1" t="n">
-        <v>46294.1875</v>
+        <v>46294.25</v>
       </c>
       <c r="M207" s="1" t="n">
-        <v>46294.5625</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="208">
@@ -11839,13 +11839,13 @@
         </is>
       </c>
       <c r="K208" s="1" t="n">
-        <v>46296.33333333334</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="L208" s="1" t="n">
-        <v>46296.375</v>
+        <v>46296.83333333334</v>
       </c>
       <c r="M208" s="1" t="n">
-        <v>46296.625</v>
+        <v>46297.08333333334</v>
       </c>
     </row>
     <row r="209">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="K209" s="1" t="n">
-        <v>46296.75</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="L209" s="1" t="n">
-        <v>46296.875</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="M209" s="1" t="n">
-        <v>46298.375</v>
+        <v>46298.83333333334</v>
       </c>
     </row>
     <row r="210">
@@ -11949,13 +11949,13 @@
         </is>
       </c>
       <c r="K210" s="1" t="n">
-        <v>46298.58333333334</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="L210" s="1" t="n">
-        <v>46298.625</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="M210" s="1" t="n">
-        <v>46299.04166666666</v>
+        <v>46299.5</v>
       </c>
     </row>
     <row r="211">
@@ -12004,13 +12004,13 @@
         </is>
       </c>
       <c r="K211" s="1" t="n">
-        <v>46300.66666666666</v>
+        <v>46301.125</v>
       </c>
       <c r="L211" s="1" t="n">
-        <v>46300.83333333334</v>
+        <v>46301.29166666666</v>
       </c>
       <c r="M211" s="1" t="n">
-        <v>46301.375</v>
+        <v>46301.83333333334</v>
       </c>
     </row>
     <row r="212">
@@ -12059,13 +12059,13 @@
         </is>
       </c>
       <c r="K212" s="1" t="n">
-        <v>46306.95833333334</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="L212" s="1" t="n">
-        <v>46307</v>
+        <v>46307.45833333334</v>
       </c>
       <c r="M212" s="1" t="n">
-        <v>46308.08333333334</v>
+        <v>46308.54166666666</v>
       </c>
     </row>
     <row r="213">
@@ -12114,13 +12114,13 @@
         </is>
       </c>
       <c r="K213" s="1" t="n">
-        <v>46308.20833333334</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="L213" s="1" t="n">
-        <v>46308.25</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="M213" s="1" t="n">
-        <v>46308.5</v>
+        <v>46308.95833333334</v>
       </c>
     </row>
     <row r="214">
@@ -12169,13 +12169,13 @@
         </is>
       </c>
       <c r="K214" s="1" t="n">
-        <v>46308.875</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="L214" s="1" t="n">
-        <v>46308.9375</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="M214" s="1" t="n">
-        <v>46309.27083333334</v>
+        <v>46309.72916666666</v>
       </c>
     </row>
     <row r="215">
@@ -12224,13 +12224,13 @@
         </is>
       </c>
       <c r="K215" s="1" t="n">
-        <v>46314.29166666666</v>
+        <v>46314.75</v>
       </c>
       <c r="L215" s="1" t="n">
-        <v>46314.45833333334</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="M215" s="1" t="n">
-        <v>46315.08333333334</v>
+        <v>46315.54166666666</v>
       </c>
     </row>
     <row r="216">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="K216" s="1" t="n">
-        <v>46316.875</v>
+        <v>46317.33333333334</v>
       </c>
       <c r="L216" s="1" t="n">
-        <v>46316.91666666666</v>
+        <v>46317.375</v>
       </c>
       <c r="M216" s="1" t="n">
-        <v>46317.16666666666</v>
+        <v>46317.625</v>
       </c>
     </row>
     <row r="217">
@@ -12334,13 +12334,13 @@
         </is>
       </c>
       <c r="K217" s="1" t="n">
-        <v>46317.45833333334</v>
+        <v>46317.91666666666</v>
       </c>
       <c r="L217" s="1" t="n">
-        <v>46317.58333333334</v>
+        <v>46318.04166666666</v>
       </c>
       <c r="M217" s="1" t="n">
-        <v>46319.08333333334</v>
+        <v>46319.54166666666</v>
       </c>
     </row>
     <row r="218">
@@ -12389,13 +12389,13 @@
         </is>
       </c>
       <c r="K218" s="1" t="n">
-        <v>46319.29166666666</v>
+        <v>46319.75</v>
       </c>
       <c r="L218" s="1" t="n">
-        <v>46319.33333333334</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="M218" s="1" t="n">
-        <v>46319.75</v>
+        <v>46320.20833333334</v>
       </c>
     </row>
     <row r="219">
@@ -12444,13 +12444,13 @@
         </is>
       </c>
       <c r="K219" s="1" t="n">
-        <v>46321.33333333334</v>
+        <v>46321.79166666666</v>
       </c>
       <c r="L219" s="1" t="n">
-        <v>46321.5</v>
+        <v>46321.95833333334</v>
       </c>
       <c r="M219" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46322.5</v>
       </c>
     </row>
     <row r="220">
@@ -12499,13 +12499,13 @@
         </is>
       </c>
       <c r="K220" s="1" t="n">
-        <v>46325.95833333334</v>
+        <v>46326.41666666666</v>
       </c>
       <c r="L220" s="1" t="n">
-        <v>46326</v>
+        <v>46326.45833333334</v>
       </c>
       <c r="M220" s="1" t="n">
-        <v>46327.08333333334</v>
+        <v>46327.54166666666</v>
       </c>
     </row>
     <row r="221">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="K221" s="1" t="n">
-        <v>46327.20833333334</v>
+        <v>46327.66666666666</v>
       </c>
       <c r="L221" s="1" t="n">
-        <v>46327.25</v>
+        <v>46327.70833333334</v>
       </c>
       <c r="M221" s="1" t="n">
-        <v>46327.5</v>
+        <v>46327.95833333334</v>
       </c>
     </row>
     <row r="222">
@@ -12609,13 +12609,13 @@
         </is>
       </c>
       <c r="K222" s="1" t="n">
-        <v>46327.91666666666</v>
+        <v>46328.375</v>
       </c>
       <c r="L222" s="1" t="n">
-        <v>46328</v>
+        <v>46328.45833333334</v>
       </c>
       <c r="M222" s="1" t="n">
-        <v>46328.33333333334</v>
+        <v>46328.79166666666</v>
       </c>
     </row>
     <row r="223">
@@ -12664,13 +12664,13 @@
         </is>
       </c>
       <c r="K223" s="1" t="n">
-        <v>46333.33333333334</v>
+        <v>46333.79166666666</v>
       </c>
       <c r="L223" s="1" t="n">
-        <v>46333.5</v>
+        <v>46333.95833333334</v>
       </c>
       <c r="M223" s="1" t="n">
-        <v>46334.125</v>
+        <v>46334.58333333334</v>
       </c>
     </row>
     <row r="224">
@@ -12719,13 +12719,13 @@
         </is>
       </c>
       <c r="K224" s="1" t="n">
-        <v>46335.91666666666</v>
+        <v>46336.375</v>
       </c>
       <c r="L224" s="1" t="n">
-        <v>46335.95833333334</v>
+        <v>46336.41666666666</v>
       </c>
       <c r="M224" s="1" t="n">
-        <v>46336.20833333334</v>
+        <v>46336.66666666666</v>
       </c>
     </row>
     <row r="225">
@@ -12774,13 +12774,13 @@
         </is>
       </c>
       <c r="K225" s="1" t="n">
-        <v>46336.5</v>
+        <v>46336.95833333334</v>
       </c>
       <c r="L225" s="1" t="n">
-        <v>46336.625</v>
+        <v>46337.08333333334</v>
       </c>
       <c r="M225" s="1" t="n">
-        <v>46338.125</v>
+        <v>46338.58333333334</v>
       </c>
     </row>
     <row r="226">
@@ -12829,13 +12829,13 @@
         </is>
       </c>
       <c r="K226" s="1" t="n">
-        <v>46338.33333333334</v>
+        <v>46338.79166666666</v>
       </c>
       <c r="L226" s="1" t="n">
-        <v>46338.375</v>
+        <v>46338.83333333334</v>
       </c>
       <c r="M226" s="1" t="n">
-        <v>46338.79166666666</v>
+        <v>46339.25</v>
       </c>
     </row>
     <row r="227">
@@ -12884,13 +12884,13 @@
         </is>
       </c>
       <c r="K227" s="1" t="n">
-        <v>46340.375</v>
+        <v>46340.83333333334</v>
       </c>
       <c r="L227" s="1" t="n">
-        <v>46340.54166666666</v>
+        <v>46341</v>
       </c>
       <c r="M227" s="1" t="n">
-        <v>46341.08333333334</v>
+        <v>46341.54166666666</v>
       </c>
     </row>
     <row r="228">
@@ -12939,13 +12939,13 @@
         </is>
       </c>
       <c r="K228" s="1" t="n">
-        <v>46344.625</v>
+        <v>46345.08333333334</v>
       </c>
       <c r="L228" s="1" t="n">
-        <v>46344.66666666666</v>
+        <v>46345.125</v>
       </c>
       <c r="M228" s="1" t="n">
-        <v>46345.75</v>
+        <v>46346.20833333334</v>
       </c>
     </row>
     <row r="229">
@@ -12994,13 +12994,13 @@
         </is>
       </c>
       <c r="K229" s="1" t="n">
-        <v>46345.875</v>
+        <v>46346.33333333334</v>
       </c>
       <c r="L229" s="1" t="n">
-        <v>46345.91666666666</v>
+        <v>46346.375</v>
       </c>
       <c r="M229" s="1" t="n">
-        <v>46346.16666666666</v>
+        <v>46346.625</v>
       </c>
     </row>
     <row r="230">
@@ -13049,13 +13049,13 @@
         </is>
       </c>
       <c r="K230" s="1" t="n">
-        <v>46346.58333333334</v>
+        <v>46347.04166666666</v>
       </c>
       <c r="L230" s="1" t="n">
-        <v>46346.66666666666</v>
+        <v>46347.125</v>
       </c>
       <c r="M230" s="1" t="n">
-        <v>46347</v>
+        <v>46347.45833333334</v>
       </c>
     </row>
     <row r="231">
@@ -13104,13 +13104,13 @@
         </is>
       </c>
       <c r="K231" s="1" t="n">
-        <v>46352</v>
+        <v>46352.45833333334</v>
       </c>
       <c r="L231" s="1" t="n">
-        <v>46352.16666666666</v>
+        <v>46352.625</v>
       </c>
       <c r="M231" s="1" t="n">
-        <v>46352.79166666666</v>
+        <v>46353.25</v>
       </c>
     </row>
     <row r="232">
@@ -13159,13 +13159,13 @@
         </is>
       </c>
       <c r="K232" s="1" t="n">
-        <v>46354.58333333334</v>
+        <v>46355.04166666666</v>
       </c>
       <c r="L232" s="1" t="n">
-        <v>46354.625</v>
+        <v>46355.08333333334</v>
       </c>
       <c r="M232" s="1" t="n">
-        <v>46354.875</v>
+        <v>46355.33333333334</v>
       </c>
     </row>
     <row r="233">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="K233" s="1" t="n">
-        <v>46355.16666666666</v>
+        <v>46355.625</v>
       </c>
       <c r="L233" s="1" t="n">
-        <v>46355.29166666666</v>
+        <v>46355.75</v>
       </c>
       <c r="M233" s="1" t="n">
-        <v>46356.79166666666</v>
+        <v>46357.25</v>
       </c>
     </row>
     <row r="234">
@@ -13269,13 +13269,13 @@
         </is>
       </c>
       <c r="K234" s="1" t="n">
-        <v>46357</v>
+        <v>46357.45833333334</v>
       </c>
       <c r="L234" s="1" t="n">
-        <v>46357.04166666666</v>
+        <v>46357.5</v>
       </c>
       <c r="M234" s="1" t="n">
-        <v>46357.45833333334</v>
+        <v>46357.91666666666</v>
       </c>
     </row>
     <row r="235">
@@ -13320,13 +13320,13 @@
       </c>
       <c r="J235" t="inlineStr"/>
       <c r="K235" s="1" t="n">
-        <v>46359.04166666666</v>
+        <v>46359.5</v>
       </c>
       <c r="L235" s="1" t="n">
-        <v>46359.20833333334</v>
+        <v>46359.66666666666</v>
       </c>
       <c r="M235" s="1" t="n">
-        <v>46359.75</v>
+        <v>46360.20833333334</v>
       </c>
     </row>
     <row r="236">
@@ -50926,10 +50926,10 @@
         <v>46294.35416666666</v>
       </c>
       <c r="L920" s="1" t="n">
-        <v>46295.04166666666</v>
+        <v>46295.41666666666</v>
       </c>
       <c r="M920" s="1" t="n">
-        <v>46295.95833333334</v>
+        <v>46296.5</v>
       </c>
     </row>
     <row r="921">
@@ -50978,13 +50978,13 @@
         </is>
       </c>
       <c r="K921" s="1" t="n">
-        <v>46296.25</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="L921" s="1" t="n">
-        <v>46296.3125</v>
+        <v>46296.85416666666</v>
       </c>
       <c r="M921" s="1" t="n">
-        <v>46296.58333333334</v>
+        <v>46297.125</v>
       </c>
     </row>
     <row r="922">
@@ -51033,13 +51033,13 @@
         </is>
       </c>
       <c r="K922" s="1" t="n">
-        <v>46299.41666666666</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="L922" s="1" t="n">
-        <v>46299.45833333334</v>
+        <v>46300</v>
       </c>
       <c r="M922" s="1" t="n">
-        <v>46299.91666666666</v>
+        <v>46300.45833333334</v>
       </c>
     </row>
     <row r="923">
@@ -51088,13 +51088,13 @@
         </is>
       </c>
       <c r="K923" s="1" t="n">
-        <v>46302.08333333334</v>
+        <v>46302.625</v>
       </c>
       <c r="L923" s="1" t="n">
-        <v>46302.25</v>
+        <v>46302.79166666666</v>
       </c>
       <c r="M923" s="1" t="n">
-        <v>46302.70833333334</v>
+        <v>46303.25</v>
       </c>
     </row>
     <row r="924">
@@ -51143,13 +51143,13 @@
         </is>
       </c>
       <c r="K924" s="1" t="n">
-        <v>46304.29166666666</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="L924" s="1" t="n">
-        <v>46304.33333333334</v>
+        <v>46304.875</v>
       </c>
       <c r="M924" s="1" t="n">
-        <v>46304.58333333334</v>
+        <v>46305.125</v>
       </c>
     </row>
     <row r="925">
@@ -51198,13 +51198,13 @@
         </is>
       </c>
       <c r="K925" s="1" t="n">
-        <v>46304.75</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="L925" s="1" t="n">
-        <v>46304.875</v>
+        <v>46305.41666666666</v>
       </c>
       <c r="M925" s="1" t="n">
-        <v>46306.375</v>
+        <v>46306.91666666666</v>
       </c>
     </row>
     <row r="926">
@@ -51253,13 +51253,13 @@
         </is>
       </c>
       <c r="K926" s="1" t="n">
-        <v>46306.54166666666</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="L926" s="1" t="n">
-        <v>46306.58333333334</v>
+        <v>46307.125</v>
       </c>
       <c r="M926" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46307.375</v>
       </c>
     </row>
     <row r="927">
@@ -51308,13 +51308,13 @@
         </is>
       </c>
       <c r="K927" s="1" t="n">
-        <v>46310.5625</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="L927" s="1" t="n">
-        <v>46310.625</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="M927" s="1" t="n">
-        <v>46311.08333333334</v>
+        <v>46311.625</v>
       </c>
     </row>
     <row r="928">
@@ -51363,13 +51363,13 @@
         </is>
       </c>
       <c r="K928" s="1" t="n">
-        <v>46311.95833333334</v>
+        <v>46312.41666666666</v>
       </c>
       <c r="L928" s="1" t="n">
-        <v>46312</v>
+        <v>46312.45833333334</v>
       </c>
       <c r="M928" s="1" t="n">
-        <v>46312.58333333334</v>
+        <v>46313.04166666666</v>
       </c>
     </row>
     <row r="929">
@@ -51418,13 +51418,13 @@
         </is>
       </c>
       <c r="K929" s="1" t="n">
-        <v>46314.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="L929" s="1" t="n">
-        <v>46314.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="M929" s="1" t="n">
-        <v>46315.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
     </row>
     <row r="930">
@@ -51473,13 +51473,13 @@
         </is>
       </c>
       <c r="K930" s="1" t="n">
-        <v>46315.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="L930" s="1" t="n">
-        <v>46315.52083333334</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="M930" s="1" t="n">
-        <v>46315.79166666666</v>
+        <v>46316.79166666666</v>
       </c>
     </row>
     <row r="931">
@@ -51528,13 +51528,13 @@
         </is>
       </c>
       <c r="K931" s="1" t="n">
-        <v>46318.70833333334</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="L931" s="1" t="n">
-        <v>46318.75</v>
+        <v>46319.75</v>
       </c>
       <c r="M931" s="1" t="n">
-        <v>46319.20833333334</v>
+        <v>46320.20833333334</v>
       </c>
     </row>
     <row r="932">
@@ -51583,13 +51583,13 @@
         </is>
       </c>
       <c r="K932" s="1" t="n">
-        <v>46321.41666666666</v>
+        <v>46322.41666666666</v>
       </c>
       <c r="L932" s="1" t="n">
-        <v>46321.58333333334</v>
+        <v>46322.58333333334</v>
       </c>
       <c r="M932" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46323.04166666666</v>
       </c>
     </row>
     <row r="933">
@@ -51638,13 +51638,13 @@
         </is>
       </c>
       <c r="K933" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46324.70833333334</v>
       </c>
       <c r="L933" s="1" t="n">
-        <v>46323.75</v>
+        <v>46324.75</v>
       </c>
       <c r="M933" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="934">
@@ -51693,13 +51693,13 @@
         </is>
       </c>
       <c r="K934" s="1" t="n">
-        <v>46324.16666666666</v>
+        <v>46325.16666666666</v>
       </c>
       <c r="L934" s="1" t="n">
-        <v>46324.29166666666</v>
+        <v>46325.29166666666</v>
       </c>
       <c r="M934" s="1" t="n">
-        <v>46325.79166666666</v>
+        <v>46326.79166666666</v>
       </c>
     </row>
     <row r="935">
@@ -51748,13 +51748,13 @@
         </is>
       </c>
       <c r="K935" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="L935" s="1" t="n">
-        <v>46326.04166666666</v>
+        <v>46327.04166666666</v>
       </c>
       <c r="M935" s="1" t="n">
-        <v>46326.29166666666</v>
+        <v>46327.29166666666</v>
       </c>
     </row>
     <row r="936">
@@ -51803,13 +51803,13 @@
         </is>
       </c>
       <c r="K936" s="1" t="n">
-        <v>46330.125</v>
+        <v>46331.125</v>
       </c>
       <c r="L936" s="1" t="n">
-        <v>46330.16666666666</v>
+        <v>46331.16666666666</v>
       </c>
       <c r="M936" s="1" t="n">
-        <v>46330.625</v>
+        <v>46331.625</v>
       </c>
     </row>
     <row r="937">
@@ -51858,13 +51858,13 @@
         </is>
       </c>
       <c r="K937" s="1" t="n">
-        <v>46331.375</v>
+        <v>46332.375</v>
       </c>
       <c r="L937" s="1" t="n">
-        <v>46331.41666666666</v>
+        <v>46332.41666666666</v>
       </c>
       <c r="M937" s="1" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
     </row>
     <row r="938">
@@ -51913,13 +51913,13 @@
         </is>
       </c>
       <c r="K938" s="1" t="n">
-        <v>46334.16666666666</v>
+        <v>46335.29166666666</v>
       </c>
       <c r="L938" s="1" t="n">
-        <v>46334.20833333334</v>
+        <v>46335.33333333334</v>
       </c>
       <c r="M938" s="1" t="n">
-        <v>46334.91666666666</v>
+        <v>46336.04166666666</v>
       </c>
     </row>
     <row r="939">
@@ -51968,13 +51968,13 @@
         </is>
       </c>
       <c r="K939" s="1" t="n">
-        <v>46335.25</v>
+        <v>46336.375</v>
       </c>
       <c r="L939" s="1" t="n">
-        <v>46335.33333333334</v>
+        <v>46336.45833333334</v>
       </c>
       <c r="M939" s="1" t="n">
-        <v>46335.58333333334</v>
+        <v>46336.70833333334</v>
       </c>
     </row>
     <row r="940">
@@ -52023,13 +52023,13 @@
         </is>
       </c>
       <c r="K940" s="1" t="n">
-        <v>46338.5</v>
+        <v>46339.625</v>
       </c>
       <c r="L940" s="1" t="n">
-        <v>46338.54166666666</v>
+        <v>46339.66666666666</v>
       </c>
       <c r="M940" s="1" t="n">
-        <v>46339</v>
+        <v>46340.125</v>
       </c>
     </row>
     <row r="941">
@@ -52078,13 +52078,13 @@
         </is>
       </c>
       <c r="K941" s="1" t="n">
-        <v>46341.20833333334</v>
+        <v>46342.33333333334</v>
       </c>
       <c r="L941" s="1" t="n">
-        <v>46341.375</v>
+        <v>46342.5</v>
       </c>
       <c r="M941" s="1" t="n">
-        <v>46341.83333333334</v>
+        <v>46342.95833333334</v>
       </c>
     </row>
     <row r="942">
@@ -52133,13 +52133,13 @@
         </is>
       </c>
       <c r="K942" s="1" t="n">
-        <v>46343.58333333334</v>
+        <v>46344.70833333334</v>
       </c>
       <c r="L942" s="1" t="n">
-        <v>46343.625</v>
+        <v>46344.75</v>
       </c>
       <c r="M942" s="1" t="n">
-        <v>46343.79166666666</v>
+        <v>46344.91666666666</v>
       </c>
     </row>
     <row r="943">
@@ -52188,13 +52188,13 @@
         </is>
       </c>
       <c r="K943" s="1" t="n">
-        <v>46344.04166666666</v>
+        <v>46345.16666666666</v>
       </c>
       <c r="L943" s="1" t="n">
-        <v>46344.16666666666</v>
+        <v>46345.29166666666</v>
       </c>
       <c r="M943" s="1" t="n">
-        <v>46345.5</v>
+        <v>46346.625</v>
       </c>
     </row>
     <row r="944">
@@ -52243,13 +52243,13 @@
         </is>
       </c>
       <c r="K944" s="1" t="n">
-        <v>46346</v>
+        <v>46347.125</v>
       </c>
       <c r="L944" s="1" t="n">
-        <v>46346.04166666666</v>
+        <v>46347.16666666666</v>
       </c>
       <c r="M944" s="1" t="n">
-        <v>46346.33333333334</v>
+        <v>46347.45833333334</v>
       </c>
     </row>
     <row r="945">
@@ -52298,13 +52298,13 @@
         </is>
       </c>
       <c r="K945" s="1" t="n">
-        <v>46350.41666666666</v>
+        <v>46351.54166666666</v>
       </c>
       <c r="L945" s="1" t="n">
-        <v>46350.45833333334</v>
+        <v>46351.58333333334</v>
       </c>
       <c r="M945" s="1" t="n">
-        <v>46350.91666666666</v>
+        <v>46352.04166666666</v>
       </c>
     </row>
     <row r="946">
@@ -52353,13 +52353,13 @@
         </is>
       </c>
       <c r="K946" s="1" t="n">
-        <v>46352</v>
+        <v>46353.125</v>
       </c>
       <c r="L946" s="1" t="n">
-        <v>46352.04166666666</v>
+        <v>46353.16666666666</v>
       </c>
       <c r="M946" s="1" t="n">
-        <v>46352.625</v>
+        <v>46353.75</v>
       </c>
     </row>
     <row r="947">
@@ -58552,13 +58552,13 @@
         </is>
       </c>
       <c r="K1059" s="1" t="n">
-        <v>46301.95833333334</v>
+        <v>46308</v>
       </c>
       <c r="L1059" s="1" t="n">
-        <v>46302.04166666666</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="M1059" s="1" t="n">
-        <v>46302.875</v>
+        <v>46308.91666666666</v>
       </c>
     </row>
     <row r="1060">
@@ -58607,13 +58607,13 @@
         </is>
       </c>
       <c r="K1060" s="1" t="n">
-        <v>46303.875</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="L1060" s="1" t="n">
-        <v>46303.95833333334</v>
+        <v>46310</v>
       </c>
       <c r="M1060" s="1" t="n">
-        <v>46304.45833333334</v>
+        <v>46310.5</v>
       </c>
     </row>
     <row r="1061">
@@ -58662,13 +58662,13 @@
         </is>
       </c>
       <c r="K1061" s="1" t="n">
-        <v>46305.625</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="L1061" s="1" t="n">
-        <v>46305.79166666666</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="M1061" s="1" t="n">
-        <v>46306.54166666666</v>
+        <v>46312.58333333334</v>
       </c>
     </row>
     <row r="1062">
@@ -58717,13 +58717,13 @@
         </is>
       </c>
       <c r="K1062" s="1" t="n">
-        <v>46312.875</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="L1062" s="1" t="n">
-        <v>46312.91666666666</v>
+        <v>46318.95833333334</v>
       </c>
       <c r="M1062" s="1" t="n">
-        <v>46313.20833333334</v>
+        <v>46319.25</v>
       </c>
     </row>
     <row r="1063">
@@ -58772,13 +58772,13 @@
         </is>
       </c>
       <c r="K1063" s="1" t="n">
-        <v>46313.5</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="L1063" s="1" t="n">
-        <v>46313.5</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="M1063" s="1" t="n">
-        <v>46314.875</v>
+        <v>46320.91666666666</v>
       </c>
     </row>
     <row r="1064">
@@ -58827,13 +58827,13 @@
         </is>
       </c>
       <c r="K1064" s="1" t="n">
-        <v>46315.125</v>
+        <v>46321.16666666666</v>
       </c>
       <c r="L1064" s="1" t="n">
-        <v>46315.16666666666</v>
+        <v>46321.20833333334</v>
       </c>
       <c r="M1064" s="1" t="n">
-        <v>46315.625</v>
+        <v>46321.66666666666</v>
       </c>
     </row>
     <row r="1065">
@@ -58882,13 +58882,13 @@
         </is>
       </c>
       <c r="K1065" s="1" t="n">
-        <v>46319.45833333334</v>
+        <v>46325.5</v>
       </c>
       <c r="L1065" s="1" t="n">
-        <v>46319.45833333334</v>
+        <v>46325.5</v>
       </c>
       <c r="M1065" s="1" t="n">
-        <v>46319.91666666666</v>
+        <v>46325.95833333334</v>
       </c>
     </row>
     <row r="1066">
@@ -58937,13 +58937,13 @@
         </is>
       </c>
       <c r="K1066" s="1" t="n">
-        <v>46320.91666666666</v>
+        <v>46326.95833333334</v>
       </c>
       <c r="L1066" s="1" t="n">
-        <v>46320.91666666666</v>
+        <v>46326.95833333334</v>
       </c>
       <c r="M1066" s="1" t="n">
-        <v>46321.41666666666</v>
+        <v>46327.45833333334</v>
       </c>
     </row>
     <row r="1067">
@@ -58992,13 +58992,13 @@
         </is>
       </c>
       <c r="K1067" s="1" t="n">
-        <v>46323.875</v>
+        <v>46329.91666666666</v>
       </c>
       <c r="L1067" s="1" t="n">
-        <v>46323.91666666666</v>
+        <v>46329.95833333334</v>
       </c>
       <c r="M1067" s="1" t="n">
-        <v>46324.54166666666</v>
+        <v>46330.58333333334</v>
       </c>
     </row>
     <row r="1068">
@@ -59047,13 +59047,13 @@
         </is>
       </c>
       <c r="K1068" s="1" t="n">
-        <v>46325.54166666666</v>
+        <v>46331.58333333334</v>
       </c>
       <c r="L1068" s="1" t="n">
-        <v>46325.58333333334</v>
+        <v>46331.625</v>
       </c>
       <c r="M1068" s="1" t="n">
-        <v>46326.08333333334</v>
+        <v>46332.125</v>
       </c>
     </row>
     <row r="1069">
@@ -59102,13 +59102,13 @@
         </is>
       </c>
       <c r="K1069" s="1" t="n">
-        <v>46327.16666666666</v>
+        <v>46333.20833333334</v>
       </c>
       <c r="L1069" s="1" t="n">
-        <v>46327.33333333334</v>
+        <v>46333.375</v>
       </c>
       <c r="M1069" s="1" t="n">
-        <v>46328.125</v>
+        <v>46334.16666666666</v>
       </c>
     </row>
     <row r="1070">
@@ -59157,13 +59157,13 @@
         </is>
       </c>
       <c r="K1070" s="1" t="n">
-        <v>46333.875</v>
+        <v>46339.91666666666</v>
       </c>
       <c r="L1070" s="1" t="n">
-        <v>46333.91666666666</v>
+        <v>46339.95833333334</v>
       </c>
       <c r="M1070" s="1" t="n">
-        <v>46334.20833333334</v>
+        <v>46340.25</v>
       </c>
     </row>
     <row r="1071">
@@ -59212,13 +59212,13 @@
         </is>
       </c>
       <c r="K1071" s="1" t="n">
-        <v>46334.5</v>
+        <v>46340.54166666666</v>
       </c>
       <c r="L1071" s="1" t="n">
-        <v>46334.5</v>
+        <v>46340.54166666666</v>
       </c>
       <c r="M1071" s="1" t="n">
-        <v>46335.875</v>
+        <v>46341.91666666666</v>
       </c>
     </row>
     <row r="1072">
@@ -59267,13 +59267,13 @@
         </is>
       </c>
       <c r="K1072" s="1" t="n">
-        <v>46336.125</v>
+        <v>46342.16666666666</v>
       </c>
       <c r="L1072" s="1" t="n">
-        <v>46336.16666666666</v>
+        <v>46342.20833333334</v>
       </c>
       <c r="M1072" s="1" t="n">
-        <v>46336.625</v>
+        <v>46342.66666666666</v>
       </c>
     </row>
     <row r="1073">
@@ -59322,13 +59322,13 @@
         </is>
       </c>
       <c r="K1073" s="1" t="n">
-        <v>46340.45833333334</v>
+        <v>46346.5</v>
       </c>
       <c r="L1073" s="1" t="n">
-        <v>46340.45833333334</v>
+        <v>46346.5</v>
       </c>
       <c r="M1073" s="1" t="n">
-        <v>46340.91666666666</v>
+        <v>46346.95833333334</v>
       </c>
     </row>
     <row r="1074">
@@ -59377,13 +59377,13 @@
         </is>
       </c>
       <c r="K1074" s="1" t="n">
-        <v>46341.91666666666</v>
+        <v>46347.95833333334</v>
       </c>
       <c r="L1074" s="1" t="n">
-        <v>46341.91666666666</v>
+        <v>46347.95833333334</v>
       </c>
       <c r="M1074" s="1" t="n">
-        <v>46342.41666666666</v>
+        <v>46348.45833333334</v>
       </c>
     </row>
     <row r="1075">
@@ -59432,13 +59432,13 @@
         </is>
       </c>
       <c r="K1075" s="1" t="n">
-        <v>46344.875</v>
+        <v>46350.91666666666</v>
       </c>
       <c r="L1075" s="1" t="n">
-        <v>46344.91666666666</v>
+        <v>46350.95833333334</v>
       </c>
       <c r="M1075" s="1" t="n">
-        <v>46345.54166666666</v>
+        <v>46351.58333333334</v>
       </c>
     </row>
     <row r="1076">
@@ -59487,13 +59487,13 @@
         </is>
       </c>
       <c r="K1076" s="1" t="n">
-        <v>46346.54166666666</v>
+        <v>46352.58333333334</v>
       </c>
       <c r="L1076" s="1" t="n">
-        <v>46346.58333333334</v>
+        <v>46352.625</v>
       </c>
       <c r="M1076" s="1" t="n">
-        <v>46347.08333333334</v>
+        <v>46353.125</v>
       </c>
     </row>
     <row r="1077">
@@ -59542,13 +59542,13 @@
         </is>
       </c>
       <c r="K1077" s="1" t="n">
-        <v>46348.16666666666</v>
+        <v>46354.20833333334</v>
       </c>
       <c r="L1077" s="1" t="n">
-        <v>46348.33333333334</v>
+        <v>46354.375</v>
       </c>
       <c r="M1077" s="1" t="n">
-        <v>46349.125</v>
+        <v>46355.16666666666</v>
       </c>
     </row>
     <row r="1078">
@@ -59597,13 +59597,13 @@
         </is>
       </c>
       <c r="K1078" s="1" t="n">
-        <v>46354.875</v>
+        <v>46360.91666666666</v>
       </c>
       <c r="L1078" s="1" t="n">
-        <v>46354.91666666666</v>
+        <v>46360.95833333334</v>
       </c>
       <c r="M1078" s="1" t="n">
-        <v>46355.20833333334</v>
+        <v>46361.25</v>
       </c>
     </row>
     <row r="1079">
@@ -59652,13 +59652,13 @@
         </is>
       </c>
       <c r="K1079" s="1" t="n">
-        <v>46355.5</v>
+        <v>46361.54166666666</v>
       </c>
       <c r="L1079" s="1" t="n">
-        <v>46355.5</v>
+        <v>46361.54166666666</v>
       </c>
       <c r="M1079" s="1" t="n">
-        <v>46356.875</v>
+        <v>46362.91666666666</v>
       </c>
     </row>
     <row r="1080">
@@ -59707,13 +59707,13 @@
         </is>
       </c>
       <c r="K1080" s="1" t="n">
-        <v>46357.125</v>
+        <v>46363.16666666666</v>
       </c>
       <c r="L1080" s="1" t="n">
-        <v>46357.16666666666</v>
+        <v>46363.20833333334</v>
       </c>
       <c r="M1080" s="1" t="n">
-        <v>46357.625</v>
+        <v>46363.66666666666</v>
       </c>
     </row>
     <row r="1081">
@@ -59762,13 +59762,13 @@
         </is>
       </c>
       <c r="K1081" s="1" t="n">
-        <v>46361.45833333334</v>
+        <v>46367.5</v>
       </c>
       <c r="L1081" s="1" t="n">
-        <v>46361.45833333334</v>
+        <v>46367.5</v>
       </c>
       <c r="M1081" s="1" t="n">
-        <v>46361.91666666666</v>
+        <v>46367.95833333334</v>
       </c>
     </row>
     <row r="1082">
@@ -59813,13 +59813,13 @@
       </c>
       <c r="J1082" t="inlineStr"/>
       <c r="K1082" s="1" t="n">
-        <v>46362.91666666666</v>
+        <v>46368.95833333334</v>
       </c>
       <c r="L1082" s="1" t="n">
-        <v>46362.91666666666</v>
+        <v>46368.95833333334</v>
       </c>
       <c r="M1082" s="1" t="n">
-        <v>46363.41666666666</v>
+        <v>46369.45833333334</v>
       </c>
     </row>
     <row r="1083">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -8550,10 +8550,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>46296.33333333334</v>
+        <v>46296.41666666666</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>46298</v>
+        <v>46298.08333333334</v>
       </c>
     </row>
     <row r="149">
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46298.29166666666</v>
+        <v>46298.375</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>46298.35416666666</v>
+        <v>46298.4375</v>
       </c>
       <c r="M149" s="1" t="n">
-        <v>46298.97916666666</v>
+        <v>46299.0625</v>
       </c>
     </row>
     <row r="150">
@@ -8657,13 +8657,13 @@
         </is>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46300.47916666666</v>
+        <v>46300.5625</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>46300.6875</v>
+        <v>46300.77083333334</v>
       </c>
       <c r="M150" s="1" t="n">
-        <v>46301.35416666666</v>
+        <v>46301.4375</v>
       </c>
     </row>
     <row r="151">
@@ -8712,13 +8712,13 @@
         </is>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46308.35416666666</v>
+        <v>46308.4375</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>46308.4375</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="M151" s="1" t="n">
-        <v>46309.27083333334</v>
+        <v>46309.35416666666</v>
       </c>
     </row>
     <row r="152">
@@ -8767,13 +8767,13 @@
         </is>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46310.35416666666</v>
+        <v>46310.4375</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>46310.4375</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="M152" s="1" t="n">
-        <v>46310.9375</v>
+        <v>46311.02083333334</v>
       </c>
     </row>
     <row r="153">
@@ -8822,13 +8822,13 @@
         </is>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46314.9375</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>46314.97916666666</v>
+        <v>46315.0625</v>
       </c>
       <c r="M153" s="1" t="n">
-        <v>46315.64583333334</v>
+        <v>46315.72916666666</v>
       </c>
     </row>
     <row r="154">
@@ -8877,13 +8877,13 @@
         </is>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46322.0625</v>
+        <v>46322.14583333334</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>46322.27083333334</v>
+        <v>46322.35416666666</v>
       </c>
       <c r="M154" s="1" t="n">
-        <v>46322.9375</v>
+        <v>46323.02083333334</v>
       </c>
     </row>
     <row r="155">
@@ -27272,7 +27272,7 @@
         <v>46293.79166666666</v>
       </c>
       <c r="M489" s="1" t="n">
-        <v>46296.25</v>
+        <v>46296.33333333334</v>
       </c>
     </row>
     <row r="490">
@@ -27376,13 +27376,13 @@
         </is>
       </c>
       <c r="K491" s="1" t="n">
-        <v>46296.54166666666</v>
+        <v>46296.625</v>
       </c>
       <c r="L491" s="1" t="n">
-        <v>46296.60416666666</v>
+        <v>46296.6875</v>
       </c>
       <c r="M491" s="1" t="n">
-        <v>46297.125</v>
+        <v>46297.20833333334</v>
       </c>
     </row>
     <row r="492">
@@ -27431,13 +27431,13 @@
         </is>
       </c>
       <c r="K492" s="1" t="n">
-        <v>46298.58333333334</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="L492" s="1" t="n">
-        <v>46299.66666666666</v>
+        <v>46299.75</v>
       </c>
       <c r="M492" s="1" t="n">
-        <v>46300.16666666666</v>
+        <v>46300.25</v>
       </c>
     </row>
     <row r="493">
@@ -27486,13 +27486,13 @@
         </is>
       </c>
       <c r="K493" s="1" t="n">
-        <v>46303.125</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="L493" s="1" t="n">
-        <v>46303.25</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="M493" s="1" t="n">
-        <v>46303.66666666666</v>
+        <v>46303.75</v>
       </c>
     </row>
     <row r="494">
@@ -27541,13 +27541,13 @@
         </is>
       </c>
       <c r="K494" s="1" t="n">
-        <v>46315.91666666666</v>
+        <v>46316</v>
       </c>
       <c r="L494" s="1" t="n">
-        <v>46317</v>
+        <v>46317.08333333334</v>
       </c>
       <c r="M494" s="1" t="n">
-        <v>46317.66666666666</v>
+        <v>46317.75</v>
       </c>
     </row>
     <row r="495">
@@ -27596,13 +27596,13 @@
         </is>
       </c>
       <c r="K495" s="1" t="n">
-        <v>46318.91666666666</v>
+        <v>46319</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>46319</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="M495" s="1" t="n">
-        <v>46319.5</v>
+        <v>46319.58333333334</v>
       </c>
     </row>
     <row r="496">
@@ -27651,13 +27651,13 @@
         </is>
       </c>
       <c r="K496" s="1" t="n">
-        <v>46320.41666666666</v>
+        <v>46320.5</v>
       </c>
       <c r="L496" s="1" t="n">
-        <v>46320.5</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="M496" s="1" t="n">
-        <v>46321.08333333334</v>
+        <v>46321.16666666666</v>
       </c>
     </row>
     <row r="497">
@@ -27706,13 +27706,13 @@
         </is>
       </c>
       <c r="K497" s="1" t="n">
-        <v>46329.95833333334</v>
+        <v>46330.04166666666</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>46331</v>
+        <v>46331.08333333334</v>
       </c>
       <c r="M497" s="1" t="n">
-        <v>46331.58333333334</v>
+        <v>46331.66666666666</v>
       </c>
     </row>
     <row r="498">
@@ -27757,13 +27757,13 @@
       </c>
       <c r="J498" t="inlineStr"/>
       <c r="K498" s="1" t="n">
-        <v>46340.375</v>
+        <v>46340.45833333334</v>
       </c>
       <c r="L498" s="1" t="n">
-        <v>46340.41666666666</v>
+        <v>46340.5</v>
       </c>
       <c r="M498" s="1" t="n">
-        <v>46341.16666666666</v>
+        <v>46341.25</v>
       </c>
     </row>
     <row r="499">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46297.75</v>
+        <v>46297.66666666666</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>46297.79166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="M116" s="1" t="n">
-        <v>46298.79166666666</v>
+        <v>46299.04166666666</v>
       </c>
     </row>
     <row r="117">
@@ -6846,19 +6846,19 @@
         </is>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46300.70833333334</v>
+        <v>46300.875</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>46300.75</v>
+        <v>46300.91666666666</v>
       </c>
       <c r="M117" s="1" t="n">
-        <v>46302.75</v>
+        <v>46302.91666666666</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KHS1</t>
+          <t>PVS2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
-        <v>2612</v>
+        <v>9002</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>9002S</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6901,19 +6901,19 @@
         </is>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46304.5</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>46304.54166666666</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="M118" s="1" t="n">
-        <v>46305.625</v>
+        <v>46305.66666666666</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PVS2</t>
+          <t>KHS1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="n">
-        <v>9002</v>
+        <v>2612</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>9002S</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6956,13 +6956,13 @@
         </is>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46304.75</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>46304.79166666666</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="M119" s="1" t="n">
-        <v>46305.5</v>
+        <v>46306.66666666666</v>
       </c>
     </row>
     <row r="120">
@@ -7011,13 +7011,13 @@
         </is>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46305.75</v>
+        <v>46306.79166666666</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>46305.79166666666</v>
+        <v>46306.83333333334</v>
       </c>
       <c r="M120" s="1" t="n">
-        <v>46306.04166666666</v>
+        <v>46307.08333333334</v>
       </c>
     </row>
     <row r="121">
@@ -7066,13 +7066,13 @@
         </is>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46306.45833333334</v>
+        <v>46307.5</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>46306.54166666666</v>
+        <v>46307.58333333334</v>
       </c>
       <c r="M121" s="1" t="n">
-        <v>46306.875</v>
+        <v>46307.91666666666</v>
       </c>
     </row>
     <row r="122">
@@ -7121,13 +7121,13 @@
         </is>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46311.95833333334</v>
+        <v>46313</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>46312.125</v>
+        <v>46313.16666666666</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>46312.75</v>
+        <v>46313.79166666666</v>
       </c>
     </row>
     <row r="123">
@@ -7176,13 +7176,13 @@
         </is>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46314.54166666666</v>
+        <v>46315.58333333334</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>46314.58333333334</v>
+        <v>46315.625</v>
       </c>
       <c r="M123" s="1" t="n">
-        <v>46314.83333333334</v>
+        <v>46315.875</v>
       </c>
     </row>
     <row r="124">
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46315.125</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>46315.25</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="M124" s="1" t="n">
-        <v>46316.75</v>
+        <v>46317.79166666666</v>
       </c>
     </row>
     <row r="125">
@@ -7286,13 +7286,13 @@
         </is>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46316.95833333334</v>
+        <v>46318</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>46317</v>
+        <v>46318.04166666666</v>
       </c>
       <c r="M125" s="1" t="n">
-        <v>46317.41666666666</v>
+        <v>46318.45833333334</v>
       </c>
     </row>
     <row r="126">
@@ -7341,13 +7341,13 @@
         </is>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46319</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>46319.16666666666</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="M126" s="1" t="n">
-        <v>46319.70833333334</v>
+        <v>46320.75</v>
       </c>
     </row>
     <row r="127">
@@ -7396,13 +7396,13 @@
         </is>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46327.04166666666</v>
+        <v>46328.08333333334</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>46327.08333333334</v>
+        <v>46328.125</v>
       </c>
       <c r="M127" s="1" t="n">
-        <v>46328.16666666666</v>
+        <v>46329.20833333334</v>
       </c>
     </row>
     <row r="128">
@@ -7451,13 +7451,13 @@
         </is>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46328.29166666666</v>
+        <v>46329.33333333334</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>46328.33333333334</v>
+        <v>46329.375</v>
       </c>
       <c r="M128" s="1" t="n">
-        <v>46328.58333333334</v>
+        <v>46329.625</v>
       </c>
     </row>
     <row r="129">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="K129" s="1" t="n">
-        <v>46329</v>
+        <v>46330.04166666666</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>46329.08333333334</v>
+        <v>46330.125</v>
       </c>
       <c r="M129" s="1" t="n">
-        <v>46329.41666666666</v>
+        <v>46330.45833333334</v>
       </c>
     </row>
     <row r="130">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="K130" s="1" t="n">
-        <v>46334.5</v>
+        <v>46335.54166666666</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>46334.66666666666</v>
+        <v>46335.70833333334</v>
       </c>
       <c r="M130" s="1" t="n">
-        <v>46335.29166666666</v>
+        <v>46336.33333333334</v>
       </c>
     </row>
     <row r="131">
@@ -7616,13 +7616,13 @@
         </is>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46337.08333333334</v>
+        <v>46338.125</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>46337.125</v>
+        <v>46338.16666666666</v>
       </c>
       <c r="M131" s="1" t="n">
-        <v>46337.375</v>
+        <v>46338.41666666666</v>
       </c>
     </row>
     <row r="132">
@@ -7671,13 +7671,13 @@
         </is>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46337.66666666666</v>
+        <v>46338.70833333334</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>46337.79166666666</v>
+        <v>46338.83333333334</v>
       </c>
       <c r="M132" s="1" t="n">
-        <v>46339.29166666666</v>
+        <v>46340.33333333334</v>
       </c>
     </row>
     <row r="133">
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46339.5</v>
+        <v>46340.54166666666</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>46339.54166666666</v>
+        <v>46340.58333333334</v>
       </c>
       <c r="M133" s="1" t="n">
-        <v>46339.95833333334</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="134">
@@ -7781,13 +7781,13 @@
         </is>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46341.54166666666</v>
+        <v>46342.58333333334</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>46341.70833333334</v>
+        <v>46342.75</v>
       </c>
       <c r="M134" s="1" t="n">
-        <v>46342.25</v>
+        <v>46343.29166666666</v>
       </c>
     </row>
     <row r="135">
@@ -7836,13 +7836,13 @@
         </is>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46347.95833333334</v>
+        <v>46349</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>46348</v>
+        <v>46349.04166666666</v>
       </c>
       <c r="M135" s="1" t="n">
-        <v>46349.08333333334</v>
+        <v>46350.125</v>
       </c>
     </row>
     <row r="136">
@@ -7891,13 +7891,13 @@
         </is>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46349.20833333334</v>
+        <v>46350.25</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>46349.25</v>
+        <v>46350.29166666666</v>
       </c>
       <c r="M136" s="1" t="n">
-        <v>46349.5</v>
+        <v>46350.54166666666</v>
       </c>
     </row>
     <row r="137">
@@ -7946,13 +7946,13 @@
         </is>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46349.91666666666</v>
+        <v>46350.95833333334</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>46350</v>
+        <v>46351.04166666666</v>
       </c>
       <c r="M137" s="1" t="n">
-        <v>46350.33333333334</v>
+        <v>46351.375</v>
       </c>
     </row>
     <row r="138">
@@ -8001,13 +8001,13 @@
         </is>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46355.41666666666</v>
+        <v>46356.45833333334</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>46355.58333333334</v>
+        <v>46356.625</v>
       </c>
       <c r="M138" s="1" t="n">
-        <v>46356.20833333334</v>
+        <v>46357.25</v>
       </c>
     </row>
     <row r="139">
@@ -8056,13 +8056,13 @@
         </is>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46358</v>
+        <v>46359.04166666666</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>46358.04166666666</v>
+        <v>46359.08333333334</v>
       </c>
       <c r="M139" s="1" t="n">
-        <v>46358.29166666666</v>
+        <v>46359.33333333334</v>
       </c>
     </row>
     <row r="140">
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46358.58333333334</v>
+        <v>46359.625</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>46358.70833333334</v>
+        <v>46359.75</v>
       </c>
       <c r="M140" s="1" t="n">
-        <v>46360.20833333334</v>
+        <v>46361.25</v>
       </c>
     </row>
     <row r="141">
@@ -8166,13 +8166,13 @@
         </is>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46360.41666666666</v>
+        <v>46361.45833333334</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>46360.45833333334</v>
+        <v>46361.5</v>
       </c>
       <c r="M141" s="1" t="n">
-        <v>46360.875</v>
+        <v>46361.91666666666</v>
       </c>
     </row>
     <row r="142">
@@ -8217,13 +8217,13 @@
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" s="1" t="n">
-        <v>46362.45833333334</v>
+        <v>46363.5</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>46362.625</v>
+        <v>46363.66666666666</v>
       </c>
       <c r="M142" s="1" t="n">
-        <v>46363.16666666666</v>
+        <v>46364.20833333334</v>
       </c>
     </row>
     <row r="143">
@@ -10358,13 +10358,13 @@
         </is>
       </c>
       <c r="K181" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>46310.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="M181" s="1" t="n">
-        <v>46310.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
     </row>
     <row r="182">
@@ -10413,13 +10413,13 @@
         </is>
       </c>
       <c r="K182" s="1" t="n">
-        <v>46311.20833333334</v>
+        <v>46312.20833333334</v>
       </c>
       <c r="L182" s="1" t="n">
-        <v>46311.27083333334</v>
+        <v>46312.27083333334</v>
       </c>
       <c r="M182" s="1" t="n">
-        <v>46311.75</v>
+        <v>46312.75</v>
       </c>
     </row>
     <row r="183">
@@ -10468,13 +10468,13 @@
         </is>
       </c>
       <c r="K183" s="1" t="n">
-        <v>46312.75</v>
+        <v>46313.75</v>
       </c>
       <c r="L183" s="1" t="n">
-        <v>46313.25</v>
+        <v>46314.25</v>
       </c>
       <c r="M183" s="1" t="n">
-        <v>46314.25</v>
+        <v>46315.25</v>
       </c>
     </row>
     <row r="184">
@@ -10523,13 +10523,13 @@
         </is>
       </c>
       <c r="K184" s="1" t="n">
-        <v>46321.25</v>
+        <v>46322.25</v>
       </c>
       <c r="L184" s="1" t="n">
-        <v>46321.33333333334</v>
+        <v>46322.33333333334</v>
       </c>
       <c r="M184" s="1" t="n">
-        <v>46322.70833333334</v>
+        <v>46323.70833333334</v>
       </c>
     </row>
     <row r="185">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="K185" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46324.70833333334</v>
       </c>
       <c r="L185" s="1" t="n">
-        <v>46323.79166666666</v>
+        <v>46324.79166666666</v>
       </c>
       <c r="M185" s="1" t="n">
-        <v>46324.79166666666</v>
+        <v>46325.79166666666</v>
       </c>
     </row>
     <row r="186">
@@ -10633,13 +10633,13 @@
         </is>
       </c>
       <c r="K186" s="1" t="n">
-        <v>46331.79166666666</v>
+        <v>46332.79166666666</v>
       </c>
       <c r="L186" s="1" t="n">
-        <v>46332.29166666666</v>
+        <v>46333.29166666666</v>
       </c>
       <c r="M186" s="1" t="n">
-        <v>46333.29166666666</v>
+        <v>46334.29166666666</v>
       </c>
     </row>
     <row r="187">
@@ -10688,13 +10688,13 @@
         </is>
       </c>
       <c r="K187" s="1" t="n">
-        <v>46334.66666666666</v>
+        <v>46335.66666666666</v>
       </c>
       <c r="L187" s="1" t="n">
-        <v>46334.70833333334</v>
+        <v>46335.70833333334</v>
       </c>
       <c r="M187" s="1" t="n">
-        <v>46336.41666666666</v>
+        <v>46337.41666666666</v>
       </c>
     </row>
     <row r="188">
@@ -10743,13 +10743,13 @@
         </is>
       </c>
       <c r="K188" s="1" t="n">
-        <v>46336.70833333334</v>
+        <v>46337.70833333334</v>
       </c>
       <c r="L188" s="1" t="n">
-        <v>46336.77083333334</v>
+        <v>46337.77083333334</v>
       </c>
       <c r="M188" s="1" t="n">
-        <v>46337.25</v>
+        <v>46338.25</v>
       </c>
     </row>
     <row r="189">
@@ -10798,13 +10798,13 @@
         </is>
       </c>
       <c r="K189" s="1" t="n">
-        <v>46338.25</v>
+        <v>46339.25</v>
       </c>
       <c r="L189" s="1" t="n">
-        <v>46338.45833333334</v>
+        <v>46339.45833333334</v>
       </c>
       <c r="M189" s="1" t="n">
-        <v>46339.45833333334</v>
+        <v>46340.45833333334</v>
       </c>
     </row>
     <row r="190">
@@ -10853,13 +10853,13 @@
         </is>
       </c>
       <c r="K190" s="1" t="n">
-        <v>46346.45833333334</v>
+        <v>46347.45833333334</v>
       </c>
       <c r="L190" s="1" t="n">
-        <v>46346.54166666666</v>
+        <v>46347.54166666666</v>
       </c>
       <c r="M190" s="1" t="n">
-        <v>46347.91666666666</v>
+        <v>46348.91666666666</v>
       </c>
     </row>
     <row r="191">
@@ -10908,13 +10908,13 @@
         </is>
       </c>
       <c r="K191" s="1" t="n">
-        <v>46348.91666666666</v>
+        <v>46349.91666666666</v>
       </c>
       <c r="L191" s="1" t="n">
-        <v>46349</v>
+        <v>46350</v>
       </c>
       <c r="M191" s="1" t="n">
-        <v>46350</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="192">
@@ -10963,13 +10963,13 @@
         </is>
       </c>
       <c r="K192" s="1" t="n">
-        <v>46353.41666666666</v>
+        <v>46354.41666666666</v>
       </c>
       <c r="L192" s="1" t="n">
-        <v>46353.58333333334</v>
+        <v>46354.58333333334</v>
       </c>
       <c r="M192" s="1" t="n">
-        <v>46354.41666666666</v>
+        <v>46355.41666666666</v>
       </c>
     </row>
     <row r="193">
@@ -11014,13 +11014,13 @@
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" s="1" t="n">
-        <v>46359</v>
+        <v>46360</v>
       </c>
       <c r="L193" s="1" t="n">
-        <v>46359.16666666666</v>
+        <v>46360.16666666666</v>
       </c>
       <c r="M193" s="1" t="n">
-        <v>46360.16666666666</v>
+        <v>46361.16666666666</v>
       </c>
     </row>
     <row r="194">
@@ -13980,13 +13980,13 @@
         </is>
       </c>
       <c r="K247" s="1" t="n">
-        <v>46294.41666666666</v>
+        <v>46294.39583333334</v>
       </c>
       <c r="L247" s="1" t="n">
-        <v>46294.75</v>
+        <v>46294.72916666666</v>
       </c>
       <c r="M247" s="1" t="n">
-        <v>46295.16666666666</v>
+        <v>46295.22916666666</v>
       </c>
     </row>
     <row r="248">
@@ -14035,13 +14035,13 @@
         </is>
       </c>
       <c r="K248" s="1" t="n">
-        <v>46299.04166666666</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="L248" s="1" t="n">
-        <v>46299.10416666666</v>
+        <v>46299.22916666666</v>
       </c>
       <c r="M248" s="1" t="n">
-        <v>46299.5625</v>
+        <v>46299.6875</v>
       </c>
     </row>
     <row r="249">
@@ -14090,13 +14090,13 @@
         </is>
       </c>
       <c r="K249" s="1" t="n">
-        <v>46300.41666666666</v>
+        <v>46300.54166666666</v>
       </c>
       <c r="L249" s="1" t="n">
-        <v>46300.45833333334</v>
+        <v>46300.58333333334</v>
       </c>
       <c r="M249" s="1" t="n">
-        <v>46300.95833333334</v>
+        <v>46301.08333333334</v>
       </c>
     </row>
     <row r="250">
@@ -14145,13 +14145,13 @@
         </is>
       </c>
       <c r="K250" s="1" t="n">
-        <v>46303.41666666666</v>
+        <v>46303.625</v>
       </c>
       <c r="L250" s="1" t="n">
-        <v>46303.45833333334</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="M250" s="1" t="n">
-        <v>46304.08333333334</v>
+        <v>46304.29166666666</v>
       </c>
     </row>
     <row r="251">
@@ -14200,13 +14200,13 @@
         </is>
       </c>
       <c r="K251" s="1" t="n">
-        <v>46305.08333333334</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="L251" s="1" t="n">
-        <v>46305.125</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="M251" s="1" t="n">
-        <v>46305.625</v>
+        <v>46305.83333333334</v>
       </c>
     </row>
     <row r="252">
@@ -14255,13 +14255,13 @@
         </is>
       </c>
       <c r="K252" s="1" t="n">
-        <v>46306.70833333334</v>
+        <v>46306.91666666666</v>
       </c>
       <c r="L252" s="1" t="n">
-        <v>46306.875</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="M252" s="1" t="n">
-        <v>46307.66666666666</v>
+        <v>46307.875</v>
       </c>
     </row>
     <row r="253">
@@ -14310,13 +14310,13 @@
         </is>
       </c>
       <c r="K253" s="1" t="n">
-        <v>46313.41666666666</v>
+        <v>46313.625</v>
       </c>
       <c r="L253" s="1" t="n">
-        <v>46313.45833333334</v>
+        <v>46313.66666666666</v>
       </c>
       <c r="M253" s="1" t="n">
-        <v>46313.75</v>
+        <v>46313.95833333334</v>
       </c>
     </row>
     <row r="254">
@@ -14365,13 +14365,13 @@
         </is>
       </c>
       <c r="K254" s="1" t="n">
-        <v>46314.04166666666</v>
+        <v>46314.25</v>
       </c>
       <c r="L254" s="1" t="n">
-        <v>46314.04166666666</v>
+        <v>46314.25</v>
       </c>
       <c r="M254" s="1" t="n">
-        <v>46315.41666666666</v>
+        <v>46315.625</v>
       </c>
     </row>
     <row r="255">
@@ -14420,13 +14420,13 @@
         </is>
       </c>
       <c r="K255" s="1" t="n">
-        <v>46315.66666666666</v>
+        <v>46315.875</v>
       </c>
       <c r="L255" s="1" t="n">
-        <v>46315.70833333334</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="M255" s="1" t="n">
-        <v>46316.16666666666</v>
+        <v>46316.375</v>
       </c>
     </row>
     <row r="256">
@@ -14475,13 +14475,13 @@
         </is>
       </c>
       <c r="K256" s="1" t="n">
-        <v>46320</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="L256" s="1" t="n">
-        <v>46320</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="M256" s="1" t="n">
-        <v>46320.45833333334</v>
+        <v>46320.66666666666</v>
       </c>
     </row>
     <row r="257">
@@ -14530,13 +14530,13 @@
         </is>
       </c>
       <c r="K257" s="1" t="n">
-        <v>46321.45833333334</v>
+        <v>46321.66666666666</v>
       </c>
       <c r="L257" s="1" t="n">
-        <v>46321.45833333334</v>
+        <v>46321.66666666666</v>
       </c>
       <c r="M257" s="1" t="n">
-        <v>46321.95833333334</v>
+        <v>46322.16666666666</v>
       </c>
     </row>
     <row r="258">
@@ -14585,13 +14585,13 @@
         </is>
       </c>
       <c r="K258" s="1" t="n">
-        <v>46324.41666666666</v>
+        <v>46324.625</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>46324.45833333334</v>
+        <v>46324.66666666666</v>
       </c>
       <c r="M258" s="1" t="n">
-        <v>46325.08333333334</v>
+        <v>46325.29166666666</v>
       </c>
     </row>
     <row r="259">
@@ -14640,13 +14640,13 @@
         </is>
       </c>
       <c r="K259" s="1" t="n">
-        <v>46326.08333333334</v>
+        <v>46326.29166666666</v>
       </c>
       <c r="L259" s="1" t="n">
-        <v>46326.125</v>
+        <v>46326.33333333334</v>
       </c>
       <c r="M259" s="1" t="n">
-        <v>46326.625</v>
+        <v>46326.83333333334</v>
       </c>
     </row>
     <row r="260">
@@ -14695,13 +14695,13 @@
         </is>
       </c>
       <c r="K260" s="1" t="n">
-        <v>46327.70833333334</v>
+        <v>46327.91666666666</v>
       </c>
       <c r="L260" s="1" t="n">
-        <v>46327.875</v>
+        <v>46328.08333333334</v>
       </c>
       <c r="M260" s="1" t="n">
-        <v>46328.66666666666</v>
+        <v>46328.875</v>
       </c>
     </row>
     <row r="261">
@@ -14750,13 +14750,13 @@
         </is>
       </c>
       <c r="K261" s="1" t="n">
-        <v>46334.41666666666</v>
+        <v>46334.625</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>46334.45833333334</v>
+        <v>46334.66666666666</v>
       </c>
       <c r="M261" s="1" t="n">
-        <v>46334.75</v>
+        <v>46334.95833333334</v>
       </c>
     </row>
     <row r="262">
@@ -14805,13 +14805,13 @@
         </is>
       </c>
       <c r="K262" s="1" t="n">
-        <v>46335.04166666666</v>
+        <v>46335.25</v>
       </c>
       <c r="L262" s="1" t="n">
-        <v>46335.04166666666</v>
+        <v>46335.25</v>
       </c>
       <c r="M262" s="1" t="n">
-        <v>46336.41666666666</v>
+        <v>46336.625</v>
       </c>
     </row>
     <row r="263">
@@ -14860,13 +14860,13 @@
         </is>
       </c>
       <c r="K263" s="1" t="n">
-        <v>46336.66666666666</v>
+        <v>46336.875</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>46336.70833333334</v>
+        <v>46336.91666666666</v>
       </c>
       <c r="M263" s="1" t="n">
-        <v>46337.16666666666</v>
+        <v>46337.375</v>
       </c>
     </row>
     <row r="264">
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="K264" s="1" t="n">
-        <v>46341</v>
+        <v>46341.20833333334</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>46341</v>
+        <v>46341.20833333334</v>
       </c>
       <c r="M264" s="1" t="n">
-        <v>46341.45833333334</v>
+        <v>46341.66666666666</v>
       </c>
     </row>
     <row r="265">
@@ -14970,13 +14970,13 @@
         </is>
       </c>
       <c r="K265" s="1" t="n">
-        <v>46342.45833333334</v>
+        <v>46342.66666666666</v>
       </c>
       <c r="L265" s="1" t="n">
-        <v>46342.45833333334</v>
+        <v>46342.66666666666</v>
       </c>
       <c r="M265" s="1" t="n">
-        <v>46342.95833333334</v>
+        <v>46343.16666666666</v>
       </c>
     </row>
     <row r="266">
@@ -15025,13 +15025,13 @@
         </is>
       </c>
       <c r="K266" s="1" t="n">
-        <v>46345.41666666666</v>
+        <v>46345.625</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>46345.45833333334</v>
+        <v>46345.66666666666</v>
       </c>
       <c r="M266" s="1" t="n">
-        <v>46346.08333333334</v>
+        <v>46346.29166666666</v>
       </c>
     </row>
     <row r="267">
@@ -15080,13 +15080,13 @@
         </is>
       </c>
       <c r="K267" s="1" t="n">
-        <v>46347.08333333334</v>
+        <v>46347.29166666666</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>46347.125</v>
+        <v>46347.33333333334</v>
       </c>
       <c r="M267" s="1" t="n">
-        <v>46347.625</v>
+        <v>46347.83333333334</v>
       </c>
     </row>
     <row r="268">
@@ -15135,13 +15135,13 @@
         </is>
       </c>
       <c r="K268" s="1" t="n">
-        <v>46348.70833333334</v>
+        <v>46348.91666666666</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>46348.875</v>
+        <v>46349.08333333334</v>
       </c>
       <c r="M268" s="1" t="n">
-        <v>46349.66666666666</v>
+        <v>46349.875</v>
       </c>
     </row>
     <row r="269">
@@ -15190,13 +15190,13 @@
         </is>
       </c>
       <c r="K269" s="1" t="n">
-        <v>46355.41666666666</v>
+        <v>46355.625</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>46355.45833333334</v>
+        <v>46355.66666666666</v>
       </c>
       <c r="M269" s="1" t="n">
-        <v>46355.75</v>
+        <v>46355.95833333334</v>
       </c>
     </row>
     <row r="270">
@@ -15245,13 +15245,13 @@
         </is>
       </c>
       <c r="K270" s="1" t="n">
-        <v>46356.04166666666</v>
+        <v>46356.25</v>
       </c>
       <c r="L270" s="1" t="n">
-        <v>46356.04166666666</v>
+        <v>46356.25</v>
       </c>
       <c r="M270" s="1" t="n">
-        <v>46357.41666666666</v>
+        <v>46357.625</v>
       </c>
     </row>
     <row r="271">
@@ -15300,13 +15300,13 @@
         </is>
       </c>
       <c r="K271" s="1" t="n">
-        <v>46357.66666666666</v>
+        <v>46357.875</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>46357.70833333334</v>
+        <v>46357.91666666666</v>
       </c>
       <c r="M271" s="1" t="n">
-        <v>46358.16666666666</v>
+        <v>46358.375</v>
       </c>
     </row>
     <row r="272">
@@ -15355,13 +15355,13 @@
         </is>
       </c>
       <c r="K272" s="1" t="n">
-        <v>46362</v>
+        <v>46362.20833333334</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>46362</v>
+        <v>46362.20833333334</v>
       </c>
       <c r="M272" s="1" t="n">
-        <v>46362.45833333334</v>
+        <v>46362.66666666666</v>
       </c>
     </row>
     <row r="273">
@@ -15406,13 +15406,13 @@
       </c>
       <c r="J273" t="inlineStr"/>
       <c r="K273" s="1" t="n">
-        <v>46363.45833333334</v>
+        <v>46363.66666666666</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>46363.45833333334</v>
+        <v>46363.66666666666</v>
       </c>
       <c r="M273" s="1" t="n">
-        <v>46363.95833333334</v>
+        <v>46364.16666666666</v>
       </c>
     </row>
     <row r="274">
@@ -25180,13 +25180,13 @@
         </is>
       </c>
       <c r="K451" s="1" t="n">
-        <v>46290.79166666666</v>
+        <v>46291.25</v>
       </c>
       <c r="L451" s="1" t="n">
-        <v>46290.83333333334</v>
+        <v>46291.29166666666</v>
       </c>
       <c r="M451" s="1" t="n">
-        <v>46291.5</v>
+        <v>46292.29166666666</v>
       </c>
     </row>
     <row r="452">
@@ -25290,13 +25290,13 @@
         </is>
       </c>
       <c r="K453" s="1" t="n">
-        <v>46295.125</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="L453" s="1" t="n">
-        <v>46295.16666666666</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="M453" s="1" t="n">
-        <v>46295.625</v>
+        <v>46295.95833333334</v>
       </c>
     </row>
     <row r="454">
@@ -25345,13 +25345,13 @@
         </is>
       </c>
       <c r="K454" s="1" t="n">
-        <v>46296.70833333334</v>
+        <v>46297.04166666666</v>
       </c>
       <c r="L454" s="1" t="n">
-        <v>46296.875</v>
+        <v>46297.25</v>
       </c>
       <c r="M454" s="1" t="n">
-        <v>46297.375</v>
+        <v>46297.79166666666</v>
       </c>
     </row>
     <row r="455">
@@ -25400,13 +25400,13 @@
         </is>
       </c>
       <c r="K455" s="1" t="n">
-        <v>46301.29166666666</v>
+        <v>46301.70833333334</v>
       </c>
       <c r="L455" s="1" t="n">
-        <v>46301.95833333334</v>
+        <v>46302.375</v>
       </c>
       <c r="M455" s="1" t="n">
-        <v>46302.79166666666</v>
+        <v>46303.20833333334</v>
       </c>
     </row>
     <row r="456">
@@ -25455,13 +25455,13 @@
         </is>
       </c>
       <c r="K456" s="1" t="n">
-        <v>46304.33333333334</v>
+        <v>46304.75</v>
       </c>
       <c r="L456" s="1" t="n">
-        <v>46304.375</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="M456" s="1" t="n">
-        <v>46305.20833333334</v>
+        <v>46305.625</v>
       </c>
     </row>
     <row r="457">
@@ -25510,13 +25510,13 @@
         </is>
       </c>
       <c r="K457" s="1" t="n">
-        <v>46308.14583333334</v>
+        <v>46308.5625</v>
       </c>
       <c r="L457" s="1" t="n">
-        <v>46309.20833333334</v>
+        <v>46309.625</v>
       </c>
       <c r="M457" s="1" t="n">
-        <v>46310.91666666666</v>
+        <v>46311.33333333334</v>
       </c>
     </row>
     <row r="458">
@@ -25565,13 +25565,13 @@
         </is>
       </c>
       <c r="K458" s="1" t="n">
-        <v>46313.375</v>
+        <v>46313.79166666666</v>
       </c>
       <c r="L458" s="1" t="n">
-        <v>46313.54166666666</v>
+        <v>46313.95833333334</v>
       </c>
       <c r="M458" s="1" t="n">
-        <v>46314.375</v>
+        <v>46314.79166666666</v>
       </c>
     </row>
     <row r="459">
@@ -25620,13 +25620,13 @@
         </is>
       </c>
       <c r="K459" s="1" t="n">
-        <v>46316.6875</v>
+        <v>46317.10416666666</v>
       </c>
       <c r="L459" s="1" t="n">
-        <v>46316.75</v>
+        <v>46317.16666666666</v>
       </c>
       <c r="M459" s="1" t="n">
-        <v>46317.25</v>
+        <v>46317.66666666666</v>
       </c>
     </row>
     <row r="460">
@@ -25675,13 +25675,13 @@
         </is>
       </c>
       <c r="K460" s="1" t="n">
-        <v>46317.47916666666</v>
+        <v>46317.89583333334</v>
       </c>
       <c r="L460" s="1" t="n">
-        <v>46317.52083333334</v>
+        <v>46317.9375</v>
       </c>
       <c r="M460" s="1" t="n">
-        <v>46318.02083333334</v>
+        <v>46318.4375</v>
       </c>
     </row>
     <row r="461">
@@ -25730,13 +25730,13 @@
         </is>
       </c>
       <c r="K461" s="1" t="n">
-        <v>46321.10416666666</v>
+        <v>46321.52083333334</v>
       </c>
       <c r="L461" s="1" t="n">
-        <v>46321.14583333334</v>
+        <v>46321.5625</v>
       </c>
       <c r="M461" s="1" t="n">
-        <v>46321.8125</v>
+        <v>46322.22916666666</v>
       </c>
     </row>
     <row r="462">
@@ -25785,13 +25785,13 @@
         </is>
       </c>
       <c r="K462" s="1" t="n">
-        <v>46322.89583333334</v>
+        <v>46323.3125</v>
       </c>
       <c r="L462" s="1" t="n">
-        <v>46322.9375</v>
+        <v>46323.35416666666</v>
       </c>
       <c r="M462" s="1" t="n">
-        <v>46323.52083333334</v>
+        <v>46323.9375</v>
       </c>
     </row>
     <row r="463">
@@ -25840,13 +25840,13 @@
         </is>
       </c>
       <c r="K463" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46324.125</v>
       </c>
       <c r="L463" s="1" t="n">
-        <v>46323.77083333334</v>
+        <v>46324.1875</v>
       </c>
       <c r="M463" s="1" t="n">
-        <v>46324.10416666666</v>
+        <v>46324.52083333334</v>
       </c>
     </row>
     <row r="464">
@@ -25895,13 +25895,13 @@
         </is>
       </c>
       <c r="K464" s="1" t="n">
-        <v>46325.39583333334</v>
+        <v>46325.8125</v>
       </c>
       <c r="L464" s="1" t="n">
-        <v>46325.5625</v>
+        <v>46325.97916666666</v>
       </c>
       <c r="M464" s="1" t="n">
-        <v>46326.0625</v>
+        <v>46326.47916666666</v>
       </c>
     </row>
     <row r="465">
@@ -25950,13 +25950,13 @@
         </is>
       </c>
       <c r="K465" s="1" t="n">
-        <v>46330.22916666666</v>
+        <v>46330.64583333334</v>
       </c>
       <c r="L465" s="1" t="n">
-        <v>46330.39583333334</v>
+        <v>46330.8125</v>
       </c>
       <c r="M465" s="1" t="n">
-        <v>46331.22916666666</v>
+        <v>46331.64583333334</v>
       </c>
     </row>
     <row r="466">
@@ -26005,13 +26005,13 @@
         </is>
       </c>
       <c r="K466" s="1" t="n">
-        <v>46332.89583333334</v>
+        <v>46333.3125</v>
       </c>
       <c r="L466" s="1" t="n">
-        <v>46332.9375</v>
+        <v>46333.35416666666</v>
       </c>
       <c r="M466" s="1" t="n">
-        <v>46333.77083333334</v>
+        <v>46334.1875</v>
       </c>
     </row>
     <row r="467">
@@ -26060,13 +26060,13 @@
         </is>
       </c>
       <c r="K467" s="1" t="n">
-        <v>46336.9375</v>
+        <v>46337.35416666666</v>
       </c>
       <c r="L467" s="1" t="n">
-        <v>46337.02083333334</v>
+        <v>46337.4375</v>
       </c>
       <c r="M467" s="1" t="n">
-        <v>46338.6875</v>
+        <v>46339.10416666666</v>
       </c>
     </row>
     <row r="468">
@@ -26115,13 +26115,13 @@
         </is>
       </c>
       <c r="K468" s="1" t="n">
-        <v>46341.14583333334</v>
+        <v>46341.5625</v>
       </c>
       <c r="L468" s="1" t="n">
-        <v>46341.3125</v>
+        <v>46341.72916666666</v>
       </c>
       <c r="M468" s="1" t="n">
-        <v>46342.14583333334</v>
+        <v>46342.5625</v>
       </c>
     </row>
     <row r="469">
@@ -26170,13 +26170,13 @@
         </is>
       </c>
       <c r="K469" s="1" t="n">
-        <v>46344.6875</v>
+        <v>46345.10416666666</v>
       </c>
       <c r="L469" s="1" t="n">
-        <v>46344.75</v>
+        <v>46345.16666666666</v>
       </c>
       <c r="M469" s="1" t="n">
-        <v>46345.25</v>
+        <v>46345.66666666666</v>
       </c>
     </row>
     <row r="470">
@@ -26225,13 +26225,13 @@
         </is>
       </c>
       <c r="K470" s="1" t="n">
-        <v>46345.47916666666</v>
+        <v>46345.89583333334</v>
       </c>
       <c r="L470" s="1" t="n">
-        <v>46345.52083333334</v>
+        <v>46345.9375</v>
       </c>
       <c r="M470" s="1" t="n">
-        <v>46346.02083333334</v>
+        <v>46346.4375</v>
       </c>
     </row>
     <row r="471">
@@ -26280,13 +26280,13 @@
         </is>
       </c>
       <c r="K471" s="1" t="n">
-        <v>46349.10416666666</v>
+        <v>46349.52083333334</v>
       </c>
       <c r="L471" s="1" t="n">
-        <v>46349.14583333334</v>
+        <v>46349.5625</v>
       </c>
       <c r="M471" s="1" t="n">
-        <v>46349.8125</v>
+        <v>46350.22916666666</v>
       </c>
     </row>
     <row r="472">
@@ -26335,13 +26335,13 @@
         </is>
       </c>
       <c r="K472" s="1" t="n">
-        <v>46350.89583333334</v>
+        <v>46351.3125</v>
       </c>
       <c r="L472" s="1" t="n">
-        <v>46350.9375</v>
+        <v>46351.35416666666</v>
       </c>
       <c r="M472" s="1" t="n">
-        <v>46351.52083333334</v>
+        <v>46351.9375</v>
       </c>
     </row>
     <row r="473">
@@ -26390,13 +26390,13 @@
         </is>
       </c>
       <c r="K473" s="1" t="n">
-        <v>46351.70833333334</v>
+        <v>46352.125</v>
       </c>
       <c r="L473" s="1" t="n">
-        <v>46351.77083333334</v>
+        <v>46352.1875</v>
       </c>
       <c r="M473" s="1" t="n">
-        <v>46352.10416666666</v>
+        <v>46352.52083333334</v>
       </c>
     </row>
     <row r="474">
@@ -26445,13 +26445,13 @@
         </is>
       </c>
       <c r="K474" s="1" t="n">
-        <v>46353.39583333334</v>
+        <v>46353.8125</v>
       </c>
       <c r="L474" s="1" t="n">
-        <v>46353.5625</v>
+        <v>46353.97916666666</v>
       </c>
       <c r="M474" s="1" t="n">
-        <v>46354.0625</v>
+        <v>46354.47916666666</v>
       </c>
     </row>
     <row r="475">
@@ -26500,13 +26500,13 @@
         </is>
       </c>
       <c r="K475" s="1" t="n">
-        <v>46358.22916666666</v>
+        <v>46358.64583333334</v>
       </c>
       <c r="L475" s="1" t="n">
-        <v>46358.39583333334</v>
+        <v>46358.8125</v>
       </c>
       <c r="M475" s="1" t="n">
-        <v>46359.22916666666</v>
+        <v>46359.64583333334</v>
       </c>
     </row>
     <row r="476">
@@ -26555,13 +26555,13 @@
         </is>
       </c>
       <c r="K476" s="1" t="n">
-        <v>46360.89583333334</v>
+        <v>46361.3125</v>
       </c>
       <c r="L476" s="1" t="n">
-        <v>46360.9375</v>
+        <v>46361.35416666666</v>
       </c>
       <c r="M476" s="1" t="n">
-        <v>46361.77083333334</v>
+        <v>46362.1875</v>
       </c>
     </row>
     <row r="477">
@@ -26610,13 +26610,13 @@
         </is>
       </c>
       <c r="K477" s="1" t="n">
-        <v>46364.9375</v>
+        <v>46365.35416666666</v>
       </c>
       <c r="L477" s="1" t="n">
-        <v>46365.02083333334</v>
+        <v>46365.4375</v>
       </c>
       <c r="M477" s="1" t="n">
-        <v>46366.6875</v>
+        <v>46367.10416666666</v>
       </c>
     </row>
     <row r="478">
@@ -26665,13 +26665,13 @@
         </is>
       </c>
       <c r="K478" s="1" t="n">
-        <v>46369.14583333334</v>
+        <v>46369.5625</v>
       </c>
       <c r="L478" s="1" t="n">
-        <v>46369.3125</v>
+        <v>46369.72916666666</v>
       </c>
       <c r="M478" s="1" t="n">
-        <v>46370.14583333334</v>
+        <v>46370.5625</v>
       </c>
     </row>
     <row r="479">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="K479" s="1" t="n">
-        <v>46372.6875</v>
+        <v>46373.10416666666</v>
       </c>
       <c r="L479" s="1" t="n">
-        <v>46372.75</v>
+        <v>46373.16666666666</v>
       </c>
       <c r="M479" s="1" t="n">
-        <v>46373.25</v>
+        <v>46373.66666666666</v>
       </c>
     </row>
     <row r="480">
@@ -26771,13 +26771,13 @@
       </c>
       <c r="J480" t="inlineStr"/>
       <c r="K480" s="1" t="n">
-        <v>46373.47916666666</v>
+        <v>46373.89583333334</v>
       </c>
       <c r="L480" s="1" t="n">
-        <v>46373.52083333334</v>
+        <v>46373.9375</v>
       </c>
       <c r="M480" s="1" t="n">
-        <v>46374.02083333334</v>
+        <v>46374.4375</v>
       </c>
     </row>
     <row r="481">
@@ -27162,7 +27162,7 @@
         <v>46293.775</v>
       </c>
       <c r="M487" s="1" t="n">
-        <v>46296.08333333334</v>
+        <v>46296.33333333334</v>
       </c>
     </row>
     <row r="488">
@@ -27217,7 +27217,7 @@
         <v>46293.775</v>
       </c>
       <c r="M488" s="1" t="n">
-        <v>46296.08333333334</v>
+        <v>46296.33333333334</v>
       </c>
     </row>
     <row r="489">
@@ -27269,7 +27269,7 @@
         <v>46290.45833333334</v>
       </c>
       <c r="L489" s="1" t="n">
-        <v>46293.79166666666</v>
+        <v>46293.775</v>
       </c>
       <c r="M489" s="1" t="n">
         <v>46296.33333333334</v>
@@ -27321,13 +27321,13 @@
         </is>
       </c>
       <c r="K490" s="1" t="n">
-        <v>46296.375</v>
+        <v>46296.625</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>46296.4375</v>
+        <v>46296.6875</v>
       </c>
       <c r="M490" s="1" t="n">
-        <v>46296.95833333334</v>
+        <v>46297.16666666666</v>
       </c>
     </row>
     <row r="491">
@@ -27382,7 +27382,7 @@
         <v>46296.6875</v>
       </c>
       <c r="M491" s="1" t="n">
-        <v>46297.20833333334</v>
+        <v>46297.16666666666</v>
       </c>
     </row>
     <row r="492">
@@ -27431,13 +27431,13 @@
         </is>
       </c>
       <c r="K492" s="1" t="n">
-        <v>46298.66666666666</v>
+        <v>46298.625</v>
       </c>
       <c r="L492" s="1" t="n">
-        <v>46299.75</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="M492" s="1" t="n">
-        <v>46300.25</v>
+        <v>46300.20833333334</v>
       </c>
     </row>
     <row r="493">
@@ -27486,13 +27486,13 @@
         </is>
       </c>
       <c r="K493" s="1" t="n">
-        <v>46303.20833333334</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="L493" s="1" t="n">
-        <v>46303.33333333334</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="M493" s="1" t="n">
-        <v>46303.75</v>
+        <v>46303.70833333334</v>
       </c>
     </row>
     <row r="494">
@@ -27541,13 +27541,13 @@
         </is>
       </c>
       <c r="K494" s="1" t="n">
-        <v>46316</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="L494" s="1" t="n">
-        <v>46317.08333333334</v>
+        <v>46317.04166666666</v>
       </c>
       <c r="M494" s="1" t="n">
-        <v>46317.75</v>
+        <v>46317.70833333334</v>
       </c>
     </row>
     <row r="495">
@@ -27596,13 +27596,13 @@
         </is>
       </c>
       <c r="K495" s="1" t="n">
-        <v>46319</v>
+        <v>46318.95833333334</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>46319.08333333334</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="M495" s="1" t="n">
-        <v>46319.58333333334</v>
+        <v>46319.54166666666</v>
       </c>
     </row>
     <row r="496">
@@ -27651,13 +27651,13 @@
         </is>
       </c>
       <c r="K496" s="1" t="n">
-        <v>46320.5</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="L496" s="1" t="n">
-        <v>46320.58333333334</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="M496" s="1" t="n">
-        <v>46321.16666666666</v>
+        <v>46321.125</v>
       </c>
     </row>
     <row r="497">
@@ -27706,13 +27706,13 @@
         </is>
       </c>
       <c r="K497" s="1" t="n">
-        <v>46330.04166666666</v>
+        <v>46330</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>46331.08333333334</v>
+        <v>46331.04166666666</v>
       </c>
       <c r="M497" s="1" t="n">
-        <v>46331.66666666666</v>
+        <v>46331.625</v>
       </c>
     </row>
     <row r="498">
@@ -27757,13 +27757,13 @@
       </c>
       <c r="J498" t="inlineStr"/>
       <c r="K498" s="1" t="n">
+        <v>46340.41666666666</v>
+      </c>
+      <c r="L498" s="1" t="n">
         <v>46340.45833333334</v>
       </c>
-      <c r="L498" s="1" t="n">
-        <v>46340.5</v>
-      </c>
       <c r="M498" s="1" t="n">
-        <v>46341.25</v>
+        <v>46341.20833333334</v>
       </c>
     </row>
     <row r="499">
@@ -28403,27 +28403,27 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
           <t>CNSHA</t>
         </is>
       </c>
-      <c r="J510" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
       <c r="K510" s="1" t="n">
-        <v>46303.1875</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>46304.35416666666</v>
+        <v>46304.375</v>
       </c>
       <c r="M510" s="1" t="n">
-        <v>46305.1875</v>
+        <v>46305.375</v>
       </c>
     </row>
     <row r="511">
@@ -28468,7 +28468,7 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K511" s="1" t="n">
@@ -28523,7 +28523,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K512" s="1" t="n">
@@ -28568,12 +28568,12 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
@@ -28582,13 +28582,13 @@
         </is>
       </c>
       <c r="K513" s="1" t="n">
-        <v>46306.4375</v>
+        <v>46306.75</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>46306.47916666666</v>
+        <v>46309.95833333334</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46307.47916666666</v>
+        <v>46310.95833333334</v>
       </c>
     </row>
     <row r="514">
@@ -31489,13 +31489,13 @@
         </is>
       </c>
       <c r="K566" s="1" t="n">
+        <v>46298.20833333334</v>
+      </c>
+      <c r="L566" s="1" t="n">
         <v>46298.25</v>
       </c>
-      <c r="L566" s="1" t="n">
-        <v>46298.3125</v>
-      </c>
       <c r="M566" s="1" t="n">
-        <v>46298.5625</v>
+        <v>46298.875</v>
       </c>
     </row>
     <row r="567">
@@ -31544,13 +31544,13 @@
         </is>
       </c>
       <c r="K567" s="1" t="n">
-        <v>46299.45833333334</v>
+        <v>46299.75</v>
       </c>
       <c r="L567" s="1" t="n">
-        <v>46299.52083333334</v>
+        <v>46299.8125</v>
       </c>
       <c r="M567" s="1" t="n">
-        <v>46299.9375</v>
+        <v>46300.22916666666</v>
       </c>
     </row>
     <row r="568">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="K568" s="1" t="n">
-        <v>46300.20833333334</v>
+        <v>46300.5</v>
       </c>
       <c r="L568" s="1" t="n">
-        <v>46300.22916666666</v>
+        <v>46300.54166666666</v>
       </c>
       <c r="M568" s="1" t="n">
-        <v>46300.83333333334</v>
+        <v>46301.125</v>
       </c>
     </row>
     <row r="569">
@@ -31654,13 +31654,13 @@
         </is>
       </c>
       <c r="K569" s="1" t="n">
-        <v>46305.75</v>
+        <v>46306.04166666666</v>
       </c>
       <c r="L569" s="1" t="n">
-        <v>46305.91666666666</v>
+        <v>46306.20833333334</v>
       </c>
       <c r="M569" s="1" t="n">
-        <v>46306.5</v>
+        <v>46306.79166666666</v>
       </c>
     </row>
     <row r="570">
@@ -31709,13 +31709,13 @@
         </is>
       </c>
       <c r="K570" s="1" t="n">
-        <v>46308.14583333334</v>
+        <v>46308.4375</v>
       </c>
       <c r="L570" s="1" t="n">
-        <v>46308.1875</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="M570" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.83333333334</v>
       </c>
     </row>
     <row r="571">
@@ -31764,13 +31764,13 @@
         </is>
       </c>
       <c r="K571" s="1" t="n">
-        <v>46308.66666666666</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="L571" s="1" t="n">
-        <v>46308.75</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="M571" s="1" t="n">
-        <v>46309.75</v>
+        <v>46310.04166666666</v>
       </c>
     </row>
     <row r="572">
@@ -31819,13 +31819,13 @@
         </is>
       </c>
       <c r="K572" s="1" t="n">
-        <v>46309.95833333334</v>
+        <v>46310.25</v>
       </c>
       <c r="L572" s="1" t="n">
-        <v>46310</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="M572" s="1" t="n">
-        <v>46310.5</v>
+        <v>46310.79166666666</v>
       </c>
     </row>
     <row r="573">
@@ -31874,13 +31874,13 @@
         </is>
       </c>
       <c r="K573" s="1" t="n">
-        <v>46312.3125</v>
+        <v>46312.60416666666</v>
       </c>
       <c r="L573" s="1" t="n">
-        <v>46312.47916666666</v>
+        <v>46312.77083333334</v>
       </c>
       <c r="M573" s="1" t="n">
-        <v>46313.16666666666</v>
+        <v>46313.45833333334</v>
       </c>
     </row>
     <row r="574">
@@ -31929,13 +31929,13 @@
         </is>
       </c>
       <c r="K574" s="1" t="n">
-        <v>46318.375</v>
+        <v>46318.66666666666</v>
       </c>
       <c r="L574" s="1" t="n">
-        <v>46318.41666666666</v>
+        <v>46318.70833333334</v>
       </c>
       <c r="M574" s="1" t="n">
-        <v>46319.08333333334</v>
+        <v>46319.375</v>
       </c>
     </row>
     <row r="575">
@@ -31984,13 +31984,13 @@
         </is>
       </c>
       <c r="K575" s="1" t="n">
-        <v>46319.25</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="L575" s="1" t="n">
-        <v>46319.3125</v>
+        <v>46319.60416666666</v>
       </c>
       <c r="M575" s="1" t="n">
-        <v>46319.5625</v>
+        <v>46319.85416666666</v>
       </c>
     </row>
     <row r="576">
@@ -32039,13 +32039,13 @@
         </is>
       </c>
       <c r="K576" s="1" t="n">
-        <v>46320.45833333334</v>
+        <v>46320.75</v>
       </c>
       <c r="L576" s="1" t="n">
-        <v>46320.52083333334</v>
+        <v>46320.8125</v>
       </c>
       <c r="M576" s="1" t="n">
-        <v>46320.9375</v>
+        <v>46321.22916666666</v>
       </c>
     </row>
     <row r="577">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="K577" s="1" t="n">
-        <v>46321.20833333334</v>
+        <v>46321.5</v>
       </c>
       <c r="L577" s="1" t="n">
-        <v>46321.22916666666</v>
+        <v>46321.52083333334</v>
       </c>
       <c r="M577" s="1" t="n">
-        <v>46321.83333333334</v>
+        <v>46322.125</v>
       </c>
     </row>
     <row r="578">
@@ -32149,13 +32149,13 @@
         </is>
       </c>
       <c r="K578" s="1" t="n">
-        <v>46326.75</v>
+        <v>46327.04166666666</v>
       </c>
       <c r="L578" s="1" t="n">
-        <v>46326.91666666666</v>
+        <v>46327.20833333334</v>
       </c>
       <c r="M578" s="1" t="n">
-        <v>46327.5</v>
+        <v>46327.79166666666</v>
       </c>
     </row>
     <row r="579">
@@ -32204,13 +32204,13 @@
         </is>
       </c>
       <c r="K579" s="1" t="n">
-        <v>46329.14583333334</v>
+        <v>46329.4375</v>
       </c>
       <c r="L579" s="1" t="n">
-        <v>46329.1875</v>
+        <v>46329.47916666666</v>
       </c>
       <c r="M579" s="1" t="n">
-        <v>46329.54166666666</v>
+        <v>46329.83333333334</v>
       </c>
     </row>
     <row r="580">
@@ -32259,13 +32259,13 @@
         </is>
       </c>
       <c r="K580" s="1" t="n">
-        <v>46329.66666666666</v>
+        <v>46329.95833333334</v>
       </c>
       <c r="L580" s="1" t="n">
-        <v>46329.75</v>
+        <v>46330.04166666666</v>
       </c>
       <c r="M580" s="1" t="n">
-        <v>46330.75</v>
+        <v>46331.04166666666</v>
       </c>
     </row>
     <row r="581">
@@ -32314,13 +32314,13 @@
         </is>
       </c>
       <c r="K581" s="1" t="n">
-        <v>46330.95833333334</v>
+        <v>46331.25</v>
       </c>
       <c r="L581" s="1" t="n">
-        <v>46331</v>
+        <v>46331.29166666666</v>
       </c>
       <c r="M581" s="1" t="n">
-        <v>46331.5</v>
+        <v>46331.79166666666</v>
       </c>
     </row>
     <row r="582">
@@ -32369,13 +32369,13 @@
         </is>
       </c>
       <c r="K582" s="1" t="n">
-        <v>46333.3125</v>
+        <v>46333.60416666666</v>
       </c>
       <c r="L582" s="1" t="n">
-        <v>46333.47916666666</v>
+        <v>46333.77083333334</v>
       </c>
       <c r="M582" s="1" t="n">
-        <v>46334.16666666666</v>
+        <v>46334.45833333334</v>
       </c>
     </row>
     <row r="583">
@@ -32424,13 +32424,13 @@
         </is>
       </c>
       <c r="K583" s="1" t="n">
-        <v>46339.375</v>
+        <v>46339.66666666666</v>
       </c>
       <c r="L583" s="1" t="n">
-        <v>46339.41666666666</v>
+        <v>46339.70833333334</v>
       </c>
       <c r="M583" s="1" t="n">
-        <v>46340.08333333334</v>
+        <v>46340.375</v>
       </c>
     </row>
     <row r="584">
@@ -32479,13 +32479,13 @@
         </is>
       </c>
       <c r="K584" s="1" t="n">
-        <v>46340.25</v>
+        <v>46340.54166666666</v>
       </c>
       <c r="L584" s="1" t="n">
-        <v>46340.3125</v>
+        <v>46340.60416666666</v>
       </c>
       <c r="M584" s="1" t="n">
-        <v>46340.5625</v>
+        <v>46340.85416666666</v>
       </c>
     </row>
     <row r="585">
@@ -32534,13 +32534,13 @@
         </is>
       </c>
       <c r="K585" s="1" t="n">
-        <v>46341.45833333334</v>
+        <v>46341.75</v>
       </c>
       <c r="L585" s="1" t="n">
-        <v>46341.52083333334</v>
+        <v>46341.8125</v>
       </c>
       <c r="M585" s="1" t="n">
-        <v>46341.9375</v>
+        <v>46342.22916666666</v>
       </c>
     </row>
     <row r="586">
@@ -32589,13 +32589,13 @@
         </is>
       </c>
       <c r="K586" s="1" t="n">
-        <v>46342.20833333334</v>
+        <v>46342.5</v>
       </c>
       <c r="L586" s="1" t="n">
-        <v>46342.22916666666</v>
+        <v>46342.52083333334</v>
       </c>
       <c r="M586" s="1" t="n">
-        <v>46342.83333333334</v>
+        <v>46343.125</v>
       </c>
     </row>
     <row r="587">
@@ -32644,13 +32644,13 @@
         </is>
       </c>
       <c r="K587" s="1" t="n">
-        <v>46347.75</v>
+        <v>46348.04166666666</v>
       </c>
       <c r="L587" s="1" t="n">
-        <v>46347.91666666666</v>
+        <v>46348.20833333334</v>
       </c>
       <c r="M587" s="1" t="n">
-        <v>46348.5</v>
+        <v>46348.79166666666</v>
       </c>
     </row>
     <row r="588">
@@ -32699,13 +32699,13 @@
         </is>
       </c>
       <c r="K588" s="1" t="n">
-        <v>46350.14583333334</v>
+        <v>46350.4375</v>
       </c>
       <c r="L588" s="1" t="n">
-        <v>46350.1875</v>
+        <v>46350.47916666666</v>
       </c>
       <c r="M588" s="1" t="n">
-        <v>46350.54166666666</v>
+        <v>46350.83333333334</v>
       </c>
     </row>
     <row r="589">
@@ -32754,13 +32754,13 @@
         </is>
       </c>
       <c r="K589" s="1" t="n">
-        <v>46350.66666666666</v>
+        <v>46350.95833333334</v>
       </c>
       <c r="L589" s="1" t="n">
-        <v>46350.75</v>
+        <v>46351.04166666666</v>
       </c>
       <c r="M589" s="1" t="n">
-        <v>46351.75</v>
+        <v>46352.04166666666</v>
       </c>
     </row>
     <row r="590">
@@ -32809,13 +32809,13 @@
         </is>
       </c>
       <c r="K590" s="1" t="n">
-        <v>46351.95833333334</v>
+        <v>46352.25</v>
       </c>
       <c r="L590" s="1" t="n">
-        <v>46352</v>
+        <v>46352.29166666666</v>
       </c>
       <c r="M590" s="1" t="n">
-        <v>46352.5</v>
+        <v>46352.79166666666</v>
       </c>
     </row>
     <row r="591">
@@ -32860,13 +32860,13 @@
       </c>
       <c r="J591" t="inlineStr"/>
       <c r="K591" s="1" t="n">
-        <v>46354.3125</v>
+        <v>46354.60416666666</v>
       </c>
       <c r="L591" s="1" t="n">
-        <v>46354.47916666666</v>
+        <v>46354.77083333334</v>
       </c>
       <c r="M591" s="1" t="n">
-        <v>46355.16666666666</v>
+        <v>46355.45833333334</v>
       </c>
     </row>
     <row r="592">
@@ -33633,10 +33633,10 @@
         <v>46295.95833333334</v>
       </c>
       <c r="L605" s="1" t="n">
-        <v>46296.125</v>
+        <v>46296.625</v>
       </c>
       <c r="M605" s="1" t="n">
-        <v>46297.33333333334</v>
+        <v>46297.08333333334</v>
       </c>
     </row>
     <row r="606">
@@ -33685,13 +33685,13 @@
         </is>
       </c>
       <c r="K606" s="1" t="n">
-        <v>46302.83333333334</v>
+        <v>46302.41666666666</v>
       </c>
       <c r="L606" s="1" t="n">
-        <v>46302.875</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="M606" s="1" t="n">
-        <v>46303.875</v>
+        <v>46303.45833333334</v>
       </c>
     </row>
     <row r="607">
@@ -33740,13 +33740,13 @@
         </is>
       </c>
       <c r="K607" s="1" t="n">
-        <v>46304.875</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="L607" s="1" t="n">
-        <v>46304.91666666666</v>
+        <v>46304.5</v>
       </c>
       <c r="M607" s="1" t="n">
-        <v>46305.91666666666</v>
+        <v>46305.5</v>
       </c>
     </row>
     <row r="608">
@@ -33795,13 +33795,13 @@
         </is>
       </c>
       <c r="K608" s="1" t="n">
-        <v>46310.54166666666</v>
+        <v>46310.125</v>
       </c>
       <c r="L608" s="1" t="n">
-        <v>46310.70833333334</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="M608" s="1" t="n">
-        <v>46311.08333333334</v>
+        <v>46310.66666666666</v>
       </c>
     </row>
     <row r="609">
@@ -33850,13 +33850,13 @@
         </is>
       </c>
       <c r="K609" s="1" t="n">
-        <v>46312.91666666666</v>
+        <v>46312.5</v>
       </c>
       <c r="L609" s="1" t="n">
+        <v>46312.54166666666</v>
+      </c>
+      <c r="M609" s="1" t="n">
         <v>46312.95833333334</v>
-      </c>
-      <c r="M609" s="1" t="n">
-        <v>46313.375</v>
       </c>
     </row>
     <row r="610">
@@ -33905,13 +33905,13 @@
         </is>
       </c>
       <c r="K610" s="1" t="n">
-        <v>46313.5</v>
+        <v>46313.08333333334</v>
       </c>
       <c r="L610" s="1" t="n">
-        <v>46313.58333333334</v>
+        <v>46313.16666666666</v>
       </c>
       <c r="M610" s="1" t="n">
-        <v>46314.625</v>
+        <v>46314.20833333334</v>
       </c>
     </row>
     <row r="611">
@@ -33960,13 +33960,13 @@
         </is>
       </c>
       <c r="K611" s="1" t="n">
-        <v>46314.79166666666</v>
+        <v>46314.375</v>
       </c>
       <c r="L611" s="1" t="n">
-        <v>46314.83333333334</v>
+        <v>46314.41666666666</v>
       </c>
       <c r="M611" s="1" t="n">
-        <v>46315.33333333334</v>
+        <v>46314.91666666666</v>
       </c>
     </row>
     <row r="612">
@@ -34015,10 +34015,10 @@
         </is>
       </c>
       <c r="K612" s="1" t="n">
-        <v>46316.79166666666</v>
+        <v>46316.375</v>
       </c>
       <c r="L612" s="1" t="n">
-        <v>46316.95833333334</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="M612" s="1" t="n">
         <v>46317.58333333334</v>
@@ -35496,13 +35496,13 @@
         </is>
       </c>
       <c r="K639" s="1" t="n">
-        <v>46296.08333333334</v>
+        <v>46296.20833333334</v>
       </c>
       <c r="L639" s="1" t="n">
-        <v>46296.125</v>
+        <v>46296.27083333334</v>
       </c>
       <c r="M639" s="1" t="n">
-        <v>46296.75</v>
+        <v>46296.91666666666</v>
       </c>
     </row>
     <row r="640">
@@ -35551,13 +35551,13 @@
         </is>
       </c>
       <c r="K640" s="1" t="n">
-        <v>46298.70833333334</v>
+        <v>46298.875</v>
       </c>
       <c r="L640" s="1" t="n">
-        <v>46298.875</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="M640" s="1" t="n">
-        <v>46299.41666666666</v>
+        <v>46299.58333333334</v>
       </c>
     </row>
     <row r="641">
@@ -35606,13 +35606,13 @@
         </is>
       </c>
       <c r="K641" s="1" t="n">
-        <v>46301.20833333334</v>
+        <v>46301.375</v>
       </c>
       <c r="L641" s="1" t="n">
-        <v>46301.25</v>
+        <v>46301.41666666666</v>
       </c>
       <c r="M641" s="1" t="n">
-        <v>46301.5</v>
+        <v>46301.66666666666</v>
       </c>
     </row>
     <row r="642">
@@ -35661,13 +35661,13 @@
         </is>
       </c>
       <c r="K642" s="1" t="n">
-        <v>46301.91666666666</v>
+        <v>46302.08333333334</v>
       </c>
       <c r="L642" s="1" t="n">
-        <v>46302.04166666666</v>
+        <v>46302.20833333334</v>
       </c>
       <c r="M642" s="1" t="n">
-        <v>46303.16666666666</v>
+        <v>46303.33333333334</v>
       </c>
     </row>
     <row r="643">
@@ -35716,13 +35716,13 @@
         </is>
       </c>
       <c r="K643" s="1" t="n">
-        <v>46303.5</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="L643" s="1" t="n">
-        <v>46303.54166666666</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="M643" s="1" t="n">
-        <v>46303.875</v>
+        <v>46304.04166666666</v>
       </c>
     </row>
     <row r="644">
@@ -35771,13 +35771,13 @@
         </is>
       </c>
       <c r="K644" s="1" t="n">
-        <v>46307.75</v>
+        <v>46307.91666666666</v>
       </c>
       <c r="L644" s="1" t="n">
-        <v>46307.79166666666</v>
+        <v>46307.95833333334</v>
       </c>
       <c r="M644" s="1" t="n">
-        <v>46308.20833333334</v>
+        <v>46308.375</v>
       </c>
     </row>
     <row r="645">
@@ -35826,13 +35826,13 @@
         </is>
       </c>
       <c r="K645" s="1" t="n">
-        <v>46308.45833333334</v>
+        <v>46308.625</v>
       </c>
       <c r="L645" s="1" t="n">
-        <v>46308.45833333334</v>
+        <v>46308.625</v>
       </c>
       <c r="M645" s="1" t="n">
-        <v>46308.83333333334</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="646">
@@ -35881,13 +35881,13 @@
         </is>
       </c>
       <c r="K646" s="1" t="n">
-        <v>46310.16666666666</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="L646" s="1" t="n">
-        <v>46310.16666666666</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="M646" s="1" t="n">
-        <v>46310.41666666666</v>
+        <v>46310.58333333334</v>
       </c>
     </row>
     <row r="647">
@@ -38578,7 +38578,7 @@
         <v>46295</v>
       </c>
       <c r="M695" s="1" t="n">
-        <v>46295.5</v>
+        <v>46295.625</v>
       </c>
     </row>
     <row r="696">
@@ -38627,13 +38627,13 @@
         </is>
       </c>
       <c r="K696" s="1" t="n">
-        <v>46295.66666666666</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="L696" s="1" t="n">
-        <v>46295.79166666666</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="M696" s="1" t="n">
-        <v>46296.29166666666</v>
+        <v>46297.625</v>
       </c>
     </row>
     <row r="697">
@@ -38682,13 +38682,13 @@
         </is>
       </c>
       <c r="K697" s="1" t="n">
-        <v>46297.3125</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="L697" s="1" t="n">
-        <v>46297.375</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="M697" s="1" t="n">
-        <v>46297.79166666666</v>
+        <v>46299.14583333334</v>
       </c>
     </row>
     <row r="698">
@@ -38737,13 +38737,13 @@
         </is>
       </c>
       <c r="K698" s="1" t="n">
-        <v>46298.10416666666</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="L698" s="1" t="n">
-        <v>46298.125</v>
+        <v>46299.5</v>
       </c>
       <c r="M698" s="1" t="n">
-        <v>46298.72916666666</v>
+        <v>46300.10416666666</v>
       </c>
     </row>
     <row r="699">
@@ -38792,13 +38792,13 @@
         </is>
       </c>
       <c r="K699" s="1" t="n">
-        <v>46304.14583333334</v>
+        <v>46305.52083333334</v>
       </c>
       <c r="L699" s="1" t="n">
-        <v>46304.3125</v>
+        <v>46305.6875</v>
       </c>
       <c r="M699" s="1" t="n">
-        <v>46304.89583333334</v>
+        <v>46306.27083333334</v>
       </c>
     </row>
     <row r="700">
@@ -38847,13 +38847,13 @@
         </is>
       </c>
       <c r="K700" s="1" t="n">
-        <v>46306.64583333334</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="L700" s="1" t="n">
-        <v>46306.6875</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="M700" s="1" t="n">
-        <v>46307.04166666666</v>
+        <v>46308.4375</v>
       </c>
     </row>
     <row r="701">
@@ -38902,13 +38902,13 @@
         </is>
       </c>
       <c r="K701" s="1" t="n">
-        <v>46307.16666666666</v>
+        <v>46308.5625</v>
       </c>
       <c r="L701" s="1" t="n">
-        <v>46307.25</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="M701" s="1" t="n">
-        <v>46308.25</v>
+        <v>46309.64583333334</v>
       </c>
     </row>
     <row r="702">
@@ -38957,13 +38957,13 @@
         </is>
       </c>
       <c r="K702" s="1" t="n">
-        <v>46308.45833333334</v>
+        <v>46309.85416666666</v>
       </c>
       <c r="L702" s="1" t="n">
-        <v>46308.5</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="M702" s="1" t="n">
-        <v>46309</v>
+        <v>46310.39583333334</v>
       </c>
     </row>
     <row r="703">
@@ -39012,13 +39012,13 @@
         </is>
       </c>
       <c r="K703" s="1" t="n">
-        <v>46310.8125</v>
+        <v>46312.20833333334</v>
       </c>
       <c r="L703" s="1" t="n">
-        <v>46310.97916666666</v>
+        <v>46312.375</v>
       </c>
       <c r="M703" s="1" t="n">
-        <v>46311.66666666666</v>
+        <v>46313.0625</v>
       </c>
     </row>
     <row r="704">
@@ -39067,13 +39067,13 @@
         </is>
       </c>
       <c r="K704" s="1" t="n">
-        <v>46317.66666666666</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="L704" s="1" t="n">
-        <v>46317.70833333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="M704" s="1" t="n">
-        <v>46318.375</v>
+        <v>46319.75</v>
       </c>
     </row>
     <row r="705">
@@ -39122,13 +39122,13 @@
         </is>
       </c>
       <c r="K705" s="1" t="n">
-        <v>46318.54166666666</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="L705" s="1" t="n">
-        <v>46318.60416666666</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="M705" s="1" t="n">
-        <v>46318.85416666666</v>
+        <v>46320.22916666666</v>
       </c>
     </row>
     <row r="706">
@@ -39177,13 +39177,13 @@
         </is>
       </c>
       <c r="K706" s="1" t="n">
-        <v>46319.75</v>
+        <v>46321.125</v>
       </c>
       <c r="L706" s="1" t="n">
-        <v>46319.8125</v>
+        <v>46321.1875</v>
       </c>
       <c r="M706" s="1" t="n">
-        <v>46320.22916666666</v>
+        <v>46321.60416666666</v>
       </c>
     </row>
     <row r="707">
@@ -39232,13 +39232,13 @@
         </is>
       </c>
       <c r="K707" s="1" t="n">
-        <v>46320.5</v>
+        <v>46321.875</v>
       </c>
       <c r="L707" s="1" t="n">
-        <v>46320.52083333334</v>
+        <v>46321.89583333334</v>
       </c>
       <c r="M707" s="1" t="n">
-        <v>46321.125</v>
+        <v>46322.5</v>
       </c>
     </row>
     <row r="708">
@@ -39287,13 +39287,13 @@
         </is>
       </c>
       <c r="K708" s="1" t="n">
-        <v>46325.95833333334</v>
+        <v>46327.33333333334</v>
       </c>
       <c r="L708" s="1" t="n">
-        <v>46326.125</v>
+        <v>46327.5</v>
       </c>
       <c r="M708" s="1" t="n">
-        <v>46326.70833333334</v>
+        <v>46328.08333333334</v>
       </c>
     </row>
     <row r="709">
@@ -39342,13 +39342,13 @@
         </is>
       </c>
       <c r="K709" s="1" t="n">
-        <v>46328.3125</v>
+        <v>46329.6875</v>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46328.35416666666</v>
+        <v>46329.72916666666</v>
       </c>
       <c r="M709" s="1" t="n">
-        <v>46328.70833333334</v>
+        <v>46330.08333333334</v>
       </c>
     </row>
     <row r="710">
@@ -39397,13 +39397,13 @@
         </is>
       </c>
       <c r="K710" s="1" t="n">
-        <v>46328.83333333334</v>
+        <v>46330.20833333334</v>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46328.91666666666</v>
+        <v>46330.29166666666</v>
       </c>
       <c r="M710" s="1" t="n">
-        <v>46329.91666666666</v>
+        <v>46331.29166666666</v>
       </c>
     </row>
     <row r="711">
@@ -39452,13 +39452,13 @@
         </is>
       </c>
       <c r="K711" s="1" t="n">
-        <v>46330.125</v>
+        <v>46331.5</v>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46330.16666666666</v>
+        <v>46331.54166666666</v>
       </c>
       <c r="M711" s="1" t="n">
-        <v>46330.66666666666</v>
+        <v>46332.04166666666</v>
       </c>
     </row>
     <row r="712">
@@ -39507,13 +39507,13 @@
         </is>
       </c>
       <c r="K712" s="1" t="n">
-        <v>46332.47916666666</v>
+        <v>46333.85416666666</v>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46332.64583333334</v>
+        <v>46334.02083333334</v>
       </c>
       <c r="M712" s="1" t="n">
-        <v>46333.33333333334</v>
+        <v>46334.70833333334</v>
       </c>
     </row>
     <row r="713">
@@ -39562,13 +39562,13 @@
         </is>
       </c>
       <c r="K713" s="1" t="n">
-        <v>46338.25</v>
+        <v>46339.91666666666</v>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46338.29166666666</v>
+        <v>46339.95833333334</v>
       </c>
       <c r="M713" s="1" t="n">
-        <v>46338.95833333334</v>
+        <v>46340.625</v>
       </c>
     </row>
     <row r="714">
@@ -39617,13 +39617,13 @@
         </is>
       </c>
       <c r="K714" s="1" t="n">
-        <v>46339.125</v>
+        <v>46340.79166666666</v>
       </c>
       <c r="L714" s="1" t="n">
-        <v>46339.1875</v>
+        <v>46340.85416666666</v>
       </c>
       <c r="M714" s="1" t="n">
-        <v>46339.4375</v>
+        <v>46341.10416666666</v>
       </c>
     </row>
     <row r="715">
@@ -39672,13 +39672,13 @@
         </is>
       </c>
       <c r="K715" s="1" t="n">
-        <v>46340.33333333334</v>
+        <v>46342</v>
       </c>
       <c r="L715" s="1" t="n">
-        <v>46340.39583333334</v>
+        <v>46342.0625</v>
       </c>
       <c r="M715" s="1" t="n">
-        <v>46340.8125</v>
+        <v>46342.47916666666</v>
       </c>
     </row>
     <row r="716">
@@ -39727,13 +39727,13 @@
         </is>
       </c>
       <c r="K716" s="1" t="n">
-        <v>46341.08333333334</v>
+        <v>46342.75</v>
       </c>
       <c r="L716" s="1" t="n">
-        <v>46341.10416666666</v>
+        <v>46342.77083333334</v>
       </c>
       <c r="M716" s="1" t="n">
-        <v>46341.70833333334</v>
+        <v>46343.375</v>
       </c>
     </row>
     <row r="717">
@@ -39782,13 +39782,13 @@
         </is>
       </c>
       <c r="K717" s="1" t="n">
-        <v>46346.54166666666</v>
+        <v>46348.20833333334</v>
       </c>
       <c r="L717" s="1" t="n">
-        <v>46346.70833333334</v>
+        <v>46348.375</v>
       </c>
       <c r="M717" s="1" t="n">
-        <v>46347.29166666666</v>
+        <v>46348.95833333334</v>
       </c>
     </row>
     <row r="718">
@@ -39837,13 +39837,13 @@
         </is>
       </c>
       <c r="K718" s="1" t="n">
-        <v>46348.93958333333</v>
+        <v>46350.60625</v>
       </c>
       <c r="L718" s="1" t="n">
-        <v>46348.98125</v>
+        <v>46350.64791666667</v>
       </c>
       <c r="M718" s="1" t="n">
-        <v>46349.33541666667</v>
+        <v>46351.00208333333</v>
       </c>
     </row>
     <row r="719">
@@ -39892,13 +39892,13 @@
         </is>
       </c>
       <c r="K719" s="1" t="n">
-        <v>46349.46041666667</v>
+        <v>46351.12708333333</v>
       </c>
       <c r="L719" s="1" t="n">
-        <v>46349.54375</v>
+        <v>46351.21041666667</v>
       </c>
       <c r="M719" s="1" t="n">
-        <v>46350.54375</v>
+        <v>46352.21041666667</v>
       </c>
     </row>
     <row r="720">
@@ -39947,13 +39947,13 @@
         </is>
       </c>
       <c r="K720" s="1" t="n">
-        <v>46350.75208333333</v>
+        <v>46352.41875</v>
       </c>
       <c r="L720" s="1" t="n">
-        <v>46350.79375</v>
+        <v>46352.46041666667</v>
       </c>
       <c r="M720" s="1" t="n">
-        <v>46351.29375</v>
+        <v>46352.96041666667</v>
       </c>
     </row>
     <row r="721">
@@ -39998,13 +39998,13 @@
       </c>
       <c r="J721" t="inlineStr"/>
       <c r="K721" s="1" t="n">
-        <v>46353.10625</v>
+        <v>46354.77291666667</v>
       </c>
       <c r="L721" s="1" t="n">
-        <v>46353.27291666667</v>
+        <v>46354.93958333333</v>
       </c>
       <c r="M721" s="1" t="n">
-        <v>46353.96041666667</v>
+        <v>46355.62708333333</v>
       </c>
     </row>
     <row r="722">
@@ -43132,10 +43132,10 @@
         <v>46296.41666666666</v>
       </c>
       <c r="L778" s="1" t="n">
-        <v>46297.29166666666</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="M778" s="1" t="n">
-        <v>46298.41666666666</v>
+        <v>46298.25</v>
       </c>
     </row>
     <row r="779">
@@ -43184,13 +43184,13 @@
         </is>
       </c>
       <c r="K779" s="1" t="n">
-        <v>46298.54166666666</v>
+        <v>46298.375</v>
       </c>
       <c r="L779" s="1" t="n">
-        <v>46298.58333333334</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="M779" s="1" t="n">
-        <v>46298.83333333334</v>
+        <v>46298.66666666666</v>
       </c>
     </row>
     <row r="780">
@@ -43239,13 +43239,13 @@
         </is>
       </c>
       <c r="K780" s="1" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="L780" s="1" t="n">
-        <v>46299.41666666666</v>
+        <v>46299.25</v>
       </c>
       <c r="M780" s="1" t="n">
-        <v>46299.75</v>
+        <v>46299.58333333334</v>
       </c>
     </row>
     <row r="781">
@@ -43294,13 +43294,13 @@
         </is>
       </c>
       <c r="K781" s="1" t="n">
+        <v>46304.54166666666</v>
+      </c>
+      <c r="L781" s="1" t="n">
         <v>46304.70833333334</v>
       </c>
-      <c r="L781" s="1" t="n">
-        <v>46304.875</v>
-      </c>
       <c r="M781" s="1" t="n">
-        <v>46305.5</v>
+        <v>46305.33333333334</v>
       </c>
     </row>
     <row r="782">
@@ -43349,13 +43349,13 @@
         </is>
       </c>
       <c r="K782" s="1" t="n">
-        <v>46307.16666666666</v>
+        <v>46307</v>
       </c>
       <c r="L782" s="1" t="n">
-        <v>46307.20833333334</v>
+        <v>46307.04166666666</v>
       </c>
       <c r="M782" s="1" t="n">
-        <v>46307.45833333334</v>
+        <v>46307.29166666666</v>
       </c>
     </row>
     <row r="783">
@@ -43404,13 +43404,13 @@
         </is>
       </c>
       <c r="K783" s="1" t="n">
-        <v>46307.54166666666</v>
+        <v>46307.375</v>
       </c>
       <c r="L783" s="1" t="n">
-        <v>46307.66666666666</v>
+        <v>46307.5</v>
       </c>
       <c r="M783" s="1" t="n">
-        <v>46309.16666666666</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="784">
@@ -43459,13 +43459,13 @@
         </is>
       </c>
       <c r="K784" s="1" t="n">
-        <v>46309.375</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="L784" s="1" t="n">
-        <v>46309.41666666666</v>
+        <v>46309.25</v>
       </c>
       <c r="M784" s="1" t="n">
-        <v>46309.83333333334</v>
+        <v>46309.66666666666</v>
       </c>
     </row>
     <row r="785">
@@ -43514,13 +43514,13 @@
         </is>
       </c>
       <c r="K785" s="1" t="n">
+        <v>46311.29166666666</v>
+      </c>
+      <c r="L785" s="1" t="n">
         <v>46311.45833333334</v>
       </c>
-      <c r="L785" s="1" t="n">
-        <v>46311.625</v>
-      </c>
       <c r="M785" s="1" t="n">
-        <v>46312.16666666666</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="786">
@@ -43569,13 +43569,13 @@
         </is>
       </c>
       <c r="K786" s="1" t="n">
-        <v>46317.45833333334</v>
+        <v>46317.29166666666</v>
       </c>
       <c r="L786" s="1" t="n">
-        <v>46317.5</v>
+        <v>46317.33333333334</v>
       </c>
       <c r="M786" s="1" t="n">
-        <v>46318.58333333334</v>
+        <v>46318.41666666666</v>
       </c>
     </row>
     <row r="787">
@@ -43624,13 +43624,13 @@
         </is>
       </c>
       <c r="K787" s="1" t="n">
-        <v>46318.70833333334</v>
+        <v>46318.54166666666</v>
       </c>
       <c r="L787" s="1" t="n">
-        <v>46318.75</v>
+        <v>46318.58333333334</v>
       </c>
       <c r="M787" s="1" t="n">
-        <v>46319</v>
+        <v>46318.83333333334</v>
       </c>
     </row>
     <row r="788">
@@ -43679,13 +43679,13 @@
         </is>
       </c>
       <c r="K788" s="1" t="n">
-        <v>46319.5</v>
+        <v>46319.33333333334</v>
       </c>
       <c r="L788" s="1" t="n">
-        <v>46319.58333333334</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="M788" s="1" t="n">
-        <v>46319.91666666666</v>
+        <v>46319.75</v>
       </c>
     </row>
     <row r="789">
@@ -43734,13 +43734,13 @@
         </is>
       </c>
       <c r="K789" s="1" t="n">
+        <v>46324.625</v>
+      </c>
+      <c r="L789" s="1" t="n">
         <v>46324.79166666666</v>
       </c>
-      <c r="L789" s="1" t="n">
-        <v>46324.95833333334</v>
-      </c>
       <c r="M789" s="1" t="n">
-        <v>46325.58333333334</v>
+        <v>46325.41666666666</v>
       </c>
     </row>
     <row r="790">
@@ -43789,13 +43789,13 @@
         </is>
       </c>
       <c r="K790" s="1" t="n">
-        <v>46327.25</v>
+        <v>46327.08333333334</v>
       </c>
       <c r="L790" s="1" t="n">
-        <v>46327.29166666666</v>
+        <v>46327.125</v>
       </c>
       <c r="M790" s="1" t="n">
-        <v>46327.54166666666</v>
+        <v>46327.375</v>
       </c>
     </row>
     <row r="791">
@@ -43844,13 +43844,13 @@
         </is>
       </c>
       <c r="K791" s="1" t="n">
-        <v>46327.66666666666</v>
+        <v>46327.5</v>
       </c>
       <c r="L791" s="1" t="n">
-        <v>46327.79166666666</v>
+        <v>46327.625</v>
       </c>
       <c r="M791" s="1" t="n">
-        <v>46329.29166666666</v>
+        <v>46329.125</v>
       </c>
     </row>
     <row r="792">
@@ -43899,13 +43899,13 @@
         </is>
       </c>
       <c r="K792" s="1" t="n">
-        <v>46329.5</v>
+        <v>46329.33333333334</v>
       </c>
       <c r="L792" s="1" t="n">
-        <v>46329.54166666666</v>
+        <v>46329.375</v>
       </c>
       <c r="M792" s="1" t="n">
-        <v>46329.95833333334</v>
+        <v>46329.79166666666</v>
       </c>
     </row>
     <row r="793">
@@ -43954,13 +43954,13 @@
         </is>
       </c>
       <c r="K793" s="1" t="n">
+        <v>46331.33333333334</v>
+      </c>
+      <c r="L793" s="1" t="n">
         <v>46331.5</v>
       </c>
-      <c r="L793" s="1" t="n">
-        <v>46331.66666666666</v>
-      </c>
       <c r="M793" s="1" t="n">
-        <v>46332.20833333334</v>
+        <v>46332.04166666666</v>
       </c>
     </row>
     <row r="794">
@@ -44009,13 +44009,13 @@
         </is>
       </c>
       <c r="K794" s="1" t="n">
-        <v>46337.58333333334</v>
+        <v>46337.41666666666</v>
       </c>
       <c r="L794" s="1" t="n">
-        <v>46337.625</v>
+        <v>46337.45833333334</v>
       </c>
       <c r="M794" s="1" t="n">
-        <v>46338.70833333334</v>
+        <v>46338.54166666666</v>
       </c>
     </row>
     <row r="795">
@@ -44064,13 +44064,13 @@
         </is>
       </c>
       <c r="K795" s="1" t="n">
-        <v>46338.875</v>
+        <v>46338.70833333334</v>
       </c>
       <c r="L795" s="1" t="n">
-        <v>46338.91666666666</v>
+        <v>46338.75</v>
       </c>
       <c r="M795" s="1" t="n">
-        <v>46339.16666666666</v>
+        <v>46339</v>
       </c>
     </row>
     <row r="796">
@@ -44119,13 +44119,13 @@
         </is>
       </c>
       <c r="K796" s="1" t="n">
-        <v>46339.625</v>
+        <v>46339.45833333334</v>
       </c>
       <c r="L796" s="1" t="n">
-        <v>46339.70833333334</v>
+        <v>46339.54166666666</v>
       </c>
       <c r="M796" s="1" t="n">
-        <v>46340.04166666666</v>
+        <v>46339.875</v>
       </c>
     </row>
     <row r="797">
@@ -44174,13 +44174,13 @@
         </is>
       </c>
       <c r="K797" s="1" t="n">
+        <v>46344.875</v>
+      </c>
+      <c r="L797" s="1" t="n">
         <v>46345.04166666666</v>
       </c>
-      <c r="L797" s="1" t="n">
-        <v>46345.20833333334</v>
-      </c>
       <c r="M797" s="1" t="n">
-        <v>46345.83333333334</v>
+        <v>46345.66666666666</v>
       </c>
     </row>
     <row r="798">
@@ -44229,13 +44229,13 @@
         </is>
       </c>
       <c r="K798" s="1" t="n">
-        <v>46347.625</v>
+        <v>46347.45833333334</v>
       </c>
       <c r="L798" s="1" t="n">
-        <v>46347.66666666666</v>
+        <v>46347.5</v>
       </c>
       <c r="M798" s="1" t="n">
-        <v>46347.91666666666</v>
+        <v>46347.75</v>
       </c>
     </row>
     <row r="799">
@@ -44284,13 +44284,13 @@
         </is>
       </c>
       <c r="K799" s="1" t="n">
-        <v>46348.20833333334</v>
+        <v>46348.04166666666</v>
       </c>
       <c r="L799" s="1" t="n">
-        <v>46348.33333333334</v>
+        <v>46348.16666666666</v>
       </c>
       <c r="M799" s="1" t="n">
-        <v>46349.83333333334</v>
+        <v>46349.66666666666</v>
       </c>
     </row>
     <row r="800">
@@ -44339,13 +44339,13 @@
         </is>
       </c>
       <c r="K800" s="1" t="n">
-        <v>46350.04166666666</v>
+        <v>46349.875</v>
       </c>
       <c r="L800" s="1" t="n">
-        <v>46350.08333333334</v>
+        <v>46349.91666666666</v>
       </c>
       <c r="M800" s="1" t="n">
-        <v>46350.5</v>
+        <v>46350.33333333334</v>
       </c>
     </row>
     <row r="801">
@@ -44390,13 +44390,13 @@
       </c>
       <c r="J801" t="inlineStr"/>
       <c r="K801" s="1" t="n">
+        <v>46351.91666666666</v>
+      </c>
+      <c r="L801" s="1" t="n">
         <v>46352.08333333334</v>
       </c>
-      <c r="L801" s="1" t="n">
-        <v>46352.25</v>
-      </c>
       <c r="M801" s="1" t="n">
-        <v>46352.79166666666</v>
+        <v>46352.625</v>
       </c>
     </row>
     <row r="802">
@@ -50871,10 +50871,10 @@
         <v>46294.35416666666</v>
       </c>
       <c r="L919" s="1" t="n">
-        <v>46295.41666666666</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M919" s="1" t="n">
-        <v>46296.5</v>
+        <v>46296.875</v>
       </c>
     </row>
     <row r="920">
@@ -50923,13 +50923,13 @@
         </is>
       </c>
       <c r="K920" s="1" t="n">
-        <v>46296.79166666666</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="L920" s="1" t="n">
-        <v>46296.85416666666</v>
+        <v>46297.22916666666</v>
       </c>
       <c r="M920" s="1" t="n">
-        <v>46297.125</v>
+        <v>46297.5</v>
       </c>
     </row>
     <row r="921">
@@ -50978,13 +50978,13 @@
         </is>
       </c>
       <c r="K921" s="1" t="n">
-        <v>46299.95833333334</v>
+        <v>46300.33333333334</v>
       </c>
       <c r="L921" s="1" t="n">
-        <v>46300</v>
+        <v>46300.375</v>
       </c>
       <c r="M921" s="1" t="n">
-        <v>46300.45833333334</v>
+        <v>46300.83333333334</v>
       </c>
     </row>
     <row r="922">
@@ -51033,13 +51033,13 @@
         </is>
       </c>
       <c r="K922" s="1" t="n">
-        <v>46302.625</v>
+        <v>46303</v>
       </c>
       <c r="L922" s="1" t="n">
-        <v>46302.79166666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="M922" s="1" t="n">
-        <v>46303.25</v>
+        <v>46303.625</v>
       </c>
     </row>
     <row r="923">
@@ -51088,13 +51088,13 @@
         </is>
       </c>
       <c r="K923" s="1" t="n">
-        <v>46304.83333333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="L923" s="1" t="n">
-        <v>46304.875</v>
+        <v>46305.25</v>
       </c>
       <c r="M923" s="1" t="n">
-        <v>46305.125</v>
+        <v>46305.5</v>
       </c>
     </row>
     <row r="924">
@@ -51143,13 +51143,13 @@
         </is>
       </c>
       <c r="K924" s="1" t="n">
-        <v>46305.29166666666</v>
+        <v>46305.66666666666</v>
       </c>
       <c r="L924" s="1" t="n">
-        <v>46305.41666666666</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="M924" s="1" t="n">
-        <v>46306.91666666666</v>
+        <v>46307.29166666666</v>
       </c>
     </row>
     <row r="925">
@@ -51198,13 +51198,13 @@
         </is>
       </c>
       <c r="K925" s="1" t="n">
-        <v>46307.08333333334</v>
+        <v>46307.45833333334</v>
       </c>
       <c r="L925" s="1" t="n">
-        <v>46307.125</v>
+        <v>46307.5</v>
       </c>
       <c r="M925" s="1" t="n">
-        <v>46307.375</v>
+        <v>46307.75</v>
       </c>
     </row>
     <row r="926">
@@ -51253,13 +51253,13 @@
         </is>
       </c>
       <c r="K926" s="1" t="n">
-        <v>46311.10416666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="L926" s="1" t="n">
-        <v>46311.16666666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="M926" s="1" t="n">
-        <v>46311.625</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="927">
@@ -51308,13 +51308,13 @@
         </is>
       </c>
       <c r="K927" s="1" t="n">
-        <v>46312.41666666666</v>
+        <v>46312.79166666666</v>
       </c>
       <c r="L927" s="1" t="n">
-        <v>46312.45833333334</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="M927" s="1" t="n">
-        <v>46313.04166666666</v>
+        <v>46313.41666666666</v>
       </c>
     </row>
     <row r="928">
@@ -51363,13 +51363,13 @@
         </is>
       </c>
       <c r="K928" s="1" t="n">
-        <v>46315.41666666666</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="L928" s="1" t="n">
-        <v>46315.45833333334</v>
+        <v>46315.83333333334</v>
       </c>
       <c r="M928" s="1" t="n">
-        <v>46316.16666666666</v>
+        <v>46316.54166666666</v>
       </c>
     </row>
     <row r="929">
@@ -51418,13 +51418,13 @@
         </is>
       </c>
       <c r="K929" s="1" t="n">
-        <v>46316.45833333334</v>
+        <v>46316.83333333334</v>
       </c>
       <c r="L929" s="1" t="n">
-        <v>46316.52083333334</v>
+        <v>46316.89583333334</v>
       </c>
       <c r="M929" s="1" t="n">
-        <v>46316.79166666666</v>
+        <v>46317.16666666666</v>
       </c>
     </row>
     <row r="930">
@@ -51473,13 +51473,13 @@
         </is>
       </c>
       <c r="K930" s="1" t="n">
-        <v>46319.70833333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="L930" s="1" t="n">
-        <v>46319.75</v>
+        <v>46320.125</v>
       </c>
       <c r="M930" s="1" t="n">
-        <v>46320.20833333334</v>
+        <v>46320.58333333334</v>
       </c>
     </row>
     <row r="931">
@@ -51528,13 +51528,13 @@
         </is>
       </c>
       <c r="K931" s="1" t="n">
-        <v>46322.41666666666</v>
+        <v>46322.79166666666</v>
       </c>
       <c r="L931" s="1" t="n">
-        <v>46322.58333333334</v>
+        <v>46322.95833333334</v>
       </c>
       <c r="M931" s="1" t="n">
-        <v>46323.04166666666</v>
+        <v>46323.41666666666</v>
       </c>
     </row>
     <row r="932">
@@ -51583,13 +51583,13 @@
         </is>
       </c>
       <c r="K932" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46325.08333333334</v>
       </c>
       <c r="L932" s="1" t="n">
-        <v>46324.75</v>
+        <v>46325.125</v>
       </c>
       <c r="M932" s="1" t="n">
-        <v>46325</v>
+        <v>46325.375</v>
       </c>
     </row>
     <row r="933">
@@ -51638,13 +51638,13 @@
         </is>
       </c>
       <c r="K933" s="1" t="n">
-        <v>46325.16666666666</v>
+        <v>46325.54166666666</v>
       </c>
       <c r="L933" s="1" t="n">
-        <v>46325.29166666666</v>
+        <v>46325.66666666666</v>
       </c>
       <c r="M933" s="1" t="n">
-        <v>46326.79166666666</v>
+        <v>46327.16666666666</v>
       </c>
     </row>
     <row r="934">
@@ -51693,13 +51693,13 @@
         </is>
       </c>
       <c r="K934" s="1" t="n">
-        <v>46327</v>
+        <v>46327.375</v>
       </c>
       <c r="L934" s="1" t="n">
-        <v>46327.04166666666</v>
+        <v>46327.41666666666</v>
       </c>
       <c r="M934" s="1" t="n">
-        <v>46327.29166666666</v>
+        <v>46327.66666666666</v>
       </c>
     </row>
     <row r="935">
@@ -51748,13 +51748,13 @@
         </is>
       </c>
       <c r="K935" s="1" t="n">
-        <v>46331.125</v>
+        <v>46331.5</v>
       </c>
       <c r="L935" s="1" t="n">
-        <v>46331.16666666666</v>
+        <v>46331.54166666666</v>
       </c>
       <c r="M935" s="1" t="n">
-        <v>46331.625</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="936">
@@ -51803,13 +51803,13 @@
         </is>
       </c>
       <c r="K936" s="1" t="n">
-        <v>46332.375</v>
+        <v>46332.75</v>
       </c>
       <c r="L936" s="1" t="n">
-        <v>46332.41666666666</v>
+        <v>46332.79166666666</v>
       </c>
       <c r="M936" s="1" t="n">
-        <v>46333</v>
+        <v>46333.375</v>
       </c>
     </row>
     <row r="937">
@@ -53397,10 +53397,10 @@
         <v>46294.97916666666</v>
       </c>
       <c r="L965" s="1" t="n">
-        <v>46295.04166666666</v>
+        <v>46295</v>
       </c>
       <c r="M965" s="1" t="n">
-        <v>46296.41666666666</v>
+        <v>46296.45833333334</v>
       </c>
     </row>
     <row r="966">
@@ -53449,13 +53449,13 @@
         </is>
       </c>
       <c r="K966" s="1" t="n">
-        <v>46297.125</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="L966" s="1" t="n">
-        <v>46297.20833333334</v>
+        <v>46297.25</v>
       </c>
       <c r="M966" s="1" t="n">
-        <v>46297.70833333334</v>
+        <v>46297.75</v>
       </c>
     </row>
     <row r="967">
@@ -53504,13 +53504,13 @@
         </is>
       </c>
       <c r="K967" s="1" t="n">
-        <v>46301.4375</v>
+        <v>46301.47916666666</v>
       </c>
       <c r="L967" s="1" t="n">
-        <v>46301.47916666666</v>
+        <v>46301.52083333334</v>
       </c>
       <c r="M967" s="1" t="n">
-        <v>46302.14583333334</v>
+        <v>46302.1875</v>
       </c>
     </row>
     <row r="968">
@@ -53559,13 +53559,13 @@
         </is>
       </c>
       <c r="K968" s="1" t="n">
-        <v>46308.20833333334</v>
+        <v>46308.25</v>
       </c>
       <c r="L968" s="1" t="n">
-        <v>46308.41666666666</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="M968" s="1" t="n">
-        <v>46309.08333333334</v>
+        <v>46309.125</v>
       </c>
     </row>
     <row r="969">
@@ -53614,13 +53614,13 @@
         </is>
       </c>
       <c r="K969" s="1" t="n">
-        <v>46310.47916666666</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="L969" s="1" t="n">
-        <v>46310.52083333334</v>
+        <v>46310.5625</v>
       </c>
       <c r="M969" s="1" t="n">
-        <v>46311.52083333334</v>
+        <v>46311.5625</v>
       </c>
     </row>
     <row r="970">
@@ -53669,13 +53669,13 @@
         </is>
       </c>
       <c r="K970" s="1" t="n">
-        <v>46311.8125</v>
+        <v>46311.85416666666</v>
       </c>
       <c r="L970" s="1" t="n">
-        <v>46311.85416666666</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="M970" s="1" t="n">
-        <v>46312.47916666666</v>
+        <v>46312.52083333334</v>
       </c>
     </row>
     <row r="971">
@@ -53724,13 +53724,13 @@
         </is>
       </c>
       <c r="K971" s="1" t="n">
-        <v>46313.9375</v>
+        <v>46313.97916666666</v>
       </c>
       <c r="L971" s="1" t="n">
-        <v>46314.14583333334</v>
+        <v>46314.1875</v>
       </c>
       <c r="M971" s="1" t="n">
-        <v>46314.8125</v>
+        <v>46314.85416666666</v>
       </c>
     </row>
     <row r="972">
@@ -53779,13 +53779,13 @@
         </is>
       </c>
       <c r="K972" s="1" t="n">
-        <v>46321.8125</v>
+        <v>46321.85416666666</v>
       </c>
       <c r="L972" s="1" t="n">
-        <v>46321.89583333334</v>
+        <v>46321.9375</v>
       </c>
       <c r="M972" s="1" t="n">
-        <v>46322.72916666666</v>
+        <v>46322.77083333334</v>
       </c>
     </row>
     <row r="973">
@@ -53834,13 +53834,13 @@
         </is>
       </c>
       <c r="K973" s="1" t="n">
-        <v>46323.8125</v>
+        <v>46323.85416666666</v>
       </c>
       <c r="L973" s="1" t="n">
-        <v>46323.89583333334</v>
+        <v>46323.9375</v>
       </c>
       <c r="M973" s="1" t="n">
-        <v>46324.39583333334</v>
+        <v>46324.4375</v>
       </c>
     </row>
     <row r="974">
@@ -53889,13 +53889,13 @@
         </is>
       </c>
       <c r="K974" s="1" t="n">
-        <v>46328.39583333334</v>
+        <v>46328.4375</v>
       </c>
       <c r="L974" s="1" t="n">
-        <v>46328.4375</v>
+        <v>46328.47916666666</v>
       </c>
       <c r="M974" s="1" t="n">
-        <v>46329.10416666666</v>
+        <v>46329.14583333334</v>
       </c>
     </row>
     <row r="975">
@@ -53944,13 +53944,13 @@
         </is>
       </c>
       <c r="K975" s="1" t="n">
-        <v>46335.52083333334</v>
+        <v>46335.5625</v>
       </c>
       <c r="L975" s="1" t="n">
-        <v>46335.72916666666</v>
+        <v>46335.77083333334</v>
       </c>
       <c r="M975" s="1" t="n">
-        <v>46336.39583333334</v>
+        <v>46336.4375</v>
       </c>
     </row>
     <row r="976">
@@ -57236,13 +57236,13 @@
         </is>
       </c>
       <c r="K1035" s="1" t="n">
-        <v>46295.5</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="L1035" s="1" t="n">
-        <v>46295.66666666666</v>
+        <v>46295.75</v>
       </c>
       <c r="M1035" s="1" t="n">
-        <v>46296.33333333334</v>
+        <v>46296.3125</v>
       </c>
     </row>
     <row r="1036">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1108"/>
+  <dimension ref="A1:M1084"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46295.5</v>
+        <v>46295.25</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46295.5625</v>
+        <v>46295.3125</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>46296.04166666666</v>
+        <v>46295.8125</v>
       </c>
     </row>
     <row r="20">
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46296.125</v>
+        <v>46295.95833333334</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46296.16666666666</v>
+        <v>46296.625</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>46296.54166666666</v>
+        <v>46297.10416666666</v>
       </c>
     </row>
     <row r="21">
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46298.08333333334</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46298.125</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>46298.625</v>
+        <v>46299.33333333334</v>
       </c>
     </row>
     <row r="22">
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46300.25</v>
+        <v>46301.70833333334</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>46300.29166666666</v>
+        <v>46301.75</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>46301.29166666666</v>
+        <v>46302.75</v>
       </c>
     </row>
     <row r="23">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46301.41666666666</v>
+        <v>46302.875</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>46301.45833333334</v>
+        <v>46302.91666666666</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>46301.83333333334</v>
+        <v>46303.29166666666</v>
       </c>
     </row>
     <row r="24">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46305.25</v>
+        <v>46306.79166666666</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>46305.3125</v>
+        <v>46306.85416666666</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>46305.72916666666</v>
+        <v>46307.27083333334</v>
       </c>
     </row>
     <row r="25">
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46308.45833333334</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>46308.625</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>46309.33333333334</v>
+        <v>46310.91666666666</v>
       </c>
     </row>
     <row r="26">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46311.125</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>46311.16666666666</v>
+        <v>46312.875</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>46311.41666666666</v>
+        <v>46313.16666666666</v>
       </c>
     </row>
     <row r="27">
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46311.58333333334</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>46311.70833333334</v>
+        <v>46313.41666666666</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46314.66666666666</v>
       </c>
     </row>
     <row r="28">
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46313.16666666666</v>
+        <v>46314.875</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>46313.20833333334</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>46313.66666666666</v>
+        <v>46315.375</v>
       </c>
     </row>
     <row r="29">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46317.95833333334</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>46318.02083333334</v>
+        <v>46319.72916666666</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>46318.5</v>
+        <v>46320.20833333334</v>
       </c>
     </row>
     <row r="30">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46318.58333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>46318.625</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>46319</v>
+        <v>46320.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -2128,13 +2128,13 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46322.75</v>
+        <v>46324.45833333334</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>46322.79166666666</v>
+        <v>46324.5</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>46323.79166666666</v>
+        <v>46325.5</v>
       </c>
     </row>
     <row r="32">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46323.91666666666</v>
+        <v>46325.625</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>46323.95833333334</v>
+        <v>46325.66666666666</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>46324.33333333334</v>
+        <v>46326.04166666666</v>
       </c>
     </row>
     <row r="33">
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46327.16666666666</v>
+        <v>46328.875</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>46327.20833333334</v>
+        <v>46328.91666666666</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>46327.58333333334</v>
+        <v>46329.29166666666</v>
       </c>
     </row>
     <row r="34">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46330.04166666666</v>
+        <v>46331.75</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>46330.20833333334</v>
+        <v>46331.91666666666</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>46330.75</v>
+        <v>46332.45833333334</v>
       </c>
     </row>
     <row r="35">
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46332.54166666666</v>
+        <v>46334.25</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>46332.58333333334</v>
+        <v>46334.29166666666</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>46332.83333333334</v>
+        <v>46334.54166666666</v>
       </c>
     </row>
     <row r="36">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46333.25</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>46333.375</v>
+        <v>46335.08333333334</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>46334.5</v>
+        <v>46336.20833333334</v>
       </c>
     </row>
     <row r="37">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46334.83333333334</v>
+        <v>46336.54166666666</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>46334.875</v>
+        <v>46336.58333333334</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>46335.20833333334</v>
+        <v>46336.91666666666</v>
       </c>
     </row>
     <row r="38">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46339.08333333334</v>
+        <v>46340.79166666666</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>46339.125</v>
+        <v>46340.83333333334</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>46339.54166666666</v>
+        <v>46341.25</v>
       </c>
     </row>
     <row r="39">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46339.79166666666</v>
+        <v>46341.5</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>46339.79166666666</v>
+        <v>46341.5</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>46340.16666666666</v>
+        <v>46341.875</v>
       </c>
     </row>
     <row r="40">
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46341.41666666666</v>
+        <v>46343.125</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>46341.41666666666</v>
+        <v>46343.125</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>46341.66666666666</v>
+        <v>46343.375</v>
       </c>
     </row>
     <row r="41">
@@ -2678,13 +2678,13 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46342.625</v>
+        <v>46344.33333333334</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>46342.66666666666</v>
+        <v>46344.375</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>46343.375</v>
+        <v>46345.08333333334</v>
       </c>
     </row>
     <row r="42">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46343.58333333334</v>
+        <v>46345.29166666666</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>46343.625</v>
+        <v>46345.33333333334</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>46343.95833333334</v>
+        <v>46345.66666666666</v>
       </c>
     </row>
     <row r="43">
@@ -2788,13 +2788,13 @@
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46346.79166666666</v>
+        <v>46348.5</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>46346.83333333334</v>
+        <v>46348.54166666666</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>46347.20833333334</v>
+        <v>46348.91666666666</v>
       </c>
     </row>
     <row r="44">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46349.66666666666</v>
+        <v>46351.375</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>46349.83333333334</v>
+        <v>46351.54166666666</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>46350.375</v>
+        <v>46352.08333333334</v>
       </c>
     </row>
     <row r="45">
@@ -2898,13 +2898,13 @@
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46352.16666666666</v>
+        <v>46353.875</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>46352.20833333334</v>
+        <v>46353.91666666666</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>46352.45833333334</v>
+        <v>46354.16666666666</v>
       </c>
     </row>
     <row r="46">
@@ -2953,13 +2953,13 @@
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46352.875</v>
+        <v>46354.58333333334</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>46353</v>
+        <v>46354.70833333334</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>46354.125</v>
+        <v>46355.83333333334</v>
       </c>
     </row>
     <row r="47">
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46354.45833333334</v>
+        <v>46356.16666666666</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>46354.5</v>
+        <v>46356.20833333334</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>46354.83333333334</v>
+        <v>46356.54166666666</v>
       </c>
     </row>
     <row r="48">
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46358.70833333334</v>
+        <v>46360.41666666666</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>46358.75</v>
+        <v>46360.45833333334</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>46359.16666666666</v>
+        <v>46360.875</v>
       </c>
     </row>
     <row r="49">
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46359.41666666666</v>
+        <v>46361.125</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>46359.41666666666</v>
+        <v>46361.125</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>46359.79166666666</v>
+        <v>46361.5</v>
       </c>
     </row>
     <row r="50">
@@ -3169,13 +3169,13 @@
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" s="1" t="n">
-        <v>46361.04166666666</v>
+        <v>46362.75</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>46361.04166666666</v>
+        <v>46362.75</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>46361.29166666666</v>
+        <v>46363</v>
       </c>
     </row>
     <row r="51">
@@ -8550,10 +8550,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>46296.41666666666</v>
+        <v>46296.5</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>46298</v>
+        <v>46298.25</v>
       </c>
     </row>
     <row r="149">
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46298.29166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>46298.35416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="M149" s="1" t="n">
-        <v>46298.97916666666</v>
+        <v>46299.22916666666</v>
       </c>
     </row>
     <row r="150">
@@ -8657,13 +8657,13 @@
         </is>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46300.47916666666</v>
+        <v>46300.72916666666</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>46300.6875</v>
+        <v>46300.9375</v>
       </c>
       <c r="M150" s="1" t="n">
-        <v>46301.35416666666</v>
+        <v>46301.60416666666</v>
       </c>
     </row>
     <row r="151">
@@ -8712,13 +8712,13 @@
         </is>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46308.35416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>46308.4375</v>
+        <v>46308.6875</v>
       </c>
       <c r="M151" s="1" t="n">
-        <v>46309.27083333334</v>
+        <v>46309.52083333334</v>
       </c>
     </row>
     <row r="152">
@@ -8767,13 +8767,13 @@
         </is>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46310.35416666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>46310.4375</v>
+        <v>46310.6875</v>
       </c>
       <c r="M152" s="1" t="n">
-        <v>46310.9375</v>
+        <v>46311.1875</v>
       </c>
     </row>
     <row r="153">
@@ -8822,13 +8822,13 @@
         </is>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46314.9375</v>
+        <v>46315.1875</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>46314.97916666666</v>
+        <v>46315.22916666666</v>
       </c>
       <c r="M153" s="1" t="n">
-        <v>46315.64583333334</v>
+        <v>46315.89583333334</v>
       </c>
     </row>
     <row r="154">
@@ -8877,13 +8877,13 @@
         </is>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46322.0625</v>
+        <v>46322.3125</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>46322.27083333334</v>
+        <v>46322.52083333334</v>
       </c>
       <c r="M154" s="1" t="n">
-        <v>46322.9375</v>
+        <v>46323.1875</v>
       </c>
     </row>
     <row r="155">
@@ -28319,7 +28319,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>SIS2</t>
+          <t>ADHS</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -28334,16 +28334,16 @@
       </c>
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="n">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -28368,13 +28368,13 @@
         <v>46304.375</v>
       </c>
       <c r="M509" s="1" t="n">
-        <v>46305.375</v>
+        <v>46306.375</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>ADHS</t>
+          <t>SIS2</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -28389,16 +28389,16 @@
       </c>
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="n">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -28417,13 +28417,13 @@
         </is>
       </c>
       <c r="K510" s="1" t="n">
-        <v>46304.33333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>46304.375</v>
+        <v>46305.375</v>
       </c>
       <c r="M510" s="1" t="n">
-        <v>46306.375</v>
+        <v>46307.375</v>
       </c>
     </row>
     <row r="511">
@@ -28472,13 +28472,13 @@
         </is>
       </c>
       <c r="K511" s="1" t="n">
-        <v>46306.75</v>
+        <v>46308.75</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>46309.95833333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="M511" s="1" t="n">
-        <v>46310.95833333334</v>
+        <v>46312.95833333334</v>
       </c>
     </row>
     <row r="512">
@@ -28527,13 +28527,13 @@
         </is>
       </c>
       <c r="K512" s="1" t="n">
-        <v>46307.91666666666</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>46308.91666666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="M512" s="1" t="n">
-        <v>46309.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
     </row>
     <row r="513">
@@ -28582,13 +28582,13 @@
         </is>
       </c>
       <c r="K513" s="1" t="n">
-        <v>46310.91666666666</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>46312.91666666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46313.5</v>
+        <v>46316.5</v>
       </c>
     </row>
     <row r="514">
@@ -28637,13 +28637,13 @@
         </is>
       </c>
       <c r="K514" s="1" t="n">
-        <v>46314.25</v>
+        <v>46317.25</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>46315.33333333334</v>
+        <v>46318.33333333334</v>
       </c>
       <c r="M514" s="1" t="n">
-        <v>46316</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="515">
@@ -28692,13 +28692,13 @@
         </is>
       </c>
       <c r="K515" s="1" t="n">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="L515" s="1" t="n">
-        <v>46319.125</v>
+        <v>46322.125</v>
       </c>
       <c r="M515" s="1" t="n">
-        <v>46319.875</v>
+        <v>46322.875</v>
       </c>
     </row>
     <row r="516">
@@ -28747,13 +28747,13 @@
         </is>
       </c>
       <c r="K516" s="1" t="n">
-        <v>46335.125</v>
+        <v>46338.125</v>
       </c>
       <c r="L516" s="1" t="n">
-        <v>46340.16666666666</v>
+        <v>46343.16666666666</v>
       </c>
       <c r="M516" s="1" t="n">
-        <v>46343.16666666666</v>
+        <v>46346.16666666666</v>
       </c>
     </row>
     <row r="517">
@@ -28798,13 +28798,13 @@
       </c>
       <c r="J517" t="inlineStr"/>
       <c r="K517" s="1" t="n">
-        <v>46361.41666666666</v>
+        <v>46364.41666666666</v>
       </c>
       <c r="L517" s="1" t="n">
-        <v>46361.45833333334</v>
+        <v>46364.45833333334</v>
       </c>
       <c r="M517" s="1" t="n">
-        <v>46362.125</v>
+        <v>46365.125</v>
       </c>
     </row>
     <row r="518">
@@ -58344,22 +58344,22 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr"/>
       <c r="E1056" t="n">
-        <v>2618</v>
+        <v>2607</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -58368,53 +58368,53 @@
       </c>
       <c r="G1056" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="H1056" t="inlineStr">
         <is>
-          <t>INC03</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I1056" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1056" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K1056" s="1" t="n">
-        <v>46308</v>
+        <v>46257.41666666666</v>
       </c>
       <c r="L1056" s="1" t="n">
-        <v>46308.08333333334</v>
+        <v>46257.45833333334</v>
       </c>
       <c r="M1056" s="1" t="n">
-        <v>46308.91666666666</v>
+        <v>46258.625</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr"/>
       <c r="E1057" t="n">
-        <v>2618</v>
+        <v>2607</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -58423,17 +58423,17 @@
       </c>
       <c r="G1057" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="H1057" t="inlineStr">
         <is>
-          <t>TAO04</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="I1057" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J1057" t="inlineStr">
@@ -58442,34 +58442,34 @@
         </is>
       </c>
       <c r="K1057" s="1" t="n">
-        <v>46309.91666666666</v>
+        <v>46258.97916666666</v>
       </c>
       <c r="L1057" s="1" t="n">
-        <v>46310</v>
+        <v>46259.04166666666</v>
       </c>
       <c r="M1057" s="1" t="n">
-        <v>46310.5</v>
+        <v>46259.6125</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr"/>
       <c r="E1058" t="n">
-        <v>2618</v>
+        <v>2607</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
       </c>
       <c r="G1058" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="H1058" t="inlineStr">
@@ -58493,93 +58493,93 @@
       </c>
       <c r="J1058" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1058" s="1" t="n">
-        <v>46311.66666666666</v>
+        <v>46260.58333333334</v>
       </c>
       <c r="L1058" s="1" t="n">
-        <v>46311.83333333334</v>
+        <v>46262.97916666666</v>
       </c>
       <c r="M1058" s="1" t="n">
-        <v>46312.58333333334</v>
+        <v>46264.00416666667</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr"/>
       <c r="E1059" t="n">
-        <v>2618</v>
+        <v>2607</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1059" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="H1059" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>JKT01</t>
         </is>
       </c>
       <c r="I1059" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1059" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="K1059" s="1" t="n">
-        <v>46318.91666666666</v>
+        <v>46272.16666666666</v>
       </c>
       <c r="L1059" s="1" t="n">
-        <v>46318.95833333334</v>
+        <v>46272.34583333333</v>
       </c>
       <c r="M1059" s="1" t="n">
-        <v>46319.25</v>
+        <v>46273.925</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr"/>
       <c r="E1060" t="n">
-        <v>2618</v>
+        <v>2607</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -58588,17 +58588,17 @@
       </c>
       <c r="G1060" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="H1060" t="inlineStr">
         <is>
-          <t>BKK04</t>
+          <t>SRG02</t>
         </is>
       </c>
       <c r="I1060" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="J1060" t="inlineStr">
@@ -58607,34 +58607,34 @@
         </is>
       </c>
       <c r="K1060" s="1" t="n">
-        <v>46319.54166666666</v>
+        <v>46274.625</v>
       </c>
       <c r="L1060" s="1" t="n">
-        <v>46319.54166666666</v>
+        <v>46274.9</v>
       </c>
       <c r="M1060" s="1" t="n">
-        <v>46320.91666666666</v>
+        <v>46275.72916666666</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr"/>
       <c r="E1061" t="n">
-        <v>2618</v>
+        <v>2607</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -58643,12 +58643,12 @@
       </c>
       <c r="G1061" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="H1061" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>LCH06</t>
         </is>
       </c>
       <c r="I1061" t="inlineStr">
@@ -58658,38 +58658,38 @@
       </c>
       <c r="J1061" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1061" s="1" t="n">
-        <v>46321.16666666666</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="L1061" s="1" t="n">
-        <v>46321.20833333334</v>
+        <v>46280.45833333334</v>
       </c>
       <c r="M1061" s="1" t="n">
-        <v>46321.66666666666</v>
+        <v>46281.54166666666</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr"/>
       <c r="E1062" t="n">
-        <v>2618</v>
+        <v>2607</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -58698,53 +58698,53 @@
       </c>
       <c r="G1062" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="H1062" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1062" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K1062" s="1" t="n">
-        <v>46325.5</v>
+        <v>46287.625</v>
       </c>
       <c r="L1062" s="1" t="n">
-        <v>46325.5</v>
+        <v>46289.95833333334</v>
       </c>
       <c r="M1062" s="1" t="n">
-        <v>46325.95833333334</v>
+        <v>46290.8375</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr"/>
       <c r="E1063" t="n">
-        <v>2618</v>
+        <v>2607</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -58753,108 +58753,108 @@
       </c>
       <c r="G1063" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="H1063" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="I1063" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J1063" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1063" s="1" t="n">
-        <v>46326.95833333334</v>
+        <v>46292</v>
       </c>
       <c r="L1063" s="1" t="n">
-        <v>46326.95833333334</v>
+        <v>46292.08333333334</v>
       </c>
       <c r="M1063" s="1" t="n">
-        <v>46327.45833333334</v>
+        <v>46292.3625</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr"/>
       <c r="E1064" t="n">
-        <v>2619</v>
+        <v>2607</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1064" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="H1064" t="inlineStr">
         <is>
-          <t>INC03</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I1064" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1064" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1064" s="1" t="n">
-        <v>46329.91666666666</v>
+        <v>46292.65416666667</v>
       </c>
       <c r="L1064" s="1" t="n">
-        <v>46329.95833333334</v>
+        <v>46292.97916666666</v>
       </c>
       <c r="M1064" s="1" t="n">
-        <v>46330.58333333334</v>
+        <v>46294.33333333334</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr"/>
       <c r="E1065" t="n">
-        <v>2619</v>
+        <v>2608</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -58863,53 +58863,53 @@
       </c>
       <c r="G1065" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1065" t="inlineStr">
         <is>
-          <t>TAO04</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1065" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1065" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1065" s="1" t="n">
-        <v>46331.58333333334</v>
+        <v>46300</v>
       </c>
       <c r="L1065" s="1" t="n">
-        <v>46331.625</v>
+        <v>46300.5</v>
       </c>
       <c r="M1065" s="1" t="n">
-        <v>46332.125</v>
+        <v>46301.08333333334</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr"/>
       <c r="E1066" t="n">
-        <v>2619</v>
+        <v>2608</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -58918,53 +58918,53 @@
       </c>
       <c r="G1066" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1066" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1066" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1066" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1066" s="1" t="n">
-        <v>46333.20833333334</v>
+        <v>46302.1875</v>
       </c>
       <c r="L1066" s="1" t="n">
-        <v>46333.375</v>
+        <v>46302.25</v>
       </c>
       <c r="M1066" s="1" t="n">
-        <v>46334.16666666666</v>
+        <v>46302.58333333334</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr"/>
       <c r="E1067" t="n">
-        <v>2619</v>
+        <v>2608</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -58973,218 +58973,218 @@
       </c>
       <c r="G1067" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1067" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1067" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1067" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1067" s="1" t="n">
-        <v>46339.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="L1067" s="1" t="n">
-        <v>46339.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="M1067" s="1" t="n">
-        <v>46340.25</v>
+        <v>46304.625</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr"/>
       <c r="E1068" t="n">
-        <v>2619</v>
+        <v>2608</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1068" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1068" t="inlineStr">
         <is>
-          <t>BKK04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1068" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1068" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1068" s="1" t="n">
-        <v>46340.54166666666</v>
+        <v>46305.91666666666</v>
       </c>
       <c r="L1068" s="1" t="n">
-        <v>46340.54166666666</v>
+        <v>46306.08333333334</v>
       </c>
       <c r="M1068" s="1" t="n">
-        <v>46341.91666666666</v>
+        <v>46306.58333333334</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr"/>
       <c r="E1069" t="n">
-        <v>2619</v>
+        <v>2608</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1069" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1069" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1069" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="J1069" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="K1069" s="1" t="n">
-        <v>46342.16666666666</v>
+        <v>46310.75</v>
       </c>
       <c r="L1069" s="1" t="n">
-        <v>46342.20833333334</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="M1069" s="1" t="n">
-        <v>46342.66666666666</v>
+        <v>46311.75</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr"/>
       <c r="E1070" t="n">
-        <v>2619</v>
+        <v>2608</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1070" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1070" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1070" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1070" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1070" s="1" t="n">
-        <v>46346.5</v>
+        <v>46313.41666666666</v>
       </c>
       <c r="L1070" s="1" t="n">
-        <v>46346.5</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="M1070" s="1" t="n">
-        <v>46346.95833333334</v>
+        <v>46314.29166666666</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr"/>
       <c r="E1071" t="n">
-        <v>2619</v>
+        <v>2608</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -59193,218 +59193,218 @@
       </c>
       <c r="G1071" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1071" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1071" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1071" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1071" s="1" t="n">
-        <v>46347.95833333334</v>
+        <v>46317.45833333334</v>
       </c>
       <c r="L1071" s="1" t="n">
-        <v>46347.95833333334</v>
+        <v>46317.54166666666</v>
       </c>
       <c r="M1071" s="1" t="n">
-        <v>46348.45833333334</v>
+        <v>46319.20833333334</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr"/>
       <c r="E1072" t="n">
-        <v>2620</v>
+        <v>2608</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1072" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1072" t="inlineStr">
         <is>
-          <t>INC03</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1072" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1072" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1072" s="1" t="n">
-        <v>46350.91666666666</v>
+        <v>46321.66666666666</v>
       </c>
       <c r="L1072" s="1" t="n">
-        <v>46350.95833333334</v>
+        <v>46321.83333333334</v>
       </c>
       <c r="M1072" s="1" t="n">
-        <v>46351.58333333334</v>
+        <v>46322.66666666666</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr"/>
       <c r="E1073" t="n">
-        <v>2620</v>
+        <v>2608</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1073" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1073" t="inlineStr">
         <is>
-          <t>TAO04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1073" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1073" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1073" s="1" t="n">
-        <v>46352.58333333334</v>
+        <v>46325.20833333334</v>
       </c>
       <c r="L1073" s="1" t="n">
-        <v>46352.625</v>
+        <v>46325.27083333334</v>
       </c>
       <c r="M1073" s="1" t="n">
-        <v>46353.125</v>
+        <v>46325.77083333334</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr"/>
       <c r="E1074" t="n">
-        <v>2620</v>
+        <v>2608</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1074" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1074" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1074" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1074" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1074" s="1" t="n">
-        <v>46354.20833333334</v>
+        <v>46326</v>
       </c>
       <c r="L1074" s="1" t="n">
-        <v>46354.375</v>
+        <v>46326.04166666666</v>
       </c>
       <c r="M1074" s="1" t="n">
-        <v>46355.16666666666</v>
+        <v>46326.54166666666</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr"/>
       <c r="E1075" t="n">
-        <v>2620</v>
+        <v>2609</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -59413,254 +59413,258 @@
       </c>
       <c r="G1075" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1075" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1075" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1075" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1075" s="1" t="n">
-        <v>46360.91666666666</v>
+        <v>46329.625</v>
       </c>
       <c r="L1075" s="1" t="n">
-        <v>46360.95833333334</v>
+        <v>46329.66666666666</v>
       </c>
       <c r="M1075" s="1" t="n">
-        <v>46361.25</v>
+        <v>46330.33333333334</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr"/>
       <c r="E1076" t="n">
-        <v>2620</v>
+        <v>2609</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1076" t="inlineStr">
         <is>
-          <t>2620N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1076" t="inlineStr">
         <is>
-          <t>BKK04</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1076" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1076" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1076" s="1" t="n">
-        <v>46361.54166666666</v>
+        <v>46331.41666666666</v>
       </c>
       <c r="L1076" s="1" t="n">
-        <v>46361.54166666666</v>
+        <v>46331.45833333334</v>
       </c>
       <c r="M1076" s="1" t="n">
-        <v>46362.91666666666</v>
+        <v>46332.04166666666</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr"/>
       <c r="E1077" t="n">
-        <v>2620</v>
+        <v>2609</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1077" t="inlineStr">
         <is>
-          <t>2620N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1077" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1077" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1077" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1077" s="1" t="n">
-        <v>46363.16666666666</v>
+        <v>46332.22916666666</v>
       </c>
       <c r="L1077" s="1" t="n">
-        <v>46363.20833333334</v>
+        <v>46332.29166666666</v>
       </c>
       <c r="M1077" s="1" t="n">
-        <v>46363.66666666666</v>
+        <v>46332.625</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr"/>
       <c r="E1078" t="n">
-        <v>2620</v>
+        <v>2609</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1078" t="inlineStr">
         <is>
-          <t>2620N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1078" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1078" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1078" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1078" s="1" t="n">
-        <v>46367.5</v>
+        <v>46333.91666666666</v>
       </c>
       <c r="L1078" s="1" t="n">
-        <v>46367.5</v>
+        <v>46334.08333333334</v>
       </c>
       <c r="M1078" s="1" t="n">
-        <v>46367.95833333334</v>
+        <v>46334.58333333334</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr"/>
       <c r="E1079" t="n">
-        <v>2620</v>
+        <v>2609</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1079" t="inlineStr">
         <is>
-          <t>2620N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1079" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1079" t="inlineStr">
         <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="J1079" t="inlineStr"/>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
       <c r="K1079" s="1" t="n">
-        <v>46368.95833333334</v>
+        <v>46338.75</v>
       </c>
       <c r="L1079" s="1" t="n">
-        <v>46368.95833333334</v>
+        <v>46338.91666666666</v>
       </c>
       <c r="M1079" s="1" t="n">
-        <v>46369.45833333334</v>
+        <v>46339.75</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
@@ -59675,7 +59679,7 @@
       </c>
       <c r="D1080" t="inlineStr"/>
       <c r="E1080" t="n">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -59684,38 +59688,38 @@
       </c>
       <c r="G1080" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1080" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1080" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1080" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1080" s="1" t="n">
-        <v>46257.41666666666</v>
+        <v>46341.41666666666</v>
       </c>
       <c r="L1080" s="1" t="n">
-        <v>46257.45833333334</v>
+        <v>46341.45833333334</v>
       </c>
       <c r="M1080" s="1" t="n">
-        <v>46258.625</v>
+        <v>46342.29166666666</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
@@ -59730,47 +59734,47 @@
       </c>
       <c r="D1081" t="inlineStr"/>
       <c r="E1081" t="n">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1081" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1081" t="inlineStr">
         <is>
-          <t>KAN04</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1081" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1081" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1081" s="1" t="n">
-        <v>46258.97916666666</v>
+        <v>46345.45833333334</v>
       </c>
       <c r="L1081" s="1" t="n">
-        <v>46259.04166666666</v>
+        <v>46345.54166666666</v>
       </c>
       <c r="M1081" s="1" t="n">
-        <v>46259.6125</v>
+        <v>46347.20833333334</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
@@ -59785,47 +59789,47 @@
       </c>
       <c r="D1082" t="inlineStr"/>
       <c r="E1082" t="n">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1082" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1082" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1082" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1082" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1082" s="1" t="n">
-        <v>46260.58333333334</v>
+        <v>46349.66666666666</v>
       </c>
       <c r="L1082" s="1" t="n">
-        <v>46262.97916666666</v>
+        <v>46349.83333333334</v>
       </c>
       <c r="M1082" s="1" t="n">
-        <v>46264.00416666667</v>
+        <v>46350.66666666666</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -59840,7 +59844,7 @@
       </c>
       <c r="D1083" t="inlineStr"/>
       <c r="E1083" t="n">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -59849,38 +59853,38 @@
       </c>
       <c r="G1083" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1083" t="inlineStr">
         <is>
-          <t>JKT01</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1083" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1083" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1083" s="1" t="n">
-        <v>46272.16666666666</v>
+        <v>46353.20833333334</v>
       </c>
       <c r="L1083" s="1" t="n">
-        <v>46272.34583333333</v>
+        <v>46353.27083333334</v>
       </c>
       <c r="M1083" s="1" t="n">
-        <v>46273.925</v>
+        <v>46353.77083333334</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
@@ -59895,7 +59899,7 @@
       </c>
       <c r="D1084" t="inlineStr"/>
       <c r="E1084" t="n">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -59904,1347 +59908,27 @@
       </c>
       <c r="G1084" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1084" t="inlineStr">
         <is>
-          <t>SRG02</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1084" t="inlineStr">
         <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="J1084" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="J1084" t="inlineStr"/>
       <c r="K1084" s="1" t="n">
-        <v>46274.625</v>
+        <v>46354</v>
       </c>
       <c r="L1084" s="1" t="n">
-        <v>46274.9</v>
+        <v>46354.04166666666</v>
       </c>
       <c r="M1084" s="1" t="n">
-        <v>46275.72916666666</v>
-      </c>
-    </row>
-    <row r="1085">
-      <c r="A1085" t="inlineStr">
-        <is>
-          <t>PCI2</t>
-        </is>
-      </c>
-      <c r="B1085" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1085" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1085" t="inlineStr"/>
-      <c r="E1085" t="n">
-        <v>2607</v>
-      </c>
-      <c r="F1085" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1085" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="H1085" t="inlineStr">
-        <is>
-          <t>LCH06</t>
-        </is>
-      </c>
-      <c r="I1085" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="J1085" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="K1085" s="1" t="n">
-        <v>46280.41666666666</v>
-      </c>
-      <c r="L1085" s="1" t="n">
-        <v>46280.45833333334</v>
-      </c>
-      <c r="M1085" s="1" t="n">
-        <v>46281.54166666666</v>
-      </c>
-    </row>
-    <row r="1086">
-      <c r="A1086" t="inlineStr">
-        <is>
-          <t>PCI2</t>
-        </is>
-      </c>
-      <c r="B1086" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1086" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1086" t="inlineStr"/>
-      <c r="E1086" t="n">
-        <v>2607</v>
-      </c>
-      <c r="F1086" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1086" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="H1086" t="inlineStr">
-        <is>
-          <t>SHAW5</t>
-        </is>
-      </c>
-      <c r="I1086" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="J1086" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="K1086" s="1" t="n">
-        <v>46287.625</v>
-      </c>
-      <c r="L1086" s="1" t="n">
-        <v>46289.95833333334</v>
-      </c>
-      <c r="M1086" s="1" t="n">
-        <v>46290.8375</v>
-      </c>
-    </row>
-    <row r="1087">
-      <c r="A1087" t="inlineStr">
-        <is>
-          <t>PCI2</t>
-        </is>
-      </c>
-      <c r="B1087" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1087" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1087" t="inlineStr"/>
-      <c r="E1087" t="n">
-        <v>2607</v>
-      </c>
-      <c r="F1087" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1087" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="H1087" t="inlineStr">
-        <is>
-          <t>KAN04</t>
-        </is>
-      </c>
-      <c r="I1087" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="J1087" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="K1087" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="L1087" s="1" t="n">
-        <v>46292.08333333334</v>
-      </c>
-      <c r="M1087" s="1" t="n">
-        <v>46292.3625</v>
-      </c>
-    </row>
-    <row r="1088">
-      <c r="A1088" t="inlineStr">
-        <is>
-          <t>PCI2</t>
-        </is>
-      </c>
-      <c r="B1088" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1088" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1088" t="inlineStr"/>
-      <c r="E1088" t="n">
-        <v>2607</v>
-      </c>
-      <c r="F1088" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1088" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="H1088" t="inlineStr">
-        <is>
-          <t>PUS05</t>
-        </is>
-      </c>
-      <c r="I1088" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="J1088" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="K1088" s="1" t="n">
-        <v>46292.65416666667</v>
-      </c>
-      <c r="L1088" s="1" t="n">
-        <v>46292.97916666666</v>
-      </c>
-      <c r="M1088" s="1" t="n">
-        <v>46294.33333333334</v>
-      </c>
-    </row>
-    <row r="1089">
-      <c r="A1089" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1089" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1089" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1089" t="inlineStr"/>
-      <c r="E1089" t="n">
-        <v>2608</v>
-      </c>
-      <c r="F1089" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1089" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="H1089" t="inlineStr">
-        <is>
-          <t>PUSH4</t>
-        </is>
-      </c>
-      <c r="I1089" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="J1089" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="K1089" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="L1089" s="1" t="n">
-        <v>46300.5</v>
-      </c>
-      <c r="M1089" s="1" t="n">
-        <v>46301.08333333334</v>
-      </c>
-    </row>
-    <row r="1090">
-      <c r="A1090" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1090" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1090" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1090" t="inlineStr"/>
-      <c r="E1090" t="n">
-        <v>2608</v>
-      </c>
-      <c r="F1090" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1090" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="H1090" t="inlineStr">
-        <is>
-          <t>USN03</t>
-        </is>
-      </c>
-      <c r="I1090" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="J1090" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="K1090" s="1" t="n">
-        <v>46302.1875</v>
-      </c>
-      <c r="L1090" s="1" t="n">
-        <v>46302.25</v>
-      </c>
-      <c r="M1090" s="1" t="n">
-        <v>46302.58333333334</v>
-      </c>
-    </row>
-    <row r="1091">
-      <c r="A1091" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1091" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1091" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1091" t="inlineStr"/>
-      <c r="E1091" t="n">
-        <v>2608</v>
-      </c>
-      <c r="F1091" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1091" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="H1091" t="inlineStr">
-        <is>
-          <t>INC08</t>
-        </is>
-      </c>
-      <c r="I1091" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="J1091" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="K1091" s="1" t="n">
-        <v>46303.91666666666</v>
-      </c>
-      <c r="L1091" s="1" t="n">
-        <v>46303.95833333334</v>
-      </c>
-      <c r="M1091" s="1" t="n">
-        <v>46304.625</v>
-      </c>
-    </row>
-    <row r="1092">
-      <c r="A1092" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1092" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1092" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1092" t="inlineStr"/>
-      <c r="E1092" t="n">
-        <v>2608</v>
-      </c>
-      <c r="F1092" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1092" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="H1092" t="inlineStr">
-        <is>
-          <t>SHAW2</t>
-        </is>
-      </c>
-      <c r="I1092" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="J1092" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="K1092" s="1" t="n">
-        <v>46305.91666666666</v>
-      </c>
-      <c r="L1092" s="1" t="n">
-        <v>46306.08333333334</v>
-      </c>
-      <c r="M1092" s="1" t="n">
-        <v>46306.58333333334</v>
-      </c>
-    </row>
-    <row r="1093">
-      <c r="A1093" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1093" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1093" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1093" t="inlineStr"/>
-      <c r="E1093" t="n">
-        <v>2608</v>
-      </c>
-      <c r="F1093" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1093" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="H1093" t="inlineStr">
-        <is>
-          <t>SGN03</t>
-        </is>
-      </c>
-      <c r="I1093" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="J1093" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="K1093" s="1" t="n">
-        <v>46310.75</v>
-      </c>
-      <c r="L1093" s="1" t="n">
-        <v>46310.91666666666</v>
-      </c>
-      <c r="M1093" s="1" t="n">
-        <v>46311.75</v>
-      </c>
-    </row>
-    <row r="1094">
-      <c r="A1094" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1094" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1094" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1094" t="inlineStr"/>
-      <c r="E1094" t="n">
-        <v>2608</v>
-      </c>
-      <c r="F1094" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1094" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="H1094" t="inlineStr">
-        <is>
-          <t>LCH04</t>
-        </is>
-      </c>
-      <c r="I1094" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="J1094" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="K1094" s="1" t="n">
-        <v>46313.41666666666</v>
-      </c>
-      <c r="L1094" s="1" t="n">
-        <v>46313.45833333334</v>
-      </c>
-      <c r="M1094" s="1" t="n">
-        <v>46314.29166666666</v>
-      </c>
-    </row>
-    <row r="1095">
-      <c r="A1095" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1095" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1095" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1095" t="inlineStr"/>
-      <c r="E1095" t="n">
-        <v>2608</v>
-      </c>
-      <c r="F1095" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1095" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="H1095" t="inlineStr">
-        <is>
-          <t>JKT02</t>
-        </is>
-      </c>
-      <c r="I1095" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="J1095" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="K1095" s="1" t="n">
-        <v>46317.45833333334</v>
-      </c>
-      <c r="L1095" s="1" t="n">
-        <v>46317.54166666666</v>
-      </c>
-      <c r="M1095" s="1" t="n">
-        <v>46319.20833333334</v>
-      </c>
-    </row>
-    <row r="1096">
-      <c r="A1096" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1096" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1096" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1096" t="inlineStr"/>
-      <c r="E1096" t="n">
-        <v>2608</v>
-      </c>
-      <c r="F1096" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1096" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="H1096" t="inlineStr">
-        <is>
-          <t>SGN03</t>
-        </is>
-      </c>
-      <c r="I1096" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="J1096" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="K1096" s="1" t="n">
-        <v>46321.66666666666</v>
-      </c>
-      <c r="L1096" s="1" t="n">
-        <v>46321.83333333334</v>
-      </c>
-      <c r="M1096" s="1" t="n">
-        <v>46322.66666666666</v>
-      </c>
-    </row>
-    <row r="1097">
-      <c r="A1097" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1097" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1097" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1097" t="inlineStr"/>
-      <c r="E1097" t="n">
-        <v>2608</v>
-      </c>
-      <c r="F1097" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1097" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="H1097" t="inlineStr">
-        <is>
-          <t>HKG03</t>
-        </is>
-      </c>
-      <c r="I1097" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="J1097" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="K1097" s="1" t="n">
-        <v>46325.20833333334</v>
-      </c>
-      <c r="L1097" s="1" t="n">
-        <v>46325.27083333334</v>
-      </c>
-      <c r="M1097" s="1" t="n">
-        <v>46325.77083333334</v>
-      </c>
-    </row>
-    <row r="1098">
-      <c r="A1098" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1098" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1098" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1098" t="inlineStr"/>
-      <c r="E1098" t="n">
-        <v>2608</v>
-      </c>
-      <c r="F1098" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1098" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="H1098" t="inlineStr">
-        <is>
-          <t>SHE04</t>
-        </is>
-      </c>
-      <c r="I1098" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="J1098" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="K1098" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="L1098" s="1" t="n">
-        <v>46326.04166666666</v>
-      </c>
-      <c r="M1098" s="1" t="n">
-        <v>46326.54166666666</v>
-      </c>
-    </row>
-    <row r="1099">
-      <c r="A1099" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1099" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1099" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1099" t="inlineStr"/>
-      <c r="E1099" t="n">
-        <v>2609</v>
-      </c>
-      <c r="F1099" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1099" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="H1099" t="inlineStr">
-        <is>
-          <t>INC08</t>
-        </is>
-      </c>
-      <c r="I1099" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="J1099" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="K1099" s="1" t="n">
-        <v>46329.625</v>
-      </c>
-      <c r="L1099" s="1" t="n">
-        <v>46329.66666666666</v>
-      </c>
-      <c r="M1099" s="1" t="n">
-        <v>46330.33333333334</v>
-      </c>
-    </row>
-    <row r="1100">
-      <c r="A1100" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1100" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1100" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1100" t="inlineStr"/>
-      <c r="E1100" t="n">
-        <v>2609</v>
-      </c>
-      <c r="F1100" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1100" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="H1100" t="inlineStr">
-        <is>
-          <t>PUSH4</t>
-        </is>
-      </c>
-      <c r="I1100" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="J1100" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="K1100" s="1" t="n">
-        <v>46331.41666666666</v>
-      </c>
-      <c r="L1100" s="1" t="n">
-        <v>46331.45833333334</v>
-      </c>
-      <c r="M1100" s="1" t="n">
-        <v>46332.04166666666</v>
-      </c>
-    </row>
-    <row r="1101">
-      <c r="A1101" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1101" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1101" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1101" t="inlineStr"/>
-      <c r="E1101" t="n">
-        <v>2609</v>
-      </c>
-      <c r="F1101" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1101" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="H1101" t="inlineStr">
-        <is>
-          <t>USN03</t>
-        </is>
-      </c>
-      <c r="I1101" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="J1101" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="K1101" s="1" t="n">
-        <v>46332.22916666666</v>
-      </c>
-      <c r="L1101" s="1" t="n">
-        <v>46332.29166666666</v>
-      </c>
-      <c r="M1101" s="1" t="n">
-        <v>46332.625</v>
-      </c>
-    </row>
-    <row r="1102">
-      <c r="A1102" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1102" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1102" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1102" t="inlineStr"/>
-      <c r="E1102" t="n">
-        <v>2609</v>
-      </c>
-      <c r="F1102" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1102" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="H1102" t="inlineStr">
-        <is>
-          <t>SHAW2</t>
-        </is>
-      </c>
-      <c r="I1102" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="J1102" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="K1102" s="1" t="n">
-        <v>46333.91666666666</v>
-      </c>
-      <c r="L1102" s="1" t="n">
-        <v>46334.08333333334</v>
-      </c>
-      <c r="M1102" s="1" t="n">
-        <v>46334.58333333334</v>
-      </c>
-    </row>
-    <row r="1103">
-      <c r="A1103" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1103" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1103" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1103" t="inlineStr"/>
-      <c r="E1103" t="n">
-        <v>2609</v>
-      </c>
-      <c r="F1103" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1103" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="H1103" t="inlineStr">
-        <is>
-          <t>SGN03</t>
-        </is>
-      </c>
-      <c r="I1103" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="J1103" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="K1103" s="1" t="n">
-        <v>46338.75</v>
-      </c>
-      <c r="L1103" s="1" t="n">
-        <v>46338.91666666666</v>
-      </c>
-      <c r="M1103" s="1" t="n">
-        <v>46339.75</v>
-      </c>
-    </row>
-    <row r="1104">
-      <c r="A1104" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1104" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1104" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1104" t="inlineStr"/>
-      <c r="E1104" t="n">
-        <v>2609</v>
-      </c>
-      <c r="F1104" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G1104" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="H1104" t="inlineStr">
-        <is>
-          <t>LCH04</t>
-        </is>
-      </c>
-      <c r="I1104" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="J1104" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="K1104" s="1" t="n">
-        <v>46341.41666666666</v>
-      </c>
-      <c r="L1104" s="1" t="n">
-        <v>46341.45833333334</v>
-      </c>
-      <c r="M1104" s="1" t="n">
-        <v>46342.29166666666</v>
-      </c>
-    </row>
-    <row r="1105">
-      <c r="A1105" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1105" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1105" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1105" t="inlineStr"/>
-      <c r="E1105" t="n">
-        <v>2609</v>
-      </c>
-      <c r="F1105" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1105" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="H1105" t="inlineStr">
-        <is>
-          <t>JKT02</t>
-        </is>
-      </c>
-      <c r="I1105" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="J1105" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="K1105" s="1" t="n">
-        <v>46345.45833333334</v>
-      </c>
-      <c r="L1105" s="1" t="n">
-        <v>46345.54166666666</v>
-      </c>
-      <c r="M1105" s="1" t="n">
-        <v>46347.20833333334</v>
-      </c>
-    </row>
-    <row r="1106">
-      <c r="A1106" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1106" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1106" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1106" t="inlineStr"/>
-      <c r="E1106" t="n">
-        <v>2609</v>
-      </c>
-      <c r="F1106" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1106" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="H1106" t="inlineStr">
-        <is>
-          <t>SGN03</t>
-        </is>
-      </c>
-      <c r="I1106" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="J1106" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="K1106" s="1" t="n">
-        <v>46349.66666666666</v>
-      </c>
-      <c r="L1106" s="1" t="n">
-        <v>46349.83333333334</v>
-      </c>
-      <c r="M1106" s="1" t="n">
-        <v>46350.66666666666</v>
-      </c>
-    </row>
-    <row r="1107">
-      <c r="A1107" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1107" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1107" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1107" t="inlineStr"/>
-      <c r="E1107" t="n">
-        <v>2609</v>
-      </c>
-      <c r="F1107" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1107" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="H1107" t="inlineStr">
-        <is>
-          <t>HKG03</t>
-        </is>
-      </c>
-      <c r="I1107" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="J1107" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="K1107" s="1" t="n">
-        <v>46353.20833333334</v>
-      </c>
-      <c r="L1107" s="1" t="n">
-        <v>46353.27083333334</v>
-      </c>
-      <c r="M1107" s="1" t="n">
-        <v>46353.77083333334</v>
-      </c>
-    </row>
-    <row r="1108">
-      <c r="A1108" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="B1108" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C1108" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="D1108" t="inlineStr"/>
-      <c r="E1108" t="n">
-        <v>2609</v>
-      </c>
-      <c r="F1108" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G1108" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="H1108" t="inlineStr">
-        <is>
-          <t>SHE04</t>
-        </is>
-      </c>
-      <c r="I1108" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="J1108" t="inlineStr"/>
-      <c r="K1108" s="1" t="n">
-        <v>46354</v>
-      </c>
-      <c r="L1108" s="1" t="n">
-        <v>46354.04166666666</v>
-      </c>
-      <c r="M1108" s="1" t="n">
         <v>46354.54166666666</v>
       </c>
     </row>

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -8550,10 +8550,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>46296.5</v>
+        <v>46296.58333333334</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>46298.25</v>
+        <v>46298.33333333334</v>
       </c>
     </row>
     <row r="149">
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46298.54166666666</v>
+        <v>46298.625</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>46298.60416666666</v>
+        <v>46298.6875</v>
       </c>
       <c r="M149" s="1" t="n">
-        <v>46299.22916666666</v>
+        <v>46299.3125</v>
       </c>
     </row>
     <row r="150">
@@ -8657,13 +8657,13 @@
         </is>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46300.72916666666</v>
+        <v>46300.8125</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>46300.9375</v>
+        <v>46301.02083333334</v>
       </c>
       <c r="M150" s="1" t="n">
-        <v>46301.60416666666</v>
+        <v>46301.6875</v>
       </c>
     </row>
     <row r="151">
@@ -8712,13 +8712,13 @@
         </is>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46308.60416666666</v>
+        <v>46308.6875</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>46308.6875</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="M151" s="1" t="n">
-        <v>46309.52083333334</v>
+        <v>46309.60416666666</v>
       </c>
     </row>
     <row r="152">
@@ -8767,13 +8767,13 @@
         </is>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46310.60416666666</v>
+        <v>46310.6875</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>46310.6875</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="M152" s="1" t="n">
-        <v>46311.1875</v>
+        <v>46311.27083333334</v>
       </c>
     </row>
     <row r="153">
@@ -8822,13 +8822,13 @@
         </is>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46315.1875</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>46315.22916666666</v>
+        <v>46315.3125</v>
       </c>
       <c r="M153" s="1" t="n">
-        <v>46315.89583333334</v>
+        <v>46315.97916666666</v>
       </c>
     </row>
     <row r="154">
@@ -8877,13 +8877,13 @@
         </is>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46322.3125</v>
+        <v>46322.39583333334</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>46322.52083333334</v>
+        <v>46322.60416666666</v>
       </c>
       <c r="M154" s="1" t="n">
-        <v>46323.1875</v>
+        <v>46323.27083333334</v>
       </c>
     </row>
     <row r="155">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -979,7 +979,7 @@
         <v>46296.625</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>46297.10416666666</v>
+        <v>46297.27083333334</v>
       </c>
     </row>
     <row r="11">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46298.79166666666</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46298.83333333334</v>
+        <v>46299</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.5</v>
       </c>
     </row>
     <row r="12">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46301.70833333334</v>
+        <v>46301.875</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46301.75</v>
+        <v>46301.91666666666</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>46302.75</v>
+        <v>46302.91666666666</v>
       </c>
     </row>
     <row r="13">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46302.875</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46302.91666666666</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>46303.29166666666</v>
+        <v>46303.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46306.79166666666</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46306.85416666666</v>
+        <v>46307.02083333334</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>46307.27083333334</v>
+        <v>46307.4375</v>
       </c>
     </row>
     <row r="15">
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46310.04166666666</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46310.20833333334</v>
+        <v>46310.375</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>46310.91666666666</v>
+        <v>46311.08333333334</v>
       </c>
     </row>
     <row r="16">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46312.83333333334</v>
+        <v>46313</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46312.875</v>
+        <v>46313.04166666666</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>46313.16666666666</v>
+        <v>46313.33333333334</v>
       </c>
     </row>
     <row r="17">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46313.29166666666</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46313.41666666666</v>
+        <v>46313.58333333334</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>46314.66666666666</v>
+        <v>46314.83333333334</v>
       </c>
     </row>
     <row r="18">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46314.875</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46314.91666666666</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>46315.375</v>
+        <v>46315.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46319.66666666666</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46319.72916666666</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>46320.20833333334</v>
+        <v>46320.375</v>
       </c>
     </row>
     <row r="20">
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46320.29166666666</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46320.33333333334</v>
+        <v>46320.5</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>46320.70833333334</v>
+        <v>46320.875</v>
       </c>
     </row>
     <row r="21">
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46324.45833333334</v>
+        <v>46324.625</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46324.5</v>
+        <v>46324.66666666666</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>46325.5</v>
+        <v>46325.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46325.625</v>
+        <v>46325.79166666666</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>46325.66666666666</v>
+        <v>46325.83333333334</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>46326.04166666666</v>
+        <v>46326.20833333334</v>
       </c>
     </row>
     <row r="23">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46328.875</v>
+        <v>46329.04166666666</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>46328.91666666666</v>
+        <v>46329.08333333334</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>46329.29166666666</v>
+        <v>46329.45833333334</v>
       </c>
     </row>
     <row r="24">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46331.75</v>
+        <v>46331.91666666666</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>46331.91666666666</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>46332.45833333334</v>
+        <v>46332.625</v>
       </c>
     </row>
     <row r="25">
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46334.25</v>
+        <v>46334.41666666666</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>46334.29166666666</v>
+        <v>46334.45833333334</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>46334.54166666666</v>
+        <v>46334.70833333334</v>
       </c>
     </row>
     <row r="26">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46334.95833333334</v>
+        <v>46335.125</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>46335.08333333334</v>
+        <v>46335.25</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>46336.20833333334</v>
+        <v>46336.375</v>
       </c>
     </row>
     <row r="27">
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46336.70833333334</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>46336.58333333334</v>
+        <v>46336.75</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>46336.91666666666</v>
+        <v>46337.08333333334</v>
       </c>
     </row>
     <row r="28">
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46340.79166666666</v>
+        <v>46340.95833333334</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>46340.83333333334</v>
+        <v>46341</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>46341.25</v>
+        <v>46341.41666666666</v>
       </c>
     </row>
     <row r="29">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46341.5</v>
+        <v>46341.66666666666</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>46341.5</v>
+        <v>46341.66666666666</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>46341.875</v>
+        <v>46342.04166666666</v>
       </c>
     </row>
     <row r="30">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46343.125</v>
+        <v>46343.29166666666</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>46343.125</v>
+        <v>46343.29166666666</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>46343.375</v>
+        <v>46343.54166666666</v>
       </c>
     </row>
     <row r="31">
@@ -2128,13 +2128,13 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46344.33333333334</v>
+        <v>46344.5</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>46344.375</v>
+        <v>46344.54166666666</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>46345.08333333334</v>
+        <v>46345.25</v>
       </c>
     </row>
     <row r="32">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46345.29166666666</v>
+        <v>46345.45833333334</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>46345.33333333334</v>
+        <v>46345.5</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>46345.66666666666</v>
+        <v>46345.83333333334</v>
       </c>
     </row>
     <row r="33">
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46348.5</v>
+        <v>46348.66666666666</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>46348.54166666666</v>
+        <v>46348.70833333334</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>46348.91666666666</v>
+        <v>46349.08333333334</v>
       </c>
     </row>
     <row r="34">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46351.375</v>
+        <v>46351.54166666666</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>46351.54166666666</v>
+        <v>46351.70833333334</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>46352.08333333334</v>
+        <v>46352.25</v>
       </c>
     </row>
     <row r="35">
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46353.875</v>
+        <v>46354.04166666666</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>46353.91666666666</v>
+        <v>46354.08333333334</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>46354.16666666666</v>
+        <v>46354.33333333334</v>
       </c>
     </row>
     <row r="36">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46354.58333333334</v>
+        <v>46354.75</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>46354.70833333334</v>
+        <v>46354.875</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>46355.83333333334</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="37">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46356.16666666666</v>
+        <v>46356.33333333334</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>46356.20833333334</v>
+        <v>46356.375</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>46356.54166666666</v>
+        <v>46356.70833333334</v>
       </c>
     </row>
     <row r="38">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46360.41666666666</v>
+        <v>46360.58333333334</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>46360.45833333334</v>
+        <v>46360.625</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>46360.875</v>
+        <v>46361.04166666666</v>
       </c>
     </row>
     <row r="39">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46361.125</v>
+        <v>46361.29166666666</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>46361.125</v>
+        <v>46361.29166666666</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>46361.5</v>
+        <v>46361.66666666666</v>
       </c>
     </row>
     <row r="40">
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46362.75</v>
+        <v>46362.91666666666</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>46362.75</v>
+        <v>46362.91666666666</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>46363</v>
+        <v>46363.16666666666</v>
       </c>
     </row>
     <row r="41">
@@ -2678,13 +2678,13 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46365.33333333334</v>
+        <v>46365.5</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>46365.375</v>
+        <v>46365.54166666666</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>46366.08333333334</v>
+        <v>46366.25</v>
       </c>
     </row>
     <row r="42">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46366.29166666666</v>
+        <v>46366.45833333334</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>46366.33333333334</v>
+        <v>46366.5</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>46366.66666666666</v>
+        <v>46366.83333333334</v>
       </c>
     </row>
     <row r="43">
@@ -2788,13 +2788,13 @@
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46369.5</v>
+        <v>46369.66666666666</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>46369.54166666666</v>
+        <v>46369.70833333334</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>46369.91666666666</v>
+        <v>46370.08333333334</v>
       </c>
     </row>
     <row r="44">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46372.375</v>
+        <v>46372.54166666666</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>46372.54166666666</v>
+        <v>46372.70833333334</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>46373.08333333334</v>
+        <v>46373.25</v>
       </c>
     </row>
     <row r="45">
@@ -2898,13 +2898,13 @@
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46374.875</v>
+        <v>46375.04166666666</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>46374.91666666666</v>
+        <v>46375.08333333334</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>46375.16666666666</v>
+        <v>46375.33333333334</v>
       </c>
     </row>
     <row r="46">
@@ -2953,13 +2953,13 @@
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46375.58333333334</v>
+        <v>46375.75</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>46375.70833333334</v>
+        <v>46375.875</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>46376.83333333334</v>
+        <v>46377</v>
       </c>
     </row>
     <row r="47">
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46377.16666666666</v>
+        <v>46377.33333333334</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>46377.20833333334</v>
+        <v>46377.375</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>46377.54166666666</v>
+        <v>46377.70833333334</v>
       </c>
     </row>
     <row r="48">
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46381.41666666666</v>
+        <v>46381.58333333334</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>46381.45833333334</v>
+        <v>46381.625</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>46381.875</v>
+        <v>46382.04166666666</v>
       </c>
     </row>
     <row r="49">
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46382.125</v>
+        <v>46382.29166666666</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>46382.125</v>
+        <v>46382.29166666666</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>46382.5</v>
+        <v>46382.66666666666</v>
       </c>
     </row>
     <row r="50">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46383.75</v>
+        <v>46383.91666666666</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>46383.75</v>
+        <v>46383.91666666666</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>46384</v>
+        <v>46384.16666666666</v>
       </c>
     </row>
     <row r="51">
@@ -3228,13 +3228,13 @@
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46386.33333333334</v>
+        <v>46386.5</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>46386.375</v>
+        <v>46386.54166666666</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>46387.08333333334</v>
+        <v>46387.25</v>
       </c>
     </row>
     <row r="52">
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46387.29166666666</v>
+        <v>46387.45833333334</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>46387.33333333334</v>
+        <v>46387.5</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>46387.66666666666</v>
+        <v>46387.83333333334</v>
       </c>
     </row>
     <row r="53">
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46390.5</v>
+        <v>46390.66666666666</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>46390.54166666666</v>
+        <v>46390.70833333334</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>46390.91666666666</v>
+        <v>46391.08333333334</v>
       </c>
     </row>
     <row r="54">
@@ -3393,13 +3393,13 @@
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46393.375</v>
+        <v>46393.54166666666</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>46393.54166666666</v>
+        <v>46393.70833333334</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>46394.08333333334</v>
+        <v>46394.25</v>
       </c>
     </row>
     <row r="55">
@@ -3448,13 +3448,13 @@
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46395.875</v>
+        <v>46396.04166666666</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>46395.91666666666</v>
+        <v>46396.08333333334</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>46396.16666666666</v>
+        <v>46396.33333333334</v>
       </c>
     </row>
     <row r="56">
@@ -3503,13 +3503,13 @@
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46396.58333333334</v>
+        <v>46396.75</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>46396.70833333334</v>
+        <v>46396.875</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>46397.83333333334</v>
+        <v>46398</v>
       </c>
     </row>
     <row r="57">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46398.16666666666</v>
+        <v>46398.33333333334</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>46398.20833333334</v>
+        <v>46398.375</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>46398.54166666666</v>
+        <v>46398.70833333334</v>
       </c>
     </row>
     <row r="58">
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46402.41666666666</v>
+        <v>46402.58333333334</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>46402.45833333334</v>
+        <v>46402.625</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>46402.875</v>
+        <v>46403.04166666666</v>
       </c>
     </row>
     <row r="59">
@@ -3668,13 +3668,13 @@
         </is>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46403.125</v>
+        <v>46403.29166666666</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>46403.125</v>
+        <v>46403.29166666666</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>46403.5</v>
+        <v>46403.66666666666</v>
       </c>
     </row>
     <row r="60">
@@ -3719,13 +3719,13 @@
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" s="1" t="n">
-        <v>46404.75</v>
+        <v>46404.91666666666</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>46404.75</v>
+        <v>46404.91666666666</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>46405</v>
+        <v>46405.16666666666</v>
       </c>
     </row>
     <row r="61">
@@ -9540,10 +9540,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="L166" s="1" t="n">
-        <v>46296.125</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="M166" s="1" t="n">
-        <v>46297.79166666666</v>
+        <v>46297.91666666666</v>
       </c>
     </row>
     <row r="167">
@@ -9595,10 +9595,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="L167" s="1" t="n">
-        <v>46296.625</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="M167" s="1" t="n">
-        <v>46297.95833333334</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="168">
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46298.25</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>46298.3125</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="M168" s="1" t="n">
-        <v>46298.9375</v>
+        <v>46298.97916666666</v>
       </c>
     </row>
     <row r="169">
@@ -9702,13 +9702,13 @@
         </is>
       </c>
       <c r="K169" s="1" t="n">
-        <v>46300.4375</v>
+        <v>46300.47916666666</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>46300.64583333334</v>
+        <v>46300.6875</v>
       </c>
       <c r="M169" s="1" t="n">
-        <v>46301.3125</v>
+        <v>46301.35416666666</v>
       </c>
     </row>
     <row r="170">
@@ -9757,13 +9757,13 @@
         </is>
       </c>
       <c r="K170" s="1" t="n">
-        <v>46308.3125</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>46308.39583333334</v>
+        <v>46308.4375</v>
       </c>
       <c r="M170" s="1" t="n">
-        <v>46309.22916666666</v>
+        <v>46309.27083333334</v>
       </c>
     </row>
     <row r="171">
@@ -9812,13 +9812,13 @@
         </is>
       </c>
       <c r="K171" s="1" t="n">
-        <v>46310.3125</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>46310.39583333334</v>
+        <v>46310.4375</v>
       </c>
       <c r="M171" s="1" t="n">
-        <v>46310.89583333334</v>
+        <v>46310.9375</v>
       </c>
     </row>
     <row r="172">
@@ -9867,13 +9867,13 @@
         </is>
       </c>
       <c r="K172" s="1" t="n">
-        <v>46314.89583333334</v>
+        <v>46314.9375</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>46314.9375</v>
+        <v>46314.97916666666</v>
       </c>
       <c r="M172" s="1" t="n">
-        <v>46315.60416666666</v>
+        <v>46315.64583333334</v>
       </c>
     </row>
     <row r="173">
@@ -9922,13 +9922,13 @@
         </is>
       </c>
       <c r="K173" s="1" t="n">
-        <v>46322.02083333334</v>
+        <v>46322.0625</v>
       </c>
       <c r="L173" s="1" t="n">
-        <v>46322.22916666666</v>
+        <v>46322.27083333334</v>
       </c>
       <c r="M173" s="1" t="n">
-        <v>46322.89583333334</v>
+        <v>46322.9375</v>
       </c>
     </row>
     <row r="174">
@@ -11134,7 +11134,7 @@
         <v>46295</v>
       </c>
       <c r="M195" s="1" t="n">
-        <v>46295.54166666666</v>
+        <v>46295.75</v>
       </c>
     </row>
     <row r="196">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="K196" s="1" t="n">
-        <v>46298.08333333334</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="L196" s="1" t="n">
-        <v>46298.14583333334</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="M196" s="1" t="n">
-        <v>46298.64583333334</v>
+        <v>46298.72916666666</v>
       </c>
     </row>
     <row r="197">
@@ -11238,13 +11238,13 @@
         </is>
       </c>
       <c r="K197" s="1" t="n">
-        <v>46298.875</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>46298.91666666666</v>
+        <v>46299</v>
       </c>
       <c r="M197" s="1" t="n">
-        <v>46299.41666666666</v>
+        <v>46299.5</v>
       </c>
     </row>
     <row r="198">
@@ -11293,13 +11293,13 @@
         </is>
       </c>
       <c r="K198" s="1" t="n">
-        <v>46302.70833333334</v>
+        <v>46302.79166666666</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>46302.75</v>
+        <v>46302.83333333334</v>
       </c>
       <c r="M198" s="1" t="n">
-        <v>46303.41666666666</v>
+        <v>46303.5</v>
       </c>
     </row>
     <row r="199">
@@ -11348,13 +11348,13 @@
         </is>
       </c>
       <c r="K199" s="1" t="n">
-        <v>46304.5</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>46304.54166666666</v>
+        <v>46304.625</v>
       </c>
       <c r="M199" s="1" t="n">
-        <v>46305.125</v>
+        <v>46305.20833333334</v>
       </c>
     </row>
     <row r="200">
@@ -24249,10 +24249,10 @@
         </is>
       </c>
       <c r="K434" s="1" t="n">
+        <v>46297.95833333334</v>
+      </c>
+      <c r="L434" s="1" t="n">
         <v>46298</v>
-      </c>
-      <c r="L434" s="1" t="n">
-        <v>46298.04166666666</v>
       </c>
       <c r="M434" s="1" t="n">
         <v>46298.625</v>
@@ -29843,13 +29843,13 @@
         </is>
       </c>
       <c r="K536" s="1" t="n">
-        <v>46296.83333333334</v>
+        <v>46296.8125</v>
       </c>
       <c r="L536" s="1" t="n">
-        <v>46296.875</v>
+        <v>46296.85416666666</v>
       </c>
       <c r="M536" s="1" t="n">
-        <v>46297.5</v>
+        <v>46297.29166666666</v>
       </c>
     </row>
     <row r="537">
@@ -29898,13 +29898,13 @@
         </is>
       </c>
       <c r="K537" s="1" t="n">
-        <v>46298.58333333334</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="L537" s="1" t="n">
-        <v>46298.625</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="M537" s="1" t="n">
-        <v>46299.25</v>
+        <v>46299.45833333334</v>
       </c>
     </row>
     <row r="538">
@@ -29953,13 +29953,13 @@
         </is>
       </c>
       <c r="K538" s="1" t="n">
-        <v>46304.5</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="L538" s="1" t="n">
-        <v>46304.66666666666</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="M538" s="1" t="n">
-        <v>46305.08333333334</v>
+        <v>46305.33333333334</v>
       </c>
     </row>
     <row r="539">
@@ -30008,13 +30008,13 @@
         </is>
       </c>
       <c r="K539" s="1" t="n">
-        <v>46306.79166666666</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="L539" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46307</v>
       </c>
       <c r="M539" s="1" t="n">
-        <v>46307.25</v>
+        <v>46307.66666666666</v>
       </c>
     </row>
     <row r="540">
@@ -30063,13 +30063,13 @@
         </is>
       </c>
       <c r="K540" s="1" t="n">
-        <v>46308.875</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="L540" s="1" t="n">
-        <v>46309</v>
+        <v>46309.375</v>
       </c>
       <c r="M540" s="1" t="n">
-        <v>46309.58333333334</v>
+        <v>46309.95833333334</v>
       </c>
     </row>
     <row r="541">
@@ -39235,10 +39235,10 @@
         <v>46295.91666666666</v>
       </c>
       <c r="L707" s="1" t="n">
-        <v>46296.95833333334</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="M707" s="1" t="n">
-        <v>46297.625</v>
+        <v>46297.875</v>
       </c>
     </row>
     <row r="708">
@@ -39287,13 +39287,13 @@
         </is>
       </c>
       <c r="K708" s="1" t="n">
-        <v>46298.66666666666</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="L708" s="1" t="n">
-        <v>46298.72916666666</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="M708" s="1" t="n">
-        <v>46299.14583333334</v>
+        <v>46299.3125</v>
       </c>
     </row>
     <row r="709">
@@ -39342,13 +39342,13 @@
         </is>
       </c>
       <c r="K709" s="1" t="n">
-        <v>46299.45833333334</v>
+        <v>46299.625</v>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46299.5</v>
+        <v>46299.64583333334</v>
       </c>
       <c r="M709" s="1" t="n">
-        <v>46300.10416666666</v>
+        <v>46300.25</v>
       </c>
     </row>
     <row r="710">
@@ -39397,13 +39397,13 @@
         </is>
       </c>
       <c r="K710" s="1" t="n">
-        <v>46305.52083333334</v>
+        <v>46305.66666666666</v>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46305.6875</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="M710" s="1" t="n">
-        <v>46306.27083333334</v>
+        <v>46306.41666666666</v>
       </c>
     </row>
     <row r="711">
@@ -39452,13 +39452,13 @@
         </is>
       </c>
       <c r="K711" s="1" t="n">
-        <v>46308.04166666666</v>
+        <v>46308.1875</v>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46308.08333333334</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="M711" s="1" t="n">
-        <v>46308.4375</v>
+        <v>46308.58333333334</v>
       </c>
     </row>
     <row r="712">
@@ -39507,13 +39507,13 @@
         </is>
       </c>
       <c r="K712" s="1" t="n">
-        <v>46308.5625</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46308.64583333334</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="M712" s="1" t="n">
-        <v>46309.64583333334</v>
+        <v>46309.79166666666</v>
       </c>
     </row>
     <row r="713">
@@ -39562,13 +39562,13 @@
         </is>
       </c>
       <c r="K713" s="1" t="n">
-        <v>46309.85416666666</v>
+        <v>46310</v>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46309.89583333334</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="M713" s="1" t="n">
-        <v>46310.39583333334</v>
+        <v>46310.54166666666</v>
       </c>
     </row>
     <row r="714">
@@ -39617,13 +39617,13 @@
         </is>
       </c>
       <c r="K714" s="1" t="n">
-        <v>46312.20833333334</v>
+        <v>46312.35416666666</v>
       </c>
       <c r="L714" s="1" t="n">
-        <v>46312.375</v>
+        <v>46312.52083333334</v>
       </c>
       <c r="M714" s="1" t="n">
-        <v>46313.0625</v>
+        <v>46313.20833333334</v>
       </c>
     </row>
     <row r="715">
@@ -39672,13 +39672,13 @@
         </is>
       </c>
       <c r="K715" s="1" t="n">
-        <v>46319.04166666666</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="L715" s="1" t="n">
-        <v>46319.08333333334</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="M715" s="1" t="n">
-        <v>46319.75</v>
+        <v>46321.5</v>
       </c>
     </row>
     <row r="716">
@@ -39727,13 +39727,13 @@
         </is>
       </c>
       <c r="K716" s="1" t="n">
-        <v>46319.91666666666</v>
+        <v>46321.66666666666</v>
       </c>
       <c r="L716" s="1" t="n">
-        <v>46319.97916666666</v>
+        <v>46321.72916666666</v>
       </c>
       <c r="M716" s="1" t="n">
-        <v>46320.22916666666</v>
+        <v>46321.97916666666</v>
       </c>
     </row>
     <row r="717">
@@ -39782,13 +39782,13 @@
         </is>
       </c>
       <c r="K717" s="1" t="n">
-        <v>46321.125</v>
+        <v>46322.875</v>
       </c>
       <c r="L717" s="1" t="n">
-        <v>46321.1875</v>
+        <v>46322.9375</v>
       </c>
       <c r="M717" s="1" t="n">
-        <v>46321.60416666666</v>
+        <v>46323.35416666666</v>
       </c>
     </row>
     <row r="718">
@@ -39837,13 +39837,13 @@
         </is>
       </c>
       <c r="K718" s="1" t="n">
-        <v>46321.875</v>
+        <v>46323.625</v>
       </c>
       <c r="L718" s="1" t="n">
-        <v>46321.89583333334</v>
+        <v>46323.64583333334</v>
       </c>
       <c r="M718" s="1" t="n">
-        <v>46322.5</v>
+        <v>46324.25</v>
       </c>
     </row>
     <row r="719">
@@ -39892,13 +39892,13 @@
         </is>
       </c>
       <c r="K719" s="1" t="n">
-        <v>46327.33333333334</v>
+        <v>46329.16666666666</v>
       </c>
       <c r="L719" s="1" t="n">
-        <v>46327.5</v>
+        <v>46329.33333333334</v>
       </c>
       <c r="M719" s="1" t="n">
-        <v>46328.08333333334</v>
+        <v>46329.91666666666</v>
       </c>
     </row>
     <row r="720">
@@ -39947,13 +39947,13 @@
         </is>
       </c>
       <c r="K720" s="1" t="n">
-        <v>46329.6875</v>
+        <v>46331.5625</v>
       </c>
       <c r="L720" s="1" t="n">
-        <v>46329.72916666666</v>
+        <v>46331.60416666666</v>
       </c>
       <c r="M720" s="1" t="n">
-        <v>46330.08333333334</v>
+        <v>46331.95833333334</v>
       </c>
     </row>
     <row r="721">
@@ -40002,13 +40002,13 @@
         </is>
       </c>
       <c r="K721" s="1" t="n">
-        <v>46330.20833333334</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="L721" s="1" t="n">
-        <v>46330.29166666666</v>
+        <v>46332.16666666666</v>
       </c>
       <c r="M721" s="1" t="n">
-        <v>46331.29166666666</v>
+        <v>46333.16666666666</v>
       </c>
     </row>
     <row r="722">
@@ -40057,13 +40057,13 @@
         </is>
       </c>
       <c r="K722" s="1" t="n">
-        <v>46331.5</v>
+        <v>46333.375</v>
       </c>
       <c r="L722" s="1" t="n">
-        <v>46331.54166666666</v>
+        <v>46333.41666666666</v>
       </c>
       <c r="M722" s="1" t="n">
-        <v>46332.04166666666</v>
+        <v>46333.91666666666</v>
       </c>
     </row>
     <row r="723">
@@ -40112,13 +40112,13 @@
         </is>
       </c>
       <c r="K723" s="1" t="n">
-        <v>46333.85416666666</v>
+        <v>46335.72916666666</v>
       </c>
       <c r="L723" s="1" t="n">
-        <v>46334.02083333334</v>
+        <v>46335.89583333334</v>
       </c>
       <c r="M723" s="1" t="n">
-        <v>46334.70833333334</v>
+        <v>46336.58333333334</v>
       </c>
     </row>
     <row r="724">
@@ -40167,13 +40167,13 @@
         </is>
       </c>
       <c r="K724" s="1" t="n">
-        <v>46339.91666666666</v>
+        <v>46341.79166666666</v>
       </c>
       <c r="L724" s="1" t="n">
-        <v>46339.95833333334</v>
+        <v>46341.83333333334</v>
       </c>
       <c r="M724" s="1" t="n">
-        <v>46340.625</v>
+        <v>46342.5</v>
       </c>
     </row>
     <row r="725">
@@ -40222,13 +40222,13 @@
         </is>
       </c>
       <c r="K725" s="1" t="n">
-        <v>46340.79166666666</v>
+        <v>46342.66666666666</v>
       </c>
       <c r="L725" s="1" t="n">
-        <v>46340.85416666666</v>
+        <v>46342.72916666666</v>
       </c>
       <c r="M725" s="1" t="n">
-        <v>46341.10416666666</v>
+        <v>46342.97916666666</v>
       </c>
     </row>
     <row r="726">
@@ -40277,13 +40277,13 @@
         </is>
       </c>
       <c r="K726" s="1" t="n">
-        <v>46342</v>
+        <v>46343.875</v>
       </c>
       <c r="L726" s="1" t="n">
-        <v>46342.0625</v>
+        <v>46343.9375</v>
       </c>
       <c r="M726" s="1" t="n">
-        <v>46342.47916666666</v>
+        <v>46344.35416666666</v>
       </c>
     </row>
     <row r="727">
@@ -40332,13 +40332,13 @@
         </is>
       </c>
       <c r="K727" s="1" t="n">
-        <v>46342.75</v>
+        <v>46344.625</v>
       </c>
       <c r="L727" s="1" t="n">
-        <v>46342.77083333334</v>
+        <v>46344.64583333334</v>
       </c>
       <c r="M727" s="1" t="n">
-        <v>46343.375</v>
+        <v>46345.25</v>
       </c>
     </row>
     <row r="728">
@@ -40387,13 +40387,13 @@
         </is>
       </c>
       <c r="K728" s="1" t="n">
-        <v>46348.20833333334</v>
+        <v>46350.16666666666</v>
       </c>
       <c r="L728" s="1" t="n">
-        <v>46348.375</v>
+        <v>46350.33333333334</v>
       </c>
       <c r="M728" s="1" t="n">
-        <v>46348.95833333334</v>
+        <v>46350.91666666666</v>
       </c>
     </row>
     <row r="729">
@@ -40442,13 +40442,13 @@
         </is>
       </c>
       <c r="K729" s="1" t="n">
-        <v>46350.60625</v>
+        <v>46352.5625</v>
       </c>
       <c r="L729" s="1" t="n">
-        <v>46350.64791666667</v>
+        <v>46352.60416666666</v>
       </c>
       <c r="M729" s="1" t="n">
-        <v>46351.00208333333</v>
+        <v>46352.95833333334</v>
       </c>
     </row>
     <row r="730">
@@ -40497,13 +40497,13 @@
         </is>
       </c>
       <c r="K730" s="1" t="n">
-        <v>46351.12708333333</v>
+        <v>46353.08333333334</v>
       </c>
       <c r="L730" s="1" t="n">
-        <v>46351.21041666667</v>
+        <v>46353.16666666666</v>
       </c>
       <c r="M730" s="1" t="n">
-        <v>46352.21041666667</v>
+        <v>46354.16666666666</v>
       </c>
     </row>
     <row r="731">
@@ -40552,13 +40552,13 @@
         </is>
       </c>
       <c r="K731" s="1" t="n">
-        <v>46352.41875</v>
+        <v>46354.375</v>
       </c>
       <c r="L731" s="1" t="n">
-        <v>46352.46041666667</v>
+        <v>46354.41666666666</v>
       </c>
       <c r="M731" s="1" t="n">
-        <v>46352.96041666667</v>
+        <v>46354.91666666666</v>
       </c>
     </row>
     <row r="732">
@@ -40607,13 +40607,13 @@
         </is>
       </c>
       <c r="K732" s="1" t="n">
-        <v>46354.77291666667</v>
+        <v>46356.72916666666</v>
       </c>
       <c r="L732" s="1" t="n">
-        <v>46354.93958333333</v>
+        <v>46356.89583333334</v>
       </c>
       <c r="M732" s="1" t="n">
-        <v>46355.62708333333</v>
+        <v>46357.58333333334</v>
       </c>
     </row>
     <row r="733">
@@ -43345,7 +43345,7 @@
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K782" s="1" t="n">
@@ -43355,7 +43355,7 @@
         <v>46297.08333333334</v>
       </c>
       <c r="M782" s="1" t="n">
-        <v>46298.33333333334</v>
+        <v>46298.54166666666</v>
       </c>
     </row>
     <row r="783">
@@ -43390,27 +43390,27 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
         <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
           <t>KRUSN</t>
         </is>
       </c>
-      <c r="J783" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
       <c r="K783" s="1" t="n">
-        <v>46298.45833333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="L783" s="1" t="n">
-        <v>46298.5</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="M783" s="1" t="n">
-        <v>46298.75</v>
+        <v>46299.29166666666</v>
       </c>
     </row>
     <row r="784">
@@ -43445,12 +43445,12 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
@@ -43459,13 +43459,13 @@
         </is>
       </c>
       <c r="K784" s="1" t="n">
-        <v>46299.25</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="L784" s="1" t="n">
-        <v>46299.33333333334</v>
+        <v>46300.72916666666</v>
       </c>
       <c r="M784" s="1" t="n">
-        <v>46299.66666666666</v>
+        <v>46301.08333333334</v>
       </c>
     </row>
     <row r="785">
@@ -43514,13 +43514,13 @@
         </is>
       </c>
       <c r="K785" s="1" t="n">
-        <v>46304.625</v>
+        <v>46306.04166666666</v>
       </c>
       <c r="L785" s="1" t="n">
-        <v>46304.79166666666</v>
+        <v>46306.20833333334</v>
       </c>
       <c r="M785" s="1" t="n">
-        <v>46305.41666666666</v>
+        <v>46306.83333333334</v>
       </c>
     </row>
     <row r="786">
@@ -43569,13 +43569,13 @@
         </is>
       </c>
       <c r="K786" s="1" t="n">
-        <v>46307.08333333334</v>
+        <v>46308.5</v>
       </c>
       <c r="L786" s="1" t="n">
-        <v>46307.125</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="M786" s="1" t="n">
-        <v>46307.375</v>
+        <v>46308.79166666666</v>
       </c>
     </row>
     <row r="787">
@@ -43624,13 +43624,13 @@
         </is>
       </c>
       <c r="K787" s="1" t="n">
-        <v>46307.45833333334</v>
+        <v>46308.875</v>
       </c>
       <c r="L787" s="1" t="n">
-        <v>46307.58333333334</v>
+        <v>46309</v>
       </c>
       <c r="M787" s="1" t="n">
-        <v>46309.08333333334</v>
+        <v>46310.5</v>
       </c>
     </row>
     <row r="788">
@@ -43679,13 +43679,13 @@
         </is>
       </c>
       <c r="K788" s="1" t="n">
-        <v>46309.29166666666</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="L788" s="1" t="n">
-        <v>46309.33333333334</v>
+        <v>46310.75</v>
       </c>
       <c r="M788" s="1" t="n">
-        <v>46309.75</v>
+        <v>46311.16666666666</v>
       </c>
     </row>
     <row r="789">
@@ -43734,13 +43734,13 @@
         </is>
       </c>
       <c r="K789" s="1" t="n">
-        <v>46311.375</v>
+        <v>46312.79166666666</v>
       </c>
       <c r="L789" s="1" t="n">
-        <v>46311.54166666666</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="M789" s="1" t="n">
-        <v>46312.08333333334</v>
+        <v>46313.5</v>
       </c>
     </row>
     <row r="790">
@@ -43789,13 +43789,13 @@
         </is>
       </c>
       <c r="K790" s="1" t="n">
-        <v>46317.29166666666</v>
+        <v>46318.79166666666</v>
       </c>
       <c r="L790" s="1" t="n">
-        <v>46317.33333333334</v>
+        <v>46318.83333333334</v>
       </c>
       <c r="M790" s="1" t="n">
-        <v>46318.41666666666</v>
+        <v>46319.91666666666</v>
       </c>
     </row>
     <row r="791">
@@ -43844,13 +43844,13 @@
         </is>
       </c>
       <c r="K791" s="1" t="n">
-        <v>46318.54166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="L791" s="1" t="n">
-        <v>46318.58333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="M791" s="1" t="n">
-        <v>46318.83333333334</v>
+        <v>46320.33333333334</v>
       </c>
     </row>
     <row r="792">
@@ -43899,13 +43899,13 @@
         </is>
       </c>
       <c r="K792" s="1" t="n">
-        <v>46319.33333333334</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="L792" s="1" t="n">
-        <v>46319.41666666666</v>
+        <v>46320.91666666666</v>
       </c>
       <c r="M792" s="1" t="n">
-        <v>46319.75</v>
+        <v>46321.25</v>
       </c>
     </row>
     <row r="793">
@@ -43954,13 +43954,13 @@
         </is>
       </c>
       <c r="K793" s="1" t="n">
-        <v>46324.625</v>
+        <v>46326.125</v>
       </c>
       <c r="L793" s="1" t="n">
-        <v>46324.79166666666</v>
+        <v>46326.29166666666</v>
       </c>
       <c r="M793" s="1" t="n">
-        <v>46325.41666666666</v>
+        <v>46326.91666666666</v>
       </c>
     </row>
     <row r="794">
@@ -44009,13 +44009,13 @@
         </is>
       </c>
       <c r="K794" s="1" t="n">
-        <v>46327.08333333334</v>
+        <v>46328.58333333334</v>
       </c>
       <c r="L794" s="1" t="n">
-        <v>46327.125</v>
+        <v>46328.625</v>
       </c>
       <c r="M794" s="1" t="n">
-        <v>46327.375</v>
+        <v>46328.875</v>
       </c>
     </row>
     <row r="795">
@@ -44064,13 +44064,13 @@
         </is>
       </c>
       <c r="K795" s="1" t="n">
-        <v>46327.5</v>
+        <v>46329</v>
       </c>
       <c r="L795" s="1" t="n">
-        <v>46327.625</v>
+        <v>46329.125</v>
       </c>
       <c r="M795" s="1" t="n">
-        <v>46329.125</v>
+        <v>46330.625</v>
       </c>
     </row>
     <row r="796">
@@ -44119,13 +44119,13 @@
         </is>
       </c>
       <c r="K796" s="1" t="n">
-        <v>46329.33333333334</v>
+        <v>46330.83333333334</v>
       </c>
       <c r="L796" s="1" t="n">
-        <v>46329.375</v>
+        <v>46330.875</v>
       </c>
       <c r="M796" s="1" t="n">
-        <v>46329.79166666666</v>
+        <v>46331.29166666666</v>
       </c>
     </row>
     <row r="797">
@@ -44174,13 +44174,13 @@
         </is>
       </c>
       <c r="K797" s="1" t="n">
-        <v>46331.33333333334</v>
+        <v>46332.83333333334</v>
       </c>
       <c r="L797" s="1" t="n">
-        <v>46331.5</v>
+        <v>46333</v>
       </c>
       <c r="M797" s="1" t="n">
-        <v>46332.04166666666</v>
+        <v>46333.54166666666</v>
       </c>
     </row>
     <row r="798">
@@ -44229,13 +44229,13 @@
         </is>
       </c>
       <c r="K798" s="1" t="n">
-        <v>46337.41666666666</v>
+        <v>46338.91666666666</v>
       </c>
       <c r="L798" s="1" t="n">
-        <v>46337.45833333334</v>
+        <v>46338.95833333334</v>
       </c>
       <c r="M798" s="1" t="n">
-        <v>46338.54166666666</v>
+        <v>46340.04166666666</v>
       </c>
     </row>
     <row r="799">
@@ -44284,13 +44284,13 @@
         </is>
       </c>
       <c r="K799" s="1" t="n">
-        <v>46338.70833333334</v>
+        <v>46340.20833333334</v>
       </c>
       <c r="L799" s="1" t="n">
-        <v>46338.75</v>
+        <v>46340.25</v>
       </c>
       <c r="M799" s="1" t="n">
-        <v>46339</v>
+        <v>46340.5</v>
       </c>
     </row>
     <row r="800">
@@ -44339,13 +44339,13 @@
         </is>
       </c>
       <c r="K800" s="1" t="n">
-        <v>46339.45833333334</v>
+        <v>46340.95833333334</v>
       </c>
       <c r="L800" s="1" t="n">
-        <v>46339.54166666666</v>
+        <v>46341.04166666666</v>
       </c>
       <c r="M800" s="1" t="n">
-        <v>46339.875</v>
+        <v>46341.375</v>
       </c>
     </row>
     <row r="801">
@@ -44394,13 +44394,13 @@
         </is>
       </c>
       <c r="K801" s="1" t="n">
-        <v>46344.875</v>
+        <v>46346.375</v>
       </c>
       <c r="L801" s="1" t="n">
-        <v>46345.04166666666</v>
+        <v>46346.54166666666</v>
       </c>
       <c r="M801" s="1" t="n">
-        <v>46345.66666666666</v>
+        <v>46347.16666666666</v>
       </c>
     </row>
     <row r="802">
@@ -44449,13 +44449,13 @@
         </is>
       </c>
       <c r="K802" s="1" t="n">
-        <v>46347.45833333334</v>
+        <v>46348.95833333334</v>
       </c>
       <c r="L802" s="1" t="n">
-        <v>46347.5</v>
+        <v>46349</v>
       </c>
       <c r="M802" s="1" t="n">
-        <v>46347.75</v>
+        <v>46349.25</v>
       </c>
     </row>
     <row r="803">
@@ -44504,13 +44504,13 @@
         </is>
       </c>
       <c r="K803" s="1" t="n">
-        <v>46348.04166666666</v>
+        <v>46349.54166666666</v>
       </c>
       <c r="L803" s="1" t="n">
-        <v>46348.16666666666</v>
+        <v>46349.66666666666</v>
       </c>
       <c r="M803" s="1" t="n">
-        <v>46349.66666666666</v>
+        <v>46351.16666666666</v>
       </c>
     </row>
     <row r="804">
@@ -44559,13 +44559,13 @@
         </is>
       </c>
       <c r="K804" s="1" t="n">
-        <v>46349.875</v>
+        <v>46351.375</v>
       </c>
       <c r="L804" s="1" t="n">
-        <v>46349.91666666666</v>
+        <v>46351.41666666666</v>
       </c>
       <c r="M804" s="1" t="n">
-        <v>46350.33333333334</v>
+        <v>46351.83333333334</v>
       </c>
     </row>
     <row r="805">
@@ -44614,13 +44614,13 @@
         </is>
       </c>
       <c r="K805" s="1" t="n">
-        <v>46351.91666666666</v>
+        <v>46353.41666666666</v>
       </c>
       <c r="L805" s="1" t="n">
-        <v>46352.08333333334</v>
+        <v>46353.58333333334</v>
       </c>
       <c r="M805" s="1" t="n">
-        <v>46352.625</v>
+        <v>46354.125</v>
       </c>
     </row>
     <row r="806">
@@ -44669,13 +44669,13 @@
         </is>
       </c>
       <c r="K806" s="1" t="n">
-        <v>46358.33333333334</v>
+        <v>46359.83333333334</v>
       </c>
       <c r="L806" s="1" t="n">
-        <v>46358.375</v>
+        <v>46359.875</v>
       </c>
       <c r="M806" s="1" t="n">
-        <v>46359.45833333334</v>
+        <v>46360.95833333334</v>
       </c>
     </row>
     <row r="807">
@@ -44724,13 +44724,13 @@
         </is>
       </c>
       <c r="K807" s="1" t="n">
-        <v>46359.58333333334</v>
+        <v>46361.08333333334</v>
       </c>
       <c r="L807" s="1" t="n">
-        <v>46359.625</v>
+        <v>46361.125</v>
       </c>
       <c r="M807" s="1" t="n">
-        <v>46359.875</v>
+        <v>46361.375</v>
       </c>
     </row>
     <row r="808">
@@ -44779,13 +44779,13 @@
         </is>
       </c>
       <c r="K808" s="1" t="n">
-        <v>46360.33333333334</v>
+        <v>46361.83333333334</v>
       </c>
       <c r="L808" s="1" t="n">
-        <v>46360.41666666666</v>
+        <v>46361.91666666666</v>
       </c>
       <c r="M808" s="1" t="n">
-        <v>46360.75</v>
+        <v>46362.25</v>
       </c>
     </row>
     <row r="809">
@@ -44834,13 +44834,13 @@
         </is>
       </c>
       <c r="K809" s="1" t="n">
-        <v>46365.75</v>
+        <v>46367.25</v>
       </c>
       <c r="L809" s="1" t="n">
-        <v>46365.91666666666</v>
+        <v>46367.41666666666</v>
       </c>
       <c r="M809" s="1" t="n">
-        <v>46366.54166666666</v>
+        <v>46368.04166666666</v>
       </c>
     </row>
     <row r="810">
@@ -44889,13 +44889,13 @@
         </is>
       </c>
       <c r="K810" s="1" t="n">
-        <v>46368.33333333334</v>
+        <v>46369.83333333334</v>
       </c>
       <c r="L810" s="1" t="n">
-        <v>46368.375</v>
+        <v>46369.875</v>
       </c>
       <c r="M810" s="1" t="n">
-        <v>46368.625</v>
+        <v>46370.125</v>
       </c>
     </row>
     <row r="811">
@@ -44944,13 +44944,13 @@
         </is>
       </c>
       <c r="K811" s="1" t="n">
-        <v>46368.91666666666</v>
+        <v>46370.41666666666</v>
       </c>
       <c r="L811" s="1" t="n">
-        <v>46369.04166666666</v>
+        <v>46370.54166666666</v>
       </c>
       <c r="M811" s="1" t="n">
-        <v>46370.54166666666</v>
+        <v>46372.04166666666</v>
       </c>
     </row>
     <row r="812">
@@ -44999,13 +44999,13 @@
         </is>
       </c>
       <c r="K812" s="1" t="n">
-        <v>46370.75</v>
+        <v>46372.25</v>
       </c>
       <c r="L812" s="1" t="n">
-        <v>46370.79166666666</v>
+        <v>46372.29166666666</v>
       </c>
       <c r="M812" s="1" t="n">
-        <v>46371.20833333334</v>
+        <v>46372.70833333334</v>
       </c>
     </row>
     <row r="813">
@@ -45054,13 +45054,13 @@
         </is>
       </c>
       <c r="K813" s="1" t="n">
-        <v>46372.75</v>
+        <v>46374.25</v>
       </c>
       <c r="L813" s="1" t="n">
-        <v>46372.91666666666</v>
+        <v>46374.41666666666</v>
       </c>
       <c r="M813" s="1" t="n">
-        <v>46373.45833333334</v>
+        <v>46374.95833333334</v>
       </c>
     </row>
     <row r="814">
@@ -51088,13 +51088,13 @@
         </is>
       </c>
       <c r="K923" s="1" t="n">
-        <v>46297.41666666666</v>
+        <v>46297.45833333334</v>
       </c>
       <c r="L923" s="1" t="n">
-        <v>46297.47916666666</v>
+        <v>46297.52083333334</v>
       </c>
       <c r="M923" s="1" t="n">
-        <v>46297.75</v>
+        <v>46297.97916666666</v>
       </c>
     </row>
     <row r="924">
@@ -51143,13 +51143,13 @@
         </is>
       </c>
       <c r="K924" s="1" t="n">
-        <v>46300.58333333334</v>
+        <v>46300.8125</v>
       </c>
       <c r="L924" s="1" t="n">
-        <v>46300.625</v>
+        <v>46300.85416666666</v>
       </c>
       <c r="M924" s="1" t="n">
-        <v>46301.08333333334</v>
+        <v>46301.3125</v>
       </c>
     </row>
     <row r="925">
@@ -51198,13 +51198,13 @@
         </is>
       </c>
       <c r="K925" s="1" t="n">
-        <v>46303.25</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="L925" s="1" t="n">
-        <v>46303.41666666666</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="M925" s="1" t="n">
-        <v>46303.875</v>
+        <v>46304.10416666666</v>
       </c>
     </row>
     <row r="926">
@@ -51253,13 +51253,13 @@
         </is>
       </c>
       <c r="K926" s="1" t="n">
-        <v>46305.45833333334</v>
+        <v>46305.6875</v>
       </c>
       <c r="L926" s="1" t="n">
-        <v>46305.5</v>
+        <v>46305.72916666666</v>
       </c>
       <c r="M926" s="1" t="n">
-        <v>46305.75</v>
+        <v>46305.97916666666</v>
       </c>
     </row>
     <row r="927">
@@ -51308,13 +51308,13 @@
         </is>
       </c>
       <c r="K927" s="1" t="n">
-        <v>46305.91666666666</v>
+        <v>46306.14583333334</v>
       </c>
       <c r="L927" s="1" t="n">
-        <v>46306.04166666666</v>
+        <v>46306.27083333334</v>
       </c>
       <c r="M927" s="1" t="n">
-        <v>46307.54166666666</v>
+        <v>46307.77083333334</v>
       </c>
     </row>
     <row r="928">
@@ -51363,13 +51363,13 @@
         </is>
       </c>
       <c r="K928" s="1" t="n">
-        <v>46307.70833333334</v>
+        <v>46307.9375</v>
       </c>
       <c r="L928" s="1" t="n">
-        <v>46307.75</v>
+        <v>46307.97916666666</v>
       </c>
       <c r="M928" s="1" t="n">
-        <v>46308</v>
+        <v>46308.22916666666</v>
       </c>
     </row>
     <row r="929">
@@ -51418,13 +51418,13 @@
         </is>
       </c>
       <c r="K929" s="1" t="n">
-        <v>46311.72916666666</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="L929" s="1" t="n">
-        <v>46311.79166666666</v>
+        <v>46312.02083333334</v>
       </c>
       <c r="M929" s="1" t="n">
-        <v>46312.25</v>
+        <v>46312.47916666666</v>
       </c>
     </row>
     <row r="930">
@@ -51473,13 +51473,13 @@
         </is>
       </c>
       <c r="K930" s="1" t="n">
-        <v>46313.04166666666</v>
+        <v>46313.27083333334</v>
       </c>
       <c r="L930" s="1" t="n">
-        <v>46313.08333333334</v>
+        <v>46313.3125</v>
       </c>
       <c r="M930" s="1" t="n">
-        <v>46313.66666666666</v>
+        <v>46313.89583333334</v>
       </c>
     </row>
     <row r="931">
@@ -51528,13 +51528,13 @@
         </is>
       </c>
       <c r="K931" s="1" t="n">
-        <v>46316.04166666666</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="L931" s="1" t="n">
-        <v>46316.08333333334</v>
+        <v>46316.3125</v>
       </c>
       <c r="M931" s="1" t="n">
-        <v>46316.79166666666</v>
+        <v>46317.02083333334</v>
       </c>
     </row>
     <row r="932">
@@ -51583,13 +51583,13 @@
         </is>
       </c>
       <c r="K932" s="1" t="n">
-        <v>46317.08333333334</v>
+        <v>46317.3125</v>
       </c>
       <c r="L932" s="1" t="n">
-        <v>46317.14583333334</v>
+        <v>46317.375</v>
       </c>
       <c r="M932" s="1" t="n">
-        <v>46317.41666666666</v>
+        <v>46317.64583333334</v>
       </c>
     </row>
     <row r="933">
@@ -51638,13 +51638,13 @@
         </is>
       </c>
       <c r="K933" s="1" t="n">
-        <v>46320.33333333334</v>
+        <v>46320.5625</v>
       </c>
       <c r="L933" s="1" t="n">
-        <v>46320.375</v>
+        <v>46320.60416666666</v>
       </c>
       <c r="M933" s="1" t="n">
-        <v>46320.83333333334</v>
+        <v>46321.0625</v>
       </c>
     </row>
     <row r="934">
@@ -51693,13 +51693,13 @@
         </is>
       </c>
       <c r="K934" s="1" t="n">
-        <v>46323.04166666666</v>
+        <v>46323.27083333334</v>
       </c>
       <c r="L934" s="1" t="n">
-        <v>46323.20833333334</v>
+        <v>46323.4375</v>
       </c>
       <c r="M934" s="1" t="n">
-        <v>46323.66666666666</v>
+        <v>46323.89583333334</v>
       </c>
     </row>
     <row r="935">
@@ -51748,13 +51748,13 @@
         </is>
       </c>
       <c r="K935" s="1" t="n">
-        <v>46325.33333333334</v>
+        <v>46325.5625</v>
       </c>
       <c r="L935" s="1" t="n">
-        <v>46325.375</v>
+        <v>46325.60416666666</v>
       </c>
       <c r="M935" s="1" t="n">
-        <v>46325.625</v>
+        <v>46325.85416666666</v>
       </c>
     </row>
     <row r="936">
@@ -51803,13 +51803,13 @@
         </is>
       </c>
       <c r="K936" s="1" t="n">
-        <v>46325.79166666666</v>
+        <v>46326.02083333334</v>
       </c>
       <c r="L936" s="1" t="n">
-        <v>46325.91666666666</v>
+        <v>46326.14583333334</v>
       </c>
       <c r="M936" s="1" t="n">
-        <v>46327.41666666666</v>
+        <v>46327.64583333334</v>
       </c>
     </row>
     <row r="937">
@@ -51858,13 +51858,13 @@
         </is>
       </c>
       <c r="K937" s="1" t="n">
-        <v>46327.625</v>
+        <v>46327.85416666666</v>
       </c>
       <c r="L937" s="1" t="n">
-        <v>46327.66666666666</v>
+        <v>46327.89583333334</v>
       </c>
       <c r="M937" s="1" t="n">
-        <v>46327.91666666666</v>
+        <v>46328.14583333334</v>
       </c>
     </row>
     <row r="938">
@@ -51913,13 +51913,13 @@
         </is>
       </c>
       <c r="K938" s="1" t="n">
-        <v>46331.75</v>
+        <v>46331.97916666666</v>
       </c>
       <c r="L938" s="1" t="n">
-        <v>46331.79166666666</v>
+        <v>46332.02083333334</v>
       </c>
       <c r="M938" s="1" t="n">
-        <v>46332.25</v>
+        <v>46332.47916666666</v>
       </c>
     </row>
     <row r="939">
@@ -51968,13 +51968,13 @@
         </is>
       </c>
       <c r="K939" s="1" t="n">
-        <v>46333</v>
+        <v>46333.22916666666</v>
       </c>
       <c r="L939" s="1" t="n">
-        <v>46333.04166666666</v>
+        <v>46333.27083333334</v>
       </c>
       <c r="M939" s="1" t="n">
-        <v>46333.625</v>
+        <v>46333.85416666666</v>
       </c>
     </row>
     <row r="940">
@@ -53724,13 +53724,13 @@
         </is>
       </c>
       <c r="K971" s="1" t="n">
-        <v>46297.04166666666</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="L971" s="1" t="n">
-        <v>46297.125</v>
+        <v>46297.41666666666</v>
       </c>
       <c r="M971" s="1" t="n">
-        <v>46297.625</v>
+        <v>46297.91666666666</v>
       </c>
     </row>
     <row r="972">
@@ -53779,13 +53779,13 @@
         </is>
       </c>
       <c r="K972" s="1" t="n">
-        <v>46301.35416666666</v>
+        <v>46301.64583333334</v>
       </c>
       <c r="L972" s="1" t="n">
-        <v>46301.39583333334</v>
+        <v>46301.6875</v>
       </c>
       <c r="M972" s="1" t="n">
-        <v>46302.0625</v>
+        <v>46302.35416666666</v>
       </c>
     </row>
     <row r="973">
@@ -53834,13 +53834,13 @@
         </is>
       </c>
       <c r="K973" s="1" t="n">
-        <v>46308.125</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="L973" s="1" t="n">
-        <v>46308.33333333334</v>
+        <v>46308.625</v>
       </c>
       <c r="M973" s="1" t="n">
-        <v>46309</v>
+        <v>46309.29166666666</v>
       </c>
     </row>
     <row r="974">
@@ -53889,13 +53889,13 @@
         </is>
       </c>
       <c r="K974" s="1" t="n">
-        <v>46310.39583333334</v>
+        <v>46310.6875</v>
       </c>
       <c r="L974" s="1" t="n">
-        <v>46310.4375</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="M974" s="1" t="n">
-        <v>46311.4375</v>
+        <v>46311.72916666666</v>
       </c>
     </row>
     <row r="975">
@@ -53944,13 +53944,13 @@
         </is>
       </c>
       <c r="K975" s="1" t="n">
-        <v>46311.72916666666</v>
+        <v>46312.02083333334</v>
       </c>
       <c r="L975" s="1" t="n">
-        <v>46311.77083333334</v>
+        <v>46312.0625</v>
       </c>
       <c r="M975" s="1" t="n">
-        <v>46312.39583333334</v>
+        <v>46312.6875</v>
       </c>
     </row>
     <row r="976">
@@ -53999,13 +53999,13 @@
         </is>
       </c>
       <c r="K976" s="1" t="n">
-        <v>46313.85416666666</v>
+        <v>46314.14583333334</v>
       </c>
       <c r="L976" s="1" t="n">
-        <v>46314.0625</v>
+        <v>46314.35416666666</v>
       </c>
       <c r="M976" s="1" t="n">
-        <v>46314.72916666666</v>
+        <v>46315.02083333334</v>
       </c>
     </row>
     <row r="977">
@@ -54054,13 +54054,13 @@
         </is>
       </c>
       <c r="K977" s="1" t="n">
-        <v>46321.72916666666</v>
+        <v>46322.02083333334</v>
       </c>
       <c r="L977" s="1" t="n">
-        <v>46321.8125</v>
+        <v>46322.10416666666</v>
       </c>
       <c r="M977" s="1" t="n">
-        <v>46322.64583333334</v>
+        <v>46322.9375</v>
       </c>
     </row>
     <row r="978">
@@ -54109,13 +54109,13 @@
         </is>
       </c>
       <c r="K978" s="1" t="n">
-        <v>46323.72916666666</v>
+        <v>46324.02083333334</v>
       </c>
       <c r="L978" s="1" t="n">
-        <v>46323.8125</v>
+        <v>46324.10416666666</v>
       </c>
       <c r="M978" s="1" t="n">
-        <v>46324.3125</v>
+        <v>46324.60416666666</v>
       </c>
     </row>
     <row r="979">
@@ -54164,13 +54164,13 @@
         </is>
       </c>
       <c r="K979" s="1" t="n">
-        <v>46328.3125</v>
+        <v>46328.60416666666</v>
       </c>
       <c r="L979" s="1" t="n">
-        <v>46328.35416666666</v>
+        <v>46328.64583333334</v>
       </c>
       <c r="M979" s="1" t="n">
-        <v>46329.02083333334</v>
+        <v>46329.3125</v>
       </c>
     </row>
     <row r="980">
@@ -54219,13 +54219,13 @@
         </is>
       </c>
       <c r="K980" s="1" t="n">
-        <v>46335.4375</v>
+        <v>46335.72916666666</v>
       </c>
       <c r="L980" s="1" t="n">
-        <v>46335.64583333334</v>
+        <v>46335.9375</v>
       </c>
       <c r="M980" s="1" t="n">
-        <v>46336.3125</v>
+        <v>46336.60416666666</v>
       </c>
     </row>
     <row r="981">
@@ -57401,13 +57401,13 @@
         </is>
       </c>
       <c r="K1038" s="1" t="n">
-        <v>46295.58333333334</v>
+        <v>46295.625</v>
       </c>
       <c r="L1038" s="1" t="n">
-        <v>46295.75</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="M1038" s="1" t="n">
-        <v>46296.3125</v>
+        <v>46296.52083333334</v>
       </c>
     </row>
     <row r="1039">
@@ -57456,13 +57456,13 @@
         </is>
       </c>
       <c r="K1039" s="1" t="n">
-        <v>46298.66666666666</v>
+        <v>46298.875</v>
       </c>
       <c r="L1039" s="1" t="n">
-        <v>46298.72916666666</v>
+        <v>46298.9375</v>
       </c>
       <c r="M1039" s="1" t="n">
-        <v>46299.22916666666</v>
+        <v>46299.4375</v>
       </c>
     </row>
     <row r="1040">
@@ -57511,13 +57511,13 @@
         </is>
       </c>
       <c r="K1040" s="1" t="n">
-        <v>46299.35416666666</v>
+        <v>46299.5625</v>
       </c>
       <c r="L1040" s="1" t="n">
-        <v>46299.47916666666</v>
+        <v>46299.6875</v>
       </c>
       <c r="M1040" s="1" t="n">
-        <v>46299.9375</v>
+        <v>46300.14583333334</v>
       </c>
     </row>
     <row r="1041">
@@ -57566,13 +57566,13 @@
         </is>
       </c>
       <c r="K1041" s="1" t="n">
-        <v>46303.02083333334</v>
+        <v>46303.25</v>
       </c>
       <c r="L1041" s="1" t="n">
-        <v>46303.0625</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="M1041" s="1" t="n">
-        <v>46303.72916666666</v>
+        <v>46303.95833333334</v>
       </c>
     </row>
     <row r="1042">
@@ -57621,13 +57621,13 @@
         </is>
       </c>
       <c r="K1042" s="1" t="n">
-        <v>46304.8125</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="L1042" s="1" t="n">
-        <v>46304.85416666666</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="M1042" s="1" t="n">
-        <v>46305.4375</v>
+        <v>46305.66666666666</v>
       </c>
     </row>
     <row r="1043">
@@ -57676,13 +57676,13 @@
         </is>
       </c>
       <c r="K1043" s="1" t="n">
-        <v>46305.625</v>
+        <v>46305.875</v>
       </c>
       <c r="L1043" s="1" t="n">
-        <v>46305.6875</v>
+        <v>46305.91666666666</v>
       </c>
       <c r="M1043" s="1" t="n">
-        <v>46306.02083333334</v>
+        <v>46306.25</v>
       </c>
     </row>
     <row r="1044">
@@ -57731,13 +57731,13 @@
         </is>
       </c>
       <c r="K1044" s="1" t="n">
-        <v>46307.3125</v>
+        <v>46307.54166666666</v>
       </c>
       <c r="L1044" s="1" t="n">
-        <v>46307.47916666666</v>
+        <v>46307.70833333334</v>
       </c>
       <c r="M1044" s="1" t="n">
-        <v>46307.97916666666</v>
+        <v>46308.20833333334</v>
       </c>
     </row>
     <row r="1045">
@@ -57786,13 +57786,13 @@
         </is>
       </c>
       <c r="K1045" s="1" t="n">
-        <v>46312.14583333334</v>
+        <v>46312.375</v>
       </c>
       <c r="L1045" s="1" t="n">
-        <v>46312.3125</v>
+        <v>46312.54166666666</v>
       </c>
       <c r="M1045" s="1" t="n">
-        <v>46313.14583333334</v>
+        <v>46313.375</v>
       </c>
     </row>
     <row r="1046">
@@ -57841,13 +57841,13 @@
         </is>
       </c>
       <c r="K1046" s="1" t="n">
-        <v>46314.8125</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="L1046" s="1" t="n">
-        <v>46314.85416666666</v>
+        <v>46315.125</v>
       </c>
       <c r="M1046" s="1" t="n">
-        <v>46315.6875</v>
+        <v>46315.95833333334</v>
       </c>
     </row>
     <row r="1047">
@@ -57896,13 +57896,13 @@
         </is>
       </c>
       <c r="K1047" s="1" t="n">
-        <v>46318.85416666666</v>
+        <v>46319.125</v>
       </c>
       <c r="L1047" s="1" t="n">
-        <v>46318.9375</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="M1047" s="1" t="n">
-        <v>46320.60416666666</v>
+        <v>46320.85416666666</v>
       </c>
     </row>
     <row r="1048">
@@ -57951,13 +57951,13 @@
         </is>
       </c>
       <c r="K1048" s="1" t="n">
-        <v>46323.0625</v>
+        <v>46322.97916666666</v>
       </c>
       <c r="L1048" s="1" t="n">
-        <v>46323.22916666666</v>
+        <v>46323.14583333334</v>
       </c>
       <c r="M1048" s="1" t="n">
-        <v>46324.0625</v>
+        <v>46323.97916666666</v>
       </c>
     </row>
     <row r="1049">
@@ -58006,13 +58006,13 @@
         </is>
       </c>
       <c r="K1049" s="1" t="n">
-        <v>46326.60416666666</v>
+        <v>46326.5</v>
       </c>
       <c r="L1049" s="1" t="n">
-        <v>46326.66666666666</v>
+        <v>46326.5625</v>
       </c>
       <c r="M1049" s="1" t="n">
-        <v>46327.16666666666</v>
+        <v>46327.0625</v>
       </c>
     </row>
     <row r="1050">
@@ -58061,13 +58061,13 @@
         </is>
       </c>
       <c r="K1050" s="1" t="n">
-        <v>46327.39583333334</v>
+        <v>46327.29166666666</v>
       </c>
       <c r="L1050" s="1" t="n">
-        <v>46327.4375</v>
+        <v>46327.33333333334</v>
       </c>
       <c r="M1050" s="1" t="n">
-        <v>46327.9375</v>
+        <v>46327.83333333334</v>
       </c>
     </row>
     <row r="1051">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -3942,10 +3942,10 @@
         <v>46296.85416666666</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>46297.08333333334</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>46297.95833333334</v>
+        <v>46297.79166666666</v>
       </c>
     </row>
     <row r="65">
@@ -3994,13 +3994,13 @@
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46302.875</v>
+        <v>46302.54166666666</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>46303.04166666666</v>
+        <v>46302.70833333334</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>46303.54166666666</v>
+        <v>46303.20833333334</v>
       </c>
     </row>
     <row r="66">
@@ -4049,13 +4049,13 @@
         </is>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46305.04166666666</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="L66" s="1" t="n">
+        <v>46304.75</v>
+      </c>
+      <c r="M66" s="1" t="n">
         <v>46305.08333333334</v>
-      </c>
-      <c r="M66" s="1" t="n">
-        <v>46305.41666666666</v>
       </c>
     </row>
     <row r="67">
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46305.54166666666</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>46305.625</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>46306.625</v>
+        <v>46306.29166666666</v>
       </c>
     </row>
     <row r="68">
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46306.5</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>46306.875</v>
+        <v>46306.54166666666</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>46307.375</v>
+        <v>46307.04166666666</v>
       </c>
     </row>
     <row r="69">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46309.1875</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>46309.35416666666</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>46310.04166666666</v>
+        <v>46309.70833333334</v>
       </c>
     </row>
     <row r="70">
@@ -9598,7 +9598,7 @@
         <v>46296.66666666666</v>
       </c>
       <c r="M167" s="1" t="n">
-        <v>46298</v>
+        <v>46298.04166666666</v>
       </c>
     </row>
     <row r="168">
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46298.29166666666</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>46298.35416666666</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="M168" s="1" t="n">
-        <v>46298.97916666666</v>
+        <v>46299.02083333334</v>
       </c>
     </row>
     <row r="169">
@@ -9702,13 +9702,13 @@
         </is>
       </c>
       <c r="K169" s="1" t="n">
-        <v>46300.47916666666</v>
+        <v>46300.52083333334</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>46300.6875</v>
+        <v>46300.72916666666</v>
       </c>
       <c r="M169" s="1" t="n">
-        <v>46301.35416666666</v>
+        <v>46301.39583333334</v>
       </c>
     </row>
     <row r="170">
@@ -9757,13 +9757,13 @@
         </is>
       </c>
       <c r="K170" s="1" t="n">
-        <v>46308.35416666666</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>46308.4375</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="M170" s="1" t="n">
-        <v>46309.27083333334</v>
+        <v>46309.3125</v>
       </c>
     </row>
     <row r="171">
@@ -9812,13 +9812,13 @@
         </is>
       </c>
       <c r="K171" s="1" t="n">
-        <v>46310.35416666666</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>46310.4375</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="M171" s="1" t="n">
-        <v>46310.9375</v>
+        <v>46310.97916666666</v>
       </c>
     </row>
     <row r="172">
@@ -9867,13 +9867,13 @@
         </is>
       </c>
       <c r="K172" s="1" t="n">
-        <v>46314.9375</v>
+        <v>46314.97916666666</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>46314.97916666666</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="M172" s="1" t="n">
-        <v>46315.64583333334</v>
+        <v>46315.6875</v>
       </c>
     </row>
     <row r="173">
@@ -9922,13 +9922,13 @@
         </is>
       </c>
       <c r="K173" s="1" t="n">
-        <v>46322.0625</v>
+        <v>46322.10416666666</v>
       </c>
       <c r="L173" s="1" t="n">
-        <v>46322.27083333334</v>
+        <v>46322.3125</v>
       </c>
       <c r="M173" s="1" t="n">
-        <v>46322.9375</v>
+        <v>46322.97916666666</v>
       </c>
     </row>
     <row r="174">
@@ -43352,10 +43352,10 @@
         <v>46296.41666666666</v>
       </c>
       <c r="L782" s="1" t="n">
-        <v>46297.08333333334</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="M782" s="1" t="n">
-        <v>46298.54166666666</v>
+        <v>46298.58333333334</v>
       </c>
     </row>
     <row r="783">
@@ -43404,13 +43404,13 @@
         </is>
       </c>
       <c r="K783" s="1" t="n">
-        <v>46298.83333333334</v>
+        <v>46298.875</v>
       </c>
       <c r="L783" s="1" t="n">
-        <v>46298.89583333334</v>
+        <v>46298.9375</v>
       </c>
       <c r="M783" s="1" t="n">
-        <v>46299.29166666666</v>
+        <v>46299.33333333334</v>
       </c>
     </row>
     <row r="784">
@@ -43459,13 +43459,13 @@
         </is>
       </c>
       <c r="K784" s="1" t="n">
-        <v>46299.70833333334</v>
+        <v>46299.75</v>
       </c>
       <c r="L784" s="1" t="n">
-        <v>46300.72916666666</v>
+        <v>46300.77083333334</v>
       </c>
       <c r="M784" s="1" t="n">
-        <v>46301.08333333334</v>
+        <v>46301.125</v>
       </c>
     </row>
     <row r="785">
@@ -43514,13 +43514,13 @@
         </is>
       </c>
       <c r="K785" s="1" t="n">
-        <v>46306.04166666666</v>
+        <v>46306.08333333334</v>
       </c>
       <c r="L785" s="1" t="n">
-        <v>46306.20833333334</v>
+        <v>46306.25</v>
       </c>
       <c r="M785" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46306.875</v>
       </c>
     </row>
     <row r="786">
@@ -43569,13 +43569,13 @@
         </is>
       </c>
       <c r="K786" s="1" t="n">
-        <v>46308.5</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="L786" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="M786" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46308.83333333334</v>
       </c>
     </row>
     <row r="787">
@@ -43624,13 +43624,13 @@
         </is>
       </c>
       <c r="K787" s="1" t="n">
-        <v>46308.875</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="L787" s="1" t="n">
-        <v>46309</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="M787" s="1" t="n">
-        <v>46310.5</v>
+        <v>46310.54166666666</v>
       </c>
     </row>
     <row r="788">
@@ -43679,13 +43679,13 @@
         </is>
       </c>
       <c r="K788" s="1" t="n">
-        <v>46310.70833333334</v>
+        <v>46310.75</v>
       </c>
       <c r="L788" s="1" t="n">
-        <v>46310.75</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="M788" s="1" t="n">
-        <v>46311.16666666666</v>
+        <v>46311.20833333334</v>
       </c>
     </row>
     <row r="789">
@@ -43734,13 +43734,13 @@
         </is>
       </c>
       <c r="K789" s="1" t="n">
-        <v>46312.79166666666</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="L789" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46313</v>
       </c>
       <c r="M789" s="1" t="n">
-        <v>46313.5</v>
+        <v>46313.54166666666</v>
       </c>
     </row>
     <row r="790">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -43352,10 +43352,10 @@
         <v>46296.41666666666</v>
       </c>
       <c r="L782" s="1" t="n">
-        <v>46297.16666666666</v>
+        <v>46297.25</v>
       </c>
       <c r="M782" s="1" t="n">
-        <v>46298.58333333334</v>
+        <v>46298.66666666666</v>
       </c>
     </row>
     <row r="783">
@@ -43404,13 +43404,13 @@
         </is>
       </c>
       <c r="K783" s="1" t="n">
-        <v>46298.875</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="L783" s="1" t="n">
-        <v>46298.9375</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="M783" s="1" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.41666666666</v>
       </c>
     </row>
     <row r="784">
@@ -43459,13 +43459,13 @@
         </is>
       </c>
       <c r="K784" s="1" t="n">
-        <v>46299.75</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="L784" s="1" t="n">
-        <v>46300.77083333334</v>
+        <v>46300.85416666666</v>
       </c>
       <c r="M784" s="1" t="n">
-        <v>46301.125</v>
+        <v>46301.20833333334</v>
       </c>
     </row>
     <row r="785">
@@ -43514,13 +43514,13 @@
         </is>
       </c>
       <c r="K785" s="1" t="n">
-        <v>46306.08333333334</v>
+        <v>46306.16666666666</v>
       </c>
       <c r="L785" s="1" t="n">
-        <v>46306.25</v>
+        <v>46306.33333333334</v>
       </c>
       <c r="M785" s="1" t="n">
-        <v>46306.875</v>
+        <v>46306.95833333334</v>
       </c>
     </row>
     <row r="786">
@@ -43569,13 +43569,13 @@
         </is>
       </c>
       <c r="K786" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.625</v>
       </c>
       <c r="L786" s="1" t="n">
-        <v>46308.58333333334</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="M786" s="1" t="n">
-        <v>46308.83333333334</v>
+        <v>46308.91666666666</v>
       </c>
     </row>
     <row r="787">
@@ -43624,13 +43624,13 @@
         </is>
       </c>
       <c r="K787" s="1" t="n">
-        <v>46308.91666666666</v>
+        <v>46309</v>
       </c>
       <c r="L787" s="1" t="n">
-        <v>46309.04166666666</v>
+        <v>46309.125</v>
       </c>
       <c r="M787" s="1" t="n">
-        <v>46310.54166666666</v>
+        <v>46310.625</v>
       </c>
     </row>
     <row r="788">
@@ -43679,13 +43679,13 @@
         </is>
       </c>
       <c r="K788" s="1" t="n">
-        <v>46310.75</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="L788" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.875</v>
       </c>
       <c r="M788" s="1" t="n">
-        <v>46311.20833333334</v>
+        <v>46311.29166666666</v>
       </c>
     </row>
     <row r="789">
@@ -43734,13 +43734,13 @@
         </is>
       </c>
       <c r="K789" s="1" t="n">
-        <v>46312.83333333334</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="L789" s="1" t="n">
-        <v>46313</v>
+        <v>46313.08333333334</v>
       </c>
       <c r="M789" s="1" t="n">
-        <v>46313.54166666666</v>
+        <v>46313.625</v>
       </c>
     </row>
     <row r="790">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -3945,7 +3945,7 @@
         <v>46296.79166666666</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>46297.79166666666</v>
+        <v>46297.75</v>
       </c>
     </row>
     <row r="65">
@@ -3994,13 +3994,13 @@
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46302.54166666666</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>46302.70833333334</v>
+        <v>46302.625</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>46303.20833333334</v>
+        <v>46303.125</v>
       </c>
     </row>
     <row r="66">
@@ -4049,13 +4049,13 @@
         </is>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46304.70833333334</v>
+        <v>46304.625</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>46304.75</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>46305.08333333334</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="67">
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="K67" s="1" t="n">
+        <v>46305.125</v>
+      </c>
+      <c r="L67" s="1" t="n">
         <v>46305.20833333334</v>
       </c>
-      <c r="L67" s="1" t="n">
-        <v>46305.29166666666</v>
-      </c>
       <c r="M67" s="1" t="n">
-        <v>46306.29166666666</v>
+        <v>46306.20833333334</v>
       </c>
     </row>
     <row r="68">
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46306.5</v>
+        <v>46306.41666666666</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>46306.54166666666</v>
+        <v>46306.45833333334</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>46307.04166666666</v>
+        <v>46306.95833333334</v>
       </c>
     </row>
     <row r="69">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46308.85416666666</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>46309.02083333334</v>
+        <v>46308.9375</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46309.625</v>
       </c>
     </row>
     <row r="70">
@@ -43352,10 +43352,10 @@
         <v>46296.41666666666</v>
       </c>
       <c r="L782" s="1" t="n">
-        <v>46297.25</v>
+        <v>46297.29166666666</v>
       </c>
       <c r="M782" s="1" t="n">
-        <v>46298.66666666666</v>
+        <v>46298.70833333334</v>
       </c>
     </row>
     <row r="783">
@@ -43404,13 +43404,13 @@
         </is>
       </c>
       <c r="K783" s="1" t="n">
-        <v>46298.95833333334</v>
+        <v>46299</v>
       </c>
       <c r="L783" s="1" t="n">
-        <v>46299.02083333334</v>
+        <v>46299.0625</v>
       </c>
       <c r="M783" s="1" t="n">
-        <v>46299.41666666666</v>
+        <v>46299.45833333334</v>
       </c>
     </row>
     <row r="784">
@@ -43459,13 +43459,13 @@
         </is>
       </c>
       <c r="K784" s="1" t="n">
-        <v>46299.83333333334</v>
+        <v>46299.875</v>
       </c>
       <c r="L784" s="1" t="n">
-        <v>46300.85416666666</v>
+        <v>46300.89583333334</v>
       </c>
       <c r="M784" s="1" t="n">
-        <v>46301.20833333334</v>
+        <v>46301.25</v>
       </c>
     </row>
     <row r="785">
@@ -43514,13 +43514,13 @@
         </is>
       </c>
       <c r="K785" s="1" t="n">
-        <v>46306.16666666666</v>
+        <v>46306.20833333334</v>
       </c>
       <c r="L785" s="1" t="n">
-        <v>46306.33333333334</v>
+        <v>46306.375</v>
       </c>
       <c r="M785" s="1" t="n">
-        <v>46306.95833333334</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="786">
@@ -43569,13 +43569,13 @@
         </is>
       </c>
       <c r="K786" s="1" t="n">
-        <v>46308.625</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="L786" s="1" t="n">
-        <v>46308.66666666666</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="M786" s="1" t="n">
-        <v>46308.91666666666</v>
+        <v>46308.95833333334</v>
       </c>
     </row>
     <row r="787">
@@ -43624,13 +43624,13 @@
         </is>
       </c>
       <c r="K787" s="1" t="n">
-        <v>46309</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="L787" s="1" t="n">
-        <v>46309.125</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="M787" s="1" t="n">
-        <v>46310.625</v>
+        <v>46310.66666666666</v>
       </c>
     </row>
     <row r="788">
@@ -43679,13 +43679,13 @@
         </is>
       </c>
       <c r="K788" s="1" t="n">
-        <v>46310.83333333334</v>
+        <v>46310.875</v>
       </c>
       <c r="L788" s="1" t="n">
-        <v>46310.875</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="M788" s="1" t="n">
-        <v>46311.29166666666</v>
+        <v>46311.33333333334</v>
       </c>
     </row>
     <row r="789">
@@ -43734,13 +43734,13 @@
         </is>
       </c>
       <c r="K789" s="1" t="n">
-        <v>46312.91666666666</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="L789" s="1" t="n">
-        <v>46313.08333333334</v>
+        <v>46313.125</v>
       </c>
       <c r="M789" s="1" t="n">
-        <v>46313.625</v>
+        <v>46313.66666666666</v>
       </c>
     </row>
     <row r="790">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -9598,7 +9598,7 @@
         <v>46296.66666666666</v>
       </c>
       <c r="M167" s="1" t="n">
-        <v>46298.04166666666</v>
+        <v>46298.125</v>
       </c>
     </row>
     <row r="168">
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46298.33333333334</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>46298.39583333334</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="M168" s="1" t="n">
-        <v>46299.02083333334</v>
+        <v>46299.10416666666</v>
       </c>
     </row>
     <row r="169">
@@ -9702,13 +9702,13 @@
         </is>
       </c>
       <c r="K169" s="1" t="n">
-        <v>46300.52083333334</v>
+        <v>46300.16666666666</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>46300.72916666666</v>
+        <v>46300.375</v>
       </c>
       <c r="M169" s="1" t="n">
-        <v>46301.39583333334</v>
+        <v>46301.04166666666</v>
       </c>
     </row>
     <row r="170">
@@ -9757,13 +9757,13 @@
         </is>
       </c>
       <c r="K170" s="1" t="n">
-        <v>46308.39583333334</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>46308.47916666666</v>
+        <v>46308.125</v>
       </c>
       <c r="M170" s="1" t="n">
-        <v>46309.3125</v>
+        <v>46308.95833333334</v>
       </c>
     </row>
     <row r="171">
@@ -9812,13 +9812,13 @@
         </is>
       </c>
       <c r="K171" s="1" t="n">
-        <v>46310.39583333334</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>46310.47916666666</v>
+        <v>46310.125</v>
       </c>
       <c r="M171" s="1" t="n">
-        <v>46310.97916666666</v>
+        <v>46310.625</v>
       </c>
     </row>
     <row r="172">
@@ -9867,13 +9867,13 @@
         </is>
       </c>
       <c r="K172" s="1" t="n">
-        <v>46314.97916666666</v>
+        <v>46314.625</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>46315.02083333334</v>
+        <v>46314.66666666666</v>
       </c>
       <c r="M172" s="1" t="n">
-        <v>46315.6875</v>
+        <v>46315.33333333334</v>
       </c>
     </row>
     <row r="173">
@@ -9922,13 +9922,13 @@
         </is>
       </c>
       <c r="K173" s="1" t="n">
-        <v>46322.10416666666</v>
+        <v>46321.75</v>
       </c>
       <c r="L173" s="1" t="n">
-        <v>46322.3125</v>
+        <v>46321.95833333334</v>
       </c>
       <c r="M173" s="1" t="n">
-        <v>46322.97916666666</v>
+        <v>46322.625</v>
       </c>
     </row>
     <row r="174">
@@ -9977,13 +9977,13 @@
         </is>
       </c>
       <c r="K174" s="1" t="n">
-        <v>46324.14583333334</v>
+        <v>46323.70833333334</v>
       </c>
       <c r="L174" s="1" t="n">
-        <v>46324.1875</v>
+        <v>46323.75</v>
       </c>
       <c r="M174" s="1" t="n">
-        <v>46325.1875</v>
+        <v>46324.75</v>
       </c>
     </row>
     <row r="175">
@@ -10032,13 +10032,13 @@
         </is>
       </c>
       <c r="K175" s="1" t="n">
-        <v>46325.8125</v>
+        <v>46325.375</v>
       </c>
       <c r="L175" s="1" t="n">
-        <v>46325.85416666666</v>
+        <v>46325.41666666666</v>
       </c>
       <c r="M175" s="1" t="n">
-        <v>46326.47916666666</v>
+        <v>46326.04166666666</v>
       </c>
     </row>
     <row r="176">
@@ -10087,13 +10087,13 @@
         </is>
       </c>
       <c r="K176" s="1" t="n">
-        <v>46327.97916666666</v>
+        <v>46327.54166666666</v>
       </c>
       <c r="L176" s="1" t="n">
-        <v>46328.1875</v>
+        <v>46327.75</v>
       </c>
       <c r="M176" s="1" t="n">
-        <v>46328.85416666666</v>
+        <v>46328.41666666666</v>
       </c>
     </row>
     <row r="177">
@@ -10142,13 +10142,13 @@
         </is>
       </c>
       <c r="K177" s="1" t="n">
-        <v>46335.85416666666</v>
+        <v>46335.41666666666</v>
       </c>
       <c r="L177" s="1" t="n">
-        <v>46335.9375</v>
+        <v>46335.5</v>
       </c>
       <c r="M177" s="1" t="n">
-        <v>46336.77083333334</v>
+        <v>46336.33333333334</v>
       </c>
     </row>
     <row r="178">
@@ -10197,13 +10197,13 @@
         </is>
       </c>
       <c r="K178" s="1" t="n">
-        <v>46337.85416666666</v>
+        <v>46337.41666666666</v>
       </c>
       <c r="L178" s="1" t="n">
-        <v>46337.9375</v>
+        <v>46337.5</v>
       </c>
       <c r="M178" s="1" t="n">
-        <v>46338.4375</v>
+        <v>46338</v>
       </c>
     </row>
     <row r="179">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="K179" s="1" t="n">
-        <v>46342.4375</v>
+        <v>46342</v>
       </c>
       <c r="L179" s="1" t="n">
-        <v>46342.47916666666</v>
+        <v>46342.04166666666</v>
       </c>
       <c r="M179" s="1" t="n">
-        <v>46343.14583333334</v>
+        <v>46342.70833333334</v>
       </c>
     </row>
     <row r="180">
@@ -10307,13 +10307,13 @@
         </is>
       </c>
       <c r="K180" s="1" t="n">
-        <v>46349.5625</v>
+        <v>46349.125</v>
       </c>
       <c r="L180" s="1" t="n">
-        <v>46349.77083333334</v>
+        <v>46349.33333333334</v>
       </c>
       <c r="M180" s="1" t="n">
-        <v>46350.4375</v>
+        <v>46350</v>
       </c>
     </row>
     <row r="181">
@@ -10362,13 +10362,13 @@
         </is>
       </c>
       <c r="K181" s="1" t="n">
-        <v>46352.14583333334</v>
+        <v>46351.70833333334</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>46352.1875</v>
+        <v>46351.75</v>
       </c>
       <c r="M181" s="1" t="n">
-        <v>46353.1875</v>
+        <v>46352.75</v>
       </c>
     </row>
     <row r="182">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="K182" s="1" t="n">
-        <v>46353.8125</v>
+        <v>46353.375</v>
       </c>
       <c r="L182" s="1" t="n">
-        <v>46353.85416666666</v>
+        <v>46353.41666666666</v>
       </c>
       <c r="M182" s="1" t="n">
-        <v>46354.47916666666</v>
+        <v>46354.04166666666</v>
       </c>
     </row>
     <row r="183">
@@ -10472,13 +10472,13 @@
         </is>
       </c>
       <c r="K183" s="1" t="n">
-        <v>46355.97916666666</v>
+        <v>46355.54166666666</v>
       </c>
       <c r="L183" s="1" t="n">
-        <v>46356.1875</v>
+        <v>46355.75</v>
       </c>
       <c r="M183" s="1" t="n">
-        <v>46356.85416666666</v>
+        <v>46356.41666666666</v>
       </c>
     </row>
     <row r="184">
@@ -10527,13 +10527,13 @@
         </is>
       </c>
       <c r="K184" s="1" t="n">
-        <v>46363.85416666666</v>
+        <v>46363.41666666666</v>
       </c>
       <c r="L184" s="1" t="n">
-        <v>46363.9375</v>
+        <v>46363.5</v>
       </c>
       <c r="M184" s="1" t="n">
-        <v>46364.77083333334</v>
+        <v>46364.33333333334</v>
       </c>
     </row>
     <row r="185">
@@ -10582,13 +10582,13 @@
         </is>
       </c>
       <c r="K185" s="1" t="n">
-        <v>46365.85416666666</v>
+        <v>46365.41666666666</v>
       </c>
       <c r="L185" s="1" t="n">
-        <v>46365.9375</v>
+        <v>46365.5</v>
       </c>
       <c r="M185" s="1" t="n">
-        <v>46366.4375</v>
+        <v>46366</v>
       </c>
     </row>
     <row r="186">
@@ -10637,13 +10637,13 @@
         </is>
       </c>
       <c r="K186" s="1" t="n">
-        <v>46370.4375</v>
+        <v>46370</v>
       </c>
       <c r="L186" s="1" t="n">
-        <v>46370.47916666666</v>
+        <v>46370.04166666666</v>
       </c>
       <c r="M186" s="1" t="n">
-        <v>46371.14583333334</v>
+        <v>46370.70833333334</v>
       </c>
     </row>
     <row r="187">
@@ -10688,13 +10688,13 @@
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" s="1" t="n">
-        <v>46377.5625</v>
+        <v>46377.125</v>
       </c>
       <c r="L187" s="1" t="n">
-        <v>46377.77083333334</v>
+        <v>46377.33333333334</v>
       </c>
       <c r="M187" s="1" t="n">
-        <v>46378.4375</v>
+        <v>46378</v>
       </c>
     </row>
     <row r="188">
@@ -22273,13 +22273,13 @@
         </is>
       </c>
       <c r="K398" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46295.5625</v>
       </c>
       <c r="L398" s="1" t="n">
-        <v>46296.70833333334</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="M398" s="1" t="n">
-        <v>46297.70833333334</v>
+        <v>46298.25</v>
       </c>
     </row>
     <row r="399">
@@ -22328,13 +22328,13 @@
         </is>
       </c>
       <c r="K399" s="1" t="n">
-        <v>46298</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="L399" s="1" t="n">
-        <v>46298.0625</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="M399" s="1" t="n">
-        <v>46298.39583333334</v>
+        <v>46298.9375</v>
       </c>
     </row>
     <row r="400">
@@ -22383,13 +22383,13 @@
         </is>
       </c>
       <c r="K400" s="1" t="n">
-        <v>46301.29166666666</v>
+        <v>46301.83333333334</v>
       </c>
       <c r="L400" s="1" t="n">
-        <v>46301.35416666666</v>
+        <v>46301.89583333334</v>
       </c>
       <c r="M400" s="1" t="n">
-        <v>46301.85416666666</v>
+        <v>46302.39583333334</v>
       </c>
     </row>
     <row r="401">
@@ -22438,13 +22438,13 @@
         </is>
       </c>
       <c r="K401" s="1" t="n">
-        <v>46304.20833333334</v>
+        <v>46304.75</v>
       </c>
       <c r="L401" s="1" t="n">
-        <v>46304.375</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="M401" s="1" t="n">
-        <v>46305</v>
+        <v>46305.54166666666</v>
       </c>
     </row>
     <row r="402">
@@ -22493,13 +22493,13 @@
         </is>
       </c>
       <c r="K402" s="1" t="n">
-        <v>46306.66666666666</v>
+        <v>46307.20833333334</v>
       </c>
       <c r="L402" s="1" t="n">
-        <v>46306.70833333334</v>
+        <v>46307.25</v>
       </c>
       <c r="M402" s="1" t="n">
-        <v>46306.91666666666</v>
+        <v>46307.45833333334</v>
       </c>
     </row>
     <row r="403">
@@ -22548,13 +22548,13 @@
         </is>
       </c>
       <c r="K403" s="1" t="n">
-        <v>46307.04166666666</v>
+        <v>46307.58333333334</v>
       </c>
       <c r="L403" s="1" t="n">
-        <v>46307.16666666666</v>
+        <v>46307.70833333334</v>
       </c>
       <c r="M403" s="1" t="n">
-        <v>46308.625</v>
+        <v>46309.16666666666</v>
       </c>
     </row>
     <row r="404">
@@ -22603,13 +22603,13 @@
         </is>
       </c>
       <c r="K404" s="1" t="n">
-        <v>46308.83333333334</v>
+        <v>46309.375</v>
       </c>
       <c r="L404" s="1" t="n">
-        <v>46308.875</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="M404" s="1" t="n">
-        <v>46309.20833333334</v>
+        <v>46309.75</v>
       </c>
     </row>
     <row r="405">
@@ -22658,13 +22658,13 @@
         </is>
       </c>
       <c r="K405" s="1" t="n">
-        <v>46313.04166666666</v>
+        <v>46313.58333333334</v>
       </c>
       <c r="L405" s="1" t="n">
-        <v>46313.10416666666</v>
+        <v>46313.64583333334</v>
       </c>
       <c r="M405" s="1" t="n">
-        <v>46313.60416666666</v>
+        <v>46314.14583333334</v>
       </c>
     </row>
     <row r="406">
@@ -22713,13 +22713,13 @@
         </is>
       </c>
       <c r="K406" s="1" t="n">
-        <v>46314.45833333334</v>
+        <v>46315</v>
       </c>
       <c r="L406" s="1" t="n">
-        <v>46314.5</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="M406" s="1" t="n">
-        <v>46315.125</v>
+        <v>46315.66666666666</v>
       </c>
     </row>
     <row r="407">
@@ -22768,13 +22768,13 @@
         </is>
       </c>
       <c r="K407" s="1" t="n">
-        <v>46315.95833333334</v>
+        <v>46317.83333333334</v>
       </c>
       <c r="L407" s="1" t="n">
-        <v>46316</v>
+        <v>46317.875</v>
       </c>
       <c r="M407" s="1" t="n">
-        <v>46316.70833333334</v>
+        <v>46318.58333333334</v>
       </c>
     </row>
     <row r="408">
@@ -22823,13 +22823,13 @@
         </is>
       </c>
       <c r="K408" s="1" t="n">
-        <v>46317.04166666666</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="L408" s="1" t="n">
-        <v>46317.125</v>
+        <v>46319</v>
       </c>
       <c r="M408" s="1" t="n">
-        <v>46317.375</v>
+        <v>46319.25</v>
       </c>
     </row>
     <row r="409">
@@ -22878,13 +22878,13 @@
         </is>
       </c>
       <c r="K409" s="1" t="n">
-        <v>46320.29166666666</v>
+        <v>46322.16666666666</v>
       </c>
       <c r="L409" s="1" t="n">
-        <v>46320.33333333334</v>
+        <v>46322.20833333334</v>
       </c>
       <c r="M409" s="1" t="n">
-        <v>46320.79166666666</v>
+        <v>46322.66666666666</v>
       </c>
     </row>
     <row r="410">
@@ -22933,13 +22933,13 @@
         </is>
       </c>
       <c r="K410" s="1" t="n">
-        <v>46323</v>
+        <v>46324.875</v>
       </c>
       <c r="L410" s="1" t="n">
-        <v>46323.16666666666</v>
+        <v>46325.04166666666</v>
       </c>
       <c r="M410" s="1" t="n">
-        <v>46323.625</v>
+        <v>46325.5</v>
       </c>
     </row>
     <row r="411">
@@ -22988,13 +22988,13 @@
         </is>
       </c>
       <c r="K411" s="1" t="n">
-        <v>46325.375</v>
+        <v>46327.25</v>
       </c>
       <c r="L411" s="1" t="n">
-        <v>46325.41666666666</v>
+        <v>46327.29166666666</v>
       </c>
       <c r="M411" s="1" t="n">
-        <v>46325.58333333334</v>
+        <v>46327.45833333334</v>
       </c>
     </row>
     <row r="412">
@@ -23043,13 +23043,13 @@
         </is>
       </c>
       <c r="K412" s="1" t="n">
-        <v>46325.83333333334</v>
+        <v>46327.70833333334</v>
       </c>
       <c r="L412" s="1" t="n">
-        <v>46325.95833333334</v>
+        <v>46327.83333333334</v>
       </c>
       <c r="M412" s="1" t="n">
-        <v>46327.29166666666</v>
+        <v>46329.16666666666</v>
       </c>
     </row>
     <row r="413">
@@ -23098,13 +23098,13 @@
         </is>
       </c>
       <c r="K413" s="1" t="n">
-        <v>46327.79166666666</v>
+        <v>46329.66666666666</v>
       </c>
       <c r="L413" s="1" t="n">
-        <v>46327.83333333334</v>
+        <v>46329.70833333334</v>
       </c>
       <c r="M413" s="1" t="n">
-        <v>46328.125</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="414">
@@ -23153,13 +23153,13 @@
         </is>
       </c>
       <c r="K414" s="1" t="n">
-        <v>46332.20833333334</v>
+        <v>46334.08333333334</v>
       </c>
       <c r="L414" s="1" t="n">
-        <v>46332.25</v>
+        <v>46334.125</v>
       </c>
       <c r="M414" s="1" t="n">
-        <v>46332.70833333334</v>
+        <v>46334.58333333334</v>
       </c>
     </row>
     <row r="415">
@@ -23208,13 +23208,13 @@
         </is>
       </c>
       <c r="K415" s="1" t="n">
-        <v>46333.79166666666</v>
+        <v>46335.66666666666</v>
       </c>
       <c r="L415" s="1" t="n">
-        <v>46333.83333333334</v>
+        <v>46335.70833333334</v>
       </c>
       <c r="M415" s="1" t="n">
-        <v>46334.41666666666</v>
+        <v>46336.29166666666</v>
       </c>
     </row>
     <row r="416">
@@ -23263,13 +23263,13 @@
         </is>
       </c>
       <c r="K416" s="1" t="n">
-        <v>46336.70833333334</v>
+        <v>46338.83333333334</v>
       </c>
       <c r="L416" s="1" t="n">
-        <v>46336.75</v>
+        <v>46338.875</v>
       </c>
       <c r="M416" s="1" t="n">
-        <v>46337.45833333334</v>
+        <v>46339.58333333334</v>
       </c>
     </row>
     <row r="417">
@@ -23318,13 +23318,13 @@
         </is>
       </c>
       <c r="K417" s="1" t="n">
-        <v>46337.79166666666</v>
+        <v>46339.91666666666</v>
       </c>
       <c r="L417" s="1" t="n">
-        <v>46337.875</v>
+        <v>46340</v>
       </c>
       <c r="M417" s="1" t="n">
-        <v>46338.125</v>
+        <v>46340.25</v>
       </c>
     </row>
     <row r="418">
@@ -23373,13 +23373,13 @@
         </is>
       </c>
       <c r="K418" s="1" t="n">
-        <v>46341.04166666666</v>
+        <v>46343.16666666666</v>
       </c>
       <c r="L418" s="1" t="n">
-        <v>46341.08333333334</v>
+        <v>46343.20833333334</v>
       </c>
       <c r="M418" s="1" t="n">
-        <v>46341.54166666666</v>
+        <v>46343.66666666666</v>
       </c>
     </row>
     <row r="419">
@@ -23428,13 +23428,13 @@
         </is>
       </c>
       <c r="K419" s="1" t="n">
-        <v>46343.75</v>
+        <v>46345.875</v>
       </c>
       <c r="L419" s="1" t="n">
-        <v>46343.91666666666</v>
+        <v>46346.04166666666</v>
       </c>
       <c r="M419" s="1" t="n">
-        <v>46344.375</v>
+        <v>46346.5</v>
       </c>
     </row>
     <row r="420">
@@ -23483,13 +23483,13 @@
         </is>
       </c>
       <c r="K420" s="1" t="n">
-        <v>46346.125</v>
+        <v>46348.25</v>
       </c>
       <c r="L420" s="1" t="n">
-        <v>46346.16666666666</v>
+        <v>46348.29166666666</v>
       </c>
       <c r="M420" s="1" t="n">
-        <v>46346.33333333334</v>
+        <v>46348.45833333334</v>
       </c>
     </row>
     <row r="421">
@@ -23538,13 +23538,13 @@
         </is>
       </c>
       <c r="K421" s="1" t="n">
-        <v>46346.58333333334</v>
+        <v>46348.70833333334</v>
       </c>
       <c r="L421" s="1" t="n">
-        <v>46346.70833333334</v>
+        <v>46348.83333333334</v>
       </c>
       <c r="M421" s="1" t="n">
-        <v>46348.04166666666</v>
+        <v>46350.16666666666</v>
       </c>
     </row>
     <row r="422">
@@ -23593,13 +23593,13 @@
         </is>
       </c>
       <c r="K422" s="1" t="n">
-        <v>46348.54166666666</v>
+        <v>46350.66666666666</v>
       </c>
       <c r="L422" s="1" t="n">
-        <v>46348.58333333334</v>
+        <v>46350.70833333334</v>
       </c>
       <c r="M422" s="1" t="n">
-        <v>46348.875</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="423">
@@ -23648,13 +23648,13 @@
         </is>
       </c>
       <c r="K423" s="1" t="n">
-        <v>46352.95833333334</v>
+        <v>46355.08333333334</v>
       </c>
       <c r="L423" s="1" t="n">
-        <v>46353</v>
+        <v>46355.125</v>
       </c>
       <c r="M423" s="1" t="n">
-        <v>46353.45833333334</v>
+        <v>46355.58333333334</v>
       </c>
     </row>
     <row r="424">
@@ -23703,13 +23703,13 @@
         </is>
       </c>
       <c r="K424" s="1" t="n">
-        <v>46354.54166666666</v>
+        <v>46356.66666666666</v>
       </c>
       <c r="L424" s="1" t="n">
-        <v>46354.58333333334</v>
+        <v>46356.70833333334</v>
       </c>
       <c r="M424" s="1" t="n">
-        <v>46355.16666666666</v>
+        <v>46357.29166666666</v>
       </c>
     </row>
     <row r="425">
@@ -23758,13 +23758,13 @@
         </is>
       </c>
       <c r="K425" s="1" t="n">
-        <v>46357.70833333334</v>
+        <v>46359.83333333334</v>
       </c>
       <c r="L425" s="1" t="n">
-        <v>46357.75</v>
+        <v>46359.875</v>
       </c>
       <c r="M425" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46360.58333333334</v>
       </c>
     </row>
     <row r="426">
@@ -23813,13 +23813,13 @@
         </is>
       </c>
       <c r="K426" s="1" t="n">
-        <v>46358.79166666666</v>
+        <v>46360.91666666666</v>
       </c>
       <c r="L426" s="1" t="n">
-        <v>46358.875</v>
+        <v>46361</v>
       </c>
       <c r="M426" s="1" t="n">
-        <v>46359.125</v>
+        <v>46361.25</v>
       </c>
     </row>
     <row r="427">
@@ -23868,13 +23868,13 @@
         </is>
       </c>
       <c r="K427" s="1" t="n">
-        <v>46362.04166666666</v>
+        <v>46364.16666666666</v>
       </c>
       <c r="L427" s="1" t="n">
-        <v>46362.08333333334</v>
+        <v>46364.20833333334</v>
       </c>
       <c r="M427" s="1" t="n">
-        <v>46362.54166666666</v>
+        <v>46364.66666666666</v>
       </c>
     </row>
     <row r="428">
@@ -23923,13 +23923,13 @@
         </is>
       </c>
       <c r="K428" s="1" t="n">
-        <v>46364.75</v>
+        <v>46366.875</v>
       </c>
       <c r="L428" s="1" t="n">
-        <v>46364.91666666666</v>
+        <v>46367.04166666666</v>
       </c>
       <c r="M428" s="1" t="n">
-        <v>46365.375</v>
+        <v>46367.5</v>
       </c>
     </row>
     <row r="429">
@@ -23978,13 +23978,13 @@
         </is>
       </c>
       <c r="K429" s="1" t="n">
-        <v>46367.125</v>
+        <v>46369.25</v>
       </c>
       <c r="L429" s="1" t="n">
-        <v>46367.16666666666</v>
+        <v>46369.29166666666</v>
       </c>
       <c r="M429" s="1" t="n">
-        <v>46367.33333333334</v>
+        <v>46369.45833333334</v>
       </c>
     </row>
     <row r="430">
@@ -24033,13 +24033,13 @@
         </is>
       </c>
       <c r="K430" s="1" t="n">
-        <v>46367.58333333334</v>
+        <v>46369.70833333334</v>
       </c>
       <c r="L430" s="1" t="n">
-        <v>46367.70833333334</v>
+        <v>46369.83333333334</v>
       </c>
       <c r="M430" s="1" t="n">
-        <v>46369.04166666666</v>
+        <v>46371.16666666666</v>
       </c>
     </row>
     <row r="431">
@@ -24088,13 +24088,13 @@
         </is>
       </c>
       <c r="K431" s="1" t="n">
-        <v>46369.54166666666</v>
+        <v>46371.66666666666</v>
       </c>
       <c r="L431" s="1" t="n">
-        <v>46369.58333333334</v>
+        <v>46371.70833333334</v>
       </c>
       <c r="M431" s="1" t="n">
-        <v>46369.875</v>
+        <v>46372</v>
       </c>
     </row>
     <row r="432">
@@ -24143,13 +24143,13 @@
         </is>
       </c>
       <c r="K432" s="1" t="n">
-        <v>46373.95833333334</v>
+        <v>46376.08333333334</v>
       </c>
       <c r="L432" s="1" t="n">
-        <v>46374</v>
+        <v>46376.125</v>
       </c>
       <c r="M432" s="1" t="n">
-        <v>46374.45833333334</v>
+        <v>46376.58333333334</v>
       </c>
     </row>
     <row r="433">
@@ -24194,13 +24194,13 @@
       </c>
       <c r="J433" t="inlineStr"/>
       <c r="K433" s="1" t="n">
-        <v>46375.54166666666</v>
+        <v>46377.66666666666</v>
       </c>
       <c r="L433" s="1" t="n">
-        <v>46375.58333333334</v>
+        <v>46377.70833333334</v>
       </c>
       <c r="M433" s="1" t="n">
-        <v>46376.16666666666</v>
+        <v>46378.29166666666</v>
       </c>
     </row>
     <row r="434">
@@ -28152,7 +28152,7 @@
         <v>46293.775</v>
       </c>
       <c r="M505" s="1" t="n">
-        <v>46296.33333333334</v>
+        <v>46296.57916666667</v>
       </c>
     </row>
     <row r="506">
@@ -28207,7 +28207,7 @@
         <v>46293.775</v>
       </c>
       <c r="M506" s="1" t="n">
-        <v>46296.33333333334</v>
+        <v>46296.57916666667</v>
       </c>
     </row>
     <row r="507">
@@ -28262,7 +28262,7 @@
         <v>46293.775</v>
       </c>
       <c r="M507" s="1" t="n">
-        <v>46296.33333333334</v>
+        <v>46296.57916666667</v>
       </c>
     </row>
     <row r="508">
@@ -28311,13 +28311,13 @@
         </is>
       </c>
       <c r="K508" s="1" t="n">
-        <v>46296.625</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="L508" s="1" t="n">
-        <v>46296.6875</v>
+        <v>46297.09166666667</v>
       </c>
       <c r="M508" s="1" t="n">
-        <v>46297.16666666666</v>
+        <v>46297.5</v>
       </c>
     </row>
     <row r="509">
@@ -28366,13 +28366,13 @@
         </is>
       </c>
       <c r="K509" s="1" t="n">
-        <v>46296.625</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>46296.6875</v>
+        <v>46297.09166666667</v>
       </c>
       <c r="M509" s="1" t="n">
-        <v>46297.16666666666</v>
+        <v>46297.5</v>
       </c>
     </row>
     <row r="510">
@@ -28421,13 +28421,13 @@
         </is>
       </c>
       <c r="K510" s="1" t="n">
-        <v>46298.625</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>46299.70833333334</v>
+        <v>46300.04166666666</v>
       </c>
       <c r="M510" s="1" t="n">
-        <v>46300.20833333334</v>
+        <v>46300.54166666666</v>
       </c>
     </row>
     <row r="511">
@@ -28476,13 +28476,13 @@
         </is>
       </c>
       <c r="K511" s="1" t="n">
-        <v>46303.16666666666</v>
+        <v>46303.5</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>46303.29166666666</v>
+        <v>46303.625</v>
       </c>
       <c r="M511" s="1" t="n">
-        <v>46303.70833333334</v>
+        <v>46304.04166666666</v>
       </c>
     </row>
     <row r="512">
@@ -28531,13 +28531,13 @@
         </is>
       </c>
       <c r="K512" s="1" t="n">
-        <v>46315.95833333334</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>46317.04166666666</v>
+        <v>46317.375</v>
       </c>
       <c r="M512" s="1" t="n">
-        <v>46317.70833333334</v>
+        <v>46318.04166666666</v>
       </c>
     </row>
     <row r="513">
@@ -28586,13 +28586,13 @@
         </is>
       </c>
       <c r="K513" s="1" t="n">
-        <v>46318.95833333334</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>46319.04166666666</v>
+        <v>46319.375</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46319.54166666666</v>
+        <v>46319.875</v>
       </c>
     </row>
     <row r="514">
@@ -28641,13 +28641,13 @@
         </is>
       </c>
       <c r="K514" s="1" t="n">
-        <v>46320.45833333334</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>46320.54166666666</v>
+        <v>46320.875</v>
       </c>
       <c r="M514" s="1" t="n">
-        <v>46321.125</v>
+        <v>46321.45833333334</v>
       </c>
     </row>
     <row r="515">
@@ -28696,13 +28696,13 @@
         </is>
       </c>
       <c r="K515" s="1" t="n">
-        <v>46330</v>
+        <v>46330.33333333334</v>
       </c>
       <c r="L515" s="1" t="n">
-        <v>46331.04166666666</v>
+        <v>46331.375</v>
       </c>
       <c r="M515" s="1" t="n">
-        <v>46331.625</v>
+        <v>46331.95833333334</v>
       </c>
     </row>
     <row r="516">
@@ -28747,13 +28747,13 @@
       </c>
       <c r="J516" t="inlineStr"/>
       <c r="K516" s="1" t="n">
-        <v>46340.41666666666</v>
+        <v>46340.75</v>
       </c>
       <c r="L516" s="1" t="n">
-        <v>46340.45833333334</v>
+        <v>46340.79166666666</v>
       </c>
       <c r="M516" s="1" t="n">
-        <v>46341.20833333334</v>
+        <v>46341.54166666666</v>
       </c>
     </row>
     <row r="517">
@@ -29297,13 +29297,13 @@
         </is>
       </c>
       <c r="K526" s="1" t="n">
-        <v>46295.83333333334</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="L526" s="1" t="n">
-        <v>46295.91666666666</v>
+        <v>46295.9625</v>
       </c>
       <c r="M526" s="1" t="n">
-        <v>46296.91666666666</v>
+        <v>46297.375</v>
       </c>
     </row>
     <row r="527">
@@ -29407,13 +29407,13 @@
         </is>
       </c>
       <c r="K528" s="1" t="n">
-        <v>46305.33333333334</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="L528" s="1" t="n">
-        <v>46305.375</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="M528" s="1" t="n">
-        <v>46307.375</v>
+        <v>46307.83333333334</v>
       </c>
     </row>
     <row r="529">
@@ -29462,13 +29462,13 @@
         </is>
       </c>
       <c r="K529" s="1" t="n">
-        <v>46308.75</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="L529" s="1" t="n">
-        <v>46311.95833333334</v>
+        <v>46312.41666666666</v>
       </c>
       <c r="M529" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.41666666666</v>
       </c>
     </row>
     <row r="530">
@@ -39287,13 +39287,13 @@
         </is>
       </c>
       <c r="K708" s="1" t="n">
-        <v>46298.83333333334</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="L708" s="1" t="n">
-        <v>46298.89583333334</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="M708" s="1" t="n">
-        <v>46299.3125</v>
+        <v>46299.45833333334</v>
       </c>
     </row>
     <row r="709">
@@ -39342,13 +39342,13 @@
         </is>
       </c>
       <c r="K709" s="1" t="n">
-        <v>46299.625</v>
+        <v>46299.79166666666</v>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46299.64583333334</v>
+        <v>46300.08333333334</v>
       </c>
       <c r="M709" s="1" t="n">
-        <v>46300.25</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="710">
@@ -39397,13 +39397,13 @@
         </is>
       </c>
       <c r="K710" s="1" t="n">
-        <v>46305.66666666666</v>
+        <v>46306.41666666666</v>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46305.83333333334</v>
+        <v>46306.58333333334</v>
       </c>
       <c r="M710" s="1" t="n">
-        <v>46306.41666666666</v>
+        <v>46307.16666666666</v>
       </c>
     </row>
     <row r="711">
@@ -39452,13 +39452,13 @@
         </is>
       </c>
       <c r="K711" s="1" t="n">
-        <v>46308.1875</v>
+        <v>46308.9375</v>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46308.22916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="M711" s="1" t="n">
-        <v>46308.58333333334</v>
+        <v>46309.33333333334</v>
       </c>
     </row>
     <row r="712">
@@ -39507,13 +39507,13 @@
         </is>
       </c>
       <c r="K712" s="1" t="n">
-        <v>46308.70833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="M712" s="1" t="n">
-        <v>46309.79166666666</v>
+        <v>46310.54166666666</v>
       </c>
     </row>
     <row r="713">
@@ -39562,13 +39562,13 @@
         </is>
       </c>
       <c r="K713" s="1" t="n">
-        <v>46310</v>
+        <v>46310.75</v>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46310.04166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="M713" s="1" t="n">
-        <v>46310.54166666666</v>
+        <v>46311.29166666666</v>
       </c>
     </row>
     <row r="714">
@@ -39617,13 +39617,13 @@
         </is>
       </c>
       <c r="K714" s="1" t="n">
-        <v>46312.35416666666</v>
+        <v>46313.10416666666</v>
       </c>
       <c r="L714" s="1" t="n">
-        <v>46312.52083333334</v>
+        <v>46313.27083333334</v>
       </c>
       <c r="M714" s="1" t="n">
-        <v>46313.20833333334</v>
+        <v>46313.95833333334</v>
       </c>
     </row>
     <row r="715">
@@ -39672,13 +39672,13 @@
         </is>
       </c>
       <c r="K715" s="1" t="n">
-        <v>46320.79166666666</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="L715" s="1" t="n">
-        <v>46320.83333333334</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="M715" s="1" t="n">
-        <v>46321.5</v>
+        <v>46320.5</v>
       </c>
     </row>
     <row r="716">
@@ -39727,13 +39727,13 @@
         </is>
       </c>
       <c r="K716" s="1" t="n">
-        <v>46321.66666666666</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="L716" s="1" t="n">
-        <v>46321.72916666666</v>
+        <v>46320.72916666666</v>
       </c>
       <c r="M716" s="1" t="n">
-        <v>46321.97916666666</v>
+        <v>46320.97916666666</v>
       </c>
     </row>
     <row r="717">
@@ -39782,13 +39782,13 @@
         </is>
       </c>
       <c r="K717" s="1" t="n">
-        <v>46322.875</v>
+        <v>46321.875</v>
       </c>
       <c r="L717" s="1" t="n">
-        <v>46322.9375</v>
+        <v>46321.9375</v>
       </c>
       <c r="M717" s="1" t="n">
-        <v>46323.35416666666</v>
+        <v>46322.35416666666</v>
       </c>
     </row>
     <row r="718">
@@ -39837,13 +39837,13 @@
         </is>
       </c>
       <c r="K718" s="1" t="n">
-        <v>46323.625</v>
+        <v>46322.625</v>
       </c>
       <c r="L718" s="1" t="n">
-        <v>46323.64583333334</v>
+        <v>46322.64583333334</v>
       </c>
       <c r="M718" s="1" t="n">
-        <v>46324.25</v>
+        <v>46323.25</v>
       </c>
     </row>
     <row r="719">
@@ -39892,13 +39892,13 @@
         </is>
       </c>
       <c r="K719" s="1" t="n">
-        <v>46329.16666666666</v>
+        <v>46328.16666666666</v>
       </c>
       <c r="L719" s="1" t="n">
-        <v>46329.33333333334</v>
+        <v>46328.33333333334</v>
       </c>
       <c r="M719" s="1" t="n">
-        <v>46329.91666666666</v>
+        <v>46328.91666666666</v>
       </c>
     </row>
     <row r="720">
@@ -39947,13 +39947,13 @@
         </is>
       </c>
       <c r="K720" s="1" t="n">
-        <v>46331.5625</v>
+        <v>46330.5625</v>
       </c>
       <c r="L720" s="1" t="n">
-        <v>46331.60416666666</v>
+        <v>46330.60416666666</v>
       </c>
       <c r="M720" s="1" t="n">
-        <v>46331.95833333334</v>
+        <v>46330.95833333334</v>
       </c>
     </row>
     <row r="721">
@@ -40002,13 +40002,13 @@
         </is>
       </c>
       <c r="K721" s="1" t="n">
-        <v>46332.08333333334</v>
+        <v>46331.08333333334</v>
       </c>
       <c r="L721" s="1" t="n">
+        <v>46331.16666666666</v>
+      </c>
+      <c r="M721" s="1" t="n">
         <v>46332.16666666666</v>
-      </c>
-      <c r="M721" s="1" t="n">
-        <v>46333.16666666666</v>
       </c>
     </row>
     <row r="722">
@@ -40057,13 +40057,13 @@
         </is>
       </c>
       <c r="K722" s="1" t="n">
-        <v>46333.375</v>
+        <v>46332.375</v>
       </c>
       <c r="L722" s="1" t="n">
-        <v>46333.41666666666</v>
+        <v>46332.41666666666</v>
       </c>
       <c r="M722" s="1" t="n">
-        <v>46333.91666666666</v>
+        <v>46332.91666666666</v>
       </c>
     </row>
     <row r="723">
@@ -40112,13 +40112,13 @@
         </is>
       </c>
       <c r="K723" s="1" t="n">
-        <v>46335.72916666666</v>
+        <v>46334.72916666666</v>
       </c>
       <c r="L723" s="1" t="n">
-        <v>46335.89583333334</v>
+        <v>46334.89583333334</v>
       </c>
       <c r="M723" s="1" t="n">
-        <v>46336.58333333334</v>
+        <v>46335.58333333334</v>
       </c>
     </row>
     <row r="724">
@@ -40662,13 +40662,13 @@
         </is>
       </c>
       <c r="K733" s="1" t="n">
-        <v>46360.83541666667</v>
+        <v>46362.79166666666</v>
       </c>
       <c r="L733" s="1" t="n">
-        <v>46360.87708333333</v>
+        <v>46362.83333333334</v>
       </c>
       <c r="M733" s="1" t="n">
-        <v>46361.54375</v>
+        <v>46363.5</v>
       </c>
     </row>
     <row r="734">
@@ -40717,13 +40717,13 @@
         </is>
       </c>
       <c r="K734" s="1" t="n">
-        <v>46361.71041666667</v>
+        <v>46363.66666666666</v>
       </c>
       <c r="L734" s="1" t="n">
-        <v>46361.77291666667</v>
+        <v>46363.72916666666</v>
       </c>
       <c r="M734" s="1" t="n">
-        <v>46362.02291666667</v>
+        <v>46363.97916666666</v>
       </c>
     </row>
     <row r="735">
@@ -40772,13 +40772,13 @@
         </is>
       </c>
       <c r="K735" s="1" t="n">
-        <v>46362.91875</v>
+        <v>46364.875</v>
       </c>
       <c r="L735" s="1" t="n">
-        <v>46362.98125</v>
+        <v>46364.9375</v>
       </c>
       <c r="M735" s="1" t="n">
-        <v>46363.39791666667</v>
+        <v>46365.35416666666</v>
       </c>
     </row>
     <row r="736">
@@ -40827,13 +40827,13 @@
         </is>
       </c>
       <c r="K736" s="1" t="n">
-        <v>46363.66875</v>
+        <v>46365.625</v>
       </c>
       <c r="L736" s="1" t="n">
-        <v>46363.68958333333</v>
+        <v>46365.64583333334</v>
       </c>
       <c r="M736" s="1" t="n">
-        <v>46364.29375</v>
+        <v>46366.25</v>
       </c>
     </row>
     <row r="737">
@@ -40882,13 +40882,13 @@
         </is>
       </c>
       <c r="K737" s="1" t="n">
-        <v>46369.12708333333</v>
+        <v>46371.16666666666</v>
       </c>
       <c r="L737" s="1" t="n">
-        <v>46369.29375</v>
+        <v>46371.33333333334</v>
       </c>
       <c r="M737" s="1" t="n">
-        <v>46369.87708333333</v>
+        <v>46371.91666666666</v>
       </c>
     </row>
     <row r="738">
@@ -40937,13 +40937,13 @@
         </is>
       </c>
       <c r="K738" s="1" t="n">
-        <v>46371.525</v>
+        <v>46373.5625</v>
       </c>
       <c r="L738" s="1" t="n">
-        <v>46371.56666666667</v>
+        <v>46373.60416666666</v>
       </c>
       <c r="M738" s="1" t="n">
-        <v>46371.92083333333</v>
+        <v>46373.95833333334</v>
       </c>
     </row>
     <row r="739">
@@ -40992,13 +40992,13 @@
         </is>
       </c>
       <c r="K739" s="1" t="n">
-        <v>46372.04583333333</v>
+        <v>46374.08333333334</v>
       </c>
       <c r="L739" s="1" t="n">
-        <v>46372.12916666667</v>
+        <v>46374.16666666666</v>
       </c>
       <c r="M739" s="1" t="n">
-        <v>46373.12916666667</v>
+        <v>46375.16666666666</v>
       </c>
     </row>
     <row r="740">
@@ -41047,13 +41047,13 @@
         </is>
       </c>
       <c r="K740" s="1" t="n">
-        <v>46373.3375</v>
+        <v>46375.375</v>
       </c>
       <c r="L740" s="1" t="n">
-        <v>46373.37916666667</v>
+        <v>46375.41666666666</v>
       </c>
       <c r="M740" s="1" t="n">
-        <v>46373.87916666667</v>
+        <v>46375.91666666666</v>
       </c>
     </row>
     <row r="741">
@@ -41098,13 +41098,13 @@
       </c>
       <c r="J741" t="inlineStr"/>
       <c r="K741" s="1" t="n">
-        <v>46375.69166666667</v>
+        <v>46377.72916666666</v>
       </c>
       <c r="L741" s="1" t="n">
-        <v>46375.85833333333</v>
+        <v>46377.89583333334</v>
       </c>
       <c r="M741" s="1" t="n">
-        <v>46376.54583333333</v>
+        <v>46378.58333333334</v>
       </c>
     </row>
     <row r="742">
@@ -43410,7 +43410,7 @@
         <v>46299.0625</v>
       </c>
       <c r="M783" s="1" t="n">
-        <v>46299.45833333334</v>
+        <v>46299.33333333334</v>
       </c>
     </row>
     <row r="784">
@@ -43459,13 +43459,13 @@
         </is>
       </c>
       <c r="K784" s="1" t="n">
-        <v>46299.875</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="L784" s="1" t="n">
-        <v>46300.89583333334</v>
+        <v>46300.75</v>
       </c>
       <c r="M784" s="1" t="n">
-        <v>46301.25</v>
+        <v>46301.08333333334</v>
       </c>
     </row>
     <row r="785">
@@ -43514,13 +43514,13 @@
         </is>
       </c>
       <c r="K785" s="1" t="n">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="L785" s="1" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="L785" s="1" t="n">
-        <v>46306.375</v>
-      </c>
       <c r="M785" s="1" t="n">
-        <v>46307</v>
+        <v>46306.83333333334</v>
       </c>
     </row>
     <row r="786">
@@ -43569,13 +43569,13 @@
         </is>
       </c>
       <c r="K786" s="1" t="n">
-        <v>46308.66666666666</v>
+        <v>46308.5</v>
       </c>
       <c r="L786" s="1" t="n">
-        <v>46308.70833333334</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="M786" s="1" t="n">
-        <v>46308.95833333334</v>
+        <v>46308.79166666666</v>
       </c>
     </row>
     <row r="787">
@@ -43624,13 +43624,13 @@
         </is>
       </c>
       <c r="K787" s="1" t="n">
-        <v>46309.04166666666</v>
+        <v>46308.875</v>
       </c>
       <c r="L787" s="1" t="n">
-        <v>46309.16666666666</v>
+        <v>46309</v>
       </c>
       <c r="M787" s="1" t="n">
-        <v>46310.66666666666</v>
+        <v>46310.5</v>
       </c>
     </row>
     <row r="788">
@@ -43679,13 +43679,13 @@
         </is>
       </c>
       <c r="K788" s="1" t="n">
-        <v>46310.875</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="L788" s="1" t="n">
-        <v>46310.91666666666</v>
+        <v>46310.75</v>
       </c>
       <c r="M788" s="1" t="n">
-        <v>46311.33333333334</v>
+        <v>46311.16666666666</v>
       </c>
     </row>
     <row r="789">
@@ -43734,13 +43734,13 @@
         </is>
       </c>
       <c r="K789" s="1" t="n">
+        <v>46312.79166666666</v>
+      </c>
+      <c r="L789" s="1" t="n">
         <v>46312.95833333334</v>
       </c>
-      <c r="L789" s="1" t="n">
-        <v>46313.125</v>
-      </c>
       <c r="M789" s="1" t="n">
-        <v>46313.66666666666</v>
+        <v>46313.5</v>
       </c>
     </row>
     <row r="790">
@@ -43789,13 +43789,13 @@
         </is>
       </c>
       <c r="K790" s="1" t="n">
-        <v>46318.79166666666</v>
+        <v>46318.625</v>
       </c>
       <c r="L790" s="1" t="n">
-        <v>46318.83333333334</v>
+        <v>46318.66666666666</v>
       </c>
       <c r="M790" s="1" t="n">
-        <v>46319.91666666666</v>
+        <v>46319.75</v>
       </c>
     </row>
     <row r="791">
@@ -43844,13 +43844,13 @@
         </is>
       </c>
       <c r="K791" s="1" t="n">
-        <v>46320.04166666666</v>
+        <v>46319.875</v>
       </c>
       <c r="L791" s="1" t="n">
-        <v>46320.08333333334</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="M791" s="1" t="n">
-        <v>46320.33333333334</v>
+        <v>46320.16666666666</v>
       </c>
     </row>
     <row r="792">
@@ -43899,13 +43899,13 @@
         </is>
       </c>
       <c r="K792" s="1" t="n">
-        <v>46320.83333333334</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="L792" s="1" t="n">
-        <v>46320.91666666666</v>
+        <v>46320.75</v>
       </c>
       <c r="M792" s="1" t="n">
-        <v>46321.25</v>
+        <v>46321.08333333334</v>
       </c>
     </row>
     <row r="793">
@@ -43954,13 +43954,13 @@
         </is>
       </c>
       <c r="K793" s="1" t="n">
+        <v>46325.95833333334</v>
+      </c>
+      <c r="L793" s="1" t="n">
         <v>46326.125</v>
       </c>
-      <c r="L793" s="1" t="n">
-        <v>46326.29166666666</v>
-      </c>
       <c r="M793" s="1" t="n">
-        <v>46326.91666666666</v>
+        <v>46326.75</v>
       </c>
     </row>
     <row r="794">
@@ -44009,13 +44009,13 @@
         </is>
       </c>
       <c r="K794" s="1" t="n">
-        <v>46328.58333333334</v>
+        <v>46328.41666666666</v>
       </c>
       <c r="L794" s="1" t="n">
-        <v>46328.625</v>
+        <v>46328.45833333334</v>
       </c>
       <c r="M794" s="1" t="n">
-        <v>46328.875</v>
+        <v>46328.70833333334</v>
       </c>
     </row>
     <row r="795">
@@ -44064,13 +44064,13 @@
         </is>
       </c>
       <c r="K795" s="1" t="n">
-        <v>46329</v>
+        <v>46328.83333333334</v>
       </c>
       <c r="L795" s="1" t="n">
-        <v>46329.125</v>
+        <v>46328.95833333334</v>
       </c>
       <c r="M795" s="1" t="n">
-        <v>46330.625</v>
+        <v>46330.45833333334</v>
       </c>
     </row>
     <row r="796">
@@ -44119,13 +44119,13 @@
         </is>
       </c>
       <c r="K796" s="1" t="n">
-        <v>46330.83333333334</v>
+        <v>46330.66666666666</v>
       </c>
       <c r="L796" s="1" t="n">
-        <v>46330.875</v>
+        <v>46330.70833333334</v>
       </c>
       <c r="M796" s="1" t="n">
-        <v>46331.29166666666</v>
+        <v>46331.125</v>
       </c>
     </row>
     <row r="797">
@@ -44174,13 +44174,13 @@
         </is>
       </c>
       <c r="K797" s="1" t="n">
+        <v>46332.66666666666</v>
+      </c>
+      <c r="L797" s="1" t="n">
         <v>46332.83333333334</v>
       </c>
-      <c r="L797" s="1" t="n">
-        <v>46333</v>
-      </c>
       <c r="M797" s="1" t="n">
-        <v>46333.54166666666</v>
+        <v>46333.375</v>
       </c>
     </row>
     <row r="798">
@@ -44229,13 +44229,13 @@
         </is>
       </c>
       <c r="K798" s="1" t="n">
-        <v>46338.91666666666</v>
+        <v>46338.75</v>
       </c>
       <c r="L798" s="1" t="n">
-        <v>46338.95833333334</v>
+        <v>46338.79166666666</v>
       </c>
       <c r="M798" s="1" t="n">
-        <v>46340.04166666666</v>
+        <v>46339.875</v>
       </c>
     </row>
     <row r="799">
@@ -44284,13 +44284,13 @@
         </is>
       </c>
       <c r="K799" s="1" t="n">
-        <v>46340.20833333334</v>
+        <v>46340.04166666666</v>
       </c>
       <c r="L799" s="1" t="n">
-        <v>46340.25</v>
+        <v>46340.08333333334</v>
       </c>
       <c r="M799" s="1" t="n">
-        <v>46340.5</v>
+        <v>46340.33333333334</v>
       </c>
     </row>
     <row r="800">
@@ -44339,13 +44339,13 @@
         </is>
       </c>
       <c r="K800" s="1" t="n">
-        <v>46340.95833333334</v>
+        <v>46340.79166666666</v>
       </c>
       <c r="L800" s="1" t="n">
-        <v>46341.04166666666</v>
+        <v>46340.875</v>
       </c>
       <c r="M800" s="1" t="n">
-        <v>46341.375</v>
+        <v>46341.20833333334</v>
       </c>
     </row>
     <row r="801">
@@ -44394,13 +44394,13 @@
         </is>
       </c>
       <c r="K801" s="1" t="n">
+        <v>46346.20833333334</v>
+      </c>
+      <c r="L801" s="1" t="n">
         <v>46346.375</v>
       </c>
-      <c r="L801" s="1" t="n">
-        <v>46346.54166666666</v>
-      </c>
       <c r="M801" s="1" t="n">
-        <v>46347.16666666666</v>
+        <v>46347</v>
       </c>
     </row>
     <row r="802">
@@ -44449,13 +44449,13 @@
         </is>
       </c>
       <c r="K802" s="1" t="n">
-        <v>46348.95833333334</v>
+        <v>46348.79166666666</v>
       </c>
       <c r="L802" s="1" t="n">
-        <v>46349</v>
+        <v>46348.83333333334</v>
       </c>
       <c r="M802" s="1" t="n">
-        <v>46349.25</v>
+        <v>46349.08333333334</v>
       </c>
     </row>
     <row r="803">
@@ -44504,13 +44504,13 @@
         </is>
       </c>
       <c r="K803" s="1" t="n">
-        <v>46349.54166666666</v>
+        <v>46349.375</v>
       </c>
       <c r="L803" s="1" t="n">
-        <v>46349.66666666666</v>
+        <v>46349.5</v>
       </c>
       <c r="M803" s="1" t="n">
-        <v>46351.16666666666</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="804">
@@ -44559,13 +44559,13 @@
         </is>
       </c>
       <c r="K804" s="1" t="n">
-        <v>46351.375</v>
+        <v>46351.20833333334</v>
       </c>
       <c r="L804" s="1" t="n">
-        <v>46351.41666666666</v>
+        <v>46351.25</v>
       </c>
       <c r="M804" s="1" t="n">
-        <v>46351.83333333334</v>
+        <v>46351.66666666666</v>
       </c>
     </row>
     <row r="805">
@@ -44614,13 +44614,13 @@
         </is>
       </c>
       <c r="K805" s="1" t="n">
+        <v>46353.25</v>
+      </c>
+      <c r="L805" s="1" t="n">
         <v>46353.41666666666</v>
       </c>
-      <c r="L805" s="1" t="n">
-        <v>46353.58333333334</v>
-      </c>
       <c r="M805" s="1" t="n">
-        <v>46354.125</v>
+        <v>46353.95833333334</v>
       </c>
     </row>
     <row r="806">
@@ -44669,13 +44669,13 @@
         </is>
       </c>
       <c r="K806" s="1" t="n">
-        <v>46359.83333333334</v>
+        <v>46359.66666666666</v>
       </c>
       <c r="L806" s="1" t="n">
-        <v>46359.875</v>
+        <v>46359.70833333334</v>
       </c>
       <c r="M806" s="1" t="n">
-        <v>46360.95833333334</v>
+        <v>46360.79166666666</v>
       </c>
     </row>
     <row r="807">
@@ -44724,13 +44724,13 @@
         </is>
       </c>
       <c r="K807" s="1" t="n">
-        <v>46361.08333333334</v>
+        <v>46360.91666666666</v>
       </c>
       <c r="L807" s="1" t="n">
-        <v>46361.125</v>
+        <v>46360.95833333334</v>
       </c>
       <c r="M807" s="1" t="n">
-        <v>46361.375</v>
+        <v>46361.20833333334</v>
       </c>
     </row>
     <row r="808">
@@ -44779,13 +44779,13 @@
         </is>
       </c>
       <c r="K808" s="1" t="n">
-        <v>46361.83333333334</v>
+        <v>46361.66666666666</v>
       </c>
       <c r="L808" s="1" t="n">
-        <v>46361.91666666666</v>
+        <v>46361.75</v>
       </c>
       <c r="M808" s="1" t="n">
-        <v>46362.25</v>
+        <v>46362.08333333334</v>
       </c>
     </row>
     <row r="809">
@@ -44834,13 +44834,13 @@
         </is>
       </c>
       <c r="K809" s="1" t="n">
+        <v>46367.08333333334</v>
+      </c>
+      <c r="L809" s="1" t="n">
         <v>46367.25</v>
       </c>
-      <c r="L809" s="1" t="n">
-        <v>46367.41666666666</v>
-      </c>
       <c r="M809" s="1" t="n">
-        <v>46368.04166666666</v>
+        <v>46367.875</v>
       </c>
     </row>
     <row r="810">
@@ -44889,13 +44889,13 @@
         </is>
       </c>
       <c r="K810" s="1" t="n">
-        <v>46369.83333333334</v>
+        <v>46369.66666666666</v>
       </c>
       <c r="L810" s="1" t="n">
-        <v>46369.875</v>
+        <v>46369.70833333334</v>
       </c>
       <c r="M810" s="1" t="n">
-        <v>46370.125</v>
+        <v>46369.95833333334</v>
       </c>
     </row>
     <row r="811">
@@ -44944,13 +44944,13 @@
         </is>
       </c>
       <c r="K811" s="1" t="n">
-        <v>46370.41666666666</v>
+        <v>46370.25</v>
       </c>
       <c r="L811" s="1" t="n">
-        <v>46370.54166666666</v>
+        <v>46370.375</v>
       </c>
       <c r="M811" s="1" t="n">
-        <v>46372.04166666666</v>
+        <v>46371.875</v>
       </c>
     </row>
     <row r="812">
@@ -44999,13 +44999,13 @@
         </is>
       </c>
       <c r="K812" s="1" t="n">
-        <v>46372.25</v>
+        <v>46372.08333333334</v>
       </c>
       <c r="L812" s="1" t="n">
-        <v>46372.29166666666</v>
+        <v>46372.125</v>
       </c>
       <c r="M812" s="1" t="n">
-        <v>46372.70833333334</v>
+        <v>46372.54166666666</v>
       </c>
     </row>
     <row r="813">
@@ -45054,13 +45054,13 @@
         </is>
       </c>
       <c r="K813" s="1" t="n">
+        <v>46374.08333333334</v>
+      </c>
+      <c r="L813" s="1" t="n">
         <v>46374.25</v>
       </c>
-      <c r="L813" s="1" t="n">
-        <v>46374.41666666666</v>
-      </c>
       <c r="M813" s="1" t="n">
-        <v>46374.95833333334</v>
+        <v>46374.79166666666</v>
       </c>
     </row>
     <row r="814">
@@ -45109,13 +45109,13 @@
         </is>
       </c>
       <c r="K814" s="1" t="n">
-        <v>46378.125</v>
+        <v>46377.95833333334</v>
       </c>
       <c r="L814" s="1" t="n">
-        <v>46378.16666666666</v>
+        <v>46378</v>
       </c>
       <c r="M814" s="1" t="n">
-        <v>46379.25</v>
+        <v>46379.08333333334</v>
       </c>
     </row>
     <row r="815">
@@ -45164,13 +45164,13 @@
         </is>
       </c>
       <c r="K815" s="1" t="n">
-        <v>46379.375</v>
+        <v>46379.20833333334</v>
       </c>
       <c r="L815" s="1" t="n">
-        <v>46379.41666666666</v>
+        <v>46379.25</v>
       </c>
       <c r="M815" s="1" t="n">
-        <v>46379.66666666666</v>
+        <v>46379.5</v>
       </c>
     </row>
     <row r="816">
@@ -45219,13 +45219,13 @@
         </is>
       </c>
       <c r="K816" s="1" t="n">
-        <v>46380.125</v>
+        <v>46379.95833333334</v>
       </c>
       <c r="L816" s="1" t="n">
-        <v>46380.20833333334</v>
+        <v>46380.04166666666</v>
       </c>
       <c r="M816" s="1" t="n">
-        <v>46380.54166666666</v>
+        <v>46380.375</v>
       </c>
     </row>
     <row r="817">
@@ -45274,13 +45274,13 @@
         </is>
       </c>
       <c r="K817" s="1" t="n">
+        <v>46385.375</v>
+      </c>
+      <c r="L817" s="1" t="n">
         <v>46385.54166666666</v>
       </c>
-      <c r="L817" s="1" t="n">
-        <v>46385.70833333334</v>
-      </c>
       <c r="M817" s="1" t="n">
-        <v>46386.33333333334</v>
+        <v>46386.16666666666</v>
       </c>
     </row>
     <row r="818">
@@ -45329,13 +45329,13 @@
         </is>
       </c>
       <c r="K818" s="1" t="n">
-        <v>46388.125</v>
+        <v>46387.95833333334</v>
       </c>
       <c r="L818" s="1" t="n">
-        <v>46388.16666666666</v>
+        <v>46388</v>
       </c>
       <c r="M818" s="1" t="n">
-        <v>46388.41666666666</v>
+        <v>46388.25</v>
       </c>
     </row>
     <row r="819">
@@ -45384,13 +45384,13 @@
         </is>
       </c>
       <c r="K819" s="1" t="n">
-        <v>46388.70833333334</v>
+        <v>46388.54166666666</v>
       </c>
       <c r="L819" s="1" t="n">
-        <v>46388.83333333334</v>
+        <v>46388.66666666666</v>
       </c>
       <c r="M819" s="1" t="n">
-        <v>46390.33333333334</v>
+        <v>46390.16666666666</v>
       </c>
     </row>
     <row r="820">
@@ -45439,13 +45439,13 @@
         </is>
       </c>
       <c r="K820" s="1" t="n">
-        <v>46390.54166666666</v>
+        <v>46390.375</v>
       </c>
       <c r="L820" s="1" t="n">
-        <v>46390.58333333334</v>
+        <v>46390.41666666666</v>
       </c>
       <c r="M820" s="1" t="n">
-        <v>46391</v>
+        <v>46390.83333333334</v>
       </c>
     </row>
     <row r="821">
@@ -45490,13 +45490,13 @@
       </c>
       <c r="J821" t="inlineStr"/>
       <c r="K821" s="1" t="n">
+        <v>46392.41666666666</v>
+      </c>
+      <c r="L821" s="1" t="n">
         <v>46392.58333333334</v>
       </c>
-      <c r="L821" s="1" t="n">
-        <v>46392.75</v>
-      </c>
       <c r="M821" s="1" t="n">
-        <v>46393.29166666666</v>
+        <v>46393.125</v>
       </c>
     </row>
     <row r="822">
@@ -45551,7 +45551,7 @@
         <v>46299.4375</v>
       </c>
       <c r="M822" s="1" t="n">
-        <v>46299.6875</v>
+        <v>46300.16666666666</v>
       </c>
     </row>
     <row r="823">
@@ -45600,13 +45600,13 @@
         </is>
       </c>
       <c r="K823" s="1" t="n">
-        <v>46300.70833333334</v>
+        <v>46301.1875</v>
       </c>
       <c r="L823" s="1" t="n">
-        <v>46300.77083333334</v>
+        <v>46301.25</v>
       </c>
       <c r="M823" s="1" t="n">
-        <v>46301.1875</v>
+        <v>46301.66666666666</v>
       </c>
     </row>
     <row r="824">
@@ -45655,13 +45655,13 @@
         </is>
       </c>
       <c r="K824" s="1" t="n">
-        <v>46301.54166666666</v>
+        <v>46302.02083333334</v>
       </c>
       <c r="L824" s="1" t="n">
-        <v>46301.58333333334</v>
+        <v>46302.0625</v>
       </c>
       <c r="M824" s="1" t="n">
-        <v>46302.20833333334</v>
+        <v>46302.6875</v>
       </c>
     </row>
     <row r="825">
@@ -45710,13 +45710,13 @@
         </is>
       </c>
       <c r="K825" s="1" t="n">
-        <v>46303.39583333334</v>
+        <v>46303.875</v>
       </c>
       <c r="L825" s="1" t="n">
-        <v>46307</v>
+        <v>46307.47916666666</v>
       </c>
       <c r="M825" s="1" t="n">
-        <v>46308</v>
+        <v>46308.47916666666</v>
       </c>
     </row>
     <row r="826">
@@ -45765,13 +45765,13 @@
         </is>
       </c>
       <c r="K826" s="1" t="n">
-        <v>46312.20833333334</v>
+        <v>46312.6875</v>
       </c>
       <c r="L826" s="1" t="n">
-        <v>46313.33333333334</v>
+        <v>46313.8125</v>
       </c>
       <c r="M826" s="1" t="n">
-        <v>46313.83333333334</v>
+        <v>46314.3125</v>
       </c>
     </row>
     <row r="827">
@@ -45820,13 +45820,13 @@
         </is>
       </c>
       <c r="K827" s="1" t="n">
-        <v>46315.41666666666</v>
+        <v>46315.89583333334</v>
       </c>
       <c r="L827" s="1" t="n">
-        <v>46315.45833333334</v>
+        <v>46315.9375</v>
       </c>
       <c r="M827" s="1" t="n">
-        <v>46315.875</v>
+        <v>46316.35416666666</v>
       </c>
     </row>
     <row r="828">
@@ -45875,13 +45875,13 @@
         </is>
       </c>
       <c r="K828" s="1" t="n">
-        <v>46316.04166666666</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="L828" s="1" t="n">
-        <v>46316.16666666666</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="M828" s="1" t="n">
-        <v>46317.16666666666</v>
+        <v>46317.64583333334</v>
       </c>
     </row>
     <row r="829">
@@ -45930,13 +45930,13 @@
         </is>
       </c>
       <c r="K829" s="1" t="n">
-        <v>46317.41666666666</v>
+        <v>46317.89583333334</v>
       </c>
       <c r="L829" s="1" t="n">
-        <v>46317.45833333334</v>
+        <v>46317.9375</v>
       </c>
       <c r="M829" s="1" t="n">
-        <v>46317.875</v>
+        <v>46318.35416666666</v>
       </c>
     </row>
     <row r="830">
@@ -45985,13 +45985,13 @@
         </is>
       </c>
       <c r="K830" s="1" t="n">
-        <v>46319.375</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="L830" s="1" t="n">
-        <v>46320.5</v>
+        <v>46320.97916666666</v>
       </c>
       <c r="M830" s="1" t="n">
-        <v>46321</v>
+        <v>46321.47916666666</v>
       </c>
     </row>
     <row r="831">
@@ -46040,13 +46040,13 @@
         </is>
       </c>
       <c r="K831" s="1" t="n">
-        <v>46327.10416666666</v>
+        <v>46327.58333333334</v>
       </c>
       <c r="L831" s="1" t="n">
-        <v>46327.16666666666</v>
+        <v>46327.64583333334</v>
       </c>
       <c r="M831" s="1" t="n">
-        <v>46327.41666666666</v>
+        <v>46327.89583333334</v>
       </c>
     </row>
     <row r="832">
@@ -46095,13 +46095,13 @@
         </is>
       </c>
       <c r="K832" s="1" t="n">
-        <v>46328.375</v>
+        <v>46328.85416666666</v>
       </c>
       <c r="L832" s="1" t="n">
-        <v>46328.4375</v>
+        <v>46328.91666666666</v>
       </c>
       <c r="M832" s="1" t="n">
-        <v>46328.85416666666</v>
+        <v>46329.33333333334</v>
       </c>
     </row>
     <row r="833">
@@ -46150,13 +46150,13 @@
         </is>
       </c>
       <c r="K833" s="1" t="n">
-        <v>46329.20833333334</v>
+        <v>46329.6875</v>
       </c>
       <c r="L833" s="1" t="n">
-        <v>46329.25</v>
+        <v>46329.72916666666</v>
       </c>
       <c r="M833" s="1" t="n">
-        <v>46329.875</v>
+        <v>46330.35416666666</v>
       </c>
     </row>
     <row r="834">
@@ -46205,13 +46205,13 @@
         </is>
       </c>
       <c r="K834" s="1" t="n">
-        <v>46330.95833333334</v>
+        <v>46331.4375</v>
       </c>
       <c r="L834" s="1" t="n">
-        <v>46331.125</v>
+        <v>46331.60416666666</v>
       </c>
       <c r="M834" s="1" t="n">
-        <v>46332.125</v>
+        <v>46332.60416666666</v>
       </c>
     </row>
     <row r="835">
@@ -46260,13 +46260,13 @@
         </is>
       </c>
       <c r="K835" s="1" t="n">
-        <v>46336.33333333334</v>
+        <v>46336.8125</v>
       </c>
       <c r="L835" s="1" t="n">
-        <v>46336.45833333334</v>
+        <v>46336.9375</v>
       </c>
       <c r="M835" s="1" t="n">
-        <v>46336.95833333334</v>
+        <v>46337.4375</v>
       </c>
     </row>
     <row r="836">
@@ -46315,13 +46315,13 @@
         </is>
       </c>
       <c r="K836" s="1" t="n">
-        <v>46338.54166666666</v>
+        <v>46339.02083333334</v>
       </c>
       <c r="L836" s="1" t="n">
-        <v>46338.58333333334</v>
+        <v>46339.0625</v>
       </c>
       <c r="M836" s="1" t="n">
-        <v>46339</v>
+        <v>46339.47916666666</v>
       </c>
     </row>
     <row r="837">
@@ -46370,13 +46370,13 @@
         </is>
       </c>
       <c r="K837" s="1" t="n">
-        <v>46339.16666666666</v>
+        <v>46339.64583333334</v>
       </c>
       <c r="L837" s="1" t="n">
-        <v>46339.29166666666</v>
+        <v>46339.77083333334</v>
       </c>
       <c r="M837" s="1" t="n">
-        <v>46340.29166666666</v>
+        <v>46340.77083333334</v>
       </c>
     </row>
     <row r="838">
@@ -46425,13 +46425,13 @@
         </is>
       </c>
       <c r="K838" s="1" t="n">
-        <v>46340.54166666666</v>
+        <v>46341.02083333334</v>
       </c>
       <c r="L838" s="1" t="n">
-        <v>46340.58333333334</v>
+        <v>46341.0625</v>
       </c>
       <c r="M838" s="1" t="n">
-        <v>46341</v>
+        <v>46341.47916666666</v>
       </c>
     </row>
     <row r="839">
@@ -46480,13 +46480,13 @@
         </is>
       </c>
       <c r="K839" s="1" t="n">
-        <v>46342.5</v>
+        <v>46342.97916666666</v>
       </c>
       <c r="L839" s="1" t="n">
-        <v>46342.625</v>
+        <v>46343.10416666666</v>
       </c>
       <c r="M839" s="1" t="n">
-        <v>46343.125</v>
+        <v>46343.60416666666</v>
       </c>
     </row>
     <row r="840">
@@ -46535,13 +46535,13 @@
         </is>
       </c>
       <c r="K840" s="1" t="n">
-        <v>46348.14583333334</v>
+        <v>46348.625</v>
       </c>
       <c r="L840" s="1" t="n">
-        <v>46348.20833333334</v>
+        <v>46348.6875</v>
       </c>
       <c r="M840" s="1" t="n">
-        <v>46348.45833333334</v>
+        <v>46348.9375</v>
       </c>
     </row>
     <row r="841">
@@ -46590,13 +46590,13 @@
         </is>
       </c>
       <c r="K841" s="1" t="n">
-        <v>46349.40416666667</v>
+        <v>46349.88333333333</v>
       </c>
       <c r="L841" s="1" t="n">
-        <v>46349.46666666667</v>
+        <v>46349.94583333333</v>
       </c>
       <c r="M841" s="1" t="n">
-        <v>46349.88333333333</v>
+        <v>46350.3625</v>
       </c>
     </row>
     <row r="842">
@@ -46645,13 +46645,13 @@
         </is>
       </c>
       <c r="K842" s="1" t="n">
-        <v>46350.225</v>
+        <v>46350.70416666667</v>
       </c>
       <c r="L842" s="1" t="n">
-        <v>46350.26666666667</v>
+        <v>46350.74583333333</v>
       </c>
       <c r="M842" s="1" t="n">
-        <v>46350.89166666667</v>
+        <v>46351.37083333333</v>
       </c>
     </row>
     <row r="843">
@@ -46700,13 +46700,13 @@
         </is>
       </c>
       <c r="K843" s="1" t="n">
-        <v>46351.975</v>
+        <v>46352.45416666667</v>
       </c>
       <c r="L843" s="1" t="n">
-        <v>46352.14166666667</v>
+        <v>46352.62083333333</v>
       </c>
       <c r="M843" s="1" t="n">
-        <v>46353.14166666667</v>
+        <v>46353.62083333333</v>
       </c>
     </row>
     <row r="844">
@@ -46755,13 +46755,13 @@
         </is>
       </c>
       <c r="K844" s="1" t="n">
-        <v>46357.35</v>
+        <v>46357.82916666667</v>
       </c>
       <c r="L844" s="1" t="n">
-        <v>46357.475</v>
+        <v>46357.95416666667</v>
       </c>
       <c r="M844" s="1" t="n">
-        <v>46357.975</v>
+        <v>46358.45416666667</v>
       </c>
     </row>
     <row r="845">
@@ -46810,13 +46810,13 @@
         </is>
       </c>
       <c r="K845" s="1" t="n">
-        <v>46359.55833333333</v>
+        <v>46360.0375</v>
       </c>
       <c r="L845" s="1" t="n">
-        <v>46359.6</v>
+        <v>46360.07916666667</v>
       </c>
       <c r="M845" s="1" t="n">
-        <v>46360.01666666667</v>
+        <v>46360.49583333333</v>
       </c>
     </row>
     <row r="846">
@@ -46865,13 +46865,13 @@
         </is>
       </c>
       <c r="K846" s="1" t="n">
-        <v>46360.18333333333</v>
+        <v>46360.6625</v>
       </c>
       <c r="L846" s="1" t="n">
-        <v>46360.30833333333</v>
+        <v>46360.7875</v>
       </c>
       <c r="M846" s="1" t="n">
-        <v>46361.30833333333</v>
+        <v>46361.7875</v>
       </c>
     </row>
     <row r="847">
@@ -46920,13 +46920,13 @@
         </is>
       </c>
       <c r="K847" s="1" t="n">
-        <v>46361.55833333333</v>
+        <v>46362.0375</v>
       </c>
       <c r="L847" s="1" t="n">
-        <v>46361.6</v>
+        <v>46362.07916666667</v>
       </c>
       <c r="M847" s="1" t="n">
-        <v>46362.01666666667</v>
+        <v>46362.49583333333</v>
       </c>
     </row>
     <row r="848">
@@ -46975,13 +46975,13 @@
         </is>
       </c>
       <c r="K848" s="1" t="n">
-        <v>46363.51666666667</v>
+        <v>46363.99583333333</v>
       </c>
       <c r="L848" s="1" t="n">
-        <v>46363.64166666667</v>
+        <v>46364.12083333333</v>
       </c>
       <c r="M848" s="1" t="n">
-        <v>46364.14166666667</v>
+        <v>46364.62083333333</v>
       </c>
     </row>
     <row r="849">
@@ -47030,13 +47030,13 @@
         </is>
       </c>
       <c r="K849" s="1" t="n">
-        <v>46369.1625</v>
+        <v>46369.64166666667</v>
       </c>
       <c r="L849" s="1" t="n">
-        <v>46369.225</v>
+        <v>46369.70416666667</v>
       </c>
       <c r="M849" s="1" t="n">
-        <v>46369.475</v>
+        <v>46369.95416666667</v>
       </c>
     </row>
     <row r="850">
@@ -47085,13 +47085,13 @@
         </is>
       </c>
       <c r="K850" s="1" t="n">
-        <v>46370.42083333333</v>
+        <v>46370.9</v>
       </c>
       <c r="L850" s="1" t="n">
-        <v>46370.48333333333</v>
+        <v>46370.9625</v>
       </c>
       <c r="M850" s="1" t="n">
-        <v>46370.9</v>
+        <v>46371.37916666667</v>
       </c>
     </row>
     <row r="851">
@@ -47140,13 +47140,13 @@
         </is>
       </c>
       <c r="K851" s="1" t="n">
-        <v>46371.24166666667</v>
+        <v>46371.72083333333</v>
       </c>
       <c r="L851" s="1" t="n">
-        <v>46371.28333333333</v>
+        <v>46371.7625</v>
       </c>
       <c r="M851" s="1" t="n">
-        <v>46371.90833333333</v>
+        <v>46372.3875</v>
       </c>
     </row>
     <row r="852">
@@ -47195,13 +47195,13 @@
         </is>
       </c>
       <c r="K852" s="1" t="n">
-        <v>46372.99166666667</v>
+        <v>46373.47083333333</v>
       </c>
       <c r="L852" s="1" t="n">
-        <v>46373.15833333333</v>
+        <v>46373.6375</v>
       </c>
       <c r="M852" s="1" t="n">
-        <v>46374.15833333333</v>
+        <v>46374.6375</v>
       </c>
     </row>
     <row r="853">
@@ -47250,13 +47250,13 @@
         </is>
       </c>
       <c r="K853" s="1" t="n">
-        <v>46378.36666666667</v>
+        <v>46378.84583333333</v>
       </c>
       <c r="L853" s="1" t="n">
-        <v>46378.49166666667</v>
+        <v>46378.97083333333</v>
       </c>
       <c r="M853" s="1" t="n">
-        <v>46378.99166666667</v>
+        <v>46379.47083333333</v>
       </c>
     </row>
     <row r="854">
@@ -47305,13 +47305,13 @@
         </is>
       </c>
       <c r="K854" s="1" t="n">
-        <v>46380.575</v>
+        <v>46381.05416666667</v>
       </c>
       <c r="L854" s="1" t="n">
-        <v>46380.61666666667</v>
+        <v>46381.09583333333</v>
       </c>
       <c r="M854" s="1" t="n">
-        <v>46381.03333333333</v>
+        <v>46381.5125</v>
       </c>
     </row>
     <row r="855">
@@ -47360,13 +47360,13 @@
         </is>
       </c>
       <c r="K855" s="1" t="n">
-        <v>46381.2</v>
+        <v>46381.67916666667</v>
       </c>
       <c r="L855" s="1" t="n">
-        <v>46381.325</v>
+        <v>46381.80416666667</v>
       </c>
       <c r="M855" s="1" t="n">
-        <v>46382.325</v>
+        <v>46382.80416666667</v>
       </c>
     </row>
     <row r="856">
@@ -47415,13 +47415,13 @@
         </is>
       </c>
       <c r="K856" s="1" t="n">
-        <v>46382.575</v>
+        <v>46383.05416666667</v>
       </c>
       <c r="L856" s="1" t="n">
-        <v>46382.61666666667</v>
+        <v>46383.09583333333</v>
       </c>
       <c r="M856" s="1" t="n">
-        <v>46383.03333333333</v>
+        <v>46383.5125</v>
       </c>
     </row>
     <row r="857">
@@ -47466,13 +47466,13 @@
       </c>
       <c r="J857" t="inlineStr"/>
       <c r="K857" s="1" t="n">
-        <v>46384.53333333333</v>
+        <v>46385.0125</v>
       </c>
       <c r="L857" s="1" t="n">
-        <v>46384.65833333333</v>
+        <v>46385.1375</v>
       </c>
       <c r="M857" s="1" t="n">
-        <v>46385.15833333333</v>
+        <v>46385.6375</v>
       </c>
     </row>
     <row r="858">
@@ -47686,13 +47686,13 @@
         </is>
       </c>
       <c r="K861" s="1" t="n">
-        <v>46299.33333333334</v>
+        <v>46301.95833333334</v>
       </c>
       <c r="L861" s="1" t="n">
-        <v>46301.5</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="M861" s="1" t="n">
-        <v>46302.33333333334</v>
+        <v>46303.91666666666</v>
       </c>
     </row>
     <row r="862">
@@ -47741,13 +47741,13 @@
         </is>
       </c>
       <c r="K862" s="1" t="n">
-        <v>46303.0625</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="L862" s="1" t="n">
-        <v>46303.14583333334</v>
+        <v>46304.625</v>
       </c>
       <c r="M862" s="1" t="n">
-        <v>46304.04166666666</v>
+        <v>46305.375</v>
       </c>
     </row>
     <row r="863">
@@ -47796,13 +47796,13 @@
         </is>
       </c>
       <c r="K863" s="1" t="n">
-        <v>46307.77083333334</v>
+        <v>46309</v>
       </c>
       <c r="L863" s="1" t="n">
-        <v>46307.8125</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="M863" s="1" t="n">
-        <v>46308.47916666666</v>
+        <v>46309.70833333334</v>
       </c>
     </row>
     <row r="864">
@@ -47851,13 +47851,13 @@
         </is>
       </c>
       <c r="K864" s="1" t="n">
-        <v>46314.54166666666</v>
+        <v>46315.77083333334</v>
       </c>
       <c r="L864" s="1" t="n">
-        <v>46314.75</v>
+        <v>46315.97916666666</v>
       </c>
       <c r="M864" s="1" t="n">
-        <v>46315.41666666666</v>
+        <v>46316.64583333334</v>
       </c>
     </row>
     <row r="865">
@@ -47906,13 +47906,13 @@
         </is>
       </c>
       <c r="K865" s="1" t="n">
-        <v>46316.8125</v>
+        <v>46318.04166666666</v>
       </c>
       <c r="L865" s="1" t="n">
-        <v>46316.85416666666</v>
+        <v>46318.08333333334</v>
       </c>
       <c r="M865" s="1" t="n">
-        <v>46317.85416666666</v>
+        <v>46319.08333333334</v>
       </c>
     </row>
     <row r="866">
@@ -47961,13 +47961,13 @@
         </is>
       </c>
       <c r="K866" s="1" t="n">
-        <v>46318.14583333334</v>
+        <v>46319.375</v>
       </c>
       <c r="L866" s="1" t="n">
-        <v>46318.1875</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="M866" s="1" t="n">
-        <v>46318.8125</v>
+        <v>46320.04166666666</v>
       </c>
     </row>
     <row r="867">
@@ -48016,13 +48016,13 @@
         </is>
       </c>
       <c r="K867" s="1" t="n">
-        <v>46320.3125</v>
+        <v>46321.54166666666</v>
       </c>
       <c r="L867" s="1" t="n">
-        <v>46320.52083333334</v>
+        <v>46321.75</v>
       </c>
       <c r="M867" s="1" t="n">
-        <v>46321.1875</v>
+        <v>46322.41666666666</v>
       </c>
     </row>
     <row r="868">
@@ -48071,13 +48071,13 @@
         </is>
       </c>
       <c r="K868" s="1" t="n">
-        <v>46328.1875</v>
+        <v>46329.41666666666</v>
       </c>
       <c r="L868" s="1" t="n">
-        <v>46328.27083333334</v>
+        <v>46329.5</v>
       </c>
       <c r="M868" s="1" t="n">
-        <v>46329.10416666666</v>
+        <v>46330.33333333334</v>
       </c>
     </row>
     <row r="869">
@@ -48126,13 +48126,13 @@
         </is>
       </c>
       <c r="K869" s="1" t="n">
-        <v>46330.1875</v>
+        <v>46331.41666666666</v>
       </c>
       <c r="L869" s="1" t="n">
-        <v>46330.27083333334</v>
+        <v>46331.5</v>
       </c>
       <c r="M869" s="1" t="n">
-        <v>46330.77083333334</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="870">
@@ -48181,13 +48181,13 @@
         </is>
       </c>
       <c r="K870" s="1" t="n">
-        <v>46334.77083333334</v>
+        <v>46336</v>
       </c>
       <c r="L870" s="1" t="n">
-        <v>46334.8125</v>
+        <v>46336.04166666666</v>
       </c>
       <c r="M870" s="1" t="n">
-        <v>46335.47916666666</v>
+        <v>46336.70833333334</v>
       </c>
     </row>
     <row r="871">
@@ -48236,13 +48236,13 @@
         </is>
       </c>
       <c r="K871" s="1" t="n">
-        <v>46341.89583333334</v>
+        <v>46343.125</v>
       </c>
       <c r="L871" s="1" t="n">
-        <v>46342.10416666666</v>
+        <v>46343.33333333334</v>
       </c>
       <c r="M871" s="1" t="n">
-        <v>46342.77083333334</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="872">
@@ -48291,13 +48291,13 @@
         </is>
       </c>
       <c r="K872" s="1" t="n">
-        <v>46344.22916666666</v>
+        <v>46345.45833333334</v>
       </c>
       <c r="L872" s="1" t="n">
-        <v>46344.27083333334</v>
+        <v>46345.5</v>
       </c>
       <c r="M872" s="1" t="n">
-        <v>46345.27083333334</v>
+        <v>46346.5</v>
       </c>
     </row>
     <row r="873">
@@ -48346,13 +48346,13 @@
         </is>
       </c>
       <c r="K873" s="1" t="n">
-        <v>46345.89583333334</v>
+        <v>46347.125</v>
       </c>
       <c r="L873" s="1" t="n">
-        <v>46345.9375</v>
+        <v>46347.16666666666</v>
       </c>
       <c r="M873" s="1" t="n">
-        <v>46346.5625</v>
+        <v>46347.79166666666</v>
       </c>
     </row>
     <row r="874">
@@ -48401,13 +48401,13 @@
         </is>
       </c>
       <c r="K874" s="1" t="n">
-        <v>46348.0625</v>
+        <v>46349.29166666666</v>
       </c>
       <c r="L874" s="1" t="n">
-        <v>46348.27083333334</v>
+        <v>46349.5</v>
       </c>
       <c r="M874" s="1" t="n">
-        <v>46348.9375</v>
+        <v>46350.16666666666</v>
       </c>
     </row>
     <row r="875">
@@ -48456,13 +48456,13 @@
         </is>
       </c>
       <c r="K875" s="1" t="n">
-        <v>46355.9375</v>
+        <v>46357.16666666666</v>
       </c>
       <c r="L875" s="1" t="n">
-        <v>46356.02083333334</v>
+        <v>46357.25</v>
       </c>
       <c r="M875" s="1" t="n">
-        <v>46356.85416666666</v>
+        <v>46358.08333333334</v>
       </c>
     </row>
     <row r="876">
@@ -48511,13 +48511,13 @@
         </is>
       </c>
       <c r="K876" s="1" t="n">
-        <v>46357.9375</v>
+        <v>46359.16666666666</v>
       </c>
       <c r="L876" s="1" t="n">
-        <v>46358.02083333334</v>
+        <v>46359.25</v>
       </c>
       <c r="M876" s="1" t="n">
-        <v>46358.52083333334</v>
+        <v>46359.75</v>
       </c>
     </row>
     <row r="877">
@@ -48566,13 +48566,13 @@
         </is>
       </c>
       <c r="K877" s="1" t="n">
-        <v>46362.52083333334</v>
+        <v>46363.75</v>
       </c>
       <c r="L877" s="1" t="n">
-        <v>46362.5625</v>
+        <v>46363.79166666666</v>
       </c>
       <c r="M877" s="1" t="n">
-        <v>46363.22916666666</v>
+        <v>46364.45833333334</v>
       </c>
     </row>
     <row r="878">
@@ -48621,13 +48621,13 @@
         </is>
       </c>
       <c r="K878" s="1" t="n">
-        <v>46369.64583333334</v>
+        <v>46370.875</v>
       </c>
       <c r="L878" s="1" t="n">
-        <v>46369.85416666666</v>
+        <v>46371.08333333334</v>
       </c>
       <c r="M878" s="1" t="n">
-        <v>46370.52083333334</v>
+        <v>46371.75</v>
       </c>
     </row>
     <row r="879">
@@ -48676,13 +48676,13 @@
         </is>
       </c>
       <c r="K879" s="1" t="n">
-        <v>46372.22916666666</v>
+        <v>46373.45833333334</v>
       </c>
       <c r="L879" s="1" t="n">
-        <v>46372.27083333334</v>
+        <v>46373.5</v>
       </c>
       <c r="M879" s="1" t="n">
-        <v>46373.27083333334</v>
+        <v>46374.5</v>
       </c>
     </row>
     <row r="880">
@@ -48731,13 +48731,13 @@
         </is>
       </c>
       <c r="K880" s="1" t="n">
-        <v>46373.89583333334</v>
+        <v>46375.125</v>
       </c>
       <c r="L880" s="1" t="n">
-        <v>46373.9375</v>
+        <v>46375.16666666666</v>
       </c>
       <c r="M880" s="1" t="n">
-        <v>46374.5625</v>
+        <v>46375.79166666666</v>
       </c>
     </row>
     <row r="881">
@@ -48786,13 +48786,13 @@
         </is>
       </c>
       <c r="K881" s="1" t="n">
-        <v>46376.0625</v>
+        <v>46377.29166666666</v>
       </c>
       <c r="L881" s="1" t="n">
-        <v>46376.27083333334</v>
+        <v>46377.5</v>
       </c>
       <c r="M881" s="1" t="n">
-        <v>46376.9375</v>
+        <v>46378.16666666666</v>
       </c>
     </row>
     <row r="882">
@@ -48841,13 +48841,13 @@
         </is>
       </c>
       <c r="K882" s="1" t="n">
-        <v>46383.9375</v>
+        <v>46385.16666666666</v>
       </c>
       <c r="L882" s="1" t="n">
-        <v>46384.02083333334</v>
+        <v>46385.25</v>
       </c>
       <c r="M882" s="1" t="n">
-        <v>46384.85416666666</v>
+        <v>46386.08333333334</v>
       </c>
     </row>
     <row r="883">
@@ -48896,13 +48896,13 @@
         </is>
       </c>
       <c r="K883" s="1" t="n">
-        <v>46385.9375</v>
+        <v>46387.16666666666</v>
       </c>
       <c r="L883" s="1" t="n">
-        <v>46386.02083333334</v>
+        <v>46387.25</v>
       </c>
       <c r="M883" s="1" t="n">
-        <v>46386.52083333334</v>
+        <v>46387.75</v>
       </c>
     </row>
     <row r="884">
@@ -48951,13 +48951,13 @@
         </is>
       </c>
       <c r="K884" s="1" t="n">
-        <v>46390.52083333334</v>
+        <v>46391.75</v>
       </c>
       <c r="L884" s="1" t="n">
-        <v>46390.5625</v>
+        <v>46391.79166666666</v>
       </c>
       <c r="M884" s="1" t="n">
-        <v>46391.22916666666</v>
+        <v>46392.45833333334</v>
       </c>
     </row>
     <row r="885">
@@ -49002,13 +49002,13 @@
       </c>
       <c r="J885" t="inlineStr"/>
       <c r="K885" s="1" t="n">
-        <v>46397.64583333334</v>
+        <v>46398.875</v>
       </c>
       <c r="L885" s="1" t="n">
-        <v>46397.85416666666</v>
+        <v>46399.08333333334</v>
       </c>
       <c r="M885" s="1" t="n">
-        <v>46398.52083333334</v>
+        <v>46399.75</v>
       </c>
     </row>
     <row r="886">
@@ -51033,7 +51033,7 @@
         </is>
       </c>
       <c r="K922" s="1" t="n">
-        <v>46294.35416666666</v>
+        <v>46295.375</v>
       </c>
       <c r="L922" s="1" t="n">
         <v>46295.45833333334</v>
@@ -51143,13 +51143,13 @@
         </is>
       </c>
       <c r="K924" s="1" t="n">
-        <v>46300.8125</v>
+        <v>46300.83333333334</v>
       </c>
       <c r="L924" s="1" t="n">
-        <v>46300.85416666666</v>
+        <v>46300.875</v>
       </c>
       <c r="M924" s="1" t="n">
-        <v>46301.3125</v>
+        <v>46301.33333333334</v>
       </c>
     </row>
     <row r="925">
@@ -51198,13 +51198,13 @@
         </is>
       </c>
       <c r="K925" s="1" t="n">
-        <v>46303.47916666666</v>
+        <v>46303.5</v>
       </c>
       <c r="L925" s="1" t="n">
-        <v>46303.64583333334</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="M925" s="1" t="n">
-        <v>46304.10416666666</v>
+        <v>46304.125</v>
       </c>
     </row>
     <row r="926">
@@ -51253,13 +51253,13 @@
         </is>
       </c>
       <c r="K926" s="1" t="n">
-        <v>46305.6875</v>
+        <v>46305.70833333334</v>
       </c>
       <c r="L926" s="1" t="n">
-        <v>46305.72916666666</v>
+        <v>46305.75</v>
       </c>
       <c r="M926" s="1" t="n">
-        <v>46305.97916666666</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="927">
@@ -51308,13 +51308,13 @@
         </is>
       </c>
       <c r="K927" s="1" t="n">
-        <v>46306.14583333334</v>
+        <v>46306.16666666666</v>
       </c>
       <c r="L927" s="1" t="n">
-        <v>46306.27083333334</v>
+        <v>46306.29166666666</v>
       </c>
       <c r="M927" s="1" t="n">
-        <v>46307.77083333334</v>
+        <v>46307.79166666666</v>
       </c>
     </row>
     <row r="928">
@@ -51363,13 +51363,13 @@
         </is>
       </c>
       <c r="K928" s="1" t="n">
-        <v>46307.9375</v>
+        <v>46307.95833333334</v>
       </c>
       <c r="L928" s="1" t="n">
-        <v>46307.97916666666</v>
+        <v>46308</v>
       </c>
       <c r="M928" s="1" t="n">
-        <v>46308.22916666666</v>
+        <v>46308.25</v>
       </c>
     </row>
     <row r="929">
@@ -51418,13 +51418,13 @@
         </is>
       </c>
       <c r="K929" s="1" t="n">
-        <v>46311.95833333334</v>
+        <v>46311.97916666666</v>
       </c>
       <c r="L929" s="1" t="n">
-        <v>46312.02083333334</v>
+        <v>46312.04166666666</v>
       </c>
       <c r="M929" s="1" t="n">
-        <v>46312.47916666666</v>
+        <v>46312.5</v>
       </c>
     </row>
     <row r="930">
@@ -51473,13 +51473,13 @@
         </is>
       </c>
       <c r="K930" s="1" t="n">
-        <v>46313.27083333334</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="L930" s="1" t="n">
-        <v>46313.3125</v>
+        <v>46313.33333333334</v>
       </c>
       <c r="M930" s="1" t="n">
-        <v>46313.89583333334</v>
+        <v>46313.91666666666</v>
       </c>
     </row>
     <row r="931">
@@ -51528,13 +51528,13 @@
         </is>
       </c>
       <c r="K931" s="1" t="n">
-        <v>46316.27083333334</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="L931" s="1" t="n">
-        <v>46316.3125</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="M931" s="1" t="n">
-        <v>46317.02083333334</v>
+        <v>46317.04166666666</v>
       </c>
     </row>
     <row r="932">
@@ -51583,13 +51583,13 @@
         </is>
       </c>
       <c r="K932" s="1" t="n">
-        <v>46317.3125</v>
+        <v>46317.33333333334</v>
       </c>
       <c r="L932" s="1" t="n">
-        <v>46317.375</v>
+        <v>46317.39583333334</v>
       </c>
       <c r="M932" s="1" t="n">
-        <v>46317.64583333334</v>
+        <v>46317.66666666666</v>
       </c>
     </row>
     <row r="933">
@@ -51638,13 +51638,13 @@
         </is>
       </c>
       <c r="K933" s="1" t="n">
-        <v>46320.5625</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="L933" s="1" t="n">
-        <v>46320.60416666666</v>
+        <v>46320.625</v>
       </c>
       <c r="M933" s="1" t="n">
-        <v>46321.0625</v>
+        <v>46321.08333333334</v>
       </c>
     </row>
     <row r="934">
@@ -51693,13 +51693,13 @@
         </is>
       </c>
       <c r="K934" s="1" t="n">
-        <v>46323.27083333334</v>
+        <v>46323.29166666666</v>
       </c>
       <c r="L934" s="1" t="n">
-        <v>46323.4375</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M934" s="1" t="n">
-        <v>46323.89583333334</v>
+        <v>46323.91666666666</v>
       </c>
     </row>
     <row r="935">
@@ -51748,13 +51748,13 @@
         </is>
       </c>
       <c r="K935" s="1" t="n">
-        <v>46325.5625</v>
+        <v>46325.58333333334</v>
       </c>
       <c r="L935" s="1" t="n">
-        <v>46325.60416666666</v>
+        <v>46325.625</v>
       </c>
       <c r="M935" s="1" t="n">
-        <v>46325.85416666666</v>
+        <v>46325.875</v>
       </c>
     </row>
     <row r="936">
@@ -51803,13 +51803,13 @@
         </is>
       </c>
       <c r="K936" s="1" t="n">
-        <v>46326.02083333334</v>
+        <v>46326.04166666666</v>
       </c>
       <c r="L936" s="1" t="n">
-        <v>46326.14583333334</v>
+        <v>46326.16666666666</v>
       </c>
       <c r="M936" s="1" t="n">
-        <v>46327.64583333334</v>
+        <v>46327.66666666666</v>
       </c>
     </row>
     <row r="937">
@@ -51858,13 +51858,13 @@
         </is>
       </c>
       <c r="K937" s="1" t="n">
-        <v>46327.85416666666</v>
+        <v>46327.875</v>
       </c>
       <c r="L937" s="1" t="n">
-        <v>46327.89583333334</v>
+        <v>46327.91666666666</v>
       </c>
       <c r="M937" s="1" t="n">
-        <v>46328.14583333334</v>
+        <v>46328.16666666666</v>
       </c>
     </row>
     <row r="938">
@@ -51913,13 +51913,13 @@
         </is>
       </c>
       <c r="K938" s="1" t="n">
-        <v>46331.97916666666</v>
+        <v>46332</v>
       </c>
       <c r="L938" s="1" t="n">
-        <v>46332.02083333334</v>
+        <v>46332.04166666666</v>
       </c>
       <c r="M938" s="1" t="n">
-        <v>46332.47916666666</v>
+        <v>46332.5</v>
       </c>
     </row>
     <row r="939">
@@ -51968,13 +51968,13 @@
         </is>
       </c>
       <c r="K939" s="1" t="n">
-        <v>46333.22916666666</v>
+        <v>46333.25</v>
       </c>
       <c r="L939" s="1" t="n">
-        <v>46333.27083333334</v>
+        <v>46333.29166666666</v>
       </c>
       <c r="M939" s="1" t="n">
-        <v>46333.85416666666</v>
+        <v>46333.875</v>
       </c>
     </row>
     <row r="940">
@@ -52023,13 +52023,13 @@
         </is>
       </c>
       <c r="K940" s="1" t="n">
-        <v>46335.29166666666</v>
+        <v>46335.91666666666</v>
       </c>
       <c r="L940" s="1" t="n">
-        <v>46335.33333333334</v>
+        <v>46335.95833333334</v>
       </c>
       <c r="M940" s="1" t="n">
-        <v>46336.04166666666</v>
+        <v>46336.66666666666</v>
       </c>
     </row>
     <row r="941">
@@ -52078,13 +52078,13 @@
         </is>
       </c>
       <c r="K941" s="1" t="n">
-        <v>46336.375</v>
+        <v>46337</v>
       </c>
       <c r="L941" s="1" t="n">
-        <v>46336.45833333334</v>
+        <v>46337.08333333334</v>
       </c>
       <c r="M941" s="1" t="n">
-        <v>46336.70833333334</v>
+        <v>46337.33333333334</v>
       </c>
     </row>
     <row r="942">
@@ -52133,13 +52133,13 @@
         </is>
       </c>
       <c r="K942" s="1" t="n">
-        <v>46339.625</v>
+        <v>46340.25</v>
       </c>
       <c r="L942" s="1" t="n">
-        <v>46339.66666666666</v>
+        <v>46340.29166666666</v>
       </c>
       <c r="M942" s="1" t="n">
-        <v>46340.125</v>
+        <v>46340.75</v>
       </c>
     </row>
     <row r="943">
@@ -52188,13 +52188,13 @@
         </is>
       </c>
       <c r="K943" s="1" t="n">
-        <v>46342.33333333334</v>
+        <v>46342.95833333334</v>
       </c>
       <c r="L943" s="1" t="n">
-        <v>46342.5</v>
+        <v>46343.125</v>
       </c>
       <c r="M943" s="1" t="n">
-        <v>46342.95833333334</v>
+        <v>46343.58333333334</v>
       </c>
     </row>
     <row r="944">
@@ -52243,13 +52243,13 @@
         </is>
       </c>
       <c r="K944" s="1" t="n">
-        <v>46344.70833333334</v>
+        <v>46345.33333333334</v>
       </c>
       <c r="L944" s="1" t="n">
-        <v>46344.75</v>
+        <v>46345.375</v>
       </c>
       <c r="M944" s="1" t="n">
-        <v>46344.91666666666</v>
+        <v>46345.54166666666</v>
       </c>
     </row>
     <row r="945">
@@ -52298,13 +52298,13 @@
         </is>
       </c>
       <c r="K945" s="1" t="n">
-        <v>46345.16666666666</v>
+        <v>46345.79166666666</v>
       </c>
       <c r="L945" s="1" t="n">
-        <v>46345.29166666666</v>
+        <v>46345.91666666666</v>
       </c>
       <c r="M945" s="1" t="n">
-        <v>46346.625</v>
+        <v>46347.25</v>
       </c>
     </row>
     <row r="946">
@@ -52353,13 +52353,13 @@
         </is>
       </c>
       <c r="K946" s="1" t="n">
-        <v>46347.125</v>
+        <v>46347.75</v>
       </c>
       <c r="L946" s="1" t="n">
-        <v>46347.16666666666</v>
+        <v>46347.79166666666</v>
       </c>
       <c r="M946" s="1" t="n">
-        <v>46347.45833333334</v>
+        <v>46348.08333333334</v>
       </c>
     </row>
     <row r="947">
@@ -52408,13 +52408,13 @@
         </is>
       </c>
       <c r="K947" s="1" t="n">
-        <v>46351.54166666666</v>
+        <v>46352.16666666666</v>
       </c>
       <c r="L947" s="1" t="n">
-        <v>46351.58333333334</v>
+        <v>46352.20833333334</v>
       </c>
       <c r="M947" s="1" t="n">
-        <v>46352.04166666666</v>
+        <v>46352.66666666666</v>
       </c>
     </row>
     <row r="948">
@@ -52463,13 +52463,13 @@
         </is>
       </c>
       <c r="K948" s="1" t="n">
-        <v>46353.125</v>
+        <v>46353.75</v>
       </c>
       <c r="L948" s="1" t="n">
-        <v>46353.16666666666</v>
+        <v>46353.79166666666</v>
       </c>
       <c r="M948" s="1" t="n">
-        <v>46353.75</v>
+        <v>46354.375</v>
       </c>
     </row>
     <row r="949">
@@ -52518,13 +52518,13 @@
         </is>
       </c>
       <c r="K949" s="1" t="n">
-        <v>46355.08333333334</v>
+        <v>46355.91666666666</v>
       </c>
       <c r="L949" s="1" t="n">
-        <v>46355.125</v>
+        <v>46355.95833333334</v>
       </c>
       <c r="M949" s="1" t="n">
-        <v>46355.83333333334</v>
+        <v>46356.66666666666</v>
       </c>
     </row>
     <row r="950">
@@ -52573,13 +52573,13 @@
         </is>
       </c>
       <c r="K950" s="1" t="n">
-        <v>46356.16666666666</v>
+        <v>46357</v>
       </c>
       <c r="L950" s="1" t="n">
-        <v>46356.25</v>
+        <v>46357.08333333334</v>
       </c>
       <c r="M950" s="1" t="n">
-        <v>46356.5</v>
+        <v>46357.33333333334</v>
       </c>
     </row>
     <row r="951">
@@ -52628,13 +52628,13 @@
         </is>
       </c>
       <c r="K951" s="1" t="n">
-        <v>46359.41666666666</v>
+        <v>46360.25</v>
       </c>
       <c r="L951" s="1" t="n">
-        <v>46359.45833333334</v>
+        <v>46360.29166666666</v>
       </c>
       <c r="M951" s="1" t="n">
-        <v>46359.91666666666</v>
+        <v>46360.75</v>
       </c>
     </row>
     <row r="952">
@@ -52683,13 +52683,13 @@
         </is>
       </c>
       <c r="K952" s="1" t="n">
-        <v>46362.125</v>
+        <v>46362.95833333334</v>
       </c>
       <c r="L952" s="1" t="n">
-        <v>46362.29166666666</v>
+        <v>46363.125</v>
       </c>
       <c r="M952" s="1" t="n">
-        <v>46362.75</v>
+        <v>46363.58333333334</v>
       </c>
     </row>
     <row r="953">
@@ -52738,13 +52738,13 @@
         </is>
       </c>
       <c r="K953" s="1" t="n">
-        <v>46364.5</v>
+        <v>46365.33333333334</v>
       </c>
       <c r="L953" s="1" t="n">
-        <v>46364.54166666666</v>
+        <v>46365.375</v>
       </c>
       <c r="M953" s="1" t="n">
-        <v>46364.70833333334</v>
+        <v>46365.54166666666</v>
       </c>
     </row>
     <row r="954">
@@ -52793,13 +52793,13 @@
         </is>
       </c>
       <c r="K954" s="1" t="n">
-        <v>46364.95833333334</v>
+        <v>46365.79166666666</v>
       </c>
       <c r="L954" s="1" t="n">
-        <v>46365.08333333334</v>
+        <v>46365.91666666666</v>
       </c>
       <c r="M954" s="1" t="n">
-        <v>46366.41666666666</v>
+        <v>46367.25</v>
       </c>
     </row>
     <row r="955">
@@ -52848,13 +52848,13 @@
         </is>
       </c>
       <c r="K955" s="1" t="n">
-        <v>46366.91666666666</v>
+        <v>46367.75</v>
       </c>
       <c r="L955" s="1" t="n">
-        <v>46366.95833333334</v>
+        <v>46367.79166666666</v>
       </c>
       <c r="M955" s="1" t="n">
-        <v>46367.25</v>
+        <v>46368.08333333334</v>
       </c>
     </row>
     <row r="956">
@@ -52903,13 +52903,13 @@
         </is>
       </c>
       <c r="K956" s="1" t="n">
-        <v>46371.33333333334</v>
+        <v>46372.16666666666</v>
       </c>
       <c r="L956" s="1" t="n">
-        <v>46371.375</v>
+        <v>46372.20833333334</v>
       </c>
       <c r="M956" s="1" t="n">
-        <v>46371.83333333334</v>
+        <v>46372.66666666666</v>
       </c>
     </row>
     <row r="957">
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="K957" s="1" t="n">
-        <v>46372.91666666666</v>
+        <v>46373.75</v>
       </c>
       <c r="L957" s="1" t="n">
-        <v>46372.95833333334</v>
+        <v>46373.79166666666</v>
       </c>
       <c r="M957" s="1" t="n">
-        <v>46373.54166666666</v>
+        <v>46374.375</v>
       </c>
     </row>
     <row r="958">
@@ -53013,13 +53013,13 @@
         </is>
       </c>
       <c r="K958" s="1" t="n">
-        <v>46376.08333333334</v>
+        <v>46376.91666666666</v>
       </c>
       <c r="L958" s="1" t="n">
-        <v>46376.125</v>
+        <v>46376.95833333334</v>
       </c>
       <c r="M958" s="1" t="n">
-        <v>46376.83333333334</v>
+        <v>46377.66666666666</v>
       </c>
     </row>
     <row r="959">
@@ -53068,13 +53068,13 @@
         </is>
       </c>
       <c r="K959" s="1" t="n">
-        <v>46377.16666666666</v>
+        <v>46378</v>
       </c>
       <c r="L959" s="1" t="n">
-        <v>46377.25</v>
+        <v>46378.08333333334</v>
       </c>
       <c r="M959" s="1" t="n">
-        <v>46377.5</v>
+        <v>46378.33333333334</v>
       </c>
     </row>
     <row r="960">
@@ -53123,13 +53123,13 @@
         </is>
       </c>
       <c r="K960" s="1" t="n">
-        <v>46380.41666666666</v>
+        <v>46381.25</v>
       </c>
       <c r="L960" s="1" t="n">
-        <v>46380.45833333334</v>
+        <v>46381.29166666666</v>
       </c>
       <c r="M960" s="1" t="n">
-        <v>46380.91666666666</v>
+        <v>46381.75</v>
       </c>
     </row>
     <row r="961">
@@ -53178,13 +53178,13 @@
         </is>
       </c>
       <c r="K961" s="1" t="n">
-        <v>46383.125</v>
+        <v>46383.95833333334</v>
       </c>
       <c r="L961" s="1" t="n">
-        <v>46383.29166666666</v>
+        <v>46384.125</v>
       </c>
       <c r="M961" s="1" t="n">
-        <v>46383.75</v>
+        <v>46384.58333333334</v>
       </c>
     </row>
     <row r="962">
@@ -53233,13 +53233,13 @@
         </is>
       </c>
       <c r="K962" s="1" t="n">
-        <v>46385.5</v>
+        <v>46386.33333333334</v>
       </c>
       <c r="L962" s="1" t="n">
-        <v>46385.54166666666</v>
+        <v>46386.375</v>
       </c>
       <c r="M962" s="1" t="n">
-        <v>46385.70833333334</v>
+        <v>46386.54166666666</v>
       </c>
     </row>
     <row r="963">
@@ -53288,13 +53288,13 @@
         </is>
       </c>
       <c r="K963" s="1" t="n">
-        <v>46385.95833333334</v>
+        <v>46386.79166666666</v>
       </c>
       <c r="L963" s="1" t="n">
-        <v>46386.08333333334</v>
+        <v>46386.91666666666</v>
       </c>
       <c r="M963" s="1" t="n">
-        <v>46387.41666666666</v>
+        <v>46388.25</v>
       </c>
     </row>
     <row r="964">
@@ -53343,13 +53343,13 @@
         </is>
       </c>
       <c r="K964" s="1" t="n">
-        <v>46387.91666666666</v>
+        <v>46388.75</v>
       </c>
       <c r="L964" s="1" t="n">
-        <v>46387.95833333334</v>
+        <v>46388.79166666666</v>
       </c>
       <c r="M964" s="1" t="n">
-        <v>46388.25</v>
+        <v>46389.08333333334</v>
       </c>
     </row>
     <row r="965">
@@ -53398,13 +53398,13 @@
         </is>
       </c>
       <c r="K965" s="1" t="n">
-        <v>46392.33333333334</v>
+        <v>46393.16666666666</v>
       </c>
       <c r="L965" s="1" t="n">
-        <v>46392.375</v>
+        <v>46393.20833333334</v>
       </c>
       <c r="M965" s="1" t="n">
-        <v>46392.83333333334</v>
+        <v>46393.66666666666</v>
       </c>
     </row>
     <row r="966">
@@ -53449,13 +53449,13 @@
       </c>
       <c r="J966" t="inlineStr"/>
       <c r="K966" s="1" t="n">
-        <v>46393.91666666666</v>
+        <v>46394.75</v>
       </c>
       <c r="L966" s="1" t="n">
-        <v>46393.95833333334</v>
+        <v>46394.79166666666</v>
       </c>
       <c r="M966" s="1" t="n">
-        <v>46394.54166666666</v>
+        <v>46395.375</v>
       </c>
     </row>
     <row r="967">
@@ -53675,7 +53675,7 @@
         <v>46295</v>
       </c>
       <c r="M970" s="1" t="n">
-        <v>46296.33333333334</v>
+        <v>46296.35833333333</v>
       </c>
     </row>
     <row r="971">
@@ -53727,10 +53727,10 @@
         <v>46297.33333333334</v>
       </c>
       <c r="L971" s="1" t="n">
-        <v>46297.41666666666</v>
+        <v>46297.375</v>
       </c>
       <c r="M971" s="1" t="n">
-        <v>46297.91666666666</v>
+        <v>46298.45833333334</v>
       </c>
     </row>
     <row r="972">
@@ -53779,13 +53779,13 @@
         </is>
       </c>
       <c r="K972" s="1" t="n">
-        <v>46301.64583333334</v>
+        <v>46302.1875</v>
       </c>
       <c r="L972" s="1" t="n">
-        <v>46301.6875</v>
+        <v>46302.22916666666</v>
       </c>
       <c r="M972" s="1" t="n">
-        <v>46302.35416666666</v>
+        <v>46302.89583333334</v>
       </c>
     </row>
     <row r="973">
@@ -53834,13 +53834,13 @@
         </is>
       </c>
       <c r="K973" s="1" t="n">
-        <v>46308.41666666666</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="L973" s="1" t="n">
-        <v>46308.625</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="M973" s="1" t="n">
-        <v>46309.29166666666</v>
+        <v>46309.83333333334</v>
       </c>
     </row>
     <row r="974">
@@ -53889,13 +53889,13 @@
         </is>
       </c>
       <c r="K974" s="1" t="n">
-        <v>46310.6875</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="L974" s="1" t="n">
-        <v>46310.72916666666</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="M974" s="1" t="n">
-        <v>46311.72916666666</v>
+        <v>46312.27083333334</v>
       </c>
     </row>
     <row r="975">
@@ -53944,13 +53944,13 @@
         </is>
       </c>
       <c r="K975" s="1" t="n">
-        <v>46312.02083333334</v>
+        <v>46312.5625</v>
       </c>
       <c r="L975" s="1" t="n">
-        <v>46312.0625</v>
+        <v>46312.60416666666</v>
       </c>
       <c r="M975" s="1" t="n">
-        <v>46312.6875</v>
+        <v>46313.22916666666</v>
       </c>
     </row>
     <row r="976">
@@ -53999,13 +53999,13 @@
         </is>
       </c>
       <c r="K976" s="1" t="n">
-        <v>46314.14583333334</v>
+        <v>46314.6875</v>
       </c>
       <c r="L976" s="1" t="n">
-        <v>46314.35416666666</v>
+        <v>46314.89583333334</v>
       </c>
       <c r="M976" s="1" t="n">
-        <v>46315.02083333334</v>
+        <v>46315.5625</v>
       </c>
     </row>
     <row r="977">
@@ -54054,13 +54054,13 @@
         </is>
       </c>
       <c r="K977" s="1" t="n">
-        <v>46322.02083333334</v>
+        <v>46322.5625</v>
       </c>
       <c r="L977" s="1" t="n">
-        <v>46322.10416666666</v>
+        <v>46322.64583333334</v>
       </c>
       <c r="M977" s="1" t="n">
-        <v>46322.9375</v>
+        <v>46323.47916666666</v>
       </c>
     </row>
     <row r="978">
@@ -54109,13 +54109,13 @@
         </is>
       </c>
       <c r="K978" s="1" t="n">
-        <v>46324.02083333334</v>
+        <v>46324.5625</v>
       </c>
       <c r="L978" s="1" t="n">
-        <v>46324.10416666666</v>
+        <v>46324.64583333334</v>
       </c>
       <c r="M978" s="1" t="n">
-        <v>46324.60416666666</v>
+        <v>46325.14583333334</v>
       </c>
     </row>
     <row r="979">
@@ -54164,13 +54164,13 @@
         </is>
       </c>
       <c r="K979" s="1" t="n">
-        <v>46328.60416666666</v>
+        <v>46329.14583333334</v>
       </c>
       <c r="L979" s="1" t="n">
-        <v>46328.64583333334</v>
+        <v>46329.1875</v>
       </c>
       <c r="M979" s="1" t="n">
-        <v>46329.3125</v>
+        <v>46329.85416666666</v>
       </c>
     </row>
     <row r="980">
@@ -54219,13 +54219,13 @@
         </is>
       </c>
       <c r="K980" s="1" t="n">
-        <v>46335.72916666666</v>
+        <v>46336.27083333334</v>
       </c>
       <c r="L980" s="1" t="n">
-        <v>46335.9375</v>
+        <v>46336.47916666666</v>
       </c>
       <c r="M980" s="1" t="n">
-        <v>46336.60416666666</v>
+        <v>46337.14583333334</v>
       </c>
     </row>
     <row r="981">
@@ -54274,13 +54274,13 @@
         </is>
       </c>
       <c r="K981" s="1" t="n">
-        <v>46338.10416666666</v>
+        <v>46338.64583333334</v>
       </c>
       <c r="L981" s="1" t="n">
-        <v>46338.14583333334</v>
+        <v>46338.6875</v>
       </c>
       <c r="M981" s="1" t="n">
-        <v>46339.14583333334</v>
+        <v>46339.6875</v>
       </c>
     </row>
     <row r="982">
@@ -54329,13 +54329,13 @@
         </is>
       </c>
       <c r="K982" s="1" t="n">
-        <v>46339.77083333334</v>
+        <v>46340.3125</v>
       </c>
       <c r="L982" s="1" t="n">
-        <v>46339.8125</v>
+        <v>46340.35416666666</v>
       </c>
       <c r="M982" s="1" t="n">
-        <v>46340.4375</v>
+        <v>46340.97916666666</v>
       </c>
     </row>
     <row r="983">
@@ -54384,13 +54384,13 @@
         </is>
       </c>
       <c r="K983" s="1" t="n">
-        <v>46341.9375</v>
+        <v>46342.47916666666</v>
       </c>
       <c r="L983" s="1" t="n">
-        <v>46342.14583333334</v>
+        <v>46342.6875</v>
       </c>
       <c r="M983" s="1" t="n">
-        <v>46342.8125</v>
+        <v>46343.35416666666</v>
       </c>
     </row>
     <row r="984">
@@ -54439,13 +54439,13 @@
         </is>
       </c>
       <c r="K984" s="1" t="n">
-        <v>46349.8125</v>
+        <v>46350.35416666666</v>
       </c>
       <c r="L984" s="1" t="n">
-        <v>46349.89583333334</v>
+        <v>46350.4375</v>
       </c>
       <c r="M984" s="1" t="n">
-        <v>46350.72916666666</v>
+        <v>46351.27083333334</v>
       </c>
     </row>
     <row r="985">
@@ -54494,13 +54494,13 @@
         </is>
       </c>
       <c r="K985" s="1" t="n">
-        <v>46351.8125</v>
+        <v>46352.35416666666</v>
       </c>
       <c r="L985" s="1" t="n">
-        <v>46351.89583333334</v>
+        <v>46352.4375</v>
       </c>
       <c r="M985" s="1" t="n">
-        <v>46352.39583333334</v>
+        <v>46352.9375</v>
       </c>
     </row>
     <row r="986">
@@ -54549,13 +54549,13 @@
         </is>
       </c>
       <c r="K986" s="1" t="n">
-        <v>46356.39583333334</v>
+        <v>46356.9375</v>
       </c>
       <c r="L986" s="1" t="n">
-        <v>46356.4375</v>
+        <v>46356.97916666666</v>
       </c>
       <c r="M986" s="1" t="n">
-        <v>46357.10416666666</v>
+        <v>46357.64583333334</v>
       </c>
     </row>
     <row r="987">
@@ -54604,13 +54604,13 @@
         </is>
       </c>
       <c r="K987" s="1" t="n">
-        <v>46363.52083333334</v>
+        <v>46364.0625</v>
       </c>
       <c r="L987" s="1" t="n">
-        <v>46363.72916666666</v>
+        <v>46364.27083333334</v>
       </c>
       <c r="M987" s="1" t="n">
-        <v>46364.39583333334</v>
+        <v>46364.9375</v>
       </c>
     </row>
     <row r="988">
@@ -54659,13 +54659,13 @@
         </is>
       </c>
       <c r="K988" s="1" t="n">
-        <v>46366.10416666666</v>
+        <v>46366.64583333334</v>
       </c>
       <c r="L988" s="1" t="n">
-        <v>46366.14583333334</v>
+        <v>46366.6875</v>
       </c>
       <c r="M988" s="1" t="n">
-        <v>46367.14583333334</v>
+        <v>46367.6875</v>
       </c>
     </row>
     <row r="989">
@@ -54714,13 +54714,13 @@
         </is>
       </c>
       <c r="K989" s="1" t="n">
-        <v>46367.77083333334</v>
+        <v>46368.3125</v>
       </c>
       <c r="L989" s="1" t="n">
-        <v>46367.8125</v>
+        <v>46368.35416666666</v>
       </c>
       <c r="M989" s="1" t="n">
-        <v>46368.4375</v>
+        <v>46368.97916666666</v>
       </c>
     </row>
     <row r="990">
@@ -54769,13 +54769,13 @@
         </is>
       </c>
       <c r="K990" s="1" t="n">
-        <v>46369.9375</v>
+        <v>46370.47916666666</v>
       </c>
       <c r="L990" s="1" t="n">
-        <v>46370.14583333334</v>
+        <v>46370.6875</v>
       </c>
       <c r="M990" s="1" t="n">
-        <v>46370.8125</v>
+        <v>46371.35416666666</v>
       </c>
     </row>
     <row r="991">
@@ -54824,13 +54824,13 @@
         </is>
       </c>
       <c r="K991" s="1" t="n">
-        <v>46377.8125</v>
+        <v>46378.35416666666</v>
       </c>
       <c r="L991" s="1" t="n">
-        <v>46377.89583333334</v>
+        <v>46378.4375</v>
       </c>
       <c r="M991" s="1" t="n">
-        <v>46378.72916666666</v>
+        <v>46379.27083333334</v>
       </c>
     </row>
     <row r="992">
@@ -54879,13 +54879,13 @@
         </is>
       </c>
       <c r="K992" s="1" t="n">
-        <v>46379.8125</v>
+        <v>46380.35416666666</v>
       </c>
       <c r="L992" s="1" t="n">
-        <v>46379.89583333334</v>
+        <v>46380.4375</v>
       </c>
       <c r="M992" s="1" t="n">
-        <v>46380.39583333334</v>
+        <v>46380.9375</v>
       </c>
     </row>
     <row r="993">
@@ -54934,13 +54934,13 @@
         </is>
       </c>
       <c r="K993" s="1" t="n">
-        <v>46384.39583333334</v>
+        <v>46384.9375</v>
       </c>
       <c r="L993" s="1" t="n">
-        <v>46384.4375</v>
+        <v>46384.97916666666</v>
       </c>
       <c r="M993" s="1" t="n">
-        <v>46385.10416666666</v>
+        <v>46385.64583333334</v>
       </c>
     </row>
     <row r="994">
@@ -54985,13 +54985,13 @@
       </c>
       <c r="J994" t="inlineStr"/>
       <c r="K994" s="1" t="n">
-        <v>46391.52083333334</v>
+        <v>46392.0625</v>
       </c>
       <c r="L994" s="1" t="n">
-        <v>46391.72916666666</v>
+        <v>46392.27083333334</v>
       </c>
       <c r="M994" s="1" t="n">
-        <v>46392.39583333334</v>
+        <v>46392.9375</v>
       </c>
     </row>
     <row r="995">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -1034,7 +1034,7 @@
         <v>46299</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>46299.5</v>
+        <v>46299.75</v>
       </c>
     </row>
     <row r="12">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46301.875</v>
+        <v>46302.125</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46301.91666666666</v>
+        <v>46302.16666666666</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>46302.91666666666</v>
+        <v>46303.16666666666</v>
       </c>
     </row>
     <row r="13">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46303.04166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46303.08333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>46303.45833333334</v>
+        <v>46303.70833333334</v>
       </c>
     </row>
     <row r="14">
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46306.95833333334</v>
+        <v>46307.20833333334</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46307.02083333334</v>
+        <v>46307.27083333334</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>46307.4375</v>
+        <v>46307.6875</v>
       </c>
     </row>
     <row r="15">
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46310.20833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46310.375</v>
+        <v>46310.625</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>46311.08333333334</v>
+        <v>46311.33333333334</v>
       </c>
     </row>
     <row r="16">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46313</v>
+        <v>46313.25</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46313.04166666666</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>46313.33333333334</v>
+        <v>46313.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46313.45833333334</v>
+        <v>46313.70833333334</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46313.58333333334</v>
+        <v>46313.83333333334</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>46314.83333333334</v>
+        <v>46315.08333333334</v>
       </c>
     </row>
     <row r="18">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46315.04166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46315.08333333334</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>46315.54166666666</v>
+        <v>46315.79166666666</v>
       </c>
     </row>
     <row r="19">
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46319.83333333334</v>
+        <v>46320</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46319.89583333334</v>
+        <v>46320.0625</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>46320.375</v>
+        <v>46320.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46320.45833333334</v>
+        <v>46320.625</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46320.5</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>46320.875</v>
+        <v>46321.04166666666</v>
       </c>
     </row>
     <row r="21">
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46324.625</v>
+        <v>46324.79166666666</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46324.66666666666</v>
+        <v>46324.83333333334</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>46325.66666666666</v>
+        <v>46325.83333333334</v>
       </c>
     </row>
     <row r="22">
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46325.79166666666</v>
+        <v>46325.95833333334</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>46325.83333333334</v>
+        <v>46326</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>46326.20833333334</v>
+        <v>46326.375</v>
       </c>
     </row>
     <row r="23">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46329.04166666666</v>
+        <v>46329.20833333334</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>46329.08333333334</v>
+        <v>46329.25</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>46329.45833333334</v>
+        <v>46329.625</v>
       </c>
     </row>
     <row r="24">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46331.91666666666</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>46332.08333333334</v>
+        <v>46332.25</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>46332.625</v>
+        <v>46332.79166666666</v>
       </c>
     </row>
     <row r="25">
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46334.41666666666</v>
+        <v>46334.58333333334</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>46334.45833333334</v>
+        <v>46334.625</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>46334.70833333334</v>
+        <v>46334.875</v>
       </c>
     </row>
     <row r="26">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46335.125</v>
+        <v>46335.29166666666</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>46335.25</v>
+        <v>46335.41666666666</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>46336.375</v>
+        <v>46336.54166666666</v>
       </c>
     </row>
     <row r="27">
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46336.70833333334</v>
+        <v>46336.875</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>46336.75</v>
+        <v>46336.91666666666</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>46337.08333333334</v>
+        <v>46337.25</v>
       </c>
     </row>
     <row r="28">
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46340.95833333334</v>
+        <v>46341.125</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>46341</v>
+        <v>46341.16666666666</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>46341.41666666666</v>
+        <v>46341.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46341.66666666666</v>
+        <v>46341.83333333334</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>46341.66666666666</v>
+        <v>46341.83333333334</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>46342.04166666666</v>
+        <v>46342.20833333334</v>
       </c>
     </row>
     <row r="30">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46343.29166666666</v>
+        <v>46343.45833333334</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>46343.29166666666</v>
+        <v>46343.45833333334</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>46343.54166666666</v>
+        <v>46343.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -2128,13 +2128,13 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46344.5</v>
+        <v>46344.66666666666</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>46344.54166666666</v>
+        <v>46344.70833333334</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>46345.25</v>
+        <v>46345.41666666666</v>
       </c>
     </row>
     <row r="32">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46345.45833333334</v>
+        <v>46345.625</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>46345.5</v>
+        <v>46345.66666666666</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>46345.83333333334</v>
+        <v>46346</v>
       </c>
     </row>
     <row r="33">
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46348.66666666666</v>
+        <v>46348.83333333334</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>46348.70833333334</v>
+        <v>46348.875</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>46349.08333333334</v>
+        <v>46349.25</v>
       </c>
     </row>
     <row r="34">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46351.54166666666</v>
+        <v>46351.70833333334</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>46351.70833333334</v>
+        <v>46351.875</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>46352.25</v>
+        <v>46352.41666666666</v>
       </c>
     </row>
     <row r="35">
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46354.04166666666</v>
+        <v>46354.20833333334</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>46354.08333333334</v>
+        <v>46354.25</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>46354.33333333334</v>
+        <v>46354.5</v>
       </c>
     </row>
     <row r="36">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46354.75</v>
+        <v>46354.91666666666</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>46354.875</v>
+        <v>46355.04166666666</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>46356</v>
+        <v>46356.16666666666</v>
       </c>
     </row>
     <row r="37">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46356.33333333334</v>
+        <v>46356.5</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>46356.375</v>
+        <v>46356.54166666666</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>46356.70833333334</v>
+        <v>46356.875</v>
       </c>
     </row>
     <row r="38">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46360.58333333334</v>
+        <v>46360.75</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>46360.625</v>
+        <v>46360.79166666666</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>46361.04166666666</v>
+        <v>46361.20833333334</v>
       </c>
     </row>
     <row r="39">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46361.29166666666</v>
+        <v>46361.45833333334</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>46361.29166666666</v>
+        <v>46361.45833333334</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>46361.66666666666</v>
+        <v>46361.83333333334</v>
       </c>
     </row>
     <row r="40">
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46362.91666666666</v>
+        <v>46363.08333333334</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>46362.91666666666</v>
+        <v>46363.08333333334</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>46363.16666666666</v>
+        <v>46363.33333333334</v>
       </c>
     </row>
     <row r="41">
@@ -2678,13 +2678,13 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46365.5</v>
+        <v>46365.66666666666</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>46365.54166666666</v>
+        <v>46365.70833333334</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>46366.25</v>
+        <v>46366.41666666666</v>
       </c>
     </row>
     <row r="42">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46366.45833333334</v>
+        <v>46366.625</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>46366.5</v>
+        <v>46366.66666666666</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>46366.83333333334</v>
+        <v>46367</v>
       </c>
     </row>
     <row r="43">
@@ -2788,13 +2788,13 @@
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46369.66666666666</v>
+        <v>46369.83333333334</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>46369.70833333334</v>
+        <v>46369.875</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>46370.08333333334</v>
+        <v>46370.25</v>
       </c>
     </row>
     <row r="44">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46372.54166666666</v>
+        <v>46372.70833333334</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>46372.70833333334</v>
+        <v>46372.875</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>46373.25</v>
+        <v>46373.41666666666</v>
       </c>
     </row>
     <row r="45">
@@ -2898,13 +2898,13 @@
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46375.04166666666</v>
+        <v>46375.20833333334</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>46375.08333333334</v>
+        <v>46375.25</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>46375.33333333334</v>
+        <v>46375.5</v>
       </c>
     </row>
     <row r="46">
@@ -2953,13 +2953,13 @@
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46375.75</v>
+        <v>46375.91666666666</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>46375.875</v>
+        <v>46376.04166666666</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>46377</v>
+        <v>46377.16666666666</v>
       </c>
     </row>
     <row r="47">
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46377.33333333334</v>
+        <v>46377.5</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>46377.375</v>
+        <v>46377.54166666666</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>46377.70833333334</v>
+        <v>46377.875</v>
       </c>
     </row>
     <row r="48">
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46381.58333333334</v>
+        <v>46381.75</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>46381.625</v>
+        <v>46381.79166666666</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>46382.04166666666</v>
+        <v>46382.20833333334</v>
       </c>
     </row>
     <row r="49">
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46382.29166666666</v>
+        <v>46382.45833333334</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>46382.29166666666</v>
+        <v>46382.45833333334</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>46382.66666666666</v>
+        <v>46382.83333333334</v>
       </c>
     </row>
     <row r="50">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46383.91666666666</v>
+        <v>46384.08333333334</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>46383.91666666666</v>
+        <v>46384.08333333334</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>46384.16666666666</v>
+        <v>46384.33333333334</v>
       </c>
     </row>
     <row r="51">
@@ -3228,13 +3228,13 @@
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46386.5</v>
+        <v>46386.66666666666</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>46386.54166666666</v>
+        <v>46386.70833333334</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>46387.25</v>
+        <v>46387.41666666666</v>
       </c>
     </row>
     <row r="52">
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46387.45833333334</v>
+        <v>46387.625</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>46387.5</v>
+        <v>46387.66666666666</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>46387.83333333334</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="53">
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46390.66666666666</v>
+        <v>46390.83333333334</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>46390.70833333334</v>
+        <v>46390.875</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>46391.08333333334</v>
+        <v>46391.25</v>
       </c>
     </row>
     <row r="54">
@@ -3393,13 +3393,13 @@
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46393.54166666666</v>
+        <v>46393.70833333334</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>46393.70833333334</v>
+        <v>46393.875</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>46394.25</v>
+        <v>46394.41666666666</v>
       </c>
     </row>
     <row r="55">
@@ -3448,13 +3448,13 @@
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46396.04166666666</v>
+        <v>46396.20833333334</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>46396.08333333334</v>
+        <v>46396.25</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>46396.33333333334</v>
+        <v>46396.5</v>
       </c>
     </row>
     <row r="56">
@@ -3503,13 +3503,13 @@
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46396.75</v>
+        <v>46396.91666666666</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>46396.875</v>
+        <v>46397.04166666666</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>46398</v>
+        <v>46398.16666666666</v>
       </c>
     </row>
     <row r="57">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46398.33333333334</v>
+        <v>46398.5</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>46398.375</v>
+        <v>46398.54166666666</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>46398.70833333334</v>
+        <v>46398.875</v>
       </c>
     </row>
     <row r="58">
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46402.58333333334</v>
+        <v>46402.75</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>46402.625</v>
+        <v>46402.79166666666</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>46403.04166666666</v>
+        <v>46403.20833333334</v>
       </c>
     </row>
     <row r="59">
@@ -3668,13 +3668,13 @@
         </is>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46403.29166666666</v>
+        <v>46403.45833333334</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>46403.29166666666</v>
+        <v>46403.45833333334</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>46403.66666666666</v>
+        <v>46403.83333333334</v>
       </c>
     </row>
     <row r="60">
@@ -3719,13 +3719,13 @@
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" s="1" t="n">
-        <v>46404.91666666666</v>
+        <v>46405.08333333334</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>46404.91666666666</v>
+        <v>46405.08333333334</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>46405.16666666666</v>
+        <v>46405.33333333334</v>
       </c>
     </row>
     <row r="61">
@@ -5973,10 +5973,10 @@
         <v>46298.29166666666</v>
       </c>
       <c r="L101" s="1" t="n">
-        <v>46299.5</v>
+        <v>46299.54166666666</v>
       </c>
       <c r="M101" s="1" t="n">
-        <v>46300.16666666666</v>
+        <v>46300.20833333334</v>
       </c>
     </row>
     <row r="102">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46301.5625</v>
+        <v>46301.58333333334</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>46301.60416666666</v>
+        <v>46301.625</v>
       </c>
       <c r="M102" s="1" t="n">
-        <v>46303.60416666666</v>
+        <v>46303.625</v>
       </c>
     </row>
     <row r="103">
@@ -6080,13 +6080,13 @@
         </is>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46303.89583333334</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>46303.9375</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="M103" s="1" t="n">
-        <v>46304.5625</v>
+        <v>46304.58333333334</v>
       </c>
     </row>
     <row r="104">
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46305.58333333334</v>
+        <v>46305.60416666666</v>
       </c>
       <c r="L104" s="1" t="n">
-        <v>46305.79166666666</v>
+        <v>46305.8125</v>
       </c>
       <c r="M104" s="1" t="n">
-        <v>46306.45833333334</v>
+        <v>46306.47916666666</v>
       </c>
     </row>
     <row r="105">
@@ -6190,13 +6190,13 @@
         </is>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46313.45833333334</v>
+        <v>46313.47916666666</v>
       </c>
       <c r="L105" s="1" t="n">
-        <v>46313.54166666666</v>
+        <v>46313.5625</v>
       </c>
       <c r="M105" s="1" t="n">
-        <v>46314.375</v>
+        <v>46314.39583333334</v>
       </c>
     </row>
     <row r="106">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46315.45833333334</v>
+        <v>46315.47916666666</v>
       </c>
       <c r="L106" s="1" t="n">
-        <v>46315.54166666666</v>
+        <v>46315.5625</v>
       </c>
       <c r="M106" s="1" t="n">
-        <v>46316.04166666666</v>
+        <v>46316.0625</v>
       </c>
     </row>
     <row r="107">
@@ -6300,13 +6300,13 @@
         </is>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46320.04166666666</v>
+        <v>46320.0625</v>
       </c>
       <c r="L107" s="1" t="n">
-        <v>46320.08333333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="M107" s="1" t="n">
-        <v>46320.75</v>
+        <v>46320.77083333334</v>
       </c>
     </row>
     <row r="108">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46327.16666666666</v>
+        <v>46327.1875</v>
       </c>
       <c r="L108" s="1" t="n">
-        <v>46327.375</v>
+        <v>46327.39583333334</v>
       </c>
       <c r="M108" s="1" t="n">
-        <v>46328.04166666666</v>
+        <v>46328.0625</v>
       </c>
     </row>
     <row r="109">
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46329.75</v>
+        <v>46329.77083333334</v>
       </c>
       <c r="L109" s="1" t="n">
-        <v>46329.79166666666</v>
+        <v>46329.8125</v>
       </c>
       <c r="M109" s="1" t="n">
-        <v>46330.79166666666</v>
+        <v>46330.8125</v>
       </c>
     </row>
     <row r="110">
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46331.41666666666</v>
+        <v>46331.4375</v>
       </c>
       <c r="L110" s="1" t="n">
-        <v>46331.45833333334</v>
+        <v>46331.47916666666</v>
       </c>
       <c r="M110" s="1" t="n">
-        <v>46332.08333333334</v>
+        <v>46332.10416666666</v>
       </c>
     </row>
     <row r="111">
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="K111" s="1" t="n">
-        <v>46333.58333333334</v>
+        <v>46333.60416666666</v>
       </c>
       <c r="L111" s="1" t="n">
-        <v>46333.79166666666</v>
+        <v>46333.8125</v>
       </c>
       <c r="M111" s="1" t="n">
-        <v>46334.45833333334</v>
+        <v>46334.47916666666</v>
       </c>
     </row>
     <row r="112">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="K112" s="1" t="n">
-        <v>46341.45833333334</v>
+        <v>46341.47916666666</v>
       </c>
       <c r="L112" s="1" t="n">
-        <v>46341.54166666666</v>
+        <v>46341.5625</v>
       </c>
       <c r="M112" s="1" t="n">
-        <v>46342.375</v>
+        <v>46342.39583333334</v>
       </c>
     </row>
     <row r="113">
@@ -6630,13 +6630,13 @@
         </is>
       </c>
       <c r="K113" s="1" t="n">
-        <v>46343.45833333334</v>
+        <v>46343.47916666666</v>
       </c>
       <c r="L113" s="1" t="n">
-        <v>46343.54166666666</v>
+        <v>46343.5625</v>
       </c>
       <c r="M113" s="1" t="n">
-        <v>46344.04166666666</v>
+        <v>46344.0625</v>
       </c>
     </row>
     <row r="114">
@@ -6685,13 +6685,13 @@
         </is>
       </c>
       <c r="K114" s="1" t="n">
-        <v>46348.04166666666</v>
+        <v>46348.0625</v>
       </c>
       <c r="L114" s="1" t="n">
-        <v>46348.08333333334</v>
+        <v>46348.10416666666</v>
       </c>
       <c r="M114" s="1" t="n">
-        <v>46348.75</v>
+        <v>46348.77083333334</v>
       </c>
     </row>
     <row r="115">
@@ -6740,13 +6740,13 @@
         </is>
       </c>
       <c r="K115" s="1" t="n">
-        <v>46355.16666666666</v>
+        <v>46355.1875</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>46355.375</v>
+        <v>46355.39583333334</v>
       </c>
       <c r="M115" s="1" t="n">
-        <v>46356.04166666666</v>
+        <v>46356.0625</v>
       </c>
     </row>
     <row r="116">
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46357.75</v>
+        <v>46357.77083333334</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>46357.79166666666</v>
+        <v>46357.8125</v>
       </c>
       <c r="M116" s="1" t="n">
-        <v>46358.79166666666</v>
+        <v>46358.8125</v>
       </c>
     </row>
     <row r="117">
@@ -6850,13 +6850,13 @@
         </is>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46359.41666666666</v>
+        <v>46359.4375</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>46359.45833333334</v>
+        <v>46359.47916666666</v>
       </c>
       <c r="M117" s="1" t="n">
-        <v>46360.08333333334</v>
+        <v>46360.10416666666</v>
       </c>
     </row>
     <row r="118">
@@ -6905,13 +6905,13 @@
         </is>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46361.58333333334</v>
+        <v>46361.60416666666</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>46361.79166666666</v>
+        <v>46361.8125</v>
       </c>
       <c r="M118" s="1" t="n">
-        <v>46362.45833333334</v>
+        <v>46362.47916666666</v>
       </c>
     </row>
     <row r="119">
@@ -6960,13 +6960,13 @@
         </is>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46369.45833333334</v>
+        <v>46369.47916666666</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>46369.54166666666</v>
+        <v>46369.5625</v>
       </c>
       <c r="M119" s="1" t="n">
-        <v>46370.375</v>
+        <v>46370.39583333334</v>
       </c>
     </row>
     <row r="120">
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46371.45833333334</v>
+        <v>46371.47916666666</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>46371.54166666666</v>
+        <v>46371.5625</v>
       </c>
       <c r="M120" s="1" t="n">
-        <v>46372.04166666666</v>
+        <v>46372.0625</v>
       </c>
     </row>
     <row r="121">
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46376.04166666666</v>
+        <v>46376.0625</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>46376.08333333334</v>
+        <v>46376.10416666666</v>
       </c>
       <c r="M121" s="1" t="n">
-        <v>46376.75</v>
+        <v>46376.77083333334</v>
       </c>
     </row>
     <row r="122">
@@ -7125,13 +7125,13 @@
         </is>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46383.16666666666</v>
+        <v>46383.1875</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>46383.375</v>
+        <v>46383.39583333334</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>46384.04166666666</v>
+        <v>46384.0625</v>
       </c>
     </row>
     <row r="123">
@@ -7180,13 +7180,13 @@
         </is>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46385.75</v>
+        <v>46385.77083333334</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>46385.79166666666</v>
+        <v>46385.8125</v>
       </c>
       <c r="M123" s="1" t="n">
-        <v>46386.79166666666</v>
+        <v>46386.8125</v>
       </c>
     </row>
     <row r="124">
@@ -7235,13 +7235,13 @@
         </is>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46387.41666666666</v>
+        <v>46387.4375</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>46387.45833333334</v>
+        <v>46387.47916666666</v>
       </c>
       <c r="M124" s="1" t="n">
-        <v>46388.08333333334</v>
+        <v>46388.10416666666</v>
       </c>
     </row>
     <row r="125">
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46389.58333333334</v>
+        <v>46389.60416666666</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>46389.79166666666</v>
+        <v>46389.8125</v>
       </c>
       <c r="M125" s="1" t="n">
-        <v>46390.45833333334</v>
+        <v>46390.47916666666</v>
       </c>
     </row>
     <row r="126">
@@ -7345,13 +7345,13 @@
         </is>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46397.45833333334</v>
+        <v>46397.47916666666</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>46397.54166666666</v>
+        <v>46397.5625</v>
       </c>
       <c r="M126" s="1" t="n">
-        <v>46398.375</v>
+        <v>46398.39583333334</v>
       </c>
     </row>
     <row r="127">
@@ -7400,13 +7400,13 @@
         </is>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46399.45833333334</v>
+        <v>46399.47916666666</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>46399.54166666666</v>
+        <v>46399.5625</v>
       </c>
       <c r="M127" s="1" t="n">
-        <v>46400.04166666666</v>
+        <v>46400.0625</v>
       </c>
     </row>
     <row r="128">
@@ -7455,13 +7455,13 @@
         </is>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46404.04166666666</v>
+        <v>46404.0625</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>46404.08333333334</v>
+        <v>46404.10416666666</v>
       </c>
       <c r="M128" s="1" t="n">
-        <v>46404.75</v>
+        <v>46404.77083333334</v>
       </c>
     </row>
     <row r="129">
@@ -7506,13 +7506,13 @@
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" s="1" t="n">
-        <v>46411.16666666666</v>
+        <v>46411.1875</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>46411.375</v>
+        <v>46411.39583333334</v>
       </c>
       <c r="M129" s="1" t="n">
-        <v>46412.04166666666</v>
+        <v>46412.0625</v>
       </c>
     </row>
     <row r="130">
@@ -7564,10 +7564,10 @@
         <v>46297.66666666666</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>46298.04166666666</v>
+        <v>46297.83333333334</v>
       </c>
       <c r="M130" s="1" t="n">
-        <v>46299.04166666666</v>
+        <v>46298.75</v>
       </c>
     </row>
     <row r="131">
@@ -7616,13 +7616,13 @@
         </is>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46300.875</v>
+        <v>46300.58333333334</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>46300.91666666666</v>
+        <v>46300.625</v>
       </c>
       <c r="M131" s="1" t="n">
-        <v>46302.91666666666</v>
+        <v>46302.625</v>
       </c>
     </row>
     <row r="132">
@@ -7671,13 +7671,13 @@
         </is>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46304.91666666666</v>
+        <v>46304.625</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>46304.95833333334</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="M132" s="1" t="n">
-        <v>46305.66666666666</v>
+        <v>46305.375</v>
       </c>
     </row>
     <row r="133">
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46304.91666666666</v>
+        <v>46304.625</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>46304.95833333334</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="M133" s="1" t="n">
-        <v>46306.66666666666</v>
+        <v>46305.75</v>
       </c>
     </row>
     <row r="134">
@@ -7781,13 +7781,13 @@
         </is>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46306.79166666666</v>
+        <v>46305.875</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46305.91666666666</v>
       </c>
       <c r="M134" s="1" t="n">
-        <v>46307.08333333334</v>
+        <v>46306.16666666666</v>
       </c>
     </row>
     <row r="135">
@@ -7836,13 +7836,13 @@
         </is>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46307.5</v>
+        <v>46306.58333333334</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>46307.58333333334</v>
+        <v>46306.66666666666</v>
       </c>
       <c r="M135" s="1" t="n">
-        <v>46307.91666666666</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="136">
@@ -7891,13 +7891,13 @@
         </is>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46313</v>
+        <v>46312.08333333334</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>46313.16666666666</v>
+        <v>46312.25</v>
       </c>
       <c r="M136" s="1" t="n">
-        <v>46313.79166666666</v>
+        <v>46312.875</v>
       </c>
     </row>
     <row r="137">
@@ -7946,13 +7946,13 @@
         </is>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46315.58333333334</v>
+        <v>46314.66666666666</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>46315.625</v>
+        <v>46314.70833333334</v>
       </c>
       <c r="M137" s="1" t="n">
-        <v>46315.875</v>
+        <v>46314.95833333334</v>
       </c>
     </row>
     <row r="138">
@@ -8001,13 +8001,13 @@
         </is>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46316.16666666666</v>
+        <v>46315.25</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>46316.29166666666</v>
+        <v>46315.375</v>
       </c>
       <c r="M138" s="1" t="n">
-        <v>46317.79166666666</v>
+        <v>46316.875</v>
       </c>
     </row>
     <row r="139">
@@ -8056,13 +8056,13 @@
         </is>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46318</v>
+        <v>46317.08333333334</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>46318.04166666666</v>
+        <v>46317.125</v>
       </c>
       <c r="M139" s="1" t="n">
-        <v>46318.45833333334</v>
+        <v>46317.54166666666</v>
       </c>
     </row>
     <row r="140">
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46320.04166666666</v>
+        <v>46319.125</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>46320.20833333334</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="M140" s="1" t="n">
-        <v>46320.75</v>
+        <v>46319.83333333334</v>
       </c>
     </row>
     <row r="141">
@@ -8166,13 +8166,13 @@
         </is>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46328.08333333334</v>
+        <v>46327.16666666666</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>46328.125</v>
+        <v>46327.20833333334</v>
       </c>
       <c r="M141" s="1" t="n">
-        <v>46329.20833333334</v>
+        <v>46328.29166666666</v>
       </c>
     </row>
     <row r="142">
@@ -8221,13 +8221,13 @@
         </is>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46329.33333333334</v>
+        <v>46328.41666666666</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>46329.375</v>
+        <v>46328.45833333334</v>
       </c>
       <c r="M142" s="1" t="n">
-        <v>46329.625</v>
+        <v>46328.70833333334</v>
       </c>
     </row>
     <row r="143">
@@ -8276,13 +8276,13 @@
         </is>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46330.04166666666</v>
+        <v>46329.125</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>46330.125</v>
+        <v>46329.20833333334</v>
       </c>
       <c r="M143" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46329.54166666666</v>
       </c>
     </row>
     <row r="144">
@@ -8331,13 +8331,13 @@
         </is>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46335.54166666666</v>
+        <v>46334.625</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>46335.70833333334</v>
+        <v>46334.79166666666</v>
       </c>
       <c r="M144" s="1" t="n">
-        <v>46336.33333333334</v>
+        <v>46335.41666666666</v>
       </c>
     </row>
     <row r="145">
@@ -8386,13 +8386,13 @@
         </is>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46338.125</v>
+        <v>46337.20833333334</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>46338.16666666666</v>
+        <v>46337.25</v>
       </c>
       <c r="M145" s="1" t="n">
-        <v>46338.41666666666</v>
+        <v>46337.5</v>
       </c>
     </row>
     <row r="146">
@@ -8441,13 +8441,13 @@
         </is>
       </c>
       <c r="K146" s="1" t="n">
-        <v>46338.70833333334</v>
+        <v>46337.79166666666</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>46338.83333333334</v>
+        <v>46337.91666666666</v>
       </c>
       <c r="M146" s="1" t="n">
-        <v>46340.33333333334</v>
+        <v>46339.41666666666</v>
       </c>
     </row>
     <row r="147">
@@ -8496,13 +8496,13 @@
         </is>
       </c>
       <c r="K147" s="1" t="n">
-        <v>46340.54166666666</v>
+        <v>46339.625</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>46340.58333333334</v>
+        <v>46339.66666666666</v>
       </c>
       <c r="M147" s="1" t="n">
-        <v>46341</v>
+        <v>46340.08333333334</v>
       </c>
     </row>
     <row r="148">
@@ -8551,13 +8551,13 @@
         </is>
       </c>
       <c r="K148" s="1" t="n">
-        <v>46342.58333333334</v>
+        <v>46341.66666666666</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>46342.75</v>
+        <v>46341.83333333334</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>46343.29166666666</v>
+        <v>46342.375</v>
       </c>
     </row>
     <row r="149">
@@ -8606,13 +8606,13 @@
         </is>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46349</v>
+        <v>46348.08333333334</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>46349.04166666666</v>
+        <v>46348.125</v>
       </c>
       <c r="M149" s="1" t="n">
-        <v>46350.125</v>
+        <v>46349.20833333334</v>
       </c>
     </row>
     <row r="150">
@@ -8661,13 +8661,13 @@
         </is>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46350.25</v>
+        <v>46349.33333333334</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>46350.29166666666</v>
+        <v>46349.375</v>
       </c>
       <c r="M150" s="1" t="n">
-        <v>46350.54166666666</v>
+        <v>46349.625</v>
       </c>
     </row>
     <row r="151">
@@ -8716,13 +8716,13 @@
         </is>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46350.95833333334</v>
+        <v>46350.04166666666</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>46351.04166666666</v>
+        <v>46350.125</v>
       </c>
       <c r="M151" s="1" t="n">
-        <v>46351.375</v>
+        <v>46350.45833333334</v>
       </c>
     </row>
     <row r="152">
@@ -8771,13 +8771,13 @@
         </is>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46356.45833333334</v>
+        <v>46355.54166666666</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>46356.625</v>
+        <v>46355.70833333334</v>
       </c>
       <c r="M152" s="1" t="n">
-        <v>46357.25</v>
+        <v>46356.33333333334</v>
       </c>
     </row>
     <row r="153">
@@ -8826,13 +8826,13 @@
         </is>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46359.04166666666</v>
+        <v>46358.125</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>46359.08333333334</v>
+        <v>46358.16666666666</v>
       </c>
       <c r="M153" s="1" t="n">
-        <v>46359.33333333334</v>
+        <v>46358.41666666666</v>
       </c>
     </row>
     <row r="154">
@@ -8881,13 +8881,13 @@
         </is>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46359.625</v>
+        <v>46358.70833333334</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>46359.75</v>
+        <v>46358.83333333334</v>
       </c>
       <c r="M154" s="1" t="n">
-        <v>46361.25</v>
+        <v>46360.33333333334</v>
       </c>
     </row>
     <row r="155">
@@ -8936,13 +8936,13 @@
         </is>
       </c>
       <c r="K155" s="1" t="n">
-        <v>46361.45833333334</v>
+        <v>46360.54166666666</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>46361.5</v>
+        <v>46360.58333333334</v>
       </c>
       <c r="M155" s="1" t="n">
-        <v>46361.91666666666</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="156">
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="K156" s="1" t="n">
-        <v>46363.5</v>
+        <v>46362.58333333334</v>
       </c>
       <c r="L156" s="1" t="n">
-        <v>46363.66666666666</v>
+        <v>46362.75</v>
       </c>
       <c r="M156" s="1" t="n">
-        <v>46364.20833333334</v>
+        <v>46363.29166666666</v>
       </c>
     </row>
     <row r="157">
@@ -9046,13 +9046,13 @@
         </is>
       </c>
       <c r="K157" s="1" t="n">
-        <v>46369.04166666666</v>
+        <v>46368.125</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>46369.08333333334</v>
+        <v>46368.16666666666</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>46370.16666666666</v>
+        <v>46369.25</v>
       </c>
     </row>
     <row r="158">
@@ -9101,13 +9101,13 @@
         </is>
       </c>
       <c r="K158" s="1" t="n">
-        <v>46370.29166666666</v>
+        <v>46369.375</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>46370.33333333334</v>
+        <v>46369.41666666666</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>46370.58333333334</v>
+        <v>46369.66666666666</v>
       </c>
     </row>
     <row r="159">
@@ -9156,13 +9156,13 @@
         </is>
       </c>
       <c r="K159" s="1" t="n">
-        <v>46371</v>
+        <v>46370.08333333334</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>46371.08333333334</v>
+        <v>46370.16666666666</v>
       </c>
       <c r="M159" s="1" t="n">
-        <v>46371.41666666666</v>
+        <v>46370.5</v>
       </c>
     </row>
     <row r="160">
@@ -9211,13 +9211,13 @@
         </is>
       </c>
       <c r="K160" s="1" t="n">
-        <v>46376.5</v>
+        <v>46375.58333333334</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>46376.66666666666</v>
+        <v>46375.75</v>
       </c>
       <c r="M160" s="1" t="n">
-        <v>46377.29166666666</v>
+        <v>46376.375</v>
       </c>
     </row>
     <row r="161">
@@ -9266,13 +9266,13 @@
         </is>
       </c>
       <c r="K161" s="1" t="n">
-        <v>46379.08333333334</v>
+        <v>46378.16666666666</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>46379.125</v>
+        <v>46378.20833333334</v>
       </c>
       <c r="M161" s="1" t="n">
-        <v>46379.375</v>
+        <v>46378.45833333334</v>
       </c>
     </row>
     <row r="162">
@@ -9321,13 +9321,13 @@
         </is>
       </c>
       <c r="K162" s="1" t="n">
-        <v>46379.66666666666</v>
+        <v>46378.75</v>
       </c>
       <c r="L162" s="1" t="n">
-        <v>46379.79166666666</v>
+        <v>46378.875</v>
       </c>
       <c r="M162" s="1" t="n">
-        <v>46381.29166666666</v>
+        <v>46380.375</v>
       </c>
     </row>
     <row r="163">
@@ -9376,13 +9376,13 @@
         </is>
       </c>
       <c r="K163" s="1" t="n">
-        <v>46381.5</v>
+        <v>46380.58333333334</v>
       </c>
       <c r="L163" s="1" t="n">
-        <v>46381.54166666666</v>
+        <v>46380.625</v>
       </c>
       <c r="M163" s="1" t="n">
-        <v>46381.95833333334</v>
+        <v>46381.04166666666</v>
       </c>
     </row>
     <row r="164">
@@ -9427,13 +9427,13 @@
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" s="1" t="n">
-        <v>46383.54166666666</v>
+        <v>46382.625</v>
       </c>
       <c r="L164" s="1" t="n">
-        <v>46383.70833333334</v>
+        <v>46382.79166666666</v>
       </c>
       <c r="M164" s="1" t="n">
-        <v>46384.25</v>
+        <v>46383.33333333334</v>
       </c>
     </row>
     <row r="165">
@@ -17386,13 +17386,13 @@
         </is>
       </c>
       <c r="K309" s="1" t="n">
-        <v>46298.41666666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="L309" s="1" t="n">
-        <v>46298.45833333334</v>
+        <v>46298.75</v>
       </c>
       <c r="M309" s="1" t="n">
-        <v>46298.95833333334</v>
+        <v>46299.25</v>
       </c>
     </row>
     <row r="310">
@@ -17441,13 +17441,13 @@
         </is>
       </c>
       <c r="K310" s="1" t="n">
-        <v>46300.83333333334</v>
+        <v>46301.125</v>
       </c>
       <c r="L310" s="1" t="n">
-        <v>46300.875</v>
+        <v>46301.16666666666</v>
       </c>
       <c r="M310" s="1" t="n">
-        <v>46301.875</v>
+        <v>46302.16666666666</v>
       </c>
     </row>
     <row r="311">
@@ -17496,13 +17496,13 @@
         </is>
       </c>
       <c r="K311" s="1" t="n">
-        <v>46302</v>
+        <v>46302.29166666666</v>
       </c>
       <c r="L311" s="1" t="n">
-        <v>46302.04166666666</v>
+        <v>46302.33333333334</v>
       </c>
       <c r="M311" s="1" t="n">
-        <v>46302.41666666666</v>
+        <v>46302.70833333334</v>
       </c>
     </row>
     <row r="312">
@@ -17551,13 +17551,13 @@
         </is>
       </c>
       <c r="K312" s="1" t="n">
-        <v>46307.41666666666</v>
+        <v>46307.6875</v>
       </c>
       <c r="L312" s="1" t="n">
-        <v>46307.58333333334</v>
+        <v>46307.85416666666</v>
       </c>
       <c r="M312" s="1" t="n">
-        <v>46308.29166666666</v>
+        <v>46308.5625</v>
       </c>
     </row>
     <row r="313">
@@ -17606,13 +17606,13 @@
         </is>
       </c>
       <c r="K313" s="1" t="n">
-        <v>46309.95833333334</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="L313" s="1" t="n">
-        <v>46310</v>
+        <v>46310.25</v>
       </c>
       <c r="M313" s="1" t="n">
-        <v>46310.29166666666</v>
+        <v>46310.54166666666</v>
       </c>
     </row>
     <row r="314">
@@ -17661,13 +17661,13 @@
         </is>
       </c>
       <c r="K314" s="1" t="n">
-        <v>46310.41666666666</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="L314" s="1" t="n">
-        <v>46310.54166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="M314" s="1" t="n">
-        <v>46311.79166666666</v>
+        <v>46312.04166666666</v>
       </c>
     </row>
     <row r="315">
@@ -17716,13 +17716,13 @@
         </is>
       </c>
       <c r="K315" s="1" t="n">
-        <v>46312</v>
+        <v>46312.25</v>
       </c>
       <c r="L315" s="1" t="n">
-        <v>46312.04166666666</v>
+        <v>46312.29166666666</v>
       </c>
       <c r="M315" s="1" t="n">
-        <v>46312.5</v>
+        <v>46312.75</v>
       </c>
     </row>
     <row r="316">
@@ -17771,13 +17771,13 @@
         </is>
       </c>
       <c r="K316" s="1" t="n">
-        <v>46316.29166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="L316" s="1" t="n">
-        <v>46316.35416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="M316" s="1" t="n">
-        <v>46316.8125</v>
+        <v>46317.0625</v>
       </c>
     </row>
     <row r="317">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="K317" s="1" t="n">
-        <v>46318.08333333334</v>
+        <v>46318.33333333334</v>
       </c>
       <c r="L317" s="1" t="n">
-        <v>46318.125</v>
+        <v>46318.375</v>
       </c>
       <c r="M317" s="1" t="n">
-        <v>46318.625</v>
+        <v>46318.875</v>
       </c>
     </row>
     <row r="318">
@@ -17881,13 +17881,13 @@
         </is>
       </c>
       <c r="K318" s="1" t="n">
-        <v>46321.58333333334</v>
+        <v>46321.83333333334</v>
       </c>
       <c r="L318" s="1" t="n">
-        <v>46321.625</v>
+        <v>46321.875</v>
       </c>
       <c r="M318" s="1" t="n">
-        <v>46322.33333333334</v>
+        <v>46322.58333333334</v>
       </c>
     </row>
     <row r="319">
@@ -17936,13 +17936,13 @@
         </is>
       </c>
       <c r="K319" s="1" t="n">
-        <v>46322.54166666666</v>
+        <v>46322.79166666666</v>
       </c>
       <c r="L319" s="1" t="n">
-        <v>46322.58333333334</v>
+        <v>46322.83333333334</v>
       </c>
       <c r="M319" s="1" t="n">
-        <v>46322.91666666666</v>
+        <v>46323.16666666666</v>
       </c>
     </row>
     <row r="320">
@@ -17991,13 +17991,13 @@
         </is>
       </c>
       <c r="K320" s="1" t="n">
-        <v>46325.75</v>
+        <v>46326</v>
       </c>
       <c r="L320" s="1" t="n">
-        <v>46325.79166666666</v>
+        <v>46326.04166666666</v>
       </c>
       <c r="M320" s="1" t="n">
-        <v>46326.16666666666</v>
+        <v>46326.41666666666</v>
       </c>
     </row>
     <row r="321">
@@ -18046,13 +18046,13 @@
         </is>
       </c>
       <c r="K321" s="1" t="n">
-        <v>46328.625</v>
+        <v>46328.875</v>
       </c>
       <c r="L321" s="1" t="n">
-        <v>46328.79166666666</v>
+        <v>46329.04166666666</v>
       </c>
       <c r="M321" s="1" t="n">
-        <v>46329.33333333334</v>
+        <v>46329.58333333334</v>
       </c>
     </row>
     <row r="322">
@@ -18101,13 +18101,13 @@
         </is>
       </c>
       <c r="K322" s="1" t="n">
-        <v>46331.125</v>
+        <v>46331.375</v>
       </c>
       <c r="L322" s="1" t="n">
-        <v>46331.16666666666</v>
+        <v>46331.41666666666</v>
       </c>
       <c r="M322" s="1" t="n">
-        <v>46331.41666666666</v>
+        <v>46331.66666666666</v>
       </c>
     </row>
     <row r="323">
@@ -18156,13 +18156,13 @@
         </is>
       </c>
       <c r="K323" s="1" t="n">
-        <v>46331.83333333334</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="L323" s="1" t="n">
-        <v>46331.95833333334</v>
+        <v>46332.20833333334</v>
       </c>
       <c r="M323" s="1" t="n">
-        <v>46333.08333333334</v>
+        <v>46333.33333333334</v>
       </c>
     </row>
     <row r="324">
@@ -18211,13 +18211,13 @@
         </is>
       </c>
       <c r="K324" s="1" t="n">
-        <v>46333.41666666666</v>
+        <v>46333.66666666666</v>
       </c>
       <c r="L324" s="1" t="n">
-        <v>46333.45833333334</v>
+        <v>46333.70833333334</v>
       </c>
       <c r="M324" s="1" t="n">
-        <v>46333.79166666666</v>
+        <v>46334.04166666666</v>
       </c>
     </row>
     <row r="325">
@@ -18266,13 +18266,13 @@
         </is>
       </c>
       <c r="K325" s="1" t="n">
-        <v>46337.66666666666</v>
+        <v>46337.91666666666</v>
       </c>
       <c r="L325" s="1" t="n">
-        <v>46337.70833333334</v>
+        <v>46337.95833333334</v>
       </c>
       <c r="M325" s="1" t="n">
-        <v>46338.125</v>
+        <v>46338.375</v>
       </c>
     </row>
     <row r="326">
@@ -18321,13 +18321,13 @@
         </is>
       </c>
       <c r="K326" s="1" t="n">
-        <v>46338.375</v>
+        <v>46338.625</v>
       </c>
       <c r="L326" s="1" t="n">
-        <v>46338.375</v>
+        <v>46338.625</v>
       </c>
       <c r="M326" s="1" t="n">
-        <v>46338.75</v>
+        <v>46339</v>
       </c>
     </row>
     <row r="327">
@@ -18376,13 +18376,13 @@
         </is>
       </c>
       <c r="K327" s="1" t="n">
-        <v>46340</v>
+        <v>46340.25</v>
       </c>
       <c r="L327" s="1" t="n">
-        <v>46340</v>
+        <v>46340.25</v>
       </c>
       <c r="M327" s="1" t="n">
-        <v>46340.25</v>
+        <v>46340.5</v>
       </c>
     </row>
     <row r="328">
@@ -18431,13 +18431,13 @@
         </is>
       </c>
       <c r="K328" s="1" t="n">
-        <v>46342.58333333334</v>
+        <v>46342.83333333334</v>
       </c>
       <c r="L328" s="1" t="n">
-        <v>46342.625</v>
+        <v>46342.875</v>
       </c>
       <c r="M328" s="1" t="n">
-        <v>46343.33333333334</v>
+        <v>46343.58333333334</v>
       </c>
     </row>
     <row r="329">
@@ -18486,13 +18486,13 @@
         </is>
       </c>
       <c r="K329" s="1" t="n">
-        <v>46343.54166666666</v>
+        <v>46343.79166666666</v>
       </c>
       <c r="L329" s="1" t="n">
-        <v>46343.58333333334</v>
+        <v>46343.83333333334</v>
       </c>
       <c r="M329" s="1" t="n">
-        <v>46343.91666666666</v>
+        <v>46344.16666666666</v>
       </c>
     </row>
     <row r="330">
@@ -18541,13 +18541,13 @@
         </is>
       </c>
       <c r="K330" s="1" t="n">
-        <v>46346.75</v>
+        <v>46347</v>
       </c>
       <c r="L330" s="1" t="n">
-        <v>46346.79166666666</v>
+        <v>46347.04166666666</v>
       </c>
       <c r="M330" s="1" t="n">
-        <v>46347.16666666666</v>
+        <v>46347.41666666666</v>
       </c>
     </row>
     <row r="331">
@@ -18596,13 +18596,13 @@
         </is>
       </c>
       <c r="K331" s="1" t="n">
-        <v>46349.625</v>
+        <v>46349.875</v>
       </c>
       <c r="L331" s="1" t="n">
-        <v>46349.79166666666</v>
+        <v>46350.04166666666</v>
       </c>
       <c r="M331" s="1" t="n">
-        <v>46350.33333333334</v>
+        <v>46350.58333333334</v>
       </c>
     </row>
     <row r="332">
@@ -18651,13 +18651,13 @@
         </is>
       </c>
       <c r="K332" s="1" t="n">
-        <v>46352.125</v>
+        <v>46352.375</v>
       </c>
       <c r="L332" s="1" t="n">
-        <v>46352.16666666666</v>
+        <v>46352.41666666666</v>
       </c>
       <c r="M332" s="1" t="n">
-        <v>46352.41666666666</v>
+        <v>46352.66666666666</v>
       </c>
     </row>
     <row r="333">
@@ -18706,13 +18706,13 @@
         </is>
       </c>
       <c r="K333" s="1" t="n">
-        <v>46352.83333333334</v>
+        <v>46353.08333333334</v>
       </c>
       <c r="L333" s="1" t="n">
-        <v>46352.95833333334</v>
+        <v>46353.20833333334</v>
       </c>
       <c r="M333" s="1" t="n">
-        <v>46354.08333333334</v>
+        <v>46354.33333333334</v>
       </c>
     </row>
     <row r="334">
@@ -18761,13 +18761,13 @@
         </is>
       </c>
       <c r="K334" s="1" t="n">
-        <v>46354.41666666666</v>
+        <v>46354.66666666666</v>
       </c>
       <c r="L334" s="1" t="n">
-        <v>46354.45833333334</v>
+        <v>46354.70833333334</v>
       </c>
       <c r="M334" s="1" t="n">
-        <v>46354.79166666666</v>
+        <v>46355.04166666666</v>
       </c>
     </row>
     <row r="335">
@@ -18816,13 +18816,13 @@
         </is>
       </c>
       <c r="K335" s="1" t="n">
-        <v>46358.66666666666</v>
+        <v>46358.91666666666</v>
       </c>
       <c r="L335" s="1" t="n">
-        <v>46358.70833333334</v>
+        <v>46358.95833333334</v>
       </c>
       <c r="M335" s="1" t="n">
-        <v>46359.125</v>
+        <v>46359.375</v>
       </c>
     </row>
     <row r="336">
@@ -18871,13 +18871,13 @@
         </is>
       </c>
       <c r="K336" s="1" t="n">
-        <v>46359.375</v>
+        <v>46359.625</v>
       </c>
       <c r="L336" s="1" t="n">
-        <v>46359.375</v>
+        <v>46359.625</v>
       </c>
       <c r="M336" s="1" t="n">
-        <v>46359.75</v>
+        <v>46360</v>
       </c>
     </row>
     <row r="337">
@@ -18926,13 +18926,13 @@
         </is>
       </c>
       <c r="K337" s="1" t="n">
-        <v>46361</v>
+        <v>46361.25</v>
       </c>
       <c r="L337" s="1" t="n">
-        <v>46361</v>
+        <v>46361.25</v>
       </c>
       <c r="M337" s="1" t="n">
-        <v>46361.25</v>
+        <v>46361.5</v>
       </c>
     </row>
     <row r="338">
@@ -18981,13 +18981,13 @@
         </is>
       </c>
       <c r="K338" s="1" t="n">
-        <v>46363.58333333334</v>
+        <v>46363.83333333334</v>
       </c>
       <c r="L338" s="1" t="n">
-        <v>46363.625</v>
+        <v>46363.875</v>
       </c>
       <c r="M338" s="1" t="n">
-        <v>46364.33333333334</v>
+        <v>46364.58333333334</v>
       </c>
     </row>
     <row r="339">
@@ -19036,13 +19036,13 @@
         </is>
       </c>
       <c r="K339" s="1" t="n">
-        <v>46364.54166666666</v>
+        <v>46364.79166666666</v>
       </c>
       <c r="L339" s="1" t="n">
-        <v>46364.58333333334</v>
+        <v>46364.83333333334</v>
       </c>
       <c r="M339" s="1" t="n">
-        <v>46364.91666666666</v>
+        <v>46365.16666666666</v>
       </c>
     </row>
     <row r="340">
@@ -19091,13 +19091,13 @@
         </is>
       </c>
       <c r="K340" s="1" t="n">
-        <v>46367.75</v>
+        <v>46368</v>
       </c>
       <c r="L340" s="1" t="n">
-        <v>46367.79166666666</v>
+        <v>46368.04166666666</v>
       </c>
       <c r="M340" s="1" t="n">
-        <v>46368.16666666666</v>
+        <v>46368.41666666666</v>
       </c>
     </row>
     <row r="341">
@@ -19146,13 +19146,13 @@
         </is>
       </c>
       <c r="K341" s="1" t="n">
-        <v>46370.625</v>
+        <v>46370.875</v>
       </c>
       <c r="L341" s="1" t="n">
-        <v>46370.79166666666</v>
+        <v>46371.04166666666</v>
       </c>
       <c r="M341" s="1" t="n">
-        <v>46371.33333333334</v>
+        <v>46371.58333333334</v>
       </c>
     </row>
     <row r="342">
@@ -19201,13 +19201,13 @@
         </is>
       </c>
       <c r="K342" s="1" t="n">
-        <v>46373.125</v>
+        <v>46373.375</v>
       </c>
       <c r="L342" s="1" t="n">
-        <v>46373.16666666666</v>
+        <v>46373.41666666666</v>
       </c>
       <c r="M342" s="1" t="n">
-        <v>46373.41666666666</v>
+        <v>46373.66666666666</v>
       </c>
     </row>
     <row r="343">
@@ -19256,13 +19256,13 @@
         </is>
       </c>
       <c r="K343" s="1" t="n">
-        <v>46373.83333333334</v>
+        <v>46374.08333333334</v>
       </c>
       <c r="L343" s="1" t="n">
-        <v>46373.95833333334</v>
+        <v>46374.20833333334</v>
       </c>
       <c r="M343" s="1" t="n">
-        <v>46375.08333333334</v>
+        <v>46375.33333333334</v>
       </c>
     </row>
     <row r="344">
@@ -19311,13 +19311,13 @@
         </is>
       </c>
       <c r="K344" s="1" t="n">
-        <v>46375.41666666666</v>
+        <v>46375.66666666666</v>
       </c>
       <c r="L344" s="1" t="n">
-        <v>46375.45833333334</v>
+        <v>46375.70833333334</v>
       </c>
       <c r="M344" s="1" t="n">
-        <v>46375.79166666666</v>
+        <v>46376.04166666666</v>
       </c>
     </row>
     <row r="345">
@@ -19366,13 +19366,13 @@
         </is>
       </c>
       <c r="K345" s="1" t="n">
-        <v>46379.66666666666</v>
+        <v>46379.91666666666</v>
       </c>
       <c r="L345" s="1" t="n">
-        <v>46379.70833333334</v>
+        <v>46379.95833333334</v>
       </c>
       <c r="M345" s="1" t="n">
-        <v>46380.125</v>
+        <v>46380.375</v>
       </c>
     </row>
     <row r="346">
@@ -19421,13 +19421,13 @@
         </is>
       </c>
       <c r="K346" s="1" t="n">
-        <v>46380.375</v>
+        <v>46380.625</v>
       </c>
       <c r="L346" s="1" t="n">
-        <v>46380.375</v>
+        <v>46380.625</v>
       </c>
       <c r="M346" s="1" t="n">
-        <v>46380.75</v>
+        <v>46381</v>
       </c>
     </row>
     <row r="347">
@@ -19476,13 +19476,13 @@
         </is>
       </c>
       <c r="K347" s="1" t="n">
-        <v>46382</v>
+        <v>46382.25</v>
       </c>
       <c r="L347" s="1" t="n">
-        <v>46382</v>
+        <v>46382.25</v>
       </c>
       <c r="M347" s="1" t="n">
-        <v>46382.25</v>
+        <v>46382.5</v>
       </c>
     </row>
     <row r="348">
@@ -19531,13 +19531,13 @@
         </is>
       </c>
       <c r="K348" s="1" t="n">
-        <v>46384.58333333334</v>
+        <v>46384.83333333334</v>
       </c>
       <c r="L348" s="1" t="n">
-        <v>46384.625</v>
+        <v>46384.875</v>
       </c>
       <c r="M348" s="1" t="n">
-        <v>46385.33333333334</v>
+        <v>46385.58333333334</v>
       </c>
     </row>
     <row r="349">
@@ -19586,13 +19586,13 @@
         </is>
       </c>
       <c r="K349" s="1" t="n">
-        <v>46385.54166666666</v>
+        <v>46385.79166666666</v>
       </c>
       <c r="L349" s="1" t="n">
-        <v>46385.58333333334</v>
+        <v>46385.83333333334</v>
       </c>
       <c r="M349" s="1" t="n">
-        <v>46385.91666666666</v>
+        <v>46386.16666666666</v>
       </c>
     </row>
     <row r="350">
@@ -19641,13 +19641,13 @@
         </is>
       </c>
       <c r="K350" s="1" t="n">
-        <v>46388.75</v>
+        <v>46389</v>
       </c>
       <c r="L350" s="1" t="n">
-        <v>46388.79166666666</v>
+        <v>46389.04166666666</v>
       </c>
       <c r="M350" s="1" t="n">
-        <v>46389.16666666666</v>
+        <v>46389.41666666666</v>
       </c>
     </row>
     <row r="351">
@@ -19696,13 +19696,13 @@
         </is>
       </c>
       <c r="K351" s="1" t="n">
-        <v>46391.625</v>
+        <v>46391.875</v>
       </c>
       <c r="L351" s="1" t="n">
-        <v>46391.79166666666</v>
+        <v>46392.04166666666</v>
       </c>
       <c r="M351" s="1" t="n">
-        <v>46392.33333333334</v>
+        <v>46392.58333333334</v>
       </c>
     </row>
     <row r="352">
@@ -19751,13 +19751,13 @@
         </is>
       </c>
       <c r="K352" s="1" t="n">
-        <v>46394.125</v>
+        <v>46394.375</v>
       </c>
       <c r="L352" s="1" t="n">
-        <v>46394.16666666666</v>
+        <v>46394.41666666666</v>
       </c>
       <c r="M352" s="1" t="n">
-        <v>46394.41666666666</v>
+        <v>46394.66666666666</v>
       </c>
     </row>
     <row r="353">
@@ -19806,13 +19806,13 @@
         </is>
       </c>
       <c r="K353" s="1" t="n">
-        <v>46394.83333333334</v>
+        <v>46395.08333333334</v>
       </c>
       <c r="L353" s="1" t="n">
-        <v>46394.95833333334</v>
+        <v>46395.20833333334</v>
       </c>
       <c r="M353" s="1" t="n">
-        <v>46396.08333333334</v>
+        <v>46396.33333333334</v>
       </c>
     </row>
     <row r="354">
@@ -19861,13 +19861,13 @@
         </is>
       </c>
       <c r="K354" s="1" t="n">
-        <v>46396.41666666666</v>
+        <v>46396.66666666666</v>
       </c>
       <c r="L354" s="1" t="n">
-        <v>46396.45833333334</v>
+        <v>46396.70833333334</v>
       </c>
       <c r="M354" s="1" t="n">
-        <v>46396.79166666666</v>
+        <v>46397.04166666666</v>
       </c>
     </row>
     <row r="355">
@@ -19916,13 +19916,13 @@
         </is>
       </c>
       <c r="K355" s="1" t="n">
-        <v>46400.66666666666</v>
+        <v>46400.91666666666</v>
       </c>
       <c r="L355" s="1" t="n">
-        <v>46400.70833333334</v>
+        <v>46400.95833333334</v>
       </c>
       <c r="M355" s="1" t="n">
-        <v>46401.125</v>
+        <v>46401.375</v>
       </c>
     </row>
     <row r="356">
@@ -19971,13 +19971,13 @@
         </is>
       </c>
       <c r="K356" s="1" t="n">
-        <v>46401.375</v>
+        <v>46401.625</v>
       </c>
       <c r="L356" s="1" t="n">
-        <v>46401.375</v>
+        <v>46401.625</v>
       </c>
       <c r="M356" s="1" t="n">
-        <v>46401.75</v>
+        <v>46402</v>
       </c>
     </row>
     <row r="357">
@@ -20022,13 +20022,13 @@
       </c>
       <c r="J357" t="inlineStr"/>
       <c r="K357" s="1" t="n">
-        <v>46403</v>
+        <v>46403.25</v>
       </c>
       <c r="L357" s="1" t="n">
-        <v>46403</v>
+        <v>46403.25</v>
       </c>
       <c r="M357" s="1" t="n">
-        <v>46403.25</v>
+        <v>46403.5</v>
       </c>
     </row>
     <row r="358">
@@ -29309,7 +29309,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>ADHS</t>
+          <t>SIS2</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -29324,16 +29324,16 @@
       </c>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="n">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -29352,19 +29352,19 @@
         </is>
       </c>
       <c r="K527" s="1" t="n">
-        <v>46304.33333333334</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="L527" s="1" t="n">
-        <v>46304.375</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="M527" s="1" t="n">
-        <v>46306.375</v>
+        <v>46307.83333333334</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>SIS2</t>
+          <t>ADHS</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -29379,16 +29379,16 @@
       </c>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="n">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -34458,10 +34458,10 @@
         <v>46295.95833333334</v>
       </c>
       <c r="L620" s="1" t="n">
-        <v>46296.625</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="M620" s="1" t="n">
-        <v>46297.08333333334</v>
+        <v>46297.625</v>
       </c>
     </row>
     <row r="621">
@@ -34510,13 +34510,13 @@
         </is>
       </c>
       <c r="K621" s="1" t="n">
-        <v>46302.41666666666</v>
+        <v>46302.95833333334</v>
       </c>
       <c r="L621" s="1" t="n">
-        <v>46302.45833333334</v>
+        <v>46303</v>
       </c>
       <c r="M621" s="1" t="n">
-        <v>46303.45833333334</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="622">
@@ -34565,13 +34565,13 @@
         </is>
       </c>
       <c r="K622" s="1" t="n">
-        <v>46304.45833333334</v>
+        <v>46305</v>
       </c>
       <c r="L622" s="1" t="n">
-        <v>46304.5</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="M622" s="1" t="n">
-        <v>46305.5</v>
+        <v>46306.04166666666</v>
       </c>
     </row>
     <row r="623">
@@ -34620,13 +34620,13 @@
         </is>
       </c>
       <c r="K623" s="1" t="n">
-        <v>46310.125</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="L623" s="1" t="n">
-        <v>46310.29166666666</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="M623" s="1" t="n">
-        <v>46310.66666666666</v>
+        <v>46311.08333333334</v>
       </c>
     </row>
     <row r="624">
@@ -34675,13 +34675,13 @@
         </is>
       </c>
       <c r="K624" s="1" t="n">
-        <v>46312.5</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="L624" s="1" t="n">
-        <v>46312.54166666666</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="M624" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.375</v>
       </c>
     </row>
     <row r="625">
@@ -34730,13 +34730,13 @@
         </is>
       </c>
       <c r="K625" s="1" t="n">
-        <v>46313.08333333334</v>
+        <v>46313.5</v>
       </c>
       <c r="L625" s="1" t="n">
-        <v>46313.16666666666</v>
+        <v>46313.58333333334</v>
       </c>
       <c r="M625" s="1" t="n">
-        <v>46314.20833333334</v>
+        <v>46314.625</v>
       </c>
     </row>
     <row r="626">
@@ -34785,13 +34785,13 @@
         </is>
       </c>
       <c r="K626" s="1" t="n">
-        <v>46314.375</v>
+        <v>46314.79166666666</v>
       </c>
       <c r="L626" s="1" t="n">
-        <v>46314.41666666666</v>
+        <v>46314.83333333334</v>
       </c>
       <c r="M626" s="1" t="n">
-        <v>46314.91666666666</v>
+        <v>46315.33333333334</v>
       </c>
     </row>
     <row r="627">
@@ -34840,13 +34840,13 @@
         </is>
       </c>
       <c r="K627" s="1" t="n">
-        <v>46316.375</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="L627" s="1" t="n">
-        <v>46316.54166666666</v>
+        <v>46316.95833333334</v>
       </c>
       <c r="M627" s="1" t="n">
-        <v>46317.58333333334</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="628">
@@ -39345,10 +39345,10 @@
         <v>46299.79166666666</v>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46300.08333333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="M709" s="1" t="n">
-        <v>46301</v>
+        <v>46300.75</v>
       </c>
     </row>
     <row r="710">
@@ -39397,13 +39397,13 @@
         </is>
       </c>
       <c r="K710" s="1" t="n">
-        <v>46306.41666666666</v>
+        <v>46306.16666666666</v>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46306.58333333334</v>
+        <v>46306.33333333334</v>
       </c>
       <c r="M710" s="1" t="n">
-        <v>46307.16666666666</v>
+        <v>46306.91666666666</v>
       </c>
     </row>
     <row r="711">
@@ -39452,13 +39452,13 @@
         </is>
       </c>
       <c r="K711" s="1" t="n">
-        <v>46308.9375</v>
+        <v>46308.6875</v>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46308.97916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="M711" s="1" t="n">
-        <v>46309.33333333334</v>
+        <v>46309.08333333334</v>
       </c>
     </row>
     <row r="712">
@@ -39507,13 +39507,13 @@
         </is>
       </c>
       <c r="K712" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46309.54166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="M712" s="1" t="n">
-        <v>46310.54166666666</v>
+        <v>46310.29166666666</v>
       </c>
     </row>
     <row r="713">
@@ -39562,13 +39562,13 @@
         </is>
       </c>
       <c r="K713" s="1" t="n">
-        <v>46310.75</v>
+        <v>46310.5</v>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="M713" s="1" t="n">
-        <v>46311.29166666666</v>
+        <v>46311.04166666666</v>
       </c>
     </row>
     <row r="714">
@@ -39617,13 +39617,13 @@
         </is>
       </c>
       <c r="K714" s="1" t="n">
-        <v>46313.10416666666</v>
+        <v>46312.85416666666</v>
       </c>
       <c r="L714" s="1" t="n">
-        <v>46313.27083333334</v>
+        <v>46313.02083333334</v>
       </c>
       <c r="M714" s="1" t="n">
-        <v>46313.95833333334</v>
+        <v>46313.70833333334</v>
       </c>
     </row>
     <row r="715">
@@ -41318,13 +41318,13 @@
         </is>
       </c>
       <c r="K745" s="1" t="n">
-        <v>46299.375</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="L745" s="1" t="n">
-        <v>46299.41666666666</v>
+        <v>46299.5</v>
       </c>
       <c r="M745" s="1" t="n">
-        <v>46299.70833333334</v>
+        <v>46299.79166666666</v>
       </c>
     </row>
     <row r="746">
@@ -41373,13 +41373,13 @@
         </is>
       </c>
       <c r="K746" s="1" t="n">
-        <v>46300</v>
+        <v>46299.875</v>
       </c>
       <c r="L746" s="1" t="n">
-        <v>46300</v>
+        <v>46300.625</v>
       </c>
       <c r="M746" s="1" t="n">
-        <v>46301.375</v>
+        <v>46302.5</v>
       </c>
     </row>
     <row r="747">
@@ -41428,13 +41428,13 @@
         </is>
       </c>
       <c r="K747" s="1" t="n">
-        <v>46301.625</v>
+        <v>46302.70833333334</v>
       </c>
       <c r="L747" s="1" t="n">
-        <v>46301.66666666666</v>
+        <v>46302.75</v>
       </c>
       <c r="M747" s="1" t="n">
-        <v>46302.125</v>
+        <v>46303.20833333334</v>
       </c>
     </row>
     <row r="748">
@@ -41483,13 +41483,13 @@
         </is>
       </c>
       <c r="K748" s="1" t="n">
-        <v>46305.95833333334</v>
+        <v>46307.04166666666</v>
       </c>
       <c r="L748" s="1" t="n">
-        <v>46305.95833333334</v>
+        <v>46307.04166666666</v>
       </c>
       <c r="M748" s="1" t="n">
-        <v>46306.41666666666</v>
+        <v>46307.5</v>
       </c>
     </row>
     <row r="749">
@@ -41538,13 +41538,13 @@
         </is>
       </c>
       <c r="K749" s="1" t="n">
-        <v>46307.41666666666</v>
+        <v>46308.5</v>
       </c>
       <c r="L749" s="1" t="n">
-        <v>46307.41666666666</v>
+        <v>46308.5</v>
       </c>
       <c r="M749" s="1" t="n">
-        <v>46307.875</v>
+        <v>46308.95833333334</v>
       </c>
     </row>
     <row r="750">
@@ -41593,13 +41593,13 @@
         </is>
       </c>
       <c r="K750" s="1" t="n">
-        <v>46310.375</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="L750" s="1" t="n">
-        <v>46310.41666666666</v>
+        <v>46311.5</v>
       </c>
       <c r="M750" s="1" t="n">
-        <v>46311.04166666666</v>
+        <v>46312.125</v>
       </c>
     </row>
     <row r="751">
@@ -41648,13 +41648,13 @@
         </is>
       </c>
       <c r="K751" s="1" t="n">
-        <v>46312.04166666666</v>
+        <v>46313.125</v>
       </c>
       <c r="L751" s="1" t="n">
-        <v>46312.08333333334</v>
+        <v>46313.16666666666</v>
       </c>
       <c r="M751" s="1" t="n">
-        <v>46312.58333333334</v>
+        <v>46313.66666666666</v>
       </c>
     </row>
     <row r="752">
@@ -41703,13 +41703,13 @@
         </is>
       </c>
       <c r="K752" s="1" t="n">
-        <v>46313.66666666666</v>
+        <v>46314.75</v>
       </c>
       <c r="L752" s="1" t="n">
-        <v>46313.83333333334</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="M752" s="1" t="n">
-        <v>46314.625</v>
+        <v>46315.70833333334</v>
       </c>
     </row>
     <row r="753">
@@ -41758,13 +41758,13 @@
         </is>
       </c>
       <c r="K753" s="1" t="n">
-        <v>46320.375</v>
+        <v>46321.45833333334</v>
       </c>
       <c r="L753" s="1" t="n">
-        <v>46320.41666666666</v>
+        <v>46321.5</v>
       </c>
       <c r="M753" s="1" t="n">
-        <v>46320.70833333334</v>
+        <v>46321.79166666666</v>
       </c>
     </row>
     <row r="754">
@@ -41813,13 +41813,13 @@
         </is>
       </c>
       <c r="K754" s="1" t="n">
-        <v>46321</v>
+        <v>46322.08333333334</v>
       </c>
       <c r="L754" s="1" t="n">
-        <v>46321</v>
+        <v>46322.08333333334</v>
       </c>
       <c r="M754" s="1" t="n">
-        <v>46322.375</v>
+        <v>46323.45833333334</v>
       </c>
     </row>
     <row r="755">
@@ -41868,13 +41868,13 @@
         </is>
       </c>
       <c r="K755" s="1" t="n">
-        <v>46322.625</v>
+        <v>46323.70833333334</v>
       </c>
       <c r="L755" s="1" t="n">
-        <v>46322.66666666666</v>
+        <v>46323.75</v>
       </c>
       <c r="M755" s="1" t="n">
-        <v>46323.125</v>
+        <v>46324.20833333334</v>
       </c>
     </row>
     <row r="756">
@@ -41923,13 +41923,13 @@
         </is>
       </c>
       <c r="K756" s="1" t="n">
-        <v>46326.95833333334</v>
+        <v>46328.04166666666</v>
       </c>
       <c r="L756" s="1" t="n">
-        <v>46326.95833333334</v>
+        <v>46328.04166666666</v>
       </c>
       <c r="M756" s="1" t="n">
-        <v>46327.41666666666</v>
+        <v>46328.5</v>
       </c>
     </row>
     <row r="757">
@@ -41978,13 +41978,13 @@
         </is>
       </c>
       <c r="K757" s="1" t="n">
-        <v>46328.41666666666</v>
+        <v>46329.5</v>
       </c>
       <c r="L757" s="1" t="n">
-        <v>46328.41666666666</v>
+        <v>46329.5</v>
       </c>
       <c r="M757" s="1" t="n">
-        <v>46328.91666666666</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="758">
@@ -42033,13 +42033,13 @@
         </is>
       </c>
       <c r="K758" s="1" t="n">
-        <v>46331.375</v>
+        <v>46332.45833333334</v>
       </c>
       <c r="L758" s="1" t="n">
-        <v>46331.41666666666</v>
+        <v>46332.5</v>
       </c>
       <c r="M758" s="1" t="n">
-        <v>46332.04166666666</v>
+        <v>46333.125</v>
       </c>
     </row>
     <row r="759">
@@ -42088,13 +42088,13 @@
         </is>
       </c>
       <c r="K759" s="1" t="n">
-        <v>46333.04166666666</v>
+        <v>46334.125</v>
       </c>
       <c r="L759" s="1" t="n">
-        <v>46333.08333333334</v>
+        <v>46334.16666666666</v>
       </c>
       <c r="M759" s="1" t="n">
-        <v>46333.58333333334</v>
+        <v>46334.66666666666</v>
       </c>
     </row>
     <row r="760">
@@ -42143,13 +42143,13 @@
         </is>
       </c>
       <c r="K760" s="1" t="n">
-        <v>46334.66666666666</v>
+        <v>46335.75</v>
       </c>
       <c r="L760" s="1" t="n">
-        <v>46334.83333333334</v>
+        <v>46335.91666666666</v>
       </c>
       <c r="M760" s="1" t="n">
-        <v>46335.625</v>
+        <v>46336.70833333334</v>
       </c>
     </row>
     <row r="761">
@@ -42198,13 +42198,13 @@
         </is>
       </c>
       <c r="K761" s="1" t="n">
-        <v>46341.375</v>
+        <v>46342.45833333334</v>
       </c>
       <c r="L761" s="1" t="n">
-        <v>46341.41666666666</v>
+        <v>46342.5</v>
       </c>
       <c r="M761" s="1" t="n">
-        <v>46341.70833333334</v>
+        <v>46342.79166666666</v>
       </c>
     </row>
     <row r="762">
@@ -42253,13 +42253,13 @@
         </is>
       </c>
       <c r="K762" s="1" t="n">
-        <v>46342</v>
+        <v>46343.08333333334</v>
       </c>
       <c r="L762" s="1" t="n">
-        <v>46342</v>
+        <v>46343.08333333334</v>
       </c>
       <c r="M762" s="1" t="n">
-        <v>46343.375</v>
+        <v>46344.45833333334</v>
       </c>
     </row>
     <row r="763">
@@ -42308,13 +42308,13 @@
         </is>
       </c>
       <c r="K763" s="1" t="n">
-        <v>46343.625</v>
+        <v>46344.70833333334</v>
       </c>
       <c r="L763" s="1" t="n">
-        <v>46343.66666666666</v>
+        <v>46344.75</v>
       </c>
       <c r="M763" s="1" t="n">
-        <v>46344.125</v>
+        <v>46345.20833333334</v>
       </c>
     </row>
     <row r="764">
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="K764" s="1" t="n">
-        <v>46347.95833333334</v>
+        <v>46349.04166666666</v>
       </c>
       <c r="L764" s="1" t="n">
-        <v>46347.95833333334</v>
+        <v>46349.04166666666</v>
       </c>
       <c r="M764" s="1" t="n">
-        <v>46348.41666666666</v>
+        <v>46349.5</v>
       </c>
     </row>
     <row r="765">
@@ -42418,13 +42418,13 @@
         </is>
       </c>
       <c r="K765" s="1" t="n">
-        <v>46349.41666666666</v>
+        <v>46350.5</v>
       </c>
       <c r="L765" s="1" t="n">
-        <v>46349.41666666666</v>
+        <v>46350.5</v>
       </c>
       <c r="M765" s="1" t="n">
-        <v>46349.91666666666</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="766">
@@ -42473,13 +42473,13 @@
         </is>
       </c>
       <c r="K766" s="1" t="n">
-        <v>46352.375</v>
+        <v>46353.45833333334</v>
       </c>
       <c r="L766" s="1" t="n">
-        <v>46352.41666666666</v>
+        <v>46353.5</v>
       </c>
       <c r="M766" s="1" t="n">
-        <v>46353.04166666666</v>
+        <v>46354.125</v>
       </c>
     </row>
     <row r="767">
@@ -42528,13 +42528,13 @@
         </is>
       </c>
       <c r="K767" s="1" t="n">
-        <v>46354.04166666666</v>
+        <v>46355.125</v>
       </c>
       <c r="L767" s="1" t="n">
-        <v>46354.08333333334</v>
+        <v>46355.16666666666</v>
       </c>
       <c r="M767" s="1" t="n">
-        <v>46354.58333333334</v>
+        <v>46355.66666666666</v>
       </c>
     </row>
     <row r="768">
@@ -42583,13 +42583,13 @@
         </is>
       </c>
       <c r="K768" s="1" t="n">
-        <v>46355.66666666666</v>
+        <v>46356.75</v>
       </c>
       <c r="L768" s="1" t="n">
-        <v>46355.83333333334</v>
+        <v>46356.91666666666</v>
       </c>
       <c r="M768" s="1" t="n">
-        <v>46356.625</v>
+        <v>46357.70833333334</v>
       </c>
     </row>
     <row r="769">
@@ -42638,13 +42638,13 @@
         </is>
       </c>
       <c r="K769" s="1" t="n">
-        <v>46362.375</v>
+        <v>46363.45833333334</v>
       </c>
       <c r="L769" s="1" t="n">
-        <v>46362.41666666666</v>
+        <v>46363.5</v>
       </c>
       <c r="M769" s="1" t="n">
-        <v>46362.70833333334</v>
+        <v>46363.79166666666</v>
       </c>
     </row>
     <row r="770">
@@ -42693,13 +42693,13 @@
         </is>
       </c>
       <c r="K770" s="1" t="n">
-        <v>46363</v>
+        <v>46364.08333333334</v>
       </c>
       <c r="L770" s="1" t="n">
-        <v>46363</v>
+        <v>46364.08333333334</v>
       </c>
       <c r="M770" s="1" t="n">
-        <v>46364.375</v>
+        <v>46365.45833333334</v>
       </c>
     </row>
     <row r="771">
@@ -42748,13 +42748,13 @@
         </is>
       </c>
       <c r="K771" s="1" t="n">
-        <v>46364.625</v>
+        <v>46365.70833333334</v>
       </c>
       <c r="L771" s="1" t="n">
-        <v>46364.66666666666</v>
+        <v>46365.75</v>
       </c>
       <c r="M771" s="1" t="n">
-        <v>46365.125</v>
+        <v>46366.20833333334</v>
       </c>
     </row>
     <row r="772">
@@ -42803,13 +42803,13 @@
         </is>
       </c>
       <c r="K772" s="1" t="n">
-        <v>46368.95833333334</v>
+        <v>46370.04166666666</v>
       </c>
       <c r="L772" s="1" t="n">
-        <v>46368.95833333334</v>
+        <v>46370.04166666666</v>
       </c>
       <c r="M772" s="1" t="n">
-        <v>46369.41666666666</v>
+        <v>46370.5</v>
       </c>
     </row>
     <row r="773">
@@ -42858,13 +42858,13 @@
         </is>
       </c>
       <c r="K773" s="1" t="n">
-        <v>46370.41666666666</v>
+        <v>46371.5</v>
       </c>
       <c r="L773" s="1" t="n">
-        <v>46370.41666666666</v>
+        <v>46371.5</v>
       </c>
       <c r="M773" s="1" t="n">
-        <v>46370.91666666666</v>
+        <v>46372</v>
       </c>
     </row>
     <row r="774">
@@ -42913,13 +42913,13 @@
         </is>
       </c>
       <c r="K774" s="1" t="n">
-        <v>46373.375</v>
+        <v>46374.45833333334</v>
       </c>
       <c r="L774" s="1" t="n">
-        <v>46373.41666666666</v>
+        <v>46374.5</v>
       </c>
       <c r="M774" s="1" t="n">
-        <v>46374.04166666666</v>
+        <v>46375.125</v>
       </c>
     </row>
     <row r="775">
@@ -42968,13 +42968,13 @@
         </is>
       </c>
       <c r="K775" s="1" t="n">
-        <v>46375.04166666666</v>
+        <v>46376.125</v>
       </c>
       <c r="L775" s="1" t="n">
-        <v>46375.08333333334</v>
+        <v>46376.16666666666</v>
       </c>
       <c r="M775" s="1" t="n">
-        <v>46375.58333333334</v>
+        <v>46376.66666666666</v>
       </c>
     </row>
     <row r="776">
@@ -43023,13 +43023,13 @@
         </is>
       </c>
       <c r="K776" s="1" t="n">
-        <v>46376.66666666666</v>
+        <v>46377.75</v>
       </c>
       <c r="L776" s="1" t="n">
-        <v>46376.83333333334</v>
+        <v>46377.91666666666</v>
       </c>
       <c r="M776" s="1" t="n">
-        <v>46377.625</v>
+        <v>46378.70833333334</v>
       </c>
     </row>
     <row r="777">
@@ -43078,13 +43078,13 @@
         </is>
       </c>
       <c r="K777" s="1" t="n">
-        <v>46383.375</v>
+        <v>46384.45833333334</v>
       </c>
       <c r="L777" s="1" t="n">
-        <v>46383.41666666666</v>
+        <v>46384.5</v>
       </c>
       <c r="M777" s="1" t="n">
-        <v>46383.70833333334</v>
+        <v>46384.79166666666</v>
       </c>
     </row>
     <row r="778">
@@ -43133,13 +43133,13 @@
         </is>
       </c>
       <c r="K778" s="1" t="n">
-        <v>46384</v>
+        <v>46385.08333333334</v>
       </c>
       <c r="L778" s="1" t="n">
-        <v>46384</v>
+        <v>46385.08333333334</v>
       </c>
       <c r="M778" s="1" t="n">
-        <v>46385.375</v>
+        <v>46386.45833333334</v>
       </c>
     </row>
     <row r="779">
@@ -43188,13 +43188,13 @@
         </is>
       </c>
       <c r="K779" s="1" t="n">
-        <v>46385.625</v>
+        <v>46386.70833333334</v>
       </c>
       <c r="L779" s="1" t="n">
-        <v>46385.66666666666</v>
+        <v>46386.75</v>
       </c>
       <c r="M779" s="1" t="n">
-        <v>46386.125</v>
+        <v>46387.20833333334</v>
       </c>
     </row>
     <row r="780">
@@ -43243,13 +43243,13 @@
         </is>
       </c>
       <c r="K780" s="1" t="n">
-        <v>46389.95833333334</v>
+        <v>46391.04166666666</v>
       </c>
       <c r="L780" s="1" t="n">
-        <v>46389.95833333334</v>
+        <v>46391.04166666666</v>
       </c>
       <c r="M780" s="1" t="n">
-        <v>46390.41666666666</v>
+        <v>46391.5</v>
       </c>
     </row>
     <row r="781">
@@ -43294,13 +43294,13 @@
       </c>
       <c r="J781" t="inlineStr"/>
       <c r="K781" s="1" t="n">
-        <v>46391.41666666666</v>
+        <v>46392.5</v>
       </c>
       <c r="L781" s="1" t="n">
-        <v>46391.41666666666</v>
+        <v>46392.5</v>
       </c>
       <c r="M781" s="1" t="n">
-        <v>46391.91666666666</v>
+        <v>46393</v>
       </c>
     </row>
     <row r="782">
@@ -45600,13 +45600,13 @@
         </is>
       </c>
       <c r="K823" s="1" t="n">
-        <v>46301.1875</v>
+        <v>46301.14583333334</v>
       </c>
       <c r="L823" s="1" t="n">
-        <v>46301.25</v>
+        <v>46301.20833333334</v>
       </c>
       <c r="M823" s="1" t="n">
-        <v>46301.66666666666</v>
+        <v>46301.58333333334</v>
       </c>
     </row>
     <row r="824">
@@ -45655,13 +45655,13 @@
         </is>
       </c>
       <c r="K824" s="1" t="n">
-        <v>46302.02083333334</v>
+        <v>46301.9375</v>
       </c>
       <c r="L824" s="1" t="n">
-        <v>46302.0625</v>
+        <v>46301.97916666666</v>
       </c>
       <c r="M824" s="1" t="n">
-        <v>46302.6875</v>
+        <v>46302.60416666666</v>
       </c>
     </row>
     <row r="825">
@@ -45710,13 +45710,13 @@
         </is>
       </c>
       <c r="K825" s="1" t="n">
-        <v>46303.875</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="L825" s="1" t="n">
-        <v>46307.47916666666</v>
+        <v>46307.39583333334</v>
       </c>
       <c r="M825" s="1" t="n">
-        <v>46308.47916666666</v>
+        <v>46308.39583333334</v>
       </c>
     </row>
     <row r="826">
@@ -45765,13 +45765,13 @@
         </is>
       </c>
       <c r="K826" s="1" t="n">
-        <v>46312.6875</v>
+        <v>46312.60416666666</v>
       </c>
       <c r="L826" s="1" t="n">
-        <v>46313.8125</v>
+        <v>46313.72916666666</v>
       </c>
       <c r="M826" s="1" t="n">
-        <v>46314.3125</v>
+        <v>46314.22916666666</v>
       </c>
     </row>
     <row r="827">
@@ -45820,13 +45820,13 @@
         </is>
       </c>
       <c r="K827" s="1" t="n">
-        <v>46315.89583333334</v>
+        <v>46315.8125</v>
       </c>
       <c r="L827" s="1" t="n">
-        <v>46315.9375</v>
+        <v>46315.85416666666</v>
       </c>
       <c r="M827" s="1" t="n">
-        <v>46316.35416666666</v>
+        <v>46316.27083333334</v>
       </c>
     </row>
     <row r="828">
@@ -45875,13 +45875,13 @@
         </is>
       </c>
       <c r="K828" s="1" t="n">
-        <v>46316.52083333334</v>
+        <v>46316.4375</v>
       </c>
       <c r="L828" s="1" t="n">
-        <v>46316.64583333334</v>
+        <v>46316.5625</v>
       </c>
       <c r="M828" s="1" t="n">
-        <v>46317.64583333334</v>
+        <v>46317.5625</v>
       </c>
     </row>
     <row r="829">
@@ -45930,13 +45930,13 @@
         </is>
       </c>
       <c r="K829" s="1" t="n">
-        <v>46317.89583333334</v>
+        <v>46317.8125</v>
       </c>
       <c r="L829" s="1" t="n">
-        <v>46317.9375</v>
+        <v>46317.85416666666</v>
       </c>
       <c r="M829" s="1" t="n">
-        <v>46318.35416666666</v>
+        <v>46318.27083333334</v>
       </c>
     </row>
     <row r="830">
@@ -45985,13 +45985,13 @@
         </is>
       </c>
       <c r="K830" s="1" t="n">
-        <v>46319.85416666666</v>
+        <v>46319.77083333334</v>
       </c>
       <c r="L830" s="1" t="n">
-        <v>46320.97916666666</v>
+        <v>46320.89583333334</v>
       </c>
       <c r="M830" s="1" t="n">
-        <v>46321.47916666666</v>
+        <v>46321.39583333334</v>
       </c>
     </row>
     <row r="831">
@@ -46040,13 +46040,13 @@
         </is>
       </c>
       <c r="K831" s="1" t="n">
-        <v>46327.58333333334</v>
+        <v>46327.5</v>
       </c>
       <c r="L831" s="1" t="n">
-        <v>46327.64583333334</v>
+        <v>46327.5625</v>
       </c>
       <c r="M831" s="1" t="n">
-        <v>46327.89583333334</v>
+        <v>46327.8125</v>
       </c>
     </row>
     <row r="832">
@@ -46095,13 +46095,13 @@
         </is>
       </c>
       <c r="K832" s="1" t="n">
-        <v>46328.85416666666</v>
+        <v>46328.77083333334</v>
       </c>
       <c r="L832" s="1" t="n">
-        <v>46328.91666666666</v>
+        <v>46328.83333333334</v>
       </c>
       <c r="M832" s="1" t="n">
-        <v>46329.33333333334</v>
+        <v>46329.25</v>
       </c>
     </row>
     <row r="833">
@@ -46150,13 +46150,13 @@
         </is>
       </c>
       <c r="K833" s="1" t="n">
-        <v>46329.6875</v>
+        <v>46329.60416666666</v>
       </c>
       <c r="L833" s="1" t="n">
-        <v>46329.72916666666</v>
+        <v>46329.64583333334</v>
       </c>
       <c r="M833" s="1" t="n">
-        <v>46330.35416666666</v>
+        <v>46330.27083333334</v>
       </c>
     </row>
     <row r="834">
@@ -46205,13 +46205,13 @@
         </is>
       </c>
       <c r="K834" s="1" t="n">
-        <v>46331.4375</v>
+        <v>46331.35416666666</v>
       </c>
       <c r="L834" s="1" t="n">
-        <v>46331.60416666666</v>
+        <v>46331.52083333334</v>
       </c>
       <c r="M834" s="1" t="n">
-        <v>46332.60416666666</v>
+        <v>46332.52083333334</v>
       </c>
     </row>
     <row r="835">
@@ -46260,13 +46260,13 @@
         </is>
       </c>
       <c r="K835" s="1" t="n">
-        <v>46336.8125</v>
+        <v>46336.72916666666</v>
       </c>
       <c r="L835" s="1" t="n">
-        <v>46336.9375</v>
+        <v>46336.85416666666</v>
       </c>
       <c r="M835" s="1" t="n">
-        <v>46337.4375</v>
+        <v>46337.35416666666</v>
       </c>
     </row>
     <row r="836">
@@ -46315,13 +46315,13 @@
         </is>
       </c>
       <c r="K836" s="1" t="n">
-        <v>46339.02083333334</v>
+        <v>46338.9375</v>
       </c>
       <c r="L836" s="1" t="n">
-        <v>46339.0625</v>
+        <v>46338.97916666666</v>
       </c>
       <c r="M836" s="1" t="n">
-        <v>46339.47916666666</v>
+        <v>46339.39583333334</v>
       </c>
     </row>
     <row r="837">
@@ -46370,13 +46370,13 @@
         </is>
       </c>
       <c r="K837" s="1" t="n">
-        <v>46339.64583333334</v>
+        <v>46339.5625</v>
       </c>
       <c r="L837" s="1" t="n">
-        <v>46339.77083333334</v>
+        <v>46339.6875</v>
       </c>
       <c r="M837" s="1" t="n">
-        <v>46340.77083333334</v>
+        <v>46340.6875</v>
       </c>
     </row>
     <row r="838">
@@ -46425,13 +46425,13 @@
         </is>
       </c>
       <c r="K838" s="1" t="n">
-        <v>46341.02083333334</v>
+        <v>46340.9375</v>
       </c>
       <c r="L838" s="1" t="n">
-        <v>46341.0625</v>
+        <v>46340.97916666666</v>
       </c>
       <c r="M838" s="1" t="n">
-        <v>46341.47916666666</v>
+        <v>46341.39583333334</v>
       </c>
     </row>
     <row r="839">
@@ -46480,13 +46480,13 @@
         </is>
       </c>
       <c r="K839" s="1" t="n">
-        <v>46342.97916666666</v>
+        <v>46342.89583333334</v>
       </c>
       <c r="L839" s="1" t="n">
-        <v>46343.10416666666</v>
+        <v>46343.02083333334</v>
       </c>
       <c r="M839" s="1" t="n">
-        <v>46343.60416666666</v>
+        <v>46343.52083333334</v>
       </c>
     </row>
     <row r="840">
@@ -46535,13 +46535,13 @@
         </is>
       </c>
       <c r="K840" s="1" t="n">
-        <v>46348.625</v>
+        <v>46348.54166666666</v>
       </c>
       <c r="L840" s="1" t="n">
-        <v>46348.6875</v>
+        <v>46348.60416666666</v>
       </c>
       <c r="M840" s="1" t="n">
-        <v>46348.9375</v>
+        <v>46348.85416666666</v>
       </c>
     </row>
     <row r="841">
@@ -46590,13 +46590,13 @@
         </is>
       </c>
       <c r="K841" s="1" t="n">
-        <v>46349.88333333333</v>
+        <v>46349.8</v>
       </c>
       <c r="L841" s="1" t="n">
-        <v>46349.94583333333</v>
+        <v>46349.8625</v>
       </c>
       <c r="M841" s="1" t="n">
-        <v>46350.3625</v>
+        <v>46350.27916666667</v>
       </c>
     </row>
     <row r="842">
@@ -46645,13 +46645,13 @@
         </is>
       </c>
       <c r="K842" s="1" t="n">
-        <v>46350.70416666667</v>
+        <v>46350.62083333333</v>
       </c>
       <c r="L842" s="1" t="n">
-        <v>46350.74583333333</v>
+        <v>46350.6625</v>
       </c>
       <c r="M842" s="1" t="n">
-        <v>46351.37083333333</v>
+        <v>46351.2875</v>
       </c>
     </row>
     <row r="843">
@@ -46700,13 +46700,13 @@
         </is>
       </c>
       <c r="K843" s="1" t="n">
-        <v>46352.45416666667</v>
+        <v>46352.37083333333</v>
       </c>
       <c r="L843" s="1" t="n">
-        <v>46352.62083333333</v>
+        <v>46352.5375</v>
       </c>
       <c r="M843" s="1" t="n">
-        <v>46353.62083333333</v>
+        <v>46353.5375</v>
       </c>
     </row>
     <row r="844">
@@ -46755,13 +46755,13 @@
         </is>
       </c>
       <c r="K844" s="1" t="n">
-        <v>46357.82916666667</v>
+        <v>46357.74583333333</v>
       </c>
       <c r="L844" s="1" t="n">
-        <v>46357.95416666667</v>
+        <v>46357.87083333333</v>
       </c>
       <c r="M844" s="1" t="n">
-        <v>46358.45416666667</v>
+        <v>46358.37083333333</v>
       </c>
     </row>
     <row r="845">
@@ -46810,13 +46810,13 @@
         </is>
       </c>
       <c r="K845" s="1" t="n">
-        <v>46360.0375</v>
+        <v>46359.95416666667</v>
       </c>
       <c r="L845" s="1" t="n">
-        <v>46360.07916666667</v>
+        <v>46359.99583333333</v>
       </c>
       <c r="M845" s="1" t="n">
-        <v>46360.49583333333</v>
+        <v>46360.4125</v>
       </c>
     </row>
     <row r="846">
@@ -46865,13 +46865,13 @@
         </is>
       </c>
       <c r="K846" s="1" t="n">
-        <v>46360.6625</v>
+        <v>46360.57916666667</v>
       </c>
       <c r="L846" s="1" t="n">
-        <v>46360.7875</v>
+        <v>46360.70416666667</v>
       </c>
       <c r="M846" s="1" t="n">
-        <v>46361.7875</v>
+        <v>46361.70416666667</v>
       </c>
     </row>
     <row r="847">
@@ -46920,13 +46920,13 @@
         </is>
       </c>
       <c r="K847" s="1" t="n">
-        <v>46362.0375</v>
+        <v>46361.95416666667</v>
       </c>
       <c r="L847" s="1" t="n">
-        <v>46362.07916666667</v>
+        <v>46361.99583333333</v>
       </c>
       <c r="M847" s="1" t="n">
-        <v>46362.49583333333</v>
+        <v>46362.4125</v>
       </c>
     </row>
     <row r="848">
@@ -46975,13 +46975,13 @@
         </is>
       </c>
       <c r="K848" s="1" t="n">
-        <v>46363.99583333333</v>
+        <v>46363.9125</v>
       </c>
       <c r="L848" s="1" t="n">
-        <v>46364.12083333333</v>
+        <v>46364.0375</v>
       </c>
       <c r="M848" s="1" t="n">
-        <v>46364.62083333333</v>
+        <v>46364.5375</v>
       </c>
     </row>
     <row r="849">
@@ -47030,13 +47030,13 @@
         </is>
       </c>
       <c r="K849" s="1" t="n">
-        <v>46369.64166666667</v>
+        <v>46369.55833333333</v>
       </c>
       <c r="L849" s="1" t="n">
-        <v>46369.70416666667</v>
+        <v>46369.62083333333</v>
       </c>
       <c r="M849" s="1" t="n">
-        <v>46369.95416666667</v>
+        <v>46369.87083333333</v>
       </c>
     </row>
     <row r="850">
@@ -47085,13 +47085,13 @@
         </is>
       </c>
       <c r="K850" s="1" t="n">
-        <v>46370.9</v>
+        <v>46370.81666666667</v>
       </c>
       <c r="L850" s="1" t="n">
-        <v>46370.9625</v>
+        <v>46370.87916666667</v>
       </c>
       <c r="M850" s="1" t="n">
-        <v>46371.37916666667</v>
+        <v>46371.29583333333</v>
       </c>
     </row>
     <row r="851">
@@ -47140,13 +47140,13 @@
         </is>
       </c>
       <c r="K851" s="1" t="n">
-        <v>46371.72083333333</v>
+        <v>46371.6375</v>
       </c>
       <c r="L851" s="1" t="n">
-        <v>46371.7625</v>
+        <v>46371.67916666667</v>
       </c>
       <c r="M851" s="1" t="n">
-        <v>46372.3875</v>
+        <v>46372.30416666667</v>
       </c>
     </row>
     <row r="852">
@@ -47195,13 +47195,13 @@
         </is>
       </c>
       <c r="K852" s="1" t="n">
-        <v>46373.47083333333</v>
+        <v>46373.3875</v>
       </c>
       <c r="L852" s="1" t="n">
-        <v>46373.6375</v>
+        <v>46373.55416666667</v>
       </c>
       <c r="M852" s="1" t="n">
-        <v>46374.6375</v>
+        <v>46374.55416666667</v>
       </c>
     </row>
     <row r="853">
@@ -47250,13 +47250,13 @@
         </is>
       </c>
       <c r="K853" s="1" t="n">
-        <v>46378.84583333333</v>
+        <v>46378.7625</v>
       </c>
       <c r="L853" s="1" t="n">
-        <v>46378.97083333333</v>
+        <v>46378.8875</v>
       </c>
       <c r="M853" s="1" t="n">
-        <v>46379.47083333333</v>
+        <v>46379.3875</v>
       </c>
     </row>
     <row r="854">
@@ -47305,13 +47305,13 @@
         </is>
       </c>
       <c r="K854" s="1" t="n">
-        <v>46381.05416666667</v>
+        <v>46380.97083333333</v>
       </c>
       <c r="L854" s="1" t="n">
-        <v>46381.09583333333</v>
+        <v>46381.0125</v>
       </c>
       <c r="M854" s="1" t="n">
-        <v>46381.5125</v>
+        <v>46381.42916666667</v>
       </c>
     </row>
     <row r="855">
@@ -47360,13 +47360,13 @@
         </is>
       </c>
       <c r="K855" s="1" t="n">
-        <v>46381.67916666667</v>
+        <v>46381.59583333333</v>
       </c>
       <c r="L855" s="1" t="n">
-        <v>46381.80416666667</v>
+        <v>46381.72083333333</v>
       </c>
       <c r="M855" s="1" t="n">
-        <v>46382.80416666667</v>
+        <v>46382.72083333333</v>
       </c>
     </row>
     <row r="856">
@@ -47415,13 +47415,13 @@
         </is>
       </c>
       <c r="K856" s="1" t="n">
-        <v>46383.05416666667</v>
+        <v>46382.97083333333</v>
       </c>
       <c r="L856" s="1" t="n">
-        <v>46383.09583333333</v>
+        <v>46383.0125</v>
       </c>
       <c r="M856" s="1" t="n">
-        <v>46383.5125</v>
+        <v>46383.42916666667</v>
       </c>
     </row>
     <row r="857">
@@ -47466,13 +47466,13 @@
       </c>
       <c r="J857" t="inlineStr"/>
       <c r="K857" s="1" t="n">
-        <v>46385.0125</v>
+        <v>46384.92916666667</v>
       </c>
       <c r="L857" s="1" t="n">
-        <v>46385.1375</v>
+        <v>46385.05416666667</v>
       </c>
       <c r="M857" s="1" t="n">
-        <v>46385.6375</v>
+        <v>46385.55416666667</v>
       </c>
     </row>
     <row r="858">
@@ -49280,10 +49280,10 @@
         <v>46297.6875</v>
       </c>
       <c r="L890" s="1" t="n">
-        <v>46298.8125</v>
+        <v>46298.25</v>
       </c>
       <c r="M890" s="1" t="n">
-        <v>46299.3125</v>
+        <v>46298.60416666666</v>
       </c>
     </row>
     <row r="891">
@@ -49332,13 +49332,13 @@
         </is>
       </c>
       <c r="K891" s="1" t="n">
-        <v>46300.89583333334</v>
+        <v>46300.1875</v>
       </c>
       <c r="L891" s="1" t="n">
-        <v>46300.9375</v>
+        <v>46300.22916666666</v>
       </c>
       <c r="M891" s="1" t="n">
-        <v>46301.35416666666</v>
+        <v>46300.64583333334</v>
       </c>
     </row>
     <row r="892">
@@ -49387,13 +49387,13 @@
         </is>
       </c>
       <c r="K892" s="1" t="n">
-        <v>46301.52083333334</v>
+        <v>46300.8125</v>
       </c>
       <c r="L892" s="1" t="n">
-        <v>46301.64583333334</v>
+        <v>46300.9375</v>
       </c>
       <c r="M892" s="1" t="n">
-        <v>46302.64583333334</v>
+        <v>46301.9375</v>
       </c>
     </row>
     <row r="893">
@@ -49442,13 +49442,13 @@
         </is>
       </c>
       <c r="K893" s="1" t="n">
-        <v>46302.89583333334</v>
+        <v>46302.1875</v>
       </c>
       <c r="L893" s="1" t="n">
-        <v>46302.9375</v>
+        <v>46302.22916666666</v>
       </c>
       <c r="M893" s="1" t="n">
-        <v>46303.35416666666</v>
+        <v>46302.64583333334</v>
       </c>
     </row>
     <row r="894">
@@ -49497,13 +49497,13 @@
         </is>
       </c>
       <c r="K894" s="1" t="n">
-        <v>46304.85416666666</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="L894" s="1" t="n">
-        <v>46305.02083333334</v>
+        <v>46304.3125</v>
       </c>
       <c r="M894" s="1" t="n">
-        <v>46305.52083333334</v>
+        <v>46304.8125</v>
       </c>
     </row>
     <row r="895">
@@ -49552,13 +49552,13 @@
         </is>
       </c>
       <c r="K895" s="1" t="n">
-        <v>46310.54166666666</v>
+        <v>46309.83333333334</v>
       </c>
       <c r="L895" s="1" t="n">
-        <v>46310.60416666666</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="M895" s="1" t="n">
-        <v>46310.85416666666</v>
+        <v>46310.14583333334</v>
       </c>
     </row>
     <row r="896">
@@ -49607,13 +49607,13 @@
         </is>
       </c>
       <c r="K896" s="1" t="n">
-        <v>46311.79166666666</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="L896" s="1" t="n">
-        <v>46311.85416666666</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="M896" s="1" t="n">
-        <v>46312.27083333334</v>
+        <v>46311.5625</v>
       </c>
     </row>
     <row r="897">
@@ -49662,13 +49662,13 @@
         </is>
       </c>
       <c r="K897" s="1" t="n">
-        <v>46312.60416666666</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="L897" s="1" t="n">
-        <v>46312.64583333334</v>
+        <v>46311.9375</v>
       </c>
       <c r="M897" s="1" t="n">
-        <v>46313.27083333334</v>
+        <v>46312.5625</v>
       </c>
     </row>
     <row r="898">
@@ -49717,13 +49717,13 @@
         </is>
       </c>
       <c r="K898" s="1" t="n">
-        <v>46314.35416666666</v>
+        <v>46313.64583333334</v>
       </c>
       <c r="L898" s="1" t="n">
-        <v>46314.52083333334</v>
+        <v>46313.8125</v>
       </c>
       <c r="M898" s="1" t="n">
-        <v>46315.52083333334</v>
+        <v>46314.8125</v>
       </c>
     </row>
     <row r="899">
@@ -49772,13 +49772,13 @@
         </is>
       </c>
       <c r="K899" s="1" t="n">
-        <v>46319.72916666666</v>
+        <v>46319.02083333334</v>
       </c>
       <c r="L899" s="1" t="n">
-        <v>46319.85416666666</v>
+        <v>46319.14583333334</v>
       </c>
       <c r="M899" s="1" t="n">
-        <v>46320.35416666666</v>
+        <v>46319.64583333334</v>
       </c>
     </row>
     <row r="900">
@@ -49827,13 +49827,13 @@
         </is>
       </c>
       <c r="K900" s="1" t="n">
-        <v>46321.9375</v>
+        <v>46321.22916666666</v>
       </c>
       <c r="L900" s="1" t="n">
-        <v>46321.97916666666</v>
+        <v>46321.27083333334</v>
       </c>
       <c r="M900" s="1" t="n">
-        <v>46322.39583333334</v>
+        <v>46321.6875</v>
       </c>
     </row>
     <row r="901">
@@ -49882,13 +49882,13 @@
         </is>
       </c>
       <c r="K901" s="1" t="n">
-        <v>46322.5625</v>
+        <v>46321.85416666666</v>
       </c>
       <c r="L901" s="1" t="n">
-        <v>46322.6875</v>
+        <v>46321.97916666666</v>
       </c>
       <c r="M901" s="1" t="n">
-        <v>46323.6875</v>
+        <v>46322.97916666666</v>
       </c>
     </row>
     <row r="902">
@@ -49937,13 +49937,13 @@
         </is>
       </c>
       <c r="K902" s="1" t="n">
-        <v>46323.9375</v>
+        <v>46323.22916666666</v>
       </c>
       <c r="L902" s="1" t="n">
-        <v>46323.97916666666</v>
+        <v>46323.27083333334</v>
       </c>
       <c r="M902" s="1" t="n">
-        <v>46324.39583333334</v>
+        <v>46323.6875</v>
       </c>
     </row>
     <row r="903">
@@ -49992,13 +49992,13 @@
         </is>
       </c>
       <c r="K903" s="1" t="n">
-        <v>46325.89583333334</v>
+        <v>46325.1875</v>
       </c>
       <c r="L903" s="1" t="n">
-        <v>46326.02083333334</v>
+        <v>46325.3125</v>
       </c>
       <c r="M903" s="1" t="n">
-        <v>46326.52083333334</v>
+        <v>46325.8125</v>
       </c>
     </row>
     <row r="904">
@@ -50047,13 +50047,13 @@
         </is>
       </c>
       <c r="K904" s="1" t="n">
-        <v>46333.08333333334</v>
+        <v>46332.375</v>
       </c>
       <c r="L904" s="1" t="n">
-        <v>46333.14583333334</v>
+        <v>46332.4375</v>
       </c>
       <c r="M904" s="1" t="n">
-        <v>46333.39583333334</v>
+        <v>46332.6875</v>
       </c>
     </row>
     <row r="905">
@@ -50102,13 +50102,13 @@
         </is>
       </c>
       <c r="K905" s="1" t="n">
-        <v>46334.33333333334</v>
+        <v>46333.625</v>
       </c>
       <c r="L905" s="1" t="n">
-        <v>46334.39583333334</v>
+        <v>46333.6875</v>
       </c>
       <c r="M905" s="1" t="n">
-        <v>46334.8125</v>
+        <v>46334.10416666666</v>
       </c>
     </row>
     <row r="906">
@@ -50157,13 +50157,13 @@
         </is>
       </c>
       <c r="K906" s="1" t="n">
-        <v>46335.14583333334</v>
+        <v>46334.4375</v>
       </c>
       <c r="L906" s="1" t="n">
-        <v>46335.1875</v>
+        <v>46334.47916666666</v>
       </c>
       <c r="M906" s="1" t="n">
-        <v>46335.8125</v>
+        <v>46335.10416666666</v>
       </c>
     </row>
     <row r="907">
@@ -50212,13 +50212,13 @@
         </is>
       </c>
       <c r="K907" s="1" t="n">
-        <v>46336.89305555556</v>
+        <v>46336.18472222222</v>
       </c>
       <c r="L907" s="1" t="n">
-        <v>46337.05972222222</v>
+        <v>46336.35138888889</v>
       </c>
       <c r="M907" s="1" t="n">
-        <v>46338.05972222222</v>
+        <v>46337.35138888889</v>
       </c>
     </row>
     <row r="908">
@@ -50267,13 +50267,13 @@
         </is>
       </c>
       <c r="K908" s="1" t="n">
-        <v>46342.26805555556</v>
+        <v>46341.55972222222</v>
       </c>
       <c r="L908" s="1" t="n">
-        <v>46342.39305555556</v>
+        <v>46341.68472222222</v>
       </c>
       <c r="M908" s="1" t="n">
-        <v>46342.89305555556</v>
+        <v>46342.18472222222</v>
       </c>
     </row>
     <row r="909">
@@ -50322,13 +50322,13 @@
         </is>
       </c>
       <c r="K909" s="1" t="n">
-        <v>46344.47638888889</v>
+        <v>46343.76805555556</v>
       </c>
       <c r="L909" s="1" t="n">
-        <v>46344.51805555556</v>
+        <v>46343.80972222222</v>
       </c>
       <c r="M909" s="1" t="n">
-        <v>46344.93472222222</v>
+        <v>46344.22638888889</v>
       </c>
     </row>
     <row r="910">
@@ -50377,13 +50377,13 @@
         </is>
       </c>
       <c r="K910" s="1" t="n">
-        <v>46345.10138888889</v>
+        <v>46344.39305555556</v>
       </c>
       <c r="L910" s="1" t="n">
-        <v>46345.22638888889</v>
+        <v>46344.51805555556</v>
       </c>
       <c r="M910" s="1" t="n">
-        <v>46346.22638888889</v>
+        <v>46345.51805555556</v>
       </c>
     </row>
     <row r="911">
@@ -50432,13 +50432,13 @@
         </is>
       </c>
       <c r="K911" s="1" t="n">
-        <v>46346.47638888889</v>
+        <v>46345.76805555556</v>
       </c>
       <c r="L911" s="1" t="n">
-        <v>46346.51805555556</v>
+        <v>46345.80972222222</v>
       </c>
       <c r="M911" s="1" t="n">
-        <v>46346.93472222222</v>
+        <v>46346.22638888889</v>
       </c>
     </row>
     <row r="912">
@@ -50487,13 +50487,13 @@
         </is>
       </c>
       <c r="K912" s="1" t="n">
-        <v>46348.43472222222</v>
+        <v>46347.72638888889</v>
       </c>
       <c r="L912" s="1" t="n">
-        <v>46348.55972222222</v>
+        <v>46347.85138888889</v>
       </c>
       <c r="M912" s="1" t="n">
-        <v>46349.05972222222</v>
+        <v>46348.35138888889</v>
       </c>
     </row>
     <row r="913">
@@ -50542,13 +50542,13 @@
         </is>
       </c>
       <c r="K913" s="1" t="n">
-        <v>46354.08055555556</v>
+        <v>46353.37222222222</v>
       </c>
       <c r="L913" s="1" t="n">
-        <v>46354.14305555556</v>
+        <v>46353.43472222222</v>
       </c>
       <c r="M913" s="1" t="n">
-        <v>46354.39305555556</v>
+        <v>46353.68472222222</v>
       </c>
     </row>
     <row r="914">
@@ -50597,13 +50597,13 @@
         </is>
       </c>
       <c r="K914" s="1" t="n">
-        <v>46355.33055555556</v>
+        <v>46354.62222222222</v>
       </c>
       <c r="L914" s="1" t="n">
-        <v>46355.39305555556</v>
+        <v>46354.68472222222</v>
       </c>
       <c r="M914" s="1" t="n">
-        <v>46355.80972222222</v>
+        <v>46355.10138888889</v>
       </c>
     </row>
     <row r="915">
@@ -50652,13 +50652,13 @@
         </is>
       </c>
       <c r="K915" s="1" t="n">
-        <v>46356.14305555556</v>
+        <v>46355.43472222222</v>
       </c>
       <c r="L915" s="1" t="n">
-        <v>46356.18472222222</v>
+        <v>46355.47638888889</v>
       </c>
       <c r="M915" s="1" t="n">
-        <v>46356.80972222222</v>
+        <v>46356.10138888889</v>
       </c>
     </row>
     <row r="916">
@@ -50707,13 +50707,13 @@
         </is>
       </c>
       <c r="K916" s="1" t="n">
-        <v>46357.89027777778</v>
+        <v>46357.18194444444</v>
       </c>
       <c r="L916" s="1" t="n">
-        <v>46358.05694444444</v>
+        <v>46357.34861111111</v>
       </c>
       <c r="M916" s="1" t="n">
-        <v>46359.05694444444</v>
+        <v>46358.34861111111</v>
       </c>
     </row>
     <row r="917">
@@ -50762,13 +50762,13 @@
         </is>
       </c>
       <c r="K917" s="1" t="n">
-        <v>46363.26527777778</v>
+        <v>46362.55694444444</v>
       </c>
       <c r="L917" s="1" t="n">
-        <v>46363.39027777778</v>
+        <v>46362.68194444444</v>
       </c>
       <c r="M917" s="1" t="n">
-        <v>46363.89027777778</v>
+        <v>46363.18194444444</v>
       </c>
     </row>
     <row r="918">
@@ -50817,13 +50817,13 @@
         </is>
       </c>
       <c r="K918" s="1" t="n">
-        <v>46365.47361111111</v>
+        <v>46364.76527777778</v>
       </c>
       <c r="L918" s="1" t="n">
-        <v>46365.51527777778</v>
+        <v>46364.80694444444</v>
       </c>
       <c r="M918" s="1" t="n">
-        <v>46365.93194444444</v>
+        <v>46365.22361111111</v>
       </c>
     </row>
     <row r="919">
@@ -50872,13 +50872,13 @@
         </is>
       </c>
       <c r="K919" s="1" t="n">
-        <v>46366.09861111111</v>
+        <v>46365.39027777778</v>
       </c>
       <c r="L919" s="1" t="n">
-        <v>46366.22361111111</v>
+        <v>46365.51527777778</v>
       </c>
       <c r="M919" s="1" t="n">
-        <v>46367.22361111111</v>
+        <v>46366.51527777778</v>
       </c>
     </row>
     <row r="920">
@@ -50927,13 +50927,13 @@
         </is>
       </c>
       <c r="K920" s="1" t="n">
-        <v>46367.47361111111</v>
+        <v>46366.76527777778</v>
       </c>
       <c r="L920" s="1" t="n">
-        <v>46367.51527777778</v>
+        <v>46366.80694444444</v>
       </c>
       <c r="M920" s="1" t="n">
-        <v>46367.93194444444</v>
+        <v>46367.22361111111</v>
       </c>
     </row>
     <row r="921">
@@ -50978,13 +50978,13 @@
       </c>
       <c r="J921" t="inlineStr"/>
       <c r="K921" s="1" t="n">
-        <v>46369.43194444444</v>
+        <v>46368.72361111111</v>
       </c>
       <c r="L921" s="1" t="n">
-        <v>46369.55694444444</v>
+        <v>46368.84861111111</v>
       </c>
       <c r="M921" s="1" t="n">
-        <v>46370.05694444444</v>
+        <v>46369.34861111111</v>
       </c>
     </row>
     <row r="922">
@@ -53727,10 +53727,10 @@
         <v>46297.33333333334</v>
       </c>
       <c r="L971" s="1" t="n">
-        <v>46297.375</v>
+        <v>46297.38333333333</v>
       </c>
       <c r="M971" s="1" t="n">
-        <v>46298.45833333334</v>
+        <v>46297.95833333334</v>
       </c>
     </row>
     <row r="972">
@@ -53779,13 +53779,13 @@
         </is>
       </c>
       <c r="K972" s="1" t="n">
-        <v>46302.1875</v>
+        <v>46301.6875</v>
       </c>
       <c r="L972" s="1" t="n">
-        <v>46302.22916666666</v>
+        <v>46301.72916666666</v>
       </c>
       <c r="M972" s="1" t="n">
-        <v>46302.89583333334</v>
+        <v>46302.39583333334</v>
       </c>
     </row>
     <row r="973">
@@ -53834,13 +53834,13 @@
         </is>
       </c>
       <c r="K973" s="1" t="n">
-        <v>46308.95833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="L973" s="1" t="n">
-        <v>46309.16666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="M973" s="1" t="n">
-        <v>46309.83333333334</v>
+        <v>46309.33333333334</v>
       </c>
     </row>
     <row r="974">
@@ -53889,13 +53889,13 @@
         </is>
       </c>
       <c r="K974" s="1" t="n">
-        <v>46311.22916666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="L974" s="1" t="n">
-        <v>46311.27083333334</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="M974" s="1" t="n">
-        <v>46312.27083333334</v>
+        <v>46311.77083333334</v>
       </c>
     </row>
     <row r="975">
@@ -53944,13 +53944,13 @@
         </is>
       </c>
       <c r="K975" s="1" t="n">
-        <v>46312.5625</v>
+        <v>46312.0625</v>
       </c>
       <c r="L975" s="1" t="n">
-        <v>46312.60416666666</v>
+        <v>46312.10416666666</v>
       </c>
       <c r="M975" s="1" t="n">
-        <v>46313.22916666666</v>
+        <v>46312.72916666666</v>
       </c>
     </row>
     <row r="976">
@@ -53999,13 +53999,13 @@
         </is>
       </c>
       <c r="K976" s="1" t="n">
-        <v>46314.6875</v>
+        <v>46314.1875</v>
       </c>
       <c r="L976" s="1" t="n">
-        <v>46314.89583333334</v>
+        <v>46314.39583333334</v>
       </c>
       <c r="M976" s="1" t="n">
-        <v>46315.5625</v>
+        <v>46315.0625</v>
       </c>
     </row>
     <row r="977">
@@ -54054,13 +54054,13 @@
         </is>
       </c>
       <c r="K977" s="1" t="n">
-        <v>46322.5625</v>
+        <v>46322.0625</v>
       </c>
       <c r="L977" s="1" t="n">
-        <v>46322.64583333334</v>
+        <v>46322.14583333334</v>
       </c>
       <c r="M977" s="1" t="n">
-        <v>46323.47916666666</v>
+        <v>46322.97916666666</v>
       </c>
     </row>
     <row r="978">
@@ -54109,13 +54109,13 @@
         </is>
       </c>
       <c r="K978" s="1" t="n">
-        <v>46324.5625</v>
+        <v>46324.0625</v>
       </c>
       <c r="L978" s="1" t="n">
+        <v>46324.14583333334</v>
+      </c>
+      <c r="M978" s="1" t="n">
         <v>46324.64583333334</v>
-      </c>
-      <c r="M978" s="1" t="n">
-        <v>46325.14583333334</v>
       </c>
     </row>
     <row r="979">
@@ -54164,13 +54164,13 @@
         </is>
       </c>
       <c r="K979" s="1" t="n">
-        <v>46329.14583333334</v>
+        <v>46328.64583333334</v>
       </c>
       <c r="L979" s="1" t="n">
-        <v>46329.1875</v>
+        <v>46328.6875</v>
       </c>
       <c r="M979" s="1" t="n">
-        <v>46329.85416666666</v>
+        <v>46329.35416666666</v>
       </c>
     </row>
     <row r="980">
@@ -54219,13 +54219,13 @@
         </is>
       </c>
       <c r="K980" s="1" t="n">
-        <v>46336.27083333334</v>
+        <v>46335.77083333334</v>
       </c>
       <c r="L980" s="1" t="n">
-        <v>46336.47916666666</v>
+        <v>46335.97916666666</v>
       </c>
       <c r="M980" s="1" t="n">
-        <v>46337.14583333334</v>
+        <v>46336.64583333334</v>
       </c>
     </row>
     <row r="981">
@@ -54274,13 +54274,13 @@
         </is>
       </c>
       <c r="K981" s="1" t="n">
-        <v>46338.64583333334</v>
+        <v>46338.14583333334</v>
       </c>
       <c r="L981" s="1" t="n">
-        <v>46338.6875</v>
+        <v>46338.1875</v>
       </c>
       <c r="M981" s="1" t="n">
-        <v>46339.6875</v>
+        <v>46339.1875</v>
       </c>
     </row>
     <row r="982">
@@ -54329,13 +54329,13 @@
         </is>
       </c>
       <c r="K982" s="1" t="n">
-        <v>46340.3125</v>
+        <v>46339.8125</v>
       </c>
       <c r="L982" s="1" t="n">
-        <v>46340.35416666666</v>
+        <v>46339.85416666666</v>
       </c>
       <c r="M982" s="1" t="n">
-        <v>46340.97916666666</v>
+        <v>46340.47916666666</v>
       </c>
     </row>
     <row r="983">
@@ -54384,13 +54384,13 @@
         </is>
       </c>
       <c r="K983" s="1" t="n">
-        <v>46342.47916666666</v>
+        <v>46341.97916666666</v>
       </c>
       <c r="L983" s="1" t="n">
-        <v>46342.6875</v>
+        <v>46342.1875</v>
       </c>
       <c r="M983" s="1" t="n">
-        <v>46343.35416666666</v>
+        <v>46342.85416666666</v>
       </c>
     </row>
     <row r="984">
@@ -54439,13 +54439,13 @@
         </is>
       </c>
       <c r="K984" s="1" t="n">
-        <v>46350.35416666666</v>
+        <v>46349.85416666666</v>
       </c>
       <c r="L984" s="1" t="n">
-        <v>46350.4375</v>
+        <v>46349.9375</v>
       </c>
       <c r="M984" s="1" t="n">
-        <v>46351.27083333334</v>
+        <v>46350.77083333334</v>
       </c>
     </row>
     <row r="985">
@@ -54494,13 +54494,13 @@
         </is>
       </c>
       <c r="K985" s="1" t="n">
-        <v>46352.35416666666</v>
+        <v>46351.85416666666</v>
       </c>
       <c r="L985" s="1" t="n">
+        <v>46351.9375</v>
+      </c>
+      <c r="M985" s="1" t="n">
         <v>46352.4375</v>
-      </c>
-      <c r="M985" s="1" t="n">
-        <v>46352.9375</v>
       </c>
     </row>
     <row r="986">
@@ -54549,13 +54549,13 @@
         </is>
       </c>
       <c r="K986" s="1" t="n">
-        <v>46356.9375</v>
+        <v>46356.4375</v>
       </c>
       <c r="L986" s="1" t="n">
-        <v>46356.97916666666</v>
+        <v>46356.47916666666</v>
       </c>
       <c r="M986" s="1" t="n">
-        <v>46357.64583333334</v>
+        <v>46357.14583333334</v>
       </c>
     </row>
     <row r="987">
@@ -54604,13 +54604,13 @@
         </is>
       </c>
       <c r="K987" s="1" t="n">
-        <v>46364.0625</v>
+        <v>46363.5625</v>
       </c>
       <c r="L987" s="1" t="n">
-        <v>46364.27083333334</v>
+        <v>46363.77083333334</v>
       </c>
       <c r="M987" s="1" t="n">
-        <v>46364.9375</v>
+        <v>46364.4375</v>
       </c>
     </row>
     <row r="988">
@@ -54659,13 +54659,13 @@
         </is>
       </c>
       <c r="K988" s="1" t="n">
-        <v>46366.64583333334</v>
+        <v>46366.14583333334</v>
       </c>
       <c r="L988" s="1" t="n">
-        <v>46366.6875</v>
+        <v>46366.1875</v>
       </c>
       <c r="M988" s="1" t="n">
-        <v>46367.6875</v>
+        <v>46367.1875</v>
       </c>
     </row>
     <row r="989">
@@ -54714,13 +54714,13 @@
         </is>
       </c>
       <c r="K989" s="1" t="n">
-        <v>46368.3125</v>
+        <v>46367.8125</v>
       </c>
       <c r="L989" s="1" t="n">
-        <v>46368.35416666666</v>
+        <v>46367.85416666666</v>
       </c>
       <c r="M989" s="1" t="n">
-        <v>46368.97916666666</v>
+        <v>46368.47916666666</v>
       </c>
     </row>
     <row r="990">
@@ -54769,13 +54769,13 @@
         </is>
       </c>
       <c r="K990" s="1" t="n">
-        <v>46370.47916666666</v>
+        <v>46369.97916666666</v>
       </c>
       <c r="L990" s="1" t="n">
-        <v>46370.6875</v>
+        <v>46370.1875</v>
       </c>
       <c r="M990" s="1" t="n">
-        <v>46371.35416666666</v>
+        <v>46370.85416666666</v>
       </c>
     </row>
     <row r="991">
@@ -54824,13 +54824,13 @@
         </is>
       </c>
       <c r="K991" s="1" t="n">
-        <v>46378.35416666666</v>
+        <v>46377.85416666666</v>
       </c>
       <c r="L991" s="1" t="n">
-        <v>46378.4375</v>
+        <v>46377.9375</v>
       </c>
       <c r="M991" s="1" t="n">
-        <v>46379.27083333334</v>
+        <v>46378.77083333334</v>
       </c>
     </row>
     <row r="992">
@@ -54879,13 +54879,13 @@
         </is>
       </c>
       <c r="K992" s="1" t="n">
-        <v>46380.35416666666</v>
+        <v>46379.85416666666</v>
       </c>
       <c r="L992" s="1" t="n">
+        <v>46379.9375</v>
+      </c>
+      <c r="M992" s="1" t="n">
         <v>46380.4375</v>
-      </c>
-      <c r="M992" s="1" t="n">
-        <v>46380.9375</v>
       </c>
     </row>
     <row r="993">
@@ -54934,13 +54934,13 @@
         </is>
       </c>
       <c r="K993" s="1" t="n">
-        <v>46384.9375</v>
+        <v>46384.4375</v>
       </c>
       <c r="L993" s="1" t="n">
-        <v>46384.97916666666</v>
+        <v>46384.47916666666</v>
       </c>
       <c r="M993" s="1" t="n">
-        <v>46385.64583333334</v>
+        <v>46385.14583333334</v>
       </c>
     </row>
     <row r="994">
@@ -54985,13 +54985,13 @@
       </c>
       <c r="J994" t="inlineStr"/>
       <c r="K994" s="1" t="n">
-        <v>46392.0625</v>
+        <v>46391.5625</v>
       </c>
       <c r="L994" s="1" t="n">
-        <v>46392.27083333334</v>
+        <v>46391.77083333334</v>
       </c>
       <c r="M994" s="1" t="n">
-        <v>46392.9375</v>
+        <v>46392.4375</v>
       </c>
     </row>
     <row r="995">
@@ -55538,10 +55538,10 @@
         <v>46302.125</v>
       </c>
       <c r="L1004" s="1" t="n">
-        <v>46302.16666666666</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="M1004" s="1" t="n">
-        <v>46302.875</v>
+        <v>46304.41666666666</v>
       </c>
     </row>
     <row r="1005">
@@ -55590,13 +55590,13 @@
         </is>
       </c>
       <c r="K1005" s="1" t="n">
-        <v>46303.16666666666</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="L1005" s="1" t="n">
-        <v>46303.22916666666</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="M1005" s="1" t="n">
-        <v>46303.5625</v>
+        <v>46305.10416666666</v>
       </c>
     </row>
     <row r="1006">
@@ -55645,13 +55645,13 @@
         </is>
       </c>
       <c r="K1006" s="1" t="n">
-        <v>46306.45833333334</v>
+        <v>46308</v>
       </c>
       <c r="L1006" s="1" t="n">
-        <v>46306.52083333334</v>
+        <v>46308.0625</v>
       </c>
       <c r="M1006" s="1" t="n">
-        <v>46307.02083333334</v>
+        <v>46308.5625</v>
       </c>
     </row>
     <row r="1007">
@@ -55700,13 +55700,13 @@
         </is>
       </c>
       <c r="K1007" s="1" t="n">
-        <v>46309.25</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="L1007" s="1" t="n">
-        <v>46309.41666666666</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="M1007" s="1" t="n">
-        <v>46310.04166666666</v>
+        <v>46311.58333333334</v>
       </c>
     </row>
     <row r="1008">
@@ -55755,13 +55755,13 @@
         </is>
       </c>
       <c r="K1008" s="1" t="n">
-        <v>46311.625</v>
+        <v>46313.16666666666</v>
       </c>
       <c r="L1008" s="1" t="n">
-        <v>46311.66666666666</v>
+        <v>46313.20833333334</v>
       </c>
       <c r="M1008" s="1" t="n">
-        <v>46311.875</v>
+        <v>46313.41666666666</v>
       </c>
     </row>
     <row r="1009">
@@ -55810,13 +55810,13 @@
         </is>
       </c>
       <c r="K1009" s="1" t="n">
-        <v>46312</v>
+        <v>46313.54166666666</v>
       </c>
       <c r="L1009" s="1" t="n">
-        <v>46312.125</v>
+        <v>46313.66666666666</v>
       </c>
       <c r="M1009" s="1" t="n">
-        <v>46313.58333333334</v>
+        <v>46315.125</v>
       </c>
     </row>
     <row r="1010">
@@ -55865,13 +55865,13 @@
         </is>
       </c>
       <c r="K1010" s="1" t="n">
-        <v>46313.79166666666</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="L1010" s="1" t="n">
-        <v>46313.83333333334</v>
+        <v>46315.375</v>
       </c>
       <c r="M1010" s="1" t="n">
-        <v>46314.16666666666</v>
+        <v>46315.70833333334</v>
       </c>
     </row>
     <row r="1011">
@@ -55920,13 +55920,13 @@
         </is>
       </c>
       <c r="K1011" s="1" t="n">
-        <v>46317.875</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="L1011" s="1" t="n">
-        <v>46317.9375</v>
+        <v>46319.47916666666</v>
       </c>
       <c r="M1011" s="1" t="n">
-        <v>46318.4375</v>
+        <v>46319.97916666666</v>
       </c>
     </row>
     <row r="1012">
@@ -55975,13 +55975,13 @@
         </is>
       </c>
       <c r="K1012" s="1" t="n">
-        <v>46319.25</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="L1012" s="1" t="n">
-        <v>46319.3125</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="M1012" s="1" t="n">
-        <v>46319.9375</v>
+        <v>46321.47916666666</v>
       </c>
     </row>
     <row r="1013">
@@ -56030,13 +56030,13 @@
         </is>
       </c>
       <c r="K1013" s="1" t="n">
-        <v>46321.29166666666</v>
+        <v>46323.83333333334</v>
       </c>
       <c r="L1013" s="1" t="n">
-        <v>46321.33333333334</v>
+        <v>46323.875</v>
       </c>
       <c r="M1013" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46324.58333333334</v>
       </c>
     </row>
     <row r="1014">
@@ -56085,13 +56085,13 @@
         </is>
       </c>
       <c r="K1014" s="1" t="n">
-        <v>46322.375</v>
+        <v>46324.91666666666</v>
       </c>
       <c r="L1014" s="1" t="n">
-        <v>46322.45833333334</v>
+        <v>46325</v>
       </c>
       <c r="M1014" s="1" t="n">
-        <v>46322.70833333334</v>
+        <v>46325.25</v>
       </c>
     </row>
     <row r="1015">
@@ -56140,13 +56140,13 @@
         </is>
       </c>
       <c r="K1015" s="1" t="n">
-        <v>46325.625</v>
+        <v>46328.16666666666</v>
       </c>
       <c r="L1015" s="1" t="n">
-        <v>46325.66666666666</v>
+        <v>46328.20833333334</v>
       </c>
       <c r="M1015" s="1" t="n">
-        <v>46326.125</v>
+        <v>46328.66666666666</v>
       </c>
     </row>
     <row r="1016">
@@ -56195,13 +56195,13 @@
         </is>
       </c>
       <c r="K1016" s="1" t="n">
-        <v>46328.33333333334</v>
+        <v>46330.875</v>
       </c>
       <c r="L1016" s="1" t="n">
-        <v>46328.5</v>
+        <v>46331.04166666666</v>
       </c>
       <c r="M1016" s="1" t="n">
-        <v>46328.95833333334</v>
+        <v>46331.5</v>
       </c>
     </row>
     <row r="1017">
@@ -56250,13 +56250,13 @@
         </is>
       </c>
       <c r="K1017" s="1" t="n">
-        <v>46330.70833333334</v>
+        <v>46333.25</v>
       </c>
       <c r="L1017" s="1" t="n">
-        <v>46330.75</v>
+        <v>46333.29166666666</v>
       </c>
       <c r="M1017" s="1" t="n">
-        <v>46330.91666666666</v>
+        <v>46333.45833333334</v>
       </c>
     </row>
     <row r="1018">
@@ -56305,13 +56305,13 @@
         </is>
       </c>
       <c r="K1018" s="1" t="n">
-        <v>46331.16666666666</v>
+        <v>46333.70833333334</v>
       </c>
       <c r="L1018" s="1" t="n">
-        <v>46331.29166666666</v>
+        <v>46333.83333333334</v>
       </c>
       <c r="M1018" s="1" t="n">
-        <v>46332.625</v>
+        <v>46335.16666666666</v>
       </c>
     </row>
     <row r="1019">
@@ -56360,13 +56360,13 @@
         </is>
       </c>
       <c r="K1019" s="1" t="n">
-        <v>46333.125</v>
+        <v>46335.66666666666</v>
       </c>
       <c r="L1019" s="1" t="n">
-        <v>46333.16666666666</v>
+        <v>46335.70833333334</v>
       </c>
       <c r="M1019" s="1" t="n">
-        <v>46333.45833333334</v>
+        <v>46336</v>
       </c>
     </row>
     <row r="1020">
@@ -56415,13 +56415,13 @@
         </is>
       </c>
       <c r="K1020" s="1" t="n">
-        <v>46337.54166666666</v>
+        <v>46340.08333333334</v>
       </c>
       <c r="L1020" s="1" t="n">
-        <v>46337.58333333334</v>
+        <v>46340.125</v>
       </c>
       <c r="M1020" s="1" t="n">
-        <v>46338.04166666666</v>
+        <v>46340.58333333334</v>
       </c>
     </row>
     <row r="1021">
@@ -56470,13 +56470,13 @@
         </is>
       </c>
       <c r="K1021" s="1" t="n">
-        <v>46339.125</v>
+        <v>46341.66666666666</v>
       </c>
       <c r="L1021" s="1" t="n">
-        <v>46339.16666666666</v>
+        <v>46341.70833333334</v>
       </c>
       <c r="M1021" s="1" t="n">
-        <v>46339.75</v>
+        <v>46342.29166666666</v>
       </c>
     </row>
     <row r="1022">
@@ -56525,13 +56525,13 @@
         </is>
       </c>
       <c r="K1022" s="1" t="n">
-        <v>46342.29166666666</v>
+        <v>46344.83333333334</v>
       </c>
       <c r="L1022" s="1" t="n">
-        <v>46342.33333333334</v>
+        <v>46344.875</v>
       </c>
       <c r="M1022" s="1" t="n">
-        <v>46343.04166666666</v>
+        <v>46345.58333333334</v>
       </c>
     </row>
     <row r="1023">
@@ -56580,13 +56580,13 @@
         </is>
       </c>
       <c r="K1023" s="1" t="n">
-        <v>46343.375</v>
+        <v>46345.91666666666</v>
       </c>
       <c r="L1023" s="1" t="n">
-        <v>46343.45833333334</v>
+        <v>46346</v>
       </c>
       <c r="M1023" s="1" t="n">
-        <v>46343.70833333334</v>
+        <v>46346.25</v>
       </c>
     </row>
     <row r="1024">
@@ -56635,13 +56635,13 @@
         </is>
       </c>
       <c r="K1024" s="1" t="n">
-        <v>46346.625</v>
+        <v>46349.16666666666</v>
       </c>
       <c r="L1024" s="1" t="n">
-        <v>46346.66666666666</v>
+        <v>46349.20833333334</v>
       </c>
       <c r="M1024" s="1" t="n">
-        <v>46347.125</v>
+        <v>46349.66666666666</v>
       </c>
     </row>
     <row r="1025">
@@ -56690,13 +56690,13 @@
         </is>
       </c>
       <c r="K1025" s="1" t="n">
-        <v>46349.33333333334</v>
+        <v>46351.875</v>
       </c>
       <c r="L1025" s="1" t="n">
-        <v>46349.5</v>
+        <v>46352.04166666666</v>
       </c>
       <c r="M1025" s="1" t="n">
-        <v>46349.95833333334</v>
+        <v>46352.5</v>
       </c>
     </row>
     <row r="1026">
@@ -56745,13 +56745,13 @@
         </is>
       </c>
       <c r="K1026" s="1" t="n">
-        <v>46351.70833333334</v>
+        <v>46354.25</v>
       </c>
       <c r="L1026" s="1" t="n">
-        <v>46351.75</v>
+        <v>46354.29166666666</v>
       </c>
       <c r="M1026" s="1" t="n">
-        <v>46351.91666666666</v>
+        <v>46354.45833333334</v>
       </c>
     </row>
     <row r="1027">
@@ -56800,13 +56800,13 @@
         </is>
       </c>
       <c r="K1027" s="1" t="n">
-        <v>46352.16666666666</v>
+        <v>46354.70833333334</v>
       </c>
       <c r="L1027" s="1" t="n">
-        <v>46352.29166666666</v>
+        <v>46354.83333333334</v>
       </c>
       <c r="M1027" s="1" t="n">
-        <v>46353.625</v>
+        <v>46356.16666666666</v>
       </c>
     </row>
     <row r="1028">
@@ -56855,13 +56855,13 @@
         </is>
       </c>
       <c r="K1028" s="1" t="n">
-        <v>46354.125</v>
+        <v>46356.66666666666</v>
       </c>
       <c r="L1028" s="1" t="n">
-        <v>46354.16666666666</v>
+        <v>46356.70833333334</v>
       </c>
       <c r="M1028" s="1" t="n">
-        <v>46354.45833333334</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="1029">
@@ -56910,13 +56910,13 @@
         </is>
       </c>
       <c r="K1029" s="1" t="n">
-        <v>46358.54166666666</v>
+        <v>46361.08333333334</v>
       </c>
       <c r="L1029" s="1" t="n">
-        <v>46358.58333333334</v>
+        <v>46361.125</v>
       </c>
       <c r="M1029" s="1" t="n">
-        <v>46359.04166666666</v>
+        <v>46361.58333333334</v>
       </c>
     </row>
     <row r="1030">
@@ -56961,13 +56961,13 @@
       </c>
       <c r="J1030" t="inlineStr"/>
       <c r="K1030" s="1" t="n">
-        <v>46360.125</v>
+        <v>46362.66666666666</v>
       </c>
       <c r="L1030" s="1" t="n">
-        <v>46360.16666666666</v>
+        <v>46362.70833333334</v>
       </c>
       <c r="M1030" s="1" t="n">
-        <v>46360.75</v>
+        <v>46363.29166666666</v>
       </c>
     </row>
     <row r="1031">
@@ -59212,13 +59212,13 @@
         </is>
       </c>
       <c r="K1071" s="1" t="n">
-        <v>46300</v>
+        <v>46301.5</v>
       </c>
       <c r="L1071" s="1" t="n">
-        <v>46300.5</v>
+        <v>46301.58333333334</v>
       </c>
       <c r="M1071" s="1" t="n">
-        <v>46301.08333333334</v>
+        <v>46301.91666666666</v>
       </c>
     </row>
     <row r="1072">
@@ -59267,13 +59267,13 @@
         </is>
       </c>
       <c r="K1072" s="1" t="n">
-        <v>46302.1875</v>
+        <v>46302.04166666666</v>
       </c>
       <c r="L1072" s="1" t="n">
-        <v>46302.25</v>
+        <v>46302.10416666666</v>
       </c>
       <c r="M1072" s="1" t="n">
-        <v>46302.58333333334</v>
+        <v>46302.4375</v>
       </c>
     </row>
     <row r="1073">
@@ -59322,13 +59322,13 @@
         </is>
       </c>
       <c r="K1073" s="1" t="n">
-        <v>46303.91666666666</v>
+        <v>46303.5</v>
       </c>
       <c r="L1073" s="1" t="n">
-        <v>46303.95833333334</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="M1073" s="1" t="n">
-        <v>46304.625</v>
+        <v>46304.20833333334</v>
       </c>
     </row>
     <row r="1074">
@@ -59377,13 +59377,13 @@
         </is>
       </c>
       <c r="K1074" s="1" t="n">
-        <v>46305.91666666666</v>
+        <v>46305.5</v>
       </c>
       <c r="L1074" s="1" t="n">
-        <v>46306.08333333334</v>
+        <v>46305.66666666666</v>
       </c>
       <c r="M1074" s="1" t="n">
-        <v>46306.58333333334</v>
+        <v>46306.16666666666</v>
       </c>
     </row>
     <row r="1075">
@@ -59432,13 +59432,13 @@
         </is>
       </c>
       <c r="K1075" s="1" t="n">
-        <v>46310.75</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="L1075" s="1" t="n">
-        <v>46310.91666666666</v>
+        <v>46310.5</v>
       </c>
       <c r="M1075" s="1" t="n">
-        <v>46311.75</v>
+        <v>46311.33333333334</v>
       </c>
     </row>
     <row r="1076">
@@ -59487,13 +59487,13 @@
         </is>
       </c>
       <c r="K1076" s="1" t="n">
-        <v>46313.41666666666</v>
+        <v>46313</v>
       </c>
       <c r="L1076" s="1" t="n">
-        <v>46313.45833333334</v>
+        <v>46313.04166666666</v>
       </c>
       <c r="M1076" s="1" t="n">
-        <v>46314.29166666666</v>
+        <v>46313.875</v>
       </c>
     </row>
     <row r="1077">
@@ -59542,13 +59542,13 @@
         </is>
       </c>
       <c r="K1077" s="1" t="n">
-        <v>46317.45833333334</v>
+        <v>46317.04166666666</v>
       </c>
       <c r="L1077" s="1" t="n">
-        <v>46317.54166666666</v>
+        <v>46317.125</v>
       </c>
       <c r="M1077" s="1" t="n">
-        <v>46319.20833333334</v>
+        <v>46318.79166666666</v>
       </c>
     </row>
     <row r="1078">
@@ -59597,13 +59597,13 @@
         </is>
       </c>
       <c r="K1078" s="1" t="n">
-        <v>46321.66666666666</v>
+        <v>46321.25</v>
       </c>
       <c r="L1078" s="1" t="n">
-        <v>46321.83333333334</v>
+        <v>46321.41666666666</v>
       </c>
       <c r="M1078" s="1" t="n">
-        <v>46322.66666666666</v>
+        <v>46322.25</v>
       </c>
     </row>
     <row r="1079">
@@ -59652,13 +59652,13 @@
         </is>
       </c>
       <c r="K1079" s="1" t="n">
-        <v>46325.20833333334</v>
+        <v>46324.79166666666</v>
       </c>
       <c r="L1079" s="1" t="n">
-        <v>46325.27083333334</v>
+        <v>46324.85416666666</v>
       </c>
       <c r="M1079" s="1" t="n">
-        <v>46325.77083333334</v>
+        <v>46325.35416666666</v>
       </c>
     </row>
     <row r="1080">
@@ -59707,13 +59707,13 @@
         </is>
       </c>
       <c r="K1080" s="1" t="n">
-        <v>46326</v>
+        <v>46325.58333333334</v>
       </c>
       <c r="L1080" s="1" t="n">
-        <v>46326.04166666666</v>
+        <v>46325.625</v>
       </c>
       <c r="M1080" s="1" t="n">
-        <v>46326.54166666666</v>
+        <v>46326.125</v>
       </c>
     </row>
     <row r="1081">
@@ -59762,13 +59762,13 @@
         </is>
       </c>
       <c r="K1081" s="1" t="n">
-        <v>46329.625</v>
+        <v>46329.20833333334</v>
       </c>
       <c r="L1081" s="1" t="n">
-        <v>46329.66666666666</v>
+        <v>46329.25</v>
       </c>
       <c r="M1081" s="1" t="n">
-        <v>46330.33333333334</v>
+        <v>46329.91666666666</v>
       </c>
     </row>
     <row r="1082">
@@ -59817,13 +59817,13 @@
         </is>
       </c>
       <c r="K1082" s="1" t="n">
-        <v>46331.41666666666</v>
+        <v>46331</v>
       </c>
       <c r="L1082" s="1" t="n">
-        <v>46331.45833333334</v>
+        <v>46331.04166666666</v>
       </c>
       <c r="M1082" s="1" t="n">
-        <v>46332.04166666666</v>
+        <v>46331.625</v>
       </c>
     </row>
     <row r="1083">
@@ -59872,13 +59872,13 @@
         </is>
       </c>
       <c r="K1083" s="1" t="n">
-        <v>46332.22916666666</v>
+        <v>46331.8125</v>
       </c>
       <c r="L1083" s="1" t="n">
-        <v>46332.29166666666</v>
+        <v>46331.875</v>
       </c>
       <c r="M1083" s="1" t="n">
-        <v>46332.625</v>
+        <v>46332.20833333334</v>
       </c>
     </row>
     <row r="1084">
@@ -59927,13 +59927,13 @@
         </is>
       </c>
       <c r="K1084" s="1" t="n">
-        <v>46333.91666666666</v>
+        <v>46333.5</v>
       </c>
       <c r="L1084" s="1" t="n">
-        <v>46334.08333333334</v>
+        <v>46333.66666666666</v>
       </c>
       <c r="M1084" s="1" t="n">
-        <v>46334.58333333334</v>
+        <v>46334.16666666666</v>
       </c>
     </row>
     <row r="1085">
@@ -59982,13 +59982,13 @@
         </is>
       </c>
       <c r="K1085" s="1" t="n">
-        <v>46338.75</v>
+        <v>46338.33333333334</v>
       </c>
       <c r="L1085" s="1" t="n">
-        <v>46338.91666666666</v>
+        <v>46338.5</v>
       </c>
       <c r="M1085" s="1" t="n">
-        <v>46339.75</v>
+        <v>46339.33333333334</v>
       </c>
     </row>
     <row r="1086">
@@ -60037,13 +60037,13 @@
         </is>
       </c>
       <c r="K1086" s="1" t="n">
-        <v>46341.41666666666</v>
+        <v>46341</v>
       </c>
       <c r="L1086" s="1" t="n">
-        <v>46341.45833333334</v>
+        <v>46341.04166666666</v>
       </c>
       <c r="M1086" s="1" t="n">
-        <v>46342.29166666666</v>
+        <v>46341.875</v>
       </c>
     </row>
     <row r="1087">
@@ -60092,13 +60092,13 @@
         </is>
       </c>
       <c r="K1087" s="1" t="n">
-        <v>46345.45833333334</v>
+        <v>46345.04166666666</v>
       </c>
       <c r="L1087" s="1" t="n">
-        <v>46345.54166666666</v>
+        <v>46345.125</v>
       </c>
       <c r="M1087" s="1" t="n">
-        <v>46347.20833333334</v>
+        <v>46346.79166666666</v>
       </c>
     </row>
     <row r="1088">
@@ -60147,13 +60147,13 @@
         </is>
       </c>
       <c r="K1088" s="1" t="n">
-        <v>46349.66666666666</v>
+        <v>46349.25</v>
       </c>
       <c r="L1088" s="1" t="n">
-        <v>46349.83333333334</v>
+        <v>46349.41666666666</v>
       </c>
       <c r="M1088" s="1" t="n">
-        <v>46350.66666666666</v>
+        <v>46350.25</v>
       </c>
     </row>
     <row r="1089">
@@ -60202,13 +60202,13 @@
         </is>
       </c>
       <c r="K1089" s="1" t="n">
-        <v>46353.20833333334</v>
+        <v>46352.79166666666</v>
       </c>
       <c r="L1089" s="1" t="n">
-        <v>46353.27083333334</v>
+        <v>46352.85416666666</v>
       </c>
       <c r="M1089" s="1" t="n">
-        <v>46353.77083333334</v>
+        <v>46353.35416666666</v>
       </c>
     </row>
     <row r="1090">
@@ -60257,13 +60257,13 @@
         </is>
       </c>
       <c r="K1090" s="1" t="n">
-        <v>46354</v>
+        <v>46353.58333333334</v>
       </c>
       <c r="L1090" s="1" t="n">
-        <v>46354.04166666666</v>
+        <v>46353.625</v>
       </c>
       <c r="M1090" s="1" t="n">
-        <v>46354.54166666666</v>
+        <v>46354.125</v>
       </c>
     </row>
     <row r="1091">
@@ -60312,13 +60312,13 @@
         </is>
       </c>
       <c r="K1091" s="1" t="n">
-        <v>46357.625</v>
+        <v>46357.25</v>
       </c>
       <c r="L1091" s="1" t="n">
-        <v>46357.66666666666</v>
+        <v>46357.29166666666</v>
       </c>
       <c r="M1091" s="1" t="n">
-        <v>46358.33333333334</v>
+        <v>46357.95833333334</v>
       </c>
     </row>
     <row r="1092">
@@ -60367,13 +60367,13 @@
         </is>
       </c>
       <c r="K1092" s="1" t="n">
-        <v>46359.41666666666</v>
+        <v>46359.04166666666</v>
       </c>
       <c r="L1092" s="1" t="n">
-        <v>46359.45833333334</v>
+        <v>46359.08333333334</v>
       </c>
       <c r="M1092" s="1" t="n">
-        <v>46360.04166666666</v>
+        <v>46359.66666666666</v>
       </c>
     </row>
     <row r="1093">
@@ -60422,13 +60422,13 @@
         </is>
       </c>
       <c r="K1093" s="1" t="n">
-        <v>46360.22916666666</v>
+        <v>46359.85416666666</v>
       </c>
       <c r="L1093" s="1" t="n">
-        <v>46360.29166666666</v>
+        <v>46359.91666666666</v>
       </c>
       <c r="M1093" s="1" t="n">
-        <v>46360.625</v>
+        <v>46360.25</v>
       </c>
     </row>
     <row r="1094">
@@ -60477,13 +60477,13 @@
         </is>
       </c>
       <c r="K1094" s="1" t="n">
-        <v>46361.91666666666</v>
+        <v>46361.54166666666</v>
       </c>
       <c r="L1094" s="1" t="n">
-        <v>46362.08333333334</v>
+        <v>46361.70833333334</v>
       </c>
       <c r="M1094" s="1" t="n">
-        <v>46362.58333333334</v>
+        <v>46362.20833333334</v>
       </c>
     </row>
     <row r="1095">
@@ -60532,13 +60532,13 @@
         </is>
       </c>
       <c r="K1095" s="1" t="n">
-        <v>46366.75</v>
+        <v>46366.375</v>
       </c>
       <c r="L1095" s="1" t="n">
-        <v>46366.91666666666</v>
+        <v>46366.54166666666</v>
       </c>
       <c r="M1095" s="1" t="n">
-        <v>46367.75</v>
+        <v>46367.375</v>
       </c>
     </row>
     <row r="1096">
@@ -60587,13 +60587,13 @@
         </is>
       </c>
       <c r="K1096" s="1" t="n">
-        <v>46369.41666666666</v>
+        <v>46369.04166666666</v>
       </c>
       <c r="L1096" s="1" t="n">
-        <v>46369.45833333334</v>
+        <v>46369.08333333334</v>
       </c>
       <c r="M1096" s="1" t="n">
-        <v>46370.29166666666</v>
+        <v>46369.91666666666</v>
       </c>
     </row>
     <row r="1097">
@@ -60642,13 +60642,13 @@
         </is>
       </c>
       <c r="K1097" s="1" t="n">
-        <v>46373.45833333334</v>
+        <v>46373.08333333334</v>
       </c>
       <c r="L1097" s="1" t="n">
-        <v>46373.54166666666</v>
+        <v>46373.16666666666</v>
       </c>
       <c r="M1097" s="1" t="n">
-        <v>46375.20833333334</v>
+        <v>46374.83333333334</v>
       </c>
     </row>
     <row r="1098">
@@ -60697,13 +60697,13 @@
         </is>
       </c>
       <c r="K1098" s="1" t="n">
-        <v>46377.66666666666</v>
+        <v>46377.29166666666</v>
       </c>
       <c r="L1098" s="1" t="n">
-        <v>46377.83333333334</v>
+        <v>46377.45833333334</v>
       </c>
       <c r="M1098" s="1" t="n">
-        <v>46378.66666666666</v>
+        <v>46378.29166666666</v>
       </c>
     </row>
     <row r="1099">
@@ -60752,13 +60752,13 @@
         </is>
       </c>
       <c r="K1099" s="1" t="n">
-        <v>46381.20833333334</v>
+        <v>46380.83333333334</v>
       </c>
       <c r="L1099" s="1" t="n">
-        <v>46381.27083333334</v>
+        <v>46380.89583333334</v>
       </c>
       <c r="M1099" s="1" t="n">
-        <v>46381.77083333334</v>
+        <v>46381.39583333334</v>
       </c>
     </row>
     <row r="1100">
@@ -60807,13 +60807,13 @@
         </is>
       </c>
       <c r="K1100" s="1" t="n">
-        <v>46382</v>
+        <v>46381.625</v>
       </c>
       <c r="L1100" s="1" t="n">
-        <v>46382.04166666666</v>
+        <v>46381.66666666666</v>
       </c>
       <c r="M1100" s="1" t="n">
-        <v>46382.54166666666</v>
+        <v>46382.16666666666</v>
       </c>
     </row>
     <row r="1101">
@@ -60862,13 +60862,13 @@
         </is>
       </c>
       <c r="K1101" s="1" t="n">
-        <v>46385.625</v>
+        <v>46385.25</v>
       </c>
       <c r="L1101" s="1" t="n">
-        <v>46385.66666666666</v>
+        <v>46385.29166666666</v>
       </c>
       <c r="M1101" s="1" t="n">
-        <v>46386.33333333334</v>
+        <v>46385.95833333334</v>
       </c>
     </row>
     <row r="1102">
@@ -60917,13 +60917,13 @@
         </is>
       </c>
       <c r="K1102" s="1" t="n">
-        <v>46387.41666666666</v>
+        <v>46387.04166666666</v>
       </c>
       <c r="L1102" s="1" t="n">
-        <v>46387.45833333334</v>
+        <v>46387.08333333334</v>
       </c>
       <c r="M1102" s="1" t="n">
-        <v>46388.04166666666</v>
+        <v>46387.66666666666</v>
       </c>
     </row>
     <row r="1103">
@@ -60972,13 +60972,13 @@
         </is>
       </c>
       <c r="K1103" s="1" t="n">
-        <v>46388.22916666666</v>
+        <v>46387.85416666666</v>
       </c>
       <c r="L1103" s="1" t="n">
-        <v>46388.29166666666</v>
+        <v>46387.91666666666</v>
       </c>
       <c r="M1103" s="1" t="n">
-        <v>46388.625</v>
+        <v>46388.25</v>
       </c>
     </row>
     <row r="1104">
@@ -61027,13 +61027,13 @@
         </is>
       </c>
       <c r="K1104" s="1" t="n">
-        <v>46389.91666666666</v>
+        <v>46389.54166666666</v>
       </c>
       <c r="L1104" s="1" t="n">
-        <v>46390.08333333334</v>
+        <v>46389.70833333334</v>
       </c>
       <c r="M1104" s="1" t="n">
-        <v>46390.58333333334</v>
+        <v>46390.20833333334</v>
       </c>
     </row>
     <row r="1105">
@@ -61082,13 +61082,13 @@
         </is>
       </c>
       <c r="K1105" s="1" t="n">
-        <v>46394.75</v>
+        <v>46394.375</v>
       </c>
       <c r="L1105" s="1" t="n">
-        <v>46394.91666666666</v>
+        <v>46394.54166666666</v>
       </c>
       <c r="M1105" s="1" t="n">
-        <v>46395.75</v>
+        <v>46395.375</v>
       </c>
     </row>
     <row r="1106">
@@ -61137,13 +61137,13 @@
         </is>
       </c>
       <c r="K1106" s="1" t="n">
-        <v>46397.41666666666</v>
+        <v>46397.04166666666</v>
       </c>
       <c r="L1106" s="1" t="n">
-        <v>46397.45833333334</v>
+        <v>46397.08333333334</v>
       </c>
       <c r="M1106" s="1" t="n">
-        <v>46398.29166666666</v>
+        <v>46397.91666666666</v>
       </c>
     </row>
     <row r="1107">
@@ -61192,13 +61192,13 @@
         </is>
       </c>
       <c r="K1107" s="1" t="n">
-        <v>46401.45833333334</v>
+        <v>46401.08333333334</v>
       </c>
       <c r="L1107" s="1" t="n">
-        <v>46401.54166666666</v>
+        <v>46401.16666666666</v>
       </c>
       <c r="M1107" s="1" t="n">
-        <v>46403.20833333334</v>
+        <v>46402.83333333334</v>
       </c>
     </row>
     <row r="1108">
@@ -61247,13 +61247,13 @@
         </is>
       </c>
       <c r="K1108" s="1" t="n">
-        <v>46405.66666666666</v>
+        <v>46405.29166666666</v>
       </c>
       <c r="L1108" s="1" t="n">
-        <v>46405.83333333334</v>
+        <v>46405.45833333334</v>
       </c>
       <c r="M1108" s="1" t="n">
-        <v>46406.66666666666</v>
+        <v>46406.29166666666</v>
       </c>
     </row>
     <row r="1109">
@@ -61302,13 +61302,13 @@
         </is>
       </c>
       <c r="K1109" s="1" t="n">
-        <v>46409.20833333334</v>
+        <v>46408.83333333334</v>
       </c>
       <c r="L1109" s="1" t="n">
-        <v>46409.27083333334</v>
+        <v>46408.89583333334</v>
       </c>
       <c r="M1109" s="1" t="n">
-        <v>46409.77083333334</v>
+        <v>46409.39583333334</v>
       </c>
     </row>
     <row r="1110">
@@ -61353,13 +61353,13 @@
       </c>
       <c r="J1110" t="inlineStr"/>
       <c r="K1110" s="1" t="n">
-        <v>46410</v>
+        <v>46409.625</v>
       </c>
       <c r="L1110" s="1" t="n">
-        <v>46410.04166666666</v>
+        <v>46409.66666666666</v>
       </c>
       <c r="M1110" s="1" t="n">
-        <v>46410.54166666666</v>
+        <v>46410.16666666666</v>
       </c>
     </row>
   </sheetData>

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -51039,7 +51039,7 @@
         <v>46297.52083333334</v>
       </c>
       <c r="M922" s="1" t="n">
-        <v>46297.97916666666</v>
+        <v>46297.95833333334</v>
       </c>
     </row>
     <row r="923">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -9598,7 +9598,7 @@
         <v>46296.66666666666</v>
       </c>
       <c r="M167" s="1" t="n">
-        <v>46298.125</v>
+        <v>46298.25</v>
       </c>
     </row>
     <row r="168">
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46298.41666666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>46298.47916666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="M168" s="1" t="n">
-        <v>46299.10416666666</v>
+        <v>46299.22916666666</v>
       </c>
     </row>
     <row r="169">
@@ -9702,13 +9702,13 @@
         </is>
       </c>
       <c r="K169" s="1" t="n">
-        <v>46300.16666666666</v>
+        <v>46300.29166666666</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>46300.375</v>
+        <v>46300.5</v>
       </c>
       <c r="M169" s="1" t="n">
-        <v>46301.04166666666</v>
+        <v>46301.16666666666</v>
       </c>
     </row>
     <row r="170">
@@ -9757,13 +9757,13 @@
         </is>
       </c>
       <c r="K170" s="1" t="n">
-        <v>46308.04166666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>46308.125</v>
+        <v>46308.25</v>
       </c>
       <c r="M170" s="1" t="n">
-        <v>46308.95833333334</v>
+        <v>46309.08333333334</v>
       </c>
     </row>
     <row r="171">
@@ -9812,13 +9812,13 @@
         </is>
       </c>
       <c r="K171" s="1" t="n">
-        <v>46310.04166666666</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>46310.125</v>
+        <v>46310.25</v>
       </c>
       <c r="M171" s="1" t="n">
-        <v>46310.625</v>
+        <v>46310.75</v>
       </c>
     </row>
     <row r="172">
@@ -9867,13 +9867,13 @@
         </is>
       </c>
       <c r="K172" s="1" t="n">
-        <v>46314.625</v>
+        <v>46314.75</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>46314.66666666666</v>
+        <v>46314.79166666666</v>
       </c>
       <c r="M172" s="1" t="n">
-        <v>46315.33333333334</v>
+        <v>46315.45833333334</v>
       </c>
     </row>
     <row r="173">
@@ -9922,13 +9922,13 @@
         </is>
       </c>
       <c r="K173" s="1" t="n">
-        <v>46321.75</v>
+        <v>46321.875</v>
       </c>
       <c r="L173" s="1" t="n">
-        <v>46321.95833333334</v>
+        <v>46322.08333333334</v>
       </c>
       <c r="M173" s="1" t="n">
-        <v>46322.625</v>
+        <v>46322.75</v>
       </c>
     </row>
     <row r="174">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -7567,7 +7567,7 @@
         <v>46297.83333333334</v>
       </c>
       <c r="M130" s="1" t="n">
-        <v>46298.79166666666</v>
+        <v>46298.91666666666</v>
       </c>
     </row>
     <row r="131">
@@ -7616,13 +7616,13 @@
         </is>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46300.66666666666</v>
+        <v>46300.91666666666</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>46300.70833333334</v>
+        <v>46300.95833333334</v>
       </c>
       <c r="M131" s="1" t="n">
-        <v>46302.70833333334</v>
+        <v>46302.95833333334</v>
       </c>
     </row>
     <row r="132">
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46304.70833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>46304.75</v>
+        <v>46305</v>
       </c>
       <c r="M133" s="1" t="n">
-        <v>46305.45833333334</v>
+        <v>46305.70833333334</v>
       </c>
     </row>
     <row r="134">
@@ -43300,7 +43300,7 @@
         <v>46297.29166666666</v>
       </c>
       <c r="M781" s="1" t="n">
-        <v>46298.70833333334</v>
+        <v>46298.83333333334</v>
       </c>
     </row>
     <row r="782">
@@ -43349,13 +43349,13 @@
         </is>
       </c>
       <c r="K782" s="1" t="n">
-        <v>46299</v>
+        <v>46299.25</v>
       </c>
       <c r="L782" s="1" t="n">
-        <v>46299.0625</v>
+        <v>46299.3125</v>
       </c>
       <c r="M782" s="1" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.58333333334</v>
       </c>
     </row>
     <row r="783">
@@ -43404,13 +43404,13 @@
         </is>
       </c>
       <c r="K783" s="1" t="n">
-        <v>46299.70833333334</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="L783" s="1" t="n">
-        <v>46300.75</v>
+        <v>46301</v>
       </c>
       <c r="M783" s="1" t="n">
-        <v>46301.08333333334</v>
+        <v>46301.33333333334</v>
       </c>
     </row>
     <row r="784">
@@ -43459,13 +43459,13 @@
         </is>
       </c>
       <c r="K784" s="1" t="n">
-        <v>46306.04166666666</v>
+        <v>46306.29166666666</v>
       </c>
       <c r="L784" s="1" t="n">
-        <v>46306.20833333334</v>
+        <v>46306.45833333334</v>
       </c>
       <c r="M784" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46307.08333333334</v>
       </c>
     </row>
     <row r="785">
@@ -43514,13 +43514,13 @@
         </is>
       </c>
       <c r="K785" s="1" t="n">
-        <v>46308.5</v>
+        <v>46308.75</v>
       </c>
       <c r="L785" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="M785" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46309.04166666666</v>
       </c>
     </row>
     <row r="786">
@@ -43569,13 +43569,13 @@
         </is>
       </c>
       <c r="K786" s="1" t="n">
-        <v>46308.875</v>
+        <v>46309.125</v>
       </c>
       <c r="L786" s="1" t="n">
-        <v>46309</v>
+        <v>46309.25</v>
       </c>
       <c r="M786" s="1" t="n">
-        <v>46310.5</v>
+        <v>46310.75</v>
       </c>
     </row>
     <row r="787">
@@ -43624,13 +43624,13 @@
         </is>
       </c>
       <c r="K787" s="1" t="n">
-        <v>46310.70833333334</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="L787" s="1" t="n">
-        <v>46310.75</v>
+        <v>46311</v>
       </c>
       <c r="M787" s="1" t="n">
-        <v>46311.16666666666</v>
+        <v>46311.41666666666</v>
       </c>
     </row>
     <row r="788">
@@ -43679,13 +43679,13 @@
         </is>
       </c>
       <c r="K788" s="1" t="n">
-        <v>46312.79166666666</v>
+        <v>46313.04166666666</v>
       </c>
       <c r="L788" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.20833333334</v>
       </c>
       <c r="M788" s="1" t="n">
-        <v>46313.5</v>
+        <v>46313.75</v>
       </c>
     </row>
     <row r="789">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -39238,7 +39238,7 @@
         <v>46299.02083333334</v>
       </c>
       <c r="M707" s="1" t="n">
-        <v>46299.45833333334</v>
+        <v>46299.75</v>
       </c>
     </row>
     <row r="708">
@@ -39287,13 +39287,13 @@
         </is>
       </c>
       <c r="K708" s="1" t="n">
-        <v>46299.79166666666</v>
+        <v>46300.125</v>
       </c>
       <c r="L708" s="1" t="n">
-        <v>46299.83333333334</v>
+        <v>46300.16666666666</v>
       </c>
       <c r="M708" s="1" t="n">
-        <v>46300.75</v>
+        <v>46301.08333333334</v>
       </c>
     </row>
     <row r="709">
@@ -39342,13 +39342,13 @@
         </is>
       </c>
       <c r="K709" s="1" t="n">
-        <v>46306.16666666666</v>
+        <v>46306.5</v>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46306.33333333334</v>
+        <v>46306.66666666666</v>
       </c>
       <c r="M709" s="1" t="n">
-        <v>46306.91666666666</v>
+        <v>46307.25</v>
       </c>
     </row>
     <row r="710">
@@ -39397,13 +39397,13 @@
         </is>
       </c>
       <c r="K710" s="1" t="n">
-        <v>46308.6875</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46308.72916666666</v>
+        <v>46309.0625</v>
       </c>
       <c r="M710" s="1" t="n">
-        <v>46309.08333333334</v>
+        <v>46309.41666666666</v>
       </c>
     </row>
     <row r="711">
@@ -39452,13 +39452,13 @@
         </is>
       </c>
       <c r="K711" s="1" t="n">
-        <v>46309.20833333334</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46309.29166666666</v>
+        <v>46309.625</v>
       </c>
       <c r="M711" s="1" t="n">
-        <v>46310.29166666666</v>
+        <v>46310.625</v>
       </c>
     </row>
     <row r="712">
@@ -39507,13 +39507,13 @@
         </is>
       </c>
       <c r="K712" s="1" t="n">
-        <v>46310.5</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46310.54166666666</v>
+        <v>46310.875</v>
       </c>
       <c r="M712" s="1" t="n">
-        <v>46311.04166666666</v>
+        <v>46311.375</v>
       </c>
     </row>
     <row r="713">
@@ -39562,13 +39562,13 @@
         </is>
       </c>
       <c r="K713" s="1" t="n">
-        <v>46312.85416666666</v>
+        <v>46313.1875</v>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46313.02083333334</v>
+        <v>46313.35416666666</v>
       </c>
       <c r="M713" s="1" t="n">
-        <v>46313.70833333334</v>
+        <v>46314.04166666666</v>
       </c>
     </row>
     <row r="714">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -7567,7 +7567,7 @@
         <v>46297.83333333334</v>
       </c>
       <c r="M130" s="1" t="n">
-        <v>46298.91666666666</v>
+        <v>46298.875</v>
       </c>
     </row>
     <row r="131">
@@ -7616,13 +7616,13 @@
         </is>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46300.91666666666</v>
+        <v>46300.83333333334</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>46300.95833333334</v>
+        <v>46300.875</v>
       </c>
       <c r="M131" s="1" t="n">
-        <v>46302.95833333334</v>
+        <v>46302.875</v>
       </c>
     </row>
     <row r="132">
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46304.95833333334</v>
+        <v>46304.875</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>46305</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="M133" s="1" t="n">
-        <v>46305.70833333334</v>
+        <v>46305.625</v>
       </c>
     </row>
     <row r="134">
@@ -43300,7 +43300,7 @@
         <v>46297.29166666666</v>
       </c>
       <c r="M781" s="1" t="n">
-        <v>46298.83333333334</v>
+        <v>46298.875</v>
       </c>
     </row>
     <row r="782">
@@ -43349,13 +43349,13 @@
         </is>
       </c>
       <c r="K782" s="1" t="n">
-        <v>46299.25</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="L782" s="1" t="n">
-        <v>46299.3125</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="M782" s="1" t="n">
-        <v>46299.58333333334</v>
+        <v>46299.66666666666</v>
       </c>
     </row>
     <row r="783">
@@ -43404,13 +43404,13 @@
         </is>
       </c>
       <c r="K783" s="1" t="n">
-        <v>46299.95833333334</v>
+        <v>46300.04166666666</v>
       </c>
       <c r="L783" s="1" t="n">
-        <v>46301</v>
+        <v>46301.08333333334</v>
       </c>
       <c r="M783" s="1" t="n">
-        <v>46301.33333333334</v>
+        <v>46301.41666666666</v>
       </c>
     </row>
     <row r="784">
@@ -43459,13 +43459,13 @@
         </is>
       </c>
       <c r="K784" s="1" t="n">
-        <v>46306.29166666666</v>
+        <v>46306.375</v>
       </c>
       <c r="L784" s="1" t="n">
-        <v>46306.45833333334</v>
+        <v>46306.54166666666</v>
       </c>
       <c r="M784" s="1" t="n">
-        <v>46307.08333333334</v>
+        <v>46307.16666666666</v>
       </c>
     </row>
     <row r="785">
@@ -43514,13 +43514,13 @@
         </is>
       </c>
       <c r="K785" s="1" t="n">
-        <v>46308.75</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="L785" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46308.875</v>
       </c>
       <c r="M785" s="1" t="n">
-        <v>46309.04166666666</v>
+        <v>46309.125</v>
       </c>
     </row>
     <row r="786">
@@ -43569,13 +43569,13 @@
         </is>
       </c>
       <c r="K786" s="1" t="n">
-        <v>46309.125</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="L786" s="1" t="n">
-        <v>46309.25</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="M786" s="1" t="n">
-        <v>46310.75</v>
+        <v>46310.83333333334</v>
       </c>
     </row>
     <row r="787">
@@ -43624,13 +43624,13 @@
         </is>
       </c>
       <c r="K787" s="1" t="n">
-        <v>46310.95833333334</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="L787" s="1" t="n">
-        <v>46311</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="M787" s="1" t="n">
-        <v>46311.41666666666</v>
+        <v>46311.5</v>
       </c>
     </row>
     <row r="788">
@@ -43679,13 +43679,13 @@
         </is>
       </c>
       <c r="K788" s="1" t="n">
-        <v>46313.04166666666</v>
+        <v>46313.125</v>
       </c>
       <c r="L788" s="1" t="n">
-        <v>46313.20833333334</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="M788" s="1" t="n">
-        <v>46313.75</v>
+        <v>46313.83333333334</v>
       </c>
     </row>
     <row r="789">
@@ -49225,10 +49225,10 @@
         <v>46297.6875</v>
       </c>
       <c r="L889" s="1" t="n">
-        <v>46298.25</v>
+        <v>46298.3125</v>
       </c>
       <c r="M889" s="1" t="n">
-        <v>46298.60416666666</v>
+        <v>46298.66666666666</v>
       </c>
     </row>
     <row r="890">
@@ -49277,13 +49277,13 @@
         </is>
       </c>
       <c r="K890" s="1" t="n">
-        <v>46300.1875</v>
+        <v>46300.25</v>
       </c>
       <c r="L890" s="1" t="n">
-        <v>46300.22916666666</v>
+        <v>46300.29166666666</v>
       </c>
       <c r="M890" s="1" t="n">
-        <v>46300.64583333334</v>
+        <v>46300.70833333334</v>
       </c>
     </row>
     <row r="891">
@@ -49332,13 +49332,13 @@
         </is>
       </c>
       <c r="K891" s="1" t="n">
-        <v>46300.8125</v>
+        <v>46300.875</v>
       </c>
       <c r="L891" s="1" t="n">
-        <v>46300.9375</v>
+        <v>46301</v>
       </c>
       <c r="M891" s="1" t="n">
-        <v>46301.9375</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="892">
@@ -49387,13 +49387,13 @@
         </is>
       </c>
       <c r="K892" s="1" t="n">
-        <v>46302.1875</v>
+        <v>46302.25</v>
       </c>
       <c r="L892" s="1" t="n">
-        <v>46302.22916666666</v>
+        <v>46302.29166666666</v>
       </c>
       <c r="M892" s="1" t="n">
-        <v>46302.64583333334</v>
+        <v>46302.70833333334</v>
       </c>
     </row>
     <row r="893">
@@ -49442,13 +49442,13 @@
         </is>
       </c>
       <c r="K893" s="1" t="n">
-        <v>46304.14583333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="L893" s="1" t="n">
-        <v>46304.3125</v>
+        <v>46304.375</v>
       </c>
       <c r="M893" s="1" t="n">
-        <v>46304.8125</v>
+        <v>46304.875</v>
       </c>
     </row>
     <row r="894">
@@ -49497,13 +49497,13 @@
         </is>
       </c>
       <c r="K894" s="1" t="n">
-        <v>46309.83333333334</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="L894" s="1" t="n">
-        <v>46309.89583333334</v>
+        <v>46309.95833333334</v>
       </c>
       <c r="M894" s="1" t="n">
-        <v>46310.14583333334</v>
+        <v>46310.20833333334</v>
       </c>
     </row>
     <row r="895">
@@ -49552,13 +49552,13 @@
         </is>
       </c>
       <c r="K895" s="1" t="n">
-        <v>46311.08333333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="L895" s="1" t="n">
-        <v>46311.14583333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="M895" s="1" t="n">
-        <v>46311.5625</v>
+        <v>46311.625</v>
       </c>
     </row>
     <row r="896">
@@ -49607,13 +49607,13 @@
         </is>
       </c>
       <c r="K896" s="1" t="n">
-        <v>46311.89583333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="L896" s="1" t="n">
-        <v>46311.9375</v>
+        <v>46312</v>
       </c>
       <c r="M896" s="1" t="n">
-        <v>46312.5625</v>
+        <v>46312.625</v>
       </c>
     </row>
     <row r="897">
@@ -49662,13 +49662,13 @@
         </is>
       </c>
       <c r="K897" s="1" t="n">
-        <v>46313.64583333334</v>
+        <v>46313.70833333334</v>
       </c>
       <c r="L897" s="1" t="n">
-        <v>46313.8125</v>
+        <v>46313.875</v>
       </c>
       <c r="M897" s="1" t="n">
-        <v>46314.8125</v>
+        <v>46314.875</v>
       </c>
     </row>
     <row r="898">
@@ -49717,13 +49717,13 @@
         </is>
       </c>
       <c r="K898" s="1" t="n">
-        <v>46319.02083333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="L898" s="1" t="n">
-        <v>46319.14583333334</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="M898" s="1" t="n">
-        <v>46319.64583333334</v>
+        <v>46319.70833333334</v>
       </c>
     </row>
     <row r="899">
@@ -49772,13 +49772,13 @@
         </is>
       </c>
       <c r="K899" s="1" t="n">
-        <v>46321.22916666666</v>
+        <v>46321.29166666666</v>
       </c>
       <c r="L899" s="1" t="n">
-        <v>46321.27083333334</v>
+        <v>46321.33333333334</v>
       </c>
       <c r="M899" s="1" t="n">
-        <v>46321.6875</v>
+        <v>46321.75</v>
       </c>
     </row>
     <row r="900">
@@ -49827,13 +49827,13 @@
         </is>
       </c>
       <c r="K900" s="1" t="n">
-        <v>46321.85416666666</v>
+        <v>46321.91666666666</v>
       </c>
       <c r="L900" s="1" t="n">
-        <v>46321.97916666666</v>
+        <v>46322.04166666666</v>
       </c>
       <c r="M900" s="1" t="n">
-        <v>46322.97916666666</v>
+        <v>46323.04166666666</v>
       </c>
     </row>
     <row r="901">
@@ -49882,13 +49882,13 @@
         </is>
       </c>
       <c r="K901" s="1" t="n">
-        <v>46323.22916666666</v>
+        <v>46323.29166666666</v>
       </c>
       <c r="L901" s="1" t="n">
-        <v>46323.27083333334</v>
+        <v>46323.33333333334</v>
       </c>
       <c r="M901" s="1" t="n">
-        <v>46323.6875</v>
+        <v>46323.75</v>
       </c>
     </row>
     <row r="902">
@@ -49937,13 +49937,13 @@
         </is>
       </c>
       <c r="K902" s="1" t="n">
-        <v>46325.1875</v>
+        <v>46325.25</v>
       </c>
       <c r="L902" s="1" t="n">
-        <v>46325.3125</v>
+        <v>46325.375</v>
       </c>
       <c r="M902" s="1" t="n">
-        <v>46325.8125</v>
+        <v>46325.875</v>
       </c>
     </row>
     <row r="903">
@@ -49992,13 +49992,13 @@
         </is>
       </c>
       <c r="K903" s="1" t="n">
-        <v>46332.375</v>
+        <v>46332.4375</v>
       </c>
       <c r="L903" s="1" t="n">
-        <v>46332.4375</v>
+        <v>46332.5</v>
       </c>
       <c r="M903" s="1" t="n">
-        <v>46332.6875</v>
+        <v>46332.75</v>
       </c>
     </row>
     <row r="904">
@@ -50047,13 +50047,13 @@
         </is>
       </c>
       <c r="K904" s="1" t="n">
-        <v>46333.625</v>
+        <v>46333.6875</v>
       </c>
       <c r="L904" s="1" t="n">
-        <v>46333.6875</v>
+        <v>46333.75</v>
       </c>
       <c r="M904" s="1" t="n">
-        <v>46334.10416666666</v>
+        <v>46334.16666666666</v>
       </c>
     </row>
     <row r="905">
@@ -50102,13 +50102,13 @@
         </is>
       </c>
       <c r="K905" s="1" t="n">
-        <v>46334.4375</v>
+        <v>46334.5</v>
       </c>
       <c r="L905" s="1" t="n">
-        <v>46334.47916666666</v>
+        <v>46334.54166666666</v>
       </c>
       <c r="M905" s="1" t="n">
-        <v>46335.10416666666</v>
+        <v>46335.16666666666</v>
       </c>
     </row>
     <row r="906">
@@ -50157,13 +50157,13 @@
         </is>
       </c>
       <c r="K906" s="1" t="n">
-        <v>46336.18472222222</v>
+        <v>46336.24722222222</v>
       </c>
       <c r="L906" s="1" t="n">
-        <v>46336.35138888889</v>
+        <v>46336.41388888889</v>
       </c>
       <c r="M906" s="1" t="n">
-        <v>46337.35138888889</v>
+        <v>46337.41388888889</v>
       </c>
     </row>
     <row r="907">
@@ -50212,13 +50212,13 @@
         </is>
       </c>
       <c r="K907" s="1" t="n">
-        <v>46341.55972222222</v>
+        <v>46341.62222222222</v>
       </c>
       <c r="L907" s="1" t="n">
-        <v>46341.68472222222</v>
+        <v>46341.74722222222</v>
       </c>
       <c r="M907" s="1" t="n">
-        <v>46342.18472222222</v>
+        <v>46342.24722222222</v>
       </c>
     </row>
     <row r="908">
@@ -50267,13 +50267,13 @@
         </is>
       </c>
       <c r="K908" s="1" t="n">
-        <v>46343.76805555556</v>
+        <v>46343.83055555556</v>
       </c>
       <c r="L908" s="1" t="n">
-        <v>46343.80972222222</v>
+        <v>46343.87222222222</v>
       </c>
       <c r="M908" s="1" t="n">
-        <v>46344.22638888889</v>
+        <v>46344.28888888889</v>
       </c>
     </row>
     <row r="909">
@@ -50322,13 +50322,13 @@
         </is>
       </c>
       <c r="K909" s="1" t="n">
-        <v>46344.39305555556</v>
+        <v>46344.45555555556</v>
       </c>
       <c r="L909" s="1" t="n">
-        <v>46344.51805555556</v>
+        <v>46344.58055555556</v>
       </c>
       <c r="M909" s="1" t="n">
-        <v>46345.51805555556</v>
+        <v>46345.58055555556</v>
       </c>
     </row>
     <row r="910">
@@ -50377,13 +50377,13 @@
         </is>
       </c>
       <c r="K910" s="1" t="n">
-        <v>46345.76805555556</v>
+        <v>46345.83055555556</v>
       </c>
       <c r="L910" s="1" t="n">
-        <v>46345.80972222222</v>
+        <v>46345.87222222222</v>
       </c>
       <c r="M910" s="1" t="n">
-        <v>46346.22638888889</v>
+        <v>46346.28888888889</v>
       </c>
     </row>
     <row r="911">
@@ -50432,13 +50432,13 @@
         </is>
       </c>
       <c r="K911" s="1" t="n">
-        <v>46347.72638888889</v>
+        <v>46347.78888888889</v>
       </c>
       <c r="L911" s="1" t="n">
-        <v>46347.85138888889</v>
+        <v>46347.91388888889</v>
       </c>
       <c r="M911" s="1" t="n">
-        <v>46348.35138888889</v>
+        <v>46348.41388888889</v>
       </c>
     </row>
     <row r="912">
@@ -50487,13 +50487,13 @@
         </is>
       </c>
       <c r="K912" s="1" t="n">
-        <v>46353.37222222222</v>
+        <v>46353.43472222222</v>
       </c>
       <c r="L912" s="1" t="n">
-        <v>46353.43472222222</v>
+        <v>46353.49722222222</v>
       </c>
       <c r="M912" s="1" t="n">
-        <v>46353.68472222222</v>
+        <v>46353.74722222222</v>
       </c>
     </row>
     <row r="913">
@@ -50542,13 +50542,13 @@
         </is>
       </c>
       <c r="K913" s="1" t="n">
-        <v>46354.62222222222</v>
+        <v>46354.68472222222</v>
       </c>
       <c r="L913" s="1" t="n">
-        <v>46354.68472222222</v>
+        <v>46354.74722222222</v>
       </c>
       <c r="M913" s="1" t="n">
-        <v>46355.10138888889</v>
+        <v>46355.16388888889</v>
       </c>
     </row>
     <row r="914">
@@ -50597,13 +50597,13 @@
         </is>
       </c>
       <c r="K914" s="1" t="n">
-        <v>46355.43472222222</v>
+        <v>46355.49722222222</v>
       </c>
       <c r="L914" s="1" t="n">
-        <v>46355.47638888889</v>
+        <v>46355.53888888889</v>
       </c>
       <c r="M914" s="1" t="n">
-        <v>46356.10138888889</v>
+        <v>46356.16388888889</v>
       </c>
     </row>
     <row r="915">
@@ -50652,13 +50652,13 @@
         </is>
       </c>
       <c r="K915" s="1" t="n">
-        <v>46357.18194444444</v>
+        <v>46357.24444444444</v>
       </c>
       <c r="L915" s="1" t="n">
-        <v>46357.34861111111</v>
+        <v>46357.41111111111</v>
       </c>
       <c r="M915" s="1" t="n">
-        <v>46358.34861111111</v>
+        <v>46358.41111111111</v>
       </c>
     </row>
     <row r="916">
@@ -50707,13 +50707,13 @@
         </is>
       </c>
       <c r="K916" s="1" t="n">
-        <v>46362.55694444444</v>
+        <v>46362.61944444444</v>
       </c>
       <c r="L916" s="1" t="n">
-        <v>46362.68194444444</v>
+        <v>46362.74444444444</v>
       </c>
       <c r="M916" s="1" t="n">
-        <v>46363.18194444444</v>
+        <v>46363.24444444444</v>
       </c>
     </row>
     <row r="917">
@@ -50762,13 +50762,13 @@
         </is>
       </c>
       <c r="K917" s="1" t="n">
-        <v>46364.76527777778</v>
+        <v>46364.82777777778</v>
       </c>
       <c r="L917" s="1" t="n">
-        <v>46364.80694444444</v>
+        <v>46364.86944444444</v>
       </c>
       <c r="M917" s="1" t="n">
-        <v>46365.22361111111</v>
+        <v>46365.28611111111</v>
       </c>
     </row>
     <row r="918">
@@ -50817,13 +50817,13 @@
         </is>
       </c>
       <c r="K918" s="1" t="n">
-        <v>46365.39027777778</v>
+        <v>46365.45277777778</v>
       </c>
       <c r="L918" s="1" t="n">
-        <v>46365.51527777778</v>
+        <v>46365.57777777778</v>
       </c>
       <c r="M918" s="1" t="n">
-        <v>46366.51527777778</v>
+        <v>46366.57777777778</v>
       </c>
     </row>
     <row r="919">
@@ -50872,13 +50872,13 @@
         </is>
       </c>
       <c r="K919" s="1" t="n">
-        <v>46366.76527777778</v>
+        <v>46366.82777777778</v>
       </c>
       <c r="L919" s="1" t="n">
-        <v>46366.80694444444</v>
+        <v>46366.86944444444</v>
       </c>
       <c r="M919" s="1" t="n">
-        <v>46367.22361111111</v>
+        <v>46367.28611111111</v>
       </c>
     </row>
     <row r="920">
@@ -50923,13 +50923,13 @@
       </c>
       <c r="J920" t="inlineStr"/>
       <c r="K920" s="1" t="n">
-        <v>46368.72361111111</v>
+        <v>46368.78611111111</v>
       </c>
       <c r="L920" s="1" t="n">
-        <v>46368.84861111111</v>
+        <v>46368.91111111111</v>
       </c>
       <c r="M920" s="1" t="n">
-        <v>46369.34861111111</v>
+        <v>46369.41111111111</v>
       </c>
     </row>
     <row r="921">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -11186,7 +11186,7 @@
         <v>46298.16666666666</v>
       </c>
       <c r="L196" s="1" t="n">
-        <v>46298.22916666666</v>
+        <v>46298.2375</v>
       </c>
       <c r="M196" s="1" t="n">
         <v>46299</v>
@@ -11238,13 +11238,13 @@
         </is>
       </c>
       <c r="K197" s="1" t="n">
-        <v>46299.22916666666</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>46299.27083333334</v>
+        <v>46301.25</v>
       </c>
       <c r="M197" s="1" t="n">
-        <v>46299.77083333334</v>
+        <v>46301.75</v>
       </c>
     </row>
     <row r="198">
@@ -11293,13 +11293,13 @@
         </is>
       </c>
       <c r="K198" s="1" t="n">
-        <v>46303.0625</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>46303.10416666666</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="M198" s="1" t="n">
-        <v>46303.77083333334</v>
+        <v>46305.75</v>
       </c>
     </row>
     <row r="199">
@@ -11348,13 +11348,13 @@
         </is>
       </c>
       <c r="K199" s="1" t="n">
-        <v>46304.85416666666</v>
+        <v>46306.83333333334</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>46304.89583333334</v>
+        <v>46306.875</v>
       </c>
       <c r="M199" s="1" t="n">
-        <v>46305.47916666666</v>
+        <v>46307.45833333334</v>
       </c>
     </row>
     <row r="200">
@@ -36544,10 +36544,10 @@
         <v>46298.875</v>
       </c>
       <c r="L658" s="1" t="n">
-        <v>46299.04166666666</v>
+        <v>46300.41666666666</v>
       </c>
       <c r="M658" s="1" t="n">
-        <v>46299.58333333334</v>
+        <v>46300.66666666666</v>
       </c>
     </row>
     <row r="659">
@@ -36596,13 +36596,13 @@
         </is>
       </c>
       <c r="K659" s="1" t="n">
-        <v>46301.375</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="L659" s="1" t="n">
-        <v>46301.41666666666</v>
+        <v>46302.5</v>
       </c>
       <c r="M659" s="1" t="n">
-        <v>46301.66666666666</v>
+        <v>46302.75</v>
       </c>
     </row>
     <row r="660">
@@ -36651,13 +36651,13 @@
         </is>
       </c>
       <c r="K660" s="1" t="n">
-        <v>46302.08333333334</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="L660" s="1" t="n">
-        <v>46302.20833333334</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="M660" s="1" t="n">
-        <v>46303.33333333334</v>
+        <v>46304.41666666666</v>
       </c>
     </row>
     <row r="661">
@@ -36706,13 +36706,13 @@
         </is>
       </c>
       <c r="K661" s="1" t="n">
-        <v>46303.66666666666</v>
+        <v>46304.75</v>
       </c>
       <c r="L661" s="1" t="n">
-        <v>46303.70833333334</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="M661" s="1" t="n">
-        <v>46304.04166666666</v>
+        <v>46305.125</v>
       </c>
     </row>
     <row r="662">
@@ -36761,13 +36761,13 @@
         </is>
       </c>
       <c r="K662" s="1" t="n">
-        <v>46307.91666666666</v>
+        <v>46309</v>
       </c>
       <c r="L662" s="1" t="n">
-        <v>46307.95833333334</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="M662" s="1" t="n">
-        <v>46308.375</v>
+        <v>46309.45833333334</v>
       </c>
     </row>
     <row r="663">
@@ -36816,13 +36816,13 @@
         </is>
       </c>
       <c r="K663" s="1" t="n">
-        <v>46308.625</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="L663" s="1" t="n">
-        <v>46308.625</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="M663" s="1" t="n">
-        <v>46309</v>
+        <v>46310.08333333334</v>
       </c>
     </row>
     <row r="664">
@@ -36871,13 +36871,13 @@
         </is>
       </c>
       <c r="K664" s="1" t="n">
-        <v>46310.33333333334</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="L664" s="1" t="n">
-        <v>46310.33333333334</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="M664" s="1" t="n">
-        <v>46310.58333333334</v>
+        <v>46311.66666666666</v>
       </c>
     </row>
     <row r="665">
@@ -36926,13 +36926,13 @@
         </is>
       </c>
       <c r="K665" s="1" t="n">
-        <v>46312.41666666666</v>
+        <v>46313.66666666666</v>
       </c>
       <c r="L665" s="1" t="n">
-        <v>46312.45833333334</v>
+        <v>46313.70833333334</v>
       </c>
       <c r="M665" s="1" t="n">
-        <v>46313.16666666666</v>
+        <v>46314.41666666666</v>
       </c>
     </row>
     <row r="666">
@@ -36981,13 +36981,13 @@
         </is>
       </c>
       <c r="K666" s="1" t="n">
-        <v>46313.375</v>
+        <v>46314.625</v>
       </c>
       <c r="L666" s="1" t="n">
-        <v>46313.41666666666</v>
+        <v>46314.66666666666</v>
       </c>
       <c r="M666" s="1" t="n">
-        <v>46313.75</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="667">
@@ -37036,13 +37036,13 @@
         </is>
       </c>
       <c r="K667" s="1" t="n">
-        <v>46317</v>
+        <v>46318.25</v>
       </c>
       <c r="L667" s="1" t="n">
-        <v>46317.04166666666</v>
+        <v>46318.29166666666</v>
       </c>
       <c r="M667" s="1" t="n">
-        <v>46317.41666666666</v>
+        <v>46318.66666666666</v>
       </c>
     </row>
     <row r="668">
@@ -37091,13 +37091,13 @@
         </is>
       </c>
       <c r="K668" s="1" t="n">
-        <v>46319.875</v>
+        <v>46321.125</v>
       </c>
       <c r="L668" s="1" t="n">
-        <v>46320.04166666666</v>
+        <v>46321.29166666666</v>
       </c>
       <c r="M668" s="1" t="n">
-        <v>46320.58333333334</v>
+        <v>46321.83333333334</v>
       </c>
     </row>
     <row r="669">
@@ -37146,13 +37146,13 @@
         </is>
       </c>
       <c r="K669" s="1" t="n">
-        <v>46322.375</v>
+        <v>46323.625</v>
       </c>
       <c r="L669" s="1" t="n">
-        <v>46322.41666666666</v>
+        <v>46323.66666666666</v>
       </c>
       <c r="M669" s="1" t="n">
-        <v>46322.66666666666</v>
+        <v>46323.91666666666</v>
       </c>
     </row>
     <row r="670">
@@ -37201,13 +37201,13 @@
         </is>
       </c>
       <c r="K670" s="1" t="n">
-        <v>46323.08333333334</v>
+        <v>46324.33333333334</v>
       </c>
       <c r="L670" s="1" t="n">
-        <v>46323.20833333334</v>
+        <v>46324.45833333334</v>
       </c>
       <c r="M670" s="1" t="n">
-        <v>46324.33333333334</v>
+        <v>46325.58333333334</v>
       </c>
     </row>
     <row r="671">
@@ -37256,13 +37256,13 @@
         </is>
       </c>
       <c r="K671" s="1" t="n">
-        <v>46324.66666666666</v>
+        <v>46325.91666666666</v>
       </c>
       <c r="L671" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46325.95833333334</v>
       </c>
       <c r="M671" s="1" t="n">
-        <v>46325.04166666666</v>
+        <v>46326.29166666666</v>
       </c>
     </row>
     <row r="672">
@@ -37311,13 +37311,13 @@
         </is>
       </c>
       <c r="K672" s="1" t="n">
-        <v>46328.91666666666</v>
+        <v>46330.16666666666</v>
       </c>
       <c r="L672" s="1" t="n">
-        <v>46328.95833333334</v>
+        <v>46330.20833333334</v>
       </c>
       <c r="M672" s="1" t="n">
-        <v>46329.375</v>
+        <v>46330.625</v>
       </c>
     </row>
     <row r="673">
@@ -37366,13 +37366,13 @@
         </is>
       </c>
       <c r="K673" s="1" t="n">
-        <v>46329.625</v>
+        <v>46330.875</v>
       </c>
       <c r="L673" s="1" t="n">
-        <v>46329.625</v>
+        <v>46330.875</v>
       </c>
       <c r="M673" s="1" t="n">
-        <v>46330</v>
+        <v>46331.25</v>
       </c>
     </row>
     <row r="674">
@@ -37421,13 +37421,13 @@
         </is>
       </c>
       <c r="K674" s="1" t="n">
-        <v>46331.25</v>
+        <v>46332.5</v>
       </c>
       <c r="L674" s="1" t="n">
-        <v>46331.25</v>
+        <v>46332.5</v>
       </c>
       <c r="M674" s="1" t="n">
-        <v>46331.5</v>
+        <v>46332.75</v>
       </c>
     </row>
     <row r="675">
@@ -37476,13 +37476,13 @@
         </is>
       </c>
       <c r="K675" s="1" t="n">
-        <v>46334.04097222222</v>
+        <v>46335.29097222222</v>
       </c>
       <c r="L675" s="1" t="n">
-        <v>46334.08263888889</v>
+        <v>46335.33263888889</v>
       </c>
       <c r="M675" s="1" t="n">
-        <v>46334.79097222222</v>
+        <v>46336.04097222222</v>
       </c>
     </row>
     <row r="676">
@@ -37531,13 +37531,13 @@
         </is>
       </c>
       <c r="K676" s="1" t="n">
-        <v>46334.99930555555</v>
+        <v>46336.24930555555</v>
       </c>
       <c r="L676" s="1" t="n">
-        <v>46335.04097222222</v>
+        <v>46336.29097222222</v>
       </c>
       <c r="M676" s="1" t="n">
-        <v>46335.37430555555</v>
+        <v>46336.62430555555</v>
       </c>
     </row>
     <row r="677">
@@ -37586,13 +37586,13 @@
         </is>
       </c>
       <c r="K677" s="1" t="n">
-        <v>46338.20763888889</v>
+        <v>46339.45763888889</v>
       </c>
       <c r="L677" s="1" t="n">
-        <v>46338.24930555555</v>
+        <v>46339.49930555555</v>
       </c>
       <c r="M677" s="1" t="n">
-        <v>46338.62430555555</v>
+        <v>46339.87430555555</v>
       </c>
     </row>
     <row r="678">
@@ -37641,13 +37641,13 @@
         </is>
       </c>
       <c r="K678" s="1" t="n">
-        <v>46341.08263888889</v>
+        <v>46342.33263888889</v>
       </c>
       <c r="L678" s="1" t="n">
-        <v>46341.24930555555</v>
+        <v>46342.49930555555</v>
       </c>
       <c r="M678" s="1" t="n">
-        <v>46341.79097222222</v>
+        <v>46343.04097222222</v>
       </c>
     </row>
     <row r="679">
@@ -37696,13 +37696,13 @@
         </is>
       </c>
       <c r="K679" s="1" t="n">
-        <v>46343.58263888889</v>
+        <v>46344.83263888889</v>
       </c>
       <c r="L679" s="1" t="n">
-        <v>46343.62430555555</v>
+        <v>46344.87430555555</v>
       </c>
       <c r="M679" s="1" t="n">
-        <v>46343.87430555555</v>
+        <v>46345.12430555555</v>
       </c>
     </row>
     <row r="680">
@@ -37751,13 +37751,13 @@
         </is>
       </c>
       <c r="K680" s="1" t="n">
-        <v>46344.29097222222</v>
+        <v>46345.54097222222</v>
       </c>
       <c r="L680" s="1" t="n">
-        <v>46344.41597222222</v>
+        <v>46345.66597222222</v>
       </c>
       <c r="M680" s="1" t="n">
-        <v>46345.54097222222</v>
+        <v>46346.79097222222</v>
       </c>
     </row>
     <row r="681">
@@ -37806,13 +37806,13 @@
         </is>
       </c>
       <c r="K681" s="1" t="n">
-        <v>46345.87430555555</v>
+        <v>46347.12430555555</v>
       </c>
       <c r="L681" s="1" t="n">
-        <v>46345.91597222222</v>
+        <v>46347.16597222222</v>
       </c>
       <c r="M681" s="1" t="n">
-        <v>46346.24930555555</v>
+        <v>46347.49930555555</v>
       </c>
     </row>
     <row r="682">
@@ -37861,13 +37861,13 @@
         </is>
       </c>
       <c r="K682" s="1" t="n">
-        <v>46350.12430555555</v>
+        <v>46351.37430555555</v>
       </c>
       <c r="L682" s="1" t="n">
-        <v>46350.16597222222</v>
+        <v>46351.41597222222</v>
       </c>
       <c r="M682" s="1" t="n">
-        <v>46350.58263888889</v>
+        <v>46351.83263888889</v>
       </c>
     </row>
     <row r="683">
@@ -37916,13 +37916,13 @@
         </is>
       </c>
       <c r="K683" s="1" t="n">
-        <v>46350.83263888889</v>
+        <v>46352.08263888889</v>
       </c>
       <c r="L683" s="1" t="n">
-        <v>46350.83263888889</v>
+        <v>46352.08263888889</v>
       </c>
       <c r="M683" s="1" t="n">
-        <v>46351.20763888889</v>
+        <v>46352.45763888889</v>
       </c>
     </row>
     <row r="684">
@@ -37971,13 +37971,13 @@
         </is>
       </c>
       <c r="K684" s="1" t="n">
-        <v>46352.45763888889</v>
+        <v>46353.70763888889</v>
       </c>
       <c r="L684" s="1" t="n">
-        <v>46352.45763888889</v>
+        <v>46353.70763888889</v>
       </c>
       <c r="M684" s="1" t="n">
-        <v>46352.70763888889</v>
+        <v>46353.95763888889</v>
       </c>
     </row>
     <row r="685">
@@ -38026,13 +38026,13 @@
         </is>
       </c>
       <c r="K685" s="1" t="n">
-        <v>46355.04097222222</v>
+        <v>46356.29097222222</v>
       </c>
       <c r="L685" s="1" t="n">
-        <v>46355.08263888889</v>
+        <v>46356.33263888889</v>
       </c>
       <c r="M685" s="1" t="n">
-        <v>46355.79097222222</v>
+        <v>46357.04097222222</v>
       </c>
     </row>
     <row r="686">
@@ -38081,13 +38081,13 @@
         </is>
       </c>
       <c r="K686" s="1" t="n">
-        <v>46355.99930555555</v>
+        <v>46357.24930555555</v>
       </c>
       <c r="L686" s="1" t="n">
-        <v>46356.04097222222</v>
+        <v>46357.29097222222</v>
       </c>
       <c r="M686" s="1" t="n">
-        <v>46356.37430555555</v>
+        <v>46357.62430555555</v>
       </c>
     </row>
     <row r="687">
@@ -38136,13 +38136,13 @@
         </is>
       </c>
       <c r="K687" s="1" t="n">
-        <v>46359.20763888889</v>
+        <v>46360.45763888889</v>
       </c>
       <c r="L687" s="1" t="n">
-        <v>46359.24930555555</v>
+        <v>46360.49930555555</v>
       </c>
       <c r="M687" s="1" t="n">
-        <v>46359.62430555555</v>
+        <v>46360.87430555555</v>
       </c>
     </row>
     <row r="688">
@@ -38191,13 +38191,13 @@
         </is>
       </c>
       <c r="K688" s="1" t="n">
-        <v>46362.08263888889</v>
+        <v>46363.33263888889</v>
       </c>
       <c r="L688" s="1" t="n">
-        <v>46362.24930555555</v>
+        <v>46363.49930555555</v>
       </c>
       <c r="M688" s="1" t="n">
-        <v>46362.79097222222</v>
+        <v>46364.04097222222</v>
       </c>
     </row>
     <row r="689">
@@ -38246,13 +38246,13 @@
         </is>
       </c>
       <c r="K689" s="1" t="n">
-        <v>46364.58263888889</v>
+        <v>46365.83263888889</v>
       </c>
       <c r="L689" s="1" t="n">
-        <v>46364.62430555555</v>
+        <v>46365.87430555555</v>
       </c>
       <c r="M689" s="1" t="n">
-        <v>46364.87430555555</v>
+        <v>46366.12430555555</v>
       </c>
     </row>
     <row r="690">
@@ -38301,13 +38301,13 @@
         </is>
       </c>
       <c r="K690" s="1" t="n">
-        <v>46365.29097222222</v>
+        <v>46366.54097222222</v>
       </c>
       <c r="L690" s="1" t="n">
-        <v>46365.41597222222</v>
+        <v>46366.66597222222</v>
       </c>
       <c r="M690" s="1" t="n">
-        <v>46366.54097222222</v>
+        <v>46367.79097222222</v>
       </c>
     </row>
     <row r="691">
@@ -38356,13 +38356,13 @@
         </is>
       </c>
       <c r="K691" s="1" t="n">
-        <v>46366.87430555555</v>
+        <v>46368.12430555555</v>
       </c>
       <c r="L691" s="1" t="n">
-        <v>46366.91597222222</v>
+        <v>46368.16597222222</v>
       </c>
       <c r="M691" s="1" t="n">
-        <v>46367.24930555555</v>
+        <v>46368.49930555555</v>
       </c>
     </row>
     <row r="692">
@@ -38411,13 +38411,13 @@
         </is>
       </c>
       <c r="K692" s="1" t="n">
-        <v>46371.12430555555</v>
+        <v>46372.37430555555</v>
       </c>
       <c r="L692" s="1" t="n">
-        <v>46371.16597222222</v>
+        <v>46372.41597222222</v>
       </c>
       <c r="M692" s="1" t="n">
-        <v>46371.58263888889</v>
+        <v>46372.83263888889</v>
       </c>
     </row>
     <row r="693">
@@ -38466,13 +38466,13 @@
         </is>
       </c>
       <c r="K693" s="1" t="n">
-        <v>46371.83263888889</v>
+        <v>46373.08263888889</v>
       </c>
       <c r="L693" s="1" t="n">
-        <v>46371.83263888889</v>
+        <v>46373.08263888889</v>
       </c>
       <c r="M693" s="1" t="n">
-        <v>46372.20763888889</v>
+        <v>46373.45763888889</v>
       </c>
     </row>
     <row r="694">
@@ -38521,13 +38521,13 @@
         </is>
       </c>
       <c r="K694" s="1" t="n">
-        <v>46373.45763888889</v>
+        <v>46374.70763888889</v>
       </c>
       <c r="L694" s="1" t="n">
-        <v>46373.45763888889</v>
+        <v>46374.70763888889</v>
       </c>
       <c r="M694" s="1" t="n">
-        <v>46373.70763888889</v>
+        <v>46374.95763888889</v>
       </c>
     </row>
     <row r="695">
@@ -38576,13 +38576,13 @@
         </is>
       </c>
       <c r="K695" s="1" t="n">
-        <v>46376.04097222222</v>
+        <v>46377.29097222222</v>
       </c>
       <c r="L695" s="1" t="n">
-        <v>46376.08263888889</v>
+        <v>46377.33263888889</v>
       </c>
       <c r="M695" s="1" t="n">
-        <v>46376.79097222222</v>
+        <v>46378.04097222222</v>
       </c>
     </row>
     <row r="696">
@@ -38631,13 +38631,13 @@
         </is>
       </c>
       <c r="K696" s="1" t="n">
-        <v>46376.99930555555</v>
+        <v>46378.24930555555</v>
       </c>
       <c r="L696" s="1" t="n">
-        <v>46377.04097222222</v>
+        <v>46378.29097222222</v>
       </c>
       <c r="M696" s="1" t="n">
-        <v>46377.37430555555</v>
+        <v>46378.62430555555</v>
       </c>
     </row>
     <row r="697">
@@ -38686,13 +38686,13 @@
         </is>
       </c>
       <c r="K697" s="1" t="n">
-        <v>46380.20763888889</v>
+        <v>46381.45763888889</v>
       </c>
       <c r="L697" s="1" t="n">
-        <v>46380.24930555555</v>
+        <v>46381.49930555555</v>
       </c>
       <c r="M697" s="1" t="n">
-        <v>46380.62430555555</v>
+        <v>46381.87430555555</v>
       </c>
     </row>
     <row r="698">
@@ -38741,13 +38741,13 @@
         </is>
       </c>
       <c r="K698" s="1" t="n">
-        <v>46383.08263888889</v>
+        <v>46384.33263888889</v>
       </c>
       <c r="L698" s="1" t="n">
-        <v>46383.24930555555</v>
+        <v>46384.49930555555</v>
       </c>
       <c r="M698" s="1" t="n">
-        <v>46383.79097222222</v>
+        <v>46385.04097222222</v>
       </c>
     </row>
     <row r="699">
@@ -38796,13 +38796,13 @@
         </is>
       </c>
       <c r="K699" s="1" t="n">
-        <v>46385.58263888889</v>
+        <v>46386.83263888889</v>
       </c>
       <c r="L699" s="1" t="n">
-        <v>46385.62430555555</v>
+        <v>46386.87430555555</v>
       </c>
       <c r="M699" s="1" t="n">
-        <v>46385.87430555555</v>
+        <v>46387.12430555555</v>
       </c>
     </row>
     <row r="700">
@@ -38851,13 +38851,13 @@
         </is>
       </c>
       <c r="K700" s="1" t="n">
-        <v>46386.29097222222</v>
+        <v>46387.54097222222</v>
       </c>
       <c r="L700" s="1" t="n">
-        <v>46386.41597222222</v>
+        <v>46387.66597222222</v>
       </c>
       <c r="M700" s="1" t="n">
-        <v>46387.54097222222</v>
+        <v>46388.79097222222</v>
       </c>
     </row>
     <row r="701">
@@ -38906,13 +38906,13 @@
         </is>
       </c>
       <c r="K701" s="1" t="n">
-        <v>46387.87430555555</v>
+        <v>46389.12430555555</v>
       </c>
       <c r="L701" s="1" t="n">
-        <v>46387.91597222222</v>
+        <v>46389.16597222222</v>
       </c>
       <c r="M701" s="1" t="n">
-        <v>46388.24930555555</v>
+        <v>46389.49930555555</v>
       </c>
     </row>
     <row r="702">
@@ -38961,13 +38961,13 @@
         </is>
       </c>
       <c r="K702" s="1" t="n">
-        <v>46392.12430555555</v>
+        <v>46393.37430555555</v>
       </c>
       <c r="L702" s="1" t="n">
-        <v>46392.16597222222</v>
+        <v>46393.41597222222</v>
       </c>
       <c r="M702" s="1" t="n">
-        <v>46392.58263888889</v>
+        <v>46393.83263888889</v>
       </c>
     </row>
     <row r="703">
@@ -39016,13 +39016,13 @@
         </is>
       </c>
       <c r="K703" s="1" t="n">
-        <v>46392.83263888889</v>
+        <v>46394.08263888889</v>
       </c>
       <c r="L703" s="1" t="n">
-        <v>46392.83263888889</v>
+        <v>46394.08263888889</v>
       </c>
       <c r="M703" s="1" t="n">
-        <v>46393.20763888889</v>
+        <v>46394.45763888889</v>
       </c>
     </row>
     <row r="704">
@@ -39067,13 +39067,13 @@
       </c>
       <c r="J704" t="inlineStr"/>
       <c r="K704" s="1" t="n">
-        <v>46394.45763888889</v>
+        <v>46395.70763888889</v>
       </c>
       <c r="L704" s="1" t="n">
-        <v>46394.45763888889</v>
+        <v>46395.70763888889</v>
       </c>
       <c r="M704" s="1" t="n">
-        <v>46394.70763888889</v>
+        <v>46395.95763888889</v>
       </c>
     </row>
     <row r="705">
@@ -57404,10 +57404,10 @@
         <v>46298.875</v>
       </c>
       <c r="L1038" s="1" t="n">
-        <v>46298.9375</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="M1038" s="1" t="n">
-        <v>46299.4375</v>
+        <v>46300.20833333334</v>
       </c>
     </row>
     <row r="1039">
@@ -57456,13 +57456,13 @@
         </is>
       </c>
       <c r="K1039" s="1" t="n">
-        <v>46299.5625</v>
+        <v>46300.33333333334</v>
       </c>
       <c r="L1039" s="1" t="n">
-        <v>46299.6875</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="M1039" s="1" t="n">
-        <v>46300.14583333334</v>
+        <v>46302.91666666666</v>
       </c>
     </row>
     <row r="1040">
@@ -57511,13 +57511,13 @@
         </is>
       </c>
       <c r="K1040" s="1" t="n">
-        <v>46303.25</v>
+        <v>46306</v>
       </c>
       <c r="L1040" s="1" t="n">
-        <v>46303.29166666666</v>
+        <v>46306.04166666666</v>
       </c>
       <c r="M1040" s="1" t="n">
-        <v>46303.95833333334</v>
+        <v>46306.70833333334</v>
       </c>
     </row>
     <row r="1041">
@@ -57566,13 +57566,13 @@
         </is>
       </c>
       <c r="K1041" s="1" t="n">
-        <v>46305.04166666666</v>
+        <v>46307.79166666666</v>
       </c>
       <c r="L1041" s="1" t="n">
-        <v>46305.08333333334</v>
+        <v>46307.83333333334</v>
       </c>
       <c r="M1041" s="1" t="n">
-        <v>46305.66666666666</v>
+        <v>46308.41666666666</v>
       </c>
     </row>
     <row r="1042">
@@ -57621,13 +57621,13 @@
         </is>
       </c>
       <c r="K1042" s="1" t="n">
-        <v>46305.875</v>
+        <v>46308.625</v>
       </c>
       <c r="L1042" s="1" t="n">
-        <v>46305.91666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="M1042" s="1" t="n">
-        <v>46306.25</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1043">
@@ -57676,13 +57676,13 @@
         </is>
       </c>
       <c r="K1043" s="1" t="n">
-        <v>46307.54166666666</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="L1043" s="1" t="n">
-        <v>46307.70833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="M1043" s="1" t="n">
-        <v>46308.20833333334</v>
+        <v>46310.95833333334</v>
       </c>
     </row>
     <row r="1044">
@@ -57731,13 +57731,13 @@
         </is>
       </c>
       <c r="K1044" s="1" t="n">
-        <v>46312.375</v>
+        <v>46315.125</v>
       </c>
       <c r="L1044" s="1" t="n">
-        <v>46312.54166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="M1044" s="1" t="n">
-        <v>46313.375</v>
+        <v>46316.125</v>
       </c>
     </row>
     <row r="1045">
@@ -57786,13 +57786,13 @@
         </is>
       </c>
       <c r="K1045" s="1" t="n">
-        <v>46315.08333333334</v>
+        <v>46317.83333333334</v>
       </c>
       <c r="L1045" s="1" t="n">
-        <v>46315.125</v>
+        <v>46317.875</v>
       </c>
       <c r="M1045" s="1" t="n">
-        <v>46315.95833333334</v>
+        <v>46318.70833333334</v>
       </c>
     </row>
     <row r="1046">
@@ -57841,13 +57841,13 @@
         </is>
       </c>
       <c r="K1046" s="1" t="n">
-        <v>46319.125</v>
+        <v>46321.875</v>
       </c>
       <c r="L1046" s="1" t="n">
-        <v>46319.16666666666</v>
+        <v>46321.91666666666</v>
       </c>
       <c r="M1046" s="1" t="n">
-        <v>46320.85416666666</v>
+        <v>46323.60416666666</v>
       </c>
     </row>
     <row r="1047">
@@ -57896,13 +57896,13 @@
         </is>
       </c>
       <c r="K1047" s="1" t="n">
-        <v>46322.97916666666</v>
+        <v>46325.72916666666</v>
       </c>
       <c r="L1047" s="1" t="n">
-        <v>46323.14583333334</v>
+        <v>46325.89583333334</v>
       </c>
       <c r="M1047" s="1" t="n">
-        <v>46323.97916666666</v>
+        <v>46326.72916666666</v>
       </c>
     </row>
     <row r="1048">
@@ -57951,13 +57951,13 @@
         </is>
       </c>
       <c r="K1048" s="1" t="n">
-        <v>46326.5</v>
+        <v>46329.25</v>
       </c>
       <c r="L1048" s="1" t="n">
-        <v>46326.5625</v>
+        <v>46329.3125</v>
       </c>
       <c r="M1048" s="1" t="n">
-        <v>46327.0625</v>
+        <v>46329.8125</v>
       </c>
     </row>
     <row r="1049">
@@ -58006,13 +58006,13 @@
         </is>
       </c>
       <c r="K1049" s="1" t="n">
-        <v>46327.29166666666</v>
+        <v>46330.04166666666</v>
       </c>
       <c r="L1049" s="1" t="n">
-        <v>46327.33333333334</v>
+        <v>46330.08333333334</v>
       </c>
       <c r="M1049" s="1" t="n">
-        <v>46327.83333333334</v>
+        <v>46330.58333333334</v>
       </c>
     </row>
     <row r="1050">
@@ -58061,13 +58061,13 @@
         </is>
       </c>
       <c r="K1050" s="1" t="n">
-        <v>46331.02083333334</v>
+        <v>46333.77083333334</v>
       </c>
       <c r="L1050" s="1" t="n">
-        <v>46331.0625</v>
+        <v>46333.8125</v>
       </c>
       <c r="M1050" s="1" t="n">
-        <v>46331.72916666666</v>
+        <v>46334.47916666666</v>
       </c>
     </row>
     <row r="1051">
@@ -58116,13 +58116,13 @@
         </is>
       </c>
       <c r="K1051" s="1" t="n">
-        <v>46332.8125</v>
+        <v>46335.5625</v>
       </c>
       <c r="L1051" s="1" t="n">
-        <v>46332.85416666666</v>
+        <v>46335.60416666666</v>
       </c>
       <c r="M1051" s="1" t="n">
-        <v>46333.4375</v>
+        <v>46336.1875</v>
       </c>
     </row>
     <row r="1052">
@@ -58171,13 +58171,13 @@
         </is>
       </c>
       <c r="K1052" s="1" t="n">
-        <v>46333.625</v>
+        <v>46336.375</v>
       </c>
       <c r="L1052" s="1" t="n">
-        <v>46333.6875</v>
+        <v>46336.4375</v>
       </c>
       <c r="M1052" s="1" t="n">
-        <v>46334.02083333334</v>
+        <v>46336.77083333334</v>
       </c>
     </row>
     <row r="1053">
@@ -58226,13 +58226,13 @@
         </is>
       </c>
       <c r="K1053" s="1" t="n">
-        <v>46335.3125</v>
+        <v>46338.0625</v>
       </c>
       <c r="L1053" s="1" t="n">
-        <v>46335.47916666666</v>
+        <v>46338.22916666666</v>
       </c>
       <c r="M1053" s="1" t="n">
-        <v>46335.97916666666</v>
+        <v>46338.72916666666</v>
       </c>
     </row>
     <row r="1054">
@@ -58281,13 +58281,13 @@
         </is>
       </c>
       <c r="K1054" s="1" t="n">
-        <v>46340.14583333334</v>
+        <v>46342.89583333334</v>
       </c>
       <c r="L1054" s="1" t="n">
-        <v>46340.3125</v>
+        <v>46343.0625</v>
       </c>
       <c r="M1054" s="1" t="n">
-        <v>46341.14583333334</v>
+        <v>46343.89583333334</v>
       </c>
     </row>
     <row r="1055">
@@ -58336,13 +58336,13 @@
         </is>
       </c>
       <c r="K1055" s="1" t="n">
-        <v>46342.8125</v>
+        <v>46345.5625</v>
       </c>
       <c r="L1055" s="1" t="n">
-        <v>46342.85416666666</v>
+        <v>46345.60416666666</v>
       </c>
       <c r="M1055" s="1" t="n">
-        <v>46343.6875</v>
+        <v>46346.4375</v>
       </c>
     </row>
     <row r="1056">
@@ -58391,13 +58391,13 @@
         </is>
       </c>
       <c r="K1056" s="1" t="n">
-        <v>46346.85416666666</v>
+        <v>46349.60416666666</v>
       </c>
       <c r="L1056" s="1" t="n">
-        <v>46346.9375</v>
+        <v>46349.6875</v>
       </c>
       <c r="M1056" s="1" t="n">
-        <v>46348.60416666666</v>
+        <v>46351.35416666666</v>
       </c>
     </row>
     <row r="1057">
@@ -58446,13 +58446,13 @@
         </is>
       </c>
       <c r="K1057" s="1" t="n">
-        <v>46351.0625</v>
+        <v>46353.8125</v>
       </c>
       <c r="L1057" s="1" t="n">
-        <v>46351.22916666666</v>
+        <v>46353.97916666666</v>
       </c>
       <c r="M1057" s="1" t="n">
-        <v>46352.0625</v>
+        <v>46354.8125</v>
       </c>
     </row>
     <row r="1058">
@@ -58501,13 +58501,13 @@
         </is>
       </c>
       <c r="K1058" s="1" t="n">
-        <v>46354.60416666666</v>
+        <v>46357.35416666666</v>
       </c>
       <c r="L1058" s="1" t="n">
-        <v>46354.66666666666</v>
+        <v>46357.41666666666</v>
       </c>
       <c r="M1058" s="1" t="n">
-        <v>46355.16666666666</v>
+        <v>46357.91666666666</v>
       </c>
     </row>
     <row r="1059">
@@ -58556,13 +58556,13 @@
         </is>
       </c>
       <c r="K1059" s="1" t="n">
-        <v>46355.39583333334</v>
+        <v>46358.14583333334</v>
       </c>
       <c r="L1059" s="1" t="n">
-        <v>46355.4375</v>
+        <v>46358.1875</v>
       </c>
       <c r="M1059" s="1" t="n">
-        <v>46355.9375</v>
+        <v>46358.6875</v>
       </c>
     </row>
     <row r="1060">
@@ -58611,13 +58611,13 @@
         </is>
       </c>
       <c r="K1060" s="1" t="n">
-        <v>46359.02083333334</v>
+        <v>46361.77083333334</v>
       </c>
       <c r="L1060" s="1" t="n">
-        <v>46359.0625</v>
+        <v>46361.8125</v>
       </c>
       <c r="M1060" s="1" t="n">
-        <v>46359.72916666666</v>
+        <v>46362.47916666666</v>
       </c>
     </row>
     <row r="1061">
@@ -58666,13 +58666,13 @@
         </is>
       </c>
       <c r="K1061" s="1" t="n">
-        <v>46360.8125</v>
+        <v>46363.5625</v>
       </c>
       <c r="L1061" s="1" t="n">
-        <v>46360.85416666666</v>
+        <v>46363.60416666666</v>
       </c>
       <c r="M1061" s="1" t="n">
-        <v>46361.4375</v>
+        <v>46364.1875</v>
       </c>
     </row>
     <row r="1062">
@@ -58721,13 +58721,13 @@
         </is>
       </c>
       <c r="K1062" s="1" t="n">
-        <v>46361.625</v>
+        <v>46364.375</v>
       </c>
       <c r="L1062" s="1" t="n">
-        <v>46361.6875</v>
+        <v>46364.4375</v>
       </c>
       <c r="M1062" s="1" t="n">
-        <v>46362.02083333334</v>
+        <v>46364.77083333334</v>
       </c>
     </row>
     <row r="1063">
@@ -58776,13 +58776,13 @@
         </is>
       </c>
       <c r="K1063" s="1" t="n">
-        <v>46363.3125</v>
+        <v>46366.0625</v>
       </c>
       <c r="L1063" s="1" t="n">
-        <v>46363.47916666666</v>
+        <v>46366.22916666666</v>
       </c>
       <c r="M1063" s="1" t="n">
-        <v>46363.97916666666</v>
+        <v>46366.72916666666</v>
       </c>
     </row>
     <row r="1064">
@@ -58831,13 +58831,13 @@
         </is>
       </c>
       <c r="K1064" s="1" t="n">
-        <v>46368.14583333334</v>
+        <v>46370.89583333334</v>
       </c>
       <c r="L1064" s="1" t="n">
-        <v>46368.3125</v>
+        <v>46371.0625</v>
       </c>
       <c r="M1064" s="1" t="n">
-        <v>46369.14583333334</v>
+        <v>46371.89583333334</v>
       </c>
     </row>
     <row r="1065">
@@ -58886,13 +58886,13 @@
         </is>
       </c>
       <c r="K1065" s="1" t="n">
-        <v>46370.8125</v>
+        <v>46373.5625</v>
       </c>
       <c r="L1065" s="1" t="n">
-        <v>46370.85416666666</v>
+        <v>46373.60416666666</v>
       </c>
       <c r="M1065" s="1" t="n">
-        <v>46371.6875</v>
+        <v>46374.4375</v>
       </c>
     </row>
     <row r="1066">
@@ -58941,13 +58941,13 @@
         </is>
       </c>
       <c r="K1066" s="1" t="n">
-        <v>46374.85416666666</v>
+        <v>46377.60416666666</v>
       </c>
       <c r="L1066" s="1" t="n">
-        <v>46374.9375</v>
+        <v>46377.6875</v>
       </c>
       <c r="M1066" s="1" t="n">
-        <v>46376.60416666666</v>
+        <v>46379.35416666666</v>
       </c>
     </row>
     <row r="1067">
@@ -58996,13 +58996,13 @@
         </is>
       </c>
       <c r="K1067" s="1" t="n">
-        <v>46379.0625</v>
+        <v>46381.8125</v>
       </c>
       <c r="L1067" s="1" t="n">
-        <v>46379.22916666666</v>
+        <v>46381.97916666666</v>
       </c>
       <c r="M1067" s="1" t="n">
-        <v>46380.0625</v>
+        <v>46382.8125</v>
       </c>
     </row>
     <row r="1068">
@@ -59051,13 +59051,13 @@
         </is>
       </c>
       <c r="K1068" s="1" t="n">
-        <v>46382.60416666666</v>
+        <v>46385.35416666666</v>
       </c>
       <c r="L1068" s="1" t="n">
-        <v>46382.66666666666</v>
+        <v>46385.41666666666</v>
       </c>
       <c r="M1068" s="1" t="n">
-        <v>46383.16666666666</v>
+        <v>46385.91666666666</v>
       </c>
     </row>
     <row r="1069">
@@ -59102,13 +59102,13 @@
       </c>
       <c r="J1069" t="inlineStr"/>
       <c r="K1069" s="1" t="n">
-        <v>46383.39583333334</v>
+        <v>46386.14583333334</v>
       </c>
       <c r="L1069" s="1" t="n">
-        <v>46383.4375</v>
+        <v>46386.1875</v>
       </c>
       <c r="M1069" s="1" t="n">
-        <v>46383.9375</v>
+        <v>46386.6875</v>
       </c>
     </row>
     <row r="1070">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -20245,10 +20245,10 @@
         <v>46281.77083333334</v>
       </c>
       <c r="L361" s="1" t="n">
-        <v>46283.95833333334</v>
+        <v>46283.66666666666</v>
       </c>
       <c r="M361" s="1" t="n">
-        <v>46284.625</v>
+        <v>46284.22916666666</v>
       </c>
     </row>
     <row r="362">
@@ -20297,13 +20297,13 @@
         </is>
       </c>
       <c r="K362" s="1" t="n">
-        <v>46288.54166666666</v>
+        <v>46288.14583333334</v>
       </c>
       <c r="L362" s="1" t="n">
-        <v>46289.20833333334</v>
+        <v>46289.5625</v>
       </c>
       <c r="M362" s="1" t="n">
-        <v>46290.04166666666</v>
+        <v>46290.17708333334</v>
       </c>
     </row>
     <row r="363">
@@ -20352,13 +20352,13 @@
         </is>
       </c>
       <c r="K363" s="1" t="n">
-        <v>46292.16666666666</v>
+        <v>46292.29166666666</v>
       </c>
       <c r="L363" s="1" t="n">
-        <v>46292.41666666666</v>
+        <v>46292.39166666667</v>
       </c>
       <c r="M363" s="1" t="n">
-        <v>46293.45833333334</v>
+        <v>46293.5375</v>
       </c>
     </row>
     <row r="364">
@@ -20407,13 +20407,13 @@
         </is>
       </c>
       <c r="K364" s="1" t="n">
-        <v>46296.39583333334</v>
+        <v>46296.5</v>
       </c>
       <c r="L364" s="1" t="n">
-        <v>46296.45833333334</v>
+        <v>46297.79166666666</v>
       </c>
       <c r="M364" s="1" t="n">
-        <v>46298.04166666666</v>
+        <v>46300.125</v>
       </c>
     </row>
     <row r="365">
@@ -20462,13 +20462,13 @@
         </is>
       </c>
       <c r="K365" s="1" t="n">
-        <v>46300.4375</v>
+        <v>46302.58333333334</v>
       </c>
       <c r="L365" s="1" t="n">
-        <v>46301.10416666666</v>
+        <v>46302.75</v>
       </c>
       <c r="M365" s="1" t="n">
-        <v>46301.9375</v>
+        <v>46303.58333333334</v>
       </c>
     </row>
     <row r="366">
@@ -20517,13 +20517,13 @@
         </is>
       </c>
       <c r="K366" s="1" t="n">
-        <v>46304.25</v>
+        <v>46305.875</v>
       </c>
       <c r="L366" s="1" t="n">
-        <v>46304.3125</v>
+        <v>46305.9375</v>
       </c>
       <c r="M366" s="1" t="n">
-        <v>46304.8125</v>
+        <v>46306.4375</v>
       </c>
     </row>
     <row r="367">
@@ -20572,13 +20572,13 @@
         </is>
       </c>
       <c r="K367" s="1" t="n">
-        <v>46304.91666666666</v>
+        <v>46306.54166666666</v>
       </c>
       <c r="L367" s="1" t="n">
-        <v>46305.04166666666</v>
+        <v>46307.66666666666</v>
       </c>
       <c r="M367" s="1" t="n">
-        <v>46305.5</v>
+        <v>46308.125</v>
       </c>
     </row>
     <row r="368">
@@ -20627,13 +20627,13 @@
         </is>
       </c>
       <c r="K368" s="1" t="n">
-        <v>46308.45833333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="L368" s="1" t="n">
-        <v>46308.5</v>
+        <v>46311.125</v>
       </c>
       <c r="M368" s="1" t="n">
-        <v>46309.16666666666</v>
+        <v>46311.79166666666</v>
       </c>
     </row>
     <row r="369">
@@ -20682,13 +20682,13 @@
         </is>
       </c>
       <c r="K369" s="1" t="n">
-        <v>46310.14583333334</v>
+        <v>46312.77083333334</v>
       </c>
       <c r="L369" s="1" t="n">
-        <v>46310.1875</v>
+        <v>46312.8125</v>
       </c>
       <c r="M369" s="1" t="n">
-        <v>46310.77083333334</v>
+        <v>46313.39583333334</v>
       </c>
     </row>
     <row r="370">
@@ -20737,13 +20737,13 @@
         </is>
       </c>
       <c r="K370" s="1" t="n">
-        <v>46310.875</v>
+        <v>46313.5</v>
       </c>
       <c r="L370" s="1" t="n">
-        <v>46310.9375</v>
+        <v>46313.5625</v>
       </c>
       <c r="M370" s="1" t="n">
-        <v>46311.27083333334</v>
+        <v>46313.89583333334</v>
       </c>
     </row>
     <row r="371">
@@ -20792,13 +20792,13 @@
         </is>
       </c>
       <c r="K371" s="1" t="n">
-        <v>46312.35416666666</v>
+        <v>46314.97916666666</v>
       </c>
       <c r="L371" s="1" t="n">
-        <v>46312.52083333334</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="M371" s="1" t="n">
-        <v>46313.02083333334</v>
+        <v>46315.64583333334</v>
       </c>
     </row>
     <row r="372">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="K372" s="1" t="n">
-        <v>46317.1875</v>
+        <v>46319.8125</v>
       </c>
       <c r="L372" s="1" t="n">
-        <v>46317.35416666666</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="M372" s="1" t="n">
-        <v>46318.1875</v>
+        <v>46320.8125</v>
       </c>
     </row>
     <row r="373">
@@ -20902,13 +20902,13 @@
         </is>
       </c>
       <c r="K373" s="1" t="n">
-        <v>46319.85416666666</v>
+        <v>46322.47916666666</v>
       </c>
       <c r="L373" s="1" t="n">
-        <v>46319.89583333334</v>
+        <v>46322.52083333334</v>
       </c>
       <c r="M373" s="1" t="n">
-        <v>46320.72916666666</v>
+        <v>46323.35416666666</v>
       </c>
     </row>
     <row r="374">
@@ -20957,13 +20957,13 @@
         </is>
       </c>
       <c r="K374" s="1" t="n">
-        <v>46323.89583333334</v>
+        <v>46326.52083333334</v>
       </c>
       <c r="L374" s="1" t="n">
-        <v>46323.97916666666</v>
+        <v>46326.60416666666</v>
       </c>
       <c r="M374" s="1" t="n">
-        <v>46325.64583333334</v>
+        <v>46328.27083333334</v>
       </c>
     </row>
     <row r="375">
@@ -21012,13 +21012,13 @@
         </is>
       </c>
       <c r="K375" s="1" t="n">
-        <v>46328.10416666666</v>
+        <v>46330.72916666666</v>
       </c>
       <c r="L375" s="1" t="n">
-        <v>46328.27083333334</v>
+        <v>46330.89583333334</v>
       </c>
       <c r="M375" s="1" t="n">
-        <v>46329.10416666666</v>
+        <v>46331.72916666666</v>
       </c>
     </row>
     <row r="376">
@@ -21067,13 +21067,13 @@
         </is>
       </c>
       <c r="K376" s="1" t="n">
-        <v>46331.64583333334</v>
+        <v>46334.27083333334</v>
       </c>
       <c r="L376" s="1" t="n">
-        <v>46331.70833333334</v>
+        <v>46334.33333333334</v>
       </c>
       <c r="M376" s="1" t="n">
-        <v>46332.20833333334</v>
+        <v>46334.83333333334</v>
       </c>
     </row>
     <row r="377">
@@ -21122,13 +21122,13 @@
         </is>
       </c>
       <c r="K377" s="1" t="n">
-        <v>46332.4375</v>
+        <v>46335.0625</v>
       </c>
       <c r="L377" s="1" t="n">
-        <v>46332.47916666666</v>
+        <v>46335.10416666666</v>
       </c>
       <c r="M377" s="1" t="n">
-        <v>46332.97916666666</v>
+        <v>46335.60416666666</v>
       </c>
     </row>
     <row r="378">
@@ -21177,13 +21177,13 @@
         </is>
       </c>
       <c r="K378" s="1" t="n">
-        <v>46336.27083333334</v>
+        <v>46338.89583333334</v>
       </c>
       <c r="L378" s="1" t="n">
-        <v>46336.3125</v>
+        <v>46338.9375</v>
       </c>
       <c r="M378" s="1" t="n">
-        <v>46336.97916666666</v>
+        <v>46339.60416666666</v>
       </c>
     </row>
     <row r="379">
@@ -21232,13 +21232,13 @@
         </is>
       </c>
       <c r="K379" s="1" t="n">
-        <v>46338.0625</v>
+        <v>46340.6875</v>
       </c>
       <c r="L379" s="1" t="n">
-        <v>46338.10416666666</v>
+        <v>46340.72916666666</v>
       </c>
       <c r="M379" s="1" t="n">
-        <v>46338.6875</v>
+        <v>46341.3125</v>
       </c>
     </row>
     <row r="380">
@@ -21287,13 +21287,13 @@
         </is>
       </c>
       <c r="K380" s="1" t="n">
-        <v>46338.875</v>
+        <v>46341.5</v>
       </c>
       <c r="L380" s="1" t="n">
-        <v>46338.9375</v>
+        <v>46341.5625</v>
       </c>
       <c r="M380" s="1" t="n">
-        <v>46339.27083333334</v>
+        <v>46341.89583333334</v>
       </c>
     </row>
     <row r="381">
@@ -21342,13 +21342,13 @@
         </is>
       </c>
       <c r="K381" s="1" t="n">
-        <v>46340.5625</v>
+        <v>46343.1875</v>
       </c>
       <c r="L381" s="1" t="n">
-        <v>46340.72916666666</v>
+        <v>46343.35416666666</v>
       </c>
       <c r="M381" s="1" t="n">
-        <v>46341.22916666666</v>
+        <v>46343.85416666666</v>
       </c>
     </row>
     <row r="382">
@@ -21397,13 +21397,13 @@
         </is>
       </c>
       <c r="K382" s="1" t="n">
-        <v>46345.39583333334</v>
+        <v>46348.02083333334</v>
       </c>
       <c r="L382" s="1" t="n">
-        <v>46345.5625</v>
+        <v>46348.1875</v>
       </c>
       <c r="M382" s="1" t="n">
-        <v>46346.39583333334</v>
+        <v>46349.02083333334</v>
       </c>
     </row>
     <row r="383">
@@ -21452,13 +21452,13 @@
         </is>
       </c>
       <c r="K383" s="1" t="n">
-        <v>46348.0625</v>
+        <v>46350.6875</v>
       </c>
       <c r="L383" s="1" t="n">
-        <v>46348.10416666666</v>
+        <v>46350.72916666666</v>
       </c>
       <c r="M383" s="1" t="n">
-        <v>46348.9375</v>
+        <v>46351.5625</v>
       </c>
     </row>
     <row r="384">
@@ -21507,13 +21507,13 @@
         </is>
       </c>
       <c r="K384" s="1" t="n">
-        <v>46352.10416666666</v>
+        <v>46354.72916666666</v>
       </c>
       <c r="L384" s="1" t="n">
-        <v>46352.1875</v>
+        <v>46354.8125</v>
       </c>
       <c r="M384" s="1" t="n">
-        <v>46353.85416666666</v>
+        <v>46356.47916666666</v>
       </c>
     </row>
     <row r="385">
@@ -21562,13 +21562,13 @@
         </is>
       </c>
       <c r="K385" s="1" t="n">
-        <v>46356.3125</v>
+        <v>46358.9375</v>
       </c>
       <c r="L385" s="1" t="n">
-        <v>46356.47916666666</v>
+        <v>46359.10416666666</v>
       </c>
       <c r="M385" s="1" t="n">
-        <v>46357.3125</v>
+        <v>46359.9375</v>
       </c>
     </row>
     <row r="386">
@@ -21617,13 +21617,13 @@
         </is>
       </c>
       <c r="K386" s="1" t="n">
-        <v>46359.85416666666</v>
+        <v>46362.47916666666</v>
       </c>
       <c r="L386" s="1" t="n">
-        <v>46359.91666666666</v>
+        <v>46362.54166666666</v>
       </c>
       <c r="M386" s="1" t="n">
-        <v>46360.41666666666</v>
+        <v>46363.04166666666</v>
       </c>
     </row>
     <row r="387">
@@ -21672,13 +21672,13 @@
         </is>
       </c>
       <c r="K387" s="1" t="n">
-        <v>46360.64583333334</v>
+        <v>46363.27083333334</v>
       </c>
       <c r="L387" s="1" t="n">
-        <v>46360.6875</v>
+        <v>46363.3125</v>
       </c>
       <c r="M387" s="1" t="n">
-        <v>46361.1875</v>
+        <v>46363.8125</v>
       </c>
     </row>
     <row r="388">
@@ -21727,13 +21727,13 @@
         </is>
       </c>
       <c r="K388" s="1" t="n">
-        <v>46366.1875</v>
+        <v>46368.8125</v>
       </c>
       <c r="L388" s="1" t="n">
-        <v>46366.22916666666</v>
+        <v>46368.85416666666</v>
       </c>
       <c r="M388" s="1" t="n">
-        <v>46366.89583333334</v>
+        <v>46369.52083333334</v>
       </c>
     </row>
     <row r="389">
@@ -21782,13 +21782,13 @@
         </is>
       </c>
       <c r="K389" s="1" t="n">
-        <v>46367.97916666666</v>
+        <v>46370.60416666666</v>
       </c>
       <c r="L389" s="1" t="n">
-        <v>46368.02083333334</v>
+        <v>46370.64583333334</v>
       </c>
       <c r="M389" s="1" t="n">
-        <v>46368.60416666666</v>
+        <v>46371.22916666666</v>
       </c>
     </row>
     <row r="390">
@@ -21837,13 +21837,13 @@
         </is>
       </c>
       <c r="K390" s="1" t="n">
-        <v>46368.79166666666</v>
+        <v>46371.41666666666</v>
       </c>
       <c r="L390" s="1" t="n">
-        <v>46368.85416666666</v>
+        <v>46371.47916666666</v>
       </c>
       <c r="M390" s="1" t="n">
-        <v>46369.1875</v>
+        <v>46371.8125</v>
       </c>
     </row>
     <row r="391">
@@ -21892,13 +21892,13 @@
         </is>
       </c>
       <c r="K391" s="1" t="n">
-        <v>46370.47916666666</v>
+        <v>46373.10416666666</v>
       </c>
       <c r="L391" s="1" t="n">
-        <v>46370.64583333334</v>
+        <v>46373.27083333334</v>
       </c>
       <c r="M391" s="1" t="n">
-        <v>46371.14583333334</v>
+        <v>46373.77083333334</v>
       </c>
     </row>
     <row r="392">
@@ -21947,13 +21947,13 @@
         </is>
       </c>
       <c r="K392" s="1" t="n">
-        <v>46375.3125</v>
+        <v>46377.9375</v>
       </c>
       <c r="L392" s="1" t="n">
-        <v>46375.47916666666</v>
+        <v>46378.10416666666</v>
       </c>
       <c r="M392" s="1" t="n">
-        <v>46376.3125</v>
+        <v>46378.9375</v>
       </c>
     </row>
     <row r="393">
@@ -22002,13 +22002,13 @@
         </is>
       </c>
       <c r="K393" s="1" t="n">
-        <v>46377.97916666666</v>
+        <v>46380.60416666666</v>
       </c>
       <c r="L393" s="1" t="n">
-        <v>46378.02083333334</v>
+        <v>46380.64583333334</v>
       </c>
       <c r="M393" s="1" t="n">
-        <v>46378.85416666666</v>
+        <v>46381.47916666666</v>
       </c>
     </row>
     <row r="394">
@@ -22057,13 +22057,13 @@
         </is>
       </c>
       <c r="K394" s="1" t="n">
-        <v>46382.02083333334</v>
+        <v>46384.64583333334</v>
       </c>
       <c r="L394" s="1" t="n">
-        <v>46382.10416666666</v>
+        <v>46384.72916666666</v>
       </c>
       <c r="M394" s="1" t="n">
-        <v>46383.77083333334</v>
+        <v>46386.39583333334</v>
       </c>
     </row>
     <row r="395">
@@ -22112,13 +22112,13 @@
         </is>
       </c>
       <c r="K395" s="1" t="n">
-        <v>46386.22916666666</v>
+        <v>46388.85416666666</v>
       </c>
       <c r="L395" s="1" t="n">
-        <v>46386.39583333334</v>
+        <v>46389.02083333334</v>
       </c>
       <c r="M395" s="1" t="n">
-        <v>46387.22916666666</v>
+        <v>46389.85416666666</v>
       </c>
     </row>
     <row r="396">
@@ -22167,13 +22167,13 @@
         </is>
       </c>
       <c r="K396" s="1" t="n">
-        <v>46389.77083333334</v>
+        <v>46392.39583333334</v>
       </c>
       <c r="L396" s="1" t="n">
-        <v>46389.83333333334</v>
+        <v>46392.45833333334</v>
       </c>
       <c r="M396" s="1" t="n">
-        <v>46390.33333333334</v>
+        <v>46392.95833333334</v>
       </c>
     </row>
     <row r="397">
@@ -22218,13 +22218,13 @@
       </c>
       <c r="J397" t="inlineStr"/>
       <c r="K397" s="1" t="n">
-        <v>46390.5625</v>
+        <v>46393.1875</v>
       </c>
       <c r="L397" s="1" t="n">
-        <v>46390.60416666666</v>
+        <v>46393.22916666666</v>
       </c>
       <c r="M397" s="1" t="n">
-        <v>46391.10416666666</v>
+        <v>46393.72916666666</v>
       </c>
     </row>
     <row r="398">
@@ -26173,7 +26173,7 @@
         <v>46291.25</v>
       </c>
       <c r="L469" s="1" t="n">
-        <v>46291.29166666666</v>
+        <v>46291.29583333333</v>
       </c>
       <c r="M469" s="1" t="n">
         <v>46292.29166666666</v>
@@ -26228,10 +26228,10 @@
         <v>46293.29166666666</v>
       </c>
       <c r="L470" s="1" t="n">
-        <v>46294.04166666666</v>
+        <v>46294.00694444445</v>
       </c>
       <c r="M470" s="1" t="n">
-        <v>46295</v>
+        <v>46295.20138888889</v>
       </c>
     </row>
     <row r="471">
@@ -26280,13 +26280,13 @@
         </is>
       </c>
       <c r="K471" s="1" t="n">
-        <v>46295.29166666666</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="L471" s="1" t="n">
-        <v>46295.33333333334</v>
+        <v>46295.35763888889</v>
       </c>
       <c r="M471" s="1" t="n">
-        <v>46295.95833333334</v>
+        <v>46295.92361111111</v>
       </c>
     </row>
     <row r="472">
@@ -26335,13 +26335,13 @@
         </is>
       </c>
       <c r="K472" s="1" t="n">
-        <v>46297.04166666666</v>
+        <v>46297</v>
       </c>
       <c r="L472" s="1" t="n">
-        <v>46297.25</v>
+        <v>46297.23611111111</v>
       </c>
       <c r="M472" s="1" t="n">
-        <v>46297.79166666666</v>
+        <v>46297.77083333334</v>
       </c>
     </row>
     <row r="473">
@@ -26390,13 +26390,13 @@
         </is>
       </c>
       <c r="K473" s="1" t="n">
-        <v>46301.70833333334</v>
+        <v>46301.91666666666</v>
       </c>
       <c r="L473" s="1" t="n">
-        <v>46302.375</v>
+        <v>46302.20833333334</v>
       </c>
       <c r="M473" s="1" t="n">
-        <v>46303.20833333334</v>
+        <v>46303.1875</v>
       </c>
     </row>
     <row r="474">
@@ -26445,13 +26445,13 @@
         </is>
       </c>
       <c r="K474" s="1" t="n">
-        <v>46304.75</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="L474" s="1" t="n">
-        <v>46304.79166666666</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="M474" s="1" t="n">
-        <v>46305.625</v>
+        <v>46305.60416666666</v>
       </c>
     </row>
     <row r="475">
@@ -26500,13 +26500,13 @@
         </is>
       </c>
       <c r="K475" s="1" t="n">
-        <v>46308.5625</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="L475" s="1" t="n">
-        <v>46309.625</v>
+        <v>46309.60416666666</v>
       </c>
       <c r="M475" s="1" t="n">
-        <v>46311.33333333334</v>
+        <v>46311.3125</v>
       </c>
     </row>
     <row r="476">
@@ -26555,13 +26555,13 @@
         </is>
       </c>
       <c r="K476" s="1" t="n">
-        <v>46313.79166666666</v>
+        <v>46313.77083333334</v>
       </c>
       <c r="L476" s="1" t="n">
-        <v>46313.95833333334</v>
+        <v>46314.4375</v>
       </c>
       <c r="M476" s="1" t="n">
-        <v>46314.79166666666</v>
+        <v>46315.27083333334</v>
       </c>
     </row>
     <row r="477">
@@ -26610,13 +26610,13 @@
         </is>
       </c>
       <c r="K477" s="1" t="n">
-        <v>46317.10416666666</v>
+        <v>46317.58333333334</v>
       </c>
       <c r="L477" s="1" t="n">
-        <v>46317.16666666666</v>
+        <v>46317.64583333334</v>
       </c>
       <c r="M477" s="1" t="n">
-        <v>46317.66666666666</v>
+        <v>46318.14583333334</v>
       </c>
     </row>
     <row r="478">
@@ -26665,13 +26665,13 @@
         </is>
       </c>
       <c r="K478" s="1" t="n">
-        <v>46317.89583333334</v>
+        <v>46318.25</v>
       </c>
       <c r="L478" s="1" t="n">
-        <v>46317.9375</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="M478" s="1" t="n">
-        <v>46318.4375</v>
+        <v>46319.83333333334</v>
       </c>
     </row>
     <row r="479">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="K479" s="1" t="n">
-        <v>46321.52083333334</v>
+        <v>46322.79166666666</v>
       </c>
       <c r="L479" s="1" t="n">
-        <v>46321.5625</v>
+        <v>46322.83333333334</v>
       </c>
       <c r="M479" s="1" t="n">
-        <v>46322.22916666666</v>
+        <v>46323.5</v>
       </c>
     </row>
     <row r="480">
@@ -26775,13 +26775,13 @@
         </is>
       </c>
       <c r="K480" s="1" t="n">
-        <v>46323.3125</v>
+        <v>46324.58333333334</v>
       </c>
       <c r="L480" s="1" t="n">
-        <v>46323.35416666666</v>
+        <v>46324.625</v>
       </c>
       <c r="M480" s="1" t="n">
-        <v>46323.9375</v>
+        <v>46325.20833333334</v>
       </c>
     </row>
     <row r="481">
@@ -26830,13 +26830,13 @@
         </is>
       </c>
       <c r="K481" s="1" t="n">
-        <v>46324.125</v>
+        <v>46325.39583333334</v>
       </c>
       <c r="L481" s="1" t="n">
-        <v>46324.1875</v>
+        <v>46325.45833333334</v>
       </c>
       <c r="M481" s="1" t="n">
-        <v>46324.52083333334</v>
+        <v>46325.79166666666</v>
       </c>
     </row>
     <row r="482">
@@ -26885,13 +26885,13 @@
         </is>
       </c>
       <c r="K482" s="1" t="n">
-        <v>46325.8125</v>
+        <v>46327.08333333334</v>
       </c>
       <c r="L482" s="1" t="n">
-        <v>46325.97916666666</v>
+        <v>46327.25</v>
       </c>
       <c r="M482" s="1" t="n">
-        <v>46326.47916666666</v>
+        <v>46327.75</v>
       </c>
     </row>
     <row r="483">
@@ -26940,13 +26940,13 @@
         </is>
       </c>
       <c r="K483" s="1" t="n">
-        <v>46330.64583333334</v>
+        <v>46331.91666666666</v>
       </c>
       <c r="L483" s="1" t="n">
-        <v>46330.8125</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="M483" s="1" t="n">
-        <v>46331.64583333334</v>
+        <v>46332.91666666666</v>
       </c>
     </row>
     <row r="484">
@@ -26995,13 +26995,13 @@
         </is>
       </c>
       <c r="K484" s="1" t="n">
-        <v>46333.3125</v>
+        <v>46334.58333333334</v>
       </c>
       <c r="L484" s="1" t="n">
-        <v>46333.35416666666</v>
+        <v>46334.625</v>
       </c>
       <c r="M484" s="1" t="n">
-        <v>46334.1875</v>
+        <v>46335.45833333334</v>
       </c>
     </row>
     <row r="485">
@@ -27050,13 +27050,13 @@
         </is>
       </c>
       <c r="K485" s="1" t="n">
-        <v>46337.35416666666</v>
+        <v>46338.625</v>
       </c>
       <c r="L485" s="1" t="n">
-        <v>46337.4375</v>
+        <v>46338.70833333334</v>
       </c>
       <c r="M485" s="1" t="n">
-        <v>46339.10416666666</v>
+        <v>46340.375</v>
       </c>
     </row>
     <row r="486">
@@ -27105,13 +27105,13 @@
         </is>
       </c>
       <c r="K486" s="1" t="n">
-        <v>46341.5625</v>
+        <v>46342.83333333334</v>
       </c>
       <c r="L486" s="1" t="n">
-        <v>46341.72916666666</v>
+        <v>46343</v>
       </c>
       <c r="M486" s="1" t="n">
-        <v>46342.5625</v>
+        <v>46343.83333333334</v>
       </c>
     </row>
     <row r="487">
@@ -27160,13 +27160,13 @@
         </is>
       </c>
       <c r="K487" s="1" t="n">
-        <v>46345.10416666666</v>
+        <v>46346.375</v>
       </c>
       <c r="L487" s="1" t="n">
-        <v>46345.16666666666</v>
+        <v>46346.4375</v>
       </c>
       <c r="M487" s="1" t="n">
-        <v>46345.66666666666</v>
+        <v>46346.9375</v>
       </c>
     </row>
     <row r="488">
@@ -27215,13 +27215,13 @@
         </is>
       </c>
       <c r="K488" s="1" t="n">
-        <v>46345.89583333334</v>
+        <v>46347.16666666666</v>
       </c>
       <c r="L488" s="1" t="n">
-        <v>46345.9375</v>
+        <v>46347.20833333334</v>
       </c>
       <c r="M488" s="1" t="n">
-        <v>46346.4375</v>
+        <v>46347.70833333334</v>
       </c>
     </row>
     <row r="489">
@@ -27270,13 +27270,13 @@
         </is>
       </c>
       <c r="K489" s="1" t="n">
-        <v>46349.52083333334</v>
+        <v>46350.79166666666</v>
       </c>
       <c r="L489" s="1" t="n">
-        <v>46349.5625</v>
+        <v>46350.83333333334</v>
       </c>
       <c r="M489" s="1" t="n">
-        <v>46350.22916666666</v>
+        <v>46351.5</v>
       </c>
     </row>
     <row r="490">
@@ -27325,13 +27325,13 @@
         </is>
       </c>
       <c r="K490" s="1" t="n">
-        <v>46351.3125</v>
+        <v>46352.58333333334</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>46351.35416666666</v>
+        <v>46352.625</v>
       </c>
       <c r="M490" s="1" t="n">
-        <v>46351.9375</v>
+        <v>46353.20833333334</v>
       </c>
     </row>
     <row r="491">
@@ -27380,13 +27380,13 @@
         </is>
       </c>
       <c r="K491" s="1" t="n">
-        <v>46352.125</v>
+        <v>46353.39583333334</v>
       </c>
       <c r="L491" s="1" t="n">
-        <v>46352.1875</v>
+        <v>46353.45833333334</v>
       </c>
       <c r="M491" s="1" t="n">
-        <v>46352.52083333334</v>
+        <v>46353.79166666666</v>
       </c>
     </row>
     <row r="492">
@@ -27435,13 +27435,13 @@
         </is>
       </c>
       <c r="K492" s="1" t="n">
-        <v>46353.8125</v>
+        <v>46355.08333333334</v>
       </c>
       <c r="L492" s="1" t="n">
-        <v>46353.97916666666</v>
+        <v>46355.25</v>
       </c>
       <c r="M492" s="1" t="n">
-        <v>46354.47916666666</v>
+        <v>46355.75</v>
       </c>
     </row>
     <row r="493">
@@ -27490,13 +27490,13 @@
         </is>
       </c>
       <c r="K493" s="1" t="n">
-        <v>46358.64583333334</v>
+        <v>46359.91666666666</v>
       </c>
       <c r="L493" s="1" t="n">
-        <v>46358.8125</v>
+        <v>46360.08333333334</v>
       </c>
       <c r="M493" s="1" t="n">
-        <v>46359.64583333334</v>
+        <v>46360.91666666666</v>
       </c>
     </row>
     <row r="494">
@@ -27545,13 +27545,13 @@
         </is>
       </c>
       <c r="K494" s="1" t="n">
-        <v>46361.3125</v>
+        <v>46362.58333333334</v>
       </c>
       <c r="L494" s="1" t="n">
-        <v>46361.35416666666</v>
+        <v>46362.625</v>
       </c>
       <c r="M494" s="1" t="n">
-        <v>46362.1875</v>
+        <v>46363.45833333334</v>
       </c>
     </row>
     <row r="495">
@@ -27600,13 +27600,13 @@
         </is>
       </c>
       <c r="K495" s="1" t="n">
-        <v>46365.35416666666</v>
+        <v>46366.625</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>46365.4375</v>
+        <v>46366.70833333334</v>
       </c>
       <c r="M495" s="1" t="n">
-        <v>46367.10416666666</v>
+        <v>46368.375</v>
       </c>
     </row>
     <row r="496">
@@ -27655,13 +27655,13 @@
         </is>
       </c>
       <c r="K496" s="1" t="n">
-        <v>46369.5625</v>
+        <v>46370.83333333334</v>
       </c>
       <c r="L496" s="1" t="n">
-        <v>46369.72916666666</v>
+        <v>46371</v>
       </c>
       <c r="M496" s="1" t="n">
-        <v>46370.5625</v>
+        <v>46371.83333333334</v>
       </c>
     </row>
     <row r="497">
@@ -27710,13 +27710,13 @@
         </is>
       </c>
       <c r="K497" s="1" t="n">
-        <v>46373.10416666666</v>
+        <v>46374.375</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>46373.16666666666</v>
+        <v>46374.4375</v>
       </c>
       <c r="M497" s="1" t="n">
-        <v>46373.66666666666</v>
+        <v>46374.9375</v>
       </c>
     </row>
     <row r="498">
@@ -27761,13 +27761,13 @@
       </c>
       <c r="J498" t="inlineStr"/>
       <c r="K498" s="1" t="n">
-        <v>46373.89583333334</v>
+        <v>46375.16666666666</v>
       </c>
       <c r="L498" s="1" t="n">
-        <v>46373.9375</v>
+        <v>46375.20833333334</v>
       </c>
       <c r="M498" s="1" t="n">
-        <v>46374.4375</v>
+        <v>46375.70833333334</v>
       </c>
     </row>
     <row r="499">
@@ -60257,13 +60257,13 @@
         </is>
       </c>
       <c r="K1090" s="1" t="n">
+        <v>46357.20833333334</v>
+      </c>
+      <c r="L1090" s="1" t="n">
         <v>46357.25</v>
       </c>
-      <c r="L1090" s="1" t="n">
-        <v>46357.29166666666</v>
-      </c>
       <c r="M1090" s="1" t="n">
-        <v>46357.95833333334</v>
+        <v>46357.91666666666</v>
       </c>
     </row>
     <row r="1091">
@@ -60312,13 +60312,13 @@
         </is>
       </c>
       <c r="K1091" s="1" t="n">
+        <v>46359</v>
+      </c>
+      <c r="L1091" s="1" t="n">
         <v>46359.04166666666</v>
       </c>
-      <c r="L1091" s="1" t="n">
-        <v>46359.08333333334</v>
-      </c>
       <c r="M1091" s="1" t="n">
-        <v>46359.66666666666</v>
+        <v>46359.625</v>
       </c>
     </row>
     <row r="1092">
@@ -60367,13 +60367,13 @@
         </is>
       </c>
       <c r="K1092" s="1" t="n">
-        <v>46359.85416666666</v>
+        <v>46359.8125</v>
       </c>
       <c r="L1092" s="1" t="n">
-        <v>46359.91666666666</v>
+        <v>46359.875</v>
       </c>
       <c r="M1092" s="1" t="n">
-        <v>46360.25</v>
+        <v>46360.20833333334</v>
       </c>
     </row>
     <row r="1093">
@@ -60422,13 +60422,13 @@
         </is>
       </c>
       <c r="K1093" s="1" t="n">
-        <v>46361.54166666666</v>
+        <v>46361.5</v>
       </c>
       <c r="L1093" s="1" t="n">
-        <v>46361.70833333334</v>
+        <v>46361.66666666666</v>
       </c>
       <c r="M1093" s="1" t="n">
-        <v>46362.20833333334</v>
+        <v>46362.16666666666</v>
       </c>
     </row>
     <row r="1094">
@@ -60477,13 +60477,13 @@
         </is>
       </c>
       <c r="K1094" s="1" t="n">
-        <v>46366.375</v>
+        <v>46366.33333333334</v>
       </c>
       <c r="L1094" s="1" t="n">
-        <v>46366.54166666666</v>
+        <v>46366.5</v>
       </c>
       <c r="M1094" s="1" t="n">
-        <v>46367.375</v>
+        <v>46367.33333333334</v>
       </c>
     </row>
     <row r="1095">
@@ -60532,13 +60532,13 @@
         </is>
       </c>
       <c r="K1095" s="1" t="n">
+        <v>46369</v>
+      </c>
+      <c r="L1095" s="1" t="n">
         <v>46369.04166666666</v>
       </c>
-      <c r="L1095" s="1" t="n">
-        <v>46369.08333333334</v>
-      </c>
       <c r="M1095" s="1" t="n">
-        <v>46369.91666666666</v>
+        <v>46369.875</v>
       </c>
     </row>
     <row r="1096">
@@ -60587,13 +60587,13 @@
         </is>
       </c>
       <c r="K1096" s="1" t="n">
-        <v>46373.08333333334</v>
+        <v>46373.04166666666</v>
       </c>
       <c r="L1096" s="1" t="n">
-        <v>46373.16666666666</v>
+        <v>46373.125</v>
       </c>
       <c r="M1096" s="1" t="n">
-        <v>46374.83333333334</v>
+        <v>46374.79166666666</v>
       </c>
     </row>
     <row r="1097">
@@ -60642,13 +60642,13 @@
         </is>
       </c>
       <c r="K1097" s="1" t="n">
-        <v>46377.29166666666</v>
+        <v>46377.25</v>
       </c>
       <c r="L1097" s="1" t="n">
-        <v>46377.45833333334</v>
+        <v>46377.41666666666</v>
       </c>
       <c r="M1097" s="1" t="n">
-        <v>46378.29166666666</v>
+        <v>46378.25</v>
       </c>
     </row>
     <row r="1098">
@@ -60697,13 +60697,13 @@
         </is>
       </c>
       <c r="K1098" s="1" t="n">
-        <v>46380.83333333334</v>
+        <v>46380.79166666666</v>
       </c>
       <c r="L1098" s="1" t="n">
-        <v>46380.89583333334</v>
+        <v>46380.85416666666</v>
       </c>
       <c r="M1098" s="1" t="n">
-        <v>46381.39583333334</v>
+        <v>46381.35416666666</v>
       </c>
     </row>
     <row r="1099">
@@ -60752,13 +60752,13 @@
         </is>
       </c>
       <c r="K1099" s="1" t="n">
+        <v>46381.58333333334</v>
+      </c>
+      <c r="L1099" s="1" t="n">
         <v>46381.625</v>
       </c>
-      <c r="L1099" s="1" t="n">
-        <v>46381.66666666666</v>
-      </c>
       <c r="M1099" s="1" t="n">
-        <v>46382.16666666666</v>
+        <v>46382.125</v>
       </c>
     </row>
     <row r="1100">
@@ -60807,13 +60807,13 @@
         </is>
       </c>
       <c r="K1100" s="1" t="n">
+        <v>46385.20833333334</v>
+      </c>
+      <c r="L1100" s="1" t="n">
         <v>46385.25</v>
       </c>
-      <c r="L1100" s="1" t="n">
-        <v>46385.29166666666</v>
-      </c>
       <c r="M1100" s="1" t="n">
-        <v>46385.95833333334</v>
+        <v>46385.91666666666</v>
       </c>
     </row>
     <row r="1101">
@@ -60862,13 +60862,13 @@
         </is>
       </c>
       <c r="K1101" s="1" t="n">
+        <v>46387</v>
+      </c>
+      <c r="L1101" s="1" t="n">
         <v>46387.04166666666</v>
       </c>
-      <c r="L1101" s="1" t="n">
-        <v>46387.08333333334</v>
-      </c>
       <c r="M1101" s="1" t="n">
-        <v>46387.66666666666</v>
+        <v>46387.625</v>
       </c>
     </row>
     <row r="1102">
@@ -60917,13 +60917,13 @@
         </is>
       </c>
       <c r="K1102" s="1" t="n">
-        <v>46387.85416666666</v>
+        <v>46387.8125</v>
       </c>
       <c r="L1102" s="1" t="n">
-        <v>46387.91666666666</v>
+        <v>46387.875</v>
       </c>
       <c r="M1102" s="1" t="n">
-        <v>46388.25</v>
+        <v>46388.20833333334</v>
       </c>
     </row>
     <row r="1103">
@@ -60972,13 +60972,13 @@
         </is>
       </c>
       <c r="K1103" s="1" t="n">
-        <v>46389.54166666666</v>
+        <v>46389.5</v>
       </c>
       <c r="L1103" s="1" t="n">
-        <v>46389.70833333334</v>
+        <v>46389.66666666666</v>
       </c>
       <c r="M1103" s="1" t="n">
-        <v>46390.20833333334</v>
+        <v>46390.16666666666</v>
       </c>
     </row>
     <row r="1104">
@@ -61027,13 +61027,13 @@
         </is>
       </c>
       <c r="K1104" s="1" t="n">
-        <v>46394.375</v>
+        <v>46394.33333333334</v>
       </c>
       <c r="L1104" s="1" t="n">
-        <v>46394.54166666666</v>
+        <v>46394.5</v>
       </c>
       <c r="M1104" s="1" t="n">
-        <v>46395.375</v>
+        <v>46395.33333333334</v>
       </c>
     </row>
     <row r="1105">
@@ -61082,13 +61082,13 @@
         </is>
       </c>
       <c r="K1105" s="1" t="n">
+        <v>46397</v>
+      </c>
+      <c r="L1105" s="1" t="n">
         <v>46397.04166666666</v>
       </c>
-      <c r="L1105" s="1" t="n">
-        <v>46397.08333333334</v>
-      </c>
       <c r="M1105" s="1" t="n">
-        <v>46397.91666666666</v>
+        <v>46397.875</v>
       </c>
     </row>
     <row r="1106">
@@ -61137,13 +61137,13 @@
         </is>
       </c>
       <c r="K1106" s="1" t="n">
-        <v>46401.08333333334</v>
+        <v>46401.04166666666</v>
       </c>
       <c r="L1106" s="1" t="n">
-        <v>46401.16666666666</v>
+        <v>46401.125</v>
       </c>
       <c r="M1106" s="1" t="n">
-        <v>46402.83333333334</v>
+        <v>46402.79166666666</v>
       </c>
     </row>
     <row r="1107">
@@ -61192,13 +61192,13 @@
         </is>
       </c>
       <c r="K1107" s="1" t="n">
-        <v>46405.29166666666</v>
+        <v>46405.25</v>
       </c>
       <c r="L1107" s="1" t="n">
-        <v>46405.45833333334</v>
+        <v>46405.41666666666</v>
       </c>
       <c r="M1107" s="1" t="n">
-        <v>46406.29166666666</v>
+        <v>46406.25</v>
       </c>
     </row>
     <row r="1108">
@@ -61247,13 +61247,13 @@
         </is>
       </c>
       <c r="K1108" s="1" t="n">
-        <v>46408.83333333334</v>
+        <v>46408.79166666666</v>
       </c>
       <c r="L1108" s="1" t="n">
-        <v>46408.89583333334</v>
+        <v>46408.85416666666</v>
       </c>
       <c r="M1108" s="1" t="n">
-        <v>46409.39583333334</v>
+        <v>46409.35416666666</v>
       </c>
     </row>
     <row r="1109">
@@ -61298,13 +61298,13 @@
       </c>
       <c r="J1109" t="inlineStr"/>
       <c r="K1109" s="1" t="n">
+        <v>46409.58333333334</v>
+      </c>
+      <c r="L1109" s="1" t="n">
         <v>46409.625</v>
       </c>
-      <c r="L1109" s="1" t="n">
-        <v>46409.66666666666</v>
-      </c>
       <c r="M1109" s="1" t="n">
-        <v>46410.16666666666</v>
+        <v>46410.125</v>
       </c>
     </row>
   </sheetData>

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -39290,10 +39290,10 @@
         <v>46300.125</v>
       </c>
       <c r="L708" s="1" t="n">
-        <v>46300.16666666666</v>
+        <v>46300.20833333334</v>
       </c>
       <c r="M708" s="1" t="n">
-        <v>46301.08333333334</v>
+        <v>46301.16666666666</v>
       </c>
     </row>
     <row r="709">
@@ -39342,13 +39342,13 @@
         </is>
       </c>
       <c r="K709" s="1" t="n">
-        <v>46306.5</v>
+        <v>46306.58333333334</v>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46306.66666666666</v>
+        <v>46306.75</v>
       </c>
       <c r="M709" s="1" t="n">
-        <v>46307.25</v>
+        <v>46307.33333333334</v>
       </c>
     </row>
     <row r="710">
@@ -39397,13 +39397,13 @@
         </is>
       </c>
       <c r="K710" s="1" t="n">
-        <v>46309.02083333334</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46309.0625</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="M710" s="1" t="n">
-        <v>46309.41666666666</v>
+        <v>46309.5</v>
       </c>
     </row>
     <row r="711">
@@ -39452,13 +39452,13 @@
         </is>
       </c>
       <c r="K711" s="1" t="n">
-        <v>46309.54166666666</v>
+        <v>46309.625</v>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46309.625</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="M711" s="1" t="n">
-        <v>46310.625</v>
+        <v>46310.70833333334</v>
       </c>
     </row>
     <row r="712">
@@ -39507,13 +39507,13 @@
         </is>
       </c>
       <c r="K712" s="1" t="n">
-        <v>46310.83333333334</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46310.875</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="M712" s="1" t="n">
-        <v>46311.375</v>
+        <v>46311.45833333334</v>
       </c>
     </row>
     <row r="713">
@@ -39562,13 +39562,13 @@
         </is>
       </c>
       <c r="K713" s="1" t="n">
-        <v>46313.1875</v>
+        <v>46313.27083333334</v>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46313.35416666666</v>
+        <v>46313.4375</v>
       </c>
       <c r="M713" s="1" t="n">
-        <v>46314.04166666666</v>
+        <v>46314.125</v>
       </c>
     </row>
     <row r="714">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -39293,7 +39293,7 @@
         <v>46300.20833333334</v>
       </c>
       <c r="M708" s="1" t="n">
-        <v>46301.16666666666</v>
+        <v>46301.29166666666</v>
       </c>
     </row>
     <row r="709">
@@ -39342,13 +39342,13 @@
         </is>
       </c>
       <c r="K709" s="1" t="n">
-        <v>46306.58333333334</v>
+        <v>46306.83333333334</v>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46306.75</v>
+        <v>46307</v>
       </c>
       <c r="M709" s="1" t="n">
-        <v>46307.33333333334</v>
+        <v>46307.58333333334</v>
       </c>
     </row>
     <row r="710">
@@ -39397,13 +39397,13 @@
         </is>
       </c>
       <c r="K710" s="1" t="n">
-        <v>46309.10416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46309.14583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="M710" s="1" t="n">
-        <v>46309.5</v>
+        <v>46309.75</v>
       </c>
     </row>
     <row r="711">
@@ -39452,13 +39452,13 @@
         </is>
       </c>
       <c r="K711" s="1" t="n">
-        <v>46309.625</v>
+        <v>46309.875</v>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46309.95833333334</v>
       </c>
       <c r="M711" s="1" t="n">
-        <v>46310.70833333334</v>
+        <v>46310.95833333334</v>
       </c>
     </row>
     <row r="712">
@@ -39507,13 +39507,13 @@
         </is>
       </c>
       <c r="K712" s="1" t="n">
-        <v>46310.91666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46310.95833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="M712" s="1" t="n">
-        <v>46311.45833333334</v>
+        <v>46311.70833333334</v>
       </c>
     </row>
     <row r="713">
@@ -39562,13 +39562,13 @@
         </is>
       </c>
       <c r="K713" s="1" t="n">
-        <v>46313.27083333334</v>
+        <v>46313.52083333334</v>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46313.4375</v>
+        <v>46313.6875</v>
       </c>
       <c r="M713" s="1" t="n">
-        <v>46314.125</v>
+        <v>46314.375</v>
       </c>
     </row>
     <row r="714">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -5973,10 +5973,10 @@
         <v>46298.29166666666</v>
       </c>
       <c r="L101" s="1" t="n">
-        <v>46299.54166666666</v>
+        <v>46299.74583333333</v>
       </c>
       <c r="M101" s="1" t="n">
-        <v>46300.20833333334</v>
+        <v>46300.375</v>
       </c>
     </row>
     <row r="102">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46301.58333333334</v>
+        <v>46301.66666666666</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>46301.625</v>
+        <v>46301.70833333334</v>
       </c>
       <c r="M102" s="1" t="n">
-        <v>46303.625</v>
+        <v>46303.54166666666</v>
       </c>
     </row>
     <row r="103">
@@ -6080,13 +6080,13 @@
         </is>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46303.91666666666</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>46303.95833333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="M103" s="1" t="n">
-        <v>46304.58333333334</v>
+        <v>46304.52083333334</v>
       </c>
     </row>
     <row r="104">
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46305.60416666666</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="L104" s="1" t="n">
-        <v>46305.8125</v>
+        <v>46305.75</v>
       </c>
       <c r="M104" s="1" t="n">
-        <v>46306.47916666666</v>
+        <v>46306.41666666666</v>
       </c>
     </row>
     <row r="105">
@@ -6190,13 +6190,13 @@
         </is>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46313.47916666666</v>
+        <v>46313.41666666666</v>
       </c>
       <c r="L105" s="1" t="n">
-        <v>46313.5625</v>
+        <v>46313.5</v>
       </c>
       <c r="M105" s="1" t="n">
-        <v>46314.39583333334</v>
+        <v>46314.33333333334</v>
       </c>
     </row>
     <row r="106">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46315.47916666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="L106" s="1" t="n">
-        <v>46315.5625</v>
+        <v>46315.5</v>
       </c>
       <c r="M106" s="1" t="n">
-        <v>46316.0625</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="107">
@@ -6300,13 +6300,13 @@
         </is>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46320.0625</v>
+        <v>46320</v>
       </c>
       <c r="L107" s="1" t="n">
-        <v>46320.10416666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="M107" s="1" t="n">
-        <v>46320.77083333334</v>
+        <v>46320.70833333334</v>
       </c>
     </row>
     <row r="108">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46327.1875</v>
+        <v>46327.125</v>
       </c>
       <c r="L108" s="1" t="n">
-        <v>46327.39583333334</v>
+        <v>46327.33333333334</v>
       </c>
       <c r="M108" s="1" t="n">
-        <v>46328.0625</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="109">
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46329.77083333334</v>
+        <v>46329.70833333334</v>
       </c>
       <c r="L109" s="1" t="n">
-        <v>46329.8125</v>
+        <v>46329.75</v>
       </c>
       <c r="M109" s="1" t="n">
-        <v>46330.8125</v>
+        <v>46330.75</v>
       </c>
     </row>
     <row r="110">
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46331.4375</v>
+        <v>46331.375</v>
       </c>
       <c r="L110" s="1" t="n">
-        <v>46331.47916666666</v>
+        <v>46331.41666666666</v>
       </c>
       <c r="M110" s="1" t="n">
-        <v>46332.10416666666</v>
+        <v>46332.04166666666</v>
       </c>
     </row>
     <row r="111">
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="K111" s="1" t="n">
-        <v>46333.60416666666</v>
+        <v>46333.54166666666</v>
       </c>
       <c r="L111" s="1" t="n">
-        <v>46333.8125</v>
+        <v>46333.75</v>
       </c>
       <c r="M111" s="1" t="n">
-        <v>46334.47916666666</v>
+        <v>46334.41666666666</v>
       </c>
     </row>
     <row r="112">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="K112" s="1" t="n">
-        <v>46341.47916666666</v>
+        <v>46341.41666666666</v>
       </c>
       <c r="L112" s="1" t="n">
-        <v>46341.5625</v>
+        <v>46341.5</v>
       </c>
       <c r="M112" s="1" t="n">
-        <v>46342.39583333334</v>
+        <v>46342.33333333334</v>
       </c>
     </row>
     <row r="113">
@@ -6630,13 +6630,13 @@
         </is>
       </c>
       <c r="K113" s="1" t="n">
-        <v>46343.47916666666</v>
+        <v>46343.41666666666</v>
       </c>
       <c r="L113" s="1" t="n">
-        <v>46343.5625</v>
+        <v>46343.5</v>
       </c>
       <c r="M113" s="1" t="n">
-        <v>46344.0625</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="114">
@@ -6685,13 +6685,13 @@
         </is>
       </c>
       <c r="K114" s="1" t="n">
-        <v>46348.0625</v>
+        <v>46348</v>
       </c>
       <c r="L114" s="1" t="n">
-        <v>46348.10416666666</v>
+        <v>46348.04166666666</v>
       </c>
       <c r="M114" s="1" t="n">
-        <v>46348.77083333334</v>
+        <v>46348.70833333334</v>
       </c>
     </row>
     <row r="115">
@@ -6740,13 +6740,13 @@
         </is>
       </c>
       <c r="K115" s="1" t="n">
-        <v>46355.1875</v>
+        <v>46355.125</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>46355.39583333334</v>
+        <v>46355.33333333334</v>
       </c>
       <c r="M115" s="1" t="n">
-        <v>46356.0625</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="116">
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46357.77083333334</v>
+        <v>46357.70833333334</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>46357.8125</v>
+        <v>46357.75</v>
       </c>
       <c r="M116" s="1" t="n">
-        <v>46358.8125</v>
+        <v>46358.75</v>
       </c>
     </row>
     <row r="117">
@@ -6850,13 +6850,13 @@
         </is>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46359.4375</v>
+        <v>46359.375</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>46359.47916666666</v>
+        <v>46359.41666666666</v>
       </c>
       <c r="M117" s="1" t="n">
-        <v>46360.10416666666</v>
+        <v>46360.04166666666</v>
       </c>
     </row>
     <row r="118">
@@ -6905,13 +6905,13 @@
         </is>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46361.60416666666</v>
+        <v>46361.54166666666</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>46361.8125</v>
+        <v>46361.75</v>
       </c>
       <c r="M118" s="1" t="n">
-        <v>46362.47916666666</v>
+        <v>46362.41666666666</v>
       </c>
     </row>
     <row r="119">
@@ -6960,13 +6960,13 @@
         </is>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46369.47916666666</v>
+        <v>46369.41666666666</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>46369.5625</v>
+        <v>46369.5</v>
       </c>
       <c r="M119" s="1" t="n">
-        <v>46370.39583333334</v>
+        <v>46370.33333333334</v>
       </c>
     </row>
     <row r="120">
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46371.47916666666</v>
+        <v>46371.41666666666</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>46371.5625</v>
+        <v>46371.5</v>
       </c>
       <c r="M120" s="1" t="n">
-        <v>46372.0625</v>
+        <v>46372</v>
       </c>
     </row>
     <row r="121">
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46376.0625</v>
+        <v>46376</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>46376.10416666666</v>
+        <v>46376.04166666666</v>
       </c>
       <c r="M121" s="1" t="n">
-        <v>46376.77083333334</v>
+        <v>46376.70833333334</v>
       </c>
     </row>
     <row r="122">
@@ -7125,13 +7125,13 @@
         </is>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46383.1875</v>
+        <v>46383.125</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>46383.39583333334</v>
+        <v>46383.33333333334</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>46384.0625</v>
+        <v>46384</v>
       </c>
     </row>
     <row r="123">
@@ -7180,13 +7180,13 @@
         </is>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46385.77083333334</v>
+        <v>46385.70833333334</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>46385.8125</v>
+        <v>46385.75</v>
       </c>
       <c r="M123" s="1" t="n">
-        <v>46386.8125</v>
+        <v>46386.75</v>
       </c>
     </row>
     <row r="124">
@@ -7235,13 +7235,13 @@
         </is>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46387.4375</v>
+        <v>46387.375</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>46387.47916666666</v>
+        <v>46387.41666666666</v>
       </c>
       <c r="M124" s="1" t="n">
-        <v>46388.10416666666</v>
+        <v>46388.04166666666</v>
       </c>
     </row>
     <row r="125">
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46389.60416666666</v>
+        <v>46389.54166666666</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>46389.8125</v>
+        <v>46389.75</v>
       </c>
       <c r="M125" s="1" t="n">
-        <v>46390.47916666666</v>
+        <v>46390.41666666666</v>
       </c>
     </row>
     <row r="126">
@@ -7345,13 +7345,13 @@
         </is>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46397.47916666666</v>
+        <v>46397.41666666666</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>46397.5625</v>
+        <v>46397.5</v>
       </c>
       <c r="M126" s="1" t="n">
-        <v>46398.39583333334</v>
+        <v>46398.33333333334</v>
       </c>
     </row>
     <row r="127">
@@ -7400,13 +7400,13 @@
         </is>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46399.47916666666</v>
+        <v>46399.41666666666</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>46399.5625</v>
+        <v>46399.5</v>
       </c>
       <c r="M127" s="1" t="n">
-        <v>46400.0625</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="128">
@@ -7455,13 +7455,13 @@
         </is>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46404.0625</v>
+        <v>46404</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>46404.10416666666</v>
+        <v>46404.04166666666</v>
       </c>
       <c r="M128" s="1" t="n">
-        <v>46404.77083333334</v>
+        <v>46404.70833333334</v>
       </c>
     </row>
     <row r="129">
@@ -7506,13 +7506,13 @@
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" s="1" t="n">
-        <v>46411.1875</v>
+        <v>46411.125</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>46411.39583333334</v>
+        <v>46411.33333333334</v>
       </c>
       <c r="M129" s="1" t="n">
-        <v>46412.0625</v>
+        <v>46412</v>
       </c>
     </row>
     <row r="130">
@@ -7616,19 +7616,19 @@
         </is>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46300.83333333334</v>
+        <v>46300.54166666666</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>46300.875</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="M131" s="1" t="n">
-        <v>46302.875</v>
+        <v>46305.79166666666</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KHS1</t>
+          <t>PVS2</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="n">
-        <v>2612</v>
+        <v>9002</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>9002S</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -7671,19 +7671,19 @@
         </is>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46304.625</v>
+        <v>46307.54166666666</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>46304.66666666666</v>
+        <v>46307.58333333334</v>
       </c>
       <c r="M132" s="1" t="n">
-        <v>46305.75</v>
+        <v>46308.29166666666</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PVS2</t>
+          <t>KHS1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
-        <v>9002</v>
+        <v>2612</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>9002S</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46304.875</v>
+        <v>46307.54166666666</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>46304.91666666666</v>
+        <v>46307.58333333334</v>
       </c>
       <c r="M133" s="1" t="n">
-        <v>46305.625</v>
+        <v>46308.66666666666</v>
       </c>
     </row>
     <row r="134">
@@ -7781,13 +7781,13 @@
         </is>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46305.875</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>46305.91666666666</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="M134" s="1" t="n">
-        <v>46306.16666666666</v>
+        <v>46309.08333333334</v>
       </c>
     </row>
     <row r="135">
@@ -7836,13 +7836,13 @@
         </is>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46306.58333333334</v>
+        <v>46309.5</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>46306.66666666666</v>
+        <v>46309.58333333334</v>
       </c>
       <c r="M135" s="1" t="n">
-        <v>46307</v>
+        <v>46309.91666666666</v>
       </c>
     </row>
     <row r="136">
@@ -7891,13 +7891,13 @@
         </is>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46312.08333333334</v>
+        <v>46315</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>46312.25</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="M136" s="1" t="n">
-        <v>46312.875</v>
+        <v>46315.79166666666</v>
       </c>
     </row>
     <row r="137">
@@ -7946,13 +7946,13 @@
         </is>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46314.66666666666</v>
+        <v>46317.58333333334</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>46314.70833333334</v>
+        <v>46317.625</v>
       </c>
       <c r="M137" s="1" t="n">
-        <v>46314.95833333334</v>
+        <v>46317.875</v>
       </c>
     </row>
     <row r="138">
@@ -8001,13 +8001,13 @@
         </is>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46315.25</v>
+        <v>46318.16666666666</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>46315.375</v>
+        <v>46318.29166666666</v>
       </c>
       <c r="M138" s="1" t="n">
-        <v>46316.875</v>
+        <v>46319.79166666666</v>
       </c>
     </row>
     <row r="139">
@@ -8056,13 +8056,13 @@
         </is>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46317.08333333334</v>
+        <v>46320</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>46317.125</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="M139" s="1" t="n">
-        <v>46317.54166666666</v>
+        <v>46320.45833333334</v>
       </c>
     </row>
     <row r="140">
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46319.125</v>
+        <v>46322.04166666666</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>46319.29166666666</v>
+        <v>46322.20833333334</v>
       </c>
       <c r="M140" s="1" t="n">
-        <v>46319.83333333334</v>
+        <v>46322.75</v>
       </c>
     </row>
     <row r="141">
@@ -8166,13 +8166,13 @@
         </is>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46327.16666666666</v>
+        <v>46327.875</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>46327.20833333334</v>
+        <v>46327.91666666666</v>
       </c>
       <c r="M141" s="1" t="n">
-        <v>46328.29166666666</v>
+        <v>46329</v>
       </c>
     </row>
     <row r="142">
@@ -8221,13 +8221,13 @@
         </is>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46328.41666666666</v>
+        <v>46329.125</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>46328.45833333334</v>
+        <v>46329.16666666666</v>
       </c>
       <c r="M142" s="1" t="n">
-        <v>46328.70833333334</v>
+        <v>46329.41666666666</v>
       </c>
     </row>
     <row r="143">
@@ -8276,13 +8276,13 @@
         </is>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46329.125</v>
+        <v>46329.875</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>46329.20833333334</v>
+        <v>46329.95833333334</v>
       </c>
       <c r="M143" s="1" t="n">
-        <v>46329.54166666666</v>
+        <v>46330.29166666666</v>
       </c>
     </row>
     <row r="144">
@@ -8331,13 +8331,13 @@
         </is>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46334.625</v>
+        <v>46335.33333333334</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>46334.79166666666</v>
+        <v>46335.5</v>
       </c>
       <c r="M144" s="1" t="n">
-        <v>46335.41666666666</v>
+        <v>46336.125</v>
       </c>
     </row>
     <row r="145">
@@ -8386,13 +8386,13 @@
         </is>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46337.20833333334</v>
+        <v>46338.08333333334</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>46337.25</v>
+        <v>46338.125</v>
       </c>
       <c r="M145" s="1" t="n">
-        <v>46337.5</v>
+        <v>46338.375</v>
       </c>
     </row>
     <row r="146">
@@ -8441,13 +8441,13 @@
         </is>
       </c>
       <c r="K146" s="1" t="n">
-        <v>46337.79166666666</v>
+        <v>46338.70833333334</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>46337.91666666666</v>
+        <v>46338.83333333334</v>
       </c>
       <c r="M146" s="1" t="n">
-        <v>46339.41666666666</v>
+        <v>46340.33333333334</v>
       </c>
     </row>
     <row r="147">
@@ -8496,13 +8496,13 @@
         </is>
       </c>
       <c r="K147" s="1" t="n">
-        <v>46339.625</v>
+        <v>46340.66666666666</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>46339.66666666666</v>
+        <v>46340.70833333334</v>
       </c>
       <c r="M147" s="1" t="n">
-        <v>46340.08333333334</v>
+        <v>46341.125</v>
       </c>
     </row>
     <row r="148">
@@ -8551,13 +8551,13 @@
         </is>
       </c>
       <c r="K148" s="1" t="n">
-        <v>46341.66666666666</v>
+        <v>46342.75</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>46341.83333333334</v>
+        <v>46342.91666666666</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>46342.375</v>
+        <v>46343.45833333334</v>
       </c>
     </row>
     <row r="149">
@@ -8606,13 +8606,13 @@
         </is>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46348.08333333334</v>
+        <v>46348.58333333334</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>46348.125</v>
+        <v>46348.625</v>
       </c>
       <c r="M149" s="1" t="n">
-        <v>46349.20833333334</v>
+        <v>46349.70833333334</v>
       </c>
     </row>
     <row r="150">
@@ -8661,13 +8661,13 @@
         </is>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46349.33333333334</v>
+        <v>46349.875</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>46349.375</v>
+        <v>46349.91666666666</v>
       </c>
       <c r="M150" s="1" t="n">
-        <v>46349.625</v>
+        <v>46350.16666666666</v>
       </c>
     </row>
     <row r="151">
@@ -8716,13 +8716,13 @@
         </is>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46350.04166666666</v>
+        <v>46350.625</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>46350.125</v>
+        <v>46350.70833333334</v>
       </c>
       <c r="M151" s="1" t="n">
-        <v>46350.45833333334</v>
+        <v>46351.04166666666</v>
       </c>
     </row>
     <row r="152">
@@ -8771,13 +8771,13 @@
         </is>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46355.54166666666</v>
+        <v>46356.08333333334</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>46355.70833333334</v>
+        <v>46356.25</v>
       </c>
       <c r="M152" s="1" t="n">
-        <v>46356.33333333334</v>
+        <v>46356.875</v>
       </c>
     </row>
     <row r="153">
@@ -8826,13 +8826,13 @@
         </is>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46358.125</v>
+        <v>46358.83333333334</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>46358.16666666666</v>
+        <v>46358.875</v>
       </c>
       <c r="M153" s="1" t="n">
-        <v>46358.41666666666</v>
+        <v>46359.125</v>
       </c>
     </row>
     <row r="154">
@@ -8881,13 +8881,13 @@
         </is>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46358.70833333334</v>
+        <v>46359.45833333334</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>46358.83333333334</v>
+        <v>46359.58333333334</v>
       </c>
       <c r="M154" s="1" t="n">
-        <v>46360.33333333334</v>
+        <v>46361.08333333334</v>
       </c>
     </row>
     <row r="155">
@@ -8936,13 +8936,13 @@
         </is>
       </c>
       <c r="K155" s="1" t="n">
-        <v>46360.54166666666</v>
+        <v>46361.41666666666</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>46360.58333333334</v>
+        <v>46361.45833333334</v>
       </c>
       <c r="M155" s="1" t="n">
-        <v>46361</v>
+        <v>46361.875</v>
       </c>
     </row>
     <row r="156">
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="K156" s="1" t="n">
-        <v>46362.58333333334</v>
+        <v>46363.5</v>
       </c>
       <c r="L156" s="1" t="n">
-        <v>46362.75</v>
+        <v>46363.66666666666</v>
       </c>
       <c r="M156" s="1" t="n">
-        <v>46363.29166666666</v>
+        <v>46364.20833333334</v>
       </c>
     </row>
     <row r="157">
@@ -9046,13 +9046,13 @@
         </is>
       </c>
       <c r="K157" s="1" t="n">
-        <v>46368.125</v>
+        <v>46369.83333333334</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>46368.16666666666</v>
+        <v>46369.875</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>46369.25</v>
+        <v>46370.95833333334</v>
       </c>
     </row>
     <row r="158">
@@ -9101,13 +9101,13 @@
         </is>
       </c>
       <c r="K158" s="1" t="n">
-        <v>46369.375</v>
+        <v>46371.08333333334</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>46369.41666666666</v>
+        <v>46371.125</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>46369.66666666666</v>
+        <v>46371.375</v>
       </c>
     </row>
     <row r="159">
@@ -9156,13 +9156,13 @@
         </is>
       </c>
       <c r="K159" s="1" t="n">
-        <v>46370.08333333334</v>
+        <v>46371.79166666666</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>46370.16666666666</v>
+        <v>46371.875</v>
       </c>
       <c r="M159" s="1" t="n">
-        <v>46370.5</v>
+        <v>46372.20833333334</v>
       </c>
     </row>
     <row r="160">
@@ -9211,13 +9211,13 @@
         </is>
       </c>
       <c r="K160" s="1" t="n">
-        <v>46375.58333333334</v>
+        <v>46377.29166666666</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>46375.75</v>
+        <v>46377.45833333334</v>
       </c>
       <c r="M160" s="1" t="n">
-        <v>46376.375</v>
+        <v>46378.08333333334</v>
       </c>
     </row>
     <row r="161">
@@ -9266,13 +9266,13 @@
         </is>
       </c>
       <c r="K161" s="1" t="n">
-        <v>46378.16666666666</v>
+        <v>46379.875</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>46378.20833333334</v>
+        <v>46379.91666666666</v>
       </c>
       <c r="M161" s="1" t="n">
-        <v>46378.45833333334</v>
+        <v>46380.16666666666</v>
       </c>
     </row>
     <row r="162">
@@ -9321,13 +9321,13 @@
         </is>
       </c>
       <c r="K162" s="1" t="n">
-        <v>46378.75</v>
+        <v>46380.45833333334</v>
       </c>
       <c r="L162" s="1" t="n">
-        <v>46378.875</v>
+        <v>46380.58333333334</v>
       </c>
       <c r="M162" s="1" t="n">
-        <v>46380.375</v>
+        <v>46382.08333333334</v>
       </c>
     </row>
     <row r="163">
@@ -9376,13 +9376,13 @@
         </is>
       </c>
       <c r="K163" s="1" t="n">
-        <v>46380.58333333334</v>
+        <v>46382.29166666666</v>
       </c>
       <c r="L163" s="1" t="n">
-        <v>46380.625</v>
+        <v>46382.33333333334</v>
       </c>
       <c r="M163" s="1" t="n">
-        <v>46381.04166666666</v>
+        <v>46382.75</v>
       </c>
     </row>
     <row r="164">
@@ -9427,13 +9427,13 @@
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" s="1" t="n">
-        <v>46382.625</v>
+        <v>46384.33333333334</v>
       </c>
       <c r="L164" s="1" t="n">
-        <v>46382.79166666666</v>
+        <v>46384.5</v>
       </c>
       <c r="M164" s="1" t="n">
-        <v>46383.33333333334</v>
+        <v>46385.04166666666</v>
       </c>
     </row>
     <row r="165">
@@ -28424,10 +28424,10 @@
         <v>46298.95833333334</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>46300.04166666666</v>
+        <v>46301.04166666666</v>
       </c>
       <c r="M510" s="1" t="n">
-        <v>46300.54166666666</v>
+        <v>46301.54166666666</v>
       </c>
     </row>
     <row r="511">
@@ -28476,13 +28476,13 @@
         </is>
       </c>
       <c r="K511" s="1" t="n">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="M511" s="1" t="n">
-        <v>46304.04166666666</v>
+        <v>46305.04166666666</v>
       </c>
     </row>
     <row r="512">
@@ -28531,13 +28531,13 @@
         </is>
       </c>
       <c r="K512" s="1" t="n">
-        <v>46316.29166666666</v>
+        <v>46317.29166666666</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>46317.375</v>
+        <v>46318.375</v>
       </c>
       <c r="M512" s="1" t="n">
-        <v>46318.04166666666</v>
+        <v>46319.04166666666</v>
       </c>
     </row>
     <row r="513">
@@ -28586,13 +28586,13 @@
         </is>
       </c>
       <c r="K513" s="1" t="n">
-        <v>46319.29166666666</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>46319.375</v>
+        <v>46320.375</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46319.875</v>
+        <v>46320.875</v>
       </c>
     </row>
     <row r="514">
@@ -28641,13 +28641,13 @@
         </is>
       </c>
       <c r="K514" s="1" t="n">
-        <v>46320.79166666666</v>
+        <v>46321.79166666666</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>46320.875</v>
+        <v>46321.875</v>
       </c>
       <c r="M514" s="1" t="n">
-        <v>46321.45833333334</v>
+        <v>46322.45833333334</v>
       </c>
     </row>
     <row r="515">
@@ -28696,13 +28696,13 @@
         </is>
       </c>
       <c r="K515" s="1" t="n">
-        <v>46330.33333333334</v>
+        <v>46331.33333333334</v>
       </c>
       <c r="L515" s="1" t="n">
-        <v>46331.375</v>
+        <v>46332.375</v>
       </c>
       <c r="M515" s="1" t="n">
-        <v>46331.95833333334</v>
+        <v>46332.95833333334</v>
       </c>
     </row>
     <row r="516">
@@ -28747,13 +28747,13 @@
       </c>
       <c r="J516" t="inlineStr"/>
       <c r="K516" s="1" t="n">
-        <v>46340.75</v>
+        <v>46341.75</v>
       </c>
       <c r="L516" s="1" t="n">
-        <v>46340.79166666666</v>
+        <v>46341.79166666666</v>
       </c>
       <c r="M516" s="1" t="n">
-        <v>46341.54166666666</v>
+        <v>46342.54166666666</v>
       </c>
     </row>
     <row r="517">
@@ -31767,10 +31767,10 @@
         <v>46300.5</v>
       </c>
       <c r="L571" s="1" t="n">
-        <v>46300.54166666666</v>
+        <v>46300.66666666666</v>
       </c>
       <c r="M571" s="1" t="n">
-        <v>46301.125</v>
+        <v>46301.58333333334</v>
       </c>
     </row>
     <row r="572">
@@ -31819,13 +31819,13 @@
         </is>
       </c>
       <c r="K572" s="1" t="n">
-        <v>46306.04166666666</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="L572" s="1" t="n">
-        <v>46306.20833333334</v>
+        <v>46307.125</v>
       </c>
       <c r="M572" s="1" t="n">
-        <v>46306.79166666666</v>
+        <v>46307.70833333334</v>
       </c>
     </row>
     <row r="573">
@@ -31874,13 +31874,13 @@
         </is>
       </c>
       <c r="K573" s="1" t="n">
-        <v>46308.4375</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="L573" s="1" t="n">
-        <v>46308.47916666666</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="M573" s="1" t="n">
-        <v>46308.83333333334</v>
+        <v>46309.75</v>
       </c>
     </row>
     <row r="574">
@@ -31929,13 +31929,13 @@
         </is>
       </c>
       <c r="K574" s="1" t="n">
-        <v>46308.95833333334</v>
+        <v>46309.875</v>
       </c>
       <c r="L574" s="1" t="n">
-        <v>46309.04166666666</v>
+        <v>46309.95833333334</v>
       </c>
       <c r="M574" s="1" t="n">
-        <v>46310.04166666666</v>
+        <v>46310.95833333334</v>
       </c>
     </row>
     <row r="575">
@@ -31984,13 +31984,13 @@
         </is>
       </c>
       <c r="K575" s="1" t="n">
-        <v>46310.25</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="L575" s="1" t="n">
-        <v>46310.29166666666</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="M575" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46311.70833333334</v>
       </c>
     </row>
     <row r="576">
@@ -32039,13 +32039,13 @@
         </is>
       </c>
       <c r="K576" s="1" t="n">
-        <v>46312.60416666666</v>
+        <v>46313.52083333334</v>
       </c>
       <c r="L576" s="1" t="n">
-        <v>46312.77083333334</v>
+        <v>46313.6875</v>
       </c>
       <c r="M576" s="1" t="n">
-        <v>46313.45833333334</v>
+        <v>46314.375</v>
       </c>
     </row>
     <row r="577">
@@ -45493,10 +45493,10 @@
         <v>46299.375</v>
       </c>
       <c r="L821" s="1" t="n">
-        <v>46299.4375</v>
+        <v>46299.44166666667</v>
       </c>
       <c r="M821" s="1" t="n">
-        <v>46300.16666666666</v>
+        <v>46300.30833333333</v>
       </c>
     </row>
     <row r="822">
@@ -45545,13 +45545,13 @@
         </is>
       </c>
       <c r="K822" s="1" t="n">
-        <v>46301.14583333334</v>
+        <v>46301.27083333334</v>
       </c>
       <c r="L822" s="1" t="n">
-        <v>46301.20833333334</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="M822" s="1" t="n">
-        <v>46301.58333333334</v>
+        <v>46301.70833333334</v>
       </c>
     </row>
     <row r="823">
@@ -45600,13 +45600,13 @@
         </is>
       </c>
       <c r="K823" s="1" t="n">
-        <v>46301.9375</v>
+        <v>46302</v>
       </c>
       <c r="L823" s="1" t="n">
-        <v>46301.97916666666</v>
+        <v>46302.04166666666</v>
       </c>
       <c r="M823" s="1" t="n">
-        <v>46302.60416666666</v>
+        <v>46303.08333333334</v>
       </c>
     </row>
     <row r="824">
@@ -45655,13 +45655,13 @@
         </is>
       </c>
       <c r="K824" s="1" t="n">
-        <v>46303.79166666666</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="L824" s="1" t="n">
-        <v>46307.39583333334</v>
+        <v>46307.875</v>
       </c>
       <c r="M824" s="1" t="n">
-        <v>46308.39583333334</v>
+        <v>46308.875</v>
       </c>
     </row>
     <row r="825">
@@ -45710,13 +45710,13 @@
         </is>
       </c>
       <c r="K825" s="1" t="n">
-        <v>46312.60416666666</v>
+        <v>46313.08333333334</v>
       </c>
       <c r="L825" s="1" t="n">
-        <v>46313.72916666666</v>
+        <v>46314.20833333334</v>
       </c>
       <c r="M825" s="1" t="n">
-        <v>46314.22916666666</v>
+        <v>46314.70833333334</v>
       </c>
     </row>
     <row r="826">
@@ -45765,13 +45765,13 @@
         </is>
       </c>
       <c r="K826" s="1" t="n">
-        <v>46315.8125</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="L826" s="1" t="n">
-        <v>46315.85416666666</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="M826" s="1" t="n">
-        <v>46316.27083333334</v>
+        <v>46316.75</v>
       </c>
     </row>
     <row r="827">
@@ -45820,13 +45820,13 @@
         </is>
       </c>
       <c r="K827" s="1" t="n">
-        <v>46316.4375</v>
+        <v>46316.91666666666</v>
       </c>
       <c r="L827" s="1" t="n">
-        <v>46316.5625</v>
+        <v>46317.04166666666</v>
       </c>
       <c r="M827" s="1" t="n">
-        <v>46317.5625</v>
+        <v>46318.04166666666</v>
       </c>
     </row>
     <row r="828">
@@ -45875,13 +45875,13 @@
         </is>
       </c>
       <c r="K828" s="1" t="n">
-        <v>46317.8125</v>
+        <v>46318.29166666666</v>
       </c>
       <c r="L828" s="1" t="n">
-        <v>46317.85416666666</v>
+        <v>46318.33333333334</v>
       </c>
       <c r="M828" s="1" t="n">
-        <v>46318.27083333334</v>
+        <v>46318.75</v>
       </c>
     </row>
     <row r="829">
@@ -45930,13 +45930,13 @@
         </is>
       </c>
       <c r="K829" s="1" t="n">
-        <v>46319.77083333334</v>
+        <v>46320.25</v>
       </c>
       <c r="L829" s="1" t="n">
-        <v>46320.89583333334</v>
+        <v>46321.375</v>
       </c>
       <c r="M829" s="1" t="n">
-        <v>46321.39583333334</v>
+        <v>46321.875</v>
       </c>
     </row>
     <row r="830">
@@ -45985,13 +45985,13 @@
         </is>
       </c>
       <c r="K830" s="1" t="n">
-        <v>46327.5</v>
+        <v>46327.97916666666</v>
       </c>
       <c r="L830" s="1" t="n">
-        <v>46327.5625</v>
+        <v>46328.04166666666</v>
       </c>
       <c r="M830" s="1" t="n">
-        <v>46327.8125</v>
+        <v>46328.29166666666</v>
       </c>
     </row>
     <row r="831">
@@ -46040,13 +46040,13 @@
         </is>
       </c>
       <c r="K831" s="1" t="n">
-        <v>46328.77083333334</v>
+        <v>46329.25</v>
       </c>
       <c r="L831" s="1" t="n">
-        <v>46328.83333333334</v>
+        <v>46329.3125</v>
       </c>
       <c r="M831" s="1" t="n">
-        <v>46329.25</v>
+        <v>46329.72916666666</v>
       </c>
     </row>
     <row r="832">
@@ -46095,13 +46095,13 @@
         </is>
       </c>
       <c r="K832" s="1" t="n">
-        <v>46329.60416666666</v>
+        <v>46330.08333333334</v>
       </c>
       <c r="L832" s="1" t="n">
-        <v>46329.64583333334</v>
+        <v>46330.125</v>
       </c>
       <c r="M832" s="1" t="n">
-        <v>46330.27083333334</v>
+        <v>46330.75</v>
       </c>
     </row>
     <row r="833">
@@ -46150,13 +46150,13 @@
         </is>
       </c>
       <c r="K833" s="1" t="n">
-        <v>46331.35416666666</v>
+        <v>46331.83333333334</v>
       </c>
       <c r="L833" s="1" t="n">
-        <v>46331.52083333334</v>
+        <v>46332</v>
       </c>
       <c r="M833" s="1" t="n">
-        <v>46332.52083333334</v>
+        <v>46333</v>
       </c>
     </row>
     <row r="834">
@@ -46205,13 +46205,13 @@
         </is>
       </c>
       <c r="K834" s="1" t="n">
-        <v>46336.72916666666</v>
+        <v>46337.20833333334</v>
       </c>
       <c r="L834" s="1" t="n">
-        <v>46336.85416666666</v>
+        <v>46337.33333333334</v>
       </c>
       <c r="M834" s="1" t="n">
-        <v>46337.35416666666</v>
+        <v>46337.83333333334</v>
       </c>
     </row>
     <row r="835">
@@ -46260,13 +46260,13 @@
         </is>
       </c>
       <c r="K835" s="1" t="n">
-        <v>46338.9375</v>
+        <v>46339.41666666666</v>
       </c>
       <c r="L835" s="1" t="n">
-        <v>46338.97916666666</v>
+        <v>46339.45833333334</v>
       </c>
       <c r="M835" s="1" t="n">
-        <v>46339.39583333334</v>
+        <v>46339.875</v>
       </c>
     </row>
     <row r="836">
@@ -46315,13 +46315,13 @@
         </is>
       </c>
       <c r="K836" s="1" t="n">
-        <v>46339.5625</v>
+        <v>46340.04166666666</v>
       </c>
       <c r="L836" s="1" t="n">
-        <v>46339.6875</v>
+        <v>46340.16666666666</v>
       </c>
       <c r="M836" s="1" t="n">
-        <v>46340.6875</v>
+        <v>46341.16666666666</v>
       </c>
     </row>
     <row r="837">
@@ -46370,13 +46370,13 @@
         </is>
       </c>
       <c r="K837" s="1" t="n">
-        <v>46340.9375</v>
+        <v>46341.41666666666</v>
       </c>
       <c r="L837" s="1" t="n">
-        <v>46340.97916666666</v>
+        <v>46341.45833333334</v>
       </c>
       <c r="M837" s="1" t="n">
-        <v>46341.39583333334</v>
+        <v>46341.875</v>
       </c>
     </row>
     <row r="838">
@@ -46425,13 +46425,13 @@
         </is>
       </c>
       <c r="K838" s="1" t="n">
-        <v>46342.89583333334</v>
+        <v>46343.375</v>
       </c>
       <c r="L838" s="1" t="n">
-        <v>46343.02083333334</v>
+        <v>46343.5</v>
       </c>
       <c r="M838" s="1" t="n">
-        <v>46343.52083333334</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="839">
@@ -46480,13 +46480,13 @@
         </is>
       </c>
       <c r="K839" s="1" t="n">
-        <v>46348.54166666666</v>
+        <v>46349.02083333334</v>
       </c>
       <c r="L839" s="1" t="n">
-        <v>46348.60416666666</v>
+        <v>46349.08333333334</v>
       </c>
       <c r="M839" s="1" t="n">
-        <v>46348.85416666666</v>
+        <v>46349.33333333334</v>
       </c>
     </row>
     <row r="840">
@@ -46535,13 +46535,13 @@
         </is>
       </c>
       <c r="K840" s="1" t="n">
-        <v>46349.8</v>
+        <v>46350.27916666667</v>
       </c>
       <c r="L840" s="1" t="n">
-        <v>46349.8625</v>
+        <v>46350.34166666667</v>
       </c>
       <c r="M840" s="1" t="n">
-        <v>46350.27916666667</v>
+        <v>46350.75833333333</v>
       </c>
     </row>
     <row r="841">
@@ -46590,13 +46590,13 @@
         </is>
       </c>
       <c r="K841" s="1" t="n">
-        <v>46350.62083333333</v>
+        <v>46351.1</v>
       </c>
       <c r="L841" s="1" t="n">
-        <v>46350.6625</v>
+        <v>46351.14166666667</v>
       </c>
       <c r="M841" s="1" t="n">
-        <v>46351.2875</v>
+        <v>46351.76666666667</v>
       </c>
     </row>
     <row r="842">
@@ -46645,13 +46645,13 @@
         </is>
       </c>
       <c r="K842" s="1" t="n">
-        <v>46352.37083333333</v>
+        <v>46352.85</v>
       </c>
       <c r="L842" s="1" t="n">
-        <v>46352.5375</v>
+        <v>46353.01666666667</v>
       </c>
       <c r="M842" s="1" t="n">
-        <v>46353.5375</v>
+        <v>46354.01666666667</v>
       </c>
     </row>
     <row r="843">
@@ -46700,13 +46700,13 @@
         </is>
       </c>
       <c r="K843" s="1" t="n">
-        <v>46357.74583333333</v>
+        <v>46358.225</v>
       </c>
       <c r="L843" s="1" t="n">
-        <v>46357.87083333333</v>
+        <v>46358.35</v>
       </c>
       <c r="M843" s="1" t="n">
-        <v>46358.37083333333</v>
+        <v>46358.85</v>
       </c>
     </row>
     <row r="844">
@@ -46755,13 +46755,13 @@
         </is>
       </c>
       <c r="K844" s="1" t="n">
-        <v>46359.95416666667</v>
+        <v>46360.43333333333</v>
       </c>
       <c r="L844" s="1" t="n">
-        <v>46359.99583333333</v>
+        <v>46360.475</v>
       </c>
       <c r="M844" s="1" t="n">
-        <v>46360.4125</v>
+        <v>46360.89166666667</v>
       </c>
     </row>
     <row r="845">
@@ -46810,13 +46810,13 @@
         </is>
       </c>
       <c r="K845" s="1" t="n">
-        <v>46360.57916666667</v>
+        <v>46361.05833333333</v>
       </c>
       <c r="L845" s="1" t="n">
-        <v>46360.70416666667</v>
+        <v>46361.18333333333</v>
       </c>
       <c r="M845" s="1" t="n">
-        <v>46361.70416666667</v>
+        <v>46362.18333333333</v>
       </c>
     </row>
     <row r="846">
@@ -46865,13 +46865,13 @@
         </is>
       </c>
       <c r="K846" s="1" t="n">
-        <v>46361.95416666667</v>
+        <v>46362.43333333333</v>
       </c>
       <c r="L846" s="1" t="n">
-        <v>46361.99583333333</v>
+        <v>46362.475</v>
       </c>
       <c r="M846" s="1" t="n">
-        <v>46362.4125</v>
+        <v>46362.89166666667</v>
       </c>
     </row>
     <row r="847">
@@ -46920,13 +46920,13 @@
         </is>
       </c>
       <c r="K847" s="1" t="n">
-        <v>46363.9125</v>
+        <v>46364.39166666667</v>
       </c>
       <c r="L847" s="1" t="n">
-        <v>46364.0375</v>
+        <v>46364.51666666667</v>
       </c>
       <c r="M847" s="1" t="n">
-        <v>46364.5375</v>
+        <v>46365.01666666667</v>
       </c>
     </row>
     <row r="848">
@@ -46975,13 +46975,13 @@
         </is>
       </c>
       <c r="K848" s="1" t="n">
-        <v>46369.55833333333</v>
+        <v>46370.0375</v>
       </c>
       <c r="L848" s="1" t="n">
-        <v>46369.62083333333</v>
+        <v>46370.1</v>
       </c>
       <c r="M848" s="1" t="n">
-        <v>46369.87083333333</v>
+        <v>46370.35</v>
       </c>
     </row>
     <row r="849">
@@ -47030,13 +47030,13 @@
         </is>
       </c>
       <c r="K849" s="1" t="n">
-        <v>46370.81666666667</v>
+        <v>46371.29583333333</v>
       </c>
       <c r="L849" s="1" t="n">
-        <v>46370.87916666667</v>
+        <v>46371.35833333333</v>
       </c>
       <c r="M849" s="1" t="n">
-        <v>46371.29583333333</v>
+        <v>46371.775</v>
       </c>
     </row>
     <row r="850">
@@ -47085,13 +47085,13 @@
         </is>
       </c>
       <c r="K850" s="1" t="n">
-        <v>46371.6375</v>
+        <v>46372.11666666667</v>
       </c>
       <c r="L850" s="1" t="n">
-        <v>46371.67916666667</v>
+        <v>46372.15833333333</v>
       </c>
       <c r="M850" s="1" t="n">
-        <v>46372.30416666667</v>
+        <v>46372.78333333333</v>
       </c>
     </row>
     <row r="851">
@@ -47140,13 +47140,13 @@
         </is>
       </c>
       <c r="K851" s="1" t="n">
-        <v>46373.3875</v>
+        <v>46373.86666666667</v>
       </c>
       <c r="L851" s="1" t="n">
-        <v>46373.55416666667</v>
+        <v>46374.03333333333</v>
       </c>
       <c r="M851" s="1" t="n">
-        <v>46374.55416666667</v>
+        <v>46375.03333333333</v>
       </c>
     </row>
     <row r="852">
@@ -47195,13 +47195,13 @@
         </is>
       </c>
       <c r="K852" s="1" t="n">
-        <v>46378.7625</v>
+        <v>46379.24166666667</v>
       </c>
       <c r="L852" s="1" t="n">
-        <v>46378.8875</v>
+        <v>46379.36666666667</v>
       </c>
       <c r="M852" s="1" t="n">
-        <v>46379.3875</v>
+        <v>46379.86666666667</v>
       </c>
     </row>
     <row r="853">
@@ -47250,13 +47250,13 @@
         </is>
       </c>
       <c r="K853" s="1" t="n">
-        <v>46380.97083333333</v>
+        <v>46381.45</v>
       </c>
       <c r="L853" s="1" t="n">
-        <v>46381.0125</v>
+        <v>46381.49166666667</v>
       </c>
       <c r="M853" s="1" t="n">
-        <v>46381.42916666667</v>
+        <v>46381.90833333333</v>
       </c>
     </row>
     <row r="854">
@@ -47305,13 +47305,13 @@
         </is>
       </c>
       <c r="K854" s="1" t="n">
-        <v>46381.59583333333</v>
+        <v>46382.075</v>
       </c>
       <c r="L854" s="1" t="n">
-        <v>46381.72083333333</v>
+        <v>46382.2</v>
       </c>
       <c r="M854" s="1" t="n">
-        <v>46382.72083333333</v>
+        <v>46383.2</v>
       </c>
     </row>
     <row r="855">
@@ -47360,13 +47360,13 @@
         </is>
       </c>
       <c r="K855" s="1" t="n">
-        <v>46382.97083333333</v>
+        <v>46383.45</v>
       </c>
       <c r="L855" s="1" t="n">
-        <v>46383.0125</v>
+        <v>46383.49166666667</v>
       </c>
       <c r="M855" s="1" t="n">
-        <v>46383.42916666667</v>
+        <v>46383.90833333333</v>
       </c>
     </row>
     <row r="856">
@@ -47411,13 +47411,13 @@
       </c>
       <c r="J856" t="inlineStr"/>
       <c r="K856" s="1" t="n">
-        <v>46384.92916666667</v>
+        <v>46385.40833333333</v>
       </c>
       <c r="L856" s="1" t="n">
-        <v>46385.05416666667</v>
+        <v>46385.53333333333</v>
       </c>
       <c r="M856" s="1" t="n">
-        <v>46385.55416666667</v>
+        <v>46386.03333333333</v>
       </c>
     </row>
     <row r="857">
@@ -49228,7 +49228,7 @@
         <v>46298.3125</v>
       </c>
       <c r="M889" s="1" t="n">
-        <v>46298.66666666666</v>
+        <v>46298.67083333333</v>
       </c>
     </row>
     <row r="890">
@@ -49277,13 +49277,13 @@
         </is>
       </c>
       <c r="K890" s="1" t="n">
-        <v>46300.25</v>
+        <v>46300.33333333334</v>
       </c>
       <c r="L890" s="1" t="n">
-        <v>46300.29166666666</v>
+        <v>46300.375</v>
       </c>
       <c r="M890" s="1" t="n">
-        <v>46300.70833333334</v>
+        <v>46300.79166666666</v>
       </c>
     </row>
     <row r="891">
@@ -49335,10 +49335,10 @@
         <v>46300.875</v>
       </c>
       <c r="L891" s="1" t="n">
-        <v>46301</v>
+        <v>46301.66666666666</v>
       </c>
       <c r="M891" s="1" t="n">
-        <v>46302</v>
+        <v>46303.54166666666</v>
       </c>
     </row>
     <row r="892">
@@ -49387,13 +49387,13 @@
         </is>
       </c>
       <c r="K892" s="1" t="n">
-        <v>46302.25</v>
+        <v>46303.75</v>
       </c>
       <c r="L892" s="1" t="n">
-        <v>46302.29166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="M892" s="1" t="n">
-        <v>46302.70833333334</v>
+        <v>46304.20833333334</v>
       </c>
     </row>
     <row r="893">
@@ -49442,13 +49442,13 @@
         </is>
       </c>
       <c r="K893" s="1" t="n">
-        <v>46304.20833333334</v>
+        <v>46305.70833333334</v>
       </c>
       <c r="L893" s="1" t="n">
-        <v>46304.375</v>
+        <v>46305.875</v>
       </c>
       <c r="M893" s="1" t="n">
-        <v>46304.875</v>
+        <v>46306.375</v>
       </c>
     </row>
     <row r="894">
@@ -49497,13 +49497,13 @@
         </is>
       </c>
       <c r="K894" s="1" t="n">
-        <v>46309.89583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="L894" s="1" t="n">
-        <v>46309.95833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="M894" s="1" t="n">
-        <v>46310.20833333334</v>
+        <v>46311.70833333334</v>
       </c>
     </row>
     <row r="895">
@@ -49552,13 +49552,13 @@
         </is>
       </c>
       <c r="K895" s="1" t="n">
-        <v>46311.14583333334</v>
+        <v>46312.64583333334</v>
       </c>
       <c r="L895" s="1" t="n">
-        <v>46311.20833333334</v>
+        <v>46312.70833333334</v>
       </c>
       <c r="M895" s="1" t="n">
-        <v>46311.625</v>
+        <v>46313.125</v>
       </c>
     </row>
     <row r="896">
@@ -49607,13 +49607,13 @@
         </is>
       </c>
       <c r="K896" s="1" t="n">
-        <v>46311.95833333334</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="L896" s="1" t="n">
-        <v>46312</v>
+        <v>46313.5</v>
       </c>
       <c r="M896" s="1" t="n">
-        <v>46312.625</v>
+        <v>46314.125</v>
       </c>
     </row>
     <row r="897">
@@ -49662,13 +49662,13 @@
         </is>
       </c>
       <c r="K897" s="1" t="n">
-        <v>46313.70833333334</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="L897" s="1" t="n">
-        <v>46313.875</v>
+        <v>46315.375</v>
       </c>
       <c r="M897" s="1" t="n">
-        <v>46314.875</v>
+        <v>46316.375</v>
       </c>
     </row>
     <row r="898">
@@ -49717,13 +49717,13 @@
         </is>
       </c>
       <c r="K898" s="1" t="n">
-        <v>46319.08333333334</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="L898" s="1" t="n">
-        <v>46319.20833333334</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="M898" s="1" t="n">
-        <v>46319.70833333334</v>
+        <v>46321.20833333334</v>
       </c>
     </row>
     <row r="899">
@@ -49772,13 +49772,13 @@
         </is>
       </c>
       <c r="K899" s="1" t="n">
-        <v>46321.29166666666</v>
+        <v>46322.79166666666</v>
       </c>
       <c r="L899" s="1" t="n">
-        <v>46321.33333333334</v>
+        <v>46322.83333333334</v>
       </c>
       <c r="M899" s="1" t="n">
-        <v>46321.75</v>
+        <v>46323.25</v>
       </c>
     </row>
     <row r="900">
@@ -49827,13 +49827,13 @@
         </is>
       </c>
       <c r="K900" s="1" t="n">
-        <v>46321.91666666666</v>
+        <v>46323.41666666666</v>
       </c>
       <c r="L900" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46323.54166666666</v>
       </c>
       <c r="M900" s="1" t="n">
-        <v>46323.04166666666</v>
+        <v>46324.54166666666</v>
       </c>
     </row>
     <row r="901">
@@ -49882,13 +49882,13 @@
         </is>
       </c>
       <c r="K901" s="1" t="n">
-        <v>46323.29166666666</v>
+        <v>46324.79166666666</v>
       </c>
       <c r="L901" s="1" t="n">
-        <v>46323.33333333334</v>
+        <v>46324.83333333334</v>
       </c>
       <c r="M901" s="1" t="n">
-        <v>46323.75</v>
+        <v>46325.25</v>
       </c>
     </row>
     <row r="902">
@@ -49937,13 +49937,13 @@
         </is>
       </c>
       <c r="K902" s="1" t="n">
-        <v>46325.25</v>
+        <v>46326.75</v>
       </c>
       <c r="L902" s="1" t="n">
-        <v>46325.375</v>
+        <v>46326.875</v>
       </c>
       <c r="M902" s="1" t="n">
-        <v>46325.875</v>
+        <v>46327.375</v>
       </c>
     </row>
     <row r="903">
@@ -49992,13 +49992,13 @@
         </is>
       </c>
       <c r="K903" s="1" t="n">
-        <v>46332.4375</v>
+        <v>46333.9375</v>
       </c>
       <c r="L903" s="1" t="n">
-        <v>46332.5</v>
+        <v>46334</v>
       </c>
       <c r="M903" s="1" t="n">
-        <v>46332.75</v>
+        <v>46334.25</v>
       </c>
     </row>
     <row r="904">
@@ -50047,13 +50047,13 @@
         </is>
       </c>
       <c r="K904" s="1" t="n">
-        <v>46333.6875</v>
+        <v>46335.1875</v>
       </c>
       <c r="L904" s="1" t="n">
-        <v>46333.75</v>
+        <v>46335.25</v>
       </c>
       <c r="M904" s="1" t="n">
-        <v>46334.16666666666</v>
+        <v>46335.66666666666</v>
       </c>
     </row>
     <row r="905">
@@ -50102,13 +50102,13 @@
         </is>
       </c>
       <c r="K905" s="1" t="n">
-        <v>46334.5</v>
+        <v>46336</v>
       </c>
       <c r="L905" s="1" t="n">
-        <v>46334.54166666666</v>
+        <v>46336.04166666666</v>
       </c>
       <c r="M905" s="1" t="n">
-        <v>46335.16666666666</v>
+        <v>46336.66666666666</v>
       </c>
     </row>
     <row r="906">
@@ -50157,13 +50157,13 @@
         </is>
       </c>
       <c r="K906" s="1" t="n">
-        <v>46336.24722222222</v>
+        <v>46337.74722222222</v>
       </c>
       <c r="L906" s="1" t="n">
-        <v>46336.41388888889</v>
+        <v>46337.91388888889</v>
       </c>
       <c r="M906" s="1" t="n">
-        <v>46337.41388888889</v>
+        <v>46338.91388888889</v>
       </c>
     </row>
     <row r="907">
@@ -50212,13 +50212,13 @@
         </is>
       </c>
       <c r="K907" s="1" t="n">
-        <v>46341.62222222222</v>
+        <v>46343.12222222222</v>
       </c>
       <c r="L907" s="1" t="n">
-        <v>46341.74722222222</v>
+        <v>46343.24722222222</v>
       </c>
       <c r="M907" s="1" t="n">
-        <v>46342.24722222222</v>
+        <v>46343.74722222222</v>
       </c>
     </row>
     <row r="908">
@@ -50267,13 +50267,13 @@
         </is>
       </c>
       <c r="K908" s="1" t="n">
-        <v>46343.83055555556</v>
+        <v>46345.33055555556</v>
       </c>
       <c r="L908" s="1" t="n">
-        <v>46343.87222222222</v>
+        <v>46345.37222222222</v>
       </c>
       <c r="M908" s="1" t="n">
-        <v>46344.28888888889</v>
+        <v>46345.78888888889</v>
       </c>
     </row>
     <row r="909">
@@ -50322,13 +50322,13 @@
         </is>
       </c>
       <c r="K909" s="1" t="n">
-        <v>46344.45555555556</v>
+        <v>46345.95555555556</v>
       </c>
       <c r="L909" s="1" t="n">
-        <v>46344.58055555556</v>
+        <v>46346.08055555556</v>
       </c>
       <c r="M909" s="1" t="n">
-        <v>46345.58055555556</v>
+        <v>46347.08055555556</v>
       </c>
     </row>
     <row r="910">
@@ -50377,13 +50377,13 @@
         </is>
       </c>
       <c r="K910" s="1" t="n">
-        <v>46345.83055555556</v>
+        <v>46347.33055555556</v>
       </c>
       <c r="L910" s="1" t="n">
-        <v>46345.87222222222</v>
+        <v>46347.37222222222</v>
       </c>
       <c r="M910" s="1" t="n">
-        <v>46346.28888888889</v>
+        <v>46347.78888888889</v>
       </c>
     </row>
     <row r="911">
@@ -50432,13 +50432,13 @@
         </is>
       </c>
       <c r="K911" s="1" t="n">
-        <v>46347.78888888889</v>
+        <v>46349.28888888889</v>
       </c>
       <c r="L911" s="1" t="n">
-        <v>46347.91388888889</v>
+        <v>46349.41388888889</v>
       </c>
       <c r="M911" s="1" t="n">
-        <v>46348.41388888889</v>
+        <v>46349.91388888889</v>
       </c>
     </row>
     <row r="912">
@@ -50487,13 +50487,13 @@
         </is>
       </c>
       <c r="K912" s="1" t="n">
-        <v>46353.43472222222</v>
+        <v>46354.93472222222</v>
       </c>
       <c r="L912" s="1" t="n">
-        <v>46353.49722222222</v>
+        <v>46354.99722222222</v>
       </c>
       <c r="M912" s="1" t="n">
-        <v>46353.74722222222</v>
+        <v>46355.24722222222</v>
       </c>
     </row>
     <row r="913">
@@ -50542,13 +50542,13 @@
         </is>
       </c>
       <c r="K913" s="1" t="n">
-        <v>46354.68472222222</v>
+        <v>46356.18472222222</v>
       </c>
       <c r="L913" s="1" t="n">
-        <v>46354.74722222222</v>
+        <v>46356.24722222222</v>
       </c>
       <c r="M913" s="1" t="n">
-        <v>46355.16388888889</v>
+        <v>46356.66388888889</v>
       </c>
     </row>
     <row r="914">
@@ -50597,13 +50597,13 @@
         </is>
       </c>
       <c r="K914" s="1" t="n">
-        <v>46355.49722222222</v>
+        <v>46356.99722222222</v>
       </c>
       <c r="L914" s="1" t="n">
-        <v>46355.53888888889</v>
+        <v>46357.03888888889</v>
       </c>
       <c r="M914" s="1" t="n">
-        <v>46356.16388888889</v>
+        <v>46357.66388888889</v>
       </c>
     </row>
     <row r="915">
@@ -50652,13 +50652,13 @@
         </is>
       </c>
       <c r="K915" s="1" t="n">
-        <v>46357.24444444444</v>
+        <v>46358.74444444444</v>
       </c>
       <c r="L915" s="1" t="n">
-        <v>46357.41111111111</v>
+        <v>46358.91111111111</v>
       </c>
       <c r="M915" s="1" t="n">
-        <v>46358.41111111111</v>
+        <v>46359.91111111111</v>
       </c>
     </row>
     <row r="916">
@@ -50707,13 +50707,13 @@
         </is>
       </c>
       <c r="K916" s="1" t="n">
-        <v>46362.61944444444</v>
+        <v>46364.11944444444</v>
       </c>
       <c r="L916" s="1" t="n">
-        <v>46362.74444444444</v>
+        <v>46364.24444444444</v>
       </c>
       <c r="M916" s="1" t="n">
-        <v>46363.24444444444</v>
+        <v>46364.74444444444</v>
       </c>
     </row>
     <row r="917">
@@ -50762,13 +50762,13 @@
         </is>
       </c>
       <c r="K917" s="1" t="n">
-        <v>46364.82777777778</v>
+        <v>46366.32777777778</v>
       </c>
       <c r="L917" s="1" t="n">
-        <v>46364.86944444444</v>
+        <v>46366.36944444444</v>
       </c>
       <c r="M917" s="1" t="n">
-        <v>46365.28611111111</v>
+        <v>46366.78611111111</v>
       </c>
     </row>
     <row r="918">
@@ -50817,13 +50817,13 @@
         </is>
       </c>
       <c r="K918" s="1" t="n">
-        <v>46365.45277777778</v>
+        <v>46366.95277777778</v>
       </c>
       <c r="L918" s="1" t="n">
-        <v>46365.57777777778</v>
+        <v>46367.07777777778</v>
       </c>
       <c r="M918" s="1" t="n">
-        <v>46366.57777777778</v>
+        <v>46368.07777777778</v>
       </c>
     </row>
     <row r="919">
@@ -50872,13 +50872,13 @@
         </is>
       </c>
       <c r="K919" s="1" t="n">
-        <v>46366.82777777778</v>
+        <v>46368.32777777778</v>
       </c>
       <c r="L919" s="1" t="n">
-        <v>46366.86944444444</v>
+        <v>46368.36944444444</v>
       </c>
       <c r="M919" s="1" t="n">
-        <v>46367.28611111111</v>
+        <v>46368.78611111111</v>
       </c>
     </row>
     <row r="920">
@@ -50923,13 +50923,13 @@
       </c>
       <c r="J920" t="inlineStr"/>
       <c r="K920" s="1" t="n">
-        <v>46368.78611111111</v>
+        <v>46370.28611111111</v>
       </c>
       <c r="L920" s="1" t="n">
-        <v>46368.91111111111</v>
+        <v>46370.41111111111</v>
       </c>
       <c r="M920" s="1" t="n">
-        <v>46369.41111111111</v>
+        <v>46370.91111111111</v>
       </c>
     </row>
     <row r="921">
@@ -53675,7 +53675,7 @@
         <v>46297.38333333333</v>
       </c>
       <c r="M970" s="1" t="n">
-        <v>46297.95833333334</v>
+        <v>46297.98333333333</v>
       </c>
     </row>
     <row r="971">
@@ -53724,13 +53724,13 @@
         </is>
       </c>
       <c r="K971" s="1" t="n">
-        <v>46301.6875</v>
+        <v>46301.70833333334</v>
       </c>
       <c r="L971" s="1" t="n">
-        <v>46301.72916666666</v>
+        <v>46301.75</v>
       </c>
       <c r="M971" s="1" t="n">
-        <v>46302.39583333334</v>
+        <v>46302.45833333334</v>
       </c>
     </row>
     <row r="972">
@@ -53779,13 +53779,13 @@
         </is>
       </c>
       <c r="K972" s="1" t="n">
-        <v>46308.45833333334</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="L972" s="1" t="n">
-        <v>46308.66666666666</v>
+        <v>46308.625</v>
       </c>
       <c r="M972" s="1" t="n">
-        <v>46309.33333333334</v>
+        <v>46309.29166666666</v>
       </c>
     </row>
     <row r="973">
@@ -53834,13 +53834,13 @@
         </is>
       </c>
       <c r="K973" s="1" t="n">
+        <v>46310.6875</v>
+      </c>
+      <c r="L973" s="1" t="n">
         <v>46310.72916666666</v>
       </c>
-      <c r="L973" s="1" t="n">
-        <v>46310.77083333334</v>
-      </c>
       <c r="M973" s="1" t="n">
-        <v>46311.77083333334</v>
+        <v>46311.72916666666</v>
       </c>
     </row>
     <row r="974">
@@ -53889,13 +53889,13 @@
         </is>
       </c>
       <c r="K974" s="1" t="n">
+        <v>46312.02083333334</v>
+      </c>
+      <c r="L974" s="1" t="n">
         <v>46312.0625</v>
       </c>
-      <c r="L974" s="1" t="n">
-        <v>46312.10416666666</v>
-      </c>
       <c r="M974" s="1" t="n">
-        <v>46312.72916666666</v>
+        <v>46312.6875</v>
       </c>
     </row>
     <row r="975">
@@ -53944,13 +53944,13 @@
         </is>
       </c>
       <c r="K975" s="1" t="n">
-        <v>46314.1875</v>
+        <v>46314.14583333334</v>
       </c>
       <c r="L975" s="1" t="n">
-        <v>46314.39583333334</v>
+        <v>46314.35416666666</v>
       </c>
       <c r="M975" s="1" t="n">
-        <v>46315.0625</v>
+        <v>46315.02083333334</v>
       </c>
     </row>
     <row r="976">
@@ -53999,13 +53999,13 @@
         </is>
       </c>
       <c r="K976" s="1" t="n">
-        <v>46322.0625</v>
+        <v>46322.02083333334</v>
       </c>
       <c r="L976" s="1" t="n">
-        <v>46322.14583333334</v>
+        <v>46322.10416666666</v>
       </c>
       <c r="M976" s="1" t="n">
-        <v>46322.97916666666</v>
+        <v>46322.9375</v>
       </c>
     </row>
     <row r="977">
@@ -54054,13 +54054,13 @@
         </is>
       </c>
       <c r="K977" s="1" t="n">
-        <v>46324.0625</v>
+        <v>46324.02083333334</v>
       </c>
       <c r="L977" s="1" t="n">
-        <v>46324.14583333334</v>
+        <v>46324.10416666666</v>
       </c>
       <c r="M977" s="1" t="n">
-        <v>46324.64583333334</v>
+        <v>46324.60416666666</v>
       </c>
     </row>
     <row r="978">
@@ -54109,13 +54109,13 @@
         </is>
       </c>
       <c r="K978" s="1" t="n">
+        <v>46328.60416666666</v>
+      </c>
+      <c r="L978" s="1" t="n">
         <v>46328.64583333334</v>
       </c>
-      <c r="L978" s="1" t="n">
-        <v>46328.6875</v>
-      </c>
       <c r="M978" s="1" t="n">
-        <v>46329.35416666666</v>
+        <v>46329.3125</v>
       </c>
     </row>
     <row r="979">
@@ -54164,13 +54164,13 @@
         </is>
       </c>
       <c r="K979" s="1" t="n">
-        <v>46335.77083333334</v>
+        <v>46335.72916666666</v>
       </c>
       <c r="L979" s="1" t="n">
-        <v>46335.97916666666</v>
+        <v>46335.9375</v>
       </c>
       <c r="M979" s="1" t="n">
-        <v>46336.64583333334</v>
+        <v>46336.60416666666</v>
       </c>
     </row>
     <row r="980">
@@ -54219,13 +54219,13 @@
         </is>
       </c>
       <c r="K980" s="1" t="n">
+        <v>46338.10416666666</v>
+      </c>
+      <c r="L980" s="1" t="n">
         <v>46338.14583333334</v>
       </c>
-      <c r="L980" s="1" t="n">
-        <v>46338.1875</v>
-      </c>
       <c r="M980" s="1" t="n">
-        <v>46339.1875</v>
+        <v>46339.14583333334</v>
       </c>
     </row>
     <row r="981">
@@ -54274,13 +54274,13 @@
         </is>
       </c>
       <c r="K981" s="1" t="n">
+        <v>46339.77083333334</v>
+      </c>
+      <c r="L981" s="1" t="n">
         <v>46339.8125</v>
       </c>
-      <c r="L981" s="1" t="n">
-        <v>46339.85416666666</v>
-      </c>
       <c r="M981" s="1" t="n">
-        <v>46340.47916666666</v>
+        <v>46340.4375</v>
       </c>
     </row>
     <row r="982">
@@ -54329,13 +54329,13 @@
         </is>
       </c>
       <c r="K982" s="1" t="n">
-        <v>46341.97916666666</v>
+        <v>46341.9375</v>
       </c>
       <c r="L982" s="1" t="n">
-        <v>46342.1875</v>
+        <v>46342.14583333334</v>
       </c>
       <c r="M982" s="1" t="n">
-        <v>46342.85416666666</v>
+        <v>46342.8125</v>
       </c>
     </row>
     <row r="983">
@@ -54384,13 +54384,13 @@
         </is>
       </c>
       <c r="K983" s="1" t="n">
-        <v>46349.85416666666</v>
+        <v>46349.8125</v>
       </c>
       <c r="L983" s="1" t="n">
-        <v>46349.9375</v>
+        <v>46349.89583333334</v>
       </c>
       <c r="M983" s="1" t="n">
-        <v>46350.77083333334</v>
+        <v>46350.72916666666</v>
       </c>
     </row>
     <row r="984">
@@ -54439,13 +54439,13 @@
         </is>
       </c>
       <c r="K984" s="1" t="n">
-        <v>46351.85416666666</v>
+        <v>46351.8125</v>
       </c>
       <c r="L984" s="1" t="n">
-        <v>46351.9375</v>
+        <v>46351.89583333334</v>
       </c>
       <c r="M984" s="1" t="n">
-        <v>46352.4375</v>
+        <v>46352.39583333334</v>
       </c>
     </row>
     <row r="985">
@@ -54494,13 +54494,13 @@
         </is>
       </c>
       <c r="K985" s="1" t="n">
+        <v>46356.39583333334</v>
+      </c>
+      <c r="L985" s="1" t="n">
         <v>46356.4375</v>
       </c>
-      <c r="L985" s="1" t="n">
-        <v>46356.47916666666</v>
-      </c>
       <c r="M985" s="1" t="n">
-        <v>46357.14583333334</v>
+        <v>46357.10416666666</v>
       </c>
     </row>
     <row r="986">
@@ -54549,13 +54549,13 @@
         </is>
       </c>
       <c r="K986" s="1" t="n">
-        <v>46363.5625</v>
+        <v>46363.52083333334</v>
       </c>
       <c r="L986" s="1" t="n">
-        <v>46363.77083333334</v>
+        <v>46363.72916666666</v>
       </c>
       <c r="M986" s="1" t="n">
-        <v>46364.4375</v>
+        <v>46364.39583333334</v>
       </c>
     </row>
     <row r="987">
@@ -54604,13 +54604,13 @@
         </is>
       </c>
       <c r="K987" s="1" t="n">
+        <v>46366.10416666666</v>
+      </c>
+      <c r="L987" s="1" t="n">
         <v>46366.14583333334</v>
       </c>
-      <c r="L987" s="1" t="n">
-        <v>46366.1875</v>
-      </c>
       <c r="M987" s="1" t="n">
-        <v>46367.1875</v>
+        <v>46367.14583333334</v>
       </c>
     </row>
     <row r="988">
@@ -54659,13 +54659,13 @@
         </is>
       </c>
       <c r="K988" s="1" t="n">
+        <v>46367.77083333334</v>
+      </c>
+      <c r="L988" s="1" t="n">
         <v>46367.8125</v>
       </c>
-      <c r="L988" s="1" t="n">
-        <v>46367.85416666666</v>
-      </c>
       <c r="M988" s="1" t="n">
-        <v>46368.47916666666</v>
+        <v>46368.4375</v>
       </c>
     </row>
     <row r="989">
@@ -54714,13 +54714,13 @@
         </is>
       </c>
       <c r="K989" s="1" t="n">
-        <v>46369.97916666666</v>
+        <v>46369.9375</v>
       </c>
       <c r="L989" s="1" t="n">
-        <v>46370.1875</v>
+        <v>46370.14583333334</v>
       </c>
       <c r="M989" s="1" t="n">
-        <v>46370.85416666666</v>
+        <v>46370.8125</v>
       </c>
     </row>
     <row r="990">
@@ -54769,13 +54769,13 @@
         </is>
       </c>
       <c r="K990" s="1" t="n">
-        <v>46377.85416666666</v>
+        <v>46377.8125</v>
       </c>
       <c r="L990" s="1" t="n">
-        <v>46377.9375</v>
+        <v>46377.89583333334</v>
       </c>
       <c r="M990" s="1" t="n">
-        <v>46378.77083333334</v>
+        <v>46378.72916666666</v>
       </c>
     </row>
     <row r="991">
@@ -54824,13 +54824,13 @@
         </is>
       </c>
       <c r="K991" s="1" t="n">
-        <v>46379.85416666666</v>
+        <v>46379.8125</v>
       </c>
       <c r="L991" s="1" t="n">
-        <v>46379.9375</v>
+        <v>46379.89583333334</v>
       </c>
       <c r="M991" s="1" t="n">
-        <v>46380.4375</v>
+        <v>46380.39583333334</v>
       </c>
     </row>
     <row r="992">
@@ -54879,13 +54879,13 @@
         </is>
       </c>
       <c r="K992" s="1" t="n">
+        <v>46384.39583333334</v>
+      </c>
+      <c r="L992" s="1" t="n">
         <v>46384.4375</v>
       </c>
-      <c r="L992" s="1" t="n">
-        <v>46384.47916666666</v>
-      </c>
       <c r="M992" s="1" t="n">
-        <v>46385.14583333334</v>
+        <v>46385.10416666666</v>
       </c>
     </row>
     <row r="993">
@@ -54930,13 +54930,13 @@
       </c>
       <c r="J993" t="inlineStr"/>
       <c r="K993" s="1" t="n">
-        <v>46391.5625</v>
+        <v>46391.52083333334</v>
       </c>
       <c r="L993" s="1" t="n">
-        <v>46391.77083333334</v>
+        <v>46391.72916666666</v>
       </c>
       <c r="M993" s="1" t="n">
-        <v>46392.4375</v>
+        <v>46392.39583333334</v>
       </c>
     </row>
     <row r="994">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -11241,10 +11241,10 @@
         <v>46299.20833333334</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>46301.25</v>
+        <v>46301.5</v>
       </c>
       <c r="M197" s="1" t="n">
-        <v>46301.75</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="198">
@@ -11293,13 +11293,13 @@
         </is>
       </c>
       <c r="K198" s="1" t="n">
-        <v>46305.04166666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>46305.08333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="M198" s="1" t="n">
-        <v>46305.75</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="199">
@@ -11348,13 +11348,13 @@
         </is>
       </c>
       <c r="K199" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>46306.875</v>
+        <v>46307.125</v>
       </c>
       <c r="M199" s="1" t="n">
-        <v>46307.45833333334</v>
+        <v>46307.70833333334</v>
       </c>
     </row>
     <row r="200">
@@ -15025,13 +15025,13 @@
         </is>
       </c>
       <c r="K266" s="1" t="n">
-        <v>46299.08333333334</v>
+        <v>46299.25</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>46299.14583333334</v>
+        <v>46299.3125</v>
       </c>
       <c r="M266" s="1" t="n">
-        <v>46299.77083333334</v>
+        <v>46300.125</v>
       </c>
     </row>
     <row r="267">
@@ -15080,13 +15080,13 @@
         </is>
       </c>
       <c r="K267" s="1" t="n">
-        <v>46300.625</v>
+        <v>46300.97916666666</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>46300.66666666666</v>
+        <v>46301.02083333334</v>
       </c>
       <c r="M267" s="1" t="n">
-        <v>46301.16666666666</v>
+        <v>46301.52083333334</v>
       </c>
     </row>
     <row r="268">
@@ -15135,13 +15135,13 @@
         </is>
       </c>
       <c r="K268" s="1" t="n">
-        <v>46303.70833333334</v>
+        <v>46304.0625</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>46303.75</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="M268" s="1" t="n">
-        <v>46304.375</v>
+        <v>46304.72916666666</v>
       </c>
     </row>
     <row r="269">
@@ -15190,13 +15190,13 @@
         </is>
       </c>
       <c r="K269" s="1" t="n">
-        <v>46305.20833333334</v>
+        <v>46305.5625</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>46305.25</v>
+        <v>46305.60416666666</v>
       </c>
       <c r="M269" s="1" t="n">
-        <v>46305.75</v>
+        <v>46306.10416666666</v>
       </c>
     </row>
     <row r="270">
@@ -15245,13 +15245,13 @@
         </is>
       </c>
       <c r="K270" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46307.1875</v>
       </c>
       <c r="L270" s="1" t="n">
-        <v>46307</v>
+        <v>46307.35416666666</v>
       </c>
       <c r="M270" s="1" t="n">
-        <v>46307.79166666666</v>
+        <v>46308.14583333334</v>
       </c>
     </row>
     <row r="271">
@@ -15300,13 +15300,13 @@
         </is>
       </c>
       <c r="K271" s="1" t="n">
-        <v>46313.54166666666</v>
+        <v>46313.89583333334</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>46313.58333333334</v>
+        <v>46313.9375</v>
       </c>
       <c r="M271" s="1" t="n">
-        <v>46313.875</v>
+        <v>46314.22916666666</v>
       </c>
     </row>
     <row r="272">
@@ -15355,13 +15355,13 @@
         </is>
       </c>
       <c r="K272" s="1" t="n">
-        <v>46314.16666666666</v>
+        <v>46314.52083333334</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>46314.16666666666</v>
+        <v>46314.52083333334</v>
       </c>
       <c r="M272" s="1" t="n">
-        <v>46315.54166666666</v>
+        <v>46315.89583333334</v>
       </c>
     </row>
     <row r="273">
@@ -15410,13 +15410,13 @@
         </is>
       </c>
       <c r="K273" s="1" t="n">
-        <v>46315.79166666666</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>46315.83333333334</v>
+        <v>46316.1875</v>
       </c>
       <c r="M273" s="1" t="n">
-        <v>46316.29166666666</v>
+        <v>46316.64583333334</v>
       </c>
     </row>
     <row r="274">
@@ -15465,13 +15465,13 @@
         </is>
       </c>
       <c r="K274" s="1" t="n">
-        <v>46320.125</v>
+        <v>46320.47916666666</v>
       </c>
       <c r="L274" s="1" t="n">
-        <v>46320.125</v>
+        <v>46320.47916666666</v>
       </c>
       <c r="M274" s="1" t="n">
-        <v>46320.58333333334</v>
+        <v>46320.9375</v>
       </c>
     </row>
     <row r="275">
@@ -15520,13 +15520,13 @@
         </is>
       </c>
       <c r="K275" s="1" t="n">
-        <v>46321.58333333334</v>
+        <v>46321.9375</v>
       </c>
       <c r="L275" s="1" t="n">
-        <v>46321.58333333334</v>
+        <v>46321.9375</v>
       </c>
       <c r="M275" s="1" t="n">
-        <v>46322.08333333334</v>
+        <v>46322.4375</v>
       </c>
     </row>
     <row r="276">
@@ -15575,13 +15575,13 @@
         </is>
       </c>
       <c r="K276" s="1" t="n">
-        <v>46324.54166666666</v>
+        <v>46324.89583333334</v>
       </c>
       <c r="L276" s="1" t="n">
-        <v>46324.58333333334</v>
+        <v>46324.9375</v>
       </c>
       <c r="M276" s="1" t="n">
-        <v>46325.20833333334</v>
+        <v>46325.5625</v>
       </c>
     </row>
     <row r="277">
@@ -15630,13 +15630,13 @@
         </is>
       </c>
       <c r="K277" s="1" t="n">
-        <v>46326.20833333334</v>
+        <v>46326.5625</v>
       </c>
       <c r="L277" s="1" t="n">
-        <v>46326.25</v>
+        <v>46326.60416666666</v>
       </c>
       <c r="M277" s="1" t="n">
-        <v>46326.75</v>
+        <v>46327.10416666666</v>
       </c>
     </row>
     <row r="278">
@@ -15685,13 +15685,13 @@
         </is>
       </c>
       <c r="K278" s="1" t="n">
-        <v>46327.83333333334</v>
+        <v>46328.1875</v>
       </c>
       <c r="L278" s="1" t="n">
-        <v>46328</v>
+        <v>46328.35416666666</v>
       </c>
       <c r="M278" s="1" t="n">
-        <v>46328.79166666666</v>
+        <v>46329.14583333334</v>
       </c>
     </row>
     <row r="279">
@@ -15740,13 +15740,13 @@
         </is>
       </c>
       <c r="K279" s="1" t="n">
-        <v>46334.54166666666</v>
+        <v>46334.89583333334</v>
       </c>
       <c r="L279" s="1" t="n">
-        <v>46334.58333333334</v>
+        <v>46334.9375</v>
       </c>
       <c r="M279" s="1" t="n">
-        <v>46334.875</v>
+        <v>46335.22916666666</v>
       </c>
     </row>
     <row r="280">
@@ -15795,13 +15795,13 @@
         </is>
       </c>
       <c r="K280" s="1" t="n">
-        <v>46335.16666666666</v>
+        <v>46335.52083333334</v>
       </c>
       <c r="L280" s="1" t="n">
-        <v>46335.16666666666</v>
+        <v>46335.52083333334</v>
       </c>
       <c r="M280" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46336.89583333334</v>
       </c>
     </row>
     <row r="281">
@@ -15850,13 +15850,13 @@
         </is>
       </c>
       <c r="K281" s="1" t="n">
-        <v>46336.79166666666</v>
+        <v>46337.14583333334</v>
       </c>
       <c r="L281" s="1" t="n">
-        <v>46336.83333333334</v>
+        <v>46337.1875</v>
       </c>
       <c r="M281" s="1" t="n">
-        <v>46337.29166666666</v>
+        <v>46337.64583333334</v>
       </c>
     </row>
     <row r="282">
@@ -15905,13 +15905,13 @@
         </is>
       </c>
       <c r="K282" s="1" t="n">
-        <v>46341.125</v>
+        <v>46341.47916666666</v>
       </c>
       <c r="L282" s="1" t="n">
-        <v>46341.125</v>
+        <v>46341.47916666666</v>
       </c>
       <c r="M282" s="1" t="n">
-        <v>46341.58333333334</v>
+        <v>46341.9375</v>
       </c>
     </row>
     <row r="283">
@@ -15960,13 +15960,13 @@
         </is>
       </c>
       <c r="K283" s="1" t="n">
-        <v>46342.58333333334</v>
+        <v>46342.9375</v>
       </c>
       <c r="L283" s="1" t="n">
-        <v>46342.58333333334</v>
+        <v>46342.9375</v>
       </c>
       <c r="M283" s="1" t="n">
-        <v>46343.08333333334</v>
+        <v>46343.4375</v>
       </c>
     </row>
     <row r="284">
@@ -16015,13 +16015,13 @@
         </is>
       </c>
       <c r="K284" s="1" t="n">
-        <v>46345.54166666666</v>
+        <v>46345.89583333334</v>
       </c>
       <c r="L284" s="1" t="n">
-        <v>46345.58333333334</v>
+        <v>46345.9375</v>
       </c>
       <c r="M284" s="1" t="n">
-        <v>46346.20833333334</v>
+        <v>46346.5625</v>
       </c>
     </row>
     <row r="285">
@@ -16070,13 +16070,13 @@
         </is>
       </c>
       <c r="K285" s="1" t="n">
-        <v>46347.20833333334</v>
+        <v>46347.5625</v>
       </c>
       <c r="L285" s="1" t="n">
-        <v>46347.25</v>
+        <v>46347.60416666666</v>
       </c>
       <c r="M285" s="1" t="n">
-        <v>46347.75</v>
+        <v>46348.10416666666</v>
       </c>
     </row>
     <row r="286">
@@ -16125,13 +16125,13 @@
         </is>
       </c>
       <c r="K286" s="1" t="n">
-        <v>46348.83333333334</v>
+        <v>46349.1875</v>
       </c>
       <c r="L286" s="1" t="n">
-        <v>46349</v>
+        <v>46349.35416666666</v>
       </c>
       <c r="M286" s="1" t="n">
-        <v>46349.79166666666</v>
+        <v>46350.14583333334</v>
       </c>
     </row>
     <row r="287">
@@ -16180,13 +16180,13 @@
         </is>
       </c>
       <c r="K287" s="1" t="n">
-        <v>46355.54166666666</v>
+        <v>46355.89583333334</v>
       </c>
       <c r="L287" s="1" t="n">
-        <v>46355.58333333334</v>
+        <v>46355.9375</v>
       </c>
       <c r="M287" s="1" t="n">
-        <v>46355.875</v>
+        <v>46356.22916666666</v>
       </c>
     </row>
     <row r="288">
@@ -16235,13 +16235,13 @@
         </is>
       </c>
       <c r="K288" s="1" t="n">
-        <v>46356.16666666666</v>
+        <v>46356.52083333334</v>
       </c>
       <c r="L288" s="1" t="n">
-        <v>46356.16666666666</v>
+        <v>46356.52083333334</v>
       </c>
       <c r="M288" s="1" t="n">
-        <v>46357.54166666666</v>
+        <v>46357.89583333334</v>
       </c>
     </row>
     <row r="289">
@@ -16290,13 +16290,13 @@
         </is>
       </c>
       <c r="K289" s="1" t="n">
-        <v>46357.79166666666</v>
+        <v>46358.14583333334</v>
       </c>
       <c r="L289" s="1" t="n">
-        <v>46357.83333333334</v>
+        <v>46358.1875</v>
       </c>
       <c r="M289" s="1" t="n">
-        <v>46358.29166666666</v>
+        <v>46358.64583333334</v>
       </c>
     </row>
     <row r="290">
@@ -16345,13 +16345,13 @@
         </is>
       </c>
       <c r="K290" s="1" t="n">
-        <v>46362.125</v>
+        <v>46362.47916666666</v>
       </c>
       <c r="L290" s="1" t="n">
-        <v>46362.125</v>
+        <v>46362.47916666666</v>
       </c>
       <c r="M290" s="1" t="n">
-        <v>46362.58333333334</v>
+        <v>46362.9375</v>
       </c>
     </row>
     <row r="291">
@@ -16400,13 +16400,13 @@
         </is>
       </c>
       <c r="K291" s="1" t="n">
-        <v>46363.58333333334</v>
+        <v>46363.9375</v>
       </c>
       <c r="L291" s="1" t="n">
-        <v>46363.58333333334</v>
+        <v>46363.9375</v>
       </c>
       <c r="M291" s="1" t="n">
-        <v>46364.08333333334</v>
+        <v>46364.4375</v>
       </c>
     </row>
     <row r="292">
@@ -16455,13 +16455,13 @@
         </is>
       </c>
       <c r="K292" s="1" t="n">
-        <v>46366.54166666666</v>
+        <v>46366.89583333334</v>
       </c>
       <c r="L292" s="1" t="n">
-        <v>46366.58333333334</v>
+        <v>46366.9375</v>
       </c>
       <c r="M292" s="1" t="n">
-        <v>46367.20833333334</v>
+        <v>46367.5625</v>
       </c>
     </row>
     <row r="293">
@@ -16510,13 +16510,13 @@
         </is>
       </c>
       <c r="K293" s="1" t="n">
-        <v>46368.20833333334</v>
+        <v>46368.5625</v>
       </c>
       <c r="L293" s="1" t="n">
-        <v>46368.25</v>
+        <v>46368.60416666666</v>
       </c>
       <c r="M293" s="1" t="n">
-        <v>46368.75</v>
+        <v>46369.10416666666</v>
       </c>
     </row>
     <row r="294">
@@ -16565,13 +16565,13 @@
         </is>
       </c>
       <c r="K294" s="1" t="n">
-        <v>46369.83333333334</v>
+        <v>46370.1875</v>
       </c>
       <c r="L294" s="1" t="n">
-        <v>46370</v>
+        <v>46370.35416666666</v>
       </c>
       <c r="M294" s="1" t="n">
-        <v>46370.79166666666</v>
+        <v>46371.14583333334</v>
       </c>
     </row>
     <row r="295">
@@ -16620,13 +16620,13 @@
         </is>
       </c>
       <c r="K295" s="1" t="n">
-        <v>46376.54166666666</v>
+        <v>46376.89583333334</v>
       </c>
       <c r="L295" s="1" t="n">
-        <v>46376.58333333334</v>
+        <v>46376.9375</v>
       </c>
       <c r="M295" s="1" t="n">
-        <v>46376.875</v>
+        <v>46377.22916666666</v>
       </c>
     </row>
     <row r="296">
@@ -16675,13 +16675,13 @@
         </is>
       </c>
       <c r="K296" s="1" t="n">
-        <v>46377.16666666666</v>
+        <v>46377.52083333334</v>
       </c>
       <c r="L296" s="1" t="n">
-        <v>46377.16666666666</v>
+        <v>46377.52083333334</v>
       </c>
       <c r="M296" s="1" t="n">
-        <v>46378.54166666666</v>
+        <v>46378.89583333334</v>
       </c>
     </row>
     <row r="297">
@@ -16730,13 +16730,13 @@
         </is>
       </c>
       <c r="K297" s="1" t="n">
-        <v>46378.79166666666</v>
+        <v>46379.14583333334</v>
       </c>
       <c r="L297" s="1" t="n">
-        <v>46378.83333333334</v>
+        <v>46379.1875</v>
       </c>
       <c r="M297" s="1" t="n">
-        <v>46379.29166666666</v>
+        <v>46379.64583333334</v>
       </c>
     </row>
     <row r="298">
@@ -16785,13 +16785,13 @@
         </is>
       </c>
       <c r="K298" s="1" t="n">
-        <v>46383.125</v>
+        <v>46383.47916666666</v>
       </c>
       <c r="L298" s="1" t="n">
-        <v>46383.125</v>
+        <v>46383.47916666666</v>
       </c>
       <c r="M298" s="1" t="n">
-        <v>46383.58333333334</v>
+        <v>46383.9375</v>
       </c>
     </row>
     <row r="299">
@@ -16836,13 +16836,13 @@
       </c>
       <c r="J299" t="inlineStr"/>
       <c r="K299" s="1" t="n">
-        <v>46384.58333333334</v>
+        <v>46384.9375</v>
       </c>
       <c r="L299" s="1" t="n">
-        <v>46384.58333333334</v>
+        <v>46384.9375</v>
       </c>
       <c r="M299" s="1" t="n">
-        <v>46385.08333333334</v>
+        <v>46385.4375</v>
       </c>
     </row>
     <row r="300">
@@ -39293,7 +39293,7 @@
         <v>46300.20833333334</v>
       </c>
       <c r="M708" s="1" t="n">
-        <v>46301.29166666666</v>
+        <v>46301.25</v>
       </c>
     </row>
     <row r="709">
@@ -39342,13 +39342,13 @@
         </is>
       </c>
       <c r="K709" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46306.75</v>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46307</v>
+        <v>46306.91666666666</v>
       </c>
       <c r="M709" s="1" t="n">
-        <v>46307.58333333334</v>
+        <v>46307.5</v>
       </c>
     </row>
     <row r="710">
@@ -39397,13 +39397,13 @@
         </is>
       </c>
       <c r="K710" s="1" t="n">
-        <v>46309.35416666666</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46309.39583333334</v>
+        <v>46309.3125</v>
       </c>
       <c r="M710" s="1" t="n">
-        <v>46309.75</v>
+        <v>46309.66666666666</v>
       </c>
     </row>
     <row r="711">
@@ -39452,13 +39452,13 @@
         </is>
       </c>
       <c r="K711" s="1" t="n">
+        <v>46309.79166666666</v>
+      </c>
+      <c r="L711" s="1" t="n">
         <v>46309.875</v>
       </c>
-      <c r="L711" s="1" t="n">
-        <v>46309.95833333334</v>
-      </c>
       <c r="M711" s="1" t="n">
-        <v>46310.95833333334</v>
+        <v>46310.875</v>
       </c>
     </row>
     <row r="712">
@@ -39507,13 +39507,13 @@
         </is>
       </c>
       <c r="K712" s="1" t="n">
-        <v>46311.16666666666</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46311.20833333334</v>
+        <v>46311.125</v>
       </c>
       <c r="M712" s="1" t="n">
-        <v>46311.70833333334</v>
+        <v>46311.625</v>
       </c>
     </row>
     <row r="713">
@@ -39562,13 +39562,13 @@
         </is>
       </c>
       <c r="K713" s="1" t="n">
-        <v>46313.52083333334</v>
+        <v>46313.4375</v>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46313.6875</v>
+        <v>46313.60416666666</v>
       </c>
       <c r="M713" s="1" t="n">
-        <v>46314.375</v>
+        <v>46314.29166666666</v>
       </c>
     </row>
     <row r="714">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -31770,7 +31770,7 @@
         <v>46300.66666666666</v>
       </c>
       <c r="M571" s="1" t="n">
-        <v>46301.58333333334</v>
+        <v>46301.5</v>
       </c>
     </row>
     <row r="572">
@@ -31819,13 +31819,13 @@
         </is>
       </c>
       <c r="K572" s="1" t="n">
+        <v>46306.79166666666</v>
+      </c>
+      <c r="L572" s="1" t="n">
         <v>46306.95833333334</v>
       </c>
-      <c r="L572" s="1" t="n">
-        <v>46307.125</v>
-      </c>
       <c r="M572" s="1" t="n">
-        <v>46307.70833333334</v>
+        <v>46307.54166666666</v>
       </c>
     </row>
     <row r="573">
@@ -31874,13 +31874,13 @@
         </is>
       </c>
       <c r="K573" s="1" t="n">
-        <v>46309.35416666666</v>
+        <v>46309.1875</v>
       </c>
       <c r="L573" s="1" t="n">
-        <v>46309.39583333334</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="M573" s="1" t="n">
-        <v>46309.75</v>
+        <v>46309.58333333334</v>
       </c>
     </row>
     <row r="574">
@@ -31929,13 +31929,13 @@
         </is>
       </c>
       <c r="K574" s="1" t="n">
-        <v>46309.875</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="L574" s="1" t="n">
-        <v>46309.95833333334</v>
+        <v>46309.79166666666</v>
       </c>
       <c r="M574" s="1" t="n">
-        <v>46310.95833333334</v>
+        <v>46310.79166666666</v>
       </c>
     </row>
     <row r="575">
@@ -31984,13 +31984,13 @@
         </is>
       </c>
       <c r="K575" s="1" t="n">
-        <v>46311.16666666666</v>
+        <v>46311</v>
       </c>
       <c r="L575" s="1" t="n">
-        <v>46311.20833333334</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="M575" s="1" t="n">
-        <v>46311.70833333334</v>
+        <v>46311.54166666666</v>
       </c>
     </row>
     <row r="576">
@@ -32039,13 +32039,13 @@
         </is>
       </c>
       <c r="K576" s="1" t="n">
+        <v>46313.35416666666</v>
+      </c>
+      <c r="L576" s="1" t="n">
         <v>46313.52083333334</v>
       </c>
-      <c r="L576" s="1" t="n">
-        <v>46313.6875</v>
-      </c>
       <c r="M576" s="1" t="n">
-        <v>46314.375</v>
+        <v>46314.20833333334</v>
       </c>
     </row>
     <row r="577">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -5426,7 +5426,7 @@
         <v>46301.79166666666</v>
       </c>
       <c r="M91" s="1" t="n">
-        <v>46303.45833333334</v>
+        <v>46302.875</v>
       </c>
     </row>
     <row r="92">
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46303.625</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="L92" s="1" t="n">
-        <v>46303.6875</v>
+        <v>46302.52083333334</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>46304.3125</v>
+        <v>46303.14583333334</v>
       </c>
     </row>
     <row r="93">
@@ -5530,13 +5530,13 @@
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46305.33333333334</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>46305.54166666666</v>
+        <v>46304.375</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>46306.20833333334</v>
+        <v>46305.04166666666</v>
       </c>
     </row>
     <row r="94">
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46313.20833333334</v>
+        <v>46312.04166666666</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>46313.29166666666</v>
+        <v>46312.125</v>
       </c>
       <c r="M94" s="1" t="n">
-        <v>46314.125</v>
+        <v>46312.95833333334</v>
       </c>
     </row>
     <row r="95">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46315.20833333334</v>
+        <v>46314.04166666666</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>46315.29166666666</v>
+        <v>46314.125</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>46315.79166666666</v>
+        <v>46314.625</v>
       </c>
     </row>
     <row r="96">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46319.79166666666</v>
+        <v>46318.625</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>46319.83333333334</v>
+        <v>46318.66666666666</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>46320.5</v>
+        <v>46319.33333333334</v>
       </c>
     </row>
     <row r="97">
@@ -5750,13 +5750,13 @@
         </is>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46326.91666666666</v>
+        <v>46325.75</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>46327.125</v>
+        <v>46325.95833333334</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>46327.79166666666</v>
+        <v>46326.625</v>
       </c>
     </row>
     <row r="98">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -5426,7 +5426,7 @@
         <v>46301.79166666666</v>
       </c>
       <c r="M91" s="1" t="n">
-        <v>46302.875</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="92">
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46302.45833333334</v>
+        <v>46302.70833333334</v>
       </c>
       <c r="L92" s="1" t="n">
-        <v>46302.52083333334</v>
+        <v>46302.77083333334</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>46303.14583333334</v>
+        <v>46303.39583333334</v>
       </c>
     </row>
     <row r="93">
@@ -5530,13 +5530,13 @@
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46304.16666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>46304.375</v>
+        <v>46304.625</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>46305.04166666666</v>
+        <v>46305.29166666666</v>
       </c>
     </row>
     <row r="94">
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46312.04166666666</v>
+        <v>46312.29166666666</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>46312.125</v>
+        <v>46312.375</v>
       </c>
       <c r="M94" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.20833333334</v>
       </c>
     </row>
     <row r="95">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46314.04166666666</v>
+        <v>46314.29166666666</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>46314.125</v>
+        <v>46314.375</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>46314.625</v>
+        <v>46314.875</v>
       </c>
     </row>
     <row r="96">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46318.625</v>
+        <v>46318.875</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>46318.66666666666</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>46319.33333333334</v>
+        <v>46319.58333333334</v>
       </c>
     </row>
     <row r="97">
@@ -5750,13 +5750,13 @@
         </is>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46325.75</v>
+        <v>46326</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>46325.95833333334</v>
+        <v>46326.20833333334</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>46326.625</v>
+        <v>46326.875</v>
       </c>
     </row>
     <row r="98">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -5426,7 +5426,7 @@
         <v>46301.79166666666</v>
       </c>
       <c r="M91" s="1" t="n">
-        <v>46303</v>
+        <v>46302.95833333334</v>
       </c>
     </row>
     <row r="92">
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46302.70833333334</v>
+        <v>46302.625</v>
       </c>
       <c r="L92" s="1" t="n">
-        <v>46302.77083333334</v>
+        <v>46302.6875</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>46303.39583333334</v>
+        <v>46303.3125</v>
       </c>
     </row>
     <row r="93">
@@ -5530,13 +5530,13 @@
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46304.41666666666</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>46304.625</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>46305.29166666666</v>
+        <v>46305.20833333334</v>
       </c>
     </row>
     <row r="94">
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="K94" s="1" t="n">
+        <v>46312.20833333334</v>
+      </c>
+      <c r="L94" s="1" t="n">
         <v>46312.29166666666</v>
       </c>
-      <c r="L94" s="1" t="n">
-        <v>46312.375</v>
-      </c>
       <c r="M94" s="1" t="n">
-        <v>46313.20833333334</v>
+        <v>46313.125</v>
       </c>
     </row>
     <row r="95">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="K95" s="1" t="n">
+        <v>46314.20833333334</v>
+      </c>
+      <c r="L95" s="1" t="n">
         <v>46314.29166666666</v>
       </c>
-      <c r="L95" s="1" t="n">
-        <v>46314.375</v>
-      </c>
       <c r="M95" s="1" t="n">
-        <v>46314.875</v>
+        <v>46314.79166666666</v>
       </c>
     </row>
     <row r="96">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46318.875</v>
+        <v>46318.79166666666</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>46318.91666666666</v>
+        <v>46318.83333333334</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>46319.58333333334</v>
+        <v>46319.5</v>
       </c>
     </row>
     <row r="97">
@@ -5750,13 +5750,13 @@
         </is>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46326</v>
+        <v>46325.91666666666</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>46326.20833333334</v>
+        <v>46326.125</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>46326.875</v>
+        <v>46326.79166666666</v>
       </c>
     </row>
     <row r="98">
@@ -10639,7 +10639,7 @@
         <v>46301.52083333334</v>
       </c>
       <c r="M186" s="1" t="n">
-        <v>46302.1875</v>
+        <v>46302.19583333333</v>
       </c>
     </row>
     <row r="187">
@@ -10688,13 +10688,13 @@
         </is>
       </c>
       <c r="K187" s="1" t="n">
-        <v>46305.47916666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="L187" s="1" t="n">
-        <v>46305.52083333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="M187" s="1" t="n">
-        <v>46306.1875</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="188">
@@ -10743,13 +10743,13 @@
         </is>
       </c>
       <c r="K188" s="1" t="n">
-        <v>46307.27083333334</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="L188" s="1" t="n">
-        <v>46307.3125</v>
+        <v>46307.125</v>
       </c>
       <c r="M188" s="1" t="n">
-        <v>46307.89583333334</v>
+        <v>46307.70833333334</v>
       </c>
     </row>
     <row r="189">
@@ -38300,10 +38300,10 @@
         <v>46295.91666666666</v>
       </c>
       <c r="L690" s="1" t="n">
-        <v>46297.33333333334</v>
+        <v>46297.375</v>
       </c>
       <c r="M690" s="1" t="n">
-        <v>46297.875</v>
+        <v>46298.07638888889</v>
       </c>
     </row>
     <row r="691">
@@ -38352,13 +38352,13 @@
         </is>
       </c>
       <c r="K691" s="1" t="n">
-        <v>46298.95833333334</v>
+        <v>46299.125</v>
       </c>
       <c r="L691" s="1" t="n">
-        <v>46299.02083333334</v>
+        <v>46299.1875</v>
       </c>
       <c r="M691" s="1" t="n">
-        <v>46299.75</v>
+        <v>46299.64583333334</v>
       </c>
     </row>
     <row r="692">
@@ -38407,13 +38407,13 @@
         </is>
       </c>
       <c r="K692" s="1" t="n">
-        <v>46300.125</v>
+        <v>46300.02083333334</v>
       </c>
       <c r="L692" s="1" t="n">
-        <v>46300.20833333334</v>
+        <v>46300.20416666667</v>
       </c>
       <c r="M692" s="1" t="n">
-        <v>46301.25</v>
+        <v>46301.16666666666</v>
       </c>
     </row>
     <row r="693">
@@ -38462,13 +38462,13 @@
         </is>
       </c>
       <c r="K693" s="1" t="n">
-        <v>46306.66666666666</v>
+        <v>46306.41666666666</v>
       </c>
       <c r="L693" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46306.58333333334</v>
       </c>
       <c r="M693" s="1" t="n">
-        <v>46307.41666666666</v>
+        <v>46307.16666666666</v>
       </c>
     </row>
     <row r="694">
@@ -38517,13 +38517,13 @@
         </is>
       </c>
       <c r="K694" s="1" t="n">
-        <v>46309.1875</v>
+        <v>46308.9375</v>
       </c>
       <c r="L694" s="1" t="n">
-        <v>46309.22916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="M694" s="1" t="n">
-        <v>46309.58333333334</v>
+        <v>46309.33333333334</v>
       </c>
     </row>
     <row r="695">
@@ -38572,13 +38572,13 @@
         </is>
       </c>
       <c r="K695" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="L695" s="1" t="n">
-        <v>46309.79166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="M695" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.54166666666</v>
       </c>
     </row>
     <row r="696">
@@ -38627,13 +38627,13 @@
         </is>
       </c>
       <c r="K696" s="1" t="n">
-        <v>46311</v>
+        <v>46310.75</v>
       </c>
       <c r="L696" s="1" t="n">
-        <v>46311.04166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="M696" s="1" t="n">
-        <v>46311.54166666666</v>
+        <v>46311.29166666666</v>
       </c>
     </row>
     <row r="697">
@@ -38682,13 +38682,13 @@
         </is>
       </c>
       <c r="K697" s="1" t="n">
-        <v>46313.35416666666</v>
+        <v>46313.10416666666</v>
       </c>
       <c r="L697" s="1" t="n">
-        <v>46313.52083333334</v>
+        <v>46313.27083333334</v>
       </c>
       <c r="M697" s="1" t="n">
-        <v>46314.20833333334</v>
+        <v>46313.95833333334</v>
       </c>
     </row>
     <row r="698">
@@ -44671,7 +44671,7 @@
         <v>46301.33333333334</v>
       </c>
       <c r="M806" s="1" t="n">
-        <v>46301.75</v>
+        <v>46301.72083333333</v>
       </c>
     </row>
     <row r="807">
@@ -44720,10 +44720,10 @@
         </is>
       </c>
       <c r="K807" s="1" t="n">
-        <v>46302.04166666666</v>
+        <v>46302.07638888889</v>
       </c>
       <c r="L807" s="1" t="n">
-        <v>46302.08333333334</v>
+        <v>46302.09583333333</v>
       </c>
       <c r="M807" s="1" t="n">
         <v>46303.125</v>
@@ -48452,10 +48452,10 @@
         </is>
       </c>
       <c r="K875" s="1" t="n">
-        <v>46300.875</v>
+        <v>46300.8875</v>
       </c>
       <c r="L875" s="1" t="n">
-        <v>46301.66666666666</v>
+        <v>46301.64583333334</v>
       </c>
       <c r="M875" s="1" t="n">
         <v>46303.54166666666</v>

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -5423,7 +5423,7 @@
         <v>46301.75</v>
       </c>
       <c r="L91" s="1" t="n">
-        <v>46301.79166666666</v>
+        <v>46301.775</v>
       </c>
       <c r="M91" s="1" t="n">
         <v>46302.95833333334</v>
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46302.625</v>
+        <v>46303.25</v>
       </c>
       <c r="L92" s="1" t="n">
-        <v>46302.6875</v>
+        <v>46303.3125</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>46303.3125</v>
+        <v>46303.9375</v>
       </c>
     </row>
     <row r="93">
@@ -5530,13 +5530,13 @@
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46304.33333333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>46304.54166666666</v>
+        <v>46305.16666666666</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>46305.20833333334</v>
+        <v>46305.83333333334</v>
       </c>
     </row>
     <row r="94">
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46312.20833333334</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>46312.29166666666</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="M94" s="1" t="n">
-        <v>46313.125</v>
+        <v>46313.75</v>
       </c>
     </row>
     <row r="95">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46314.20833333334</v>
+        <v>46314.83333333334</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>46314.29166666666</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>46314.79166666666</v>
+        <v>46315.41666666666</v>
       </c>
     </row>
     <row r="96">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46318.79166666666</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>46318.83333333334</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>46319.5</v>
+        <v>46320.125</v>
       </c>
     </row>
     <row r="97">
@@ -5750,13 +5750,13 @@
         </is>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46325.91666666666</v>
+        <v>46326.54166666666</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>46326.125</v>
+        <v>46326.75</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>46326.79166666666</v>
+        <v>46327.41666666666</v>
       </c>
     </row>
     <row r="98">
@@ -5805,13 +5805,13 @@
         </is>
       </c>
       <c r="K98" s="1" t="n">
-        <v>46329.75</v>
+        <v>46330.375</v>
       </c>
       <c r="L98" s="1" t="n">
-        <v>46329.79166666666</v>
+        <v>46330.41666666666</v>
       </c>
       <c r="M98" s="1" t="n">
-        <v>46330.79166666666</v>
+        <v>46331.41666666666</v>
       </c>
     </row>
     <row r="99">
@@ -5860,13 +5860,13 @@
         </is>
       </c>
       <c r="K99" s="1" t="n">
-        <v>46331.41666666666</v>
+        <v>46332.04166666666</v>
       </c>
       <c r="L99" s="1" t="n">
-        <v>46331.45833333334</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="M99" s="1" t="n">
-        <v>46332.08333333334</v>
+        <v>46332.70833333334</v>
       </c>
     </row>
     <row r="100">
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46333.58333333334</v>
+        <v>46334.20833333334</v>
       </c>
       <c r="L100" s="1" t="n">
-        <v>46333.79166666666</v>
+        <v>46334.41666666666</v>
       </c>
       <c r="M100" s="1" t="n">
-        <v>46334.45833333334</v>
+        <v>46335.08333333334</v>
       </c>
     </row>
     <row r="101">
@@ -5970,13 +5970,13 @@
         </is>
       </c>
       <c r="K101" s="1" t="n">
-        <v>46341.45833333334</v>
+        <v>46342.08333333334</v>
       </c>
       <c r="L101" s="1" t="n">
-        <v>46341.54166666666</v>
+        <v>46342.16666666666</v>
       </c>
       <c r="M101" s="1" t="n">
-        <v>46342.375</v>
+        <v>46343</v>
       </c>
     </row>
     <row r="102">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46343.45833333334</v>
+        <v>46344.08333333334</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>46343.54166666666</v>
+        <v>46344.16666666666</v>
       </c>
       <c r="M102" s="1" t="n">
-        <v>46344.04166666666</v>
+        <v>46344.66666666666</v>
       </c>
     </row>
     <row r="103">
@@ -6080,13 +6080,13 @@
         </is>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46348.04166666666</v>
+        <v>46348.66666666666</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>46348.08333333334</v>
+        <v>46348.70833333334</v>
       </c>
       <c r="M103" s="1" t="n">
-        <v>46348.75</v>
+        <v>46349.375</v>
       </c>
     </row>
     <row r="104">
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46355.16666666666</v>
+        <v>46355.79166666666</v>
       </c>
       <c r="L104" s="1" t="n">
-        <v>46355.375</v>
+        <v>46356</v>
       </c>
       <c r="M104" s="1" t="n">
-        <v>46356.04166666666</v>
+        <v>46356.66666666666</v>
       </c>
     </row>
     <row r="105">
@@ -6190,13 +6190,13 @@
         </is>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46357.75</v>
+        <v>46358.375</v>
       </c>
       <c r="L105" s="1" t="n">
-        <v>46357.79166666666</v>
+        <v>46358.41666666666</v>
       </c>
       <c r="M105" s="1" t="n">
-        <v>46358.79166666666</v>
+        <v>46359.41666666666</v>
       </c>
     </row>
     <row r="106">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46359.41666666666</v>
+        <v>46360.04166666666</v>
       </c>
       <c r="L106" s="1" t="n">
-        <v>46359.45833333334</v>
+        <v>46360.08333333334</v>
       </c>
       <c r="M106" s="1" t="n">
-        <v>46360.08333333334</v>
+        <v>46360.70833333334</v>
       </c>
     </row>
     <row r="107">
@@ -6300,13 +6300,13 @@
         </is>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46361.58333333334</v>
+        <v>46362.20833333334</v>
       </c>
       <c r="L107" s="1" t="n">
-        <v>46361.79166666666</v>
+        <v>46362.41666666666</v>
       </c>
       <c r="M107" s="1" t="n">
-        <v>46362.45833333334</v>
+        <v>46363.08333333334</v>
       </c>
     </row>
     <row r="108">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46369.45833333334</v>
+        <v>46370.08333333334</v>
       </c>
       <c r="L108" s="1" t="n">
-        <v>46369.54166666666</v>
+        <v>46370.16666666666</v>
       </c>
       <c r="M108" s="1" t="n">
-        <v>46370.375</v>
+        <v>46371</v>
       </c>
     </row>
     <row r="109">
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46371.45833333334</v>
+        <v>46372.08333333334</v>
       </c>
       <c r="L109" s="1" t="n">
-        <v>46371.54166666666</v>
+        <v>46372.16666666666</v>
       </c>
       <c r="M109" s="1" t="n">
-        <v>46372.04166666666</v>
+        <v>46372.66666666666</v>
       </c>
     </row>
     <row r="110">
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46376.04166666666</v>
+        <v>46376.66666666666</v>
       </c>
       <c r="L110" s="1" t="n">
-        <v>46376.08333333334</v>
+        <v>46376.70833333334</v>
       </c>
       <c r="M110" s="1" t="n">
-        <v>46376.75</v>
+        <v>46377.375</v>
       </c>
     </row>
     <row r="111">
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="K111" s="1" t="n">
-        <v>46383.16666666666</v>
+        <v>46383.79166666666</v>
       </c>
       <c r="L111" s="1" t="n">
-        <v>46383.375</v>
+        <v>46384</v>
       </c>
       <c r="M111" s="1" t="n">
-        <v>46384.04166666666</v>
+        <v>46384.66666666666</v>
       </c>
     </row>
     <row r="112">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="K112" s="1" t="n">
-        <v>46385.75</v>
+        <v>46386.375</v>
       </c>
       <c r="L112" s="1" t="n">
-        <v>46385.79166666666</v>
+        <v>46386.41666666666</v>
       </c>
       <c r="M112" s="1" t="n">
-        <v>46386.79166666666</v>
+        <v>46387.41666666666</v>
       </c>
     </row>
     <row r="113">
@@ -6630,13 +6630,13 @@
         </is>
       </c>
       <c r="K113" s="1" t="n">
-        <v>46387.41666666666</v>
+        <v>46388.04166666666</v>
       </c>
       <c r="L113" s="1" t="n">
-        <v>46387.45833333334</v>
+        <v>46388.08333333334</v>
       </c>
       <c r="M113" s="1" t="n">
-        <v>46388.08333333334</v>
+        <v>46388.70833333334</v>
       </c>
     </row>
     <row r="114">
@@ -6685,13 +6685,13 @@
         </is>
       </c>
       <c r="K114" s="1" t="n">
-        <v>46389.58333333334</v>
+        <v>46390.20833333334</v>
       </c>
       <c r="L114" s="1" t="n">
-        <v>46389.79166666666</v>
+        <v>46390.41666666666</v>
       </c>
       <c r="M114" s="1" t="n">
-        <v>46390.45833333334</v>
+        <v>46391.08333333334</v>
       </c>
     </row>
     <row r="115">
@@ -6740,13 +6740,13 @@
         </is>
       </c>
       <c r="K115" s="1" t="n">
-        <v>46397.45833333334</v>
+        <v>46398.08333333334</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>46397.54166666666</v>
+        <v>46398.16666666666</v>
       </c>
       <c r="M115" s="1" t="n">
-        <v>46398.375</v>
+        <v>46399</v>
       </c>
     </row>
     <row r="116">
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46399.45833333334</v>
+        <v>46400.08333333334</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>46399.54166666666</v>
+        <v>46400.16666666666</v>
       </c>
       <c r="M116" s="1" t="n">
-        <v>46400.04166666666</v>
+        <v>46400.66666666666</v>
       </c>
     </row>
     <row r="117">
@@ -6850,13 +6850,13 @@
         </is>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46404.04166666666</v>
+        <v>46404.66666666666</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>46404.08333333334</v>
+        <v>46404.70833333334</v>
       </c>
       <c r="M117" s="1" t="n">
-        <v>46404.75</v>
+        <v>46405.375</v>
       </c>
     </row>
     <row r="118">
@@ -6901,13 +6901,13 @@
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" s="1" t="n">
-        <v>46411.16666666666</v>
+        <v>46411.79166666666</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>46411.375</v>
+        <v>46412</v>
       </c>
       <c r="M118" s="1" t="n">
-        <v>46412.04166666666</v>
+        <v>46412.66666666666</v>
       </c>
     </row>
     <row r="119">
@@ -7014,10 +7014,10 @@
         <v>46300.54166666666</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>46303.79166666666</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="M120" s="1" t="n">
-        <v>46305.79166666666</v>
+        <v>46307.25</v>
       </c>
     </row>
     <row r="121">
@@ -7066,13 +7066,13 @@
         </is>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46307.54166666666</v>
+        <v>46309</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>46307.58333333334</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="M121" s="1" t="n">
-        <v>46308.29166666666</v>
+        <v>46309.75</v>
       </c>
     </row>
     <row r="122">
@@ -7121,13 +7121,13 @@
         </is>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46307.54166666666</v>
+        <v>46309</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>46307.58333333334</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>46308.66666666666</v>
+        <v>46310.125</v>
       </c>
     </row>
     <row r="123">
@@ -7176,13 +7176,13 @@
         </is>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46310.25</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>46308.83333333334</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="M123" s="1" t="n">
-        <v>46309.08333333334</v>
+        <v>46310.54166666666</v>
       </c>
     </row>
     <row r="124">
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46309.5</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>46309.58333333334</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="M124" s="1" t="n">
-        <v>46309.91666666666</v>
+        <v>46311.375</v>
       </c>
     </row>
     <row r="125">
@@ -7286,13 +7286,13 @@
         </is>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46315</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>46315.16666666666</v>
+        <v>46316.625</v>
       </c>
       <c r="M125" s="1" t="n">
-        <v>46315.79166666666</v>
+        <v>46317.25</v>
       </c>
     </row>
     <row r="126">
@@ -7341,13 +7341,13 @@
         </is>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46317.58333333334</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>46317.625</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="M126" s="1" t="n">
-        <v>46317.875</v>
+        <v>46319.33333333334</v>
       </c>
     </row>
     <row r="127">
@@ -7396,13 +7396,13 @@
         </is>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46318.16666666666</v>
+        <v>46319.625</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>46318.29166666666</v>
+        <v>46319.75</v>
       </c>
       <c r="M127" s="1" t="n">
-        <v>46319.79166666666</v>
+        <v>46321.25</v>
       </c>
     </row>
     <row r="128">
@@ -7451,13 +7451,13 @@
         </is>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46320</v>
+        <v>46321.45833333334</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>46320.04166666666</v>
+        <v>46321.5</v>
       </c>
       <c r="M128" s="1" t="n">
-        <v>46320.45833333334</v>
+        <v>46321.91666666666</v>
       </c>
     </row>
     <row r="129">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="K129" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46323.5</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>46322.20833333334</v>
+        <v>46323.66666666666</v>
       </c>
       <c r="M129" s="1" t="n">
-        <v>46322.75</v>
+        <v>46324.20833333334</v>
       </c>
     </row>
     <row r="130">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="K130" s="1" t="n">
-        <v>46327.875</v>
+        <v>46329.33333333334</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>46327.91666666666</v>
+        <v>46329.375</v>
       </c>
       <c r="M130" s="1" t="n">
-        <v>46329</v>
+        <v>46330.45833333334</v>
       </c>
     </row>
     <row r="131">
@@ -7616,13 +7616,13 @@
         </is>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46329.125</v>
+        <v>46330.58333333334</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>46329.16666666666</v>
+        <v>46330.625</v>
       </c>
       <c r="M131" s="1" t="n">
-        <v>46329.41666666666</v>
+        <v>46330.875</v>
       </c>
     </row>
     <row r="132">
@@ -7671,13 +7671,13 @@
         </is>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46329.875</v>
+        <v>46331.33333333334</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>46329.95833333334</v>
+        <v>46331.41666666666</v>
       </c>
       <c r="M132" s="1" t="n">
-        <v>46330.29166666666</v>
+        <v>46331.75</v>
       </c>
     </row>
     <row r="133">
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46335.33333333334</v>
+        <v>46336.79166666666</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>46335.5</v>
+        <v>46336.95833333334</v>
       </c>
       <c r="M133" s="1" t="n">
-        <v>46336.125</v>
+        <v>46337.58333333334</v>
       </c>
     </row>
     <row r="134">
@@ -7781,13 +7781,13 @@
         </is>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46338.08333333334</v>
+        <v>46339.54166666666</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>46338.125</v>
+        <v>46339.58333333334</v>
       </c>
       <c r="M134" s="1" t="n">
-        <v>46338.375</v>
+        <v>46339.83333333334</v>
       </c>
     </row>
     <row r="135">
@@ -7836,13 +7836,13 @@
         </is>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46338.70833333334</v>
+        <v>46340.16666666666</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>46338.83333333334</v>
+        <v>46340.29166666666</v>
       </c>
       <c r="M135" s="1" t="n">
-        <v>46340.33333333334</v>
+        <v>46341.79166666666</v>
       </c>
     </row>
     <row r="136">
@@ -7891,13 +7891,13 @@
         </is>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46340.66666666666</v>
+        <v>46342.125</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>46340.70833333334</v>
+        <v>46342.16666666666</v>
       </c>
       <c r="M136" s="1" t="n">
-        <v>46341.125</v>
+        <v>46342.58333333334</v>
       </c>
     </row>
     <row r="137">
@@ -7946,13 +7946,13 @@
         </is>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46342.75</v>
+        <v>46344.20833333334</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>46342.91666666666</v>
+        <v>46344.375</v>
       </c>
       <c r="M137" s="1" t="n">
-        <v>46343.45833333334</v>
+        <v>46344.91666666666</v>
       </c>
     </row>
     <row r="138">
@@ -8001,13 +8001,13 @@
         </is>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46348.58333333334</v>
+        <v>46350.04166666666</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>46348.625</v>
+        <v>46350.08333333334</v>
       </c>
       <c r="M138" s="1" t="n">
-        <v>46349.70833333334</v>
+        <v>46351.16666666666</v>
       </c>
     </row>
     <row r="139">
@@ -8056,13 +8056,13 @@
         </is>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46349.875</v>
+        <v>46351.33333333334</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>46349.91666666666</v>
+        <v>46351.375</v>
       </c>
       <c r="M139" s="1" t="n">
-        <v>46350.16666666666</v>
+        <v>46351.625</v>
       </c>
     </row>
     <row r="140">
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46350.625</v>
+        <v>46352.08333333334</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>46350.70833333334</v>
+        <v>46352.16666666666</v>
       </c>
       <c r="M140" s="1" t="n">
-        <v>46351.04166666666</v>
+        <v>46352.5</v>
       </c>
     </row>
     <row r="141">
@@ -8166,13 +8166,13 @@
         </is>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46356.08333333334</v>
+        <v>46357.54166666666</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>46356.25</v>
+        <v>46357.70833333334</v>
       </c>
       <c r="M141" s="1" t="n">
-        <v>46356.875</v>
+        <v>46358.33333333334</v>
       </c>
     </row>
     <row r="142">
@@ -8221,13 +8221,13 @@
         </is>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46358.83333333334</v>
+        <v>46360.29166666666</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>46358.875</v>
+        <v>46360.33333333334</v>
       </c>
       <c r="M142" s="1" t="n">
-        <v>46359.125</v>
+        <v>46360.58333333334</v>
       </c>
     </row>
     <row r="143">
@@ -8276,13 +8276,13 @@
         </is>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46359.45833333334</v>
+        <v>46360.91666666666</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>46359.58333333334</v>
+        <v>46361.04166666666</v>
       </c>
       <c r="M143" s="1" t="n">
-        <v>46361.08333333334</v>
+        <v>46362.54166666666</v>
       </c>
     </row>
     <row r="144">
@@ -8331,13 +8331,13 @@
         </is>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46361.41666666666</v>
+        <v>46362.875</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>46361.45833333334</v>
+        <v>46362.91666666666</v>
       </c>
       <c r="M144" s="1" t="n">
-        <v>46361.875</v>
+        <v>46363.33333333334</v>
       </c>
     </row>
     <row r="145">
@@ -8386,13 +8386,13 @@
         </is>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46363.5</v>
+        <v>46364.95833333334</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>46363.66666666666</v>
+        <v>46365.125</v>
       </c>
       <c r="M145" s="1" t="n">
-        <v>46364.20833333334</v>
+        <v>46365.66666666666</v>
       </c>
     </row>
     <row r="146">
@@ -8441,13 +8441,13 @@
         </is>
       </c>
       <c r="K146" s="1" t="n">
-        <v>46369.83333333334</v>
+        <v>46371.29166666666</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>46369.875</v>
+        <v>46371.33333333334</v>
       </c>
       <c r="M146" s="1" t="n">
-        <v>46370.95833333334</v>
+        <v>46372.41666666666</v>
       </c>
     </row>
     <row r="147">
@@ -8496,13 +8496,13 @@
         </is>
       </c>
       <c r="K147" s="1" t="n">
-        <v>46371.08333333334</v>
+        <v>46372.54166666666</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>46371.125</v>
+        <v>46372.58333333334</v>
       </c>
       <c r="M147" s="1" t="n">
-        <v>46371.375</v>
+        <v>46372.83333333334</v>
       </c>
     </row>
     <row r="148">
@@ -8551,13 +8551,13 @@
         </is>
       </c>
       <c r="K148" s="1" t="n">
-        <v>46371.79166666666</v>
+        <v>46373.25</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>46371.875</v>
+        <v>46373.33333333334</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>46372.20833333334</v>
+        <v>46373.66666666666</v>
       </c>
     </row>
     <row r="149">
@@ -8606,13 +8606,13 @@
         </is>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46377.29166666666</v>
+        <v>46378.75</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>46377.45833333334</v>
+        <v>46378.91666666666</v>
       </c>
       <c r="M149" s="1" t="n">
-        <v>46378.08333333334</v>
+        <v>46379.54166666666</v>
       </c>
     </row>
     <row r="150">
@@ -8661,13 +8661,13 @@
         </is>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46379.875</v>
+        <v>46381.33333333334</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>46379.91666666666</v>
+        <v>46381.375</v>
       </c>
       <c r="M150" s="1" t="n">
-        <v>46380.16666666666</v>
+        <v>46381.625</v>
       </c>
     </row>
     <row r="151">
@@ -8716,13 +8716,13 @@
         </is>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46380.45833333334</v>
+        <v>46381.91666666666</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>46380.58333333334</v>
+        <v>46382.04166666666</v>
       </c>
       <c r="M151" s="1" t="n">
-        <v>46382.08333333334</v>
+        <v>46383.54166666666</v>
       </c>
     </row>
     <row r="152">
@@ -8771,13 +8771,13 @@
         </is>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46382.29166666666</v>
+        <v>46383.75</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>46382.33333333334</v>
+        <v>46383.79166666666</v>
       </c>
       <c r="M152" s="1" t="n">
-        <v>46382.75</v>
+        <v>46384.20833333334</v>
       </c>
     </row>
     <row r="153">
@@ -8822,13 +8822,13 @@
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" s="1" t="n">
-        <v>46384.33333333334</v>
+        <v>46385.79166666666</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>46384.5</v>
+        <v>46385.95833333334</v>
       </c>
       <c r="M153" s="1" t="n">
-        <v>46385.04166666666</v>
+        <v>46386.5</v>
       </c>
     </row>
     <row r="154">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="K158" s="1" t="n">
-        <v>46300.08333333334</v>
+        <v>46300.25</v>
       </c>
       <c r="L158" s="1" t="n">
         <v>46302.95833333334</v>
@@ -9207,13 +9207,13 @@
         </is>
       </c>
       <c r="K160" s="1" t="n">
-        <v>46312.625</v>
+        <v>46312.25</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>46312.70833333334</v>
+        <v>46312.33333333334</v>
       </c>
       <c r="M160" s="1" t="n">
-        <v>46313.20833333334</v>
+        <v>46312.83333333334</v>
       </c>
     </row>
     <row r="161">
@@ -9262,13 +9262,13 @@
         </is>
       </c>
       <c r="K161" s="1" t="n">
-        <v>46317.20833333334</v>
+        <v>46316.5625</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>46317.25</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="M161" s="1" t="n">
-        <v>46317.91666666666</v>
+        <v>46317.27083333334</v>
       </c>
     </row>
     <row r="162">
@@ -9317,13 +9317,13 @@
         </is>
       </c>
       <c r="K162" s="1" t="n">
-        <v>46324.33333333334</v>
+        <v>46323.33333333334</v>
       </c>
       <c r="L162" s="1" t="n">
-        <v>46324.54166666666</v>
+        <v>46323.54166666666</v>
       </c>
       <c r="M162" s="1" t="n">
-        <v>46325.20833333334</v>
+        <v>46324.20833333334</v>
       </c>
     </row>
     <row r="163">
@@ -9372,13 +9372,13 @@
         </is>
       </c>
       <c r="K163" s="1" t="n">
-        <v>46326.16666666666</v>
+        <v>46325.60416666666</v>
       </c>
       <c r="L163" s="1" t="n">
-        <v>46326.20833333334</v>
+        <v>46325.64583333334</v>
       </c>
       <c r="M163" s="1" t="n">
-        <v>46327.20833333334</v>
+        <v>46326.64583333334</v>
       </c>
     </row>
     <row r="164">
@@ -9427,13 +9427,13 @@
         </is>
       </c>
       <c r="K164" s="1" t="n">
-        <v>46327.83333333334</v>
+        <v>46326.9375</v>
       </c>
       <c r="L164" s="1" t="n">
-        <v>46327.875</v>
+        <v>46326.97916666666</v>
       </c>
       <c r="M164" s="1" t="n">
-        <v>46328.5</v>
+        <v>46327.60416666666</v>
       </c>
     </row>
     <row r="165">
@@ -9482,13 +9482,13 @@
         </is>
       </c>
       <c r="K165" s="1" t="n">
-        <v>46330</v>
+        <v>46329.10416666666</v>
       </c>
       <c r="L165" s="1" t="n">
-        <v>46330.20833333334</v>
+        <v>46329.3125</v>
       </c>
       <c r="M165" s="1" t="n">
-        <v>46330.875</v>
+        <v>46329.97916666666</v>
       </c>
     </row>
     <row r="166">
@@ -9537,13 +9537,13 @@
         </is>
       </c>
       <c r="K166" s="1" t="n">
-        <v>46337.875</v>
+        <v>46336.97916666666</v>
       </c>
       <c r="L166" s="1" t="n">
-        <v>46337.95833333334</v>
+        <v>46337.0625</v>
       </c>
       <c r="M166" s="1" t="n">
-        <v>46338.79166666666</v>
+        <v>46337.89583333334</v>
       </c>
     </row>
     <row r="167">
@@ -9592,13 +9592,13 @@
         </is>
       </c>
       <c r="K167" s="1" t="n">
-        <v>46339.875</v>
+        <v>46338.97916666666</v>
       </c>
       <c r="L167" s="1" t="n">
-        <v>46339.95833333334</v>
+        <v>46339.0625</v>
       </c>
       <c r="M167" s="1" t="n">
-        <v>46340.45833333334</v>
+        <v>46339.5625</v>
       </c>
     </row>
     <row r="168">
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46344.45833333334</v>
+        <v>46343.5625</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>46344.5</v>
+        <v>46343.60416666666</v>
       </c>
       <c r="M168" s="1" t="n">
-        <v>46345.16666666666</v>
+        <v>46344.27083333334</v>
       </c>
     </row>
     <row r="169">
@@ -9702,13 +9702,13 @@
         </is>
       </c>
       <c r="K169" s="1" t="n">
-        <v>46351.58333333334</v>
+        <v>46350.6875</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>46351.79166666666</v>
+        <v>46350.89583333334</v>
       </c>
       <c r="M169" s="1" t="n">
-        <v>46352.45833333334</v>
+        <v>46351.5625</v>
       </c>
     </row>
     <row r="170">
@@ -9757,13 +9757,13 @@
         </is>
       </c>
       <c r="K170" s="1" t="n">
-        <v>46354.16666666666</v>
+        <v>46353.27083333334</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>46354.20833333334</v>
+        <v>46353.3125</v>
       </c>
       <c r="M170" s="1" t="n">
-        <v>46355.20833333334</v>
+        <v>46354.3125</v>
       </c>
     </row>
     <row r="171">
@@ -9812,13 +9812,13 @@
         </is>
       </c>
       <c r="K171" s="1" t="n">
-        <v>46355.83333333334</v>
+        <v>46354.9375</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>46355.875</v>
+        <v>46354.97916666666</v>
       </c>
       <c r="M171" s="1" t="n">
-        <v>46356.5</v>
+        <v>46355.60416666666</v>
       </c>
     </row>
     <row r="172">
@@ -9867,13 +9867,13 @@
         </is>
       </c>
       <c r="K172" s="1" t="n">
-        <v>46358</v>
+        <v>46357.10416666666</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>46358.20833333334</v>
+        <v>46357.3125</v>
       </c>
       <c r="M172" s="1" t="n">
-        <v>46358.875</v>
+        <v>46357.97916666666</v>
       </c>
     </row>
     <row r="173">
@@ -9922,13 +9922,13 @@
         </is>
       </c>
       <c r="K173" s="1" t="n">
-        <v>46365.875</v>
+        <v>46364.97916666666</v>
       </c>
       <c r="L173" s="1" t="n">
-        <v>46365.95833333334</v>
+        <v>46365.0625</v>
       </c>
       <c r="M173" s="1" t="n">
-        <v>46366.79166666666</v>
+        <v>46365.89583333334</v>
       </c>
     </row>
     <row r="174">
@@ -9977,13 +9977,13 @@
         </is>
       </c>
       <c r="K174" s="1" t="n">
-        <v>46367.875</v>
+        <v>46366.97916666666</v>
       </c>
       <c r="L174" s="1" t="n">
-        <v>46367.95833333334</v>
+        <v>46367.0625</v>
       </c>
       <c r="M174" s="1" t="n">
-        <v>46368.45833333334</v>
+        <v>46367.5625</v>
       </c>
     </row>
     <row r="175">
@@ -10032,13 +10032,13 @@
         </is>
       </c>
       <c r="K175" s="1" t="n">
-        <v>46372.45833333334</v>
+        <v>46371.5625</v>
       </c>
       <c r="L175" s="1" t="n">
-        <v>46372.5</v>
+        <v>46371.60416666666</v>
       </c>
       <c r="M175" s="1" t="n">
-        <v>46373.16666666666</v>
+        <v>46372.27083333334</v>
       </c>
     </row>
     <row r="176">
@@ -10083,13 +10083,13 @@
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" s="1" t="n">
-        <v>46379.58333333334</v>
+        <v>46378.6875</v>
       </c>
       <c r="L176" s="1" t="n">
-        <v>46379.79166666666</v>
+        <v>46378.89583333334</v>
       </c>
       <c r="M176" s="1" t="n">
-        <v>46380.45833333334</v>
+        <v>46379.5625</v>
       </c>
     </row>
     <row r="177">
@@ -16836,13 +16836,13 @@
         </is>
       </c>
       <c r="K299" s="1" t="n">
-        <v>46301.125</v>
+        <v>46302.54166666666</v>
       </c>
       <c r="L299" s="1" t="n">
-        <v>46301.16666666666</v>
+        <v>46302.58333333334</v>
       </c>
       <c r="M299" s="1" t="n">
-        <v>46302.16666666666</v>
+        <v>46303.75</v>
       </c>
     </row>
     <row r="300">
@@ -16891,13 +16891,13 @@
         </is>
       </c>
       <c r="K300" s="1" t="n">
-        <v>46302.29166666666</v>
+        <v>46303.875</v>
       </c>
       <c r="L300" s="1" t="n">
-        <v>46302.33333333334</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="M300" s="1" t="n">
-        <v>46302.70833333334</v>
+        <v>46304.25</v>
       </c>
     </row>
     <row r="301">
@@ -16946,13 +16946,13 @@
         </is>
       </c>
       <c r="K301" s="1" t="n">
-        <v>46307.6875</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="L301" s="1" t="n">
-        <v>46307.85416666666</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="M301" s="1" t="n">
-        <v>46308.5625</v>
+        <v>46310.10416666666</v>
       </c>
     </row>
     <row r="302">
@@ -17001,13 +17001,13 @@
         </is>
       </c>
       <c r="K302" s="1" t="n">
-        <v>46310.20833333334</v>
+        <v>46311.75</v>
       </c>
       <c r="L302" s="1" t="n">
-        <v>46310.25</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="M302" s="1" t="n">
-        <v>46310.54166666666</v>
+        <v>46312.08333333334</v>
       </c>
     </row>
     <row r="303">
@@ -17056,13 +17056,13 @@
         </is>
       </c>
       <c r="K303" s="1" t="n">
-        <v>46310.66666666666</v>
+        <v>46312.20833333334</v>
       </c>
       <c r="L303" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46312.33333333334</v>
       </c>
       <c r="M303" s="1" t="n">
-        <v>46312.04166666666</v>
+        <v>46313.58333333334</v>
       </c>
     </row>
     <row r="304">
@@ -17111,13 +17111,13 @@
         </is>
       </c>
       <c r="K304" s="1" t="n">
-        <v>46312.25</v>
+        <v>46313.79166666666</v>
       </c>
       <c r="L304" s="1" t="n">
-        <v>46312.29166666666</v>
+        <v>46313.83333333334</v>
       </c>
       <c r="M304" s="1" t="n">
-        <v>46312.75</v>
+        <v>46314.29166666666</v>
       </c>
     </row>
     <row r="305">
@@ -17166,13 +17166,13 @@
         </is>
       </c>
       <c r="K305" s="1" t="n">
-        <v>46316.54166666666</v>
+        <v>46318.08333333334</v>
       </c>
       <c r="L305" s="1" t="n">
-        <v>46316.60416666666</v>
+        <v>46318.14583333334</v>
       </c>
       <c r="M305" s="1" t="n">
-        <v>46317.0625</v>
+        <v>46318.60416666666</v>
       </c>
     </row>
     <row r="306">
@@ -17221,13 +17221,13 @@
         </is>
       </c>
       <c r="K306" s="1" t="n">
-        <v>46318.33333333334</v>
+        <v>46319.875</v>
       </c>
       <c r="L306" s="1" t="n">
-        <v>46318.375</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="M306" s="1" t="n">
-        <v>46318.875</v>
+        <v>46320.41666666666</v>
       </c>
     </row>
     <row r="307">
@@ -17276,13 +17276,13 @@
         </is>
       </c>
       <c r="K307" s="1" t="n">
-        <v>46321.83333333334</v>
+        <v>46322.41666666666</v>
       </c>
       <c r="L307" s="1" t="n">
-        <v>46321.875</v>
+        <v>46322.45833333334</v>
       </c>
       <c r="M307" s="1" t="n">
-        <v>46322.58333333334</v>
+        <v>46323.16666666666</v>
       </c>
     </row>
     <row r="308">
@@ -17331,13 +17331,13 @@
         </is>
       </c>
       <c r="K308" s="1" t="n">
-        <v>46322.79166666666</v>
+        <v>46323.375</v>
       </c>
       <c r="L308" s="1" t="n">
-        <v>46322.83333333334</v>
+        <v>46323.41666666666</v>
       </c>
       <c r="M308" s="1" t="n">
-        <v>46323.16666666666</v>
+        <v>46323.75</v>
       </c>
     </row>
     <row r="309">
@@ -17386,13 +17386,13 @@
         </is>
       </c>
       <c r="K309" s="1" t="n">
-        <v>46326</v>
+        <v>46326.58333333334</v>
       </c>
       <c r="L309" s="1" t="n">
-        <v>46326.04166666666</v>
+        <v>46326.625</v>
       </c>
       <c r="M309" s="1" t="n">
-        <v>46326.41666666666</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="310">
@@ -17441,13 +17441,13 @@
         </is>
       </c>
       <c r="K310" s="1" t="n">
-        <v>46328.875</v>
+        <v>46329.45833333334</v>
       </c>
       <c r="L310" s="1" t="n">
-        <v>46329.04166666666</v>
+        <v>46329.625</v>
       </c>
       <c r="M310" s="1" t="n">
-        <v>46329.58333333334</v>
+        <v>46330.16666666666</v>
       </c>
     </row>
     <row r="311">
@@ -17496,13 +17496,13 @@
         </is>
       </c>
       <c r="K311" s="1" t="n">
-        <v>46331.375</v>
+        <v>46331.95833333334</v>
       </c>
       <c r="L311" s="1" t="n">
-        <v>46331.41666666666</v>
+        <v>46332</v>
       </c>
       <c r="M311" s="1" t="n">
-        <v>46331.66666666666</v>
+        <v>46332.25</v>
       </c>
     </row>
     <row r="312">
@@ -17551,13 +17551,13 @@
         </is>
       </c>
       <c r="K312" s="1" t="n">
-        <v>46332.08333333334</v>
+        <v>46332.66666666666</v>
       </c>
       <c r="L312" s="1" t="n">
-        <v>46332.20833333334</v>
+        <v>46332.79166666666</v>
       </c>
       <c r="M312" s="1" t="n">
-        <v>46333.33333333334</v>
+        <v>46333.91666666666</v>
       </c>
     </row>
     <row r="313">
@@ -17606,13 +17606,13 @@
         </is>
       </c>
       <c r="K313" s="1" t="n">
-        <v>46333.66666666666</v>
+        <v>46334.25</v>
       </c>
       <c r="L313" s="1" t="n">
-        <v>46333.70833333334</v>
+        <v>46334.29166666666</v>
       </c>
       <c r="M313" s="1" t="n">
-        <v>46334.04166666666</v>
+        <v>46334.625</v>
       </c>
     </row>
     <row r="314">
@@ -17661,13 +17661,13 @@
         </is>
       </c>
       <c r="K314" s="1" t="n">
-        <v>46337.91666666666</v>
+        <v>46338.5</v>
       </c>
       <c r="L314" s="1" t="n">
-        <v>46337.95833333334</v>
+        <v>46338.54166666666</v>
       </c>
       <c r="M314" s="1" t="n">
-        <v>46338.375</v>
+        <v>46338.95833333334</v>
       </c>
     </row>
     <row r="315">
@@ -17716,13 +17716,13 @@
         </is>
       </c>
       <c r="K315" s="1" t="n">
-        <v>46338.625</v>
+        <v>46339.20833333334</v>
       </c>
       <c r="L315" s="1" t="n">
-        <v>46338.625</v>
+        <v>46339.20833333334</v>
       </c>
       <c r="M315" s="1" t="n">
-        <v>46339</v>
+        <v>46339.58333333334</v>
       </c>
     </row>
     <row r="316">
@@ -17771,13 +17771,13 @@
         </is>
       </c>
       <c r="K316" s="1" t="n">
-        <v>46340.25</v>
+        <v>46340.83333333334</v>
       </c>
       <c r="L316" s="1" t="n">
-        <v>46340.25</v>
+        <v>46340.83333333334</v>
       </c>
       <c r="M316" s="1" t="n">
-        <v>46340.5</v>
+        <v>46341.08333333334</v>
       </c>
     </row>
     <row r="317">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="K317" s="1" t="n">
-        <v>46342.83333333334</v>
+        <v>46343.41666666666</v>
       </c>
       <c r="L317" s="1" t="n">
-        <v>46342.875</v>
+        <v>46343.45833333334</v>
       </c>
       <c r="M317" s="1" t="n">
-        <v>46343.58333333334</v>
+        <v>46344.16666666666</v>
       </c>
     </row>
     <row r="318">
@@ -17881,13 +17881,13 @@
         </is>
       </c>
       <c r="K318" s="1" t="n">
-        <v>46343.79166666666</v>
+        <v>46344.375</v>
       </c>
       <c r="L318" s="1" t="n">
-        <v>46343.83333333334</v>
+        <v>46344.41666666666</v>
       </c>
       <c r="M318" s="1" t="n">
-        <v>46344.16666666666</v>
+        <v>46344.75</v>
       </c>
     </row>
     <row r="319">
@@ -17936,13 +17936,13 @@
         </is>
       </c>
       <c r="K319" s="1" t="n">
-        <v>46347</v>
+        <v>46347.58333333334</v>
       </c>
       <c r="L319" s="1" t="n">
-        <v>46347.04166666666</v>
+        <v>46347.625</v>
       </c>
       <c r="M319" s="1" t="n">
-        <v>46347.41666666666</v>
+        <v>46348</v>
       </c>
     </row>
     <row r="320">
@@ -17991,13 +17991,13 @@
         </is>
       </c>
       <c r="K320" s="1" t="n">
-        <v>46349.875</v>
+        <v>46350.45833333334</v>
       </c>
       <c r="L320" s="1" t="n">
-        <v>46350.04166666666</v>
+        <v>46350.625</v>
       </c>
       <c r="M320" s="1" t="n">
-        <v>46350.58333333334</v>
+        <v>46351.16666666666</v>
       </c>
     </row>
     <row r="321">
@@ -18046,13 +18046,13 @@
         </is>
       </c>
       <c r="K321" s="1" t="n">
-        <v>46352.375</v>
+        <v>46352.95833333334</v>
       </c>
       <c r="L321" s="1" t="n">
-        <v>46352.41666666666</v>
+        <v>46353</v>
       </c>
       <c r="M321" s="1" t="n">
-        <v>46352.66666666666</v>
+        <v>46353.25</v>
       </c>
     </row>
     <row r="322">
@@ -18101,13 +18101,13 @@
         </is>
       </c>
       <c r="K322" s="1" t="n">
-        <v>46353.08333333334</v>
+        <v>46353.66666666666</v>
       </c>
       <c r="L322" s="1" t="n">
-        <v>46353.20833333334</v>
+        <v>46353.79166666666</v>
       </c>
       <c r="M322" s="1" t="n">
-        <v>46354.33333333334</v>
+        <v>46354.91666666666</v>
       </c>
     </row>
     <row r="323">
@@ -18156,13 +18156,13 @@
         </is>
       </c>
       <c r="K323" s="1" t="n">
-        <v>46354.66666666666</v>
+        <v>46355.25</v>
       </c>
       <c r="L323" s="1" t="n">
-        <v>46354.70833333334</v>
+        <v>46355.29166666666</v>
       </c>
       <c r="M323" s="1" t="n">
-        <v>46355.04166666666</v>
+        <v>46355.625</v>
       </c>
     </row>
     <row r="324">
@@ -18211,13 +18211,13 @@
         </is>
       </c>
       <c r="K324" s="1" t="n">
-        <v>46358.91666666666</v>
+        <v>46359.5</v>
       </c>
       <c r="L324" s="1" t="n">
-        <v>46358.95833333334</v>
+        <v>46359.54166666666</v>
       </c>
       <c r="M324" s="1" t="n">
-        <v>46359.375</v>
+        <v>46359.95833333334</v>
       </c>
     </row>
     <row r="325">
@@ -18266,13 +18266,13 @@
         </is>
       </c>
       <c r="K325" s="1" t="n">
-        <v>46359.625</v>
+        <v>46360.20833333334</v>
       </c>
       <c r="L325" s="1" t="n">
-        <v>46359.625</v>
+        <v>46360.20833333334</v>
       </c>
       <c r="M325" s="1" t="n">
-        <v>46360</v>
+        <v>46360.58333333334</v>
       </c>
     </row>
     <row r="326">
@@ -18321,13 +18321,13 @@
         </is>
       </c>
       <c r="K326" s="1" t="n">
-        <v>46361.25</v>
+        <v>46361.83333333334</v>
       </c>
       <c r="L326" s="1" t="n">
-        <v>46361.25</v>
+        <v>46361.83333333334</v>
       </c>
       <c r="M326" s="1" t="n">
-        <v>46361.5</v>
+        <v>46362.08333333334</v>
       </c>
     </row>
     <row r="327">
@@ -18376,13 +18376,13 @@
         </is>
       </c>
       <c r="K327" s="1" t="n">
-        <v>46363.83333333334</v>
+        <v>46364.41666666666</v>
       </c>
       <c r="L327" s="1" t="n">
-        <v>46363.875</v>
+        <v>46364.45833333334</v>
       </c>
       <c r="M327" s="1" t="n">
-        <v>46364.58333333334</v>
+        <v>46365.16666666666</v>
       </c>
     </row>
     <row r="328">
@@ -18431,13 +18431,13 @@
         </is>
       </c>
       <c r="K328" s="1" t="n">
-        <v>46364.79166666666</v>
+        <v>46365.375</v>
       </c>
       <c r="L328" s="1" t="n">
-        <v>46364.83333333334</v>
+        <v>46365.41666666666</v>
       </c>
       <c r="M328" s="1" t="n">
-        <v>46365.16666666666</v>
+        <v>46365.75</v>
       </c>
     </row>
     <row r="329">
@@ -18486,13 +18486,13 @@
         </is>
       </c>
       <c r="K329" s="1" t="n">
-        <v>46368</v>
+        <v>46368.58333333334</v>
       </c>
       <c r="L329" s="1" t="n">
-        <v>46368.04166666666</v>
+        <v>46368.625</v>
       </c>
       <c r="M329" s="1" t="n">
-        <v>46368.41666666666</v>
+        <v>46369</v>
       </c>
     </row>
     <row r="330">
@@ -18541,13 +18541,13 @@
         </is>
       </c>
       <c r="K330" s="1" t="n">
-        <v>46370.875</v>
+        <v>46371.45833333334</v>
       </c>
       <c r="L330" s="1" t="n">
-        <v>46371.04166666666</v>
+        <v>46371.625</v>
       </c>
       <c r="M330" s="1" t="n">
-        <v>46371.58333333334</v>
+        <v>46372.16666666666</v>
       </c>
     </row>
     <row r="331">
@@ -18596,13 +18596,13 @@
         </is>
       </c>
       <c r="K331" s="1" t="n">
-        <v>46373.375</v>
+        <v>46373.95833333334</v>
       </c>
       <c r="L331" s="1" t="n">
-        <v>46373.41666666666</v>
+        <v>46374</v>
       </c>
       <c r="M331" s="1" t="n">
-        <v>46373.66666666666</v>
+        <v>46374.25</v>
       </c>
     </row>
     <row r="332">
@@ -18651,13 +18651,13 @@
         </is>
       </c>
       <c r="K332" s="1" t="n">
-        <v>46374.08333333334</v>
+        <v>46374.66666666666</v>
       </c>
       <c r="L332" s="1" t="n">
-        <v>46374.20833333334</v>
+        <v>46374.79166666666</v>
       </c>
       <c r="M332" s="1" t="n">
-        <v>46375.33333333334</v>
+        <v>46375.91666666666</v>
       </c>
     </row>
     <row r="333">
@@ -18706,13 +18706,13 @@
         </is>
       </c>
       <c r="K333" s="1" t="n">
-        <v>46375.66666666666</v>
+        <v>46376.25</v>
       </c>
       <c r="L333" s="1" t="n">
-        <v>46375.70833333334</v>
+        <v>46376.29166666666</v>
       </c>
       <c r="M333" s="1" t="n">
-        <v>46376.04166666666</v>
+        <v>46376.625</v>
       </c>
     </row>
     <row r="334">
@@ -18761,13 +18761,13 @@
         </is>
       </c>
       <c r="K334" s="1" t="n">
-        <v>46379.91666666666</v>
+        <v>46380.5</v>
       </c>
       <c r="L334" s="1" t="n">
-        <v>46379.95833333334</v>
+        <v>46380.54166666666</v>
       </c>
       <c r="M334" s="1" t="n">
-        <v>46380.375</v>
+        <v>46380.95833333334</v>
       </c>
     </row>
     <row r="335">
@@ -18816,13 +18816,13 @@
         </is>
       </c>
       <c r="K335" s="1" t="n">
-        <v>46380.625</v>
+        <v>46381.20833333334</v>
       </c>
       <c r="L335" s="1" t="n">
-        <v>46380.625</v>
+        <v>46381.20833333334</v>
       </c>
       <c r="M335" s="1" t="n">
-        <v>46381</v>
+        <v>46381.58333333334</v>
       </c>
     </row>
     <row r="336">
@@ -18871,13 +18871,13 @@
         </is>
       </c>
       <c r="K336" s="1" t="n">
-        <v>46382.25</v>
+        <v>46382.83333333334</v>
       </c>
       <c r="L336" s="1" t="n">
-        <v>46382.25</v>
+        <v>46382.83333333334</v>
       </c>
       <c r="M336" s="1" t="n">
-        <v>46382.5</v>
+        <v>46383.08333333334</v>
       </c>
     </row>
     <row r="337">
@@ -18926,13 +18926,13 @@
         </is>
       </c>
       <c r="K337" s="1" t="n">
-        <v>46384.83333333334</v>
+        <v>46385.41666666666</v>
       </c>
       <c r="L337" s="1" t="n">
-        <v>46384.875</v>
+        <v>46385.45833333334</v>
       </c>
       <c r="M337" s="1" t="n">
-        <v>46385.58333333334</v>
+        <v>46386.16666666666</v>
       </c>
     </row>
     <row r="338">
@@ -18981,13 +18981,13 @@
         </is>
       </c>
       <c r="K338" s="1" t="n">
-        <v>46385.79166666666</v>
+        <v>46386.375</v>
       </c>
       <c r="L338" s="1" t="n">
-        <v>46385.83333333334</v>
+        <v>46386.41666666666</v>
       </c>
       <c r="M338" s="1" t="n">
-        <v>46386.16666666666</v>
+        <v>46386.75</v>
       </c>
     </row>
     <row r="339">
@@ -19036,13 +19036,13 @@
         </is>
       </c>
       <c r="K339" s="1" t="n">
-        <v>46389</v>
+        <v>46389.58333333334</v>
       </c>
       <c r="L339" s="1" t="n">
-        <v>46389.04166666666</v>
+        <v>46389.625</v>
       </c>
       <c r="M339" s="1" t="n">
-        <v>46389.41666666666</v>
+        <v>46390</v>
       </c>
     </row>
     <row r="340">
@@ -19091,13 +19091,13 @@
         </is>
       </c>
       <c r="K340" s="1" t="n">
-        <v>46391.875</v>
+        <v>46392.45833333334</v>
       </c>
       <c r="L340" s="1" t="n">
-        <v>46392.04166666666</v>
+        <v>46392.625</v>
       </c>
       <c r="M340" s="1" t="n">
-        <v>46392.58333333334</v>
+        <v>46393.16666666666</v>
       </c>
     </row>
     <row r="341">
@@ -19146,13 +19146,13 @@
         </is>
       </c>
       <c r="K341" s="1" t="n">
-        <v>46394.375</v>
+        <v>46394.95833333334</v>
       </c>
       <c r="L341" s="1" t="n">
-        <v>46394.41666666666</v>
+        <v>46395</v>
       </c>
       <c r="M341" s="1" t="n">
-        <v>46394.66666666666</v>
+        <v>46395.25</v>
       </c>
     </row>
     <row r="342">
@@ -19201,13 +19201,13 @@
         </is>
       </c>
       <c r="K342" s="1" t="n">
-        <v>46395.08333333334</v>
+        <v>46395.66666666666</v>
       </c>
       <c r="L342" s="1" t="n">
-        <v>46395.20833333334</v>
+        <v>46395.79166666666</v>
       </c>
       <c r="M342" s="1" t="n">
-        <v>46396.33333333334</v>
+        <v>46396.91666666666</v>
       </c>
     </row>
     <row r="343">
@@ -19256,13 +19256,13 @@
         </is>
       </c>
       <c r="K343" s="1" t="n">
-        <v>46396.66666666666</v>
+        <v>46397.25</v>
       </c>
       <c r="L343" s="1" t="n">
-        <v>46396.70833333334</v>
+        <v>46397.29166666666</v>
       </c>
       <c r="M343" s="1" t="n">
-        <v>46397.04166666666</v>
+        <v>46397.625</v>
       </c>
     </row>
     <row r="344">
@@ -19311,13 +19311,13 @@
         </is>
       </c>
       <c r="K344" s="1" t="n">
-        <v>46400.91666666666</v>
+        <v>46401.5</v>
       </c>
       <c r="L344" s="1" t="n">
-        <v>46400.95833333334</v>
+        <v>46401.54166666666</v>
       </c>
       <c r="M344" s="1" t="n">
-        <v>46401.375</v>
+        <v>46401.95833333334</v>
       </c>
     </row>
     <row r="345">
@@ -19366,13 +19366,13 @@
         </is>
       </c>
       <c r="K345" s="1" t="n">
-        <v>46401.625</v>
+        <v>46402.20833333334</v>
       </c>
       <c r="L345" s="1" t="n">
-        <v>46401.625</v>
+        <v>46402.20833333334</v>
       </c>
       <c r="M345" s="1" t="n">
-        <v>46402</v>
+        <v>46402.58333333334</v>
       </c>
     </row>
     <row r="346">
@@ -19417,13 +19417,13 @@
       </c>
       <c r="J346" t="inlineStr"/>
       <c r="K346" s="1" t="n">
-        <v>46403.25</v>
+        <v>46403.83333333334</v>
       </c>
       <c r="L346" s="1" t="n">
-        <v>46403.25</v>
+        <v>46403.83333333334</v>
       </c>
       <c r="M346" s="1" t="n">
-        <v>46403.5</v>
+        <v>46404.08333333334</v>
       </c>
     </row>
     <row r="347">
@@ -28843,7 +28843,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>TAO06</t>
+          <t>TAO04</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -29008,7 +29008,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>NGB02</t>
+          <t>NGB06</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -29131,10 +29131,10 @@
         <v>46329.20833333334</v>
       </c>
       <c r="L523" s="1" t="n">
-        <v>46334.25</v>
+        <v>46339.20833333334</v>
       </c>
       <c r="M523" s="1" t="n">
-        <v>46337.25</v>
+        <v>46346.20833333334</v>
       </c>
     </row>
     <row r="524">
@@ -33581,7 +33581,7 @@
         <v>46303</v>
       </c>
       <c r="M604" s="1" t="n">
-        <v>46303.66666666666</v>
+        <v>46303.625</v>
       </c>
     </row>
     <row r="605">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>PUS09</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -33630,13 +33630,13 @@
         </is>
       </c>
       <c r="K605" s="1" t="n">
+        <v>46304.625</v>
+      </c>
+      <c r="L605" s="1" t="n">
         <v>46304.66666666666</v>
       </c>
-      <c r="L605" s="1" t="n">
-        <v>46304.70833333334</v>
-      </c>
       <c r="M605" s="1" t="n">
-        <v>46305.70833333334</v>
+        <v>46305.66666666666</v>
       </c>
     </row>
     <row r="606">
@@ -44726,7 +44726,7 @@
         <v>46302.09583333333</v>
       </c>
       <c r="M807" s="1" t="n">
-        <v>46303.125</v>
+        <v>46303.20833333334</v>
       </c>
     </row>
     <row r="808">
@@ -44775,13 +44775,13 @@
         </is>
       </c>
       <c r="K808" s="1" t="n">
-        <v>46304.3125</v>
+        <v>46304.5</v>
       </c>
       <c r="L808" s="1" t="n">
-        <v>46307.91666666666</v>
+        <v>46306.66666666666</v>
       </c>
       <c r="M808" s="1" t="n">
-        <v>46308.91666666666</v>
+        <v>46307.66666666666</v>
       </c>
     </row>
     <row r="809">
@@ -44830,13 +44830,13 @@
         </is>
       </c>
       <c r="K809" s="1" t="n">
-        <v>46313.125</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="L809" s="1" t="n">
-        <v>46314.25</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="M809" s="1" t="n">
-        <v>46314.75</v>
+        <v>46313.45833333334</v>
       </c>
     </row>
     <row r="810">
@@ -44885,13 +44885,13 @@
         </is>
       </c>
       <c r="K810" s="1" t="n">
-        <v>46316.33333333334</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="L810" s="1" t="n">
-        <v>46316.375</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="M810" s="1" t="n">
-        <v>46316.79166666666</v>
+        <v>46315.5</v>
       </c>
     </row>
     <row r="811">
@@ -44940,13 +44940,13 @@
         </is>
       </c>
       <c r="K811" s="1" t="n">
-        <v>46316.95833333334</v>
+        <v>46315.66666666666</v>
       </c>
       <c r="L811" s="1" t="n">
-        <v>46317.08333333334</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="M811" s="1" t="n">
-        <v>46318.08333333334</v>
+        <v>46316.79166666666</v>
       </c>
     </row>
     <row r="812">
@@ -44995,13 +44995,13 @@
         </is>
       </c>
       <c r="K812" s="1" t="n">
-        <v>46318.33333333334</v>
+        <v>46317.04166666666</v>
       </c>
       <c r="L812" s="1" t="n">
-        <v>46318.375</v>
+        <v>46317.08333333334</v>
       </c>
       <c r="M812" s="1" t="n">
-        <v>46318.79166666666</v>
+        <v>46317.5</v>
       </c>
     </row>
     <row r="813">
@@ -45050,13 +45050,13 @@
         </is>
       </c>
       <c r="K813" s="1" t="n">
-        <v>46320.29166666666</v>
+        <v>46319</v>
       </c>
       <c r="L813" s="1" t="n">
-        <v>46321.41666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="M813" s="1" t="n">
-        <v>46321.91666666666</v>
+        <v>46320.625</v>
       </c>
     </row>
     <row r="814">
@@ -45105,13 +45105,13 @@
         </is>
       </c>
       <c r="K814" s="1" t="n">
-        <v>46328.02083333334</v>
+        <v>46326.72916666666</v>
       </c>
       <c r="L814" s="1" t="n">
-        <v>46328.08333333334</v>
+        <v>46326.79166666666</v>
       </c>
       <c r="M814" s="1" t="n">
-        <v>46328.33333333334</v>
+        <v>46327.04166666666</v>
       </c>
     </row>
     <row r="815">
@@ -45160,13 +45160,13 @@
         </is>
       </c>
       <c r="K815" s="1" t="n">
-        <v>46329.29166666666</v>
+        <v>46327.97916666666</v>
       </c>
       <c r="L815" s="1" t="n">
-        <v>46329.35416666666</v>
+        <v>46328.04166666666</v>
       </c>
       <c r="M815" s="1" t="n">
-        <v>46329.77083333334</v>
+        <v>46328.45833333334</v>
       </c>
     </row>
     <row r="816">
@@ -45215,13 +45215,13 @@
         </is>
       </c>
       <c r="K816" s="1" t="n">
-        <v>46330.125</v>
+        <v>46328.8125</v>
       </c>
       <c r="L816" s="1" t="n">
-        <v>46330.16666666666</v>
+        <v>46328.85416666666</v>
       </c>
       <c r="M816" s="1" t="n">
-        <v>46330.79166666666</v>
+        <v>46329.47916666666</v>
       </c>
     </row>
     <row r="817">
@@ -45270,13 +45270,13 @@
         </is>
       </c>
       <c r="K817" s="1" t="n">
-        <v>46331.875</v>
+        <v>46330.52083333334</v>
       </c>
       <c r="L817" s="1" t="n">
-        <v>46332.04166666666</v>
+        <v>46330.6875</v>
       </c>
       <c r="M817" s="1" t="n">
-        <v>46333.04166666666</v>
+        <v>46331.6875</v>
       </c>
     </row>
     <row r="818">
@@ -45325,13 +45325,13 @@
         </is>
       </c>
       <c r="K818" s="1" t="n">
-        <v>46337.25</v>
+        <v>46335.91666666666</v>
       </c>
       <c r="L818" s="1" t="n">
-        <v>46337.375</v>
+        <v>46336.04166666666</v>
       </c>
       <c r="M818" s="1" t="n">
-        <v>46337.875</v>
+        <v>46336.54166666666</v>
       </c>
     </row>
     <row r="819">
@@ -45380,13 +45380,13 @@
         </is>
       </c>
       <c r="K819" s="1" t="n">
-        <v>46339.45833333334</v>
+        <v>46338.125</v>
       </c>
       <c r="L819" s="1" t="n">
-        <v>46339.5</v>
+        <v>46338.16666666666</v>
       </c>
       <c r="M819" s="1" t="n">
-        <v>46339.91666666666</v>
+        <v>46338.58333333334</v>
       </c>
     </row>
     <row r="820">
@@ -45435,13 +45435,13 @@
         </is>
       </c>
       <c r="K820" s="1" t="n">
-        <v>46340.08333333334</v>
+        <v>46338.75</v>
       </c>
       <c r="L820" s="1" t="n">
-        <v>46340.20833333334</v>
+        <v>46338.875</v>
       </c>
       <c r="M820" s="1" t="n">
-        <v>46341.20833333334</v>
+        <v>46339.875</v>
       </c>
     </row>
     <row r="821">
@@ -45490,13 +45490,13 @@
         </is>
       </c>
       <c r="K821" s="1" t="n">
-        <v>46341.45833333334</v>
+        <v>46340.125</v>
       </c>
       <c r="L821" s="1" t="n">
-        <v>46341.5</v>
+        <v>46340.16666666666</v>
       </c>
       <c r="M821" s="1" t="n">
-        <v>46341.91666666666</v>
+        <v>46340.58333333334</v>
       </c>
     </row>
     <row r="822">
@@ -45545,13 +45545,13 @@
         </is>
       </c>
       <c r="K822" s="1" t="n">
-        <v>46343.41666666666</v>
+        <v>46342.08333333334</v>
       </c>
       <c r="L822" s="1" t="n">
-        <v>46343.54166666666</v>
+        <v>46342.20833333334</v>
       </c>
       <c r="M822" s="1" t="n">
-        <v>46344.04166666666</v>
+        <v>46342.70833333334</v>
       </c>
     </row>
     <row r="823">
@@ -45600,13 +45600,13 @@
         </is>
       </c>
       <c r="K823" s="1" t="n">
-        <v>46349.0625</v>
+        <v>46347.72916666666</v>
       </c>
       <c r="L823" s="1" t="n">
-        <v>46349.125</v>
+        <v>46347.79166666666</v>
       </c>
       <c r="M823" s="1" t="n">
-        <v>46349.375</v>
+        <v>46348.04166666666</v>
       </c>
     </row>
     <row r="824">
@@ -45655,13 +45655,13 @@
         </is>
       </c>
       <c r="K824" s="1" t="n">
-        <v>46350.32083333333</v>
+        <v>46348.97916666666</v>
       </c>
       <c r="L824" s="1" t="n">
-        <v>46350.38333333333</v>
+        <v>46349.04166666666</v>
       </c>
       <c r="M824" s="1" t="n">
-        <v>46350.8</v>
+        <v>46349.45833333334</v>
       </c>
     </row>
     <row r="825">
@@ -45710,13 +45710,13 @@
         </is>
       </c>
       <c r="K825" s="1" t="n">
-        <v>46351.14166666667</v>
+        <v>46349.79166666666</v>
       </c>
       <c r="L825" s="1" t="n">
-        <v>46351.18333333333</v>
+        <v>46349.83333333334</v>
       </c>
       <c r="M825" s="1" t="n">
-        <v>46351.80833333333</v>
+        <v>46350.45833333334</v>
       </c>
     </row>
     <row r="826">
@@ -45765,13 +45765,13 @@
         </is>
       </c>
       <c r="K826" s="1" t="n">
-        <v>46352.89166666667</v>
+        <v>46351.54166666666</v>
       </c>
       <c r="L826" s="1" t="n">
-        <v>46353.05833333333</v>
+        <v>46351.70833333334</v>
       </c>
       <c r="M826" s="1" t="n">
-        <v>46354.05833333333</v>
+        <v>46352.70833333334</v>
       </c>
     </row>
     <row r="827">
@@ -45820,13 +45820,13 @@
         </is>
       </c>
       <c r="K827" s="1" t="n">
-        <v>46358.26666666667</v>
+        <v>46356.91666666666</v>
       </c>
       <c r="L827" s="1" t="n">
-        <v>46358.39166666667</v>
+        <v>46357.04166666666</v>
       </c>
       <c r="M827" s="1" t="n">
-        <v>46358.89166666667</v>
+        <v>46357.54166666666</v>
       </c>
     </row>
     <row r="828">
@@ -45875,13 +45875,13 @@
         </is>
       </c>
       <c r="K828" s="1" t="n">
-        <v>46360.475</v>
+        <v>46359.125</v>
       </c>
       <c r="L828" s="1" t="n">
-        <v>46360.51666666667</v>
+        <v>46359.16666666666</v>
       </c>
       <c r="M828" s="1" t="n">
-        <v>46360.93333333333</v>
+        <v>46359.58333333334</v>
       </c>
     </row>
     <row r="829">
@@ -45930,13 +45930,13 @@
         </is>
       </c>
       <c r="K829" s="1" t="n">
-        <v>46361.1</v>
+        <v>46359.75</v>
       </c>
       <c r="L829" s="1" t="n">
-        <v>46361.225</v>
+        <v>46359.875</v>
       </c>
       <c r="M829" s="1" t="n">
-        <v>46362.225</v>
+        <v>46360.875</v>
       </c>
     </row>
     <row r="830">
@@ -45985,13 +45985,13 @@
         </is>
       </c>
       <c r="K830" s="1" t="n">
-        <v>46362.475</v>
+        <v>46361.125</v>
       </c>
       <c r="L830" s="1" t="n">
-        <v>46362.51666666667</v>
+        <v>46361.16666666666</v>
       </c>
       <c r="M830" s="1" t="n">
-        <v>46362.93333333333</v>
+        <v>46361.58333333334</v>
       </c>
     </row>
     <row r="831">
@@ -46040,13 +46040,13 @@
         </is>
       </c>
       <c r="K831" s="1" t="n">
-        <v>46364.43333333333</v>
+        <v>46363.08333333334</v>
       </c>
       <c r="L831" s="1" t="n">
-        <v>46364.55833333333</v>
+        <v>46363.20833333334</v>
       </c>
       <c r="M831" s="1" t="n">
-        <v>46365.05833333333</v>
+        <v>46363.70833333334</v>
       </c>
     </row>
     <row r="832">
@@ -46095,13 +46095,13 @@
         </is>
       </c>
       <c r="K832" s="1" t="n">
-        <v>46370.07916666667</v>
+        <v>46368.72916666666</v>
       </c>
       <c r="L832" s="1" t="n">
-        <v>46370.14166666667</v>
+        <v>46368.79166666666</v>
       </c>
       <c r="M832" s="1" t="n">
-        <v>46370.39166666667</v>
+        <v>46369.04166666666</v>
       </c>
     </row>
     <row r="833">
@@ -46150,13 +46150,13 @@
         </is>
       </c>
       <c r="K833" s="1" t="n">
-        <v>46371.3375</v>
+        <v>46369.9875</v>
       </c>
       <c r="L833" s="1" t="n">
-        <v>46371.4</v>
+        <v>46370.05</v>
       </c>
       <c r="M833" s="1" t="n">
-        <v>46371.81666666667</v>
+        <v>46370.46666666667</v>
       </c>
     </row>
     <row r="834">
@@ -46205,13 +46205,13 @@
         </is>
       </c>
       <c r="K834" s="1" t="n">
-        <v>46372.15833333333</v>
+        <v>46370.80833333333</v>
       </c>
       <c r="L834" s="1" t="n">
-        <v>46372.2</v>
+        <v>46370.85</v>
       </c>
       <c r="M834" s="1" t="n">
-        <v>46372.825</v>
+        <v>46371.475</v>
       </c>
     </row>
     <row r="835">
@@ -46260,13 +46260,13 @@
         </is>
       </c>
       <c r="K835" s="1" t="n">
-        <v>46373.90833333333</v>
+        <v>46372.55833333333</v>
       </c>
       <c r="L835" s="1" t="n">
-        <v>46374.075</v>
+        <v>46372.725</v>
       </c>
       <c r="M835" s="1" t="n">
-        <v>46375.075</v>
+        <v>46373.725</v>
       </c>
     </row>
     <row r="836">
@@ -46315,13 +46315,13 @@
         </is>
       </c>
       <c r="K836" s="1" t="n">
-        <v>46379.28333333333</v>
+        <v>46377.93333333333</v>
       </c>
       <c r="L836" s="1" t="n">
-        <v>46379.40833333333</v>
+        <v>46378.05833333333</v>
       </c>
       <c r="M836" s="1" t="n">
-        <v>46379.90833333333</v>
+        <v>46378.55833333333</v>
       </c>
     </row>
     <row r="837">
@@ -46370,13 +46370,13 @@
         </is>
       </c>
       <c r="K837" s="1" t="n">
-        <v>46381.49166666667</v>
+        <v>46380.14166666667</v>
       </c>
       <c r="L837" s="1" t="n">
-        <v>46381.53333333333</v>
+        <v>46380.18333333333</v>
       </c>
       <c r="M837" s="1" t="n">
-        <v>46381.95</v>
+        <v>46380.6</v>
       </c>
     </row>
     <row r="838">
@@ -46425,13 +46425,13 @@
         </is>
       </c>
       <c r="K838" s="1" t="n">
-        <v>46382.11666666667</v>
+        <v>46380.76666666667</v>
       </c>
       <c r="L838" s="1" t="n">
-        <v>46382.24166666667</v>
+        <v>46380.89166666667</v>
       </c>
       <c r="M838" s="1" t="n">
-        <v>46383.24166666667</v>
+        <v>46381.89166666667</v>
       </c>
     </row>
     <row r="839">
@@ -46480,13 +46480,13 @@
         </is>
       </c>
       <c r="K839" s="1" t="n">
-        <v>46383.49166666667</v>
+        <v>46382.14166666667</v>
       </c>
       <c r="L839" s="1" t="n">
-        <v>46383.53333333333</v>
+        <v>46382.18333333333</v>
       </c>
       <c r="M839" s="1" t="n">
-        <v>46383.95</v>
+        <v>46382.6</v>
       </c>
     </row>
     <row r="840">
@@ -46531,13 +46531,13 @@
       </c>
       <c r="J840" t="inlineStr"/>
       <c r="K840" s="1" t="n">
-        <v>46385.45</v>
+        <v>46384.1</v>
       </c>
       <c r="L840" s="1" t="n">
-        <v>46385.575</v>
+        <v>46384.225</v>
       </c>
       <c r="M840" s="1" t="n">
-        <v>46386.075</v>
+        <v>46384.725</v>
       </c>
     </row>
     <row r="841">
@@ -46754,7 +46754,7 @@
         <v>46301.95833333334</v>
       </c>
       <c r="L844" s="1" t="n">
-        <v>46302.125</v>
+        <v>46302.07083333333</v>
       </c>
       <c r="M844" s="1" t="n">
         <v>46303.45833333334</v>
@@ -48513,7 +48513,7 @@
         <v>46303.79166666666</v>
       </c>
       <c r="M876" s="1" t="n">
-        <v>46304.20833333334</v>
+        <v>46304.25</v>
       </c>
     </row>
     <row r="877">
@@ -48562,13 +48562,13 @@
         </is>
       </c>
       <c r="K877" s="1" t="n">
-        <v>46305.70833333334</v>
+        <v>46305.75</v>
       </c>
       <c r="L877" s="1" t="n">
-        <v>46306.875</v>
+        <v>46306.91666666666</v>
       </c>
       <c r="M877" s="1" t="n">
-        <v>46307.375</v>
+        <v>46307.41666666666</v>
       </c>
     </row>
     <row r="878">
@@ -48617,13 +48617,13 @@
         </is>
       </c>
       <c r="K878" s="1" t="n">
-        <v>46312.39583333334</v>
+        <v>46312.4375</v>
       </c>
       <c r="L878" s="1" t="n">
-        <v>46312.45833333334</v>
+        <v>46312.5</v>
       </c>
       <c r="M878" s="1" t="n">
-        <v>46312.70833333334</v>
+        <v>46312.75</v>
       </c>
     </row>
     <row r="879">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="K879" s="1" t="n">
-        <v>46313.64583333334</v>
+        <v>46313.6875</v>
       </c>
       <c r="L879" s="1" t="n">
-        <v>46313.70833333334</v>
+        <v>46313.75</v>
       </c>
       <c r="M879" s="1" t="n">
-        <v>46314.125</v>
+        <v>46314.16666666666</v>
       </c>
     </row>
     <row r="880">
@@ -48727,13 +48727,13 @@
         </is>
       </c>
       <c r="K880" s="1" t="n">
-        <v>46314.45833333334</v>
+        <v>46314.5</v>
       </c>
       <c r="L880" s="1" t="n">
-        <v>46314.5</v>
+        <v>46314.54166666666</v>
       </c>
       <c r="M880" s="1" t="n">
-        <v>46315.125</v>
+        <v>46315.16666666666</v>
       </c>
     </row>
     <row r="881">
@@ -48782,13 +48782,13 @@
         </is>
       </c>
       <c r="K881" s="1" t="n">
-        <v>46316.20833333334</v>
+        <v>46316.25</v>
       </c>
       <c r="L881" s="1" t="n">
-        <v>46316.375</v>
+        <v>46318.41666666666</v>
       </c>
       <c r="M881" s="1" t="n">
-        <v>46317.375</v>
+        <v>46319.41666666666</v>
       </c>
     </row>
     <row r="882">
@@ -48837,13 +48837,13 @@
         </is>
       </c>
       <c r="K882" s="1" t="n">
-        <v>46321.58333333334</v>
+        <v>46323.625</v>
       </c>
       <c r="L882" s="1" t="n">
-        <v>46321.70833333334</v>
+        <v>46324.75</v>
       </c>
       <c r="M882" s="1" t="n">
-        <v>46322.20833333334</v>
+        <v>46325.25</v>
       </c>
     </row>
     <row r="883">
@@ -48892,13 +48892,13 @@
         </is>
       </c>
       <c r="K883" s="1" t="n">
-        <v>46323.79166666666</v>
+        <v>46326.83333333334</v>
       </c>
       <c r="L883" s="1" t="n">
-        <v>46323.83333333334</v>
+        <v>46326.875</v>
       </c>
       <c r="M883" s="1" t="n">
-        <v>46324.25</v>
+        <v>46327.29166666666</v>
       </c>
     </row>
     <row r="884">
@@ -48947,13 +48947,13 @@
         </is>
       </c>
       <c r="K884" s="1" t="n">
-        <v>46324.41666666666</v>
+        <v>46327.45833333334</v>
       </c>
       <c r="L884" s="1" t="n">
-        <v>46324.54166666666</v>
+        <v>46327.58333333334</v>
       </c>
       <c r="M884" s="1" t="n">
-        <v>46325.54166666666</v>
+        <v>46328.58333333334</v>
       </c>
     </row>
     <row r="885">
@@ -49002,13 +49002,13 @@
         </is>
       </c>
       <c r="K885" s="1" t="n">
-        <v>46325.79166666666</v>
+        <v>46328.83333333334</v>
       </c>
       <c r="L885" s="1" t="n">
-        <v>46325.83333333334</v>
+        <v>46328.875</v>
       </c>
       <c r="M885" s="1" t="n">
-        <v>46326.25</v>
+        <v>46329.29166666666</v>
       </c>
     </row>
     <row r="886">
@@ -49057,13 +49057,13 @@
         </is>
       </c>
       <c r="K886" s="1" t="n">
-        <v>46327.75</v>
+        <v>46330.79166666666</v>
       </c>
       <c r="L886" s="1" t="n">
-        <v>46327.875</v>
+        <v>46331.91666666666</v>
       </c>
       <c r="M886" s="1" t="n">
-        <v>46328.375</v>
+        <v>46332.41666666666</v>
       </c>
     </row>
     <row r="887">
@@ -49112,13 +49112,13 @@
         </is>
       </c>
       <c r="K887" s="1" t="n">
-        <v>46334.9375</v>
+        <v>46338.97916666666</v>
       </c>
       <c r="L887" s="1" t="n">
-        <v>46335</v>
+        <v>46339.04166666666</v>
       </c>
       <c r="M887" s="1" t="n">
-        <v>46335.25</v>
+        <v>46339.29166666666</v>
       </c>
     </row>
     <row r="888">
@@ -49167,13 +49167,13 @@
         </is>
       </c>
       <c r="K888" s="1" t="n">
-        <v>46336.1875</v>
+        <v>46340.22916666666</v>
       </c>
       <c r="L888" s="1" t="n">
-        <v>46336.25</v>
+        <v>46340.29166666666</v>
       </c>
       <c r="M888" s="1" t="n">
-        <v>46336.66666666666</v>
+        <v>46340.70833333334</v>
       </c>
     </row>
     <row r="889">
@@ -49222,13 +49222,13 @@
         </is>
       </c>
       <c r="K889" s="1" t="n">
-        <v>46337</v>
+        <v>46341.04166666666</v>
       </c>
       <c r="L889" s="1" t="n">
-        <v>46337.04166666666</v>
+        <v>46341.08333333334</v>
       </c>
       <c r="M889" s="1" t="n">
-        <v>46337.66666666666</v>
+        <v>46341.70833333334</v>
       </c>
     </row>
     <row r="890">
@@ -49277,13 +49277,13 @@
         </is>
       </c>
       <c r="K890" s="1" t="n">
-        <v>46338.74722222222</v>
+        <v>46342.78888888889</v>
       </c>
       <c r="L890" s="1" t="n">
-        <v>46338.91388888889</v>
+        <v>46342.95555555556</v>
       </c>
       <c r="M890" s="1" t="n">
-        <v>46339.91388888889</v>
+        <v>46343.95555555556</v>
       </c>
     </row>
     <row r="891">
@@ -49332,13 +49332,13 @@
         </is>
       </c>
       <c r="K891" s="1" t="n">
-        <v>46344.12222222222</v>
+        <v>46348.16388888889</v>
       </c>
       <c r="L891" s="1" t="n">
-        <v>46344.24722222222</v>
+        <v>46348.28888888889</v>
       </c>
       <c r="M891" s="1" t="n">
-        <v>46344.74722222222</v>
+        <v>46348.78888888889</v>
       </c>
     </row>
     <row r="892">
@@ -49387,13 +49387,13 @@
         </is>
       </c>
       <c r="K892" s="1" t="n">
-        <v>46346.33055555556</v>
+        <v>46350.37222222222</v>
       </c>
       <c r="L892" s="1" t="n">
-        <v>46346.37222222222</v>
+        <v>46350.41388888889</v>
       </c>
       <c r="M892" s="1" t="n">
-        <v>46346.78888888889</v>
+        <v>46350.83055555556</v>
       </c>
     </row>
     <row r="893">
@@ -49442,13 +49442,13 @@
         </is>
       </c>
       <c r="K893" s="1" t="n">
-        <v>46346.95555555556</v>
+        <v>46350.99722222222</v>
       </c>
       <c r="L893" s="1" t="n">
-        <v>46347.08055555556</v>
+        <v>46351.12222222222</v>
       </c>
       <c r="M893" s="1" t="n">
-        <v>46348.08055555556</v>
+        <v>46352.12222222222</v>
       </c>
     </row>
     <row r="894">
@@ -49497,13 +49497,13 @@
         </is>
       </c>
       <c r="K894" s="1" t="n">
-        <v>46348.33055555556</v>
+        <v>46352.37222222222</v>
       </c>
       <c r="L894" s="1" t="n">
-        <v>46348.37222222222</v>
+        <v>46352.41388888889</v>
       </c>
       <c r="M894" s="1" t="n">
-        <v>46348.78888888889</v>
+        <v>46352.83055555556</v>
       </c>
     </row>
     <row r="895">
@@ -49552,13 +49552,13 @@
         </is>
       </c>
       <c r="K895" s="1" t="n">
-        <v>46350.28888888889</v>
+        <v>46354.33055555556</v>
       </c>
       <c r="L895" s="1" t="n">
-        <v>46350.41388888889</v>
+        <v>46354.45555555556</v>
       </c>
       <c r="M895" s="1" t="n">
-        <v>46350.91388888889</v>
+        <v>46354.95555555556</v>
       </c>
     </row>
     <row r="896">
@@ -49607,13 +49607,13 @@
         </is>
       </c>
       <c r="K896" s="1" t="n">
-        <v>46355.93472222222</v>
+        <v>46359.97638888889</v>
       </c>
       <c r="L896" s="1" t="n">
-        <v>46355.99722222222</v>
+        <v>46360.03888888889</v>
       </c>
       <c r="M896" s="1" t="n">
-        <v>46356.24722222222</v>
+        <v>46360.28888888889</v>
       </c>
     </row>
     <row r="897">
@@ -49662,13 +49662,13 @@
         </is>
       </c>
       <c r="K897" s="1" t="n">
-        <v>46357.18472222222</v>
+        <v>46361.22638888889</v>
       </c>
       <c r="L897" s="1" t="n">
-        <v>46357.24722222222</v>
+        <v>46361.28888888889</v>
       </c>
       <c r="M897" s="1" t="n">
-        <v>46357.66388888889</v>
+        <v>46361.70555555556</v>
       </c>
     </row>
     <row r="898">
@@ -49717,13 +49717,13 @@
         </is>
       </c>
       <c r="K898" s="1" t="n">
-        <v>46357.99722222222</v>
+        <v>46362.03888888889</v>
       </c>
       <c r="L898" s="1" t="n">
-        <v>46358.03888888889</v>
+        <v>46362.08055555556</v>
       </c>
       <c r="M898" s="1" t="n">
-        <v>46358.66388888889</v>
+        <v>46362.70555555556</v>
       </c>
     </row>
     <row r="899">
@@ -49772,13 +49772,13 @@
         </is>
       </c>
       <c r="K899" s="1" t="n">
-        <v>46359.74444444444</v>
+        <v>46363.78611111111</v>
       </c>
       <c r="L899" s="1" t="n">
-        <v>46359.91111111111</v>
+        <v>46363.95277777778</v>
       </c>
       <c r="M899" s="1" t="n">
-        <v>46360.91111111111</v>
+        <v>46364.95277777778</v>
       </c>
     </row>
     <row r="900">
@@ -49827,13 +49827,13 @@
         </is>
       </c>
       <c r="K900" s="1" t="n">
-        <v>46365.11944444444</v>
+        <v>46369.16111111111</v>
       </c>
       <c r="L900" s="1" t="n">
-        <v>46365.24444444444</v>
+        <v>46369.28611111111</v>
       </c>
       <c r="M900" s="1" t="n">
-        <v>46365.74444444444</v>
+        <v>46369.78611111111</v>
       </c>
     </row>
     <row r="901">
@@ -49882,13 +49882,13 @@
         </is>
       </c>
       <c r="K901" s="1" t="n">
-        <v>46367.32777777778</v>
+        <v>46371.36944444444</v>
       </c>
       <c r="L901" s="1" t="n">
-        <v>46367.36944444444</v>
+        <v>46371.41111111111</v>
       </c>
       <c r="M901" s="1" t="n">
-        <v>46367.78611111111</v>
+        <v>46371.82777777778</v>
       </c>
     </row>
     <row r="902">
@@ -49937,13 +49937,13 @@
         </is>
       </c>
       <c r="K902" s="1" t="n">
-        <v>46367.95277777778</v>
+        <v>46371.99444444444</v>
       </c>
       <c r="L902" s="1" t="n">
-        <v>46368.07777777778</v>
+        <v>46372.11944444444</v>
       </c>
       <c r="M902" s="1" t="n">
-        <v>46369.07777777778</v>
+        <v>46373.11944444444</v>
       </c>
     </row>
     <row r="903">
@@ -49992,13 +49992,13 @@
         </is>
       </c>
       <c r="K903" s="1" t="n">
-        <v>46369.32777777778</v>
+        <v>46373.36944444444</v>
       </c>
       <c r="L903" s="1" t="n">
-        <v>46369.36944444444</v>
+        <v>46373.41111111111</v>
       </c>
       <c r="M903" s="1" t="n">
-        <v>46369.78611111111</v>
+        <v>46373.82777777778</v>
       </c>
     </row>
     <row r="904">
@@ -50043,13 +50043,13 @@
       </c>
       <c r="J904" t="inlineStr"/>
       <c r="K904" s="1" t="n">
-        <v>46371.28611111111</v>
+        <v>46375.32777777778</v>
       </c>
       <c r="L904" s="1" t="n">
-        <v>46371.41111111111</v>
+        <v>46375.45277777778</v>
       </c>
       <c r="M904" s="1" t="n">
-        <v>46371.91111111111</v>
+        <v>46375.95277777778</v>
       </c>
     </row>
     <row r="905">
@@ -50214,7 +50214,7 @@
         <v>46300.9375</v>
       </c>
       <c r="M907" s="1" t="n">
-        <v>46301.41666666666</v>
+        <v>46301.875</v>
       </c>
     </row>
     <row r="908">
@@ -50263,13 +50263,13 @@
         </is>
       </c>
       <c r="K908" s="1" t="n">
-        <v>46303.58333333334</v>
+        <v>46304.25</v>
       </c>
       <c r="L908" s="1" t="n">
-        <v>46303.75</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="M908" s="1" t="n">
-        <v>46304.20833333334</v>
+        <v>46304.875</v>
       </c>
     </row>
     <row r="909">
@@ -50318,13 +50318,13 @@
         </is>
       </c>
       <c r="K909" s="1" t="n">
-        <v>46305.79166666666</v>
+        <v>46306.45833333334</v>
       </c>
       <c r="L909" s="1" t="n">
-        <v>46305.83333333334</v>
+        <v>46306.5</v>
       </c>
       <c r="M909" s="1" t="n">
-        <v>46306.08333333334</v>
+        <v>46306.75</v>
       </c>
     </row>
     <row r="910">
@@ -50373,13 +50373,13 @@
         </is>
       </c>
       <c r="K910" s="1" t="n">
-        <v>46306.25</v>
+        <v>46306.91666666666</v>
       </c>
       <c r="L910" s="1" t="n">
-        <v>46306.375</v>
+        <v>46307.04166666666</v>
       </c>
       <c r="M910" s="1" t="n">
-        <v>46307.875</v>
+        <v>46308.54166666666</v>
       </c>
     </row>
     <row r="911">
@@ -50428,13 +50428,13 @@
         </is>
       </c>
       <c r="K911" s="1" t="n">
-        <v>46308.04166666666</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="L911" s="1" t="n">
-        <v>46308.08333333334</v>
+        <v>46308.75</v>
       </c>
       <c r="M911" s="1" t="n">
-        <v>46308.33333333334</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="912">
@@ -50483,13 +50483,13 @@
         </is>
       </c>
       <c r="K912" s="1" t="n">
-        <v>46312.0625</v>
+        <v>46312.72916666666</v>
       </c>
       <c r="L912" s="1" t="n">
-        <v>46312.125</v>
+        <v>46312.79166666666</v>
       </c>
       <c r="M912" s="1" t="n">
-        <v>46312.58333333334</v>
+        <v>46313.25</v>
       </c>
     </row>
     <row r="913">
@@ -50538,13 +50538,13 @@
         </is>
       </c>
       <c r="K913" s="1" t="n">
-        <v>46313.375</v>
+        <v>46314.04166666666</v>
       </c>
       <c r="L913" s="1" t="n">
-        <v>46313.41666666666</v>
+        <v>46314.08333333334</v>
       </c>
       <c r="M913" s="1" t="n">
-        <v>46314</v>
+        <v>46314.66666666666</v>
       </c>
     </row>
     <row r="914">
@@ -50593,13 +50593,13 @@
         </is>
       </c>
       <c r="K914" s="1" t="n">
-        <v>46316.375</v>
+        <v>46317.04166666666</v>
       </c>
       <c r="L914" s="1" t="n">
-        <v>46316.41666666666</v>
+        <v>46317.08333333334</v>
       </c>
       <c r="M914" s="1" t="n">
-        <v>46317.125</v>
+        <v>46317.79166666666</v>
       </c>
     </row>
     <row r="915">
@@ -50648,13 +50648,13 @@
         </is>
       </c>
       <c r="K915" s="1" t="n">
-        <v>46317.41666666666</v>
+        <v>46318.08333333334</v>
       </c>
       <c r="L915" s="1" t="n">
-        <v>46317.47916666666</v>
+        <v>46318.14583333334</v>
       </c>
       <c r="M915" s="1" t="n">
-        <v>46317.75</v>
+        <v>46318.41666666666</v>
       </c>
     </row>
     <row r="916">
@@ -50703,13 +50703,13 @@
         </is>
       </c>
       <c r="K916" s="1" t="n">
-        <v>46320.66666666666</v>
+        <v>46321.33333333334</v>
       </c>
       <c r="L916" s="1" t="n">
-        <v>46320.70833333334</v>
+        <v>46321.375</v>
       </c>
       <c r="M916" s="1" t="n">
-        <v>46321.16666666666</v>
+        <v>46321.83333333334</v>
       </c>
     </row>
     <row r="917">
@@ -50758,13 +50758,13 @@
         </is>
       </c>
       <c r="K917" s="1" t="n">
-        <v>46323.375</v>
+        <v>46324.04166666666</v>
       </c>
       <c r="L917" s="1" t="n">
-        <v>46323.54166666666</v>
+        <v>46324.20833333334</v>
       </c>
       <c r="M917" s="1" t="n">
-        <v>46324</v>
+        <v>46324.66666666666</v>
       </c>
     </row>
     <row r="918">
@@ -50813,13 +50813,13 @@
         </is>
       </c>
       <c r="K918" s="1" t="n">
-        <v>46325.66666666666</v>
+        <v>46326.33333333334</v>
       </c>
       <c r="L918" s="1" t="n">
-        <v>46325.70833333334</v>
+        <v>46326.375</v>
       </c>
       <c r="M918" s="1" t="n">
-        <v>46325.95833333334</v>
+        <v>46326.625</v>
       </c>
     </row>
     <row r="919">
@@ -50868,13 +50868,13 @@
         </is>
       </c>
       <c r="K919" s="1" t="n">
-        <v>46326.125</v>
+        <v>46326.79166666666</v>
       </c>
       <c r="L919" s="1" t="n">
-        <v>46326.25</v>
+        <v>46326.91666666666</v>
       </c>
       <c r="M919" s="1" t="n">
-        <v>46327.75</v>
+        <v>46328.41666666666</v>
       </c>
     </row>
     <row r="920">
@@ -50923,13 +50923,13 @@
         </is>
       </c>
       <c r="K920" s="1" t="n">
-        <v>46327.95833333334</v>
+        <v>46328.625</v>
       </c>
       <c r="L920" s="1" t="n">
-        <v>46328</v>
+        <v>46328.66666666666</v>
       </c>
       <c r="M920" s="1" t="n">
-        <v>46328.25</v>
+        <v>46328.91666666666</v>
       </c>
     </row>
     <row r="921">
@@ -50978,13 +50978,13 @@
         </is>
       </c>
       <c r="K921" s="1" t="n">
-        <v>46332.08333333334</v>
+        <v>46332.75</v>
       </c>
       <c r="L921" s="1" t="n">
-        <v>46332.125</v>
+        <v>46332.79166666666</v>
       </c>
       <c r="M921" s="1" t="n">
-        <v>46332.58333333334</v>
+        <v>46333.25</v>
       </c>
     </row>
     <row r="922">
@@ -51033,13 +51033,13 @@
         </is>
       </c>
       <c r="K922" s="1" t="n">
-        <v>46333.33333333334</v>
+        <v>46334</v>
       </c>
       <c r="L922" s="1" t="n">
-        <v>46333.375</v>
+        <v>46334.04166666666</v>
       </c>
       <c r="M922" s="1" t="n">
-        <v>46333.95833333334</v>
+        <v>46334.625</v>
       </c>
     </row>
     <row r="923">
@@ -51088,13 +51088,13 @@
         </is>
       </c>
       <c r="K923" s="1" t="n">
-        <v>46336.41666666666</v>
+        <v>46337.08333333334</v>
       </c>
       <c r="L923" s="1" t="n">
-        <v>46336.45833333334</v>
+        <v>46337.125</v>
       </c>
       <c r="M923" s="1" t="n">
-        <v>46337.16666666666</v>
+        <v>46337.83333333334</v>
       </c>
     </row>
     <row r="924">
@@ -51143,13 +51143,13 @@
         </is>
       </c>
       <c r="K924" s="1" t="n">
-        <v>46337.5</v>
+        <v>46338.16666666666</v>
       </c>
       <c r="L924" s="1" t="n">
-        <v>46337.58333333334</v>
+        <v>46338.25</v>
       </c>
       <c r="M924" s="1" t="n">
-        <v>46337.83333333334</v>
+        <v>46338.5</v>
       </c>
     </row>
     <row r="925">
@@ -51198,13 +51198,13 @@
         </is>
       </c>
       <c r="K925" s="1" t="n">
-        <v>46340.75</v>
+        <v>46341.41666666666</v>
       </c>
       <c r="L925" s="1" t="n">
-        <v>46340.79166666666</v>
+        <v>46341.45833333334</v>
       </c>
       <c r="M925" s="1" t="n">
-        <v>46341.25</v>
+        <v>46341.91666666666</v>
       </c>
     </row>
     <row r="926">
@@ -51253,13 +51253,13 @@
         </is>
       </c>
       <c r="K926" s="1" t="n">
-        <v>46343.45833333334</v>
+        <v>46344.125</v>
       </c>
       <c r="L926" s="1" t="n">
-        <v>46343.625</v>
+        <v>46344.29166666666</v>
       </c>
       <c r="M926" s="1" t="n">
-        <v>46344.08333333334</v>
+        <v>46344.75</v>
       </c>
     </row>
     <row r="927">
@@ -51308,13 +51308,13 @@
         </is>
       </c>
       <c r="K927" s="1" t="n">
-        <v>46345.83333333334</v>
+        <v>46346.5</v>
       </c>
       <c r="L927" s="1" t="n">
-        <v>46345.875</v>
+        <v>46346.54166666666</v>
       </c>
       <c r="M927" s="1" t="n">
-        <v>46346.04166666666</v>
+        <v>46346.70833333334</v>
       </c>
     </row>
     <row r="928">
@@ -51363,13 +51363,13 @@
         </is>
       </c>
       <c r="K928" s="1" t="n">
-        <v>46346.29166666666</v>
+        <v>46346.95833333334</v>
       </c>
       <c r="L928" s="1" t="n">
-        <v>46346.41666666666</v>
+        <v>46347.08333333334</v>
       </c>
       <c r="M928" s="1" t="n">
-        <v>46347.75</v>
+        <v>46348.41666666666</v>
       </c>
     </row>
     <row r="929">
@@ -51418,13 +51418,13 @@
         </is>
       </c>
       <c r="K929" s="1" t="n">
-        <v>46348.25</v>
+        <v>46348.91666666666</v>
       </c>
       <c r="L929" s="1" t="n">
-        <v>46348.29166666666</v>
+        <v>46348.95833333334</v>
       </c>
       <c r="M929" s="1" t="n">
-        <v>46348.58333333334</v>
+        <v>46349.25</v>
       </c>
     </row>
     <row r="930">
@@ -51473,13 +51473,13 @@
         </is>
       </c>
       <c r="K930" s="1" t="n">
-        <v>46352.66666666666</v>
+        <v>46353.33333333334</v>
       </c>
       <c r="L930" s="1" t="n">
-        <v>46352.70833333334</v>
+        <v>46353.375</v>
       </c>
       <c r="M930" s="1" t="n">
-        <v>46353.16666666666</v>
+        <v>46353.83333333334</v>
       </c>
     </row>
     <row r="931">
@@ -51528,13 +51528,13 @@
         </is>
       </c>
       <c r="K931" s="1" t="n">
-        <v>46354.25</v>
+        <v>46354.91666666666</v>
       </c>
       <c r="L931" s="1" t="n">
-        <v>46354.29166666666</v>
+        <v>46354.95833333334</v>
       </c>
       <c r="M931" s="1" t="n">
-        <v>46354.875</v>
+        <v>46355.54166666666</v>
       </c>
     </row>
     <row r="932">
@@ -51583,13 +51583,13 @@
         </is>
       </c>
       <c r="K932" s="1" t="n">
-        <v>46357.41666666666</v>
+        <v>46358.08333333334</v>
       </c>
       <c r="L932" s="1" t="n">
-        <v>46357.45833333334</v>
+        <v>46358.125</v>
       </c>
       <c r="M932" s="1" t="n">
-        <v>46358.16666666666</v>
+        <v>46358.83333333334</v>
       </c>
     </row>
     <row r="933">
@@ -51638,13 +51638,13 @@
         </is>
       </c>
       <c r="K933" s="1" t="n">
-        <v>46358.5</v>
+        <v>46359.16666666666</v>
       </c>
       <c r="L933" s="1" t="n">
-        <v>46358.58333333334</v>
+        <v>46359.25</v>
       </c>
       <c r="M933" s="1" t="n">
-        <v>46358.83333333334</v>
+        <v>46359.5</v>
       </c>
     </row>
     <row r="934">
@@ -51693,13 +51693,13 @@
         </is>
       </c>
       <c r="K934" s="1" t="n">
-        <v>46361.75</v>
+        <v>46362.41666666666</v>
       </c>
       <c r="L934" s="1" t="n">
-        <v>46361.79166666666</v>
+        <v>46362.45833333334</v>
       </c>
       <c r="M934" s="1" t="n">
-        <v>46362.25</v>
+        <v>46362.91666666666</v>
       </c>
     </row>
     <row r="935">
@@ -51748,13 +51748,13 @@
         </is>
       </c>
       <c r="K935" s="1" t="n">
-        <v>46364.45833333334</v>
+        <v>46365.125</v>
       </c>
       <c r="L935" s="1" t="n">
-        <v>46364.625</v>
+        <v>46365.29166666666</v>
       </c>
       <c r="M935" s="1" t="n">
-        <v>46365.08333333334</v>
+        <v>46365.75</v>
       </c>
     </row>
     <row r="936">
@@ -51803,13 +51803,13 @@
         </is>
       </c>
       <c r="K936" s="1" t="n">
-        <v>46366.83333333334</v>
+        <v>46367.5</v>
       </c>
       <c r="L936" s="1" t="n">
-        <v>46366.875</v>
+        <v>46367.54166666666</v>
       </c>
       <c r="M936" s="1" t="n">
-        <v>46367.04166666666</v>
+        <v>46367.70833333334</v>
       </c>
     </row>
     <row r="937">
@@ -51858,13 +51858,13 @@
         </is>
       </c>
       <c r="K937" s="1" t="n">
-        <v>46367.29166666666</v>
+        <v>46367.95833333334</v>
       </c>
       <c r="L937" s="1" t="n">
-        <v>46367.41666666666</v>
+        <v>46368.08333333334</v>
       </c>
       <c r="M937" s="1" t="n">
-        <v>46368.75</v>
+        <v>46369.41666666666</v>
       </c>
     </row>
     <row r="938">
@@ -51913,13 +51913,13 @@
         </is>
       </c>
       <c r="K938" s="1" t="n">
-        <v>46369.25</v>
+        <v>46369.91666666666</v>
       </c>
       <c r="L938" s="1" t="n">
-        <v>46369.29166666666</v>
+        <v>46369.95833333334</v>
       </c>
       <c r="M938" s="1" t="n">
-        <v>46369.58333333334</v>
+        <v>46370.25</v>
       </c>
     </row>
     <row r="939">
@@ -51968,13 +51968,13 @@
         </is>
       </c>
       <c r="K939" s="1" t="n">
-        <v>46373.66666666666</v>
+        <v>46374.33333333334</v>
       </c>
       <c r="L939" s="1" t="n">
-        <v>46373.70833333334</v>
+        <v>46374.375</v>
       </c>
       <c r="M939" s="1" t="n">
-        <v>46374.16666666666</v>
+        <v>46374.83333333334</v>
       </c>
     </row>
     <row r="940">
@@ -52023,13 +52023,13 @@
         </is>
       </c>
       <c r="K940" s="1" t="n">
-        <v>46375.25</v>
+        <v>46375.91666666666</v>
       </c>
       <c r="L940" s="1" t="n">
-        <v>46375.29166666666</v>
+        <v>46375.95833333334</v>
       </c>
       <c r="M940" s="1" t="n">
-        <v>46375.875</v>
+        <v>46376.54166666666</v>
       </c>
     </row>
     <row r="941">
@@ -52078,13 +52078,13 @@
         </is>
       </c>
       <c r="K941" s="1" t="n">
-        <v>46378.41666666666</v>
+        <v>46379.08333333334</v>
       </c>
       <c r="L941" s="1" t="n">
-        <v>46378.45833333334</v>
+        <v>46379.125</v>
       </c>
       <c r="M941" s="1" t="n">
-        <v>46379.16666666666</v>
+        <v>46379.83333333334</v>
       </c>
     </row>
     <row r="942">
@@ -52133,13 +52133,13 @@
         </is>
       </c>
       <c r="K942" s="1" t="n">
-        <v>46379.5</v>
+        <v>46380.16666666666</v>
       </c>
       <c r="L942" s="1" t="n">
-        <v>46379.58333333334</v>
+        <v>46380.25</v>
       </c>
       <c r="M942" s="1" t="n">
-        <v>46379.83333333334</v>
+        <v>46380.5</v>
       </c>
     </row>
     <row r="943">
@@ -52188,13 +52188,13 @@
         </is>
       </c>
       <c r="K943" s="1" t="n">
-        <v>46382.75</v>
+        <v>46383.41666666666</v>
       </c>
       <c r="L943" s="1" t="n">
-        <v>46382.79166666666</v>
+        <v>46383.45833333334</v>
       </c>
       <c r="M943" s="1" t="n">
-        <v>46383.25</v>
+        <v>46383.91666666666</v>
       </c>
     </row>
     <row r="944">
@@ -52243,13 +52243,13 @@
         </is>
       </c>
       <c r="K944" s="1" t="n">
-        <v>46385.45833333334</v>
+        <v>46386.125</v>
       </c>
       <c r="L944" s="1" t="n">
-        <v>46385.625</v>
+        <v>46386.29166666666</v>
       </c>
       <c r="M944" s="1" t="n">
-        <v>46386.08333333334</v>
+        <v>46386.75</v>
       </c>
     </row>
     <row r="945">
@@ -52298,13 +52298,13 @@
         </is>
       </c>
       <c r="K945" s="1" t="n">
-        <v>46387.83333333334</v>
+        <v>46388.5</v>
       </c>
       <c r="L945" s="1" t="n">
-        <v>46387.875</v>
+        <v>46388.54166666666</v>
       </c>
       <c r="M945" s="1" t="n">
-        <v>46388.04166666666</v>
+        <v>46388.70833333334</v>
       </c>
     </row>
     <row r="946">
@@ -52353,13 +52353,13 @@
         </is>
       </c>
       <c r="K946" s="1" t="n">
-        <v>46388.29166666666</v>
+        <v>46388.95833333334</v>
       </c>
       <c r="L946" s="1" t="n">
-        <v>46388.41666666666</v>
+        <v>46389.08333333334</v>
       </c>
       <c r="M946" s="1" t="n">
-        <v>46389.75</v>
+        <v>46390.41666666666</v>
       </c>
     </row>
     <row r="947">
@@ -52408,13 +52408,13 @@
         </is>
       </c>
       <c r="K947" s="1" t="n">
-        <v>46390.25</v>
+        <v>46390.91666666666</v>
       </c>
       <c r="L947" s="1" t="n">
-        <v>46390.29166666666</v>
+        <v>46390.95833333334</v>
       </c>
       <c r="M947" s="1" t="n">
-        <v>46390.58333333334</v>
+        <v>46391.25</v>
       </c>
     </row>
     <row r="948">
@@ -52463,13 +52463,13 @@
         </is>
       </c>
       <c r="K948" s="1" t="n">
-        <v>46394.66666666666</v>
+        <v>46395.33333333334</v>
       </c>
       <c r="L948" s="1" t="n">
-        <v>46394.70833333334</v>
+        <v>46395.375</v>
       </c>
       <c r="M948" s="1" t="n">
-        <v>46395.16666666666</v>
+        <v>46395.83333333334</v>
       </c>
     </row>
     <row r="949">
@@ -52514,13 +52514,13 @@
       </c>
       <c r="J949" t="inlineStr"/>
       <c r="K949" s="1" t="n">
-        <v>46396.25</v>
+        <v>46396.91666666666</v>
       </c>
       <c r="L949" s="1" t="n">
-        <v>46396.29166666666</v>
+        <v>46396.95833333334</v>
       </c>
       <c r="M949" s="1" t="n">
-        <v>46396.875</v>
+        <v>46397.54166666666</v>
       </c>
     </row>
     <row r="950">
@@ -52847,10 +52847,10 @@
         <v>46301.70833333334</v>
       </c>
       <c r="L955" s="1" t="n">
-        <v>46301.75</v>
+        <v>46301.82916666667</v>
       </c>
       <c r="M955" s="1" t="n">
-        <v>46302.45833333334</v>
+        <v>46302.625</v>
       </c>
     </row>
     <row r="956">
@@ -52899,13 +52899,13 @@
         </is>
       </c>
       <c r="K956" s="1" t="n">
-        <v>46308.41666666666</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="L956" s="1" t="n">
-        <v>46308.625</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="M956" s="1" t="n">
-        <v>46309.29166666666</v>
+        <v>46309.45833333334</v>
       </c>
     </row>
     <row r="957">
@@ -52954,13 +52954,13 @@
         </is>
       </c>
       <c r="K957" s="1" t="n">
-        <v>46310.6875</v>
+        <v>46310.85416666666</v>
       </c>
       <c r="L957" s="1" t="n">
-        <v>46310.72916666666</v>
+        <v>46310.89583333334</v>
       </c>
       <c r="M957" s="1" t="n">
-        <v>46311.72916666666</v>
+        <v>46311.89583333334</v>
       </c>
     </row>
     <row r="958">
@@ -53009,13 +53009,13 @@
         </is>
       </c>
       <c r="K958" s="1" t="n">
-        <v>46312.02083333334</v>
+        <v>46312.1875</v>
       </c>
       <c r="L958" s="1" t="n">
-        <v>46312.0625</v>
+        <v>46312.22916666666</v>
       </c>
       <c r="M958" s="1" t="n">
-        <v>46312.6875</v>
+        <v>46312.85416666666</v>
       </c>
     </row>
     <row r="959">
@@ -53064,13 +53064,13 @@
         </is>
       </c>
       <c r="K959" s="1" t="n">
-        <v>46314.14583333334</v>
+        <v>46314.3125</v>
       </c>
       <c r="L959" s="1" t="n">
-        <v>46314.35416666666</v>
+        <v>46314.52083333334</v>
       </c>
       <c r="M959" s="1" t="n">
-        <v>46315.02083333334</v>
+        <v>46315.1875</v>
       </c>
     </row>
     <row r="960">
@@ -53119,13 +53119,13 @@
         </is>
       </c>
       <c r="K960" s="1" t="n">
-        <v>46322.02083333334</v>
+        <v>46322.1875</v>
       </c>
       <c r="L960" s="1" t="n">
-        <v>46322.10416666666</v>
+        <v>46322.27083333334</v>
       </c>
       <c r="M960" s="1" t="n">
-        <v>46322.9375</v>
+        <v>46323.10416666666</v>
       </c>
     </row>
     <row r="961">
@@ -53174,13 +53174,13 @@
         </is>
       </c>
       <c r="K961" s="1" t="n">
-        <v>46324.02083333334</v>
+        <v>46324.1875</v>
       </c>
       <c r="L961" s="1" t="n">
-        <v>46324.10416666666</v>
+        <v>46324.27083333334</v>
       </c>
       <c r="M961" s="1" t="n">
-        <v>46324.60416666666</v>
+        <v>46324.77083333334</v>
       </c>
     </row>
     <row r="962">
@@ -53229,13 +53229,13 @@
         </is>
       </c>
       <c r="K962" s="1" t="n">
-        <v>46328.60416666666</v>
+        <v>46328.77083333334</v>
       </c>
       <c r="L962" s="1" t="n">
-        <v>46328.64583333334</v>
+        <v>46328.8125</v>
       </c>
       <c r="M962" s="1" t="n">
-        <v>46329.3125</v>
+        <v>46329.47916666666</v>
       </c>
     </row>
     <row r="963">
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="K963" s="1" t="n">
-        <v>46335.72916666666</v>
+        <v>46335.89583333334</v>
       </c>
       <c r="L963" s="1" t="n">
-        <v>46335.9375</v>
+        <v>46336.10416666666</v>
       </c>
       <c r="M963" s="1" t="n">
-        <v>46336.60416666666</v>
+        <v>46336.77083333334</v>
       </c>
     </row>
     <row r="964">
@@ -53339,13 +53339,13 @@
         </is>
       </c>
       <c r="K964" s="1" t="n">
-        <v>46338.10416666666</v>
+        <v>46338.27083333334</v>
       </c>
       <c r="L964" s="1" t="n">
-        <v>46338.14583333334</v>
+        <v>46338.3125</v>
       </c>
       <c r="M964" s="1" t="n">
-        <v>46339.14583333334</v>
+        <v>46339.3125</v>
       </c>
     </row>
     <row r="965">
@@ -53394,13 +53394,13 @@
         </is>
       </c>
       <c r="K965" s="1" t="n">
-        <v>46339.77083333334</v>
+        <v>46339.9375</v>
       </c>
       <c r="L965" s="1" t="n">
-        <v>46339.8125</v>
+        <v>46339.97916666666</v>
       </c>
       <c r="M965" s="1" t="n">
-        <v>46340.4375</v>
+        <v>46340.60416666666</v>
       </c>
     </row>
     <row r="966">
@@ -53449,13 +53449,13 @@
         </is>
       </c>
       <c r="K966" s="1" t="n">
-        <v>46341.9375</v>
+        <v>46342.10416666666</v>
       </c>
       <c r="L966" s="1" t="n">
-        <v>46342.14583333334</v>
+        <v>46342.3125</v>
       </c>
       <c r="M966" s="1" t="n">
-        <v>46342.8125</v>
+        <v>46342.97916666666</v>
       </c>
     </row>
     <row r="967">
@@ -53504,13 +53504,13 @@
         </is>
       </c>
       <c r="K967" s="1" t="n">
-        <v>46349.8125</v>
+        <v>46349.97916666666</v>
       </c>
       <c r="L967" s="1" t="n">
-        <v>46349.89583333334</v>
+        <v>46350.0625</v>
       </c>
       <c r="M967" s="1" t="n">
-        <v>46350.72916666666</v>
+        <v>46350.89583333334</v>
       </c>
     </row>
     <row r="968">
@@ -53559,13 +53559,13 @@
         </is>
       </c>
       <c r="K968" s="1" t="n">
-        <v>46351.8125</v>
+        <v>46351.97916666666</v>
       </c>
       <c r="L968" s="1" t="n">
-        <v>46351.89583333334</v>
+        <v>46352.0625</v>
       </c>
       <c r="M968" s="1" t="n">
-        <v>46352.39583333334</v>
+        <v>46352.5625</v>
       </c>
     </row>
     <row r="969">
@@ -53614,13 +53614,13 @@
         </is>
       </c>
       <c r="K969" s="1" t="n">
-        <v>46356.39583333334</v>
+        <v>46356.5625</v>
       </c>
       <c r="L969" s="1" t="n">
-        <v>46356.4375</v>
+        <v>46356.60416666666</v>
       </c>
       <c r="M969" s="1" t="n">
-        <v>46357.10416666666</v>
+        <v>46357.27083333334</v>
       </c>
     </row>
     <row r="970">
@@ -53669,13 +53669,13 @@
         </is>
       </c>
       <c r="K970" s="1" t="n">
-        <v>46363.52083333334</v>
+        <v>46363.6875</v>
       </c>
       <c r="L970" s="1" t="n">
-        <v>46363.72916666666</v>
+        <v>46363.89583333334</v>
       </c>
       <c r="M970" s="1" t="n">
-        <v>46364.39583333334</v>
+        <v>46364.5625</v>
       </c>
     </row>
     <row r="971">
@@ -53724,13 +53724,13 @@
         </is>
       </c>
       <c r="K971" s="1" t="n">
-        <v>46366.10416666666</v>
+        <v>46366.27083333334</v>
       </c>
       <c r="L971" s="1" t="n">
-        <v>46366.14583333334</v>
+        <v>46366.3125</v>
       </c>
       <c r="M971" s="1" t="n">
-        <v>46367.14583333334</v>
+        <v>46367.3125</v>
       </c>
     </row>
     <row r="972">
@@ -53779,13 +53779,13 @@
         </is>
       </c>
       <c r="K972" s="1" t="n">
-        <v>46367.77083333334</v>
+        <v>46367.9375</v>
       </c>
       <c r="L972" s="1" t="n">
-        <v>46367.8125</v>
+        <v>46367.97916666666</v>
       </c>
       <c r="M972" s="1" t="n">
-        <v>46368.4375</v>
+        <v>46368.60416666666</v>
       </c>
     </row>
     <row r="973">
@@ -53834,13 +53834,13 @@
         </is>
       </c>
       <c r="K973" s="1" t="n">
-        <v>46369.9375</v>
+        <v>46370.10416666666</v>
       </c>
       <c r="L973" s="1" t="n">
-        <v>46370.14583333334</v>
+        <v>46370.3125</v>
       </c>
       <c r="M973" s="1" t="n">
-        <v>46370.8125</v>
+        <v>46370.97916666666</v>
       </c>
     </row>
     <row r="974">
@@ -53889,13 +53889,13 @@
         </is>
       </c>
       <c r="K974" s="1" t="n">
-        <v>46377.8125</v>
+        <v>46377.97916666666</v>
       </c>
       <c r="L974" s="1" t="n">
-        <v>46377.89583333334</v>
+        <v>46378.0625</v>
       </c>
       <c r="M974" s="1" t="n">
-        <v>46378.72916666666</v>
+        <v>46378.89583333334</v>
       </c>
     </row>
     <row r="975">
@@ -53944,13 +53944,13 @@
         </is>
       </c>
       <c r="K975" s="1" t="n">
-        <v>46379.8125</v>
+        <v>46379.97916666666</v>
       </c>
       <c r="L975" s="1" t="n">
-        <v>46379.89583333334</v>
+        <v>46380.0625</v>
       </c>
       <c r="M975" s="1" t="n">
-        <v>46380.39583333334</v>
+        <v>46380.5625</v>
       </c>
     </row>
     <row r="976">
@@ -53999,13 +53999,13 @@
         </is>
       </c>
       <c r="K976" s="1" t="n">
-        <v>46384.39583333334</v>
+        <v>46384.5625</v>
       </c>
       <c r="L976" s="1" t="n">
-        <v>46384.4375</v>
+        <v>46384.60416666666</v>
       </c>
       <c r="M976" s="1" t="n">
-        <v>46385.10416666666</v>
+        <v>46385.27083333334</v>
       </c>
     </row>
     <row r="977">
@@ -54050,13 +54050,13 @@
       </c>
       <c r="J977" t="inlineStr"/>
       <c r="K977" s="1" t="n">
-        <v>46391.52083333334</v>
+        <v>46391.6875</v>
       </c>
       <c r="L977" s="1" t="n">
-        <v>46391.72916666666</v>
+        <v>46391.89583333334</v>
       </c>
       <c r="M977" s="1" t="n">
-        <v>46392.39583333334</v>
+        <v>46392.5625</v>
       </c>
     </row>
     <row r="978">
@@ -56582,7 +56582,7 @@
         <v>46302.33333333334</v>
       </c>
       <c r="M1023" s="1" t="n">
-        <v>46302.79166666666</v>
+        <v>46303.02083333334</v>
       </c>
     </row>
     <row r="1024">
@@ -56631,13 +56631,13 @@
         </is>
       </c>
       <c r="K1024" s="1" t="n">
-        <v>46305.875</v>
+        <v>46306.125</v>
       </c>
       <c r="L1024" s="1" t="n">
-        <v>46305.91666666666</v>
+        <v>46306.16666666666</v>
       </c>
       <c r="M1024" s="1" t="n">
-        <v>46306.58333333334</v>
+        <v>46306.83333333334</v>
       </c>
     </row>
     <row r="1025">
@@ -56686,13 +56686,13 @@
         </is>
       </c>
       <c r="K1025" s="1" t="n">
-        <v>46307.66666666666</v>
+        <v>46307.91666666666</v>
       </c>
       <c r="L1025" s="1" t="n">
-        <v>46307.70833333334</v>
+        <v>46307.95833333334</v>
       </c>
       <c r="M1025" s="1" t="n">
-        <v>46308.29166666666</v>
+        <v>46308.54166666666</v>
       </c>
     </row>
     <row r="1026">
@@ -56741,13 +56741,13 @@
         </is>
       </c>
       <c r="K1026" s="1" t="n">
-        <v>46308.5</v>
+        <v>46308.75</v>
       </c>
       <c r="L1026" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="M1026" s="1" t="n">
-        <v>46308.875</v>
+        <v>46309.125</v>
       </c>
     </row>
     <row r="1027">
@@ -56796,13 +56796,13 @@
         </is>
       </c>
       <c r="K1027" s="1" t="n">
-        <v>46310.16666666666</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="L1027" s="1" t="n">
-        <v>46310.33333333334</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="M1027" s="1" t="n">
-        <v>46310.83333333334</v>
+        <v>46311.08333333334</v>
       </c>
     </row>
     <row r="1028">
@@ -56851,13 +56851,13 @@
         </is>
       </c>
       <c r="K1028" s="1" t="n">
-        <v>46315</v>
+        <v>46315.25</v>
       </c>
       <c r="L1028" s="1" t="n">
-        <v>46315.16666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="M1028" s="1" t="n">
-        <v>46316</v>
+        <v>46316.25</v>
       </c>
     </row>
     <row r="1029">
@@ -56906,13 +56906,13 @@
         </is>
       </c>
       <c r="K1029" s="1" t="n">
-        <v>46317.70833333334</v>
+        <v>46317.95833333334</v>
       </c>
       <c r="L1029" s="1" t="n">
-        <v>46317.75</v>
+        <v>46318</v>
       </c>
       <c r="M1029" s="1" t="n">
-        <v>46318.58333333334</v>
+        <v>46318.83333333334</v>
       </c>
     </row>
     <row r="1030">
@@ -56961,13 +56961,13 @@
         </is>
       </c>
       <c r="K1030" s="1" t="n">
-        <v>46321.75</v>
+        <v>46322</v>
       </c>
       <c r="L1030" s="1" t="n">
-        <v>46321.79166666666</v>
+        <v>46322.04166666666</v>
       </c>
       <c r="M1030" s="1" t="n">
-        <v>46323.47916666666</v>
+        <v>46323.72916666666</v>
       </c>
     </row>
     <row r="1031">
@@ -57016,13 +57016,13 @@
         </is>
       </c>
       <c r="K1031" s="1" t="n">
-        <v>46325.60416666666</v>
+        <v>46325.85416666666</v>
       </c>
       <c r="L1031" s="1" t="n">
-        <v>46325.77083333334</v>
+        <v>46326.02083333334</v>
       </c>
       <c r="M1031" s="1" t="n">
-        <v>46326.60416666666</v>
+        <v>46326.85416666666</v>
       </c>
     </row>
     <row r="1032">
@@ -57071,13 +57071,13 @@
         </is>
       </c>
       <c r="K1032" s="1" t="n">
-        <v>46329.125</v>
+        <v>46329.375</v>
       </c>
       <c r="L1032" s="1" t="n">
-        <v>46329.1875</v>
+        <v>46329.4375</v>
       </c>
       <c r="M1032" s="1" t="n">
-        <v>46329.6875</v>
+        <v>46329.9375</v>
       </c>
     </row>
     <row r="1033">
@@ -57126,13 +57126,13 @@
         </is>
       </c>
       <c r="K1033" s="1" t="n">
-        <v>46329.91666666666</v>
+        <v>46330.16666666666</v>
       </c>
       <c r="L1033" s="1" t="n">
-        <v>46329.95833333334</v>
+        <v>46330.20833333334</v>
       </c>
       <c r="M1033" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46330.70833333334</v>
       </c>
     </row>
     <row r="1034">
@@ -57181,13 +57181,13 @@
         </is>
       </c>
       <c r="K1034" s="1" t="n">
-        <v>46333.64583333334</v>
+        <v>46333.89583333334</v>
       </c>
       <c r="L1034" s="1" t="n">
-        <v>46333.6875</v>
+        <v>46333.9375</v>
       </c>
       <c r="M1034" s="1" t="n">
-        <v>46334.35416666666</v>
+        <v>46334.60416666666</v>
       </c>
     </row>
     <row r="1035">
@@ -57236,13 +57236,13 @@
         </is>
       </c>
       <c r="K1035" s="1" t="n">
-        <v>46335.4375</v>
+        <v>46335.6875</v>
       </c>
       <c r="L1035" s="1" t="n">
-        <v>46335.47916666666</v>
+        <v>46335.72916666666</v>
       </c>
       <c r="M1035" s="1" t="n">
-        <v>46336.0625</v>
+        <v>46336.3125</v>
       </c>
     </row>
     <row r="1036">
@@ -57291,13 +57291,13 @@
         </is>
       </c>
       <c r="K1036" s="1" t="n">
-        <v>46336.25</v>
+        <v>46336.5</v>
       </c>
       <c r="L1036" s="1" t="n">
-        <v>46336.3125</v>
+        <v>46336.5625</v>
       </c>
       <c r="M1036" s="1" t="n">
-        <v>46336.64583333334</v>
+        <v>46336.89583333334</v>
       </c>
     </row>
     <row r="1037">
@@ -57346,13 +57346,13 @@
         </is>
       </c>
       <c r="K1037" s="1" t="n">
-        <v>46337.9375</v>
+        <v>46338.1875</v>
       </c>
       <c r="L1037" s="1" t="n">
-        <v>46338.10416666666</v>
+        <v>46338.35416666666</v>
       </c>
       <c r="M1037" s="1" t="n">
-        <v>46338.60416666666</v>
+        <v>46338.85416666666</v>
       </c>
     </row>
     <row r="1038">
@@ -57401,13 +57401,13 @@
         </is>
       </c>
       <c r="K1038" s="1" t="n">
-        <v>46342.77083333334</v>
+        <v>46343.02083333334</v>
       </c>
       <c r="L1038" s="1" t="n">
-        <v>46342.9375</v>
+        <v>46343.1875</v>
       </c>
       <c r="M1038" s="1" t="n">
-        <v>46343.77083333334</v>
+        <v>46344.02083333334</v>
       </c>
     </row>
     <row r="1039">
@@ -57456,13 +57456,13 @@
         </is>
       </c>
       <c r="K1039" s="1" t="n">
-        <v>46345.4375</v>
+        <v>46345.6875</v>
       </c>
       <c r="L1039" s="1" t="n">
-        <v>46345.47916666666</v>
+        <v>46345.72916666666</v>
       </c>
       <c r="M1039" s="1" t="n">
-        <v>46346.3125</v>
+        <v>46346.5625</v>
       </c>
     </row>
     <row r="1040">
@@ -57511,13 +57511,13 @@
         </is>
       </c>
       <c r="K1040" s="1" t="n">
-        <v>46349.47916666666</v>
+        <v>46349.72916666666</v>
       </c>
       <c r="L1040" s="1" t="n">
-        <v>46349.5625</v>
+        <v>46349.8125</v>
       </c>
       <c r="M1040" s="1" t="n">
-        <v>46351.22916666666</v>
+        <v>46351.47916666666</v>
       </c>
     </row>
     <row r="1041">
@@ -57566,13 +57566,13 @@
         </is>
       </c>
       <c r="K1041" s="1" t="n">
-        <v>46353.6875</v>
+        <v>46353.9375</v>
       </c>
       <c r="L1041" s="1" t="n">
-        <v>46353.85416666666</v>
+        <v>46354.10416666666</v>
       </c>
       <c r="M1041" s="1" t="n">
-        <v>46354.6875</v>
+        <v>46354.9375</v>
       </c>
     </row>
     <row r="1042">
@@ -57621,13 +57621,13 @@
         </is>
       </c>
       <c r="K1042" s="1" t="n">
-        <v>46357.22916666666</v>
+        <v>46357.47916666666</v>
       </c>
       <c r="L1042" s="1" t="n">
-        <v>46357.29166666666</v>
+        <v>46357.54166666666</v>
       </c>
       <c r="M1042" s="1" t="n">
-        <v>46357.79166666666</v>
+        <v>46358.04166666666</v>
       </c>
     </row>
     <row r="1043">
@@ -57676,13 +57676,13 @@
         </is>
       </c>
       <c r="K1043" s="1" t="n">
-        <v>46358.02083333334</v>
+        <v>46358.27083333334</v>
       </c>
       <c r="L1043" s="1" t="n">
-        <v>46358.0625</v>
+        <v>46358.3125</v>
       </c>
       <c r="M1043" s="1" t="n">
-        <v>46358.5625</v>
+        <v>46358.8125</v>
       </c>
     </row>
     <row r="1044">
@@ -57731,13 +57731,13 @@
         </is>
       </c>
       <c r="K1044" s="1" t="n">
-        <v>46361.64583333334</v>
+        <v>46361.89583333334</v>
       </c>
       <c r="L1044" s="1" t="n">
-        <v>46361.6875</v>
+        <v>46361.9375</v>
       </c>
       <c r="M1044" s="1" t="n">
-        <v>46362.35416666666</v>
+        <v>46362.60416666666</v>
       </c>
     </row>
     <row r="1045">
@@ -57786,13 +57786,13 @@
         </is>
       </c>
       <c r="K1045" s="1" t="n">
-        <v>46363.4375</v>
+        <v>46363.6875</v>
       </c>
       <c r="L1045" s="1" t="n">
-        <v>46363.47916666666</v>
+        <v>46363.72916666666</v>
       </c>
       <c r="M1045" s="1" t="n">
-        <v>46364.0625</v>
+        <v>46364.3125</v>
       </c>
     </row>
     <row r="1046">
@@ -57841,13 +57841,13 @@
         </is>
       </c>
       <c r="K1046" s="1" t="n">
-        <v>46364.25</v>
+        <v>46364.5</v>
       </c>
       <c r="L1046" s="1" t="n">
-        <v>46364.3125</v>
+        <v>46364.5625</v>
       </c>
       <c r="M1046" s="1" t="n">
-        <v>46364.64583333334</v>
+        <v>46364.89583333334</v>
       </c>
     </row>
     <row r="1047">
@@ -57896,13 +57896,13 @@
         </is>
       </c>
       <c r="K1047" s="1" t="n">
-        <v>46365.9375</v>
+        <v>46366.1875</v>
       </c>
       <c r="L1047" s="1" t="n">
-        <v>46366.10416666666</v>
+        <v>46366.35416666666</v>
       </c>
       <c r="M1047" s="1" t="n">
-        <v>46366.60416666666</v>
+        <v>46366.85416666666</v>
       </c>
     </row>
     <row r="1048">
@@ -57951,13 +57951,13 @@
         </is>
       </c>
       <c r="K1048" s="1" t="n">
-        <v>46370.77083333334</v>
+        <v>46371.02083333334</v>
       </c>
       <c r="L1048" s="1" t="n">
-        <v>46370.9375</v>
+        <v>46371.1875</v>
       </c>
       <c r="M1048" s="1" t="n">
-        <v>46371.77083333334</v>
+        <v>46372.02083333334</v>
       </c>
     </row>
     <row r="1049">
@@ -58006,13 +58006,13 @@
         </is>
       </c>
       <c r="K1049" s="1" t="n">
-        <v>46373.4375</v>
+        <v>46373.6875</v>
       </c>
       <c r="L1049" s="1" t="n">
-        <v>46373.47916666666</v>
+        <v>46373.72916666666</v>
       </c>
       <c r="M1049" s="1" t="n">
-        <v>46374.3125</v>
+        <v>46374.5625</v>
       </c>
     </row>
     <row r="1050">
@@ -58061,13 +58061,13 @@
         </is>
       </c>
       <c r="K1050" s="1" t="n">
-        <v>46377.47916666666</v>
+        <v>46377.72916666666</v>
       </c>
       <c r="L1050" s="1" t="n">
-        <v>46377.5625</v>
+        <v>46377.8125</v>
       </c>
       <c r="M1050" s="1" t="n">
-        <v>46379.22916666666</v>
+        <v>46379.47916666666</v>
       </c>
     </row>
     <row r="1051">
@@ -58116,13 +58116,13 @@
         </is>
       </c>
       <c r="K1051" s="1" t="n">
-        <v>46381.6875</v>
+        <v>46381.9375</v>
       </c>
       <c r="L1051" s="1" t="n">
-        <v>46381.85416666666</v>
+        <v>46382.10416666666</v>
       </c>
       <c r="M1051" s="1" t="n">
-        <v>46382.6875</v>
+        <v>46382.9375</v>
       </c>
     </row>
     <row r="1052">
@@ -58171,13 +58171,13 @@
         </is>
       </c>
       <c r="K1052" s="1" t="n">
-        <v>46385.22916666666</v>
+        <v>46385.47916666666</v>
       </c>
       <c r="L1052" s="1" t="n">
-        <v>46385.29166666666</v>
+        <v>46385.54166666666</v>
       </c>
       <c r="M1052" s="1" t="n">
-        <v>46385.79166666666</v>
+        <v>46386.04166666666</v>
       </c>
     </row>
     <row r="1053">
@@ -58222,13 +58222,13 @@
       </c>
       <c r="J1053" t="inlineStr"/>
       <c r="K1053" s="1" t="n">
-        <v>46386.02083333334</v>
+        <v>46386.27083333334</v>
       </c>
       <c r="L1053" s="1" t="n">
-        <v>46386.0625</v>
+        <v>46386.3125</v>
       </c>
       <c r="M1053" s="1" t="n">
-        <v>46386.5625</v>
+        <v>46386.8125</v>
       </c>
     </row>
     <row r="1054">
@@ -58332,13 +58332,13 @@
         </is>
       </c>
       <c r="K1055" s="1" t="n">
-        <v>46303.66666666666</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="L1055" s="1" t="n">
-        <v>46303.70833333334</v>
+        <v>46303.6875</v>
       </c>
       <c r="M1055" s="1" t="n">
-        <v>46304.125</v>
+        <v>46304.01041666666</v>
       </c>
     </row>
     <row r="1056">
@@ -58387,13 +58387,13 @@
         </is>
       </c>
       <c r="K1056" s="1" t="n">
-        <v>46305.1875</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="L1056" s="1" t="n">
-        <v>46305.22916666666</v>
+        <v>46305.125</v>
       </c>
       <c r="M1056" s="1" t="n">
-        <v>46305.89583333334</v>
+        <v>46305.79166666666</v>
       </c>
     </row>
     <row r="1057">
@@ -58442,13 +58442,13 @@
         </is>
       </c>
       <c r="K1057" s="1" t="n">
-        <v>46307.16666666666</v>
+        <v>46307.0625</v>
       </c>
       <c r="L1057" s="1" t="n">
-        <v>46307.33333333334</v>
+        <v>46307.22916666666</v>
       </c>
       <c r="M1057" s="1" t="n">
-        <v>46307.83333333334</v>
+        <v>46307.72916666666</v>
       </c>
     </row>
     <row r="1058">
@@ -58497,13 +58497,13 @@
         </is>
       </c>
       <c r="K1058" s="1" t="n">
-        <v>46312</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="L1058" s="1" t="n">
-        <v>46312.16666666666</v>
+        <v>46312.0625</v>
       </c>
       <c r="M1058" s="1" t="n">
-        <v>46313</v>
+        <v>46312.89583333334</v>
       </c>
     </row>
     <row r="1059">
@@ -58552,13 +58552,13 @@
         </is>
       </c>
       <c r="K1059" s="1" t="n">
-        <v>46314.66666666666</v>
+        <v>46314.5625</v>
       </c>
       <c r="L1059" s="1" t="n">
-        <v>46314.70833333334</v>
+        <v>46314.60416666666</v>
       </c>
       <c r="M1059" s="1" t="n">
-        <v>46315.54166666666</v>
+        <v>46315.4375</v>
       </c>
     </row>
     <row r="1060">
@@ -58607,13 +58607,13 @@
         </is>
       </c>
       <c r="K1060" s="1" t="n">
-        <v>46318.70833333334</v>
+        <v>46318.60416666666</v>
       </c>
       <c r="L1060" s="1" t="n">
-        <v>46318.79166666666</v>
+        <v>46318.6875</v>
       </c>
       <c r="M1060" s="1" t="n">
-        <v>46320.45833333334</v>
+        <v>46320.35416666666</v>
       </c>
     </row>
     <row r="1061">
@@ -58662,13 +58662,13 @@
         </is>
       </c>
       <c r="K1061" s="1" t="n">
-        <v>46322.91666666666</v>
+        <v>46322.8125</v>
       </c>
       <c r="L1061" s="1" t="n">
-        <v>46323.08333333334</v>
+        <v>46322.97916666666</v>
       </c>
       <c r="M1061" s="1" t="n">
-        <v>46323.91666666666</v>
+        <v>46323.8125</v>
       </c>
     </row>
     <row r="1062">
@@ -58717,13 +58717,13 @@
         </is>
       </c>
       <c r="K1062" s="1" t="n">
-        <v>46326.45833333334</v>
+        <v>46326.35416666666</v>
       </c>
       <c r="L1062" s="1" t="n">
-        <v>46326.52083333334</v>
+        <v>46326.41666666666</v>
       </c>
       <c r="M1062" s="1" t="n">
-        <v>46327.02083333334</v>
+        <v>46326.91666666666</v>
       </c>
     </row>
     <row r="1063">
@@ -58772,13 +58772,13 @@
         </is>
       </c>
       <c r="K1063" s="1" t="n">
-        <v>46327.25</v>
+        <v>46327.14583333334</v>
       </c>
       <c r="L1063" s="1" t="n">
-        <v>46327.29166666666</v>
+        <v>46327.1875</v>
       </c>
       <c r="M1063" s="1" t="n">
-        <v>46327.79166666666</v>
+        <v>46327.6875</v>
       </c>
     </row>
     <row r="1064">
@@ -58827,13 +58827,13 @@
         </is>
       </c>
       <c r="K1064" s="1" t="n">
-        <v>46330.875</v>
+        <v>46330.77083333334</v>
       </c>
       <c r="L1064" s="1" t="n">
-        <v>46330.91666666666</v>
+        <v>46330.8125</v>
       </c>
       <c r="M1064" s="1" t="n">
-        <v>46331.58333333334</v>
+        <v>46331.47916666666</v>
       </c>
     </row>
     <row r="1065">
@@ -58882,13 +58882,13 @@
         </is>
       </c>
       <c r="K1065" s="1" t="n">
-        <v>46332.66666666666</v>
+        <v>46332.5625</v>
       </c>
       <c r="L1065" s="1" t="n">
-        <v>46332.70833333334</v>
+        <v>46332.60416666666</v>
       </c>
       <c r="M1065" s="1" t="n">
-        <v>46333.29166666666</v>
+        <v>46333.1875</v>
       </c>
     </row>
     <row r="1066">
@@ -58937,13 +58937,13 @@
         </is>
       </c>
       <c r="K1066" s="1" t="n">
-        <v>46333.47916666666</v>
+        <v>46333.375</v>
       </c>
       <c r="L1066" s="1" t="n">
-        <v>46333.54166666666</v>
+        <v>46333.4375</v>
       </c>
       <c r="M1066" s="1" t="n">
-        <v>46333.875</v>
+        <v>46333.77083333334</v>
       </c>
     </row>
     <row r="1067">
@@ -58992,13 +58992,13 @@
         </is>
       </c>
       <c r="K1067" s="1" t="n">
-        <v>46335.16666666666</v>
+        <v>46335.0625</v>
       </c>
       <c r="L1067" s="1" t="n">
-        <v>46335.33333333334</v>
+        <v>46335.22916666666</v>
       </c>
       <c r="M1067" s="1" t="n">
-        <v>46335.83333333334</v>
+        <v>46335.72916666666</v>
       </c>
     </row>
     <row r="1068">
@@ -59047,13 +59047,13 @@
         </is>
       </c>
       <c r="K1068" s="1" t="n">
-        <v>46340</v>
+        <v>46339.89583333334</v>
       </c>
       <c r="L1068" s="1" t="n">
-        <v>46340.16666666666</v>
+        <v>46340.0625</v>
       </c>
       <c r="M1068" s="1" t="n">
-        <v>46341</v>
+        <v>46340.89583333334</v>
       </c>
     </row>
     <row r="1069">
@@ -59102,13 +59102,13 @@
         </is>
       </c>
       <c r="K1069" s="1" t="n">
-        <v>46342.66666666666</v>
+        <v>46342.5625</v>
       </c>
       <c r="L1069" s="1" t="n">
-        <v>46342.70833333334</v>
+        <v>46342.60416666666</v>
       </c>
       <c r="M1069" s="1" t="n">
-        <v>46343.54166666666</v>
+        <v>46343.4375</v>
       </c>
     </row>
     <row r="1070">
@@ -59157,13 +59157,13 @@
         </is>
       </c>
       <c r="K1070" s="1" t="n">
-        <v>46346.70833333334</v>
+        <v>46346.60416666666</v>
       </c>
       <c r="L1070" s="1" t="n">
-        <v>46346.79166666666</v>
+        <v>46346.6875</v>
       </c>
       <c r="M1070" s="1" t="n">
-        <v>46348.45833333334</v>
+        <v>46348.35416666666</v>
       </c>
     </row>
     <row r="1071">
@@ -59212,13 +59212,13 @@
         </is>
       </c>
       <c r="K1071" s="1" t="n">
-        <v>46350.91666666666</v>
+        <v>46350.8125</v>
       </c>
       <c r="L1071" s="1" t="n">
-        <v>46351.08333333334</v>
+        <v>46350.97916666666</v>
       </c>
       <c r="M1071" s="1" t="n">
-        <v>46351.91666666666</v>
+        <v>46351.8125</v>
       </c>
     </row>
     <row r="1072">
@@ -59267,13 +59267,13 @@
         </is>
       </c>
       <c r="K1072" s="1" t="n">
-        <v>46354.45833333334</v>
+        <v>46354.35416666666</v>
       </c>
       <c r="L1072" s="1" t="n">
-        <v>46354.52083333334</v>
+        <v>46354.41666666666</v>
       </c>
       <c r="M1072" s="1" t="n">
-        <v>46355.02083333334</v>
+        <v>46354.91666666666</v>
       </c>
     </row>
     <row r="1073">
@@ -59322,13 +59322,13 @@
         </is>
       </c>
       <c r="K1073" s="1" t="n">
-        <v>46355.25</v>
+        <v>46355.14583333334</v>
       </c>
       <c r="L1073" s="1" t="n">
-        <v>46355.29166666666</v>
+        <v>46355.1875</v>
       </c>
       <c r="M1073" s="1" t="n">
-        <v>46355.79166666666</v>
+        <v>46355.6875</v>
       </c>
     </row>
     <row r="1074">
@@ -59377,13 +59377,13 @@
         </is>
       </c>
       <c r="K1074" s="1" t="n">
-        <v>46358.875</v>
+        <v>46358.77083333334</v>
       </c>
       <c r="L1074" s="1" t="n">
-        <v>46358.91666666666</v>
+        <v>46358.8125</v>
       </c>
       <c r="M1074" s="1" t="n">
-        <v>46359.58333333334</v>
+        <v>46359.47916666666</v>
       </c>
     </row>
     <row r="1075">
@@ -59432,13 +59432,13 @@
         </is>
       </c>
       <c r="K1075" s="1" t="n">
-        <v>46360.66666666666</v>
+        <v>46360.5625</v>
       </c>
       <c r="L1075" s="1" t="n">
-        <v>46360.70833333334</v>
+        <v>46360.60416666666</v>
       </c>
       <c r="M1075" s="1" t="n">
-        <v>46361.29166666666</v>
+        <v>46361.1875</v>
       </c>
     </row>
     <row r="1076">
@@ -59487,13 +59487,13 @@
         </is>
       </c>
       <c r="K1076" s="1" t="n">
-        <v>46361.47916666666</v>
+        <v>46361.375</v>
       </c>
       <c r="L1076" s="1" t="n">
-        <v>46361.54166666666</v>
+        <v>46361.4375</v>
       </c>
       <c r="M1076" s="1" t="n">
-        <v>46361.875</v>
+        <v>46361.77083333334</v>
       </c>
     </row>
     <row r="1077">
@@ -59542,13 +59542,13 @@
         </is>
       </c>
       <c r="K1077" s="1" t="n">
-        <v>46363.16666666666</v>
+        <v>46363.0625</v>
       </c>
       <c r="L1077" s="1" t="n">
-        <v>46363.33333333334</v>
+        <v>46363.22916666666</v>
       </c>
       <c r="M1077" s="1" t="n">
-        <v>46363.83333333334</v>
+        <v>46363.72916666666</v>
       </c>
     </row>
     <row r="1078">
@@ -59597,13 +59597,13 @@
         </is>
       </c>
       <c r="K1078" s="1" t="n">
-        <v>46368</v>
+        <v>46367.89583333334</v>
       </c>
       <c r="L1078" s="1" t="n">
-        <v>46368.16666666666</v>
+        <v>46368.0625</v>
       </c>
       <c r="M1078" s="1" t="n">
-        <v>46369</v>
+        <v>46368.89583333334</v>
       </c>
     </row>
     <row r="1079">
@@ -59652,13 +59652,13 @@
         </is>
       </c>
       <c r="K1079" s="1" t="n">
-        <v>46370.66666666666</v>
+        <v>46370.5625</v>
       </c>
       <c r="L1079" s="1" t="n">
-        <v>46370.70833333334</v>
+        <v>46370.60416666666</v>
       </c>
       <c r="M1079" s="1" t="n">
-        <v>46371.54166666666</v>
+        <v>46371.4375</v>
       </c>
     </row>
     <row r="1080">
@@ -59707,13 +59707,13 @@
         </is>
       </c>
       <c r="K1080" s="1" t="n">
-        <v>46374.70833333334</v>
+        <v>46374.60416666666</v>
       </c>
       <c r="L1080" s="1" t="n">
-        <v>46374.79166666666</v>
+        <v>46374.6875</v>
       </c>
       <c r="M1080" s="1" t="n">
-        <v>46376.45833333334</v>
+        <v>46376.35416666666</v>
       </c>
     </row>
     <row r="1081">
@@ -59762,13 +59762,13 @@
         </is>
       </c>
       <c r="K1081" s="1" t="n">
-        <v>46378.91666666666</v>
+        <v>46378.8125</v>
       </c>
       <c r="L1081" s="1" t="n">
-        <v>46379.08333333334</v>
+        <v>46378.97916666666</v>
       </c>
       <c r="M1081" s="1" t="n">
-        <v>46379.91666666666</v>
+        <v>46379.8125</v>
       </c>
     </row>
     <row r="1082">
@@ -59817,13 +59817,13 @@
         </is>
       </c>
       <c r="K1082" s="1" t="n">
-        <v>46382.45833333334</v>
+        <v>46382.35416666666</v>
       </c>
       <c r="L1082" s="1" t="n">
-        <v>46382.52083333334</v>
+        <v>46382.41666666666</v>
       </c>
       <c r="M1082" s="1" t="n">
-        <v>46383.02083333334</v>
+        <v>46382.91666666666</v>
       </c>
     </row>
     <row r="1083">
@@ -59872,13 +59872,13 @@
         </is>
       </c>
       <c r="K1083" s="1" t="n">
-        <v>46383.25</v>
+        <v>46383.14583333334</v>
       </c>
       <c r="L1083" s="1" t="n">
-        <v>46383.29166666666</v>
+        <v>46383.1875</v>
       </c>
       <c r="M1083" s="1" t="n">
-        <v>46383.79166666666</v>
+        <v>46383.6875</v>
       </c>
     </row>
     <row r="1084">
@@ -59927,13 +59927,13 @@
         </is>
       </c>
       <c r="K1084" s="1" t="n">
-        <v>46386.875</v>
+        <v>46386.77083333334</v>
       </c>
       <c r="L1084" s="1" t="n">
-        <v>46386.91666666666</v>
+        <v>46386.8125</v>
       </c>
       <c r="M1084" s="1" t="n">
-        <v>46387.58333333334</v>
+        <v>46387.47916666666</v>
       </c>
     </row>
     <row r="1085">
@@ -59982,13 +59982,13 @@
         </is>
       </c>
       <c r="K1085" s="1" t="n">
-        <v>46388.66666666666</v>
+        <v>46388.5625</v>
       </c>
       <c r="L1085" s="1" t="n">
-        <v>46388.70833333334</v>
+        <v>46388.60416666666</v>
       </c>
       <c r="M1085" s="1" t="n">
-        <v>46389.29166666666</v>
+        <v>46389.1875</v>
       </c>
     </row>
     <row r="1086">
@@ -60037,13 +60037,13 @@
         </is>
       </c>
       <c r="K1086" s="1" t="n">
-        <v>46389.47916666666</v>
+        <v>46389.375</v>
       </c>
       <c r="L1086" s="1" t="n">
-        <v>46389.54166666666</v>
+        <v>46389.4375</v>
       </c>
       <c r="M1086" s="1" t="n">
-        <v>46389.875</v>
+        <v>46389.77083333334</v>
       </c>
     </row>
     <row r="1087">
@@ -60092,13 +60092,13 @@
         </is>
       </c>
       <c r="K1087" s="1" t="n">
-        <v>46391.16666666666</v>
+        <v>46391.0625</v>
       </c>
       <c r="L1087" s="1" t="n">
-        <v>46391.33333333334</v>
+        <v>46391.22916666666</v>
       </c>
       <c r="M1087" s="1" t="n">
-        <v>46391.83333333334</v>
+        <v>46391.72916666666</v>
       </c>
     </row>
     <row r="1088">
@@ -60147,13 +60147,13 @@
         </is>
       </c>
       <c r="K1088" s="1" t="n">
-        <v>46396</v>
+        <v>46395.89583333334</v>
       </c>
       <c r="L1088" s="1" t="n">
-        <v>46396.16666666666</v>
+        <v>46396.0625</v>
       </c>
       <c r="M1088" s="1" t="n">
-        <v>46397</v>
+        <v>46396.89583333334</v>
       </c>
     </row>
     <row r="1089">
@@ -60202,13 +60202,13 @@
         </is>
       </c>
       <c r="K1089" s="1" t="n">
-        <v>46398.66666666666</v>
+        <v>46398.5625</v>
       </c>
       <c r="L1089" s="1" t="n">
-        <v>46398.70833333334</v>
+        <v>46398.60416666666</v>
       </c>
       <c r="M1089" s="1" t="n">
-        <v>46399.54166666666</v>
+        <v>46399.4375</v>
       </c>
     </row>
     <row r="1090">
@@ -60257,13 +60257,13 @@
         </is>
       </c>
       <c r="K1090" s="1" t="n">
-        <v>46402.70833333334</v>
+        <v>46402.60416666666</v>
       </c>
       <c r="L1090" s="1" t="n">
-        <v>46402.79166666666</v>
+        <v>46402.6875</v>
       </c>
       <c r="M1090" s="1" t="n">
-        <v>46404.45833333334</v>
+        <v>46404.35416666666</v>
       </c>
     </row>
     <row r="1091">
@@ -60312,13 +60312,13 @@
         </is>
       </c>
       <c r="K1091" s="1" t="n">
-        <v>46406.91666666666</v>
+        <v>46406.8125</v>
       </c>
       <c r="L1091" s="1" t="n">
-        <v>46407.08333333334</v>
+        <v>46406.97916666666</v>
       </c>
       <c r="M1091" s="1" t="n">
-        <v>46407.91666666666</v>
+        <v>46407.8125</v>
       </c>
     </row>
     <row r="1092">
@@ -60367,13 +60367,13 @@
         </is>
       </c>
       <c r="K1092" s="1" t="n">
-        <v>46410.45833333334</v>
+        <v>46410.35416666666</v>
       </c>
       <c r="L1092" s="1" t="n">
-        <v>46410.52083333334</v>
+        <v>46410.41666666666</v>
       </c>
       <c r="M1092" s="1" t="n">
-        <v>46411.02083333334</v>
+        <v>46410.91666666666</v>
       </c>
     </row>
     <row r="1093">
@@ -60418,13 +60418,13 @@
       </c>
       <c r="J1093" t="inlineStr"/>
       <c r="K1093" s="1" t="n">
-        <v>46411.25</v>
+        <v>46411.14583333334</v>
       </c>
       <c r="L1093" s="1" t="n">
-        <v>46411.29166666666</v>
+        <v>46411.1875</v>
       </c>
       <c r="M1093" s="1" t="n">
-        <v>46411.79166666666</v>
+        <v>46411.6875</v>
       </c>
     </row>
   </sheetData>

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1094"/>
+  <dimension ref="A1:M1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14530,13 +14530,13 @@
         </is>
       </c>
       <c r="K257" s="1" t="n">
-        <v>46304.20833333334</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="L257" s="1" t="n">
-        <v>46304.25</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="M257" s="1" t="n">
-        <v>46304.875</v>
+        <v>46305.125</v>
       </c>
     </row>
     <row r="258">
@@ -14585,13 +14585,13 @@
         </is>
       </c>
       <c r="K258" s="1" t="n">
-        <v>46305.70833333334</v>
+        <v>46305.95833333334</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>46305.75</v>
+        <v>46306.02083333334</v>
       </c>
       <c r="M258" s="1" t="n">
-        <v>46306.25</v>
+        <v>46306.52083333334</v>
       </c>
     </row>
     <row r="259">
@@ -14640,13 +14640,13 @@
         </is>
       </c>
       <c r="K259" s="1" t="n">
-        <v>46307.33333333334</v>
+        <v>46307.5</v>
       </c>
       <c r="L259" s="1" t="n">
-        <v>46307.5</v>
+        <v>46307.66666666666</v>
       </c>
       <c r="M259" s="1" t="n">
-        <v>46308.29166666666</v>
+        <v>46308.45833333334</v>
       </c>
     </row>
     <row r="260">
@@ -14695,13 +14695,13 @@
         </is>
       </c>
       <c r="K260" s="1" t="n">
-        <v>46314.04166666666</v>
+        <v>46314.29166666666</v>
       </c>
       <c r="L260" s="1" t="n">
-        <v>46314.08333333334</v>
+        <v>46314.33333333334</v>
       </c>
       <c r="M260" s="1" t="n">
-        <v>46314.375</v>
+        <v>46314.625</v>
       </c>
     </row>
     <row r="261">
@@ -14750,13 +14750,13 @@
         </is>
       </c>
       <c r="K261" s="1" t="n">
-        <v>46314.66666666666</v>
+        <v>46314.75</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>46314.66666666666</v>
+        <v>46314.875</v>
       </c>
       <c r="M261" s="1" t="n">
-        <v>46316.04166666666</v>
+        <v>46316.25</v>
       </c>
     </row>
     <row r="262">
@@ -14805,13 +14805,13 @@
         </is>
       </c>
       <c r="K262" s="1" t="n">
-        <v>46316.29166666666</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="L262" s="1" t="n">
-        <v>46316.33333333334</v>
+        <v>46316.5</v>
       </c>
       <c r="M262" s="1" t="n">
-        <v>46316.79166666666</v>
+        <v>46316.95833333334</v>
       </c>
     </row>
     <row r="263">
@@ -14860,13 +14860,13 @@
         </is>
       </c>
       <c r="K263" s="1" t="n">
-        <v>46320.625</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>46320.625</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="M263" s="1" t="n">
-        <v>46321.08333333334</v>
+        <v>46321.25</v>
       </c>
     </row>
     <row r="264">
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="K264" s="1" t="n">
-        <v>46322.08333333334</v>
+        <v>46322.25</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>46322.08333333334</v>
+        <v>46322.25</v>
       </c>
       <c r="M264" s="1" t="n">
-        <v>46322.58333333334</v>
+        <v>46322.75</v>
       </c>
     </row>
     <row r="265">
@@ -14970,13 +14970,13 @@
         </is>
       </c>
       <c r="K265" s="1" t="n">
-        <v>46325.04166666666</v>
+        <v>46325.20833333334</v>
       </c>
       <c r="L265" s="1" t="n">
-        <v>46325.08333333334</v>
+        <v>46325.25</v>
       </c>
       <c r="M265" s="1" t="n">
-        <v>46325.70833333334</v>
+        <v>46325.875</v>
       </c>
     </row>
     <row r="266">
@@ -15025,13 +15025,13 @@
         </is>
       </c>
       <c r="K266" s="1" t="n">
-        <v>46326.70833333334</v>
+        <v>46326.875</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>46326.75</v>
+        <v>46326.91666666666</v>
       </c>
       <c r="M266" s="1" t="n">
-        <v>46327.25</v>
+        <v>46327.41666666666</v>
       </c>
     </row>
     <row r="267">
@@ -15080,13 +15080,13 @@
         </is>
       </c>
       <c r="K267" s="1" t="n">
-        <v>46328.33333333334</v>
+        <v>46328.5</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>46328.5</v>
+        <v>46328.66666666666</v>
       </c>
       <c r="M267" s="1" t="n">
-        <v>46329.29166666666</v>
+        <v>46329.45833333334</v>
       </c>
     </row>
     <row r="268">
@@ -15135,13 +15135,13 @@
         </is>
       </c>
       <c r="K268" s="1" t="n">
-        <v>46335.04166666666</v>
+        <v>46335.20833333334</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>46335.08333333334</v>
+        <v>46335.25</v>
       </c>
       <c r="M268" s="1" t="n">
-        <v>46335.375</v>
+        <v>46335.54166666666</v>
       </c>
     </row>
     <row r="269">
@@ -15190,13 +15190,13 @@
         </is>
       </c>
       <c r="K269" s="1" t="n">
-        <v>46335.66666666666</v>
+        <v>46335.83333333334</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>46335.66666666666</v>
+        <v>46335.83333333334</v>
       </c>
       <c r="M269" s="1" t="n">
-        <v>46337.04166666666</v>
+        <v>46337.20833333334</v>
       </c>
     </row>
     <row r="270">
@@ -15245,13 +15245,13 @@
         </is>
       </c>
       <c r="K270" s="1" t="n">
-        <v>46337.29166666666</v>
+        <v>46337.45833333334</v>
       </c>
       <c r="L270" s="1" t="n">
-        <v>46337.33333333334</v>
+        <v>46337.5</v>
       </c>
       <c r="M270" s="1" t="n">
-        <v>46337.79166666666</v>
+        <v>46337.95833333334</v>
       </c>
     </row>
     <row r="271">
@@ -15300,13 +15300,13 @@
         </is>
       </c>
       <c r="K271" s="1" t="n">
-        <v>46341.625</v>
+        <v>46341.79166666666</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>46341.625</v>
+        <v>46341.79166666666</v>
       </c>
       <c r="M271" s="1" t="n">
-        <v>46342.08333333334</v>
+        <v>46342.25</v>
       </c>
     </row>
     <row r="272">
@@ -15355,13 +15355,13 @@
         </is>
       </c>
       <c r="K272" s="1" t="n">
-        <v>46343.08333333334</v>
+        <v>46343.25</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>46343.08333333334</v>
+        <v>46343.25</v>
       </c>
       <c r="M272" s="1" t="n">
-        <v>46343.58333333334</v>
+        <v>46343.75</v>
       </c>
     </row>
     <row r="273">
@@ -15410,13 +15410,13 @@
         </is>
       </c>
       <c r="K273" s="1" t="n">
-        <v>46346.04166666666</v>
+        <v>46346.20833333334</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>46346.08333333334</v>
+        <v>46346.25</v>
       </c>
       <c r="M273" s="1" t="n">
-        <v>46346.70833333334</v>
+        <v>46346.875</v>
       </c>
     </row>
     <row r="274">
@@ -15465,13 +15465,13 @@
         </is>
       </c>
       <c r="K274" s="1" t="n">
-        <v>46347.70833333334</v>
+        <v>46347.875</v>
       </c>
       <c r="L274" s="1" t="n">
-        <v>46347.75</v>
+        <v>46347.91666666666</v>
       </c>
       <c r="M274" s="1" t="n">
-        <v>46348.25</v>
+        <v>46348.41666666666</v>
       </c>
     </row>
     <row r="275">
@@ -15520,13 +15520,13 @@
         </is>
       </c>
       <c r="K275" s="1" t="n">
-        <v>46349.33333333334</v>
+        <v>46349.5</v>
       </c>
       <c r="L275" s="1" t="n">
-        <v>46349.5</v>
+        <v>46349.66666666666</v>
       </c>
       <c r="M275" s="1" t="n">
-        <v>46350.29166666666</v>
+        <v>46350.45833333334</v>
       </c>
     </row>
     <row r="276">
@@ -15575,13 +15575,13 @@
         </is>
       </c>
       <c r="K276" s="1" t="n">
-        <v>46356.04166666666</v>
+        <v>46356.20833333334</v>
       </c>
       <c r="L276" s="1" t="n">
-        <v>46356.08333333334</v>
+        <v>46356.25</v>
       </c>
       <c r="M276" s="1" t="n">
-        <v>46356.375</v>
+        <v>46356.54166666666</v>
       </c>
     </row>
     <row r="277">
@@ -15630,13 +15630,13 @@
         </is>
       </c>
       <c r="K277" s="1" t="n">
-        <v>46356.66666666666</v>
+        <v>46356.83333333334</v>
       </c>
       <c r="L277" s="1" t="n">
-        <v>46356.66666666666</v>
+        <v>46356.83333333334</v>
       </c>
       <c r="M277" s="1" t="n">
-        <v>46358.04166666666</v>
+        <v>46358.20833333334</v>
       </c>
     </row>
     <row r="278">
@@ -15685,13 +15685,13 @@
         </is>
       </c>
       <c r="K278" s="1" t="n">
-        <v>46358.29166666666</v>
+        <v>46358.45833333334</v>
       </c>
       <c r="L278" s="1" t="n">
-        <v>46358.33333333334</v>
+        <v>46358.5</v>
       </c>
       <c r="M278" s="1" t="n">
-        <v>46358.79166666666</v>
+        <v>46358.95833333334</v>
       </c>
     </row>
     <row r="279">
@@ -15740,13 +15740,13 @@
         </is>
       </c>
       <c r="K279" s="1" t="n">
-        <v>46362.625</v>
+        <v>46362.79166666666</v>
       </c>
       <c r="L279" s="1" t="n">
-        <v>46362.625</v>
+        <v>46362.79166666666</v>
       </c>
       <c r="M279" s="1" t="n">
-        <v>46363.08333333334</v>
+        <v>46363.25</v>
       </c>
     </row>
     <row r="280">
@@ -15795,13 +15795,13 @@
         </is>
       </c>
       <c r="K280" s="1" t="n">
-        <v>46364.08333333334</v>
+        <v>46364.25</v>
       </c>
       <c r="L280" s="1" t="n">
-        <v>46364.08333333334</v>
+        <v>46364.25</v>
       </c>
       <c r="M280" s="1" t="n">
-        <v>46364.58333333334</v>
+        <v>46364.75</v>
       </c>
     </row>
     <row r="281">
@@ -15850,13 +15850,13 @@
         </is>
       </c>
       <c r="K281" s="1" t="n">
-        <v>46367.04166666666</v>
+        <v>46367.20833333334</v>
       </c>
       <c r="L281" s="1" t="n">
-        <v>46367.08333333334</v>
+        <v>46367.25</v>
       </c>
       <c r="M281" s="1" t="n">
-        <v>46367.70833333334</v>
+        <v>46367.875</v>
       </c>
     </row>
     <row r="282">
@@ -15905,13 +15905,13 @@
         </is>
       </c>
       <c r="K282" s="1" t="n">
-        <v>46368.70833333334</v>
+        <v>46368.875</v>
       </c>
       <c r="L282" s="1" t="n">
-        <v>46368.75</v>
+        <v>46368.91666666666</v>
       </c>
       <c r="M282" s="1" t="n">
-        <v>46369.25</v>
+        <v>46369.41666666666</v>
       </c>
     </row>
     <row r="283">
@@ -15960,13 +15960,13 @@
         </is>
       </c>
       <c r="K283" s="1" t="n">
-        <v>46370.33333333334</v>
+        <v>46370.5</v>
       </c>
       <c r="L283" s="1" t="n">
-        <v>46370.5</v>
+        <v>46370.66666666666</v>
       </c>
       <c r="M283" s="1" t="n">
-        <v>46371.29166666666</v>
+        <v>46371.45833333334</v>
       </c>
     </row>
     <row r="284">
@@ -16015,13 +16015,13 @@
         </is>
       </c>
       <c r="K284" s="1" t="n">
-        <v>46377.04166666666</v>
+        <v>46377.20833333334</v>
       </c>
       <c r="L284" s="1" t="n">
-        <v>46377.08333333334</v>
+        <v>46377.25</v>
       </c>
       <c r="M284" s="1" t="n">
-        <v>46377.375</v>
+        <v>46377.54166666666</v>
       </c>
     </row>
     <row r="285">
@@ -16070,13 +16070,13 @@
         </is>
       </c>
       <c r="K285" s="1" t="n">
-        <v>46377.66666666666</v>
+        <v>46377.83333333334</v>
       </c>
       <c r="L285" s="1" t="n">
-        <v>46377.66666666666</v>
+        <v>46377.83333333334</v>
       </c>
       <c r="M285" s="1" t="n">
-        <v>46379.04166666666</v>
+        <v>46379.20833333334</v>
       </c>
     </row>
     <row r="286">
@@ -16125,13 +16125,13 @@
         </is>
       </c>
       <c r="K286" s="1" t="n">
-        <v>46379.29166666666</v>
+        <v>46379.45833333334</v>
       </c>
       <c r="L286" s="1" t="n">
-        <v>46379.33333333334</v>
+        <v>46379.5</v>
       </c>
       <c r="M286" s="1" t="n">
-        <v>46379.79166666666</v>
+        <v>46379.95833333334</v>
       </c>
     </row>
     <row r="287">
@@ -16180,13 +16180,13 @@
         </is>
       </c>
       <c r="K287" s="1" t="n">
-        <v>46383.625</v>
+        <v>46383.79166666666</v>
       </c>
       <c r="L287" s="1" t="n">
-        <v>46383.625</v>
+        <v>46383.79166666666</v>
       </c>
       <c r="M287" s="1" t="n">
-        <v>46384.08333333334</v>
+        <v>46384.25</v>
       </c>
     </row>
     <row r="288">
@@ -16231,13 +16231,13 @@
       </c>
       <c r="J288" t="inlineStr"/>
       <c r="K288" s="1" t="n">
-        <v>46385.08333333334</v>
+        <v>46385.25</v>
       </c>
       <c r="L288" s="1" t="n">
-        <v>46385.08333333334</v>
+        <v>46385.25</v>
       </c>
       <c r="M288" s="1" t="n">
-        <v>46385.58333333334</v>
+        <v>46385.75</v>
       </c>
     </row>
     <row r="289">
@@ -29022,13 +29022,13 @@
         </is>
       </c>
       <c r="K521" s="1" t="n">
-        <v>46313.375</v>
+        <v>46313.625</v>
       </c>
       <c r="L521" s="1" t="n">
-        <v>46314.45833333334</v>
+        <v>46314.70833333334</v>
       </c>
       <c r="M521" s="1" t="n">
-        <v>46315.125</v>
+        <v>46315.375</v>
       </c>
     </row>
     <row r="522">
@@ -29077,13 +29077,13 @@
         </is>
       </c>
       <c r="K522" s="1" t="n">
-        <v>46317.04166666666</v>
+        <v>46317.29166666666</v>
       </c>
       <c r="L522" s="1" t="n">
-        <v>46317.16666666666</v>
+        <v>46317.41666666666</v>
       </c>
       <c r="M522" s="1" t="n">
-        <v>46317.91666666666</v>
+        <v>46318.16666666666</v>
       </c>
     </row>
     <row r="523">
@@ -29132,13 +29132,13 @@
         </is>
       </c>
       <c r="K523" s="1" t="n">
-        <v>46329.20833333334</v>
+        <v>46329.45833333334</v>
       </c>
       <c r="L523" s="1" t="n">
-        <v>46339.20833333334</v>
+        <v>46339.45833333334</v>
       </c>
       <c r="M523" s="1" t="n">
-        <v>46346.20833333334</v>
+        <v>46346.45833333334</v>
       </c>
     </row>
     <row r="524">
@@ -29183,13 +29183,13 @@
       </c>
       <c r="J524" t="inlineStr"/>
       <c r="K524" s="1" t="n">
-        <v>46360.29166666666</v>
+        <v>46360.54166666666</v>
       </c>
       <c r="L524" s="1" t="n">
-        <v>46360.33333333334</v>
+        <v>46360.58333333334</v>
       </c>
       <c r="M524" s="1" t="n">
-        <v>46361.33333333334</v>
+        <v>46361.58333333334</v>
       </c>
     </row>
     <row r="525">
@@ -50324,7 +50324,7 @@
         <v>46304.41666666666</v>
       </c>
       <c r="M909" s="1" t="n">
-        <v>46304.875</v>
+        <v>46304.95833333334</v>
       </c>
     </row>
     <row r="910">
@@ -50373,13 +50373,13 @@
         </is>
       </c>
       <c r="K910" s="1" t="n">
-        <v>46306.45833333334</v>
+        <v>46306.54166666666</v>
       </c>
       <c r="L910" s="1" t="n">
-        <v>46306.5</v>
+        <v>46306.58333333334</v>
       </c>
       <c r="M910" s="1" t="n">
-        <v>46306.75</v>
+        <v>46306.83333333334</v>
       </c>
     </row>
     <row r="911">
@@ -50428,13 +50428,13 @@
         </is>
       </c>
       <c r="K911" s="1" t="n">
-        <v>46306.91666666666</v>
+        <v>46307</v>
       </c>
       <c r="L911" s="1" t="n">
-        <v>46307.04166666666</v>
+        <v>46307.125</v>
       </c>
       <c r="M911" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.625</v>
       </c>
     </row>
     <row r="912">
@@ -50483,13 +50483,13 @@
         </is>
       </c>
       <c r="K912" s="1" t="n">
-        <v>46308.70833333334</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="L912" s="1" t="n">
-        <v>46308.75</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="M912" s="1" t="n">
-        <v>46309</v>
+        <v>46309.08333333334</v>
       </c>
     </row>
     <row r="913">
@@ -50538,13 +50538,13 @@
         </is>
       </c>
       <c r="K913" s="1" t="n">
-        <v>46312.72916666666</v>
+        <v>46312.8125</v>
       </c>
       <c r="L913" s="1" t="n">
-        <v>46312.79166666666</v>
+        <v>46312.875</v>
       </c>
       <c r="M913" s="1" t="n">
-        <v>46313.25</v>
+        <v>46313.33333333334</v>
       </c>
     </row>
     <row r="914">
@@ -50589,17 +50589,17 @@
       </c>
       <c r="J914" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K914" s="1" t="n">
-        <v>46314.04166666666</v>
+        <v>46314.125</v>
       </c>
       <c r="L914" s="1" t="n">
-        <v>46314.08333333334</v>
+        <v>46314.16666666666</v>
       </c>
       <c r="M914" s="1" t="n">
-        <v>46314.66666666666</v>
+        <v>46314.75</v>
       </c>
     </row>
     <row r="915">
@@ -50620,47 +50620,47 @@
       </c>
       <c r="D915" t="inlineStr"/>
       <c r="E915" t="n">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G915" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I915" t="inlineStr">
         <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="J915" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
       <c r="K915" s="1" t="n">
-        <v>46317.04166666666</v>
+        <v>46317.08333333334</v>
       </c>
       <c r="L915" s="1" t="n">
-        <v>46317.08333333334</v>
+        <v>46317.14583333334</v>
       </c>
       <c r="M915" s="1" t="n">
-        <v>46317.79166666666</v>
+        <v>46317.58333333334</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -50689,27 +50689,27 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
           <t>KRKAN</t>
         </is>
       </c>
-      <c r="J916" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="K916" s="1" t="n">
-        <v>46318.08333333334</v>
+        <v>46317.33333333334</v>
       </c>
       <c r="L916" s="1" t="n">
-        <v>46318.14583333334</v>
+        <v>46317.375</v>
       </c>
       <c r="M916" s="1" t="n">
-        <v>46318.41666666666</v>
+        <v>46318.375</v>
       </c>
     </row>
     <row r="917">
@@ -50730,47 +50730,47 @@
       </c>
       <c r="D917" t="inlineStr"/>
       <c r="E917" t="n">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G917" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J917" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K917" s="1" t="n">
-        <v>46321.33333333334</v>
+        <v>46317.875</v>
       </c>
       <c r="L917" s="1" t="n">
-        <v>46321.375</v>
+        <v>46317.91666666666</v>
       </c>
       <c r="M917" s="1" t="n">
-        <v>46321.83333333334</v>
+        <v>46318.58333333334</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -50799,33 +50799,33 @@
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J918" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K918" s="1" t="n">
-        <v>46324.04166666666</v>
+        <v>46319</v>
       </c>
       <c r="L918" s="1" t="n">
-        <v>46324.20833333334</v>
+        <v>46319.0625</v>
       </c>
       <c r="M918" s="1" t="n">
-        <v>46324.66666666666</v>
+        <v>46319.64583333334</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -50854,33 +50854,33 @@
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW1</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J919" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K919" s="1" t="n">
-        <v>46326.33333333334</v>
+        <v>46321.16666666666</v>
       </c>
       <c r="L919" s="1" t="n">
-        <v>46326.375</v>
+        <v>46321.375</v>
       </c>
       <c r="M919" s="1" t="n">
-        <v>46326.625</v>
+        <v>46322.04166666666</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -50909,33 +50909,33 @@
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J920" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="K920" s="1" t="n">
-        <v>46326.79166666666</v>
+        <v>46329.04166666666</v>
       </c>
       <c r="L920" s="1" t="n">
-        <v>46326.91666666666</v>
+        <v>46329.125</v>
       </c>
       <c r="M920" s="1" t="n">
-        <v>46328.41666666666</v>
+        <v>46329.95833333334</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -50964,33 +50964,33 @@
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SRG02</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
         <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="J921" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="K921" s="1" t="n">
-        <v>46328.625</v>
+        <v>46331.04166666666</v>
       </c>
       <c r="L921" s="1" t="n">
-        <v>46328.66666666666</v>
+        <v>46331.125</v>
       </c>
       <c r="M921" s="1" t="n">
-        <v>46328.91666666666</v>
+        <v>46331.625</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -51019,33 +51019,33 @@
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>LCH06</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J922" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K922" s="1" t="n">
-        <v>46332.75</v>
+        <v>46335.625</v>
       </c>
       <c r="L922" s="1" t="n">
-        <v>46332.79166666666</v>
+        <v>46335.66666666666</v>
       </c>
       <c r="M922" s="1" t="n">
-        <v>46333.25</v>
+        <v>46336.33333333334</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -51074,12 +51074,12 @@
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J923" t="inlineStr">
@@ -51088,19 +51088,19 @@
         </is>
       </c>
       <c r="K923" s="1" t="n">
-        <v>46334</v>
+        <v>46342.75</v>
       </c>
       <c r="L923" s="1" t="n">
-        <v>46334.04166666666</v>
+        <v>46342.95833333334</v>
       </c>
       <c r="M923" s="1" t="n">
-        <v>46334.625</v>
+        <v>46343.625</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -51129,7 +51129,7 @@
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
@@ -51143,19 +51143,19 @@
         </is>
       </c>
       <c r="K924" s="1" t="n">
-        <v>46337.08333333334</v>
+        <v>46345.33333333334</v>
       </c>
       <c r="L924" s="1" t="n">
-        <v>46337.125</v>
+        <v>46345.375</v>
       </c>
       <c r="M924" s="1" t="n">
-        <v>46337.83333333334</v>
+        <v>46346.375</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -51184,7 +51184,7 @@
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -51194,23 +51194,23 @@
       </c>
       <c r="J925" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K925" s="1" t="n">
-        <v>46338.16666666666</v>
+        <v>46347</v>
       </c>
       <c r="L925" s="1" t="n">
-        <v>46338.25</v>
+        <v>46347.0625</v>
       </c>
       <c r="M925" s="1" t="n">
-        <v>46338.5</v>
+        <v>46347.64583333334</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -51239,33 +51239,33 @@
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>SHAW1</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J926" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K926" s="1" t="n">
-        <v>46341.41666666666</v>
+        <v>46349.16666666666</v>
       </c>
       <c r="L926" s="1" t="n">
-        <v>46341.45833333334</v>
+        <v>46349.375</v>
       </c>
       <c r="M926" s="1" t="n">
-        <v>46341.91666666666</v>
+        <v>46350.04166666666</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -51284,43 +51284,43 @@
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I927" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J927" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="K927" s="1" t="n">
-        <v>46344.125</v>
+        <v>46357.04166666666</v>
       </c>
       <c r="L927" s="1" t="n">
-        <v>46344.29166666666</v>
+        <v>46357.125</v>
       </c>
       <c r="M927" s="1" t="n">
-        <v>46344.75</v>
+        <v>46357.95833333334</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -51339,43 +51339,43 @@
       </c>
       <c r="F928" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SRG02</t>
         </is>
       </c>
       <c r="I928" t="inlineStr">
         <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="J928" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
       <c r="K928" s="1" t="n">
-        <v>46346.5</v>
+        <v>46359.04166666666</v>
       </c>
       <c r="L928" s="1" t="n">
-        <v>46346.54166666666</v>
+        <v>46359.125</v>
       </c>
       <c r="M928" s="1" t="n">
-        <v>46346.70833333334</v>
+        <v>46359.625</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -51404,33 +51404,33 @@
       </c>
       <c r="H929" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>LCH06</t>
         </is>
       </c>
       <c r="I929" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J929" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K929" s="1" t="n">
-        <v>46346.95833333334</v>
+        <v>46363.625</v>
       </c>
       <c r="L929" s="1" t="n">
-        <v>46347.08333333334</v>
+        <v>46363.66666666666</v>
       </c>
       <c r="M929" s="1" t="n">
-        <v>46348.41666666666</v>
+        <v>46364.33333333334</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -51459,33 +51459,33 @@
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I930" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J930" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K930" s="1" t="n">
-        <v>46348.91666666666</v>
+        <v>46370.75</v>
       </c>
       <c r="L930" s="1" t="n">
-        <v>46348.95833333334</v>
+        <v>46370.95833333334</v>
       </c>
       <c r="M930" s="1" t="n">
-        <v>46349.25</v>
+        <v>46371.625</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -51500,47 +51500,47 @@
       </c>
       <c r="D931" t="inlineStr"/>
       <c r="E931" t="n">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H931" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I931" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J931" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K931" s="1" t="n">
-        <v>46353.33333333334</v>
+        <v>46373.33333333334</v>
       </c>
       <c r="L931" s="1" t="n">
-        <v>46353.375</v>
+        <v>46373.375</v>
       </c>
       <c r="M931" s="1" t="n">
-        <v>46353.83333333334</v>
+        <v>46374.375</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -51555,47 +51555,47 @@
       </c>
       <c r="D932" t="inlineStr"/>
       <c r="E932" t="n">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="I932" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J932" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K932" s="1" t="n">
-        <v>46354.91666666666</v>
+        <v>46375</v>
       </c>
       <c r="L932" s="1" t="n">
-        <v>46354.95833333334</v>
+        <v>46375.0625</v>
       </c>
       <c r="M932" s="1" t="n">
-        <v>46355.54166666666</v>
+        <v>46375.64583333334</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -51624,33 +51624,33 @@
       </c>
       <c r="H933" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHAW1</t>
         </is>
       </c>
       <c r="I933" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J933" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K933" s="1" t="n">
-        <v>46358.08333333334</v>
+        <v>46377.16666666666</v>
       </c>
       <c r="L933" s="1" t="n">
-        <v>46358.125</v>
+        <v>46377.375</v>
       </c>
       <c r="M933" s="1" t="n">
-        <v>46358.83333333334</v>
+        <v>46378.04166666666</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -51669,43 +51669,43 @@
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J934" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="K934" s="1" t="n">
-        <v>46359.16666666666</v>
+        <v>46385.04166666666</v>
       </c>
       <c r="L934" s="1" t="n">
-        <v>46359.25</v>
+        <v>46385.125</v>
       </c>
       <c r="M934" s="1" t="n">
-        <v>46359.5</v>
+        <v>46385.95833333334</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -51724,43 +51724,43 @@
       </c>
       <c r="F935" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>SRG02</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="J935" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K935" s="1" t="n">
-        <v>46362.41666666666</v>
+        <v>46387.04166666666</v>
       </c>
       <c r="L935" s="1" t="n">
-        <v>46362.45833333334</v>
+        <v>46387.125</v>
       </c>
       <c r="M935" s="1" t="n">
-        <v>46362.91666666666</v>
+        <v>46387.625</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -51779,43 +51779,43 @@
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH06</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J936" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K936" s="1" t="n">
-        <v>46365.125</v>
+        <v>46391.625</v>
       </c>
       <c r="L936" s="1" t="n">
-        <v>46365.29166666666</v>
+        <v>46391.66666666666</v>
       </c>
       <c r="M936" s="1" t="n">
-        <v>46365.75</v>
+        <v>46392.33333333334</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -51834,223 +51834,219 @@
       </c>
       <c r="F937" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I937" t="inlineStr">
         <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="J937" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr"/>
       <c r="K937" s="1" t="n">
-        <v>46367.5</v>
+        <v>46398.75</v>
       </c>
       <c r="L937" s="1" t="n">
-        <v>46367.54166666666</v>
+        <v>46398.95833333334</v>
       </c>
       <c r="M937" s="1" t="n">
-        <v>46367.70833333334</v>
+        <v>46399.625</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D938" t="inlineStr"/>
       <c r="E938" t="n">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I938" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J938" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K938" s="1" t="n">
-        <v>46367.95833333334</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="L938" s="1" t="n">
-        <v>46368.08333333334</v>
+        <v>46278.28333333333</v>
       </c>
       <c r="M938" s="1" t="n">
-        <v>46369.41666666666</v>
+        <v>46279.99166666667</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D939" t="inlineStr"/>
       <c r="E939" t="n">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G939" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="I939" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J939" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K939" s="1" t="n">
-        <v>46369.91666666666</v>
+        <v>46280.25</v>
       </c>
       <c r="L939" s="1" t="n">
-        <v>46369.95833333334</v>
+        <v>46280.325</v>
       </c>
       <c r="M939" s="1" t="n">
-        <v>46370.25</v>
+        <v>46280.675</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D940" t="inlineStr"/>
       <c r="E940" t="n">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G940" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>SHAW1</t>
         </is>
       </c>
       <c r="I940" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J940" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K940" s="1" t="n">
-        <v>46374.33333333334</v>
+        <v>46281.75</v>
       </c>
       <c r="L940" s="1" t="n">
-        <v>46374.375</v>
+        <v>46287.06666666667</v>
       </c>
       <c r="M940" s="1" t="n">
-        <v>46374.83333333334</v>
+        <v>46287.875</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D941" t="inlineStr"/>
       <c r="E941" t="n">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -52059,197 +52055,197 @@
       </c>
       <c r="G941" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H941" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I941" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J941" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="K941" s="1" t="n">
-        <v>46375.91666666666</v>
+        <v>46294.97916666666</v>
       </c>
       <c r="L941" s="1" t="n">
-        <v>46375.95833333334</v>
+        <v>46295</v>
       </c>
       <c r="M941" s="1" t="n">
-        <v>46376.54166666666</v>
+        <v>46296.35833333333</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D942" t="inlineStr"/>
       <c r="E942" t="n">
-        <v>2615</v>
+        <v>2612</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H942" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SRG02</t>
         </is>
       </c>
       <c r="I942" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="J942" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K942" s="1" t="n">
-        <v>46379.08333333334</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="L942" s="1" t="n">
-        <v>46379.125</v>
+        <v>46297.38333333333</v>
       </c>
       <c r="M942" s="1" t="n">
-        <v>46379.83333333334</v>
+        <v>46297.98333333333</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D943" t="inlineStr"/>
       <c r="E943" t="n">
-        <v>2615</v>
+        <v>2612</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H943" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>LCH06</t>
         </is>
       </c>
       <c r="I943" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J943" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K943" s="1" t="n">
-        <v>46380.16666666666</v>
+        <v>46301.70833333334</v>
       </c>
       <c r="L943" s="1" t="n">
-        <v>46380.25</v>
+        <v>46301.82916666667</v>
       </c>
       <c r="M943" s="1" t="n">
-        <v>46380.5</v>
+        <v>46302.625</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D944" t="inlineStr"/>
       <c r="E944" t="n">
-        <v>2615</v>
+        <v>2612</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I944" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J944" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K944" s="1" t="n">
-        <v>46383.41666666666</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="L944" s="1" t="n">
-        <v>46383.45833333334</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="M944" s="1" t="n">
-        <v>46383.91666666666</v>
+        <v>46309.45833333334</v>
       </c>
     </row>
     <row r="945">
@@ -52260,17 +52256,17 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D945" t="inlineStr"/>
       <c r="E945" t="n">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -52279,32 +52275,32 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J945" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K945" s="1" t="n">
-        <v>46386.125</v>
+        <v>46313.5</v>
       </c>
       <c r="L945" s="1" t="n">
-        <v>46386.29166666666</v>
+        <v>46313.54166666666</v>
       </c>
       <c r="M945" s="1" t="n">
-        <v>46386.75</v>
+        <v>46314.25</v>
       </c>
     </row>
     <row r="946">
@@ -52315,17 +52311,17 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D946" t="inlineStr"/>
       <c r="E946" t="n">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -52334,32 +52330,32 @@
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I946" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J946" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K946" s="1" t="n">
-        <v>46388.5</v>
+        <v>46314.58333333334</v>
       </c>
       <c r="L946" s="1" t="n">
-        <v>46388.54166666666</v>
+        <v>46314.66666666666</v>
       </c>
       <c r="M946" s="1" t="n">
-        <v>46388.70833333334</v>
+        <v>46314.91666666666</v>
       </c>
     </row>
     <row r="947">
@@ -52370,51 +52366,51 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D947" t="inlineStr"/>
       <c r="E947" t="n">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G947" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H947" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I947" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J947" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K947" s="1" t="n">
-        <v>46388.95833333334</v>
+        <v>46317.83333333334</v>
       </c>
       <c r="L947" s="1" t="n">
-        <v>46389.08333333334</v>
+        <v>46317.875</v>
       </c>
       <c r="M947" s="1" t="n">
-        <v>46390.41666666666</v>
+        <v>46318.33333333334</v>
       </c>
     </row>
     <row r="948">
@@ -52425,51 +52421,51 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D948" t="inlineStr"/>
       <c r="E948" t="n">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G948" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H948" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I948" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="J948" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="K948" s="1" t="n">
-        <v>46390.91666666666</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="L948" s="1" t="n">
-        <v>46390.95833333334</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="M948" s="1" t="n">
-        <v>46391.25</v>
+        <v>46321.16666666666</v>
       </c>
     </row>
     <row r="949">
@@ -52480,51 +52476,51 @@
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D949" t="inlineStr"/>
       <c r="E949" t="n">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H949" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I949" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J949" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K949" s="1" t="n">
-        <v>46395.33333333334</v>
+        <v>46322.91666666666</v>
       </c>
       <c r="L949" s="1" t="n">
-        <v>46395.375</v>
+        <v>46322.95833333334</v>
       </c>
       <c r="M949" s="1" t="n">
-        <v>46395.83333333334</v>
+        <v>46323.125</v>
       </c>
     </row>
     <row r="950">
@@ -52535,17 +52531,17 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D950" t="inlineStr"/>
       <c r="E950" t="n">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -52554,34 +52550,38 @@
       </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H950" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I950" t="inlineStr">
         <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="J950" t="inlineStr"/>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
       <c r="K950" s="1" t="n">
-        <v>46396.91666666666</v>
+        <v>46323.375</v>
       </c>
       <c r="L950" s="1" t="n">
-        <v>46396.95833333334</v>
+        <v>46323.5</v>
       </c>
       <c r="M950" s="1" t="n">
-        <v>46397.54166666666</v>
+        <v>46324.83333333334</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -52596,47 +52596,47 @@
       </c>
       <c r="D951" t="inlineStr"/>
       <c r="E951" t="n">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G951" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I951" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J951" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K951" s="1" t="n">
-        <v>46278.04166666666</v>
+        <v>46325.33333333334</v>
       </c>
       <c r="L951" s="1" t="n">
-        <v>46278.28333333333</v>
+        <v>46325.375</v>
       </c>
       <c r="M951" s="1" t="n">
-        <v>46279.99166666667</v>
+        <v>46325.66666666666</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
@@ -52651,47 +52651,47 @@
       </c>
       <c r="D952" t="inlineStr"/>
       <c r="E952" t="n">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H952" t="inlineStr">
         <is>
-          <t>KAN04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I952" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J952" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K952" s="1" t="n">
-        <v>46280.25</v>
+        <v>46329.75</v>
       </c>
       <c r="L952" s="1" t="n">
-        <v>46280.325</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="M952" s="1" t="n">
-        <v>46280.675</v>
+        <v>46330.25</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
@@ -52706,47 +52706,47 @@
       </c>
       <c r="D953" t="inlineStr"/>
       <c r="E953" t="n">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H953" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I953" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J953" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K953" s="1" t="n">
-        <v>46281.75</v>
+        <v>46331.33333333334</v>
       </c>
       <c r="L953" s="1" t="n">
-        <v>46287.06666666667</v>
+        <v>46331.375</v>
       </c>
       <c r="M953" s="1" t="n">
-        <v>46287.875</v>
+        <v>46331.95833333334</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
@@ -52761,47 +52761,47 @@
       </c>
       <c r="D954" t="inlineStr"/>
       <c r="E954" t="n">
-        <v>2612</v>
+        <v>2614</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G954" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H954" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I954" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J954" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K954" s="1" t="n">
-        <v>46294.97916666666</v>
+        <v>46334.5</v>
       </c>
       <c r="L954" s="1" t="n">
-        <v>46295</v>
+        <v>46334.54166666666</v>
       </c>
       <c r="M954" s="1" t="n">
-        <v>46296.35833333333</v>
+        <v>46335.25</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
@@ -52816,47 +52816,47 @@
       </c>
       <c r="D955" t="inlineStr"/>
       <c r="E955" t="n">
-        <v>2612</v>
+        <v>2614</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G955" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H955" t="inlineStr">
         <is>
-          <t>SRG02</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I955" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J955" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K955" s="1" t="n">
-        <v>46297.33333333334</v>
+        <v>46335.58333333334</v>
       </c>
       <c r="L955" s="1" t="n">
-        <v>46297.38333333333</v>
+        <v>46335.66666666666</v>
       </c>
       <c r="M955" s="1" t="n">
-        <v>46297.98333333333</v>
+        <v>46335.91666666666</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
@@ -52871,47 +52871,47 @@
       </c>
       <c r="D956" t="inlineStr"/>
       <c r="E956" t="n">
-        <v>2612</v>
+        <v>2614</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H956" t="inlineStr">
         <is>
-          <t>LCH06</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I956" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J956" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K956" s="1" t="n">
-        <v>46301.70833333334</v>
+        <v>46338.83333333334</v>
       </c>
       <c r="L956" s="1" t="n">
-        <v>46301.82916666667</v>
+        <v>46338.875</v>
       </c>
       <c r="M956" s="1" t="n">
-        <v>46302.625</v>
+        <v>46339.33333333334</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -52926,47 +52926,47 @@
       </c>
       <c r="D957" t="inlineStr"/>
       <c r="E957" t="n">
-        <v>2612</v>
+        <v>2614</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H957" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I957" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J957" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K957" s="1" t="n">
-        <v>46308.58333333334</v>
+        <v>46341.54166666666</v>
       </c>
       <c r="L957" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46341.70833333334</v>
       </c>
       <c r="M957" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46342.16666666666</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
@@ -52981,7 +52981,7 @@
       </c>
       <c r="D958" t="inlineStr"/>
       <c r="E958" t="n">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -52990,38 +52990,38 @@
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H958" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I958" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J958" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K958" s="1" t="n">
-        <v>46310.85416666666</v>
+        <v>46343.91666666666</v>
       </c>
       <c r="L958" s="1" t="n">
-        <v>46310.89583333334</v>
+        <v>46343.95833333334</v>
       </c>
       <c r="M958" s="1" t="n">
-        <v>46311.89583333334</v>
+        <v>46344.125</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
@@ -53036,47 +53036,47 @@
       </c>
       <c r="D959" t="inlineStr"/>
       <c r="E959" t="n">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H959" t="inlineStr">
         <is>
-          <t>KAN04</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I959" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J959" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K959" s="1" t="n">
-        <v>46312.1875</v>
+        <v>46344.375</v>
       </c>
       <c r="L959" s="1" t="n">
-        <v>46312.22916666666</v>
+        <v>46344.5</v>
       </c>
       <c r="M959" s="1" t="n">
-        <v>46312.85416666666</v>
+        <v>46345.83333333334</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
@@ -53091,47 +53091,47 @@
       </c>
       <c r="D960" t="inlineStr"/>
       <c r="E960" t="n">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H960" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I960" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J960" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K960" s="1" t="n">
-        <v>46314.3125</v>
+        <v>46346.33333333334</v>
       </c>
       <c r="L960" s="1" t="n">
-        <v>46314.52083333334</v>
+        <v>46346.375</v>
       </c>
       <c r="M960" s="1" t="n">
-        <v>46315.1875</v>
+        <v>46346.66666666666</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
@@ -53146,7 +53146,7 @@
       </c>
       <c r="D961" t="inlineStr"/>
       <c r="E961" t="n">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -53155,38 +53155,38 @@
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H961" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J961" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K961" s="1" t="n">
-        <v>46322.1875</v>
+        <v>46350.75</v>
       </c>
       <c r="L961" s="1" t="n">
-        <v>46322.27083333334</v>
+        <v>46350.79166666666</v>
       </c>
       <c r="M961" s="1" t="n">
-        <v>46323.10416666666</v>
+        <v>46351.25</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
@@ -53201,7 +53201,7 @@
       </c>
       <c r="D962" t="inlineStr"/>
       <c r="E962" t="n">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -53210,38 +53210,38 @@
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H962" t="inlineStr">
         <is>
-          <t>SRG02</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I962" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J962" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K962" s="1" t="n">
-        <v>46324.1875</v>
+        <v>46352.33333333334</v>
       </c>
       <c r="L962" s="1" t="n">
-        <v>46324.27083333334</v>
+        <v>46352.375</v>
       </c>
       <c r="M962" s="1" t="n">
-        <v>46324.77083333334</v>
+        <v>46352.95833333334</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
@@ -53256,47 +53256,47 @@
       </c>
       <c r="D963" t="inlineStr"/>
       <c r="E963" t="n">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="H963" t="inlineStr">
         <is>
-          <t>LCH06</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I963" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J963" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K963" s="1" t="n">
-        <v>46328.77083333334</v>
+        <v>46355.5</v>
       </c>
       <c r="L963" s="1" t="n">
-        <v>46328.8125</v>
+        <v>46355.54166666666</v>
       </c>
       <c r="M963" s="1" t="n">
-        <v>46329.47916666666</v>
+        <v>46356.25</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
@@ -53311,47 +53311,47 @@
       </c>
       <c r="D964" t="inlineStr"/>
       <c r="E964" t="n">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I964" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J964" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K964" s="1" t="n">
-        <v>46335.89583333334</v>
+        <v>46356.58333333334</v>
       </c>
       <c r="L964" s="1" t="n">
-        <v>46336.10416666666</v>
+        <v>46356.66666666666</v>
       </c>
       <c r="M964" s="1" t="n">
-        <v>46336.77083333334</v>
+        <v>46356.91666666666</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
@@ -53366,7 +53366,7 @@
       </c>
       <c r="D965" t="inlineStr"/>
       <c r="E965" t="n">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -53375,38 +53375,38 @@
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I965" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J965" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K965" s="1" t="n">
-        <v>46338.27083333334</v>
+        <v>46359.83333333334</v>
       </c>
       <c r="L965" s="1" t="n">
-        <v>46338.3125</v>
+        <v>46359.875</v>
       </c>
       <c r="M965" s="1" t="n">
-        <v>46339.3125</v>
+        <v>46360.33333333334</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
@@ -53421,7 +53421,7 @@
       </c>
       <c r="D966" t="inlineStr"/>
       <c r="E966" t="n">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -53430,38 +53430,38 @@
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="H966" t="inlineStr">
         <is>
-          <t>KAN04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I966" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J966" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K966" s="1" t="n">
-        <v>46339.9375</v>
+        <v>46362.54166666666</v>
       </c>
       <c r="L966" s="1" t="n">
-        <v>46339.97916666666</v>
+        <v>46362.70833333334</v>
       </c>
       <c r="M966" s="1" t="n">
-        <v>46340.60416666666</v>
+        <v>46363.16666666666</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
@@ -53476,7 +53476,7 @@
       </c>
       <c r="D967" t="inlineStr"/>
       <c r="E967" t="n">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -53485,38 +53485,38 @@
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I967" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J967" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K967" s="1" t="n">
-        <v>46342.10416666666</v>
+        <v>46364.91666666666</v>
       </c>
       <c r="L967" s="1" t="n">
-        <v>46342.3125</v>
+        <v>46364.95833333334</v>
       </c>
       <c r="M967" s="1" t="n">
-        <v>46342.97916666666</v>
+        <v>46365.125</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
@@ -53531,7 +53531,7 @@
       </c>
       <c r="D968" t="inlineStr"/>
       <c r="E968" t="n">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -53540,38 +53540,38 @@
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="H968" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I968" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J968" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K968" s="1" t="n">
-        <v>46349.97916666666</v>
+        <v>46365.375</v>
       </c>
       <c r="L968" s="1" t="n">
-        <v>46350.0625</v>
+        <v>46365.5</v>
       </c>
       <c r="M968" s="1" t="n">
-        <v>46350.89583333334</v>
+        <v>46366.83333333334</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -53586,7 +53586,7 @@
       </c>
       <c r="D969" t="inlineStr"/>
       <c r="E969" t="n">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -53595,38 +53595,38 @@
       </c>
       <c r="G969" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="H969" t="inlineStr">
         <is>
-          <t>SRG02</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I969" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J969" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K969" s="1" t="n">
-        <v>46351.97916666666</v>
+        <v>46367.33333333334</v>
       </c>
       <c r="L969" s="1" t="n">
-        <v>46352.0625</v>
+        <v>46367.375</v>
       </c>
       <c r="M969" s="1" t="n">
-        <v>46352.5625</v>
+        <v>46367.66666666666</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
@@ -53641,7 +53641,7 @@
       </c>
       <c r="D970" t="inlineStr"/>
       <c r="E970" t="n">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -53650,38 +53650,38 @@
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="H970" t="inlineStr">
         <is>
-          <t>LCH06</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J970" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K970" s="1" t="n">
-        <v>46356.5625</v>
+        <v>46371.75</v>
       </c>
       <c r="L970" s="1" t="n">
-        <v>46356.60416666666</v>
+        <v>46371.79166666666</v>
       </c>
       <c r="M970" s="1" t="n">
-        <v>46357.27083333334</v>
+        <v>46372.25</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -53696,7 +53696,7 @@
       </c>
       <c r="D971" t="inlineStr"/>
       <c r="E971" t="n">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -53705,17 +53705,17 @@
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="H971" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I971" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J971" t="inlineStr">
@@ -53724,19 +53724,19 @@
         </is>
       </c>
       <c r="K971" s="1" t="n">
-        <v>46363.6875</v>
+        <v>46373.33333333334</v>
       </c>
       <c r="L971" s="1" t="n">
-        <v>46363.89583333334</v>
+        <v>46373.375</v>
       </c>
       <c r="M971" s="1" t="n">
-        <v>46364.5625</v>
+        <v>46373.95833333334</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
@@ -53751,7 +53751,7 @@
       </c>
       <c r="D972" t="inlineStr"/>
       <c r="E972" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -53760,12 +53760,12 @@
       </c>
       <c r="G972" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
@@ -53779,19 +53779,19 @@
         </is>
       </c>
       <c r="K972" s="1" t="n">
-        <v>46366.27083333334</v>
+        <v>46376.5</v>
       </c>
       <c r="L972" s="1" t="n">
-        <v>46366.3125</v>
+        <v>46376.54166666666</v>
       </c>
       <c r="M972" s="1" t="n">
-        <v>46367.3125</v>
+        <v>46377.25</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -53806,7 +53806,7 @@
       </c>
       <c r="D973" t="inlineStr"/>
       <c r="E973" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -53815,12 +53815,12 @@
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>KAN04</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I973" t="inlineStr">
@@ -53830,23 +53830,23 @@
       </c>
       <c r="J973" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K973" s="1" t="n">
-        <v>46367.9375</v>
+        <v>46377.58333333334</v>
       </c>
       <c r="L973" s="1" t="n">
-        <v>46367.97916666666</v>
+        <v>46377.66666666666</v>
       </c>
       <c r="M973" s="1" t="n">
-        <v>46368.60416666666</v>
+        <v>46377.91666666666</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
@@ -53861,7 +53861,7 @@
       </c>
       <c r="D974" t="inlineStr"/>
       <c r="E974" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -53870,38 +53870,38 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="H974" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I974" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J974" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K974" s="1" t="n">
-        <v>46370.10416666666</v>
+        <v>46380.83333333334</v>
       </c>
       <c r="L974" s="1" t="n">
-        <v>46370.3125</v>
+        <v>46380.875</v>
       </c>
       <c r="M974" s="1" t="n">
-        <v>46370.97916666666</v>
+        <v>46381.33333333334</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -53916,47 +53916,47 @@
       </c>
       <c r="D975" t="inlineStr"/>
       <c r="E975" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="H975" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J975" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K975" s="1" t="n">
-        <v>46377.97916666666</v>
+        <v>46383.54166666666</v>
       </c>
       <c r="L975" s="1" t="n">
-        <v>46378.0625</v>
+        <v>46383.70833333334</v>
       </c>
       <c r="M975" s="1" t="n">
-        <v>46378.89583333334</v>
+        <v>46384.16666666666</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
@@ -53971,47 +53971,47 @@
       </c>
       <c r="D976" t="inlineStr"/>
       <c r="E976" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>SRG02</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J976" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K976" s="1" t="n">
-        <v>46379.97916666666</v>
+        <v>46385.91666666666</v>
       </c>
       <c r="L976" s="1" t="n">
-        <v>46380.0625</v>
+        <v>46385.95833333334</v>
       </c>
       <c r="M976" s="1" t="n">
-        <v>46380.5625</v>
+        <v>46386.125</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
@@ -54026,7 +54026,7 @@
       </c>
       <c r="D977" t="inlineStr"/>
       <c r="E977" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -54035,38 +54035,38 @@
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="H977" t="inlineStr">
         <is>
-          <t>LCH06</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I977" t="inlineStr">
         <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="J977" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
       <c r="K977" s="1" t="n">
-        <v>46384.5625</v>
+        <v>46386.375</v>
       </c>
       <c r="L977" s="1" t="n">
-        <v>46384.60416666666</v>
+        <v>46386.5</v>
       </c>
       <c r="M977" s="1" t="n">
-        <v>46385.27083333334</v>
+        <v>46387.83333333334</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
@@ -54081,7 +54081,7 @@
       </c>
       <c r="D978" t="inlineStr"/>
       <c r="E978" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -54090,28 +54090,32 @@
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="H978" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I978" t="inlineStr">
         <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="J978" t="inlineStr"/>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
       <c r="K978" s="1" t="n">
-        <v>46391.6875</v>
+        <v>46388.33333333334</v>
       </c>
       <c r="L978" s="1" t="n">
-        <v>46391.89583333334</v>
+        <v>46388.375</v>
       </c>
       <c r="M978" s="1" t="n">
-        <v>46392.5625</v>
+        <v>46388.66666666666</v>
       </c>
     </row>
     <row r="979">
@@ -54122,51 +54126,51 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D979" t="inlineStr"/>
       <c r="E979" t="n">
-        <v>2611</v>
+        <v>2616</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I979" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J979" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K979" s="1" t="n">
-        <v>46279.5625</v>
+        <v>46392.75</v>
       </c>
       <c r="L979" s="1" t="n">
-        <v>46279.58333333334</v>
+        <v>46392.79166666666</v>
       </c>
       <c r="M979" s="1" t="n">
-        <v>46280.91666666666</v>
+        <v>46393.25</v>
       </c>
     </row>
     <row r="980">
@@ -54177,51 +54181,47 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D980" t="inlineStr"/>
       <c r="E980" t="n">
-        <v>2611</v>
+        <v>2616</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G980" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I980" t="inlineStr">
         <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="J980" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr"/>
       <c r="K980" s="1" t="n">
-        <v>46281.125</v>
+        <v>46394.33333333334</v>
       </c>
       <c r="L980" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46394.375</v>
       </c>
       <c r="M980" s="1" t="n">
-        <v>46281.97916666666</v>
+        <v>46394.95833333334</v>
       </c>
     </row>
     <row r="981">
@@ -54256,27 +54256,27 @@
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I981" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J981" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K981" s="1" t="n">
-        <v>46284.64583333334</v>
+        <v>46279.5625</v>
       </c>
       <c r="L981" s="1" t="n">
-        <v>46284.6875</v>
+        <v>46279.58333333334</v>
       </c>
       <c r="M981" s="1" t="n">
-        <v>46285.22916666666</v>
+        <v>46280.91666666666</v>
       </c>
     </row>
     <row r="982">
@@ -54311,27 +54311,27 @@
       </c>
       <c r="H982" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I982" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J982" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K982" s="1" t="n">
-        <v>46287.35416666666</v>
+        <v>46281.125</v>
       </c>
       <c r="L982" s="1" t="n">
-        <v>46288.16666666666</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M982" s="1" t="n">
-        <v>46288.5</v>
+        <v>46281.97916666666</v>
       </c>
     </row>
     <row r="983">
@@ -54366,27 +54366,27 @@
       </c>
       <c r="H983" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I983" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J983" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K983" s="1" t="n">
-        <v>46290.1875</v>
+        <v>46284.64583333334</v>
       </c>
       <c r="L983" s="1" t="n">
-        <v>46290.39583333334</v>
+        <v>46284.6875</v>
       </c>
       <c r="M983" s="1" t="n">
-        <v>46290.70833333334</v>
+        <v>46285.22916666666</v>
       </c>
     </row>
     <row r="984">
@@ -54411,22 +54411,22 @@
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G984" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J984" t="inlineStr">
@@ -54435,13 +54435,13 @@
         </is>
       </c>
       <c r="K984" s="1" t="n">
-        <v>46290.8125</v>
+        <v>46287.35416666666</v>
       </c>
       <c r="L984" s="1" t="n">
-        <v>46290.91666666666</v>
+        <v>46288.16666666666</v>
       </c>
       <c r="M984" s="1" t="n">
-        <v>46292.58333333334</v>
+        <v>46288.5</v>
       </c>
     </row>
     <row r="985">
@@ -54466,12 +54466,12 @@
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G985" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="H985" t="inlineStr">
@@ -54486,17 +54486,17 @@
       </c>
       <c r="J985" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K985" s="1" t="n">
-        <v>46293.29166666666</v>
+        <v>46290.1875</v>
       </c>
       <c r="L985" s="1" t="n">
-        <v>46293.4375</v>
+        <v>46290.39583333334</v>
       </c>
       <c r="M985" s="1" t="n">
-        <v>46293.8125</v>
+        <v>46290.70833333334</v>
       </c>
     </row>
     <row r="986">
@@ -54531,27 +54531,27 @@
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I986" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J986" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K986" s="1" t="n">
-        <v>46297.5</v>
+        <v>46290.8125</v>
       </c>
       <c r="L986" s="1" t="n">
-        <v>46297.5625</v>
+        <v>46290.91666666666</v>
       </c>
       <c r="M986" s="1" t="n">
-        <v>46298.0625</v>
+        <v>46292.58333333334</v>
       </c>
     </row>
     <row r="987">
@@ -54586,27 +54586,27 @@
       </c>
       <c r="H987" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I987" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J987" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K987" s="1" t="n">
-        <v>46299.08333333334</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="L987" s="1" t="n">
-        <v>46299.35416666666</v>
+        <v>46293.4375</v>
       </c>
       <c r="M987" s="1" t="n">
-        <v>46300.14583333334</v>
+        <v>46293.8125</v>
       </c>
     </row>
     <row r="988">
@@ -54627,41 +54627,41 @@
       </c>
       <c r="D988" t="inlineStr"/>
       <c r="E988" t="n">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G988" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="H988" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I988" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J988" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K988" s="1" t="n">
-        <v>46302.60416666666</v>
+        <v>46297.5</v>
       </c>
       <c r="L988" s="1" t="n">
-        <v>46304.08333333334</v>
+        <v>46297.5625</v>
       </c>
       <c r="M988" s="1" t="n">
-        <v>46305.25</v>
+        <v>46298.0625</v>
       </c>
     </row>
     <row r="989">
@@ -54682,41 +54682,41 @@
       </c>
       <c r="D989" t="inlineStr"/>
       <c r="E989" t="n">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G989" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I989" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J989" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K989" s="1" t="n">
-        <v>46305.54166666666</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="L989" s="1" t="n">
-        <v>46305.60416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="M989" s="1" t="n">
-        <v>46305.9375</v>
+        <v>46300.14583333334</v>
       </c>
     </row>
     <row r="990">
@@ -54751,27 +54751,27 @@
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I990" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J990" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K990" s="1" t="n">
-        <v>46308.83333333334</v>
+        <v>46302.60416666666</v>
       </c>
       <c r="L990" s="1" t="n">
-        <v>46308.89583333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="M990" s="1" t="n">
-        <v>46309.39583333334</v>
+        <v>46305.25</v>
       </c>
     </row>
     <row r="991">
@@ -54806,27 +54806,27 @@
       </c>
       <c r="H991" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I991" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J991" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K991" s="1" t="n">
-        <v>46311.625</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="L991" s="1" t="n">
-        <v>46311.79166666666</v>
+        <v>46305.60416666666</v>
       </c>
       <c r="M991" s="1" t="n">
-        <v>46312.41666666666</v>
+        <v>46305.9375</v>
       </c>
     </row>
     <row r="992">
@@ -54861,27 +54861,27 @@
       </c>
       <c r="H992" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I992" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J992" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K992" s="1" t="n">
-        <v>46314</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="L992" s="1" t="n">
-        <v>46314.04166666666</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="M992" s="1" t="n">
-        <v>46314.25</v>
+        <v>46309.39583333334</v>
       </c>
     </row>
     <row r="993">
@@ -54906,22 +54906,22 @@
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G993" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I993" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J993" t="inlineStr">
@@ -54930,13 +54930,13 @@
         </is>
       </c>
       <c r="K993" s="1" t="n">
-        <v>46314.375</v>
+        <v>46311.625</v>
       </c>
       <c r="L993" s="1" t="n">
-        <v>46314.5</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="M993" s="1" t="n">
-        <v>46315.95833333334</v>
+        <v>46312.41666666666</v>
       </c>
     </row>
     <row r="994">
@@ -54961,12 +54961,12 @@
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G994" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H994" t="inlineStr">
@@ -54981,17 +54981,17 @@
       </c>
       <c r="J994" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K994" s="1" t="n">
-        <v>46316.16666666666</v>
+        <v>46314</v>
       </c>
       <c r="L994" s="1" t="n">
-        <v>46316.20833333334</v>
+        <v>46314.04166666666</v>
       </c>
       <c r="M994" s="1" t="n">
-        <v>46316.54166666666</v>
+        <v>46314.25</v>
       </c>
     </row>
     <row r="995">
@@ -55026,27 +55026,27 @@
       </c>
       <c r="H995" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I995" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J995" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K995" s="1" t="n">
-        <v>46320.25</v>
+        <v>46314.375</v>
       </c>
       <c r="L995" s="1" t="n">
-        <v>46320.3125</v>
+        <v>46314.5</v>
       </c>
       <c r="M995" s="1" t="n">
-        <v>46320.8125</v>
+        <v>46315.95833333334</v>
       </c>
     </row>
     <row r="996">
@@ -55081,27 +55081,27 @@
       </c>
       <c r="H996" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I996" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J996" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K996" s="1" t="n">
-        <v>46321.625</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="L996" s="1" t="n">
-        <v>46321.6875</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="M996" s="1" t="n">
-        <v>46322.3125</v>
+        <v>46316.54166666666</v>
       </c>
     </row>
     <row r="997">
@@ -55122,41 +55122,41 @@
       </c>
       <c r="D997" t="inlineStr"/>
       <c r="E997" t="n">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H997" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I997" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J997" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K997" s="1" t="n">
-        <v>46324.66666666666</v>
+        <v>46320.25</v>
       </c>
       <c r="L997" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46320.3125</v>
       </c>
       <c r="M997" s="1" t="n">
-        <v>46325.41666666666</v>
+        <v>46320.8125</v>
       </c>
     </row>
     <row r="998">
@@ -55177,41 +55177,41 @@
       </c>
       <c r="D998" t="inlineStr"/>
       <c r="E998" t="n">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G998" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J998" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K998" s="1" t="n">
-        <v>46325.75</v>
+        <v>46321.625</v>
       </c>
       <c r="L998" s="1" t="n">
-        <v>46325.83333333334</v>
+        <v>46321.6875</v>
       </c>
       <c r="M998" s="1" t="n">
-        <v>46326.08333333334</v>
+        <v>46322.3125</v>
       </c>
     </row>
     <row r="999">
@@ -55246,27 +55246,27 @@
       </c>
       <c r="H999" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I999" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J999" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K999" s="1" t="n">
-        <v>46329</v>
+        <v>46324.66666666666</v>
       </c>
       <c r="L999" s="1" t="n">
-        <v>46329.04166666666</v>
+        <v>46324.70833333334</v>
       </c>
       <c r="M999" s="1" t="n">
-        <v>46329.5</v>
+        <v>46325.41666666666</v>
       </c>
     </row>
     <row r="1000">
@@ -55301,27 +55301,27 @@
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I1000" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J1000" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1000" s="1" t="n">
-        <v>46331.70833333334</v>
+        <v>46325.75</v>
       </c>
       <c r="L1000" s="1" t="n">
-        <v>46331.875</v>
+        <v>46325.83333333334</v>
       </c>
       <c r="M1000" s="1" t="n">
-        <v>46332.33333333334</v>
+        <v>46326.08333333334</v>
       </c>
     </row>
     <row r="1001">
@@ -55356,27 +55356,27 @@
       </c>
       <c r="H1001" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1001" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1001" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1001" s="1" t="n">
-        <v>46334.08333333334</v>
+        <v>46329</v>
       </c>
       <c r="L1001" s="1" t="n">
-        <v>46334.125</v>
+        <v>46329.04166666666</v>
       </c>
       <c r="M1001" s="1" t="n">
-        <v>46334.29166666666</v>
+        <v>46329.5</v>
       </c>
     </row>
     <row r="1002">
@@ -55401,22 +55401,22 @@
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1002" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H1002" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1002" t="inlineStr">
@@ -55425,13 +55425,13 @@
         </is>
       </c>
       <c r="K1002" s="1" t="n">
-        <v>46334.54166666666</v>
+        <v>46331.70833333334</v>
       </c>
       <c r="L1002" s="1" t="n">
-        <v>46334.66666666666</v>
+        <v>46331.875</v>
       </c>
       <c r="M1002" s="1" t="n">
-        <v>46336</v>
+        <v>46332.33333333334</v>
       </c>
     </row>
     <row r="1003">
@@ -55456,12 +55456,12 @@
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1003" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H1003" t="inlineStr">
@@ -55476,17 +55476,17 @@
       </c>
       <c r="J1003" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K1003" s="1" t="n">
-        <v>46336.5</v>
+        <v>46334.08333333334</v>
       </c>
       <c r="L1003" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46334.125</v>
       </c>
       <c r="M1003" s="1" t="n">
-        <v>46336.83333333334</v>
+        <v>46334.29166666666</v>
       </c>
     </row>
     <row r="1004">
@@ -55521,27 +55521,27 @@
       </c>
       <c r="H1004" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I1004" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J1004" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1004" s="1" t="n">
-        <v>46340.91666666666</v>
+        <v>46334.54166666666</v>
       </c>
       <c r="L1004" s="1" t="n">
-        <v>46340.95833333334</v>
+        <v>46334.66666666666</v>
       </c>
       <c r="M1004" s="1" t="n">
-        <v>46341.41666666666</v>
+        <v>46336</v>
       </c>
     </row>
     <row r="1005">
@@ -55576,27 +55576,27 @@
       </c>
       <c r="H1005" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1005" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1005" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1005" s="1" t="n">
-        <v>46342.5</v>
+        <v>46336.5</v>
       </c>
       <c r="L1005" s="1" t="n">
-        <v>46342.54166666666</v>
+        <v>46336.54166666666</v>
       </c>
       <c r="M1005" s="1" t="n">
-        <v>46343.125</v>
+        <v>46336.83333333334</v>
       </c>
     </row>
     <row r="1006">
@@ -55617,41 +55617,41 @@
       </c>
       <c r="D1006" t="inlineStr"/>
       <c r="E1006" t="n">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1006" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H1006" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1006" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1006" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K1006" s="1" t="n">
-        <v>46344.83333333334</v>
+        <v>46340.91666666666</v>
       </c>
       <c r="L1006" s="1" t="n">
-        <v>46344.875</v>
+        <v>46340.95833333334</v>
       </c>
       <c r="M1006" s="1" t="n">
-        <v>46345.58333333334</v>
+        <v>46341.41666666666</v>
       </c>
     </row>
     <row r="1007">
@@ -55672,41 +55672,41 @@
       </c>
       <c r="D1007" t="inlineStr"/>
       <c r="E1007" t="n">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1007" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J1007" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1007" s="1" t="n">
-        <v>46345.91666666666</v>
+        <v>46342.5</v>
       </c>
       <c r="L1007" s="1" t="n">
-        <v>46346</v>
+        <v>46342.54166666666</v>
       </c>
       <c r="M1007" s="1" t="n">
-        <v>46346.25</v>
+        <v>46343.125</v>
       </c>
     </row>
     <row r="1008">
@@ -55741,27 +55741,27 @@
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1008" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1008" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K1008" s="1" t="n">
-        <v>46349.16666666666</v>
+        <v>46344.83333333334</v>
       </c>
       <c r="L1008" s="1" t="n">
-        <v>46349.20833333334</v>
+        <v>46344.875</v>
       </c>
       <c r="M1008" s="1" t="n">
-        <v>46349.66666666666</v>
+        <v>46345.58333333334</v>
       </c>
     </row>
     <row r="1009">
@@ -55796,27 +55796,27 @@
       </c>
       <c r="H1009" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I1009" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J1009" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1009" s="1" t="n">
-        <v>46351.875</v>
+        <v>46345.91666666666</v>
       </c>
       <c r="L1009" s="1" t="n">
-        <v>46352.04166666666</v>
+        <v>46346</v>
       </c>
       <c r="M1009" s="1" t="n">
-        <v>46352.5</v>
+        <v>46346.25</v>
       </c>
     </row>
     <row r="1010">
@@ -55851,27 +55851,27 @@
       </c>
       <c r="H1010" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1010" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1010" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1010" s="1" t="n">
-        <v>46354.25</v>
+        <v>46349.16666666666</v>
       </c>
       <c r="L1010" s="1" t="n">
-        <v>46354.29166666666</v>
+        <v>46349.20833333334</v>
       </c>
       <c r="M1010" s="1" t="n">
-        <v>46354.45833333334</v>
+        <v>46349.66666666666</v>
       </c>
     </row>
     <row r="1011">
@@ -55896,22 +55896,22 @@
       </c>
       <c r="F1011" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1011" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H1011" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1011" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1011" t="inlineStr">
@@ -55920,13 +55920,13 @@
         </is>
       </c>
       <c r="K1011" s="1" t="n">
-        <v>46354.70833333334</v>
+        <v>46351.875</v>
       </c>
       <c r="L1011" s="1" t="n">
-        <v>46354.83333333334</v>
+        <v>46352.04166666666</v>
       </c>
       <c r="M1011" s="1" t="n">
-        <v>46356.16666666666</v>
+        <v>46352.5</v>
       </c>
     </row>
     <row r="1012">
@@ -55951,12 +55951,12 @@
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1012" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H1012" t="inlineStr">
@@ -55971,17 +55971,17 @@
       </c>
       <c r="J1012" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K1012" s="1" t="n">
-        <v>46356.66666666666</v>
+        <v>46354.25</v>
       </c>
       <c r="L1012" s="1" t="n">
-        <v>46356.70833333334</v>
+        <v>46354.29166666666</v>
       </c>
       <c r="M1012" s="1" t="n">
-        <v>46357</v>
+        <v>46354.45833333334</v>
       </c>
     </row>
     <row r="1013">
@@ -56016,27 +56016,27 @@
       </c>
       <c r="H1013" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I1013" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J1013" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1013" s="1" t="n">
-        <v>46361.08333333334</v>
+        <v>46354.70833333334</v>
       </c>
       <c r="L1013" s="1" t="n">
-        <v>46361.125</v>
+        <v>46354.83333333334</v>
       </c>
       <c r="M1013" s="1" t="n">
-        <v>46361.58333333334</v>
+        <v>46356.16666666666</v>
       </c>
     </row>
     <row r="1014">
@@ -56071,133 +56071,133 @@
       </c>
       <c r="H1014" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1014" t="inlineStr">
         <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="J1014" t="inlineStr"/>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
       <c r="K1014" s="1" t="n">
-        <v>46362.66666666666</v>
+        <v>46356.66666666666</v>
       </c>
       <c r="L1014" s="1" t="n">
-        <v>46362.70833333334</v>
+        <v>46356.70833333334</v>
       </c>
       <c r="M1014" s="1" t="n">
-        <v>46363.29166666666</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>ANX</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>STARSHIP JUPITER</t>
+          <t>SKY ORION</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr"/>
       <c r="E1015" t="n">
-        <v>2607</v>
+        <v>2614</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1015" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H1015" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1015" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K1015" s="1" t="n">
-        <v>46266.45833333334</v>
+        <v>46361.08333333334</v>
       </c>
       <c r="L1015" s="1" t="n">
-        <v>46266.5</v>
+        <v>46361.125</v>
       </c>
       <c r="M1015" s="1" t="n">
-        <v>46267.1875</v>
+        <v>46361.58333333334</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>ANX</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>STARSHIP JUPITER</t>
+          <t>SKY ORION</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr"/>
       <c r="E1016" t="n">
-        <v>2607</v>
+        <v>2614</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1016" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H1016" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
         <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="J1016" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="J1016" t="inlineStr"/>
       <c r="K1016" s="1" t="n">
-        <v>46268.20833333334</v>
+        <v>46362.66666666666</v>
       </c>
       <c r="L1016" s="1" t="n">
-        <v>46268.5</v>
+        <v>46362.70833333334</v>
       </c>
       <c r="M1016" s="1" t="n">
-        <v>46270.04166666666</v>
+        <v>46363.29166666666</v>
       </c>
     </row>
     <row r="1017">
@@ -56232,27 +56232,27 @@
       </c>
       <c r="H1017" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1017" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1017" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1017" s="1" t="n">
-        <v>46270.125</v>
+        <v>46266.45833333334</v>
       </c>
       <c r="L1017" s="1" t="n">
-        <v>46270.16666666666</v>
+        <v>46266.5</v>
       </c>
       <c r="M1017" s="1" t="n">
-        <v>46270.375</v>
+        <v>46267.1875</v>
       </c>
     </row>
     <row r="1018">
@@ -56287,27 +56287,27 @@
       </c>
       <c r="H1018" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1018" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1018" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1018" s="1" t="n">
-        <v>46271.54166666666</v>
+        <v>46268.20833333334</v>
       </c>
       <c r="L1018" s="1" t="n">
-        <v>46278.52083333334</v>
+        <v>46268.5</v>
       </c>
       <c r="M1018" s="1" t="n">
-        <v>46279.54166666666</v>
+        <v>46270.04166666666</v>
       </c>
     </row>
     <row r="1019">
@@ -56342,27 +56342,27 @@
       </c>
       <c r="H1019" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1019" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1019" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1019" s="1" t="n">
-        <v>46283.75</v>
+        <v>46270.125</v>
       </c>
       <c r="L1019" s="1" t="n">
-        <v>46284.29166666666</v>
+        <v>46270.16666666666</v>
       </c>
       <c r="M1019" s="1" t="n">
-        <v>46284.85416666666</v>
+        <v>46270.375</v>
       </c>
     </row>
     <row r="1020">
@@ -56397,27 +56397,27 @@
       </c>
       <c r="H1020" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I1020" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1020" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1020" s="1" t="n">
-        <v>46286.52083333334</v>
+        <v>46271.54166666666</v>
       </c>
       <c r="L1020" s="1" t="n">
-        <v>46286.85416666666</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="M1020" s="1" t="n">
-        <v>46287.58333333334</v>
+        <v>46279.54166666666</v>
       </c>
     </row>
     <row r="1021">
@@ -56442,37 +56442,37 @@
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1021" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="H1021" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1021" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1021" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1021" s="1" t="n">
-        <v>46291.41666666666</v>
+        <v>46283.75</v>
       </c>
       <c r="L1021" s="1" t="n">
-        <v>46291.45833333334</v>
+        <v>46284.29166666666</v>
       </c>
       <c r="M1021" s="1" t="n">
-        <v>46293.04166666666</v>
+        <v>46284.85416666666</v>
       </c>
     </row>
     <row r="1022">
@@ -56497,37 +56497,37 @@
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1022" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1022" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1022" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1022" s="1" t="n">
-        <v>46295.625</v>
+        <v>46286.52083333334</v>
       </c>
       <c r="L1022" s="1" t="n">
-        <v>46295.79166666666</v>
+        <v>46286.85416666666</v>
       </c>
       <c r="M1022" s="1" t="n">
-        <v>46296.52083333334</v>
+        <v>46287.58333333334</v>
       </c>
     </row>
     <row r="1023">
@@ -56562,27 +56562,27 @@
       </c>
       <c r="H1023" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1023" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1023" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1023" s="1" t="n">
-        <v>46298.875</v>
+        <v>46291.41666666666</v>
       </c>
       <c r="L1023" s="1" t="n">
-        <v>46299.29166666666</v>
+        <v>46291.45833333334</v>
       </c>
       <c r="M1023" s="1" t="n">
-        <v>46300.20833333334</v>
+        <v>46293.04166666666</v>
       </c>
     </row>
     <row r="1024">
@@ -56617,27 +56617,27 @@
       </c>
       <c r="H1024" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1024" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1024" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1024" s="1" t="n">
-        <v>46300.33333333334</v>
+        <v>46295.625</v>
       </c>
       <c r="L1024" s="1" t="n">
-        <v>46302.33333333334</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="M1024" s="1" t="n">
-        <v>46303.02083333334</v>
+        <v>46296.52083333334</v>
       </c>
     </row>
     <row r="1025">
@@ -56658,41 +56658,41 @@
       </c>
       <c r="D1025" t="inlineStr"/>
       <c r="E1025" t="n">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1025" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="H1025" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1025" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1025" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1025" s="1" t="n">
-        <v>46306.125</v>
+        <v>46298.875</v>
       </c>
       <c r="L1025" s="1" t="n">
-        <v>46306.16666666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="M1025" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46300.20833333334</v>
       </c>
     </row>
     <row r="1026">
@@ -56713,41 +56713,41 @@
       </c>
       <c r="D1026" t="inlineStr"/>
       <c r="E1026" t="n">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1026" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="H1026" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1026" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1026" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1026" s="1" t="n">
-        <v>46307.91666666666</v>
+        <v>46300.33333333334</v>
       </c>
       <c r="L1026" s="1" t="n">
-        <v>46307.95833333334</v>
+        <v>46302.33333333334</v>
       </c>
       <c r="M1026" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46303.02083333334</v>
       </c>
     </row>
     <row r="1027">
@@ -56782,27 +56782,27 @@
       </c>
       <c r="H1027" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1027" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1027" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1027" s="1" t="n">
-        <v>46308.75</v>
+        <v>46306.125</v>
       </c>
       <c r="L1027" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46306.16666666666</v>
       </c>
       <c r="M1027" s="1" t="n">
-        <v>46309.125</v>
+        <v>46306.83333333334</v>
       </c>
     </row>
     <row r="1028">
@@ -56837,27 +56837,27 @@
       </c>
       <c r="H1028" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1028" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1028" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1028" s="1" t="n">
-        <v>46310.41666666666</v>
+        <v>46307.91666666666</v>
       </c>
       <c r="L1028" s="1" t="n">
-        <v>46310.58333333334</v>
+        <v>46307.95833333334</v>
       </c>
       <c r="M1028" s="1" t="n">
-        <v>46311.08333333334</v>
+        <v>46308.54166666666</v>
       </c>
     </row>
     <row r="1029">
@@ -56892,27 +56892,27 @@
       </c>
       <c r="H1029" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1029" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1029" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1029" s="1" t="n">
-        <v>46315.25</v>
+        <v>46308.75</v>
       </c>
       <c r="L1029" s="1" t="n">
-        <v>46315.41666666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="M1029" s="1" t="n">
-        <v>46316.25</v>
+        <v>46309.125</v>
       </c>
     </row>
     <row r="1030">
@@ -56947,27 +56947,27 @@
       </c>
       <c r="H1030" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1030" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1030" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1030" s="1" t="n">
-        <v>46317.95833333334</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="L1030" s="1" t="n">
-        <v>46318</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="M1030" s="1" t="n">
-        <v>46318.83333333334</v>
+        <v>46311.08333333334</v>
       </c>
     </row>
     <row r="1031">
@@ -56992,37 +56992,37 @@
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1031" t="inlineStr">
         <is>
-          <t>2608N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1031" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1031" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1031" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1031" s="1" t="n">
-        <v>46322</v>
+        <v>46315.25</v>
       </c>
       <c r="L1031" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="M1031" s="1" t="n">
-        <v>46323.72916666666</v>
+        <v>46316.25</v>
       </c>
     </row>
     <row r="1032">
@@ -57047,37 +57047,37 @@
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t>2608N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1032" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1032" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1032" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1032" s="1" t="n">
-        <v>46325.85416666666</v>
+        <v>46317.95833333334</v>
       </c>
       <c r="L1032" s="1" t="n">
-        <v>46326.02083333334</v>
+        <v>46318</v>
       </c>
       <c r="M1032" s="1" t="n">
-        <v>46326.85416666666</v>
+        <v>46318.83333333334</v>
       </c>
     </row>
     <row r="1033">
@@ -57112,27 +57112,27 @@
       </c>
       <c r="H1033" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1033" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1033" s="1" t="n">
-        <v>46329.375</v>
+        <v>46322</v>
       </c>
       <c r="L1033" s="1" t="n">
-        <v>46329.4375</v>
+        <v>46322.04166666666</v>
       </c>
       <c r="M1033" s="1" t="n">
-        <v>46329.9375</v>
+        <v>46323.72916666666</v>
       </c>
     </row>
     <row r="1034">
@@ -57167,27 +57167,27 @@
       </c>
       <c r="H1034" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1034" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1034" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1034" s="1" t="n">
-        <v>46330.16666666666</v>
+        <v>46325.85416666666</v>
       </c>
       <c r="L1034" s="1" t="n">
-        <v>46330.20833333334</v>
+        <v>46326.02083333334</v>
       </c>
       <c r="M1034" s="1" t="n">
-        <v>46330.70833333334</v>
+        <v>46326.85416666666</v>
       </c>
     </row>
     <row r="1035">
@@ -57208,41 +57208,41 @@
       </c>
       <c r="D1035" t="inlineStr"/>
       <c r="E1035" t="n">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1035" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1035" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1035" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1035" s="1" t="n">
-        <v>46333.89583333334</v>
+        <v>46329.375</v>
       </c>
       <c r="L1035" s="1" t="n">
-        <v>46333.9375</v>
+        <v>46329.4375</v>
       </c>
       <c r="M1035" s="1" t="n">
-        <v>46334.60416666666</v>
+        <v>46329.9375</v>
       </c>
     </row>
     <row r="1036">
@@ -57263,41 +57263,41 @@
       </c>
       <c r="D1036" t="inlineStr"/>
       <c r="E1036" t="n">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1036" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1036" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1036" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1036" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1036" s="1" t="n">
-        <v>46335.6875</v>
+        <v>46330.16666666666</v>
       </c>
       <c r="L1036" s="1" t="n">
-        <v>46335.72916666666</v>
+        <v>46330.20833333334</v>
       </c>
       <c r="M1036" s="1" t="n">
-        <v>46336.3125</v>
+        <v>46330.70833333334</v>
       </c>
     </row>
     <row r="1037">
@@ -57332,27 +57332,27 @@
       </c>
       <c r="H1037" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1037" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1037" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1037" s="1" t="n">
-        <v>46336.5</v>
+        <v>46333.89583333334</v>
       </c>
       <c r="L1037" s="1" t="n">
-        <v>46336.5625</v>
+        <v>46333.9375</v>
       </c>
       <c r="M1037" s="1" t="n">
-        <v>46336.89583333334</v>
+        <v>46334.60416666666</v>
       </c>
     </row>
     <row r="1038">
@@ -57387,27 +57387,27 @@
       </c>
       <c r="H1038" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1038" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1038" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1038" s="1" t="n">
-        <v>46338.1875</v>
+        <v>46335.6875</v>
       </c>
       <c r="L1038" s="1" t="n">
-        <v>46338.35416666666</v>
+        <v>46335.72916666666</v>
       </c>
       <c r="M1038" s="1" t="n">
-        <v>46338.85416666666</v>
+        <v>46336.3125</v>
       </c>
     </row>
     <row r="1039">
@@ -57442,27 +57442,27 @@
       </c>
       <c r="H1039" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1039" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1039" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1039" s="1" t="n">
-        <v>46343.02083333334</v>
+        <v>46336.5</v>
       </c>
       <c r="L1039" s="1" t="n">
-        <v>46343.1875</v>
+        <v>46336.5625</v>
       </c>
       <c r="M1039" s="1" t="n">
-        <v>46344.02083333334</v>
+        <v>46336.89583333334</v>
       </c>
     </row>
     <row r="1040">
@@ -57497,27 +57497,27 @@
       </c>
       <c r="H1040" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1040" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1040" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1040" s="1" t="n">
-        <v>46345.6875</v>
+        <v>46338.1875</v>
       </c>
       <c r="L1040" s="1" t="n">
-        <v>46345.72916666666</v>
+        <v>46338.35416666666</v>
       </c>
       <c r="M1040" s="1" t="n">
-        <v>46346.5625</v>
+        <v>46338.85416666666</v>
       </c>
     </row>
     <row r="1041">
@@ -57542,37 +57542,37 @@
       </c>
       <c r="F1041" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1041" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1041" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1041" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1041" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1041" s="1" t="n">
-        <v>46349.72916666666</v>
+        <v>46343.02083333334</v>
       </c>
       <c r="L1041" s="1" t="n">
-        <v>46349.8125</v>
+        <v>46343.1875</v>
       </c>
       <c r="M1041" s="1" t="n">
-        <v>46351.47916666666</v>
+        <v>46344.02083333334</v>
       </c>
     </row>
     <row r="1042">
@@ -57597,37 +57597,37 @@
       </c>
       <c r="F1042" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1042" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1042" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1042" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1042" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1042" s="1" t="n">
-        <v>46353.9375</v>
+        <v>46345.6875</v>
       </c>
       <c r="L1042" s="1" t="n">
-        <v>46354.10416666666</v>
+        <v>46345.72916666666</v>
       </c>
       <c r="M1042" s="1" t="n">
-        <v>46354.9375</v>
+        <v>46346.5625</v>
       </c>
     </row>
     <row r="1043">
@@ -57662,27 +57662,27 @@
       </c>
       <c r="H1043" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1043" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1043" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1043" s="1" t="n">
-        <v>46357.47916666666</v>
+        <v>46349.72916666666</v>
       </c>
       <c r="L1043" s="1" t="n">
-        <v>46357.54166666666</v>
+        <v>46349.8125</v>
       </c>
       <c r="M1043" s="1" t="n">
-        <v>46358.04166666666</v>
+        <v>46351.47916666666</v>
       </c>
     </row>
     <row r="1044">
@@ -57717,27 +57717,27 @@
       </c>
       <c r="H1044" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1044" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1044" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1044" s="1" t="n">
-        <v>46358.27083333334</v>
+        <v>46353.9375</v>
       </c>
       <c r="L1044" s="1" t="n">
-        <v>46358.3125</v>
+        <v>46354.10416666666</v>
       </c>
       <c r="M1044" s="1" t="n">
-        <v>46358.8125</v>
+        <v>46354.9375</v>
       </c>
     </row>
     <row r="1045">
@@ -57758,41 +57758,41 @@
       </c>
       <c r="D1045" t="inlineStr"/>
       <c r="E1045" t="n">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1045" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1045" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1045" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1045" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1045" s="1" t="n">
-        <v>46361.89583333334</v>
+        <v>46357.47916666666</v>
       </c>
       <c r="L1045" s="1" t="n">
-        <v>46361.9375</v>
+        <v>46357.54166666666</v>
       </c>
       <c r="M1045" s="1" t="n">
-        <v>46362.60416666666</v>
+        <v>46358.04166666666</v>
       </c>
     </row>
     <row r="1046">
@@ -57813,41 +57813,41 @@
       </c>
       <c r="D1046" t="inlineStr"/>
       <c r="E1046" t="n">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1046" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1046" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1046" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1046" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1046" s="1" t="n">
-        <v>46363.6875</v>
+        <v>46358.27083333334</v>
       </c>
       <c r="L1046" s="1" t="n">
-        <v>46363.72916666666</v>
+        <v>46358.3125</v>
       </c>
       <c r="M1046" s="1" t="n">
-        <v>46364.3125</v>
+        <v>46358.8125</v>
       </c>
     </row>
     <row r="1047">
@@ -57882,27 +57882,27 @@
       </c>
       <c r="H1047" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1047" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1047" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1047" s="1" t="n">
-        <v>46364.5</v>
+        <v>46361.89583333334</v>
       </c>
       <c r="L1047" s="1" t="n">
-        <v>46364.5625</v>
+        <v>46361.9375</v>
       </c>
       <c r="M1047" s="1" t="n">
-        <v>46364.89583333334</v>
+        <v>46362.60416666666</v>
       </c>
     </row>
     <row r="1048">
@@ -57937,27 +57937,27 @@
       </c>
       <c r="H1048" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1048" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1048" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1048" s="1" t="n">
-        <v>46366.1875</v>
+        <v>46363.6875</v>
       </c>
       <c r="L1048" s="1" t="n">
-        <v>46366.35416666666</v>
+        <v>46363.72916666666</v>
       </c>
       <c r="M1048" s="1" t="n">
-        <v>46366.85416666666</v>
+        <v>46364.3125</v>
       </c>
     </row>
     <row r="1049">
@@ -57992,27 +57992,27 @@
       </c>
       <c r="H1049" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1049" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1049" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1049" s="1" t="n">
-        <v>46371.02083333334</v>
+        <v>46364.5</v>
       </c>
       <c r="L1049" s="1" t="n">
-        <v>46371.1875</v>
+        <v>46364.5625</v>
       </c>
       <c r="M1049" s="1" t="n">
-        <v>46372.02083333334</v>
+        <v>46364.89583333334</v>
       </c>
     </row>
     <row r="1050">
@@ -58047,27 +58047,27 @@
       </c>
       <c r="H1050" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1050" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1050" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1050" s="1" t="n">
-        <v>46373.6875</v>
+        <v>46366.1875</v>
       </c>
       <c r="L1050" s="1" t="n">
-        <v>46373.72916666666</v>
+        <v>46366.35416666666</v>
       </c>
       <c r="M1050" s="1" t="n">
-        <v>46374.5625</v>
+        <v>46366.85416666666</v>
       </c>
     </row>
     <row r="1051">
@@ -58092,37 +58092,37 @@
       </c>
       <c r="F1051" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1051" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="H1051" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1051" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1051" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1051" s="1" t="n">
-        <v>46377.72916666666</v>
+        <v>46371.02083333334</v>
       </c>
       <c r="L1051" s="1" t="n">
-        <v>46377.8125</v>
+        <v>46371.1875</v>
       </c>
       <c r="M1051" s="1" t="n">
-        <v>46379.47916666666</v>
+        <v>46372.02083333334</v>
       </c>
     </row>
     <row r="1052">
@@ -58147,37 +58147,37 @@
       </c>
       <c r="F1052" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1052" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="H1052" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1052" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1052" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1052" s="1" t="n">
-        <v>46381.9375</v>
+        <v>46373.6875</v>
       </c>
       <c r="L1052" s="1" t="n">
-        <v>46382.10416666666</v>
+        <v>46373.72916666666</v>
       </c>
       <c r="M1052" s="1" t="n">
-        <v>46382.9375</v>
+        <v>46374.5625</v>
       </c>
     </row>
     <row r="1053">
@@ -58212,27 +58212,27 @@
       </c>
       <c r="H1053" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1053" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1053" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1053" s="1" t="n">
-        <v>46385.47916666666</v>
+        <v>46377.72916666666</v>
       </c>
       <c r="L1053" s="1" t="n">
-        <v>46385.54166666666</v>
+        <v>46377.8125</v>
       </c>
       <c r="M1053" s="1" t="n">
-        <v>46386.04166666666</v>
+        <v>46379.47916666666</v>
       </c>
     </row>
     <row r="1054">
@@ -58267,23 +58267,27 @@
       </c>
       <c r="H1054" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1054" t="inlineStr">
         <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="J1054" t="inlineStr"/>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
       <c r="K1054" s="1" t="n">
-        <v>46386.27083333334</v>
+        <v>46381.9375</v>
       </c>
       <c r="L1054" s="1" t="n">
-        <v>46386.3125</v>
+        <v>46382.10416666666</v>
       </c>
       <c r="M1054" s="1" t="n">
-        <v>46386.8125</v>
+        <v>46382.9375</v>
       </c>
     </row>
     <row r="1055">
@@ -58294,51 +58298,51 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>YEOSU VOYAGER</t>
+          <t>STARSHIP JUPITER</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr"/>
       <c r="E1055" t="n">
-        <v>2608</v>
+        <v>2610</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1055" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="H1055" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1055" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1055" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1055" s="1" t="n">
-        <v>46301.5</v>
+        <v>46385.47916666666</v>
       </c>
       <c r="L1055" s="1" t="n">
-        <v>46302.875</v>
+        <v>46385.54166666666</v>
       </c>
       <c r="M1055" s="1" t="n">
-        <v>46303.54166666666</v>
+        <v>46386.04166666666</v>
       </c>
     </row>
     <row r="1056">
@@ -58349,51 +58353,47 @@
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>YEOSU VOYAGER</t>
+          <t>STARSHIP JUPITER</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr"/>
       <c r="E1056" t="n">
-        <v>2608</v>
+        <v>2610</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1056" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="H1056" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1056" t="inlineStr">
         <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="J1056" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="J1056" t="inlineStr"/>
       <c r="K1056" s="1" t="n">
-        <v>46303.64583333334</v>
+        <v>46386.27083333334</v>
       </c>
       <c r="L1056" s="1" t="n">
-        <v>46303.6875</v>
+        <v>46386.3125</v>
       </c>
       <c r="M1056" s="1" t="n">
-        <v>46304.01041666666</v>
+        <v>46386.8125</v>
       </c>
     </row>
     <row r="1057">
@@ -58428,27 +58428,27 @@
       </c>
       <c r="H1057" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1057" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1057" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1057" s="1" t="n">
-        <v>46305.08333333334</v>
+        <v>46301.5</v>
       </c>
       <c r="L1057" s="1" t="n">
-        <v>46305.125</v>
+        <v>46302.875</v>
       </c>
       <c r="M1057" s="1" t="n">
-        <v>46305.79166666666</v>
+        <v>46303.54166666666</v>
       </c>
     </row>
     <row r="1058">
@@ -58483,27 +58483,27 @@
       </c>
       <c r="H1058" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1058" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1058" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1058" s="1" t="n">
-        <v>46307.0625</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="L1058" s="1" t="n">
-        <v>46307.22916666666</v>
+        <v>46303.6875</v>
       </c>
       <c r="M1058" s="1" t="n">
-        <v>46307.72916666666</v>
+        <v>46304.01041666666</v>
       </c>
     </row>
     <row r="1059">
@@ -58538,27 +58538,27 @@
       </c>
       <c r="H1059" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1059" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1059" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1059" s="1" t="n">
-        <v>46311.89583333334</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="L1059" s="1" t="n">
-        <v>46312.0625</v>
+        <v>46305.125</v>
       </c>
       <c r="M1059" s="1" t="n">
-        <v>46312.89583333334</v>
+        <v>46305.79166666666</v>
       </c>
     </row>
     <row r="1060">
@@ -58593,27 +58593,27 @@
       </c>
       <c r="H1060" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1060" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1060" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1060" s="1" t="n">
-        <v>46314.5625</v>
+        <v>46307.0625</v>
       </c>
       <c r="L1060" s="1" t="n">
-        <v>46314.60416666666</v>
+        <v>46307.22916666666</v>
       </c>
       <c r="M1060" s="1" t="n">
-        <v>46315.4375</v>
+        <v>46307.72916666666</v>
       </c>
     </row>
     <row r="1061">
@@ -58638,37 +58638,37 @@
       </c>
       <c r="F1061" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1061" t="inlineStr">
         <is>
-          <t>2608N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1061" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1061" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1061" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1061" s="1" t="n">
-        <v>46318.60416666666</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="L1061" s="1" t="n">
-        <v>46318.6875</v>
+        <v>46312.0625</v>
       </c>
       <c r="M1061" s="1" t="n">
-        <v>46320.35416666666</v>
+        <v>46312.89583333334</v>
       </c>
     </row>
     <row r="1062">
@@ -58693,37 +58693,37 @@
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1062" t="inlineStr">
         <is>
-          <t>2608N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1062" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1062" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1062" s="1" t="n">
-        <v>46322.8125</v>
+        <v>46314.5625</v>
       </c>
       <c r="L1062" s="1" t="n">
-        <v>46322.97916666666</v>
+        <v>46314.60416666666</v>
       </c>
       <c r="M1062" s="1" t="n">
-        <v>46323.8125</v>
+        <v>46315.4375</v>
       </c>
     </row>
     <row r="1063">
@@ -58758,27 +58758,27 @@
       </c>
       <c r="H1063" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1063" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1063" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1063" s="1" t="n">
-        <v>46326.35416666666</v>
+        <v>46318.60416666666</v>
       </c>
       <c r="L1063" s="1" t="n">
-        <v>46326.41666666666</v>
+        <v>46318.6875</v>
       </c>
       <c r="M1063" s="1" t="n">
-        <v>46326.91666666666</v>
+        <v>46320.35416666666</v>
       </c>
     </row>
     <row r="1064">
@@ -58813,27 +58813,27 @@
       </c>
       <c r="H1064" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1064" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1064" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1064" s="1" t="n">
-        <v>46327.14583333334</v>
+        <v>46322.8125</v>
       </c>
       <c r="L1064" s="1" t="n">
-        <v>46327.1875</v>
+        <v>46322.97916666666</v>
       </c>
       <c r="M1064" s="1" t="n">
-        <v>46327.6875</v>
+        <v>46323.8125</v>
       </c>
     </row>
     <row r="1065">
@@ -58854,41 +58854,41 @@
       </c>
       <c r="D1065" t="inlineStr"/>
       <c r="E1065" t="n">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1065" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1065" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1065" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1065" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1065" s="1" t="n">
-        <v>46330.77083333334</v>
+        <v>46326.35416666666</v>
       </c>
       <c r="L1065" s="1" t="n">
-        <v>46330.8125</v>
+        <v>46326.41666666666</v>
       </c>
       <c r="M1065" s="1" t="n">
-        <v>46331.47916666666</v>
+        <v>46326.91666666666</v>
       </c>
     </row>
     <row r="1066">
@@ -58909,41 +58909,41 @@
       </c>
       <c r="D1066" t="inlineStr"/>
       <c r="E1066" t="n">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1066" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1066" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1066" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1066" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1066" s="1" t="n">
-        <v>46332.5625</v>
+        <v>46327.14583333334</v>
       </c>
       <c r="L1066" s="1" t="n">
-        <v>46332.60416666666</v>
+        <v>46327.1875</v>
       </c>
       <c r="M1066" s="1" t="n">
-        <v>46333.1875</v>
+        <v>46327.6875</v>
       </c>
     </row>
     <row r="1067">
@@ -58978,27 +58978,27 @@
       </c>
       <c r="H1067" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1067" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1067" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1067" s="1" t="n">
-        <v>46333.375</v>
+        <v>46330.77083333334</v>
       </c>
       <c r="L1067" s="1" t="n">
-        <v>46333.4375</v>
+        <v>46330.8125</v>
       </c>
       <c r="M1067" s="1" t="n">
-        <v>46333.77083333334</v>
+        <v>46331.47916666666</v>
       </c>
     </row>
     <row r="1068">
@@ -59033,27 +59033,27 @@
       </c>
       <c r="H1068" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1068" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1068" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1068" s="1" t="n">
-        <v>46335.0625</v>
+        <v>46332.5625</v>
       </c>
       <c r="L1068" s="1" t="n">
-        <v>46335.22916666666</v>
+        <v>46332.60416666666</v>
       </c>
       <c r="M1068" s="1" t="n">
-        <v>46335.72916666666</v>
+        <v>46333.1875</v>
       </c>
     </row>
     <row r="1069">
@@ -59088,27 +59088,27 @@
       </c>
       <c r="H1069" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1069" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1069" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1069" s="1" t="n">
-        <v>46339.89583333334</v>
+        <v>46333.375</v>
       </c>
       <c r="L1069" s="1" t="n">
-        <v>46340.0625</v>
+        <v>46333.4375</v>
       </c>
       <c r="M1069" s="1" t="n">
-        <v>46340.89583333334</v>
+        <v>46333.77083333334</v>
       </c>
     </row>
     <row r="1070">
@@ -59143,27 +59143,27 @@
       </c>
       <c r="H1070" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1070" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1070" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1070" s="1" t="n">
-        <v>46342.5625</v>
+        <v>46335.0625</v>
       </c>
       <c r="L1070" s="1" t="n">
-        <v>46342.60416666666</v>
+        <v>46335.22916666666</v>
       </c>
       <c r="M1070" s="1" t="n">
-        <v>46343.4375</v>
+        <v>46335.72916666666</v>
       </c>
     </row>
     <row r="1071">
@@ -59188,37 +59188,37 @@
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1071" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1071" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1071" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1071" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1071" s="1" t="n">
-        <v>46346.60416666666</v>
+        <v>46339.89583333334</v>
       </c>
       <c r="L1071" s="1" t="n">
-        <v>46346.6875</v>
+        <v>46340.0625</v>
       </c>
       <c r="M1071" s="1" t="n">
-        <v>46348.35416666666</v>
+        <v>46340.89583333334</v>
       </c>
     </row>
     <row r="1072">
@@ -59243,37 +59243,37 @@
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1072" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1072" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1072" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1072" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1072" s="1" t="n">
-        <v>46350.8125</v>
+        <v>46342.5625</v>
       </c>
       <c r="L1072" s="1" t="n">
-        <v>46350.97916666666</v>
+        <v>46342.60416666666</v>
       </c>
       <c r="M1072" s="1" t="n">
-        <v>46351.8125</v>
+        <v>46343.4375</v>
       </c>
     </row>
     <row r="1073">
@@ -59308,27 +59308,27 @@
       </c>
       <c r="H1073" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1073" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1073" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1073" s="1" t="n">
-        <v>46354.35416666666</v>
+        <v>46346.60416666666</v>
       </c>
       <c r="L1073" s="1" t="n">
-        <v>46354.41666666666</v>
+        <v>46346.6875</v>
       </c>
       <c r="M1073" s="1" t="n">
-        <v>46354.91666666666</v>
+        <v>46348.35416666666</v>
       </c>
     </row>
     <row r="1074">
@@ -59363,27 +59363,27 @@
       </c>
       <c r="H1074" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1074" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1074" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1074" s="1" t="n">
-        <v>46355.14583333334</v>
+        <v>46350.8125</v>
       </c>
       <c r="L1074" s="1" t="n">
-        <v>46355.1875</v>
+        <v>46350.97916666666</v>
       </c>
       <c r="M1074" s="1" t="n">
-        <v>46355.6875</v>
+        <v>46351.8125</v>
       </c>
     </row>
     <row r="1075">
@@ -59404,41 +59404,41 @@
       </c>
       <c r="D1075" t="inlineStr"/>
       <c r="E1075" t="n">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1075" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1075" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1075" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1075" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1075" s="1" t="n">
-        <v>46358.77083333334</v>
+        <v>46354.35416666666</v>
       </c>
       <c r="L1075" s="1" t="n">
-        <v>46358.8125</v>
+        <v>46354.41666666666</v>
       </c>
       <c r="M1075" s="1" t="n">
-        <v>46359.47916666666</v>
+        <v>46354.91666666666</v>
       </c>
     </row>
     <row r="1076">
@@ -59459,41 +59459,41 @@
       </c>
       <c r="D1076" t="inlineStr"/>
       <c r="E1076" t="n">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1076" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1076" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1076" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1076" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1076" s="1" t="n">
-        <v>46360.5625</v>
+        <v>46355.14583333334</v>
       </c>
       <c r="L1076" s="1" t="n">
-        <v>46360.60416666666</v>
+        <v>46355.1875</v>
       </c>
       <c r="M1076" s="1" t="n">
-        <v>46361.1875</v>
+        <v>46355.6875</v>
       </c>
     </row>
     <row r="1077">
@@ -59528,27 +59528,27 @@
       </c>
       <c r="H1077" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1077" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1077" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1077" s="1" t="n">
-        <v>46361.375</v>
+        <v>46358.77083333334</v>
       </c>
       <c r="L1077" s="1" t="n">
-        <v>46361.4375</v>
+        <v>46358.8125</v>
       </c>
       <c r="M1077" s="1" t="n">
-        <v>46361.77083333334</v>
+        <v>46359.47916666666</v>
       </c>
     </row>
     <row r="1078">
@@ -59583,27 +59583,27 @@
       </c>
       <c r="H1078" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1078" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1078" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1078" s="1" t="n">
-        <v>46363.0625</v>
+        <v>46360.5625</v>
       </c>
       <c r="L1078" s="1" t="n">
-        <v>46363.22916666666</v>
+        <v>46360.60416666666</v>
       </c>
       <c r="M1078" s="1" t="n">
-        <v>46363.72916666666</v>
+        <v>46361.1875</v>
       </c>
     </row>
     <row r="1079">
@@ -59638,27 +59638,27 @@
       </c>
       <c r="H1079" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1079" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1079" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1079" s="1" t="n">
-        <v>46367.89583333334</v>
+        <v>46361.375</v>
       </c>
       <c r="L1079" s="1" t="n">
-        <v>46368.0625</v>
+        <v>46361.4375</v>
       </c>
       <c r="M1079" s="1" t="n">
-        <v>46368.89583333334</v>
+        <v>46361.77083333334</v>
       </c>
     </row>
     <row r="1080">
@@ -59693,27 +59693,27 @@
       </c>
       <c r="H1080" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1080" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1080" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1080" s="1" t="n">
-        <v>46370.5625</v>
+        <v>46363.0625</v>
       </c>
       <c r="L1080" s="1" t="n">
-        <v>46370.60416666666</v>
+        <v>46363.22916666666</v>
       </c>
       <c r="M1080" s="1" t="n">
-        <v>46371.4375</v>
+        <v>46363.72916666666</v>
       </c>
     </row>
     <row r="1081">
@@ -59738,37 +59738,37 @@
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1081" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="H1081" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1081" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1081" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1081" s="1" t="n">
-        <v>46374.60416666666</v>
+        <v>46367.89583333334</v>
       </c>
       <c r="L1081" s="1" t="n">
-        <v>46374.6875</v>
+        <v>46368.0625</v>
       </c>
       <c r="M1081" s="1" t="n">
-        <v>46376.35416666666</v>
+        <v>46368.89583333334</v>
       </c>
     </row>
     <row r="1082">
@@ -59793,37 +59793,37 @@
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1082" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="H1082" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1082" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1082" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1082" s="1" t="n">
-        <v>46378.8125</v>
+        <v>46370.5625</v>
       </c>
       <c r="L1082" s="1" t="n">
-        <v>46378.97916666666</v>
+        <v>46370.60416666666</v>
       </c>
       <c r="M1082" s="1" t="n">
-        <v>46379.8125</v>
+        <v>46371.4375</v>
       </c>
     </row>
     <row r="1083">
@@ -59858,27 +59858,27 @@
       </c>
       <c r="H1083" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1083" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1083" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1083" s="1" t="n">
-        <v>46382.35416666666</v>
+        <v>46374.60416666666</v>
       </c>
       <c r="L1083" s="1" t="n">
-        <v>46382.41666666666</v>
+        <v>46374.6875</v>
       </c>
       <c r="M1083" s="1" t="n">
-        <v>46382.91666666666</v>
+        <v>46376.35416666666</v>
       </c>
     </row>
     <row r="1084">
@@ -59913,27 +59913,27 @@
       </c>
       <c r="H1084" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1084" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1084" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1084" s="1" t="n">
-        <v>46383.14583333334</v>
+        <v>46378.8125</v>
       </c>
       <c r="L1084" s="1" t="n">
-        <v>46383.1875</v>
+        <v>46378.97916666666</v>
       </c>
       <c r="M1084" s="1" t="n">
-        <v>46383.6875</v>
+        <v>46379.8125</v>
       </c>
     </row>
     <row r="1085">
@@ -59954,41 +59954,41 @@
       </c>
       <c r="D1085" t="inlineStr"/>
       <c r="E1085" t="n">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1085" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="H1085" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1085" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1085" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1085" s="1" t="n">
-        <v>46386.77083333334</v>
+        <v>46382.35416666666</v>
       </c>
       <c r="L1085" s="1" t="n">
-        <v>46386.8125</v>
+        <v>46382.41666666666</v>
       </c>
       <c r="M1085" s="1" t="n">
-        <v>46387.47916666666</v>
+        <v>46382.91666666666</v>
       </c>
     </row>
     <row r="1086">
@@ -60009,41 +60009,41 @@
       </c>
       <c r="D1086" t="inlineStr"/>
       <c r="E1086" t="n">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1086" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="H1086" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1086" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1086" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1086" s="1" t="n">
-        <v>46388.5625</v>
+        <v>46383.14583333334</v>
       </c>
       <c r="L1086" s="1" t="n">
-        <v>46388.60416666666</v>
+        <v>46383.1875</v>
       </c>
       <c r="M1086" s="1" t="n">
-        <v>46389.1875</v>
+        <v>46383.6875</v>
       </c>
     </row>
     <row r="1087">
@@ -60078,27 +60078,27 @@
       </c>
       <c r="H1087" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1087" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1087" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1087" s="1" t="n">
-        <v>46389.375</v>
+        <v>46386.77083333334</v>
       </c>
       <c r="L1087" s="1" t="n">
-        <v>46389.4375</v>
+        <v>46386.8125</v>
       </c>
       <c r="M1087" s="1" t="n">
-        <v>46389.77083333334</v>
+        <v>46387.47916666666</v>
       </c>
     </row>
     <row r="1088">
@@ -60133,27 +60133,27 @@
       </c>
       <c r="H1088" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1088" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1088" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1088" s="1" t="n">
-        <v>46391.0625</v>
+        <v>46388.5625</v>
       </c>
       <c r="L1088" s="1" t="n">
-        <v>46391.22916666666</v>
+        <v>46388.60416666666</v>
       </c>
       <c r="M1088" s="1" t="n">
-        <v>46391.72916666666</v>
+        <v>46389.1875</v>
       </c>
     </row>
     <row r="1089">
@@ -60188,27 +60188,27 @@
       </c>
       <c r="H1089" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1089" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1089" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1089" s="1" t="n">
-        <v>46395.89583333334</v>
+        <v>46389.375</v>
       </c>
       <c r="L1089" s="1" t="n">
-        <v>46396.0625</v>
+        <v>46389.4375</v>
       </c>
       <c r="M1089" s="1" t="n">
-        <v>46396.89583333334</v>
+        <v>46389.77083333334</v>
       </c>
     </row>
     <row r="1090">
@@ -60243,27 +60243,27 @@
       </c>
       <c r="H1090" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1090" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1090" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1090" s="1" t="n">
-        <v>46398.5625</v>
+        <v>46391.0625</v>
       </c>
       <c r="L1090" s="1" t="n">
-        <v>46398.60416666666</v>
+        <v>46391.22916666666</v>
       </c>
       <c r="M1090" s="1" t="n">
-        <v>46399.4375</v>
+        <v>46391.72916666666</v>
       </c>
     </row>
     <row r="1091">
@@ -60288,37 +60288,37 @@
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1091" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="H1091" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1091" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1091" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1091" s="1" t="n">
-        <v>46402.60416666666</v>
+        <v>46395.89583333334</v>
       </c>
       <c r="L1091" s="1" t="n">
-        <v>46402.6875</v>
+        <v>46396.0625</v>
       </c>
       <c r="M1091" s="1" t="n">
-        <v>46404.35416666666</v>
+        <v>46396.89583333334</v>
       </c>
     </row>
     <row r="1092">
@@ -60343,37 +60343,37 @@
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1092" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="H1092" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1092" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1092" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1092" s="1" t="n">
-        <v>46406.8125</v>
+        <v>46398.5625</v>
       </c>
       <c r="L1092" s="1" t="n">
-        <v>46406.97916666666</v>
+        <v>46398.60416666666</v>
       </c>
       <c r="M1092" s="1" t="n">
-        <v>46407.8125</v>
+        <v>46399.4375</v>
       </c>
     </row>
     <row r="1093">
@@ -60408,27 +60408,27 @@
       </c>
       <c r="H1093" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1093" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1093" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1093" s="1" t="n">
-        <v>46410.35416666666</v>
+        <v>46402.60416666666</v>
       </c>
       <c r="L1093" s="1" t="n">
-        <v>46410.41666666666</v>
+        <v>46402.6875</v>
       </c>
       <c r="M1093" s="1" t="n">
-        <v>46410.91666666666</v>
+        <v>46404.35416666666</v>
       </c>
     </row>
     <row r="1094">
@@ -60463,22 +60463,132 @@
       </c>
       <c r="H1094" t="inlineStr">
         <is>
+          <t>SGN03</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="K1094" s="1" t="n">
+        <v>46406.8125</v>
+      </c>
+      <c r="L1094" s="1" t="n">
+        <v>46406.97916666666</v>
+      </c>
+      <c r="M1094" s="1" t="n">
+        <v>46407.8125</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>ANX</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>YEOSU VOYAGER</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr"/>
+      <c r="E1095" t="n">
+        <v>2611</v>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>HKG03</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="K1095" s="1" t="n">
+        <v>46410.35416666666</v>
+      </c>
+      <c r="L1095" s="1" t="n">
+        <v>46410.41666666666</v>
+      </c>
+      <c r="M1095" s="1" t="n">
+        <v>46410.91666666666</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>ANX</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>YEOSU VOYAGER</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr"/>
+      <c r="E1096" t="n">
+        <v>2611</v>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
           <t>SHE04</t>
         </is>
       </c>
-      <c r="I1094" t="inlineStr">
+      <c r="I1096" t="inlineStr">
         <is>
           <t>CNSHK</t>
         </is>
       </c>
-      <c r="J1094" t="inlineStr"/>
-      <c r="K1094" s="1" t="n">
+      <c r="J1096" t="inlineStr"/>
+      <c r="K1096" s="1" t="n">
         <v>46411.14583333334</v>
       </c>
-      <c r="L1094" s="1" t="n">
+      <c r="L1096" s="1" t="n">
         <v>46411.1875</v>
       </c>
-      <c r="M1094" s="1" t="n">
+      <c r="M1096" s="1" t="n">
         <v>46411.6875</v>
       </c>
     </row>

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -5423,10 +5423,10 @@
         <v>46301.75</v>
       </c>
       <c r="L91" s="1" t="n">
-        <v>46301.775</v>
+        <v>46301.79166666666</v>
       </c>
       <c r="M91" s="1" t="n">
-        <v>46302.95833333334</v>
+        <v>46303.04166666666</v>
       </c>
     </row>
     <row r="92">
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46303.25</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="L92" s="1" t="n">
-        <v>46303.3125</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>46303.9375</v>
+        <v>46304.02083333334</v>
       </c>
     </row>
     <row r="93">
@@ -5530,13 +5530,13 @@
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46304.95833333334</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>46305.16666666666</v>
+        <v>46305.25</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>46305.83333333334</v>
+        <v>46305.91666666666</v>
       </c>
     </row>
     <row r="94">
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46312.83333333334</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>46312.91666666666</v>
+        <v>46313</v>
       </c>
       <c r="M94" s="1" t="n">
-        <v>46313.75</v>
+        <v>46313.83333333334</v>
       </c>
     </row>
     <row r="95">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46314.83333333334</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>46314.91666666666</v>
+        <v>46315</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>46315.41666666666</v>
+        <v>46315.5</v>
       </c>
     </row>
     <row r="96">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46319.41666666666</v>
+        <v>46319.5</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>46319.45833333334</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>46320.125</v>
+        <v>46320.20833333334</v>
       </c>
     </row>
     <row r="97">
@@ -5750,13 +5750,13 @@
         </is>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46326.54166666666</v>
+        <v>46326.625</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>46326.75</v>
+        <v>46326.83333333334</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>46327.41666666666</v>
+        <v>46327.5</v>
       </c>
     </row>
     <row r="98">
@@ -40603,13 +40603,13 @@
         </is>
       </c>
       <c r="K732" s="1" t="n">
-        <v>46306.875</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="L732" s="1" t="n">
-        <v>46306.875</v>
+        <v>46307</v>
       </c>
       <c r="M732" s="1" t="n">
-        <v>46307.33333333334</v>
+        <v>46307.45833333334</v>
       </c>
     </row>
     <row r="733">
@@ -40658,13 +40658,13 @@
         </is>
       </c>
       <c r="K733" s="1" t="n">
-        <v>46308.33333333334</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="L733" s="1" t="n">
-        <v>46308.33333333334</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="M733" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46308.875</v>
       </c>
     </row>
     <row r="734">
@@ -40713,13 +40713,13 @@
         </is>
       </c>
       <c r="K734" s="1" t="n">
-        <v>46311.29166666666</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="L734" s="1" t="n">
-        <v>46311.33333333334</v>
+        <v>46311.5</v>
       </c>
       <c r="M734" s="1" t="n">
-        <v>46311.95833333334</v>
+        <v>46312.125</v>
       </c>
     </row>
     <row r="735">
@@ -40768,13 +40768,13 @@
         </is>
       </c>
       <c r="K735" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.125</v>
       </c>
       <c r="L735" s="1" t="n">
-        <v>46313</v>
+        <v>46313.16666666666</v>
       </c>
       <c r="M735" s="1" t="n">
-        <v>46313.5</v>
+        <v>46313.66666666666</v>
       </c>
     </row>
     <row r="736">
@@ -40823,13 +40823,13 @@
         </is>
       </c>
       <c r="K736" s="1" t="n">
-        <v>46314.58333333334</v>
+        <v>46314.75</v>
       </c>
       <c r="L736" s="1" t="n">
-        <v>46314.75</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="M736" s="1" t="n">
-        <v>46315.54166666666</v>
+        <v>46315.70833333334</v>
       </c>
     </row>
     <row r="737">
@@ -40878,13 +40878,13 @@
         </is>
       </c>
       <c r="K737" s="1" t="n">
-        <v>46321.29166666666</v>
+        <v>46321.45833333334</v>
       </c>
       <c r="L737" s="1" t="n">
-        <v>46321.33333333334</v>
+        <v>46321.5</v>
       </c>
       <c r="M737" s="1" t="n">
-        <v>46321.625</v>
+        <v>46321.79166666666</v>
       </c>
     </row>
     <row r="738">
@@ -40933,13 +40933,13 @@
         </is>
       </c>
       <c r="K738" s="1" t="n">
-        <v>46321.91666666666</v>
+        <v>46322.08333333334</v>
       </c>
       <c r="L738" s="1" t="n">
-        <v>46321.91666666666</v>
+        <v>46322.08333333334</v>
       </c>
       <c r="M738" s="1" t="n">
-        <v>46323.29166666666</v>
+        <v>46323.45833333334</v>
       </c>
     </row>
     <row r="739">
@@ -40988,13 +40988,13 @@
         </is>
       </c>
       <c r="K739" s="1" t="n">
-        <v>46323.54166666666</v>
+        <v>46323.70833333334</v>
       </c>
       <c r="L739" s="1" t="n">
-        <v>46323.58333333334</v>
+        <v>46323.75</v>
       </c>
       <c r="M739" s="1" t="n">
-        <v>46324.04166666666</v>
+        <v>46324.20833333334</v>
       </c>
     </row>
     <row r="740">
@@ -41043,13 +41043,13 @@
         </is>
       </c>
       <c r="K740" s="1" t="n">
-        <v>46327.875</v>
+        <v>46328.04166666666</v>
       </c>
       <c r="L740" s="1" t="n">
-        <v>46327.875</v>
+        <v>46328.04166666666</v>
       </c>
       <c r="M740" s="1" t="n">
-        <v>46328.33333333334</v>
+        <v>46328.5</v>
       </c>
     </row>
     <row r="741">
@@ -41098,13 +41098,13 @@
         </is>
       </c>
       <c r="K741" s="1" t="n">
-        <v>46329.33333333334</v>
+        <v>46329.5</v>
       </c>
       <c r="L741" s="1" t="n">
-        <v>46329.33333333334</v>
+        <v>46329.5</v>
       </c>
       <c r="M741" s="1" t="n">
-        <v>46329.83333333334</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="742">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1085"/>
+  <dimension ref="A1:M1087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46304.625</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>46304.66666666666</v>
+        <v>46305</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>46305</v>
+        <v>46305.33333333334</v>
       </c>
     </row>
     <row r="56">
@@ -3499,13 +3499,13 @@
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46305.125</v>
+        <v>46305.45833333334</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>46305.20833333334</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>46306.20833333334</v>
+        <v>46306.54166666666</v>
       </c>
     </row>
     <row r="57">
@@ -3554,13 +3554,13 @@
         </is>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46306.41666666666</v>
+        <v>46306.75</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>46306.45833333334</v>
+        <v>46306.79166666666</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>46306.95833333334</v>
+        <v>46307.29166666666</v>
       </c>
     </row>
     <row r="58">
@@ -3609,13 +3609,13 @@
         </is>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46308.77083333334</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>46308.9375</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>46309.625</v>
+        <v>46309.64583333334</v>
       </c>
     </row>
     <row r="59">
@@ -3664,13 +3664,13 @@
         </is>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46314.83333333334</v>
+        <v>46314.85416666666</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>46314.875</v>
+        <v>46314.89583333334</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>46315.54166666666</v>
+        <v>46315.5625</v>
       </c>
     </row>
     <row r="60">
@@ -3719,13 +3719,13 @@
         </is>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46315.70833333334</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>46315.77083333334</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>46316.02083333334</v>
+        <v>46316.04166666666</v>
       </c>
     </row>
     <row r="61">
@@ -3774,13 +3774,13 @@
         </is>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46316.91666666666</v>
+        <v>46316.9375</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>46316.97916666666</v>
+        <v>46317</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>46317.39583333334</v>
+        <v>46317.41666666666</v>
       </c>
     </row>
     <row r="62">
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46317.66666666666</v>
+        <v>46317.6875</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>46317.6875</v>
+        <v>46317.70833333334</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>46318.29166666666</v>
+        <v>46318.3125</v>
       </c>
     </row>
     <row r="63">
@@ -3884,13 +3884,13 @@
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46323.20833333334</v>
+        <v>46323.22916666666</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>46323.375</v>
+        <v>46323.39583333334</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>46323.95833333334</v>
+        <v>46323.97916666666</v>
       </c>
     </row>
     <row r="64">
@@ -3939,13 +3939,13 @@
         </is>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46325.60416666666</v>
+        <v>46325.625</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>46325.64583333334</v>
+        <v>46325.66666666666</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>46326</v>
+        <v>46326.02083333334</v>
       </c>
     </row>
     <row r="65">
@@ -3994,13 +3994,13 @@
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46326.125</v>
+        <v>46326.14583333334</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>46326.20833333334</v>
+        <v>46326.22916666666</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>46327.20833333334</v>
+        <v>46327.22916666666</v>
       </c>
     </row>
     <row r="66">
@@ -4049,13 +4049,13 @@
         </is>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46327.41666666666</v>
+        <v>46327.4375</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>46327.45833333334</v>
+        <v>46327.47916666666</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>46327.95833333334</v>
+        <v>46327.97916666666</v>
       </c>
     </row>
     <row r="67">
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46329.77083333334</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>46329.9375</v>
+        <v>46329.95833333334</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>46330.625</v>
+        <v>46330.64583333334</v>
       </c>
     </row>
     <row r="68">
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46335.83333333334</v>
+        <v>46335.85416666666</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>46335.875</v>
+        <v>46335.89583333334</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46336.5625</v>
       </c>
     </row>
     <row r="69">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46336.70833333334</v>
+        <v>46336.72916666666</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>46336.77083333334</v>
+        <v>46336.79166666666</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>46337.02083333334</v>
+        <v>46337.04166666666</v>
       </c>
     </row>
     <row r="70">
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46337.91666666666</v>
+        <v>46337.9375</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>46337.97916666666</v>
+        <v>46338</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>46338.39583333334</v>
+        <v>46338.41666666666</v>
       </c>
     </row>
     <row r="71">
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46338.66666666666</v>
+        <v>46338.6875</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>46338.6875</v>
+        <v>46338.70833333334</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>46339.29166666666</v>
+        <v>46339.3125</v>
       </c>
     </row>
     <row r="72">
@@ -4379,13 +4379,13 @@
         </is>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46344.20833333334</v>
+        <v>46344.22916666666</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>46344.375</v>
+        <v>46344.39583333334</v>
       </c>
       <c r="M72" s="1" t="n">
-        <v>46344.95833333334</v>
+        <v>46344.97916666666</v>
       </c>
     </row>
     <row r="73">
@@ -4434,13 +4434,13 @@
         </is>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46346.60416666666</v>
+        <v>46346.625</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>46346.64583333334</v>
+        <v>46346.66666666666</v>
       </c>
       <c r="M73" s="1" t="n">
-        <v>46347</v>
+        <v>46347.02083333334</v>
       </c>
     </row>
     <row r="74">
@@ -4489,13 +4489,13 @@
         </is>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46347.125</v>
+        <v>46347.14583333334</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>46347.20833333334</v>
+        <v>46347.22916666666</v>
       </c>
       <c r="M74" s="1" t="n">
-        <v>46348.20833333334</v>
+        <v>46348.22916666666</v>
       </c>
     </row>
     <row r="75">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46348.41666666666</v>
+        <v>46348.4375</v>
       </c>
       <c r="L75" s="1" t="n">
-        <v>46348.45833333334</v>
+        <v>46348.47916666666</v>
       </c>
       <c r="M75" s="1" t="n">
-        <v>46348.95833333334</v>
+        <v>46348.97916666666</v>
       </c>
     </row>
     <row r="76">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46350.77083333334</v>
+        <v>46350.79166666666</v>
       </c>
       <c r="L76" s="1" t="n">
-        <v>46350.9375</v>
+        <v>46350.95833333334</v>
       </c>
       <c r="M76" s="1" t="n">
-        <v>46351.625</v>
+        <v>46351.64583333334</v>
       </c>
     </row>
     <row r="77">
@@ -4654,13 +4654,13 @@
         </is>
       </c>
       <c r="K77" s="1" t="n">
-        <v>46356.83333333334</v>
+        <v>46356.85416666666</v>
       </c>
       <c r="L77" s="1" t="n">
-        <v>46356.875</v>
+        <v>46356.89583333334</v>
       </c>
       <c r="M77" s="1" t="n">
-        <v>46357.54166666666</v>
+        <v>46357.5625</v>
       </c>
     </row>
     <row r="78">
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="K78" s="1" t="n">
-        <v>46357.70833333334</v>
+        <v>46357.72916666666</v>
       </c>
       <c r="L78" s="1" t="n">
-        <v>46357.77083333334</v>
+        <v>46357.79166666666</v>
       </c>
       <c r="M78" s="1" t="n">
-        <v>46358.02083333334</v>
+        <v>46358.04166666666</v>
       </c>
     </row>
     <row r="79">
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="K79" s="1" t="n">
-        <v>46358.91666666666</v>
+        <v>46358.9375</v>
       </c>
       <c r="L79" s="1" t="n">
-        <v>46358.97916666666</v>
+        <v>46359</v>
       </c>
       <c r="M79" s="1" t="n">
-        <v>46359.39583333334</v>
+        <v>46359.41666666666</v>
       </c>
     </row>
     <row r="80">
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="K80" s="1" t="n">
-        <v>46359.66666666666</v>
+        <v>46359.6875</v>
       </c>
       <c r="L80" s="1" t="n">
-        <v>46359.6875</v>
+        <v>46359.70833333334</v>
       </c>
       <c r="M80" s="1" t="n">
-        <v>46360.29166666666</v>
+        <v>46360.3125</v>
       </c>
     </row>
     <row r="81">
@@ -4874,13 +4874,13 @@
         </is>
       </c>
       <c r="K81" s="1" t="n">
-        <v>46365.20833333334</v>
+        <v>46365.22916666666</v>
       </c>
       <c r="L81" s="1" t="n">
-        <v>46365.375</v>
+        <v>46365.39583333334</v>
       </c>
       <c r="M81" s="1" t="n">
-        <v>46365.95833333334</v>
+        <v>46365.97916666666</v>
       </c>
     </row>
     <row r="82">
@@ -4929,13 +4929,13 @@
         </is>
       </c>
       <c r="K82" s="1" t="n">
-        <v>46367.60416666666</v>
+        <v>46367.625</v>
       </c>
       <c r="L82" s="1" t="n">
-        <v>46367.64583333334</v>
+        <v>46367.66666666666</v>
       </c>
       <c r="M82" s="1" t="n">
-        <v>46368</v>
+        <v>46368.02083333334</v>
       </c>
     </row>
     <row r="83">
@@ -4984,13 +4984,13 @@
         </is>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46368.125</v>
+        <v>46368.14583333334</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>46368.20833333334</v>
+        <v>46368.22916666666</v>
       </c>
       <c r="M83" s="1" t="n">
-        <v>46369.20833333334</v>
+        <v>46369.22916666666</v>
       </c>
     </row>
     <row r="84">
@@ -5039,13 +5039,13 @@
         </is>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46369.41666666666</v>
+        <v>46369.4375</v>
       </c>
       <c r="L84" s="1" t="n">
-        <v>46369.45833333334</v>
+        <v>46369.47916666666</v>
       </c>
       <c r="M84" s="1" t="n">
-        <v>46369.95833333334</v>
+        <v>46369.97916666666</v>
       </c>
     </row>
     <row r="85">
@@ -5090,13 +5090,13 @@
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" s="1" t="n">
-        <v>46371.77083333334</v>
+        <v>46371.79166666666</v>
       </c>
       <c r="L85" s="1" t="n">
-        <v>46371.9375</v>
+        <v>46371.95833333334</v>
       </c>
       <c r="M85" s="1" t="n">
-        <v>46372.625</v>
+        <v>46372.64583333334</v>
       </c>
     </row>
     <row r="86">
@@ -7124,10 +7124,10 @@
         <v>46308.41666666666</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>46308.45833333334</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>46309.54166666666</v>
+        <v>46310.625</v>
       </c>
     </row>
     <row r="123">
@@ -7176,13 +7176,13 @@
         </is>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46309.66666666666</v>
+        <v>46310.75</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="M123" s="1" t="n">
-        <v>46309.95833333334</v>
+        <v>46311.04166666666</v>
       </c>
     </row>
     <row r="124">
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46310.375</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>46310.45833333334</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="M124" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46311.875</v>
       </c>
     </row>
     <row r="125">
@@ -7286,13 +7286,13 @@
         </is>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46315.875</v>
+        <v>46316.95833333334</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>46316.04166666666</v>
+        <v>46317.125</v>
       </c>
       <c r="M125" s="1" t="n">
-        <v>46316.66666666666</v>
+        <v>46317.75</v>
       </c>
     </row>
     <row r="126">
@@ -7341,13 +7341,13 @@
         </is>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46318.45833333334</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>46318.5</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="M126" s="1" t="n">
-        <v>46318.75</v>
+        <v>46319.83333333334</v>
       </c>
     </row>
     <row r="127">
@@ -7396,13 +7396,13 @@
         </is>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46319.04166666666</v>
+        <v>46320.125</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>46319.16666666666</v>
+        <v>46320.25</v>
       </c>
       <c r="M127" s="1" t="n">
-        <v>46320.66666666666</v>
+        <v>46321.75</v>
       </c>
     </row>
     <row r="128">
@@ -7451,13 +7451,13 @@
         </is>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46320.875</v>
+        <v>46321.95833333334</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>46320.91666666666</v>
+        <v>46322</v>
       </c>
       <c r="M128" s="1" t="n">
-        <v>46321.33333333334</v>
+        <v>46322.41666666666</v>
       </c>
     </row>
     <row r="129">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="K129" s="1" t="n">
-        <v>46322.91666666666</v>
+        <v>46324</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>46323.08333333334</v>
+        <v>46324.16666666666</v>
       </c>
       <c r="M129" s="1" t="n">
-        <v>46323.625</v>
+        <v>46324.70833333334</v>
       </c>
     </row>
     <row r="130">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="K130" s="1" t="n">
-        <v>46332.25</v>
+        <v>46333.33333333334</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>46332.29166666666</v>
+        <v>46333.375</v>
       </c>
       <c r="M130" s="1" t="n">
-        <v>46333.375</v>
+        <v>46334.45833333334</v>
       </c>
     </row>
     <row r="131">
@@ -7616,13 +7616,13 @@
         </is>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46333.5</v>
+        <v>46334.58333333334</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>46333.54166666666</v>
+        <v>46334.625</v>
       </c>
       <c r="M131" s="1" t="n">
-        <v>46333.79166666666</v>
+        <v>46334.875</v>
       </c>
     </row>
     <row r="132">
@@ -7671,13 +7671,13 @@
         </is>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46334.20833333334</v>
+        <v>46335.29166666666</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>46334.29166666666</v>
+        <v>46335.375</v>
       </c>
       <c r="M132" s="1" t="n">
-        <v>46334.625</v>
+        <v>46335.70833333334</v>
       </c>
     </row>
     <row r="133">
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46339.70833333334</v>
+        <v>46340.79166666666</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>46339.875</v>
+        <v>46340.95833333334</v>
       </c>
       <c r="M133" s="1" t="n">
-        <v>46340.5</v>
+        <v>46341.58333333334</v>
       </c>
     </row>
     <row r="134">
@@ -7781,13 +7781,13 @@
         </is>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46342.29166666666</v>
+        <v>46343.375</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>46342.33333333334</v>
+        <v>46343.41666666666</v>
       </c>
       <c r="M134" s="1" t="n">
-        <v>46342.58333333334</v>
+        <v>46343.66666666666</v>
       </c>
     </row>
     <row r="135">
@@ -7836,13 +7836,13 @@
         </is>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46342.875</v>
+        <v>46343.95833333334</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>46343</v>
+        <v>46344.08333333334</v>
       </c>
       <c r="M135" s="1" t="n">
-        <v>46344.5</v>
+        <v>46345.58333333334</v>
       </c>
     </row>
     <row r="136">
@@ -7891,13 +7891,13 @@
         </is>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46344.70833333334</v>
+        <v>46345.79166666666</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>46344.75</v>
+        <v>46345.83333333334</v>
       </c>
       <c r="M136" s="1" t="n">
-        <v>46345.16666666666</v>
+        <v>46346.25</v>
       </c>
     </row>
     <row r="137">
@@ -7946,13 +7946,13 @@
         </is>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46346.79166666666</v>
+        <v>46347.875</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>46346.95833333334</v>
+        <v>46348.04166666666</v>
       </c>
       <c r="M137" s="1" t="n">
-        <v>46347.5</v>
+        <v>46348.58333333334</v>
       </c>
     </row>
     <row r="138">
@@ -8001,13 +8001,13 @@
         </is>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46353.25</v>
+        <v>46354.33333333334</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>46353.29166666666</v>
+        <v>46354.375</v>
       </c>
       <c r="M138" s="1" t="n">
-        <v>46354.375</v>
+        <v>46355.45833333334</v>
       </c>
     </row>
     <row r="139">
@@ -8056,13 +8056,13 @@
         </is>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46354.5</v>
+        <v>46355.58333333334</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>46354.54166666666</v>
+        <v>46355.625</v>
       </c>
       <c r="M139" s="1" t="n">
-        <v>46354.79166666666</v>
+        <v>46355.875</v>
       </c>
     </row>
     <row r="140">
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46355.20833333334</v>
+        <v>46356.29166666666</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>46355.29166666666</v>
+        <v>46356.375</v>
       </c>
       <c r="M140" s="1" t="n">
-        <v>46355.625</v>
+        <v>46356.70833333334</v>
       </c>
     </row>
     <row r="141">
@@ -8166,13 +8166,13 @@
         </is>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46360.70833333334</v>
+        <v>46361.79166666666</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>46360.875</v>
+        <v>46361.95833333334</v>
       </c>
       <c r="M141" s="1" t="n">
-        <v>46361.5</v>
+        <v>46362.58333333334</v>
       </c>
     </row>
     <row r="142">
@@ -8221,13 +8221,13 @@
         </is>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46363.29166666666</v>
+        <v>46364.375</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>46363.33333333334</v>
+        <v>46364.41666666666</v>
       </c>
       <c r="M142" s="1" t="n">
-        <v>46363.58333333334</v>
+        <v>46364.66666666666</v>
       </c>
     </row>
     <row r="143">
@@ -8276,13 +8276,13 @@
         </is>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46363.875</v>
+        <v>46364.95833333334</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>46364</v>
+        <v>46365.08333333334</v>
       </c>
       <c r="M143" s="1" t="n">
-        <v>46365.5</v>
+        <v>46366.58333333334</v>
       </c>
     </row>
     <row r="144">
@@ -8331,13 +8331,13 @@
         </is>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46365.70833333334</v>
+        <v>46366.79166666666</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>46365.75</v>
+        <v>46366.83333333334</v>
       </c>
       <c r="M144" s="1" t="n">
-        <v>46366.16666666666</v>
+        <v>46367.25</v>
       </c>
     </row>
     <row r="145">
@@ -8386,13 +8386,13 @@
         </is>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46367.75</v>
+        <v>46368.83333333334</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>46367.91666666666</v>
+        <v>46369</v>
       </c>
       <c r="M145" s="1" t="n">
-        <v>46368.45833333334</v>
+        <v>46369.54166666666</v>
       </c>
     </row>
     <row r="146">
@@ -8441,13 +8441,13 @@
         </is>
       </c>
       <c r="K146" s="1" t="n">
-        <v>46374.25</v>
+        <v>46375.33333333334</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>46374.29166666666</v>
+        <v>46375.375</v>
       </c>
       <c r="M146" s="1" t="n">
-        <v>46375.375</v>
+        <v>46376.45833333334</v>
       </c>
     </row>
     <row r="147">
@@ -8496,13 +8496,13 @@
         </is>
       </c>
       <c r="K147" s="1" t="n">
-        <v>46375.5</v>
+        <v>46376.58333333334</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>46375.54166666666</v>
+        <v>46376.625</v>
       </c>
       <c r="M147" s="1" t="n">
-        <v>46375.79166666666</v>
+        <v>46376.875</v>
       </c>
     </row>
     <row r="148">
@@ -8551,13 +8551,13 @@
         </is>
       </c>
       <c r="K148" s="1" t="n">
-        <v>46376.20833333334</v>
+        <v>46377.29166666666</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>46376.29166666666</v>
+        <v>46377.375</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>46376.625</v>
+        <v>46377.70833333334</v>
       </c>
     </row>
     <row r="149">
@@ -8606,13 +8606,13 @@
         </is>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46381.70833333334</v>
+        <v>46382.79166666666</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>46381.875</v>
+        <v>46382.95833333334</v>
       </c>
       <c r="M149" s="1" t="n">
-        <v>46382.5</v>
+        <v>46383.58333333334</v>
       </c>
     </row>
     <row r="150">
@@ -8661,13 +8661,13 @@
         </is>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46384.29166666666</v>
+        <v>46385.375</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>46384.33333333334</v>
+        <v>46385.41666666666</v>
       </c>
       <c r="M150" s="1" t="n">
-        <v>46384.58333333334</v>
+        <v>46385.66666666666</v>
       </c>
     </row>
     <row r="151">
@@ -8716,13 +8716,13 @@
         </is>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46384.875</v>
+        <v>46385.95833333334</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>46385</v>
+        <v>46386.08333333334</v>
       </c>
       <c r="M151" s="1" t="n">
-        <v>46386.5</v>
+        <v>46387.58333333334</v>
       </c>
     </row>
     <row r="152">
@@ -8771,13 +8771,13 @@
         </is>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46386.70833333334</v>
+        <v>46387.79166666666</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>46386.75</v>
+        <v>46387.83333333334</v>
       </c>
       <c r="M152" s="1" t="n">
-        <v>46387.16666666666</v>
+        <v>46388.25</v>
       </c>
     </row>
     <row r="153">
@@ -8822,13 +8822,13 @@
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" s="1" t="n">
-        <v>46388.75</v>
+        <v>46389.83333333334</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>46388.91666666666</v>
+        <v>46390</v>
       </c>
       <c r="M153" s="1" t="n">
-        <v>46389.45833333334</v>
+        <v>46390.54166666666</v>
       </c>
     </row>
     <row r="154">
@@ -10746,10 +10746,10 @@
         <v>46307.08333333334</v>
       </c>
       <c r="L188" s="1" t="n">
-        <v>46307.125</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="M188" s="1" t="n">
-        <v>46307.70833333334</v>
+        <v>46307.91666666666</v>
       </c>
     </row>
     <row r="189">
@@ -10798,13 +10798,13 @@
         </is>
       </c>
       <c r="K189" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L189" s="1" t="n">
-        <v>46311.04166666666</v>
+        <v>46312.04166666666</v>
       </c>
       <c r="M189" s="1" t="n">
-        <v>46311.91666666666</v>
+        <v>46312.91666666666</v>
       </c>
     </row>
     <row r="190">
@@ -10853,13 +10853,13 @@
         </is>
       </c>
       <c r="K190" s="1" t="n">
-        <v>46312.20833333334</v>
+        <v>46313.20833333334</v>
       </c>
       <c r="L190" s="1" t="n">
-        <v>46312.27083333334</v>
+        <v>46313.27083333334</v>
       </c>
       <c r="M190" s="1" t="n">
-        <v>46312.75</v>
+        <v>46313.75</v>
       </c>
     </row>
     <row r="191">
@@ -10908,13 +10908,13 @@
         </is>
       </c>
       <c r="K191" s="1" t="n">
-        <v>46313.75</v>
+        <v>46314.75</v>
       </c>
       <c r="L191" s="1" t="n">
-        <v>46314.25</v>
+        <v>46315.25</v>
       </c>
       <c r="M191" s="1" t="n">
-        <v>46315.25</v>
+        <v>46316.25</v>
       </c>
     </row>
     <row r="192">
@@ -10963,13 +10963,13 @@
         </is>
       </c>
       <c r="K192" s="1" t="n">
-        <v>46322.25</v>
+        <v>46323.25</v>
       </c>
       <c r="L192" s="1" t="n">
-        <v>46322.33333333334</v>
+        <v>46323.33333333334</v>
       </c>
       <c r="M192" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46324.70833333334</v>
       </c>
     </row>
     <row r="193">
@@ -11018,13 +11018,13 @@
         </is>
       </c>
       <c r="K193" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46325.70833333334</v>
       </c>
       <c r="L193" s="1" t="n">
-        <v>46324.79166666666</v>
+        <v>46325.79166666666</v>
       </c>
       <c r="M193" s="1" t="n">
-        <v>46325.79166666666</v>
+        <v>46326.79166666666</v>
       </c>
     </row>
     <row r="194">
@@ -11073,13 +11073,13 @@
         </is>
       </c>
       <c r="K194" s="1" t="n">
-        <v>46332.79166666666</v>
+        <v>46333.79166666666</v>
       </c>
       <c r="L194" s="1" t="n">
-        <v>46333.29166666666</v>
+        <v>46334.29166666666</v>
       </c>
       <c r="M194" s="1" t="n">
-        <v>46334.29166666666</v>
+        <v>46335.29166666666</v>
       </c>
     </row>
     <row r="195">
@@ -11128,13 +11128,13 @@
         </is>
       </c>
       <c r="K195" s="1" t="n">
-        <v>46335.66666666666</v>
+        <v>46336.66666666666</v>
       </c>
       <c r="L195" s="1" t="n">
-        <v>46335.70833333334</v>
+        <v>46336.70833333334</v>
       </c>
       <c r="M195" s="1" t="n">
-        <v>46337.41666666666</v>
+        <v>46338.41666666666</v>
       </c>
     </row>
     <row r="196">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="K196" s="1" t="n">
-        <v>46337.70833333334</v>
+        <v>46338.70833333334</v>
       </c>
       <c r="L196" s="1" t="n">
-        <v>46337.77083333334</v>
+        <v>46338.77083333334</v>
       </c>
       <c r="M196" s="1" t="n">
-        <v>46338.25</v>
+        <v>46339.25</v>
       </c>
     </row>
     <row r="197">
@@ -11238,13 +11238,13 @@
         </is>
       </c>
       <c r="K197" s="1" t="n">
-        <v>46339.25</v>
+        <v>46340.25</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>46339.45833333334</v>
+        <v>46340.45833333334</v>
       </c>
       <c r="M197" s="1" t="n">
-        <v>46340.45833333334</v>
+        <v>46341.45833333334</v>
       </c>
     </row>
     <row r="198">
@@ -11293,13 +11293,13 @@
         </is>
       </c>
       <c r="K198" s="1" t="n">
-        <v>46347.45833333334</v>
+        <v>46348.45833333334</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>46347.54166666666</v>
+        <v>46348.54166666666</v>
       </c>
       <c r="M198" s="1" t="n">
-        <v>46348.91666666666</v>
+        <v>46349.91666666666</v>
       </c>
     </row>
     <row r="199">
@@ -11348,13 +11348,13 @@
         </is>
       </c>
       <c r="K199" s="1" t="n">
-        <v>46349.91666666666</v>
+        <v>46350.91666666666</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>46350</v>
+        <v>46351</v>
       </c>
       <c r="M199" s="1" t="n">
-        <v>46351</v>
+        <v>46352</v>
       </c>
     </row>
     <row r="200">
@@ -11403,13 +11403,13 @@
         </is>
       </c>
       <c r="K200" s="1" t="n">
-        <v>46354.41666666666</v>
+        <v>46355.41666666666</v>
       </c>
       <c r="L200" s="1" t="n">
-        <v>46354.58333333334</v>
+        <v>46355.58333333334</v>
       </c>
       <c r="M200" s="1" t="n">
-        <v>46355.41666666666</v>
+        <v>46356.41666666666</v>
       </c>
     </row>
     <row r="201">
@@ -11458,13 +11458,13 @@
         </is>
       </c>
       <c r="K201" s="1" t="n">
-        <v>46360</v>
+        <v>46361</v>
       </c>
       <c r="L201" s="1" t="n">
-        <v>46360.16666666666</v>
+        <v>46361.16666666666</v>
       </c>
       <c r="M201" s="1" t="n">
-        <v>46361.16666666666</v>
+        <v>46362.16666666666</v>
       </c>
     </row>
     <row r="202">
@@ -20300,10 +20300,10 @@
         <v>46329.91666666666</v>
       </c>
       <c r="L362" s="1" t="n">
-        <v>46330.97916666666</v>
+        <v>46329.97916666666</v>
       </c>
       <c r="M362" s="1" t="n">
-        <v>46332.6875</v>
+        <v>46331.6875</v>
       </c>
     </row>
     <row r="363">
@@ -20352,13 +20352,13 @@
         </is>
       </c>
       <c r="K363" s="1" t="n">
+        <v>46334.14583333334</v>
+      </c>
+      <c r="L363" s="1" t="n">
+        <v>46334.3125</v>
+      </c>
+      <c r="M363" s="1" t="n">
         <v>46335.14583333334</v>
-      </c>
-      <c r="L363" s="1" t="n">
-        <v>46335.3125</v>
-      </c>
-      <c r="M363" s="1" t="n">
-        <v>46336.14583333334</v>
       </c>
     </row>
     <row r="364">
@@ -20407,13 +20407,13 @@
         </is>
       </c>
       <c r="K364" s="1" t="n">
-        <v>46338.6875</v>
+        <v>46337.6875</v>
       </c>
       <c r="L364" s="1" t="n">
-        <v>46338.75</v>
+        <v>46337.75</v>
       </c>
       <c r="M364" s="1" t="n">
-        <v>46339.25</v>
+        <v>46338.25</v>
       </c>
     </row>
     <row r="365">
@@ -20462,13 +20462,13 @@
         </is>
       </c>
       <c r="K365" s="1" t="n">
-        <v>46339.47916666666</v>
+        <v>46338.47916666666</v>
       </c>
       <c r="L365" s="1" t="n">
-        <v>46339.52083333334</v>
+        <v>46338.52083333334</v>
       </c>
       <c r="M365" s="1" t="n">
-        <v>46340.02083333334</v>
+        <v>46339.02083333334</v>
       </c>
     </row>
     <row r="366">
@@ -20517,13 +20517,13 @@
         </is>
       </c>
       <c r="K366" s="1" t="n">
-        <v>46343.3125</v>
+        <v>46342.3125</v>
       </c>
       <c r="L366" s="1" t="n">
-        <v>46343.35416666666</v>
+        <v>46342.35416666666</v>
       </c>
       <c r="M366" s="1" t="n">
-        <v>46344.02083333334</v>
+        <v>46343.02083333334</v>
       </c>
     </row>
     <row r="367">
@@ -20572,13 +20572,13 @@
         </is>
       </c>
       <c r="K367" s="1" t="n">
-        <v>46345.10416666666</v>
+        <v>46344.10416666666</v>
       </c>
       <c r="L367" s="1" t="n">
-        <v>46345.14583333334</v>
+        <v>46344.14583333334</v>
       </c>
       <c r="M367" s="1" t="n">
-        <v>46345.72916666666</v>
+        <v>46344.72916666666</v>
       </c>
     </row>
     <row r="368">
@@ -20627,13 +20627,13 @@
         </is>
       </c>
       <c r="K368" s="1" t="n">
-        <v>46345.91666666666</v>
+        <v>46344.91666666666</v>
       </c>
       <c r="L368" s="1" t="n">
-        <v>46345.97916666666</v>
+        <v>46344.97916666666</v>
       </c>
       <c r="M368" s="1" t="n">
-        <v>46346.3125</v>
+        <v>46345.3125</v>
       </c>
     </row>
     <row r="369">
@@ -20682,13 +20682,13 @@
         </is>
       </c>
       <c r="K369" s="1" t="n">
-        <v>46347.60416666666</v>
+        <v>46346.60416666666</v>
       </c>
       <c r="L369" s="1" t="n">
-        <v>46347.77083333334</v>
+        <v>46346.77083333334</v>
       </c>
       <c r="M369" s="1" t="n">
-        <v>46348.27083333334</v>
+        <v>46347.27083333334</v>
       </c>
     </row>
     <row r="370">
@@ -20737,13 +20737,13 @@
         </is>
       </c>
       <c r="K370" s="1" t="n">
+        <v>46351.4375</v>
+      </c>
+      <c r="L370" s="1" t="n">
+        <v>46351.60416666666</v>
+      </c>
+      <c r="M370" s="1" t="n">
         <v>46352.4375</v>
-      </c>
-      <c r="L370" s="1" t="n">
-        <v>46352.60416666666</v>
-      </c>
-      <c r="M370" s="1" t="n">
-        <v>46353.4375</v>
       </c>
     </row>
     <row r="371">
@@ -20792,13 +20792,13 @@
         </is>
       </c>
       <c r="K371" s="1" t="n">
-        <v>46355.10416666666</v>
+        <v>46354.10416666666</v>
       </c>
       <c r="L371" s="1" t="n">
-        <v>46355.14583333334</v>
+        <v>46354.14583333334</v>
       </c>
       <c r="M371" s="1" t="n">
-        <v>46355.97916666666</v>
+        <v>46354.97916666666</v>
       </c>
     </row>
     <row r="372">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="K372" s="1" t="n">
-        <v>46359.14583333334</v>
+        <v>46358.14583333334</v>
       </c>
       <c r="L372" s="1" t="n">
-        <v>46359.22916666666</v>
+        <v>46358.22916666666</v>
       </c>
       <c r="M372" s="1" t="n">
-        <v>46360.89583333334</v>
+        <v>46359.89583333334</v>
       </c>
     </row>
     <row r="373">
@@ -20902,13 +20902,13 @@
         </is>
       </c>
       <c r="K373" s="1" t="n">
+        <v>46362.35416666666</v>
+      </c>
+      <c r="L373" s="1" t="n">
+        <v>46362.52083333334</v>
+      </c>
+      <c r="M373" s="1" t="n">
         <v>46363.35416666666</v>
-      </c>
-      <c r="L373" s="1" t="n">
-        <v>46363.52083333334</v>
-      </c>
-      <c r="M373" s="1" t="n">
-        <v>46364.35416666666</v>
       </c>
     </row>
     <row r="374">
@@ -20957,13 +20957,13 @@
         </is>
       </c>
       <c r="K374" s="1" t="n">
-        <v>46366.89583333334</v>
+        <v>46365.89583333334</v>
       </c>
       <c r="L374" s="1" t="n">
-        <v>46366.95833333334</v>
+        <v>46365.95833333334</v>
       </c>
       <c r="M374" s="1" t="n">
-        <v>46367.45833333334</v>
+        <v>46366.45833333334</v>
       </c>
     </row>
     <row r="375">
@@ -21012,13 +21012,13 @@
         </is>
       </c>
       <c r="K375" s="1" t="n">
-        <v>46367.6875</v>
+        <v>46366.6875</v>
       </c>
       <c r="L375" s="1" t="n">
-        <v>46367.72916666666</v>
+        <v>46366.72916666666</v>
       </c>
       <c r="M375" s="1" t="n">
-        <v>46368.22916666666</v>
+        <v>46367.22916666666</v>
       </c>
     </row>
     <row r="376">
@@ -21067,13 +21067,13 @@
         </is>
       </c>
       <c r="K376" s="1" t="n">
-        <v>46373.22916666666</v>
+        <v>46372.22916666666</v>
       </c>
       <c r="L376" s="1" t="n">
-        <v>46373.27083333334</v>
+        <v>46372.27083333334</v>
       </c>
       <c r="M376" s="1" t="n">
-        <v>46373.9375</v>
+        <v>46372.9375</v>
       </c>
     </row>
     <row r="377">
@@ -21122,13 +21122,13 @@
         </is>
       </c>
       <c r="K377" s="1" t="n">
-        <v>46375.02083333334</v>
+        <v>46374.02083333334</v>
       </c>
       <c r="L377" s="1" t="n">
-        <v>46375.0625</v>
+        <v>46374.0625</v>
       </c>
       <c r="M377" s="1" t="n">
-        <v>46375.64583333334</v>
+        <v>46374.64583333334</v>
       </c>
     </row>
     <row r="378">
@@ -21177,13 +21177,13 @@
         </is>
       </c>
       <c r="K378" s="1" t="n">
-        <v>46375.83333333334</v>
+        <v>46374.83333333334</v>
       </c>
       <c r="L378" s="1" t="n">
-        <v>46375.89583333334</v>
+        <v>46374.89583333334</v>
       </c>
       <c r="M378" s="1" t="n">
-        <v>46376.22916666666</v>
+        <v>46375.22916666666</v>
       </c>
     </row>
     <row r="379">
@@ -21232,13 +21232,13 @@
         </is>
       </c>
       <c r="K379" s="1" t="n">
-        <v>46377.52083333334</v>
+        <v>46376.52083333334</v>
       </c>
       <c r="L379" s="1" t="n">
-        <v>46377.6875</v>
+        <v>46376.6875</v>
       </c>
       <c r="M379" s="1" t="n">
-        <v>46378.1875</v>
+        <v>46377.1875</v>
       </c>
     </row>
     <row r="380">
@@ -21287,13 +21287,13 @@
         </is>
       </c>
       <c r="K380" s="1" t="n">
+        <v>46381.35416666666</v>
+      </c>
+      <c r="L380" s="1" t="n">
+        <v>46381.52083333334</v>
+      </c>
+      <c r="M380" s="1" t="n">
         <v>46382.35416666666</v>
-      </c>
-      <c r="L380" s="1" t="n">
-        <v>46382.52083333334</v>
-      </c>
-      <c r="M380" s="1" t="n">
-        <v>46383.35416666666</v>
       </c>
     </row>
     <row r="381">
@@ -21342,13 +21342,13 @@
         </is>
       </c>
       <c r="K381" s="1" t="n">
-        <v>46385.02083333334</v>
+        <v>46384.02083333334</v>
       </c>
       <c r="L381" s="1" t="n">
-        <v>46385.0625</v>
+        <v>46384.0625</v>
       </c>
       <c r="M381" s="1" t="n">
-        <v>46385.89583333334</v>
+        <v>46384.89583333334</v>
       </c>
     </row>
     <row r="382">
@@ -21397,13 +21397,13 @@
         </is>
       </c>
       <c r="K382" s="1" t="n">
-        <v>46389.0625</v>
+        <v>46388.0625</v>
       </c>
       <c r="L382" s="1" t="n">
-        <v>46389.14583333334</v>
+        <v>46388.14583333334</v>
       </c>
       <c r="M382" s="1" t="n">
-        <v>46390.8125</v>
+        <v>46389.8125</v>
       </c>
     </row>
     <row r="383">
@@ -21452,13 +21452,13 @@
         </is>
       </c>
       <c r="K383" s="1" t="n">
+        <v>46392.27083333334</v>
+      </c>
+      <c r="L383" s="1" t="n">
+        <v>46392.4375</v>
+      </c>
+      <c r="M383" s="1" t="n">
         <v>46393.27083333334</v>
-      </c>
-      <c r="L383" s="1" t="n">
-        <v>46393.4375</v>
-      </c>
-      <c r="M383" s="1" t="n">
-        <v>46394.27083333334</v>
       </c>
     </row>
     <row r="384">
@@ -21507,13 +21507,13 @@
         </is>
       </c>
       <c r="K384" s="1" t="n">
-        <v>46396.8125</v>
+        <v>46395.8125</v>
       </c>
       <c r="L384" s="1" t="n">
-        <v>46396.875</v>
+        <v>46395.875</v>
       </c>
       <c r="M384" s="1" t="n">
-        <v>46397.375</v>
+        <v>46396.375</v>
       </c>
     </row>
     <row r="385">
@@ -21558,13 +21558,13 @@
       </c>
       <c r="J385" t="inlineStr"/>
       <c r="K385" s="1" t="n">
-        <v>46397.60416666666</v>
+        <v>46396.60416666666</v>
       </c>
       <c r="L385" s="1" t="n">
-        <v>46397.64583333334</v>
+        <v>46396.64583333334</v>
       </c>
       <c r="M385" s="1" t="n">
-        <v>46398.14583333334</v>
+        <v>46397.14583333334</v>
       </c>
     </row>
     <row r="386">
@@ -21778,13 +21778,13 @@
         </is>
       </c>
       <c r="K389" s="1" t="n">
-        <v>46305.33333333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="L389" s="1" t="n">
-        <v>46305.5</v>
+        <v>46305.375</v>
       </c>
       <c r="M389" s="1" t="n">
-        <v>46306.125</v>
+        <v>46305.875</v>
       </c>
     </row>
     <row r="390">
@@ -21833,13 +21833,13 @@
         </is>
       </c>
       <c r="K390" s="1" t="n">
+        <v>46307.54166666666</v>
+      </c>
+      <c r="L390" s="1" t="n">
+        <v>46307.58333333334</v>
+      </c>
+      <c r="M390" s="1" t="n">
         <v>46307.79166666666</v>
-      </c>
-      <c r="L390" s="1" t="n">
-        <v>46307.83333333334</v>
-      </c>
-      <c r="M390" s="1" t="n">
-        <v>46308.04166666666</v>
       </c>
     </row>
     <row r="391">
@@ -21888,13 +21888,13 @@
         </is>
       </c>
       <c r="K391" s="1" t="n">
-        <v>46308.16666666666</v>
+        <v>46307.91666666666</v>
       </c>
       <c r="L391" s="1" t="n">
-        <v>46308.29166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="M391" s="1" t="n">
-        <v>46309.75</v>
+        <v>46309.5</v>
       </c>
     </row>
     <row r="392">
@@ -21943,13 +21943,13 @@
         </is>
       </c>
       <c r="K392" s="1" t="n">
-        <v>46309.95833333334</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="L392" s="1" t="n">
-        <v>46310</v>
+        <v>46309.75</v>
       </c>
       <c r="M392" s="1" t="n">
-        <v>46310.33333333334</v>
+        <v>46310.08333333334</v>
       </c>
     </row>
     <row r="393">
@@ -21998,13 +21998,13 @@
         </is>
       </c>
       <c r="K393" s="1" t="n">
-        <v>46314.16666666666</v>
+        <v>46313.91666666666</v>
       </c>
       <c r="L393" s="1" t="n">
-        <v>46314.22916666666</v>
+        <v>46313.97916666666</v>
       </c>
       <c r="M393" s="1" t="n">
-        <v>46314.72916666666</v>
+        <v>46314.47916666666</v>
       </c>
     </row>
     <row r="394">
@@ -22053,13 +22053,13 @@
         </is>
       </c>
       <c r="K394" s="1" t="n">
-        <v>46315.58333333334</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="L394" s="1" t="n">
-        <v>46315.625</v>
+        <v>46315.375</v>
       </c>
       <c r="M394" s="1" t="n">
-        <v>46316.25</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="395">
@@ -22108,13 +22108,13 @@
         </is>
       </c>
       <c r="K395" s="1" t="n">
-        <v>46318.54166666666</v>
+        <v>46318.29166666666</v>
       </c>
       <c r="L395" s="1" t="n">
-        <v>46318.58333333334</v>
+        <v>46318.33333333334</v>
       </c>
       <c r="M395" s="1" t="n">
-        <v>46319.58333333334</v>
+        <v>46319.33333333334</v>
       </c>
     </row>
     <row r="396">
@@ -22163,13 +22163,13 @@
         </is>
       </c>
       <c r="K396" s="1" t="n">
-        <v>46319.875</v>
+        <v>46319.625</v>
       </c>
       <c r="L396" s="1" t="n">
-        <v>46319.9375</v>
+        <v>46319.6875</v>
       </c>
       <c r="M396" s="1" t="n">
-        <v>46320.27083333334</v>
+        <v>46320.02083333334</v>
       </c>
     </row>
     <row r="397">
@@ -22218,13 +22218,13 @@
         </is>
       </c>
       <c r="K397" s="1" t="n">
-        <v>46323.20833333334</v>
+        <v>46322.91666666666</v>
       </c>
       <c r="L397" s="1" t="n">
-        <v>46323.25</v>
+        <v>46322.95833333334</v>
       </c>
       <c r="M397" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46323.47916666666</v>
       </c>
     </row>
     <row r="398">
@@ -22273,13 +22273,13 @@
         </is>
       </c>
       <c r="K398" s="1" t="n">
-        <v>46325.91666666666</v>
+        <v>46325.70833333334</v>
       </c>
       <c r="L398" s="1" t="n">
-        <v>46326.08333333334</v>
+        <v>46325.875</v>
       </c>
       <c r="M398" s="1" t="n">
-        <v>46326.54166666666</v>
+        <v>46326.33333333334</v>
       </c>
     </row>
     <row r="399">
@@ -22328,13 +22328,13 @@
         </is>
       </c>
       <c r="K399" s="1" t="n">
+        <v>46328.08333333334</v>
+      </c>
+      <c r="L399" s="1" t="n">
+        <v>46328.125</v>
+      </c>
+      <c r="M399" s="1" t="n">
         <v>46328.29166666666</v>
-      </c>
-      <c r="L399" s="1" t="n">
-        <v>46328.33333333334</v>
-      </c>
-      <c r="M399" s="1" t="n">
-        <v>46328.5</v>
       </c>
     </row>
     <row r="400">
@@ -22383,13 +22383,13 @@
         </is>
       </c>
       <c r="K400" s="1" t="n">
-        <v>46328.75</v>
+        <v>46328.54166666666</v>
       </c>
       <c r="L400" s="1" t="n">
-        <v>46328.875</v>
+        <v>46328.66666666666</v>
       </c>
       <c r="M400" s="1" t="n">
-        <v>46330.20833333334</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="401">
@@ -22438,13 +22438,13 @@
         </is>
       </c>
       <c r="K401" s="1" t="n">
-        <v>46330.70833333334</v>
+        <v>46330.5</v>
       </c>
       <c r="L401" s="1" t="n">
-        <v>46330.75</v>
+        <v>46330.54166666666</v>
       </c>
       <c r="M401" s="1" t="n">
-        <v>46331.04166666666</v>
+        <v>46330.83333333334</v>
       </c>
     </row>
     <row r="402">
@@ -22493,13 +22493,13 @@
         </is>
       </c>
       <c r="K402" s="1" t="n">
-        <v>46335.125</v>
+        <v>46334.91666666666</v>
       </c>
       <c r="L402" s="1" t="n">
-        <v>46335.16666666666</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="M402" s="1" t="n">
-        <v>46335.625</v>
+        <v>46335.41666666666</v>
       </c>
     </row>
     <row r="403">
@@ -22548,13 +22548,13 @@
         </is>
       </c>
       <c r="K403" s="1" t="n">
-        <v>46336.70833333334</v>
+        <v>46336.5</v>
       </c>
       <c r="L403" s="1" t="n">
-        <v>46336.75</v>
+        <v>46336.54166666666</v>
       </c>
       <c r="M403" s="1" t="n">
-        <v>46337.33333333334</v>
+        <v>46337.125</v>
       </c>
     </row>
     <row r="404">
@@ -25733,10 +25733,10 @@
         <v>46301.91666666666</v>
       </c>
       <c r="L461" s="1" t="n">
-        <v>46302.20833333334</v>
+        <v>46302.375</v>
       </c>
       <c r="M461" s="1" t="n">
-        <v>46303.1875</v>
+        <v>46303.45833333334</v>
       </c>
     </row>
     <row r="462">
@@ -25785,13 +25785,13 @@
         </is>
       </c>
       <c r="K462" s="1" t="n">
-        <v>46304.72916666666</v>
+        <v>46305</v>
       </c>
       <c r="L462" s="1" t="n">
-        <v>46304.77083333334</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="M462" s="1" t="n">
-        <v>46305.60416666666</v>
+        <v>46305.875</v>
       </c>
     </row>
     <row r="463">
@@ -25840,13 +25840,13 @@
         </is>
       </c>
       <c r="K463" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.8125</v>
       </c>
       <c r="L463" s="1" t="n">
-        <v>46309.60416666666</v>
+        <v>46309.875</v>
       </c>
       <c r="M463" s="1" t="n">
-        <v>46311.3125</v>
+        <v>46311.58333333334</v>
       </c>
     </row>
     <row r="464">
@@ -25895,13 +25895,13 @@
         </is>
       </c>
       <c r="K464" s="1" t="n">
-        <v>46313.77083333334</v>
+        <v>46314.04166666666</v>
       </c>
       <c r="L464" s="1" t="n">
-        <v>46314.4375</v>
+        <v>46314.70833333334</v>
       </c>
       <c r="M464" s="1" t="n">
-        <v>46315.27083333334</v>
+        <v>46315.54166666666</v>
       </c>
     </row>
     <row r="465">
@@ -25950,13 +25950,13 @@
         </is>
       </c>
       <c r="K465" s="1" t="n">
-        <v>46317.58333333334</v>
+        <v>46317.85416666666</v>
       </c>
       <c r="L465" s="1" t="n">
-        <v>46317.64583333334</v>
+        <v>46317.91666666666</v>
       </c>
       <c r="M465" s="1" t="n">
-        <v>46318.14583333334</v>
+        <v>46318.41666666666</v>
       </c>
     </row>
     <row r="466">
@@ -26005,13 +26005,13 @@
         </is>
       </c>
       <c r="K466" s="1" t="n">
-        <v>46318.25</v>
+        <v>46318.52083333334</v>
       </c>
       <c r="L466" s="1" t="n">
-        <v>46319.29166666666</v>
+        <v>46319.5625</v>
       </c>
       <c r="M466" s="1" t="n">
-        <v>46319.83333333334</v>
+        <v>46320.10416666666</v>
       </c>
     </row>
     <row r="467">
@@ -26060,13 +26060,13 @@
         </is>
       </c>
       <c r="K467" s="1" t="n">
-        <v>46322.79166666666</v>
+        <v>46323.0625</v>
       </c>
       <c r="L467" s="1" t="n">
-        <v>46322.83333333334</v>
+        <v>46323.10416666666</v>
       </c>
       <c r="M467" s="1" t="n">
-        <v>46323.5</v>
+        <v>46323.77083333334</v>
       </c>
     </row>
     <row r="468">
@@ -26115,13 +26115,13 @@
         </is>
       </c>
       <c r="K468" s="1" t="n">
-        <v>46324.58333333334</v>
+        <v>46324.75</v>
       </c>
       <c r="L468" s="1" t="n">
-        <v>46324.625</v>
+        <v>46324.79166666666</v>
       </c>
       <c r="M468" s="1" t="n">
-        <v>46325.20833333334</v>
+        <v>46325.375</v>
       </c>
     </row>
     <row r="469">
@@ -26170,13 +26170,13 @@
         </is>
       </c>
       <c r="K469" s="1" t="n">
-        <v>46325.39583333334</v>
+        <v>46325.47916666666</v>
       </c>
       <c r="L469" s="1" t="n">
-        <v>46325.45833333334</v>
+        <v>46325.54166666666</v>
       </c>
       <c r="M469" s="1" t="n">
-        <v>46325.79166666666</v>
+        <v>46325.875</v>
       </c>
     </row>
     <row r="470">
@@ -26225,13 +26225,13 @@
         </is>
       </c>
       <c r="K470" s="1" t="n">
-        <v>46327.08333333334</v>
+        <v>46326.95833333334</v>
       </c>
       <c r="L470" s="1" t="n">
-        <v>46327.25</v>
+        <v>46327.125</v>
       </c>
       <c r="M470" s="1" t="n">
-        <v>46327.75</v>
+        <v>46327.625</v>
       </c>
     </row>
     <row r="471">
@@ -26280,13 +26280,13 @@
         </is>
       </c>
       <c r="K471" s="1" t="n">
-        <v>46331.91666666666</v>
+        <v>46331.54166666666</v>
       </c>
       <c r="L471" s="1" t="n">
-        <v>46332.08333333334</v>
+        <v>46331.70833333334</v>
       </c>
       <c r="M471" s="1" t="n">
-        <v>46332.91666666666</v>
+        <v>46332.54166666666</v>
       </c>
     </row>
     <row r="472">
@@ -26335,13 +26335,13 @@
         </is>
       </c>
       <c r="K472" s="1" t="n">
-        <v>46334.58333333334</v>
+        <v>46334.20833333334</v>
       </c>
       <c r="L472" s="1" t="n">
-        <v>46334.625</v>
+        <v>46334.25</v>
       </c>
       <c r="M472" s="1" t="n">
-        <v>46335.45833333334</v>
+        <v>46335.08333333334</v>
       </c>
     </row>
     <row r="473">
@@ -26390,13 +26390,13 @@
         </is>
       </c>
       <c r="K473" s="1" t="n">
-        <v>46338.625</v>
+        <v>46338.25</v>
       </c>
       <c r="L473" s="1" t="n">
-        <v>46338.70833333334</v>
+        <v>46338.33333333334</v>
       </c>
       <c r="M473" s="1" t="n">
-        <v>46340.375</v>
+        <v>46340</v>
       </c>
     </row>
     <row r="474">
@@ -26445,13 +26445,13 @@
         </is>
       </c>
       <c r="K474" s="1" t="n">
-        <v>46342.83333333334</v>
+        <v>46342.45833333334</v>
       </c>
       <c r="L474" s="1" t="n">
-        <v>46343</v>
+        <v>46342.625</v>
       </c>
       <c r="M474" s="1" t="n">
-        <v>46343.83333333334</v>
+        <v>46343.45833333334</v>
       </c>
     </row>
     <row r="475">
@@ -26500,13 +26500,13 @@
         </is>
       </c>
       <c r="K475" s="1" t="n">
-        <v>46346.375</v>
+        <v>46346</v>
       </c>
       <c r="L475" s="1" t="n">
-        <v>46346.4375</v>
+        <v>46346.0625</v>
       </c>
       <c r="M475" s="1" t="n">
-        <v>46346.9375</v>
+        <v>46346.5625</v>
       </c>
     </row>
     <row r="476">
@@ -26555,13 +26555,13 @@
         </is>
       </c>
       <c r="K476" s="1" t="n">
-        <v>46347.16666666666</v>
+        <v>46346.79166666666</v>
       </c>
       <c r="L476" s="1" t="n">
-        <v>46347.20833333334</v>
+        <v>46346.83333333334</v>
       </c>
       <c r="M476" s="1" t="n">
-        <v>46347.70833333334</v>
+        <v>46347.33333333334</v>
       </c>
     </row>
     <row r="477">
@@ -26610,13 +26610,13 @@
         </is>
       </c>
       <c r="K477" s="1" t="n">
-        <v>46350.79166666666</v>
+        <v>46350.41666666666</v>
       </c>
       <c r="L477" s="1" t="n">
-        <v>46350.83333333334</v>
+        <v>46350.45833333334</v>
       </c>
       <c r="M477" s="1" t="n">
-        <v>46351.5</v>
+        <v>46351.125</v>
       </c>
     </row>
     <row r="478">
@@ -26665,13 +26665,13 @@
         </is>
       </c>
       <c r="K478" s="1" t="n">
-        <v>46352.58333333334</v>
+        <v>46352.20833333334</v>
       </c>
       <c r="L478" s="1" t="n">
-        <v>46352.625</v>
+        <v>46352.25</v>
       </c>
       <c r="M478" s="1" t="n">
-        <v>46353.20833333334</v>
+        <v>46352.83333333334</v>
       </c>
     </row>
     <row r="479">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="K479" s="1" t="n">
-        <v>46353.39583333334</v>
+        <v>46353.02083333334</v>
       </c>
       <c r="L479" s="1" t="n">
-        <v>46353.45833333334</v>
+        <v>46353.08333333334</v>
       </c>
       <c r="M479" s="1" t="n">
-        <v>46353.79166666666</v>
+        <v>46353.41666666666</v>
       </c>
     </row>
     <row r="480">
@@ -26775,13 +26775,13 @@
         </is>
       </c>
       <c r="K480" s="1" t="n">
-        <v>46355.08333333334</v>
+        <v>46354.70833333334</v>
       </c>
       <c r="L480" s="1" t="n">
-        <v>46355.25</v>
+        <v>46354.875</v>
       </c>
       <c r="M480" s="1" t="n">
-        <v>46355.75</v>
+        <v>46355.375</v>
       </c>
     </row>
     <row r="481">
@@ -26830,13 +26830,13 @@
         </is>
       </c>
       <c r="K481" s="1" t="n">
-        <v>46359.91666666666</v>
+        <v>46359.54166666666</v>
       </c>
       <c r="L481" s="1" t="n">
-        <v>46360.08333333334</v>
+        <v>46359.70833333334</v>
       </c>
       <c r="M481" s="1" t="n">
-        <v>46360.91666666666</v>
+        <v>46360.54166666666</v>
       </c>
     </row>
     <row r="482">
@@ -26885,13 +26885,13 @@
         </is>
       </c>
       <c r="K482" s="1" t="n">
-        <v>46362.58333333334</v>
+        <v>46362.20833333334</v>
       </c>
       <c r="L482" s="1" t="n">
-        <v>46362.625</v>
+        <v>46362.25</v>
       </c>
       <c r="M482" s="1" t="n">
-        <v>46363.45833333334</v>
+        <v>46363.08333333334</v>
       </c>
     </row>
     <row r="483">
@@ -26940,13 +26940,13 @@
         </is>
       </c>
       <c r="K483" s="1" t="n">
-        <v>46366.625</v>
+        <v>46366.25</v>
       </c>
       <c r="L483" s="1" t="n">
-        <v>46366.70833333334</v>
+        <v>46366.33333333334</v>
       </c>
       <c r="M483" s="1" t="n">
-        <v>46368.375</v>
+        <v>46368</v>
       </c>
     </row>
     <row r="484">
@@ -26995,13 +26995,13 @@
         </is>
       </c>
       <c r="K484" s="1" t="n">
-        <v>46370.83333333334</v>
+        <v>46370.45833333334</v>
       </c>
       <c r="L484" s="1" t="n">
-        <v>46371</v>
+        <v>46370.625</v>
       </c>
       <c r="M484" s="1" t="n">
-        <v>46371.83333333334</v>
+        <v>46371.45833333334</v>
       </c>
     </row>
     <row r="485">
@@ -27050,13 +27050,13 @@
         </is>
       </c>
       <c r="K485" s="1" t="n">
-        <v>46374.375</v>
+        <v>46374</v>
       </c>
       <c r="L485" s="1" t="n">
-        <v>46374.4375</v>
+        <v>46374.0625</v>
       </c>
       <c r="M485" s="1" t="n">
-        <v>46374.9375</v>
+        <v>46374.5625</v>
       </c>
     </row>
     <row r="486">
@@ -27101,13 +27101,13 @@
       </c>
       <c r="J486" t="inlineStr"/>
       <c r="K486" s="1" t="n">
-        <v>46375.16666666666</v>
+        <v>46374.79166666666</v>
       </c>
       <c r="L486" s="1" t="n">
-        <v>46375.20833333334</v>
+        <v>46374.83333333334</v>
       </c>
       <c r="M486" s="1" t="n">
-        <v>46375.70833333334</v>
+        <v>46375.33333333334</v>
       </c>
     </row>
     <row r="487">
@@ -35832,7 +35832,7 @@
         <v>46306.375</v>
       </c>
       <c r="M645" s="1" t="n">
-        <v>46306.70833333334</v>
+        <v>46306.75</v>
       </c>
     </row>
     <row r="646">
@@ -35881,13 +35881,13 @@
         </is>
       </c>
       <c r="K646" s="1" t="n">
-        <v>46310.58333333334</v>
+        <v>46310.625</v>
       </c>
       <c r="L646" s="1" t="n">
-        <v>46310.625</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="M646" s="1" t="n">
-        <v>46311.04166666666</v>
+        <v>46311.08333333334</v>
       </c>
     </row>
     <row r="647">
@@ -35936,13 +35936,13 @@
         </is>
       </c>
       <c r="K647" s="1" t="n">
-        <v>46311.29166666666</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="L647" s="1" t="n">
-        <v>46311.29166666666</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="M647" s="1" t="n">
-        <v>46311.66666666666</v>
+        <v>46311.70833333334</v>
       </c>
     </row>
     <row r="648">
@@ -35991,13 +35991,13 @@
         </is>
       </c>
       <c r="K648" s="1" t="n">
-        <v>46313</v>
+        <v>46313.04166666666</v>
       </c>
       <c r="L648" s="1" t="n">
-        <v>46313</v>
+        <v>46313.04166666666</v>
       </c>
       <c r="M648" s="1" t="n">
-        <v>46313.25</v>
+        <v>46313.29166666666</v>
       </c>
     </row>
     <row r="649">
@@ -44775,7 +44775,7 @@
         </is>
       </c>
       <c r="K808" s="1" t="n">
-        <v>46304.5</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="L808" s="1" t="n">
         <v>46306.66666666666</v>
@@ -46757,7 +46757,7 @@
         <v>46302.07083333333</v>
       </c>
       <c r="M844" s="1" t="n">
-        <v>46303.45833333334</v>
+        <v>46303.225</v>
       </c>
     </row>
     <row r="845">
@@ -46806,13 +46806,13 @@
         </is>
       </c>
       <c r="K845" s="1" t="n">
-        <v>46304.16666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="L845" s="1" t="n">
-        <v>46304.20833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="M845" s="1" t="n">
-        <v>46304.95833333334</v>
+        <v>46304.70833333334</v>
       </c>
     </row>
     <row r="846">
@@ -46861,13 +46861,13 @@
         </is>
       </c>
       <c r="K846" s="1" t="n">
-        <v>46308.58333333334</v>
+        <v>46308.375</v>
       </c>
       <c r="L846" s="1" t="n">
-        <v>46308.625</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="M846" s="1" t="n">
-        <v>46309.29166666666</v>
+        <v>46309.08333333334</v>
       </c>
     </row>
     <row r="847">
@@ -46916,13 +46916,13 @@
         </is>
       </c>
       <c r="K847" s="1" t="n">
-        <v>46315.35416666666</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="L847" s="1" t="n">
-        <v>46315.5625</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="M847" s="1" t="n">
-        <v>46316.22916666666</v>
+        <v>46316.58333333334</v>
       </c>
     </row>
     <row r="848">
@@ -46971,13 +46971,13 @@
         </is>
       </c>
       <c r="K848" s="1" t="n">
-        <v>46317.625</v>
+        <v>46318.02083333334</v>
       </c>
       <c r="L848" s="1" t="n">
-        <v>46317.66666666666</v>
+        <v>46318.0625</v>
       </c>
       <c r="M848" s="1" t="n">
-        <v>46318.66666666666</v>
+        <v>46319.0625</v>
       </c>
     </row>
     <row r="849">
@@ -47026,13 +47026,13 @@
         </is>
       </c>
       <c r="K849" s="1" t="n">
-        <v>46318.95833333334</v>
+        <v>46319.35416666666</v>
       </c>
       <c r="L849" s="1" t="n">
-        <v>46319</v>
+        <v>46319.39583333334</v>
       </c>
       <c r="M849" s="1" t="n">
-        <v>46319.625</v>
+        <v>46320.02083333334</v>
       </c>
     </row>
     <row r="850">
@@ -47081,13 +47081,13 @@
         </is>
       </c>
       <c r="K850" s="1" t="n">
-        <v>46321.125</v>
+        <v>46321.47916666666</v>
       </c>
       <c r="L850" s="1" t="n">
-        <v>46321.33333333334</v>
+        <v>46321.6875</v>
       </c>
       <c r="M850" s="1" t="n">
-        <v>46322</v>
+        <v>46322.35416666666</v>
       </c>
     </row>
     <row r="851">
@@ -47136,13 +47136,13 @@
         </is>
       </c>
       <c r="K851" s="1" t="n">
-        <v>46329</v>
+        <v>46329.35416666666</v>
       </c>
       <c r="L851" s="1" t="n">
-        <v>46329.08333333334</v>
+        <v>46329.4375</v>
       </c>
       <c r="M851" s="1" t="n">
-        <v>46329.91666666666</v>
+        <v>46330.27083333334</v>
       </c>
     </row>
     <row r="852">
@@ -47191,13 +47191,13 @@
         </is>
       </c>
       <c r="K852" s="1" t="n">
-        <v>46331</v>
+        <v>46331.35416666666</v>
       </c>
       <c r="L852" s="1" t="n">
-        <v>46331.08333333334</v>
+        <v>46331.4375</v>
       </c>
       <c r="M852" s="1" t="n">
-        <v>46331.58333333334</v>
+        <v>46331.9375</v>
       </c>
     </row>
     <row r="853">
@@ -47246,13 +47246,13 @@
         </is>
       </c>
       <c r="K853" s="1" t="n">
-        <v>46335.58333333334</v>
+        <v>46335.9375</v>
       </c>
       <c r="L853" s="1" t="n">
-        <v>46335.625</v>
+        <v>46335.97916666666</v>
       </c>
       <c r="M853" s="1" t="n">
-        <v>46336.29166666666</v>
+        <v>46336.64583333334</v>
       </c>
     </row>
     <row r="854">
@@ -47301,13 +47301,13 @@
         </is>
       </c>
       <c r="K854" s="1" t="n">
-        <v>46342.70833333334</v>
+        <v>46343.0625</v>
       </c>
       <c r="L854" s="1" t="n">
-        <v>46342.91666666666</v>
+        <v>46343.27083333334</v>
       </c>
       <c r="M854" s="1" t="n">
-        <v>46343.58333333334</v>
+        <v>46343.9375</v>
       </c>
     </row>
     <row r="855">
@@ -47356,13 +47356,13 @@
         </is>
       </c>
       <c r="K855" s="1" t="n">
-        <v>46345.04166666666</v>
+        <v>46345.39583333334</v>
       </c>
       <c r="L855" s="1" t="n">
-        <v>46345.08333333334</v>
+        <v>46345.4375</v>
       </c>
       <c r="M855" s="1" t="n">
-        <v>46346.08333333334</v>
+        <v>46346.4375</v>
       </c>
     </row>
     <row r="856">
@@ -47411,13 +47411,13 @@
         </is>
       </c>
       <c r="K856" s="1" t="n">
-        <v>46346.70833333334</v>
+        <v>46347.0625</v>
       </c>
       <c r="L856" s="1" t="n">
-        <v>46346.75</v>
+        <v>46347.10416666666</v>
       </c>
       <c r="M856" s="1" t="n">
-        <v>46347.375</v>
+        <v>46347.72916666666</v>
       </c>
     </row>
     <row r="857">
@@ -47466,13 +47466,13 @@
         </is>
       </c>
       <c r="K857" s="1" t="n">
-        <v>46348.875</v>
+        <v>46349.1875</v>
       </c>
       <c r="L857" s="1" t="n">
-        <v>46349.08333333334</v>
+        <v>46349.39583333334</v>
       </c>
       <c r="M857" s="1" t="n">
-        <v>46349.75</v>
+        <v>46350.0625</v>
       </c>
     </row>
     <row r="858">
@@ -47521,13 +47521,13 @@
         </is>
       </c>
       <c r="K858" s="1" t="n">
-        <v>46356.75</v>
+        <v>46357.0625</v>
       </c>
       <c r="L858" s="1" t="n">
-        <v>46356.83333333334</v>
+        <v>46357.14583333334</v>
       </c>
       <c r="M858" s="1" t="n">
-        <v>46357.66666666666</v>
+        <v>46357.97916666666</v>
       </c>
     </row>
     <row r="859">
@@ -47576,13 +47576,13 @@
         </is>
       </c>
       <c r="K859" s="1" t="n">
-        <v>46358.75</v>
+        <v>46359.0625</v>
       </c>
       <c r="L859" s="1" t="n">
-        <v>46358.83333333334</v>
+        <v>46359.14583333334</v>
       </c>
       <c r="M859" s="1" t="n">
-        <v>46359.33333333334</v>
+        <v>46359.64583333334</v>
       </c>
     </row>
     <row r="860">
@@ -47631,13 +47631,13 @@
         </is>
       </c>
       <c r="K860" s="1" t="n">
-        <v>46363.33333333334</v>
+        <v>46363.64583333334</v>
       </c>
       <c r="L860" s="1" t="n">
-        <v>46363.375</v>
+        <v>46363.6875</v>
       </c>
       <c r="M860" s="1" t="n">
-        <v>46364.04166666666</v>
+        <v>46364.35416666666</v>
       </c>
     </row>
     <row r="861">
@@ -47686,13 +47686,13 @@
         </is>
       </c>
       <c r="K861" s="1" t="n">
-        <v>46370.45833333334</v>
+        <v>46370.77083333334</v>
       </c>
       <c r="L861" s="1" t="n">
-        <v>46370.66666666666</v>
+        <v>46370.97916666666</v>
       </c>
       <c r="M861" s="1" t="n">
-        <v>46371.33333333334</v>
+        <v>46371.64583333334</v>
       </c>
     </row>
     <row r="862">
@@ -47741,13 +47741,13 @@
         </is>
       </c>
       <c r="K862" s="1" t="n">
-        <v>46373.04166666666</v>
+        <v>46373.35416666666</v>
       </c>
       <c r="L862" s="1" t="n">
-        <v>46373.08333333334</v>
+        <v>46373.39583333334</v>
       </c>
       <c r="M862" s="1" t="n">
-        <v>46374.08333333334</v>
+        <v>46374.39583333334</v>
       </c>
     </row>
     <row r="863">
@@ -47796,13 +47796,13 @@
         </is>
       </c>
       <c r="K863" s="1" t="n">
-        <v>46374.70833333334</v>
+        <v>46375.02083333334</v>
       </c>
       <c r="L863" s="1" t="n">
-        <v>46374.75</v>
+        <v>46375.0625</v>
       </c>
       <c r="M863" s="1" t="n">
-        <v>46375.375</v>
+        <v>46375.6875</v>
       </c>
     </row>
     <row r="864">
@@ -47851,13 +47851,13 @@
         </is>
       </c>
       <c r="K864" s="1" t="n">
-        <v>46376.875</v>
+        <v>46377.1875</v>
       </c>
       <c r="L864" s="1" t="n">
-        <v>46377.08333333334</v>
+        <v>46377.39583333334</v>
       </c>
       <c r="M864" s="1" t="n">
-        <v>46377.75</v>
+        <v>46378.0625</v>
       </c>
     </row>
     <row r="865">
@@ -47906,13 +47906,13 @@
         </is>
       </c>
       <c r="K865" s="1" t="n">
-        <v>46384.75</v>
+        <v>46385.0625</v>
       </c>
       <c r="L865" s="1" t="n">
-        <v>46384.83333333334</v>
+        <v>46385.14583333334</v>
       </c>
       <c r="M865" s="1" t="n">
-        <v>46385.66666666666</v>
+        <v>46385.97916666666</v>
       </c>
     </row>
     <row r="866">
@@ -47961,13 +47961,13 @@
         </is>
       </c>
       <c r="K866" s="1" t="n">
-        <v>46386.75</v>
+        <v>46387.0625</v>
       </c>
       <c r="L866" s="1" t="n">
-        <v>46386.83333333334</v>
+        <v>46387.14583333334</v>
       </c>
       <c r="M866" s="1" t="n">
-        <v>46387.33333333334</v>
+        <v>46387.64583333334</v>
       </c>
     </row>
     <row r="867">
@@ -48016,13 +48016,13 @@
         </is>
       </c>
       <c r="K867" s="1" t="n">
-        <v>46391.33333333334</v>
+        <v>46391.64583333334</v>
       </c>
       <c r="L867" s="1" t="n">
-        <v>46391.375</v>
+        <v>46391.6875</v>
       </c>
       <c r="M867" s="1" t="n">
-        <v>46392.04166666666</v>
+        <v>46392.35416666666</v>
       </c>
     </row>
     <row r="868">
@@ -48067,13 +48067,13 @@
       </c>
       <c r="J868" t="inlineStr"/>
       <c r="K868" s="1" t="n">
-        <v>46398.45833333334</v>
+        <v>46398.77083333334</v>
       </c>
       <c r="L868" s="1" t="n">
-        <v>46398.66666666666</v>
+        <v>46398.97916666666</v>
       </c>
       <c r="M868" s="1" t="n">
-        <v>46399.33333333334</v>
+        <v>46399.64583333334</v>
       </c>
     </row>
     <row r="869">
@@ -50263,13 +50263,13 @@
         </is>
       </c>
       <c r="K908" s="1" t="n">
-        <v>46304.20833333334</v>
+        <v>46304.25</v>
       </c>
       <c r="L908" s="1" t="n">
-        <v>46304.375</v>
+        <v>46304.625</v>
       </c>
       <c r="M908" s="1" t="n">
-        <v>46304.91666666666</v>
+        <v>46305.125</v>
       </c>
     </row>
     <row r="909">
@@ -50318,13 +50318,13 @@
         </is>
       </c>
       <c r="K909" s="1" t="n">
-        <v>46306.5</v>
+        <v>46306.75</v>
       </c>
       <c r="L909" s="1" t="n">
-        <v>46306.54166666666</v>
+        <v>46306.79166666666</v>
       </c>
       <c r="M909" s="1" t="n">
-        <v>46306.79166666666</v>
+        <v>46307.04166666666</v>
       </c>
     </row>
     <row r="910">
@@ -50373,13 +50373,13 @@
         </is>
       </c>
       <c r="K910" s="1" t="n">
-        <v>46306.95833333334</v>
+        <v>46307.20833333334</v>
       </c>
       <c r="L910" s="1" t="n">
-        <v>46307.08333333334</v>
+        <v>46307.70833333334</v>
       </c>
       <c r="M910" s="1" t="n">
-        <v>46308.58333333334</v>
+        <v>46309.20833333334</v>
       </c>
     </row>
     <row r="911">
@@ -50428,13 +50428,13 @@
         </is>
       </c>
       <c r="K911" s="1" t="n">
-        <v>46308.75</v>
+        <v>46309.375</v>
       </c>
       <c r="L911" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="M911" s="1" t="n">
-        <v>46309.04166666666</v>
+        <v>46309.66666666666</v>
       </c>
     </row>
     <row r="912">
@@ -50479,23 +50479,23 @@
       </c>
       <c r="J912" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K912" s="1" t="n">
-        <v>46312.77083333334</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="L912" s="1" t="n">
-        <v>46312.83333333334</v>
+        <v>46313.52083333334</v>
       </c>
       <c r="M912" s="1" t="n">
-        <v>46313.29166666666</v>
+        <v>46313.97916666666</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -50510,41 +50510,41 @@
       </c>
       <c r="D913" t="inlineStr"/>
       <c r="E913" t="n">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G913" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I913" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
           <t>CNXMN</t>
         </is>
       </c>
-      <c r="J913" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
       <c r="K913" s="1" t="n">
-        <v>46314.08333333334</v>
+        <v>46314.33333333334</v>
       </c>
       <c r="L913" s="1" t="n">
-        <v>46314.125</v>
+        <v>46314.375</v>
       </c>
       <c r="M913" s="1" t="n">
-        <v>46314.70833333334</v>
+        <v>46315.375</v>
       </c>
     </row>
     <row r="914">
@@ -50579,27 +50579,27 @@
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I914" t="inlineStr">
         <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
           <t>KRKAN</t>
         </is>
       </c>
-      <c r="J914" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
       <c r="K914" s="1" t="n">
-        <v>46317.04166666666</v>
+        <v>46314.75</v>
       </c>
       <c r="L914" s="1" t="n">
-        <v>46317.10416666666</v>
+        <v>46314.79166666666</v>
       </c>
       <c r="M914" s="1" t="n">
-        <v>46317.54166666666</v>
+        <v>46315.375</v>
       </c>
     </row>
     <row r="915">
@@ -50634,27 +50634,27 @@
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="I915" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J915" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K915" s="1" t="n">
-        <v>46317.33333333334</v>
+        <v>46316</v>
       </c>
       <c r="L915" s="1" t="n">
-        <v>46317.375</v>
+        <v>46316.0625</v>
       </c>
       <c r="M915" s="1" t="n">
-        <v>46318.375</v>
+        <v>46316.64583333334</v>
       </c>
     </row>
     <row r="916">
@@ -50689,27 +50689,27 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J916" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K916" s="1" t="n">
-        <v>46317.83333333334</v>
+        <v>46317.66666666666</v>
       </c>
       <c r="L916" s="1" t="n">
-        <v>46317.875</v>
+        <v>46317.72916666666</v>
       </c>
       <c r="M916" s="1" t="n">
-        <v>46318.54166666666</v>
+        <v>46318.16666666666</v>
       </c>
     </row>
     <row r="917">
@@ -50744,33 +50744,33 @@
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>KAN04</t>
+          <t>SHAW1</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J917" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K917" s="1" t="n">
-        <v>46319</v>
+        <v>46318.16666666666</v>
       </c>
       <c r="L917" s="1" t="n">
-        <v>46319.0625</v>
+        <v>46318.375</v>
       </c>
       <c r="M917" s="1" t="n">
-        <v>46319.64583333334</v>
+        <v>46319.04166666666</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -50785,26 +50785,26 @@
       </c>
       <c r="D918" t="inlineStr"/>
       <c r="E918" t="n">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G918" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J918" t="inlineStr">
@@ -50813,13 +50813,13 @@
         </is>
       </c>
       <c r="K918" s="1" t="n">
-        <v>46321.16666666666</v>
+        <v>46318.45833333334</v>
       </c>
       <c r="L918" s="1" t="n">
-        <v>46321.375</v>
+        <v>46318.5</v>
       </c>
       <c r="M918" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46319.16666666666</v>
       </c>
     </row>
     <row r="919">
@@ -50868,13 +50868,13 @@
         </is>
       </c>
       <c r="K919" s="1" t="n">
-        <v>46329.04166666666</v>
+        <v>46326.04166666666</v>
       </c>
       <c r="L919" s="1" t="n">
-        <v>46329.125</v>
+        <v>46326.125</v>
       </c>
       <c r="M919" s="1" t="n">
-        <v>46329.95833333334</v>
+        <v>46326.95833333334</v>
       </c>
     </row>
     <row r="920">
@@ -50923,13 +50923,13 @@
         </is>
       </c>
       <c r="K920" s="1" t="n">
-        <v>46331.04166666666</v>
+        <v>46328.04166666666</v>
       </c>
       <c r="L920" s="1" t="n">
-        <v>46331.125</v>
+        <v>46328.125</v>
       </c>
       <c r="M920" s="1" t="n">
-        <v>46331.625</v>
+        <v>46328.625</v>
       </c>
     </row>
     <row r="921">
@@ -50978,13 +50978,13 @@
         </is>
       </c>
       <c r="K921" s="1" t="n">
-        <v>46335.625</v>
+        <v>46332.625</v>
       </c>
       <c r="L921" s="1" t="n">
-        <v>46335.66666666666</v>
+        <v>46332.66666666666</v>
       </c>
       <c r="M921" s="1" t="n">
-        <v>46336.33333333334</v>
+        <v>46333.33333333334</v>
       </c>
     </row>
     <row r="922">
@@ -51033,13 +51033,13 @@
         </is>
       </c>
       <c r="K922" s="1" t="n">
-        <v>46342.75</v>
+        <v>46339.75</v>
       </c>
       <c r="L922" s="1" t="n">
-        <v>46342.95833333334</v>
+        <v>46339.95833333334</v>
       </c>
       <c r="M922" s="1" t="n">
-        <v>46343.625</v>
+        <v>46340.625</v>
       </c>
     </row>
     <row r="923">
@@ -51088,13 +51088,13 @@
         </is>
       </c>
       <c r="K923" s="1" t="n">
-        <v>46345.33333333334</v>
+        <v>46342.33333333334</v>
       </c>
       <c r="L923" s="1" t="n">
-        <v>46345.375</v>
+        <v>46342.375</v>
       </c>
       <c r="M923" s="1" t="n">
-        <v>46346.375</v>
+        <v>46343.375</v>
       </c>
     </row>
     <row r="924">
@@ -51143,13 +51143,13 @@
         </is>
       </c>
       <c r="K924" s="1" t="n">
-        <v>46347</v>
+        <v>46344</v>
       </c>
       <c r="L924" s="1" t="n">
-        <v>46347.0625</v>
+        <v>46344.0625</v>
       </c>
       <c r="M924" s="1" t="n">
-        <v>46347.64583333334</v>
+        <v>46344.64583333334</v>
       </c>
     </row>
     <row r="925">
@@ -51198,13 +51198,13 @@
         </is>
       </c>
       <c r="K925" s="1" t="n">
-        <v>46349.16666666666</v>
+        <v>46346.16666666666</v>
       </c>
       <c r="L925" s="1" t="n">
-        <v>46349.375</v>
+        <v>46346.375</v>
       </c>
       <c r="M925" s="1" t="n">
-        <v>46350.04166666666</v>
+        <v>46347.04166666666</v>
       </c>
     </row>
     <row r="926">
@@ -51253,13 +51253,13 @@
         </is>
       </c>
       <c r="K926" s="1" t="n">
-        <v>46357.04166666666</v>
+        <v>46354.04166666666</v>
       </c>
       <c r="L926" s="1" t="n">
-        <v>46357.125</v>
+        <v>46354.125</v>
       </c>
       <c r="M926" s="1" t="n">
-        <v>46357.95833333334</v>
+        <v>46354.95833333334</v>
       </c>
     </row>
     <row r="927">
@@ -51308,13 +51308,13 @@
         </is>
       </c>
       <c r="K927" s="1" t="n">
-        <v>46359.04166666666</v>
+        <v>46356.04166666666</v>
       </c>
       <c r="L927" s="1" t="n">
-        <v>46359.125</v>
+        <v>46356.125</v>
       </c>
       <c r="M927" s="1" t="n">
-        <v>46359.625</v>
+        <v>46356.625</v>
       </c>
     </row>
     <row r="928">
@@ -51363,13 +51363,13 @@
         </is>
       </c>
       <c r="K928" s="1" t="n">
-        <v>46363.625</v>
+        <v>46360.625</v>
       </c>
       <c r="L928" s="1" t="n">
-        <v>46363.66666666666</v>
+        <v>46360.66666666666</v>
       </c>
       <c r="M928" s="1" t="n">
-        <v>46364.33333333334</v>
+        <v>46361.33333333334</v>
       </c>
     </row>
     <row r="929">
@@ -51418,13 +51418,13 @@
         </is>
       </c>
       <c r="K929" s="1" t="n">
-        <v>46370.75</v>
+        <v>46367.75</v>
       </c>
       <c r="L929" s="1" t="n">
-        <v>46370.95833333334</v>
+        <v>46367.95833333334</v>
       </c>
       <c r="M929" s="1" t="n">
-        <v>46371.625</v>
+        <v>46368.625</v>
       </c>
     </row>
     <row r="930">
@@ -51473,13 +51473,13 @@
         </is>
       </c>
       <c r="K930" s="1" t="n">
-        <v>46373.33333333334</v>
+        <v>46370.33333333334</v>
       </c>
       <c r="L930" s="1" t="n">
-        <v>46373.375</v>
+        <v>46370.375</v>
       </c>
       <c r="M930" s="1" t="n">
-        <v>46374.375</v>
+        <v>46371.375</v>
       </c>
     </row>
     <row r="931">
@@ -51528,13 +51528,13 @@
         </is>
       </c>
       <c r="K931" s="1" t="n">
-        <v>46375</v>
+        <v>46372</v>
       </c>
       <c r="L931" s="1" t="n">
-        <v>46375.0625</v>
+        <v>46372.0625</v>
       </c>
       <c r="M931" s="1" t="n">
-        <v>46375.64583333334</v>
+        <v>46372.64583333334</v>
       </c>
     </row>
     <row r="932">
@@ -51583,13 +51583,13 @@
         </is>
       </c>
       <c r="K932" s="1" t="n">
-        <v>46377.16666666666</v>
+        <v>46374.16666666666</v>
       </c>
       <c r="L932" s="1" t="n">
-        <v>46377.375</v>
+        <v>46374.375</v>
       </c>
       <c r="M932" s="1" t="n">
-        <v>46378.04166666666</v>
+        <v>46375.04166666666</v>
       </c>
     </row>
     <row r="933">
@@ -51638,13 +51638,13 @@
         </is>
       </c>
       <c r="K933" s="1" t="n">
-        <v>46385.04166666666</v>
+        <v>46382.04166666666</v>
       </c>
       <c r="L933" s="1" t="n">
-        <v>46385.125</v>
+        <v>46382.125</v>
       </c>
       <c r="M933" s="1" t="n">
-        <v>46385.95833333334</v>
+        <v>46382.95833333334</v>
       </c>
     </row>
     <row r="934">
@@ -51693,13 +51693,13 @@
         </is>
       </c>
       <c r="K934" s="1" t="n">
-        <v>46387.04166666666</v>
+        <v>46384.04166666666</v>
       </c>
       <c r="L934" s="1" t="n">
-        <v>46387.125</v>
+        <v>46384.125</v>
       </c>
       <c r="M934" s="1" t="n">
-        <v>46387.625</v>
+        <v>46384.625</v>
       </c>
     </row>
     <row r="935">
@@ -51748,13 +51748,13 @@
         </is>
       </c>
       <c r="K935" s="1" t="n">
-        <v>46391.625</v>
+        <v>46388.625</v>
       </c>
       <c r="L935" s="1" t="n">
-        <v>46391.66666666666</v>
+        <v>46388.66666666666</v>
       </c>
       <c r="M935" s="1" t="n">
-        <v>46392.33333333334</v>
+        <v>46389.33333333334</v>
       </c>
     </row>
     <row r="936">
@@ -51799,13 +51799,13 @@
       </c>
       <c r="J936" t="inlineStr"/>
       <c r="K936" s="1" t="n">
-        <v>46398.75</v>
+        <v>46395.75</v>
       </c>
       <c r="L936" s="1" t="n">
-        <v>46398.95833333334</v>
+        <v>46395.95833333334</v>
       </c>
       <c r="M936" s="1" t="n">
-        <v>46399.625</v>
+        <v>46396.625</v>
       </c>
     </row>
     <row r="937">
@@ -52135,7 +52135,7 @@
         <v>46301.82916666667</v>
       </c>
       <c r="M942" s="1" t="n">
-        <v>46302.625</v>
+        <v>46302.62083333333</v>
       </c>
     </row>
     <row r="943">
@@ -52180,7 +52180,7 @@
       </c>
       <c r="J943" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K943" s="1" t="n">
@@ -52196,7 +52196,7 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
@@ -52211,47 +52211,47 @@
       </c>
       <c r="D944" t="inlineStr"/>
       <c r="E944" t="n">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="I944" t="inlineStr">
         <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="J944" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
       <c r="K944" s="1" t="n">
-        <v>46313.5</v>
+        <v>46310.625</v>
       </c>
       <c r="L944" s="1" t="n">
-        <v>46313.54166666666</v>
+        <v>46310.6875</v>
       </c>
       <c r="M944" s="1" t="n">
-        <v>46314.25</v>
+        <v>46311.25</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -52266,41 +52266,41 @@
       </c>
       <c r="D945" t="inlineStr"/>
       <c r="E945" t="n">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
           <t>KRKAN</t>
         </is>
       </c>
-      <c r="J945" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="K945" s="1" t="n">
-        <v>46314.58333333334</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="L945" s="1" t="n">
-        <v>46314.66666666666</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="M945" s="1" t="n">
-        <v>46314.91666666666</v>
+        <v>46312.58333333334</v>
       </c>
     </row>
     <row r="946">
@@ -52335,27 +52335,27 @@
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I946" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J946" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K946" s="1" t="n">
-        <v>46317.83333333334</v>
+        <v>46313.5</v>
       </c>
       <c r="L946" s="1" t="n">
-        <v>46317.875</v>
+        <v>46313.54166666666</v>
       </c>
       <c r="M946" s="1" t="n">
-        <v>46318.33333333334</v>
+        <v>46314.25</v>
       </c>
     </row>
     <row r="947">
@@ -52390,27 +52390,27 @@
       </c>
       <c r="H947" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I947" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J947" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K947" s="1" t="n">
-        <v>46320.54166666666</v>
+        <v>46314.58333333334</v>
       </c>
       <c r="L947" s="1" t="n">
-        <v>46320.70833333334</v>
+        <v>46314.66666666666</v>
       </c>
       <c r="M947" s="1" t="n">
-        <v>46321.16666666666</v>
+        <v>46314.91666666666</v>
       </c>
     </row>
     <row r="948">
@@ -52445,27 +52445,27 @@
       </c>
       <c r="H948" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I948" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J948" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K948" s="1" t="n">
-        <v>46322.91666666666</v>
+        <v>46317.83333333334</v>
       </c>
       <c r="L948" s="1" t="n">
-        <v>46322.95833333334</v>
+        <v>46317.875</v>
       </c>
       <c r="M948" s="1" t="n">
-        <v>46323.125</v>
+        <v>46318.33333333334</v>
       </c>
     </row>
     <row r="949">
@@ -52490,22 +52490,22 @@
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H949" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I949" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J949" t="inlineStr">
@@ -52514,13 +52514,13 @@
         </is>
       </c>
       <c r="K949" s="1" t="n">
-        <v>46323.375</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="L949" s="1" t="n">
-        <v>46323.5</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="M949" s="1" t="n">
-        <v>46324.83333333334</v>
+        <v>46321.16666666666</v>
       </c>
     </row>
     <row r="950">
@@ -52545,12 +52545,12 @@
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H950" t="inlineStr">
@@ -52565,17 +52565,17 @@
       </c>
       <c r="J950" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K950" s="1" t="n">
-        <v>46325.33333333334</v>
+        <v>46322.91666666666</v>
       </c>
       <c r="L950" s="1" t="n">
-        <v>46325.375</v>
+        <v>46322.95833333334</v>
       </c>
       <c r="M950" s="1" t="n">
-        <v>46325.66666666666</v>
+        <v>46323.125</v>
       </c>
     </row>
     <row r="951">
@@ -52610,27 +52610,27 @@
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I951" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J951" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K951" s="1" t="n">
-        <v>46329.75</v>
+        <v>46323.375</v>
       </c>
       <c r="L951" s="1" t="n">
-        <v>46329.79166666666</v>
+        <v>46323.5</v>
       </c>
       <c r="M951" s="1" t="n">
-        <v>46330.25</v>
+        <v>46324.83333333334</v>
       </c>
     </row>
     <row r="952">
@@ -52665,27 +52665,27 @@
       </c>
       <c r="H952" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I952" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J952" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K952" s="1" t="n">
-        <v>46331.33333333334</v>
+        <v>46325.33333333334</v>
       </c>
       <c r="L952" s="1" t="n">
-        <v>46331.375</v>
+        <v>46325.375</v>
       </c>
       <c r="M952" s="1" t="n">
-        <v>46331.95833333334</v>
+        <v>46325.66666666666</v>
       </c>
     </row>
     <row r="953">
@@ -52706,41 +52706,41 @@
       </c>
       <c r="D953" t="inlineStr"/>
       <c r="E953" t="n">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H953" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I953" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J953" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K953" s="1" t="n">
-        <v>46334.5</v>
+        <v>46329.75</v>
       </c>
       <c r="L953" s="1" t="n">
-        <v>46334.54166666666</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="M953" s="1" t="n">
-        <v>46335.25</v>
+        <v>46330.25</v>
       </c>
     </row>
     <row r="954">
@@ -52761,41 +52761,41 @@
       </c>
       <c r="D954" t="inlineStr"/>
       <c r="E954" t="n">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G954" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H954" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I954" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J954" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K954" s="1" t="n">
-        <v>46335.58333333334</v>
+        <v>46331.33333333334</v>
       </c>
       <c r="L954" s="1" t="n">
-        <v>46335.66666666666</v>
+        <v>46331.375</v>
       </c>
       <c r="M954" s="1" t="n">
-        <v>46335.91666666666</v>
+        <v>46331.95833333334</v>
       </c>
     </row>
     <row r="955">
@@ -52830,27 +52830,27 @@
       </c>
       <c r="H955" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I955" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J955" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K955" s="1" t="n">
-        <v>46338.83333333334</v>
+        <v>46334.5</v>
       </c>
       <c r="L955" s="1" t="n">
-        <v>46338.875</v>
+        <v>46334.54166666666</v>
       </c>
       <c r="M955" s="1" t="n">
-        <v>46339.33333333334</v>
+        <v>46335.25</v>
       </c>
     </row>
     <row r="956">
@@ -52885,27 +52885,27 @@
       </c>
       <c r="H956" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I956" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J956" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K956" s="1" t="n">
-        <v>46341.54166666666</v>
+        <v>46335.58333333334</v>
       </c>
       <c r="L956" s="1" t="n">
-        <v>46341.70833333334</v>
+        <v>46335.66666666666</v>
       </c>
       <c r="M956" s="1" t="n">
-        <v>46342.16666666666</v>
+        <v>46335.91666666666</v>
       </c>
     </row>
     <row r="957">
@@ -52940,27 +52940,27 @@
       </c>
       <c r="H957" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I957" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J957" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K957" s="1" t="n">
-        <v>46343.91666666666</v>
+        <v>46338.83333333334</v>
       </c>
       <c r="L957" s="1" t="n">
-        <v>46343.95833333334</v>
+        <v>46338.875</v>
       </c>
       <c r="M957" s="1" t="n">
-        <v>46344.125</v>
+        <v>46339.33333333334</v>
       </c>
     </row>
     <row r="958">
@@ -52985,22 +52985,22 @@
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H958" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I958" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J958" t="inlineStr">
@@ -53009,13 +53009,13 @@
         </is>
       </c>
       <c r="K958" s="1" t="n">
-        <v>46344.375</v>
+        <v>46341.54166666666</v>
       </c>
       <c r="L958" s="1" t="n">
-        <v>46344.5</v>
+        <v>46341.70833333334</v>
       </c>
       <c r="M958" s="1" t="n">
-        <v>46345.83333333334</v>
+        <v>46342.16666666666</v>
       </c>
     </row>
     <row r="959">
@@ -53040,12 +53040,12 @@
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H959" t="inlineStr">
@@ -53060,17 +53060,17 @@
       </c>
       <c r="J959" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K959" s="1" t="n">
-        <v>46346.33333333334</v>
+        <v>46343.91666666666</v>
       </c>
       <c r="L959" s="1" t="n">
-        <v>46346.375</v>
+        <v>46343.95833333334</v>
       </c>
       <c r="M959" s="1" t="n">
-        <v>46346.66666666666</v>
+        <v>46344.125</v>
       </c>
     </row>
     <row r="960">
@@ -53105,27 +53105,27 @@
       </c>
       <c r="H960" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I960" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J960" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K960" s="1" t="n">
-        <v>46350.75</v>
+        <v>46344.375</v>
       </c>
       <c r="L960" s="1" t="n">
-        <v>46350.79166666666</v>
+        <v>46344.5</v>
       </c>
       <c r="M960" s="1" t="n">
-        <v>46351.25</v>
+        <v>46345.83333333334</v>
       </c>
     </row>
     <row r="961">
@@ -53160,27 +53160,27 @@
       </c>
       <c r="H961" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J961" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K961" s="1" t="n">
-        <v>46352.33333333334</v>
+        <v>46346.33333333334</v>
       </c>
       <c r="L961" s="1" t="n">
-        <v>46352.375</v>
+        <v>46346.375</v>
       </c>
       <c r="M961" s="1" t="n">
-        <v>46352.95833333334</v>
+        <v>46346.66666666666</v>
       </c>
     </row>
     <row r="962">
@@ -53201,41 +53201,41 @@
       </c>
       <c r="D962" t="inlineStr"/>
       <c r="E962" t="n">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H962" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I962" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J962" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K962" s="1" t="n">
-        <v>46355.5</v>
+        <v>46350.75</v>
       </c>
       <c r="L962" s="1" t="n">
-        <v>46355.54166666666</v>
+        <v>46350.79166666666</v>
       </c>
       <c r="M962" s="1" t="n">
-        <v>46356.25</v>
+        <v>46351.25</v>
       </c>
     </row>
     <row r="963">
@@ -53256,41 +53256,41 @@
       </c>
       <c r="D963" t="inlineStr"/>
       <c r="E963" t="n">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H963" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I963" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J963" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K963" s="1" t="n">
-        <v>46356.58333333334</v>
+        <v>46352.33333333334</v>
       </c>
       <c r="L963" s="1" t="n">
-        <v>46356.66666666666</v>
+        <v>46352.375</v>
       </c>
       <c r="M963" s="1" t="n">
-        <v>46356.91666666666</v>
+        <v>46352.95833333334</v>
       </c>
     </row>
     <row r="964">
@@ -53325,27 +53325,27 @@
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I964" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J964" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K964" s="1" t="n">
-        <v>46359.83333333334</v>
+        <v>46355.5</v>
       </c>
       <c r="L964" s="1" t="n">
-        <v>46359.875</v>
+        <v>46355.54166666666</v>
       </c>
       <c r="M964" s="1" t="n">
-        <v>46360.33333333334</v>
+        <v>46356.25</v>
       </c>
     </row>
     <row r="965">
@@ -53380,27 +53380,27 @@
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I965" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J965" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K965" s="1" t="n">
-        <v>46362.54166666666</v>
+        <v>46356.58333333334</v>
       </c>
       <c r="L965" s="1" t="n">
-        <v>46362.70833333334</v>
+        <v>46356.66666666666</v>
       </c>
       <c r="M965" s="1" t="n">
-        <v>46363.16666666666</v>
+        <v>46356.91666666666</v>
       </c>
     </row>
     <row r="966">
@@ -53435,27 +53435,27 @@
       </c>
       <c r="H966" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I966" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J966" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K966" s="1" t="n">
-        <v>46364.91666666666</v>
+        <v>46359.83333333334</v>
       </c>
       <c r="L966" s="1" t="n">
-        <v>46364.95833333334</v>
+        <v>46359.875</v>
       </c>
       <c r="M966" s="1" t="n">
-        <v>46365.125</v>
+        <v>46360.33333333334</v>
       </c>
     </row>
     <row r="967">
@@ -53480,22 +53480,22 @@
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I967" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J967" t="inlineStr">
@@ -53504,13 +53504,13 @@
         </is>
       </c>
       <c r="K967" s="1" t="n">
-        <v>46365.375</v>
+        <v>46362.54166666666</v>
       </c>
       <c r="L967" s="1" t="n">
-        <v>46365.5</v>
+        <v>46362.70833333334</v>
       </c>
       <c r="M967" s="1" t="n">
-        <v>46366.83333333334</v>
+        <v>46363.16666666666</v>
       </c>
     </row>
     <row r="968">
@@ -53535,12 +53535,12 @@
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="H968" t="inlineStr">
@@ -53555,17 +53555,17 @@
       </c>
       <c r="J968" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K968" s="1" t="n">
-        <v>46367.33333333334</v>
+        <v>46364.91666666666</v>
       </c>
       <c r="L968" s="1" t="n">
-        <v>46367.375</v>
+        <v>46364.95833333334</v>
       </c>
       <c r="M968" s="1" t="n">
-        <v>46367.66666666666</v>
+        <v>46365.125</v>
       </c>
     </row>
     <row r="969">
@@ -53600,27 +53600,27 @@
       </c>
       <c r="H969" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I969" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J969" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K969" s="1" t="n">
-        <v>46371.75</v>
+        <v>46365.375</v>
       </c>
       <c r="L969" s="1" t="n">
-        <v>46371.79166666666</v>
+        <v>46365.5</v>
       </c>
       <c r="M969" s="1" t="n">
-        <v>46372.25</v>
+        <v>46366.83333333334</v>
       </c>
     </row>
     <row r="970">
@@ -53655,27 +53655,27 @@
       </c>
       <c r="H970" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J970" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K970" s="1" t="n">
-        <v>46373.33333333334</v>
+        <v>46367.33333333334</v>
       </c>
       <c r="L970" s="1" t="n">
-        <v>46373.375</v>
+        <v>46367.375</v>
       </c>
       <c r="M970" s="1" t="n">
-        <v>46373.95833333334</v>
+        <v>46367.66666666666</v>
       </c>
     </row>
     <row r="971">
@@ -53696,41 +53696,41 @@
       </c>
       <c r="D971" t="inlineStr"/>
       <c r="E971" t="n">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>2616S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="H971" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I971" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J971" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K971" s="1" t="n">
-        <v>46376.5</v>
+        <v>46371.75</v>
       </c>
       <c r="L971" s="1" t="n">
-        <v>46376.54166666666</v>
+        <v>46371.79166666666</v>
       </c>
       <c r="M971" s="1" t="n">
-        <v>46377.25</v>
+        <v>46372.25</v>
       </c>
     </row>
     <row r="972">
@@ -53751,41 +53751,41 @@
       </c>
       <c r="D972" t="inlineStr"/>
       <c r="E972" t="n">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G972" t="inlineStr">
         <is>
-          <t>2616S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J972" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K972" s="1" t="n">
-        <v>46377.58333333334</v>
+        <v>46373.33333333334</v>
       </c>
       <c r="L972" s="1" t="n">
-        <v>46377.66666666666</v>
+        <v>46373.375</v>
       </c>
       <c r="M972" s="1" t="n">
-        <v>46377.91666666666</v>
+        <v>46373.95833333334</v>
       </c>
     </row>
     <row r="973">
@@ -53820,27 +53820,27 @@
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I973" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J973" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K973" s="1" t="n">
-        <v>46380.83333333334</v>
+        <v>46376.5</v>
       </c>
       <c r="L973" s="1" t="n">
-        <v>46380.875</v>
+        <v>46376.54166666666</v>
       </c>
       <c r="M973" s="1" t="n">
-        <v>46381.33333333334</v>
+        <v>46377.25</v>
       </c>
     </row>
     <row r="974">
@@ -53875,27 +53875,27 @@
       </c>
       <c r="H974" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I974" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J974" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K974" s="1" t="n">
-        <v>46383.54166666666</v>
+        <v>46377.58333333334</v>
       </c>
       <c r="L974" s="1" t="n">
-        <v>46383.70833333334</v>
+        <v>46377.66666666666</v>
       </c>
       <c r="M974" s="1" t="n">
-        <v>46384.16666666666</v>
+        <v>46377.91666666666</v>
       </c>
     </row>
     <row r="975">
@@ -53930,27 +53930,27 @@
       </c>
       <c r="H975" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J975" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K975" s="1" t="n">
-        <v>46385.91666666666</v>
+        <v>46380.83333333334</v>
       </c>
       <c r="L975" s="1" t="n">
-        <v>46385.95833333334</v>
+        <v>46380.875</v>
       </c>
       <c r="M975" s="1" t="n">
-        <v>46386.125</v>
+        <v>46381.33333333334</v>
       </c>
     </row>
     <row r="976">
@@ -53975,22 +53975,22 @@
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J976" t="inlineStr">
@@ -53999,13 +53999,13 @@
         </is>
       </c>
       <c r="K976" s="1" t="n">
-        <v>46386.375</v>
+        <v>46383.54166666666</v>
       </c>
       <c r="L976" s="1" t="n">
-        <v>46386.5</v>
+        <v>46383.70833333334</v>
       </c>
       <c r="M976" s="1" t="n">
-        <v>46387.83333333334</v>
+        <v>46384.16666666666</v>
       </c>
     </row>
     <row r="977">
@@ -54030,12 +54030,12 @@
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="H977" t="inlineStr">
@@ -54050,17 +54050,17 @@
       </c>
       <c r="J977" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K977" s="1" t="n">
-        <v>46388.33333333334</v>
+        <v>46385.91666666666</v>
       </c>
       <c r="L977" s="1" t="n">
-        <v>46388.375</v>
+        <v>46385.95833333334</v>
       </c>
       <c r="M977" s="1" t="n">
-        <v>46388.66666666666</v>
+        <v>46386.125</v>
       </c>
     </row>
     <row r="978">
@@ -54095,27 +54095,27 @@
       </c>
       <c r="H978" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I978" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J978" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K978" s="1" t="n">
-        <v>46392.75</v>
+        <v>46386.375</v>
       </c>
       <c r="L978" s="1" t="n">
-        <v>46392.79166666666</v>
+        <v>46386.5</v>
       </c>
       <c r="M978" s="1" t="n">
-        <v>46393.25</v>
+        <v>46387.83333333334</v>
       </c>
     </row>
     <row r="979">
@@ -54150,23 +54150,27 @@
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I979" t="inlineStr">
         <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="J979" t="inlineStr"/>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
       <c r="K979" s="1" t="n">
-        <v>46394.33333333334</v>
+        <v>46388.33333333334</v>
       </c>
       <c r="L979" s="1" t="n">
-        <v>46394.375</v>
+        <v>46388.375</v>
       </c>
       <c r="M979" s="1" t="n">
-        <v>46394.95833333334</v>
+        <v>46388.66666666666</v>
       </c>
     </row>
     <row r="980">
@@ -54177,51 +54181,51 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D980" t="inlineStr"/>
       <c r="E980" t="n">
-        <v>2611</v>
+        <v>2616</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G980" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I980" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J980" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K980" s="1" t="n">
-        <v>46279.5625</v>
+        <v>46392.75</v>
       </c>
       <c r="L980" s="1" t="n">
-        <v>46279.58333333334</v>
+        <v>46392.79166666666</v>
       </c>
       <c r="M980" s="1" t="n">
-        <v>46280.91666666666</v>
+        <v>46393.25</v>
       </c>
     </row>
     <row r="981">
@@ -54232,51 +54236,47 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE VEGA</t>
         </is>
       </c>
       <c r="D981" t="inlineStr"/>
       <c r="E981" t="n">
-        <v>2611</v>
+        <v>2616</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G981" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I981" t="inlineStr">
         <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="J981" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr"/>
       <c r="K981" s="1" t="n">
-        <v>46281.125</v>
+        <v>46394.33333333334</v>
       </c>
       <c r="L981" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46394.375</v>
       </c>
       <c r="M981" s="1" t="n">
-        <v>46281.97916666666</v>
+        <v>46394.95833333334</v>
       </c>
     </row>
     <row r="982">
@@ -54311,27 +54311,27 @@
       </c>
       <c r="H982" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I982" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J982" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K982" s="1" t="n">
-        <v>46284.64583333334</v>
+        <v>46279.5625</v>
       </c>
       <c r="L982" s="1" t="n">
-        <v>46284.6875</v>
+        <v>46279.58333333334</v>
       </c>
       <c r="M982" s="1" t="n">
-        <v>46285.22916666666</v>
+        <v>46280.91666666666</v>
       </c>
     </row>
     <row r="983">
@@ -54366,27 +54366,27 @@
       </c>
       <c r="H983" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I983" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J983" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K983" s="1" t="n">
-        <v>46287.35416666666</v>
+        <v>46281.125</v>
       </c>
       <c r="L983" s="1" t="n">
-        <v>46288.16666666666</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M983" s="1" t="n">
-        <v>46288.5</v>
+        <v>46281.97916666666</v>
       </c>
     </row>
     <row r="984">
@@ -54421,27 +54421,27 @@
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J984" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K984" s="1" t="n">
-        <v>46290.1875</v>
+        <v>46284.64583333334</v>
       </c>
       <c r="L984" s="1" t="n">
-        <v>46290.39583333334</v>
+        <v>46284.6875</v>
       </c>
       <c r="M984" s="1" t="n">
-        <v>46290.70833333334</v>
+        <v>46285.22916666666</v>
       </c>
     </row>
     <row r="985">
@@ -54466,22 +54466,22 @@
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G985" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I985" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J985" t="inlineStr">
@@ -54490,13 +54490,13 @@
         </is>
       </c>
       <c r="K985" s="1" t="n">
-        <v>46290.8125</v>
+        <v>46287.35416666666</v>
       </c>
       <c r="L985" s="1" t="n">
-        <v>46290.91666666666</v>
+        <v>46288.16666666666</v>
       </c>
       <c r="M985" s="1" t="n">
-        <v>46292.58333333334</v>
+        <v>46288.5</v>
       </c>
     </row>
     <row r="986">
@@ -54521,12 +54521,12 @@
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G986" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="H986" t="inlineStr">
@@ -54541,17 +54541,17 @@
       </c>
       <c r="J986" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K986" s="1" t="n">
-        <v>46293.29166666666</v>
+        <v>46290.1875</v>
       </c>
       <c r="L986" s="1" t="n">
-        <v>46293.4375</v>
+        <v>46290.39583333334</v>
       </c>
       <c r="M986" s="1" t="n">
-        <v>46293.8125</v>
+        <v>46290.70833333334</v>
       </c>
     </row>
     <row r="987">
@@ -54586,27 +54586,27 @@
       </c>
       <c r="H987" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I987" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J987" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K987" s="1" t="n">
-        <v>46297.5</v>
+        <v>46290.8125</v>
       </c>
       <c r="L987" s="1" t="n">
-        <v>46297.5625</v>
+        <v>46290.91666666666</v>
       </c>
       <c r="M987" s="1" t="n">
-        <v>46298.0625</v>
+        <v>46292.58333333334</v>
       </c>
     </row>
     <row r="988">
@@ -54641,27 +54641,27 @@
       </c>
       <c r="H988" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I988" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J988" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K988" s="1" t="n">
-        <v>46299.08333333334</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="L988" s="1" t="n">
-        <v>46299.35416666666</v>
+        <v>46293.4375</v>
       </c>
       <c r="M988" s="1" t="n">
-        <v>46300.14583333334</v>
+        <v>46293.8125</v>
       </c>
     </row>
     <row r="989">
@@ -54682,41 +54682,41 @@
       </c>
       <c r="D989" t="inlineStr"/>
       <c r="E989" t="n">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G989" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I989" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J989" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K989" s="1" t="n">
-        <v>46302.60416666666</v>
+        <v>46297.5</v>
       </c>
       <c r="L989" s="1" t="n">
-        <v>46304.08333333334</v>
+        <v>46297.5625</v>
       </c>
       <c r="M989" s="1" t="n">
-        <v>46305.25</v>
+        <v>46298.0625</v>
       </c>
     </row>
     <row r="990">
@@ -54737,41 +54737,41 @@
       </c>
       <c r="D990" t="inlineStr"/>
       <c r="E990" t="n">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G990" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I990" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J990" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K990" s="1" t="n">
-        <v>46305.54166666666</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="L990" s="1" t="n">
-        <v>46305.60416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="M990" s="1" t="n">
-        <v>46305.9375</v>
+        <v>46300.14583333334</v>
       </c>
     </row>
     <row r="991">
@@ -54806,27 +54806,27 @@
       </c>
       <c r="H991" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I991" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J991" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K991" s="1" t="n">
-        <v>46308.83333333334</v>
+        <v>46302.60416666666</v>
       </c>
       <c r="L991" s="1" t="n">
-        <v>46308.89583333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="M991" s="1" t="n">
-        <v>46309.39583333334</v>
+        <v>46305.25</v>
       </c>
     </row>
     <row r="992">
@@ -54861,27 +54861,27 @@
       </c>
       <c r="H992" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I992" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J992" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K992" s="1" t="n">
-        <v>46311.625</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="L992" s="1" t="n">
-        <v>46311.79166666666</v>
+        <v>46305.60416666666</v>
       </c>
       <c r="M992" s="1" t="n">
-        <v>46312.41666666666</v>
+        <v>46305.9375</v>
       </c>
     </row>
     <row r="993">
@@ -54916,27 +54916,27 @@
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I993" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J993" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K993" s="1" t="n">
-        <v>46314</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="L993" s="1" t="n">
-        <v>46314.04166666666</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="M993" s="1" t="n">
-        <v>46314.25</v>
+        <v>46309.39583333334</v>
       </c>
     </row>
     <row r="994">
@@ -54961,22 +54961,22 @@
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G994" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H994" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I994" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J994" t="inlineStr">
@@ -54985,13 +54985,13 @@
         </is>
       </c>
       <c r="K994" s="1" t="n">
-        <v>46314.375</v>
+        <v>46311.625</v>
       </c>
       <c r="L994" s="1" t="n">
-        <v>46314.5</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="M994" s="1" t="n">
-        <v>46315.95833333334</v>
+        <v>46312.41666666666</v>
       </c>
     </row>
     <row r="995">
@@ -55016,12 +55016,12 @@
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G995" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H995" t="inlineStr">
@@ -55036,17 +55036,17 @@
       </c>
       <c r="J995" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K995" s="1" t="n">
-        <v>46316.16666666666</v>
+        <v>46314</v>
       </c>
       <c r="L995" s="1" t="n">
-        <v>46316.20833333334</v>
+        <v>46314.04166666666</v>
       </c>
       <c r="M995" s="1" t="n">
-        <v>46316.54166666666</v>
+        <v>46314.25</v>
       </c>
     </row>
     <row r="996">
@@ -55081,27 +55081,27 @@
       </c>
       <c r="H996" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I996" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J996" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K996" s="1" t="n">
-        <v>46320.25</v>
+        <v>46314.375</v>
       </c>
       <c r="L996" s="1" t="n">
-        <v>46320.3125</v>
+        <v>46314.5</v>
       </c>
       <c r="M996" s="1" t="n">
-        <v>46320.8125</v>
+        <v>46315.95833333334</v>
       </c>
     </row>
     <row r="997">
@@ -55136,27 +55136,27 @@
       </c>
       <c r="H997" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I997" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J997" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K997" s="1" t="n">
-        <v>46321.625</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="L997" s="1" t="n">
-        <v>46321.6875</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="M997" s="1" t="n">
-        <v>46322.3125</v>
+        <v>46316.54166666666</v>
       </c>
     </row>
     <row r="998">
@@ -55177,41 +55177,41 @@
       </c>
       <c r="D998" t="inlineStr"/>
       <c r="E998" t="n">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G998" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J998" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K998" s="1" t="n">
-        <v>46324.66666666666</v>
+        <v>46320.25</v>
       </c>
       <c r="L998" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46320.3125</v>
       </c>
       <c r="M998" s="1" t="n">
-        <v>46325.41666666666</v>
+        <v>46320.8125</v>
       </c>
     </row>
     <row r="999">
@@ -55232,41 +55232,41 @@
       </c>
       <c r="D999" t="inlineStr"/>
       <c r="E999" t="n">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G999" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H999" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I999" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J999" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K999" s="1" t="n">
-        <v>46325.75</v>
+        <v>46321.625</v>
       </c>
       <c r="L999" s="1" t="n">
-        <v>46325.83333333334</v>
+        <v>46321.6875</v>
       </c>
       <c r="M999" s="1" t="n">
-        <v>46326.08333333334</v>
+        <v>46322.3125</v>
       </c>
     </row>
     <row r="1000">
@@ -55301,27 +55301,27 @@
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1000" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1000" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K1000" s="1" t="n">
-        <v>46329</v>
+        <v>46324.66666666666</v>
       </c>
       <c r="L1000" s="1" t="n">
-        <v>46329.04166666666</v>
+        <v>46324.70833333334</v>
       </c>
       <c r="M1000" s="1" t="n">
-        <v>46329.5</v>
+        <v>46325.41666666666</v>
       </c>
     </row>
     <row r="1001">
@@ -55356,27 +55356,27 @@
       </c>
       <c r="H1001" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I1001" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J1001" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1001" s="1" t="n">
-        <v>46331.70833333334</v>
+        <v>46325.75</v>
       </c>
       <c r="L1001" s="1" t="n">
-        <v>46331.875</v>
+        <v>46325.83333333334</v>
       </c>
       <c r="M1001" s="1" t="n">
-        <v>46332.33333333334</v>
+        <v>46326.08333333334</v>
       </c>
     </row>
     <row r="1002">
@@ -55411,27 +55411,27 @@
       </c>
       <c r="H1002" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1002" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1002" s="1" t="n">
-        <v>46334.08333333334</v>
+        <v>46329</v>
       </c>
       <c r="L1002" s="1" t="n">
-        <v>46334.125</v>
+        <v>46329.04166666666</v>
       </c>
       <c r="M1002" s="1" t="n">
-        <v>46334.29166666666</v>
+        <v>46329.5</v>
       </c>
     </row>
     <row r="1003">
@@ -55456,22 +55456,22 @@
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1003" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H1003" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1003" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1003" t="inlineStr">
@@ -55480,13 +55480,13 @@
         </is>
       </c>
       <c r="K1003" s="1" t="n">
-        <v>46334.54166666666</v>
+        <v>46331.70833333334</v>
       </c>
       <c r="L1003" s="1" t="n">
-        <v>46334.66666666666</v>
+        <v>46331.875</v>
       </c>
       <c r="M1003" s="1" t="n">
-        <v>46336</v>
+        <v>46332.33333333334</v>
       </c>
     </row>
     <row r="1004">
@@ -55511,12 +55511,12 @@
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1004" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H1004" t="inlineStr">
@@ -55531,17 +55531,17 @@
       </c>
       <c r="J1004" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K1004" s="1" t="n">
-        <v>46336.5</v>
+        <v>46334.08333333334</v>
       </c>
       <c r="L1004" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46334.125</v>
       </c>
       <c r="M1004" s="1" t="n">
-        <v>46336.83333333334</v>
+        <v>46334.29166666666</v>
       </c>
     </row>
     <row r="1005">
@@ -55576,27 +55576,27 @@
       </c>
       <c r="H1005" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I1005" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J1005" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1005" s="1" t="n">
-        <v>46340.91666666666</v>
+        <v>46334.54166666666</v>
       </c>
       <c r="L1005" s="1" t="n">
-        <v>46340.95833333334</v>
+        <v>46334.66666666666</v>
       </c>
       <c r="M1005" s="1" t="n">
-        <v>46341.41666666666</v>
+        <v>46336</v>
       </c>
     </row>
     <row r="1006">
@@ -55631,27 +55631,27 @@
       </c>
       <c r="H1006" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1006" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1006" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1006" s="1" t="n">
-        <v>46342.5</v>
+        <v>46336.5</v>
       </c>
       <c r="L1006" s="1" t="n">
-        <v>46342.54166666666</v>
+        <v>46336.54166666666</v>
       </c>
       <c r="M1006" s="1" t="n">
-        <v>46343.125</v>
+        <v>46336.83333333334</v>
       </c>
     </row>
     <row r="1007">
@@ -55672,41 +55672,41 @@
       </c>
       <c r="D1007" t="inlineStr"/>
       <c r="E1007" t="n">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1007" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1007" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K1007" s="1" t="n">
-        <v>46344.83333333334</v>
+        <v>46340.91666666666</v>
       </c>
       <c r="L1007" s="1" t="n">
-        <v>46344.875</v>
+        <v>46340.95833333334</v>
       </c>
       <c r="M1007" s="1" t="n">
-        <v>46345.58333333334</v>
+        <v>46341.41666666666</v>
       </c>
     </row>
     <row r="1008">
@@ -55727,41 +55727,41 @@
       </c>
       <c r="D1008" t="inlineStr"/>
       <c r="E1008" t="n">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1008" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I1008" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="J1008" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1008" s="1" t="n">
-        <v>46345.91666666666</v>
+        <v>46342.5</v>
       </c>
       <c r="L1008" s="1" t="n">
-        <v>46346</v>
+        <v>46342.54166666666</v>
       </c>
       <c r="M1008" s="1" t="n">
-        <v>46346.25</v>
+        <v>46343.125</v>
       </c>
     </row>
     <row r="1009">
@@ -55796,27 +55796,27 @@
       </c>
       <c r="H1009" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1009" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1009" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K1009" s="1" t="n">
-        <v>46349.16666666666</v>
+        <v>46344.83333333334</v>
       </c>
       <c r="L1009" s="1" t="n">
-        <v>46349.20833333334</v>
+        <v>46344.875</v>
       </c>
       <c r="M1009" s="1" t="n">
-        <v>46349.66666666666</v>
+        <v>46345.58333333334</v>
       </c>
     </row>
     <row r="1010">
@@ -55851,27 +55851,27 @@
       </c>
       <c r="H1010" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I1010" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J1010" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1010" s="1" t="n">
-        <v>46351.875</v>
+        <v>46345.91666666666</v>
       </c>
       <c r="L1010" s="1" t="n">
-        <v>46352.04166666666</v>
+        <v>46346</v>
       </c>
       <c r="M1010" s="1" t="n">
-        <v>46352.5</v>
+        <v>46346.25</v>
       </c>
     </row>
     <row r="1011">
@@ -55906,27 +55906,27 @@
       </c>
       <c r="H1011" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1011" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1011" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1011" s="1" t="n">
-        <v>46354.25</v>
+        <v>46349.16666666666</v>
       </c>
       <c r="L1011" s="1" t="n">
-        <v>46354.29166666666</v>
+        <v>46349.20833333334</v>
       </c>
       <c r="M1011" s="1" t="n">
-        <v>46354.45833333334</v>
+        <v>46349.66666666666</v>
       </c>
     </row>
     <row r="1012">
@@ -55951,22 +55951,22 @@
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1012" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H1012" t="inlineStr">
         <is>
-          <t>BKK01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1012" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1012" t="inlineStr">
@@ -55975,13 +55975,13 @@
         </is>
       </c>
       <c r="K1012" s="1" t="n">
-        <v>46354.70833333334</v>
+        <v>46351.875</v>
       </c>
       <c r="L1012" s="1" t="n">
-        <v>46354.83333333334</v>
+        <v>46352.04166666666</v>
       </c>
       <c r="M1012" s="1" t="n">
-        <v>46356.16666666666</v>
+        <v>46352.5</v>
       </c>
     </row>
     <row r="1013">
@@ -56006,12 +56006,12 @@
       </c>
       <c r="F1013" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1013" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="H1013" t="inlineStr">
@@ -56026,17 +56026,17 @@
       </c>
       <c r="J1013" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="K1013" s="1" t="n">
-        <v>46356.66666666666</v>
+        <v>46354.25</v>
       </c>
       <c r="L1013" s="1" t="n">
-        <v>46356.70833333334</v>
+        <v>46354.29166666666</v>
       </c>
       <c r="M1013" s="1" t="n">
-        <v>46357</v>
+        <v>46354.45833333334</v>
       </c>
     </row>
     <row r="1014">
@@ -56071,27 +56071,27 @@
       </c>
       <c r="H1014" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>BKK01</t>
         </is>
       </c>
       <c r="I1014" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="J1014" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1014" s="1" t="n">
-        <v>46361.08333333334</v>
+        <v>46354.70833333334</v>
       </c>
       <c r="L1014" s="1" t="n">
-        <v>46361.125</v>
+        <v>46354.83333333334</v>
       </c>
       <c r="M1014" s="1" t="n">
-        <v>46361.58333333334</v>
+        <v>46356.16666666666</v>
       </c>
     </row>
     <row r="1015">
@@ -56126,133 +56126,133 @@
       </c>
       <c r="H1015" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
         <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="J1015" t="inlineStr"/>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
       <c r="K1015" s="1" t="n">
-        <v>46362.66666666666</v>
+        <v>46356.66666666666</v>
       </c>
       <c r="L1015" s="1" t="n">
-        <v>46362.70833333334</v>
+        <v>46356.70833333334</v>
       </c>
       <c r="M1015" s="1" t="n">
-        <v>46363.29166666666</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>ANX</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>STARSHIP JUPITER</t>
+          <t>SKY ORION</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr"/>
       <c r="E1016" t="n">
-        <v>2607</v>
+        <v>2614</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1016" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H1016" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1016" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="K1016" s="1" t="n">
-        <v>46266.45833333334</v>
+        <v>46361.08333333334</v>
       </c>
       <c r="L1016" s="1" t="n">
-        <v>46266.5</v>
+        <v>46361.125</v>
       </c>
       <c r="M1016" s="1" t="n">
-        <v>46267.1875</v>
+        <v>46361.58333333334</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>ANX</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>STARSHIP JUPITER</t>
+          <t>SKY ORION</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr"/>
       <c r="E1017" t="n">
-        <v>2607</v>
+        <v>2614</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1017" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="H1017" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>XMN01</t>
         </is>
       </c>
       <c r="I1017" t="inlineStr">
         <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="J1017" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="J1017" t="inlineStr"/>
       <c r="K1017" s="1" t="n">
-        <v>46268.20833333334</v>
+        <v>46362.66666666666</v>
       </c>
       <c r="L1017" s="1" t="n">
-        <v>46268.5</v>
+        <v>46362.70833333334</v>
       </c>
       <c r="M1017" s="1" t="n">
-        <v>46270.04166666666</v>
+        <v>46363.29166666666</v>
       </c>
     </row>
     <row r="1018">
@@ -56287,27 +56287,27 @@
       </c>
       <c r="H1018" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1018" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1018" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1018" s="1" t="n">
-        <v>46270.125</v>
+        <v>46266.45833333334</v>
       </c>
       <c r="L1018" s="1" t="n">
-        <v>46270.16666666666</v>
+        <v>46266.5</v>
       </c>
       <c r="M1018" s="1" t="n">
-        <v>46270.375</v>
+        <v>46267.1875</v>
       </c>
     </row>
     <row r="1019">
@@ -56342,27 +56342,27 @@
       </c>
       <c r="H1019" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1019" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1019" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1019" s="1" t="n">
-        <v>46271.54166666666</v>
+        <v>46268.20833333334</v>
       </c>
       <c r="L1019" s="1" t="n">
-        <v>46278.52083333334</v>
+        <v>46268.5</v>
       </c>
       <c r="M1019" s="1" t="n">
-        <v>46279.54166666666</v>
+        <v>46270.04166666666</v>
       </c>
     </row>
     <row r="1020">
@@ -56397,27 +56397,27 @@
       </c>
       <c r="H1020" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1020" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1020" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1020" s="1" t="n">
-        <v>46283.75</v>
+        <v>46270.125</v>
       </c>
       <c r="L1020" s="1" t="n">
-        <v>46284.29166666666</v>
+        <v>46270.16666666666</v>
       </c>
       <c r="M1020" s="1" t="n">
-        <v>46284.85416666666</v>
+        <v>46270.375</v>
       </c>
     </row>
     <row r="1021">
@@ -56452,27 +56452,27 @@
       </c>
       <c r="H1021" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I1021" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1021" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1021" s="1" t="n">
-        <v>46286.52083333334</v>
+        <v>46271.54166666666</v>
       </c>
       <c r="L1021" s="1" t="n">
-        <v>46286.85416666666</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="M1021" s="1" t="n">
-        <v>46287.58333333334</v>
+        <v>46279.54166666666</v>
       </c>
     </row>
     <row r="1022">
@@ -56497,37 +56497,37 @@
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1022" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1022" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1022" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1022" s="1" t="n">
-        <v>46291.41666666666</v>
+        <v>46283.75</v>
       </c>
       <c r="L1022" s="1" t="n">
-        <v>46291.45833333334</v>
+        <v>46284.29166666666</v>
       </c>
       <c r="M1022" s="1" t="n">
-        <v>46293.04166666666</v>
+        <v>46284.85416666666</v>
       </c>
     </row>
     <row r="1023">
@@ -56552,37 +56552,37 @@
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1023" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="H1023" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1023" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1023" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1023" s="1" t="n">
-        <v>46295.625</v>
+        <v>46286.52083333334</v>
       </c>
       <c r="L1023" s="1" t="n">
-        <v>46295.79166666666</v>
+        <v>46286.85416666666</v>
       </c>
       <c r="M1023" s="1" t="n">
-        <v>46296.52083333334</v>
+        <v>46287.58333333334</v>
       </c>
     </row>
     <row r="1024">
@@ -56617,27 +56617,27 @@
       </c>
       <c r="H1024" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1024" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1024" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1024" s="1" t="n">
-        <v>46298.875</v>
+        <v>46291.41666666666</v>
       </c>
       <c r="L1024" s="1" t="n">
-        <v>46299.29166666666</v>
+        <v>46291.45833333334</v>
       </c>
       <c r="M1024" s="1" t="n">
-        <v>46300.20833333334</v>
+        <v>46293.04166666666</v>
       </c>
     </row>
     <row r="1025">
@@ -56672,27 +56672,27 @@
       </c>
       <c r="H1025" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1025" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1025" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1025" s="1" t="n">
-        <v>46300.33333333334</v>
+        <v>46295.625</v>
       </c>
       <c r="L1025" s="1" t="n">
-        <v>46302.33333333334</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="M1025" s="1" t="n">
-        <v>46303.02083333334</v>
+        <v>46296.52083333334</v>
       </c>
     </row>
     <row r="1026">
@@ -56713,41 +56713,41 @@
       </c>
       <c r="D1026" t="inlineStr"/>
       <c r="E1026" t="n">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1026" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="H1026" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1026" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1026" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1026" s="1" t="n">
-        <v>46306.125</v>
+        <v>46298.875</v>
       </c>
       <c r="L1026" s="1" t="n">
-        <v>46306.16666666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="M1026" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46300.20833333334</v>
       </c>
     </row>
     <row r="1027">
@@ -56768,41 +56768,41 @@
       </c>
       <c r="D1027" t="inlineStr"/>
       <c r="E1027" t="n">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1027" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="H1027" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1027" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1027" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1027" s="1" t="n">
-        <v>46307.91666666666</v>
+        <v>46300.33333333334</v>
       </c>
       <c r="L1027" s="1" t="n">
-        <v>46307.95833333334</v>
+        <v>46302.33333333334</v>
       </c>
       <c r="M1027" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46303.04166666666</v>
       </c>
     </row>
     <row r="1028">
@@ -56837,27 +56837,27 @@
       </c>
       <c r="H1028" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1028" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1028" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1028" s="1" t="n">
-        <v>46308.75</v>
+        <v>46306.125</v>
       </c>
       <c r="L1028" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46306.16666666666</v>
       </c>
       <c r="M1028" s="1" t="n">
-        <v>46309.125</v>
+        <v>46306.83333333334</v>
       </c>
     </row>
     <row r="1029">
@@ -56892,27 +56892,27 @@
       </c>
       <c r="H1029" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1029" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1029" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1029" s="1" t="n">
-        <v>46310.41666666666</v>
+        <v>46307.91666666666</v>
       </c>
       <c r="L1029" s="1" t="n">
-        <v>46310.58333333334</v>
+        <v>46307.95833333334</v>
       </c>
       <c r="M1029" s="1" t="n">
-        <v>46311.08333333334</v>
+        <v>46308.54166666666</v>
       </c>
     </row>
     <row r="1030">
@@ -56947,27 +56947,27 @@
       </c>
       <c r="H1030" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1030" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1030" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1030" s="1" t="n">
-        <v>46315.25</v>
+        <v>46308.75</v>
       </c>
       <c r="L1030" s="1" t="n">
-        <v>46315.41666666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="M1030" s="1" t="n">
-        <v>46316.25</v>
+        <v>46309.125</v>
       </c>
     </row>
     <row r="1031">
@@ -57002,27 +57002,27 @@
       </c>
       <c r="H1031" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1031" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1031" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1031" s="1" t="n">
-        <v>46317.95833333334</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="L1031" s="1" t="n">
-        <v>46318</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="M1031" s="1" t="n">
-        <v>46318.83333333334</v>
+        <v>46311.08333333334</v>
       </c>
     </row>
     <row r="1032">
@@ -57047,37 +57047,37 @@
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t>2608N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1032" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1032" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1032" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1032" s="1" t="n">
-        <v>46322</v>
+        <v>46315.25</v>
       </c>
       <c r="L1032" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="M1032" s="1" t="n">
-        <v>46323.72916666666</v>
+        <v>46316.25</v>
       </c>
     </row>
     <row r="1033">
@@ -57102,37 +57102,37 @@
       </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>2608N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1033" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1033" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1033" s="1" t="n">
-        <v>46325.85416666666</v>
+        <v>46317.95833333334</v>
       </c>
       <c r="L1033" s="1" t="n">
-        <v>46326.02083333334</v>
+        <v>46318</v>
       </c>
       <c r="M1033" s="1" t="n">
-        <v>46326.85416666666</v>
+        <v>46318.83333333334</v>
       </c>
     </row>
     <row r="1034">
@@ -57167,27 +57167,27 @@
       </c>
       <c r="H1034" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1034" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1034" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1034" s="1" t="n">
-        <v>46329.375</v>
+        <v>46322</v>
       </c>
       <c r="L1034" s="1" t="n">
-        <v>46329.4375</v>
+        <v>46322.04166666666</v>
       </c>
       <c r="M1034" s="1" t="n">
-        <v>46329.9375</v>
+        <v>46323.72916666666</v>
       </c>
     </row>
     <row r="1035">
@@ -57222,27 +57222,27 @@
       </c>
       <c r="H1035" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1035" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1035" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1035" s="1" t="n">
-        <v>46330.16666666666</v>
+        <v>46325.85416666666</v>
       </c>
       <c r="L1035" s="1" t="n">
-        <v>46330.20833333334</v>
+        <v>46326.02083333334</v>
       </c>
       <c r="M1035" s="1" t="n">
-        <v>46330.70833333334</v>
+        <v>46326.85416666666</v>
       </c>
     </row>
     <row r="1036">
@@ -57263,41 +57263,41 @@
       </c>
       <c r="D1036" t="inlineStr"/>
       <c r="E1036" t="n">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1036" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1036" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1036" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1036" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1036" s="1" t="n">
-        <v>46333.89583333334</v>
+        <v>46329.375</v>
       </c>
       <c r="L1036" s="1" t="n">
-        <v>46333.9375</v>
+        <v>46329.4375</v>
       </c>
       <c r="M1036" s="1" t="n">
-        <v>46334.60416666666</v>
+        <v>46329.9375</v>
       </c>
     </row>
     <row r="1037">
@@ -57318,41 +57318,41 @@
       </c>
       <c r="D1037" t="inlineStr"/>
       <c r="E1037" t="n">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1037" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1037" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1037" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1037" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1037" s="1" t="n">
-        <v>46335.6875</v>
+        <v>46330.16666666666</v>
       </c>
       <c r="L1037" s="1" t="n">
-        <v>46335.72916666666</v>
+        <v>46330.20833333334</v>
       </c>
       <c r="M1037" s="1" t="n">
-        <v>46336.3125</v>
+        <v>46330.70833333334</v>
       </c>
     </row>
     <row r="1038">
@@ -57387,27 +57387,27 @@
       </c>
       <c r="H1038" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1038" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1038" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1038" s="1" t="n">
-        <v>46336.5</v>
+        <v>46333.89583333334</v>
       </c>
       <c r="L1038" s="1" t="n">
-        <v>46336.5625</v>
+        <v>46333.9375</v>
       </c>
       <c r="M1038" s="1" t="n">
-        <v>46336.89583333334</v>
+        <v>46334.60416666666</v>
       </c>
     </row>
     <row r="1039">
@@ -57442,27 +57442,27 @@
       </c>
       <c r="H1039" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1039" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1039" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1039" s="1" t="n">
-        <v>46338.1875</v>
+        <v>46335.6875</v>
       </c>
       <c r="L1039" s="1" t="n">
-        <v>46338.35416666666</v>
+        <v>46335.72916666666</v>
       </c>
       <c r="M1039" s="1" t="n">
-        <v>46338.85416666666</v>
+        <v>46336.3125</v>
       </c>
     </row>
     <row r="1040">
@@ -57497,27 +57497,27 @@
       </c>
       <c r="H1040" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1040" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1040" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1040" s="1" t="n">
-        <v>46343.02083333334</v>
+        <v>46336.5</v>
       </c>
       <c r="L1040" s="1" t="n">
-        <v>46343.1875</v>
+        <v>46336.5625</v>
       </c>
       <c r="M1040" s="1" t="n">
-        <v>46344.02083333334</v>
+        <v>46336.89583333334</v>
       </c>
     </row>
     <row r="1041">
@@ -57552,27 +57552,27 @@
       </c>
       <c r="H1041" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1041" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1041" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1041" s="1" t="n">
-        <v>46345.6875</v>
+        <v>46338.1875</v>
       </c>
       <c r="L1041" s="1" t="n">
-        <v>46345.72916666666</v>
+        <v>46338.35416666666</v>
       </c>
       <c r="M1041" s="1" t="n">
-        <v>46346.5625</v>
+        <v>46338.85416666666</v>
       </c>
     </row>
     <row r="1042">
@@ -57597,37 +57597,37 @@
       </c>
       <c r="F1042" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1042" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1042" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1042" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1042" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1042" s="1" t="n">
-        <v>46349.72916666666</v>
+        <v>46343.02083333334</v>
       </c>
       <c r="L1042" s="1" t="n">
-        <v>46349.8125</v>
+        <v>46343.1875</v>
       </c>
       <c r="M1042" s="1" t="n">
-        <v>46351.47916666666</v>
+        <v>46344.02083333334</v>
       </c>
     </row>
     <row r="1043">
@@ -57652,37 +57652,37 @@
       </c>
       <c r="F1043" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1043" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1043" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1043" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1043" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1043" s="1" t="n">
-        <v>46353.9375</v>
+        <v>46345.6875</v>
       </c>
       <c r="L1043" s="1" t="n">
-        <v>46354.10416666666</v>
+        <v>46345.72916666666</v>
       </c>
       <c r="M1043" s="1" t="n">
-        <v>46354.9375</v>
+        <v>46346.5625</v>
       </c>
     </row>
     <row r="1044">
@@ -57717,27 +57717,27 @@
       </c>
       <c r="H1044" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1044" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1044" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1044" s="1" t="n">
-        <v>46357.47916666666</v>
+        <v>46349.72916666666</v>
       </c>
       <c r="L1044" s="1" t="n">
-        <v>46357.54166666666</v>
+        <v>46349.8125</v>
       </c>
       <c r="M1044" s="1" t="n">
-        <v>46358.04166666666</v>
+        <v>46351.47916666666</v>
       </c>
     </row>
     <row r="1045">
@@ -57772,27 +57772,27 @@
       </c>
       <c r="H1045" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1045" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1045" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1045" s="1" t="n">
-        <v>46358.27083333334</v>
+        <v>46353.9375</v>
       </c>
       <c r="L1045" s="1" t="n">
-        <v>46358.3125</v>
+        <v>46354.10416666666</v>
       </c>
       <c r="M1045" s="1" t="n">
-        <v>46358.8125</v>
+        <v>46354.9375</v>
       </c>
     </row>
     <row r="1046">
@@ -57813,41 +57813,41 @@
       </c>
       <c r="D1046" t="inlineStr"/>
       <c r="E1046" t="n">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1046" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1046" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1046" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1046" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1046" s="1" t="n">
-        <v>46361.89583333334</v>
+        <v>46357.47916666666</v>
       </c>
       <c r="L1046" s="1" t="n">
-        <v>46361.9375</v>
+        <v>46357.54166666666</v>
       </c>
       <c r="M1046" s="1" t="n">
-        <v>46362.60416666666</v>
+        <v>46358.04166666666</v>
       </c>
     </row>
     <row r="1047">
@@ -57868,41 +57868,41 @@
       </c>
       <c r="D1047" t="inlineStr"/>
       <c r="E1047" t="n">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1047" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1047" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1047" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1047" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1047" s="1" t="n">
-        <v>46363.6875</v>
+        <v>46358.27083333334</v>
       </c>
       <c r="L1047" s="1" t="n">
-        <v>46363.72916666666</v>
+        <v>46358.3125</v>
       </c>
       <c r="M1047" s="1" t="n">
-        <v>46364.3125</v>
+        <v>46358.8125</v>
       </c>
     </row>
     <row r="1048">
@@ -57937,27 +57937,27 @@
       </c>
       <c r="H1048" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1048" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1048" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1048" s="1" t="n">
-        <v>46364.5</v>
+        <v>46361.89583333334</v>
       </c>
       <c r="L1048" s="1" t="n">
-        <v>46364.5625</v>
+        <v>46361.9375</v>
       </c>
       <c r="M1048" s="1" t="n">
-        <v>46364.89583333334</v>
+        <v>46362.60416666666</v>
       </c>
     </row>
     <row r="1049">
@@ -57992,27 +57992,27 @@
       </c>
       <c r="H1049" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1049" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1049" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1049" s="1" t="n">
-        <v>46366.1875</v>
+        <v>46363.6875</v>
       </c>
       <c r="L1049" s="1" t="n">
-        <v>46366.35416666666</v>
+        <v>46363.72916666666</v>
       </c>
       <c r="M1049" s="1" t="n">
-        <v>46366.85416666666</v>
+        <v>46364.3125</v>
       </c>
     </row>
     <row r="1050">
@@ -58047,27 +58047,27 @@
       </c>
       <c r="H1050" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1050" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1050" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1050" s="1" t="n">
-        <v>46371.02083333334</v>
+        <v>46364.5</v>
       </c>
       <c r="L1050" s="1" t="n">
-        <v>46371.1875</v>
+        <v>46364.5625</v>
       </c>
       <c r="M1050" s="1" t="n">
-        <v>46372.02083333334</v>
+        <v>46364.89583333334</v>
       </c>
     </row>
     <row r="1051">
@@ -58102,27 +58102,27 @@
       </c>
       <c r="H1051" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1051" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1051" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1051" s="1" t="n">
-        <v>46373.6875</v>
+        <v>46366.1875</v>
       </c>
       <c r="L1051" s="1" t="n">
-        <v>46373.72916666666</v>
+        <v>46366.35416666666</v>
       </c>
       <c r="M1051" s="1" t="n">
-        <v>46374.5625</v>
+        <v>46366.85416666666</v>
       </c>
     </row>
     <row r="1052">
@@ -58147,37 +58147,37 @@
       </c>
       <c r="F1052" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1052" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="H1052" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1052" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1052" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1052" s="1" t="n">
-        <v>46377.72916666666</v>
+        <v>46371.02083333334</v>
       </c>
       <c r="L1052" s="1" t="n">
-        <v>46377.8125</v>
+        <v>46371.1875</v>
       </c>
       <c r="M1052" s="1" t="n">
-        <v>46379.47916666666</v>
+        <v>46372.02083333334</v>
       </c>
     </row>
     <row r="1053">
@@ -58202,37 +58202,37 @@
       </c>
       <c r="F1053" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1053" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="H1053" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1053" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1053" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1053" s="1" t="n">
-        <v>46381.9375</v>
+        <v>46373.6875</v>
       </c>
       <c r="L1053" s="1" t="n">
-        <v>46382.10416666666</v>
+        <v>46373.72916666666</v>
       </c>
       <c r="M1053" s="1" t="n">
-        <v>46382.9375</v>
+        <v>46374.5625</v>
       </c>
     </row>
     <row r="1054">
@@ -58267,27 +58267,27 @@
       </c>
       <c r="H1054" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1054" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1054" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1054" s="1" t="n">
-        <v>46385.47916666666</v>
+        <v>46377.72916666666</v>
       </c>
       <c r="L1054" s="1" t="n">
-        <v>46385.54166666666</v>
+        <v>46377.8125</v>
       </c>
       <c r="M1054" s="1" t="n">
-        <v>46386.04166666666</v>
+        <v>46379.47916666666</v>
       </c>
     </row>
     <row r="1055">
@@ -58322,23 +58322,27 @@
       </c>
       <c r="H1055" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1055" t="inlineStr">
         <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="J1055" t="inlineStr"/>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
       <c r="K1055" s="1" t="n">
-        <v>46386.27083333334</v>
+        <v>46381.9375</v>
       </c>
       <c r="L1055" s="1" t="n">
-        <v>46386.3125</v>
+        <v>46382.10416666666</v>
       </c>
       <c r="M1055" s="1" t="n">
-        <v>46386.8125</v>
+        <v>46382.9375</v>
       </c>
     </row>
     <row r="1056">
@@ -58349,51 +58353,51 @@
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>YEOSU VOYAGER</t>
+          <t>STARSHIP JUPITER</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr"/>
       <c r="E1056" t="n">
-        <v>2608</v>
+        <v>2610</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1056" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="H1056" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1056" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1056" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1056" s="1" t="n">
-        <v>46301.5</v>
+        <v>46385.47916666666</v>
       </c>
       <c r="L1056" s="1" t="n">
-        <v>46303.1875</v>
+        <v>46385.54166666666</v>
       </c>
       <c r="M1056" s="1" t="n">
-        <v>46304</v>
+        <v>46386.04166666666</v>
       </c>
     </row>
     <row r="1057">
@@ -58404,51 +58408,47 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>YEOSU VOYAGER</t>
+          <t>STARSHIP JUPITER</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr"/>
       <c r="E1057" t="n">
-        <v>2608</v>
+        <v>2610</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1057" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="H1057" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1057" t="inlineStr">
         <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="J1057" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="J1057" t="inlineStr"/>
       <c r="K1057" s="1" t="n">
-        <v>46304.10416666666</v>
+        <v>46386.27083333334</v>
       </c>
       <c r="L1057" s="1" t="n">
-        <v>46304.14583333334</v>
+        <v>46386.3125</v>
       </c>
       <c r="M1057" s="1" t="n">
-        <v>46304.70833333334</v>
+        <v>46386.8125</v>
       </c>
     </row>
     <row r="1058">
@@ -58483,27 +58483,27 @@
       </c>
       <c r="H1058" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1058" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1058" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1058" s="1" t="n">
-        <v>46305.79166666666</v>
+        <v>46301.5</v>
       </c>
       <c r="L1058" s="1" t="n">
-        <v>46305.83333333334</v>
+        <v>46303.1875</v>
       </c>
       <c r="M1058" s="1" t="n">
-        <v>46306.5</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="1059">
@@ -58538,27 +58538,27 @@
       </c>
       <c r="H1059" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1059" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1059" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1059" s="1" t="n">
-        <v>46307.77083333334</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="L1059" s="1" t="n">
-        <v>46307.9375</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="M1059" s="1" t="n">
-        <v>46308.4375</v>
+        <v>46304.70833333334</v>
       </c>
     </row>
     <row r="1060">
@@ -58593,27 +58593,27 @@
       </c>
       <c r="H1060" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1060" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1060" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1060" s="1" t="n">
-        <v>46312.60416666666</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="L1060" s="1" t="n">
-        <v>46312.77083333334</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="M1060" s="1" t="n">
-        <v>46313.60416666666</v>
+        <v>46306.5</v>
       </c>
     </row>
     <row r="1061">
@@ -58648,27 +58648,27 @@
       </c>
       <c r="H1061" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1061" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1061" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1061" s="1" t="n">
-        <v>46315.27083333334</v>
+        <v>46307.77083333334</v>
       </c>
       <c r="L1061" s="1" t="n">
-        <v>46315.3125</v>
+        <v>46307.9375</v>
       </c>
       <c r="M1061" s="1" t="n">
-        <v>46316.14583333334</v>
+        <v>46308.4375</v>
       </c>
     </row>
     <row r="1062">
@@ -58693,37 +58693,37 @@
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1062" t="inlineStr">
         <is>
-          <t>2608N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1062" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1062" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1062" s="1" t="n">
-        <v>46319.3125</v>
+        <v>46312.60416666666</v>
       </c>
       <c r="L1062" s="1" t="n">
-        <v>46319.39583333334</v>
+        <v>46312.77083333334</v>
       </c>
       <c r="M1062" s="1" t="n">
-        <v>46321.0625</v>
+        <v>46313.60416666666</v>
       </c>
     </row>
     <row r="1063">
@@ -58748,37 +58748,37 @@
       </c>
       <c r="F1063" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1063" t="inlineStr">
         <is>
-          <t>2608N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="H1063" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1063" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1063" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1063" s="1" t="n">
-        <v>46323.52083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="L1063" s="1" t="n">
-        <v>46323.6875</v>
+        <v>46315.3125</v>
       </c>
       <c r="M1063" s="1" t="n">
-        <v>46324.52083333334</v>
+        <v>46316.14583333334</v>
       </c>
     </row>
     <row r="1064">
@@ -58813,27 +58813,27 @@
       </c>
       <c r="H1064" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1064" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1064" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1064" s="1" t="n">
-        <v>46327.0625</v>
+        <v>46319.3125</v>
       </c>
       <c r="L1064" s="1" t="n">
-        <v>46327.125</v>
+        <v>46319.39583333334</v>
       </c>
       <c r="M1064" s="1" t="n">
-        <v>46327.625</v>
+        <v>46321.0625</v>
       </c>
     </row>
     <row r="1065">
@@ -58868,27 +58868,27 @@
       </c>
       <c r="H1065" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1065" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1065" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1065" s="1" t="n">
-        <v>46327.85416666666</v>
+        <v>46323.52083333334</v>
       </c>
       <c r="L1065" s="1" t="n">
-        <v>46327.89583333334</v>
+        <v>46323.6875</v>
       </c>
       <c r="M1065" s="1" t="n">
-        <v>46328.39583333334</v>
+        <v>46324.52083333334</v>
       </c>
     </row>
     <row r="1066">
@@ -58909,41 +58909,41 @@
       </c>
       <c r="D1066" t="inlineStr"/>
       <c r="E1066" t="n">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1066" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1066" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1066" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1066" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1066" s="1" t="n">
-        <v>46331.47916666666</v>
+        <v>46327.0625</v>
       </c>
       <c r="L1066" s="1" t="n">
-        <v>46331.52083333334</v>
+        <v>46327.125</v>
       </c>
       <c r="M1066" s="1" t="n">
-        <v>46332.1875</v>
+        <v>46327.625</v>
       </c>
     </row>
     <row r="1067">
@@ -58964,41 +58964,41 @@
       </c>
       <c r="D1067" t="inlineStr"/>
       <c r="E1067" t="n">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1067" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H1067" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1067" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1067" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1067" s="1" t="n">
-        <v>46333.27083333334</v>
+        <v>46327.85416666666</v>
       </c>
       <c r="L1067" s="1" t="n">
-        <v>46333.3125</v>
+        <v>46327.89583333334</v>
       </c>
       <c r="M1067" s="1" t="n">
-        <v>46333.89583333334</v>
+        <v>46328.39583333334</v>
       </c>
     </row>
     <row r="1068">
@@ -59033,27 +59033,27 @@
       </c>
       <c r="H1068" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1068" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1068" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1068" s="1" t="n">
-        <v>46334.08333333334</v>
+        <v>46331.47916666666</v>
       </c>
       <c r="L1068" s="1" t="n">
-        <v>46334.14583333334</v>
+        <v>46331.52083333334</v>
       </c>
       <c r="M1068" s="1" t="n">
-        <v>46334.47916666666</v>
+        <v>46332.1875</v>
       </c>
     </row>
     <row r="1069">
@@ -59088,27 +59088,27 @@
       </c>
       <c r="H1069" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1069" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1069" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1069" s="1" t="n">
-        <v>46335.77083333334</v>
+        <v>46333.27083333334</v>
       </c>
       <c r="L1069" s="1" t="n">
-        <v>46335.9375</v>
+        <v>46333.3125</v>
       </c>
       <c r="M1069" s="1" t="n">
-        <v>46336.4375</v>
+        <v>46333.89583333334</v>
       </c>
     </row>
     <row r="1070">
@@ -59143,27 +59143,27 @@
       </c>
       <c r="H1070" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1070" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1070" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1070" s="1" t="n">
-        <v>46340.60416666666</v>
+        <v>46334.08333333334</v>
       </c>
       <c r="L1070" s="1" t="n">
-        <v>46340.77083333334</v>
+        <v>46334.14583333334</v>
       </c>
       <c r="M1070" s="1" t="n">
-        <v>46341.60416666666</v>
+        <v>46334.47916666666</v>
       </c>
     </row>
     <row r="1071">
@@ -59198,27 +59198,27 @@
       </c>
       <c r="H1071" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1071" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1071" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1071" s="1" t="n">
-        <v>46343.27083333334</v>
+        <v>46335.77083333334</v>
       </c>
       <c r="L1071" s="1" t="n">
-        <v>46343.3125</v>
+        <v>46335.9375</v>
       </c>
       <c r="M1071" s="1" t="n">
-        <v>46344.14583333334</v>
+        <v>46336.4375</v>
       </c>
     </row>
     <row r="1072">
@@ -59243,37 +59243,37 @@
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1072" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1072" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1072" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1072" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1072" s="1" t="n">
-        <v>46347.3125</v>
+        <v>46340.60416666666</v>
       </c>
       <c r="L1072" s="1" t="n">
-        <v>46347.39583333334</v>
+        <v>46340.77083333334</v>
       </c>
       <c r="M1072" s="1" t="n">
-        <v>46349.0625</v>
+        <v>46341.60416666666</v>
       </c>
     </row>
     <row r="1073">
@@ -59298,37 +59298,37 @@
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1073" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="H1073" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1073" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1073" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1073" s="1" t="n">
-        <v>46351.52083333334</v>
+        <v>46343.27083333334</v>
       </c>
       <c r="L1073" s="1" t="n">
-        <v>46351.6875</v>
+        <v>46343.3125</v>
       </c>
       <c r="M1073" s="1" t="n">
-        <v>46352.52083333334</v>
+        <v>46344.14583333334</v>
       </c>
     </row>
     <row r="1074">
@@ -59363,27 +59363,27 @@
       </c>
       <c r="H1074" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1074" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1074" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1074" s="1" t="n">
-        <v>46355.0625</v>
+        <v>46347.3125</v>
       </c>
       <c r="L1074" s="1" t="n">
-        <v>46355.125</v>
+        <v>46347.39583333334</v>
       </c>
       <c r="M1074" s="1" t="n">
-        <v>46355.625</v>
+        <v>46349.0625</v>
       </c>
     </row>
     <row r="1075">
@@ -59418,27 +59418,27 @@
       </c>
       <c r="H1075" t="inlineStr">
         <is>
-          <t>SHE04</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1075" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1075" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K1075" s="1" t="n">
-        <v>46355.85416666666</v>
+        <v>46351.52083333334</v>
       </c>
       <c r="L1075" s="1" t="n">
-        <v>46355.89583333334</v>
+        <v>46351.6875</v>
       </c>
       <c r="M1075" s="1" t="n">
-        <v>46356.39583333334</v>
+        <v>46352.52083333334</v>
       </c>
     </row>
     <row r="1076">
@@ -59459,41 +59459,41 @@
       </c>
       <c r="D1076" t="inlineStr"/>
       <c r="E1076" t="n">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1076" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1076" t="inlineStr">
         <is>
-          <t>INC08</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="I1076" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="J1076" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="K1076" s="1" t="n">
-        <v>46359.47916666666</v>
+        <v>46355.0625</v>
       </c>
       <c r="L1076" s="1" t="n">
-        <v>46359.52083333334</v>
+        <v>46355.125</v>
       </c>
       <c r="M1076" s="1" t="n">
-        <v>46360.1875</v>
+        <v>46355.625</v>
       </c>
     </row>
     <row r="1077">
@@ -59514,41 +59514,41 @@
       </c>
       <c r="D1077" t="inlineStr"/>
       <c r="E1077" t="n">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G1077" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="H1077" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="I1077" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="J1077" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="K1077" s="1" t="n">
-        <v>46361.27083333334</v>
+        <v>46355.85416666666</v>
       </c>
       <c r="L1077" s="1" t="n">
-        <v>46361.3125</v>
+        <v>46355.89583333334</v>
       </c>
       <c r="M1077" s="1" t="n">
-        <v>46361.89583333334</v>
+        <v>46356.39583333334</v>
       </c>
     </row>
     <row r="1078">
@@ -59583,27 +59583,27 @@
       </c>
       <c r="H1078" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="I1078" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J1078" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K1078" s="1" t="n">
-        <v>46362.08333333334</v>
+        <v>46359.47916666666</v>
       </c>
       <c r="L1078" s="1" t="n">
-        <v>46362.14583333334</v>
+        <v>46359.52083333334</v>
       </c>
       <c r="M1078" s="1" t="n">
-        <v>46362.47916666666</v>
+        <v>46360.1875</v>
       </c>
     </row>
     <row r="1079">
@@ -59638,27 +59638,27 @@
       </c>
       <c r="H1079" t="inlineStr">
         <is>
-          <t>SHAW2</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I1079" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="J1079" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="K1079" s="1" t="n">
-        <v>46363.77083333334</v>
+        <v>46361.27083333334</v>
       </c>
       <c r="L1079" s="1" t="n">
-        <v>46363.9375</v>
+        <v>46361.3125</v>
       </c>
       <c r="M1079" s="1" t="n">
-        <v>46364.4375</v>
+        <v>46361.89583333334</v>
       </c>
     </row>
     <row r="1080">
@@ -59693,27 +59693,27 @@
       </c>
       <c r="H1080" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="I1080" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="J1080" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K1080" s="1" t="n">
-        <v>46368.60416666666</v>
+        <v>46362.08333333334</v>
       </c>
       <c r="L1080" s="1" t="n">
-        <v>46368.77083333334</v>
+        <v>46362.14583333334</v>
       </c>
       <c r="M1080" s="1" t="n">
-        <v>46369.60416666666</v>
+        <v>46362.47916666666</v>
       </c>
     </row>
     <row r="1081">
@@ -59748,27 +59748,27 @@
       </c>
       <c r="H1081" t="inlineStr">
         <is>
-          <t>LCH04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="I1081" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J1081" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1081" s="1" t="n">
-        <v>46371.27083333334</v>
+        <v>46363.77083333334</v>
       </c>
       <c r="L1081" s="1" t="n">
-        <v>46371.3125</v>
+        <v>46363.9375</v>
       </c>
       <c r="M1081" s="1" t="n">
-        <v>46372.14583333334</v>
+        <v>46364.4375</v>
       </c>
     </row>
     <row r="1082">
@@ -59793,37 +59793,37 @@
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1082" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="H1082" t="inlineStr">
         <is>
-          <t>JKT02</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="I1082" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="J1082" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="K1082" s="1" t="n">
-        <v>46375.3125</v>
+        <v>46368.60416666666</v>
       </c>
       <c r="L1082" s="1" t="n">
-        <v>46375.39583333334</v>
+        <v>46368.77083333334</v>
       </c>
       <c r="M1082" s="1" t="n">
-        <v>46377.0625</v>
+        <v>46369.60416666666</v>
       </c>
     </row>
     <row r="1083">
@@ -59848,37 +59848,37 @@
       </c>
       <c r="F1083" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G1083" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="H1083" t="inlineStr">
         <is>
-          <t>SGN03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="I1083" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="J1083" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="K1083" s="1" t="n">
-        <v>46379.52083333334</v>
+        <v>46371.27083333334</v>
       </c>
       <c r="L1083" s="1" t="n">
-        <v>46379.6875</v>
+        <v>46371.3125</v>
       </c>
       <c r="M1083" s="1" t="n">
-        <v>46380.52083333334</v>
+        <v>46372.14583333334</v>
       </c>
     </row>
     <row r="1084">
@@ -59913,27 +59913,27 @@
       </c>
       <c r="H1084" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="I1084" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="J1084" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="K1084" s="1" t="n">
-        <v>46383.0625</v>
+        <v>46375.3125</v>
       </c>
       <c r="L1084" s="1" t="n">
-        <v>46383.125</v>
+        <v>46375.39583333334</v>
       </c>
       <c r="M1084" s="1" t="n">
-        <v>46383.625</v>
+        <v>46377.0625</v>
       </c>
     </row>
     <row r="1085">
@@ -59968,22 +59968,132 @@
       </c>
       <c r="H1085" t="inlineStr">
         <is>
+          <t>SGN03</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="K1085" s="1" t="n">
+        <v>46379.52083333334</v>
+      </c>
+      <c r="L1085" s="1" t="n">
+        <v>46379.6875</v>
+      </c>
+      <c r="M1085" s="1" t="n">
+        <v>46380.52083333334</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>ANX</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>YEOSU VOYAGER</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr"/>
+      <c r="E1086" t="n">
+        <v>2610</v>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>HKG03</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="K1086" s="1" t="n">
+        <v>46383.0625</v>
+      </c>
+      <c r="L1086" s="1" t="n">
+        <v>46383.125</v>
+      </c>
+      <c r="M1086" s="1" t="n">
+        <v>46383.625</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>ANX</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>YEOSU VOYAGER</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr"/>
+      <c r="E1087" t="n">
+        <v>2610</v>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
           <t>SHE04</t>
         </is>
       </c>
-      <c r="I1085" t="inlineStr">
+      <c r="I1087" t="inlineStr">
         <is>
           <t>CNSHK</t>
         </is>
       </c>
-      <c r="J1085" t="inlineStr"/>
-      <c r="K1085" s="1" t="n">
+      <c r="J1087" t="inlineStr"/>
+      <c r="K1087" s="1" t="n">
         <v>46383.85416666666</v>
       </c>
-      <c r="L1085" s="1" t="n">
+      <c r="L1087" s="1" t="n">
         <v>46383.89583333334</v>
       </c>
-      <c r="M1085" s="1" t="n">
+      <c r="M1087" s="1" t="n">
         <v>46384.39583333334</v>
       </c>
     </row>

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -8715,7 +8715,7 @@
         <v>46300.25</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>46302.95833333334</v>
+        <v>46302.9625</v>
       </c>
       <c r="M151" s="1" t="n">
         <v>46303.625</v>
@@ -8767,13 +8767,13 @@
         </is>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46310.625</v>
+        <v>46310.4375</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>46310.70833333334</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="M152" s="1" t="n">
-        <v>46311.54166666666</v>
+        <v>46311.35416666666</v>
       </c>
     </row>
     <row r="153">
@@ -8822,13 +8822,13 @@
         </is>
       </c>
       <c r="K153" s="1" t="n">
-        <v>46312.25</v>
+        <v>46312.0625</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>46312.33333333334</v>
+        <v>46312.14583333334</v>
       </c>
       <c r="M153" s="1" t="n">
-        <v>46312.83333333334</v>
+        <v>46312.64583333334</v>
       </c>
     </row>
     <row r="154">
@@ -8877,13 +8877,13 @@
         </is>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46316.5625</v>
+        <v>46316.375</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>46316.60416666666</v>
+        <v>46316.41666666666</v>
       </c>
       <c r="M154" s="1" t="n">
-        <v>46317.27083333334</v>
+        <v>46317.08333333334</v>
       </c>
     </row>
     <row r="155">
@@ -8932,13 +8932,13 @@
         </is>
       </c>
       <c r="K155" s="1" t="n">
-        <v>46323.33333333334</v>
+        <v>46323.1875</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>46323.54166666666</v>
+        <v>46323.39583333334</v>
       </c>
       <c r="M155" s="1" t="n">
-        <v>46324.20833333334</v>
+        <v>46324.0625</v>
       </c>
     </row>
     <row r="156">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="K156" s="1" t="n">
-        <v>46325.60416666666</v>
+        <v>46325.5</v>
       </c>
       <c r="L156" s="1" t="n">
-        <v>46325.64583333334</v>
+        <v>46325.54166666666</v>
       </c>
       <c r="M156" s="1" t="n">
-        <v>46326.64583333334</v>
+        <v>46326.54166666666</v>
       </c>
     </row>
     <row r="157">
@@ -9042,13 +9042,13 @@
         </is>
       </c>
       <c r="K157" s="1" t="n">
-        <v>46326.9375</v>
+        <v>46326.83333333334</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>46326.97916666666</v>
+        <v>46326.875</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>46327.60416666666</v>
+        <v>46327.5</v>
       </c>
     </row>
     <row r="158">
@@ -9097,13 +9097,13 @@
         </is>
       </c>
       <c r="K158" s="1" t="n">
-        <v>46329.10416666666</v>
+        <v>46328.97916666666</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>46329.3125</v>
+        <v>46329.1875</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>46329.97916666666</v>
+        <v>46329.85416666666</v>
       </c>
     </row>
     <row r="159">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="K159" s="1" t="n">
-        <v>46336.97916666666</v>
+        <v>46336.85416666666</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>46337.0625</v>
+        <v>46336.9375</v>
       </c>
       <c r="M159" s="1" t="n">
-        <v>46337.89583333334</v>
+        <v>46337.77083333334</v>
       </c>
     </row>
     <row r="160">
@@ -9207,13 +9207,13 @@
         </is>
       </c>
       <c r="K160" s="1" t="n">
-        <v>46338.97916666666</v>
+        <v>46338.85416666666</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>46339.0625</v>
+        <v>46338.9375</v>
       </c>
       <c r="M160" s="1" t="n">
-        <v>46339.5625</v>
+        <v>46339.4375</v>
       </c>
     </row>
     <row r="161">
@@ -9262,13 +9262,13 @@
         </is>
       </c>
       <c r="K161" s="1" t="n">
-        <v>46343.5625</v>
+        <v>46343.4375</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>46343.60416666666</v>
+        <v>46343.47916666666</v>
       </c>
       <c r="M161" s="1" t="n">
-        <v>46344.27083333334</v>
+        <v>46344.14583333334</v>
       </c>
     </row>
     <row r="162">
@@ -9317,13 +9317,13 @@
         </is>
       </c>
       <c r="K162" s="1" t="n">
-        <v>46350.6875</v>
+        <v>46350.5625</v>
       </c>
       <c r="L162" s="1" t="n">
-        <v>46350.89583333334</v>
+        <v>46350.77083333334</v>
       </c>
       <c r="M162" s="1" t="n">
-        <v>46351.5625</v>
+        <v>46351.4375</v>
       </c>
     </row>
     <row r="163">
@@ -9372,13 +9372,13 @@
         </is>
       </c>
       <c r="K163" s="1" t="n">
-        <v>46353.27083333334</v>
+        <v>46353.14583333334</v>
       </c>
       <c r="L163" s="1" t="n">
-        <v>46353.3125</v>
+        <v>46353.1875</v>
       </c>
       <c r="M163" s="1" t="n">
-        <v>46354.3125</v>
+        <v>46354.1875</v>
       </c>
     </row>
     <row r="164">
@@ -9427,13 +9427,13 @@
         </is>
       </c>
       <c r="K164" s="1" t="n">
-        <v>46354.9375</v>
+        <v>46354.8125</v>
       </c>
       <c r="L164" s="1" t="n">
-        <v>46354.97916666666</v>
+        <v>46354.85416666666</v>
       </c>
       <c r="M164" s="1" t="n">
-        <v>46355.60416666666</v>
+        <v>46355.47916666666</v>
       </c>
     </row>
     <row r="165">
@@ -9482,13 +9482,13 @@
         </is>
       </c>
       <c r="K165" s="1" t="n">
-        <v>46357.10416666666</v>
+        <v>46356.97916666666</v>
       </c>
       <c r="L165" s="1" t="n">
-        <v>46357.3125</v>
+        <v>46357.1875</v>
       </c>
       <c r="M165" s="1" t="n">
-        <v>46357.97916666666</v>
+        <v>46357.85416666666</v>
       </c>
     </row>
     <row r="166">
@@ -9537,13 +9537,13 @@
         </is>
       </c>
       <c r="K166" s="1" t="n">
-        <v>46364.97916666666</v>
+        <v>46364.85416666666</v>
       </c>
       <c r="L166" s="1" t="n">
-        <v>46365.0625</v>
+        <v>46364.9375</v>
       </c>
       <c r="M166" s="1" t="n">
-        <v>46365.89583333334</v>
+        <v>46365.77083333334</v>
       </c>
     </row>
     <row r="167">
@@ -9592,13 +9592,13 @@
         </is>
       </c>
       <c r="K167" s="1" t="n">
-        <v>46366.97916666666</v>
+        <v>46366.85416666666</v>
       </c>
       <c r="L167" s="1" t="n">
-        <v>46367.0625</v>
+        <v>46366.9375</v>
       </c>
       <c r="M167" s="1" t="n">
-        <v>46367.5625</v>
+        <v>46367.4375</v>
       </c>
     </row>
     <row r="168">
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="K168" s="1" t="n">
-        <v>46371.5625</v>
+        <v>46371.4375</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>46371.60416666666</v>
+        <v>46371.47916666666</v>
       </c>
       <c r="M168" s="1" t="n">
-        <v>46372.27083333334</v>
+        <v>46372.14583333334</v>
       </c>
     </row>
     <row r="169">
@@ -9698,13 +9698,13 @@
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" s="1" t="n">
-        <v>46378.6875</v>
+        <v>46378.5625</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>46378.89583333334</v>
+        <v>46378.77083333334</v>
       </c>
       <c r="M169" s="1" t="n">
-        <v>46379.5625</v>
+        <v>46379.4375</v>
       </c>
     </row>
     <row r="170">
@@ -28154,7 +28154,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>SIS2</t>
+          <t>ADHS</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -28169,16 +28169,16 @@
       </c>
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="n">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -28193,23 +28193,23 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="K506" s="1" t="n">
         <v>46304</v>
       </c>
       <c r="L506" s="1" t="n">
-        <v>46304.04166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="M506" s="1" t="n">
-        <v>46306.04166666666</v>
+        <v>46305.54166666666</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>ADHS</t>
+          <t>SIS2</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -28224,16 +28224,16 @@
       </c>
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="n">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -28248,23 +28248,23 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="K507" s="1" t="n">
         <v>46304</v>
       </c>
       <c r="L507" s="1" t="n">
-        <v>46304.29166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="M507" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46306.04166666666</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>SIS2</t>
+          <t>ADHS</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -28279,47 +28279,47 @@
       </c>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="n">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>TAO04</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
           <t>CNSHA</t>
         </is>
       </c>
-      <c r="J508" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
       <c r="K508" s="1" t="n">
-        <v>46307.41666666666</v>
+        <v>46305.45833333334</v>
       </c>
       <c r="L508" s="1" t="n">
-        <v>46310.625</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="M508" s="1" t="n">
-        <v>46311.625</v>
+        <v>46310.70833333334</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>ADHS</t>
+          <t>SIS2</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -28334,41 +28334,41 @@
       </c>
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="n">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>TAO04</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNNGB</t>
         </is>
       </c>
       <c r="K509" s="1" t="n">
-        <v>46308.04166666666</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>46312.29166666666</v>
+        <v>46310.625</v>
       </c>
       <c r="M509" s="1" t="n">
-        <v>46313.29166666666</v>
+        <v>46311.625</v>
       </c>
     </row>
     <row r="510">
@@ -28417,13 +28417,13 @@
         </is>
       </c>
       <c r="K510" s="1" t="n">
+        <v>46311.70833333334</v>
+      </c>
+      <c r="L510" s="1" t="n">
+        <v>46313.70833333334</v>
+      </c>
+      <c r="M510" s="1" t="n">
         <v>46314.29166666666</v>
-      </c>
-      <c r="L510" s="1" t="n">
-        <v>46316.29166666666</v>
-      </c>
-      <c r="M510" s="1" t="n">
-        <v>46316.875</v>
       </c>
     </row>
     <row r="511">
@@ -28472,13 +28472,13 @@
         </is>
       </c>
       <c r="K511" s="1" t="n">
-        <v>46317.625</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>46318.70833333334</v>
+        <v>46316.125</v>
       </c>
       <c r="M511" s="1" t="n">
-        <v>46319.375</v>
+        <v>46316.79166666666</v>
       </c>
     </row>
     <row r="512">
@@ -28527,13 +28527,13 @@
         </is>
       </c>
       <c r="K512" s="1" t="n">
-        <v>46321.29166666666</v>
+        <v>46318.70833333334</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>46321.41666666666</v>
+        <v>46318.83333333334</v>
       </c>
       <c r="M512" s="1" t="n">
-        <v>46322.16666666666</v>
+        <v>46319.58333333334</v>
       </c>
     </row>
     <row r="513">
@@ -28582,13 +28582,13 @@
         </is>
       </c>
       <c r="K513" s="1" t="n">
-        <v>46333.91666666666</v>
+        <v>46331.33333333334</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>46343.91666666666</v>
+        <v>46341.33333333334</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46350.91666666666</v>
+        <v>46348.33333333334</v>
       </c>
     </row>
     <row r="514">
@@ -28633,13 +28633,13 @@
       </c>
       <c r="J514" t="inlineStr"/>
       <c r="K514" s="1" t="n">
-        <v>46365</v>
+        <v>46362.41666666666</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>46365.04166666666</v>
+        <v>46362.45833333334</v>
       </c>
       <c r="M514" s="1" t="n">
-        <v>46366.04166666666</v>
+        <v>46363.45833333334</v>
       </c>
     </row>
     <row r="515">
@@ -46314,10 +46314,10 @@
         <v>46303.91666666666</v>
       </c>
       <c r="L836" s="1" t="n">
-        <v>46303.95833333334</v>
+        <v>46304.625</v>
       </c>
       <c r="M836" s="1" t="n">
-        <v>46304.70833333334</v>
+        <v>46305.5</v>
       </c>
     </row>
     <row r="837">
@@ -46366,13 +46366,13 @@
         </is>
       </c>
       <c r="K837" s="1" t="n">
-        <v>46308.375</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="L837" s="1" t="n">
-        <v>46308.41666666666</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="M837" s="1" t="n">
-        <v>46309.08333333334</v>
+        <v>46309.875</v>
       </c>
     </row>
     <row r="838">
@@ -46421,13 +46421,13 @@
         </is>
       </c>
       <c r="K838" s="1" t="n">
-        <v>46315.14583333334</v>
+        <v>46315.9375</v>
       </c>
       <c r="L838" s="1" t="n">
-        <v>46315.91666666666</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="M838" s="1" t="n">
-        <v>46316.58333333334</v>
+        <v>46317.375</v>
       </c>
     </row>
     <row r="839">
@@ -46476,13 +46476,13 @@
         </is>
       </c>
       <c r="K839" s="1" t="n">
-        <v>46318.02083333334</v>
+        <v>46318.8125</v>
       </c>
       <c r="L839" s="1" t="n">
-        <v>46318.0625</v>
+        <v>46318.85416666666</v>
       </c>
       <c r="M839" s="1" t="n">
-        <v>46319.0625</v>
+        <v>46319.85416666666</v>
       </c>
     </row>
     <row r="840">
@@ -46531,13 +46531,13 @@
         </is>
       </c>
       <c r="K840" s="1" t="n">
-        <v>46319.35416666666</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="L840" s="1" t="n">
-        <v>46319.39583333334</v>
+        <v>46320.1875</v>
       </c>
       <c r="M840" s="1" t="n">
-        <v>46320.02083333334</v>
+        <v>46320.8125</v>
       </c>
     </row>
     <row r="841">
@@ -46586,13 +46586,13 @@
         </is>
       </c>
       <c r="K841" s="1" t="n">
-        <v>46321.47916666666</v>
+        <v>46322.27083333334</v>
       </c>
       <c r="L841" s="1" t="n">
-        <v>46321.6875</v>
+        <v>46322.47916666666</v>
       </c>
       <c r="M841" s="1" t="n">
-        <v>46322.35416666666</v>
+        <v>46323.14583333334</v>
       </c>
     </row>
     <row r="842">
@@ -46641,13 +46641,13 @@
         </is>
       </c>
       <c r="K842" s="1" t="n">
-        <v>46329.35416666666</v>
+        <v>46330.14583333334</v>
       </c>
       <c r="L842" s="1" t="n">
-        <v>46329.4375</v>
+        <v>46330.22916666666</v>
       </c>
       <c r="M842" s="1" t="n">
-        <v>46330.27083333334</v>
+        <v>46331.0625</v>
       </c>
     </row>
     <row r="843">
@@ -46696,13 +46696,13 @@
         </is>
       </c>
       <c r="K843" s="1" t="n">
-        <v>46331.35416666666</v>
+        <v>46332.14583333334</v>
       </c>
       <c r="L843" s="1" t="n">
-        <v>46331.4375</v>
+        <v>46332.22916666666</v>
       </c>
       <c r="M843" s="1" t="n">
-        <v>46331.9375</v>
+        <v>46332.72916666666</v>
       </c>
     </row>
     <row r="844">
@@ -46751,13 +46751,13 @@
         </is>
       </c>
       <c r="K844" s="1" t="n">
-        <v>46335.9375</v>
+        <v>46336.72916666666</v>
       </c>
       <c r="L844" s="1" t="n">
-        <v>46335.97916666666</v>
+        <v>46336.77083333334</v>
       </c>
       <c r="M844" s="1" t="n">
-        <v>46336.64583333334</v>
+        <v>46337.4375</v>
       </c>
     </row>
     <row r="845">
@@ -46806,13 +46806,13 @@
         </is>
       </c>
       <c r="K845" s="1" t="n">
-        <v>46343.0625</v>
+        <v>46343.85416666666</v>
       </c>
       <c r="L845" s="1" t="n">
-        <v>46343.27083333334</v>
+        <v>46344.0625</v>
       </c>
       <c r="M845" s="1" t="n">
-        <v>46343.9375</v>
+        <v>46344.72916666666</v>
       </c>
     </row>
     <row r="846">
@@ -46861,13 +46861,13 @@
         </is>
       </c>
       <c r="K846" s="1" t="n">
-        <v>46345.39583333334</v>
+        <v>46346.1875</v>
       </c>
       <c r="L846" s="1" t="n">
-        <v>46345.4375</v>
+        <v>46346.22916666666</v>
       </c>
       <c r="M846" s="1" t="n">
-        <v>46346.4375</v>
+        <v>46347.22916666666</v>
       </c>
     </row>
     <row r="847">
@@ -46916,13 +46916,13 @@
         </is>
       </c>
       <c r="K847" s="1" t="n">
-        <v>46347.0625</v>
+        <v>46347.85416666666</v>
       </c>
       <c r="L847" s="1" t="n">
-        <v>46347.10416666666</v>
+        <v>46347.89583333334</v>
       </c>
       <c r="M847" s="1" t="n">
-        <v>46347.72916666666</v>
+        <v>46348.52083333334</v>
       </c>
     </row>
     <row r="848">
@@ -46971,13 +46971,13 @@
         </is>
       </c>
       <c r="K848" s="1" t="n">
-        <v>46349.1875</v>
+        <v>46349.97916666666</v>
       </c>
       <c r="L848" s="1" t="n">
-        <v>46349.39583333334</v>
+        <v>46350.1875</v>
       </c>
       <c r="M848" s="1" t="n">
-        <v>46350.0625</v>
+        <v>46350.85416666666</v>
       </c>
     </row>
     <row r="849">
@@ -47026,13 +47026,13 @@
         </is>
       </c>
       <c r="K849" s="1" t="n">
-        <v>46357.0625</v>
+        <v>46357.85416666666</v>
       </c>
       <c r="L849" s="1" t="n">
-        <v>46357.14583333334</v>
+        <v>46357.9375</v>
       </c>
       <c r="M849" s="1" t="n">
-        <v>46357.97916666666</v>
+        <v>46358.77083333334</v>
       </c>
     </row>
     <row r="850">
@@ -47081,13 +47081,13 @@
         </is>
       </c>
       <c r="K850" s="1" t="n">
-        <v>46359.0625</v>
+        <v>46359.85416666666</v>
       </c>
       <c r="L850" s="1" t="n">
-        <v>46359.14583333334</v>
+        <v>46359.9375</v>
       </c>
       <c r="M850" s="1" t="n">
-        <v>46359.64583333334</v>
+        <v>46360.4375</v>
       </c>
     </row>
     <row r="851">
@@ -47136,13 +47136,13 @@
         </is>
       </c>
       <c r="K851" s="1" t="n">
-        <v>46363.64583333334</v>
+        <v>46364.4375</v>
       </c>
       <c r="L851" s="1" t="n">
-        <v>46363.6875</v>
+        <v>46364.47916666666</v>
       </c>
       <c r="M851" s="1" t="n">
-        <v>46364.35416666666</v>
+        <v>46365.14583333334</v>
       </c>
     </row>
     <row r="852">
@@ -47191,13 +47191,13 @@
         </is>
       </c>
       <c r="K852" s="1" t="n">
-        <v>46370.77083333334</v>
+        <v>46371.5625</v>
       </c>
       <c r="L852" s="1" t="n">
-        <v>46370.97916666666</v>
+        <v>46371.77083333334</v>
       </c>
       <c r="M852" s="1" t="n">
-        <v>46371.64583333334</v>
+        <v>46372.4375</v>
       </c>
     </row>
     <row r="853">
@@ -47246,13 +47246,13 @@
         </is>
       </c>
       <c r="K853" s="1" t="n">
-        <v>46373.35416666666</v>
+        <v>46374.14583333334</v>
       </c>
       <c r="L853" s="1" t="n">
-        <v>46373.39583333334</v>
+        <v>46374.1875</v>
       </c>
       <c r="M853" s="1" t="n">
-        <v>46374.39583333334</v>
+        <v>46375.1875</v>
       </c>
     </row>
     <row r="854">
@@ -47301,13 +47301,13 @@
         </is>
       </c>
       <c r="K854" s="1" t="n">
-        <v>46375.02083333334</v>
+        <v>46375.8125</v>
       </c>
       <c r="L854" s="1" t="n">
-        <v>46375.0625</v>
+        <v>46375.85416666666</v>
       </c>
       <c r="M854" s="1" t="n">
-        <v>46375.6875</v>
+        <v>46376.47916666666</v>
       </c>
     </row>
     <row r="855">
@@ -47356,13 +47356,13 @@
         </is>
       </c>
       <c r="K855" s="1" t="n">
-        <v>46377.1875</v>
+        <v>46377.97916666666</v>
       </c>
       <c r="L855" s="1" t="n">
-        <v>46377.39583333334</v>
+        <v>46378.1875</v>
       </c>
       <c r="M855" s="1" t="n">
-        <v>46378.0625</v>
+        <v>46378.85416666666</v>
       </c>
     </row>
     <row r="856">
@@ -47411,13 +47411,13 @@
         </is>
       </c>
       <c r="K856" s="1" t="n">
-        <v>46385.0625</v>
+        <v>46385.85416666666</v>
       </c>
       <c r="L856" s="1" t="n">
-        <v>46385.14583333334</v>
+        <v>46385.9375</v>
       </c>
       <c r="M856" s="1" t="n">
-        <v>46385.97916666666</v>
+        <v>46386.77083333334</v>
       </c>
     </row>
     <row r="857">
@@ -47466,13 +47466,13 @@
         </is>
       </c>
       <c r="K857" s="1" t="n">
-        <v>46387.0625</v>
+        <v>46387.85416666666</v>
       </c>
       <c r="L857" s="1" t="n">
-        <v>46387.14583333334</v>
+        <v>46387.9375</v>
       </c>
       <c r="M857" s="1" t="n">
-        <v>46387.64583333334</v>
+        <v>46388.4375</v>
       </c>
     </row>
     <row r="858">
@@ -47521,13 +47521,13 @@
         </is>
       </c>
       <c r="K858" s="1" t="n">
-        <v>46391.64583333334</v>
+        <v>46392.4375</v>
       </c>
       <c r="L858" s="1" t="n">
-        <v>46391.6875</v>
+        <v>46392.47916666666</v>
       </c>
       <c r="M858" s="1" t="n">
-        <v>46392.35416666666</v>
+        <v>46393.14583333334</v>
       </c>
     </row>
     <row r="859">
@@ -47572,13 +47572,13 @@
       </c>
       <c r="J859" t="inlineStr"/>
       <c r="K859" s="1" t="n">
-        <v>46398.77083333334</v>
+        <v>46399.5625</v>
       </c>
       <c r="L859" s="1" t="n">
-        <v>46398.97916666666</v>
+        <v>46399.77083333334</v>
       </c>
       <c r="M859" s="1" t="n">
-        <v>46399.64583333334</v>
+        <v>46400.4375</v>
       </c>
     </row>
     <row r="860">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -28307,13 +28307,13 @@
         </is>
       </c>
       <c r="K508" s="1" t="n">
-        <v>46305.45833333334</v>
+        <v>46307.20833333334</v>
       </c>
       <c r="L508" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46312.29166666666</v>
       </c>
       <c r="M508" s="1" t="n">
-        <v>46310.70833333334</v>
+        <v>46313.29166666666</v>
       </c>
     </row>
     <row r="509">
@@ -28417,13 +28417,13 @@
         </is>
       </c>
       <c r="K510" s="1" t="n">
-        <v>46311.70833333334</v>
+        <v>46314.29166666666</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>46313.70833333334</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="M510" s="1" t="n">
-        <v>46314.29166666666</v>
+        <v>46316.875</v>
       </c>
     </row>
     <row r="511">
@@ -28472,13 +28472,13 @@
         </is>
       </c>
       <c r="K511" s="1" t="n">
-        <v>46315.04166666666</v>
+        <v>46317.625</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>46316.125</v>
+        <v>46318.70833333334</v>
       </c>
       <c r="M511" s="1" t="n">
-        <v>46316.79166666666</v>
+        <v>46319.375</v>
       </c>
     </row>
     <row r="512">
@@ -28527,13 +28527,13 @@
         </is>
       </c>
       <c r="K512" s="1" t="n">
-        <v>46318.70833333334</v>
+        <v>46321.29166666666</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>46318.83333333334</v>
+        <v>46321.41666666666</v>
       </c>
       <c r="M512" s="1" t="n">
-        <v>46319.58333333334</v>
+        <v>46322.16666666666</v>
       </c>
     </row>
     <row r="513">
@@ -28582,13 +28582,13 @@
         </is>
       </c>
       <c r="K513" s="1" t="n">
-        <v>46331.33333333334</v>
+        <v>46333.91666666666</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>46341.33333333334</v>
+        <v>46343.91666666666</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46348.33333333334</v>
+        <v>46350.91666666666</v>
       </c>
     </row>
     <row r="514">
@@ -28633,13 +28633,13 @@
       </c>
       <c r="J514" t="inlineStr"/>
       <c r="K514" s="1" t="n">
-        <v>46362.41666666666</v>
+        <v>46365</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>46362.45833333334</v>
+        <v>46365.04166666666</v>
       </c>
       <c r="M514" s="1" t="n">
-        <v>46363.45833333334</v>
+        <v>46366.04166666666</v>
       </c>
     </row>
     <row r="515">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -28252,13 +28252,13 @@
         </is>
       </c>
       <c r="K507" s="1" t="n">
-        <v>46304</v>
+        <v>46304.25</v>
       </c>
       <c r="L507" s="1" t="n">
-        <v>46304.04166666666</v>
+        <v>46304.2875</v>
       </c>
       <c r="M507" s="1" t="n">
-        <v>46306.04166666666</v>
+        <v>46306.54166666666</v>
       </c>
     </row>
     <row r="508">
@@ -28362,13 +28362,13 @@
         </is>
       </c>
       <c r="K509" s="1" t="n">
-        <v>46307.41666666666</v>
+        <v>46308</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>46310.625</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="M509" s="1" t="n">
-        <v>46311.625</v>
+        <v>46312.20833333334</v>
       </c>
     </row>
     <row r="510">
@@ -48012,13 +48012,13 @@
         </is>
       </c>
       <c r="K867" s="1" t="n">
-        <v>46303.75</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="L867" s="1" t="n">
-        <v>46303.79166666666</v>
+        <v>46303.76666666667</v>
       </c>
       <c r="M867" s="1" t="n">
-        <v>46304.25</v>
+        <v>46304.29166666666</v>
       </c>
     </row>
     <row r="868">
@@ -48067,13 +48067,13 @@
         </is>
       </c>
       <c r="K868" s="1" t="n">
-        <v>46305.75</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="L868" s="1" t="n">
-        <v>46306.91666666666</v>
+        <v>46307</v>
       </c>
       <c r="M868" s="1" t="n">
-        <v>46307.41666666666</v>
+        <v>46307.5</v>
       </c>
     </row>
     <row r="869">
@@ -48122,13 +48122,13 @@
         </is>
       </c>
       <c r="K869" s="1" t="n">
-        <v>46312.4375</v>
+        <v>46312.52083333334</v>
       </c>
       <c r="L869" s="1" t="n">
-        <v>46312.5</v>
+        <v>46312.58333333334</v>
       </c>
       <c r="M869" s="1" t="n">
-        <v>46312.75</v>
+        <v>46312.83333333334</v>
       </c>
     </row>
     <row r="870">
@@ -48177,13 +48177,13 @@
         </is>
       </c>
       <c r="K870" s="1" t="n">
-        <v>46313.6875</v>
+        <v>46313.77083333334</v>
       </c>
       <c r="L870" s="1" t="n">
-        <v>46313.75</v>
+        <v>46313.83333333334</v>
       </c>
       <c r="M870" s="1" t="n">
-        <v>46314.16666666666</v>
+        <v>46314.25</v>
       </c>
     </row>
     <row r="871">
@@ -48232,13 +48232,13 @@
         </is>
       </c>
       <c r="K871" s="1" t="n">
-        <v>46314.5</v>
+        <v>46314.58333333334</v>
       </c>
       <c r="L871" s="1" t="n">
-        <v>46314.54166666666</v>
+        <v>46314.625</v>
       </c>
       <c r="M871" s="1" t="n">
-        <v>46315.16666666666</v>
+        <v>46315.25</v>
       </c>
     </row>
     <row r="872">
@@ -48287,13 +48287,13 @@
         </is>
       </c>
       <c r="K872" s="1" t="n">
-        <v>46316.25</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="L872" s="1" t="n">
-        <v>46318.41666666666</v>
+        <v>46318.5</v>
       </c>
       <c r="M872" s="1" t="n">
-        <v>46319.41666666666</v>
+        <v>46319.5</v>
       </c>
     </row>
     <row r="873">
@@ -48342,13 +48342,13 @@
         </is>
       </c>
       <c r="K873" s="1" t="n">
-        <v>46323.625</v>
+        <v>46323.70833333334</v>
       </c>
       <c r="L873" s="1" t="n">
-        <v>46324.75</v>
+        <v>46324.83333333334</v>
       </c>
       <c r="M873" s="1" t="n">
-        <v>46325.25</v>
+        <v>46325.33333333334</v>
       </c>
     </row>
     <row r="874">
@@ -48397,13 +48397,13 @@
         </is>
       </c>
       <c r="K874" s="1" t="n">
-        <v>46326.83333333334</v>
+        <v>46326.91666666666</v>
       </c>
       <c r="L874" s="1" t="n">
-        <v>46326.875</v>
+        <v>46326.95833333334</v>
       </c>
       <c r="M874" s="1" t="n">
-        <v>46327.29166666666</v>
+        <v>46327.375</v>
       </c>
     </row>
     <row r="875">
@@ -48452,13 +48452,13 @@
         </is>
       </c>
       <c r="K875" s="1" t="n">
-        <v>46327.45833333334</v>
+        <v>46327.54166666666</v>
       </c>
       <c r="L875" s="1" t="n">
-        <v>46327.58333333334</v>
+        <v>46327.66666666666</v>
       </c>
       <c r="M875" s="1" t="n">
-        <v>46328.58333333334</v>
+        <v>46328.66666666666</v>
       </c>
     </row>
     <row r="876">
@@ -48507,13 +48507,13 @@
         </is>
       </c>
       <c r="K876" s="1" t="n">
-        <v>46328.83333333334</v>
+        <v>46328.91666666666</v>
       </c>
       <c r="L876" s="1" t="n">
-        <v>46328.875</v>
+        <v>46328.95833333334</v>
       </c>
       <c r="M876" s="1" t="n">
-        <v>46329.29166666666</v>
+        <v>46329.375</v>
       </c>
     </row>
     <row r="877">
@@ -48562,13 +48562,13 @@
         </is>
       </c>
       <c r="K877" s="1" t="n">
-        <v>46330.79166666666</v>
+        <v>46330.875</v>
       </c>
       <c r="L877" s="1" t="n">
-        <v>46331.91666666666</v>
+        <v>46332</v>
       </c>
       <c r="M877" s="1" t="n">
-        <v>46332.41666666666</v>
+        <v>46332.5</v>
       </c>
     </row>
     <row r="878">
@@ -48617,13 +48617,13 @@
         </is>
       </c>
       <c r="K878" s="1" t="n">
-        <v>46338.97916666666</v>
+        <v>46339.0625</v>
       </c>
       <c r="L878" s="1" t="n">
-        <v>46339.04166666666</v>
+        <v>46339.125</v>
       </c>
       <c r="M878" s="1" t="n">
-        <v>46339.29166666666</v>
+        <v>46339.375</v>
       </c>
     </row>
     <row r="879">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="K879" s="1" t="n">
-        <v>46340.22916666666</v>
+        <v>46340.3125</v>
       </c>
       <c r="L879" s="1" t="n">
-        <v>46340.29166666666</v>
+        <v>46340.375</v>
       </c>
       <c r="M879" s="1" t="n">
-        <v>46340.70833333334</v>
+        <v>46340.79166666666</v>
       </c>
     </row>
     <row r="880">
@@ -48727,13 +48727,13 @@
         </is>
       </c>
       <c r="K880" s="1" t="n">
-        <v>46341.04166666666</v>
+        <v>46341.125</v>
       </c>
       <c r="L880" s="1" t="n">
-        <v>46341.08333333334</v>
+        <v>46341.16666666666</v>
       </c>
       <c r="M880" s="1" t="n">
-        <v>46341.70833333334</v>
+        <v>46341.79166666666</v>
       </c>
     </row>
     <row r="881">
@@ -48782,13 +48782,13 @@
         </is>
       </c>
       <c r="K881" s="1" t="n">
-        <v>46342.78888888889</v>
+        <v>46342.87222222222</v>
       </c>
       <c r="L881" s="1" t="n">
-        <v>46342.95555555556</v>
+        <v>46343.03888888889</v>
       </c>
       <c r="M881" s="1" t="n">
-        <v>46343.95555555556</v>
+        <v>46344.03888888889</v>
       </c>
     </row>
     <row r="882">
@@ -48837,13 +48837,13 @@
         </is>
       </c>
       <c r="K882" s="1" t="n">
-        <v>46348.16388888889</v>
+        <v>46348.24722222222</v>
       </c>
       <c r="L882" s="1" t="n">
-        <v>46348.28888888889</v>
+        <v>46348.37222222222</v>
       </c>
       <c r="M882" s="1" t="n">
-        <v>46348.78888888889</v>
+        <v>46348.87222222222</v>
       </c>
     </row>
     <row r="883">
@@ -48892,13 +48892,13 @@
         </is>
       </c>
       <c r="K883" s="1" t="n">
-        <v>46350.37222222222</v>
+        <v>46350.45555555556</v>
       </c>
       <c r="L883" s="1" t="n">
-        <v>46350.41388888889</v>
+        <v>46350.49722222222</v>
       </c>
       <c r="M883" s="1" t="n">
-        <v>46350.83055555556</v>
+        <v>46350.91388888889</v>
       </c>
     </row>
     <row r="884">
@@ -48947,13 +48947,13 @@
         </is>
       </c>
       <c r="K884" s="1" t="n">
-        <v>46350.99722222222</v>
+        <v>46351.08055555556</v>
       </c>
       <c r="L884" s="1" t="n">
-        <v>46351.12222222222</v>
+        <v>46351.20555555556</v>
       </c>
       <c r="M884" s="1" t="n">
-        <v>46352.12222222222</v>
+        <v>46352.20555555556</v>
       </c>
     </row>
     <row r="885">
@@ -49002,13 +49002,13 @@
         </is>
       </c>
       <c r="K885" s="1" t="n">
-        <v>46352.37222222222</v>
+        <v>46352.45555555556</v>
       </c>
       <c r="L885" s="1" t="n">
-        <v>46352.41388888889</v>
+        <v>46352.49722222222</v>
       </c>
       <c r="M885" s="1" t="n">
-        <v>46352.83055555556</v>
+        <v>46352.91388888889</v>
       </c>
     </row>
     <row r="886">
@@ -49057,13 +49057,13 @@
         </is>
       </c>
       <c r="K886" s="1" t="n">
-        <v>46354.33055555556</v>
+        <v>46354.41388888889</v>
       </c>
       <c r="L886" s="1" t="n">
-        <v>46354.45555555556</v>
+        <v>46354.53888888889</v>
       </c>
       <c r="M886" s="1" t="n">
-        <v>46354.95555555556</v>
+        <v>46355.03888888889</v>
       </c>
     </row>
     <row r="887">
@@ -49112,13 +49112,13 @@
         </is>
       </c>
       <c r="K887" s="1" t="n">
-        <v>46359.97638888889</v>
+        <v>46360.05972222222</v>
       </c>
       <c r="L887" s="1" t="n">
-        <v>46360.03888888889</v>
+        <v>46360.12222222222</v>
       </c>
       <c r="M887" s="1" t="n">
-        <v>46360.28888888889</v>
+        <v>46360.37222222222</v>
       </c>
     </row>
     <row r="888">
@@ -49167,13 +49167,13 @@
         </is>
       </c>
       <c r="K888" s="1" t="n">
-        <v>46361.22638888889</v>
+        <v>46361.30972222222</v>
       </c>
       <c r="L888" s="1" t="n">
-        <v>46361.28888888889</v>
+        <v>46361.37222222222</v>
       </c>
       <c r="M888" s="1" t="n">
-        <v>46361.70555555556</v>
+        <v>46361.78888888889</v>
       </c>
     </row>
     <row r="889">
@@ -49222,13 +49222,13 @@
         </is>
       </c>
       <c r="K889" s="1" t="n">
-        <v>46362.03888888889</v>
+        <v>46362.12222222222</v>
       </c>
       <c r="L889" s="1" t="n">
-        <v>46362.08055555556</v>
+        <v>46362.16388888889</v>
       </c>
       <c r="M889" s="1" t="n">
-        <v>46362.70555555556</v>
+        <v>46362.78888888889</v>
       </c>
     </row>
     <row r="890">
@@ -49277,13 +49277,13 @@
         </is>
       </c>
       <c r="K890" s="1" t="n">
-        <v>46363.78611111111</v>
+        <v>46363.86944444444</v>
       </c>
       <c r="L890" s="1" t="n">
-        <v>46363.95277777778</v>
+        <v>46364.03611111111</v>
       </c>
       <c r="M890" s="1" t="n">
-        <v>46364.95277777778</v>
+        <v>46365.03611111111</v>
       </c>
     </row>
     <row r="891">
@@ -49332,13 +49332,13 @@
         </is>
       </c>
       <c r="K891" s="1" t="n">
-        <v>46369.16111111111</v>
+        <v>46369.24444444444</v>
       </c>
       <c r="L891" s="1" t="n">
-        <v>46369.28611111111</v>
+        <v>46369.36944444444</v>
       </c>
       <c r="M891" s="1" t="n">
-        <v>46369.78611111111</v>
+        <v>46369.86944444444</v>
       </c>
     </row>
     <row r="892">
@@ -49387,13 +49387,13 @@
         </is>
       </c>
       <c r="K892" s="1" t="n">
-        <v>46371.36944444444</v>
+        <v>46371.45277777778</v>
       </c>
       <c r="L892" s="1" t="n">
-        <v>46371.41111111111</v>
+        <v>46371.49444444444</v>
       </c>
       <c r="M892" s="1" t="n">
-        <v>46371.82777777778</v>
+        <v>46371.91111111111</v>
       </c>
     </row>
     <row r="893">
@@ -49442,13 +49442,13 @@
         </is>
       </c>
       <c r="K893" s="1" t="n">
-        <v>46371.99444444444</v>
+        <v>46372.07777777778</v>
       </c>
       <c r="L893" s="1" t="n">
-        <v>46372.11944444444</v>
+        <v>46372.20277777778</v>
       </c>
       <c r="M893" s="1" t="n">
-        <v>46373.11944444444</v>
+        <v>46373.20277777778</v>
       </c>
     </row>
     <row r="894">
@@ -49497,13 +49497,13 @@
         </is>
       </c>
       <c r="K894" s="1" t="n">
-        <v>46373.36944444444</v>
+        <v>46373.45277777778</v>
       </c>
       <c r="L894" s="1" t="n">
-        <v>46373.41111111111</v>
+        <v>46373.49444444444</v>
       </c>
       <c r="M894" s="1" t="n">
-        <v>46373.82777777778</v>
+        <v>46373.91111111111</v>
       </c>
     </row>
     <row r="895">
@@ -49548,13 +49548,13 @@
       </c>
       <c r="J895" t="inlineStr"/>
       <c r="K895" s="1" t="n">
-        <v>46375.32777777778</v>
+        <v>46375.41111111111</v>
       </c>
       <c r="L895" s="1" t="n">
-        <v>46375.45277777778</v>
+        <v>46375.53611111111</v>
       </c>
       <c r="M895" s="1" t="n">
-        <v>46375.95277777778</v>
+        <v>46376.03611111111</v>
       </c>
     </row>
     <row r="896">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -10309,7 +10309,7 @@
         <v>46305.33333333334</v>
       </c>
       <c r="M180" s="1" t="n">
-        <v>46306</v>
+        <v>46305.875</v>
       </c>
     </row>
     <row r="181">
@@ -10358,13 +10358,13 @@
         </is>
       </c>
       <c r="K181" s="1" t="n">
-        <v>46307.08333333334</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>46307.29166666666</v>
+        <v>46307.16666666666</v>
       </c>
       <c r="M181" s="1" t="n">
-        <v>46307.91666666666</v>
+        <v>46307.79166666666</v>
       </c>
     </row>
     <row r="182">
@@ -28193,7 +28193,7 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K506" s="1" t="n">
@@ -28248,7 +28248,7 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="K507" s="1" t="n">
@@ -28258,13 +28258,13 @@
         <v>46304.2875</v>
       </c>
       <c r="M507" s="1" t="n">
-        <v>46306.54166666666</v>
+        <v>46305.54166666666</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>ADHS</t>
+          <t>SIS2</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -28279,47 +28279,47 @@
       </c>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="n">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>TAO04</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
           <t>CNTAO</t>
         </is>
       </c>
-      <c r="J508" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
       <c r="K508" s="1" t="n">
-        <v>46307.20833333334</v>
+        <v>46307</v>
       </c>
       <c r="L508" s="1" t="n">
-        <v>46312.29166666666</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="M508" s="1" t="n">
-        <v>46313.29166666666</v>
+        <v>46311.20833333334</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>SIS2</t>
+          <t>ADHS</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -28334,41 +28334,41 @@
       </c>
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="n">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>TAO04</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
           <t>CNSHA</t>
         </is>
       </c>
-      <c r="J509" t="inlineStr">
-        <is>
-          <t>CNNGB</t>
-        </is>
-      </c>
       <c r="K509" s="1" t="n">
-        <v>46308</v>
+        <v>46307.20833333334</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>46311.20833333334</v>
+        <v>46312.29166666666</v>
       </c>
       <c r="M509" s="1" t="n">
-        <v>46312.20833333334</v>
+        <v>46313.29166666666</v>
       </c>
     </row>
     <row r="510">
@@ -33135,13 +33135,13 @@
         </is>
       </c>
       <c r="K596" s="1" t="n">
-        <v>46304.66666666666</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="L596" s="1" t="n">
-        <v>46304.70833333334</v>
+        <v>46304.75</v>
       </c>
       <c r="M596" s="1" t="n">
-        <v>46305.625</v>
+        <v>46306.20833333334</v>
       </c>
     </row>
     <row r="597">
@@ -33190,13 +33190,13 @@
         </is>
       </c>
       <c r="K597" s="1" t="n">
-        <v>46310.16666666666</v>
+        <v>46310.75</v>
       </c>
       <c r="L597" s="1" t="n">
-        <v>46310.33333333334</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="M597" s="1" t="n">
-        <v>46311.08333333334</v>
+        <v>46311.66666666666</v>
       </c>
     </row>
     <row r="598">
@@ -33231,7 +33231,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>LCH01</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -33245,13 +33245,13 @@
         </is>
       </c>
       <c r="K598" s="1" t="n">
-        <v>46312.91666666666</v>
+        <v>46313.5</v>
       </c>
       <c r="L598" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.54166666666</v>
       </c>
       <c r="M598" s="1" t="n">
-        <v>46313.375</v>
+        <v>46313.95833333334</v>
       </c>
     </row>
     <row r="599">
@@ -33300,13 +33300,13 @@
         </is>
       </c>
       <c r="K599" s="1" t="n">
-        <v>46313.5</v>
+        <v>46314.08333333334</v>
       </c>
       <c r="L599" s="1" t="n">
-        <v>46313.58333333334</v>
+        <v>46314.16666666666</v>
       </c>
       <c r="M599" s="1" t="n">
-        <v>46314.625</v>
+        <v>46315.04166666666</v>
       </c>
     </row>
     <row r="600">
@@ -33341,7 +33341,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>LCH01</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -33355,13 +33355,13 @@
         </is>
       </c>
       <c r="K600" s="1" t="n">
-        <v>46314.79166666666</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="L600" s="1" t="n">
-        <v>46314.83333333334</v>
+        <v>46315.25</v>
       </c>
       <c r="M600" s="1" t="n">
-        <v>46315.33333333334</v>
+        <v>46315.75</v>
       </c>
     </row>
     <row r="601">
@@ -33410,13 +33410,13 @@
         </is>
       </c>
       <c r="K601" s="1" t="n">
-        <v>46316.79166666666</v>
+        <v>46317.20833333334</v>
       </c>
       <c r="L601" s="1" t="n">
-        <v>46316.95833333334</v>
+        <v>46317.375</v>
       </c>
       <c r="M601" s="1" t="n">
-        <v>46318</v>
+        <v>46318.04166666666</v>
       </c>
     </row>
     <row r="602">
@@ -58008,7 +58008,7 @@
         <v>46303.1875</v>
       </c>
       <c r="M1049" s="1" t="n">
-        <v>46304</v>
+        <v>46304.02916666667</v>
       </c>
     </row>
     <row r="1050">
@@ -58057,13 +58057,13 @@
         </is>
       </c>
       <c r="K1050" s="1" t="n">
-        <v>46304.10416666666</v>
+        <v>46304.125</v>
       </c>
       <c r="L1050" s="1" t="n">
-        <v>46304.14583333334</v>
+        <v>46304.175</v>
       </c>
       <c r="M1050" s="1" t="n">
-        <v>46304.70833333334</v>
+        <v>46304.62916666667</v>
       </c>
     </row>
     <row r="1051">
@@ -58112,13 +58112,13 @@
         </is>
       </c>
       <c r="K1051" s="1" t="n">
-        <v>46305.79166666666</v>
+        <v>46305.70833333334</v>
       </c>
       <c r="L1051" s="1" t="n">
-        <v>46305.83333333334</v>
+        <v>46305.91666666666</v>
       </c>
       <c r="M1051" s="1" t="n">
-        <v>46306.5</v>
+        <v>46306.70833333334</v>
       </c>
     </row>
     <row r="1052">
@@ -58167,13 +58167,13 @@
         </is>
       </c>
       <c r="K1052" s="1" t="n">
-        <v>46307.77083333334</v>
+        <v>46307.95833333334</v>
       </c>
       <c r="L1052" s="1" t="n">
-        <v>46307.9375</v>
+        <v>46308.125</v>
       </c>
       <c r="M1052" s="1" t="n">
-        <v>46308.4375</v>
+        <v>46308.625</v>
       </c>
     </row>
     <row r="1053">
@@ -58222,13 +58222,13 @@
         </is>
       </c>
       <c r="K1053" s="1" t="n">
-        <v>46312.60416666666</v>
+        <v>46312.79166666666</v>
       </c>
       <c r="L1053" s="1" t="n">
-        <v>46312.77083333334</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="M1053" s="1" t="n">
-        <v>46313.60416666666</v>
+        <v>46313.79166666666</v>
       </c>
     </row>
     <row r="1054">
@@ -58277,13 +58277,13 @@
         </is>
       </c>
       <c r="K1054" s="1" t="n">
-        <v>46315.27083333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="L1054" s="1" t="n">
-        <v>46315.3125</v>
+        <v>46315.5</v>
       </c>
       <c r="M1054" s="1" t="n">
-        <v>46316.14583333334</v>
+        <v>46316.33333333334</v>
       </c>
     </row>
     <row r="1055">
@@ -58332,13 +58332,13 @@
         </is>
       </c>
       <c r="K1055" s="1" t="n">
-        <v>46319.3125</v>
+        <v>46319.5</v>
       </c>
       <c r="L1055" s="1" t="n">
-        <v>46319.39583333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="M1055" s="1" t="n">
-        <v>46321.0625</v>
+        <v>46321.25</v>
       </c>
     </row>
     <row r="1056">
@@ -58387,13 +58387,13 @@
         </is>
       </c>
       <c r="K1056" s="1" t="n">
-        <v>46323.52083333334</v>
+        <v>46323.70833333334</v>
       </c>
       <c r="L1056" s="1" t="n">
-        <v>46323.6875</v>
+        <v>46323.875</v>
       </c>
       <c r="M1056" s="1" t="n">
-        <v>46324.52083333334</v>
+        <v>46324.70833333334</v>
       </c>
     </row>
     <row r="1057">
@@ -58442,13 +58442,13 @@
         </is>
       </c>
       <c r="K1057" s="1" t="n">
-        <v>46327.0625</v>
+        <v>46327.25</v>
       </c>
       <c r="L1057" s="1" t="n">
-        <v>46327.125</v>
+        <v>46327.3125</v>
       </c>
       <c r="M1057" s="1" t="n">
-        <v>46327.625</v>
+        <v>46327.8125</v>
       </c>
     </row>
     <row r="1058">
@@ -58497,13 +58497,13 @@
         </is>
       </c>
       <c r="K1058" s="1" t="n">
-        <v>46327.85416666666</v>
+        <v>46328.04166666666</v>
       </c>
       <c r="L1058" s="1" t="n">
-        <v>46327.89583333334</v>
+        <v>46328.08333333334</v>
       </c>
       <c r="M1058" s="1" t="n">
-        <v>46328.39583333334</v>
+        <v>46328.58333333334</v>
       </c>
     </row>
     <row r="1059">
@@ -58552,13 +58552,13 @@
         </is>
       </c>
       <c r="K1059" s="1" t="n">
-        <v>46331.47916666666</v>
+        <v>46331.66666666666</v>
       </c>
       <c r="L1059" s="1" t="n">
-        <v>46331.52083333334</v>
+        <v>46331.70833333334</v>
       </c>
       <c r="M1059" s="1" t="n">
-        <v>46332.1875</v>
+        <v>46332.375</v>
       </c>
     </row>
     <row r="1060">
@@ -58607,13 +58607,13 @@
         </is>
       </c>
       <c r="K1060" s="1" t="n">
-        <v>46333.27083333334</v>
+        <v>46333.45833333334</v>
       </c>
       <c r="L1060" s="1" t="n">
-        <v>46333.3125</v>
+        <v>46333.5</v>
       </c>
       <c r="M1060" s="1" t="n">
-        <v>46333.89583333334</v>
+        <v>46334.08333333334</v>
       </c>
     </row>
     <row r="1061">
@@ -58662,13 +58662,13 @@
         </is>
       </c>
       <c r="K1061" s="1" t="n">
-        <v>46334.08333333334</v>
+        <v>46334.27083333334</v>
       </c>
       <c r="L1061" s="1" t="n">
-        <v>46334.14583333334</v>
+        <v>46334.33333333334</v>
       </c>
       <c r="M1061" s="1" t="n">
-        <v>46334.47916666666</v>
+        <v>46334.66666666666</v>
       </c>
     </row>
     <row r="1062">
@@ -58717,13 +58717,13 @@
         </is>
       </c>
       <c r="K1062" s="1" t="n">
-        <v>46335.77083333334</v>
+        <v>46335.95833333334</v>
       </c>
       <c r="L1062" s="1" t="n">
-        <v>46335.9375</v>
+        <v>46336.125</v>
       </c>
       <c r="M1062" s="1" t="n">
-        <v>46336.4375</v>
+        <v>46336.625</v>
       </c>
     </row>
     <row r="1063">
@@ -58772,13 +58772,13 @@
         </is>
       </c>
       <c r="K1063" s="1" t="n">
-        <v>46340.60416666666</v>
+        <v>46340.79166666666</v>
       </c>
       <c r="L1063" s="1" t="n">
-        <v>46340.77083333334</v>
+        <v>46340.95833333334</v>
       </c>
       <c r="M1063" s="1" t="n">
-        <v>46341.60416666666</v>
+        <v>46341.79166666666</v>
       </c>
     </row>
     <row r="1064">
@@ -58827,13 +58827,13 @@
         </is>
       </c>
       <c r="K1064" s="1" t="n">
-        <v>46343.27083333334</v>
+        <v>46343.45833333334</v>
       </c>
       <c r="L1064" s="1" t="n">
-        <v>46343.3125</v>
+        <v>46343.5</v>
       </c>
       <c r="M1064" s="1" t="n">
-        <v>46344.14583333334</v>
+        <v>46344.33333333334</v>
       </c>
     </row>
     <row r="1065">
@@ -58882,13 +58882,13 @@
         </is>
       </c>
       <c r="K1065" s="1" t="n">
-        <v>46347.3125</v>
+        <v>46347.5</v>
       </c>
       <c r="L1065" s="1" t="n">
-        <v>46347.39583333334</v>
+        <v>46347.58333333334</v>
       </c>
       <c r="M1065" s="1" t="n">
-        <v>46349.0625</v>
+        <v>46349.25</v>
       </c>
     </row>
     <row r="1066">
@@ -58937,13 +58937,13 @@
         </is>
       </c>
       <c r="K1066" s="1" t="n">
-        <v>46351.52083333334</v>
+        <v>46351.70833333334</v>
       </c>
       <c r="L1066" s="1" t="n">
-        <v>46351.6875</v>
+        <v>46351.875</v>
       </c>
       <c r="M1066" s="1" t="n">
-        <v>46352.52083333334</v>
+        <v>46352.70833333334</v>
       </c>
     </row>
     <row r="1067">
@@ -58992,13 +58992,13 @@
         </is>
       </c>
       <c r="K1067" s="1" t="n">
-        <v>46355.0625</v>
+        <v>46355.25</v>
       </c>
       <c r="L1067" s="1" t="n">
-        <v>46355.125</v>
+        <v>46355.3125</v>
       </c>
       <c r="M1067" s="1" t="n">
-        <v>46355.625</v>
+        <v>46355.8125</v>
       </c>
     </row>
     <row r="1068">
@@ -59047,13 +59047,13 @@
         </is>
       </c>
       <c r="K1068" s="1" t="n">
-        <v>46355.85416666666</v>
+        <v>46356.04166666666</v>
       </c>
       <c r="L1068" s="1" t="n">
-        <v>46355.89583333334</v>
+        <v>46356.08333333334</v>
       </c>
       <c r="M1068" s="1" t="n">
-        <v>46356.39583333334</v>
+        <v>46356.58333333334</v>
       </c>
     </row>
     <row r="1069">
@@ -59102,13 +59102,13 @@
         </is>
       </c>
       <c r="K1069" s="1" t="n">
-        <v>46359.47916666666</v>
+        <v>46359.66666666666</v>
       </c>
       <c r="L1069" s="1" t="n">
-        <v>46359.52083333334</v>
+        <v>46359.70833333334</v>
       </c>
       <c r="M1069" s="1" t="n">
-        <v>46360.1875</v>
+        <v>46360.375</v>
       </c>
     </row>
     <row r="1070">
@@ -59157,13 +59157,13 @@
         </is>
       </c>
       <c r="K1070" s="1" t="n">
-        <v>46361.27083333334</v>
+        <v>46361.45833333334</v>
       </c>
       <c r="L1070" s="1" t="n">
-        <v>46361.3125</v>
+        <v>46361.5</v>
       </c>
       <c r="M1070" s="1" t="n">
-        <v>46361.89583333334</v>
+        <v>46362.08333333334</v>
       </c>
     </row>
     <row r="1071">
@@ -59212,13 +59212,13 @@
         </is>
       </c>
       <c r="K1071" s="1" t="n">
-        <v>46362.08333333334</v>
+        <v>46362.27083333334</v>
       </c>
       <c r="L1071" s="1" t="n">
-        <v>46362.14583333334</v>
+        <v>46362.33333333334</v>
       </c>
       <c r="M1071" s="1" t="n">
-        <v>46362.47916666666</v>
+        <v>46362.66666666666</v>
       </c>
     </row>
     <row r="1072">
@@ -59267,13 +59267,13 @@
         </is>
       </c>
       <c r="K1072" s="1" t="n">
-        <v>46363.77083333334</v>
+        <v>46363.95833333334</v>
       </c>
       <c r="L1072" s="1" t="n">
-        <v>46363.9375</v>
+        <v>46364.125</v>
       </c>
       <c r="M1072" s="1" t="n">
-        <v>46364.4375</v>
+        <v>46364.625</v>
       </c>
     </row>
     <row r="1073">
@@ -59322,13 +59322,13 @@
         </is>
       </c>
       <c r="K1073" s="1" t="n">
-        <v>46368.60416666666</v>
+        <v>46368.79166666666</v>
       </c>
       <c r="L1073" s="1" t="n">
-        <v>46368.77083333334</v>
+        <v>46368.95833333334</v>
       </c>
       <c r="M1073" s="1" t="n">
-        <v>46369.60416666666</v>
+        <v>46369.79166666666</v>
       </c>
     </row>
     <row r="1074">
@@ -59377,13 +59377,13 @@
         </is>
       </c>
       <c r="K1074" s="1" t="n">
-        <v>46371.27083333334</v>
+        <v>46371.45833333334</v>
       </c>
       <c r="L1074" s="1" t="n">
-        <v>46371.3125</v>
+        <v>46371.5</v>
       </c>
       <c r="M1074" s="1" t="n">
-        <v>46372.14583333334</v>
+        <v>46372.33333333334</v>
       </c>
     </row>
     <row r="1075">
@@ -59432,13 +59432,13 @@
         </is>
       </c>
       <c r="K1075" s="1" t="n">
-        <v>46375.3125</v>
+        <v>46375.5</v>
       </c>
       <c r="L1075" s="1" t="n">
-        <v>46375.39583333334</v>
+        <v>46375.58333333334</v>
       </c>
       <c r="M1075" s="1" t="n">
-        <v>46377.0625</v>
+        <v>46377.25</v>
       </c>
     </row>
     <row r="1076">
@@ -59487,13 +59487,13 @@
         </is>
       </c>
       <c r="K1076" s="1" t="n">
-        <v>46379.52083333334</v>
+        <v>46379.70833333334</v>
       </c>
       <c r="L1076" s="1" t="n">
-        <v>46379.6875</v>
+        <v>46379.875</v>
       </c>
       <c r="M1076" s="1" t="n">
-        <v>46380.52083333334</v>
+        <v>46380.70833333334</v>
       </c>
     </row>
     <row r="1077">
@@ -59542,13 +59542,13 @@
         </is>
       </c>
       <c r="K1077" s="1" t="n">
-        <v>46383.0625</v>
+        <v>46383.25</v>
       </c>
       <c r="L1077" s="1" t="n">
-        <v>46383.125</v>
+        <v>46383.3125</v>
       </c>
       <c r="M1077" s="1" t="n">
-        <v>46383.625</v>
+        <v>46383.8125</v>
       </c>
     </row>
     <row r="1078">
@@ -59593,13 +59593,13 @@
       </c>
       <c r="J1078" t="inlineStr"/>
       <c r="K1078" s="1" t="n">
-        <v>46383.85416666666</v>
+        <v>46384.04166666666</v>
       </c>
       <c r="L1078" s="1" t="n">
-        <v>46383.89583333334</v>
+        <v>46384.08333333334</v>
       </c>
       <c r="M1078" s="1" t="n">
-        <v>46384.39583333334</v>
+        <v>46384.58333333334</v>
       </c>
     </row>
   </sheetData>

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -28203,7 +28203,7 @@
         <v>46304.29166666666</v>
       </c>
       <c r="M506" s="1" t="n">
-        <v>46305.54166666666</v>
+        <v>46305.58333333334</v>
       </c>
     </row>
     <row r="507">
@@ -28362,13 +28362,13 @@
         </is>
       </c>
       <c r="K509" s="1" t="n">
-        <v>46307.20833333334</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>46312.29166666666</v>
+        <v>46312.375</v>
       </c>
       <c r="M509" s="1" t="n">
-        <v>46313.29166666666</v>
+        <v>46313.375</v>
       </c>
     </row>
     <row r="510">
@@ -28417,13 +28417,13 @@
         </is>
       </c>
       <c r="K510" s="1" t="n">
-        <v>46314.29166666666</v>
+        <v>46314.375</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>46316.29166666666</v>
+        <v>46316.375</v>
       </c>
       <c r="M510" s="1" t="n">
-        <v>46316.875</v>
+        <v>46316.95833333334</v>
       </c>
     </row>
     <row r="511">
@@ -28472,13 +28472,13 @@
         </is>
       </c>
       <c r="K511" s="1" t="n">
-        <v>46317.625</v>
+        <v>46317.70833333334</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>46318.70833333334</v>
+        <v>46318.79166666666</v>
       </c>
       <c r="M511" s="1" t="n">
-        <v>46319.375</v>
+        <v>46319.45833333334</v>
       </c>
     </row>
     <row r="512">
@@ -28527,13 +28527,13 @@
         </is>
       </c>
       <c r="K512" s="1" t="n">
-        <v>46321.29166666666</v>
+        <v>46321.375</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>46321.41666666666</v>
+        <v>46321.5</v>
       </c>
       <c r="M512" s="1" t="n">
-        <v>46322.16666666666</v>
+        <v>46322.25</v>
       </c>
     </row>
     <row r="513">
@@ -28582,13 +28582,13 @@
         </is>
       </c>
       <c r="K513" s="1" t="n">
-        <v>46333.91666666666</v>
+        <v>46334</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>46343.91666666666</v>
+        <v>46344</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46350.91666666666</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="514">
@@ -28633,13 +28633,13 @@
       </c>
       <c r="J514" t="inlineStr"/>
       <c r="K514" s="1" t="n">
-        <v>46365</v>
+        <v>46365.08333333334</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>46365.04166666666</v>
+        <v>46365.125</v>
       </c>
       <c r="M514" s="1" t="n">
-        <v>46366.04166666666</v>
+        <v>46366.125</v>
       </c>
     </row>
     <row r="515">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -28203,7 +28203,7 @@
         <v>46304.29166666666</v>
       </c>
       <c r="M506" s="1" t="n">
-        <v>46305.58333333334</v>
+        <v>46305.625</v>
       </c>
     </row>
     <row r="507">
@@ -28362,13 +28362,13 @@
         </is>
       </c>
       <c r="K509" s="1" t="n">
-        <v>46307.29166666666</v>
+        <v>46307.375</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>46312.375</v>
+        <v>46312.45833333334</v>
       </c>
       <c r="M509" s="1" t="n">
-        <v>46313.375</v>
+        <v>46313.45833333334</v>
       </c>
     </row>
     <row r="510">
@@ -28417,13 +28417,13 @@
         </is>
       </c>
       <c r="K510" s="1" t="n">
-        <v>46314.375</v>
+        <v>46314.45833333334</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>46316.375</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="M510" s="1" t="n">
-        <v>46316.95833333334</v>
+        <v>46317.04166666666</v>
       </c>
     </row>
     <row r="511">
@@ -28472,13 +28472,13 @@
         </is>
       </c>
       <c r="K511" s="1" t="n">
-        <v>46317.70833333334</v>
+        <v>46317.79166666666</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>46318.79166666666</v>
+        <v>46318.875</v>
       </c>
       <c r="M511" s="1" t="n">
-        <v>46319.45833333334</v>
+        <v>46319.54166666666</v>
       </c>
     </row>
     <row r="512">
@@ -28527,13 +28527,13 @@
         </is>
       </c>
       <c r="K512" s="1" t="n">
-        <v>46321.375</v>
+        <v>46321.45833333334</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>46321.5</v>
+        <v>46321.58333333334</v>
       </c>
       <c r="M512" s="1" t="n">
-        <v>46322.25</v>
+        <v>46322.33333333334</v>
       </c>
     </row>
     <row r="513">
@@ -28582,13 +28582,13 @@
         </is>
       </c>
       <c r="K513" s="1" t="n">
-        <v>46334</v>
+        <v>46334.08333333334</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>46344</v>
+        <v>46344.08333333334</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46351</v>
+        <v>46351.08333333334</v>
       </c>
     </row>
     <row r="514">
@@ -28633,13 +28633,13 @@
       </c>
       <c r="J514" t="inlineStr"/>
       <c r="K514" s="1" t="n">
-        <v>46365.08333333334</v>
+        <v>46365.16666666666</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>46365.125</v>
+        <v>46365.20833333334</v>
       </c>
       <c r="M514" s="1" t="n">
-        <v>46366.125</v>
+        <v>46366.20833333334</v>
       </c>
     </row>
     <row r="515">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -5533,10 +5533,10 @@
         <v>46305.08333333334</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>46305.95833333334</v>
+        <v>46309.125</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>46306.625</v>
+        <v>46309.79166666666</v>
       </c>
     </row>
     <row r="94">
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46313.625</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>46313.70833333334</v>
+        <v>46316.875</v>
       </c>
       <c r="M94" s="1" t="n">
-        <v>46314.54166666666</v>
+        <v>46317.70833333334</v>
       </c>
     </row>
     <row r="95">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46315.625</v>
+        <v>46318.79166666666</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>46315.70833333334</v>
+        <v>46318.875</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>46316.20833333334</v>
+        <v>46319.375</v>
       </c>
     </row>
     <row r="96">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46320.20833333334</v>
+        <v>46323.375</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>46320.25</v>
+        <v>46323.41666666666</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>46320.91666666666</v>
+        <v>46324.08333333334</v>
       </c>
     </row>
     <row r="97">
@@ -5750,13 +5750,13 @@
         </is>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46327.33333333334</v>
+        <v>46330.5</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>46327.54166666666</v>
+        <v>46330.70833333334</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>46328.20833333334</v>
+        <v>46331.375</v>
       </c>
     </row>
     <row r="98">
@@ -5805,13 +5805,13 @@
         </is>
       </c>
       <c r="K98" s="1" t="n">
-        <v>46331.08333333334</v>
+        <v>46334.25</v>
       </c>
       <c r="L98" s="1" t="n">
-        <v>46331.125</v>
+        <v>46334.29166666666</v>
       </c>
       <c r="M98" s="1" t="n">
-        <v>46332.125</v>
+        <v>46335.29166666666</v>
       </c>
     </row>
     <row r="99">
@@ -5860,13 +5860,13 @@
         </is>
       </c>
       <c r="K99" s="1" t="n">
-        <v>46332.75</v>
+        <v>46335.91666666666</v>
       </c>
       <c r="L99" s="1" t="n">
-        <v>46332.79166666666</v>
+        <v>46335.95833333334</v>
       </c>
       <c r="M99" s="1" t="n">
-        <v>46333.41666666666</v>
+        <v>46336.58333333334</v>
       </c>
     </row>
     <row r="100">
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46334.91666666666</v>
+        <v>46338.08333333334</v>
       </c>
       <c r="L100" s="1" t="n">
-        <v>46335.125</v>
+        <v>46338.29166666666</v>
       </c>
       <c r="M100" s="1" t="n">
-        <v>46335.79166666666</v>
+        <v>46338.95833333334</v>
       </c>
     </row>
     <row r="101">
@@ -5970,13 +5970,13 @@
         </is>
       </c>
       <c r="K101" s="1" t="n">
-        <v>46342.79166666666</v>
+        <v>46345.95833333334</v>
       </c>
       <c r="L101" s="1" t="n">
-        <v>46342.875</v>
+        <v>46346.04166666666</v>
       </c>
       <c r="M101" s="1" t="n">
-        <v>46343.70833333334</v>
+        <v>46346.875</v>
       </c>
     </row>
     <row r="102">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46344.79166666666</v>
+        <v>46347.95833333334</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>46344.875</v>
+        <v>46348.04166666666</v>
       </c>
       <c r="M102" s="1" t="n">
-        <v>46345.375</v>
+        <v>46348.54166666666</v>
       </c>
     </row>
     <row r="103">
@@ -6080,13 +6080,13 @@
         </is>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46349.375</v>
+        <v>46352.54166666666</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>46349.41666666666</v>
+        <v>46352.58333333334</v>
       </c>
       <c r="M103" s="1" t="n">
-        <v>46350.08333333334</v>
+        <v>46353.25</v>
       </c>
     </row>
     <row r="104">
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46356.5</v>
+        <v>46359.66666666666</v>
       </c>
       <c r="L104" s="1" t="n">
-        <v>46356.70833333334</v>
+        <v>46359.875</v>
       </c>
       <c r="M104" s="1" t="n">
-        <v>46357.375</v>
+        <v>46360.54166666666</v>
       </c>
     </row>
     <row r="105">
@@ -6190,13 +6190,13 @@
         </is>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46359.08333333334</v>
+        <v>46362.25</v>
       </c>
       <c r="L105" s="1" t="n">
-        <v>46359.125</v>
+        <v>46362.29166666666</v>
       </c>
       <c r="M105" s="1" t="n">
-        <v>46360.125</v>
+        <v>46363.29166666666</v>
       </c>
     </row>
     <row r="106">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46360.75</v>
+        <v>46363.91666666666</v>
       </c>
       <c r="L106" s="1" t="n">
-        <v>46360.79166666666</v>
+        <v>46363.95833333334</v>
       </c>
       <c r="M106" s="1" t="n">
-        <v>46361.41666666666</v>
+        <v>46364.58333333334</v>
       </c>
     </row>
     <row r="107">
@@ -6300,13 +6300,13 @@
         </is>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46362.91666666666</v>
+        <v>46366.08333333334</v>
       </c>
       <c r="L107" s="1" t="n">
-        <v>46363.125</v>
+        <v>46366.29166666666</v>
       </c>
       <c r="M107" s="1" t="n">
-        <v>46363.79166666666</v>
+        <v>46366.95833333334</v>
       </c>
     </row>
     <row r="108">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46370.79166666666</v>
+        <v>46373.95833333334</v>
       </c>
       <c r="L108" s="1" t="n">
-        <v>46370.875</v>
+        <v>46374.04166666666</v>
       </c>
       <c r="M108" s="1" t="n">
-        <v>46371.70833333334</v>
+        <v>46374.875</v>
       </c>
     </row>
     <row r="109">
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46372.79166666666</v>
+        <v>46375.95833333334</v>
       </c>
       <c r="L109" s="1" t="n">
-        <v>46372.875</v>
+        <v>46376.04166666666</v>
       </c>
       <c r="M109" s="1" t="n">
-        <v>46373.375</v>
+        <v>46376.54166666666</v>
       </c>
     </row>
     <row r="110">
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46377.375</v>
+        <v>46380.54166666666</v>
       </c>
       <c r="L110" s="1" t="n">
-        <v>46377.41666666666</v>
+        <v>46380.58333333334</v>
       </c>
       <c r="M110" s="1" t="n">
-        <v>46378.08333333334</v>
+        <v>46381.25</v>
       </c>
     </row>
     <row r="111">
@@ -6516,13 +6516,13 @@
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" s="1" t="n">
-        <v>46384.5</v>
+        <v>46387.66666666666</v>
       </c>
       <c r="L111" s="1" t="n">
-        <v>46384.70833333334</v>
+        <v>46387.875</v>
       </c>
       <c r="M111" s="1" t="n">
-        <v>46385.375</v>
+        <v>46388.54166666666</v>
       </c>
     </row>
     <row r="112">
@@ -33141,7 +33141,7 @@
         <v>46304.75</v>
       </c>
       <c r="M596" s="1" t="n">
-        <v>46306.20833333334</v>
+        <v>46306.25</v>
       </c>
     </row>
     <row r="597">
@@ -33190,13 +33190,13 @@
         </is>
       </c>
       <c r="K597" s="1" t="n">
-        <v>46310.75</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="L597" s="1" t="n">
-        <v>46310.91666666666</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="M597" s="1" t="n">
-        <v>46311.66666666666</v>
+        <v>46311.70833333334</v>
       </c>
     </row>
     <row r="598">
@@ -33245,13 +33245,13 @@
         </is>
       </c>
       <c r="K598" s="1" t="n">
-        <v>46313.5</v>
+        <v>46313.54166666666</v>
       </c>
       <c r="L598" s="1" t="n">
-        <v>46313.54166666666</v>
+        <v>46313.58333333334</v>
       </c>
       <c r="M598" s="1" t="n">
-        <v>46313.95833333334</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="599">
@@ -33300,13 +33300,13 @@
         </is>
       </c>
       <c r="K599" s="1" t="n">
-        <v>46314.08333333334</v>
+        <v>46314.125</v>
       </c>
       <c r="L599" s="1" t="n">
-        <v>46314.16666666666</v>
+        <v>46314.20833333334</v>
       </c>
       <c r="M599" s="1" t="n">
-        <v>46315.04166666666</v>
+        <v>46315.08333333334</v>
       </c>
     </row>
     <row r="600">
@@ -33355,13 +33355,13 @@
         </is>
       </c>
       <c r="K600" s="1" t="n">
-        <v>46315.20833333334</v>
+        <v>46315.25</v>
       </c>
       <c r="L600" s="1" t="n">
-        <v>46315.25</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="M600" s="1" t="n">
-        <v>46315.75</v>
+        <v>46315.79166666666</v>
       </c>
     </row>
     <row r="601">
@@ -33410,13 +33410,13 @@
         </is>
       </c>
       <c r="K601" s="1" t="n">
-        <v>46317.20833333334</v>
+        <v>46317.25</v>
       </c>
       <c r="L601" s="1" t="n">
-        <v>46317.375</v>
+        <v>46317.41666666666</v>
       </c>
       <c r="M601" s="1" t="n">
-        <v>46318.04166666666</v>
+        <v>46318.08333333334</v>
       </c>
     </row>
     <row r="602">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -6629,16 +6629,16 @@
         <v>46300.54166666666</v>
       </c>
       <c r="L113" s="1" t="n">
-        <v>46304.75</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="M113" s="1" t="n">
-        <v>46306.66666666666</v>
+        <v>46307.33333333334</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PVS2</t>
+          <t>KHS1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="n">
-        <v>9002</v>
+        <v>2612</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>9002S</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6684,16 +6684,16 @@
         <v>46308.41666666666</v>
       </c>
       <c r="L114" s="1" t="n">
-        <v>46308.45833333334</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="M114" s="1" t="n">
-        <v>46309.16666666666</v>
+        <v>46310.625</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KHS1</t>
+          <t>PVS2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
-        <v>2612</v>
+        <v>9002</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>9002S</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6736,13 +6736,13 @@
         </is>
       </c>
       <c r="K115" s="1" t="n">
-        <v>46308.41666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>46309.54166666666</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="M115" s="1" t="n">
-        <v>46310.625</v>
+        <v>46309.91666666666</v>
       </c>
     </row>
     <row r="116">
@@ -10306,10 +10306,10 @@
         <v>46305.29166666666</v>
       </c>
       <c r="L180" s="1" t="n">
-        <v>46305.33333333334</v>
+        <v>46305.34583333333</v>
       </c>
       <c r="M180" s="1" t="n">
-        <v>46305.875</v>
+        <v>46305.94583333333</v>
       </c>
     </row>
     <row r="181">
@@ -10358,13 +10358,13 @@
         </is>
       </c>
       <c r="K181" s="1" t="n">
-        <v>46306.95833333334</v>
+        <v>46307.04166666666</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>46307.16666666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="M181" s="1" t="n">
-        <v>46307.79166666666</v>
+        <v>46309.20833333334</v>
       </c>
     </row>
     <row r="182">
@@ -37970,10 +37970,10 @@
         <v>46306.66666666666</v>
       </c>
       <c r="L684" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46306.97916666666</v>
       </c>
       <c r="M684" s="1" t="n">
-        <v>46307.41666666666</v>
+        <v>46307.54166666666</v>
       </c>
     </row>
     <row r="685">
@@ -38022,13 +38022,13 @@
         </is>
       </c>
       <c r="K685" s="1" t="n">
-        <v>46309.1875</v>
+        <v>46309.375</v>
       </c>
       <c r="L685" s="1" t="n">
-        <v>46309.22916666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="M685" s="1" t="n">
-        <v>46309.58333333334</v>
+        <v>46309.77083333334</v>
       </c>
     </row>
     <row r="686">
@@ -38077,13 +38077,13 @@
         </is>
       </c>
       <c r="K686" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="L686" s="1" t="n">
-        <v>46309.79166666666</v>
+        <v>46309.97916666666</v>
       </c>
       <c r="M686" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.97916666666</v>
       </c>
     </row>
     <row r="687">
@@ -38132,13 +38132,13 @@
         </is>
       </c>
       <c r="K687" s="1" t="n">
-        <v>46311</v>
+        <v>46311.1875</v>
       </c>
       <c r="L687" s="1" t="n">
-        <v>46311.04166666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="M687" s="1" t="n">
-        <v>46311.54166666666</v>
+        <v>46311.72916666666</v>
       </c>
     </row>
     <row r="688">
@@ -38187,13 +38187,13 @@
         </is>
       </c>
       <c r="K688" s="1" t="n">
-        <v>46313.35416666666</v>
+        <v>46313.5</v>
       </c>
       <c r="L688" s="1" t="n">
-        <v>46313.52083333334</v>
+        <v>46313.66666666666</v>
       </c>
       <c r="M688" s="1" t="n">
-        <v>46314.20833333334</v>
+        <v>46314.35416666666</v>
       </c>
     </row>
     <row r="689">
@@ -38242,13 +38242,13 @@
         </is>
       </c>
       <c r="K689" s="1" t="n">
-        <v>46319.79166666666</v>
+        <v>46319.9375</v>
       </c>
       <c r="L689" s="1" t="n">
-        <v>46319.83333333334</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="M689" s="1" t="n">
-        <v>46320.5</v>
+        <v>46320.64583333334</v>
       </c>
     </row>
     <row r="690">
@@ -38297,13 +38297,13 @@
         </is>
       </c>
       <c r="K690" s="1" t="n">
-        <v>46320.66666666666</v>
+        <v>46320.8125</v>
       </c>
       <c r="L690" s="1" t="n">
-        <v>46320.72916666666</v>
+        <v>46320.875</v>
       </c>
       <c r="M690" s="1" t="n">
-        <v>46320.97916666666</v>
+        <v>46321.125</v>
       </c>
     </row>
     <row r="691">
@@ -38352,13 +38352,13 @@
         </is>
       </c>
       <c r="K691" s="1" t="n">
-        <v>46321.875</v>
+        <v>46322.02083333334</v>
       </c>
       <c r="L691" s="1" t="n">
-        <v>46321.9375</v>
+        <v>46322.08333333334</v>
       </c>
       <c r="M691" s="1" t="n">
-        <v>46322.35416666666</v>
+        <v>46322.5</v>
       </c>
     </row>
     <row r="692">
@@ -38407,13 +38407,13 @@
         </is>
       </c>
       <c r="K692" s="1" t="n">
-        <v>46322.625</v>
+        <v>46322.77083333334</v>
       </c>
       <c r="L692" s="1" t="n">
-        <v>46322.64583333334</v>
+        <v>46322.79166666666</v>
       </c>
       <c r="M692" s="1" t="n">
-        <v>46323.25</v>
+        <v>46323.39583333334</v>
       </c>
     </row>
     <row r="693">
@@ -38462,13 +38462,13 @@
         </is>
       </c>
       <c r="K693" s="1" t="n">
-        <v>46328.16666666666</v>
+        <v>46328.3125</v>
       </c>
       <c r="L693" s="1" t="n">
-        <v>46328.33333333334</v>
+        <v>46328.47916666666</v>
       </c>
       <c r="M693" s="1" t="n">
-        <v>46328.91666666666</v>
+        <v>46329.0625</v>
       </c>
     </row>
     <row r="694">
@@ -38517,13 +38517,13 @@
         </is>
       </c>
       <c r="K694" s="1" t="n">
-        <v>46330.5625</v>
+        <v>46330.70833333334</v>
       </c>
       <c r="L694" s="1" t="n">
-        <v>46330.60416666666</v>
+        <v>46330.75</v>
       </c>
       <c r="M694" s="1" t="n">
-        <v>46330.95833333334</v>
+        <v>46331.10416666666</v>
       </c>
     </row>
     <row r="695">
@@ -38572,13 +38572,13 @@
         </is>
       </c>
       <c r="K695" s="1" t="n">
-        <v>46331.08333333334</v>
+        <v>46331.22916666666</v>
       </c>
       <c r="L695" s="1" t="n">
-        <v>46331.16666666666</v>
+        <v>46331.3125</v>
       </c>
       <c r="M695" s="1" t="n">
-        <v>46332.16666666666</v>
+        <v>46332.3125</v>
       </c>
     </row>
     <row r="696">
@@ -38627,13 +38627,13 @@
         </is>
       </c>
       <c r="K696" s="1" t="n">
-        <v>46332.375</v>
+        <v>46332.52083333334</v>
       </c>
       <c r="L696" s="1" t="n">
-        <v>46332.41666666666</v>
+        <v>46332.5625</v>
       </c>
       <c r="M696" s="1" t="n">
-        <v>46332.91666666666</v>
+        <v>46333.0625</v>
       </c>
     </row>
     <row r="697">
@@ -38682,13 +38682,13 @@
         </is>
       </c>
       <c r="K697" s="1" t="n">
-        <v>46334.72916666666</v>
+        <v>46334.875</v>
       </c>
       <c r="L697" s="1" t="n">
-        <v>46334.89583333334</v>
+        <v>46335.04166666666</v>
       </c>
       <c r="M697" s="1" t="n">
-        <v>46335.58333333334</v>
+        <v>46335.72916666666</v>
       </c>
     </row>
     <row r="698">
@@ -38737,13 +38737,13 @@
         </is>
       </c>
       <c r="K698" s="1" t="n">
-        <v>46341.79166666666</v>
+        <v>46341.9375</v>
       </c>
       <c r="L698" s="1" t="n">
-        <v>46341.83333333334</v>
+        <v>46341.97916666666</v>
       </c>
       <c r="M698" s="1" t="n">
-        <v>46342.5</v>
+        <v>46342.64583333334</v>
       </c>
     </row>
     <row r="699">
@@ -38792,13 +38792,13 @@
         </is>
       </c>
       <c r="K699" s="1" t="n">
-        <v>46342.66666666666</v>
+        <v>46342.8125</v>
       </c>
       <c r="L699" s="1" t="n">
-        <v>46342.72916666666</v>
+        <v>46342.875</v>
       </c>
       <c r="M699" s="1" t="n">
-        <v>46342.97916666666</v>
+        <v>46343.125</v>
       </c>
     </row>
     <row r="700">
@@ -38847,13 +38847,13 @@
         </is>
       </c>
       <c r="K700" s="1" t="n">
-        <v>46343.875</v>
+        <v>46344.02083333334</v>
       </c>
       <c r="L700" s="1" t="n">
-        <v>46343.9375</v>
+        <v>46344.08333333334</v>
       </c>
       <c r="M700" s="1" t="n">
-        <v>46344.35416666666</v>
+        <v>46344.5</v>
       </c>
     </row>
     <row r="701">
@@ -38902,13 +38902,13 @@
         </is>
       </c>
       <c r="K701" s="1" t="n">
-        <v>46344.625</v>
+        <v>46344.77083333334</v>
       </c>
       <c r="L701" s="1" t="n">
-        <v>46344.64583333334</v>
+        <v>46344.79166666666</v>
       </c>
       <c r="M701" s="1" t="n">
-        <v>46345.25</v>
+        <v>46345.39583333334</v>
       </c>
     </row>
     <row r="702">
@@ -38957,13 +38957,13 @@
         </is>
       </c>
       <c r="K702" s="1" t="n">
-        <v>46350.16666666666</v>
+        <v>46350.3125</v>
       </c>
       <c r="L702" s="1" t="n">
-        <v>46350.33333333334</v>
+        <v>46350.47916666666</v>
       </c>
       <c r="M702" s="1" t="n">
-        <v>46350.91666666666</v>
+        <v>46351.0625</v>
       </c>
     </row>
     <row r="703">
@@ -39012,13 +39012,13 @@
         </is>
       </c>
       <c r="K703" s="1" t="n">
-        <v>46352.5625</v>
+        <v>46352.70833333334</v>
       </c>
       <c r="L703" s="1" t="n">
-        <v>46352.60416666666</v>
+        <v>46352.75</v>
       </c>
       <c r="M703" s="1" t="n">
-        <v>46352.95833333334</v>
+        <v>46353.10416666666</v>
       </c>
     </row>
     <row r="704">
@@ -39067,13 +39067,13 @@
         </is>
       </c>
       <c r="K704" s="1" t="n">
-        <v>46353.08333333334</v>
+        <v>46353.22916666666</v>
       </c>
       <c r="L704" s="1" t="n">
-        <v>46353.16666666666</v>
+        <v>46353.3125</v>
       </c>
       <c r="M704" s="1" t="n">
-        <v>46354.16666666666</v>
+        <v>46354.3125</v>
       </c>
     </row>
     <row r="705">
@@ -39122,13 +39122,13 @@
         </is>
       </c>
       <c r="K705" s="1" t="n">
-        <v>46354.375</v>
+        <v>46354.52083333334</v>
       </c>
       <c r="L705" s="1" t="n">
-        <v>46354.41666666666</v>
+        <v>46354.5625</v>
       </c>
       <c r="M705" s="1" t="n">
-        <v>46354.91666666666</v>
+        <v>46355.0625</v>
       </c>
     </row>
     <row r="706">
@@ -39177,13 +39177,13 @@
         </is>
       </c>
       <c r="K706" s="1" t="n">
-        <v>46356.72916666666</v>
+        <v>46356.875</v>
       </c>
       <c r="L706" s="1" t="n">
-        <v>46356.89583333334</v>
+        <v>46357.04166666666</v>
       </c>
       <c r="M706" s="1" t="n">
-        <v>46357.58333333334</v>
+        <v>46357.72916666666</v>
       </c>
     </row>
     <row r="707">
@@ -39232,13 +39232,13 @@
         </is>
       </c>
       <c r="K707" s="1" t="n">
-        <v>46362.79166666666</v>
+        <v>46362.9375</v>
       </c>
       <c r="L707" s="1" t="n">
-        <v>46362.83333333334</v>
+        <v>46362.97916666666</v>
       </c>
       <c r="M707" s="1" t="n">
-        <v>46363.5</v>
+        <v>46363.64583333334</v>
       </c>
     </row>
     <row r="708">
@@ -39287,13 +39287,13 @@
         </is>
       </c>
       <c r="K708" s="1" t="n">
-        <v>46363.66666666666</v>
+        <v>46363.8125</v>
       </c>
       <c r="L708" s="1" t="n">
-        <v>46363.72916666666</v>
+        <v>46363.875</v>
       </c>
       <c r="M708" s="1" t="n">
-        <v>46363.97916666666</v>
+        <v>46364.125</v>
       </c>
     </row>
     <row r="709">
@@ -39342,13 +39342,13 @@
         </is>
       </c>
       <c r="K709" s="1" t="n">
-        <v>46364.875</v>
+        <v>46365.02083333334</v>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46364.9375</v>
+        <v>46365.08333333334</v>
       </c>
       <c r="M709" s="1" t="n">
-        <v>46365.35416666666</v>
+        <v>46365.5</v>
       </c>
     </row>
     <row r="710">
@@ -39397,13 +39397,13 @@
         </is>
       </c>
       <c r="K710" s="1" t="n">
-        <v>46365.625</v>
+        <v>46365.77083333334</v>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46365.64583333334</v>
+        <v>46365.79166666666</v>
       </c>
       <c r="M710" s="1" t="n">
-        <v>46366.25</v>
+        <v>46366.39583333334</v>
       </c>
     </row>
     <row r="711">
@@ -39452,13 +39452,13 @@
         </is>
       </c>
       <c r="K711" s="1" t="n">
-        <v>46371.16666666666</v>
+        <v>46371.3125</v>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46371.33333333334</v>
+        <v>46371.47916666666</v>
       </c>
       <c r="M711" s="1" t="n">
-        <v>46371.91666666666</v>
+        <v>46372.0625</v>
       </c>
     </row>
     <row r="712">
@@ -39507,13 +39507,13 @@
         </is>
       </c>
       <c r="K712" s="1" t="n">
-        <v>46373.5625</v>
+        <v>46373.70833333334</v>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46373.60416666666</v>
+        <v>46373.75</v>
       </c>
       <c r="M712" s="1" t="n">
-        <v>46373.95833333334</v>
+        <v>46374.10416666666</v>
       </c>
     </row>
     <row r="713">
@@ -39562,13 +39562,13 @@
         </is>
       </c>
       <c r="K713" s="1" t="n">
-        <v>46374.08333333334</v>
+        <v>46374.22916666666</v>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46374.16666666666</v>
+        <v>46374.3125</v>
       </c>
       <c r="M713" s="1" t="n">
-        <v>46375.16666666666</v>
+        <v>46375.3125</v>
       </c>
     </row>
     <row r="714">
@@ -39617,13 +39617,13 @@
         </is>
       </c>
       <c r="K714" s="1" t="n">
-        <v>46375.375</v>
+        <v>46375.52083333334</v>
       </c>
       <c r="L714" s="1" t="n">
-        <v>46375.41666666666</v>
+        <v>46375.5625</v>
       </c>
       <c r="M714" s="1" t="n">
-        <v>46375.91666666666</v>
+        <v>46376.0625</v>
       </c>
     </row>
     <row r="715">
@@ -39668,13 +39668,13 @@
       </c>
       <c r="J715" t="inlineStr"/>
       <c r="K715" s="1" t="n">
-        <v>46377.72916666666</v>
+        <v>46377.875</v>
       </c>
       <c r="L715" s="1" t="n">
-        <v>46377.89583333334</v>
+        <v>46378.04166666666</v>
       </c>
       <c r="M715" s="1" t="n">
-        <v>46378.58333333334</v>
+        <v>46378.72916666666</v>
       </c>
     </row>
     <row r="716">
@@ -48070,10 +48070,10 @@
         <v>46305.83333333334</v>
       </c>
       <c r="L868" s="1" t="n">
-        <v>46307</v>
+        <v>46306.16666666666</v>
       </c>
       <c r="M868" s="1" t="n">
-        <v>46307.5</v>
+        <v>46306.66666666666</v>
       </c>
     </row>
     <row r="869">
@@ -48122,13 +48122,13 @@
         </is>
       </c>
       <c r="K869" s="1" t="n">
-        <v>46312.52083333334</v>
+        <v>46311.6875</v>
       </c>
       <c r="L869" s="1" t="n">
-        <v>46312.58333333334</v>
+        <v>46311.75</v>
       </c>
       <c r="M869" s="1" t="n">
-        <v>46312.83333333334</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="870">
@@ -48177,13 +48177,13 @@
         </is>
       </c>
       <c r="K870" s="1" t="n">
-        <v>46313.77083333334</v>
+        <v>46312.9375</v>
       </c>
       <c r="L870" s="1" t="n">
-        <v>46313.83333333334</v>
+        <v>46313</v>
       </c>
       <c r="M870" s="1" t="n">
-        <v>46314.25</v>
+        <v>46313.41666666666</v>
       </c>
     </row>
     <row r="871">
@@ -48232,13 +48232,13 @@
         </is>
       </c>
       <c r="K871" s="1" t="n">
-        <v>46314.58333333334</v>
+        <v>46313.75</v>
       </c>
       <c r="L871" s="1" t="n">
-        <v>46314.625</v>
+        <v>46313.79166666666</v>
       </c>
       <c r="M871" s="1" t="n">
-        <v>46315.25</v>
+        <v>46314.41666666666</v>
       </c>
     </row>
     <row r="872">
@@ -48287,13 +48287,13 @@
         </is>
       </c>
       <c r="K872" s="1" t="n">
-        <v>46316.33333333334</v>
+        <v>46315.5</v>
       </c>
       <c r="L872" s="1" t="n">
-        <v>46318.5</v>
+        <v>46317.66666666666</v>
       </c>
       <c r="M872" s="1" t="n">
-        <v>46319.5</v>
+        <v>46318.66666666666</v>
       </c>
     </row>
     <row r="873">
@@ -48342,13 +48342,13 @@
         </is>
       </c>
       <c r="K873" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46322.875</v>
       </c>
       <c r="L873" s="1" t="n">
-        <v>46324.83333333334</v>
+        <v>46324</v>
       </c>
       <c r="M873" s="1" t="n">
-        <v>46325.33333333334</v>
+        <v>46324.5</v>
       </c>
     </row>
     <row r="874">
@@ -48397,13 +48397,13 @@
         </is>
       </c>
       <c r="K874" s="1" t="n">
-        <v>46326.91666666666</v>
+        <v>46326.08333333334</v>
       </c>
       <c r="L874" s="1" t="n">
-        <v>46326.95833333334</v>
+        <v>46326.125</v>
       </c>
       <c r="M874" s="1" t="n">
-        <v>46327.375</v>
+        <v>46326.54166666666</v>
       </c>
     </row>
     <row r="875">
@@ -48452,13 +48452,13 @@
         </is>
       </c>
       <c r="K875" s="1" t="n">
-        <v>46327.54166666666</v>
+        <v>46326.70833333334</v>
       </c>
       <c r="L875" s="1" t="n">
-        <v>46327.66666666666</v>
+        <v>46326.83333333334</v>
       </c>
       <c r="M875" s="1" t="n">
-        <v>46328.66666666666</v>
+        <v>46327.83333333334</v>
       </c>
     </row>
     <row r="876">
@@ -48507,13 +48507,13 @@
         </is>
       </c>
       <c r="K876" s="1" t="n">
-        <v>46328.91666666666</v>
+        <v>46328.08333333334</v>
       </c>
       <c r="L876" s="1" t="n">
-        <v>46328.95833333334</v>
+        <v>46328.125</v>
       </c>
       <c r="M876" s="1" t="n">
-        <v>46329.375</v>
+        <v>46328.54166666666</v>
       </c>
     </row>
     <row r="877">
@@ -48562,13 +48562,13 @@
         </is>
       </c>
       <c r="K877" s="1" t="n">
-        <v>46330.875</v>
+        <v>46330.04166666666</v>
       </c>
       <c r="L877" s="1" t="n">
-        <v>46332</v>
+        <v>46331.16666666666</v>
       </c>
       <c r="M877" s="1" t="n">
-        <v>46332.5</v>
+        <v>46331.66666666666</v>
       </c>
     </row>
     <row r="878">
@@ -48617,13 +48617,13 @@
         </is>
       </c>
       <c r="K878" s="1" t="n">
-        <v>46339.0625</v>
+        <v>46338.22916666666</v>
       </c>
       <c r="L878" s="1" t="n">
-        <v>46339.125</v>
+        <v>46338.29166666666</v>
       </c>
       <c r="M878" s="1" t="n">
-        <v>46339.375</v>
+        <v>46338.54166666666</v>
       </c>
     </row>
     <row r="879">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="K879" s="1" t="n">
-        <v>46340.3125</v>
+        <v>46339.47916666666</v>
       </c>
       <c r="L879" s="1" t="n">
-        <v>46340.375</v>
+        <v>46339.54166666666</v>
       </c>
       <c r="M879" s="1" t="n">
-        <v>46340.79166666666</v>
+        <v>46339.95833333334</v>
       </c>
     </row>
     <row r="880">
@@ -48727,13 +48727,13 @@
         </is>
       </c>
       <c r="K880" s="1" t="n">
-        <v>46341.125</v>
+        <v>46340.29166666666</v>
       </c>
       <c r="L880" s="1" t="n">
-        <v>46341.16666666666</v>
+        <v>46340.33333333334</v>
       </c>
       <c r="M880" s="1" t="n">
-        <v>46341.79166666666</v>
+        <v>46340.95833333334</v>
       </c>
     </row>
     <row r="881">
@@ -48782,13 +48782,13 @@
         </is>
       </c>
       <c r="K881" s="1" t="n">
-        <v>46342.87222222222</v>
+        <v>46342.03888888889</v>
       </c>
       <c r="L881" s="1" t="n">
-        <v>46343.03888888889</v>
+        <v>46342.20555555556</v>
       </c>
       <c r="M881" s="1" t="n">
-        <v>46344.03888888889</v>
+        <v>46343.20555555556</v>
       </c>
     </row>
     <row r="882">
@@ -48837,13 +48837,13 @@
         </is>
       </c>
       <c r="K882" s="1" t="n">
-        <v>46348.24722222222</v>
+        <v>46347.41388888889</v>
       </c>
       <c r="L882" s="1" t="n">
-        <v>46348.37222222222</v>
+        <v>46347.53888888889</v>
       </c>
       <c r="M882" s="1" t="n">
-        <v>46348.87222222222</v>
+        <v>46348.03888888889</v>
       </c>
     </row>
     <row r="883">
@@ -48892,13 +48892,13 @@
         </is>
       </c>
       <c r="K883" s="1" t="n">
-        <v>46350.45555555556</v>
+        <v>46349.62222222222</v>
       </c>
       <c r="L883" s="1" t="n">
-        <v>46350.49722222222</v>
+        <v>46349.66388888889</v>
       </c>
       <c r="M883" s="1" t="n">
-        <v>46350.91388888889</v>
+        <v>46350.08055555556</v>
       </c>
     </row>
     <row r="884">
@@ -48947,13 +48947,13 @@
         </is>
       </c>
       <c r="K884" s="1" t="n">
-        <v>46351.08055555556</v>
+        <v>46350.24722222222</v>
       </c>
       <c r="L884" s="1" t="n">
-        <v>46351.20555555556</v>
+        <v>46350.37222222222</v>
       </c>
       <c r="M884" s="1" t="n">
-        <v>46352.20555555556</v>
+        <v>46351.37222222222</v>
       </c>
     </row>
     <row r="885">
@@ -49002,13 +49002,13 @@
         </is>
       </c>
       <c r="K885" s="1" t="n">
-        <v>46352.45555555556</v>
+        <v>46351.62222222222</v>
       </c>
       <c r="L885" s="1" t="n">
-        <v>46352.49722222222</v>
+        <v>46351.66388888889</v>
       </c>
       <c r="M885" s="1" t="n">
-        <v>46352.91388888889</v>
+        <v>46352.08055555556</v>
       </c>
     </row>
     <row r="886">
@@ -49057,13 +49057,13 @@
         </is>
       </c>
       <c r="K886" s="1" t="n">
-        <v>46354.41388888889</v>
+        <v>46353.58055555556</v>
       </c>
       <c r="L886" s="1" t="n">
-        <v>46354.53888888889</v>
+        <v>46353.70555555556</v>
       </c>
       <c r="M886" s="1" t="n">
-        <v>46355.03888888889</v>
+        <v>46354.20555555556</v>
       </c>
     </row>
     <row r="887">
@@ -49112,13 +49112,13 @@
         </is>
       </c>
       <c r="K887" s="1" t="n">
-        <v>46360.05972222222</v>
+        <v>46359.22638888889</v>
       </c>
       <c r="L887" s="1" t="n">
-        <v>46360.12222222222</v>
+        <v>46359.28888888889</v>
       </c>
       <c r="M887" s="1" t="n">
-        <v>46360.37222222222</v>
+        <v>46359.53888888889</v>
       </c>
     </row>
     <row r="888">
@@ -49167,13 +49167,13 @@
         </is>
       </c>
       <c r="K888" s="1" t="n">
-        <v>46361.30972222222</v>
+        <v>46360.47638888889</v>
       </c>
       <c r="L888" s="1" t="n">
-        <v>46361.37222222222</v>
+        <v>46360.53888888889</v>
       </c>
       <c r="M888" s="1" t="n">
-        <v>46361.78888888889</v>
+        <v>46360.95555555556</v>
       </c>
     </row>
     <row r="889">
@@ -49222,13 +49222,13 @@
         </is>
       </c>
       <c r="K889" s="1" t="n">
-        <v>46362.12222222222</v>
+        <v>46361.28888888889</v>
       </c>
       <c r="L889" s="1" t="n">
-        <v>46362.16388888889</v>
+        <v>46361.33055555556</v>
       </c>
       <c r="M889" s="1" t="n">
-        <v>46362.78888888889</v>
+        <v>46361.95555555556</v>
       </c>
     </row>
     <row r="890">
@@ -49277,13 +49277,13 @@
         </is>
       </c>
       <c r="K890" s="1" t="n">
-        <v>46363.86944444444</v>
+        <v>46363.03611111111</v>
       </c>
       <c r="L890" s="1" t="n">
-        <v>46364.03611111111</v>
+        <v>46363.20277777778</v>
       </c>
       <c r="M890" s="1" t="n">
-        <v>46365.03611111111</v>
+        <v>46364.20277777778</v>
       </c>
     </row>
     <row r="891">
@@ -49332,13 +49332,13 @@
         </is>
       </c>
       <c r="K891" s="1" t="n">
-        <v>46369.24444444444</v>
+        <v>46368.41111111111</v>
       </c>
       <c r="L891" s="1" t="n">
-        <v>46369.36944444444</v>
+        <v>46368.53611111111</v>
       </c>
       <c r="M891" s="1" t="n">
-        <v>46369.86944444444</v>
+        <v>46369.03611111111</v>
       </c>
     </row>
     <row r="892">
@@ -49387,13 +49387,13 @@
         </is>
       </c>
       <c r="K892" s="1" t="n">
-        <v>46371.45277777778</v>
+        <v>46370.61944444444</v>
       </c>
       <c r="L892" s="1" t="n">
-        <v>46371.49444444444</v>
+        <v>46370.66111111111</v>
       </c>
       <c r="M892" s="1" t="n">
-        <v>46371.91111111111</v>
+        <v>46371.07777777778</v>
       </c>
     </row>
     <row r="893">
@@ -49442,13 +49442,13 @@
         </is>
       </c>
       <c r="K893" s="1" t="n">
-        <v>46372.07777777778</v>
+        <v>46371.24444444444</v>
       </c>
       <c r="L893" s="1" t="n">
-        <v>46372.20277777778</v>
+        <v>46371.36944444444</v>
       </c>
       <c r="M893" s="1" t="n">
-        <v>46373.20277777778</v>
+        <v>46372.36944444444</v>
       </c>
     </row>
     <row r="894">
@@ -49497,13 +49497,13 @@
         </is>
       </c>
       <c r="K894" s="1" t="n">
-        <v>46373.45277777778</v>
+        <v>46372.61944444444</v>
       </c>
       <c r="L894" s="1" t="n">
-        <v>46373.49444444444</v>
+        <v>46372.66111111111</v>
       </c>
       <c r="M894" s="1" t="n">
-        <v>46373.91111111111</v>
+        <v>46373.07777777778</v>
       </c>
     </row>
     <row r="895">
@@ -49548,13 +49548,13 @@
       </c>
       <c r="J895" t="inlineStr"/>
       <c r="K895" s="1" t="n">
-        <v>46375.41111111111</v>
+        <v>46374.57777777778</v>
       </c>
       <c r="L895" s="1" t="n">
-        <v>46375.53611111111</v>
+        <v>46374.70277777778</v>
       </c>
       <c r="M895" s="1" t="n">
-        <v>46376.03611111111</v>
+        <v>46375.20277777778</v>
       </c>
     </row>
     <row r="896">
@@ -58115,10 +58115,10 @@
         <v>46305.70833333334</v>
       </c>
       <c r="L1051" s="1" t="n">
-        <v>46305.91666666666</v>
+        <v>46305.99166666667</v>
       </c>
       <c r="M1051" s="1" t="n">
-        <v>46306.70833333334</v>
+        <v>46306.875</v>
       </c>
     </row>
     <row r="1052">
@@ -58167,13 +58167,13 @@
         </is>
       </c>
       <c r="K1052" s="1" t="n">
-        <v>46307.95833333334</v>
+        <v>46308.125</v>
       </c>
       <c r="L1052" s="1" t="n">
-        <v>46308.125</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="M1052" s="1" t="n">
-        <v>46308.625</v>
+        <v>46308.79166666666</v>
       </c>
     </row>
     <row r="1053">
@@ -58222,13 +58222,13 @@
         </is>
       </c>
       <c r="K1053" s="1" t="n">
-        <v>46312.79166666666</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="L1053" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.125</v>
       </c>
       <c r="M1053" s="1" t="n">
-        <v>46313.79166666666</v>
+        <v>46313.95833333334</v>
       </c>
     </row>
     <row r="1054">
@@ -58277,13 +58277,13 @@
         </is>
       </c>
       <c r="K1054" s="1" t="n">
-        <v>46315.45833333334</v>
+        <v>46315.625</v>
       </c>
       <c r="L1054" s="1" t="n">
-        <v>46315.5</v>
+        <v>46315.66666666666</v>
       </c>
       <c r="M1054" s="1" t="n">
-        <v>46316.33333333334</v>
+        <v>46316.5</v>
       </c>
     </row>
     <row r="1055">
@@ -58332,13 +58332,13 @@
         </is>
       </c>
       <c r="K1055" s="1" t="n">
-        <v>46319.5</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="L1055" s="1" t="n">
-        <v>46319.58333333334</v>
+        <v>46319.75</v>
       </c>
       <c r="M1055" s="1" t="n">
-        <v>46321.25</v>
+        <v>46321.41666666666</v>
       </c>
     </row>
     <row r="1056">
@@ -58387,13 +58387,13 @@
         </is>
       </c>
       <c r="K1056" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46323.875</v>
       </c>
       <c r="L1056" s="1" t="n">
-        <v>46323.875</v>
+        <v>46324.04166666666</v>
       </c>
       <c r="M1056" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46324.875</v>
       </c>
     </row>
     <row r="1057">
@@ -58442,13 +58442,13 @@
         </is>
       </c>
       <c r="K1057" s="1" t="n">
-        <v>46327.25</v>
+        <v>46327.41666666666</v>
       </c>
       <c r="L1057" s="1" t="n">
-        <v>46327.3125</v>
+        <v>46327.47916666666</v>
       </c>
       <c r="M1057" s="1" t="n">
-        <v>46327.8125</v>
+        <v>46327.97916666666</v>
       </c>
     </row>
     <row r="1058">
@@ -58497,13 +58497,13 @@
         </is>
       </c>
       <c r="K1058" s="1" t="n">
-        <v>46328.04166666666</v>
+        <v>46328.20833333334</v>
       </c>
       <c r="L1058" s="1" t="n">
-        <v>46328.08333333334</v>
+        <v>46328.25</v>
       </c>
       <c r="M1058" s="1" t="n">
-        <v>46328.58333333334</v>
+        <v>46328.75</v>
       </c>
     </row>
     <row r="1059">
@@ -58552,13 +58552,13 @@
         </is>
       </c>
       <c r="K1059" s="1" t="n">
-        <v>46331.66666666666</v>
+        <v>46331.83333333334</v>
       </c>
       <c r="L1059" s="1" t="n">
-        <v>46331.70833333334</v>
+        <v>46331.875</v>
       </c>
       <c r="M1059" s="1" t="n">
-        <v>46332.375</v>
+        <v>46332.54166666666</v>
       </c>
     </row>
     <row r="1060">
@@ -58607,13 +58607,13 @@
         </is>
       </c>
       <c r="K1060" s="1" t="n">
-        <v>46333.45833333334</v>
+        <v>46333.625</v>
       </c>
       <c r="L1060" s="1" t="n">
-        <v>46333.5</v>
+        <v>46333.66666666666</v>
       </c>
       <c r="M1060" s="1" t="n">
-        <v>46334.08333333334</v>
+        <v>46334.25</v>
       </c>
     </row>
     <row r="1061">
@@ -58662,13 +58662,13 @@
         </is>
       </c>
       <c r="K1061" s="1" t="n">
-        <v>46334.27083333334</v>
+        <v>46334.4375</v>
       </c>
       <c r="L1061" s="1" t="n">
-        <v>46334.33333333334</v>
+        <v>46334.5</v>
       </c>
       <c r="M1061" s="1" t="n">
-        <v>46334.66666666666</v>
+        <v>46334.83333333334</v>
       </c>
     </row>
     <row r="1062">
@@ -58717,13 +58717,13 @@
         </is>
       </c>
       <c r="K1062" s="1" t="n">
-        <v>46335.95833333334</v>
+        <v>46336.125</v>
       </c>
       <c r="L1062" s="1" t="n">
-        <v>46336.125</v>
+        <v>46336.29166666666</v>
       </c>
       <c r="M1062" s="1" t="n">
-        <v>46336.625</v>
+        <v>46336.79166666666</v>
       </c>
     </row>
     <row r="1063">
@@ -58772,13 +58772,13 @@
         </is>
       </c>
       <c r="K1063" s="1" t="n">
-        <v>46340.79166666666</v>
+        <v>46340.95833333334</v>
       </c>
       <c r="L1063" s="1" t="n">
-        <v>46340.95833333334</v>
+        <v>46341.125</v>
       </c>
       <c r="M1063" s="1" t="n">
-        <v>46341.79166666666</v>
+        <v>46341.95833333334</v>
       </c>
     </row>
     <row r="1064">
@@ -58827,13 +58827,13 @@
         </is>
       </c>
       <c r="K1064" s="1" t="n">
-        <v>46343.45833333334</v>
+        <v>46343.625</v>
       </c>
       <c r="L1064" s="1" t="n">
-        <v>46343.5</v>
+        <v>46343.66666666666</v>
       </c>
       <c r="M1064" s="1" t="n">
-        <v>46344.33333333334</v>
+        <v>46344.5</v>
       </c>
     </row>
     <row r="1065">
@@ -58882,13 +58882,13 @@
         </is>
       </c>
       <c r="K1065" s="1" t="n">
-        <v>46347.5</v>
+        <v>46347.66666666666</v>
       </c>
       <c r="L1065" s="1" t="n">
-        <v>46347.58333333334</v>
+        <v>46347.75</v>
       </c>
       <c r="M1065" s="1" t="n">
-        <v>46349.25</v>
+        <v>46349.41666666666</v>
       </c>
     </row>
     <row r="1066">
@@ -58937,13 +58937,13 @@
         </is>
       </c>
       <c r="K1066" s="1" t="n">
-        <v>46351.70833333334</v>
+        <v>46351.875</v>
       </c>
       <c r="L1066" s="1" t="n">
-        <v>46351.875</v>
+        <v>46352.04166666666</v>
       </c>
       <c r="M1066" s="1" t="n">
-        <v>46352.70833333334</v>
+        <v>46352.875</v>
       </c>
     </row>
     <row r="1067">
@@ -58992,13 +58992,13 @@
         </is>
       </c>
       <c r="K1067" s="1" t="n">
-        <v>46355.25</v>
+        <v>46355.41666666666</v>
       </c>
       <c r="L1067" s="1" t="n">
-        <v>46355.3125</v>
+        <v>46355.47916666666</v>
       </c>
       <c r="M1067" s="1" t="n">
-        <v>46355.8125</v>
+        <v>46355.97916666666</v>
       </c>
     </row>
     <row r="1068">
@@ -59047,13 +59047,13 @@
         </is>
       </c>
       <c r="K1068" s="1" t="n">
-        <v>46356.04166666666</v>
+        <v>46356.20833333334</v>
       </c>
       <c r="L1068" s="1" t="n">
-        <v>46356.08333333334</v>
+        <v>46356.25</v>
       </c>
       <c r="M1068" s="1" t="n">
-        <v>46356.58333333334</v>
+        <v>46356.75</v>
       </c>
     </row>
     <row r="1069">
@@ -59102,13 +59102,13 @@
         </is>
       </c>
       <c r="K1069" s="1" t="n">
-        <v>46359.66666666666</v>
+        <v>46359.83333333334</v>
       </c>
       <c r="L1069" s="1" t="n">
-        <v>46359.70833333334</v>
+        <v>46359.875</v>
       </c>
       <c r="M1069" s="1" t="n">
-        <v>46360.375</v>
+        <v>46360.54166666666</v>
       </c>
     </row>
     <row r="1070">
@@ -59157,13 +59157,13 @@
         </is>
       </c>
       <c r="K1070" s="1" t="n">
-        <v>46361.45833333334</v>
+        <v>46361.625</v>
       </c>
       <c r="L1070" s="1" t="n">
-        <v>46361.5</v>
+        <v>46361.66666666666</v>
       </c>
       <c r="M1070" s="1" t="n">
-        <v>46362.08333333334</v>
+        <v>46362.25</v>
       </c>
     </row>
     <row r="1071">
@@ -59212,13 +59212,13 @@
         </is>
       </c>
       <c r="K1071" s="1" t="n">
-        <v>46362.27083333334</v>
+        <v>46362.4375</v>
       </c>
       <c r="L1071" s="1" t="n">
-        <v>46362.33333333334</v>
+        <v>46362.5</v>
       </c>
       <c r="M1071" s="1" t="n">
-        <v>46362.66666666666</v>
+        <v>46362.83333333334</v>
       </c>
     </row>
     <row r="1072">
@@ -59267,13 +59267,13 @@
         </is>
       </c>
       <c r="K1072" s="1" t="n">
-        <v>46363.95833333334</v>
+        <v>46364.125</v>
       </c>
       <c r="L1072" s="1" t="n">
-        <v>46364.125</v>
+        <v>46364.29166666666</v>
       </c>
       <c r="M1072" s="1" t="n">
-        <v>46364.625</v>
+        <v>46364.79166666666</v>
       </c>
     </row>
     <row r="1073">
@@ -59322,13 +59322,13 @@
         </is>
       </c>
       <c r="K1073" s="1" t="n">
-        <v>46368.79166666666</v>
+        <v>46368.95833333334</v>
       </c>
       <c r="L1073" s="1" t="n">
-        <v>46368.95833333334</v>
+        <v>46369.125</v>
       </c>
       <c r="M1073" s="1" t="n">
-        <v>46369.79166666666</v>
+        <v>46369.95833333334</v>
       </c>
     </row>
     <row r="1074">
@@ -59377,13 +59377,13 @@
         </is>
       </c>
       <c r="K1074" s="1" t="n">
-        <v>46371.45833333334</v>
+        <v>46371.625</v>
       </c>
       <c r="L1074" s="1" t="n">
-        <v>46371.5</v>
+        <v>46371.66666666666</v>
       </c>
       <c r="M1074" s="1" t="n">
-        <v>46372.33333333334</v>
+        <v>46372.5</v>
       </c>
     </row>
     <row r="1075">
@@ -59432,13 +59432,13 @@
         </is>
       </c>
       <c r="K1075" s="1" t="n">
-        <v>46375.5</v>
+        <v>46375.66666666666</v>
       </c>
       <c r="L1075" s="1" t="n">
-        <v>46375.58333333334</v>
+        <v>46375.75</v>
       </c>
       <c r="M1075" s="1" t="n">
-        <v>46377.25</v>
+        <v>46377.41666666666</v>
       </c>
     </row>
     <row r="1076">
@@ -59487,13 +59487,13 @@
         </is>
       </c>
       <c r="K1076" s="1" t="n">
-        <v>46379.70833333334</v>
+        <v>46379.875</v>
       </c>
       <c r="L1076" s="1" t="n">
-        <v>46379.875</v>
+        <v>46380.04166666666</v>
       </c>
       <c r="M1076" s="1" t="n">
-        <v>46380.70833333334</v>
+        <v>46380.875</v>
       </c>
     </row>
     <row r="1077">
@@ -59542,13 +59542,13 @@
         </is>
       </c>
       <c r="K1077" s="1" t="n">
-        <v>46383.25</v>
+        <v>46383.41666666666</v>
       </c>
       <c r="L1077" s="1" t="n">
-        <v>46383.3125</v>
+        <v>46383.47916666666</v>
       </c>
       <c r="M1077" s="1" t="n">
-        <v>46383.8125</v>
+        <v>46383.97916666666</v>
       </c>
     </row>
     <row r="1078">
@@ -59593,13 +59593,13 @@
       </c>
       <c r="J1078" t="inlineStr"/>
       <c r="K1078" s="1" t="n">
-        <v>46384.04166666666</v>
+        <v>46384.20833333334</v>
       </c>
       <c r="L1078" s="1" t="n">
-        <v>46384.08333333334</v>
+        <v>46384.25</v>
       </c>
       <c r="M1078" s="1" t="n">
-        <v>46384.58333333334</v>
+        <v>46384.75</v>
       </c>
     </row>
   </sheetData>

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46302.29166666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46304.04166666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>46305.20833333334</v>
+        <v>46305.44791666666</v>
       </c>
     </row>
     <row r="13">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46305.33333333334</v>
+        <v>46306.625</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46305.375</v>
+        <v>46306.66666666666</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>46305.75</v>
+        <v>46307.03125</v>
       </c>
     </row>
     <row r="14">
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46309.25</v>
+        <v>46310.5</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46309.3125</v>
+        <v>46310.5625</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>46309.72916666666</v>
+        <v>46310.97916666666</v>
       </c>
     </row>
     <row r="15">
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46312.5</v>
+        <v>46313.75</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46312.66666666666</v>
+        <v>46313.91666666666</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>46313.375</v>
+        <v>46314.625</v>
       </c>
     </row>
     <row r="16">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46315.29166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46315.33333333334</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>46315.625</v>
+        <v>46316.875</v>
       </c>
     </row>
     <row r="17">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46315.75</v>
+        <v>46317</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46315.875</v>
+        <v>46317.125</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>46317.125</v>
+        <v>46318.375</v>
       </c>
     </row>
     <row r="18">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46317.33333333334</v>
+        <v>46318.58333333334</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46317.375</v>
+        <v>46318.625</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>46317.83333333334</v>
+        <v>46319.08333333334</v>
       </c>
     </row>
     <row r="19">
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46323.29166666666</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46322.10416666666</v>
+        <v>46323.35416666666</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>46322.58333333334</v>
+        <v>46323.83333333334</v>
       </c>
     </row>
     <row r="20">
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46322.66666666666</v>
+        <v>46323.91666666666</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46322.70833333334</v>
+        <v>46323.95833333334</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>46323.08333333334</v>
+        <v>46324.33333333334</v>
       </c>
     </row>
     <row r="21">
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46326.66666666666</v>
+        <v>46327.91666666666</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46326.70833333334</v>
+        <v>46327.95833333334</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>46327.70833333334</v>
+        <v>46328.95833333334</v>
       </c>
     </row>
     <row r="22">
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46327.83333333334</v>
+        <v>46329.08333333334</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>46327.875</v>
+        <v>46329.125</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>46328.25</v>
+        <v>46329.5</v>
       </c>
     </row>
     <row r="23">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46331.08333333334</v>
+        <v>46332.33333333334</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>46331.125</v>
+        <v>46332.375</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>46331.5</v>
+        <v>46332.75</v>
       </c>
     </row>
     <row r="24">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46334.58333333334</v>
+        <v>46335.83333333334</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>46334.75</v>
+        <v>46336</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>46335.29166666666</v>
+        <v>46336.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46337.25</v>
+        <v>46338.5</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>46337.29166666666</v>
+        <v>46338.54166666666</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>46337.54166666666</v>
+        <v>46338.79166666666</v>
       </c>
     </row>
     <row r="26">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46337.70833333334</v>
+        <v>46338.95833333334</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>46337.83333333334</v>
+        <v>46339.08333333334</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>46339.08333333334</v>
+        <v>46340.33333333334</v>
       </c>
     </row>
     <row r="27">
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46339.29166666666</v>
+        <v>46340.54166666666</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>46339.33333333334</v>
+        <v>46340.58333333334</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>46339.79166666666</v>
+        <v>46341.04166666666</v>
       </c>
     </row>
     <row r="28">
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46344</v>
+        <v>46345.25</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>46344.04166666666</v>
+        <v>46345.29166666666</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>46344.5</v>
+        <v>46345.75</v>
       </c>
     </row>
     <row r="29">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46344.625</v>
+        <v>46345.875</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>46344.75</v>
+        <v>46346</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>46345.125</v>
+        <v>46346.375</v>
       </c>
     </row>
     <row r="30">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46348.45833333334</v>
+        <v>46349.70833333334</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>46348.5</v>
+        <v>46349.75</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>46349.5</v>
+        <v>46350.75</v>
       </c>
     </row>
     <row r="31">
@@ -2128,13 +2128,13 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46349.70833333334</v>
+        <v>46350.95833333334</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>46349.75</v>
+        <v>46351</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>46350.08333333334</v>
+        <v>46351.33333333334</v>
       </c>
     </row>
     <row r="32">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46352.91666666666</v>
+        <v>46354.16666666666</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>46352.95833333334</v>
+        <v>46354.20833333334</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>46353.33333333334</v>
+        <v>46354.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46355.79166666666</v>
+        <v>46357.04166666666</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>46355.95833333334</v>
+        <v>46357.20833333334</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>46356.5</v>
+        <v>46357.75</v>
       </c>
     </row>
     <row r="34">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46358.29166666666</v>
+        <v>46359.54166666666</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>46358.33333333334</v>
+        <v>46359.58333333334</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>46358.58333333334</v>
+        <v>46359.83333333334</v>
       </c>
     </row>
     <row r="35">
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46359</v>
+        <v>46360.25</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>46359.125</v>
+        <v>46360.375</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>46360.25</v>
+        <v>46361.5</v>
       </c>
     </row>
     <row r="36">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46360.58333333334</v>
+        <v>46361.83333333334</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>46360.625</v>
+        <v>46361.875</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>46360.95833333334</v>
+        <v>46362.20833333334</v>
       </c>
     </row>
     <row r="37">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46364.83333333334</v>
+        <v>46366.08333333334</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>46364.875</v>
+        <v>46366.125</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>46365.29166666666</v>
+        <v>46366.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46365.54166666666</v>
+        <v>46366.79166666666</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>46365.54166666666</v>
+        <v>46366.79166666666</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>46365.91666666666</v>
+        <v>46367.16666666666</v>
       </c>
     </row>
     <row r="39">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46367.16666666666</v>
+        <v>46368.41666666666</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>46367.16666666666</v>
+        <v>46368.41666666666</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>46367.41666666666</v>
+        <v>46368.66666666666</v>
       </c>
     </row>
     <row r="40">
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46369.75</v>
+        <v>46371</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>46369.79166666666</v>
+        <v>46371.04166666666</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>46370.5</v>
+        <v>46371.75</v>
       </c>
     </row>
     <row r="41">
@@ -2678,13 +2678,13 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46370.70833333334</v>
+        <v>46371.95833333334</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>46370.75</v>
+        <v>46372</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>46371.08333333334</v>
+        <v>46372.33333333334</v>
       </c>
     </row>
     <row r="42">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46373.91666666666</v>
+        <v>46375.16666666666</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>46373.95833333334</v>
+        <v>46375.20833333334</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>46374.33333333334</v>
+        <v>46375.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -2788,13 +2788,13 @@
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46376.79166666666</v>
+        <v>46378.04166666666</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>46376.95833333334</v>
+        <v>46378.20833333334</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>46377.5</v>
+        <v>46378.75</v>
       </c>
     </row>
     <row r="44">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46379.29166666666</v>
+        <v>46380.54166666666</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>46379.33333333334</v>
+        <v>46380.58333333334</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>46379.58333333334</v>
+        <v>46380.83333333334</v>
       </c>
     </row>
     <row r="45">
@@ -2898,13 +2898,13 @@
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46380</v>
+        <v>46381.25</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>46380.125</v>
+        <v>46381.375</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>46381.25</v>
+        <v>46382.5</v>
       </c>
     </row>
     <row r="46">
@@ -2953,13 +2953,13 @@
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46381.58333333334</v>
+        <v>46382.83333333334</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>46381.625</v>
+        <v>46382.875</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>46381.95833333334</v>
+        <v>46383.20833333334</v>
       </c>
     </row>
     <row r="47">
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46385.83333333334</v>
+        <v>46387.08333333334</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>46385.875</v>
+        <v>46387.125</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>46386.29166666666</v>
+        <v>46387.54166666666</v>
       </c>
     </row>
     <row r="48">
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46386.54166666666</v>
+        <v>46387.79166666666</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>46386.54166666666</v>
+        <v>46387.79166666666</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>46386.91666666666</v>
+        <v>46388.16666666666</v>
       </c>
     </row>
     <row r="49">
@@ -3114,13 +3114,13 @@
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" s="1" t="n">
-        <v>46388.16666666666</v>
+        <v>46389.41666666666</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>46388.16666666666</v>
+        <v>46389.41666666666</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>46388.41666666666</v>
+        <v>46389.66666666666</v>
       </c>
     </row>
     <row r="50">
@@ -5481,7 +5481,7 @@
         <v>46303.35</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>46304</v>
+        <v>46303.95833333334</v>
       </c>
     </row>
     <row r="93">
@@ -5530,13 +5530,13 @@
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46305.08333333334</v>
+        <v>46305.125</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>46309.125</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>46309.79166666666</v>
+        <v>46309.83333333334</v>
       </c>
     </row>
     <row r="94">
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46316.79166666666</v>
+        <v>46316.83333333334</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>46316.875</v>
+        <v>46316.91666666666</v>
       </c>
       <c r="M94" s="1" t="n">
-        <v>46317.70833333334</v>
+        <v>46317.75</v>
       </c>
     </row>
     <row r="95">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46318.79166666666</v>
+        <v>46318.83333333334</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>46318.875</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>46319.375</v>
+        <v>46319.41666666666</v>
       </c>
     </row>
     <row r="96">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46323.375</v>
+        <v>46323.41666666666</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>46323.41666666666</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>46324.08333333334</v>
+        <v>46324.125</v>
       </c>
     </row>
     <row r="97">
@@ -5750,13 +5750,13 @@
         </is>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46330.5</v>
+        <v>46330.54166666666</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>46330.70833333334</v>
+        <v>46330.75</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>46331.375</v>
+        <v>46331.41666666666</v>
       </c>
     </row>
     <row r="98">
@@ -5805,13 +5805,13 @@
         </is>
       </c>
       <c r="K98" s="1" t="n">
-        <v>46334.25</v>
+        <v>46334.29166666666</v>
       </c>
       <c r="L98" s="1" t="n">
-        <v>46334.29166666666</v>
+        <v>46334.33333333334</v>
       </c>
       <c r="M98" s="1" t="n">
-        <v>46335.29166666666</v>
+        <v>46335.33333333334</v>
       </c>
     </row>
     <row r="99">
@@ -5860,13 +5860,13 @@
         </is>
       </c>
       <c r="K99" s="1" t="n">
-        <v>46335.91666666666</v>
+        <v>46335.95833333334</v>
       </c>
       <c r="L99" s="1" t="n">
-        <v>46335.95833333334</v>
+        <v>46336</v>
       </c>
       <c r="M99" s="1" t="n">
-        <v>46336.58333333334</v>
+        <v>46336.625</v>
       </c>
     </row>
     <row r="100">
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46338.08333333334</v>
+        <v>46338.125</v>
       </c>
       <c r="L100" s="1" t="n">
-        <v>46338.29166666666</v>
+        <v>46338.33333333334</v>
       </c>
       <c r="M100" s="1" t="n">
-        <v>46338.95833333334</v>
+        <v>46339</v>
       </c>
     </row>
     <row r="101">
@@ -5970,13 +5970,13 @@
         </is>
       </c>
       <c r="K101" s="1" t="n">
-        <v>46345.95833333334</v>
+        <v>46346</v>
       </c>
       <c r="L101" s="1" t="n">
-        <v>46346.04166666666</v>
+        <v>46346.08333333334</v>
       </c>
       <c r="M101" s="1" t="n">
-        <v>46346.875</v>
+        <v>46346.91666666666</v>
       </c>
     </row>
     <row r="102">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46347.95833333334</v>
+        <v>46348</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>46348.04166666666</v>
+        <v>46348.08333333334</v>
       </c>
       <c r="M102" s="1" t="n">
-        <v>46348.54166666666</v>
+        <v>46348.58333333334</v>
       </c>
     </row>
     <row r="103">
@@ -6080,13 +6080,13 @@
         </is>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46352.54166666666</v>
+        <v>46352.58333333334</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>46352.58333333334</v>
+        <v>46352.625</v>
       </c>
       <c r="M103" s="1" t="n">
-        <v>46353.25</v>
+        <v>46353.29166666666</v>
       </c>
     </row>
     <row r="104">
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46359.66666666666</v>
+        <v>46359.70833333334</v>
       </c>
       <c r="L104" s="1" t="n">
-        <v>46359.875</v>
+        <v>46359.91666666666</v>
       </c>
       <c r="M104" s="1" t="n">
-        <v>46360.54166666666</v>
+        <v>46360.58333333334</v>
       </c>
     </row>
     <row r="105">
@@ -6190,13 +6190,13 @@
         </is>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46362.25</v>
+        <v>46362.29166666666</v>
       </c>
       <c r="L105" s="1" t="n">
-        <v>46362.29166666666</v>
+        <v>46362.33333333334</v>
       </c>
       <c r="M105" s="1" t="n">
-        <v>46363.29166666666</v>
+        <v>46363.33333333334</v>
       </c>
     </row>
     <row r="106">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46363.91666666666</v>
+        <v>46363.95833333334</v>
       </c>
       <c r="L106" s="1" t="n">
-        <v>46363.95833333334</v>
+        <v>46364</v>
       </c>
       <c r="M106" s="1" t="n">
-        <v>46364.58333333334</v>
+        <v>46364.625</v>
       </c>
     </row>
     <row r="107">
@@ -6300,13 +6300,13 @@
         </is>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46366.08333333334</v>
+        <v>46366.125</v>
       </c>
       <c r="L107" s="1" t="n">
-        <v>46366.29166666666</v>
+        <v>46366.33333333334</v>
       </c>
       <c r="M107" s="1" t="n">
-        <v>46366.95833333334</v>
+        <v>46367</v>
       </c>
     </row>
     <row r="108">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46373.95833333334</v>
+        <v>46374</v>
       </c>
       <c r="L108" s="1" t="n">
-        <v>46374.04166666666</v>
+        <v>46374.08333333334</v>
       </c>
       <c r="M108" s="1" t="n">
-        <v>46374.875</v>
+        <v>46374.91666666666</v>
       </c>
     </row>
     <row r="109">
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46375.95833333334</v>
+        <v>46376</v>
       </c>
       <c r="L109" s="1" t="n">
-        <v>46376.04166666666</v>
+        <v>46376.08333333334</v>
       </c>
       <c r="M109" s="1" t="n">
-        <v>46376.54166666666</v>
+        <v>46376.58333333334</v>
       </c>
     </row>
     <row r="110">
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46380.54166666666</v>
+        <v>46380.58333333334</v>
       </c>
       <c r="L110" s="1" t="n">
-        <v>46380.58333333334</v>
+        <v>46380.625</v>
       </c>
       <c r="M110" s="1" t="n">
-        <v>46381.25</v>
+        <v>46381.29166666666</v>
       </c>
     </row>
     <row r="111">
@@ -6516,13 +6516,13 @@
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" s="1" t="n">
-        <v>46387.66666666666</v>
+        <v>46387.70833333334</v>
       </c>
       <c r="L111" s="1" t="n">
-        <v>46387.875</v>
+        <v>46387.91666666666</v>
       </c>
       <c r="M111" s="1" t="n">
-        <v>46388.54166666666</v>
+        <v>46388.58333333334</v>
       </c>
     </row>
     <row r="112">
@@ -10361,10 +10361,10 @@
         <v>46307.04166666666</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="M181" s="1" t="n">
-        <v>46309.20833333334</v>
+        <v>46309.04166666666</v>
       </c>
     </row>
     <row r="182">
@@ -11952,10 +11952,10 @@
         <v>46307.375</v>
       </c>
       <c r="L210" s="1" t="n">
-        <v>46307.41666666666</v>
+        <v>46307.45833333334</v>
       </c>
       <c r="M210" s="1" t="n">
-        <v>46308.5</v>
+        <v>46308.54166666666</v>
       </c>
     </row>
     <row r="211">
@@ -12004,13 +12004,13 @@
         </is>
       </c>
       <c r="K211" s="1" t="n">
-        <v>46308.625</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="L211" s="1" t="n">
-        <v>46308.66666666666</v>
+        <v>46308.75</v>
       </c>
       <c r="M211" s="1" t="n">
-        <v>46308.91666666666</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="212">
@@ -12059,13 +12059,13 @@
         </is>
       </c>
       <c r="K212" s="1" t="n">
-        <v>46309.29166666666</v>
+        <v>46309.375</v>
       </c>
       <c r="L212" s="1" t="n">
-        <v>46309.35416666666</v>
+        <v>46309.4375</v>
       </c>
       <c r="M212" s="1" t="n">
-        <v>46309.6875</v>
+        <v>46309.77083333334</v>
       </c>
     </row>
     <row r="213">
@@ -12114,13 +12114,13 @@
         </is>
       </c>
       <c r="K213" s="1" t="n">
-        <v>46314.91666666666</v>
+        <v>46315</v>
       </c>
       <c r="L213" s="1" t="n">
-        <v>46315.08333333334</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="M213" s="1" t="n">
-        <v>46315.70833333334</v>
+        <v>46315.79166666666</v>
       </c>
     </row>
     <row r="214">
@@ -12169,13 +12169,13 @@
         </is>
       </c>
       <c r="K214" s="1" t="n">
-        <v>46317.45833333334</v>
+        <v>46317.54166666666</v>
       </c>
       <c r="L214" s="1" t="n">
-        <v>46317.5</v>
+        <v>46317.58333333334</v>
       </c>
       <c r="M214" s="1" t="n">
-        <v>46317.75</v>
+        <v>46317.83333333334</v>
       </c>
     </row>
     <row r="215">
@@ -12224,13 +12224,13 @@
         </is>
       </c>
       <c r="K215" s="1" t="n">
-        <v>46317.875</v>
+        <v>46317.95833333334</v>
       </c>
       <c r="L215" s="1" t="n">
-        <v>46318</v>
+        <v>46318.08333333334</v>
       </c>
       <c r="M215" s="1" t="n">
-        <v>46319.5</v>
+        <v>46319.58333333334</v>
       </c>
     </row>
     <row r="216">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="K216" s="1" t="n">
-        <v>46319.70833333334</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="L216" s="1" t="n">
-        <v>46319.75</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="M216" s="1" t="n">
-        <v>46320.16666666666</v>
+        <v>46320.25</v>
       </c>
     </row>
     <row r="217">
@@ -12334,13 +12334,13 @@
         </is>
       </c>
       <c r="K217" s="1" t="n">
-        <v>46321.79166666666</v>
+        <v>46321.875</v>
       </c>
       <c r="L217" s="1" t="n">
-        <v>46321.95833333334</v>
+        <v>46322.04166666666</v>
       </c>
       <c r="M217" s="1" t="n">
-        <v>46322.5</v>
+        <v>46322.58333333334</v>
       </c>
     </row>
     <row r="218">
@@ -14203,10 +14203,10 @@
         <v>46305.95833333334</v>
       </c>
       <c r="L251" s="1" t="n">
-        <v>46306.02083333334</v>
+        <v>46306.47916666666</v>
       </c>
       <c r="M251" s="1" t="n">
-        <v>46306.52083333334</v>
+        <v>46307.14583333334</v>
       </c>
     </row>
     <row r="252">
@@ -14255,13 +14255,13 @@
         </is>
       </c>
       <c r="K252" s="1" t="n">
-        <v>46307.5</v>
+        <v>46308.125</v>
       </c>
       <c r="L252" s="1" t="n">
-        <v>46307.66666666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="M252" s="1" t="n">
-        <v>46308.45833333334</v>
+        <v>46309.08333333334</v>
       </c>
     </row>
     <row r="253">
@@ -14310,13 +14310,13 @@
         </is>
       </c>
       <c r="K253" s="1" t="n">
-        <v>46314.29166666666</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="L253" s="1" t="n">
-        <v>46314.33333333334</v>
+        <v>46314.95833333334</v>
       </c>
       <c r="M253" s="1" t="n">
-        <v>46314.625</v>
+        <v>46315.25</v>
       </c>
     </row>
     <row r="254">
@@ -14365,13 +14365,13 @@
         </is>
       </c>
       <c r="K254" s="1" t="n">
-        <v>46314.75</v>
+        <v>46315.375</v>
       </c>
       <c r="L254" s="1" t="n">
-        <v>46314.875</v>
+        <v>46315.5</v>
       </c>
       <c r="M254" s="1" t="n">
-        <v>46316.25</v>
+        <v>46316.875</v>
       </c>
     </row>
     <row r="255">
@@ -14420,13 +14420,13 @@
         </is>
       </c>
       <c r="K255" s="1" t="n">
-        <v>46316.45833333334</v>
+        <v>46317.08333333334</v>
       </c>
       <c r="L255" s="1" t="n">
-        <v>46316.5</v>
+        <v>46317.125</v>
       </c>
       <c r="M255" s="1" t="n">
-        <v>46316.95833333334</v>
+        <v>46317.58333333334</v>
       </c>
     </row>
     <row r="256">
@@ -14475,13 +14475,13 @@
         </is>
       </c>
       <c r="K256" s="1" t="n">
-        <v>46320.79166666666</v>
+        <v>46321.41666666666</v>
       </c>
       <c r="L256" s="1" t="n">
-        <v>46320.79166666666</v>
+        <v>46321.41666666666</v>
       </c>
       <c r="M256" s="1" t="n">
-        <v>46321.25</v>
+        <v>46321.875</v>
       </c>
     </row>
     <row r="257">
@@ -14530,13 +14530,13 @@
         </is>
       </c>
       <c r="K257" s="1" t="n">
-        <v>46322.25</v>
+        <v>46322.875</v>
       </c>
       <c r="L257" s="1" t="n">
-        <v>46322.25</v>
+        <v>46322.875</v>
       </c>
       <c r="M257" s="1" t="n">
-        <v>46322.75</v>
+        <v>46323.375</v>
       </c>
     </row>
     <row r="258">
@@ -14585,13 +14585,13 @@
         </is>
       </c>
       <c r="K258" s="1" t="n">
-        <v>46325.20833333334</v>
+        <v>46325.83333333334</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>46325.25</v>
+        <v>46325.875</v>
       </c>
       <c r="M258" s="1" t="n">
-        <v>46325.875</v>
+        <v>46326.5</v>
       </c>
     </row>
     <row r="259">
@@ -14640,13 +14640,13 @@
         </is>
       </c>
       <c r="K259" s="1" t="n">
-        <v>46326.875</v>
+        <v>46327.5</v>
       </c>
       <c r="L259" s="1" t="n">
-        <v>46326.91666666666</v>
+        <v>46327.54166666666</v>
       </c>
       <c r="M259" s="1" t="n">
-        <v>46327.41666666666</v>
+        <v>46328.04166666666</v>
       </c>
     </row>
     <row r="260">
@@ -14695,13 +14695,13 @@
         </is>
       </c>
       <c r="K260" s="1" t="n">
-        <v>46328.5</v>
+        <v>46329.125</v>
       </c>
       <c r="L260" s="1" t="n">
-        <v>46328.66666666666</v>
+        <v>46329.29166666666</v>
       </c>
       <c r="M260" s="1" t="n">
-        <v>46329.45833333334</v>
+        <v>46330.08333333334</v>
       </c>
     </row>
     <row r="261">
@@ -14750,13 +14750,13 @@
         </is>
       </c>
       <c r="K261" s="1" t="n">
-        <v>46335.20833333334</v>
+        <v>46335.83333333334</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>46335.25</v>
+        <v>46335.875</v>
       </c>
       <c r="M261" s="1" t="n">
-        <v>46335.54166666666</v>
+        <v>46336.16666666666</v>
       </c>
     </row>
     <row r="262">
@@ -14805,13 +14805,13 @@
         </is>
       </c>
       <c r="K262" s="1" t="n">
-        <v>46335.83333333334</v>
+        <v>46336.45833333334</v>
       </c>
       <c r="L262" s="1" t="n">
-        <v>46335.83333333334</v>
+        <v>46336.45833333334</v>
       </c>
       <c r="M262" s="1" t="n">
-        <v>46337.20833333334</v>
+        <v>46337.83333333334</v>
       </c>
     </row>
     <row r="263">
@@ -14860,13 +14860,13 @@
         </is>
       </c>
       <c r="K263" s="1" t="n">
-        <v>46337.45833333334</v>
+        <v>46338.08333333334</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>46337.5</v>
+        <v>46338.125</v>
       </c>
       <c r="M263" s="1" t="n">
-        <v>46337.95833333334</v>
+        <v>46338.58333333334</v>
       </c>
     </row>
     <row r="264">
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="K264" s="1" t="n">
-        <v>46341.79166666666</v>
+        <v>46342.41666666666</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>46341.79166666666</v>
+        <v>46342.41666666666</v>
       </c>
       <c r="M264" s="1" t="n">
-        <v>46342.25</v>
+        <v>46342.875</v>
       </c>
     </row>
     <row r="265">
@@ -14970,13 +14970,13 @@
         </is>
       </c>
       <c r="K265" s="1" t="n">
-        <v>46343.25</v>
+        <v>46343.875</v>
       </c>
       <c r="L265" s="1" t="n">
-        <v>46343.25</v>
+        <v>46343.875</v>
       </c>
       <c r="M265" s="1" t="n">
-        <v>46343.75</v>
+        <v>46344.375</v>
       </c>
     </row>
     <row r="266">
@@ -15025,13 +15025,13 @@
         </is>
       </c>
       <c r="K266" s="1" t="n">
-        <v>46346.20833333334</v>
+        <v>46346.83333333334</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>46346.25</v>
+        <v>46346.875</v>
       </c>
       <c r="M266" s="1" t="n">
-        <v>46346.875</v>
+        <v>46347.5</v>
       </c>
     </row>
     <row r="267">
@@ -15080,13 +15080,13 @@
         </is>
       </c>
       <c r="K267" s="1" t="n">
-        <v>46347.875</v>
+        <v>46348.5</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>46347.91666666666</v>
+        <v>46348.54166666666</v>
       </c>
       <c r="M267" s="1" t="n">
-        <v>46348.41666666666</v>
+        <v>46349.04166666666</v>
       </c>
     </row>
     <row r="268">
@@ -15135,13 +15135,13 @@
         </is>
       </c>
       <c r="K268" s="1" t="n">
-        <v>46349.5</v>
+        <v>46350.125</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>46349.66666666666</v>
+        <v>46350.29166666666</v>
       </c>
       <c r="M268" s="1" t="n">
-        <v>46350.45833333334</v>
+        <v>46351.08333333334</v>
       </c>
     </row>
     <row r="269">
@@ -15190,13 +15190,13 @@
         </is>
       </c>
       <c r="K269" s="1" t="n">
-        <v>46356.20833333334</v>
+        <v>46356.83333333334</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>46356.25</v>
+        <v>46356.875</v>
       </c>
       <c r="M269" s="1" t="n">
-        <v>46356.54166666666</v>
+        <v>46357.16666666666</v>
       </c>
     </row>
     <row r="270">
@@ -15245,13 +15245,13 @@
         </is>
       </c>
       <c r="K270" s="1" t="n">
-        <v>46356.83333333334</v>
+        <v>46357.45833333334</v>
       </c>
       <c r="L270" s="1" t="n">
-        <v>46356.83333333334</v>
+        <v>46357.45833333334</v>
       </c>
       <c r="M270" s="1" t="n">
-        <v>46358.20833333334</v>
+        <v>46358.83333333334</v>
       </c>
     </row>
     <row r="271">
@@ -15300,13 +15300,13 @@
         </is>
       </c>
       <c r="K271" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46359.08333333334</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>46358.5</v>
+        <v>46359.125</v>
       </c>
       <c r="M271" s="1" t="n">
-        <v>46358.95833333334</v>
+        <v>46359.58333333334</v>
       </c>
     </row>
     <row r="272">
@@ -15355,13 +15355,13 @@
         </is>
       </c>
       <c r="K272" s="1" t="n">
-        <v>46362.79166666666</v>
+        <v>46363.41666666666</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>46362.79166666666</v>
+        <v>46363.41666666666</v>
       </c>
       <c r="M272" s="1" t="n">
-        <v>46363.25</v>
+        <v>46363.875</v>
       </c>
     </row>
     <row r="273">
@@ -15410,13 +15410,13 @@
         </is>
       </c>
       <c r="K273" s="1" t="n">
-        <v>46364.25</v>
+        <v>46364.875</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>46364.25</v>
+        <v>46364.875</v>
       </c>
       <c r="M273" s="1" t="n">
-        <v>46364.75</v>
+        <v>46365.375</v>
       </c>
     </row>
     <row r="274">
@@ -15465,13 +15465,13 @@
         </is>
       </c>
       <c r="K274" s="1" t="n">
-        <v>46367.20833333334</v>
+        <v>46367.83333333334</v>
       </c>
       <c r="L274" s="1" t="n">
-        <v>46367.25</v>
+        <v>46367.875</v>
       </c>
       <c r="M274" s="1" t="n">
-        <v>46367.875</v>
+        <v>46368.5</v>
       </c>
     </row>
     <row r="275">
@@ -15520,13 +15520,13 @@
         </is>
       </c>
       <c r="K275" s="1" t="n">
-        <v>46368.875</v>
+        <v>46369.5</v>
       </c>
       <c r="L275" s="1" t="n">
-        <v>46368.91666666666</v>
+        <v>46369.54166666666</v>
       </c>
       <c r="M275" s="1" t="n">
-        <v>46369.41666666666</v>
+        <v>46370.04166666666</v>
       </c>
     </row>
     <row r="276">
@@ -15575,13 +15575,13 @@
         </is>
       </c>
       <c r="K276" s="1" t="n">
-        <v>46370.5</v>
+        <v>46371.125</v>
       </c>
       <c r="L276" s="1" t="n">
-        <v>46370.66666666666</v>
+        <v>46371.29166666666</v>
       </c>
       <c r="M276" s="1" t="n">
-        <v>46371.45833333334</v>
+        <v>46372.08333333334</v>
       </c>
     </row>
     <row r="277">
@@ -15630,13 +15630,13 @@
         </is>
       </c>
       <c r="K277" s="1" t="n">
-        <v>46377.20833333334</v>
+        <v>46377.83333333334</v>
       </c>
       <c r="L277" s="1" t="n">
-        <v>46377.25</v>
+        <v>46377.875</v>
       </c>
       <c r="M277" s="1" t="n">
-        <v>46377.54166666666</v>
+        <v>46378.16666666666</v>
       </c>
     </row>
     <row r="278">
@@ -15685,13 +15685,13 @@
         </is>
       </c>
       <c r="K278" s="1" t="n">
-        <v>46377.83333333334</v>
+        <v>46378.45833333334</v>
       </c>
       <c r="L278" s="1" t="n">
-        <v>46377.83333333334</v>
+        <v>46378.45833333334</v>
       </c>
       <c r="M278" s="1" t="n">
-        <v>46379.20833333334</v>
+        <v>46379.83333333334</v>
       </c>
     </row>
     <row r="279">
@@ -15740,13 +15740,13 @@
         </is>
       </c>
       <c r="K279" s="1" t="n">
-        <v>46379.45833333334</v>
+        <v>46380.08333333334</v>
       </c>
       <c r="L279" s="1" t="n">
-        <v>46379.5</v>
+        <v>46380.125</v>
       </c>
       <c r="M279" s="1" t="n">
-        <v>46379.95833333334</v>
+        <v>46380.58333333334</v>
       </c>
     </row>
     <row r="280">
@@ -15795,13 +15795,13 @@
         </is>
       </c>
       <c r="K280" s="1" t="n">
-        <v>46383.79166666666</v>
+        <v>46384.41666666666</v>
       </c>
       <c r="L280" s="1" t="n">
-        <v>46383.79166666666</v>
+        <v>46384.41666666666</v>
       </c>
       <c r="M280" s="1" t="n">
-        <v>46384.25</v>
+        <v>46384.875</v>
       </c>
     </row>
     <row r="281">
@@ -15846,13 +15846,13 @@
       </c>
       <c r="J281" t="inlineStr"/>
       <c r="K281" s="1" t="n">
-        <v>46385.25</v>
+        <v>46385.875</v>
       </c>
       <c r="L281" s="1" t="n">
-        <v>46385.25</v>
+        <v>46385.875</v>
       </c>
       <c r="M281" s="1" t="n">
-        <v>46385.75</v>
+        <v>46386.375</v>
       </c>
     </row>
     <row r="282">
@@ -16457,7 +16457,7 @@
         <v>46302.5625</v>
       </c>
       <c r="M292" s="1" t="n">
-        <v>46303.95833333334</v>
+        <v>46304.07847222222</v>
       </c>
     </row>
     <row r="293">
@@ -16506,13 +16506,13 @@
         </is>
       </c>
       <c r="K293" s="1" t="n">
-        <v>46304.08333333334</v>
+        <v>46304.22222222222</v>
       </c>
       <c r="L293" s="1" t="n">
-        <v>46304.125</v>
+        <v>46304.25694444445</v>
       </c>
       <c r="M293" s="1" t="n">
-        <v>46304.41666666666</v>
+        <v>46305.27083333334</v>
       </c>
     </row>
     <row r="294">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="K294" s="1" t="n">
-        <v>46309.41666666666</v>
+        <v>46310.25</v>
       </c>
       <c r="L294" s="1" t="n">
-        <v>46309.58333333334</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="M294" s="1" t="n">
-        <v>46310.29166666666</v>
+        <v>46310.95833333334</v>
       </c>
     </row>
     <row r="295">
@@ -16616,13 +16616,13 @@
         </is>
       </c>
       <c r="K295" s="1" t="n">
-        <v>46311.95833333334</v>
+        <v>46312.625</v>
       </c>
       <c r="L295" s="1" t="n">
-        <v>46312</v>
+        <v>46312.66666666666</v>
       </c>
       <c r="M295" s="1" t="n">
-        <v>46312.29166666666</v>
+        <v>46312.95833333334</v>
       </c>
     </row>
     <row r="296">
@@ -16671,13 +16671,13 @@
         </is>
       </c>
       <c r="K296" s="1" t="n">
-        <v>46312.41666666666</v>
+        <v>46313.08333333334</v>
       </c>
       <c r="L296" s="1" t="n">
-        <v>46312.54166666666</v>
+        <v>46313.20833333334</v>
       </c>
       <c r="M296" s="1" t="n">
-        <v>46313.79166666666</v>
+        <v>46314.45833333334</v>
       </c>
     </row>
     <row r="297">
@@ -16726,13 +16726,13 @@
         </is>
       </c>
       <c r="K297" s="1" t="n">
-        <v>46314</v>
+        <v>46314.66666666666</v>
       </c>
       <c r="L297" s="1" t="n">
-        <v>46314.04166666666</v>
+        <v>46314.70833333334</v>
       </c>
       <c r="M297" s="1" t="n">
-        <v>46314.5</v>
+        <v>46315.16666666666</v>
       </c>
     </row>
     <row r="298">
@@ -16781,13 +16781,13 @@
         </is>
       </c>
       <c r="K298" s="1" t="n">
-        <v>46318.29166666666</v>
+        <v>46318.95833333334</v>
       </c>
       <c r="L298" s="1" t="n">
-        <v>46318.35416666666</v>
+        <v>46319.02083333334</v>
       </c>
       <c r="M298" s="1" t="n">
-        <v>46318.8125</v>
+        <v>46319.47916666666</v>
       </c>
     </row>
     <row r="299">
@@ -16836,13 +16836,13 @@
         </is>
       </c>
       <c r="K299" s="1" t="n">
-        <v>46320.08333333334</v>
+        <v>46320.75</v>
       </c>
       <c r="L299" s="1" t="n">
-        <v>46320.125</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="M299" s="1" t="n">
-        <v>46320.625</v>
+        <v>46321.29166666666</v>
       </c>
     </row>
     <row r="300">
@@ -16891,13 +16891,13 @@
         </is>
       </c>
       <c r="K300" s="1" t="n">
-        <v>46322.5</v>
+        <v>46323.16666666666</v>
       </c>
       <c r="L300" s="1" t="n">
-        <v>46322.54166666666</v>
+        <v>46323.20833333334</v>
       </c>
       <c r="M300" s="1" t="n">
-        <v>46323.54166666666</v>
+        <v>46324.20833333334</v>
       </c>
     </row>
     <row r="301">
@@ -16946,13 +16946,13 @@
         </is>
       </c>
       <c r="K301" s="1" t="n">
-        <v>46323.66666666666</v>
+        <v>46324.33333333334</v>
       </c>
       <c r="L301" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46324.375</v>
       </c>
       <c r="M301" s="1" t="n">
-        <v>46324.08333333334</v>
+        <v>46324.75</v>
       </c>
     </row>
     <row r="302">
@@ -17001,13 +17001,13 @@
         </is>
       </c>
       <c r="K302" s="1" t="n">
-        <v>46329.08333333334</v>
+        <v>46329.75</v>
       </c>
       <c r="L302" s="1" t="n">
-        <v>46329.25</v>
+        <v>46329.91666666666</v>
       </c>
       <c r="M302" s="1" t="n">
-        <v>46329.95833333334</v>
+        <v>46330.625</v>
       </c>
     </row>
     <row r="303">
@@ -17056,13 +17056,13 @@
         </is>
       </c>
       <c r="K303" s="1" t="n">
-        <v>46331.625</v>
+        <v>46332.29166666666</v>
       </c>
       <c r="L303" s="1" t="n">
-        <v>46331.66666666666</v>
+        <v>46332.33333333334</v>
       </c>
       <c r="M303" s="1" t="n">
-        <v>46331.95833333334</v>
+        <v>46332.625</v>
       </c>
     </row>
     <row r="304">
@@ -17111,13 +17111,13 @@
         </is>
       </c>
       <c r="K304" s="1" t="n">
-        <v>46332.08333333334</v>
+        <v>46332.75</v>
       </c>
       <c r="L304" s="1" t="n">
-        <v>46332.20833333334</v>
+        <v>46332.875</v>
       </c>
       <c r="M304" s="1" t="n">
-        <v>46333.33333333334</v>
+        <v>46334</v>
       </c>
     </row>
     <row r="305">
@@ -17166,13 +17166,13 @@
         </is>
       </c>
       <c r="K305" s="1" t="n">
-        <v>46333.66666666666</v>
+        <v>46334.33333333334</v>
       </c>
       <c r="L305" s="1" t="n">
-        <v>46333.70833333334</v>
+        <v>46334.375</v>
       </c>
       <c r="M305" s="1" t="n">
-        <v>46334.04166666666</v>
+        <v>46334.70833333334</v>
       </c>
     </row>
     <row r="306">
@@ -17221,13 +17221,13 @@
         </is>
       </c>
       <c r="K306" s="1" t="n">
-        <v>46337.91666666666</v>
+        <v>46338.58333333334</v>
       </c>
       <c r="L306" s="1" t="n">
-        <v>46337.95833333334</v>
+        <v>46338.625</v>
       </c>
       <c r="M306" s="1" t="n">
-        <v>46338.375</v>
+        <v>46339.04166666666</v>
       </c>
     </row>
     <row r="307">
@@ -17276,13 +17276,13 @@
         </is>
       </c>
       <c r="K307" s="1" t="n">
-        <v>46338.625</v>
+        <v>46339.29166666666</v>
       </c>
       <c r="L307" s="1" t="n">
-        <v>46338.625</v>
+        <v>46339.29166666666</v>
       </c>
       <c r="M307" s="1" t="n">
-        <v>46339</v>
+        <v>46339.66666666666</v>
       </c>
     </row>
     <row r="308">
@@ -17331,13 +17331,13 @@
         </is>
       </c>
       <c r="K308" s="1" t="n">
-        <v>46340.25</v>
+        <v>46340.91666666666</v>
       </c>
       <c r="L308" s="1" t="n">
-        <v>46340.25</v>
+        <v>46340.91666666666</v>
       </c>
       <c r="M308" s="1" t="n">
-        <v>46340.5</v>
+        <v>46341.16666666666</v>
       </c>
     </row>
     <row r="309">
@@ -17386,13 +17386,13 @@
         </is>
       </c>
       <c r="K309" s="1" t="n">
-        <v>46342.83333333334</v>
+        <v>46343.5</v>
       </c>
       <c r="L309" s="1" t="n">
-        <v>46342.875</v>
+        <v>46343.54166666666</v>
       </c>
       <c r="M309" s="1" t="n">
-        <v>46343.58333333334</v>
+        <v>46344.25</v>
       </c>
     </row>
     <row r="310">
@@ -17441,13 +17441,13 @@
         </is>
       </c>
       <c r="K310" s="1" t="n">
-        <v>46343.79166666666</v>
+        <v>46344.45833333334</v>
       </c>
       <c r="L310" s="1" t="n">
-        <v>46343.83333333334</v>
+        <v>46344.5</v>
       </c>
       <c r="M310" s="1" t="n">
-        <v>46344.16666666666</v>
+        <v>46344.83333333334</v>
       </c>
     </row>
     <row r="311">
@@ -17496,13 +17496,13 @@
         </is>
       </c>
       <c r="K311" s="1" t="n">
-        <v>46347</v>
+        <v>46347.66666666666</v>
       </c>
       <c r="L311" s="1" t="n">
-        <v>46347.04166666666</v>
+        <v>46347.70833333334</v>
       </c>
       <c r="M311" s="1" t="n">
-        <v>46347.41666666666</v>
+        <v>46348.08333333334</v>
       </c>
     </row>
     <row r="312">
@@ -17551,13 +17551,13 @@
         </is>
       </c>
       <c r="K312" s="1" t="n">
-        <v>46349.875</v>
+        <v>46350.54166666666</v>
       </c>
       <c r="L312" s="1" t="n">
-        <v>46350.04166666666</v>
+        <v>46350.70833333334</v>
       </c>
       <c r="M312" s="1" t="n">
-        <v>46350.58333333334</v>
+        <v>46351.25</v>
       </c>
     </row>
     <row r="313">
@@ -17606,13 +17606,13 @@
         </is>
       </c>
       <c r="K313" s="1" t="n">
-        <v>46352.375</v>
+        <v>46353.04166666666</v>
       </c>
       <c r="L313" s="1" t="n">
-        <v>46352.41666666666</v>
+        <v>46353.08333333334</v>
       </c>
       <c r="M313" s="1" t="n">
-        <v>46352.66666666666</v>
+        <v>46353.33333333334</v>
       </c>
     </row>
     <row r="314">
@@ -17661,13 +17661,13 @@
         </is>
       </c>
       <c r="K314" s="1" t="n">
-        <v>46353.08333333334</v>
+        <v>46353.75</v>
       </c>
       <c r="L314" s="1" t="n">
-        <v>46353.20833333334</v>
+        <v>46353.875</v>
       </c>
       <c r="M314" s="1" t="n">
-        <v>46354.33333333334</v>
+        <v>46355</v>
       </c>
     </row>
     <row r="315">
@@ -17716,13 +17716,13 @@
         </is>
       </c>
       <c r="K315" s="1" t="n">
-        <v>46354.66666666666</v>
+        <v>46355.33333333334</v>
       </c>
       <c r="L315" s="1" t="n">
-        <v>46354.70833333334</v>
+        <v>46355.375</v>
       </c>
       <c r="M315" s="1" t="n">
-        <v>46355.04166666666</v>
+        <v>46355.70833333334</v>
       </c>
     </row>
     <row r="316">
@@ -17771,13 +17771,13 @@
         </is>
       </c>
       <c r="K316" s="1" t="n">
-        <v>46358.91666666666</v>
+        <v>46359.58333333334</v>
       </c>
       <c r="L316" s="1" t="n">
-        <v>46358.95833333334</v>
+        <v>46359.625</v>
       </c>
       <c r="M316" s="1" t="n">
-        <v>46359.375</v>
+        <v>46360.04166666666</v>
       </c>
     </row>
     <row r="317">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="K317" s="1" t="n">
-        <v>46359.625</v>
+        <v>46360.29166666666</v>
       </c>
       <c r="L317" s="1" t="n">
-        <v>46359.625</v>
+        <v>46360.29166666666</v>
       </c>
       <c r="M317" s="1" t="n">
-        <v>46360</v>
+        <v>46360.66666666666</v>
       </c>
     </row>
     <row r="318">
@@ -17881,13 +17881,13 @@
         </is>
       </c>
       <c r="K318" s="1" t="n">
-        <v>46361.25</v>
+        <v>46361.91666666666</v>
       </c>
       <c r="L318" s="1" t="n">
-        <v>46361.25</v>
+        <v>46361.91666666666</v>
       </c>
       <c r="M318" s="1" t="n">
-        <v>46361.5</v>
+        <v>46362.16666666666</v>
       </c>
     </row>
     <row r="319">
@@ -17936,13 +17936,13 @@
         </is>
       </c>
       <c r="K319" s="1" t="n">
-        <v>46363.83333333334</v>
+        <v>46364.5</v>
       </c>
       <c r="L319" s="1" t="n">
-        <v>46363.875</v>
+        <v>46364.54166666666</v>
       </c>
       <c r="M319" s="1" t="n">
-        <v>46364.58333333334</v>
+        <v>46365.25</v>
       </c>
     </row>
     <row r="320">
@@ -17991,13 +17991,13 @@
         </is>
       </c>
       <c r="K320" s="1" t="n">
-        <v>46364.79166666666</v>
+        <v>46365.45833333334</v>
       </c>
       <c r="L320" s="1" t="n">
-        <v>46364.83333333334</v>
+        <v>46365.5</v>
       </c>
       <c r="M320" s="1" t="n">
-        <v>46365.16666666666</v>
+        <v>46365.83333333334</v>
       </c>
     </row>
     <row r="321">
@@ -18046,13 +18046,13 @@
         </is>
       </c>
       <c r="K321" s="1" t="n">
-        <v>46368</v>
+        <v>46368.66666666666</v>
       </c>
       <c r="L321" s="1" t="n">
-        <v>46368.04166666666</v>
+        <v>46368.70833333334</v>
       </c>
       <c r="M321" s="1" t="n">
-        <v>46368.41666666666</v>
+        <v>46369.08333333334</v>
       </c>
     </row>
     <row r="322">
@@ -18101,13 +18101,13 @@
         </is>
       </c>
       <c r="K322" s="1" t="n">
-        <v>46370.875</v>
+        <v>46371.54166666666</v>
       </c>
       <c r="L322" s="1" t="n">
-        <v>46371.04166666666</v>
+        <v>46371.70833333334</v>
       </c>
       <c r="M322" s="1" t="n">
-        <v>46371.58333333334</v>
+        <v>46372.25</v>
       </c>
     </row>
     <row r="323">
@@ -18156,13 +18156,13 @@
         </is>
       </c>
       <c r="K323" s="1" t="n">
-        <v>46373.375</v>
+        <v>46374.04166666666</v>
       </c>
       <c r="L323" s="1" t="n">
-        <v>46373.41666666666</v>
+        <v>46374.08333333334</v>
       </c>
       <c r="M323" s="1" t="n">
-        <v>46373.66666666666</v>
+        <v>46374.33333333334</v>
       </c>
     </row>
     <row r="324">
@@ -18211,13 +18211,13 @@
         </is>
       </c>
       <c r="K324" s="1" t="n">
-        <v>46374.08333333334</v>
+        <v>46374.75</v>
       </c>
       <c r="L324" s="1" t="n">
-        <v>46374.20833333334</v>
+        <v>46374.875</v>
       </c>
       <c r="M324" s="1" t="n">
-        <v>46375.33333333334</v>
+        <v>46376</v>
       </c>
     </row>
     <row r="325">
@@ -18266,13 +18266,13 @@
         </is>
       </c>
       <c r="K325" s="1" t="n">
-        <v>46375.66666666666</v>
+        <v>46376.33333333334</v>
       </c>
       <c r="L325" s="1" t="n">
-        <v>46375.70833333334</v>
+        <v>46376.375</v>
       </c>
       <c r="M325" s="1" t="n">
-        <v>46376.04166666666</v>
+        <v>46376.70833333334</v>
       </c>
     </row>
     <row r="326">
@@ -18321,13 +18321,13 @@
         </is>
       </c>
       <c r="K326" s="1" t="n">
-        <v>46379.91666666666</v>
+        <v>46380.58333333334</v>
       </c>
       <c r="L326" s="1" t="n">
-        <v>46379.95833333334</v>
+        <v>46380.625</v>
       </c>
       <c r="M326" s="1" t="n">
-        <v>46380.375</v>
+        <v>46381.04166666666</v>
       </c>
     </row>
     <row r="327">
@@ -18376,13 +18376,13 @@
         </is>
       </c>
       <c r="K327" s="1" t="n">
-        <v>46380.625</v>
+        <v>46381.29166666666</v>
       </c>
       <c r="L327" s="1" t="n">
-        <v>46380.625</v>
+        <v>46381.29166666666</v>
       </c>
       <c r="M327" s="1" t="n">
-        <v>46381</v>
+        <v>46381.66666666666</v>
       </c>
     </row>
     <row r="328">
@@ -18431,13 +18431,13 @@
         </is>
       </c>
       <c r="K328" s="1" t="n">
-        <v>46382.25</v>
+        <v>46382.91666666666</v>
       </c>
       <c r="L328" s="1" t="n">
-        <v>46382.25</v>
+        <v>46382.91666666666</v>
       </c>
       <c r="M328" s="1" t="n">
-        <v>46382.5</v>
+        <v>46383.16666666666</v>
       </c>
     </row>
     <row r="329">
@@ -18486,13 +18486,13 @@
         </is>
       </c>
       <c r="K329" s="1" t="n">
-        <v>46384.83333333334</v>
+        <v>46385.5</v>
       </c>
       <c r="L329" s="1" t="n">
-        <v>46384.875</v>
+        <v>46385.54166666666</v>
       </c>
       <c r="M329" s="1" t="n">
-        <v>46385.58333333334</v>
+        <v>46386.25</v>
       </c>
     </row>
     <row r="330">
@@ -18541,13 +18541,13 @@
         </is>
       </c>
       <c r="K330" s="1" t="n">
-        <v>46385.79166666666</v>
+        <v>46386.45833333334</v>
       </c>
       <c r="L330" s="1" t="n">
-        <v>46385.83333333334</v>
+        <v>46386.5</v>
       </c>
       <c r="M330" s="1" t="n">
-        <v>46386.16666666666</v>
+        <v>46386.83333333334</v>
       </c>
     </row>
     <row r="331">
@@ -18596,13 +18596,13 @@
         </is>
       </c>
       <c r="K331" s="1" t="n">
-        <v>46389</v>
+        <v>46389.66666666666</v>
       </c>
       <c r="L331" s="1" t="n">
-        <v>46389.04166666666</v>
+        <v>46389.70833333334</v>
       </c>
       <c r="M331" s="1" t="n">
-        <v>46389.41666666666</v>
+        <v>46390.08333333334</v>
       </c>
     </row>
     <row r="332">
@@ -18651,13 +18651,13 @@
         </is>
       </c>
       <c r="K332" s="1" t="n">
-        <v>46391.875</v>
+        <v>46392.54166666666</v>
       </c>
       <c r="L332" s="1" t="n">
-        <v>46392.04166666666</v>
+        <v>46392.70833333334</v>
       </c>
       <c r="M332" s="1" t="n">
-        <v>46392.58333333334</v>
+        <v>46393.25</v>
       </c>
     </row>
     <row r="333">
@@ -18706,13 +18706,13 @@
         </is>
       </c>
       <c r="K333" s="1" t="n">
-        <v>46394.375</v>
+        <v>46395.04166666666</v>
       </c>
       <c r="L333" s="1" t="n">
-        <v>46394.41666666666</v>
+        <v>46395.08333333334</v>
       </c>
       <c r="M333" s="1" t="n">
-        <v>46394.66666666666</v>
+        <v>46395.33333333334</v>
       </c>
     </row>
     <row r="334">
@@ -18761,13 +18761,13 @@
         </is>
       </c>
       <c r="K334" s="1" t="n">
-        <v>46395.08333333334</v>
+        <v>46395.75</v>
       </c>
       <c r="L334" s="1" t="n">
-        <v>46395.20833333334</v>
+        <v>46395.875</v>
       </c>
       <c r="M334" s="1" t="n">
-        <v>46396.33333333334</v>
+        <v>46397</v>
       </c>
     </row>
     <row r="335">
@@ -18816,13 +18816,13 @@
         </is>
       </c>
       <c r="K335" s="1" t="n">
-        <v>46396.66666666666</v>
+        <v>46397.33333333334</v>
       </c>
       <c r="L335" s="1" t="n">
-        <v>46396.70833333334</v>
+        <v>46397.375</v>
       </c>
       <c r="M335" s="1" t="n">
-        <v>46397.04166666666</v>
+        <v>46397.70833333334</v>
       </c>
     </row>
     <row r="336">
@@ -18871,13 +18871,13 @@
         </is>
       </c>
       <c r="K336" s="1" t="n">
-        <v>46400.91666666666</v>
+        <v>46401.58333333334</v>
       </c>
       <c r="L336" s="1" t="n">
-        <v>46400.95833333334</v>
+        <v>46401.625</v>
       </c>
       <c r="M336" s="1" t="n">
-        <v>46401.375</v>
+        <v>46402.04166666666</v>
       </c>
     </row>
     <row r="337">
@@ -18926,13 +18926,13 @@
         </is>
       </c>
       <c r="K337" s="1" t="n">
-        <v>46401.625</v>
+        <v>46402.29166666666</v>
       </c>
       <c r="L337" s="1" t="n">
-        <v>46401.625</v>
+        <v>46402.29166666666</v>
       </c>
       <c r="M337" s="1" t="n">
-        <v>46402</v>
+        <v>46402.66666666666</v>
       </c>
     </row>
     <row r="338">
@@ -18977,13 +18977,13 @@
       </c>
       <c r="J338" t="inlineStr"/>
       <c r="K338" s="1" t="n">
-        <v>46403.25</v>
+        <v>46403.91666666666</v>
       </c>
       <c r="L338" s="1" t="n">
-        <v>46403.25</v>
+        <v>46403.91666666666</v>
       </c>
       <c r="M338" s="1" t="n">
-        <v>46403.5</v>
+        <v>46404.16666666666</v>
       </c>
     </row>
     <row r="339">
@@ -19475,10 +19475,10 @@
         <v>46306.64583333334</v>
       </c>
       <c r="L347" s="1" t="n">
-        <v>46306.70833333334</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="M347" s="1" t="n">
-        <v>46307.20833333334</v>
+        <v>46308.16666666666</v>
       </c>
     </row>
     <row r="348">
@@ -19527,13 +19527,13 @@
         </is>
       </c>
       <c r="K348" s="1" t="n">
-        <v>46307.3125</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="L348" s="1" t="n">
-        <v>46309.79166666666</v>
+        <v>46308.625</v>
       </c>
       <c r="M348" s="1" t="n">
-        <v>46310.3125</v>
+        <v>46309.10416666666</v>
       </c>
     </row>
     <row r="349">
@@ -19582,13 +19582,13 @@
         </is>
       </c>
       <c r="K349" s="1" t="n">
-        <v>46313.4375</v>
+        <v>46312.22916666666</v>
       </c>
       <c r="L349" s="1" t="n">
-        <v>46313.47916666666</v>
+        <v>46312.27083333334</v>
       </c>
       <c r="M349" s="1" t="n">
-        <v>46314.14583333334</v>
+        <v>46312.9375</v>
       </c>
     </row>
     <row r="350">
@@ -19637,13 +19637,13 @@
         </is>
       </c>
       <c r="K350" s="1" t="n">
-        <v>46315.1875</v>
+        <v>46313.97916666666</v>
       </c>
       <c r="L350" s="1" t="n">
-        <v>46315.22916666666</v>
+        <v>46314.02083333334</v>
       </c>
       <c r="M350" s="1" t="n">
-        <v>46315.8125</v>
+        <v>46314.60416666666</v>
       </c>
     </row>
     <row r="351">
@@ -19692,13 +19692,13 @@
         </is>
       </c>
       <c r="K351" s="1" t="n">
-        <v>46315.91666666666</v>
+        <v>46314.70833333334</v>
       </c>
       <c r="L351" s="1" t="n">
-        <v>46315.97916666666</v>
+        <v>46314.77083333334</v>
       </c>
       <c r="M351" s="1" t="n">
-        <v>46316.3125</v>
+        <v>46315.10416666666</v>
       </c>
     </row>
     <row r="352">
@@ -19747,13 +19747,13 @@
         </is>
       </c>
       <c r="K352" s="1" t="n">
-        <v>46317.39583333334</v>
+        <v>46316.1875</v>
       </c>
       <c r="L352" s="1" t="n">
-        <v>46318.5625</v>
+        <v>46317.35416666666</v>
       </c>
       <c r="M352" s="1" t="n">
-        <v>46319.0625</v>
+        <v>46317.85416666666</v>
       </c>
     </row>
     <row r="353">
@@ -19802,13 +19802,13 @@
         </is>
       </c>
       <c r="K353" s="1" t="n">
-        <v>46322.97916666666</v>
+        <v>46321.77083333334</v>
       </c>
       <c r="L353" s="1" t="n">
-        <v>46323.64583333334</v>
+        <v>46322.4375</v>
       </c>
       <c r="M353" s="1" t="n">
-        <v>46324.47916666666</v>
+        <v>46323.27083333334</v>
       </c>
     </row>
     <row r="354">
@@ -19857,13 +19857,13 @@
         </is>
       </c>
       <c r="K354" s="1" t="n">
-        <v>46326.02083333334</v>
+        <v>46324.8125</v>
       </c>
       <c r="L354" s="1" t="n">
-        <v>46326.0625</v>
+        <v>46324.85416666666</v>
       </c>
       <c r="M354" s="1" t="n">
-        <v>46326.89583333334</v>
+        <v>46325.6875</v>
       </c>
     </row>
     <row r="355">
@@ -19912,13 +19912,13 @@
         </is>
       </c>
       <c r="K355" s="1" t="n">
-        <v>46329.91666666666</v>
+        <v>46328.70833333334</v>
       </c>
       <c r="L355" s="1" t="n">
-        <v>46329.97916666666</v>
+        <v>46328.77083333334</v>
       </c>
       <c r="M355" s="1" t="n">
-        <v>46331.6875</v>
+        <v>46330.47916666666</v>
       </c>
     </row>
     <row r="356">
@@ -19967,13 +19967,13 @@
         </is>
       </c>
       <c r="K356" s="1" t="n">
-        <v>46334.14583333334</v>
+        <v>46332.9375</v>
       </c>
       <c r="L356" s="1" t="n">
-        <v>46334.3125</v>
+        <v>46333.10416666666</v>
       </c>
       <c r="M356" s="1" t="n">
-        <v>46335.14583333334</v>
+        <v>46333.9375</v>
       </c>
     </row>
     <row r="357">
@@ -20022,13 +20022,13 @@
         </is>
       </c>
       <c r="K357" s="1" t="n">
-        <v>46337.6875</v>
+        <v>46336.47916666666</v>
       </c>
       <c r="L357" s="1" t="n">
-        <v>46337.75</v>
+        <v>46336.54166666666</v>
       </c>
       <c r="M357" s="1" t="n">
-        <v>46338.25</v>
+        <v>46337.04166666666</v>
       </c>
     </row>
     <row r="358">
@@ -20077,13 +20077,13 @@
         </is>
       </c>
       <c r="K358" s="1" t="n">
-        <v>46338.47916666666</v>
+        <v>46337.27083333334</v>
       </c>
       <c r="L358" s="1" t="n">
-        <v>46338.52083333334</v>
+        <v>46337.3125</v>
       </c>
       <c r="M358" s="1" t="n">
-        <v>46339.02083333334</v>
+        <v>46337.8125</v>
       </c>
     </row>
     <row r="359">
@@ -20132,13 +20132,13 @@
         </is>
       </c>
       <c r="K359" s="1" t="n">
-        <v>46342.3125</v>
+        <v>46341.10416666666</v>
       </c>
       <c r="L359" s="1" t="n">
-        <v>46342.35416666666</v>
+        <v>46341.14583333334</v>
       </c>
       <c r="M359" s="1" t="n">
-        <v>46343.02083333334</v>
+        <v>46341.8125</v>
       </c>
     </row>
     <row r="360">
@@ -20187,13 +20187,13 @@
         </is>
       </c>
       <c r="K360" s="1" t="n">
-        <v>46344.10416666666</v>
+        <v>46342.89583333334</v>
       </c>
       <c r="L360" s="1" t="n">
-        <v>46344.14583333334</v>
+        <v>46342.9375</v>
       </c>
       <c r="M360" s="1" t="n">
-        <v>46344.72916666666</v>
+        <v>46343.52083333334</v>
       </c>
     </row>
     <row r="361">
@@ -20242,13 +20242,13 @@
         </is>
       </c>
       <c r="K361" s="1" t="n">
-        <v>46344.91666666666</v>
+        <v>46343.70833333334</v>
       </c>
       <c r="L361" s="1" t="n">
-        <v>46344.97916666666</v>
+        <v>46343.77083333334</v>
       </c>
       <c r="M361" s="1" t="n">
-        <v>46345.3125</v>
+        <v>46344.10416666666</v>
       </c>
     </row>
     <row r="362">
@@ -20297,13 +20297,13 @@
         </is>
       </c>
       <c r="K362" s="1" t="n">
-        <v>46346.60416666666</v>
+        <v>46345.39583333334</v>
       </c>
       <c r="L362" s="1" t="n">
-        <v>46346.77083333334</v>
+        <v>46345.5625</v>
       </c>
       <c r="M362" s="1" t="n">
-        <v>46347.27083333334</v>
+        <v>46346.0625</v>
       </c>
     </row>
     <row r="363">
@@ -20352,13 +20352,13 @@
         </is>
       </c>
       <c r="K363" s="1" t="n">
-        <v>46351.4375</v>
+        <v>46350.22916666666</v>
       </c>
       <c r="L363" s="1" t="n">
-        <v>46351.60416666666</v>
+        <v>46350.39583333334</v>
       </c>
       <c r="M363" s="1" t="n">
-        <v>46352.4375</v>
+        <v>46351.22916666666</v>
       </c>
     </row>
     <row r="364">
@@ -20407,13 +20407,13 @@
         </is>
       </c>
       <c r="K364" s="1" t="n">
-        <v>46354.10416666666</v>
+        <v>46352.89583333334</v>
       </c>
       <c r="L364" s="1" t="n">
-        <v>46354.14583333334</v>
+        <v>46352.9375</v>
       </c>
       <c r="M364" s="1" t="n">
-        <v>46354.97916666666</v>
+        <v>46353.77083333334</v>
       </c>
     </row>
     <row r="365">
@@ -20462,13 +20462,13 @@
         </is>
       </c>
       <c r="K365" s="1" t="n">
-        <v>46358.14583333334</v>
+        <v>46356.9375</v>
       </c>
       <c r="L365" s="1" t="n">
-        <v>46358.22916666666</v>
+        <v>46357.02083333334</v>
       </c>
       <c r="M365" s="1" t="n">
-        <v>46359.89583333334</v>
+        <v>46358.6875</v>
       </c>
     </row>
     <row r="366">
@@ -20517,13 +20517,13 @@
         </is>
       </c>
       <c r="K366" s="1" t="n">
-        <v>46362.35416666666</v>
+        <v>46361.14583333334</v>
       </c>
       <c r="L366" s="1" t="n">
-        <v>46362.52083333334</v>
+        <v>46361.3125</v>
       </c>
       <c r="M366" s="1" t="n">
-        <v>46363.35416666666</v>
+        <v>46362.14583333334</v>
       </c>
     </row>
     <row r="367">
@@ -20572,13 +20572,13 @@
         </is>
       </c>
       <c r="K367" s="1" t="n">
-        <v>46365.89583333334</v>
+        <v>46364.6875</v>
       </c>
       <c r="L367" s="1" t="n">
-        <v>46365.95833333334</v>
+        <v>46364.75</v>
       </c>
       <c r="M367" s="1" t="n">
-        <v>46366.45833333334</v>
+        <v>46365.25</v>
       </c>
     </row>
     <row r="368">
@@ -20627,13 +20627,13 @@
         </is>
       </c>
       <c r="K368" s="1" t="n">
-        <v>46366.6875</v>
+        <v>46365.47916666666</v>
       </c>
       <c r="L368" s="1" t="n">
-        <v>46366.72916666666</v>
+        <v>46365.52083333334</v>
       </c>
       <c r="M368" s="1" t="n">
-        <v>46367.22916666666</v>
+        <v>46366.02083333334</v>
       </c>
     </row>
     <row r="369">
@@ -20682,13 +20682,13 @@
         </is>
       </c>
       <c r="K369" s="1" t="n">
-        <v>46372.22916666666</v>
+        <v>46371.02083333334</v>
       </c>
       <c r="L369" s="1" t="n">
-        <v>46372.27083333334</v>
+        <v>46371.0625</v>
       </c>
       <c r="M369" s="1" t="n">
-        <v>46372.9375</v>
+        <v>46371.72916666666</v>
       </c>
     </row>
     <row r="370">
@@ -20737,13 +20737,13 @@
         </is>
       </c>
       <c r="K370" s="1" t="n">
-        <v>46374.02083333334</v>
+        <v>46372.8125</v>
       </c>
       <c r="L370" s="1" t="n">
-        <v>46374.0625</v>
+        <v>46372.85416666666</v>
       </c>
       <c r="M370" s="1" t="n">
-        <v>46374.64583333334</v>
+        <v>46373.4375</v>
       </c>
     </row>
     <row r="371">
@@ -20792,13 +20792,13 @@
         </is>
       </c>
       <c r="K371" s="1" t="n">
-        <v>46374.83333333334</v>
+        <v>46373.625</v>
       </c>
       <c r="L371" s="1" t="n">
-        <v>46374.89583333334</v>
+        <v>46373.6875</v>
       </c>
       <c r="M371" s="1" t="n">
-        <v>46375.22916666666</v>
+        <v>46374.02083333334</v>
       </c>
     </row>
     <row r="372">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="K372" s="1" t="n">
-        <v>46376.52083333334</v>
+        <v>46375.3125</v>
       </c>
       <c r="L372" s="1" t="n">
-        <v>46376.6875</v>
+        <v>46375.47916666666</v>
       </c>
       <c r="M372" s="1" t="n">
-        <v>46377.1875</v>
+        <v>46375.97916666666</v>
       </c>
     </row>
     <row r="373">
@@ -20902,13 +20902,13 @@
         </is>
       </c>
       <c r="K373" s="1" t="n">
-        <v>46381.35416666666</v>
+        <v>46380.14583333334</v>
       </c>
       <c r="L373" s="1" t="n">
-        <v>46381.52083333334</v>
+        <v>46380.3125</v>
       </c>
       <c r="M373" s="1" t="n">
-        <v>46382.35416666666</v>
+        <v>46381.14583333334</v>
       </c>
     </row>
     <row r="374">
@@ -20957,13 +20957,13 @@
         </is>
       </c>
       <c r="K374" s="1" t="n">
-        <v>46384.02083333334</v>
+        <v>46382.8125</v>
       </c>
       <c r="L374" s="1" t="n">
-        <v>46384.0625</v>
+        <v>46382.85416666666</v>
       </c>
       <c r="M374" s="1" t="n">
-        <v>46384.89583333334</v>
+        <v>46383.6875</v>
       </c>
     </row>
     <row r="375">
@@ -21012,13 +21012,13 @@
         </is>
       </c>
       <c r="K375" s="1" t="n">
-        <v>46388.0625</v>
+        <v>46386.85416666666</v>
       </c>
       <c r="L375" s="1" t="n">
-        <v>46388.14583333334</v>
+        <v>46386.9375</v>
       </c>
       <c r="M375" s="1" t="n">
-        <v>46389.8125</v>
+        <v>46388.60416666666</v>
       </c>
     </row>
     <row r="376">
@@ -21067,13 +21067,13 @@
         </is>
       </c>
       <c r="K376" s="1" t="n">
-        <v>46392.27083333334</v>
+        <v>46391.0625</v>
       </c>
       <c r="L376" s="1" t="n">
-        <v>46392.4375</v>
+        <v>46391.22916666666</v>
       </c>
       <c r="M376" s="1" t="n">
-        <v>46393.27083333334</v>
+        <v>46392.0625</v>
       </c>
     </row>
     <row r="377">
@@ -21122,13 +21122,13 @@
         </is>
       </c>
       <c r="K377" s="1" t="n">
-        <v>46395.8125</v>
+        <v>46394.60416666666</v>
       </c>
       <c r="L377" s="1" t="n">
-        <v>46395.875</v>
+        <v>46394.66666666666</v>
       </c>
       <c r="M377" s="1" t="n">
-        <v>46396.375</v>
+        <v>46395.16666666666</v>
       </c>
     </row>
     <row r="378">
@@ -21173,13 +21173,13 @@
       </c>
       <c r="J378" t="inlineStr"/>
       <c r="K378" s="1" t="n">
-        <v>46396.60416666666</v>
+        <v>46395.39583333334</v>
       </c>
       <c r="L378" s="1" t="n">
-        <v>46396.64583333334</v>
+        <v>46395.4375</v>
       </c>
       <c r="M378" s="1" t="n">
-        <v>46397.14583333334</v>
+        <v>46395.9375</v>
       </c>
     </row>
     <row r="379">
@@ -21448,13 +21448,13 @@
         </is>
       </c>
       <c r="K383" s="1" t="n">
-        <v>46307.54166666666</v>
+        <v>46307.625</v>
       </c>
       <c r="L383" s="1" t="n">
-        <v>46307.58333333334</v>
+        <v>46307.66666666666</v>
       </c>
       <c r="M383" s="1" t="n">
-        <v>46307.79166666666</v>
+        <v>46307.95833333334</v>
       </c>
     </row>
     <row r="384">
@@ -21503,13 +21503,13 @@
         </is>
       </c>
       <c r="K384" s="1" t="n">
-        <v>46307.91666666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="L384" s="1" t="n">
-        <v>46308.04166666666</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="M384" s="1" t="n">
-        <v>46309.5</v>
+        <v>46309.625</v>
       </c>
     </row>
     <row r="385">
@@ -21558,13 +21558,13 @@
         </is>
       </c>
       <c r="K385" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46309.83333333334</v>
       </c>
       <c r="L385" s="1" t="n">
-        <v>46309.75</v>
+        <v>46309.875</v>
       </c>
       <c r="M385" s="1" t="n">
-        <v>46310.08333333334</v>
+        <v>46310.25</v>
       </c>
     </row>
     <row r="386">
@@ -21613,13 +21613,13 @@
         </is>
       </c>
       <c r="K386" s="1" t="n">
-        <v>46313.91666666666</v>
+        <v>46314.08333333334</v>
       </c>
       <c r="L386" s="1" t="n">
-        <v>46313.97916666666</v>
+        <v>46314.14583333334</v>
       </c>
       <c r="M386" s="1" t="n">
-        <v>46314.47916666666</v>
+        <v>46314.64583333334</v>
       </c>
     </row>
     <row r="387">
@@ -21668,13 +21668,13 @@
         </is>
       </c>
       <c r="K387" s="1" t="n">
-        <v>46315.33333333334</v>
+        <v>46315.5</v>
       </c>
       <c r="L387" s="1" t="n">
-        <v>46315.375</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="M387" s="1" t="n">
-        <v>46316</v>
+        <v>46316.16666666666</v>
       </c>
     </row>
     <row r="388">
@@ -21723,13 +21723,13 @@
         </is>
       </c>
       <c r="K388" s="1" t="n">
-        <v>46318.29166666666</v>
+        <v>46318.45833333334</v>
       </c>
       <c r="L388" s="1" t="n">
-        <v>46318.33333333334</v>
+        <v>46318.5</v>
       </c>
       <c r="M388" s="1" t="n">
-        <v>46319.33333333334</v>
+        <v>46319.5</v>
       </c>
     </row>
     <row r="389">
@@ -21778,13 +21778,13 @@
         </is>
       </c>
       <c r="K389" s="1" t="n">
-        <v>46319.625</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="L389" s="1" t="n">
-        <v>46319.6875</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="M389" s="1" t="n">
-        <v>46320.02083333334</v>
+        <v>46320.1875</v>
       </c>
     </row>
     <row r="390">
@@ -21833,13 +21833,13 @@
         </is>
       </c>
       <c r="K390" s="1" t="n">
-        <v>46322.91666666666</v>
+        <v>46323.08333333334</v>
       </c>
       <c r="L390" s="1" t="n">
-        <v>46322.95833333334</v>
+        <v>46323.125</v>
       </c>
       <c r="M390" s="1" t="n">
-        <v>46323.47916666666</v>
+        <v>46323.64583333334</v>
       </c>
     </row>
     <row r="391">
@@ -21888,13 +21888,13 @@
         </is>
       </c>
       <c r="K391" s="1" t="n">
-        <v>46325.70833333334</v>
+        <v>46326</v>
       </c>
       <c r="L391" s="1" t="n">
-        <v>46325.875</v>
+        <v>46326.16666666666</v>
       </c>
       <c r="M391" s="1" t="n">
-        <v>46326.33333333334</v>
+        <v>46326.79166666666</v>
       </c>
     </row>
     <row r="392">
@@ -21943,13 +21943,13 @@
         </is>
       </c>
       <c r="K392" s="1" t="n">
-        <v>46328.08333333334</v>
+        <v>46328.54166666666</v>
       </c>
       <c r="L392" s="1" t="n">
-        <v>46328.125</v>
+        <v>46328.58333333334</v>
       </c>
       <c r="M392" s="1" t="n">
-        <v>46328.29166666666</v>
+        <v>46328.75</v>
       </c>
     </row>
     <row r="393">
@@ -21998,13 +21998,13 @@
         </is>
       </c>
       <c r="K393" s="1" t="n">
-        <v>46328.54166666666</v>
+        <v>46329</v>
       </c>
       <c r="L393" s="1" t="n">
-        <v>46328.66666666666</v>
+        <v>46329.125</v>
       </c>
       <c r="M393" s="1" t="n">
-        <v>46330</v>
+        <v>46330.45833333334</v>
       </c>
     </row>
     <row r="394">
@@ -22053,13 +22053,13 @@
         </is>
       </c>
       <c r="K394" s="1" t="n">
-        <v>46330.5</v>
+        <v>46330.95833333334</v>
       </c>
       <c r="L394" s="1" t="n">
-        <v>46330.54166666666</v>
+        <v>46331</v>
       </c>
       <c r="M394" s="1" t="n">
-        <v>46330.83333333334</v>
+        <v>46331.29166666666</v>
       </c>
     </row>
     <row r="395">
@@ -22108,13 +22108,13 @@
         </is>
       </c>
       <c r="K395" s="1" t="n">
-        <v>46334.91666666666</v>
+        <v>46335.375</v>
       </c>
       <c r="L395" s="1" t="n">
-        <v>46334.95833333334</v>
+        <v>46335.41666666666</v>
       </c>
       <c r="M395" s="1" t="n">
-        <v>46335.41666666666</v>
+        <v>46335.875</v>
       </c>
     </row>
     <row r="396">
@@ -22163,13 +22163,13 @@
         </is>
       </c>
       <c r="K396" s="1" t="n">
-        <v>46336.5</v>
+        <v>46336.95833333334</v>
       </c>
       <c r="L396" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46337</v>
       </c>
       <c r="M396" s="1" t="n">
-        <v>46337.125</v>
+        <v>46337.58333333334</v>
       </c>
     </row>
     <row r="397">
@@ -28193,7 +28193,7 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="K506" s="1" t="n">
@@ -28248,7 +28248,7 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="K507" s="1" t="n">
@@ -28258,13 +28258,13 @@
         <v>46304.2875</v>
       </c>
       <c r="M507" s="1" t="n">
-        <v>46305.54166666666</v>
+        <v>46305.62083333333</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>SIS2</t>
+          <t>ADHS</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -28279,47 +28279,47 @@
       </c>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="n">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>TAO04</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
           <t>CNSHA</t>
         </is>
       </c>
-      <c r="J508" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
       <c r="K508" s="1" t="n">
-        <v>46307</v>
+        <v>46307.375</v>
       </c>
       <c r="L508" s="1" t="n">
-        <v>46310.20833333334</v>
+        <v>46312.45833333334</v>
       </c>
       <c r="M508" s="1" t="n">
-        <v>46311.20833333334</v>
+        <v>46313.45833333334</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>ADHS</t>
+          <t>SIS2</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -28334,41 +28334,41 @@
       </c>
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="n">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>TAO04</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNNGB</t>
         </is>
       </c>
       <c r="K509" s="1" t="n">
-        <v>46307.375</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>46312.45833333334</v>
+        <v>46310.625</v>
       </c>
       <c r="M509" s="1" t="n">
-        <v>46313.45833333334</v>
+        <v>46311.625</v>
       </c>
     </row>
     <row r="510">
@@ -28853,13 +28853,13 @@
         </is>
       </c>
       <c r="K518" s="1" t="n">
-        <v>46307.45833333334</v>
+        <v>46307.79166666666</v>
       </c>
       <c r="L518" s="1" t="n">
-        <v>46307.5</v>
+        <v>46308.625</v>
       </c>
       <c r="M518" s="1" t="n">
-        <v>46307.66666666666</v>
+        <v>46309.375</v>
       </c>
     </row>
     <row r="519">
@@ -28908,13 +28908,13 @@
         </is>
       </c>
       <c r="K519" s="1" t="n">
-        <v>46309.29166666666</v>
+        <v>46310.875</v>
       </c>
       <c r="L519" s="1" t="n">
-        <v>46309.41666666666</v>
+        <v>46311</v>
       </c>
       <c r="M519" s="1" t="n">
-        <v>46309.91666666666</v>
+        <v>46311.5</v>
       </c>
     </row>
     <row r="520">
@@ -28963,13 +28963,13 @@
         </is>
       </c>
       <c r="K520" s="1" t="n">
-        <v>46315.08333333334</v>
+        <v>46317.25</v>
       </c>
       <c r="L520" s="1" t="n">
-        <v>46315.125</v>
+        <v>46317.29166666666</v>
       </c>
       <c r="M520" s="1" t="n">
-        <v>46315.91666666666</v>
+        <v>46317.83333333334</v>
       </c>
     </row>
     <row r="521">
@@ -29018,13 +29018,13 @@
         </is>
       </c>
       <c r="K521" s="1" t="n">
-        <v>46317.33333333334</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="L521" s="1" t="n">
-        <v>46317.375</v>
+        <v>46318.95833333334</v>
       </c>
       <c r="M521" s="1" t="n">
-        <v>46318.08333333334</v>
+        <v>46319.66666666666</v>
       </c>
     </row>
     <row r="522">
@@ -29073,13 +29073,13 @@
         </is>
       </c>
       <c r="K522" s="1" t="n">
-        <v>46323.41666666666</v>
+        <v>46324.95833333334</v>
       </c>
       <c r="L522" s="1" t="n">
-        <v>46323.58333333334</v>
+        <v>46325.125</v>
       </c>
       <c r="M522" s="1" t="n">
-        <v>46324.66666666666</v>
+        <v>46325.75</v>
       </c>
     </row>
     <row r="523">
@@ -29128,13 +29128,13 @@
         </is>
       </c>
       <c r="K523" s="1" t="n">
-        <v>46330.66666666666</v>
+        <v>46331.41666666666</v>
       </c>
       <c r="L523" s="1" t="n">
-        <v>46330.70833333334</v>
+        <v>46331.45833333334</v>
       </c>
       <c r="M523" s="1" t="n">
-        <v>46331.29166666666</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="524">
@@ -29183,13 +29183,13 @@
         </is>
       </c>
       <c r="K524" s="1" t="n">
-        <v>46332.91666666666</v>
+        <v>46333.08333333334</v>
       </c>
       <c r="L524" s="1" t="n">
-        <v>46332.95833333334</v>
+        <v>46333.125</v>
       </c>
       <c r="M524" s="1" t="n">
-        <v>46333.5</v>
+        <v>46333.91666666666</v>
       </c>
     </row>
     <row r="525">
@@ -29238,13 +29238,13 @@
         </is>
       </c>
       <c r="K525" s="1" t="n">
-        <v>46338.54166666666</v>
+        <v>46338.95833333334</v>
       </c>
       <c r="L525" s="1" t="n">
-        <v>46338.70833333334</v>
+        <v>46339.125</v>
       </c>
       <c r="M525" s="1" t="n">
-        <v>46339.08333333334</v>
+        <v>46339.5</v>
       </c>
     </row>
     <row r="526">
@@ -29293,13 +29293,13 @@
         </is>
       </c>
       <c r="K526" s="1" t="n">
-        <v>46340.91666666666</v>
+        <v>46341.33333333334</v>
       </c>
       <c r="L526" s="1" t="n">
-        <v>46340.95833333334</v>
+        <v>46341.375</v>
       </c>
       <c r="M526" s="1" t="n">
-        <v>46341.375</v>
+        <v>46341.79166666666</v>
       </c>
     </row>
     <row r="527">
@@ -29348,13 +29348,13 @@
         </is>
       </c>
       <c r="K527" s="1" t="n">
-        <v>46341.5</v>
+        <v>46341.91666666666</v>
       </c>
       <c r="L527" s="1" t="n">
-        <v>46341.58333333334</v>
+        <v>46342</v>
       </c>
       <c r="M527" s="1" t="n">
-        <v>46342.625</v>
+        <v>46343.04166666666</v>
       </c>
     </row>
     <row r="528">
@@ -29403,13 +29403,13 @@
         </is>
       </c>
       <c r="K528" s="1" t="n">
-        <v>46342.79166666666</v>
+        <v>46343.20833333334</v>
       </c>
       <c r="L528" s="1" t="n">
-        <v>46342.83333333334</v>
+        <v>46343.25</v>
       </c>
       <c r="M528" s="1" t="n">
-        <v>46343.33333333334</v>
+        <v>46343.75</v>
       </c>
     </row>
     <row r="529">
@@ -29458,13 +29458,13 @@
         </is>
       </c>
       <c r="K529" s="1" t="n">
-        <v>46344.79166666666</v>
+        <v>46345.20833333334</v>
       </c>
       <c r="L529" s="1" t="n">
-        <v>46344.95833333334</v>
+        <v>46345.375</v>
       </c>
       <c r="M529" s="1" t="n">
-        <v>46345.58333333334</v>
+        <v>46346</v>
       </c>
     </row>
     <row r="530">
@@ -30499,13 +30499,13 @@
         </is>
       </c>
       <c r="K548" s="1" t="n">
-        <v>46306.375</v>
+        <v>46306.8125</v>
       </c>
       <c r="L548" s="1" t="n">
-        <v>46306.54166666666</v>
+        <v>46306.97916666666</v>
       </c>
       <c r="M548" s="1" t="n">
-        <v>46307.125</v>
+        <v>46307.41666666666</v>
       </c>
     </row>
     <row r="549">
@@ -30554,13 +30554,13 @@
         </is>
       </c>
       <c r="K549" s="1" t="n">
-        <v>46308.91666666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="L549" s="1" t="n">
-        <v>46308.95833333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="M549" s="1" t="n">
-        <v>46309.33333333334</v>
+        <v>46309.45833333334</v>
       </c>
     </row>
     <row r="550">
@@ -30609,13 +30609,13 @@
         </is>
       </c>
       <c r="K550" s="1" t="n">
-        <v>46309.41666666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="L550" s="1" t="n">
-        <v>46309.5</v>
+        <v>46309.625</v>
       </c>
       <c r="M550" s="1" t="n">
-        <v>46310.5</v>
+        <v>46310.625</v>
       </c>
     </row>
     <row r="551">
@@ -30664,13 +30664,13 @@
         </is>
       </c>
       <c r="K551" s="1" t="n">
-        <v>46310.70833333334</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="L551" s="1" t="n">
-        <v>46310.75</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="M551" s="1" t="n">
-        <v>46311.25</v>
+        <v>46311.33333333334</v>
       </c>
     </row>
     <row r="552">
@@ -30719,13 +30719,13 @@
         </is>
       </c>
       <c r="K552" s="1" t="n">
-        <v>46313.0625</v>
+        <v>46313.14583333334</v>
       </c>
       <c r="L552" s="1" t="n">
-        <v>46313.22916666666</v>
+        <v>46313.3125</v>
       </c>
       <c r="M552" s="1" t="n">
-        <v>46313.91666666666</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="553">
@@ -30774,13 +30774,13 @@
         </is>
       </c>
       <c r="K553" s="1" t="n">
-        <v>46319.08333333334</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="L553" s="1" t="n">
-        <v>46319.125</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="M553" s="1" t="n">
-        <v>46319.79166666666</v>
+        <v>46319.875</v>
       </c>
     </row>
     <row r="554">
@@ -30829,13 +30829,13 @@
         </is>
       </c>
       <c r="K554" s="1" t="n">
-        <v>46319.95833333334</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="L554" s="1" t="n">
-        <v>46320.02083333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="M554" s="1" t="n">
-        <v>46320.27083333334</v>
+        <v>46320.35416666666</v>
       </c>
     </row>
     <row r="555">
@@ -30884,13 +30884,13 @@
         </is>
       </c>
       <c r="K555" s="1" t="n">
-        <v>46321.28125</v>
+        <v>46321.36458333334</v>
       </c>
       <c r="L555" s="1" t="n">
-        <v>46321.30208333334</v>
+        <v>46321.38541666666</v>
       </c>
       <c r="M555" s="1" t="n">
-        <v>46321.90625</v>
+        <v>46321.98958333334</v>
       </c>
     </row>
     <row r="556">
@@ -30939,13 +30939,13 @@
         </is>
       </c>
       <c r="K556" s="1" t="n">
-        <v>46326.82291666666</v>
+        <v>46326.90625</v>
       </c>
       <c r="L556" s="1" t="n">
-        <v>46326.98958333334</v>
+        <v>46327.07291666666</v>
       </c>
       <c r="M556" s="1" t="n">
-        <v>46327.57291666666</v>
+        <v>46327.65625</v>
       </c>
     </row>
     <row r="557">
@@ -30994,13 +30994,13 @@
         </is>
       </c>
       <c r="K557" s="1" t="n">
-        <v>46329.21875</v>
+        <v>46329.30208333334</v>
       </c>
       <c r="L557" s="1" t="n">
-        <v>46329.26041666666</v>
+        <v>46329.34375</v>
       </c>
       <c r="M557" s="1" t="n">
-        <v>46329.61458333334</v>
+        <v>46329.69791666666</v>
       </c>
     </row>
     <row r="558">
@@ -31049,13 +31049,13 @@
         </is>
       </c>
       <c r="K558" s="1" t="n">
-        <v>46329.73958333334</v>
+        <v>46329.82291666666</v>
       </c>
       <c r="L558" s="1" t="n">
-        <v>46329.82291666666</v>
+        <v>46329.90625</v>
       </c>
       <c r="M558" s="1" t="n">
-        <v>46330.82291666666</v>
+        <v>46330.90625</v>
       </c>
     </row>
     <row r="559">
@@ -31104,13 +31104,13 @@
         </is>
       </c>
       <c r="K559" s="1" t="n">
-        <v>46331.03125</v>
+        <v>46331.11458333334</v>
       </c>
       <c r="L559" s="1" t="n">
-        <v>46331.07291666666</v>
+        <v>46331.15625</v>
       </c>
       <c r="M559" s="1" t="n">
-        <v>46331.57291666666</v>
+        <v>46331.65625</v>
       </c>
     </row>
     <row r="560">
@@ -31159,13 +31159,13 @@
         </is>
       </c>
       <c r="K560" s="1" t="n">
-        <v>46333.38541666666</v>
+        <v>46333.46875</v>
       </c>
       <c r="L560" s="1" t="n">
-        <v>46333.55208333334</v>
+        <v>46333.63541666666</v>
       </c>
       <c r="M560" s="1" t="n">
-        <v>46334.23958333334</v>
+        <v>46334.32291666666</v>
       </c>
     </row>
     <row r="561">
@@ -31214,13 +31214,13 @@
         </is>
       </c>
       <c r="K561" s="1" t="n">
-        <v>46339.44791666666</v>
+        <v>46339.53125</v>
       </c>
       <c r="L561" s="1" t="n">
-        <v>46339.48958333334</v>
+        <v>46339.57291666666</v>
       </c>
       <c r="M561" s="1" t="n">
-        <v>46340.15625</v>
+        <v>46340.23958333334</v>
       </c>
     </row>
     <row r="562">
@@ -31269,13 +31269,13 @@
         </is>
       </c>
       <c r="K562" s="1" t="n">
-        <v>46340.32291666666</v>
+        <v>46340.40625</v>
       </c>
       <c r="L562" s="1" t="n">
-        <v>46340.38541666666</v>
+        <v>46340.46875</v>
       </c>
       <c r="M562" s="1" t="n">
-        <v>46340.63541666666</v>
+        <v>46340.71875</v>
       </c>
     </row>
     <row r="563">
@@ -31324,13 +31324,13 @@
         </is>
       </c>
       <c r="K563" s="1" t="n">
-        <v>46341.53125</v>
+        <v>46341.61458333334</v>
       </c>
       <c r="L563" s="1" t="n">
-        <v>46341.59375</v>
+        <v>46341.67708333334</v>
       </c>
       <c r="M563" s="1" t="n">
-        <v>46342.01041666666</v>
+        <v>46342.09375</v>
       </c>
     </row>
     <row r="564">
@@ -31379,13 +31379,13 @@
         </is>
       </c>
       <c r="K564" s="1" t="n">
-        <v>46342.28125</v>
+        <v>46342.36458333334</v>
       </c>
       <c r="L564" s="1" t="n">
-        <v>46342.30208333334</v>
+        <v>46342.38541666666</v>
       </c>
       <c r="M564" s="1" t="n">
-        <v>46342.90625</v>
+        <v>46342.98958333334</v>
       </c>
     </row>
     <row r="565">
@@ -31434,13 +31434,13 @@
         </is>
       </c>
       <c r="K565" s="1" t="n">
-        <v>46347.82291666666</v>
+        <v>46347.90625</v>
       </c>
       <c r="L565" s="1" t="n">
-        <v>46347.98958333334</v>
+        <v>46348.07291666666</v>
       </c>
       <c r="M565" s="1" t="n">
-        <v>46348.57291666666</v>
+        <v>46348.65625</v>
       </c>
     </row>
     <row r="566">
@@ -31489,13 +31489,13 @@
         </is>
       </c>
       <c r="K566" s="1" t="n">
-        <v>46350.21875</v>
+        <v>46350.30208333334</v>
       </c>
       <c r="L566" s="1" t="n">
-        <v>46350.26041666666</v>
+        <v>46350.34375</v>
       </c>
       <c r="M566" s="1" t="n">
-        <v>46350.61458333334</v>
+        <v>46350.69791666666</v>
       </c>
     </row>
     <row r="567">
@@ -31544,13 +31544,13 @@
         </is>
       </c>
       <c r="K567" s="1" t="n">
-        <v>46350.73958333334</v>
+        <v>46350.82291666666</v>
       </c>
       <c r="L567" s="1" t="n">
-        <v>46350.82291666666</v>
+        <v>46350.90625</v>
       </c>
       <c r="M567" s="1" t="n">
-        <v>46351.82291666666</v>
+        <v>46351.90625</v>
       </c>
     </row>
     <row r="568">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="K568" s="1" t="n">
-        <v>46352.03125</v>
+        <v>46352.11458333334</v>
       </c>
       <c r="L568" s="1" t="n">
-        <v>46352.07291666666</v>
+        <v>46352.15625</v>
       </c>
       <c r="M568" s="1" t="n">
-        <v>46352.57291666666</v>
+        <v>46352.65625</v>
       </c>
     </row>
     <row r="569">
@@ -31654,13 +31654,13 @@
         </is>
       </c>
       <c r="K569" s="1" t="n">
-        <v>46354.38541666666</v>
+        <v>46354.46875</v>
       </c>
       <c r="L569" s="1" t="n">
-        <v>46354.55208333334</v>
+        <v>46354.63541666666</v>
       </c>
       <c r="M569" s="1" t="n">
-        <v>46355.23958333334</v>
+        <v>46355.32291666666</v>
       </c>
     </row>
     <row r="570">
@@ -31709,13 +31709,13 @@
         </is>
       </c>
       <c r="K570" s="1" t="n">
-        <v>46360.44791666666</v>
+        <v>46360.53125</v>
       </c>
       <c r="L570" s="1" t="n">
-        <v>46360.48958333334</v>
+        <v>46360.57291666666</v>
       </c>
       <c r="M570" s="1" t="n">
-        <v>46361.15625</v>
+        <v>46361.23958333334</v>
       </c>
     </row>
     <row r="571">
@@ -31764,13 +31764,13 @@
         </is>
       </c>
       <c r="K571" s="1" t="n">
-        <v>46361.32291666666</v>
+        <v>46361.40625</v>
       </c>
       <c r="L571" s="1" t="n">
-        <v>46361.38541666666</v>
+        <v>46361.46875</v>
       </c>
       <c r="M571" s="1" t="n">
-        <v>46361.63541666666</v>
+        <v>46361.71875</v>
       </c>
     </row>
     <row r="572">
@@ -31819,13 +31819,13 @@
         </is>
       </c>
       <c r="K572" s="1" t="n">
-        <v>46362.53125</v>
+        <v>46362.61458333334</v>
       </c>
       <c r="L572" s="1" t="n">
-        <v>46362.59375</v>
+        <v>46362.67708333334</v>
       </c>
       <c r="M572" s="1" t="n">
-        <v>46363.01041666666</v>
+        <v>46363.09375</v>
       </c>
     </row>
     <row r="573">
@@ -31874,13 +31874,13 @@
         </is>
       </c>
       <c r="K573" s="1" t="n">
-        <v>46363.28125</v>
+        <v>46363.36458333334</v>
       </c>
       <c r="L573" s="1" t="n">
-        <v>46363.30208333334</v>
+        <v>46363.38541666666</v>
       </c>
       <c r="M573" s="1" t="n">
-        <v>46363.90625</v>
+        <v>46363.98958333334</v>
       </c>
     </row>
     <row r="574">
@@ -31929,13 +31929,13 @@
         </is>
       </c>
       <c r="K574" s="1" t="n">
-        <v>46368.82291666666</v>
+        <v>46368.90625</v>
       </c>
       <c r="L574" s="1" t="n">
-        <v>46368.98958333334</v>
+        <v>46369.07291666666</v>
       </c>
       <c r="M574" s="1" t="n">
-        <v>46369.57291666666</v>
+        <v>46369.65625</v>
       </c>
     </row>
     <row r="575">
@@ -31984,13 +31984,13 @@
         </is>
       </c>
       <c r="K575" s="1" t="n">
-        <v>46371.21875</v>
+        <v>46371.30208333334</v>
       </c>
       <c r="L575" s="1" t="n">
-        <v>46371.26041666666</v>
+        <v>46371.34375</v>
       </c>
       <c r="M575" s="1" t="n">
-        <v>46371.61458333334</v>
+        <v>46371.69791666666</v>
       </c>
     </row>
     <row r="576">
@@ -32039,13 +32039,13 @@
         </is>
       </c>
       <c r="K576" s="1" t="n">
-        <v>46371.73958333334</v>
+        <v>46371.82291666666</v>
       </c>
       <c r="L576" s="1" t="n">
-        <v>46371.82291666666</v>
+        <v>46371.90625</v>
       </c>
       <c r="M576" s="1" t="n">
-        <v>46372.82291666666</v>
+        <v>46372.90625</v>
       </c>
     </row>
     <row r="577">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="K577" s="1" t="n">
-        <v>46373.03125</v>
+        <v>46373.11458333334</v>
       </c>
       <c r="L577" s="1" t="n">
-        <v>46373.07291666666</v>
+        <v>46373.15625</v>
       </c>
       <c r="M577" s="1" t="n">
-        <v>46373.57291666666</v>
+        <v>46373.65625</v>
       </c>
     </row>
     <row r="578">
@@ -32149,13 +32149,13 @@
         </is>
       </c>
       <c r="K578" s="1" t="n">
-        <v>46375.38541666666</v>
+        <v>46375.46875</v>
       </c>
       <c r="L578" s="1" t="n">
-        <v>46375.55208333334</v>
+        <v>46375.63541666666</v>
       </c>
       <c r="M578" s="1" t="n">
-        <v>46376.23958333334</v>
+        <v>46376.32291666666</v>
       </c>
     </row>
     <row r="579">
@@ -33141,7 +33141,7 @@
         <v>46304.75</v>
       </c>
       <c r="M596" s="1" t="n">
-        <v>46306.25</v>
+        <v>46306.28333333333</v>
       </c>
     </row>
     <row r="597">
@@ -33190,13 +33190,13 @@
         </is>
       </c>
       <c r="K597" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="L597" s="1" t="n">
-        <v>46310.95833333334</v>
+        <v>46311.125</v>
       </c>
       <c r="M597" s="1" t="n">
-        <v>46311.70833333334</v>
+        <v>46311.95833333334</v>
       </c>
     </row>
     <row r="598">
@@ -33245,13 +33245,13 @@
         </is>
       </c>
       <c r="K598" s="1" t="n">
-        <v>46313.54166666666</v>
+        <v>46313.58333333334</v>
       </c>
       <c r="L598" s="1" t="n">
-        <v>46313.58333333334</v>
+        <v>46313.625</v>
       </c>
       <c r="M598" s="1" t="n">
-        <v>46314</v>
+        <v>46314.04166666666</v>
       </c>
     </row>
     <row r="599">
@@ -33300,13 +33300,13 @@
         </is>
       </c>
       <c r="K599" s="1" t="n">
-        <v>46314.125</v>
+        <v>46314.16666666666</v>
       </c>
       <c r="L599" s="1" t="n">
-        <v>46314.20833333334</v>
+        <v>46314.25</v>
       </c>
       <c r="M599" s="1" t="n">
-        <v>46315.08333333334</v>
+        <v>46315.125</v>
       </c>
     </row>
     <row r="600">
@@ -33355,13 +33355,13 @@
         </is>
       </c>
       <c r="K600" s="1" t="n">
-        <v>46315.25</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="L600" s="1" t="n">
-        <v>46315.29166666666</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="M600" s="1" t="n">
-        <v>46315.79166666666</v>
+        <v>46315.83333333334</v>
       </c>
     </row>
     <row r="601">
@@ -33410,13 +33410,13 @@
         </is>
       </c>
       <c r="K601" s="1" t="n">
-        <v>46317.25</v>
+        <v>46317.20833333334</v>
       </c>
       <c r="L601" s="1" t="n">
-        <v>46317.41666666666</v>
+        <v>46317.375</v>
       </c>
       <c r="M601" s="1" t="n">
-        <v>46318.08333333334</v>
+        <v>46318.04166666666</v>
       </c>
     </row>
     <row r="602">
@@ -35337,7 +35337,7 @@
         <v>46306.375</v>
       </c>
       <c r="M636" s="1" t="n">
-        <v>46306.75</v>
+        <v>46307.20833333334</v>
       </c>
     </row>
     <row r="637">
@@ -35386,13 +35386,13 @@
         </is>
       </c>
       <c r="K637" s="1" t="n">
-        <v>46310.625</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="L637" s="1" t="n">
-        <v>46310.66666666666</v>
+        <v>46311.5</v>
       </c>
       <c r="M637" s="1" t="n">
-        <v>46311.08333333334</v>
+        <v>46311.91666666666</v>
       </c>
     </row>
     <row r="638">
@@ -35441,13 +35441,13 @@
         </is>
       </c>
       <c r="K638" s="1" t="n">
-        <v>46311.33333333334</v>
+        <v>46312.16666666666</v>
       </c>
       <c r="L638" s="1" t="n">
-        <v>46311.33333333334</v>
+        <v>46312.16666666666</v>
       </c>
       <c r="M638" s="1" t="n">
-        <v>46311.70833333334</v>
+        <v>46312.54166666666</v>
       </c>
     </row>
     <row r="639">
@@ -35496,13 +35496,13 @@
         </is>
       </c>
       <c r="K639" s="1" t="n">
-        <v>46313.04166666666</v>
+        <v>46313.875</v>
       </c>
       <c r="L639" s="1" t="n">
-        <v>46313.04166666666</v>
+        <v>46313.875</v>
       </c>
       <c r="M639" s="1" t="n">
-        <v>46313.29166666666</v>
+        <v>46314.125</v>
       </c>
     </row>
     <row r="640">
@@ -35551,13 +35551,13 @@
         </is>
       </c>
       <c r="K640" s="1" t="n">
-        <v>46315.25</v>
+        <v>46316.125</v>
       </c>
       <c r="L640" s="1" t="n">
-        <v>46315.29166666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="M640" s="1" t="n">
-        <v>46316</v>
+        <v>46316.875</v>
       </c>
     </row>
     <row r="641">
@@ -35606,13 +35606,13 @@
         </is>
       </c>
       <c r="K641" s="1" t="n">
-        <v>46316.20833333334</v>
+        <v>46317.08333333334</v>
       </c>
       <c r="L641" s="1" t="n">
-        <v>46316.25</v>
+        <v>46317.125</v>
       </c>
       <c r="M641" s="1" t="n">
-        <v>46316.58333333334</v>
+        <v>46317.45833333334</v>
       </c>
     </row>
     <row r="642">
@@ -35661,13 +35661,13 @@
         </is>
       </c>
       <c r="K642" s="1" t="n">
-        <v>46319.83333333334</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="L642" s="1" t="n">
-        <v>46319.875</v>
+        <v>46320.75</v>
       </c>
       <c r="M642" s="1" t="n">
-        <v>46320.25</v>
+        <v>46321.125</v>
       </c>
     </row>
     <row r="643">
@@ -35716,13 +35716,13 @@
         </is>
       </c>
       <c r="K643" s="1" t="n">
-        <v>46322.70833333334</v>
+        <v>46323.58333333334</v>
       </c>
       <c r="L643" s="1" t="n">
-        <v>46322.875</v>
+        <v>46323.75</v>
       </c>
       <c r="M643" s="1" t="n">
-        <v>46323.41666666666</v>
+        <v>46324.29166666666</v>
       </c>
     </row>
     <row r="644">
@@ -35771,13 +35771,13 @@
         </is>
       </c>
       <c r="K644" s="1" t="n">
-        <v>46325.20833333334</v>
+        <v>46326.08333333334</v>
       </c>
       <c r="L644" s="1" t="n">
-        <v>46325.25</v>
+        <v>46326.125</v>
       </c>
       <c r="M644" s="1" t="n">
-        <v>46325.5</v>
+        <v>46326.375</v>
       </c>
     </row>
     <row r="645">
@@ -35826,13 +35826,13 @@
         </is>
       </c>
       <c r="K645" s="1" t="n">
-        <v>46325.91666666666</v>
+        <v>46326.79166666666</v>
       </c>
       <c r="L645" s="1" t="n">
-        <v>46326.04166666666</v>
+        <v>46326.91666666666</v>
       </c>
       <c r="M645" s="1" t="n">
-        <v>46327.16666666666</v>
+        <v>46328.04166666666</v>
       </c>
     </row>
     <row r="646">
@@ -35881,13 +35881,13 @@
         </is>
       </c>
       <c r="K646" s="1" t="n">
-        <v>46327.5</v>
+        <v>46328.375</v>
       </c>
       <c r="L646" s="1" t="n">
-        <v>46327.54166666666</v>
+        <v>46328.41666666666</v>
       </c>
       <c r="M646" s="1" t="n">
-        <v>46327.875</v>
+        <v>46328.75</v>
       </c>
     </row>
     <row r="647">
@@ -35936,13 +35936,13 @@
         </is>
       </c>
       <c r="K647" s="1" t="n">
-        <v>46331.75</v>
+        <v>46332.625</v>
       </c>
       <c r="L647" s="1" t="n">
-        <v>46331.79166666666</v>
+        <v>46332.66666666666</v>
       </c>
       <c r="M647" s="1" t="n">
-        <v>46332.20833333334</v>
+        <v>46333.08333333334</v>
       </c>
     </row>
     <row r="648">
@@ -35991,13 +35991,13 @@
         </is>
       </c>
       <c r="K648" s="1" t="n">
-        <v>46332.45833333334</v>
+        <v>46333.33333333334</v>
       </c>
       <c r="L648" s="1" t="n">
-        <v>46332.45833333334</v>
+        <v>46333.33333333334</v>
       </c>
       <c r="M648" s="1" t="n">
-        <v>46332.83333333334</v>
+        <v>46333.70833333334</v>
       </c>
     </row>
     <row r="649">
@@ -36046,13 +36046,13 @@
         </is>
       </c>
       <c r="K649" s="1" t="n">
-        <v>46334.08333333334</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="L649" s="1" t="n">
-        <v>46334.08333333334</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="M649" s="1" t="n">
-        <v>46334.33333333334</v>
+        <v>46335.20833333334</v>
       </c>
     </row>
     <row r="650">
@@ -36101,13 +36101,13 @@
         </is>
       </c>
       <c r="K650" s="1" t="n">
-        <v>46336.33333333334</v>
+        <v>46337.20833333334</v>
       </c>
       <c r="L650" s="1" t="n">
-        <v>46336.375</v>
+        <v>46337.25</v>
       </c>
       <c r="M650" s="1" t="n">
-        <v>46337.08333333334</v>
+        <v>46337.95833333334</v>
       </c>
     </row>
     <row r="651">
@@ -36156,13 +36156,13 @@
         </is>
       </c>
       <c r="K651" s="1" t="n">
-        <v>46337.29166666666</v>
+        <v>46338.16666666666</v>
       </c>
       <c r="L651" s="1" t="n">
-        <v>46337.33333333334</v>
+        <v>46338.20833333334</v>
       </c>
       <c r="M651" s="1" t="n">
-        <v>46337.66666666666</v>
+        <v>46338.54166666666</v>
       </c>
     </row>
     <row r="652">
@@ -36211,13 +36211,13 @@
         </is>
       </c>
       <c r="K652" s="1" t="n">
-        <v>46340.5</v>
+        <v>46341.375</v>
       </c>
       <c r="L652" s="1" t="n">
-        <v>46340.54166666666</v>
+        <v>46341.41666666666</v>
       </c>
       <c r="M652" s="1" t="n">
-        <v>46340.91666666666</v>
+        <v>46341.79166666666</v>
       </c>
     </row>
     <row r="653">
@@ -36266,13 +36266,13 @@
         </is>
       </c>
       <c r="K653" s="1" t="n">
-        <v>46343.375</v>
+        <v>46344.25</v>
       </c>
       <c r="L653" s="1" t="n">
-        <v>46343.54166666666</v>
+        <v>46344.41666666666</v>
       </c>
       <c r="M653" s="1" t="n">
-        <v>46344.08333333334</v>
+        <v>46344.95833333334</v>
       </c>
     </row>
     <row r="654">
@@ -36321,13 +36321,13 @@
         </is>
       </c>
       <c r="K654" s="1" t="n">
-        <v>46345.875</v>
+        <v>46346.75</v>
       </c>
       <c r="L654" s="1" t="n">
-        <v>46345.91666666666</v>
+        <v>46346.79166666666</v>
       </c>
       <c r="M654" s="1" t="n">
-        <v>46346.16666666666</v>
+        <v>46347.04166666666</v>
       </c>
     </row>
     <row r="655">
@@ -36376,13 +36376,13 @@
         </is>
       </c>
       <c r="K655" s="1" t="n">
-        <v>46346.58333333334</v>
+        <v>46347.45833333334</v>
       </c>
       <c r="L655" s="1" t="n">
-        <v>46346.70833333334</v>
+        <v>46347.58333333334</v>
       </c>
       <c r="M655" s="1" t="n">
-        <v>46347.83333333334</v>
+        <v>46348.70833333334</v>
       </c>
     </row>
     <row r="656">
@@ -36431,13 +36431,13 @@
         </is>
       </c>
       <c r="K656" s="1" t="n">
-        <v>46348.16666666666</v>
+        <v>46349.04166666666</v>
       </c>
       <c r="L656" s="1" t="n">
-        <v>46348.20833333334</v>
+        <v>46349.08333333334</v>
       </c>
       <c r="M656" s="1" t="n">
-        <v>46348.54166666666</v>
+        <v>46349.41666666666</v>
       </c>
     </row>
     <row r="657">
@@ -36486,13 +36486,13 @@
         </is>
       </c>
       <c r="K657" s="1" t="n">
-        <v>46352.41666666666</v>
+        <v>46353.29166666666</v>
       </c>
       <c r="L657" s="1" t="n">
-        <v>46352.45833333334</v>
+        <v>46353.33333333334</v>
       </c>
       <c r="M657" s="1" t="n">
-        <v>46352.875</v>
+        <v>46353.75</v>
       </c>
     </row>
     <row r="658">
@@ -36541,13 +36541,13 @@
         </is>
       </c>
       <c r="K658" s="1" t="n">
-        <v>46353.125</v>
+        <v>46354</v>
       </c>
       <c r="L658" s="1" t="n">
-        <v>46353.125</v>
+        <v>46354</v>
       </c>
       <c r="M658" s="1" t="n">
-        <v>46353.5</v>
+        <v>46354.375</v>
       </c>
     </row>
     <row r="659">
@@ -36596,13 +36596,13 @@
         </is>
       </c>
       <c r="K659" s="1" t="n">
-        <v>46354.75</v>
+        <v>46355.625</v>
       </c>
       <c r="L659" s="1" t="n">
-        <v>46354.75</v>
+        <v>46355.625</v>
       </c>
       <c r="M659" s="1" t="n">
-        <v>46355</v>
+        <v>46355.875</v>
       </c>
     </row>
     <row r="660">
@@ -36651,13 +36651,13 @@
         </is>
       </c>
       <c r="K660" s="1" t="n">
-        <v>46357.33333333334</v>
+        <v>46358.20833333334</v>
       </c>
       <c r="L660" s="1" t="n">
-        <v>46357.375</v>
+        <v>46358.25</v>
       </c>
       <c r="M660" s="1" t="n">
-        <v>46358.08333333334</v>
+        <v>46358.95833333334</v>
       </c>
     </row>
     <row r="661">
@@ -36706,13 +36706,13 @@
         </is>
       </c>
       <c r="K661" s="1" t="n">
-        <v>46358.29166666666</v>
+        <v>46359.16666666666</v>
       </c>
       <c r="L661" s="1" t="n">
-        <v>46358.33333333334</v>
+        <v>46359.20833333334</v>
       </c>
       <c r="M661" s="1" t="n">
-        <v>46358.66666666666</v>
+        <v>46359.54166666666</v>
       </c>
     </row>
     <row r="662">
@@ -36761,13 +36761,13 @@
         </is>
       </c>
       <c r="K662" s="1" t="n">
-        <v>46361.5</v>
+        <v>46362.375</v>
       </c>
       <c r="L662" s="1" t="n">
-        <v>46361.54166666666</v>
+        <v>46362.41666666666</v>
       </c>
       <c r="M662" s="1" t="n">
-        <v>46361.91666666666</v>
+        <v>46362.79166666666</v>
       </c>
     </row>
     <row r="663">
@@ -36816,13 +36816,13 @@
         </is>
       </c>
       <c r="K663" s="1" t="n">
-        <v>46364.375</v>
+        <v>46365.25</v>
       </c>
       <c r="L663" s="1" t="n">
-        <v>46364.54166666666</v>
+        <v>46365.41666666666</v>
       </c>
       <c r="M663" s="1" t="n">
-        <v>46365.08333333334</v>
+        <v>46365.95833333334</v>
       </c>
     </row>
     <row r="664">
@@ -36871,13 +36871,13 @@
         </is>
       </c>
       <c r="K664" s="1" t="n">
-        <v>46366.875</v>
+        <v>46367.75</v>
       </c>
       <c r="L664" s="1" t="n">
-        <v>46366.91666666666</v>
+        <v>46367.79166666666</v>
       </c>
       <c r="M664" s="1" t="n">
-        <v>46367.16666666666</v>
+        <v>46368.04166666666</v>
       </c>
     </row>
     <row r="665">
@@ -36926,13 +36926,13 @@
         </is>
       </c>
       <c r="K665" s="1" t="n">
-        <v>46367.58333333334</v>
+        <v>46368.45833333334</v>
       </c>
       <c r="L665" s="1" t="n">
-        <v>46367.70833333334</v>
+        <v>46368.58333333334</v>
       </c>
       <c r="M665" s="1" t="n">
-        <v>46368.83333333334</v>
+        <v>46369.70833333334</v>
       </c>
     </row>
     <row r="666">
@@ -36981,13 +36981,13 @@
         </is>
       </c>
       <c r="K666" s="1" t="n">
-        <v>46369.16666666666</v>
+        <v>46370.04166666666</v>
       </c>
       <c r="L666" s="1" t="n">
-        <v>46369.20833333334</v>
+        <v>46370.08333333334</v>
       </c>
       <c r="M666" s="1" t="n">
-        <v>46369.54166666666</v>
+        <v>46370.41666666666</v>
       </c>
     </row>
     <row r="667">
@@ -37036,13 +37036,13 @@
         </is>
       </c>
       <c r="K667" s="1" t="n">
-        <v>46373.41666666666</v>
+        <v>46374.29166666666</v>
       </c>
       <c r="L667" s="1" t="n">
-        <v>46373.45833333334</v>
+        <v>46374.33333333334</v>
       </c>
       <c r="M667" s="1" t="n">
-        <v>46373.875</v>
+        <v>46374.75</v>
       </c>
     </row>
     <row r="668">
@@ -37091,13 +37091,13 @@
         </is>
       </c>
       <c r="K668" s="1" t="n">
-        <v>46374.125</v>
+        <v>46375</v>
       </c>
       <c r="L668" s="1" t="n">
-        <v>46374.125</v>
+        <v>46375</v>
       </c>
       <c r="M668" s="1" t="n">
-        <v>46374.5</v>
+        <v>46375.375</v>
       </c>
     </row>
     <row r="669">
@@ -37146,13 +37146,13 @@
         </is>
       </c>
       <c r="K669" s="1" t="n">
-        <v>46375.75</v>
+        <v>46376.625</v>
       </c>
       <c r="L669" s="1" t="n">
-        <v>46375.75</v>
+        <v>46376.625</v>
       </c>
       <c r="M669" s="1" t="n">
-        <v>46376</v>
+        <v>46376.875</v>
       </c>
     </row>
     <row r="670">
@@ -37201,13 +37201,13 @@
         </is>
       </c>
       <c r="K670" s="1" t="n">
-        <v>46378.33333333334</v>
+        <v>46379.20833333334</v>
       </c>
       <c r="L670" s="1" t="n">
-        <v>46378.375</v>
+        <v>46379.25</v>
       </c>
       <c r="M670" s="1" t="n">
-        <v>46379.08333333334</v>
+        <v>46379.95833333334</v>
       </c>
     </row>
     <row r="671">
@@ -37256,13 +37256,13 @@
         </is>
       </c>
       <c r="K671" s="1" t="n">
-        <v>46379.29166666666</v>
+        <v>46380.16666666666</v>
       </c>
       <c r="L671" s="1" t="n">
-        <v>46379.33333333334</v>
+        <v>46380.20833333334</v>
       </c>
       <c r="M671" s="1" t="n">
-        <v>46379.66666666666</v>
+        <v>46380.54166666666</v>
       </c>
     </row>
     <row r="672">
@@ -37311,13 +37311,13 @@
         </is>
       </c>
       <c r="K672" s="1" t="n">
-        <v>46382.5</v>
+        <v>46383.375</v>
       </c>
       <c r="L672" s="1" t="n">
-        <v>46382.54166666666</v>
+        <v>46383.41666666666</v>
       </c>
       <c r="M672" s="1" t="n">
-        <v>46382.91666666666</v>
+        <v>46383.79166666666</v>
       </c>
     </row>
     <row r="673">
@@ -37366,13 +37366,13 @@
         </is>
       </c>
       <c r="K673" s="1" t="n">
-        <v>46385.375</v>
+        <v>46386.25</v>
       </c>
       <c r="L673" s="1" t="n">
-        <v>46385.54166666666</v>
+        <v>46386.41666666666</v>
       </c>
       <c r="M673" s="1" t="n">
-        <v>46386.08333333334</v>
+        <v>46386.95833333334</v>
       </c>
     </row>
     <row r="674">
@@ -37421,13 +37421,13 @@
         </is>
       </c>
       <c r="K674" s="1" t="n">
-        <v>46387.875</v>
+        <v>46388.75</v>
       </c>
       <c r="L674" s="1" t="n">
-        <v>46387.91666666666</v>
+        <v>46388.79166666666</v>
       </c>
       <c r="M674" s="1" t="n">
-        <v>46388.16666666666</v>
+        <v>46389.04166666666</v>
       </c>
     </row>
     <row r="675">
@@ -37476,13 +37476,13 @@
         </is>
       </c>
       <c r="K675" s="1" t="n">
-        <v>46388.58333333334</v>
+        <v>46389.45833333334</v>
       </c>
       <c r="L675" s="1" t="n">
-        <v>46388.70833333334</v>
+        <v>46389.58333333334</v>
       </c>
       <c r="M675" s="1" t="n">
-        <v>46389.83333333334</v>
+        <v>46390.70833333334</v>
       </c>
     </row>
     <row r="676">
@@ -37531,13 +37531,13 @@
         </is>
       </c>
       <c r="K676" s="1" t="n">
-        <v>46390.16666666666</v>
+        <v>46391.04166666666</v>
       </c>
       <c r="L676" s="1" t="n">
-        <v>46390.20833333334</v>
+        <v>46391.08333333334</v>
       </c>
       <c r="M676" s="1" t="n">
-        <v>46390.54166666666</v>
+        <v>46391.41666666666</v>
       </c>
     </row>
     <row r="677">
@@ -37586,13 +37586,13 @@
         </is>
       </c>
       <c r="K677" s="1" t="n">
-        <v>46394.41666666666</v>
+        <v>46395.29166666666</v>
       </c>
       <c r="L677" s="1" t="n">
-        <v>46394.45833333334</v>
+        <v>46395.33333333334</v>
       </c>
       <c r="M677" s="1" t="n">
-        <v>46394.875</v>
+        <v>46395.75</v>
       </c>
     </row>
     <row r="678">
@@ -37641,13 +37641,13 @@
         </is>
       </c>
       <c r="K678" s="1" t="n">
-        <v>46395.125</v>
+        <v>46396</v>
       </c>
       <c r="L678" s="1" t="n">
-        <v>46395.125</v>
+        <v>46396</v>
       </c>
       <c r="M678" s="1" t="n">
-        <v>46395.5</v>
+        <v>46396.375</v>
       </c>
     </row>
     <row r="679">
@@ -37692,13 +37692,13 @@
       </c>
       <c r="J679" t="inlineStr"/>
       <c r="K679" s="1" t="n">
-        <v>46396.75</v>
+        <v>46397.625</v>
       </c>
       <c r="L679" s="1" t="n">
-        <v>46396.75</v>
+        <v>46397.625</v>
       </c>
       <c r="M679" s="1" t="n">
-        <v>46397</v>
+        <v>46397.875</v>
       </c>
     </row>
     <row r="680">
@@ -40059,7 +40059,7 @@
         <v>46307</v>
       </c>
       <c r="M722" s="1" t="n">
-        <v>46307.45833333334</v>
+        <v>46307.97916666666</v>
       </c>
     </row>
     <row r="723">
@@ -40108,13 +40108,13 @@
         </is>
       </c>
       <c r="K723" s="1" t="n">
-        <v>46308.41666666666</v>
+        <v>46308.75</v>
       </c>
       <c r="L723" s="1" t="n">
-        <v>46308.41666666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="M723" s="1" t="n">
-        <v>46308.875</v>
+        <v>46309.25</v>
       </c>
     </row>
     <row r="724">
@@ -40163,13 +40163,13 @@
         </is>
       </c>
       <c r="K724" s="1" t="n">
-        <v>46311.45833333334</v>
+        <v>46311.75</v>
       </c>
       <c r="L724" s="1" t="n">
-        <v>46311.5</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="M724" s="1" t="n">
-        <v>46312.125</v>
+        <v>46312.41666666666</v>
       </c>
     </row>
     <row r="725">
@@ -40218,13 +40218,13 @@
         </is>
       </c>
       <c r="K725" s="1" t="n">
-        <v>46313.125</v>
+        <v>46313.41666666666</v>
       </c>
       <c r="L725" s="1" t="n">
-        <v>46313.16666666666</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="M725" s="1" t="n">
-        <v>46313.66666666666</v>
+        <v>46313.95833333334</v>
       </c>
     </row>
     <row r="726">
@@ -40273,13 +40273,13 @@
         </is>
       </c>
       <c r="K726" s="1" t="n">
-        <v>46314.75</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="L726" s="1" t="n">
-        <v>46314.91666666666</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="M726" s="1" t="n">
-        <v>46315.70833333334</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="727">
@@ -40328,13 +40328,13 @@
         </is>
       </c>
       <c r="K727" s="1" t="n">
-        <v>46321.45833333334</v>
+        <v>46321.75</v>
       </c>
       <c r="L727" s="1" t="n">
-        <v>46321.5</v>
+        <v>46321.79166666666</v>
       </c>
       <c r="M727" s="1" t="n">
-        <v>46321.79166666666</v>
+        <v>46322.08333333334</v>
       </c>
     </row>
     <row r="728">
@@ -40383,13 +40383,13 @@
         </is>
       </c>
       <c r="K728" s="1" t="n">
-        <v>46322.08333333334</v>
+        <v>46322.375</v>
       </c>
       <c r="L728" s="1" t="n">
-        <v>46322.08333333334</v>
+        <v>46322.375</v>
       </c>
       <c r="M728" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46323.75</v>
       </c>
     </row>
     <row r="729">
@@ -40438,13 +40438,13 @@
         </is>
       </c>
       <c r="K729" s="1" t="n">
-        <v>46323.70833333334</v>
+        <v>46324</v>
       </c>
       <c r="L729" s="1" t="n">
-        <v>46323.75</v>
+        <v>46324.04166666666</v>
       </c>
       <c r="M729" s="1" t="n">
-        <v>46324.20833333334</v>
+        <v>46324.5</v>
       </c>
     </row>
     <row r="730">
@@ -40493,13 +40493,13 @@
         </is>
       </c>
       <c r="K730" s="1" t="n">
-        <v>46328.04166666666</v>
+        <v>46328.33333333334</v>
       </c>
       <c r="L730" s="1" t="n">
-        <v>46328.04166666666</v>
+        <v>46328.33333333334</v>
       </c>
       <c r="M730" s="1" t="n">
-        <v>46328.5</v>
+        <v>46328.79166666666</v>
       </c>
     </row>
     <row r="731">
@@ -40548,13 +40548,13 @@
         </is>
       </c>
       <c r="K731" s="1" t="n">
-        <v>46329.5</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="L731" s="1" t="n">
-        <v>46329.5</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="M731" s="1" t="n">
-        <v>46330</v>
+        <v>46330.29166666666</v>
       </c>
     </row>
     <row r="732">
@@ -40603,13 +40603,13 @@
         </is>
       </c>
       <c r="K732" s="1" t="n">
-        <v>46332.29166666666</v>
+        <v>46332.58333333334</v>
       </c>
       <c r="L732" s="1" t="n">
-        <v>46332.33333333334</v>
+        <v>46332.625</v>
       </c>
       <c r="M732" s="1" t="n">
-        <v>46332.95833333334</v>
+        <v>46333.25</v>
       </c>
     </row>
     <row r="733">
@@ -40658,13 +40658,13 @@
         </is>
       </c>
       <c r="K733" s="1" t="n">
-        <v>46333.95833333334</v>
+        <v>46334.25</v>
       </c>
       <c r="L733" s="1" t="n">
-        <v>46334</v>
+        <v>46334.29166666666</v>
       </c>
       <c r="M733" s="1" t="n">
-        <v>46334.5</v>
+        <v>46334.79166666666</v>
       </c>
     </row>
     <row r="734">
@@ -40713,13 +40713,13 @@
         </is>
       </c>
       <c r="K734" s="1" t="n">
-        <v>46335.58333333334</v>
+        <v>46335.875</v>
       </c>
       <c r="L734" s="1" t="n">
-        <v>46335.75</v>
+        <v>46336.04166666666</v>
       </c>
       <c r="M734" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46336.83333333334</v>
       </c>
     </row>
     <row r="735">
@@ -40768,13 +40768,13 @@
         </is>
       </c>
       <c r="K735" s="1" t="n">
-        <v>46342.29166666666</v>
+        <v>46342.58333333334</v>
       </c>
       <c r="L735" s="1" t="n">
-        <v>46342.33333333334</v>
+        <v>46342.625</v>
       </c>
       <c r="M735" s="1" t="n">
-        <v>46342.625</v>
+        <v>46342.91666666666</v>
       </c>
     </row>
     <row r="736">
@@ -40823,13 +40823,13 @@
         </is>
       </c>
       <c r="K736" s="1" t="n">
-        <v>46342.91666666666</v>
+        <v>46343.20833333334</v>
       </c>
       <c r="L736" s="1" t="n">
-        <v>46342.91666666666</v>
+        <v>46343.20833333334</v>
       </c>
       <c r="M736" s="1" t="n">
-        <v>46344.29166666666</v>
+        <v>46344.58333333334</v>
       </c>
     </row>
     <row r="737">
@@ -40878,13 +40878,13 @@
         </is>
       </c>
       <c r="K737" s="1" t="n">
-        <v>46344.54166666666</v>
+        <v>46344.83333333334</v>
       </c>
       <c r="L737" s="1" t="n">
-        <v>46344.58333333334</v>
+        <v>46344.875</v>
       </c>
       <c r="M737" s="1" t="n">
-        <v>46345.04166666666</v>
+        <v>46345.33333333334</v>
       </c>
     </row>
     <row r="738">
@@ -40933,13 +40933,13 @@
         </is>
       </c>
       <c r="K738" s="1" t="n">
-        <v>46348.875</v>
+        <v>46349.16666666666</v>
       </c>
       <c r="L738" s="1" t="n">
-        <v>46348.875</v>
+        <v>46349.16666666666</v>
       </c>
       <c r="M738" s="1" t="n">
-        <v>46349.33333333334</v>
+        <v>46349.625</v>
       </c>
     </row>
     <row r="739">
@@ -40988,13 +40988,13 @@
         </is>
       </c>
       <c r="K739" s="1" t="n">
-        <v>46350.33333333334</v>
+        <v>46350.625</v>
       </c>
       <c r="L739" s="1" t="n">
-        <v>46350.33333333334</v>
+        <v>46350.625</v>
       </c>
       <c r="M739" s="1" t="n">
-        <v>46350.83333333334</v>
+        <v>46351.125</v>
       </c>
     </row>
     <row r="740">
@@ -41043,13 +41043,13 @@
         </is>
       </c>
       <c r="K740" s="1" t="n">
-        <v>46353.29166666666</v>
+        <v>46353.58333333334</v>
       </c>
       <c r="L740" s="1" t="n">
-        <v>46353.33333333334</v>
+        <v>46353.625</v>
       </c>
       <c r="M740" s="1" t="n">
-        <v>46353.95833333334</v>
+        <v>46354.25</v>
       </c>
     </row>
     <row r="741">
@@ -41098,13 +41098,13 @@
         </is>
       </c>
       <c r="K741" s="1" t="n">
-        <v>46354.95833333334</v>
+        <v>46355.25</v>
       </c>
       <c r="L741" s="1" t="n">
-        <v>46355</v>
+        <v>46355.29166666666</v>
       </c>
       <c r="M741" s="1" t="n">
-        <v>46355.5</v>
+        <v>46355.79166666666</v>
       </c>
     </row>
     <row r="742">
@@ -41153,13 +41153,13 @@
         </is>
       </c>
       <c r="K742" s="1" t="n">
-        <v>46356.58333333334</v>
+        <v>46356.875</v>
       </c>
       <c r="L742" s="1" t="n">
-        <v>46356.75</v>
+        <v>46357.04166666666</v>
       </c>
       <c r="M742" s="1" t="n">
-        <v>46357.54166666666</v>
+        <v>46357.83333333334</v>
       </c>
     </row>
     <row r="743">
@@ -41208,13 +41208,13 @@
         </is>
       </c>
       <c r="K743" s="1" t="n">
-        <v>46363.29166666666</v>
+        <v>46363.58333333334</v>
       </c>
       <c r="L743" s="1" t="n">
-        <v>46363.33333333334</v>
+        <v>46363.625</v>
       </c>
       <c r="M743" s="1" t="n">
-        <v>46363.625</v>
+        <v>46363.91666666666</v>
       </c>
     </row>
     <row r="744">
@@ -41263,13 +41263,13 @@
         </is>
       </c>
       <c r="K744" s="1" t="n">
-        <v>46363.91666666666</v>
+        <v>46364.20833333334</v>
       </c>
       <c r="L744" s="1" t="n">
-        <v>46363.91666666666</v>
+        <v>46364.20833333334</v>
       </c>
       <c r="M744" s="1" t="n">
-        <v>46365.29166666666</v>
+        <v>46365.58333333334</v>
       </c>
     </row>
     <row r="745">
@@ -41318,13 +41318,13 @@
         </is>
       </c>
       <c r="K745" s="1" t="n">
-        <v>46365.54166666666</v>
+        <v>46365.83333333334</v>
       </c>
       <c r="L745" s="1" t="n">
-        <v>46365.58333333334</v>
+        <v>46365.875</v>
       </c>
       <c r="M745" s="1" t="n">
-        <v>46366.04166666666</v>
+        <v>46366.33333333334</v>
       </c>
     </row>
     <row r="746">
@@ -41373,13 +41373,13 @@
         </is>
       </c>
       <c r="K746" s="1" t="n">
-        <v>46369.875</v>
+        <v>46370.16666666666</v>
       </c>
       <c r="L746" s="1" t="n">
-        <v>46369.875</v>
+        <v>46370.16666666666</v>
       </c>
       <c r="M746" s="1" t="n">
-        <v>46370.33333333334</v>
+        <v>46370.625</v>
       </c>
     </row>
     <row r="747">
@@ -41428,13 +41428,13 @@
         </is>
       </c>
       <c r="K747" s="1" t="n">
-        <v>46371.33333333334</v>
+        <v>46371.625</v>
       </c>
       <c r="L747" s="1" t="n">
-        <v>46371.33333333334</v>
+        <v>46371.625</v>
       </c>
       <c r="M747" s="1" t="n">
-        <v>46371.83333333334</v>
+        <v>46372.125</v>
       </c>
     </row>
     <row r="748">
@@ -41483,13 +41483,13 @@
         </is>
       </c>
       <c r="K748" s="1" t="n">
-        <v>46374.29166666666</v>
+        <v>46374.58333333334</v>
       </c>
       <c r="L748" s="1" t="n">
-        <v>46374.33333333334</v>
+        <v>46374.625</v>
       </c>
       <c r="M748" s="1" t="n">
-        <v>46374.95833333334</v>
+        <v>46375.25</v>
       </c>
     </row>
     <row r="749">
@@ -41538,13 +41538,13 @@
         </is>
       </c>
       <c r="K749" s="1" t="n">
-        <v>46375.95833333334</v>
+        <v>46376.25</v>
       </c>
       <c r="L749" s="1" t="n">
-        <v>46376</v>
+        <v>46376.29166666666</v>
       </c>
       <c r="M749" s="1" t="n">
-        <v>46376.5</v>
+        <v>46376.79166666666</v>
       </c>
     </row>
     <row r="750">
@@ -41593,13 +41593,13 @@
         </is>
       </c>
       <c r="K750" s="1" t="n">
-        <v>46377.58333333334</v>
+        <v>46377.875</v>
       </c>
       <c r="L750" s="1" t="n">
-        <v>46377.75</v>
+        <v>46378.04166666666</v>
       </c>
       <c r="M750" s="1" t="n">
-        <v>46378.54166666666</v>
+        <v>46378.83333333334</v>
       </c>
     </row>
     <row r="751">
@@ -41648,13 +41648,13 @@
         </is>
       </c>
       <c r="K751" s="1" t="n">
-        <v>46384.29166666666</v>
+        <v>46384.58333333334</v>
       </c>
       <c r="L751" s="1" t="n">
-        <v>46384.33333333334</v>
+        <v>46384.625</v>
       </c>
       <c r="M751" s="1" t="n">
-        <v>46384.625</v>
+        <v>46384.91666666666</v>
       </c>
     </row>
     <row r="752">
@@ -41703,13 +41703,13 @@
         </is>
       </c>
       <c r="K752" s="1" t="n">
-        <v>46384.91666666666</v>
+        <v>46385.20833333334</v>
       </c>
       <c r="L752" s="1" t="n">
-        <v>46384.91666666666</v>
+        <v>46385.20833333334</v>
       </c>
       <c r="M752" s="1" t="n">
-        <v>46386.29166666666</v>
+        <v>46386.58333333334</v>
       </c>
     </row>
     <row r="753">
@@ -41758,13 +41758,13 @@
         </is>
       </c>
       <c r="K753" s="1" t="n">
-        <v>46386.54166666666</v>
+        <v>46386.83333333334</v>
       </c>
       <c r="L753" s="1" t="n">
-        <v>46386.58333333334</v>
+        <v>46386.875</v>
       </c>
       <c r="M753" s="1" t="n">
-        <v>46387.04166666666</v>
+        <v>46387.33333333334</v>
       </c>
     </row>
     <row r="754">
@@ -41813,13 +41813,13 @@
         </is>
       </c>
       <c r="K754" s="1" t="n">
-        <v>46390.875</v>
+        <v>46391.16666666666</v>
       </c>
       <c r="L754" s="1" t="n">
-        <v>46390.875</v>
+        <v>46391.16666666666</v>
       </c>
       <c r="M754" s="1" t="n">
-        <v>46391.33333333334</v>
+        <v>46391.625</v>
       </c>
     </row>
     <row r="755">
@@ -41864,13 +41864,13 @@
       </c>
       <c r="J755" t="inlineStr"/>
       <c r="K755" s="1" t="n">
-        <v>46392.33333333334</v>
+        <v>46392.625</v>
       </c>
       <c r="L755" s="1" t="n">
-        <v>46392.33333333334</v>
+        <v>46392.625</v>
       </c>
       <c r="M755" s="1" t="n">
-        <v>46392.83333333334</v>
+        <v>46393.125</v>
       </c>
     </row>
     <row r="756">
@@ -42087,10 +42087,10 @@
         <v>46305.79166666666</v>
       </c>
       <c r="L759" s="1" t="n">
-        <v>46305.95833333334</v>
+        <v>46305.98680555556</v>
       </c>
       <c r="M759" s="1" t="n">
-        <v>46306.58333333334</v>
+        <v>46306.45</v>
       </c>
     </row>
     <row r="760">
@@ -42139,10 +42139,10 @@
         </is>
       </c>
       <c r="K760" s="1" t="n">
-        <v>46308.25</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="L760" s="1" t="n">
-        <v>46308.29166666666</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="M760" s="1" t="n">
         <v>46308.54166666666</v>
@@ -49881,7 +49881,7 @@
         <v>46307.20833333334</v>
       </c>
       <c r="L901" s="1" t="n">
-        <v>46307.70833333334</v>
+        <v>46307.79166666666</v>
       </c>
       <c r="M901" s="1" t="n">
         <v>46309.20833333334</v>
@@ -49933,13 +49933,13 @@
         </is>
       </c>
       <c r="K902" s="1" t="n">
-        <v>46309.375</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="L902" s="1" t="n">
-        <v>46309.41666666666</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="M902" s="1" t="n">
-        <v>46309.66666666666</v>
+        <v>46309.70833333334</v>
       </c>
     </row>
     <row r="903">
@@ -49988,13 +49988,13 @@
         </is>
       </c>
       <c r="K903" s="1" t="n">
-        <v>46313.45833333334</v>
+        <v>46313.5</v>
       </c>
       <c r="L903" s="1" t="n">
-        <v>46313.52083333334</v>
+        <v>46313.5625</v>
       </c>
       <c r="M903" s="1" t="n">
-        <v>46313.97916666666</v>
+        <v>46314.02083333334</v>
       </c>
     </row>
     <row r="904">
@@ -50098,13 +50098,13 @@
         </is>
       </c>
       <c r="K905" s="1" t="n">
-        <v>46314.75</v>
+        <v>46314.79166666666</v>
       </c>
       <c r="L905" s="1" t="n">
-        <v>46314.79166666666</v>
+        <v>46314.83333333334</v>
       </c>
       <c r="M905" s="1" t="n">
-        <v>46315.375</v>
+        <v>46315.41666666666</v>
       </c>
     </row>
     <row r="906">
@@ -50208,13 +50208,13 @@
         </is>
       </c>
       <c r="K907" s="1" t="n">
-        <v>46317.66666666666</v>
+        <v>46317.70833333334</v>
       </c>
       <c r="L907" s="1" t="n">
-        <v>46317.72916666666</v>
+        <v>46317.77083333334</v>
       </c>
       <c r="M907" s="1" t="n">
-        <v>46318.16666666666</v>
+        <v>46318.20833333334</v>
       </c>
     </row>
     <row r="908">
@@ -50318,13 +50318,13 @@
         </is>
       </c>
       <c r="K909" s="1" t="n">
-        <v>46318.45833333334</v>
+        <v>46318.5</v>
       </c>
       <c r="L909" s="1" t="n">
-        <v>46318.5</v>
+        <v>46318.54166666666</v>
       </c>
       <c r="M909" s="1" t="n">
-        <v>46319.16666666666</v>
+        <v>46319.20833333334</v>
       </c>
     </row>
     <row r="910">
@@ -51685,17 +51685,17 @@
       </c>
       <c r="J934" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K934" s="1" t="n">
         <v>46308.58333333334</v>
       </c>
       <c r="L934" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="M934" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46309.625</v>
       </c>
     </row>
     <row r="935">
@@ -51730,27 +51730,27 @@
       </c>
       <c r="H935" t="inlineStr">
         <is>
-          <t>KAN04</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
           <t>KRKAN</t>
         </is>
       </c>
-      <c r="J935" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
       <c r="K935" s="1" t="n">
-        <v>46310.625</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="L935" s="1" t="n">
-        <v>46310.6875</v>
+        <v>46310.85416666666</v>
       </c>
       <c r="M935" s="1" t="n">
-        <v>46311.25</v>
+        <v>46311.41666666666</v>
       </c>
     </row>
     <row r="936">
@@ -51785,27 +51785,27 @@
       </c>
       <c r="H936" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
         <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="J936" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
       <c r="K936" s="1" t="n">
-        <v>46311.54166666666</v>
+        <v>46311.70833333334</v>
       </c>
       <c r="L936" s="1" t="n">
-        <v>46311.58333333334</v>
+        <v>46311.75</v>
       </c>
       <c r="M936" s="1" t="n">
-        <v>46312.58333333334</v>
+        <v>46312.75</v>
       </c>
     </row>
     <row r="937">
@@ -54325,13 +54325,13 @@
         </is>
       </c>
       <c r="K982" s="1" t="n">
-        <v>46302.60416666666</v>
+        <v>46302.66666666666</v>
       </c>
       <c r="L982" s="1" t="n">
-        <v>46304.08333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="M982" s="1" t="n">
-        <v>46305.25</v>
+        <v>46305.625</v>
       </c>
     </row>
     <row r="983">
@@ -54380,13 +54380,13 @@
         </is>
       </c>
       <c r="K983" s="1" t="n">
-        <v>46305.54166666666</v>
+        <v>46305.89583333334</v>
       </c>
       <c r="L983" s="1" t="n">
-        <v>46305.60416666666</v>
+        <v>46305.95833333334</v>
       </c>
       <c r="M983" s="1" t="n">
-        <v>46305.9375</v>
+        <v>46306.41666666666</v>
       </c>
     </row>
     <row r="984">
@@ -54435,13 +54435,13 @@
         </is>
       </c>
       <c r="K984" s="1" t="n">
-        <v>46308.83333333334</v>
+        <v>46309.25</v>
       </c>
       <c r="L984" s="1" t="n">
-        <v>46308.89583333334</v>
+        <v>46309.3125</v>
       </c>
       <c r="M984" s="1" t="n">
-        <v>46309.39583333334</v>
+        <v>46309.8125</v>
       </c>
     </row>
     <row r="985">
@@ -54490,13 +54490,13 @@
         </is>
       </c>
       <c r="K985" s="1" t="n">
-        <v>46311.625</v>
+        <v>46312.04166666666</v>
       </c>
       <c r="L985" s="1" t="n">
-        <v>46311.79166666666</v>
+        <v>46312.20833333334</v>
       </c>
       <c r="M985" s="1" t="n">
-        <v>46312.41666666666</v>
+        <v>46312.83333333334</v>
       </c>
     </row>
     <row r="986">
@@ -54545,13 +54545,13 @@
         </is>
       </c>
       <c r="K986" s="1" t="n">
-        <v>46314</v>
+        <v>46314.41666666666</v>
       </c>
       <c r="L986" s="1" t="n">
-        <v>46314.04166666666</v>
+        <v>46314.45833333334</v>
       </c>
       <c r="M986" s="1" t="n">
-        <v>46314.25</v>
+        <v>46314.66666666666</v>
       </c>
     </row>
     <row r="987">
@@ -54600,13 +54600,13 @@
         </is>
       </c>
       <c r="K987" s="1" t="n">
-        <v>46314.375</v>
+        <v>46314.79166666666</v>
       </c>
       <c r="L987" s="1" t="n">
-        <v>46314.5</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="M987" s="1" t="n">
-        <v>46315.95833333334</v>
+        <v>46316.375</v>
       </c>
     </row>
     <row r="988">
@@ -54655,13 +54655,13 @@
         </is>
       </c>
       <c r="K988" s="1" t="n">
-        <v>46316.16666666666</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="L988" s="1" t="n">
-        <v>46316.20833333334</v>
+        <v>46316.625</v>
       </c>
       <c r="M988" s="1" t="n">
-        <v>46316.54166666666</v>
+        <v>46316.95833333334</v>
       </c>
     </row>
     <row r="989">
@@ -54710,13 +54710,13 @@
         </is>
       </c>
       <c r="K989" s="1" t="n">
-        <v>46320.25</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="L989" s="1" t="n">
-        <v>46320.3125</v>
+        <v>46320.72916666666</v>
       </c>
       <c r="M989" s="1" t="n">
-        <v>46320.8125</v>
+        <v>46321.22916666666</v>
       </c>
     </row>
     <row r="990">
@@ -54765,13 +54765,13 @@
         </is>
       </c>
       <c r="K990" s="1" t="n">
-        <v>46321.625</v>
+        <v>46322.04166666666</v>
       </c>
       <c r="L990" s="1" t="n">
-        <v>46321.6875</v>
+        <v>46322.10416666666</v>
       </c>
       <c r="M990" s="1" t="n">
-        <v>46322.3125</v>
+        <v>46322.72916666666</v>
       </c>
     </row>
     <row r="991">
@@ -54820,13 +54820,13 @@
         </is>
       </c>
       <c r="K991" s="1" t="n">
-        <v>46324.66666666666</v>
+        <v>46325.08333333334</v>
       </c>
       <c r="L991" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46325.125</v>
       </c>
       <c r="M991" s="1" t="n">
-        <v>46325.41666666666</v>
+        <v>46325.83333333334</v>
       </c>
     </row>
     <row r="992">
@@ -54875,13 +54875,13 @@
         </is>
       </c>
       <c r="K992" s="1" t="n">
-        <v>46325.75</v>
+        <v>46326.125</v>
       </c>
       <c r="L992" s="1" t="n">
-        <v>46325.83333333334</v>
+        <v>46326.1875</v>
       </c>
       <c r="M992" s="1" t="n">
-        <v>46326.08333333334</v>
+        <v>46326.52083333334</v>
       </c>
     </row>
     <row r="993">
@@ -54930,13 +54930,13 @@
         </is>
       </c>
       <c r="K993" s="1" t="n">
-        <v>46329</v>
+        <v>46329.41666666666</v>
       </c>
       <c r="L993" s="1" t="n">
-        <v>46329.04166666666</v>
+        <v>46329.47916666666</v>
       </c>
       <c r="M993" s="1" t="n">
-        <v>46329.5</v>
+        <v>46329.97916666666</v>
       </c>
     </row>
     <row r="994">
@@ -54985,13 +54985,13 @@
         </is>
       </c>
       <c r="K994" s="1" t="n">
-        <v>46331.70833333334</v>
+        <v>46332.20833333334</v>
       </c>
       <c r="L994" s="1" t="n">
-        <v>46331.875</v>
+        <v>46332.375</v>
       </c>
       <c r="M994" s="1" t="n">
-        <v>46332.33333333334</v>
+        <v>46332.83333333334</v>
       </c>
     </row>
     <row r="995">
@@ -55040,13 +55040,13 @@
         </is>
       </c>
       <c r="K995" s="1" t="n">
-        <v>46334.08333333334</v>
+        <v>46334.58333333334</v>
       </c>
       <c r="L995" s="1" t="n">
-        <v>46334.125</v>
+        <v>46334.625</v>
       </c>
       <c r="M995" s="1" t="n">
-        <v>46334.29166666666</v>
+        <v>46334.83333333334</v>
       </c>
     </row>
     <row r="996">
@@ -55095,13 +55095,13 @@
         </is>
       </c>
       <c r="K996" s="1" t="n">
-        <v>46334.54166666666</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="L996" s="1" t="n">
-        <v>46334.66666666666</v>
+        <v>46335.08333333334</v>
       </c>
       <c r="M996" s="1" t="n">
-        <v>46336</v>
+        <v>46336.54166666666</v>
       </c>
     </row>
     <row r="997">
@@ -55150,13 +55150,13 @@
         </is>
       </c>
       <c r="K997" s="1" t="n">
-        <v>46336.5</v>
+        <v>46336.75</v>
       </c>
       <c r="L997" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46336.79166666666</v>
       </c>
       <c r="M997" s="1" t="n">
-        <v>46336.83333333334</v>
+        <v>46337.125</v>
       </c>
     </row>
     <row r="998">
@@ -55205,13 +55205,13 @@
         </is>
       </c>
       <c r="K998" s="1" t="n">
-        <v>46340.91666666666</v>
+        <v>46340.83333333334</v>
       </c>
       <c r="L998" s="1" t="n">
-        <v>46340.95833333334</v>
+        <v>46340.875</v>
       </c>
       <c r="M998" s="1" t="n">
-        <v>46341.41666666666</v>
+        <v>46341.39583333334</v>
       </c>
     </row>
     <row r="999">
@@ -55260,13 +55260,13 @@
         </is>
       </c>
       <c r="K999" s="1" t="n">
-        <v>46342.5</v>
+        <v>46342.20833333334</v>
       </c>
       <c r="L999" s="1" t="n">
-        <v>46342.54166666666</v>
+        <v>46342.27083333334</v>
       </c>
       <c r="M999" s="1" t="n">
-        <v>46343.125</v>
+        <v>46342.89583333334</v>
       </c>
     </row>
     <row r="1000">
@@ -56359,10 +56359,10 @@
         <v>46306.125</v>
       </c>
       <c r="L1019" s="1" t="n">
-        <v>46306.16666666666</v>
+        <v>46306.875</v>
       </c>
       <c r="M1019" s="1" t="n">
-        <v>46306.83333333334</v>
+        <v>46307.58333333334</v>
       </c>
     </row>
     <row r="1020">
@@ -56411,13 +56411,13 @@
         </is>
       </c>
       <c r="K1020" s="1" t="n">
-        <v>46307.91666666666</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="L1020" s="1" t="n">
-        <v>46307.95833333334</v>
+        <v>46308.625</v>
       </c>
       <c r="M1020" s="1" t="n">
-        <v>46308.54166666666</v>
+        <v>46309.45833333334</v>
       </c>
     </row>
     <row r="1021">
@@ -56466,13 +56466,13 @@
         </is>
       </c>
       <c r="K1021" s="1" t="n">
-        <v>46308.75</v>
+        <v>46309.66666666666</v>
       </c>
       <c r="L1021" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="M1021" s="1" t="n">
-        <v>46309.125</v>
+        <v>46310.04166666666</v>
       </c>
     </row>
     <row r="1022">
@@ -56521,13 +56521,13 @@
         </is>
       </c>
       <c r="K1022" s="1" t="n">
-        <v>46310.41666666666</v>
+        <v>46311.125</v>
       </c>
       <c r="L1022" s="1" t="n">
-        <v>46310.58333333334</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="M1022" s="1" t="n">
-        <v>46311.08333333334</v>
+        <v>46311.79166666666</v>
       </c>
     </row>
     <row r="1023">
@@ -56576,13 +56576,13 @@
         </is>
       </c>
       <c r="K1023" s="1" t="n">
-        <v>46315.25</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="L1023" s="1" t="n">
-        <v>46315.41666666666</v>
+        <v>46316.125</v>
       </c>
       <c r="M1023" s="1" t="n">
-        <v>46316.25</v>
+        <v>46316.95833333334</v>
       </c>
     </row>
     <row r="1024">
@@ -56631,13 +56631,13 @@
         </is>
       </c>
       <c r="K1024" s="1" t="n">
-        <v>46317.95833333334</v>
+        <v>46318.66666666666</v>
       </c>
       <c r="L1024" s="1" t="n">
-        <v>46318</v>
+        <v>46318.70833333334</v>
       </c>
       <c r="M1024" s="1" t="n">
-        <v>46318.83333333334</v>
+        <v>46319.54166666666</v>
       </c>
     </row>
     <row r="1025">
@@ -56686,13 +56686,13 @@
         </is>
       </c>
       <c r="K1025" s="1" t="n">
-        <v>46322</v>
+        <v>46322.70833333334</v>
       </c>
       <c r="L1025" s="1" t="n">
-        <v>46322.04166666666</v>
+        <v>46322.75</v>
       </c>
       <c r="M1025" s="1" t="n">
-        <v>46323.72916666666</v>
+        <v>46324.4375</v>
       </c>
     </row>
     <row r="1026">
@@ -56741,13 +56741,13 @@
         </is>
       </c>
       <c r="K1026" s="1" t="n">
-        <v>46325.85416666666</v>
+        <v>46326.5625</v>
       </c>
       <c r="L1026" s="1" t="n">
-        <v>46326.02083333334</v>
+        <v>46326.72916666666</v>
       </c>
       <c r="M1026" s="1" t="n">
-        <v>46326.85416666666</v>
+        <v>46327.5625</v>
       </c>
     </row>
     <row r="1027">
@@ -56796,13 +56796,13 @@
         </is>
       </c>
       <c r="K1027" s="1" t="n">
-        <v>46329.375</v>
+        <v>46330.08333333334</v>
       </c>
       <c r="L1027" s="1" t="n">
-        <v>46329.4375</v>
+        <v>46330.14583333334</v>
       </c>
       <c r="M1027" s="1" t="n">
-        <v>46329.9375</v>
+        <v>46330.64583333334</v>
       </c>
     </row>
     <row r="1028">
@@ -56851,13 +56851,13 @@
         </is>
       </c>
       <c r="K1028" s="1" t="n">
-        <v>46330.16666666666</v>
+        <v>46330.875</v>
       </c>
       <c r="L1028" s="1" t="n">
-        <v>46330.20833333334</v>
+        <v>46330.91666666666</v>
       </c>
       <c r="M1028" s="1" t="n">
-        <v>46330.70833333334</v>
+        <v>46331.41666666666</v>
       </c>
     </row>
     <row r="1029">
@@ -56906,13 +56906,13 @@
         </is>
       </c>
       <c r="K1029" s="1" t="n">
-        <v>46333.89583333334</v>
+        <v>46334.60416666666</v>
       </c>
       <c r="L1029" s="1" t="n">
-        <v>46333.9375</v>
+        <v>46334.64583333334</v>
       </c>
       <c r="M1029" s="1" t="n">
-        <v>46334.60416666666</v>
+        <v>46335.3125</v>
       </c>
     </row>
     <row r="1030">
@@ -56961,13 +56961,13 @@
         </is>
       </c>
       <c r="K1030" s="1" t="n">
-        <v>46335.6875</v>
+        <v>46336.39583333334</v>
       </c>
       <c r="L1030" s="1" t="n">
-        <v>46335.72916666666</v>
+        <v>46336.4375</v>
       </c>
       <c r="M1030" s="1" t="n">
-        <v>46336.3125</v>
+        <v>46337.02083333334</v>
       </c>
     </row>
     <row r="1031">
@@ -57016,13 +57016,13 @@
         </is>
       </c>
       <c r="K1031" s="1" t="n">
-        <v>46336.5</v>
+        <v>46337.20833333334</v>
       </c>
       <c r="L1031" s="1" t="n">
-        <v>46336.5625</v>
+        <v>46337.27083333334</v>
       </c>
       <c r="M1031" s="1" t="n">
-        <v>46336.89583333334</v>
+        <v>46337.60416666666</v>
       </c>
     </row>
     <row r="1032">
@@ -57071,13 +57071,13 @@
         </is>
       </c>
       <c r="K1032" s="1" t="n">
-        <v>46338.1875</v>
+        <v>46338.89583333334</v>
       </c>
       <c r="L1032" s="1" t="n">
-        <v>46338.35416666666</v>
+        <v>46339.0625</v>
       </c>
       <c r="M1032" s="1" t="n">
-        <v>46338.85416666666</v>
+        <v>46339.5625</v>
       </c>
     </row>
     <row r="1033">
@@ -57126,13 +57126,13 @@
         </is>
       </c>
       <c r="K1033" s="1" t="n">
-        <v>46343.02083333334</v>
+        <v>46343.72916666666</v>
       </c>
       <c r="L1033" s="1" t="n">
-        <v>46343.1875</v>
+        <v>46343.89583333334</v>
       </c>
       <c r="M1033" s="1" t="n">
-        <v>46344.02083333334</v>
+        <v>46344.72916666666</v>
       </c>
     </row>
     <row r="1034">
@@ -57181,13 +57181,13 @@
         </is>
       </c>
       <c r="K1034" s="1" t="n">
-        <v>46345.6875</v>
+        <v>46346.39583333334</v>
       </c>
       <c r="L1034" s="1" t="n">
-        <v>46345.72916666666</v>
+        <v>46346.4375</v>
       </c>
       <c r="M1034" s="1" t="n">
-        <v>46346.5625</v>
+        <v>46347.27083333334</v>
       </c>
     </row>
     <row r="1035">
@@ -57236,13 +57236,13 @@
         </is>
       </c>
       <c r="K1035" s="1" t="n">
-        <v>46349.72916666666</v>
+        <v>46350.4375</v>
       </c>
       <c r="L1035" s="1" t="n">
-        <v>46349.8125</v>
+        <v>46350.52083333334</v>
       </c>
       <c r="M1035" s="1" t="n">
-        <v>46351.47916666666</v>
+        <v>46352.1875</v>
       </c>
     </row>
     <row r="1036">
@@ -57291,13 +57291,13 @@
         </is>
       </c>
       <c r="K1036" s="1" t="n">
-        <v>46353.9375</v>
+        <v>46354.64583333334</v>
       </c>
       <c r="L1036" s="1" t="n">
-        <v>46354.10416666666</v>
+        <v>46354.8125</v>
       </c>
       <c r="M1036" s="1" t="n">
-        <v>46354.9375</v>
+        <v>46355.64583333334</v>
       </c>
     </row>
     <row r="1037">
@@ -57346,13 +57346,13 @@
         </is>
       </c>
       <c r="K1037" s="1" t="n">
-        <v>46357.47916666666</v>
+        <v>46358.1875</v>
       </c>
       <c r="L1037" s="1" t="n">
-        <v>46357.54166666666</v>
+        <v>46358.25</v>
       </c>
       <c r="M1037" s="1" t="n">
-        <v>46358.04166666666</v>
+        <v>46358.75</v>
       </c>
     </row>
     <row r="1038">
@@ -57401,13 +57401,13 @@
         </is>
       </c>
       <c r="K1038" s="1" t="n">
-        <v>46358.27083333334</v>
+        <v>46358.97916666666</v>
       </c>
       <c r="L1038" s="1" t="n">
-        <v>46358.3125</v>
+        <v>46359.02083333334</v>
       </c>
       <c r="M1038" s="1" t="n">
-        <v>46358.8125</v>
+        <v>46359.52083333334</v>
       </c>
     </row>
     <row r="1039">
@@ -57456,13 +57456,13 @@
         </is>
       </c>
       <c r="K1039" s="1" t="n">
-        <v>46361.89583333334</v>
+        <v>46362.60416666666</v>
       </c>
       <c r="L1039" s="1" t="n">
-        <v>46361.9375</v>
+        <v>46362.64583333334</v>
       </c>
       <c r="M1039" s="1" t="n">
-        <v>46362.60416666666</v>
+        <v>46363.3125</v>
       </c>
     </row>
     <row r="1040">
@@ -57511,13 +57511,13 @@
         </is>
       </c>
       <c r="K1040" s="1" t="n">
-        <v>46363.6875</v>
+        <v>46364.39583333334</v>
       </c>
       <c r="L1040" s="1" t="n">
-        <v>46363.72916666666</v>
+        <v>46364.4375</v>
       </c>
       <c r="M1040" s="1" t="n">
-        <v>46364.3125</v>
+        <v>46365.02083333334</v>
       </c>
     </row>
     <row r="1041">
@@ -57566,13 +57566,13 @@
         </is>
       </c>
       <c r="K1041" s="1" t="n">
-        <v>46364.5</v>
+        <v>46365.20833333334</v>
       </c>
       <c r="L1041" s="1" t="n">
-        <v>46364.5625</v>
+        <v>46365.27083333334</v>
       </c>
       <c r="M1041" s="1" t="n">
-        <v>46364.89583333334</v>
+        <v>46365.60416666666</v>
       </c>
     </row>
     <row r="1042">
@@ -57621,13 +57621,13 @@
         </is>
       </c>
       <c r="K1042" s="1" t="n">
-        <v>46366.1875</v>
+        <v>46366.89583333334</v>
       </c>
       <c r="L1042" s="1" t="n">
-        <v>46366.35416666666</v>
+        <v>46367.0625</v>
       </c>
       <c r="M1042" s="1" t="n">
-        <v>46366.85416666666</v>
+        <v>46367.5625</v>
       </c>
     </row>
     <row r="1043">
@@ -57676,13 +57676,13 @@
         </is>
       </c>
       <c r="K1043" s="1" t="n">
-        <v>46371.02083333334</v>
+        <v>46371.72916666666</v>
       </c>
       <c r="L1043" s="1" t="n">
-        <v>46371.1875</v>
+        <v>46371.89583333334</v>
       </c>
       <c r="M1043" s="1" t="n">
-        <v>46372.02083333334</v>
+        <v>46372.72916666666</v>
       </c>
     </row>
     <row r="1044">
@@ -57731,13 +57731,13 @@
         </is>
       </c>
       <c r="K1044" s="1" t="n">
-        <v>46373.6875</v>
+        <v>46374.39583333334</v>
       </c>
       <c r="L1044" s="1" t="n">
-        <v>46373.72916666666</v>
+        <v>46374.4375</v>
       </c>
       <c r="M1044" s="1" t="n">
-        <v>46374.5625</v>
+        <v>46375.27083333334</v>
       </c>
     </row>
     <row r="1045">
@@ -57786,13 +57786,13 @@
         </is>
       </c>
       <c r="K1045" s="1" t="n">
-        <v>46377.72916666666</v>
+        <v>46378.4375</v>
       </c>
       <c r="L1045" s="1" t="n">
-        <v>46377.8125</v>
+        <v>46378.52083333334</v>
       </c>
       <c r="M1045" s="1" t="n">
-        <v>46379.47916666666</v>
+        <v>46380.1875</v>
       </c>
     </row>
     <row r="1046">
@@ -57841,13 +57841,13 @@
         </is>
       </c>
       <c r="K1046" s="1" t="n">
-        <v>46381.9375</v>
+        <v>46382.64583333334</v>
       </c>
       <c r="L1046" s="1" t="n">
-        <v>46382.10416666666</v>
+        <v>46382.8125</v>
       </c>
       <c r="M1046" s="1" t="n">
-        <v>46382.9375</v>
+        <v>46383.64583333334</v>
       </c>
     </row>
     <row r="1047">
@@ -57896,13 +57896,13 @@
         </is>
       </c>
       <c r="K1047" s="1" t="n">
-        <v>46385.47916666666</v>
+        <v>46386.1875</v>
       </c>
       <c r="L1047" s="1" t="n">
-        <v>46385.54166666666</v>
+        <v>46386.25</v>
       </c>
       <c r="M1047" s="1" t="n">
-        <v>46386.04166666666</v>
+        <v>46386.75</v>
       </c>
     </row>
     <row r="1048">
@@ -57947,13 +57947,13 @@
       </c>
       <c r="J1048" t="inlineStr"/>
       <c r="K1048" s="1" t="n">
-        <v>46386.27083333334</v>
+        <v>46386.97916666666</v>
       </c>
       <c r="L1048" s="1" t="n">
-        <v>46386.3125</v>
+        <v>46387.02083333334</v>
       </c>
       <c r="M1048" s="1" t="n">
-        <v>46386.8125</v>
+        <v>46387.52083333334</v>
       </c>
     </row>
     <row r="1049">
@@ -58118,7 +58118,7 @@
         <v>46305.99166666667</v>
       </c>
       <c r="M1051" s="1" t="n">
-        <v>46306.875</v>
+        <v>46306.87916666667</v>
       </c>
     </row>
     <row r="1052">
@@ -58170,10 +58170,10 @@
         <v>46308.125</v>
       </c>
       <c r="L1052" s="1" t="n">
-        <v>46308.29166666666</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="M1052" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46309.47916666666</v>
       </c>
     </row>
     <row r="1053">
@@ -58222,13 +58222,13 @@
         </is>
       </c>
       <c r="K1053" s="1" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.64583333334</v>
       </c>
       <c r="L1053" s="1" t="n">
-        <v>46313.125</v>
+        <v>46313.8125</v>
       </c>
       <c r="M1053" s="1" t="n">
-        <v>46313.95833333334</v>
+        <v>46314.64583333334</v>
       </c>
     </row>
     <row r="1054">
@@ -58277,13 +58277,13 @@
         </is>
       </c>
       <c r="K1054" s="1" t="n">
-        <v>46315.625</v>
+        <v>46316.3125</v>
       </c>
       <c r="L1054" s="1" t="n">
-        <v>46315.66666666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="M1054" s="1" t="n">
-        <v>46316.5</v>
+        <v>46317.1875</v>
       </c>
     </row>
     <row r="1055">
@@ -58332,13 +58332,13 @@
         </is>
       </c>
       <c r="K1055" s="1" t="n">
-        <v>46319.66666666666</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="L1055" s="1" t="n">
-        <v>46319.75</v>
+        <v>46320.4375</v>
       </c>
       <c r="M1055" s="1" t="n">
-        <v>46321.41666666666</v>
+        <v>46322.10416666666</v>
       </c>
     </row>
     <row r="1056">
@@ -58387,13 +58387,13 @@
         </is>
       </c>
       <c r="K1056" s="1" t="n">
-        <v>46323.875</v>
+        <v>46324.5625</v>
       </c>
       <c r="L1056" s="1" t="n">
-        <v>46324.04166666666</v>
+        <v>46324.72916666666</v>
       </c>
       <c r="M1056" s="1" t="n">
-        <v>46324.875</v>
+        <v>46325.5625</v>
       </c>
     </row>
     <row r="1057">
@@ -58442,13 +58442,13 @@
         </is>
       </c>
       <c r="K1057" s="1" t="n">
-        <v>46327.41666666666</v>
+        <v>46328.10416666666</v>
       </c>
       <c r="L1057" s="1" t="n">
-        <v>46327.47916666666</v>
+        <v>46328.16666666666</v>
       </c>
       <c r="M1057" s="1" t="n">
-        <v>46327.97916666666</v>
+        <v>46328.66666666666</v>
       </c>
     </row>
     <row r="1058">
@@ -58497,13 +58497,13 @@
         </is>
       </c>
       <c r="K1058" s="1" t="n">
-        <v>46328.20833333334</v>
+        <v>46328.89583333334</v>
       </c>
       <c r="L1058" s="1" t="n">
-        <v>46328.25</v>
+        <v>46328.9375</v>
       </c>
       <c r="M1058" s="1" t="n">
-        <v>46328.75</v>
+        <v>46329.4375</v>
       </c>
     </row>
     <row r="1059">
@@ -58552,13 +58552,13 @@
         </is>
       </c>
       <c r="K1059" s="1" t="n">
-        <v>46331.83333333334</v>
+        <v>46332.52083333334</v>
       </c>
       <c r="L1059" s="1" t="n">
-        <v>46331.875</v>
+        <v>46332.5625</v>
       </c>
       <c r="M1059" s="1" t="n">
-        <v>46332.54166666666</v>
+        <v>46333.22916666666</v>
       </c>
     </row>
     <row r="1060">
@@ -58607,13 +58607,13 @@
         </is>
       </c>
       <c r="K1060" s="1" t="n">
-        <v>46333.625</v>
+        <v>46334.3125</v>
       </c>
       <c r="L1060" s="1" t="n">
-        <v>46333.66666666666</v>
+        <v>46334.35416666666</v>
       </c>
       <c r="M1060" s="1" t="n">
-        <v>46334.25</v>
+        <v>46334.9375</v>
       </c>
     </row>
     <row r="1061">
@@ -58662,13 +58662,13 @@
         </is>
       </c>
       <c r="K1061" s="1" t="n">
-        <v>46334.4375</v>
+        <v>46335.125</v>
       </c>
       <c r="L1061" s="1" t="n">
-        <v>46334.5</v>
+        <v>46335.1875</v>
       </c>
       <c r="M1061" s="1" t="n">
-        <v>46334.83333333334</v>
+        <v>46335.52083333334</v>
       </c>
     </row>
     <row r="1062">
@@ -58717,13 +58717,13 @@
         </is>
       </c>
       <c r="K1062" s="1" t="n">
-        <v>46336.125</v>
+        <v>46336.8125</v>
       </c>
       <c r="L1062" s="1" t="n">
-        <v>46336.29166666666</v>
+        <v>46336.97916666666</v>
       </c>
       <c r="M1062" s="1" t="n">
-        <v>46336.79166666666</v>
+        <v>46337.47916666666</v>
       </c>
     </row>
     <row r="1063">
@@ -58772,13 +58772,13 @@
         </is>
       </c>
       <c r="K1063" s="1" t="n">
-        <v>46340.95833333334</v>
+        <v>46341.64583333334</v>
       </c>
       <c r="L1063" s="1" t="n">
-        <v>46341.125</v>
+        <v>46341.8125</v>
       </c>
       <c r="M1063" s="1" t="n">
-        <v>46341.95833333334</v>
+        <v>46342.64583333334</v>
       </c>
     </row>
     <row r="1064">
@@ -58827,13 +58827,13 @@
         </is>
       </c>
       <c r="K1064" s="1" t="n">
-        <v>46343.625</v>
+        <v>46344.3125</v>
       </c>
       <c r="L1064" s="1" t="n">
-        <v>46343.66666666666</v>
+        <v>46344.35416666666</v>
       </c>
       <c r="M1064" s="1" t="n">
-        <v>46344.5</v>
+        <v>46345.1875</v>
       </c>
     </row>
     <row r="1065">
@@ -58882,13 +58882,13 @@
         </is>
       </c>
       <c r="K1065" s="1" t="n">
-        <v>46347.66666666666</v>
+        <v>46348.35416666666</v>
       </c>
       <c r="L1065" s="1" t="n">
-        <v>46347.75</v>
+        <v>46348.4375</v>
       </c>
       <c r="M1065" s="1" t="n">
-        <v>46349.41666666666</v>
+        <v>46350.10416666666</v>
       </c>
     </row>
     <row r="1066">
@@ -58937,13 +58937,13 @@
         </is>
       </c>
       <c r="K1066" s="1" t="n">
-        <v>46351.875</v>
+        <v>46352.5625</v>
       </c>
       <c r="L1066" s="1" t="n">
-        <v>46352.04166666666</v>
+        <v>46352.72916666666</v>
       </c>
       <c r="M1066" s="1" t="n">
-        <v>46352.875</v>
+        <v>46353.5625</v>
       </c>
     </row>
     <row r="1067">
@@ -58992,13 +58992,13 @@
         </is>
       </c>
       <c r="K1067" s="1" t="n">
-        <v>46355.41666666666</v>
+        <v>46356.10416666666</v>
       </c>
       <c r="L1067" s="1" t="n">
-        <v>46355.47916666666</v>
+        <v>46356.16666666666</v>
       </c>
       <c r="M1067" s="1" t="n">
-        <v>46355.97916666666</v>
+        <v>46356.66666666666</v>
       </c>
     </row>
     <row r="1068">
@@ -59047,13 +59047,13 @@
         </is>
       </c>
       <c r="K1068" s="1" t="n">
-        <v>46356.20833333334</v>
+        <v>46356.89583333334</v>
       </c>
       <c r="L1068" s="1" t="n">
-        <v>46356.25</v>
+        <v>46356.9375</v>
       </c>
       <c r="M1068" s="1" t="n">
-        <v>46356.75</v>
+        <v>46357.4375</v>
       </c>
     </row>
     <row r="1069">
@@ -59102,13 +59102,13 @@
         </is>
       </c>
       <c r="K1069" s="1" t="n">
-        <v>46359.83333333334</v>
+        <v>46360.52083333334</v>
       </c>
       <c r="L1069" s="1" t="n">
-        <v>46359.875</v>
+        <v>46360.5625</v>
       </c>
       <c r="M1069" s="1" t="n">
-        <v>46360.54166666666</v>
+        <v>46361.22916666666</v>
       </c>
     </row>
     <row r="1070">
@@ -59157,13 +59157,13 @@
         </is>
       </c>
       <c r="K1070" s="1" t="n">
-        <v>46361.625</v>
+        <v>46362.3125</v>
       </c>
       <c r="L1070" s="1" t="n">
-        <v>46361.66666666666</v>
+        <v>46362.35416666666</v>
       </c>
       <c r="M1070" s="1" t="n">
-        <v>46362.25</v>
+        <v>46362.9375</v>
       </c>
     </row>
     <row r="1071">
@@ -59212,13 +59212,13 @@
         </is>
       </c>
       <c r="K1071" s="1" t="n">
-        <v>46362.4375</v>
+        <v>46363.125</v>
       </c>
       <c r="L1071" s="1" t="n">
-        <v>46362.5</v>
+        <v>46363.1875</v>
       </c>
       <c r="M1071" s="1" t="n">
-        <v>46362.83333333334</v>
+        <v>46363.52083333334</v>
       </c>
     </row>
     <row r="1072">
@@ -59267,13 +59267,13 @@
         </is>
       </c>
       <c r="K1072" s="1" t="n">
-        <v>46364.125</v>
+        <v>46364.8125</v>
       </c>
       <c r="L1072" s="1" t="n">
-        <v>46364.29166666666</v>
+        <v>46364.97916666666</v>
       </c>
       <c r="M1072" s="1" t="n">
-        <v>46364.79166666666</v>
+        <v>46365.47916666666</v>
       </c>
     </row>
     <row r="1073">
@@ -59322,13 +59322,13 @@
         </is>
       </c>
       <c r="K1073" s="1" t="n">
-        <v>46368.95833333334</v>
+        <v>46369.64583333334</v>
       </c>
       <c r="L1073" s="1" t="n">
-        <v>46369.125</v>
+        <v>46369.8125</v>
       </c>
       <c r="M1073" s="1" t="n">
-        <v>46369.95833333334</v>
+        <v>46370.64583333334</v>
       </c>
     </row>
     <row r="1074">
@@ -59377,13 +59377,13 @@
         </is>
       </c>
       <c r="K1074" s="1" t="n">
-        <v>46371.625</v>
+        <v>46372.3125</v>
       </c>
       <c r="L1074" s="1" t="n">
-        <v>46371.66666666666</v>
+        <v>46372.35416666666</v>
       </c>
       <c r="M1074" s="1" t="n">
-        <v>46372.5</v>
+        <v>46373.1875</v>
       </c>
     </row>
     <row r="1075">
@@ -59432,13 +59432,13 @@
         </is>
       </c>
       <c r="K1075" s="1" t="n">
-        <v>46375.66666666666</v>
+        <v>46376.35416666666</v>
       </c>
       <c r="L1075" s="1" t="n">
-        <v>46375.75</v>
+        <v>46376.4375</v>
       </c>
       <c r="M1075" s="1" t="n">
-        <v>46377.41666666666</v>
+        <v>46378.10416666666</v>
       </c>
     </row>
     <row r="1076">
@@ -59487,13 +59487,13 @@
         </is>
       </c>
       <c r="K1076" s="1" t="n">
-        <v>46379.875</v>
+        <v>46380.5625</v>
       </c>
       <c r="L1076" s="1" t="n">
-        <v>46380.04166666666</v>
+        <v>46380.72916666666</v>
       </c>
       <c r="M1076" s="1" t="n">
-        <v>46380.875</v>
+        <v>46381.5625</v>
       </c>
     </row>
     <row r="1077">
@@ -59542,13 +59542,13 @@
         </is>
       </c>
       <c r="K1077" s="1" t="n">
-        <v>46383.41666666666</v>
+        <v>46384.10416666666</v>
       </c>
       <c r="L1077" s="1" t="n">
-        <v>46383.47916666666</v>
+        <v>46384.16666666666</v>
       </c>
       <c r="M1077" s="1" t="n">
-        <v>46383.97916666666</v>
+        <v>46384.66666666666</v>
       </c>
     </row>
     <row r="1078">
@@ -59593,13 +59593,13 @@
       </c>
       <c r="J1078" t="inlineStr"/>
       <c r="K1078" s="1" t="n">
-        <v>46384.20833333334</v>
+        <v>46384.89583333334</v>
       </c>
       <c r="L1078" s="1" t="n">
-        <v>46384.25</v>
+        <v>46384.9375</v>
       </c>
       <c r="M1078" s="1" t="n">
-        <v>46384.75</v>
+        <v>46385.4375</v>
       </c>
     </row>
   </sheetData>

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -6739,10 +6739,10 @@
         <v>46309.16666666666</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>46309.54166666666</v>
+        <v>46309.625</v>
       </c>
       <c r="M115" s="1" t="n">
-        <v>46310.625</v>
+        <v>46310.79166666666</v>
       </c>
     </row>
     <row r="116">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46310.75</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="M116" s="1" t="n">
-        <v>46311.04166666666</v>
+        <v>46311.20833333334</v>
       </c>
     </row>
     <row r="117">
@@ -6846,13 +6846,13 @@
         </is>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46311.45833333334</v>
+        <v>46311.625</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>46311.54166666666</v>
+        <v>46311.70833333334</v>
       </c>
       <c r="M117" s="1" t="n">
-        <v>46311.875</v>
+        <v>46312.04166666666</v>
       </c>
     </row>
     <row r="118">
@@ -6901,13 +6901,13 @@
         </is>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46316.95833333334</v>
+        <v>46317.125</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>46317.125</v>
+        <v>46317.29166666666</v>
       </c>
       <c r="M118" s="1" t="n">
-        <v>46317.75</v>
+        <v>46317.91666666666</v>
       </c>
     </row>
     <row r="119">
@@ -6956,13 +6956,13 @@
         </is>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46319.54166666666</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>46319.58333333334</v>
+        <v>46319.75</v>
       </c>
       <c r="M119" s="1" t="n">
-        <v>46319.83333333334</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="120">
@@ -7011,13 +7011,13 @@
         </is>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46320.125</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>46320.25</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="M120" s="1" t="n">
-        <v>46321.75</v>
+        <v>46321.91666666666</v>
       </c>
     </row>
     <row r="121">
@@ -7066,13 +7066,13 @@
         </is>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46321.95833333334</v>
+        <v>46322.125</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>46322</v>
+        <v>46322.16666666666</v>
       </c>
       <c r="M121" s="1" t="n">
-        <v>46322.41666666666</v>
+        <v>46322.58333333334</v>
       </c>
     </row>
     <row r="122">
@@ -7121,13 +7121,13 @@
         </is>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46324</v>
+        <v>46324.16666666666</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>46324.16666666666</v>
+        <v>46324.33333333334</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46324.875</v>
       </c>
     </row>
     <row r="123">
@@ -7176,13 +7176,13 @@
         </is>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46332.58333333334</v>
+        <v>46332.75</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>46332.625</v>
+        <v>46332.79166666666</v>
       </c>
       <c r="M123" s="1" t="n">
-        <v>46333.70833333334</v>
+        <v>46333.875</v>
       </c>
     </row>
     <row r="124">
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46333.83333333334</v>
+        <v>46334</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>46333.875</v>
+        <v>46334.04166666666</v>
       </c>
       <c r="M124" s="1" t="n">
-        <v>46334.125</v>
+        <v>46334.29166666666</v>
       </c>
     </row>
     <row r="125">
@@ -7286,13 +7286,13 @@
         </is>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46334.54166666666</v>
+        <v>46334.70833333334</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>46334.625</v>
+        <v>46334.79166666666</v>
       </c>
       <c r="M125" s="1" t="n">
-        <v>46334.95833333334</v>
+        <v>46335.125</v>
       </c>
     </row>
     <row r="126">
@@ -7341,13 +7341,13 @@
         </is>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46340.04166666666</v>
+        <v>46340.20833333334</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>46340.20833333334</v>
+        <v>46340.375</v>
       </c>
       <c r="M126" s="1" t="n">
-        <v>46340.83333333334</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="127">
@@ -7396,13 +7396,13 @@
         </is>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46342.625</v>
+        <v>46342.79166666666</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>46342.66666666666</v>
+        <v>46342.83333333334</v>
       </c>
       <c r="M127" s="1" t="n">
-        <v>46342.91666666666</v>
+        <v>46343.08333333334</v>
       </c>
     </row>
     <row r="128">
@@ -7451,13 +7451,13 @@
         </is>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46343.20833333334</v>
+        <v>46343.375</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>46343.33333333334</v>
+        <v>46343.5</v>
       </c>
       <c r="M128" s="1" t="n">
-        <v>46344.83333333334</v>
+        <v>46345</v>
       </c>
     </row>
     <row r="129">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="K129" s="1" t="n">
-        <v>46345.04166666666</v>
+        <v>46345.20833333334</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>46345.08333333334</v>
+        <v>46345.25</v>
       </c>
       <c r="M129" s="1" t="n">
-        <v>46345.5</v>
+        <v>46345.66666666666</v>
       </c>
     </row>
     <row r="130">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="K130" s="1" t="n">
-        <v>46347.125</v>
+        <v>46347.29166666666</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>46347.29166666666</v>
+        <v>46347.45833333334</v>
       </c>
       <c r="M130" s="1" t="n">
-        <v>46347.83333333334</v>
+        <v>46348</v>
       </c>
     </row>
     <row r="131">
@@ -7616,13 +7616,13 @@
         </is>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46353.58333333334</v>
+        <v>46353.75</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>46353.625</v>
+        <v>46353.79166666666</v>
       </c>
       <c r="M131" s="1" t="n">
-        <v>46354.70833333334</v>
+        <v>46354.875</v>
       </c>
     </row>
     <row r="132">
@@ -7671,13 +7671,13 @@
         </is>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46354.83333333334</v>
+        <v>46355</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>46354.875</v>
+        <v>46355.04166666666</v>
       </c>
       <c r="M132" s="1" t="n">
-        <v>46355.125</v>
+        <v>46355.29166666666</v>
       </c>
     </row>
     <row r="133">
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46355.54166666666</v>
+        <v>46355.70833333334</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>46355.625</v>
+        <v>46355.79166666666</v>
       </c>
       <c r="M133" s="1" t="n">
-        <v>46355.95833333334</v>
+        <v>46356.125</v>
       </c>
     </row>
     <row r="134">
@@ -7781,13 +7781,13 @@
         </is>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46361.04166666666</v>
+        <v>46361.20833333334</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>46361.20833333334</v>
+        <v>46361.375</v>
       </c>
       <c r="M134" s="1" t="n">
-        <v>46361.83333333334</v>
+        <v>46362</v>
       </c>
     </row>
     <row r="135">
@@ -7836,13 +7836,13 @@
         </is>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46363.625</v>
+        <v>46363.79166666666</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>46363.66666666666</v>
+        <v>46363.83333333334</v>
       </c>
       <c r="M135" s="1" t="n">
-        <v>46363.91666666666</v>
+        <v>46364.08333333334</v>
       </c>
     </row>
     <row r="136">
@@ -7891,13 +7891,13 @@
         </is>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46364.20833333334</v>
+        <v>46364.375</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>46364.33333333334</v>
+        <v>46364.5</v>
       </c>
       <c r="M136" s="1" t="n">
-        <v>46365.83333333334</v>
+        <v>46366</v>
       </c>
     </row>
     <row r="137">
@@ -7946,13 +7946,13 @@
         </is>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46366.04166666666</v>
+        <v>46366.20833333334</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>46366.08333333334</v>
+        <v>46366.25</v>
       </c>
       <c r="M137" s="1" t="n">
-        <v>46366.5</v>
+        <v>46366.66666666666</v>
       </c>
     </row>
     <row r="138">
@@ -8001,13 +8001,13 @@
         </is>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46368.08333333334</v>
+        <v>46368.25</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>46368.25</v>
+        <v>46368.41666666666</v>
       </c>
       <c r="M138" s="1" t="n">
-        <v>46368.79166666666</v>
+        <v>46368.95833333334</v>
       </c>
     </row>
     <row r="139">
@@ -8056,13 +8056,13 @@
         </is>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46374.58333333334</v>
+        <v>46374.75</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>46374.625</v>
+        <v>46374.79166666666</v>
       </c>
       <c r="M139" s="1" t="n">
-        <v>46375.70833333334</v>
+        <v>46375.875</v>
       </c>
     </row>
     <row r="140">
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46375.83333333334</v>
+        <v>46376</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>46375.875</v>
+        <v>46376.04166666666</v>
       </c>
       <c r="M140" s="1" t="n">
-        <v>46376.125</v>
+        <v>46376.29166666666</v>
       </c>
     </row>
     <row r="141">
@@ -8166,13 +8166,13 @@
         </is>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46376.54166666666</v>
+        <v>46376.70833333334</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>46376.625</v>
+        <v>46376.79166666666</v>
       </c>
       <c r="M141" s="1" t="n">
-        <v>46376.95833333334</v>
+        <v>46377.125</v>
       </c>
     </row>
     <row r="142">
@@ -8221,13 +8221,13 @@
         </is>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46382.04166666666</v>
+        <v>46382.20833333334</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>46382.20833333334</v>
+        <v>46382.375</v>
       </c>
       <c r="M142" s="1" t="n">
-        <v>46382.83333333334</v>
+        <v>46383</v>
       </c>
     </row>
     <row r="143">
@@ -8276,13 +8276,13 @@
         </is>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46384.625</v>
+        <v>46384.79166666666</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>46384.66666666666</v>
+        <v>46384.83333333334</v>
       </c>
       <c r="M143" s="1" t="n">
-        <v>46384.91666666666</v>
+        <v>46385.08333333334</v>
       </c>
     </row>
     <row r="144">
@@ -8331,13 +8331,13 @@
         </is>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46385.20833333334</v>
+        <v>46385.375</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>46385.33333333334</v>
+        <v>46385.5</v>
       </c>
       <c r="M144" s="1" t="n">
-        <v>46386.83333333334</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="145">
@@ -8386,13 +8386,13 @@
         </is>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46387.04166666666</v>
+        <v>46387.20833333334</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>46387.08333333334</v>
+        <v>46387.25</v>
       </c>
       <c r="M145" s="1" t="n">
-        <v>46387.5</v>
+        <v>46387.66666666666</v>
       </c>
     </row>
     <row r="146">
@@ -8437,13 +8437,13 @@
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" s="1" t="n">
-        <v>46389.08333333334</v>
+        <v>46389.25</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>46389.25</v>
+        <v>46389.41666666666</v>
       </c>
       <c r="M146" s="1" t="n">
-        <v>46389.79166666666</v>
+        <v>46389.95833333334</v>
       </c>
     </row>
     <row r="147">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -6684,10 +6684,10 @@
         <v>46309.16666666666</v>
       </c>
       <c r="L114" s="1" t="n">
-        <v>46309.20833333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="M114" s="1" t="n">
-        <v>46309.91666666666</v>
+        <v>46310.45833333334</v>
       </c>
     </row>
     <row r="115">
@@ -7176,13 +7176,13 @@
         </is>
       </c>
       <c r="K123" s="1" t="n">
-        <v>46332.75</v>
+        <v>46332.25</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>46332.79166666666</v>
+        <v>46332.29166666666</v>
       </c>
       <c r="M123" s="1" t="n">
-        <v>46333.875</v>
+        <v>46333.375</v>
       </c>
     </row>
     <row r="124">
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="K124" s="1" t="n">
-        <v>46334</v>
+        <v>46333.5</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>46334.04166666666</v>
+        <v>46333.54166666666</v>
       </c>
       <c r="M124" s="1" t="n">
-        <v>46334.29166666666</v>
+        <v>46333.79166666666</v>
       </c>
     </row>
     <row r="125">
@@ -7286,13 +7286,13 @@
         </is>
       </c>
       <c r="K125" s="1" t="n">
-        <v>46334.70833333334</v>
+        <v>46334.20833333334</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>46334.79166666666</v>
+        <v>46334.29166666666</v>
       </c>
       <c r="M125" s="1" t="n">
-        <v>46335.125</v>
+        <v>46334.625</v>
       </c>
     </row>
     <row r="126">
@@ -7341,13 +7341,13 @@
         </is>
       </c>
       <c r="K126" s="1" t="n">
-        <v>46340.20833333334</v>
+        <v>46339.70833333334</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>46340.375</v>
+        <v>46339.875</v>
       </c>
       <c r="M126" s="1" t="n">
-        <v>46341</v>
+        <v>46340.5</v>
       </c>
     </row>
     <row r="127">
@@ -7396,13 +7396,13 @@
         </is>
       </c>
       <c r="K127" s="1" t="n">
-        <v>46342.79166666666</v>
+        <v>46342.29166666666</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>46342.83333333334</v>
+        <v>46342.33333333334</v>
       </c>
       <c r="M127" s="1" t="n">
-        <v>46343.08333333334</v>
+        <v>46342.58333333334</v>
       </c>
     </row>
     <row r="128">
@@ -7451,13 +7451,13 @@
         </is>
       </c>
       <c r="K128" s="1" t="n">
-        <v>46343.375</v>
+        <v>46342.875</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>46343.5</v>
+        <v>46343</v>
       </c>
       <c r="M128" s="1" t="n">
-        <v>46345</v>
+        <v>46344.5</v>
       </c>
     </row>
     <row r="129">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="K129" s="1" t="n">
-        <v>46345.20833333334</v>
+        <v>46344.70833333334</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>46345.25</v>
+        <v>46344.75</v>
       </c>
       <c r="M129" s="1" t="n">
-        <v>46345.66666666666</v>
+        <v>46345.16666666666</v>
       </c>
     </row>
     <row r="130">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="K130" s="1" t="n">
-        <v>46347.29166666666</v>
+        <v>46346.79166666666</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>46347.45833333334</v>
+        <v>46346.95833333334</v>
       </c>
       <c r="M130" s="1" t="n">
-        <v>46348</v>
+        <v>46347.5</v>
       </c>
     </row>
     <row r="131">
@@ -7616,13 +7616,13 @@
         </is>
       </c>
       <c r="K131" s="1" t="n">
-        <v>46353.75</v>
+        <v>46353.25</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>46353.79166666666</v>
+        <v>46353.29166666666</v>
       </c>
       <c r="M131" s="1" t="n">
-        <v>46354.875</v>
+        <v>46354.375</v>
       </c>
     </row>
     <row r="132">
@@ -7671,13 +7671,13 @@
         </is>
       </c>
       <c r="K132" s="1" t="n">
-        <v>46355</v>
+        <v>46354.5</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>46355.04166666666</v>
+        <v>46354.54166666666</v>
       </c>
       <c r="M132" s="1" t="n">
-        <v>46355.29166666666</v>
+        <v>46354.79166666666</v>
       </c>
     </row>
     <row r="133">
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="K133" s="1" t="n">
-        <v>46355.70833333334</v>
+        <v>46355.20833333334</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>46355.79166666666</v>
+        <v>46355.29166666666</v>
       </c>
       <c r="M133" s="1" t="n">
-        <v>46356.125</v>
+        <v>46355.625</v>
       </c>
     </row>
     <row r="134">
@@ -7781,13 +7781,13 @@
         </is>
       </c>
       <c r="K134" s="1" t="n">
-        <v>46361.20833333334</v>
+        <v>46360.70833333334</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>46361.375</v>
+        <v>46360.875</v>
       </c>
       <c r="M134" s="1" t="n">
-        <v>46362</v>
+        <v>46361.5</v>
       </c>
     </row>
     <row r="135">
@@ -7836,13 +7836,13 @@
         </is>
       </c>
       <c r="K135" s="1" t="n">
-        <v>46363.79166666666</v>
+        <v>46363.29166666666</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>46363.83333333334</v>
+        <v>46363.33333333334</v>
       </c>
       <c r="M135" s="1" t="n">
-        <v>46364.08333333334</v>
+        <v>46363.58333333334</v>
       </c>
     </row>
     <row r="136">
@@ -7891,13 +7891,13 @@
         </is>
       </c>
       <c r="K136" s="1" t="n">
-        <v>46364.375</v>
+        <v>46363.875</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>46364.5</v>
+        <v>46364</v>
       </c>
       <c r="M136" s="1" t="n">
-        <v>46366</v>
+        <v>46365.5</v>
       </c>
     </row>
     <row r="137">
@@ -7946,13 +7946,13 @@
         </is>
       </c>
       <c r="K137" s="1" t="n">
-        <v>46366.20833333334</v>
+        <v>46365.70833333334</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>46366.25</v>
+        <v>46365.75</v>
       </c>
       <c r="M137" s="1" t="n">
-        <v>46366.66666666666</v>
+        <v>46366.16666666666</v>
       </c>
     </row>
     <row r="138">
@@ -8001,13 +8001,13 @@
         </is>
       </c>
       <c r="K138" s="1" t="n">
-        <v>46368.25</v>
+        <v>46367.75</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>46368.41666666666</v>
+        <v>46367.91666666666</v>
       </c>
       <c r="M138" s="1" t="n">
-        <v>46368.95833333334</v>
+        <v>46368.45833333334</v>
       </c>
     </row>
     <row r="139">
@@ -8056,13 +8056,13 @@
         </is>
       </c>
       <c r="K139" s="1" t="n">
-        <v>46374.75</v>
+        <v>46374.25</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>46374.79166666666</v>
+        <v>46374.29166666666</v>
       </c>
       <c r="M139" s="1" t="n">
-        <v>46375.875</v>
+        <v>46375.375</v>
       </c>
     </row>
     <row r="140">
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="K140" s="1" t="n">
-        <v>46376</v>
+        <v>46375.5</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>46376.04166666666</v>
+        <v>46375.54166666666</v>
       </c>
       <c r="M140" s="1" t="n">
-        <v>46376.29166666666</v>
+        <v>46375.79166666666</v>
       </c>
     </row>
     <row r="141">
@@ -8166,13 +8166,13 @@
         </is>
       </c>
       <c r="K141" s="1" t="n">
-        <v>46376.70833333334</v>
+        <v>46376.20833333334</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>46376.79166666666</v>
+        <v>46376.29166666666</v>
       </c>
       <c r="M141" s="1" t="n">
-        <v>46377.125</v>
+        <v>46376.625</v>
       </c>
     </row>
     <row r="142">
@@ -8221,13 +8221,13 @@
         </is>
       </c>
       <c r="K142" s="1" t="n">
-        <v>46382.20833333334</v>
+        <v>46381.70833333334</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>46382.375</v>
+        <v>46381.875</v>
       </c>
       <c r="M142" s="1" t="n">
-        <v>46383</v>
+        <v>46382.5</v>
       </c>
     </row>
     <row r="143">
@@ -8276,13 +8276,13 @@
         </is>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46384.79166666666</v>
+        <v>46384.29166666666</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>46384.83333333334</v>
+        <v>46384.33333333334</v>
       </c>
       <c r="M143" s="1" t="n">
-        <v>46385.08333333334</v>
+        <v>46384.58333333334</v>
       </c>
     </row>
     <row r="144">
@@ -8331,13 +8331,13 @@
         </is>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46385.375</v>
+        <v>46384.875</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>46385.5</v>
+        <v>46385</v>
       </c>
       <c r="M144" s="1" t="n">
-        <v>46387</v>
+        <v>46386.5</v>
       </c>
     </row>
     <row r="145">
@@ -8386,13 +8386,13 @@
         </is>
       </c>
       <c r="K145" s="1" t="n">
-        <v>46387.20833333334</v>
+        <v>46386.70833333334</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>46387.25</v>
+        <v>46386.75</v>
       </c>
       <c r="M145" s="1" t="n">
-        <v>46387.66666666666</v>
+        <v>46387.16666666666</v>
       </c>
     </row>
     <row r="146">
@@ -8437,13 +8437,13 @@
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" s="1" t="n">
-        <v>46389.25</v>
+        <v>46388.75</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>46389.41666666666</v>
+        <v>46388.91666666666</v>
       </c>
       <c r="M146" s="1" t="n">
-        <v>46389.95833333334</v>
+        <v>46389.45833333334</v>
       </c>
     </row>
     <row r="147">
@@ -10361,7 +10361,7 @@
         <v>46307.04166666666</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>46308.41666666666</v>
+        <v>46308.5</v>
       </c>
       <c r="M181" s="1" t="n">
         <v>46309.04166666666</v>
@@ -10413,13 +10413,13 @@
         </is>
       </c>
       <c r="K182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L182" s="1" t="n">
-        <v>46312.04166666666</v>
+        <v>46313.04166666666</v>
       </c>
       <c r="M182" s="1" t="n">
-        <v>46312.91666666666</v>
+        <v>46313.91666666666</v>
       </c>
     </row>
     <row r="183">
@@ -10468,13 +10468,13 @@
         </is>
       </c>
       <c r="K183" s="1" t="n">
-        <v>46313.20833333334</v>
+        <v>46314.20833333334</v>
       </c>
       <c r="L183" s="1" t="n">
-        <v>46313.27083333334</v>
+        <v>46314.27083333334</v>
       </c>
       <c r="M183" s="1" t="n">
-        <v>46313.75</v>
+        <v>46314.75</v>
       </c>
     </row>
     <row r="184">
@@ -10523,13 +10523,13 @@
         </is>
       </c>
       <c r="K184" s="1" t="n">
-        <v>46314.75</v>
+        <v>46315.75</v>
       </c>
       <c r="L184" s="1" t="n">
-        <v>46315.25</v>
+        <v>46316.25</v>
       </c>
       <c r="M184" s="1" t="n">
-        <v>46316.25</v>
+        <v>46317.25</v>
       </c>
     </row>
     <row r="185">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="K185" s="1" t="n">
-        <v>46323.25</v>
+        <v>46324.25</v>
       </c>
       <c r="L185" s="1" t="n">
-        <v>46323.33333333334</v>
+        <v>46324.33333333334</v>
       </c>
       <c r="M185" s="1" t="n">
-        <v>46324.70833333334</v>
+        <v>46325.70833333334</v>
       </c>
     </row>
     <row r="186">
@@ -10633,13 +10633,13 @@
         </is>
       </c>
       <c r="K186" s="1" t="n">
-        <v>46325.70833333334</v>
+        <v>46326.70833333334</v>
       </c>
       <c r="L186" s="1" t="n">
-        <v>46325.79166666666</v>
+        <v>46326.79166666666</v>
       </c>
       <c r="M186" s="1" t="n">
-        <v>46326.79166666666</v>
+        <v>46327.79166666666</v>
       </c>
     </row>
     <row r="187">
@@ -10688,13 +10688,13 @@
         </is>
       </c>
       <c r="K187" s="1" t="n">
-        <v>46333.79166666666</v>
+        <v>46334.79166666666</v>
       </c>
       <c r="L187" s="1" t="n">
-        <v>46334.29166666666</v>
+        <v>46335.29166666666</v>
       </c>
       <c r="M187" s="1" t="n">
-        <v>46335.29166666666</v>
+        <v>46336.29166666666</v>
       </c>
     </row>
     <row r="188">
@@ -10743,13 +10743,13 @@
         </is>
       </c>
       <c r="K188" s="1" t="n">
-        <v>46336.66666666666</v>
+        <v>46337.66666666666</v>
       </c>
       <c r="L188" s="1" t="n">
-        <v>46336.70833333334</v>
+        <v>46337.70833333334</v>
       </c>
       <c r="M188" s="1" t="n">
-        <v>46338.41666666666</v>
+        <v>46339.41666666666</v>
       </c>
     </row>
     <row r="189">
@@ -10798,13 +10798,13 @@
         </is>
       </c>
       <c r="K189" s="1" t="n">
-        <v>46338.70833333334</v>
+        <v>46339.70833333334</v>
       </c>
       <c r="L189" s="1" t="n">
-        <v>46338.77083333334</v>
+        <v>46339.77083333334</v>
       </c>
       <c r="M189" s="1" t="n">
-        <v>46339.25</v>
+        <v>46340.25</v>
       </c>
     </row>
     <row r="190">
@@ -10853,13 +10853,13 @@
         </is>
       </c>
       <c r="K190" s="1" t="n">
-        <v>46340.25</v>
+        <v>46341.25</v>
       </c>
       <c r="L190" s="1" t="n">
-        <v>46340.45833333334</v>
+        <v>46341.45833333334</v>
       </c>
       <c r="M190" s="1" t="n">
-        <v>46341.45833333334</v>
+        <v>46342.45833333334</v>
       </c>
     </row>
     <row r="191">
@@ -10908,13 +10908,13 @@
         </is>
       </c>
       <c r="K191" s="1" t="n">
-        <v>46348.45833333334</v>
+        <v>46349.45833333334</v>
       </c>
       <c r="L191" s="1" t="n">
-        <v>46348.54166666666</v>
+        <v>46349.54166666666</v>
       </c>
       <c r="M191" s="1" t="n">
-        <v>46349.91666666666</v>
+        <v>46350.91666666666</v>
       </c>
     </row>
     <row r="192">
@@ -10963,13 +10963,13 @@
         </is>
       </c>
       <c r="K192" s="1" t="n">
-        <v>46350.91666666666</v>
+        <v>46351.91666666666</v>
       </c>
       <c r="L192" s="1" t="n">
-        <v>46351</v>
+        <v>46352</v>
       </c>
       <c r="M192" s="1" t="n">
-        <v>46352</v>
+        <v>46353</v>
       </c>
     </row>
     <row r="193">
@@ -11018,13 +11018,13 @@
         </is>
       </c>
       <c r="K193" s="1" t="n">
-        <v>46355.41666666666</v>
+        <v>46356.41666666666</v>
       </c>
       <c r="L193" s="1" t="n">
-        <v>46355.58333333334</v>
+        <v>46356.58333333334</v>
       </c>
       <c r="M193" s="1" t="n">
-        <v>46356.41666666666</v>
+        <v>46357.41666666666</v>
       </c>
     </row>
     <row r="194">
@@ -11073,13 +11073,13 @@
         </is>
       </c>
       <c r="K194" s="1" t="n">
-        <v>46361</v>
+        <v>46362</v>
       </c>
       <c r="L194" s="1" t="n">
-        <v>46361.16666666666</v>
+        <v>46362.16666666666</v>
       </c>
       <c r="M194" s="1" t="n">
-        <v>46362.16666666666</v>
+        <v>46363.16666666666</v>
       </c>
     </row>
     <row r="195">
@@ -21503,13 +21503,13 @@
         </is>
       </c>
       <c r="K384" s="1" t="n">
-        <v>46308.04166666666</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="L384" s="1" t="n">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="M384" s="1" t="n">
-        <v>46309.625</v>
+        <v>46310.625</v>
       </c>
     </row>
     <row r="385">
@@ -21558,13 +21558,13 @@
         </is>
       </c>
       <c r="K385" s="1" t="n">
-        <v>46309.83333333334</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="L385" s="1" t="n">
-        <v>46309.875</v>
+        <v>46310.875</v>
       </c>
       <c r="M385" s="1" t="n">
-        <v>46310.25</v>
+        <v>46311.25</v>
       </c>
     </row>
     <row r="386">
@@ -21613,13 +21613,13 @@
         </is>
       </c>
       <c r="K386" s="1" t="n">
-        <v>46314.08333333334</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="L386" s="1" t="n">
-        <v>46314.14583333334</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="M386" s="1" t="n">
-        <v>46314.64583333334</v>
+        <v>46315.64583333334</v>
       </c>
     </row>
     <row r="387">
@@ -21668,13 +21668,13 @@
         </is>
       </c>
       <c r="K387" s="1" t="n">
-        <v>46315.5</v>
+        <v>46316.5</v>
       </c>
       <c r="L387" s="1" t="n">
-        <v>46315.54166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="M387" s="1" t="n">
-        <v>46316.16666666666</v>
+        <v>46317.16666666666</v>
       </c>
     </row>
     <row r="388">
@@ -21723,13 +21723,13 @@
         </is>
       </c>
       <c r="K388" s="1" t="n">
-        <v>46318.45833333334</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="L388" s="1" t="n">
-        <v>46318.5</v>
+        <v>46319.5</v>
       </c>
       <c r="M388" s="1" t="n">
-        <v>46319.5</v>
+        <v>46320.5</v>
       </c>
     </row>
     <row r="389">
@@ -21778,13 +21778,13 @@
         </is>
       </c>
       <c r="K389" s="1" t="n">
-        <v>46319.79166666666</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="L389" s="1" t="n">
-        <v>46319.85416666666</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="M389" s="1" t="n">
-        <v>46320.1875</v>
+        <v>46321.1875</v>
       </c>
     </row>
     <row r="390">
@@ -21833,13 +21833,13 @@
         </is>
       </c>
       <c r="K390" s="1" t="n">
-        <v>46323.08333333334</v>
+        <v>46324.08333333334</v>
       </c>
       <c r="L390" s="1" t="n">
-        <v>46323.125</v>
+        <v>46324.125</v>
       </c>
       <c r="M390" s="1" t="n">
-        <v>46323.64583333334</v>
+        <v>46324.64583333334</v>
       </c>
     </row>
     <row r="391">
@@ -21888,13 +21888,13 @@
         </is>
       </c>
       <c r="K391" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="L391" s="1" t="n">
-        <v>46326.16666666666</v>
+        <v>46327.16666666666</v>
       </c>
       <c r="M391" s="1" t="n">
-        <v>46326.79166666666</v>
+        <v>46327.79166666666</v>
       </c>
     </row>
     <row r="392">
@@ -21943,13 +21943,13 @@
         </is>
       </c>
       <c r="K392" s="1" t="n">
-        <v>46328.54166666666</v>
+        <v>46329.54166666666</v>
       </c>
       <c r="L392" s="1" t="n">
-        <v>46328.58333333334</v>
+        <v>46329.58333333334</v>
       </c>
       <c r="M392" s="1" t="n">
-        <v>46328.75</v>
+        <v>46329.75</v>
       </c>
     </row>
     <row r="393">
@@ -21998,13 +21998,13 @@
         </is>
       </c>
       <c r="K393" s="1" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="L393" s="1" t="n">
-        <v>46329.125</v>
+        <v>46330.125</v>
       </c>
       <c r="M393" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46331.45833333334</v>
       </c>
     </row>
     <row r="394">
@@ -22053,13 +22053,13 @@
         </is>
       </c>
       <c r="K394" s="1" t="n">
-        <v>46330.95833333334</v>
+        <v>46331.95833333334</v>
       </c>
       <c r="L394" s="1" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="M394" s="1" t="n">
-        <v>46331.29166666666</v>
+        <v>46332.29166666666</v>
       </c>
     </row>
     <row r="395">
@@ -22108,13 +22108,13 @@
         </is>
       </c>
       <c r="K395" s="1" t="n">
-        <v>46335.375</v>
+        <v>46336.375</v>
       </c>
       <c r="L395" s="1" t="n">
-        <v>46335.41666666666</v>
+        <v>46336.41666666666</v>
       </c>
       <c r="M395" s="1" t="n">
-        <v>46335.875</v>
+        <v>46336.875</v>
       </c>
     </row>
     <row r="396">
@@ -22163,13 +22163,13 @@
         </is>
       </c>
       <c r="K396" s="1" t="n">
-        <v>46336.95833333334</v>
+        <v>46337.95833333334</v>
       </c>
       <c r="L396" s="1" t="n">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="M396" s="1" t="n">
-        <v>46337.58333333334</v>
+        <v>46338.58333333334</v>
       </c>
     </row>
     <row r="397">
@@ -28310,10 +28310,10 @@
         <v>46307.375</v>
       </c>
       <c r="L508" s="1" t="n">
-        <v>46312.45833333334</v>
+        <v>46312.375</v>
       </c>
       <c r="M508" s="1" t="n">
-        <v>46313.45833333334</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="509">
@@ -28417,13 +28417,13 @@
         </is>
       </c>
       <c r="K510" s="1" t="n">
-        <v>46314.45833333334</v>
+        <v>46314</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>46316.45833333334</v>
+        <v>46315</v>
       </c>
       <c r="M510" s="1" t="n">
-        <v>46317.04166666666</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="511">
@@ -28472,13 +28472,13 @@
         </is>
       </c>
       <c r="K511" s="1" t="n">
-        <v>46317.79166666666</v>
+        <v>46316.75</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>46318.875</v>
+        <v>46317.83333333334</v>
       </c>
       <c r="M511" s="1" t="n">
-        <v>46319.54166666666</v>
+        <v>46318.5</v>
       </c>
     </row>
     <row r="512">
@@ -28527,13 +28527,13 @@
         </is>
       </c>
       <c r="K512" s="1" t="n">
-        <v>46321.45833333334</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>46321.58333333334</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="M512" s="1" t="n">
-        <v>46322.33333333334</v>
+        <v>46321.29166666666</v>
       </c>
     </row>
     <row r="513">
@@ -28582,13 +28582,13 @@
         </is>
       </c>
       <c r="K513" s="1" t="n">
-        <v>46334.08333333334</v>
+        <v>46333.04166666666</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>46344.08333333334</v>
+        <v>46343.04166666666</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46351.08333333334</v>
+        <v>46350.04166666666</v>
       </c>
     </row>
     <row r="514">
@@ -28633,13 +28633,13 @@
       </c>
       <c r="J514" t="inlineStr"/>
       <c r="K514" s="1" t="n">
+        <v>46364.125</v>
+      </c>
+      <c r="L514" s="1" t="n">
+        <v>46364.16666666666</v>
+      </c>
+      <c r="M514" s="1" t="n">
         <v>46365.16666666666</v>
-      </c>
-      <c r="L514" s="1" t="n">
-        <v>46365.20833333334</v>
-      </c>
-      <c r="M514" s="1" t="n">
-        <v>46366.20833333334</v>
       </c>
     </row>
     <row r="515">
@@ -28856,10 +28856,10 @@
         <v>46307.79166666666</v>
       </c>
       <c r="L518" s="1" t="n">
-        <v>46308.625</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="M518" s="1" t="n">
-        <v>46309.375</v>
+        <v>46309.41666666666</v>
       </c>
     </row>
     <row r="519">
@@ -28908,13 +28908,13 @@
         </is>
       </c>
       <c r="K519" s="1" t="n">
-        <v>46310.875</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="L519" s="1" t="n">
-        <v>46311</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="M519" s="1" t="n">
-        <v>46311.5</v>
+        <v>46311.54166666666</v>
       </c>
     </row>
     <row r="520">
@@ -30502,10 +30502,10 @@
         <v>46306.8125</v>
       </c>
       <c r="L548" s="1" t="n">
-        <v>46306.97916666666</v>
+        <v>46307.02083333334</v>
       </c>
       <c r="M548" s="1" t="n">
-        <v>46307.41666666666</v>
+        <v>46307.54166666666</v>
       </c>
     </row>
     <row r="549">
@@ -30554,13 +30554,13 @@
         </is>
       </c>
       <c r="K549" s="1" t="n">
-        <v>46309.04166666666</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="L549" s="1" t="n">
-        <v>46309.08333333334</v>
+        <v>46309.125</v>
       </c>
       <c r="M549" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46309.41666666666</v>
       </c>
     </row>
     <row r="550">
@@ -30609,13 +30609,13 @@
         </is>
       </c>
       <c r="K550" s="1" t="n">
-        <v>46309.54166666666</v>
+        <v>46309.5</v>
       </c>
       <c r="L550" s="1" t="n">
-        <v>46309.625</v>
+        <v>46309.58333333334</v>
       </c>
       <c r="M550" s="1" t="n">
-        <v>46310.625</v>
+        <v>46310.45833333334</v>
       </c>
     </row>
     <row r="551">
@@ -30664,13 +30664,13 @@
         </is>
       </c>
       <c r="K551" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.625</v>
       </c>
       <c r="L551" s="1" t="n">
-        <v>46310.83333333334</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="M551" s="1" t="n">
-        <v>46311.33333333334</v>
+        <v>46311.16666666666</v>
       </c>
     </row>
     <row r="552">
@@ -30719,13 +30719,13 @@
         </is>
       </c>
       <c r="K552" s="1" t="n">
-        <v>46313.14583333334</v>
+        <v>46312.625</v>
       </c>
       <c r="L552" s="1" t="n">
-        <v>46313.3125</v>
+        <v>46312.79166666666</v>
       </c>
       <c r="M552" s="1" t="n">
-        <v>46314</v>
+        <v>46313.47916666666</v>
       </c>
     </row>
     <row r="553">
@@ -30774,13 +30774,13 @@
         </is>
       </c>
       <c r="K553" s="1" t="n">
-        <v>46319.16666666666</v>
+        <v>46318.64583333334</v>
       </c>
       <c r="L553" s="1" t="n">
-        <v>46319.20833333334</v>
+        <v>46318.6875</v>
       </c>
       <c r="M553" s="1" t="n">
-        <v>46319.875</v>
+        <v>46319.35416666666</v>
       </c>
     </row>
     <row r="554">
@@ -30829,13 +30829,13 @@
         </is>
       </c>
       <c r="K554" s="1" t="n">
-        <v>46320.04166666666</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="L554" s="1" t="n">
-        <v>46320.10416666666</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="M554" s="1" t="n">
-        <v>46320.35416666666</v>
+        <v>46319.83333333334</v>
       </c>
     </row>
     <row r="555">
@@ -30884,13 +30884,13 @@
         </is>
       </c>
       <c r="K555" s="1" t="n">
-        <v>46321.36458333334</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="L555" s="1" t="n">
-        <v>46321.38541666666</v>
+        <v>46320.875</v>
       </c>
       <c r="M555" s="1" t="n">
-        <v>46321.98958333334</v>
+        <v>46321.47916666666</v>
       </c>
     </row>
     <row r="556">
@@ -30939,13 +30939,13 @@
         </is>
       </c>
       <c r="K556" s="1" t="n">
-        <v>46326.90625</v>
+        <v>46326.39583333334</v>
       </c>
       <c r="L556" s="1" t="n">
-        <v>46327.07291666666</v>
+        <v>46326.5625</v>
       </c>
       <c r="M556" s="1" t="n">
-        <v>46327.65625</v>
+        <v>46327.14583333334</v>
       </c>
     </row>
     <row r="557">
@@ -30994,13 +30994,13 @@
         </is>
       </c>
       <c r="K557" s="1" t="n">
-        <v>46329.30208333334</v>
+        <v>46328.79166666666</v>
       </c>
       <c r="L557" s="1" t="n">
-        <v>46329.34375</v>
+        <v>46328.83333333334</v>
       </c>
       <c r="M557" s="1" t="n">
-        <v>46329.69791666666</v>
+        <v>46329.1875</v>
       </c>
     </row>
     <row r="558">
@@ -31049,13 +31049,13 @@
         </is>
       </c>
       <c r="K558" s="1" t="n">
-        <v>46329.82291666666</v>
+        <v>46329.3125</v>
       </c>
       <c r="L558" s="1" t="n">
-        <v>46329.90625</v>
+        <v>46329.39583333334</v>
       </c>
       <c r="M558" s="1" t="n">
-        <v>46330.90625</v>
+        <v>46330.39583333334</v>
       </c>
     </row>
     <row r="559">
@@ -31104,13 +31104,13 @@
         </is>
       </c>
       <c r="K559" s="1" t="n">
-        <v>46331.11458333334</v>
+        <v>46330.60416666666</v>
       </c>
       <c r="L559" s="1" t="n">
-        <v>46331.15625</v>
+        <v>46330.64583333334</v>
       </c>
       <c r="M559" s="1" t="n">
-        <v>46331.65625</v>
+        <v>46331.14583333334</v>
       </c>
     </row>
     <row r="560">
@@ -31159,13 +31159,13 @@
         </is>
       </c>
       <c r="K560" s="1" t="n">
-        <v>46333.46875</v>
+        <v>46332.95833333334</v>
       </c>
       <c r="L560" s="1" t="n">
-        <v>46333.63541666666</v>
+        <v>46333.125</v>
       </c>
       <c r="M560" s="1" t="n">
-        <v>46334.32291666666</v>
+        <v>46333.8125</v>
       </c>
     </row>
     <row r="561">
@@ -31214,13 +31214,13 @@
         </is>
       </c>
       <c r="K561" s="1" t="n">
-        <v>46339.53125</v>
+        <v>46339.02083333334</v>
       </c>
       <c r="L561" s="1" t="n">
-        <v>46339.57291666666</v>
+        <v>46339.0625</v>
       </c>
       <c r="M561" s="1" t="n">
-        <v>46340.23958333334</v>
+        <v>46339.72916666666</v>
       </c>
     </row>
     <row r="562">
@@ -31269,13 +31269,13 @@
         </is>
       </c>
       <c r="K562" s="1" t="n">
-        <v>46340.40625</v>
+        <v>46339.89583333334</v>
       </c>
       <c r="L562" s="1" t="n">
-        <v>46340.46875</v>
+        <v>46339.95833333334</v>
       </c>
       <c r="M562" s="1" t="n">
-        <v>46340.71875</v>
+        <v>46340.20833333334</v>
       </c>
     </row>
     <row r="563">
@@ -31324,13 +31324,13 @@
         </is>
       </c>
       <c r="K563" s="1" t="n">
-        <v>46341.61458333334</v>
+        <v>46341.10416666666</v>
       </c>
       <c r="L563" s="1" t="n">
-        <v>46341.67708333334</v>
+        <v>46341.16666666666</v>
       </c>
       <c r="M563" s="1" t="n">
-        <v>46342.09375</v>
+        <v>46341.58333333334</v>
       </c>
     </row>
     <row r="564">
@@ -31379,13 +31379,13 @@
         </is>
       </c>
       <c r="K564" s="1" t="n">
-        <v>46342.36458333334</v>
+        <v>46341.85416666666</v>
       </c>
       <c r="L564" s="1" t="n">
-        <v>46342.38541666666</v>
+        <v>46341.875</v>
       </c>
       <c r="M564" s="1" t="n">
-        <v>46342.98958333334</v>
+        <v>46342.47916666666</v>
       </c>
     </row>
     <row r="565">
@@ -31434,13 +31434,13 @@
         </is>
       </c>
       <c r="K565" s="1" t="n">
-        <v>46347.90625</v>
+        <v>46347.39583333334</v>
       </c>
       <c r="L565" s="1" t="n">
-        <v>46348.07291666666</v>
+        <v>46347.5625</v>
       </c>
       <c r="M565" s="1" t="n">
-        <v>46348.65625</v>
+        <v>46348.14583333334</v>
       </c>
     </row>
     <row r="566">
@@ -31489,13 +31489,13 @@
         </is>
       </c>
       <c r="K566" s="1" t="n">
-        <v>46350.30208333334</v>
+        <v>46349.79166666666</v>
       </c>
       <c r="L566" s="1" t="n">
-        <v>46350.34375</v>
+        <v>46349.83333333334</v>
       </c>
       <c r="M566" s="1" t="n">
-        <v>46350.69791666666</v>
+        <v>46350.1875</v>
       </c>
     </row>
     <row r="567">
@@ -31544,13 +31544,13 @@
         </is>
       </c>
       <c r="K567" s="1" t="n">
-        <v>46350.82291666666</v>
+        <v>46350.3125</v>
       </c>
       <c r="L567" s="1" t="n">
-        <v>46350.90625</v>
+        <v>46350.39583333334</v>
       </c>
       <c r="M567" s="1" t="n">
-        <v>46351.90625</v>
+        <v>46351.39583333334</v>
       </c>
     </row>
     <row r="568">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="K568" s="1" t="n">
-        <v>46352.11458333334</v>
+        <v>46351.60416666666</v>
       </c>
       <c r="L568" s="1" t="n">
-        <v>46352.15625</v>
+        <v>46351.64583333334</v>
       </c>
       <c r="M568" s="1" t="n">
-        <v>46352.65625</v>
+        <v>46352.14583333334</v>
       </c>
     </row>
     <row r="569">
@@ -31654,13 +31654,13 @@
         </is>
       </c>
       <c r="K569" s="1" t="n">
-        <v>46354.46875</v>
+        <v>46353.95833333334</v>
       </c>
       <c r="L569" s="1" t="n">
-        <v>46354.63541666666</v>
+        <v>46354.125</v>
       </c>
       <c r="M569" s="1" t="n">
-        <v>46355.32291666666</v>
+        <v>46354.8125</v>
       </c>
     </row>
     <row r="570">
@@ -32204,13 +32204,13 @@
         </is>
       </c>
       <c r="K579" s="1" t="n">
-        <v>46381.91666666666</v>
+        <v>46381.5</v>
       </c>
       <c r="L579" s="1" t="n">
-        <v>46381.95833333334</v>
+        <v>46381.54166666666</v>
       </c>
       <c r="M579" s="1" t="n">
-        <v>46382.625</v>
+        <v>46382.20833333334</v>
       </c>
     </row>
     <row r="580">
@@ -32259,13 +32259,13 @@
         </is>
       </c>
       <c r="K580" s="1" t="n">
-        <v>46382.79166666666</v>
+        <v>46382.375</v>
       </c>
       <c r="L580" s="1" t="n">
-        <v>46382.85416666666</v>
+        <v>46382.4375</v>
       </c>
       <c r="M580" s="1" t="n">
-        <v>46383.10416666666</v>
+        <v>46382.6875</v>
       </c>
     </row>
     <row r="581">
@@ -32314,13 +32314,13 @@
         </is>
       </c>
       <c r="K581" s="1" t="n">
-        <v>46384</v>
+        <v>46383.58333333334</v>
       </c>
       <c r="L581" s="1" t="n">
+        <v>46383.64583333334</v>
+      </c>
+      <c r="M581" s="1" t="n">
         <v>46384.0625</v>
-      </c>
-      <c r="M581" s="1" t="n">
-        <v>46384.47916666666</v>
       </c>
     </row>
     <row r="582">
@@ -32369,13 +32369,13 @@
         </is>
       </c>
       <c r="K582" s="1" t="n">
-        <v>46384.75</v>
+        <v>46384.33333333334</v>
       </c>
       <c r="L582" s="1" t="n">
-        <v>46384.77083333334</v>
+        <v>46384.35416666666</v>
       </c>
       <c r="M582" s="1" t="n">
-        <v>46385.375</v>
+        <v>46384.95833333334</v>
       </c>
     </row>
     <row r="583">
@@ -32424,13 +32424,13 @@
         </is>
       </c>
       <c r="K583" s="1" t="n">
-        <v>46390.29166666666</v>
+        <v>46389.875</v>
       </c>
       <c r="L583" s="1" t="n">
-        <v>46390.45833333334</v>
+        <v>46390.04166666666</v>
       </c>
       <c r="M583" s="1" t="n">
-        <v>46391.04166666666</v>
+        <v>46390.625</v>
       </c>
     </row>
     <row r="584">
@@ -32479,13 +32479,13 @@
         </is>
       </c>
       <c r="K584" s="1" t="n">
-        <v>46392.6875</v>
+        <v>46392.27083333334</v>
       </c>
       <c r="L584" s="1" t="n">
-        <v>46392.72916666666</v>
+        <v>46392.3125</v>
       </c>
       <c r="M584" s="1" t="n">
-        <v>46393.08333333334</v>
+        <v>46392.66666666666</v>
       </c>
     </row>
     <row r="585">
@@ -32534,13 +32534,13 @@
         </is>
       </c>
       <c r="K585" s="1" t="n">
-        <v>46393.20833333334</v>
+        <v>46392.79166666666</v>
       </c>
       <c r="L585" s="1" t="n">
-        <v>46393.29166666666</v>
+        <v>46392.875</v>
       </c>
       <c r="M585" s="1" t="n">
-        <v>46394.29166666666</v>
+        <v>46393.875</v>
       </c>
     </row>
     <row r="586">
@@ -32589,13 +32589,13 @@
         </is>
       </c>
       <c r="K586" s="1" t="n">
-        <v>46394.5</v>
+        <v>46394.08333333334</v>
       </c>
       <c r="L586" s="1" t="n">
-        <v>46394.54166666666</v>
+        <v>46394.125</v>
       </c>
       <c r="M586" s="1" t="n">
-        <v>46395.04166666666</v>
+        <v>46394.625</v>
       </c>
     </row>
     <row r="587">
@@ -32640,13 +32640,13 @@
       </c>
       <c r="J587" t="inlineStr"/>
       <c r="K587" s="1" t="n">
-        <v>46396.85416666666</v>
+        <v>46396.4375</v>
       </c>
       <c r="L587" s="1" t="n">
-        <v>46397.02083333334</v>
+        <v>46396.60416666666</v>
       </c>
       <c r="M587" s="1" t="n">
-        <v>46397.70833333334</v>
+        <v>46397.29166666666</v>
       </c>
     </row>
     <row r="588">
@@ -38022,13 +38022,13 @@
         </is>
       </c>
       <c r="K685" s="1" t="n">
-        <v>46309.33333333334</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="L685" s="1" t="n">
-        <v>46309.375</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="M685" s="1" t="n">
-        <v>46309.72916666666</v>
+        <v>46309.625</v>
       </c>
     </row>
     <row r="686">
@@ -38077,13 +38077,13 @@
         </is>
       </c>
       <c r="K686" s="1" t="n">
-        <v>46309.85416666666</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="L686" s="1" t="n">
-        <v>46309.9375</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="M686" s="1" t="n">
-        <v>46310.9375</v>
+        <v>46311.25</v>
       </c>
     </row>
     <row r="687">
@@ -38132,13 +38132,13 @@
         </is>
       </c>
       <c r="K687" s="1" t="n">
-        <v>46311.14583333334</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="L687" s="1" t="n">
-        <v>46311.1875</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="M687" s="1" t="n">
-        <v>46311.6875</v>
+        <v>46311.95833333334</v>
       </c>
     </row>
     <row r="688">
@@ -38183,17 +38183,17 @@
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="K688" s="1" t="n">
-        <v>46313.45833333334</v>
+        <v>46313.72916666666</v>
       </c>
       <c r="L688" s="1" t="n">
-        <v>46313.625</v>
+        <v>46313.89583333334</v>
       </c>
       <c r="M688" s="1" t="n">
-        <v>46314.3125</v>
+        <v>46314.58333333334</v>
       </c>
     </row>
     <row r="689">
@@ -38228,27 +38228,27 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>INC07</t>
+          <t>PTK02</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
         <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
           <t>KRINC</t>
         </is>
       </c>
-      <c r="J689" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
       <c r="K689" s="1" t="n">
-        <v>46319.9375</v>
+        <v>46320.0625</v>
       </c>
       <c r="L689" s="1" t="n">
-        <v>46319.97916666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="M689" s="1" t="n">
-        <v>46320.64583333334</v>
+        <v>46320.77083333334</v>
       </c>
     </row>
     <row r="690">
@@ -38283,12 +38283,12 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>PTK02</t>
+          <t>INC07</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
@@ -38297,13 +38297,13 @@
         </is>
       </c>
       <c r="K690" s="1" t="n">
-        <v>46320.8125</v>
+        <v>46320.9375</v>
       </c>
       <c r="L690" s="1" t="n">
-        <v>46320.875</v>
+        <v>46321</v>
       </c>
       <c r="M690" s="1" t="n">
-        <v>46321.125</v>
+        <v>46321.25</v>
       </c>
     </row>
     <row r="691">
@@ -38352,13 +38352,13 @@
         </is>
       </c>
       <c r="K691" s="1" t="n">
-        <v>46322.02083333334</v>
+        <v>46322.1875</v>
       </c>
       <c r="L691" s="1" t="n">
-        <v>46322.08333333334</v>
+        <v>46322.25</v>
       </c>
       <c r="M691" s="1" t="n">
-        <v>46322.5</v>
+        <v>46322.66666666666</v>
       </c>
     </row>
     <row r="692">
@@ -38407,13 +38407,13 @@
         </is>
       </c>
       <c r="K692" s="1" t="n">
-        <v>46322.77083333334</v>
+        <v>46322.9375</v>
       </c>
       <c r="L692" s="1" t="n">
-        <v>46322.79166666666</v>
+        <v>46322.95833333334</v>
       </c>
       <c r="M692" s="1" t="n">
-        <v>46323.39583333334</v>
+        <v>46323.5625</v>
       </c>
     </row>
     <row r="693">
@@ -38462,13 +38462,13 @@
         </is>
       </c>
       <c r="K693" s="1" t="n">
-        <v>46328.3125</v>
+        <v>46328.47916666666</v>
       </c>
       <c r="L693" s="1" t="n">
-        <v>46328.47916666666</v>
+        <v>46328.64583333334</v>
       </c>
       <c r="M693" s="1" t="n">
-        <v>46329.0625</v>
+        <v>46329.22916666666</v>
       </c>
     </row>
     <row r="694">
@@ -38517,13 +38517,13 @@
         </is>
       </c>
       <c r="K694" s="1" t="n">
-        <v>46330.70833333334</v>
+        <v>46330.875</v>
       </c>
       <c r="L694" s="1" t="n">
-        <v>46330.75</v>
+        <v>46330.91666666666</v>
       </c>
       <c r="M694" s="1" t="n">
-        <v>46331.10416666666</v>
+        <v>46331.27083333334</v>
       </c>
     </row>
     <row r="695">
@@ -38572,13 +38572,13 @@
         </is>
       </c>
       <c r="K695" s="1" t="n">
-        <v>46331.22916666666</v>
+        <v>46331.39583333334</v>
       </c>
       <c r="L695" s="1" t="n">
-        <v>46331.3125</v>
+        <v>46331.47916666666</v>
       </c>
       <c r="M695" s="1" t="n">
-        <v>46332.3125</v>
+        <v>46332.47916666666</v>
       </c>
     </row>
     <row r="696">
@@ -38627,13 +38627,13 @@
         </is>
       </c>
       <c r="K696" s="1" t="n">
-        <v>46332.52083333334</v>
+        <v>46332.6875</v>
       </c>
       <c r="L696" s="1" t="n">
-        <v>46332.5625</v>
+        <v>46332.72916666666</v>
       </c>
       <c r="M696" s="1" t="n">
-        <v>46333.0625</v>
+        <v>46333.22916666666</v>
       </c>
     </row>
     <row r="697">
@@ -38682,13 +38682,13 @@
         </is>
       </c>
       <c r="K697" s="1" t="n">
-        <v>46334.875</v>
+        <v>46335.04166666666</v>
       </c>
       <c r="L697" s="1" t="n">
-        <v>46335.04166666666</v>
+        <v>46335.20833333334</v>
       </c>
       <c r="M697" s="1" t="n">
-        <v>46335.72916666666</v>
+        <v>46335.89583333334</v>
       </c>
     </row>
     <row r="698">
@@ -40053,13 +40053,13 @@
         </is>
       </c>
       <c r="K722" s="1" t="n">
-        <v>46306.95833333334</v>
+        <v>46307.02083333334</v>
       </c>
       <c r="L722" s="1" t="n">
-        <v>46307</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="M722" s="1" t="n">
-        <v>46307.97916666666</v>
+        <v>46308.02083333334</v>
       </c>
     </row>
     <row r="723">
@@ -40108,13 +40108,13 @@
         </is>
       </c>
       <c r="K723" s="1" t="n">
-        <v>46308.75</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="L723" s="1" t="n">
-        <v>46308.79166666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="M723" s="1" t="n">
-        <v>46309.25</v>
+        <v>46309.70833333334</v>
       </c>
     </row>
     <row r="724">
@@ -40163,13 +40163,13 @@
         </is>
       </c>
       <c r="K724" s="1" t="n">
-        <v>46311.75</v>
+        <v>46312.25</v>
       </c>
       <c r="L724" s="1" t="n">
-        <v>46311.79166666666</v>
+        <v>46312.29166666666</v>
       </c>
       <c r="M724" s="1" t="n">
-        <v>46312.41666666666</v>
+        <v>46312.91666666666</v>
       </c>
     </row>
     <row r="725">
@@ -40218,13 +40218,13 @@
         </is>
       </c>
       <c r="K725" s="1" t="n">
-        <v>46313.41666666666</v>
+        <v>46313.91666666666</v>
       </c>
       <c r="L725" s="1" t="n">
-        <v>46313.45833333334</v>
+        <v>46313.95833333334</v>
       </c>
       <c r="M725" s="1" t="n">
-        <v>46313.95833333334</v>
+        <v>46314.45833333334</v>
       </c>
     </row>
     <row r="726">
@@ -40273,13 +40273,13 @@
         </is>
       </c>
       <c r="K726" s="1" t="n">
-        <v>46315.04166666666</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="L726" s="1" t="n">
-        <v>46315.20833333334</v>
+        <v>46315.70833333334</v>
       </c>
       <c r="M726" s="1" t="n">
-        <v>46316</v>
+        <v>46316.5</v>
       </c>
     </row>
     <row r="727">
@@ -40328,13 +40328,13 @@
         </is>
       </c>
       <c r="K727" s="1" t="n">
-        <v>46321.75</v>
+        <v>46322.25</v>
       </c>
       <c r="L727" s="1" t="n">
-        <v>46321.79166666666</v>
+        <v>46322.29166666666</v>
       </c>
       <c r="M727" s="1" t="n">
-        <v>46322.08333333334</v>
+        <v>46322.58333333334</v>
       </c>
     </row>
     <row r="728">
@@ -40383,13 +40383,13 @@
         </is>
       </c>
       <c r="K728" s="1" t="n">
-        <v>46322.375</v>
+        <v>46322.875</v>
       </c>
       <c r="L728" s="1" t="n">
-        <v>46322.375</v>
+        <v>46322.875</v>
       </c>
       <c r="M728" s="1" t="n">
-        <v>46323.75</v>
+        <v>46324.25</v>
       </c>
     </row>
     <row r="729">
@@ -40438,13 +40438,13 @@
         </is>
       </c>
       <c r="K729" s="1" t="n">
-        <v>46324</v>
+        <v>46324.5</v>
       </c>
       <c r="L729" s="1" t="n">
-        <v>46324.04166666666</v>
+        <v>46324.54166666666</v>
       </c>
       <c r="M729" s="1" t="n">
-        <v>46324.5</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="730">
@@ -40493,13 +40493,13 @@
         </is>
       </c>
       <c r="K730" s="1" t="n">
-        <v>46328.33333333334</v>
+        <v>46328.83333333334</v>
       </c>
       <c r="L730" s="1" t="n">
-        <v>46328.33333333334</v>
+        <v>46328.83333333334</v>
       </c>
       <c r="M730" s="1" t="n">
-        <v>46328.79166666666</v>
+        <v>46329.29166666666</v>
       </c>
     </row>
     <row r="731">
@@ -40548,13 +40548,13 @@
         </is>
       </c>
       <c r="K731" s="1" t="n">
-        <v>46329.79166666666</v>
+        <v>46330.29166666666</v>
       </c>
       <c r="L731" s="1" t="n">
-        <v>46329.79166666666</v>
+        <v>46330.29166666666</v>
       </c>
       <c r="M731" s="1" t="n">
-        <v>46330.29166666666</v>
+        <v>46330.79166666666</v>
       </c>
     </row>
     <row r="732">
@@ -40603,13 +40603,13 @@
         </is>
       </c>
       <c r="K732" s="1" t="n">
-        <v>46332.75</v>
+        <v>46333.29166666666</v>
       </c>
       <c r="L732" s="1" t="n">
-        <v>46332.79166666666</v>
+        <v>46333.33333333334</v>
       </c>
       <c r="M732" s="1" t="n">
-        <v>46333.41666666666</v>
+        <v>46333.95833333334</v>
       </c>
     </row>
     <row r="733">
@@ -40658,13 +40658,13 @@
         </is>
       </c>
       <c r="K733" s="1" t="n">
-        <v>46334.41666666666</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="L733" s="1" t="n">
-        <v>46334.45833333334</v>
+        <v>46335</v>
       </c>
       <c r="M733" s="1" t="n">
-        <v>46334.95833333334</v>
+        <v>46335.5</v>
       </c>
     </row>
     <row r="734">
@@ -40713,13 +40713,13 @@
         </is>
       </c>
       <c r="K734" s="1" t="n">
-        <v>46336.04166666666</v>
+        <v>46336.58333333334</v>
       </c>
       <c r="L734" s="1" t="n">
-        <v>46336.20833333334</v>
+        <v>46336.75</v>
       </c>
       <c r="M734" s="1" t="n">
-        <v>46337</v>
+        <v>46337.54166666666</v>
       </c>
     </row>
     <row r="735">
@@ -40768,13 +40768,13 @@
         </is>
       </c>
       <c r="K735" s="1" t="n">
-        <v>46342.75</v>
+        <v>46343.29166666666</v>
       </c>
       <c r="L735" s="1" t="n">
-        <v>46342.79166666666</v>
+        <v>46343.33333333334</v>
       </c>
       <c r="M735" s="1" t="n">
-        <v>46343.08333333334</v>
+        <v>46343.625</v>
       </c>
     </row>
     <row r="736">
@@ -40823,13 +40823,13 @@
         </is>
       </c>
       <c r="K736" s="1" t="n">
-        <v>46343.375</v>
+        <v>46343.91666666666</v>
       </c>
       <c r="L736" s="1" t="n">
-        <v>46343.375</v>
+        <v>46343.91666666666</v>
       </c>
       <c r="M736" s="1" t="n">
-        <v>46344.75</v>
+        <v>46345.29166666666</v>
       </c>
     </row>
     <row r="737">
@@ -40878,13 +40878,13 @@
         </is>
       </c>
       <c r="K737" s="1" t="n">
-        <v>46345</v>
+        <v>46345.54166666666</v>
       </c>
       <c r="L737" s="1" t="n">
-        <v>46345.04166666666</v>
+        <v>46345.58333333334</v>
       </c>
       <c r="M737" s="1" t="n">
-        <v>46345.5</v>
+        <v>46346.04166666666</v>
       </c>
     </row>
     <row r="738">
@@ -40933,13 +40933,13 @@
         </is>
       </c>
       <c r="K738" s="1" t="n">
-        <v>46349.33333333334</v>
+        <v>46349.875</v>
       </c>
       <c r="L738" s="1" t="n">
-        <v>46349.33333333334</v>
+        <v>46349.875</v>
       </c>
       <c r="M738" s="1" t="n">
-        <v>46349.79166666666</v>
+        <v>46350.33333333334</v>
       </c>
     </row>
     <row r="739">
@@ -40988,13 +40988,13 @@
         </is>
       </c>
       <c r="K739" s="1" t="n">
-        <v>46350.79166666666</v>
+        <v>46351.33333333334</v>
       </c>
       <c r="L739" s="1" t="n">
-        <v>46350.79166666666</v>
+        <v>46351.33333333334</v>
       </c>
       <c r="M739" s="1" t="n">
-        <v>46351.29166666666</v>
+        <v>46351.83333333334</v>
       </c>
     </row>
     <row r="740">
@@ -41043,13 +41043,13 @@
         </is>
       </c>
       <c r="K740" s="1" t="n">
-        <v>46353.75</v>
+        <v>46354.29166666666</v>
       </c>
       <c r="L740" s="1" t="n">
-        <v>46353.79166666666</v>
+        <v>46354.33333333334</v>
       </c>
       <c r="M740" s="1" t="n">
-        <v>46354.41666666666</v>
+        <v>46354.95833333334</v>
       </c>
     </row>
     <row r="741">
@@ -41098,13 +41098,13 @@
         </is>
       </c>
       <c r="K741" s="1" t="n">
-        <v>46355.41666666666</v>
+        <v>46355.95833333334</v>
       </c>
       <c r="L741" s="1" t="n">
-        <v>46355.45833333334</v>
+        <v>46356</v>
       </c>
       <c r="M741" s="1" t="n">
-        <v>46355.95833333334</v>
+        <v>46356.5</v>
       </c>
     </row>
     <row r="742">
@@ -41153,13 +41153,13 @@
         </is>
       </c>
       <c r="K742" s="1" t="n">
-        <v>46357.04166666666</v>
+        <v>46357.58333333334</v>
       </c>
       <c r="L742" s="1" t="n">
-        <v>46357.20833333334</v>
+        <v>46357.75</v>
       </c>
       <c r="M742" s="1" t="n">
-        <v>46358</v>
+        <v>46358.54166666666</v>
       </c>
     </row>
     <row r="743">
@@ -41208,13 +41208,13 @@
         </is>
       </c>
       <c r="K743" s="1" t="n">
-        <v>46363.75</v>
+        <v>46364.29166666666</v>
       </c>
       <c r="L743" s="1" t="n">
-        <v>46363.79166666666</v>
+        <v>46364.33333333334</v>
       </c>
       <c r="M743" s="1" t="n">
-        <v>46364.08333333334</v>
+        <v>46364.625</v>
       </c>
     </row>
     <row r="744">
@@ -41263,13 +41263,13 @@
         </is>
       </c>
       <c r="K744" s="1" t="n">
-        <v>46364.375</v>
+        <v>46364.91666666666</v>
       </c>
       <c r="L744" s="1" t="n">
-        <v>46364.375</v>
+        <v>46364.91666666666</v>
       </c>
       <c r="M744" s="1" t="n">
-        <v>46365.75</v>
+        <v>46366.29166666666</v>
       </c>
     </row>
     <row r="745">
@@ -41318,13 +41318,13 @@
         </is>
       </c>
       <c r="K745" s="1" t="n">
-        <v>46366</v>
+        <v>46366.54166666666</v>
       </c>
       <c r="L745" s="1" t="n">
-        <v>46366.04166666666</v>
+        <v>46366.58333333334</v>
       </c>
       <c r="M745" s="1" t="n">
-        <v>46366.5</v>
+        <v>46367.04166666666</v>
       </c>
     </row>
     <row r="746">
@@ -41373,13 +41373,13 @@
         </is>
       </c>
       <c r="K746" s="1" t="n">
-        <v>46370.33333333334</v>
+        <v>46370.875</v>
       </c>
       <c r="L746" s="1" t="n">
-        <v>46370.33333333334</v>
+        <v>46370.875</v>
       </c>
       <c r="M746" s="1" t="n">
-        <v>46370.79166666666</v>
+        <v>46371.33333333334</v>
       </c>
     </row>
     <row r="747">
@@ -41428,13 +41428,13 @@
         </is>
       </c>
       <c r="K747" s="1" t="n">
-        <v>46371.79166666666</v>
+        <v>46372.33333333334</v>
       </c>
       <c r="L747" s="1" t="n">
-        <v>46371.79166666666</v>
+        <v>46372.33333333334</v>
       </c>
       <c r="M747" s="1" t="n">
-        <v>46372.29166666666</v>
+        <v>46372.83333333334</v>
       </c>
     </row>
     <row r="748">
@@ -41483,13 +41483,13 @@
         </is>
       </c>
       <c r="K748" s="1" t="n">
-        <v>46374.75</v>
+        <v>46375.29166666666</v>
       </c>
       <c r="L748" s="1" t="n">
-        <v>46374.79166666666</v>
+        <v>46375.33333333334</v>
       </c>
       <c r="M748" s="1" t="n">
-        <v>46375.41666666666</v>
+        <v>46375.95833333334</v>
       </c>
     </row>
     <row r="749">
@@ -41538,13 +41538,13 @@
         </is>
       </c>
       <c r="K749" s="1" t="n">
-        <v>46376.41666666666</v>
+        <v>46376.95833333334</v>
       </c>
       <c r="L749" s="1" t="n">
-        <v>46376.45833333334</v>
+        <v>46377</v>
       </c>
       <c r="M749" s="1" t="n">
-        <v>46376.95833333334</v>
+        <v>46377.5</v>
       </c>
     </row>
     <row r="750">
@@ -41593,13 +41593,13 @@
         </is>
       </c>
       <c r="K750" s="1" t="n">
-        <v>46378.04166666666</v>
+        <v>46378.58333333334</v>
       </c>
       <c r="L750" s="1" t="n">
-        <v>46378.20833333334</v>
+        <v>46378.75</v>
       </c>
       <c r="M750" s="1" t="n">
-        <v>46379</v>
+        <v>46379.54166666666</v>
       </c>
     </row>
     <row r="751">
@@ -41648,13 +41648,13 @@
         </is>
       </c>
       <c r="K751" s="1" t="n">
-        <v>46384.75</v>
+        <v>46385.29166666666</v>
       </c>
       <c r="L751" s="1" t="n">
-        <v>46384.79166666666</v>
+        <v>46385.33333333334</v>
       </c>
       <c r="M751" s="1" t="n">
-        <v>46385.08333333334</v>
+        <v>46385.625</v>
       </c>
     </row>
     <row r="752">
@@ -41703,13 +41703,13 @@
         </is>
       </c>
       <c r="K752" s="1" t="n">
-        <v>46385.375</v>
+        <v>46385.91666666666</v>
       </c>
       <c r="L752" s="1" t="n">
-        <v>46385.375</v>
+        <v>46385.91666666666</v>
       </c>
       <c r="M752" s="1" t="n">
-        <v>46386.75</v>
+        <v>46387.29166666666</v>
       </c>
     </row>
     <row r="753">
@@ -41758,13 +41758,13 @@
         </is>
       </c>
       <c r="K753" s="1" t="n">
-        <v>46387</v>
+        <v>46387.54166666666</v>
       </c>
       <c r="L753" s="1" t="n">
-        <v>46387.04166666666</v>
+        <v>46387.58333333334</v>
       </c>
       <c r="M753" s="1" t="n">
-        <v>46387.5</v>
+        <v>46388.04166666666</v>
       </c>
     </row>
     <row r="754">
@@ -41813,13 +41813,13 @@
         </is>
       </c>
       <c r="K754" s="1" t="n">
-        <v>46391.33333333334</v>
+        <v>46391.875</v>
       </c>
       <c r="L754" s="1" t="n">
-        <v>46391.33333333334</v>
+        <v>46391.875</v>
       </c>
       <c r="M754" s="1" t="n">
-        <v>46391.79166666666</v>
+        <v>46392.33333333334</v>
       </c>
     </row>
     <row r="755">
@@ -41864,13 +41864,13 @@
       </c>
       <c r="J755" t="inlineStr"/>
       <c r="K755" s="1" t="n">
-        <v>46392.79166666666</v>
+        <v>46393.33333333334</v>
       </c>
       <c r="L755" s="1" t="n">
-        <v>46392.79166666666</v>
+        <v>46393.33333333334</v>
       </c>
       <c r="M755" s="1" t="n">
-        <v>46393.29166666666</v>
+        <v>46393.83333333334</v>
       </c>
     </row>
     <row r="756">
@@ -46682,7 +46682,7 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>TSN09</t>
+          <t>TSN08</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -46902,7 +46902,7 @@
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>TSN09</t>
+          <t>TSN08</t>
         </is>
       </c>
       <c r="I847" t="inlineStr">
@@ -47122,7 +47122,7 @@
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>TSN09</t>
+          <t>TSN08</t>
         </is>
       </c>
       <c r="I851" t="inlineStr">
@@ -47342,7 +47342,7 @@
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>TSN09</t>
+          <t>TSN08</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -47562,7 +47562,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>TSN09</t>
+          <t>TSN08</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -47782,7 +47782,7 @@
       </c>
       <c r="H863" t="inlineStr">
         <is>
-          <t>TSN09</t>
+          <t>TSN08</t>
         </is>
       </c>
       <c r="I863" t="inlineStr">
@@ -48002,7 +48002,7 @@
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>TSN09</t>
+          <t>TSN08</t>
         </is>
       </c>
       <c r="I867" t="inlineStr">
@@ -48222,7 +48222,7 @@
       </c>
       <c r="H871" t="inlineStr">
         <is>
-          <t>TSN09</t>
+          <t>TSN08</t>
         </is>
       </c>
       <c r="I871" t="inlineStr">
@@ -48442,7 +48442,7 @@
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>TSN09</t>
+          <t>TSN08</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
@@ -48662,7 +48662,7 @@
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>TSN09</t>
+          <t>TSN08</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
@@ -51091,10 +51091,10 @@
         <v>46309.41666666666</v>
       </c>
       <c r="L923" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46309.66666666666</v>
       </c>
       <c r="M923" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46310.04166666666</v>
       </c>
     </row>
     <row r="924">
@@ -51143,13 +51143,13 @@
         </is>
       </c>
       <c r="K924" s="1" t="n">
-        <v>46313.5</v>
+        <v>46313.875</v>
       </c>
       <c r="L924" s="1" t="n">
-        <v>46313.5625</v>
+        <v>46313.9375</v>
       </c>
       <c r="M924" s="1" t="n">
-        <v>46314.02083333334</v>
+        <v>46314.39583333334</v>
       </c>
     </row>
     <row r="925">
@@ -51194,23 +51194,23 @@
       </c>
       <c r="J925" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="K925" s="1" t="n">
-        <v>46314.79166666666</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="L925" s="1" t="n">
-        <v>46314.83333333334</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="M925" s="1" t="n">
-        <v>46315.41666666666</v>
+        <v>46315.79166666666</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -51225,47 +51225,47 @@
       </c>
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="n">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
           <t>KRKAN</t>
         </is>
       </c>
-      <c r="J926" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
       <c r="K926" s="1" t="n">
-        <v>46317.70833333334</v>
+        <v>46317.97916666666</v>
       </c>
       <c r="L926" s="1" t="n">
-        <v>46317.77083333334</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="M926" s="1" t="n">
-        <v>46318</v>
+        <v>46320.29166666666</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -51280,41 +51280,41 @@
       </c>
       <c r="D927" t="inlineStr"/>
       <c r="E927" t="n">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I927" t="inlineStr">
         <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="J927" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
       <c r="K927" s="1" t="n">
-        <v>46317.97916666666</v>
+        <v>46318.08333333334</v>
       </c>
       <c r="L927" s="1" t="n">
-        <v>46319.29166666666</v>
+        <v>46318.14583333334</v>
       </c>
       <c r="M927" s="1" t="n">
-        <v>46320.29166666666</v>
+        <v>46318.375</v>
       </c>
     </row>
     <row r="928">
@@ -51363,13 +51363,13 @@
         </is>
       </c>
       <c r="K928" s="1" t="n">
-        <v>46318.29166666666</v>
+        <v>46318.66666666666</v>
       </c>
       <c r="L928" s="1" t="n">
-        <v>46318.33333333334</v>
+        <v>46318.70833333334</v>
       </c>
       <c r="M928" s="1" t="n">
-        <v>46319</v>
+        <v>46319.375</v>
       </c>
     </row>
     <row r="929">
@@ -52911,7 +52911,7 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -52926,47 +52926,47 @@
       </c>
       <c r="D957" t="inlineStr"/>
       <c r="E957" t="n">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="H957" t="inlineStr">
         <is>
-          <t>KAN04</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="I957" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
           <t>KRKAN</t>
         </is>
       </c>
-      <c r="J957" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
       <c r="K957" s="1" t="n">
-        <v>46311.83333333334</v>
+        <v>46311.75</v>
       </c>
       <c r="L957" s="1" t="n">
-        <v>46311.875</v>
+        <v>46311.91666666666</v>
       </c>
       <c r="M957" s="1" t="n">
-        <v>46312.875</v>
+        <v>46312.625</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
@@ -52981,41 +52981,41 @@
       </c>
       <c r="D958" t="inlineStr"/>
       <c r="E958" t="n">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="H958" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="I958" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="J958" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="K958" s="1" t="n">
-        <v>46313.5</v>
+        <v>46312.66666666666</v>
       </c>
       <c r="L958" s="1" t="n">
-        <v>46313.54166666666</v>
+        <v>46312.72916666666</v>
       </c>
       <c r="M958" s="1" t="n">
-        <v>46314.25</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="959">
@@ -53064,13 +53064,13 @@
         </is>
       </c>
       <c r="K959" s="1" t="n">
-        <v>46314.58333333334</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="L959" s="1" t="n">
-        <v>46314.66666666666</v>
+        <v>46313.35416666666</v>
       </c>
       <c r="M959" s="1" t="n">
-        <v>46314.91666666666</v>
+        <v>46313.625</v>
       </c>
     </row>
     <row r="960">
@@ -53119,13 +53119,13 @@
         </is>
       </c>
       <c r="K960" s="1" t="n">
-        <v>46317.83333333334</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="L960" s="1" t="n">
-        <v>46317.875</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="M960" s="1" t="n">
-        <v>46318.33333333334</v>
+        <v>46317.04166666666</v>
       </c>
     </row>
     <row r="961">
@@ -53174,13 +53174,13 @@
         </is>
       </c>
       <c r="K961" s="1" t="n">
-        <v>46320.54166666666</v>
+        <v>46319.25</v>
       </c>
       <c r="L961" s="1" t="n">
-        <v>46320.70833333334</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="M961" s="1" t="n">
-        <v>46321.16666666666</v>
+        <v>46319.875</v>
       </c>
     </row>
     <row r="962">
@@ -53229,13 +53229,13 @@
         </is>
       </c>
       <c r="K962" s="1" t="n">
-        <v>46322.91666666666</v>
+        <v>46321.5</v>
       </c>
       <c r="L962" s="1" t="n">
-        <v>46322.95833333334</v>
+        <v>46321.54166666666</v>
       </c>
       <c r="M962" s="1" t="n">
-        <v>46323.125</v>
+        <v>46321.70833333334</v>
       </c>
     </row>
     <row r="963">
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="K963" s="1" t="n">
-        <v>46323.375</v>
+        <v>46321.875</v>
       </c>
       <c r="L963" s="1" t="n">
-        <v>46323.5</v>
+        <v>46322</v>
       </c>
       <c r="M963" s="1" t="n">
-        <v>46324.83333333334</v>
+        <v>46323.33333333334</v>
       </c>
     </row>
     <row r="964">
@@ -53339,13 +53339,13 @@
         </is>
       </c>
       <c r="K964" s="1" t="n">
-        <v>46325.33333333334</v>
+        <v>46323.5</v>
       </c>
       <c r="L964" s="1" t="n">
-        <v>46325.375</v>
+        <v>46323.54166666666</v>
       </c>
       <c r="M964" s="1" t="n">
-        <v>46325.66666666666</v>
+        <v>46323.83333333334</v>
       </c>
     </row>
     <row r="965">
@@ -53394,13 +53394,13 @@
         </is>
       </c>
       <c r="K965" s="1" t="n">
-        <v>46329.75</v>
+        <v>46327.75</v>
       </c>
       <c r="L965" s="1" t="n">
-        <v>46329.79166666666</v>
+        <v>46327.79166666666</v>
       </c>
       <c r="M965" s="1" t="n">
-        <v>46330.25</v>
+        <v>46328.25</v>
       </c>
     </row>
     <row r="966">
@@ -53449,13 +53449,13 @@
         </is>
       </c>
       <c r="K966" s="1" t="n">
-        <v>46331.33333333334</v>
+        <v>46329.04166666666</v>
       </c>
       <c r="L966" s="1" t="n">
-        <v>46331.375</v>
+        <v>46329.08333333334</v>
       </c>
       <c r="M966" s="1" t="n">
-        <v>46331.95833333334</v>
+        <v>46329.66666666666</v>
       </c>
     </row>
     <row r="967">
@@ -53504,13 +53504,13 @@
         </is>
       </c>
       <c r="K967" s="1" t="n">
-        <v>46334.5</v>
+        <v>46332</v>
       </c>
       <c r="L967" s="1" t="n">
-        <v>46334.54166666666</v>
+        <v>46332.04166666666</v>
       </c>
       <c r="M967" s="1" t="n">
-        <v>46335.25</v>
+        <v>46332.75</v>
       </c>
     </row>
     <row r="968">
@@ -53559,13 +53559,13 @@
         </is>
       </c>
       <c r="K968" s="1" t="n">
-        <v>46335.58333333334</v>
+        <v>46333.08333333334</v>
       </c>
       <c r="L968" s="1" t="n">
-        <v>46335.66666666666</v>
+        <v>46333.16666666666</v>
       </c>
       <c r="M968" s="1" t="n">
-        <v>46335.91666666666</v>
+        <v>46333.41666666666</v>
       </c>
     </row>
     <row r="969">
@@ -53614,13 +53614,13 @@
         </is>
       </c>
       <c r="K969" s="1" t="n">
-        <v>46338.83333333334</v>
+        <v>46336.33333333334</v>
       </c>
       <c r="L969" s="1" t="n">
-        <v>46338.875</v>
+        <v>46336.375</v>
       </c>
       <c r="M969" s="1" t="n">
-        <v>46339.33333333334</v>
+        <v>46336.83333333334</v>
       </c>
     </row>
     <row r="970">
@@ -53669,13 +53669,13 @@
         </is>
       </c>
       <c r="K970" s="1" t="n">
-        <v>46341.54166666666</v>
+        <v>46339.04166666666</v>
       </c>
       <c r="L970" s="1" t="n">
-        <v>46341.70833333334</v>
+        <v>46339.20833333334</v>
       </c>
       <c r="M970" s="1" t="n">
-        <v>46342.16666666666</v>
+        <v>46339.66666666666</v>
       </c>
     </row>
     <row r="971">
@@ -53724,13 +53724,13 @@
         </is>
       </c>
       <c r="K971" s="1" t="n">
-        <v>46343.91666666666</v>
+        <v>46341.41666666666</v>
       </c>
       <c r="L971" s="1" t="n">
-        <v>46343.95833333334</v>
+        <v>46341.45833333334</v>
       </c>
       <c r="M971" s="1" t="n">
-        <v>46344.125</v>
+        <v>46341.625</v>
       </c>
     </row>
     <row r="972">
@@ -53779,13 +53779,13 @@
         </is>
       </c>
       <c r="K972" s="1" t="n">
-        <v>46344.375</v>
+        <v>46341.875</v>
       </c>
       <c r="L972" s="1" t="n">
-        <v>46344.5</v>
+        <v>46342</v>
       </c>
       <c r="M972" s="1" t="n">
-        <v>46345.83333333334</v>
+        <v>46343.33333333334</v>
       </c>
     </row>
     <row r="973">
@@ -53834,13 +53834,13 @@
         </is>
       </c>
       <c r="K973" s="1" t="n">
-        <v>46346.33333333334</v>
+        <v>46343.83333333334</v>
       </c>
       <c r="L973" s="1" t="n">
-        <v>46346.375</v>
+        <v>46343.875</v>
       </c>
       <c r="M973" s="1" t="n">
-        <v>46346.66666666666</v>
+        <v>46344.16666666666</v>
       </c>
     </row>
     <row r="974">
@@ -53889,13 +53889,13 @@
         </is>
       </c>
       <c r="K974" s="1" t="n">
-        <v>46350.75</v>
+        <v>46348.25</v>
       </c>
       <c r="L974" s="1" t="n">
-        <v>46350.79166666666</v>
+        <v>46348.29166666666</v>
       </c>
       <c r="M974" s="1" t="n">
-        <v>46351.25</v>
+        <v>46348.75</v>
       </c>
     </row>
     <row r="975">
@@ -53944,13 +53944,13 @@
         </is>
       </c>
       <c r="K975" s="1" t="n">
-        <v>46352.33333333334</v>
+        <v>46349.83333333334</v>
       </c>
       <c r="L975" s="1" t="n">
-        <v>46352.375</v>
+        <v>46349.875</v>
       </c>
       <c r="M975" s="1" t="n">
-        <v>46352.95833333334</v>
+        <v>46350.45833333334</v>
       </c>
     </row>
     <row r="976">
@@ -53999,13 +53999,13 @@
         </is>
       </c>
       <c r="K976" s="1" t="n">
-        <v>46355.5</v>
+        <v>46353</v>
       </c>
       <c r="L976" s="1" t="n">
-        <v>46355.54166666666</v>
+        <v>46353.04166666666</v>
       </c>
       <c r="M976" s="1" t="n">
-        <v>46356.25</v>
+        <v>46353.75</v>
       </c>
     </row>
     <row r="977">
@@ -54054,13 +54054,13 @@
         </is>
       </c>
       <c r="K977" s="1" t="n">
-        <v>46356.58333333334</v>
+        <v>46354.08333333334</v>
       </c>
       <c r="L977" s="1" t="n">
-        <v>46356.66666666666</v>
+        <v>46354.16666666666</v>
       </c>
       <c r="M977" s="1" t="n">
-        <v>46356.91666666666</v>
+        <v>46354.41666666666</v>
       </c>
     </row>
     <row r="978">
@@ -54109,13 +54109,13 @@
         </is>
       </c>
       <c r="K978" s="1" t="n">
-        <v>46359.83333333334</v>
+        <v>46357.33333333334</v>
       </c>
       <c r="L978" s="1" t="n">
-        <v>46359.875</v>
+        <v>46357.375</v>
       </c>
       <c r="M978" s="1" t="n">
-        <v>46360.33333333334</v>
+        <v>46357.83333333334</v>
       </c>
     </row>
     <row r="979">
@@ -54164,13 +54164,13 @@
         </is>
       </c>
       <c r="K979" s="1" t="n">
-        <v>46362.54166666666</v>
+        <v>46360.04166666666</v>
       </c>
       <c r="L979" s="1" t="n">
-        <v>46362.70833333334</v>
+        <v>46360.20833333334</v>
       </c>
       <c r="M979" s="1" t="n">
-        <v>46363.16666666666</v>
+        <v>46360.66666666666</v>
       </c>
     </row>
     <row r="980">
@@ -54219,13 +54219,13 @@
         </is>
       </c>
       <c r="K980" s="1" t="n">
-        <v>46364.91666666666</v>
+        <v>46362.41666666666</v>
       </c>
       <c r="L980" s="1" t="n">
-        <v>46364.95833333334</v>
+        <v>46362.45833333334</v>
       </c>
       <c r="M980" s="1" t="n">
-        <v>46365.125</v>
+        <v>46362.625</v>
       </c>
     </row>
     <row r="981">
@@ -54274,13 +54274,13 @@
         </is>
       </c>
       <c r="K981" s="1" t="n">
-        <v>46365.375</v>
+        <v>46362.875</v>
       </c>
       <c r="L981" s="1" t="n">
-        <v>46365.5</v>
+        <v>46363</v>
       </c>
       <c r="M981" s="1" t="n">
-        <v>46366.83333333334</v>
+        <v>46364.33333333334</v>
       </c>
     </row>
     <row r="982">
@@ -54329,13 +54329,13 @@
         </is>
       </c>
       <c r="K982" s="1" t="n">
-        <v>46367.33333333334</v>
+        <v>46364.83333333334</v>
       </c>
       <c r="L982" s="1" t="n">
-        <v>46367.375</v>
+        <v>46364.875</v>
       </c>
       <c r="M982" s="1" t="n">
-        <v>46367.66666666666</v>
+        <v>46365.16666666666</v>
       </c>
     </row>
     <row r="983">
@@ -54384,13 +54384,13 @@
         </is>
       </c>
       <c r="K983" s="1" t="n">
-        <v>46371.75</v>
+        <v>46369.25</v>
       </c>
       <c r="L983" s="1" t="n">
-        <v>46371.79166666666</v>
+        <v>46369.29166666666</v>
       </c>
       <c r="M983" s="1" t="n">
-        <v>46372.25</v>
+        <v>46369.75</v>
       </c>
     </row>
     <row r="984">
@@ -54439,13 +54439,13 @@
         </is>
       </c>
       <c r="K984" s="1" t="n">
-        <v>46373.33333333334</v>
+        <v>46370.83333333334</v>
       </c>
       <c r="L984" s="1" t="n">
-        <v>46373.375</v>
+        <v>46370.875</v>
       </c>
       <c r="M984" s="1" t="n">
-        <v>46373.95833333334</v>
+        <v>46371.45833333334</v>
       </c>
     </row>
     <row r="985">
@@ -54494,13 +54494,13 @@
         </is>
       </c>
       <c r="K985" s="1" t="n">
-        <v>46376.5</v>
+        <v>46374</v>
       </c>
       <c r="L985" s="1" t="n">
-        <v>46376.54166666666</v>
+        <v>46374.04166666666</v>
       </c>
       <c r="M985" s="1" t="n">
-        <v>46377.25</v>
+        <v>46374.75</v>
       </c>
     </row>
     <row r="986">
@@ -54549,13 +54549,13 @@
         </is>
       </c>
       <c r="K986" s="1" t="n">
-        <v>46377.58333333334</v>
+        <v>46375.08333333334</v>
       </c>
       <c r="L986" s="1" t="n">
-        <v>46377.66666666666</v>
+        <v>46375.16666666666</v>
       </c>
       <c r="M986" s="1" t="n">
-        <v>46377.91666666666</v>
+        <v>46375.41666666666</v>
       </c>
     </row>
     <row r="987">
@@ -54604,13 +54604,13 @@
         </is>
       </c>
       <c r="K987" s="1" t="n">
-        <v>46380.83333333334</v>
+        <v>46378.33333333334</v>
       </c>
       <c r="L987" s="1" t="n">
-        <v>46380.875</v>
+        <v>46378.375</v>
       </c>
       <c r="M987" s="1" t="n">
-        <v>46381.33333333334</v>
+        <v>46378.83333333334</v>
       </c>
     </row>
     <row r="988">
@@ -54659,13 +54659,13 @@
         </is>
       </c>
       <c r="K988" s="1" t="n">
-        <v>46383.54166666666</v>
+        <v>46381.04166666666</v>
       </c>
       <c r="L988" s="1" t="n">
-        <v>46383.70833333334</v>
+        <v>46381.20833333334</v>
       </c>
       <c r="M988" s="1" t="n">
-        <v>46384.16666666666</v>
+        <v>46381.66666666666</v>
       </c>
     </row>
     <row r="989">
@@ -54714,13 +54714,13 @@
         </is>
       </c>
       <c r="K989" s="1" t="n">
-        <v>46385.91666666666</v>
+        <v>46383.41666666666</v>
       </c>
       <c r="L989" s="1" t="n">
-        <v>46385.95833333334</v>
+        <v>46383.45833333334</v>
       </c>
       <c r="M989" s="1" t="n">
-        <v>46386.125</v>
+        <v>46383.625</v>
       </c>
     </row>
     <row r="990">
@@ -54769,13 +54769,13 @@
         </is>
       </c>
       <c r="K990" s="1" t="n">
-        <v>46386.375</v>
+        <v>46383.875</v>
       </c>
       <c r="L990" s="1" t="n">
-        <v>46386.5</v>
+        <v>46384</v>
       </c>
       <c r="M990" s="1" t="n">
-        <v>46387.83333333334</v>
+        <v>46385.33333333334</v>
       </c>
     </row>
     <row r="991">
@@ -54824,13 +54824,13 @@
         </is>
       </c>
       <c r="K991" s="1" t="n">
-        <v>46388.33333333334</v>
+        <v>46385.83333333334</v>
       </c>
       <c r="L991" s="1" t="n">
-        <v>46388.375</v>
+        <v>46385.875</v>
       </c>
       <c r="M991" s="1" t="n">
-        <v>46388.66666666666</v>
+        <v>46386.16666666666</v>
       </c>
     </row>
     <row r="992">
@@ -54879,13 +54879,13 @@
         </is>
       </c>
       <c r="K992" s="1" t="n">
-        <v>46392.75</v>
+        <v>46390.25</v>
       </c>
       <c r="L992" s="1" t="n">
-        <v>46392.79166666666</v>
+        <v>46390.29166666666</v>
       </c>
       <c r="M992" s="1" t="n">
-        <v>46393.25</v>
+        <v>46390.75</v>
       </c>
     </row>
     <row r="993">
@@ -54930,13 +54930,13 @@
       </c>
       <c r="J993" t="inlineStr"/>
       <c r="K993" s="1" t="n">
-        <v>46394.33333333334</v>
+        <v>46391.83333333334</v>
       </c>
       <c r="L993" s="1" t="n">
-        <v>46394.375</v>
+        <v>46391.875</v>
       </c>
       <c r="M993" s="1" t="n">
-        <v>46394.95833333334</v>
+        <v>46392.45833333334</v>
       </c>
     </row>
     <row r="994">
@@ -57569,10 +57569,10 @@
         <v>46308.58333333334</v>
       </c>
       <c r="L1041" s="1" t="n">
-        <v>46308.625</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="M1041" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46309.95833333334</v>
       </c>
     </row>
     <row r="1042">
@@ -57621,13 +57621,13 @@
         </is>
       </c>
       <c r="K1042" s="1" t="n">
-        <v>46309.66666666666</v>
+        <v>46310.08333333334</v>
       </c>
       <c r="L1042" s="1" t="n">
-        <v>46309.70833333334</v>
+        <v>46310.125</v>
       </c>
       <c r="M1042" s="1" t="n">
-        <v>46310.04166666666</v>
+        <v>46310.70833333334</v>
       </c>
     </row>
     <row r="1043">
@@ -57676,13 +57676,13 @@
         </is>
       </c>
       <c r="K1043" s="1" t="n">
-        <v>46311.125</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="L1043" s="1" t="n">
-        <v>46311.29166666666</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="M1043" s="1" t="n">
-        <v>46311.79166666666</v>
+        <v>46312.45833333334</v>
       </c>
     </row>
     <row r="1044">
@@ -57731,13 +57731,13 @@
         </is>
       </c>
       <c r="K1044" s="1" t="n">
-        <v>46315.95833333334</v>
+        <v>46316.625</v>
       </c>
       <c r="L1044" s="1" t="n">
-        <v>46316.125</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="M1044" s="1" t="n">
-        <v>46316.95833333334</v>
+        <v>46317.625</v>
       </c>
     </row>
     <row r="1045">
@@ -57786,13 +57786,13 @@
         </is>
       </c>
       <c r="K1045" s="1" t="n">
-        <v>46318.66666666666</v>
+        <v>46319.33333333334</v>
       </c>
       <c r="L1045" s="1" t="n">
-        <v>46318.70833333334</v>
+        <v>46319.375</v>
       </c>
       <c r="M1045" s="1" t="n">
-        <v>46319.54166666666</v>
+        <v>46320.20833333334</v>
       </c>
     </row>
     <row r="1046">
@@ -57841,13 +57841,13 @@
         </is>
       </c>
       <c r="K1046" s="1" t="n">
-        <v>46322.70833333334</v>
+        <v>46323.375</v>
       </c>
       <c r="L1046" s="1" t="n">
-        <v>46322.75</v>
+        <v>46323.41666666666</v>
       </c>
       <c r="M1046" s="1" t="n">
-        <v>46324.4375</v>
+        <v>46325.10416666666</v>
       </c>
     </row>
     <row r="1047">
@@ -57896,13 +57896,13 @@
         </is>
       </c>
       <c r="K1047" s="1" t="n">
-        <v>46326.5625</v>
+        <v>46327.5625</v>
       </c>
       <c r="L1047" s="1" t="n">
-        <v>46326.72916666666</v>
+        <v>46327.72916666666</v>
       </c>
       <c r="M1047" s="1" t="n">
-        <v>46327.5625</v>
+        <v>46328.5625</v>
       </c>
     </row>
     <row r="1048">
@@ -57951,13 +57951,13 @@
         </is>
       </c>
       <c r="K1048" s="1" t="n">
-        <v>46330.08333333334</v>
+        <v>46331.10416666666</v>
       </c>
       <c r="L1048" s="1" t="n">
-        <v>46330.14583333334</v>
+        <v>46331.16666666666</v>
       </c>
       <c r="M1048" s="1" t="n">
-        <v>46330.64583333334</v>
+        <v>46331.66666666666</v>
       </c>
     </row>
     <row r="1049">
@@ -58006,13 +58006,13 @@
         </is>
       </c>
       <c r="K1049" s="1" t="n">
-        <v>46330.875</v>
+        <v>46331.89583333334</v>
       </c>
       <c r="L1049" s="1" t="n">
-        <v>46330.91666666666</v>
+        <v>46331.9375</v>
       </c>
       <c r="M1049" s="1" t="n">
-        <v>46331.41666666666</v>
+        <v>46332.4375</v>
       </c>
     </row>
     <row r="1050">
@@ -58061,13 +58061,13 @@
         </is>
       </c>
       <c r="K1050" s="1" t="n">
-        <v>46334.60416666666</v>
+        <v>46335.52083333334</v>
       </c>
       <c r="L1050" s="1" t="n">
-        <v>46334.64583333334</v>
+        <v>46335.5625</v>
       </c>
       <c r="M1050" s="1" t="n">
-        <v>46335.3125</v>
+        <v>46336.22916666666</v>
       </c>
     </row>
     <row r="1051">
@@ -58116,13 +58116,13 @@
         </is>
       </c>
       <c r="K1051" s="1" t="n">
-        <v>46336.39583333334</v>
+        <v>46337.3125</v>
       </c>
       <c r="L1051" s="1" t="n">
-        <v>46336.4375</v>
+        <v>46337.35416666666</v>
       </c>
       <c r="M1051" s="1" t="n">
-        <v>46337.02083333334</v>
+        <v>46337.9375</v>
       </c>
     </row>
     <row r="1052">
@@ -58171,13 +58171,13 @@
         </is>
       </c>
       <c r="K1052" s="1" t="n">
-        <v>46337.20833333334</v>
+        <v>46338.125</v>
       </c>
       <c r="L1052" s="1" t="n">
-        <v>46337.27083333334</v>
+        <v>46338.1875</v>
       </c>
       <c r="M1052" s="1" t="n">
-        <v>46337.60416666666</v>
+        <v>46338.52083333334</v>
       </c>
     </row>
     <row r="1053">
@@ -58226,13 +58226,13 @@
         </is>
       </c>
       <c r="K1053" s="1" t="n">
-        <v>46338.89583333334</v>
+        <v>46339.8125</v>
       </c>
       <c r="L1053" s="1" t="n">
-        <v>46339.0625</v>
+        <v>46339.97916666666</v>
       </c>
       <c r="M1053" s="1" t="n">
-        <v>46339.5625</v>
+        <v>46340.47916666666</v>
       </c>
     </row>
     <row r="1054">
@@ -58281,13 +58281,13 @@
         </is>
       </c>
       <c r="K1054" s="1" t="n">
-        <v>46343.72916666666</v>
+        <v>46344.64583333334</v>
       </c>
       <c r="L1054" s="1" t="n">
-        <v>46343.89583333334</v>
+        <v>46344.8125</v>
       </c>
       <c r="M1054" s="1" t="n">
-        <v>46344.72916666666</v>
+        <v>46345.64583333334</v>
       </c>
     </row>
     <row r="1055">
@@ -58336,13 +58336,13 @@
         </is>
       </c>
       <c r="K1055" s="1" t="n">
-        <v>46346.39583333334</v>
+        <v>46347.3125</v>
       </c>
       <c r="L1055" s="1" t="n">
-        <v>46346.4375</v>
+        <v>46347.35416666666</v>
       </c>
       <c r="M1055" s="1" t="n">
-        <v>46347.27083333334</v>
+        <v>46348.1875</v>
       </c>
     </row>
     <row r="1056">
@@ -58391,13 +58391,13 @@
         </is>
       </c>
       <c r="K1056" s="1" t="n">
-        <v>46350.4375</v>
+        <v>46351.35416666666</v>
       </c>
       <c r="L1056" s="1" t="n">
-        <v>46350.52083333334</v>
+        <v>46351.4375</v>
       </c>
       <c r="M1056" s="1" t="n">
-        <v>46352.1875</v>
+        <v>46353.10416666666</v>
       </c>
     </row>
     <row r="1057">
@@ -58446,13 +58446,13 @@
         </is>
       </c>
       <c r="K1057" s="1" t="n">
-        <v>46354.64583333334</v>
+        <v>46355.5625</v>
       </c>
       <c r="L1057" s="1" t="n">
-        <v>46354.8125</v>
+        <v>46355.72916666666</v>
       </c>
       <c r="M1057" s="1" t="n">
-        <v>46355.64583333334</v>
+        <v>46356.5625</v>
       </c>
     </row>
     <row r="1058">
@@ -58501,13 +58501,13 @@
         </is>
       </c>
       <c r="K1058" s="1" t="n">
-        <v>46358.1875</v>
+        <v>46359.10416666666</v>
       </c>
       <c r="L1058" s="1" t="n">
-        <v>46358.25</v>
+        <v>46359.16666666666</v>
       </c>
       <c r="M1058" s="1" t="n">
-        <v>46358.75</v>
+        <v>46359.66666666666</v>
       </c>
     </row>
     <row r="1059">
@@ -58556,13 +58556,13 @@
         </is>
       </c>
       <c r="K1059" s="1" t="n">
-        <v>46358.97916666666</v>
+        <v>46359.89583333334</v>
       </c>
       <c r="L1059" s="1" t="n">
-        <v>46359.02083333334</v>
+        <v>46359.9375</v>
       </c>
       <c r="M1059" s="1" t="n">
-        <v>46359.52083333334</v>
+        <v>46360.4375</v>
       </c>
     </row>
     <row r="1060">
@@ -58611,13 +58611,13 @@
         </is>
       </c>
       <c r="K1060" s="1" t="n">
-        <v>46362.60416666666</v>
+        <v>46363.52083333334</v>
       </c>
       <c r="L1060" s="1" t="n">
-        <v>46362.64583333334</v>
+        <v>46363.5625</v>
       </c>
       <c r="M1060" s="1" t="n">
-        <v>46363.3125</v>
+        <v>46364.22916666666</v>
       </c>
     </row>
     <row r="1061">
@@ -58666,13 +58666,13 @@
         </is>
       </c>
       <c r="K1061" s="1" t="n">
-        <v>46364.39583333334</v>
+        <v>46365.3125</v>
       </c>
       <c r="L1061" s="1" t="n">
-        <v>46364.4375</v>
+        <v>46365.35416666666</v>
       </c>
       <c r="M1061" s="1" t="n">
-        <v>46365.02083333334</v>
+        <v>46365.9375</v>
       </c>
     </row>
     <row r="1062">
@@ -58721,13 +58721,13 @@
         </is>
       </c>
       <c r="K1062" s="1" t="n">
-        <v>46365.20833333334</v>
+        <v>46366.125</v>
       </c>
       <c r="L1062" s="1" t="n">
-        <v>46365.27083333334</v>
+        <v>46366.1875</v>
       </c>
       <c r="M1062" s="1" t="n">
-        <v>46365.60416666666</v>
+        <v>46366.52083333334</v>
       </c>
     </row>
     <row r="1063">
@@ -58776,13 +58776,13 @@
         </is>
       </c>
       <c r="K1063" s="1" t="n">
-        <v>46366.89583333334</v>
+        <v>46367.8125</v>
       </c>
       <c r="L1063" s="1" t="n">
-        <v>46367.0625</v>
+        <v>46367.97916666666</v>
       </c>
       <c r="M1063" s="1" t="n">
-        <v>46367.5625</v>
+        <v>46368.47916666666</v>
       </c>
     </row>
     <row r="1064">
@@ -58831,13 +58831,13 @@
         </is>
       </c>
       <c r="K1064" s="1" t="n">
-        <v>46371.72916666666</v>
+        <v>46372.64583333334</v>
       </c>
       <c r="L1064" s="1" t="n">
-        <v>46371.89583333334</v>
+        <v>46372.8125</v>
       </c>
       <c r="M1064" s="1" t="n">
-        <v>46372.72916666666</v>
+        <v>46373.64583333334</v>
       </c>
     </row>
     <row r="1065">
@@ -58886,13 +58886,13 @@
         </is>
       </c>
       <c r="K1065" s="1" t="n">
-        <v>46374.39583333334</v>
+        <v>46375.3125</v>
       </c>
       <c r="L1065" s="1" t="n">
-        <v>46374.4375</v>
+        <v>46375.35416666666</v>
       </c>
       <c r="M1065" s="1" t="n">
-        <v>46375.27083333334</v>
+        <v>46376.1875</v>
       </c>
     </row>
     <row r="1066">
@@ -58941,13 +58941,13 @@
         </is>
       </c>
       <c r="K1066" s="1" t="n">
-        <v>46378.4375</v>
+        <v>46379.35416666666</v>
       </c>
       <c r="L1066" s="1" t="n">
-        <v>46378.52083333334</v>
+        <v>46379.4375</v>
       </c>
       <c r="M1066" s="1" t="n">
-        <v>46380.1875</v>
+        <v>46381.10416666666</v>
       </c>
     </row>
     <row r="1067">
@@ -58996,13 +58996,13 @@
         </is>
       </c>
       <c r="K1067" s="1" t="n">
-        <v>46382.64583333334</v>
+        <v>46383.5625</v>
       </c>
       <c r="L1067" s="1" t="n">
-        <v>46382.8125</v>
+        <v>46383.72916666666</v>
       </c>
       <c r="M1067" s="1" t="n">
-        <v>46383.64583333334</v>
+        <v>46384.5625</v>
       </c>
     </row>
     <row r="1068">
@@ -59051,13 +59051,13 @@
         </is>
       </c>
       <c r="K1068" s="1" t="n">
-        <v>46386.1875</v>
+        <v>46387.10416666666</v>
       </c>
       <c r="L1068" s="1" t="n">
-        <v>46386.25</v>
+        <v>46387.16666666666</v>
       </c>
       <c r="M1068" s="1" t="n">
-        <v>46386.75</v>
+        <v>46387.66666666666</v>
       </c>
     </row>
     <row r="1069">
@@ -59102,13 +59102,13 @@
       </c>
       <c r="J1069" t="inlineStr"/>
       <c r="K1069" s="1" t="n">
-        <v>46386.97916666666</v>
+        <v>46387.89583333334</v>
       </c>
       <c r="L1069" s="1" t="n">
-        <v>46387.02083333334</v>
+        <v>46387.9375</v>
       </c>
       <c r="M1069" s="1" t="n">
-        <v>46387.52083333334</v>
+        <v>46388.4375</v>
       </c>
     </row>
     <row r="1070">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -6739,10 +6739,10 @@
         <v>46309.16666666666</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>46309.625</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="M115" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.75</v>
       </c>
     </row>
     <row r="116">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="K116" s="1" t="n">
+        <v>46310.875</v>
+      </c>
+      <c r="L116" s="1" t="n">
         <v>46310.91666666666</v>
       </c>
-      <c r="L116" s="1" t="n">
-        <v>46310.95833333334</v>
-      </c>
       <c r="M116" s="1" t="n">
-        <v>46311.20833333334</v>
+        <v>46311.375</v>
       </c>
     </row>
     <row r="117">
@@ -6846,13 +6846,13 @@
         </is>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46311.625</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>46311.70833333334</v>
+        <v>46311.875</v>
       </c>
       <c r="M117" s="1" t="n">
-        <v>46312.04166666666</v>
+        <v>46312.20833333334</v>
       </c>
     </row>
     <row r="118">
@@ -6901,13 +6901,13 @@
         </is>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46317.125</v>
+        <v>46317.29166666666</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>46317.29166666666</v>
+        <v>46317.45833333334</v>
       </c>
       <c r="M118" s="1" t="n">
-        <v>46317.91666666666</v>
+        <v>46318.08333333334</v>
       </c>
     </row>
     <row r="119">
@@ -6956,13 +6956,13 @@
         </is>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46319.70833333334</v>
+        <v>46319.875</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>46319.75</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="M119" s="1" t="n">
-        <v>46320</v>
+        <v>46320.16666666666</v>
       </c>
     </row>
     <row r="120">
@@ -7011,13 +7011,13 @@
         </is>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46320.29166666666</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>46320.41666666666</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="M120" s="1" t="n">
-        <v>46321.91666666666</v>
+        <v>46322.08333333334</v>
       </c>
     </row>
     <row r="121">
@@ -7066,13 +7066,13 @@
         </is>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46322.125</v>
+        <v>46322.29166666666</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>46322.16666666666</v>
+        <v>46322.33333333334</v>
       </c>
       <c r="M121" s="1" t="n">
-        <v>46322.58333333334</v>
+        <v>46322.75</v>
       </c>
     </row>
     <row r="122">
@@ -7121,13 +7121,13 @@
         </is>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46324.16666666666</v>
+        <v>46324.33333333334</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>46324.33333333334</v>
+        <v>46324.5</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>46324.875</v>
+        <v>46325.04166666666</v>
       </c>
     </row>
     <row r="123">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>SHAW5</t>
+          <t>SHAW1</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -23430,7 +23430,7 @@
         <v>46309.29166666666</v>
       </c>
       <c r="M419" s="1" t="n">
-        <v>46310.25</v>
+        <v>46309.70833333334</v>
       </c>
     </row>
     <row r="420">
@@ -23479,7 +23479,7 @@
         </is>
       </c>
       <c r="K420" s="1" t="n">
-        <v>46310.41666666666</v>
+        <v>46309.875</v>
       </c>
       <c r="L420" s="1" t="n">
         <v>46310.70833333334</v>
@@ -27113,7 +27113,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ADHS</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -27128,16 +27128,16 @@
       </c>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="n">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2606N</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -27162,13 +27162,13 @@
         <v>46297.09166666667</v>
       </c>
       <c r="M487" s="1" t="n">
-        <v>46297.5</v>
+        <v>46297.48333333333</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>ADHS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -27183,16 +27183,16 @@
       </c>
       <c r="D488" t="inlineStr"/>
       <c r="E488" t="n">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2606N</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -27266,13 +27266,13 @@
         </is>
       </c>
       <c r="K489" s="1" t="n">
-        <v>46298.95833333334</v>
+        <v>46298.75</v>
       </c>
       <c r="L489" s="1" t="n">
-        <v>46302.33333333334</v>
+        <v>46302.34583333333</v>
       </c>
       <c r="M489" s="1" t="n">
-        <v>46302.83333333334</v>
+        <v>46302.85416666666</v>
       </c>
     </row>
     <row r="490">
@@ -27324,10 +27324,10 @@
         <v>46305.79166666666</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>46305.91666666666</v>
+        <v>46305.9</v>
       </c>
       <c r="M490" s="1" t="n">
-        <v>46306.33333333334</v>
+        <v>46306.2375</v>
       </c>
     </row>
     <row r="491">
@@ -27376,13 +27376,13 @@
         </is>
       </c>
       <c r="K491" s="1" t="n">
-        <v>46318.58333333334</v>
+        <v>46318</v>
       </c>
       <c r="L491" s="1" t="n">
-        <v>46319.66666666666</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="M491" s="1" t="n">
-        <v>46320.33333333334</v>
+        <v>46319.75</v>
       </c>
     </row>
     <row r="492">
@@ -27431,13 +27431,13 @@
         </is>
       </c>
       <c r="K492" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="L492" s="1" t="n">
+        <v>46321.08333333334</v>
+      </c>
+      <c r="M492" s="1" t="n">
         <v>46321.58333333334</v>
-      </c>
-      <c r="L492" s="1" t="n">
-        <v>46321.66666666666</v>
-      </c>
-      <c r="M492" s="1" t="n">
-        <v>46322.16666666666</v>
       </c>
     </row>
     <row r="493">
@@ -27486,13 +27486,13 @@
         </is>
       </c>
       <c r="K493" s="1" t="n">
-        <v>46323.08333333334</v>
+        <v>46322.5</v>
       </c>
       <c r="L493" s="1" t="n">
+        <v>46322.58333333334</v>
+      </c>
+      <c r="M493" s="1" t="n">
         <v>46323.16666666666</v>
-      </c>
-      <c r="M493" s="1" t="n">
-        <v>46323.75</v>
       </c>
     </row>
     <row r="494">
@@ -27541,13 +27541,13 @@
         </is>
       </c>
       <c r="K494" s="1" t="n">
-        <v>46332.625</v>
+        <v>46332.04166666666</v>
       </c>
       <c r="L494" s="1" t="n">
+        <v>46333.08333333334</v>
+      </c>
+      <c r="M494" s="1" t="n">
         <v>46333.66666666666</v>
-      </c>
-      <c r="M494" s="1" t="n">
-        <v>46334.25</v>
       </c>
     </row>
     <row r="495">
@@ -27592,13 +27592,13 @@
       </c>
       <c r="J495" t="inlineStr"/>
       <c r="K495" s="1" t="n">
-        <v>46343.04166666666</v>
+        <v>46342.45833333334</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>46343.08333333334</v>
+        <v>46342.5</v>
       </c>
       <c r="M495" s="1" t="n">
-        <v>46343.83333333334</v>
+        <v>46343.25</v>
       </c>
     </row>
     <row r="496">
@@ -28523,7 +28523,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>AEFJR</t>
+          <t>AEKLF</t>
         </is>
       </c>
       <c r="K512" s="1" t="n">
@@ -28568,12 +28568,12 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>FJR01</t>
+          <t>KLF01</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>AEFJR</t>
+          <t>AEKLF</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
@@ -28588,7 +28588,7 @@
         <v>46343.04166666666</v>
       </c>
       <c r="M513" s="1" t="n">
-        <v>46350.04166666666</v>
+        <v>46346.04166666666</v>
       </c>
     </row>
     <row r="514">
@@ -28633,13 +28633,13 @@
       </c>
       <c r="J514" t="inlineStr"/>
       <c r="K514" s="1" t="n">
-        <v>46364.125</v>
+        <v>46359.91666666666</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>46364.16666666666</v>
+        <v>46359.95833333334</v>
       </c>
       <c r="M514" s="1" t="n">
-        <v>46365.16666666666</v>
+        <v>46360.95833333334</v>
       </c>
     </row>
     <row r="515">
@@ -51194,7 +51194,7 @@
       </c>
       <c r="J925" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="K925" s="1" t="n">
@@ -51210,7 +51210,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -51225,47 +51225,47 @@
       </c>
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="n">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
         <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="J926" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
       <c r="K926" s="1" t="n">
-        <v>46317.97916666666</v>
+        <v>46318.08333333334</v>
       </c>
       <c r="L926" s="1" t="n">
-        <v>46319.29166666666</v>
+        <v>46318.14583333334</v>
       </c>
       <c r="M926" s="1" t="n">
-        <v>46320.29166666666</v>
+        <v>46318.375</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -51280,41 +51280,41 @@
       </c>
       <c r="D927" t="inlineStr"/>
       <c r="E927" t="n">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="I927" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
           <t>KRKAN</t>
         </is>
       </c>
-      <c r="J927" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
       <c r="K927" s="1" t="n">
-        <v>46318.08333333334</v>
+        <v>46318.25</v>
       </c>
       <c r="L927" s="1" t="n">
-        <v>46318.14583333334</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="M927" s="1" t="n">
-        <v>46318.375</v>
+        <v>46320.41666666666</v>
       </c>
     </row>
     <row r="928">
@@ -51418,13 +51418,13 @@
         </is>
       </c>
       <c r="K929" s="1" t="n">
-        <v>46320.91666666666</v>
+        <v>46321.04166666666</v>
       </c>
       <c r="L929" s="1" t="n">
-        <v>46320.97916666666</v>
+        <v>46321.10416666666</v>
       </c>
       <c r="M929" s="1" t="n">
-        <v>46321.5625</v>
+        <v>46321.6875</v>
       </c>
     </row>
     <row r="930">
@@ -51473,13 +51473,13 @@
         </is>
       </c>
       <c r="K930" s="1" t="n">
-        <v>46323.08333333334</v>
+        <v>46323.20833333334</v>
       </c>
       <c r="L930" s="1" t="n">
-        <v>46323.29166666666</v>
+        <v>46323.41666666666</v>
       </c>
       <c r="M930" s="1" t="n">
-        <v>46323.95833333334</v>
+        <v>46324.08333333334</v>
       </c>
     </row>
     <row r="931">
@@ -51528,13 +51528,13 @@
         </is>
       </c>
       <c r="K931" s="1" t="n">
-        <v>46330.95833333334</v>
+        <v>46331.08333333334</v>
       </c>
       <c r="L931" s="1" t="n">
-        <v>46331.04166666666</v>
+        <v>46331.16666666666</v>
       </c>
       <c r="M931" s="1" t="n">
-        <v>46331.875</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="932">
@@ -51583,13 +51583,13 @@
         </is>
       </c>
       <c r="K932" s="1" t="n">
-        <v>46332.95833333334</v>
+        <v>46333.08333333334</v>
       </c>
       <c r="L932" s="1" t="n">
-        <v>46333.04166666666</v>
+        <v>46333.16666666666</v>
       </c>
       <c r="M932" s="1" t="n">
-        <v>46333.54166666666</v>
+        <v>46333.66666666666</v>
       </c>
     </row>
     <row r="933">
@@ -51638,13 +51638,13 @@
         </is>
       </c>
       <c r="K933" s="1" t="n">
-        <v>46337.54166666666</v>
+        <v>46337.66666666666</v>
       </c>
       <c r="L933" s="1" t="n">
-        <v>46337.58333333334</v>
+        <v>46337.70833333334</v>
       </c>
       <c r="M933" s="1" t="n">
-        <v>46338.25</v>
+        <v>46338.375</v>
       </c>
     </row>
     <row r="934">
@@ -51693,13 +51693,13 @@
         </is>
       </c>
       <c r="K934" s="1" t="n">
-        <v>46344.66666666666</v>
+        <v>46344.79166666666</v>
       </c>
       <c r="L934" s="1" t="n">
-        <v>46344.875</v>
+        <v>46345</v>
       </c>
       <c r="M934" s="1" t="n">
-        <v>46345.54166666666</v>
+        <v>46345.66666666666</v>
       </c>
     </row>
     <row r="935">
@@ -51748,13 +51748,13 @@
         </is>
       </c>
       <c r="K935" s="1" t="n">
-        <v>46347.25</v>
+        <v>46347.375</v>
       </c>
       <c r="L935" s="1" t="n">
-        <v>46347.29166666666</v>
+        <v>46347.41666666666</v>
       </c>
       <c r="M935" s="1" t="n">
-        <v>46348.29166666666</v>
+        <v>46348.41666666666</v>
       </c>
     </row>
     <row r="936">
@@ -51803,13 +51803,13 @@
         </is>
       </c>
       <c r="K936" s="1" t="n">
-        <v>46348.91666666666</v>
+        <v>46349.04166666666</v>
       </c>
       <c r="L936" s="1" t="n">
-        <v>46348.97916666666</v>
+        <v>46349.10416666666</v>
       </c>
       <c r="M936" s="1" t="n">
-        <v>46349.5625</v>
+        <v>46349.6875</v>
       </c>
     </row>
     <row r="937">
@@ -51858,13 +51858,13 @@
         </is>
       </c>
       <c r="K937" s="1" t="n">
-        <v>46351.08333333334</v>
+        <v>46351.20833333334</v>
       </c>
       <c r="L937" s="1" t="n">
-        <v>46351.29166666666</v>
+        <v>46351.41666666666</v>
       </c>
       <c r="M937" s="1" t="n">
-        <v>46351.95833333334</v>
+        <v>46352.08333333334</v>
       </c>
     </row>
     <row r="938">
@@ -51913,13 +51913,13 @@
         </is>
       </c>
       <c r="K938" s="1" t="n">
-        <v>46358.95833333334</v>
+        <v>46359.08333333334</v>
       </c>
       <c r="L938" s="1" t="n">
-        <v>46359.04166666666</v>
+        <v>46359.16666666666</v>
       </c>
       <c r="M938" s="1" t="n">
-        <v>46359.875</v>
+        <v>46360</v>
       </c>
     </row>
     <row r="939">
@@ -51968,13 +51968,13 @@
         </is>
       </c>
       <c r="K939" s="1" t="n">
-        <v>46360.95833333334</v>
+        <v>46361.08333333334</v>
       </c>
       <c r="L939" s="1" t="n">
-        <v>46361.04166666666</v>
+        <v>46361.16666666666</v>
       </c>
       <c r="M939" s="1" t="n">
-        <v>46361.54166666666</v>
+        <v>46361.66666666666</v>
       </c>
     </row>
     <row r="940">
@@ -52023,13 +52023,13 @@
         </is>
       </c>
       <c r="K940" s="1" t="n">
-        <v>46365.54166666666</v>
+        <v>46365.66666666666</v>
       </c>
       <c r="L940" s="1" t="n">
-        <v>46365.58333333334</v>
+        <v>46365.70833333334</v>
       </c>
       <c r="M940" s="1" t="n">
-        <v>46366.25</v>
+        <v>46366.375</v>
       </c>
     </row>
     <row r="941">
@@ -52078,13 +52078,13 @@
         </is>
       </c>
       <c r="K941" s="1" t="n">
-        <v>46372.66666666666</v>
+        <v>46372.79166666666</v>
       </c>
       <c r="L941" s="1" t="n">
-        <v>46372.875</v>
+        <v>46373</v>
       </c>
       <c r="M941" s="1" t="n">
-        <v>46373.54166666666</v>
+        <v>46373.66666666666</v>
       </c>
     </row>
     <row r="942">
@@ -52133,13 +52133,13 @@
         </is>
       </c>
       <c r="K942" s="1" t="n">
-        <v>46375.25</v>
+        <v>46375.375</v>
       </c>
       <c r="L942" s="1" t="n">
-        <v>46375.29166666666</v>
+        <v>46375.41666666666</v>
       </c>
       <c r="M942" s="1" t="n">
-        <v>46376.29166666666</v>
+        <v>46376.41666666666</v>
       </c>
     </row>
     <row r="943">
@@ -52188,13 +52188,13 @@
         </is>
       </c>
       <c r="K943" s="1" t="n">
-        <v>46376.91666666666</v>
+        <v>46377.04166666666</v>
       </c>
       <c r="L943" s="1" t="n">
-        <v>46376.97916666666</v>
+        <v>46377.10416666666</v>
       </c>
       <c r="M943" s="1" t="n">
-        <v>46377.5625</v>
+        <v>46377.6875</v>
       </c>
     </row>
     <row r="944">
@@ -52243,13 +52243,13 @@
         </is>
       </c>
       <c r="K944" s="1" t="n">
-        <v>46379.08333333334</v>
+        <v>46379.20833333334</v>
       </c>
       <c r="L944" s="1" t="n">
-        <v>46379.29166666666</v>
+        <v>46379.41666666666</v>
       </c>
       <c r="M944" s="1" t="n">
-        <v>46379.95833333334</v>
+        <v>46380.08333333334</v>
       </c>
     </row>
     <row r="945">
@@ -52298,13 +52298,13 @@
         </is>
       </c>
       <c r="K945" s="1" t="n">
-        <v>46386.95833333334</v>
+        <v>46387.08333333334</v>
       </c>
       <c r="L945" s="1" t="n">
-        <v>46387.04166666666</v>
+        <v>46387.16666666666</v>
       </c>
       <c r="M945" s="1" t="n">
-        <v>46387.875</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="946">
@@ -52353,13 +52353,13 @@
         </is>
       </c>
       <c r="K946" s="1" t="n">
-        <v>46388.95833333334</v>
+        <v>46389.08333333334</v>
       </c>
       <c r="L946" s="1" t="n">
-        <v>46389.04166666666</v>
+        <v>46389.16666666666</v>
       </c>
       <c r="M946" s="1" t="n">
-        <v>46389.54166666666</v>
+        <v>46389.66666666666</v>
       </c>
     </row>
     <row r="947">
@@ -52408,13 +52408,13 @@
         </is>
       </c>
       <c r="K947" s="1" t="n">
-        <v>46393.54166666666</v>
+        <v>46393.66666666666</v>
       </c>
       <c r="L947" s="1" t="n">
-        <v>46393.58333333334</v>
+        <v>46393.70833333334</v>
       </c>
       <c r="M947" s="1" t="n">
-        <v>46394.25</v>
+        <v>46394.375</v>
       </c>
     </row>
     <row r="948">
@@ -52459,13 +52459,13 @@
       </c>
       <c r="J948" t="inlineStr"/>
       <c r="K948" s="1" t="n">
-        <v>46400.66666666666</v>
+        <v>46400.79166666666</v>
       </c>
       <c r="L948" s="1" t="n">
-        <v>46400.875</v>
+        <v>46401</v>
       </c>
       <c r="M948" s="1" t="n">
-        <v>46401.54166666666</v>
+        <v>46401.66666666666</v>
       </c>
     </row>
     <row r="949">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -6742,7 +6742,7 @@
         <v>46309.54166666666</v>
       </c>
       <c r="M115" s="1" t="n">
-        <v>46310.75</v>
+        <v>46310.625</v>
       </c>
     </row>
     <row r="116">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46310.875</v>
+        <v>46310.75</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>46310.91666666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="M116" s="1" t="n">
-        <v>46311.375</v>
+        <v>46311.25</v>
       </c>
     </row>
     <row r="117">
@@ -6846,13 +6846,13 @@
         </is>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46311.79166666666</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>46311.875</v>
+        <v>46311.75</v>
       </c>
       <c r="M117" s="1" t="n">
-        <v>46312.20833333334</v>
+        <v>46312.08333333334</v>
       </c>
     </row>
     <row r="118">
@@ -6901,13 +6901,13 @@
         </is>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46317.29166666666</v>
+        <v>46317.16666666666</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>46317.45833333334</v>
+        <v>46317.33333333334</v>
       </c>
       <c r="M118" s="1" t="n">
-        <v>46318.08333333334</v>
+        <v>46317.95833333334</v>
       </c>
     </row>
     <row r="119">
@@ -6956,13 +6956,13 @@
         </is>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46319.875</v>
+        <v>46319.75</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>46319.91666666666</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="M119" s="1" t="n">
-        <v>46320.16666666666</v>
+        <v>46320.04166666666</v>
       </c>
     </row>
     <row r="120">
@@ -7011,13 +7011,13 @@
         </is>
       </c>
       <c r="K120" s="1" t="n">
+        <v>46320.33333333334</v>
+      </c>
+      <c r="L120" s="1" t="n">
         <v>46320.45833333334</v>
       </c>
-      <c r="L120" s="1" t="n">
-        <v>46320.58333333334</v>
-      </c>
       <c r="M120" s="1" t="n">
-        <v>46322.08333333334</v>
+        <v>46321.95833333334</v>
       </c>
     </row>
     <row r="121">
@@ -7066,13 +7066,13 @@
         </is>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46322.29166666666</v>
+        <v>46322.16666666666</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>46322.33333333334</v>
+        <v>46322.20833333334</v>
       </c>
       <c r="M121" s="1" t="n">
-        <v>46322.75</v>
+        <v>46322.625</v>
       </c>
     </row>
     <row r="122">
@@ -7121,13 +7121,13 @@
         </is>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46324.33333333334</v>
+        <v>46324.20833333334</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>46324.5</v>
+        <v>46324.375</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>46325.04166666666</v>
+        <v>46324.91666666666</v>
       </c>
     </row>
     <row r="123">
@@ -10364,7 +10364,7 @@
         <v>46308.5</v>
       </c>
       <c r="M181" s="1" t="n">
-        <v>46309.04166666666</v>
+        <v>46309.07916666667</v>
       </c>
     </row>
     <row r="182">
@@ -42634,13 +42634,13 @@
         </is>
       </c>
       <c r="K769" s="1" t="n">
-        <v>46329.83333333334</v>
+        <v>46329.625</v>
       </c>
       <c r="L769" s="1" t="n">
-        <v>46329.95833333334</v>
+        <v>46329.75</v>
       </c>
       <c r="M769" s="1" t="n">
-        <v>46331.45833333334</v>
+        <v>46331.25</v>
       </c>
     </row>
     <row r="770">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="K770" s="1" t="n">
-        <v>46331.79166666666</v>
+        <v>46331.45833333334</v>
       </c>
       <c r="L770" s="1" t="n">
-        <v>46331.83333333334</v>
+        <v>46331.5</v>
       </c>
       <c r="M770" s="1" t="n">
-        <v>46332.25</v>
+        <v>46331.91666666666</v>
       </c>
     </row>
     <row r="771">
@@ -42744,13 +42744,13 @@
         </is>
       </c>
       <c r="K771" s="1" t="n">
-        <v>46333.83333333334</v>
+        <v>46333.5</v>
       </c>
       <c r="L771" s="1" t="n">
-        <v>46334</v>
+        <v>46333.66666666666</v>
       </c>
       <c r="M771" s="1" t="n">
-        <v>46334.54166666666</v>
+        <v>46334.20833333334</v>
       </c>
     </row>
     <row r="772">
@@ -42799,13 +42799,13 @@
         </is>
       </c>
       <c r="K772" s="1" t="n">
-        <v>46340.41666666666</v>
+        <v>46339.5</v>
       </c>
       <c r="L772" s="1" t="n">
-        <v>46340.45833333334</v>
+        <v>46339.54166666666</v>
       </c>
       <c r="M772" s="1" t="n">
-        <v>46341.54166666666</v>
+        <v>46340.625</v>
       </c>
     </row>
     <row r="773">
@@ -42854,13 +42854,13 @@
         </is>
       </c>
       <c r="K773" s="1" t="n">
-        <v>46341.66666666666</v>
+        <v>46340.75</v>
       </c>
       <c r="L773" s="1" t="n">
-        <v>46341.70833333334</v>
+        <v>46340.79166666666</v>
       </c>
       <c r="M773" s="1" t="n">
-        <v>46341.95833333334</v>
+        <v>46341.04166666666</v>
       </c>
     </row>
     <row r="774">
@@ -42909,13 +42909,13 @@
         </is>
       </c>
       <c r="K774" s="1" t="n">
-        <v>46342.375</v>
+        <v>46341.45833333334</v>
       </c>
       <c r="L774" s="1" t="n">
-        <v>46342.45833333334</v>
+        <v>46341.54166666666</v>
       </c>
       <c r="M774" s="1" t="n">
-        <v>46342.79166666666</v>
+        <v>46341.875</v>
       </c>
     </row>
     <row r="775">
@@ -42964,13 +42964,13 @@
         </is>
       </c>
       <c r="K775" s="1" t="n">
-        <v>46347.79166666666</v>
+        <v>46346.875</v>
       </c>
       <c r="L775" s="1" t="n">
-        <v>46347.95833333334</v>
+        <v>46347.04166666666</v>
       </c>
       <c r="M775" s="1" t="n">
-        <v>46348.58333333334</v>
+        <v>46347.66666666666</v>
       </c>
     </row>
     <row r="776">
@@ -43019,13 +43019,13 @@
         </is>
       </c>
       <c r="K776" s="1" t="n">
-        <v>46350.54166666666</v>
+        <v>46349.625</v>
       </c>
       <c r="L776" s="1" t="n">
-        <v>46350.58333333334</v>
+        <v>46349.66666666666</v>
       </c>
       <c r="M776" s="1" t="n">
-        <v>46350.83333333334</v>
+        <v>46349.91666666666</v>
       </c>
     </row>
     <row r="777">
@@ -43074,13 +43074,13 @@
         </is>
       </c>
       <c r="K777" s="1" t="n">
-        <v>46351.125</v>
+        <v>46350</v>
       </c>
       <c r="L777" s="1" t="n">
-        <v>46351.25</v>
+        <v>46350.125</v>
       </c>
       <c r="M777" s="1" t="n">
-        <v>46352.75</v>
+        <v>46351.625</v>
       </c>
     </row>
     <row r="778">
@@ -43129,13 +43129,13 @@
         </is>
       </c>
       <c r="K778" s="1" t="n">
-        <v>46352.95833333334</v>
+        <v>46351.83333333334</v>
       </c>
       <c r="L778" s="1" t="n">
-        <v>46353</v>
+        <v>46351.875</v>
       </c>
       <c r="M778" s="1" t="n">
-        <v>46353.41666666666</v>
+        <v>46352.29166666666</v>
       </c>
     </row>
     <row r="779">
@@ -43184,13 +43184,13 @@
         </is>
       </c>
       <c r="K779" s="1" t="n">
-        <v>46355</v>
+        <v>46353.875</v>
       </c>
       <c r="L779" s="1" t="n">
-        <v>46355.16666666666</v>
+        <v>46354.04166666666</v>
       </c>
       <c r="M779" s="1" t="n">
-        <v>46355.70833333334</v>
+        <v>46354.58333333334</v>
       </c>
     </row>
     <row r="780">
@@ -43239,13 +43239,13 @@
         </is>
       </c>
       <c r="K780" s="1" t="n">
-        <v>46361.58333333334</v>
+        <v>46360.25</v>
       </c>
       <c r="L780" s="1" t="n">
-        <v>46361.625</v>
+        <v>46360.29166666666</v>
       </c>
       <c r="M780" s="1" t="n">
-        <v>46362.70833333334</v>
+        <v>46361.375</v>
       </c>
     </row>
     <row r="781">
@@ -43294,13 +43294,13 @@
         </is>
       </c>
       <c r="K781" s="1" t="n">
-        <v>46362.875</v>
+        <v>46361.5</v>
       </c>
       <c r="L781" s="1" t="n">
-        <v>46362.91666666666</v>
+        <v>46361.54166666666</v>
       </c>
       <c r="M781" s="1" t="n">
-        <v>46363.16666666666</v>
+        <v>46361.79166666666</v>
       </c>
     </row>
     <row r="782">
@@ -43349,13 +43349,13 @@
         </is>
       </c>
       <c r="K782" s="1" t="n">
-        <v>46363.58333333334</v>
+        <v>46362.20833333334</v>
       </c>
       <c r="L782" s="1" t="n">
-        <v>46363.66666666666</v>
+        <v>46362.29166666666</v>
       </c>
       <c r="M782" s="1" t="n">
-        <v>46364</v>
+        <v>46362.625</v>
       </c>
     </row>
     <row r="783">
@@ -43404,13 +43404,13 @@
         </is>
       </c>
       <c r="K783" s="1" t="n">
-        <v>46369</v>
+        <v>46367.70833333334</v>
       </c>
       <c r="L783" s="1" t="n">
-        <v>46369.16666666666</v>
+        <v>46367.875</v>
       </c>
       <c r="M783" s="1" t="n">
-        <v>46369.79166666666</v>
+        <v>46368.5</v>
       </c>
     </row>
     <row r="784">
@@ -43459,13 +43459,13 @@
         </is>
       </c>
       <c r="K784" s="1" t="n">
-        <v>46371.75</v>
+        <v>46370.29166666666</v>
       </c>
       <c r="L784" s="1" t="n">
-        <v>46371.79166666666</v>
+        <v>46370.33333333334</v>
       </c>
       <c r="M784" s="1" t="n">
-        <v>46372.04166666666</v>
+        <v>46370.58333333334</v>
       </c>
     </row>
     <row r="785">
@@ -43514,13 +43514,13 @@
         </is>
       </c>
       <c r="K785" s="1" t="n">
-        <v>46372.33333333334</v>
+        <v>46370.875</v>
       </c>
       <c r="L785" s="1" t="n">
-        <v>46372.45833333334</v>
+        <v>46371</v>
       </c>
       <c r="M785" s="1" t="n">
-        <v>46373.95833333334</v>
+        <v>46372.5</v>
       </c>
     </row>
     <row r="786">
@@ -43569,13 +43569,13 @@
         </is>
       </c>
       <c r="K786" s="1" t="n">
-        <v>46374.16666666666</v>
+        <v>46372.70833333334</v>
       </c>
       <c r="L786" s="1" t="n">
-        <v>46374.20833333334</v>
+        <v>46372.75</v>
       </c>
       <c r="M786" s="1" t="n">
-        <v>46374.625</v>
+        <v>46373.16666666666</v>
       </c>
     </row>
     <row r="787">
@@ -43624,13 +43624,13 @@
         </is>
       </c>
       <c r="K787" s="1" t="n">
-        <v>46376.20833333334</v>
+        <v>46374.75</v>
       </c>
       <c r="L787" s="1" t="n">
-        <v>46376.375</v>
+        <v>46374.91666666666</v>
       </c>
       <c r="M787" s="1" t="n">
-        <v>46376.91666666666</v>
+        <v>46375.45833333334</v>
       </c>
     </row>
     <row r="788">
@@ -43789,13 +43789,13 @@
         </is>
       </c>
       <c r="K790" s="1" t="n">
-        <v>46383.25</v>
+        <v>46383.20833333334</v>
       </c>
       <c r="L790" s="1" t="n">
-        <v>46383.33333333334</v>
+        <v>46383.29166666666</v>
       </c>
       <c r="M790" s="1" t="n">
-        <v>46383.66666666666</v>
+        <v>46383.625</v>
       </c>
     </row>
     <row r="791">

--- a/sked_current.xlsx
+++ b/sked_current.xlsx
@@ -1196,10 +1196,10 @@
         <v>46310.5</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46310.5625</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>46310.97916666666</v>
+        <v>46311.47916666666</v>
       </c>
     </row>
     <row r="15">
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46313.75</v>
+        <v>46314.08333333334</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46313.91666666666</v>
+        <v>46314.25</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>46314.625</v>
+        <v>46314.95833333334</v>
       </c>
     </row>
     <row r="16">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46316.54166666666</v>
+        <v>46316.75</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46316.58333333334</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>46316.875</v>
+        <v>46317.08333333334</v>
       </c>
     </row>
     <row r="17">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46317</v>
+        <v>46317.20833333334</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46317.125</v>
+        <v>46317.33333333334</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>46318.375</v>
+        <v>46318.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46318.58333333334</v>
+        <v>46318.79166666666</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46318.625</v>
+        <v>46318.83333333334</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>46319.08333333334</v>
+        <v>46319.29166666666</v>
       </c>
     </row>
     <row r="19">
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46323.29166666666</v>
+        <v>46323.5</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46323.35416666666</v>
+        <v>46323.5625</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>46323.83333333334</v>
+        <v>46324.04166666666</v>
       </c>
     </row>
     <row r="20">
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46323.91666666666</v>
+        <v>46324.125</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46323.95833333334</v>
+        <v>46324.16666666666</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>46324.33333333334</v>
+        <v>46324.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
+        <v>46327.875</v>
+      </c>
+      <c r="L21" s="1" t="n">
         <v>46327.91666666666</v>
       </c>
-      <c r="L21" s="1" t="n">
-        <v>46327.95833333334</v>
-      </c>
       <c r="M21" s="1" t="n">
-        <v>46328.95833333334</v>
+        <v>46328.91666666666</v>
       </c>
     </row>
     <row r="22">
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
+        <v>46329.04166666666</v>
+      </c>
+      <c r="L22" s="1" t="n">
         <v>46329.08333333334</v>
       </c>
-      <c r="L22" s="1" t="n">
-        <v>46329.125</v>
-      </c>
       <c r="M22" s="1" t="n">
-        <v>46329.5</v>
+        <v>46329.45833333334</v>
       </c>
     </row>
     <row r="23">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46332.33333333334</v>
+        <v>46332.70833333334</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>46332.375</v>
+        <v>46332.77083333334</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>46332.75</v>
+        <v>46333.1875</v>
       </c>
     </row>
     <row r="24">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46335.83333333334</v>
+        <v>46335.79166666666</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>46336</v>
+        <v>46335.95833333334</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>46336.54166666666</v>
+        <v>46336.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
+        <v>46338.45833333334</v>
+      </c>
+      <c r="L25" s="1" t="n">
         <v>46338.5</v>
-      </c>
-      <c r="L25" s="1" t="n">
-        <v>46338.54166666666</v>
       </c>
       <c r="M25" s="1" t="n">
         <v>46338.79166666666</v>
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46338.95833333334</v>
+        <v>46338.91666666666</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>46339.08333333334</v>
+        <v>46339.04166666666</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>46340.33333333334</v>
+        <v>46340.29166666666</v>
       </c>
     </row>
     <row r="27">
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
+        <v>46340.5</v>
+      </c>
+      <c r="L27" s="1" t="n">
         <v>46340.54166666666</v>
       </c>
-      <c r="L27" s="1" t="n">
-        <v>46340.58333333334</v>
-      </c>
       <c r="M27" s="1" t="n">
-        <v>46341.04166666666</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="28">
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="K28" s="1" t="n">
+        <v>46345.20833333334</v>
+      </c>
+      <c r="L28" s="1" t="n">
         <v>46345.25</v>
       </c>
-      <c r="L28" s="1" t="n">
-        <v>46345.29166666666</v>
-      </c>
       <c r="M28" s="1" t="n">
-        <v>46345.75</v>
+        <v>46345.70833333334</v>
       </c>
     </row>
     <row r="29">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46345.875</v>
+        <v>46345.83333333334</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>46346</v>
+        <v>46345.95833333334</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>46346.375</v>
+        <v>46346.33333333334</v>
       </c>
     </row>
     <row r="30">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
+        <v>46349.66666666666</v>
+      </c>
+      <c r="L30" s="1" t="n">
         <v>46349.70833333334</v>
       </c>
-      <c r="L30" s="1" t="n">
-        <v>46349.75</v>
-      </c>
       <c r="M30" s="1" t="n">
-        <v>46350.75</v>
+        <v>46350.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -2128,13 +2128,13 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
+        <v>46350.91666666666</v>
+      </c>
+      <c r="L31" s="1" t="n">
         <v>46350.95833333334</v>
       </c>
-      <c r="L31" s="1" t="n">
-        <v>46351</v>
-      </c>
       <c r="M31" s="1" t="n">
-        <v>46351.33333333334</v>
+        <v>46351.29166666666</v>
       </c>
     </row>
     <row r="32">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
+        <v>46354.125</v>
+      </c>
+      <c r="L32" s="1" t="n">
         <v>46354.16666666666</v>
       </c>
-      <c r="L32" s="1" t="n">
-        <v>46354.20833333334</v>
-      </c>
       <c r="M32" s="1" t="n">
-        <v>46354.58333333334</v>
+        <v>46354.54166666666</v>
       </c>
     </row>
     <row r="33">
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46357.04166666666</v>
+        <v>46357</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>46357.20833333334</v>
+        <v>46357.16666666666</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>46357.75</v>
+        <v>46357.70833333334</v>
       </c>
     </row>
     <row r="34">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="K34" s="1" t="n">
+        <v>46359.5</v>
+      </c>
+      <c r="L34" s="1" t="n">
         <v>46359.54166666666</v>
       </c>
-      <c r="L34" s="1" t="n">
-        <v>46359.58333333334</v>
-      </c>
       <c r="M34" s="1" t="n">
-        <v>46359.83333333334</v>
+        <v>46359.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46360.25</v>
+        <v>46360.20833333334</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>46360.375</v>
+        <v>46360.33333333334</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>46361.5</v>
+        <v>46361.45833333334</v>
       </c>
     </row>
     <row r="36">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="K36" s="1" t="n">
+        <v>46361.79166666666</v>
+      </c>
+      <c r="L36" s="1" t="n">
         <v>46361.83333333334</v>
       </c>
-      <c r="L36" s="1" t="n">
-        <v>46361.875</v>
-      </c>
       <c r="M36" s="1" t="n">
-        <v>46362.20833333334</v>
+        <v>46362.16666666666</v>
       </c>
     </row>
     <row r="37">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="K37" s="1" t="n">
+        <v>46366.04166666666</v>
+      </c>
+      <c r="L37" s="1" t="n">
         <v>46366.08333333334</v>
       </c>
-      <c r="L37" s="1" t="n">
-        <v>46366.125</v>
-      </c>
       <c r="M37" s="1" t="n">
-        <v>46366.54166666666</v>
+        <v>46366.5</v>
       </c>
     </row>
     <row r="38">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46366.79166666666</v>
+        <v>46366.75</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>46366.79166666666</v>
+        <v>46366.75</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>46367.16666666666</v>
+        <v>46367.125</v>
       </c>
     </row>
     <row r="39">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46368.41666666666</v>
+        <v>46368.375</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>46368.41666666666</v>
+        <v>46368.375</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>46368.66666666666</v>
+        <v>46368.625</v>
       </c>
     </row>
     <row r="40">
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="K40" s="1" t="n">
+        <v>46370.95833333334</v>
+      </c>
+      <c r="L40" s="1" t="n">
         <v>46371</v>
       </c>
-      <c r="L40" s="1" t="n">
-        <v>46371.04166666666</v>
-      </c>
       <c r="M40" s="1" t="n">
-        <v>46371.75</v>
+        <v>46371.70833333334</v>
       </c>
     </row>
     <row r="41">
@@ -2678,13 +2678,13 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
+        <v>46371.91666666666</v>
+      </c>
+      <c r="L41" s="1" t="n">
         <v>46371.95833333334</v>
       </c>
-      <c r="L41" s="1" t="n">
-        <v>46372</v>
-      </c>
       <c r="M41" s="1" t="n">
-        <v>46372.33333333334</v>
+        <v>46372.29166666666</v>
       </c>
     </row>
     <row r="42">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="K42" s="1" t="n">
+        <v>46375.125</v>
+      </c>
+      <c r="L42" s="1" t="n">
         <v>46375.16666666666</v>
       </c>
-      <c r="L42" s="1" t="n">
-        <v>46375.20833333334</v>
-      </c>
       <c r="M42" s="1" t="n">
-        <v>46375.58333333334</v>
+        <v>46375.54166666666</v>
       </c>
     </row>
     <row r="43">
@@ -2788,13 +2788,13 @@
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46378.04166666666</v>
+        <v>46378</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>46378.20833333334</v>
+        <v>46378.16666666666</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>46378.75</v>
+        <v>46378.70833333334</v>
       </c>
     </row>
     <row r="44">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="K44" s="1" t="n">
+        <v>46380.5</v>
+      </c>
+      <c r="L44" s="1" t="n">
         <v>46380.54166666666</v>
       </c>
-      <c r="L44" s="1" t="n">
-        <v>46380.58333333334</v>
-      </c>
       <c r="M44" s="1" t="n">
-        <v>46380.83333333334</v>
+        <v>46380.79166666666</v>
       </c>
     </row>
     <row r="45">
@@ -2898,13 +2898,13 @@
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46381.25</v>
+        <v>46381.20833333334</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>46381.375</v>
+        <v>46381.33333333334</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>46382.5</v>
+        <v>46382.45833333334</v>
       </c>
     </row>
     <row r="46">
@@ -2953,13 +2953,13 @@
         </is>
       </c>
       <c r="K46" s="1" t="n">
+        <v>46382.79166666666</v>
+      </c>
+      <c r="L46" s="1" t="n">
         <v>46382.83333333334</v>
       </c>
-      <c r="L46" s="1" t="n">
-        <v>46382.875</v>
-      </c>
       <c r="M46" s="1" t="n">
-        <v>46383.20833333334</v>
+        <v>46383.16666666666</v>
       </c>
     </row>
     <row r="47">
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="K47" s="1" t="n">
+        <v>46387.04166666666</v>
+      </c>
+      <c r="L47" s="1" t="n">
         <v>46387.08333333334</v>
       </c>
-      <c r="L47" s="1" t="n">
-        <v>46387.125</v>
-      </c>
       <c r="M47" s="1" t="n">
-        <v>46387.54166666666</v>
+        <v>46387.5</v>
       </c>
     </row>
     <row r="48">
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46387.79166666666</v>
+        <v>46387.75</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>46387.79166666666</v>
+        <v>46387.75</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>46388.16666666666</v>
+        <v>46388.125</v>
       </c>
     </row>
     <row r="49">
@@ -3114,13 +3114,13 @@
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" s="1" t="n">
-        <v>46389.41666666666</v>
+        <v>46389.375</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>46389.41666666666</v>
+        <v>46389.375</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>46389.66666666666</v>
+        <v>46389.625</v>
       </c>
     </row>
     <row r="50">
@@ -6742,7 +6742,7 @@
         <v>46309.54166666666</v>
       </c>
       <c r="M115" s="1" t="n">
-        <v>46310.625</v>
+        <v>46310.58333333334</v>
       </c>
     </row>
     <row r="116">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46310.75</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="M116" s="1" t="n">
-        <v>46311.25</v>
+        <v>46311.16666666666</v>
       </c>
     </row>
     <row r="117">
@@ -6846,13 +6846,13 @@
         </is>
       </c>
       <c r="K117" s="1" t="n">
+        <v>46311.58333333334</v>
+      </c>
+      <c r="L117" s="1" t="n">
         <v>46311.66666666666</v>
       </c>
-      <c r="L117" s="1" t="n">
-        <v>46311.75</v>
-      </c>
       <c r="M117" s="1" t="n">
-        <v>46312.08333333334</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="118">
@@ -6901,13 +6901,13 @@
         </is>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46317.16666666666</v>
+        <v>46317.08333333334</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>46317.33333333334</v>
+        <v>46317.25</v>
       </c>
       <c r="M118" s="1" t="n">
-        <v>46317.95833333334</v>
+        <v>46317.875</v>
       </c>
     </row>
     <row r="119">
@@ -6956,13 +6956,13 @@
         </is>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46319.75</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>46319.79166666666</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="M119" s="1" t="n">
-        <v>46320.04166666666</v>
+        <v>46319.95833333334</v>
       </c>
     </row>
     <row r="120">
@@ -7011,13 +7011,13 @@
         </is>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46320.33333333334</v>
+        <v>46320.25</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>46320.45833333334</v>
+        <v>46320.375</v>
       </c>
       <c r="M120" s="1" t="n">
-        <v>46321.95833333334</v>
+        <v>46321.875</v>
       </c>
     </row>
     <row r="121">
@@ -7066,13 +7066,13 @@
         </is>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46322.16666666666</v>
+        <v>46322.08333333334</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>46322.20833333334</v>
+        <v>46322.125</v>
       </c>
       <c r="M121" s="1" t="n">
-        <v>46322.625</v>
+        <v>46322.54166666666</v>
       </c>
     </row>
     <row r="122">
@@ -7121,13 +7121,13 @@
         </is>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46324.20833333334</v>
+        <v>46324.125</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>46324.375</v>
+        <v>46324.29166666666</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>46324.91666666666</v>
+        <v>46324.83333333334</v>
       </c>
     </row>
     <row r="123">
@@ -14258,7 +14258,7 @@
         <v>46308.375</v>
       </c>
       <c r="L252" s="1" t="n">
-        <v>46310.625</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="M252" s="1" t="n">
         <v>46310.875</v>
@@ -14478,10 +14478,10 @@
         <v>46323.33333333334</v>
       </c>
       <c r="L256" s="1" t="n">
-        <v>46323.33333333334</v>
+        <v>46323.39583333334</v>
       </c>
       <c r="M256" s="1" t="n">
-        <v>46323.79166666666</v>
+        <v>46323.85416666666</v>
       </c>
     </row>
     <row r="257">
@@ -14530,13 +14530,13 @@
         </is>
       </c>
       <c r="K257" s="1" t="n">
-        <v>46324.79166666666</v>
+        <v>46324.70833333334</v>
       </c>
       <c r="L257" s="1" t="n">
-        <v>46324.79166666666</v>
+        <v>46324.75</v>
       </c>
       <c r="M257" s="1" t="n">
-        <v>46325.29166666666</v>
+        <v>46325.25</v>
       </c>
     </row>
     <row r="258">
@@ -14585,13 +14585,13 @@
         </is>
       </c>
       <c r="K258" s="1" t="n">
-        <v>46327.75</v>
+        <v>46327.79166666666</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>46327.79166666666</v>
+        <v>46327.83333333334</v>
       </c>
       <c r="M258" s="1" t="n">
-        <v>46328.41666666666</v>
+        <v>46328.45833333334</v>
       </c>
     </row>
     <row r="259">
@@ -14640,13 +14640,13 @@
         </is>
       </c>
       <c r="K259" s="1" t="n">
-        <v>46329.41666666666</v>
+        <v>46329.29166666666</v>
       </c>
       <c r="L259" s="1" t="n">
-        <v>46329.45833333334</v>
+        <v>46329.35416666666</v>
       </c>
       <c r="M259" s="1" t="n">
-        <v>46329.95833333334</v>
+        <v>46329.85416666666</v>
       </c>
     </row>
     <row r="260">
@@ -14695,13 +14695,13 @@
         </is>
       </c>
       <c r="K260" s="1" t="n">
-        <v>46331.04166666666</v>
+        <v>46330.83333333334</v>
       </c>
       <c r="L260" s="1" t="n">
-        <v>46331.20833333334</v>
+        <v>46331</v>
       </c>
       <c r="M260" s="1" t="n">
-        <v>46332</v>
+        <v>46331.79166666666</v>
       </c>
     </row>
     <row r="261">
@@ -14750,13 +14750,13 @@
         </is>
       </c>
       <c r="K261" s="1" t="n">
-        <v>46337.75</v>
+        <v>46337.54166666666</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>46337.79166666666</v>
+        <v>46337.58333333334</v>
       </c>
       <c r="M261" s="1" t="n">
-        <v>46338.08333333334</v>
+        <v>46337.875</v>
       </c>
     </row>
     <row r="262">
@@ -14805,13 +14805,13 @@
         </is>
       </c>
       <c r="K262" s="1" t="n">
-        <v>46338.375</v>
+        <v>46338.16666666666</v>
       </c>
       <c r="L262" s="1" t="n">
-        <v>46338.375</v>
+        <v>46338.16666666666</v>
       </c>
       <c r="M262" s="1" t="n">
-        <v>46339.75</v>
+        <v>46339.54166666666</v>
       </c>
     </row>
     <row r="263">
@@ -14860,13 +14860,13 @@
         </is>
       </c>
       <c r="K263" s="1" t="n">
-        <v>46340</v>
+        <v>46339.79166666666</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>46340.04166666666</v>
+        <v>46339.83333333334</v>
       </c>
       <c r="M263" s="1" t="n">
-        <v>46340.5</v>
+        <v>46340.29166666666</v>
       </c>
     </row>
     <row r="264">
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="K264" s="1" t="n">
-        <v>46344.33333333334</v>
+        <v>46344.125</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>46344.33333333334</v>
+        <v>46344.125</v>
       </c>
       <c r="M264" s="1" t="n">
-        <v>46344.79166666666</v>
+        <v>46344.58333333334</v>
       </c>
     </row>
     <row r="265">
@@ -14970,13 +14970,13 @@
         </is>
       </c>
       <c r="K265" s="1" t="n">
-        <v>46345.79166666666</v>
+        <v>46345.58333333334</v>
       </c>
       <c r="L265" s="1" t="n">
-        <v>46345.79166666666</v>
+        <v>46345.58333333334</v>
       </c>
       <c r="M265" s="1" t="n">
-        <v>46346.29166666666</v>
+        <v>46346.08333333334</v>
       </c>
     </row>
     <row r="266">
@@ -15025,13 +15025,13 @@
         </is>
       </c>
       <c r="K266" s="1" t="n">
-        <v>46348.75</v>
+        <v>46348.54166666666</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>46348.79166666666</v>
+        <v>46348.58333333334</v>
       </c>
       <c r="M266" s="1" t="n">
-        <v>46349.41666666666</v>
+        <v>46349.20833333334</v>
       </c>
     </row>
     <row r="267">
@@ -15080,13 +15080,13 @@
         </is>
       </c>
       <c r="K267" s="1" t="n">
-        <v>46350.41666666666</v>
+        <v>46350.20833333334</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>46350.45833333334</v>
+        <v>46350.25</v>
       </c>
       <c r="M267" s="1" t="n">
-        <v>46350.95833333334</v>
+        <v>46350.75</v>
       </c>
     </row>
     <row r="268">
@@ -15135,13 +15135,13 @@
         </is>
       </c>
       <c r="K268" s="1" t="n">
-        <v>46352.04166666666</v>
+        <v>46351.83333333334</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>46352.20833333334</v>
+        <v>46352</v>
       </c>
       <c r="M268" s="1" t="n">
-        <v>46353</v>
+        <v>46352.79166666666</v>
       </c>
     </row>
     <row r="269">
@@ -15190,13 +15190,13 @@
         </is>
       </c>
       <c r="K269" s="1" t="n">
-        <v>46358.75</v>
+        <v>46358.54166666666</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>46358.79166666666</v>
+        <v>46358.58333333334</v>
       </c>
       <c r="M269" s="1" t="n">
-        <v>46359.08333333